--- a/backend_api/templates/container_report_template.xlsx
+++ b/backend_api/templates/container_report_template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Aaron Avila\Documents\ERP-SOM\backend_api\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{CF458EA9-2230-499F-BB5C-FA51CE0026C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{856E49EC-9204-4212-AF38-2E1771F849C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-1125" windowWidth="29040" windowHeight="15720" xr2:uid="{253FFB1B-D348-46B1-A532-0D44566D2FFD}"/>
   </bookViews>
@@ -568,7 +568,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="A41" authorId="1" shapeId="0" xr:uid="{30443301-1091-4C06-A3FA-E580BF54C74F}">
+    <comment ref="A44" authorId="1" shapeId="0" xr:uid="{30443301-1091-4C06-A3FA-E580BF54C74F}">
       <text>
         <r>
           <rPr>
@@ -583,7 +583,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="J41" authorId="1" shapeId="0" xr:uid="{36F2176C-C319-4967-9E8E-785489AA45AB}">
+    <comment ref="J44" authorId="1" shapeId="0" xr:uid="{36F2176C-C319-4967-9E8E-785489AA45AB}">
       <text>
         <r>
           <rPr>
@@ -597,7 +597,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="S41" authorId="1" shapeId="0" xr:uid="{EF231990-56B0-421A-BEF2-559550D4982B}">
+    <comment ref="S44" authorId="1" shapeId="0" xr:uid="{EF231990-56B0-421A-BEF2-559550D4982B}">
       <text>
         <r>
           <rPr>
@@ -611,7 +611,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AB41" authorId="1" shapeId="0" xr:uid="{9FC68C20-EF51-47CB-9CBA-1D201D3580EF}">
+    <comment ref="AB44" authorId="1" shapeId="0" xr:uid="{9FC68C20-EF51-47CB-9CBA-1D201D3580EF}">
       <text>
         <r>
           <rPr>
@@ -625,7 +625,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="S46" authorId="1" shapeId="0" xr:uid="{0D5099D2-C3D8-4CDE-BD1E-0AFB08D17C30}">
+    <comment ref="S49" authorId="1" shapeId="0" xr:uid="{0D5099D2-C3D8-4CDE-BD1E-0AFB08D17C30}">
       <text>
         <r>
           <rPr>
@@ -699,7 +699,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AB48" authorId="1" shapeId="0" xr:uid="{703412D1-5D8A-439E-A61F-D30F4F1283CB}">
+    <comment ref="AB51" authorId="1" shapeId="0" xr:uid="{703412D1-5D8A-439E-A61F-D30F4F1283CB}">
       <text>
         <r>
           <rPr>
@@ -713,7 +713,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="A52" authorId="1" shapeId="0" xr:uid="{ACCFB67C-ADAC-4F00-A332-CC4D5E296E84}">
+    <comment ref="A55" authorId="1" shapeId="0" xr:uid="{ACCFB67C-ADAC-4F00-A332-CC4D5E296E84}">
       <text>
         <r>
           <rPr>
@@ -727,7 +727,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AB53" authorId="1" shapeId="0" xr:uid="{FC59D6ED-F95D-44F3-88C3-22174703430C}">
+    <comment ref="AB56" authorId="1" shapeId="0" xr:uid="{FC59D6ED-F95D-44F3-88C3-22174703430C}">
       <text>
         <r>
           <rPr>
@@ -741,7 +741,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AB55" authorId="1" shapeId="0" xr:uid="{59D1CEF0-0C19-4AF8-B701-BE6BB6391D05}">
+    <comment ref="AB58" authorId="1" shapeId="0" xr:uid="{59D1CEF0-0C19-4AF8-B701-BE6BB6391D05}">
       <text>
         <r>
           <rPr>
@@ -760,7 +760,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="100">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="101">
   <si>
     <t xml:space="preserve">  INSP. PLACE</t>
   </si>
@@ -1105,24 +1105,22 @@
   <si>
     <t>LEAKING</t>
   </si>
+  <si>
+    <t>Link Picture</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
-    <numFmt numFmtId="191" formatCode="dd\-mmm\-yyyy"/>
-    <numFmt numFmtId="195" formatCode="h:mm;@"/>
+    <numFmt numFmtId="164" formatCode="dd\-mmm\-yyyy"/>
+    <numFmt numFmtId="165" formatCode="h:mm;@"/>
   </numFmts>
-  <fonts count="32">
+  <fonts count="31">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="8"/>
-      <name val="Tahoma"/>
-      <family val="2"/>
     </font>
     <font>
       <sz val="18"/>
@@ -1435,136 +1433,433 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left"/>
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="4" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="195" fontId="20" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="165" fontId="19" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="6" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="6" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="7" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="7" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="191" fontId="14" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="164" fontId="13" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyProtection="1">
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="6" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="9" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="7" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="14" fontId="14" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="6" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="9" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="7" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="14" fontId="13" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="4" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="4" fontId="13" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="9" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="6" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="2" borderId="9" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="13" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="3" fontId="13" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="2" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="3" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="4" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="5" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="3" fontId="13" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="9" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="6" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="6" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="6" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="165" fontId="13" fillId="0" borderId="8" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" wrapText="1"/>
+      <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1575,375 +1870,85 @@
     <xf numFmtId="0" fontId="7" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="22" fillId="2" borderId="9" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="2" borderId="6" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="2" borderId="7" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="8" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="2" borderId="9" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="2" borderId="6" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="2" borderId="7" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="4" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="4" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="8" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="195" fontId="14" fillId="0" borderId="8" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="14" fontId="14" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="3" fontId="14" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="3" fontId="14" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="9" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="6" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="6" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="6" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="2" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="3" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="4" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="5" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="4" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="2" borderId="9" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="4" fontId="14" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="2" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="9" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="6" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="4" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
       <protection locked="0"/>
     </xf>
   </cellXfs>
@@ -2165,13 +2170,13 @@
     <xdr:from>
       <xdr:col>29</xdr:col>
       <xdr:colOff>114300</xdr:colOff>
-      <xdr:row>54</xdr:row>
+      <xdr:row>57</xdr:row>
       <xdr:rowOff>190500</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>32</xdr:col>
       <xdr:colOff>960120</xdr:colOff>
-      <xdr:row>57</xdr:row>
+      <xdr:row>59</xdr:row>
       <xdr:rowOff>190500</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -2246,9 +2251,9 @@
         </xdr:from>
         <xdr:to>
           <xdr:col>1</xdr:col>
-          <xdr:colOff>53340</xdr:colOff>
+          <xdr:colOff>57150</xdr:colOff>
           <xdr:row>12</xdr:row>
-          <xdr:rowOff>15240</xdr:rowOff>
+          <xdr:rowOff>19050</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -2258,7 +2263,7 @@
                   <a14:compatExt spid="_x0000_s1085"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{99AE693A-2733-AC8B-AC43-00BB19268B94}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00003D040000}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -2313,9 +2318,9 @@
         </xdr:from>
         <xdr:to>
           <xdr:col>1</xdr:col>
-          <xdr:colOff>53340</xdr:colOff>
+          <xdr:colOff>57150</xdr:colOff>
           <xdr:row>13</xdr:row>
-          <xdr:rowOff>15240</xdr:rowOff>
+          <xdr:rowOff>19050</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -2325,7 +2330,7 @@
                   <a14:compatExt spid="_x0000_s1086"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{70589073-3555-AB18-5C51-DED8101E662F}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00003E040000}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -2380,9 +2385,9 @@
         </xdr:from>
         <xdr:to>
           <xdr:col>5</xdr:col>
-          <xdr:colOff>53340</xdr:colOff>
+          <xdr:colOff>57150</xdr:colOff>
           <xdr:row>12</xdr:row>
-          <xdr:rowOff>15240</xdr:rowOff>
+          <xdr:rowOff>19050</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -2392,7 +2397,7 @@
                   <a14:compatExt spid="_x0000_s1120"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0591D5A7-C097-6463-8E04-D543DDBFD1B2}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000060040000}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -2447,9 +2452,9 @@
         </xdr:from>
         <xdr:to>
           <xdr:col>5</xdr:col>
-          <xdr:colOff>53340</xdr:colOff>
+          <xdr:colOff>57150</xdr:colOff>
           <xdr:row>13</xdr:row>
-          <xdr:rowOff>15240</xdr:rowOff>
+          <xdr:rowOff>19050</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -2459,7 +2464,7 @@
                   <a14:compatExt spid="_x0000_s1121"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E071B10A-9ED4-B1E6-F5D7-879326D340F5}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000061040000}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -2514,9 +2519,9 @@
         </xdr:from>
         <xdr:to>
           <xdr:col>8</xdr:col>
-          <xdr:colOff>396240</xdr:colOff>
+          <xdr:colOff>400050</xdr:colOff>
           <xdr:row>12</xdr:row>
-          <xdr:rowOff>15240</xdr:rowOff>
+          <xdr:rowOff>19050</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -2526,7 +2531,7 @@
                   <a14:compatExt spid="_x0000_s1122"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0120973D-F5C1-B230-843B-27508407C13C}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000062040000}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -2581,9 +2586,9 @@
         </xdr:from>
         <xdr:to>
           <xdr:col>8</xdr:col>
-          <xdr:colOff>396240</xdr:colOff>
+          <xdr:colOff>400050</xdr:colOff>
           <xdr:row>13</xdr:row>
-          <xdr:rowOff>15240</xdr:rowOff>
+          <xdr:rowOff>19050</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -2593,7 +2598,7 @@
                   <a14:compatExt spid="_x0000_s1123"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{10952949-8AB1-1C9B-5A3C-6DE3B4C1113E}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000063040000}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -2648,9 +2653,9 @@
         </xdr:from>
         <xdr:to>
           <xdr:col>14</xdr:col>
-          <xdr:colOff>53340</xdr:colOff>
+          <xdr:colOff>57150</xdr:colOff>
           <xdr:row>12</xdr:row>
-          <xdr:rowOff>15240</xdr:rowOff>
+          <xdr:rowOff>19050</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -2660,7 +2665,7 @@
                   <a14:compatExt spid="_x0000_s1124"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C3A20C92-9DB5-2F54-37BF-1282B3C0D854}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000064040000}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -2715,9 +2720,9 @@
         </xdr:from>
         <xdr:to>
           <xdr:col>14</xdr:col>
-          <xdr:colOff>53340</xdr:colOff>
+          <xdr:colOff>57150</xdr:colOff>
           <xdr:row>13</xdr:row>
-          <xdr:rowOff>15240</xdr:rowOff>
+          <xdr:rowOff>19050</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -2727,7 +2732,7 @@
                   <a14:compatExt spid="_x0000_s1125"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{778CB5FA-5D15-3E48-157F-D95CB5AF1C8F}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000065040000}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -2782,9 +2787,9 @@
         </xdr:from>
         <xdr:to>
           <xdr:col>17</xdr:col>
-          <xdr:colOff>53340</xdr:colOff>
+          <xdr:colOff>57150</xdr:colOff>
           <xdr:row>12</xdr:row>
-          <xdr:rowOff>15240</xdr:rowOff>
+          <xdr:rowOff>19050</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -2794,7 +2799,7 @@
                   <a14:compatExt spid="_x0000_s1126"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BCFEF1F6-1231-614F-AF4E-93CCDA703D16}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000066040000}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -2849,9 +2854,9 @@
         </xdr:from>
         <xdr:to>
           <xdr:col>17</xdr:col>
-          <xdr:colOff>53340</xdr:colOff>
+          <xdr:colOff>57150</xdr:colOff>
           <xdr:row>13</xdr:row>
-          <xdr:rowOff>15240</xdr:rowOff>
+          <xdr:rowOff>19050</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -2861,7 +2866,7 @@
                   <a14:compatExt spid="_x0000_s1127"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5B17D85F-1AAF-F875-D441-313CDA1EDE63}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000067040000}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -2916,9 +2921,9 @@
         </xdr:from>
         <xdr:to>
           <xdr:col>23</xdr:col>
-          <xdr:colOff>53340</xdr:colOff>
+          <xdr:colOff>57150</xdr:colOff>
           <xdr:row>12</xdr:row>
-          <xdr:rowOff>15240</xdr:rowOff>
+          <xdr:rowOff>19050</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -2928,7 +2933,7 @@
                   <a14:compatExt spid="_x0000_s1128"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BBC5993C-93B4-8222-1F08-27B512695F75}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000068040000}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -2983,9 +2988,9 @@
         </xdr:from>
         <xdr:to>
           <xdr:col>23</xdr:col>
-          <xdr:colOff>53340</xdr:colOff>
+          <xdr:colOff>57150</xdr:colOff>
           <xdr:row>13</xdr:row>
-          <xdr:rowOff>15240</xdr:rowOff>
+          <xdr:rowOff>19050</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -2995,7 +3000,7 @@
                   <a14:compatExt spid="_x0000_s1129"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1991E0EF-69CC-8542-231E-71C3DA7835AA}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000069040000}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -3050,9 +3055,9 @@
         </xdr:from>
         <xdr:to>
           <xdr:col>28</xdr:col>
-          <xdr:colOff>53340</xdr:colOff>
+          <xdr:colOff>57150</xdr:colOff>
           <xdr:row>12</xdr:row>
-          <xdr:rowOff>15240</xdr:rowOff>
+          <xdr:rowOff>19050</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -3062,7 +3067,7 @@
                   <a14:compatExt spid="_x0000_s1130"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{91A7C600-E7D8-3691-3B66-99E2FED7AC16}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00006A040000}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -3117,9 +3122,9 @@
         </xdr:from>
         <xdr:to>
           <xdr:col>28</xdr:col>
-          <xdr:colOff>53340</xdr:colOff>
+          <xdr:colOff>57150</xdr:colOff>
           <xdr:row>13</xdr:row>
-          <xdr:rowOff>15240</xdr:rowOff>
+          <xdr:rowOff>19050</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -3129,7 +3134,7 @@
                   <a14:compatExt spid="_x0000_s1131"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0271C258-C378-3AE9-5180-3DB2722CF721}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00006B040000}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -3186,7 +3191,7 @@
           <xdr:col>32</xdr:col>
           <xdr:colOff>342900</xdr:colOff>
           <xdr:row>12</xdr:row>
-          <xdr:rowOff>15240</xdr:rowOff>
+          <xdr:rowOff>19050</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -3196,7 +3201,7 @@
                   <a14:compatExt spid="_x0000_s1132"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DEA4BFFF-F6A2-6E38-4360-1A3A744787B0}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00006C040000}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -3253,7 +3258,7 @@
           <xdr:col>32</xdr:col>
           <xdr:colOff>342900</xdr:colOff>
           <xdr:row>13</xdr:row>
-          <xdr:rowOff>15240</xdr:rowOff>
+          <xdr:rowOff>19050</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -3263,7 +3268,7 @@
                   <a14:compatExt spid="_x0000_s1133"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{51811FD0-7386-DBA2-4401-474903975FBA}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00006D040000}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -3318,9 +3323,9 @@
         </xdr:from>
         <xdr:to>
           <xdr:col>21</xdr:col>
-          <xdr:colOff>91440</xdr:colOff>
+          <xdr:colOff>95250</xdr:colOff>
           <xdr:row>17</xdr:row>
-          <xdr:rowOff>15240</xdr:rowOff>
+          <xdr:rowOff>19050</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -3330,7 +3335,7 @@
                   <a14:compatExt spid="_x0000_s1136"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{18D3E921-48FE-A50C-065D-6BD18022A4D1}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000070040000}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -3385,9 +3390,9 @@
         </xdr:from>
         <xdr:to>
           <xdr:col>21</xdr:col>
-          <xdr:colOff>91440</xdr:colOff>
+          <xdr:colOff>95250</xdr:colOff>
           <xdr:row>18</xdr:row>
-          <xdr:rowOff>15240</xdr:rowOff>
+          <xdr:rowOff>19050</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -3397,7 +3402,7 @@
                   <a14:compatExt spid="_x0000_s1138"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F0405227-4587-7C0D-C1AB-DAD5614605EA}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000072040000}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -3452,9 +3457,9 @@
         </xdr:from>
         <xdr:to>
           <xdr:col>21</xdr:col>
-          <xdr:colOff>91440</xdr:colOff>
+          <xdr:colOff>95250</xdr:colOff>
           <xdr:row>19</xdr:row>
-          <xdr:rowOff>15240</xdr:rowOff>
+          <xdr:rowOff>19050</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -3464,7 +3469,7 @@
                   <a14:compatExt spid="_x0000_s1139"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F962EC06-505C-E652-AE64-F092874613CF}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000073040000}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -3519,9 +3524,9 @@
         </xdr:from>
         <xdr:to>
           <xdr:col>25</xdr:col>
-          <xdr:colOff>91440</xdr:colOff>
+          <xdr:colOff>95250</xdr:colOff>
           <xdr:row>17</xdr:row>
-          <xdr:rowOff>15240</xdr:rowOff>
+          <xdr:rowOff>19050</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -3531,7 +3536,7 @@
                   <a14:compatExt spid="_x0000_s1140"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6B6525C9-637C-DAE7-9A4D-E19F03BC702A}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000074040000}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -3586,9 +3591,9 @@
         </xdr:from>
         <xdr:to>
           <xdr:col>25</xdr:col>
-          <xdr:colOff>91440</xdr:colOff>
+          <xdr:colOff>95250</xdr:colOff>
           <xdr:row>18</xdr:row>
-          <xdr:rowOff>15240</xdr:rowOff>
+          <xdr:rowOff>19050</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -3598,7 +3603,7 @@
                   <a14:compatExt spid="_x0000_s1141"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{34C9F188-A3E6-1ABB-90BC-2FAEFA7DED97}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000075040000}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -3653,9 +3658,9 @@
         </xdr:from>
         <xdr:to>
           <xdr:col>25</xdr:col>
-          <xdr:colOff>91440</xdr:colOff>
+          <xdr:colOff>95250</xdr:colOff>
           <xdr:row>19</xdr:row>
-          <xdr:rowOff>15240</xdr:rowOff>
+          <xdr:rowOff>19050</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -3665,7 +3670,7 @@
                   <a14:compatExt spid="_x0000_s1142"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5E0A188A-C64C-BE5F-A66A-113F758E5BBB}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000076040000}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -3720,9 +3725,9 @@
         </xdr:from>
         <xdr:to>
           <xdr:col>28</xdr:col>
-          <xdr:colOff>91440</xdr:colOff>
+          <xdr:colOff>95250</xdr:colOff>
           <xdr:row>17</xdr:row>
-          <xdr:rowOff>15240</xdr:rowOff>
+          <xdr:rowOff>19050</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -3732,7 +3737,7 @@
                   <a14:compatExt spid="_x0000_s1143"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{EBD772A1-DEC2-61E3-66CC-10DBE6F961DC}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000077040000}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -3787,9 +3792,9 @@
         </xdr:from>
         <xdr:to>
           <xdr:col>28</xdr:col>
-          <xdr:colOff>91440</xdr:colOff>
+          <xdr:colOff>95250</xdr:colOff>
           <xdr:row>18</xdr:row>
-          <xdr:rowOff>15240</xdr:rowOff>
+          <xdr:rowOff>19050</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -3799,7 +3804,7 @@
                   <a14:compatExt spid="_x0000_s1144"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{65BDE298-2027-7007-8097-D5E602530BDB}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000078040000}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -3854,9 +3859,9 @@
         </xdr:from>
         <xdr:to>
           <xdr:col>28</xdr:col>
-          <xdr:colOff>91440</xdr:colOff>
+          <xdr:colOff>95250</xdr:colOff>
           <xdr:row>19</xdr:row>
-          <xdr:rowOff>15240</xdr:rowOff>
+          <xdr:rowOff>19050</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -3866,208 +3871,7 @@
                   <a14:compatExt spid="_x0000_s1145"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1F798C2C-C52A-CA45-4521-1BBADA7D70F1}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off x="0" y="0"/>
-              <a:ext cx="0" cy="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="9"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-        </xdr:sp>
-        <xdr:clientData/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>53340</xdr:colOff>
-          <xdr:row>41</xdr:row>
-          <xdr:rowOff>30480</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>1</xdr:col>
-          <xdr:colOff>91440</xdr:colOff>
-          <xdr:row>42</xdr:row>
-          <xdr:rowOff>15240</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="">
-          <xdr:nvSpPr>
-            <xdr:cNvPr id="1146" name="Check Box 122" hidden="1">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1146"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{860F0780-0C64-D88F-8C1D-FC162A874B4F}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off x="0" y="0"/>
-              <a:ext cx="0" cy="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="9"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-        </xdr:sp>
-        <xdr:clientData/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>53340</xdr:colOff>
-          <xdr:row>42</xdr:row>
-          <xdr:rowOff>30480</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>1</xdr:col>
-          <xdr:colOff>91440</xdr:colOff>
-          <xdr:row>43</xdr:row>
-          <xdr:rowOff>15240</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="">
-          <xdr:nvSpPr>
-            <xdr:cNvPr id="1147" name="Check Box 123" hidden="1">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1147"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C706426A-5671-D730-3104-3582F9A61E62}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off x="0" y="0"/>
-              <a:ext cx="0" cy="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="9"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-        </xdr:sp>
-        <xdr:clientData/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>53340</xdr:colOff>
-          <xdr:row>43</xdr:row>
-          <xdr:rowOff>30480</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>1</xdr:col>
-          <xdr:colOff>91440</xdr:colOff>
-          <xdr:row>44</xdr:row>
-          <xdr:rowOff>15240</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="">
-          <xdr:nvSpPr>
-            <xdr:cNvPr id="1148" name="Check Box 124" hidden="1">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1148"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9A777AD3-3955-0069-F051-CF80AC94305D}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000079040000}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -4122,19 +3926,19 @@
         </xdr:from>
         <xdr:to>
           <xdr:col>1</xdr:col>
-          <xdr:colOff>91440</xdr:colOff>
+          <xdr:colOff>95250</xdr:colOff>
           <xdr:row>45</xdr:row>
-          <xdr:rowOff>15240</xdr:rowOff>
+          <xdr:rowOff>19050</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
-            <xdr:cNvPr id="1149" name="Check Box 125" hidden="1">
+            <xdr:cNvPr id="1146" name="Check Box 122" hidden="1">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1149"/>
+                  <a14:compatExt spid="_x0000_s1146"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E54EB984-1D32-083C-6B2D-4D231B54D8E3}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00007A040000}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -4189,19 +3993,19 @@
         </xdr:from>
         <xdr:to>
           <xdr:col>1</xdr:col>
-          <xdr:colOff>91440</xdr:colOff>
+          <xdr:colOff>95250</xdr:colOff>
           <xdr:row>46</xdr:row>
-          <xdr:rowOff>15240</xdr:rowOff>
+          <xdr:rowOff>19050</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
-            <xdr:cNvPr id="1150" name="Check Box 126" hidden="1">
+            <xdr:cNvPr id="1147" name="Check Box 123" hidden="1">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1150"/>
+                  <a14:compatExt spid="_x0000_s1147"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F4E135FD-F65C-84B8-55A0-9C3ACA7D168C}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00007B040000}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -4256,19 +4060,19 @@
         </xdr:from>
         <xdr:to>
           <xdr:col>1</xdr:col>
-          <xdr:colOff>91440</xdr:colOff>
+          <xdr:colOff>95250</xdr:colOff>
           <xdr:row>47</xdr:row>
-          <xdr:rowOff>15240</xdr:rowOff>
+          <xdr:rowOff>19050</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
-            <xdr:cNvPr id="1151" name="Check Box 127" hidden="1">
+            <xdr:cNvPr id="1148" name="Check Box 124" hidden="1">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1151"/>
+                  <a14:compatExt spid="_x0000_s1148"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A872E97B-6986-CDF0-1E60-8B9692DD2EE8}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00007C040000}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -4323,19 +4127,19 @@
         </xdr:from>
         <xdr:to>
           <xdr:col>1</xdr:col>
-          <xdr:colOff>91440</xdr:colOff>
+          <xdr:colOff>95250</xdr:colOff>
           <xdr:row>48</xdr:row>
-          <xdr:rowOff>15240</xdr:rowOff>
+          <xdr:rowOff>19050</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
-            <xdr:cNvPr id="1152" name="Check Box 128" hidden="1">
+            <xdr:cNvPr id="1149" name="Check Box 125" hidden="1">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1152"/>
+                  <a14:compatExt spid="_x0000_s1149"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{65CD19A7-02F4-7E7D-BCD4-BA49679D0720}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00007D040000}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -4390,19 +4194,19 @@
         </xdr:from>
         <xdr:to>
           <xdr:col>1</xdr:col>
-          <xdr:colOff>91440</xdr:colOff>
+          <xdr:colOff>95250</xdr:colOff>
           <xdr:row>49</xdr:row>
-          <xdr:rowOff>15240</xdr:rowOff>
+          <xdr:rowOff>19050</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
-            <xdr:cNvPr id="1153" name="Check Box 129" hidden="1">
+            <xdr:cNvPr id="1150" name="Check Box 126" hidden="1">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1153"/>
+                  <a14:compatExt spid="_x0000_s1150"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DE8122DF-A4B2-4FEC-DEE9-43AC3D1DE84B}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00007E040000}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -4457,19 +4261,19 @@
         </xdr:from>
         <xdr:to>
           <xdr:col>1</xdr:col>
-          <xdr:colOff>91440</xdr:colOff>
+          <xdr:colOff>95250</xdr:colOff>
           <xdr:row>50</xdr:row>
-          <xdr:rowOff>15240</xdr:rowOff>
+          <xdr:rowOff>19050</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
-            <xdr:cNvPr id="1154" name="Check Box 130" hidden="1">
+            <xdr:cNvPr id="1151" name="Check Box 127" hidden="1">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1154"/>
+                  <a14:compatExt spid="_x0000_s1151"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F653F7C2-C63D-016A-8286-DFA82B450F77}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00007F040000}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -4517,26 +4321,26 @@
     <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
       <xdr:twoCellAnchor editAs="oneCell">
         <xdr:from>
-          <xdr:col>9</xdr:col>
+          <xdr:col>0</xdr:col>
           <xdr:colOff>53340</xdr:colOff>
-          <xdr:row>41</xdr:row>
+          <xdr:row>50</xdr:row>
           <xdr:rowOff>30480</xdr:rowOff>
         </xdr:from>
         <xdr:to>
-          <xdr:col>10</xdr:col>
-          <xdr:colOff>91440</xdr:colOff>
-          <xdr:row>42</xdr:row>
-          <xdr:rowOff>15240</xdr:rowOff>
+          <xdr:col>1</xdr:col>
+          <xdr:colOff>95250</xdr:colOff>
+          <xdr:row>51</xdr:row>
+          <xdr:rowOff>19050</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
-            <xdr:cNvPr id="1164" name="Check Box 140" hidden="1">
+            <xdr:cNvPr id="1152" name="Check Box 128" hidden="1">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1164"/>
+                  <a14:compatExt spid="_x0000_s1152"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{250E6776-F955-268C-43A5-FF25C4832758}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000080040000}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -4584,26 +4388,26 @@
     <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
       <xdr:twoCellAnchor editAs="oneCell">
         <xdr:from>
-          <xdr:col>9</xdr:col>
+          <xdr:col>0</xdr:col>
           <xdr:colOff>53340</xdr:colOff>
-          <xdr:row>42</xdr:row>
+          <xdr:row>51</xdr:row>
           <xdr:rowOff>30480</xdr:rowOff>
         </xdr:from>
         <xdr:to>
-          <xdr:col>10</xdr:col>
-          <xdr:colOff>91440</xdr:colOff>
-          <xdr:row>43</xdr:row>
-          <xdr:rowOff>15240</xdr:rowOff>
+          <xdr:col>1</xdr:col>
+          <xdr:colOff>95250</xdr:colOff>
+          <xdr:row>52</xdr:row>
+          <xdr:rowOff>19050</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
-            <xdr:cNvPr id="1165" name="Check Box 141" hidden="1">
+            <xdr:cNvPr id="1153" name="Check Box 129" hidden="1">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1165"/>
+                  <a14:compatExt spid="_x0000_s1153"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A731AFE0-03FC-F550-147C-50785302DB71}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000081040000}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -4651,26 +4455,26 @@
     <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
       <xdr:twoCellAnchor editAs="oneCell">
         <xdr:from>
-          <xdr:col>9</xdr:col>
+          <xdr:col>0</xdr:col>
           <xdr:colOff>53340</xdr:colOff>
-          <xdr:row>43</xdr:row>
+          <xdr:row>52</xdr:row>
           <xdr:rowOff>30480</xdr:rowOff>
         </xdr:from>
         <xdr:to>
-          <xdr:col>10</xdr:col>
-          <xdr:colOff>91440</xdr:colOff>
-          <xdr:row>44</xdr:row>
-          <xdr:rowOff>15240</xdr:rowOff>
+          <xdr:col>1</xdr:col>
+          <xdr:colOff>95250</xdr:colOff>
+          <xdr:row>53</xdr:row>
+          <xdr:rowOff>19050</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
-            <xdr:cNvPr id="1166" name="Check Box 142" hidden="1">
+            <xdr:cNvPr id="1154" name="Check Box 130" hidden="1">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1166"/>
+                  <a14:compatExt spid="_x0000_s1154"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{EE030CA2-B8DB-CA32-B5C1-D418918E48B1}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000082040000}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -4725,19 +4529,19 @@
         </xdr:from>
         <xdr:to>
           <xdr:col>10</xdr:col>
-          <xdr:colOff>91440</xdr:colOff>
+          <xdr:colOff>95250</xdr:colOff>
           <xdr:row>45</xdr:row>
-          <xdr:rowOff>15240</xdr:rowOff>
+          <xdr:rowOff>19050</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
-            <xdr:cNvPr id="1167" name="Check Box 143" hidden="1">
+            <xdr:cNvPr id="1164" name="Check Box 140" hidden="1">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1167"/>
+                  <a14:compatExt spid="_x0000_s1164"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D0EB3E99-4431-9F99-70D7-7C12114B5701}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00008C040000}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -4792,19 +4596,19 @@
         </xdr:from>
         <xdr:to>
           <xdr:col>10</xdr:col>
-          <xdr:colOff>91440</xdr:colOff>
+          <xdr:colOff>95250</xdr:colOff>
           <xdr:row>46</xdr:row>
-          <xdr:rowOff>15240</xdr:rowOff>
+          <xdr:rowOff>19050</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
-            <xdr:cNvPr id="1168" name="Check Box 144" hidden="1">
+            <xdr:cNvPr id="1165" name="Check Box 141" hidden="1">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1168"/>
+                  <a14:compatExt spid="_x0000_s1165"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{366A6FA2-DDDA-A2BD-E847-50CA81FF9EF6}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00008D040000}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -4859,19 +4663,19 @@
         </xdr:from>
         <xdr:to>
           <xdr:col>10</xdr:col>
-          <xdr:colOff>91440</xdr:colOff>
+          <xdr:colOff>95250</xdr:colOff>
           <xdr:row>47</xdr:row>
-          <xdr:rowOff>15240</xdr:rowOff>
+          <xdr:rowOff>19050</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
-            <xdr:cNvPr id="1169" name="Check Box 145" hidden="1">
+            <xdr:cNvPr id="1166" name="Check Box 142" hidden="1">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1169"/>
+                  <a14:compatExt spid="_x0000_s1166"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3E226103-14D0-AF90-C81B-EE822B44612C}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00008E040000}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -4926,19 +4730,19 @@
         </xdr:from>
         <xdr:to>
           <xdr:col>10</xdr:col>
-          <xdr:colOff>91440</xdr:colOff>
+          <xdr:colOff>95250</xdr:colOff>
           <xdr:row>48</xdr:row>
-          <xdr:rowOff>15240</xdr:rowOff>
+          <xdr:rowOff>19050</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
-            <xdr:cNvPr id="1170" name="Check Box 146" hidden="1">
+            <xdr:cNvPr id="1167" name="Check Box 143" hidden="1">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1170"/>
+                  <a14:compatExt spid="_x0000_s1167"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E3F1474C-DC0B-8B89-1510-C59E18EB77FA}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00008F040000}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -4993,19 +4797,19 @@
         </xdr:from>
         <xdr:to>
           <xdr:col>10</xdr:col>
-          <xdr:colOff>91440</xdr:colOff>
+          <xdr:colOff>95250</xdr:colOff>
           <xdr:row>49</xdr:row>
-          <xdr:rowOff>15240</xdr:rowOff>
+          <xdr:rowOff>19050</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
-            <xdr:cNvPr id="1171" name="Check Box 147" hidden="1">
+            <xdr:cNvPr id="1168" name="Check Box 144" hidden="1">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1171"/>
+                  <a14:compatExt spid="_x0000_s1168"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DD3A79AA-E8D0-C74F-BF25-D5F92DA69C1C}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000090040000}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -5060,9 +4864,210 @@
         </xdr:from>
         <xdr:to>
           <xdr:col>10</xdr:col>
-          <xdr:colOff>91440</xdr:colOff>
+          <xdr:colOff>95250</xdr:colOff>
           <xdr:row>50</xdr:row>
-          <xdr:rowOff>15240</xdr:rowOff>
+          <xdr:rowOff>19050</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="1169" name="Check Box 145" hidden="1">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1169"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000091040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off x="0" y="0"/>
+              <a:ext cx="0" cy="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="9"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+        </xdr:sp>
+        <xdr:clientData/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>9</xdr:col>
+          <xdr:colOff>53340</xdr:colOff>
+          <xdr:row>50</xdr:row>
+          <xdr:rowOff>30480</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>10</xdr:col>
+          <xdr:colOff>95250</xdr:colOff>
+          <xdr:row>51</xdr:row>
+          <xdr:rowOff>19050</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="1170" name="Check Box 146" hidden="1">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1170"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000092040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off x="0" y="0"/>
+              <a:ext cx="0" cy="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="9"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+        </xdr:sp>
+        <xdr:clientData/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>9</xdr:col>
+          <xdr:colOff>53340</xdr:colOff>
+          <xdr:row>51</xdr:row>
+          <xdr:rowOff>30480</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>10</xdr:col>
+          <xdr:colOff>95250</xdr:colOff>
+          <xdr:row>52</xdr:row>
+          <xdr:rowOff>19050</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="1171" name="Check Box 147" hidden="1">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1171"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000093040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off x="0" y="0"/>
+              <a:ext cx="0" cy="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="9"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+        </xdr:sp>
+        <xdr:clientData/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>9</xdr:col>
+          <xdr:colOff>53340</xdr:colOff>
+          <xdr:row>52</xdr:row>
+          <xdr:rowOff>30480</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>10</xdr:col>
+          <xdr:colOff>95250</xdr:colOff>
+          <xdr:row>53</xdr:row>
+          <xdr:rowOff>19050</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -5072,7 +5077,7 @@
                   <a14:compatExt spid="_x0000_s1172"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6BFB983D-87D6-7BFD-73DC-7B645BDAA091}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000094040000}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -5122,14 +5127,14 @@
         <xdr:from>
           <xdr:col>18</xdr:col>
           <xdr:colOff>53340</xdr:colOff>
-          <xdr:row>46</xdr:row>
+          <xdr:row>49</xdr:row>
           <xdr:rowOff>30480</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>19</xdr:col>
-          <xdr:colOff>91440</xdr:colOff>
-          <xdr:row>47</xdr:row>
-          <xdr:rowOff>15240</xdr:rowOff>
+          <xdr:colOff>95250</xdr:colOff>
+          <xdr:row>50</xdr:row>
+          <xdr:rowOff>19050</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -5139,7 +5144,7 @@
                   <a14:compatExt spid="_x0000_s1173"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4038F1FD-EEED-0F0F-1C4F-F505E1083DA1}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000095040000}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -5189,14 +5194,14 @@
         <xdr:from>
           <xdr:col>18</xdr:col>
           <xdr:colOff>53340</xdr:colOff>
-          <xdr:row>47</xdr:row>
+          <xdr:row>50</xdr:row>
           <xdr:rowOff>30480</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>19</xdr:col>
-          <xdr:colOff>91440</xdr:colOff>
-          <xdr:row>48</xdr:row>
-          <xdr:rowOff>15240</xdr:rowOff>
+          <xdr:colOff>95250</xdr:colOff>
+          <xdr:row>51</xdr:row>
+          <xdr:rowOff>19050</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -5206,7 +5211,7 @@
                   <a14:compatExt spid="_x0000_s1174"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F3D81A26-9703-0622-35C9-97F5FA4B1114}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000096040000}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -5256,14 +5261,14 @@
         <xdr:from>
           <xdr:col>27</xdr:col>
           <xdr:colOff>53340</xdr:colOff>
-          <xdr:row>48</xdr:row>
+          <xdr:row>51</xdr:row>
           <xdr:rowOff>30480</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>28</xdr:col>
-          <xdr:colOff>91440</xdr:colOff>
-          <xdr:row>49</xdr:row>
-          <xdr:rowOff>15240</xdr:rowOff>
+          <xdr:colOff>95250</xdr:colOff>
+          <xdr:row>52</xdr:row>
+          <xdr:rowOff>19050</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -5273,7 +5278,7 @@
                   <a14:compatExt spid="_x0000_s1179"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{086705F6-9750-D924-D490-3FCF6B4882C1}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00009B040000}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -5323,14 +5328,14 @@
         <xdr:from>
           <xdr:col>27</xdr:col>
           <xdr:colOff>53340</xdr:colOff>
-          <xdr:row>49</xdr:row>
+          <xdr:row>52</xdr:row>
           <xdr:rowOff>30480</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>28</xdr:col>
-          <xdr:colOff>91440</xdr:colOff>
-          <xdr:row>50</xdr:row>
-          <xdr:rowOff>15240</xdr:rowOff>
+          <xdr:colOff>95250</xdr:colOff>
+          <xdr:row>53</xdr:row>
+          <xdr:rowOff>19050</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -5340,7 +5345,7 @@
                   <a14:compatExt spid="_x0000_s1180"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{032CFAA9-8D2B-FCA0-DD95-AA107EB6FD15}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00009C040000}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -5390,14 +5395,14 @@
         <xdr:from>
           <xdr:col>27</xdr:col>
           <xdr:colOff>53340</xdr:colOff>
-          <xdr:row>50</xdr:row>
+          <xdr:row>53</xdr:row>
           <xdr:rowOff>30480</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>28</xdr:col>
-          <xdr:colOff>91440</xdr:colOff>
-          <xdr:row>51</xdr:row>
-          <xdr:rowOff>15240</xdr:rowOff>
+          <xdr:colOff>95250</xdr:colOff>
+          <xdr:row>54</xdr:row>
+          <xdr:rowOff>19050</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -5407,7 +5412,7 @@
                   <a14:compatExt spid="_x0000_s1181"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{57A704E1-7E88-D150-E68E-93F8EBDC5B3F}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00009D040000}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -5455,13 +5460,13 @@
     <xdr:from>
       <xdr:col>22</xdr:col>
       <xdr:colOff>106680</xdr:colOff>
-      <xdr:row>48</xdr:row>
+      <xdr:row>51</xdr:row>
       <xdr:rowOff>213360</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>24</xdr:col>
       <xdr:colOff>228600</xdr:colOff>
-      <xdr:row>48</xdr:row>
+      <xdr:row>51</xdr:row>
       <xdr:rowOff>213360</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -5509,13 +5514,13 @@
     <xdr:from>
       <xdr:col>22</xdr:col>
       <xdr:colOff>121920</xdr:colOff>
-      <xdr:row>49</xdr:row>
+      <xdr:row>52</xdr:row>
       <xdr:rowOff>213360</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>25</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>49</xdr:row>
+      <xdr:row>52</xdr:row>
       <xdr:rowOff>213360</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -5563,13 +5568,13 @@
     <xdr:from>
       <xdr:col>22</xdr:col>
       <xdr:colOff>121920</xdr:colOff>
-      <xdr:row>50</xdr:row>
+      <xdr:row>53</xdr:row>
       <xdr:rowOff>213360</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>25</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>50</xdr:row>
+      <xdr:row>53</xdr:row>
       <xdr:rowOff>213360</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -5617,13 +5622,13 @@
     <xdr:from>
       <xdr:col>23</xdr:col>
       <xdr:colOff>91440</xdr:colOff>
-      <xdr:row>44</xdr:row>
+      <xdr:row>47</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>25</xdr:col>
       <xdr:colOff>220980</xdr:colOff>
-      <xdr:row>44</xdr:row>
+      <xdr:row>47</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -5671,13 +5676,13 @@
     <xdr:from>
       <xdr:col>23</xdr:col>
       <xdr:colOff>106680</xdr:colOff>
-      <xdr:row>44</xdr:row>
+      <xdr:row>47</xdr:row>
       <xdr:rowOff>213360</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>25</xdr:col>
       <xdr:colOff>228600</xdr:colOff>
-      <xdr:row>44</xdr:row>
+      <xdr:row>47</xdr:row>
       <xdr:rowOff>213360</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -5725,13 +5730,13 @@
     <xdr:from>
       <xdr:col>22</xdr:col>
       <xdr:colOff>91440</xdr:colOff>
-      <xdr:row>42</xdr:row>
+      <xdr:row>45</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>25</xdr:col>
       <xdr:colOff>259080</xdr:colOff>
-      <xdr:row>42</xdr:row>
+      <xdr:row>45</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -5779,13 +5784,13 @@
     <xdr:from>
       <xdr:col>32</xdr:col>
       <xdr:colOff>106680</xdr:colOff>
-      <xdr:row>45</xdr:row>
+      <xdr:row>48</xdr:row>
       <xdr:rowOff>213360</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>34</xdr:col>
       <xdr:colOff>228600</xdr:colOff>
-      <xdr:row>45</xdr:row>
+      <xdr:row>48</xdr:row>
       <xdr:rowOff>213360</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -5833,13 +5838,13 @@
     <xdr:from>
       <xdr:col>32</xdr:col>
       <xdr:colOff>106680</xdr:colOff>
-      <xdr:row>46</xdr:row>
+      <xdr:row>49</xdr:row>
       <xdr:rowOff>213360</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>34</xdr:col>
       <xdr:colOff>228600</xdr:colOff>
-      <xdr:row>46</xdr:row>
+      <xdr:row>49</xdr:row>
       <xdr:rowOff>213360</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -5887,13 +5892,13 @@
     <xdr:from>
       <xdr:col>30</xdr:col>
       <xdr:colOff>205740</xdr:colOff>
-      <xdr:row>42</xdr:row>
+      <xdr:row>45</xdr:row>
       <xdr:rowOff>213360</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>35</xdr:col>
       <xdr:colOff>53340</xdr:colOff>
-      <xdr:row>42</xdr:row>
+      <xdr:row>45</xdr:row>
       <xdr:rowOff>213360</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -5941,13 +5946,13 @@
     <xdr:from>
       <xdr:col>30</xdr:col>
       <xdr:colOff>205740</xdr:colOff>
-      <xdr:row>41</xdr:row>
+      <xdr:row>44</xdr:row>
       <xdr:rowOff>213360</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>35</xdr:col>
       <xdr:colOff>53340</xdr:colOff>
-      <xdr:row>41</xdr:row>
+      <xdr:row>44</xdr:row>
       <xdr:rowOff>213360</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -5995,13 +6000,13 @@
     <xdr:from>
       <xdr:col>30</xdr:col>
       <xdr:colOff>205740</xdr:colOff>
-      <xdr:row>43</xdr:row>
+      <xdr:row>46</xdr:row>
       <xdr:rowOff>213360</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>35</xdr:col>
       <xdr:colOff>53340</xdr:colOff>
-      <xdr:row>43</xdr:row>
+      <xdr:row>46</xdr:row>
       <xdr:rowOff>213360</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -6049,13 +6054,13 @@
     <xdr:from>
       <xdr:col>31</xdr:col>
       <xdr:colOff>121920</xdr:colOff>
-      <xdr:row>50</xdr:row>
+      <xdr:row>53</xdr:row>
       <xdr:rowOff>213360</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>34</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>50</xdr:row>
+      <xdr:row>53</xdr:row>
       <xdr:rowOff>213360</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -6103,13 +6108,13 @@
     <xdr:from>
       <xdr:col>30</xdr:col>
       <xdr:colOff>205740</xdr:colOff>
-      <xdr:row>44</xdr:row>
+      <xdr:row>47</xdr:row>
       <xdr:rowOff>213360</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>35</xdr:col>
       <xdr:colOff>53340</xdr:colOff>
-      <xdr:row>44</xdr:row>
+      <xdr:row>47</xdr:row>
       <xdr:rowOff>213360</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -6157,13 +6162,13 @@
     <xdr:from>
       <xdr:col>2</xdr:col>
       <xdr:colOff>220980</xdr:colOff>
-      <xdr:row>50</xdr:row>
+      <xdr:row>53</xdr:row>
       <xdr:rowOff>213360</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
       <xdr:colOff>7620</xdr:colOff>
-      <xdr:row>50</xdr:row>
+      <xdr:row>53</xdr:row>
       <xdr:rowOff>213360</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -6375,14 +6380,14 @@
         <xdr:from>
           <xdr:col>27</xdr:col>
           <xdr:colOff>53340</xdr:colOff>
-          <xdr:row>50</xdr:row>
+          <xdr:row>53</xdr:row>
           <xdr:rowOff>30480</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>28</xdr:col>
-          <xdr:colOff>91440</xdr:colOff>
-          <xdr:row>51</xdr:row>
-          <xdr:rowOff>15240</xdr:rowOff>
+          <xdr:colOff>95250</xdr:colOff>
+          <xdr:row>54</xdr:row>
+          <xdr:rowOff>19050</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -6392,7 +6397,7 @@
                   <a14:compatExt spid="_x0000_s1261"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6F2CCC1B-1FE1-06CC-EFE8-E0A9DAF53248}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-0000ED040000}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -6513,15 +6518,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>25</xdr:col>
-      <xdr:colOff>144780</xdr:colOff>
-      <xdr:row>53</xdr:row>
-      <xdr:rowOff>243840</xdr:rowOff>
+      <xdr:colOff>114423</xdr:colOff>
+      <xdr:row>56</xdr:row>
+      <xdr:rowOff>117311</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>27</xdr:col>
-      <xdr:colOff>312420</xdr:colOff>
-      <xdr:row>56</xdr:row>
-      <xdr:rowOff>266700</xdr:rowOff>
+      <xdr:colOff>243963</xdr:colOff>
+      <xdr:row>59</xdr:row>
+      <xdr:rowOff>78514</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -6561,8 +6566,8 @@
       </xdr:blipFill>
       <xdr:spPr bwMode="auto">
         <a:xfrm rot="-760793">
-          <a:off x="7581900" y="14257020"/>
-          <a:ext cx="678180" cy="685800"/>
+          <a:off x="7601073" y="14795336"/>
+          <a:ext cx="681990" cy="647003"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -6598,13 +6603,13 @@
     <xdr:from>
       <xdr:col>21</xdr:col>
       <xdr:colOff>167640</xdr:colOff>
-      <xdr:row>43</xdr:row>
+      <xdr:row>46</xdr:row>
       <xdr:rowOff>7620</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>25</xdr:col>
       <xdr:colOff>121920</xdr:colOff>
-      <xdr:row>43</xdr:row>
+      <xdr:row>46</xdr:row>
       <xdr:rowOff>7620</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -7001,7 +7006,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5B13FA25-C8DE-439A-B87F-1314C11DB30C}">
-  <dimension ref="A1:AJ655"/>
+  <dimension ref="A1:AJ658"/>
   <sheetFormatPr defaultColWidth="4" defaultRowHeight="13.2" zeroHeight="1"/>
   <cols>
     <col min="1" max="8" width="4" customWidth="1"/>
@@ -7013,7 +7018,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:36" ht="18" customHeight="1">
-      <c r="A1" s="29"/>
+      <c r="A1" s="28"/>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
       <c r="D1" s="1"/>
@@ -7023,14 +7028,14 @@
       <c r="H1" s="1"/>
       <c r="I1" s="1"/>
       <c r="J1" s="1"/>
-      <c r="L1" s="30"/>
-      <c r="M1" s="30"/>
-      <c r="N1" s="30"/>
-      <c r="O1" s="30"/>
-      <c r="P1" s="30"/>
+      <c r="L1" s="29"/>
+      <c r="M1" s="29"/>
+      <c r="N1" s="29"/>
+      <c r="O1" s="29"/>
+      <c r="P1" s="29"/>
     </row>
     <row r="2" spans="1:36" ht="18" customHeight="1">
-      <c r="A2" s="31"/>
+      <c r="A2" s="30"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
       <c r="D2" s="1"/>
@@ -7041,35 +7046,35 @@
       <c r="I2" s="1"/>
       <c r="J2" s="1"/>
       <c r="K2" s="1"/>
-      <c r="M2" s="32"/>
-      <c r="N2" s="32"/>
-      <c r="O2" s="39"/>
-      <c r="P2" s="39"/>
-      <c r="Q2" s="55" t="s">
+      <c r="M2" s="31"/>
+      <c r="N2" s="31"/>
+      <c r="O2" s="38"/>
+      <c r="P2" s="38"/>
+      <c r="Q2" s="154" t="s">
         <v>98</v>
       </c>
-      <c r="R2" s="55"/>
-      <c r="S2" s="55"/>
-      <c r="T2" s="55"/>
-      <c r="U2" s="55"/>
-      <c r="V2" s="55"/>
-      <c r="W2" s="55"/>
-      <c r="X2" s="55"/>
-      <c r="Y2" s="55"/>
-      <c r="Z2" s="55"/>
-      <c r="AA2" s="39"/>
-      <c r="AB2" s="39"/>
-      <c r="AC2" s="39"/>
-      <c r="AD2" s="39"/>
-      <c r="AE2" s="39"/>
-      <c r="AF2" s="39"/>
-      <c r="AG2" s="39"/>
-      <c r="AH2" s="39"/>
-      <c r="AI2" s="39"/>
-      <c r="AJ2" s="39"/>
+      <c r="R2" s="154"/>
+      <c r="S2" s="154"/>
+      <c r="T2" s="154"/>
+      <c r="U2" s="154"/>
+      <c r="V2" s="154"/>
+      <c r="W2" s="154"/>
+      <c r="X2" s="154"/>
+      <c r="Y2" s="154"/>
+      <c r="Z2" s="154"/>
+      <c r="AA2" s="38"/>
+      <c r="AB2" s="38"/>
+      <c r="AC2" s="38"/>
+      <c r="AD2" s="38"/>
+      <c r="AE2" s="38"/>
+      <c r="AF2" s="38"/>
+      <c r="AG2" s="38"/>
+      <c r="AH2" s="38"/>
+      <c r="AI2" s="38"/>
+      <c r="AJ2" s="38"/>
     </row>
     <row r="3" spans="1:36" ht="20.399999999999999" customHeight="1">
-      <c r="A3" s="31"/>
+      <c r="A3" s="30"/>
       <c r="B3" s="1"/>
       <c r="C3" s="1"/>
       <c r="D3" s="1"/>
@@ -7080,33 +7085,33 @@
       <c r="I3" s="1"/>
       <c r="J3" s="1"/>
       <c r="K3" s="1"/>
-      <c r="M3" s="32"/>
-      <c r="N3" s="32"/>
-      <c r="Q3" s="56"/>
-      <c r="R3" s="56"/>
-      <c r="S3" s="56"/>
-      <c r="T3" s="56"/>
-      <c r="U3" s="56"/>
-      <c r="V3" s="56"/>
-      <c r="W3" s="56"/>
-      <c r="X3" s="56"/>
-      <c r="Y3" s="56"/>
-      <c r="Z3" s="56"/>
-      <c r="AA3" s="38"/>
-      <c r="AB3" s="51" t="s">
+      <c r="M3" s="31"/>
+      <c r="N3" s="31"/>
+      <c r="Q3" s="155"/>
+      <c r="R3" s="155"/>
+      <c r="S3" s="155"/>
+      <c r="T3" s="155"/>
+      <c r="U3" s="155"/>
+      <c r="V3" s="155"/>
+      <c r="W3" s="155"/>
+      <c r="X3" s="155"/>
+      <c r="Y3" s="155"/>
+      <c r="Z3" s="155"/>
+      <c r="AA3" s="37"/>
+      <c r="AB3" s="50" t="s">
         <v>95</v>
       </c>
-      <c r="AC3" s="49"/>
-      <c r="AD3" s="70"/>
-      <c r="AE3" s="71"/>
-      <c r="AF3" s="71"/>
-      <c r="AG3" s="71"/>
-      <c r="AH3" s="71"/>
-      <c r="AI3" s="71"/>
-      <c r="AJ3" s="71"/>
+      <c r="AC3" s="48"/>
+      <c r="AD3" s="150"/>
+      <c r="AE3" s="151"/>
+      <c r="AF3" s="151"/>
+      <c r="AG3" s="151"/>
+      <c r="AH3" s="151"/>
+      <c r="AI3" s="151"/>
+      <c r="AJ3" s="151"/>
     </row>
     <row r="4" spans="1:36" ht="18" customHeight="1">
-      <c r="A4" s="31"/>
+      <c r="A4" s="30"/>
       <c r="B4" s="1"/>
       <c r="C4" s="1"/>
       <c r="D4" s="1"/>
@@ -7120,2298 +7125,2359 @@
       <c r="L4" s="1"/>
       <c r="M4" s="1"/>
       <c r="N4" s="1"/>
-      <c r="O4" s="32"/>
-      <c r="P4" s="32"/>
-      <c r="Q4" s="33"/>
+      <c r="O4" s="31"/>
+      <c r="P4" s="31"/>
+      <c r="Q4" s="32"/>
       <c r="R4" s="1"/>
       <c r="S4" s="1"/>
       <c r="T4" s="1"/>
       <c r="U4" s="1"/>
-      <c r="Y4" s="37"/>
-      <c r="Z4" s="37"/>
+      <c r="Y4" s="36"/>
+      <c r="Z4" s="36"/>
       <c r="AA4" t="s">
         <v>97</v>
       </c>
     </row>
     <row r="5" spans="1:36" ht="18" customHeight="1">
-      <c r="A5" s="77" t="s">
+      <c r="A5" s="57" t="s">
         <v>85</v>
       </c>
-      <c r="B5" s="77"/>
-      <c r="C5" s="83"/>
-      <c r="D5" s="83"/>
-      <c r="E5" s="83"/>
-      <c r="F5" s="83"/>
-      <c r="G5" s="83"/>
-      <c r="H5" s="83"/>
-      <c r="I5" s="83"/>
-      <c r="J5" s="36"/>
-      <c r="K5" s="60" t="s">
+      <c r="B5" s="57"/>
+      <c r="C5" s="85"/>
+      <c r="D5" s="85"/>
+      <c r="E5" s="85"/>
+      <c r="F5" s="85"/>
+      <c r="G5" s="85"/>
+      <c r="H5" s="85"/>
+      <c r="I5" s="85"/>
+      <c r="J5" s="35"/>
+      <c r="K5" s="109" t="s">
         <v>0</v>
       </c>
-      <c r="L5" s="60"/>
-      <c r="M5" s="60"/>
-      <c r="N5" s="60"/>
-      <c r="O5" s="60"/>
-      <c r="P5" s="73"/>
-      <c r="Q5" s="74"/>
-      <c r="R5" s="74"/>
-      <c r="S5" s="74"/>
-      <c r="T5" s="74"/>
-      <c r="U5" s="74"/>
-      <c r="V5" s="74"/>
-      <c r="W5" s="74"/>
-      <c r="X5" s="74"/>
-      <c r="Y5" s="60" t="s">
+      <c r="L5" s="109"/>
+      <c r="M5" s="109"/>
+      <c r="N5" s="109"/>
+      <c r="O5" s="109"/>
+      <c r="P5" s="152"/>
+      <c r="Q5" s="153"/>
+      <c r="R5" s="153"/>
+      <c r="S5" s="153"/>
+      <c r="T5" s="153"/>
+      <c r="U5" s="153"/>
+      <c r="V5" s="153"/>
+      <c r="W5" s="153"/>
+      <c r="X5" s="153"/>
+      <c r="Y5" s="109" t="s">
         <v>48</v>
       </c>
-      <c r="Z5" s="60"/>
-      <c r="AA5" s="83"/>
-      <c r="AB5" s="83"/>
-      <c r="AC5" s="83"/>
-      <c r="AD5" s="83"/>
-      <c r="AE5" s="83"/>
-      <c r="AF5" s="83"/>
-      <c r="AG5" s="83"/>
-      <c r="AH5" s="83"/>
-      <c r="AI5" s="83"/>
-      <c r="AJ5" s="83"/>
+      <c r="Z5" s="109"/>
+      <c r="AA5" s="85"/>
+      <c r="AB5" s="85"/>
+      <c r="AC5" s="85"/>
+      <c r="AD5" s="85"/>
+      <c r="AE5" s="85"/>
+      <c r="AF5" s="85"/>
+      <c r="AG5" s="85"/>
+      <c r="AH5" s="85"/>
+      <c r="AI5" s="85"/>
+      <c r="AJ5" s="85"/>
     </row>
     <row r="6" spans="1:36" ht="18" customHeight="1">
-      <c r="A6" s="77" t="s">
+      <c r="A6" s="57" t="s">
         <v>1</v>
       </c>
-      <c r="B6" s="77"/>
-      <c r="C6" s="81"/>
-      <c r="D6" s="81"/>
-      <c r="E6" s="81"/>
-      <c r="F6" s="81"/>
-      <c r="G6" s="81"/>
-      <c r="H6" s="81"/>
-      <c r="I6" s="81"/>
-      <c r="J6" s="36"/>
-      <c r="K6" s="60" t="s">
+      <c r="B6" s="57"/>
+      <c r="C6" s="138"/>
+      <c r="D6" s="138"/>
+      <c r="E6" s="138"/>
+      <c r="F6" s="138"/>
+      <c r="G6" s="138"/>
+      <c r="H6" s="138"/>
+      <c r="I6" s="138"/>
+      <c r="J6" s="35"/>
+      <c r="K6" s="109" t="s">
         <v>2</v>
       </c>
-      <c r="L6" s="60"/>
-      <c r="M6" s="60"/>
-      <c r="N6" s="60"/>
-      <c r="O6" s="60"/>
-      <c r="P6" s="61"/>
-      <c r="Q6" s="62"/>
-      <c r="R6" s="62"/>
-      <c r="S6" s="62"/>
-      <c r="T6" s="62"/>
-      <c r="U6" s="62"/>
-      <c r="V6" s="62"/>
-      <c r="W6" s="62"/>
-      <c r="X6" s="62"/>
-      <c r="Y6" s="72" t="s">
+      <c r="L6" s="109"/>
+      <c r="M6" s="109"/>
+      <c r="N6" s="109"/>
+      <c r="O6" s="109"/>
+      <c r="P6" s="159"/>
+      <c r="Q6" s="160"/>
+      <c r="R6" s="160"/>
+      <c r="S6" s="160"/>
+      <c r="T6" s="160"/>
+      <c r="U6" s="160"/>
+      <c r="V6" s="160"/>
+      <c r="W6" s="160"/>
+      <c r="X6" s="160"/>
+      <c r="Y6" s="109" t="s">
         <v>88</v>
       </c>
-      <c r="Z6" s="72"/>
-      <c r="AA6" s="72"/>
-      <c r="AB6" s="72"/>
-      <c r="AC6" s="72"/>
-      <c r="AD6" s="76"/>
-      <c r="AE6" s="76"/>
-      <c r="AF6" s="76"/>
-      <c r="AG6" s="45"/>
-      <c r="AH6" s="75"/>
-      <c r="AI6" s="75"/>
-      <c r="AJ6" s="45"/>
+      <c r="Z6" s="109"/>
+      <c r="AA6" s="109"/>
+      <c r="AB6" s="109"/>
+      <c r="AC6" s="109"/>
+      <c r="AD6" s="90"/>
+      <c r="AE6" s="90"/>
+      <c r="AF6" s="90"/>
+      <c r="AG6" s="44"/>
+      <c r="AH6" s="134"/>
+      <c r="AI6" s="134"/>
+      <c r="AJ6" s="44"/>
     </row>
     <row r="7" spans="1:36" ht="18" customHeight="1">
-      <c r="A7" s="77" t="s">
+      <c r="A7" s="57" t="s">
         <v>3</v>
       </c>
-      <c r="B7" s="77"/>
-      <c r="C7" s="81"/>
-      <c r="D7" s="81"/>
-      <c r="E7" s="81"/>
-      <c r="F7" s="81"/>
-      <c r="G7" s="81"/>
-      <c r="H7" s="81"/>
-      <c r="I7" s="81"/>
-      <c r="J7" s="36"/>
-      <c r="K7" s="60" t="s">
+      <c r="B7" s="57"/>
+      <c r="C7" s="138"/>
+      <c r="D7" s="138"/>
+      <c r="E7" s="138"/>
+      <c r="F7" s="138"/>
+      <c r="G7" s="138"/>
+      <c r="H7" s="138"/>
+      <c r="I7" s="138"/>
+      <c r="J7" s="35"/>
+      <c r="K7" s="109" t="s">
         <v>89</v>
       </c>
-      <c r="L7" s="60"/>
-      <c r="M7" s="60"/>
-      <c r="N7" s="60"/>
-      <c r="O7" s="60"/>
-      <c r="P7" s="76"/>
-      <c r="Q7" s="76"/>
-      <c r="R7" s="76"/>
-      <c r="S7" s="75"/>
-      <c r="T7" s="75"/>
-      <c r="U7" s="40" t="s">
+      <c r="L7" s="109"/>
+      <c r="M7" s="109"/>
+      <c r="N7" s="109"/>
+      <c r="O7" s="109"/>
+      <c r="P7" s="90"/>
+      <c r="Q7" s="90"/>
+      <c r="R7" s="90"/>
+      <c r="S7" s="134"/>
+      <c r="T7" s="134"/>
+      <c r="U7" s="39" t="s">
         <v>4</v>
       </c>
-      <c r="V7" s="75"/>
-      <c r="W7" s="75"/>
-      <c r="X7" s="60" t="s">
+      <c r="V7" s="134"/>
+      <c r="W7" s="134"/>
+      <c r="X7" s="109" t="s">
         <v>90</v>
       </c>
-      <c r="Y7" s="60"/>
-      <c r="Z7" s="60"/>
-      <c r="AA7" s="60"/>
-      <c r="AB7" s="60"/>
-      <c r="AC7" s="76"/>
-      <c r="AD7" s="76"/>
-      <c r="AE7" s="76"/>
-      <c r="AF7" s="75"/>
-      <c r="AG7" s="75"/>
-      <c r="AH7" s="40" t="s">
+      <c r="Y7" s="109"/>
+      <c r="Z7" s="109"/>
+      <c r="AA7" s="109"/>
+      <c r="AB7" s="109"/>
+      <c r="AC7" s="90"/>
+      <c r="AD7" s="90"/>
+      <c r="AE7" s="90"/>
+      <c r="AF7" s="134"/>
+      <c r="AG7" s="134"/>
+      <c r="AH7" s="39" t="s">
         <v>4</v>
       </c>
-      <c r="AI7" s="75"/>
-      <c r="AJ7" s="75"/>
+      <c r="AI7" s="134"/>
+      <c r="AJ7" s="134"/>
     </row>
     <row r="8" spans="1:36" ht="18" customHeight="1">
-      <c r="A8" s="82" t="s">
+      <c r="A8" s="97" t="s">
         <v>5</v>
       </c>
-      <c r="B8" s="82"/>
-      <c r="C8" s="82"/>
-      <c r="D8" s="54"/>
-      <c r="E8" s="54"/>
-      <c r="F8" s="54"/>
-      <c r="G8" s="54"/>
-      <c r="H8" s="54"/>
-      <c r="I8" s="54"/>
-      <c r="J8" s="54"/>
-      <c r="K8" s="54"/>
-      <c r="L8" s="54"/>
-      <c r="M8" s="54"/>
-      <c r="N8" s="54"/>
-      <c r="O8" s="54"/>
-      <c r="P8" s="54"/>
-      <c r="Q8" s="54"/>
-      <c r="R8" s="54"/>
-      <c r="S8" s="89" t="s">
+      <c r="B8" s="97"/>
+      <c r="C8" s="97"/>
+      <c r="D8" s="80"/>
+      <c r="E8" s="80"/>
+      <c r="F8" s="80"/>
+      <c r="G8" s="80"/>
+      <c r="H8" s="80"/>
+      <c r="I8" s="80"/>
+      <c r="J8" s="80"/>
+      <c r="K8" s="80"/>
+      <c r="L8" s="80"/>
+      <c r="M8" s="80"/>
+      <c r="N8" s="80"/>
+      <c r="O8" s="80"/>
+      <c r="P8" s="80"/>
+      <c r="Q8" s="80"/>
+      <c r="R8" s="80"/>
+      <c r="S8" s="139" t="s">
         <v>49</v>
       </c>
-      <c r="T8" s="89"/>
-      <c r="U8" s="72"/>
-      <c r="V8" s="89"/>
-      <c r="W8" s="89"/>
-      <c r="X8" s="54"/>
-      <c r="Y8" s="54"/>
-      <c r="Z8" s="54"/>
-      <c r="AA8" s="54"/>
-      <c r="AB8" s="54"/>
-      <c r="AC8" s="54"/>
-      <c r="AD8" s="54"/>
-      <c r="AE8" s="54"/>
-      <c r="AF8" s="54"/>
-      <c r="AG8" s="54"/>
-      <c r="AH8" s="54"/>
-      <c r="AI8" s="54"/>
-      <c r="AJ8" s="54"/>
+      <c r="T8" s="139"/>
+      <c r="U8" s="109"/>
+      <c r="V8" s="139"/>
+      <c r="W8" s="139"/>
+      <c r="X8" s="80"/>
+      <c r="Y8" s="80"/>
+      <c r="Z8" s="80"/>
+      <c r="AA8" s="80"/>
+      <c r="AB8" s="80"/>
+      <c r="AC8" s="80"/>
+      <c r="AD8" s="80"/>
+      <c r="AE8" s="80"/>
+      <c r="AF8" s="80"/>
+      <c r="AG8" s="80"/>
+      <c r="AH8" s="80"/>
+      <c r="AI8" s="80"/>
+      <c r="AJ8" s="80"/>
     </row>
     <row r="9" spans="1:36" ht="26.4" customHeight="1">
-      <c r="A9" s="77" t="s">
+      <c r="A9" s="57" t="s">
         <v>6</v>
       </c>
-      <c r="B9" s="77"/>
-      <c r="C9" s="77"/>
-      <c r="D9" s="91"/>
-      <c r="E9" s="91"/>
-      <c r="F9" s="91"/>
-      <c r="G9" s="91"/>
-      <c r="H9" s="91"/>
-      <c r="I9" s="91"/>
-      <c r="J9" s="91"/>
-      <c r="K9" s="91"/>
-      <c r="L9" s="91"/>
-      <c r="M9" s="91"/>
-      <c r="N9" s="91"/>
-      <c r="O9" s="91"/>
-      <c r="P9" s="91"/>
-      <c r="Q9" s="91"/>
-      <c r="R9" s="91"/>
-      <c r="S9" s="60" t="s">
+      <c r="B9" s="57"/>
+      <c r="C9" s="57"/>
+      <c r="D9" s="108"/>
+      <c r="E9" s="108"/>
+      <c r="F9" s="108"/>
+      <c r="G9" s="108"/>
+      <c r="H9" s="108"/>
+      <c r="I9" s="108"/>
+      <c r="J9" s="108"/>
+      <c r="K9" s="108"/>
+      <c r="L9" s="108"/>
+      <c r="M9" s="108"/>
+      <c r="N9" s="108"/>
+      <c r="O9" s="108"/>
+      <c r="P9" s="108"/>
+      <c r="Q9" s="108"/>
+      <c r="R9" s="108"/>
+      <c r="S9" s="109" t="s">
         <v>50</v>
       </c>
-      <c r="T9" s="60"/>
-      <c r="U9" s="60"/>
-      <c r="V9" s="60"/>
-      <c r="W9" s="60"/>
-      <c r="X9" s="90"/>
-      <c r="Y9" s="91"/>
-      <c r="Z9" s="91"/>
-      <c r="AA9" s="91"/>
-      <c r="AB9" s="91"/>
-      <c r="AC9" s="91"/>
-      <c r="AD9" s="91"/>
-      <c r="AE9" s="91"/>
-      <c r="AF9" s="91"/>
-      <c r="AG9" s="91"/>
-      <c r="AH9" s="91"/>
-      <c r="AI9" s="91"/>
-      <c r="AJ9" s="91"/>
+      <c r="T9" s="109"/>
+      <c r="U9" s="109"/>
+      <c r="V9" s="109"/>
+      <c r="W9" s="109"/>
+      <c r="X9" s="140"/>
+      <c r="Y9" s="108"/>
+      <c r="Z9" s="108"/>
+      <c r="AA9" s="108"/>
+      <c r="AB9" s="108"/>
+      <c r="AC9" s="108"/>
+      <c r="AD9" s="108"/>
+      <c r="AE9" s="108"/>
+      <c r="AF9" s="108"/>
+      <c r="AG9" s="108"/>
+      <c r="AH9" s="108"/>
+      <c r="AI9" s="108"/>
+      <c r="AJ9" s="108"/>
     </row>
     <row r="10" spans="1:36" ht="5.25" customHeight="1">
-      <c r="A10" s="63"/>
-      <c r="B10" s="63"/>
-      <c r="C10" s="63"/>
-      <c r="D10" s="63"/>
-      <c r="E10" s="63"/>
-      <c r="F10" s="63"/>
-      <c r="G10" s="63"/>
-      <c r="H10" s="63"/>
-      <c r="I10" s="63"/>
-      <c r="J10" s="63"/>
-      <c r="K10" s="63"/>
-      <c r="L10" s="63"/>
-      <c r="M10" s="63"/>
-      <c r="N10" s="63"/>
-      <c r="O10" s="63"/>
-      <c r="P10" s="63"/>
-      <c r="Q10" s="63"/>
-      <c r="R10" s="63"/>
-      <c r="S10" s="63"/>
-      <c r="T10" s="63"/>
-      <c r="U10" s="63"/>
-      <c r="V10" s="63"/>
-      <c r="W10" s="63"/>
-      <c r="X10" s="63"/>
-      <c r="Y10" s="63"/>
-      <c r="Z10" s="63"/>
-      <c r="AA10" s="63"/>
-      <c r="AB10" s="63"/>
-      <c r="AC10" s="63"/>
-      <c r="AD10" s="63"/>
-      <c r="AE10" s="63"/>
-      <c r="AF10" s="63"/>
-      <c r="AG10" s="63"/>
-      <c r="AH10" s="63"/>
-      <c r="AI10" s="63"/>
-      <c r="AJ10" s="63"/>
+      <c r="A10" s="73"/>
+      <c r="B10" s="73"/>
+      <c r="C10" s="73"/>
+      <c r="D10" s="73"/>
+      <c r="E10" s="73"/>
+      <c r="F10" s="73"/>
+      <c r="G10" s="73"/>
+      <c r="H10" s="73"/>
+      <c r="I10" s="73"/>
+      <c r="J10" s="73"/>
+      <c r="K10" s="73"/>
+      <c r="L10" s="73"/>
+      <c r="M10" s="73"/>
+      <c r="N10" s="73"/>
+      <c r="O10" s="73"/>
+      <c r="P10" s="73"/>
+      <c r="Q10" s="73"/>
+      <c r="R10" s="73"/>
+      <c r="S10" s="73"/>
+      <c r="T10" s="73"/>
+      <c r="U10" s="73"/>
+      <c r="V10" s="73"/>
+      <c r="W10" s="73"/>
+      <c r="X10" s="73"/>
+      <c r="Y10" s="73"/>
+      <c r="Z10" s="73"/>
+      <c r="AA10" s="73"/>
+      <c r="AB10" s="73"/>
+      <c r="AC10" s="73"/>
+      <c r="AD10" s="73"/>
+      <c r="AE10" s="73"/>
+      <c r="AF10" s="73"/>
+      <c r="AG10" s="73"/>
+      <c r="AH10" s="73"/>
+      <c r="AI10" s="73"/>
+      <c r="AJ10" s="73"/>
     </row>
     <row r="11" spans="1:36" ht="14.25" customHeight="1">
-      <c r="A11" s="57" t="s">
+      <c r="A11" s="156" t="s">
         <v>7</v>
       </c>
-      <c r="B11" s="58"/>
-      <c r="C11" s="58"/>
-      <c r="D11" s="58"/>
-      <c r="E11" s="58"/>
-      <c r="F11" s="58"/>
-      <c r="G11" s="58"/>
-      <c r="H11" s="58"/>
-      <c r="I11" s="58"/>
-      <c r="J11" s="58"/>
-      <c r="K11" s="58"/>
-      <c r="L11" s="58"/>
-      <c r="M11" s="58"/>
-      <c r="N11" s="58"/>
-      <c r="O11" s="58"/>
-      <c r="P11" s="59"/>
-      <c r="Q11" s="78" t="s">
+      <c r="B11" s="157"/>
+      <c r="C11" s="157"/>
+      <c r="D11" s="157"/>
+      <c r="E11" s="157"/>
+      <c r="F11" s="157"/>
+      <c r="G11" s="157"/>
+      <c r="H11" s="157"/>
+      <c r="I11" s="157"/>
+      <c r="J11" s="157"/>
+      <c r="K11" s="157"/>
+      <c r="L11" s="157"/>
+      <c r="M11" s="157"/>
+      <c r="N11" s="157"/>
+      <c r="O11" s="157"/>
+      <c r="P11" s="158"/>
+      <c r="Q11" s="141" t="s">
         <v>8</v>
       </c>
-      <c r="R11" s="79"/>
-      <c r="S11" s="79"/>
-      <c r="T11" s="79"/>
-      <c r="U11" s="79"/>
-      <c r="V11" s="79"/>
-      <c r="W11" s="79"/>
-      <c r="X11" s="79"/>
-      <c r="Y11" s="79"/>
-      <c r="Z11" s="79"/>
-      <c r="AA11" s="79"/>
-      <c r="AB11" s="79"/>
-      <c r="AC11" s="79"/>
-      <c r="AD11" s="79"/>
-      <c r="AE11" s="79"/>
-      <c r="AF11" s="79"/>
-      <c r="AG11" s="79"/>
-      <c r="AH11" s="79"/>
-      <c r="AI11" s="79"/>
-      <c r="AJ11" s="80"/>
+      <c r="R11" s="142"/>
+      <c r="S11" s="142"/>
+      <c r="T11" s="142"/>
+      <c r="U11" s="142"/>
+      <c r="V11" s="142"/>
+      <c r="W11" s="142"/>
+      <c r="X11" s="142"/>
+      <c r="Y11" s="142"/>
+      <c r="Z11" s="142"/>
+      <c r="AA11" s="142"/>
+      <c r="AB11" s="142"/>
+      <c r="AC11" s="142"/>
+      <c r="AD11" s="142"/>
+      <c r="AE11" s="142"/>
+      <c r="AF11" s="142"/>
+      <c r="AG11" s="142"/>
+      <c r="AH11" s="142"/>
+      <c r="AI11" s="142"/>
+      <c r="AJ11" s="143"/>
     </row>
     <row r="12" spans="1:36" ht="18" customHeight="1">
       <c r="A12" s="2"/>
-      <c r="B12" s="18" t="s">
+      <c r="B12" s="17" t="s">
         <v>51</v>
       </c>
-      <c r="C12" s="18"/>
-      <c r="D12" s="20"/>
-      <c r="E12" s="20"/>
-      <c r="F12" s="18" t="s">
+      <c r="C12" s="17"/>
+      <c r="D12" s="19"/>
+      <c r="E12" s="19"/>
+      <c r="F12" s="17" t="s">
         <v>53</v>
       </c>
-      <c r="H12" s="20"/>
-      <c r="I12" s="18"/>
-      <c r="J12" s="18" t="s">
+      <c r="H12" s="19"/>
+      <c r="I12" s="17"/>
+      <c r="J12" s="17" t="s">
         <v>96</v>
       </c>
-      <c r="K12" s="18"/>
-      <c r="L12" s="18"/>
-      <c r="M12" s="18"/>
-      <c r="N12" s="18"/>
-      <c r="O12" s="18" t="s">
+      <c r="K12" s="17"/>
+      <c r="L12" s="17"/>
+      <c r="M12" s="17"/>
+      <c r="N12" s="17"/>
+      <c r="O12" s="17" t="s">
         <v>56</v>
       </c>
-      <c r="P12" s="21"/>
-      <c r="Q12" s="22"/>
-      <c r="R12" s="20" t="s">
+      <c r="P12" s="20"/>
+      <c r="Q12" s="21"/>
+      <c r="R12" s="19" t="s">
         <v>84</v>
       </c>
-      <c r="S12" s="18"/>
-      <c r="T12" s="18"/>
-      <c r="U12" s="18"/>
-      <c r="V12" s="18"/>
-      <c r="W12" s="18"/>
-      <c r="X12" s="18" t="s">
+      <c r="S12" s="17"/>
+      <c r="T12" s="17"/>
+      <c r="U12" s="17"/>
+      <c r="V12" s="17"/>
+      <c r="W12" s="17"/>
+      <c r="X12" s="17" t="s">
         <v>59</v>
       </c>
-      <c r="Y12" s="18"/>
-      <c r="Z12" s="18"/>
-      <c r="AA12" s="18"/>
-      <c r="AB12" s="18"/>
-      <c r="AC12" s="18" t="s">
+      <c r="Y12" s="17"/>
+      <c r="Z12" s="17"/>
+      <c r="AA12" s="17"/>
+      <c r="AB12" s="17"/>
+      <c r="AC12" s="17" t="s">
         <v>99</v>
       </c>
-      <c r="AD12" s="18"/>
-      <c r="AE12" s="18"/>
-      <c r="AF12" s="18"/>
-      <c r="AG12" s="18"/>
-      <c r="AH12" s="20" t="s">
+      <c r="AD12" s="17"/>
+      <c r="AE12" s="17"/>
+      <c r="AF12" s="17"/>
+      <c r="AG12" s="17"/>
+      <c r="AH12" s="19" t="s">
         <v>62</v>
       </c>
-      <c r="AI12" s="18"/>
-      <c r="AJ12" s="21"/>
+      <c r="AI12" s="17"/>
+      <c r="AJ12" s="20"/>
     </row>
     <row r="13" spans="1:36" ht="16.5" customHeight="1">
-      <c r="A13" s="6"/>
-      <c r="B13" s="19" t="s">
+      <c r="A13" s="5"/>
+      <c r="B13" s="18" t="s">
         <v>52</v>
       </c>
-      <c r="C13" s="19"/>
-      <c r="D13" s="23"/>
-      <c r="E13" s="23"/>
-      <c r="F13" s="19" t="s">
+      <c r="C13" s="18"/>
+      <c r="D13" s="22"/>
+      <c r="E13" s="22"/>
+      <c r="F13" s="18" t="s">
         <v>54</v>
       </c>
-      <c r="H13" s="23"/>
-      <c r="I13" s="19"/>
-      <c r="J13" s="19" t="s">
+      <c r="H13" s="22"/>
+      <c r="I13" s="18"/>
+      <c r="J13" s="18" t="s">
         <v>55</v>
       </c>
-      <c r="K13" s="19"/>
-      <c r="L13" s="19"/>
-      <c r="M13" s="19"/>
-      <c r="N13" s="19"/>
-      <c r="O13" s="19" t="s">
+      <c r="K13" s="18"/>
+      <c r="L13" s="18"/>
+      <c r="M13" s="18"/>
+      <c r="N13" s="18"/>
+      <c r="O13" s="18" t="s">
         <v>57</v>
       </c>
-      <c r="P13" s="24"/>
-      <c r="Q13" s="25"/>
-      <c r="R13" s="19" t="s">
+      <c r="P13" s="23"/>
+      <c r="Q13" s="24"/>
+      <c r="R13" s="18" t="s">
         <v>58</v>
       </c>
-      <c r="S13" s="19"/>
-      <c r="T13" s="19"/>
-      <c r="U13" s="19"/>
-      <c r="V13" s="19"/>
-      <c r="W13" s="19"/>
-      <c r="X13" s="19" t="s">
+      <c r="S13" s="18"/>
+      <c r="T13" s="18"/>
+      <c r="U13" s="18"/>
+      <c r="V13" s="18"/>
+      <c r="W13" s="18"/>
+      <c r="X13" s="18" t="s">
         <v>60</v>
       </c>
-      <c r="Y13" s="19"/>
-      <c r="Z13" s="19"/>
-      <c r="AA13" s="19"/>
-      <c r="AB13" s="19"/>
-      <c r="AC13" s="23" t="s">
+      <c r="Y13" s="18"/>
+      <c r="Z13" s="18"/>
+      <c r="AA13" s="18"/>
+      <c r="AB13" s="18"/>
+      <c r="AC13" s="22" t="s">
         <v>63</v>
       </c>
-      <c r="AD13" s="19"/>
-      <c r="AE13" s="19"/>
-      <c r="AF13" s="19"/>
-      <c r="AG13" s="19"/>
-      <c r="AH13" s="19" t="s">
+      <c r="AD13" s="18"/>
+      <c r="AE13" s="18"/>
+      <c r="AF13" s="18"/>
+      <c r="AG13" s="18"/>
+      <c r="AH13" s="18" t="s">
         <v>61</v>
       </c>
-      <c r="AI13" s="19"/>
-      <c r="AJ13" s="24"/>
+      <c r="AI13" s="18"/>
+      <c r="AJ13" s="23"/>
     </row>
     <row r="14" spans="1:36" ht="16.5" customHeight="1">
-      <c r="A14" s="95" t="s">
+      <c r="A14" s="126" t="s">
         <v>86</v>
       </c>
-      <c r="B14" s="96"/>
-      <c r="C14" s="96"/>
-      <c r="D14" s="96"/>
-      <c r="E14" s="96"/>
-      <c r="F14" s="96"/>
-      <c r="G14" s="96"/>
-      <c r="H14" s="96"/>
-      <c r="I14" s="97"/>
-      <c r="J14" s="98"/>
-      <c r="K14" s="98"/>
-      <c r="L14" s="98"/>
-      <c r="M14" s="98"/>
-      <c r="N14" s="98"/>
-      <c r="O14" s="98"/>
-      <c r="P14" s="98"/>
-      <c r="Q14" s="98"/>
-      <c r="R14" s="98"/>
-      <c r="S14" s="98"/>
-      <c r="T14" s="98"/>
-      <c r="U14" s="98"/>
-      <c r="V14" s="98"/>
-      <c r="W14" s="98"/>
-      <c r="X14" s="98"/>
-      <c r="Y14" s="98"/>
-      <c r="Z14" s="98"/>
-      <c r="AA14" s="98"/>
-      <c r="AB14" s="98"/>
-      <c r="AC14" s="98"/>
-      <c r="AD14" s="98"/>
-      <c r="AE14" s="98"/>
-      <c r="AF14" s="98"/>
-      <c r="AG14" s="98"/>
-      <c r="AH14" s="98"/>
-      <c r="AI14" s="98"/>
-      <c r="AJ14" s="99"/>
+      <c r="B14" s="127"/>
+      <c r="C14" s="127"/>
+      <c r="D14" s="127"/>
+      <c r="E14" s="127"/>
+      <c r="F14" s="127"/>
+      <c r="G14" s="127"/>
+      <c r="H14" s="127"/>
+      <c r="I14" s="128"/>
+      <c r="J14" s="129"/>
+      <c r="K14" s="129"/>
+      <c r="L14" s="129"/>
+      <c r="M14" s="129"/>
+      <c r="N14" s="129"/>
+      <c r="O14" s="129"/>
+      <c r="P14" s="129"/>
+      <c r="Q14" s="129"/>
+      <c r="R14" s="129"/>
+      <c r="S14" s="129"/>
+      <c r="T14" s="129"/>
+      <c r="U14" s="129"/>
+      <c r="V14" s="129"/>
+      <c r="W14" s="129"/>
+      <c r="X14" s="129"/>
+      <c r="Y14" s="129"/>
+      <c r="Z14" s="129"/>
+      <c r="AA14" s="129"/>
+      <c r="AB14" s="129"/>
+      <c r="AC14" s="129"/>
+      <c r="AD14" s="129"/>
+      <c r="AE14" s="129"/>
+      <c r="AF14" s="129"/>
+      <c r="AG14" s="129"/>
+      <c r="AH14" s="129"/>
+      <c r="AI14" s="129"/>
+      <c r="AJ14" s="130"/>
     </row>
     <row r="15" spans="1:36" ht="3" customHeight="1">
-      <c r="A15" s="100">
+      <c r="A15" s="131">
         <v>2</v>
       </c>
-      <c r="B15" s="101"/>
-      <c r="C15" s="101"/>
-      <c r="D15" s="101"/>
-      <c r="E15" s="101"/>
-      <c r="F15" s="101"/>
-      <c r="G15" s="101"/>
-      <c r="H15" s="101"/>
-      <c r="I15" s="101"/>
-      <c r="J15" s="101"/>
-      <c r="K15" s="101"/>
-      <c r="L15" s="101"/>
-      <c r="M15" s="101"/>
-      <c r="N15" s="101"/>
-      <c r="O15" s="101"/>
-      <c r="P15" s="101"/>
-      <c r="Q15" s="101"/>
-      <c r="R15" s="101"/>
-      <c r="S15" s="101"/>
-      <c r="T15" s="101"/>
-      <c r="U15" s="101"/>
-      <c r="V15" s="101"/>
-      <c r="W15" s="101"/>
-      <c r="X15" s="101"/>
-      <c r="Y15" s="101"/>
-      <c r="Z15" s="101"/>
-      <c r="AA15" s="101"/>
-      <c r="AB15" s="101"/>
-      <c r="AC15" s="101"/>
-      <c r="AD15" s="101"/>
-      <c r="AE15" s="101"/>
-      <c r="AF15" s="101"/>
-      <c r="AG15" s="101"/>
-      <c r="AH15" s="101"/>
-      <c r="AI15" s="101"/>
-      <c r="AJ15" s="102"/>
+      <c r="B15" s="132"/>
+      <c r="C15" s="132"/>
+      <c r="D15" s="132"/>
+      <c r="E15" s="132"/>
+      <c r="F15" s="132"/>
+      <c r="G15" s="132"/>
+      <c r="H15" s="132"/>
+      <c r="I15" s="132"/>
+      <c r="J15" s="132"/>
+      <c r="K15" s="132"/>
+      <c r="L15" s="132"/>
+      <c r="M15" s="132"/>
+      <c r="N15" s="132"/>
+      <c r="O15" s="132"/>
+      <c r="P15" s="132"/>
+      <c r="Q15" s="132"/>
+      <c r="R15" s="132"/>
+      <c r="S15" s="132"/>
+      <c r="T15" s="132"/>
+      <c r="U15" s="132"/>
+      <c r="V15" s="132"/>
+      <c r="W15" s="132"/>
+      <c r="X15" s="132"/>
+      <c r="Y15" s="132"/>
+      <c r="Z15" s="132"/>
+      <c r="AA15" s="132"/>
+      <c r="AB15" s="132"/>
+      <c r="AC15" s="132"/>
+      <c r="AD15" s="132"/>
+      <c r="AE15" s="132"/>
+      <c r="AF15" s="132"/>
+      <c r="AG15" s="132"/>
+      <c r="AH15" s="132"/>
+      <c r="AI15" s="132"/>
+      <c r="AJ15" s="133"/>
     </row>
     <row r="16" spans="1:36" ht="12.75" customHeight="1">
-      <c r="A16" s="67" t="s">
+      <c r="A16" s="147" t="s">
         <v>9</v>
       </c>
-      <c r="B16" s="68"/>
-      <c r="C16" s="68"/>
-      <c r="D16" s="68"/>
-      <c r="E16" s="68"/>
-      <c r="F16" s="68"/>
-      <c r="G16" s="68"/>
-      <c r="H16" s="68"/>
-      <c r="I16" s="68"/>
-      <c r="J16" s="68"/>
-      <c r="K16" s="68"/>
-      <c r="L16" s="68"/>
-      <c r="M16" s="68"/>
-      <c r="N16" s="68"/>
-      <c r="O16" s="68"/>
-      <c r="P16" s="68"/>
-      <c r="Q16" s="68"/>
-      <c r="R16" s="68"/>
-      <c r="S16" s="68"/>
-      <c r="T16" s="69"/>
-      <c r="U16" s="86" t="s">
+      <c r="B16" s="148"/>
+      <c r="C16" s="148"/>
+      <c r="D16" s="148"/>
+      <c r="E16" s="148"/>
+      <c r="F16" s="148"/>
+      <c r="G16" s="148"/>
+      <c r="H16" s="148"/>
+      <c r="I16" s="148"/>
+      <c r="J16" s="148"/>
+      <c r="K16" s="148"/>
+      <c r="L16" s="148"/>
+      <c r="M16" s="148"/>
+      <c r="N16" s="148"/>
+      <c r="O16" s="148"/>
+      <c r="P16" s="148"/>
+      <c r="Q16" s="148"/>
+      <c r="R16" s="148"/>
+      <c r="S16" s="148"/>
+      <c r="T16" s="149"/>
+      <c r="U16" s="135" t="s">
         <v>73</v>
       </c>
-      <c r="V16" s="87"/>
-      <c r="W16" s="87"/>
-      <c r="X16" s="87"/>
-      <c r="Y16" s="87"/>
-      <c r="Z16" s="87"/>
-      <c r="AA16" s="87"/>
-      <c r="AB16" s="87"/>
-      <c r="AC16" s="87"/>
-      <c r="AD16" s="88"/>
-      <c r="AE16" s="64" t="s">
+      <c r="V16" s="136"/>
+      <c r="W16" s="136"/>
+      <c r="X16" s="136"/>
+      <c r="Y16" s="136"/>
+      <c r="Z16" s="136"/>
+      <c r="AA16" s="136"/>
+      <c r="AB16" s="136"/>
+      <c r="AC16" s="136"/>
+      <c r="AD16" s="137"/>
+      <c r="AE16" s="144" t="s">
         <v>10</v>
       </c>
-      <c r="AF16" s="65"/>
-      <c r="AG16" s="65"/>
-      <c r="AH16" s="65"/>
-      <c r="AI16" s="65"/>
-      <c r="AJ16" s="66"/>
+      <c r="AF16" s="145"/>
+      <c r="AG16" s="145"/>
+      <c r="AH16" s="145"/>
+      <c r="AI16" s="145"/>
+      <c r="AJ16" s="146"/>
     </row>
     <row r="17" spans="1:36" ht="18" customHeight="1">
-      <c r="A17" s="114"/>
-      <c r="B17" s="115"/>
-      <c r="C17" s="115"/>
-      <c r="D17" s="115"/>
-      <c r="E17" s="115"/>
-      <c r="F17" s="115"/>
-      <c r="G17" s="115"/>
-      <c r="H17" s="115"/>
-      <c r="I17" s="115"/>
-      <c r="J17" s="115"/>
-      <c r="K17" s="115"/>
-      <c r="L17" s="115"/>
-      <c r="M17" s="115"/>
-      <c r="N17" s="115"/>
-      <c r="O17" s="115"/>
-      <c r="P17" s="115"/>
-      <c r="Q17" s="115"/>
-      <c r="R17" s="115"/>
-      <c r="S17" s="115"/>
-      <c r="T17" s="116"/>
-      <c r="U17" s="26"/>
-      <c r="V17" s="18" t="s">
+      <c r="A17" s="119"/>
+      <c r="B17" s="120"/>
+      <c r="C17" s="120"/>
+      <c r="D17" s="120"/>
+      <c r="E17" s="120"/>
+      <c r="F17" s="120"/>
+      <c r="G17" s="120"/>
+      <c r="H17" s="120"/>
+      <c r="I17" s="120"/>
+      <c r="J17" s="120"/>
+      <c r="K17" s="120"/>
+      <c r="L17" s="120"/>
+      <c r="M17" s="120"/>
+      <c r="N17" s="120"/>
+      <c r="O17" s="120"/>
+      <c r="P17" s="120"/>
+      <c r="Q17" s="120"/>
+      <c r="R17" s="120"/>
+      <c r="S17" s="120"/>
+      <c r="T17" s="121"/>
+      <c r="U17" s="25"/>
+      <c r="V17" s="17" t="s">
         <v>64</v>
       </c>
-      <c r="W17" s="10"/>
-      <c r="X17" s="4"/>
-      <c r="Y17" s="4"/>
-      <c r="Z17" s="18" t="s">
+      <c r="W17" s="9"/>
+      <c r="Z17" s="17" t="s">
         <v>67</v>
       </c>
-      <c r="AA17" s="4"/>
-      <c r="AB17" s="4"/>
-      <c r="AC17" s="18" t="s">
+      <c r="AC17" s="17" t="s">
         <v>70</v>
       </c>
-      <c r="AD17" s="5"/>
-      <c r="AE17" s="15" t="s">
+      <c r="AD17" s="4"/>
+      <c r="AE17" s="14" t="s">
         <v>11</v>
       </c>
-      <c r="AF17" s="84"/>
-      <c r="AG17" s="84"/>
-      <c r="AH17" s="4"/>
-      <c r="AI17" s="84"/>
-      <c r="AJ17" s="85"/>
+      <c r="AF17" s="101"/>
+      <c r="AG17" s="101"/>
+      <c r="AI17" s="101"/>
+      <c r="AJ17" s="125"/>
     </row>
     <row r="18" spans="1:36" ht="18" customHeight="1">
-      <c r="A18" s="114"/>
-      <c r="B18" s="115"/>
-      <c r="C18" s="115"/>
-      <c r="D18" s="115"/>
-      <c r="E18" s="115"/>
-      <c r="F18" s="115"/>
-      <c r="G18" s="115"/>
-      <c r="H18" s="115"/>
-      <c r="I18" s="115"/>
-      <c r="J18" s="115"/>
-      <c r="K18" s="115"/>
-      <c r="L18" s="115"/>
-      <c r="M18" s="115"/>
-      <c r="N18" s="115"/>
-      <c r="O18" s="115"/>
-      <c r="P18" s="115"/>
-      <c r="Q18" s="115"/>
-      <c r="R18" s="115"/>
-      <c r="S18" s="115"/>
-      <c r="T18" s="116"/>
-      <c r="U18" s="27"/>
-      <c r="V18" s="18" t="s">
+      <c r="A18" s="119"/>
+      <c r="B18" s="120"/>
+      <c r="C18" s="120"/>
+      <c r="D18" s="120"/>
+      <c r="E18" s="120"/>
+      <c r="F18" s="120"/>
+      <c r="G18" s="120"/>
+      <c r="H18" s="120"/>
+      <c r="I18" s="120"/>
+      <c r="J18" s="120"/>
+      <c r="K18" s="120"/>
+      <c r="L18" s="120"/>
+      <c r="M18" s="120"/>
+      <c r="N18" s="120"/>
+      <c r="O18" s="120"/>
+      <c r="P18" s="120"/>
+      <c r="Q18" s="120"/>
+      <c r="R18" s="120"/>
+      <c r="S18" s="120"/>
+      <c r="T18" s="121"/>
+      <c r="U18" s="26"/>
+      <c r="V18" s="17" t="s">
         <v>65</v>
       </c>
-      <c r="W18" s="12"/>
-      <c r="X18" s="4"/>
-      <c r="Y18" s="4"/>
-      <c r="Z18" s="18" t="s">
+      <c r="W18" s="11"/>
+      <c r="Z18" s="17" t="s">
         <v>68</v>
       </c>
-      <c r="AA18" s="4"/>
-      <c r="AB18" s="4"/>
-      <c r="AC18" s="18" t="s">
+      <c r="AC18" s="17" t="s">
         <v>71</v>
       </c>
-      <c r="AD18" s="5"/>
-      <c r="AE18" s="15" t="s">
+      <c r="AD18" s="4"/>
+      <c r="AE18" s="14" t="s">
         <v>12</v>
       </c>
-      <c r="AF18" s="84"/>
-      <c r="AG18" s="84"/>
-      <c r="AH18" s="4"/>
-      <c r="AI18" s="84"/>
-      <c r="AJ18" s="85"/>
+      <c r="AF18" s="101"/>
+      <c r="AG18" s="101"/>
+      <c r="AI18" s="101"/>
+      <c r="AJ18" s="125"/>
     </row>
     <row r="19" spans="1:36" ht="18" customHeight="1">
-      <c r="A19" s="114"/>
-      <c r="B19" s="115"/>
-      <c r="C19" s="115"/>
-      <c r="D19" s="115"/>
-      <c r="E19" s="115"/>
-      <c r="F19" s="115"/>
-      <c r="G19" s="115"/>
-      <c r="H19" s="115"/>
-      <c r="I19" s="115"/>
-      <c r="J19" s="115"/>
-      <c r="K19" s="115"/>
-      <c r="L19" s="115"/>
-      <c r="M19" s="115"/>
-      <c r="N19" s="115"/>
-      <c r="O19" s="115"/>
-      <c r="P19" s="115"/>
-      <c r="Q19" s="115"/>
-      <c r="R19" s="115"/>
-      <c r="S19" s="115"/>
-      <c r="T19" s="116"/>
-      <c r="U19" s="27"/>
-      <c r="V19" s="18" t="s">
+      <c r="A19" s="119"/>
+      <c r="B19" s="120"/>
+      <c r="C19" s="120"/>
+      <c r="D19" s="120"/>
+      <c r="E19" s="120"/>
+      <c r="F19" s="120"/>
+      <c r="G19" s="120"/>
+      <c r="H19" s="120"/>
+      <c r="I19" s="120"/>
+      <c r="J19" s="120"/>
+      <c r="K19" s="120"/>
+      <c r="L19" s="120"/>
+      <c r="M19" s="120"/>
+      <c r="N19" s="120"/>
+      <c r="O19" s="120"/>
+      <c r="P19" s="120"/>
+      <c r="Q19" s="120"/>
+      <c r="R19" s="120"/>
+      <c r="S19" s="120"/>
+      <c r="T19" s="121"/>
+      <c r="U19" s="26"/>
+      <c r="V19" s="17" t="s">
         <v>66</v>
       </c>
-      <c r="W19" s="10"/>
-      <c r="X19" s="4"/>
-      <c r="Y19" s="4"/>
-      <c r="Z19" s="18" t="s">
+      <c r="W19" s="9"/>
+      <c r="Z19" s="17" t="s">
         <v>69</v>
       </c>
-      <c r="AA19" s="4"/>
-      <c r="AB19" s="4"/>
-      <c r="AC19" s="18" t="s">
+      <c r="AC19" s="17" t="s">
         <v>72</v>
       </c>
-      <c r="AD19" s="5"/>
-      <c r="AE19" s="15" t="s">
+      <c r="AD19" s="4"/>
+      <c r="AE19" s="14" t="s">
         <v>13</v>
       </c>
-      <c r="AF19" s="84"/>
-      <c r="AG19" s="84"/>
-      <c r="AH19" s="4"/>
-      <c r="AI19" s="84"/>
-      <c r="AJ19" s="85"/>
+      <c r="AF19" s="101"/>
+      <c r="AG19" s="101"/>
+      <c r="AI19" s="101"/>
+      <c r="AJ19" s="125"/>
     </row>
     <row r="20" spans="1:36" ht="3.75" customHeight="1">
-      <c r="A20" s="117"/>
-      <c r="B20" s="118"/>
-      <c r="C20" s="118"/>
-      <c r="D20" s="118"/>
-      <c r="E20" s="118"/>
-      <c r="F20" s="118"/>
-      <c r="G20" s="118"/>
-      <c r="H20" s="118"/>
-      <c r="I20" s="118"/>
-      <c r="J20" s="118"/>
-      <c r="K20" s="118"/>
-      <c r="L20" s="118"/>
-      <c r="M20" s="118"/>
-      <c r="N20" s="118"/>
-      <c r="O20" s="118"/>
-      <c r="P20" s="118"/>
-      <c r="Q20" s="118"/>
-      <c r="R20" s="118"/>
-      <c r="S20" s="118"/>
-      <c r="T20" s="119"/>
-      <c r="U20" s="28"/>
-      <c r="V20" s="17"/>
-      <c r="W20" s="8"/>
-      <c r="X20" s="8"/>
-      <c r="Y20" s="8"/>
-      <c r="Z20" s="8"/>
-      <c r="AA20" s="8"/>
-      <c r="AB20" s="8"/>
-      <c r="AC20" s="8"/>
-      <c r="AD20" s="9"/>
-      <c r="AE20" s="16"/>
-      <c r="AF20" s="8"/>
-      <c r="AG20" s="8"/>
-      <c r="AH20" s="8"/>
-      <c r="AI20" s="8"/>
-      <c r="AJ20" s="9"/>
+      <c r="A20" s="122"/>
+      <c r="B20" s="123"/>
+      <c r="C20" s="123"/>
+      <c r="D20" s="123"/>
+      <c r="E20" s="123"/>
+      <c r="F20" s="123"/>
+      <c r="G20" s="123"/>
+      <c r="H20" s="123"/>
+      <c r="I20" s="123"/>
+      <c r="J20" s="123"/>
+      <c r="K20" s="123"/>
+      <c r="L20" s="123"/>
+      <c r="M20" s="123"/>
+      <c r="N20" s="123"/>
+      <c r="O20" s="123"/>
+      <c r="P20" s="123"/>
+      <c r="Q20" s="123"/>
+      <c r="R20" s="123"/>
+      <c r="S20" s="123"/>
+      <c r="T20" s="124"/>
+      <c r="U20" s="27"/>
+      <c r="V20" s="16"/>
+      <c r="W20" s="7"/>
+      <c r="X20" s="7"/>
+      <c r="Y20" s="7"/>
+      <c r="Z20" s="7"/>
+      <c r="AA20" s="7"/>
+      <c r="AB20" s="7"/>
+      <c r="AC20" s="7"/>
+      <c r="AD20" s="8"/>
+      <c r="AE20" s="15"/>
+      <c r="AF20" s="7"/>
+      <c r="AG20" s="7"/>
+      <c r="AH20" s="7"/>
+      <c r="AI20" s="7"/>
+      <c r="AJ20" s="8"/>
     </row>
     <row r="21" spans="1:36" ht="12.75" customHeight="1">
-      <c r="A21" s="47" t="s">
+      <c r="A21" s="46" t="s">
         <v>14</v>
       </c>
-      <c r="B21" s="46"/>
-      <c r="C21" s="46"/>
-      <c r="D21" s="46"/>
-      <c r="E21" s="46"/>
-      <c r="F21" s="46"/>
-      <c r="G21" s="46"/>
-      <c r="H21" s="46"/>
-      <c r="I21" s="46"/>
-      <c r="J21" s="46"/>
-      <c r="K21" s="46"/>
-      <c r="L21" s="46"/>
-      <c r="M21" s="46"/>
-      <c r="N21" s="46"/>
-      <c r="O21" s="46"/>
-      <c r="P21" s="46"/>
-      <c r="Q21" s="46"/>
-      <c r="R21" s="46"/>
-      <c r="S21" s="46"/>
-      <c r="T21" s="46"/>
-      <c r="U21" s="46"/>
-      <c r="V21" s="46"/>
-      <c r="W21" s="46"/>
-      <c r="X21" s="46"/>
-      <c r="Y21" s="46"/>
-      <c r="Z21" s="46"/>
-      <c r="AA21" s="46"/>
-      <c r="AB21" s="46"/>
-      <c r="AC21" s="46"/>
-      <c r="AD21" s="46"/>
-      <c r="AE21" s="46"/>
-      <c r="AF21" s="46"/>
-      <c r="AG21" s="46"/>
-      <c r="AH21" s="46"/>
-      <c r="AI21" s="46"/>
-      <c r="AJ21" s="48"/>
+      <c r="B21" s="45"/>
+      <c r="C21" s="45"/>
+      <c r="D21" s="45"/>
+      <c r="E21" s="45"/>
+      <c r="F21" s="45"/>
+      <c r="G21" s="45"/>
+      <c r="H21" s="45"/>
+      <c r="I21" s="45"/>
+      <c r="J21" s="45"/>
+      <c r="K21" s="45"/>
+      <c r="L21" s="45"/>
+      <c r="M21" s="45"/>
+      <c r="N21" s="45"/>
+      <c r="O21" s="45"/>
+      <c r="P21" s="45"/>
+      <c r="Q21" s="45"/>
+      <c r="R21" s="45"/>
+      <c r="S21" s="45"/>
+      <c r="T21" s="45"/>
+      <c r="U21" s="45"/>
+      <c r="V21" s="45"/>
+      <c r="W21" s="45"/>
+      <c r="X21" s="45"/>
+      <c r="Y21" s="45"/>
+      <c r="Z21" s="45"/>
+      <c r="AA21" s="45"/>
+      <c r="AB21" s="45"/>
+      <c r="AC21" s="45"/>
+      <c r="AD21" s="45"/>
+      <c r="AE21" s="45"/>
+      <c r="AF21" s="45"/>
+      <c r="AG21" s="45"/>
+      <c r="AH21" s="45"/>
+      <c r="AI21" s="45"/>
+      <c r="AJ21" s="47"/>
     </row>
     <row r="22" spans="1:36" ht="16.5" customHeight="1">
-      <c r="A22" s="108"/>
-      <c r="B22" s="109"/>
-      <c r="C22" s="109"/>
-      <c r="D22" s="109"/>
-      <c r="E22" s="109"/>
-      <c r="F22" s="109"/>
-      <c r="G22" s="109"/>
-      <c r="H22" s="109"/>
-      <c r="I22" s="109"/>
-      <c r="J22" s="109"/>
-      <c r="K22" s="109"/>
-      <c r="L22" s="109"/>
-      <c r="M22" s="109"/>
-      <c r="N22" s="109"/>
-      <c r="O22" s="109"/>
-      <c r="P22" s="109"/>
-      <c r="Q22" s="109"/>
-      <c r="R22" s="109"/>
-      <c r="S22" s="109"/>
-      <c r="T22" s="109"/>
-      <c r="U22" s="109"/>
-      <c r="V22" s="109"/>
-      <c r="W22" s="109"/>
-      <c r="X22" s="109"/>
-      <c r="Y22" s="109"/>
-      <c r="Z22" s="109"/>
-      <c r="AA22" s="109"/>
-      <c r="AB22" s="109"/>
-      <c r="AC22" s="109"/>
-      <c r="AD22" s="109"/>
-      <c r="AE22" s="109"/>
-      <c r="AF22" s="109"/>
-      <c r="AG22" s="109"/>
-      <c r="AH22" s="109"/>
-      <c r="AI22" s="109"/>
-      <c r="AJ22" s="110"/>
+      <c r="A22" s="113"/>
+      <c r="B22" s="114"/>
+      <c r="C22" s="114"/>
+      <c r="D22" s="114"/>
+      <c r="E22" s="114"/>
+      <c r="F22" s="114"/>
+      <c r="G22" s="114"/>
+      <c r="H22" s="114"/>
+      <c r="I22" s="114"/>
+      <c r="J22" s="114"/>
+      <c r="K22" s="114"/>
+      <c r="L22" s="114"/>
+      <c r="M22" s="114"/>
+      <c r="N22" s="114"/>
+      <c r="O22" s="114"/>
+      <c r="P22" s="114"/>
+      <c r="Q22" s="114"/>
+      <c r="R22" s="114"/>
+      <c r="S22" s="114"/>
+      <c r="T22" s="114"/>
+      <c r="U22" s="114"/>
+      <c r="V22" s="114"/>
+      <c r="W22" s="114"/>
+      <c r="X22" s="114"/>
+      <c r="Y22" s="114"/>
+      <c r="Z22" s="114"/>
+      <c r="AA22" s="114"/>
+      <c r="AB22" s="114"/>
+      <c r="AC22" s="114"/>
+      <c r="AD22" s="114"/>
+      <c r="AE22" s="114"/>
+      <c r="AF22" s="114"/>
+      <c r="AG22" s="114"/>
+      <c r="AH22" s="114"/>
+      <c r="AI22" s="114"/>
+      <c r="AJ22" s="115"/>
     </row>
     <row r="23" spans="1:36" ht="16.5" customHeight="1">
-      <c r="A23" s="111"/>
-      <c r="B23" s="112"/>
-      <c r="C23" s="112"/>
-      <c r="D23" s="112"/>
-      <c r="E23" s="112"/>
-      <c r="F23" s="112"/>
-      <c r="G23" s="112"/>
-      <c r="H23" s="112"/>
-      <c r="I23" s="112"/>
-      <c r="J23" s="112"/>
-      <c r="K23" s="112"/>
-      <c r="L23" s="112"/>
-      <c r="M23" s="112"/>
-      <c r="N23" s="112"/>
-      <c r="O23" s="112"/>
-      <c r="P23" s="112"/>
-      <c r="Q23" s="112"/>
-      <c r="R23" s="112"/>
-      <c r="S23" s="112"/>
-      <c r="T23" s="112"/>
-      <c r="U23" s="112"/>
-      <c r="V23" s="112"/>
-      <c r="W23" s="112"/>
-      <c r="X23" s="112"/>
-      <c r="Y23" s="112"/>
-      <c r="Z23" s="112"/>
-      <c r="AA23" s="112"/>
-      <c r="AB23" s="112"/>
-      <c r="AC23" s="112"/>
-      <c r="AD23" s="112"/>
-      <c r="AE23" s="112"/>
-      <c r="AF23" s="112"/>
-      <c r="AG23" s="112"/>
-      <c r="AH23" s="112"/>
-      <c r="AI23" s="112"/>
-      <c r="AJ23" s="113"/>
+      <c r="A23" s="116"/>
+      <c r="B23" s="117"/>
+      <c r="C23" s="117"/>
+      <c r="D23" s="117"/>
+      <c r="E23" s="117"/>
+      <c r="F23" s="117"/>
+      <c r="G23" s="117"/>
+      <c r="H23" s="117"/>
+      <c r="I23" s="117"/>
+      <c r="J23" s="117"/>
+      <c r="K23" s="117"/>
+      <c r="L23" s="117"/>
+      <c r="M23" s="117"/>
+      <c r="N23" s="117"/>
+      <c r="O23" s="117"/>
+      <c r="P23" s="117"/>
+      <c r="Q23" s="117"/>
+      <c r="R23" s="117"/>
+      <c r="S23" s="117"/>
+      <c r="T23" s="117"/>
+      <c r="U23" s="117"/>
+      <c r="V23" s="117"/>
+      <c r="W23" s="117"/>
+      <c r="X23" s="117"/>
+      <c r="Y23" s="117"/>
+      <c r="Z23" s="117"/>
+      <c r="AA23" s="117"/>
+      <c r="AB23" s="117"/>
+      <c r="AC23" s="117"/>
+      <c r="AD23" s="117"/>
+      <c r="AE23" s="117"/>
+      <c r="AF23" s="117"/>
+      <c r="AG23" s="117"/>
+      <c r="AH23" s="117"/>
+      <c r="AI23" s="117"/>
+      <c r="AJ23" s="118"/>
     </row>
     <row r="24" spans="1:36" ht="12.75" customHeight="1">
-      <c r="A24" s="47" t="s">
+      <c r="A24" s="46" t="s">
         <v>15</v>
       </c>
-      <c r="B24" s="46"/>
-      <c r="C24" s="46"/>
-      <c r="D24" s="46"/>
-      <c r="E24" s="46"/>
-      <c r="F24" s="46"/>
-      <c r="G24" s="46"/>
-      <c r="H24" s="46"/>
-      <c r="I24" s="46"/>
-      <c r="J24" s="46"/>
-      <c r="K24" s="46"/>
-      <c r="L24" s="46"/>
-      <c r="M24" s="46"/>
-      <c r="N24" s="46"/>
-      <c r="O24" s="46"/>
-      <c r="P24" s="46"/>
-      <c r="Q24" s="46"/>
-      <c r="R24" s="46"/>
-      <c r="S24" s="46"/>
-      <c r="T24" s="46"/>
-      <c r="U24" s="46"/>
-      <c r="V24" s="46"/>
-      <c r="W24" s="46"/>
-      <c r="X24" s="46"/>
-      <c r="Y24" s="46"/>
-      <c r="Z24" s="46"/>
-      <c r="AA24" s="46"/>
-      <c r="AB24" s="46"/>
-      <c r="AC24" s="46"/>
-      <c r="AD24" s="46"/>
-      <c r="AE24" s="46"/>
-      <c r="AF24" s="46"/>
-      <c r="AG24" s="46"/>
-      <c r="AH24" s="46"/>
-      <c r="AI24" s="46"/>
-      <c r="AJ24" s="48"/>
+      <c r="B24" s="45"/>
+      <c r="C24" s="45"/>
+      <c r="D24" s="45"/>
+      <c r="E24" s="45"/>
+      <c r="F24" s="45"/>
+      <c r="G24" s="45"/>
+      <c r="H24" s="45"/>
+      <c r="I24" s="45"/>
+      <c r="J24" s="45"/>
+      <c r="K24" s="45"/>
+      <c r="L24" s="45"/>
+      <c r="M24" s="45"/>
+      <c r="N24" s="45"/>
+      <c r="O24" s="45"/>
+      <c r="P24" s="45"/>
+      <c r="Q24" s="45"/>
+      <c r="R24" s="45"/>
+      <c r="S24" s="45"/>
+      <c r="T24" s="45"/>
+      <c r="U24" s="45"/>
+      <c r="V24" s="45"/>
+      <c r="W24" s="45"/>
+      <c r="X24" s="45"/>
+      <c r="Y24" s="45"/>
+      <c r="Z24" s="45"/>
+      <c r="AA24" s="45"/>
+      <c r="AB24" s="45"/>
+      <c r="AC24" s="45"/>
+      <c r="AD24" s="45"/>
+      <c r="AE24" s="45"/>
+      <c r="AF24" s="45"/>
+      <c r="AG24" s="45"/>
+      <c r="AH24" s="45"/>
+      <c r="AI24" s="45"/>
+      <c r="AJ24" s="47"/>
     </row>
     <row r="25" spans="1:36" ht="18" customHeight="1">
-      <c r="A25" s="105"/>
-      <c r="B25" s="106"/>
-      <c r="C25" s="106"/>
-      <c r="D25" s="106"/>
-      <c r="E25" s="106"/>
-      <c r="F25" s="106"/>
-      <c r="G25" s="106"/>
-      <c r="H25" s="106"/>
-      <c r="I25" s="106"/>
-      <c r="J25" s="106"/>
-      <c r="K25" s="106"/>
-      <c r="L25" s="106"/>
-      <c r="M25" s="106"/>
-      <c r="N25" s="106"/>
-      <c r="O25" s="106"/>
-      <c r="P25" s="106"/>
-      <c r="Q25" s="106"/>
-      <c r="R25" s="106"/>
-      <c r="S25" s="106"/>
-      <c r="T25" s="106"/>
-      <c r="U25" s="106"/>
-      <c r="V25" s="106"/>
-      <c r="W25" s="106"/>
-      <c r="X25" s="106"/>
-      <c r="Y25" s="106"/>
-      <c r="Z25" s="106"/>
-      <c r="AA25" s="106"/>
-      <c r="AB25" s="106"/>
-      <c r="AC25" s="106"/>
-      <c r="AD25" s="106"/>
-      <c r="AE25" s="106"/>
-      <c r="AF25" s="106"/>
-      <c r="AG25" s="106"/>
-      <c r="AH25" s="106"/>
-      <c r="AI25" s="106"/>
-      <c r="AJ25" s="107"/>
+      <c r="A25" s="110"/>
+      <c r="B25" s="111"/>
+      <c r="C25" s="111"/>
+      <c r="D25" s="111"/>
+      <c r="E25" s="111"/>
+      <c r="F25" s="111"/>
+      <c r="G25" s="111"/>
+      <c r="H25" s="111"/>
+      <c r="I25" s="111"/>
+      <c r="J25" s="111"/>
+      <c r="K25" s="111"/>
+      <c r="L25" s="111"/>
+      <c r="M25" s="111"/>
+      <c r="N25" s="111"/>
+      <c r="O25" s="111"/>
+      <c r="P25" s="111"/>
+      <c r="Q25" s="111"/>
+      <c r="R25" s="111"/>
+      <c r="S25" s="111"/>
+      <c r="T25" s="111"/>
+      <c r="U25" s="111"/>
+      <c r="V25" s="111"/>
+      <c r="W25" s="111"/>
+      <c r="X25" s="111"/>
+      <c r="Y25" s="111"/>
+      <c r="Z25" s="111"/>
+      <c r="AA25" s="111"/>
+      <c r="AB25" s="111"/>
+      <c r="AC25" s="111"/>
+      <c r="AD25" s="111"/>
+      <c r="AE25" s="111"/>
+      <c r="AF25" s="111"/>
+      <c r="AG25" s="111"/>
+      <c r="AH25" s="111"/>
+      <c r="AI25" s="111"/>
+      <c r="AJ25" s="112"/>
     </row>
     <row r="26" spans="1:36" ht="12.75" customHeight="1">
-      <c r="A26" s="47" t="s">
+      <c r="A26" s="46" t="s">
         <v>16</v>
       </c>
-      <c r="B26" s="46"/>
-      <c r="C26" s="46"/>
-      <c r="D26" s="46"/>
-      <c r="E26" s="46"/>
-      <c r="F26" s="46"/>
-      <c r="G26" s="46"/>
-      <c r="H26" s="46"/>
-      <c r="I26" s="46"/>
-      <c r="J26" s="46"/>
-      <c r="K26" s="46"/>
-      <c r="L26" s="46"/>
-      <c r="M26" s="46"/>
-      <c r="N26" s="46"/>
-      <c r="O26" s="46"/>
-      <c r="P26" s="46"/>
-      <c r="Q26" s="46"/>
-      <c r="R26" s="46"/>
-      <c r="S26" s="46"/>
-      <c r="T26" s="46"/>
-      <c r="U26" s="46"/>
-      <c r="V26" s="46"/>
-      <c r="W26" s="46"/>
-      <c r="X26" s="46"/>
-      <c r="Y26" s="46"/>
-      <c r="Z26" s="46"/>
-      <c r="AA26" s="46"/>
-      <c r="AB26" s="46"/>
-      <c r="AC26" s="46"/>
-      <c r="AD26" s="46"/>
-      <c r="AE26" s="46"/>
-      <c r="AF26" s="46"/>
-      <c r="AG26" s="46"/>
-      <c r="AH26" s="46"/>
-      <c r="AI26" s="46"/>
-      <c r="AJ26" s="48"/>
+      <c r="B26" s="45"/>
+      <c r="C26" s="45"/>
+      <c r="D26" s="45"/>
+      <c r="E26" s="45"/>
+      <c r="F26" s="45"/>
+      <c r="G26" s="45"/>
+      <c r="H26" s="45"/>
+      <c r="I26" s="45"/>
+      <c r="J26" s="45"/>
+      <c r="K26" s="45"/>
+      <c r="L26" s="45"/>
+      <c r="M26" s="45"/>
+      <c r="N26" s="45"/>
+      <c r="O26" s="45"/>
+      <c r="P26" s="45"/>
+      <c r="Q26" s="45"/>
+      <c r="R26" s="45"/>
+      <c r="S26" s="45"/>
+      <c r="T26" s="45"/>
+      <c r="U26" s="45"/>
+      <c r="V26" s="45"/>
+      <c r="W26" s="45"/>
+      <c r="X26" s="45"/>
+      <c r="Y26" s="45"/>
+      <c r="Z26" s="45"/>
+      <c r="AA26" s="45"/>
+      <c r="AB26" s="45"/>
+      <c r="AC26" s="45"/>
+      <c r="AD26" s="45"/>
+      <c r="AE26" s="45"/>
+      <c r="AF26" s="45"/>
+      <c r="AG26" s="45"/>
+      <c r="AH26" s="45"/>
+      <c r="AI26" s="45"/>
+      <c r="AJ26" s="47"/>
     </row>
     <row r="27" spans="1:36" ht="15" customHeight="1">
-      <c r="A27" s="139"/>
-      <c r="B27" s="153"/>
-      <c r="C27" s="153"/>
-      <c r="D27" s="153"/>
-      <c r="E27" s="153"/>
-      <c r="F27" s="153"/>
-      <c r="G27" s="153"/>
-      <c r="H27" s="153"/>
-      <c r="I27" s="153"/>
-      <c r="J27" s="153"/>
-      <c r="K27" s="153"/>
-      <c r="L27" s="153"/>
-      <c r="M27" s="153"/>
-      <c r="N27" s="153"/>
-      <c r="O27" s="153"/>
-      <c r="P27" s="153"/>
-      <c r="Q27" s="153"/>
-      <c r="R27" s="153"/>
-      <c r="S27" s="153"/>
-      <c r="T27" s="153"/>
-      <c r="U27" s="153"/>
-      <c r="V27" s="153"/>
-      <c r="W27" s="153"/>
-      <c r="X27" s="153"/>
-      <c r="Y27" s="153"/>
-      <c r="Z27" s="153"/>
-      <c r="AA27" s="153"/>
-      <c r="AB27" s="153"/>
-      <c r="AC27" s="153"/>
-      <c r="AD27" s="153"/>
-      <c r="AE27" s="153"/>
-      <c r="AF27" s="153"/>
-      <c r="AG27" s="153"/>
-      <c r="AH27" s="153"/>
-      <c r="AI27" s="153"/>
-      <c r="AJ27" s="154"/>
+      <c r="A27" s="59"/>
+      <c r="B27" s="60"/>
+      <c r="C27" s="60"/>
+      <c r="D27" s="60"/>
+      <c r="E27" s="60"/>
+      <c r="F27" s="60"/>
+      <c r="G27" s="60"/>
+      <c r="H27" s="60"/>
+      <c r="I27" s="60"/>
+      <c r="J27" s="60"/>
+      <c r="K27" s="60"/>
+      <c r="L27" s="60"/>
+      <c r="M27" s="60"/>
+      <c r="N27" s="60"/>
+      <c r="O27" s="60"/>
+      <c r="P27" s="60"/>
+      <c r="Q27" s="60"/>
+      <c r="R27" s="60"/>
+      <c r="S27" s="60"/>
+      <c r="T27" s="60"/>
+      <c r="U27" s="60"/>
+      <c r="V27" s="60"/>
+      <c r="W27" s="60"/>
+      <c r="X27" s="60"/>
+      <c r="Y27" s="60"/>
+      <c r="Z27" s="60"/>
+      <c r="AA27" s="60"/>
+      <c r="AB27" s="60"/>
+      <c r="AC27" s="60"/>
+      <c r="AD27" s="60"/>
+      <c r="AE27" s="60"/>
+      <c r="AF27" s="60"/>
+      <c r="AG27" s="60"/>
+      <c r="AH27" s="60"/>
+      <c r="AI27" s="60"/>
+      <c r="AJ27" s="61"/>
     </row>
     <row r="28" spans="1:36" ht="15" customHeight="1">
-      <c r="A28" s="155"/>
-      <c r="B28" s="153"/>
-      <c r="C28" s="153"/>
-      <c r="D28" s="153"/>
-      <c r="E28" s="153"/>
-      <c r="F28" s="153"/>
-      <c r="G28" s="153"/>
-      <c r="H28" s="153"/>
-      <c r="I28" s="153"/>
-      <c r="J28" s="153"/>
-      <c r="K28" s="153"/>
-      <c r="L28" s="153"/>
-      <c r="M28" s="153"/>
-      <c r="N28" s="153"/>
-      <c r="O28" s="153"/>
-      <c r="P28" s="153"/>
-      <c r="Q28" s="153"/>
-      <c r="R28" s="153"/>
-      <c r="S28" s="153"/>
-      <c r="T28" s="153"/>
-      <c r="U28" s="153"/>
-      <c r="V28" s="153"/>
-      <c r="W28" s="153"/>
-      <c r="X28" s="153"/>
-      <c r="Y28" s="153"/>
-      <c r="Z28" s="153"/>
-      <c r="AA28" s="153"/>
-      <c r="AB28" s="153"/>
-      <c r="AC28" s="153"/>
-      <c r="AD28" s="153"/>
-      <c r="AE28" s="153"/>
-      <c r="AF28" s="153"/>
-      <c r="AG28" s="153"/>
-      <c r="AH28" s="153"/>
-      <c r="AI28" s="153"/>
-      <c r="AJ28" s="154"/>
+      <c r="A28" s="62"/>
+      <c r="B28" s="60"/>
+      <c r="C28" s="60"/>
+      <c r="D28" s="60"/>
+      <c r="E28" s="60"/>
+      <c r="F28" s="60"/>
+      <c r="G28" s="60"/>
+      <c r="H28" s="60"/>
+      <c r="I28" s="60"/>
+      <c r="J28" s="60"/>
+      <c r="K28" s="60"/>
+      <c r="L28" s="60"/>
+      <c r="M28" s="60"/>
+      <c r="N28" s="60"/>
+      <c r="O28" s="60"/>
+      <c r="P28" s="60"/>
+      <c r="Q28" s="60"/>
+      <c r="R28" s="60"/>
+      <c r="S28" s="60"/>
+      <c r="T28" s="60"/>
+      <c r="U28" s="60"/>
+      <c r="V28" s="60"/>
+      <c r="W28" s="60"/>
+      <c r="X28" s="60"/>
+      <c r="Y28" s="60"/>
+      <c r="Z28" s="60"/>
+      <c r="AA28" s="60"/>
+      <c r="AB28" s="60"/>
+      <c r="AC28" s="60"/>
+      <c r="AD28" s="60"/>
+      <c r="AE28" s="60"/>
+      <c r="AF28" s="60"/>
+      <c r="AG28" s="60"/>
+      <c r="AH28" s="60"/>
+      <c r="AI28" s="60"/>
+      <c r="AJ28" s="61"/>
     </row>
     <row r="29" spans="1:36" ht="217.2" customHeight="1">
-      <c r="A29" s="156"/>
-      <c r="B29" s="157"/>
-      <c r="C29" s="157"/>
-      <c r="D29" s="157"/>
-      <c r="E29" s="157"/>
-      <c r="F29" s="157"/>
-      <c r="G29" s="157"/>
-      <c r="H29" s="157"/>
-      <c r="I29" s="157"/>
-      <c r="J29" s="157"/>
-      <c r="K29" s="157"/>
-      <c r="L29" s="157"/>
-      <c r="M29" s="157"/>
-      <c r="N29" s="157"/>
-      <c r="O29" s="157"/>
-      <c r="P29" s="157"/>
-      <c r="Q29" s="157"/>
-      <c r="R29" s="157"/>
-      <c r="S29" s="157"/>
-      <c r="T29" s="157"/>
-      <c r="U29" s="157"/>
-      <c r="V29" s="157"/>
-      <c r="W29" s="157"/>
-      <c r="X29" s="157"/>
-      <c r="Y29" s="157"/>
-      <c r="Z29" s="157"/>
-      <c r="AA29" s="157"/>
-      <c r="AB29" s="157"/>
-      <c r="AC29" s="157"/>
-      <c r="AD29" s="157"/>
-      <c r="AE29" s="157"/>
-      <c r="AF29" s="157"/>
-      <c r="AG29" s="157"/>
-      <c r="AH29" s="157"/>
-      <c r="AI29" s="157"/>
-      <c r="AJ29" s="158"/>
+      <c r="A29" s="63"/>
+      <c r="B29" s="64"/>
+      <c r="C29" s="64"/>
+      <c r="D29" s="64"/>
+      <c r="E29" s="64"/>
+      <c r="F29" s="64"/>
+      <c r="G29" s="64"/>
+      <c r="H29" s="64"/>
+      <c r="I29" s="64"/>
+      <c r="J29" s="64"/>
+      <c r="K29" s="64"/>
+      <c r="L29" s="64"/>
+      <c r="M29" s="64"/>
+      <c r="N29" s="64"/>
+      <c r="O29" s="64"/>
+      <c r="P29" s="64"/>
+      <c r="Q29" s="64"/>
+      <c r="R29" s="64"/>
+      <c r="S29" s="64"/>
+      <c r="T29" s="64"/>
+      <c r="U29" s="64"/>
+      <c r="V29" s="64"/>
+      <c r="W29" s="64"/>
+      <c r="X29" s="64"/>
+      <c r="Y29" s="64"/>
+      <c r="Z29" s="64"/>
+      <c r="AA29" s="64"/>
+      <c r="AB29" s="64"/>
+      <c r="AC29" s="64"/>
+      <c r="AD29" s="64"/>
+      <c r="AE29" s="64"/>
+      <c r="AF29" s="64"/>
+      <c r="AG29" s="64"/>
+      <c r="AH29" s="64"/>
+      <c r="AI29" s="64"/>
+      <c r="AJ29" s="65"/>
     </row>
     <row r="30" spans="1:36" ht="12.75" customHeight="1">
-      <c r="A30" s="136" t="s">
+      <c r="A30" s="87" t="s">
         <v>17</v>
       </c>
-      <c r="B30" s="137"/>
-      <c r="C30" s="137"/>
-      <c r="D30" s="137"/>
-      <c r="E30" s="137"/>
-      <c r="F30" s="137"/>
-      <c r="G30" s="137"/>
-      <c r="H30" s="137"/>
-      <c r="I30" s="137"/>
-      <c r="J30" s="137"/>
-      <c r="K30" s="137"/>
-      <c r="L30" s="137"/>
-      <c r="M30" s="137"/>
-      <c r="N30" s="137"/>
-      <c r="O30" s="137"/>
-      <c r="P30" s="42"/>
-      <c r="Q30" s="42"/>
-      <c r="R30" s="42"/>
-      <c r="S30" s="42"/>
-      <c r="T30" s="42"/>
-      <c r="U30" s="42"/>
-      <c r="V30" s="42"/>
-      <c r="W30" s="42"/>
-      <c r="X30" s="42"/>
-      <c r="Y30" s="42"/>
-      <c r="Z30" s="42"/>
-      <c r="AA30" s="42"/>
-      <c r="AB30" s="42"/>
-      <c r="AC30" s="42"/>
-      <c r="AD30" s="42"/>
-      <c r="AE30" s="42"/>
-      <c r="AF30" s="42"/>
-      <c r="AG30" s="42"/>
-      <c r="AH30" s="42"/>
-      <c r="AI30" s="42"/>
-      <c r="AJ30" s="43"/>
+      <c r="B30" s="88"/>
+      <c r="C30" s="88"/>
+      <c r="D30" s="88"/>
+      <c r="E30" s="88"/>
+      <c r="F30" s="88"/>
+      <c r="G30" s="88"/>
+      <c r="H30" s="88"/>
+      <c r="I30" s="88"/>
+      <c r="J30" s="88"/>
+      <c r="K30" s="88"/>
+      <c r="L30" s="88"/>
+      <c r="M30" s="88"/>
+      <c r="N30" s="88"/>
+      <c r="O30" s="88"/>
+      <c r="P30" s="41"/>
+      <c r="Q30" s="41"/>
+      <c r="R30" s="41"/>
+      <c r="S30" s="41"/>
+      <c r="T30" s="41"/>
+      <c r="U30" s="41"/>
+      <c r="V30" s="41"/>
+      <c r="W30" s="41"/>
+      <c r="X30" s="41"/>
+      <c r="Y30" s="41"/>
+      <c r="Z30" s="41"/>
+      <c r="AA30" s="41"/>
+      <c r="AB30" s="41"/>
+      <c r="AC30" s="41"/>
+      <c r="AD30" s="41"/>
+      <c r="AE30" s="41"/>
+      <c r="AF30" s="41"/>
+      <c r="AG30" s="41"/>
+      <c r="AH30" s="41"/>
+      <c r="AI30" s="41"/>
+      <c r="AJ30" s="42"/>
     </row>
     <row r="31" spans="1:36" ht="16.5" customHeight="1">
-      <c r="A31" s="139"/>
-      <c r="B31" s="140"/>
-      <c r="C31" s="140"/>
-      <c r="D31" s="140"/>
-      <c r="E31" s="140"/>
-      <c r="F31" s="140"/>
-      <c r="G31" s="140"/>
-      <c r="H31" s="140"/>
-      <c r="I31" s="140"/>
-      <c r="J31" s="140"/>
-      <c r="K31" s="140"/>
-      <c r="L31" s="140"/>
-      <c r="M31" s="140"/>
-      <c r="N31" s="140"/>
-      <c r="O31" s="140"/>
-      <c r="P31" s="140"/>
-      <c r="Q31" s="140"/>
-      <c r="R31" s="140"/>
-      <c r="S31" s="140"/>
-      <c r="T31" s="140"/>
-      <c r="U31" s="140"/>
-      <c r="V31" s="140"/>
-      <c r="W31" s="140"/>
-      <c r="X31" s="140"/>
-      <c r="Y31" s="140"/>
-      <c r="Z31" s="140"/>
-      <c r="AA31" s="140"/>
-      <c r="AB31" s="140"/>
-      <c r="AC31" s="140"/>
-      <c r="AD31" s="140"/>
-      <c r="AE31" s="140"/>
-      <c r="AF31" s="140"/>
-      <c r="AG31" s="140"/>
-      <c r="AH31" s="140"/>
-      <c r="AI31" s="140"/>
-      <c r="AJ31" s="141"/>
+      <c r="A31" s="59"/>
+      <c r="B31" s="91"/>
+      <c r="C31" s="91"/>
+      <c r="D31" s="91"/>
+      <c r="E31" s="91"/>
+      <c r="F31" s="91"/>
+      <c r="G31" s="91"/>
+      <c r="H31" s="91"/>
+      <c r="I31" s="91"/>
+      <c r="J31" s="91"/>
+      <c r="K31" s="91"/>
+      <c r="L31" s="91"/>
+      <c r="M31" s="91"/>
+      <c r="N31" s="91"/>
+      <c r="O31" s="91"/>
+      <c r="P31" s="91"/>
+      <c r="Q31" s="91"/>
+      <c r="R31" s="91"/>
+      <c r="S31" s="91"/>
+      <c r="T31" s="91"/>
+      <c r="U31" s="91"/>
+      <c r="V31" s="91"/>
+      <c r="W31" s="91"/>
+      <c r="X31" s="91"/>
+      <c r="Y31" s="91"/>
+      <c r="Z31" s="91"/>
+      <c r="AA31" s="91"/>
+      <c r="AB31" s="91"/>
+      <c r="AC31" s="91"/>
+      <c r="AD31" s="91"/>
+      <c r="AE31" s="91"/>
+      <c r="AF31" s="91"/>
+      <c r="AG31" s="91"/>
+      <c r="AH31" s="91"/>
+      <c r="AI31" s="91"/>
+      <c r="AJ31" s="92"/>
     </row>
     <row r="32" spans="1:36" ht="16.5" customHeight="1">
-      <c r="A32" s="139"/>
-      <c r="B32" s="140"/>
-      <c r="C32" s="140"/>
-      <c r="D32" s="140"/>
-      <c r="E32" s="140"/>
-      <c r="F32" s="140"/>
-      <c r="G32" s="140"/>
-      <c r="H32" s="140"/>
-      <c r="I32" s="140"/>
-      <c r="J32" s="140"/>
-      <c r="K32" s="140"/>
-      <c r="L32" s="140"/>
-      <c r="M32" s="140"/>
-      <c r="N32" s="140"/>
-      <c r="O32" s="140"/>
-      <c r="P32" s="140"/>
-      <c r="Q32" s="140"/>
-      <c r="R32" s="140"/>
-      <c r="S32" s="140"/>
-      <c r="T32" s="140"/>
-      <c r="U32" s="140"/>
-      <c r="V32" s="140"/>
-      <c r="W32" s="140"/>
-      <c r="X32" s="140"/>
-      <c r="Y32" s="140"/>
-      <c r="Z32" s="140"/>
-      <c r="AA32" s="140"/>
-      <c r="AB32" s="140"/>
-      <c r="AC32" s="140"/>
-      <c r="AD32" s="140"/>
-      <c r="AE32" s="140"/>
-      <c r="AF32" s="140"/>
-      <c r="AG32" s="140"/>
-      <c r="AH32" s="140"/>
-      <c r="AI32" s="140"/>
-      <c r="AJ32" s="141"/>
+      <c r="A32" s="59"/>
+      <c r="B32" s="91"/>
+      <c r="C32" s="91"/>
+      <c r="D32" s="91"/>
+      <c r="E32" s="91"/>
+      <c r="F32" s="91"/>
+      <c r="G32" s="91"/>
+      <c r="H32" s="91"/>
+      <c r="I32" s="91"/>
+      <c r="J32" s="91"/>
+      <c r="K32" s="91"/>
+      <c r="L32" s="91"/>
+      <c r="M32" s="91"/>
+      <c r="N32" s="91"/>
+      <c r="O32" s="91"/>
+      <c r="P32" s="91"/>
+      <c r="Q32" s="91"/>
+      <c r="R32" s="91"/>
+      <c r="S32" s="91"/>
+      <c r="T32" s="91"/>
+      <c r="U32" s="91"/>
+      <c r="V32" s="91"/>
+      <c r="W32" s="91"/>
+      <c r="X32" s="91"/>
+      <c r="Y32" s="91"/>
+      <c r="Z32" s="91"/>
+      <c r="AA32" s="91"/>
+      <c r="AB32" s="91"/>
+      <c r="AC32" s="91"/>
+      <c r="AD32" s="91"/>
+      <c r="AE32" s="91"/>
+      <c r="AF32" s="91"/>
+      <c r="AG32" s="91"/>
+      <c r="AH32" s="91"/>
+      <c r="AI32" s="91"/>
+      <c r="AJ32" s="92"/>
     </row>
     <row r="33" spans="1:36" ht="16.5" customHeight="1">
-      <c r="A33" s="139"/>
-      <c r="B33" s="140"/>
-      <c r="C33" s="140"/>
-      <c r="D33" s="140"/>
-      <c r="E33" s="140"/>
-      <c r="F33" s="140"/>
-      <c r="G33" s="140"/>
-      <c r="H33" s="140"/>
-      <c r="I33" s="140"/>
-      <c r="J33" s="140"/>
-      <c r="K33" s="140"/>
-      <c r="L33" s="140"/>
-      <c r="M33" s="140"/>
-      <c r="N33" s="140"/>
-      <c r="O33" s="140"/>
-      <c r="P33" s="140"/>
-      <c r="Q33" s="140"/>
-      <c r="R33" s="140"/>
-      <c r="S33" s="140"/>
-      <c r="T33" s="140"/>
-      <c r="U33" s="140"/>
-      <c r="V33" s="140"/>
-      <c r="W33" s="140"/>
-      <c r="X33" s="140"/>
-      <c r="Y33" s="140"/>
-      <c r="Z33" s="140"/>
-      <c r="AA33" s="140"/>
-      <c r="AB33" s="140"/>
-      <c r="AC33" s="140"/>
-      <c r="AD33" s="140"/>
-      <c r="AE33" s="140"/>
-      <c r="AF33" s="140"/>
-      <c r="AG33" s="140"/>
-      <c r="AH33" s="140"/>
-      <c r="AI33" s="140"/>
-      <c r="AJ33" s="141"/>
+      <c r="A33" s="59"/>
+      <c r="B33" s="91"/>
+      <c r="C33" s="91"/>
+      <c r="D33" s="91"/>
+      <c r="E33" s="91"/>
+      <c r="F33" s="91"/>
+      <c r="G33" s="91"/>
+      <c r="H33" s="91"/>
+      <c r="I33" s="91"/>
+      <c r="J33" s="91"/>
+      <c r="K33" s="91"/>
+      <c r="L33" s="91"/>
+      <c r="M33" s="91"/>
+      <c r="N33" s="91"/>
+      <c r="O33" s="91"/>
+      <c r="P33" s="91"/>
+      <c r="Q33" s="91"/>
+      <c r="R33" s="91"/>
+      <c r="S33" s="91"/>
+      <c r="T33" s="91"/>
+      <c r="U33" s="91"/>
+      <c r="V33" s="91"/>
+      <c r="W33" s="91"/>
+      <c r="X33" s="91"/>
+      <c r="Y33" s="91"/>
+      <c r="Z33" s="91"/>
+      <c r="AA33" s="91"/>
+      <c r="AB33" s="91"/>
+      <c r="AC33" s="91"/>
+      <c r="AD33" s="91"/>
+      <c r="AE33" s="91"/>
+      <c r="AF33" s="91"/>
+      <c r="AG33" s="91"/>
+      <c r="AH33" s="91"/>
+      <c r="AI33" s="91"/>
+      <c r="AJ33" s="92"/>
     </row>
     <row r="34" spans="1:36" ht="61.8" customHeight="1">
-      <c r="A34" s="139"/>
-      <c r="B34" s="140"/>
-      <c r="C34" s="140"/>
-      <c r="D34" s="140"/>
-      <c r="E34" s="140"/>
-      <c r="F34" s="140"/>
-      <c r="G34" s="140"/>
-      <c r="H34" s="140"/>
-      <c r="I34" s="140"/>
-      <c r="J34" s="140"/>
-      <c r="K34" s="140"/>
-      <c r="L34" s="140"/>
-      <c r="M34" s="140"/>
-      <c r="N34" s="140"/>
-      <c r="O34" s="140"/>
-      <c r="P34" s="140"/>
-      <c r="Q34" s="140"/>
-      <c r="R34" s="140"/>
-      <c r="S34" s="140"/>
-      <c r="T34" s="140"/>
-      <c r="U34" s="140"/>
-      <c r="V34" s="140"/>
-      <c r="W34" s="140"/>
-      <c r="X34" s="140"/>
-      <c r="Y34" s="140"/>
-      <c r="Z34" s="140"/>
-      <c r="AA34" s="140"/>
-      <c r="AB34" s="140"/>
-      <c r="AC34" s="140"/>
-      <c r="AD34" s="140"/>
-      <c r="AE34" s="140"/>
-      <c r="AF34" s="140"/>
-      <c r="AG34" s="140"/>
-      <c r="AH34" s="140"/>
-      <c r="AI34" s="140"/>
-      <c r="AJ34" s="141"/>
+      <c r="A34" s="59"/>
+      <c r="B34" s="91"/>
+      <c r="C34" s="91"/>
+      <c r="D34" s="91"/>
+      <c r="E34" s="91"/>
+      <c r="F34" s="91"/>
+      <c r="G34" s="91"/>
+      <c r="H34" s="91"/>
+      <c r="I34" s="91"/>
+      <c r="J34" s="91"/>
+      <c r="K34" s="91"/>
+      <c r="L34" s="91"/>
+      <c r="M34" s="91"/>
+      <c r="N34" s="91"/>
+      <c r="O34" s="91"/>
+      <c r="P34" s="91"/>
+      <c r="Q34" s="91"/>
+      <c r="R34" s="91"/>
+      <c r="S34" s="91"/>
+      <c r="T34" s="91"/>
+      <c r="U34" s="91"/>
+      <c r="V34" s="91"/>
+      <c r="W34" s="91"/>
+      <c r="X34" s="91"/>
+      <c r="Y34" s="91"/>
+      <c r="Z34" s="91"/>
+      <c r="AA34" s="91"/>
+      <c r="AB34" s="91"/>
+      <c r="AC34" s="91"/>
+      <c r="AD34" s="91"/>
+      <c r="AE34" s="91"/>
+      <c r="AF34" s="91"/>
+      <c r="AG34" s="91"/>
+      <c r="AH34" s="91"/>
+      <c r="AI34" s="91"/>
+      <c r="AJ34" s="92"/>
     </row>
     <row r="35" spans="1:36" ht="13.2" customHeight="1">
-      <c r="A35" s="142"/>
-      <c r="B35" s="143"/>
-      <c r="C35" s="143"/>
-      <c r="D35" s="143"/>
-      <c r="E35" s="143"/>
-      <c r="F35" s="143"/>
-      <c r="G35" s="143"/>
-      <c r="H35" s="143"/>
-      <c r="I35" s="143"/>
-      <c r="J35" s="143"/>
-      <c r="K35" s="143"/>
-      <c r="L35" s="143"/>
-      <c r="M35" s="143"/>
-      <c r="N35" s="143"/>
-      <c r="O35" s="143"/>
-      <c r="P35" s="143"/>
-      <c r="Q35" s="143"/>
-      <c r="R35" s="143"/>
-      <c r="S35" s="143"/>
-      <c r="T35" s="143"/>
-      <c r="U35" s="143"/>
-      <c r="V35" s="143"/>
-      <c r="W35" s="143"/>
-      <c r="X35" s="143"/>
-      <c r="Y35" s="143"/>
-      <c r="Z35" s="143"/>
-      <c r="AA35" s="143"/>
-      <c r="AB35" s="143"/>
-      <c r="AC35" s="143"/>
-      <c r="AD35" s="143"/>
-      <c r="AE35" s="143"/>
-      <c r="AF35" s="143"/>
-      <c r="AG35" s="143"/>
-      <c r="AH35" s="143"/>
-      <c r="AI35" s="143"/>
-      <c r="AJ35" s="144"/>
+      <c r="A35" s="93"/>
+      <c r="B35" s="94"/>
+      <c r="C35" s="94"/>
+      <c r="D35" s="94"/>
+      <c r="E35" s="94"/>
+      <c r="F35" s="94"/>
+      <c r="G35" s="94"/>
+      <c r="H35" s="94"/>
+      <c r="I35" s="94"/>
+      <c r="J35" s="94"/>
+      <c r="K35" s="94"/>
+      <c r="L35" s="94"/>
+      <c r="M35" s="94"/>
+      <c r="N35" s="94"/>
+      <c r="O35" s="94"/>
+      <c r="P35" s="94"/>
+      <c r="Q35" s="94"/>
+      <c r="R35" s="94"/>
+      <c r="S35" s="94"/>
+      <c r="T35" s="94"/>
+      <c r="U35" s="94"/>
+      <c r="V35" s="94"/>
+      <c r="W35" s="94"/>
+      <c r="X35" s="94"/>
+      <c r="Y35" s="94"/>
+      <c r="Z35" s="94"/>
+      <c r="AA35" s="94"/>
+      <c r="AB35" s="94"/>
+      <c r="AC35" s="94"/>
+      <c r="AD35" s="94"/>
+      <c r="AE35" s="94"/>
+      <c r="AF35" s="94"/>
+      <c r="AG35" s="94"/>
+      <c r="AH35" s="94"/>
+      <c r="AI35" s="94"/>
+      <c r="AJ35" s="95"/>
     </row>
     <row r="36" spans="1:36" ht="13.5" customHeight="1">
-      <c r="A36" s="159" t="s">
+      <c r="A36" s="66" t="s">
         <v>94</v>
       </c>
-      <c r="B36" s="160"/>
-      <c r="C36" s="160"/>
-      <c r="D36" s="160"/>
-      <c r="E36" s="160"/>
-      <c r="F36" s="160"/>
-      <c r="G36" s="160"/>
-      <c r="H36" s="160"/>
-      <c r="I36" s="160"/>
-      <c r="J36" s="160"/>
-      <c r="K36" s="160"/>
-      <c r="L36" s="160"/>
-      <c r="M36" s="160"/>
-      <c r="N36" s="160"/>
-      <c r="O36" s="160"/>
-      <c r="P36" s="160"/>
-      <c r="Q36" s="160"/>
-      <c r="R36" s="160"/>
-      <c r="S36" s="41"/>
-      <c r="T36" s="41"/>
-      <c r="U36" s="41"/>
-      <c r="V36" s="41"/>
-      <c r="W36" s="41"/>
-      <c r="X36" s="41"/>
-      <c r="Y36" s="41"/>
-      <c r="Z36" s="41"/>
-      <c r="AA36" s="41"/>
-      <c r="AB36" s="41"/>
-      <c r="AC36" s="41"/>
-      <c r="AD36" s="41"/>
-      <c r="AE36" s="41"/>
-      <c r="AF36" s="41"/>
-      <c r="AG36" s="41"/>
-      <c r="AH36" s="41"/>
-      <c r="AI36" s="41"/>
-      <c r="AJ36" s="44"/>
+      <c r="B36" s="67"/>
+      <c r="C36" s="67"/>
+      <c r="D36" s="67"/>
+      <c r="E36" s="67"/>
+      <c r="F36" s="67"/>
+      <c r="G36" s="67"/>
+      <c r="H36" s="67"/>
+      <c r="I36" s="67"/>
+      <c r="J36" s="67"/>
+      <c r="K36" s="67"/>
+      <c r="L36" s="67"/>
+      <c r="M36" s="67"/>
+      <c r="N36" s="67"/>
+      <c r="O36" s="67"/>
+      <c r="P36" s="67"/>
+      <c r="Q36" s="67"/>
+      <c r="R36" s="67"/>
+      <c r="S36" s="40"/>
+      <c r="T36" s="40"/>
+      <c r="U36" s="40"/>
+      <c r="V36" s="40"/>
+      <c r="W36" s="40"/>
+      <c r="X36" s="40"/>
+      <c r="Y36" s="40"/>
+      <c r="Z36" s="40"/>
+      <c r="AA36" s="40"/>
+      <c r="AB36" s="40"/>
+      <c r="AC36" s="40"/>
+      <c r="AD36" s="40"/>
+      <c r="AE36" s="40"/>
+      <c r="AF36" s="40"/>
+      <c r="AG36" s="40"/>
+      <c r="AH36" s="40"/>
+      <c r="AI36" s="40"/>
+      <c r="AJ36" s="43"/>
     </row>
     <row r="37" spans="1:36" ht="14.25" customHeight="1">
-      <c r="A37" s="139"/>
-      <c r="B37" s="140"/>
-      <c r="C37" s="140"/>
-      <c r="D37" s="140"/>
-      <c r="E37" s="140"/>
-      <c r="F37" s="140"/>
-      <c r="G37" s="140"/>
-      <c r="H37" s="140"/>
-      <c r="I37" s="140"/>
-      <c r="J37" s="140"/>
-      <c r="K37" s="140"/>
-      <c r="L37" s="140"/>
-      <c r="M37" s="140"/>
-      <c r="N37" s="140"/>
-      <c r="O37" s="140"/>
-      <c r="P37" s="140"/>
-      <c r="Q37" s="140"/>
-      <c r="R37" s="140"/>
-      <c r="S37" s="140"/>
-      <c r="T37" s="140"/>
-      <c r="U37" s="140"/>
-      <c r="V37" s="140"/>
-      <c r="W37" s="140"/>
-      <c r="X37" s="140"/>
-      <c r="Y37" s="140"/>
-      <c r="Z37" s="140"/>
-      <c r="AA37" s="140"/>
-      <c r="AB37" s="140"/>
-      <c r="AC37" s="140"/>
-      <c r="AD37" s="140"/>
-      <c r="AE37" s="140"/>
-      <c r="AF37" s="140"/>
-      <c r="AG37" s="140"/>
-      <c r="AH37" s="140"/>
-      <c r="AI37" s="140"/>
-      <c r="AJ37" s="141"/>
+      <c r="A37" s="59"/>
+      <c r="B37" s="91"/>
+      <c r="C37" s="91"/>
+      <c r="D37" s="91"/>
+      <c r="E37" s="91"/>
+      <c r="F37" s="91"/>
+      <c r="G37" s="91"/>
+      <c r="H37" s="91"/>
+      <c r="I37" s="91"/>
+      <c r="J37" s="91"/>
+      <c r="K37" s="91"/>
+      <c r="L37" s="91"/>
+      <c r="M37" s="91"/>
+      <c r="N37" s="91"/>
+      <c r="O37" s="91"/>
+      <c r="P37" s="91"/>
+      <c r="Q37" s="91"/>
+      <c r="R37" s="91"/>
+      <c r="S37" s="91"/>
+      <c r="T37" s="91"/>
+      <c r="U37" s="91"/>
+      <c r="V37" s="91"/>
+      <c r="W37" s="91"/>
+      <c r="X37" s="91"/>
+      <c r="Y37" s="91"/>
+      <c r="Z37" s="91"/>
+      <c r="AA37" s="91"/>
+      <c r="AB37" s="91"/>
+      <c r="AC37" s="91"/>
+      <c r="AD37" s="91"/>
+      <c r="AE37" s="91"/>
+      <c r="AF37" s="91"/>
+      <c r="AG37" s="91"/>
+      <c r="AH37" s="91"/>
+      <c r="AI37" s="91"/>
+      <c r="AJ37" s="92"/>
     </row>
     <row r="38" spans="1:36" ht="14.25" customHeight="1">
-      <c r="A38" s="139"/>
-      <c r="B38" s="140"/>
-      <c r="C38" s="140"/>
-      <c r="D38" s="140"/>
-      <c r="E38" s="140"/>
-      <c r="F38" s="140"/>
-      <c r="G38" s="140"/>
-      <c r="H38" s="140"/>
-      <c r="I38" s="140"/>
-      <c r="J38" s="140"/>
-      <c r="K38" s="140"/>
-      <c r="L38" s="140"/>
-      <c r="M38" s="140"/>
-      <c r="N38" s="140"/>
-      <c r="O38" s="140"/>
-      <c r="P38" s="140"/>
-      <c r="Q38" s="140"/>
-      <c r="R38" s="140"/>
-      <c r="S38" s="140"/>
-      <c r="T38" s="140"/>
-      <c r="U38" s="140"/>
-      <c r="V38" s="140"/>
-      <c r="W38" s="140"/>
-      <c r="X38" s="140"/>
-      <c r="Y38" s="140"/>
-      <c r="Z38" s="140"/>
-      <c r="AA38" s="140"/>
-      <c r="AB38" s="140"/>
-      <c r="AC38" s="140"/>
-      <c r="AD38" s="140"/>
-      <c r="AE38" s="140"/>
-      <c r="AF38" s="140"/>
-      <c r="AG38" s="140"/>
-      <c r="AH38" s="140"/>
-      <c r="AI38" s="140"/>
-      <c r="AJ38" s="141"/>
+      <c r="A38" s="59"/>
+      <c r="B38" s="91"/>
+      <c r="C38" s="91"/>
+      <c r="D38" s="91"/>
+      <c r="E38" s="91"/>
+      <c r="F38" s="91"/>
+      <c r="G38" s="91"/>
+      <c r="H38" s="91"/>
+      <c r="I38" s="91"/>
+      <c r="J38" s="91"/>
+      <c r="K38" s="91"/>
+      <c r="L38" s="91"/>
+      <c r="M38" s="91"/>
+      <c r="N38" s="91"/>
+      <c r="O38" s="91"/>
+      <c r="P38" s="91"/>
+      <c r="Q38" s="91"/>
+      <c r="R38" s="91"/>
+      <c r="S38" s="91"/>
+      <c r="T38" s="91"/>
+      <c r="U38" s="91"/>
+      <c r="V38" s="91"/>
+      <c r="W38" s="91"/>
+      <c r="X38" s="91"/>
+      <c r="Y38" s="91"/>
+      <c r="Z38" s="91"/>
+      <c r="AA38" s="91"/>
+      <c r="AB38" s="91"/>
+      <c r="AC38" s="91"/>
+      <c r="AD38" s="91"/>
+      <c r="AE38" s="91"/>
+      <c r="AF38" s="91"/>
+      <c r="AG38" s="91"/>
+      <c r="AH38" s="91"/>
+      <c r="AI38" s="91"/>
+      <c r="AJ38" s="92"/>
     </row>
     <row r="39" spans="1:36" ht="27.6" customHeight="1">
-      <c r="A39" s="139"/>
-      <c r="B39" s="140"/>
-      <c r="C39" s="140"/>
-      <c r="D39" s="140"/>
-      <c r="E39" s="140"/>
-      <c r="F39" s="140"/>
-      <c r="G39" s="140"/>
-      <c r="H39" s="140"/>
-      <c r="I39" s="140"/>
-      <c r="J39" s="140"/>
-      <c r="K39" s="140"/>
-      <c r="L39" s="140"/>
-      <c r="M39" s="140"/>
-      <c r="N39" s="140"/>
-      <c r="O39" s="140"/>
-      <c r="P39" s="140"/>
-      <c r="Q39" s="140"/>
-      <c r="R39" s="140"/>
-      <c r="S39" s="140"/>
-      <c r="T39" s="140"/>
-      <c r="U39" s="140"/>
-      <c r="V39" s="140"/>
-      <c r="W39" s="140"/>
-      <c r="X39" s="140"/>
-      <c r="Y39" s="140"/>
-      <c r="Z39" s="140"/>
-      <c r="AA39" s="140"/>
-      <c r="AB39" s="140"/>
-      <c r="AC39" s="140"/>
-      <c r="AD39" s="140"/>
-      <c r="AE39" s="140"/>
-      <c r="AF39" s="140"/>
-      <c r="AG39" s="140"/>
-      <c r="AH39" s="140"/>
-      <c r="AI39" s="140"/>
-      <c r="AJ39" s="141"/>
+      <c r="A39" s="59"/>
+      <c r="B39" s="91"/>
+      <c r="C39" s="91"/>
+      <c r="D39" s="91"/>
+      <c r="E39" s="91"/>
+      <c r="F39" s="91"/>
+      <c r="G39" s="91"/>
+      <c r="H39" s="91"/>
+      <c r="I39" s="91"/>
+      <c r="J39" s="91"/>
+      <c r="K39" s="91"/>
+      <c r="L39" s="91"/>
+      <c r="M39" s="91"/>
+      <c r="N39" s="91"/>
+      <c r="O39" s="91"/>
+      <c r="P39" s="91"/>
+      <c r="Q39" s="91"/>
+      <c r="R39" s="91"/>
+      <c r="S39" s="91"/>
+      <c r="T39" s="91"/>
+      <c r="U39" s="91"/>
+      <c r="V39" s="91"/>
+      <c r="W39" s="91"/>
+      <c r="X39" s="91"/>
+      <c r="Y39" s="91"/>
+      <c r="Z39" s="91"/>
+      <c r="AA39" s="91"/>
+      <c r="AB39" s="91"/>
+      <c r="AC39" s="91"/>
+      <c r="AD39" s="91"/>
+      <c r="AE39" s="91"/>
+      <c r="AF39" s="91"/>
+      <c r="AG39" s="91"/>
+      <c r="AH39" s="91"/>
+      <c r="AI39" s="91"/>
+      <c r="AJ39" s="92"/>
     </row>
     <row r="40" spans="1:36" ht="16.8" customHeight="1">
-      <c r="A40" s="139"/>
-      <c r="B40" s="140"/>
-      <c r="C40" s="140"/>
-      <c r="D40" s="140"/>
-      <c r="E40" s="140"/>
-      <c r="F40" s="140"/>
-      <c r="G40" s="140"/>
-      <c r="H40" s="140"/>
-      <c r="I40" s="140"/>
-      <c r="J40" s="140"/>
-      <c r="K40" s="140"/>
-      <c r="L40" s="140"/>
-      <c r="M40" s="140"/>
-      <c r="N40" s="140"/>
-      <c r="O40" s="140"/>
-      <c r="P40" s="140"/>
-      <c r="Q40" s="140"/>
-      <c r="R40" s="140"/>
-      <c r="S40" s="140"/>
-      <c r="T40" s="140"/>
-      <c r="U40" s="140"/>
-      <c r="V40" s="140"/>
-      <c r="W40" s="140"/>
-      <c r="X40" s="140"/>
-      <c r="Y40" s="140"/>
-      <c r="Z40" s="140"/>
-      <c r="AA40" s="140"/>
-      <c r="AB40" s="140"/>
-      <c r="AC40" s="140"/>
-      <c r="AD40" s="140"/>
-      <c r="AE40" s="140"/>
-      <c r="AF40" s="140"/>
-      <c r="AG40" s="140"/>
-      <c r="AH40" s="140"/>
-      <c r="AI40" s="140"/>
-      <c r="AJ40" s="141"/>
+      <c r="A40" s="59"/>
+      <c r="B40" s="91"/>
+      <c r="C40" s="91"/>
+      <c r="D40" s="91"/>
+      <c r="E40" s="91"/>
+      <c r="F40" s="91"/>
+      <c r="G40" s="91"/>
+      <c r="H40" s="91"/>
+      <c r="I40" s="91"/>
+      <c r="J40" s="91"/>
+      <c r="K40" s="91"/>
+      <c r="L40" s="91"/>
+      <c r="M40" s="91"/>
+      <c r="N40" s="91"/>
+      <c r="O40" s="91"/>
+      <c r="P40" s="91"/>
+      <c r="Q40" s="91"/>
+      <c r="R40" s="91"/>
+      <c r="S40" s="91"/>
+      <c r="T40" s="91"/>
+      <c r="U40" s="91"/>
+      <c r="V40" s="91"/>
+      <c r="W40" s="91"/>
+      <c r="X40" s="91"/>
+      <c r="Y40" s="91"/>
+      <c r="Z40" s="91"/>
+      <c r="AA40" s="91"/>
+      <c r="AB40" s="91"/>
+      <c r="AC40" s="91"/>
+      <c r="AD40" s="91"/>
+      <c r="AE40" s="91"/>
+      <c r="AF40" s="91"/>
+      <c r="AG40" s="91"/>
+      <c r="AH40" s="91"/>
+      <c r="AI40" s="91"/>
+      <c r="AJ40" s="92"/>
     </row>
-    <row r="41" spans="1:36" ht="17.25" customHeight="1">
-      <c r="A41" s="92" t="s">
+    <row r="41" spans="1:36" ht="16.8" customHeight="1">
+      <c r="A41" s="66" t="s">
+        <v>100</v>
+      </c>
+      <c r="B41" s="67"/>
+      <c r="C41" s="67"/>
+      <c r="D41" s="67"/>
+      <c r="E41" s="67"/>
+      <c r="F41" s="67"/>
+      <c r="G41" s="67"/>
+      <c r="H41" s="67"/>
+      <c r="I41" s="67"/>
+      <c r="J41" s="67"/>
+      <c r="K41" s="67"/>
+      <c r="L41" s="67"/>
+      <c r="M41" s="67"/>
+      <c r="N41" s="67"/>
+      <c r="O41" s="67"/>
+      <c r="P41" s="67"/>
+      <c r="Q41" s="67"/>
+      <c r="R41" s="67"/>
+      <c r="S41" s="40"/>
+      <c r="T41" s="40"/>
+      <c r="U41" s="40"/>
+      <c r="V41" s="40"/>
+      <c r="W41" s="40"/>
+      <c r="X41" s="40"/>
+      <c r="Y41" s="40"/>
+      <c r="Z41" s="40"/>
+      <c r="AA41" s="40"/>
+      <c r="AB41" s="40"/>
+      <c r="AC41" s="40"/>
+      <c r="AD41" s="40"/>
+      <c r="AE41" s="40"/>
+      <c r="AF41" s="40"/>
+      <c r="AG41" s="40"/>
+      <c r="AH41" s="40"/>
+      <c r="AI41" s="40"/>
+      <c r="AJ41" s="43"/>
+    </row>
+    <row r="42" spans="1:36" ht="16.8" customHeight="1">
+      <c r="A42" s="161"/>
+      <c r="B42" s="162"/>
+      <c r="C42" s="162"/>
+      <c r="D42" s="162"/>
+      <c r="E42" s="162"/>
+      <c r="F42" s="162"/>
+      <c r="G42" s="162"/>
+      <c r="H42" s="162"/>
+      <c r="I42" s="162"/>
+      <c r="J42" s="162"/>
+      <c r="K42" s="162"/>
+      <c r="L42" s="162"/>
+      <c r="M42" s="162"/>
+      <c r="N42" s="162"/>
+      <c r="O42" s="162"/>
+      <c r="P42" s="162"/>
+      <c r="Q42" s="162"/>
+      <c r="R42" s="162"/>
+      <c r="S42" s="162"/>
+      <c r="T42" s="162"/>
+      <c r="U42" s="162"/>
+      <c r="V42" s="162"/>
+      <c r="W42" s="162"/>
+      <c r="X42" s="162"/>
+      <c r="Y42" s="162"/>
+      <c r="Z42" s="162"/>
+      <c r="AA42" s="162"/>
+      <c r="AB42" s="162"/>
+      <c r="AC42" s="162"/>
+      <c r="AD42" s="162"/>
+      <c r="AE42" s="162"/>
+      <c r="AF42" s="162"/>
+      <c r="AG42" s="162"/>
+      <c r="AH42" s="162"/>
+      <c r="AI42" s="162"/>
+      <c r="AJ42" s="163"/>
+    </row>
+    <row r="43" spans="1:36" ht="16.8" customHeight="1">
+      <c r="A43" s="164"/>
+      <c r="B43" s="165"/>
+      <c r="C43" s="165"/>
+      <c r="D43" s="165"/>
+      <c r="E43" s="165"/>
+      <c r="F43" s="165"/>
+      <c r="G43" s="165"/>
+      <c r="H43" s="165"/>
+      <c r="I43" s="165"/>
+      <c r="J43" s="165"/>
+      <c r="K43" s="165"/>
+      <c r="L43" s="165"/>
+      <c r="M43" s="165"/>
+      <c r="N43" s="165"/>
+      <c r="O43" s="165"/>
+      <c r="P43" s="165"/>
+      <c r="Q43" s="165"/>
+      <c r="R43" s="165"/>
+      <c r="S43" s="165"/>
+      <c r="T43" s="165"/>
+      <c r="U43" s="165"/>
+      <c r="V43" s="165"/>
+      <c r="W43" s="165"/>
+      <c r="X43" s="165"/>
+      <c r="Y43" s="165"/>
+      <c r="Z43" s="165"/>
+      <c r="AA43" s="165"/>
+      <c r="AB43" s="165"/>
+      <c r="AC43" s="165"/>
+      <c r="AD43" s="165"/>
+      <c r="AE43" s="165"/>
+      <c r="AF43" s="165"/>
+      <c r="AG43" s="165"/>
+      <c r="AH43" s="165"/>
+      <c r="AI43" s="165"/>
+      <c r="AJ43" s="166"/>
+    </row>
+    <row r="44" spans="1:36" ht="17.25" customHeight="1">
+      <c r="A44" s="68" t="s">
         <v>18</v>
       </c>
-      <c r="B41" s="93"/>
-      <c r="C41" s="93"/>
-      <c r="D41" s="93"/>
-      <c r="E41" s="93"/>
-      <c r="F41" s="93"/>
-      <c r="G41" s="93"/>
-      <c r="H41" s="93"/>
-      <c r="I41" s="94"/>
-      <c r="J41" s="92" t="s">
+      <c r="B44" s="69"/>
+      <c r="C44" s="69"/>
+      <c r="D44" s="69"/>
+      <c r="E44" s="69"/>
+      <c r="F44" s="69"/>
+      <c r="G44" s="69"/>
+      <c r="H44" s="69"/>
+      <c r="I44" s="70"/>
+      <c r="J44" s="68" t="s">
         <v>19</v>
       </c>
-      <c r="K41" s="93"/>
-      <c r="L41" s="93"/>
-      <c r="M41" s="93"/>
-      <c r="N41" s="93"/>
-      <c r="O41" s="93"/>
-      <c r="P41" s="93"/>
-      <c r="Q41" s="93"/>
-      <c r="R41" s="94"/>
-      <c r="S41" s="92" t="s">
+      <c r="K44" s="69"/>
+      <c r="L44" s="69"/>
+      <c r="M44" s="69"/>
+      <c r="N44" s="69"/>
+      <c r="O44" s="69"/>
+      <c r="P44" s="69"/>
+      <c r="Q44" s="69"/>
+      <c r="R44" s="70"/>
+      <c r="S44" s="68" t="s">
         <v>77</v>
       </c>
-      <c r="T41" s="93"/>
-      <c r="U41" s="93"/>
-      <c r="V41" s="93"/>
-      <c r="W41" s="93"/>
-      <c r="X41" s="93"/>
-      <c r="Y41" s="93"/>
-      <c r="Z41" s="93"/>
-      <c r="AA41" s="94"/>
-      <c r="AB41" s="138" t="s">
+      <c r="T44" s="69"/>
+      <c r="U44" s="69"/>
+      <c r="V44" s="69"/>
+      <c r="W44" s="69"/>
+      <c r="X44" s="69"/>
+      <c r="Y44" s="69"/>
+      <c r="Z44" s="69"/>
+      <c r="AA44" s="70"/>
+      <c r="AB44" s="89" t="s">
         <v>91</v>
       </c>
-      <c r="AC41" s="93"/>
-      <c r="AD41" s="93"/>
-      <c r="AE41" s="93"/>
-      <c r="AF41" s="93"/>
-      <c r="AG41" s="93"/>
-      <c r="AH41" s="93"/>
-      <c r="AI41" s="93"/>
-      <c r="AJ41" s="94"/>
-    </row>
-    <row r="42" spans="1:36" ht="18" customHeight="1">
-      <c r="A42" s="2"/>
-      <c r="B42" s="120" t="s">
-        <v>21</v>
-      </c>
-      <c r="C42" s="120"/>
-      <c r="D42" s="120"/>
-      <c r="E42" s="120"/>
-      <c r="F42" s="120"/>
-      <c r="G42" s="120"/>
-      <c r="H42" s="120"/>
-      <c r="I42" s="121"/>
-      <c r="J42" s="11"/>
-      <c r="K42" s="120" t="s">
-        <v>22</v>
-      </c>
-      <c r="L42" s="120"/>
-      <c r="M42" s="120"/>
-      <c r="N42" s="120"/>
-      <c r="O42" s="120"/>
-      <c r="P42" s="120"/>
-      <c r="Q42" s="120"/>
-      <c r="R42" s="121"/>
-      <c r="S42" s="103" t="s">
-        <v>81</v>
-      </c>
-      <c r="T42" s="104"/>
-      <c r="U42" s="104"/>
-      <c r="V42" s="104"/>
-      <c r="W42" s="76"/>
-      <c r="X42" s="76"/>
-      <c r="Y42" s="76"/>
-      <c r="Z42" s="50"/>
-      <c r="AA42" s="5"/>
-      <c r="AB42" s="122" t="s">
-        <v>82</v>
-      </c>
-      <c r="AC42" s="123"/>
-      <c r="AD42" s="123"/>
-      <c r="AE42" s="123"/>
-      <c r="AF42" s="135"/>
-      <c r="AG42" s="135"/>
-      <c r="AH42" s="135"/>
-      <c r="AI42" s="135"/>
-      <c r="AJ42" s="5"/>
-    </row>
-    <row r="43" spans="1:36" ht="18" customHeight="1">
-      <c r="A43" s="2"/>
-      <c r="B43" s="120" t="s">
-        <v>24</v>
-      </c>
-      <c r="C43" s="120"/>
-      <c r="D43" s="120"/>
-      <c r="E43" s="120"/>
-      <c r="F43" s="120"/>
-      <c r="G43" s="120"/>
-      <c r="H43" s="120"/>
-      <c r="I43" s="121"/>
-      <c r="J43" s="11"/>
-      <c r="K43" s="120" t="s">
-        <v>25</v>
-      </c>
-      <c r="L43" s="120"/>
-      <c r="M43" s="120"/>
-      <c r="N43" s="120"/>
-      <c r="O43" s="120"/>
-      <c r="P43" s="120"/>
-      <c r="Q43" s="120"/>
-      <c r="R43" s="121"/>
-      <c r="S43" s="103" t="s">
-        <v>80</v>
-      </c>
-      <c r="T43" s="104"/>
-      <c r="U43" s="104"/>
-      <c r="V43" s="104"/>
-      <c r="W43" s="166"/>
-      <c r="X43" s="166"/>
-      <c r="Y43" s="166"/>
-      <c r="Z43" s="166"/>
-      <c r="AA43" s="5"/>
-      <c r="AB43" s="103" t="s">
-        <v>81</v>
-      </c>
-      <c r="AC43" s="104"/>
-      <c r="AD43" s="104"/>
-      <c r="AE43" s="104"/>
-      <c r="AF43" s="166"/>
-      <c r="AG43" s="166"/>
-      <c r="AH43" s="166"/>
-      <c r="AI43" s="166"/>
-      <c r="AJ43" s="5"/>
-    </row>
-    <row r="44" spans="1:36" ht="18" customHeight="1">
-      <c r="A44" s="2"/>
-      <c r="B44" s="120" t="s">
-        <v>27</v>
-      </c>
-      <c r="C44" s="120"/>
-      <c r="D44" s="120"/>
-      <c r="E44" s="120"/>
-      <c r="F44" s="120"/>
-      <c r="G44" s="120"/>
-      <c r="H44" s="120"/>
-      <c r="I44" s="121"/>
-      <c r="J44" s="11"/>
-      <c r="K44" s="120" t="s">
-        <v>28</v>
-      </c>
-      <c r="L44" s="120"/>
-      <c r="M44" s="120"/>
-      <c r="N44" s="120"/>
-      <c r="O44" s="120"/>
-      <c r="P44" s="120"/>
-      <c r="Q44" s="120"/>
-      <c r="R44" s="121"/>
-      <c r="S44" s="122" t="s">
-        <v>78</v>
-      </c>
-      <c r="T44" s="123"/>
-      <c r="U44" s="123"/>
-      <c r="V44" s="123"/>
-      <c r="W44" s="123"/>
-      <c r="X44" s="124"/>
-      <c r="Y44" s="124"/>
-      <c r="Z44" s="124"/>
-      <c r="AA44" s="13" t="s">
-        <v>30</v>
-      </c>
-      <c r="AB44" s="103" t="s">
-        <v>80</v>
-      </c>
-      <c r="AC44" s="104"/>
-      <c r="AD44" s="104"/>
-      <c r="AE44" s="104"/>
-      <c r="AF44" s="166"/>
-      <c r="AG44" s="166"/>
-      <c r="AH44" s="166"/>
-      <c r="AI44" s="166"/>
-      <c r="AJ44" s="5"/>
+      <c r="AC44" s="69"/>
+      <c r="AD44" s="69"/>
+      <c r="AE44" s="69"/>
+      <c r="AF44" s="69"/>
+      <c r="AG44" s="69"/>
+      <c r="AH44" s="69"/>
+      <c r="AI44" s="69"/>
+      <c r="AJ44" s="70"/>
     </row>
     <row r="45" spans="1:36" ht="18" customHeight="1">
       <c r="A45" s="2"/>
-      <c r="B45" s="120" t="s">
+      <c r="B45" s="54" t="s">
+        <v>21</v>
+      </c>
+      <c r="C45" s="54"/>
+      <c r="D45" s="54"/>
+      <c r="E45" s="54"/>
+      <c r="F45" s="54"/>
+      <c r="G45" s="54"/>
+      <c r="H45" s="54"/>
+      <c r="I45" s="55"/>
+      <c r="J45" s="10"/>
+      <c r="K45" s="54" t="s">
+        <v>22</v>
+      </c>
+      <c r="L45" s="54"/>
+      <c r="M45" s="54"/>
+      <c r="N45" s="54"/>
+      <c r="O45" s="54"/>
+      <c r="P45" s="54"/>
+      <c r="Q45" s="54"/>
+      <c r="R45" s="55"/>
+      <c r="S45" s="96" t="s">
+        <v>81</v>
+      </c>
+      <c r="T45" s="97"/>
+      <c r="U45" s="97"/>
+      <c r="V45" s="97"/>
+      <c r="W45" s="90"/>
+      <c r="X45" s="90"/>
+      <c r="Y45" s="90"/>
+      <c r="Z45" s="49"/>
+      <c r="AA45" s="4"/>
+      <c r="AB45" s="56" t="s">
+        <v>82</v>
+      </c>
+      <c r="AC45" s="57"/>
+      <c r="AD45" s="57"/>
+      <c r="AE45" s="57"/>
+      <c r="AF45" s="86"/>
+      <c r="AG45" s="86"/>
+      <c r="AH45" s="86"/>
+      <c r="AI45" s="86"/>
+      <c r="AJ45" s="4"/>
+    </row>
+    <row r="46" spans="1:36" ht="18" customHeight="1">
+      <c r="A46" s="2"/>
+      <c r="B46" s="54" t="s">
+        <v>24</v>
+      </c>
+      <c r="C46" s="54"/>
+      <c r="D46" s="54"/>
+      <c r="E46" s="54"/>
+      <c r="F46" s="54"/>
+      <c r="G46" s="54"/>
+      <c r="H46" s="54"/>
+      <c r="I46" s="55"/>
+      <c r="J46" s="10"/>
+      <c r="K46" s="54" t="s">
+        <v>25</v>
+      </c>
+      <c r="L46" s="54"/>
+      <c r="M46" s="54"/>
+      <c r="N46" s="54"/>
+      <c r="O46" s="54"/>
+      <c r="P46" s="54"/>
+      <c r="Q46" s="54"/>
+      <c r="R46" s="55"/>
+      <c r="S46" s="96" t="s">
+        <v>80</v>
+      </c>
+      <c r="T46" s="97"/>
+      <c r="U46" s="97"/>
+      <c r="V46" s="97"/>
+      <c r="W46" s="53"/>
+      <c r="X46" s="53"/>
+      <c r="Y46" s="53"/>
+      <c r="Z46" s="53"/>
+      <c r="AA46" s="4"/>
+      <c r="AB46" s="96" t="s">
+        <v>81</v>
+      </c>
+      <c r="AC46" s="97"/>
+      <c r="AD46" s="97"/>
+      <c r="AE46" s="97"/>
+      <c r="AF46" s="53"/>
+      <c r="AG46" s="53"/>
+      <c r="AH46" s="53"/>
+      <c r="AI46" s="53"/>
+      <c r="AJ46" s="4"/>
+    </row>
+    <row r="47" spans="1:36" ht="18" customHeight="1">
+      <c r="A47" s="2"/>
+      <c r="B47" s="54" t="s">
+        <v>27</v>
+      </c>
+      <c r="C47" s="54"/>
+      <c r="D47" s="54"/>
+      <c r="E47" s="54"/>
+      <c r="F47" s="54"/>
+      <c r="G47" s="54"/>
+      <c r="H47" s="54"/>
+      <c r="I47" s="55"/>
+      <c r="J47" s="10"/>
+      <c r="K47" s="54" t="s">
+        <v>28</v>
+      </c>
+      <c r="L47" s="54"/>
+      <c r="M47" s="54"/>
+      <c r="N47" s="54"/>
+      <c r="O47" s="54"/>
+      <c r="P47" s="54"/>
+      <c r="Q47" s="54"/>
+      <c r="R47" s="55"/>
+      <c r="S47" s="56" t="s">
+        <v>78</v>
+      </c>
+      <c r="T47" s="57"/>
+      <c r="U47" s="57"/>
+      <c r="V47" s="57"/>
+      <c r="W47" s="57"/>
+      <c r="X47" s="78"/>
+      <c r="Y47" s="78"/>
+      <c r="Z47" s="78"/>
+      <c r="AA47" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="AB47" s="96" t="s">
+        <v>80</v>
+      </c>
+      <c r="AC47" s="97"/>
+      <c r="AD47" s="97"/>
+      <c r="AE47" s="97"/>
+      <c r="AF47" s="53"/>
+      <c r="AG47" s="53"/>
+      <c r="AH47" s="53"/>
+      <c r="AI47" s="53"/>
+      <c r="AJ47" s="4"/>
+    </row>
+    <row r="48" spans="1:36" ht="18" customHeight="1">
+      <c r="A48" s="2"/>
+      <c r="B48" s="54" t="s">
         <v>87</v>
       </c>
-      <c r="C45" s="120"/>
-      <c r="D45" s="120"/>
-      <c r="E45" s="120"/>
-      <c r="F45" s="120"/>
-      <c r="G45" s="120"/>
-      <c r="H45" s="120"/>
-      <c r="I45" s="121"/>
-      <c r="J45" s="11"/>
-      <c r="K45" s="120" t="s">
+      <c r="C48" s="54"/>
+      <c r="D48" s="54"/>
+      <c r="E48" s="54"/>
+      <c r="F48" s="54"/>
+      <c r="G48" s="54"/>
+      <c r="H48" s="54"/>
+      <c r="I48" s="55"/>
+      <c r="J48" s="10"/>
+      <c r="K48" s="54" t="s">
         <v>31</v>
       </c>
-      <c r="L45" s="120"/>
-      <c r="M45" s="120"/>
-      <c r="N45" s="120"/>
-      <c r="O45" s="120"/>
-      <c r="P45" s="120"/>
-      <c r="Q45" s="120"/>
-      <c r="R45" s="121"/>
-      <c r="S45" s="126" t="s">
+      <c r="L48" s="54"/>
+      <c r="M48" s="54"/>
+      <c r="N48" s="54"/>
+      <c r="O48" s="54"/>
+      <c r="P48" s="54"/>
+      <c r="Q48" s="54"/>
+      <c r="R48" s="55"/>
+      <c r="S48" s="98" t="s">
         <v>79</v>
       </c>
-      <c r="T45" s="127"/>
-      <c r="U45" s="127"/>
-      <c r="V45" s="127"/>
-      <c r="W45" s="127"/>
-      <c r="X45" s="149"/>
-      <c r="Y45" s="149"/>
-      <c r="Z45" s="149"/>
-      <c r="AA45" s="34" t="s">
+      <c r="T48" s="99"/>
+      <c r="U48" s="99"/>
+      <c r="V48" s="99"/>
+      <c r="W48" s="99"/>
+      <c r="X48" s="58"/>
+      <c r="Y48" s="58"/>
+      <c r="Z48" s="58"/>
+      <c r="AA48" s="33" t="s">
         <v>30</v>
       </c>
-      <c r="AB45" s="103" t="s">
+      <c r="AB48" s="96" t="s">
         <v>83</v>
       </c>
-      <c r="AC45" s="104"/>
-      <c r="AD45" s="104"/>
-      <c r="AE45" s="104"/>
-      <c r="AF45" s="129"/>
-      <c r="AG45" s="129"/>
-      <c r="AH45" s="129"/>
-      <c r="AI45" s="129"/>
-      <c r="AJ45" s="5"/>
+      <c r="AC48" s="97"/>
+      <c r="AD48" s="97"/>
+      <c r="AE48" s="97"/>
+      <c r="AF48" s="86"/>
+      <c r="AG48" s="86"/>
+      <c r="AH48" s="86"/>
+      <c r="AI48" s="86"/>
+      <c r="AJ48" s="4"/>
     </row>
-    <row r="46" spans="1:36" ht="18" customHeight="1">
-      <c r="A46" s="35"/>
-      <c r="B46" s="120" t="s">
+    <row r="49" spans="1:36" ht="18" customHeight="1">
+      <c r="A49" s="34"/>
+      <c r="B49" s="54" t="s">
         <v>33</v>
       </c>
-      <c r="C46" s="120"/>
-      <c r="D46" s="120"/>
-      <c r="E46" s="120"/>
-      <c r="F46" s="120"/>
-      <c r="G46" s="120"/>
-      <c r="H46" s="120"/>
-      <c r="I46" s="121"/>
-      <c r="J46" s="11"/>
-      <c r="K46" s="120" t="s">
+      <c r="C49" s="54"/>
+      <c r="D49" s="54"/>
+      <c r="E49" s="54"/>
+      <c r="F49" s="54"/>
+      <c r="G49" s="54"/>
+      <c r="H49" s="54"/>
+      <c r="I49" s="55"/>
+      <c r="J49" s="10"/>
+      <c r="K49" s="54" t="s">
         <v>34</v>
       </c>
-      <c r="L46" s="120"/>
-      <c r="M46" s="120"/>
-      <c r="N46" s="120"/>
-      <c r="O46" s="120"/>
-      <c r="P46" s="120"/>
-      <c r="Q46" s="120"/>
-      <c r="R46" s="121"/>
-      <c r="S46" s="163" t="s">
+      <c r="L49" s="54"/>
+      <c r="M49" s="54"/>
+      <c r="N49" s="54"/>
+      <c r="O49" s="54"/>
+      <c r="P49" s="54"/>
+      <c r="Q49" s="54"/>
+      <c r="R49" s="55"/>
+      <c r="S49" s="75" t="s">
         <v>20</v>
       </c>
-      <c r="T46" s="164"/>
-      <c r="U46" s="164"/>
-      <c r="V46" s="164"/>
-      <c r="W46" s="164"/>
-      <c r="X46" s="164"/>
-      <c r="Y46" s="164"/>
-      <c r="Z46" s="164"/>
-      <c r="AA46" s="165"/>
-      <c r="AB46" s="122" t="s">
+      <c r="T49" s="76"/>
+      <c r="U49" s="76"/>
+      <c r="V49" s="76"/>
+      <c r="W49" s="76"/>
+      <c r="X49" s="76"/>
+      <c r="Y49" s="76"/>
+      <c r="Z49" s="76"/>
+      <c r="AA49" s="77"/>
+      <c r="AB49" s="56" t="s">
         <v>78</v>
       </c>
-      <c r="AC46" s="123"/>
-      <c r="AD46" s="123"/>
-      <c r="AE46" s="123"/>
-      <c r="AF46" s="123"/>
-      <c r="AG46" s="124"/>
-      <c r="AH46" s="124"/>
-      <c r="AI46" s="124"/>
-      <c r="AJ46" s="13" t="s">
+      <c r="AC49" s="57"/>
+      <c r="AD49" s="57"/>
+      <c r="AE49" s="57"/>
+      <c r="AF49" s="57"/>
+      <c r="AG49" s="78"/>
+      <c r="AH49" s="78"/>
+      <c r="AI49" s="78"/>
+      <c r="AJ49" s="12" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="47" spans="1:36" ht="18" customHeight="1">
-      <c r="A47" s="11"/>
-      <c r="B47" s="120" t="s">
+    <row r="50" spans="1:36" ht="18" customHeight="1">
+      <c r="A50" s="10"/>
+      <c r="B50" s="54" t="s">
         <v>74</v>
       </c>
-      <c r="C47" s="120"/>
-      <c r="D47" s="120"/>
-      <c r="E47" s="120"/>
-      <c r="F47" s="120"/>
-      <c r="G47" s="120"/>
-      <c r="H47" s="120"/>
-      <c r="I47" s="121"/>
-      <c r="J47" s="11"/>
-      <c r="K47" s="120" t="s">
+      <c r="C50" s="54"/>
+      <c r="D50" s="54"/>
+      <c r="E50" s="54"/>
+      <c r="F50" s="54"/>
+      <c r="G50" s="54"/>
+      <c r="H50" s="54"/>
+      <c r="I50" s="55"/>
+      <c r="J50" s="10"/>
+      <c r="K50" s="54" t="s">
         <v>37</v>
       </c>
-      <c r="L47" s="120"/>
-      <c r="M47" s="120"/>
-      <c r="N47" s="120"/>
-      <c r="O47" s="120"/>
-      <c r="P47" s="120"/>
-      <c r="Q47" s="120"/>
-      <c r="R47" s="121"/>
-      <c r="S47" s="11"/>
-      <c r="T47" s="120" t="s">
+      <c r="L50" s="54"/>
+      <c r="M50" s="54"/>
+      <c r="N50" s="54"/>
+      <c r="O50" s="54"/>
+      <c r="P50" s="54"/>
+      <c r="Q50" s="54"/>
+      <c r="R50" s="55"/>
+      <c r="S50" s="10"/>
+      <c r="T50" s="54" t="s">
         <v>23</v>
       </c>
-      <c r="U47" s="120"/>
-      <c r="V47" s="120"/>
-      <c r="W47" s="120"/>
-      <c r="X47" s="120"/>
-      <c r="Y47" s="120"/>
-      <c r="Z47" s="120"/>
-      <c r="AA47" s="121"/>
-      <c r="AB47" s="126" t="s">
+      <c r="U50" s="54"/>
+      <c r="V50" s="54"/>
+      <c r="W50" s="54"/>
+      <c r="X50" s="54"/>
+      <c r="Y50" s="54"/>
+      <c r="Z50" s="54"/>
+      <c r="AA50" s="55"/>
+      <c r="AB50" s="98" t="s">
         <v>79</v>
       </c>
-      <c r="AC47" s="127"/>
-      <c r="AD47" s="127"/>
-      <c r="AE47" s="127"/>
-      <c r="AF47" s="127"/>
-      <c r="AG47" s="149"/>
-      <c r="AH47" s="149"/>
-      <c r="AI47" s="149"/>
-      <c r="AJ47" s="34" t="s">
+      <c r="AC50" s="99"/>
+      <c r="AD50" s="99"/>
+      <c r="AE50" s="99"/>
+      <c r="AF50" s="99"/>
+      <c r="AG50" s="58"/>
+      <c r="AH50" s="58"/>
+      <c r="AI50" s="58"/>
+      <c r="AJ50" s="33" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="48" spans="1:36" ht="18" customHeight="1">
-      <c r="A48" s="11"/>
-      <c r="B48" s="120" t="s">
+    <row r="51" spans="1:36" ht="18" customHeight="1">
+      <c r="A51" s="10"/>
+      <c r="B51" s="54" t="s">
         <v>75</v>
       </c>
-      <c r="C48" s="120"/>
-      <c r="D48" s="120"/>
-      <c r="E48" s="120"/>
-      <c r="F48" s="120"/>
-      <c r="G48" s="120"/>
-      <c r="H48" s="120"/>
-      <c r="I48" s="121"/>
-      <c r="J48" s="11"/>
-      <c r="K48" s="120" t="s">
+      <c r="C51" s="54"/>
+      <c r="D51" s="54"/>
+      <c r="E51" s="54"/>
+      <c r="F51" s="54"/>
+      <c r="G51" s="54"/>
+      <c r="H51" s="54"/>
+      <c r="I51" s="55"/>
+      <c r="J51" s="10"/>
+      <c r="K51" s="54" t="s">
         <v>39</v>
       </c>
-      <c r="L48" s="120"/>
-      <c r="M48" s="120"/>
-      <c r="N48" s="120"/>
-      <c r="O48" s="120"/>
-      <c r="P48" s="120"/>
-      <c r="Q48" s="120"/>
-      <c r="R48" s="121"/>
-      <c r="S48" s="11"/>
-      <c r="T48" s="120" t="s">
+      <c r="L51" s="54"/>
+      <c r="M51" s="54"/>
+      <c r="N51" s="54"/>
+      <c r="O51" s="54"/>
+      <c r="P51" s="54"/>
+      <c r="Q51" s="54"/>
+      <c r="R51" s="55"/>
+      <c r="S51" s="10"/>
+      <c r="T51" s="54" t="s">
         <v>26</v>
       </c>
-      <c r="U48" s="120"/>
-      <c r="V48" s="120"/>
-      <c r="W48" s="120"/>
-      <c r="X48" s="120"/>
-      <c r="Y48" s="120"/>
-      <c r="Z48" s="120"/>
-      <c r="AA48" s="121"/>
-      <c r="AB48" s="130" t="s">
+      <c r="U51" s="54"/>
+      <c r="V51" s="54"/>
+      <c r="W51" s="54"/>
+      <c r="X51" s="54"/>
+      <c r="Y51" s="54"/>
+      <c r="Z51" s="54"/>
+      <c r="AA51" s="55"/>
+      <c r="AB51" s="102" t="s">
         <v>38</v>
       </c>
-      <c r="AC48" s="131"/>
-      <c r="AD48" s="131"/>
-      <c r="AE48" s="131"/>
-      <c r="AF48" s="131"/>
-      <c r="AG48" s="131"/>
-      <c r="AH48" s="131"/>
-      <c r="AI48" s="131"/>
-      <c r="AJ48" s="132"/>
+      <c r="AC51" s="103"/>
+      <c r="AD51" s="103"/>
+      <c r="AE51" s="103"/>
+      <c r="AF51" s="103"/>
+      <c r="AG51" s="103"/>
+      <c r="AH51" s="103"/>
+      <c r="AI51" s="103"/>
+      <c r="AJ51" s="104"/>
     </row>
-    <row r="49" spans="1:36" ht="18" customHeight="1">
-      <c r="A49" s="11"/>
-      <c r="B49" s="120" t="s">
+    <row r="52" spans="1:36" ht="18" customHeight="1">
+      <c r="A52" s="10"/>
+      <c r="B52" s="54" t="s">
         <v>40</v>
       </c>
-      <c r="C49" s="120"/>
-      <c r="D49" s="120"/>
-      <c r="E49" s="120"/>
-      <c r="F49" s="120"/>
-      <c r="G49" s="120"/>
-      <c r="H49" s="120"/>
-      <c r="I49" s="121"/>
-      <c r="J49" s="11"/>
-      <c r="K49" s="120" t="s">
+      <c r="C52" s="54"/>
+      <c r="D52" s="54"/>
+      <c r="E52" s="54"/>
+      <c r="F52" s="54"/>
+      <c r="G52" s="54"/>
+      <c r="H52" s="54"/>
+      <c r="I52" s="55"/>
+      <c r="J52" s="10"/>
+      <c r="K52" s="54" t="s">
         <v>41</v>
       </c>
-      <c r="L49" s="120"/>
-      <c r="M49" s="120"/>
-      <c r="N49" s="120"/>
-      <c r="O49" s="120"/>
-      <c r="P49" s="120"/>
-      <c r="Q49" s="120"/>
-      <c r="R49" s="121"/>
-      <c r="S49" s="11"/>
-      <c r="T49" s="120" t="s">
+      <c r="L52" s="54"/>
+      <c r="M52" s="54"/>
+      <c r="N52" s="54"/>
+      <c r="O52" s="54"/>
+      <c r="P52" s="54"/>
+      <c r="Q52" s="54"/>
+      <c r="R52" s="55"/>
+      <c r="S52" s="10"/>
+      <c r="T52" s="54" t="s">
         <v>29</v>
       </c>
-      <c r="U49" s="120"/>
-      <c r="V49" s="120"/>
-      <c r="W49" s="124"/>
-      <c r="X49" s="124"/>
-      <c r="Y49" s="124"/>
-      <c r="Z49" s="3" t="s">
+      <c r="U52" s="54"/>
+      <c r="V52" s="54"/>
+      <c r="W52" s="78"/>
+      <c r="X52" s="78"/>
+      <c r="Y52" s="78"/>
+      <c r="Z52" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="AA49" s="5"/>
-      <c r="AB49" s="11"/>
-      <c r="AC49" s="133" t="s">
+      <c r="AA52" s="4"/>
+      <c r="AB52" s="10"/>
+      <c r="AC52" s="105" t="s">
         <v>76</v>
       </c>
-      <c r="AD49" s="133"/>
-      <c r="AE49" s="133"/>
-      <c r="AF49" s="133"/>
-      <c r="AG49" s="133"/>
-      <c r="AH49" s="133"/>
-      <c r="AI49" s="133"/>
-      <c r="AJ49" s="134"/>
+      <c r="AD52" s="105"/>
+      <c r="AE52" s="105"/>
+      <c r="AF52" s="105"/>
+      <c r="AG52" s="105"/>
+      <c r="AH52" s="105"/>
+      <c r="AI52" s="105"/>
+      <c r="AJ52" s="106"/>
     </row>
-    <row r="50" spans="1:36" ht="18" customHeight="1">
-      <c r="A50" s="11"/>
-      <c r="B50" s="120" t="s">
+    <row r="53" spans="1:36" ht="18" customHeight="1">
+      <c r="A53" s="10"/>
+      <c r="B53" s="54" t="s">
         <v>43</v>
       </c>
-      <c r="C50" s="120"/>
-      <c r="D50" s="125"/>
-      <c r="E50" s="125"/>
-      <c r="F50" s="125"/>
-      <c r="G50" s="125"/>
-      <c r="H50" s="125"/>
-      <c r="I50" s="5"/>
-      <c r="J50" s="11"/>
-      <c r="K50" s="120" t="s">
+      <c r="C53" s="54"/>
+      <c r="D53" s="107"/>
+      <c r="E53" s="107"/>
+      <c r="F53" s="107"/>
+      <c r="G53" s="107"/>
+      <c r="H53" s="107"/>
+      <c r="I53" s="4"/>
+      <c r="J53" s="10"/>
+      <c r="K53" s="54" t="s">
         <v>44</v>
       </c>
-      <c r="L50" s="120"/>
-      <c r="M50" s="120"/>
-      <c r="N50" s="120"/>
-      <c r="O50" s="120"/>
-      <c r="P50" s="120"/>
-      <c r="Q50" s="120"/>
-      <c r="R50" s="121"/>
-      <c r="S50" s="11"/>
-      <c r="T50" s="120" t="s">
-        <v>32</v>
-      </c>
-      <c r="U50" s="120"/>
-      <c r="V50" s="120"/>
-      <c r="W50" s="124"/>
-      <c r="X50" s="124"/>
-      <c r="Y50" s="124"/>
-      <c r="Z50" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="AA50" s="5"/>
-      <c r="AB50" s="11"/>
-      <c r="AC50" s="120" t="s">
-        <v>42</v>
-      </c>
-      <c r="AD50" s="120"/>
-      <c r="AE50" s="120"/>
-      <c r="AF50" s="120"/>
-      <c r="AG50" s="120"/>
-      <c r="AH50" s="120"/>
-      <c r="AI50" s="120"/>
-      <c r="AJ50" s="121"/>
-    </row>
-    <row r="51" spans="1:36" ht="18" customHeight="1">
-      <c r="A51" s="14"/>
-      <c r="B51" s="8"/>
-      <c r="C51" s="8"/>
-      <c r="D51" s="146"/>
-      <c r="E51" s="146"/>
-      <c r="F51" s="146"/>
-      <c r="G51" s="146"/>
-      <c r="H51" s="146"/>
-      <c r="I51" s="9"/>
-      <c r="J51" s="126"/>
-      <c r="K51" s="127"/>
-      <c r="L51" s="127"/>
-      <c r="M51" s="127"/>
-      <c r="N51" s="127"/>
-      <c r="O51" s="127"/>
-      <c r="P51" s="127"/>
-      <c r="Q51" s="127"/>
-      <c r="R51" s="128"/>
-      <c r="S51" s="14"/>
-      <c r="T51" s="147" t="s">
-        <v>35</v>
-      </c>
-      <c r="U51" s="147"/>
-      <c r="V51" s="147"/>
-      <c r="W51" s="149"/>
-      <c r="X51" s="149"/>
-      <c r="Y51" s="149"/>
-      <c r="Z51" s="7" t="s">
-        <v>36</v>
-      </c>
-      <c r="AA51" s="9"/>
-      <c r="AB51" s="14"/>
-      <c r="AC51" s="147" t="s">
-        <v>45</v>
-      </c>
-      <c r="AD51" s="147"/>
-      <c r="AE51" s="147"/>
-      <c r="AF51" s="84"/>
-      <c r="AG51" s="84"/>
-      <c r="AH51" s="84"/>
-      <c r="AI51" s="8"/>
-      <c r="AJ51" s="9"/>
-    </row>
-    <row r="52" spans="1:36" ht="18" customHeight="1">
-      <c r="A52" s="152" t="s">
-        <v>46</v>
-      </c>
-      <c r="B52" s="152"/>
-      <c r="C52" s="152"/>
-      <c r="D52" s="152"/>
-      <c r="E52" s="152"/>
-      <c r="F52" s="152"/>
-      <c r="G52" s="152"/>
-      <c r="H52" s="152"/>
-      <c r="I52" s="152"/>
-      <c r="J52" s="152"/>
-      <c r="K52" s="152"/>
-      <c r="L52" s="152"/>
-      <c r="M52" s="152"/>
-      <c r="N52" s="145"/>
-      <c r="O52" s="145"/>
-      <c r="P52" s="145"/>
-      <c r="Q52" s="145"/>
-      <c r="R52" s="145"/>
-      <c r="S52" s="145"/>
-      <c r="T52" s="145"/>
-      <c r="U52" s="145"/>
-      <c r="V52" s="145"/>
-      <c r="W52" s="145"/>
-      <c r="X52" s="145"/>
-      <c r="Y52" s="145"/>
-      <c r="Z52" s="145"/>
-      <c r="AA52" s="145"/>
-      <c r="AB52" s="145"/>
-      <c r="AC52" s="145"/>
-      <c r="AD52" s="145"/>
-      <c r="AE52" s="145"/>
-      <c r="AF52" s="145"/>
-      <c r="AG52" s="145"/>
-      <c r="AH52" s="145"/>
-      <c r="AI52" s="145"/>
-      <c r="AJ52" s="145"/>
-    </row>
-    <row r="53" spans="1:36" ht="18" customHeight="1">
-      <c r="A53" s="151"/>
-      <c r="B53" s="54"/>
-      <c r="C53" s="54"/>
-      <c r="D53" s="54"/>
-      <c r="E53" s="54"/>
-      <c r="F53" s="54"/>
-      <c r="G53" s="54"/>
-      <c r="H53" s="54"/>
-      <c r="I53" s="54"/>
-      <c r="J53" s="54"/>
-      <c r="K53" s="54"/>
       <c r="L53" s="54"/>
+      <c r="M53" s="54"/>
       <c r="N53" s="54"/>
       <c r="O53" s="54"/>
       <c r="P53" s="54"/>
       <c r="Q53" s="54"/>
-      <c r="R53" s="54"/>
-      <c r="S53" s="54"/>
-      <c r="T53" s="54"/>
+      <c r="R53" s="55"/>
+      <c r="S53" s="10"/>
+      <c r="T53" s="54" t="s">
+        <v>32</v>
+      </c>
       <c r="U53" s="54"/>
       <c r="V53" s="54"/>
-      <c r="W53" s="54"/>
-      <c r="X53" s="54"/>
-      <c r="Y53" s="150"/>
-      <c r="Z53" s="150"/>
-      <c r="AA53" s="150"/>
-      <c r="AB53" s="148" t="s">
+      <c r="W53" s="78"/>
+      <c r="X53" s="78"/>
+      <c r="Y53" s="78"/>
+      <c r="Z53" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="AA53" s="4"/>
+      <c r="AB53" s="10"/>
+      <c r="AC53" s="54" t="s">
+        <v>42</v>
+      </c>
+      <c r="AD53" s="54"/>
+      <c r="AE53" s="54"/>
+      <c r="AF53" s="54"/>
+      <c r="AG53" s="54"/>
+      <c r="AH53" s="54"/>
+      <c r="AI53" s="54"/>
+      <c r="AJ53" s="55"/>
+    </row>
+    <row r="54" spans="1:36" ht="18" customHeight="1">
+      <c r="A54" s="13"/>
+      <c r="B54" s="7"/>
+      <c r="C54" s="7"/>
+      <c r="D54" s="83"/>
+      <c r="E54" s="83"/>
+      <c r="F54" s="83"/>
+      <c r="G54" s="83"/>
+      <c r="H54" s="83"/>
+      <c r="I54" s="8"/>
+      <c r="J54" s="98"/>
+      <c r="K54" s="99"/>
+      <c r="L54" s="99"/>
+      <c r="M54" s="99"/>
+      <c r="N54" s="99"/>
+      <c r="O54" s="99"/>
+      <c r="P54" s="99"/>
+      <c r="Q54" s="99"/>
+      <c r="R54" s="100"/>
+      <c r="S54" s="13"/>
+      <c r="T54" s="79" t="s">
+        <v>35</v>
+      </c>
+      <c r="U54" s="79"/>
+      <c r="V54" s="79"/>
+      <c r="W54" s="58"/>
+      <c r="X54" s="58"/>
+      <c r="Y54" s="58"/>
+      <c r="Z54" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="AA54" s="8"/>
+      <c r="AB54" s="13"/>
+      <c r="AC54" s="79" t="s">
+        <v>45</v>
+      </c>
+      <c r="AD54" s="79"/>
+      <c r="AE54" s="79"/>
+      <c r="AF54" s="101"/>
+      <c r="AG54" s="101"/>
+      <c r="AH54" s="101"/>
+      <c r="AI54" s="7"/>
+      <c r="AJ54" s="8"/>
+    </row>
+    <row r="55" spans="1:36" ht="18" customHeight="1">
+      <c r="A55" s="81" t="s">
+        <v>46</v>
+      </c>
+      <c r="B55" s="81"/>
+      <c r="C55" s="81"/>
+      <c r="D55" s="81"/>
+      <c r="E55" s="81"/>
+      <c r="F55" s="81"/>
+      <c r="G55" s="81"/>
+      <c r="H55" s="81"/>
+      <c r="I55" s="81"/>
+      <c r="J55" s="81"/>
+      <c r="K55" s="81"/>
+      <c r="L55" s="81"/>
+      <c r="M55" s="81"/>
+      <c r="N55" s="82"/>
+      <c r="O55" s="82"/>
+      <c r="P55" s="82"/>
+      <c r="Q55" s="82"/>
+      <c r="R55" s="82"/>
+      <c r="S55" s="82"/>
+      <c r="T55" s="82"/>
+      <c r="U55" s="82"/>
+      <c r="V55" s="82"/>
+      <c r="W55" s="82"/>
+      <c r="X55" s="82"/>
+      <c r="Y55" s="82"/>
+      <c r="Z55" s="82"/>
+      <c r="AA55" s="82"/>
+      <c r="AB55" s="82"/>
+      <c r="AC55" s="82"/>
+      <c r="AD55" s="82"/>
+      <c r="AE55" s="82"/>
+      <c r="AF55" s="82"/>
+      <c r="AG55" s="82"/>
+      <c r="AH55" s="82"/>
+      <c r="AI55" s="82"/>
+      <c r="AJ55" s="82"/>
+    </row>
+    <row r="56" spans="1:36" ht="18" customHeight="1">
+      <c r="A56" s="72"/>
+      <c r="B56" s="80"/>
+      <c r="C56" s="80"/>
+      <c r="D56" s="80"/>
+      <c r="E56" s="80"/>
+      <c r="F56" s="80"/>
+      <c r="G56" s="80"/>
+      <c r="H56" s="80"/>
+      <c r="I56" s="80"/>
+      <c r="J56" s="80"/>
+      <c r="K56" s="80"/>
+      <c r="L56" s="80"/>
+      <c r="N56" s="80"/>
+      <c r="O56" s="80"/>
+      <c r="P56" s="80"/>
+      <c r="Q56" s="80"/>
+      <c r="R56" s="80"/>
+      <c r="S56" s="80"/>
+      <c r="T56" s="80"/>
+      <c r="U56" s="80"/>
+      <c r="V56" s="80"/>
+      <c r="W56" s="80"/>
+      <c r="X56" s="80"/>
+      <c r="Y56" s="72"/>
+      <c r="Z56" s="72"/>
+      <c r="AA56" s="72"/>
+      <c r="AB56" s="84" t="s">
         <v>93</v>
       </c>
-      <c r="AC53" s="83"/>
-      <c r="AD53" s="83"/>
-      <c r="AE53" s="83"/>
-      <c r="AF53" s="83"/>
-      <c r="AG53" s="83"/>
-      <c r="AH53" s="83"/>
-      <c r="AI53" s="83"/>
-      <c r="AJ53" s="83"/>
+      <c r="AC56" s="85"/>
+      <c r="AD56" s="85"/>
+      <c r="AE56" s="85"/>
+      <c r="AF56" s="85"/>
+      <c r="AG56" s="85"/>
+      <c r="AH56" s="85"/>
+      <c r="AI56" s="85"/>
+      <c r="AJ56" s="85"/>
     </row>
-    <row r="54" spans="1:36" ht="18" customHeight="1">
-      <c r="A54" s="151"/>
-      <c r="B54" s="54"/>
-      <c r="C54" s="54"/>
-      <c r="D54" s="54"/>
-      <c r="E54" s="54"/>
-      <c r="F54" s="54"/>
-      <c r="G54" s="54"/>
-      <c r="H54" s="54"/>
-      <c r="I54" s="54"/>
-      <c r="J54" s="54"/>
-      <c r="K54" s="54"/>
-      <c r="L54" s="54"/>
-      <c r="N54" s="54"/>
-      <c r="O54" s="54"/>
-      <c r="P54" s="54"/>
-      <c r="Q54" s="54"/>
-      <c r="R54" s="54"/>
-      <c r="S54" s="54"/>
-      <c r="T54" s="54"/>
-      <c r="U54" s="54"/>
-      <c r="V54" s="54"/>
-      <c r="W54" s="54"/>
-      <c r="X54" s="54"/>
-      <c r="Y54" s="150"/>
-      <c r="Z54" s="150"/>
-      <c r="AA54" s="150"/>
-      <c r="AB54" s="162" t="s">
+    <row r="57" spans="1:36" ht="18" customHeight="1">
+      <c r="A57" s="72"/>
+      <c r="B57" s="80"/>
+      <c r="C57" s="80"/>
+      <c r="D57" s="80"/>
+      <c r="E57" s="80"/>
+      <c r="F57" s="80"/>
+      <c r="G57" s="80"/>
+      <c r="H57" s="80"/>
+      <c r="I57" s="80"/>
+      <c r="J57" s="80"/>
+      <c r="K57" s="80"/>
+      <c r="L57" s="80"/>
+      <c r="N57" s="80"/>
+      <c r="O57" s="80"/>
+      <c r="P57" s="80"/>
+      <c r="Q57" s="80"/>
+      <c r="R57" s="80"/>
+      <c r="S57" s="80"/>
+      <c r="T57" s="80"/>
+      <c r="U57" s="80"/>
+      <c r="V57" s="80"/>
+      <c r="W57" s="80"/>
+      <c r="X57" s="80"/>
+      <c r="Y57" s="72"/>
+      <c r="Z57" s="72"/>
+      <c r="AA57" s="72"/>
+      <c r="AB57" s="74" t="s">
         <v>47</v>
       </c>
-      <c r="AC54" s="162"/>
-      <c r="AD54" s="162"/>
-      <c r="AE54" s="162"/>
-      <c r="AF54" s="162"/>
-      <c r="AG54" s="162"/>
-      <c r="AH54" s="162"/>
-      <c r="AI54" s="162"/>
-      <c r="AJ54" s="162"/>
-    </row>
-    <row r="55" spans="1:36" ht="18" customHeight="1">
-      <c r="A55" s="151"/>
-      <c r="B55" s="54"/>
-      <c r="C55" s="54"/>
-      <c r="D55" s="54"/>
-      <c r="E55" s="54"/>
-      <c r="F55" s="54"/>
-      <c r="G55" s="54"/>
-      <c r="H55" s="54"/>
-      <c r="I55" s="54"/>
-      <c r="J55" s="54"/>
-      <c r="K55" s="54"/>
-      <c r="L55" s="54"/>
-      <c r="N55" s="54"/>
-      <c r="O55" s="54"/>
-      <c r="P55" s="54"/>
-      <c r="Q55" s="54"/>
-      <c r="R55" s="54"/>
-      <c r="S55" s="54"/>
-      <c r="T55" s="54"/>
-      <c r="U55" s="54"/>
-      <c r="V55" s="54"/>
-      <c r="W55" s="54"/>
-      <c r="X55" s="54"/>
-      <c r="Y55" s="150"/>
-      <c r="Z55" s="150"/>
-      <c r="AA55" s="150"/>
-      <c r="AB55" s="151"/>
-      <c r="AC55" s="151"/>
-      <c r="AD55" s="151"/>
-      <c r="AE55" s="151"/>
-      <c r="AF55" s="151"/>
-      <c r="AG55" s="151"/>
-      <c r="AH55" s="151"/>
-      <c r="AI55" s="151"/>
-      <c r="AJ55" s="151"/>
-    </row>
-    <row r="56" spans="1:36" ht="18" customHeight="1">
-      <c r="A56" s="52"/>
-      <c r="B56" s="54"/>
-      <c r="C56" s="54"/>
-      <c r="D56" s="54"/>
-      <c r="E56" s="54"/>
-      <c r="F56" s="54"/>
-      <c r="G56" s="54"/>
-      <c r="H56" s="54"/>
-      <c r="I56" s="54"/>
-      <c r="J56" s="54"/>
-      <c r="K56" s="54"/>
-      <c r="L56" s="54"/>
-      <c r="N56" s="54"/>
-      <c r="O56" s="54"/>
-      <c r="P56" s="54"/>
-      <c r="Q56" s="54"/>
-      <c r="R56" s="54"/>
-      <c r="S56" s="54"/>
-      <c r="T56" s="54"/>
-      <c r="U56" s="54"/>
-      <c r="V56" s="54"/>
-      <c r="W56" s="54"/>
-      <c r="X56" s="54"/>
-      <c r="Y56" s="150"/>
-      <c r="Z56" s="150"/>
-      <c r="AA56" s="150"/>
-      <c r="AB56" s="151"/>
-      <c r="AC56" s="151"/>
-      <c r="AD56" s="151"/>
-      <c r="AE56" s="151"/>
-      <c r="AF56" s="151"/>
-      <c r="AG56" s="151"/>
-      <c r="AH56" s="151"/>
-      <c r="AI56" s="151"/>
-      <c r="AJ56" s="151"/>
-    </row>
-    <row r="57" spans="1:36" ht="18" customHeight="1">
-      <c r="A57" s="52"/>
-      <c r="B57" s="53"/>
-      <c r="C57" s="53"/>
-      <c r="D57" s="53"/>
-      <c r="E57" s="53"/>
-      <c r="F57" s="53"/>
-      <c r="G57" s="53"/>
-      <c r="H57" s="53"/>
-      <c r="I57" s="53"/>
-      <c r="J57" s="53"/>
-      <c r="K57" s="53"/>
-      <c r="L57" s="53"/>
-      <c r="N57" s="53"/>
-      <c r="O57" s="53"/>
-      <c r="P57" s="53"/>
-      <c r="Q57" s="53"/>
-      <c r="R57" s="53"/>
-      <c r="S57" s="53"/>
-      <c r="T57" s="53"/>
-      <c r="U57" s="53"/>
-      <c r="V57" s="53"/>
-      <c r="W57" s="53"/>
-      <c r="X57" s="53"/>
-      <c r="Y57" s="150"/>
-      <c r="Z57" s="150"/>
-      <c r="AA57" s="150"/>
-      <c r="AB57" s="151"/>
-      <c r="AC57" s="151"/>
-      <c r="AD57" s="151"/>
-      <c r="AE57" s="151"/>
-      <c r="AF57" s="151"/>
-      <c r="AG57" s="151"/>
-      <c r="AH57" s="151"/>
-      <c r="AI57" s="151"/>
-      <c r="AJ57" s="151"/>
+      <c r="AC57" s="74"/>
+      <c r="AD57" s="74"/>
+      <c r="AE57" s="74"/>
+      <c r="AF57" s="74"/>
+      <c r="AG57" s="74"/>
+      <c r="AH57" s="74"/>
+      <c r="AI57" s="74"/>
+      <c r="AJ57" s="74"/>
     </row>
     <row r="58" spans="1:36" ht="18" customHeight="1">
-      <c r="A58" s="150"/>
-      <c r="B58" s="150"/>
-      <c r="C58" s="150"/>
-      <c r="D58" s="150"/>
-      <c r="E58" s="150"/>
-      <c r="F58" s="150"/>
-      <c r="G58" s="150"/>
-      <c r="H58" s="150"/>
-      <c r="I58" s="150"/>
-      <c r="J58" s="150"/>
-      <c r="K58" s="150"/>
-      <c r="L58" s="150"/>
-      <c r="M58" s="150"/>
-      <c r="N58" s="150"/>
-      <c r="O58" s="150"/>
-      <c r="P58" s="150"/>
-      <c r="Q58" s="150"/>
-      <c r="R58" s="150"/>
-      <c r="S58" s="150"/>
-      <c r="T58" s="150"/>
-      <c r="U58" s="150"/>
-      <c r="V58" s="150"/>
-      <c r="W58" s="150"/>
-      <c r="X58" s="150"/>
-      <c r="Y58" s="150"/>
-      <c r="Z58" s="150"/>
-      <c r="AA58" s="150"/>
-      <c r="AB58" s="63"/>
-      <c r="AC58" s="63"/>
-      <c r="AD58" s="63"/>
-      <c r="AE58" s="63"/>
-      <c r="AF58" s="63"/>
-      <c r="AG58" s="63"/>
-      <c r="AH58" s="63"/>
-      <c r="AI58" s="63"/>
-      <c r="AJ58" s="63"/>
+      <c r="A58" s="72"/>
+      <c r="B58" s="80"/>
+      <c r="C58" s="80"/>
+      <c r="D58" s="80"/>
+      <c r="E58" s="80"/>
+      <c r="F58" s="80"/>
+      <c r="G58" s="80"/>
+      <c r="H58" s="80"/>
+      <c r="I58" s="80"/>
+      <c r="J58" s="80"/>
+      <c r="K58" s="80"/>
+      <c r="L58" s="80"/>
+      <c r="N58" s="80"/>
+      <c r="O58" s="80"/>
+      <c r="P58" s="80"/>
+      <c r="Q58" s="80"/>
+      <c r="R58" s="80"/>
+      <c r="S58" s="80"/>
+      <c r="T58" s="80"/>
+      <c r="U58" s="80"/>
+      <c r="V58" s="80"/>
+      <c r="W58" s="80"/>
+      <c r="X58" s="80"/>
+      <c r="Y58" s="72"/>
+      <c r="Z58" s="72"/>
+      <c r="AA58" s="72"/>
+      <c r="AB58" s="72"/>
+      <c r="AC58" s="72"/>
+      <c r="AD58" s="72"/>
+      <c r="AE58" s="72"/>
+      <c r="AF58" s="72"/>
+      <c r="AG58" s="72"/>
+      <c r="AH58" s="72"/>
+      <c r="AI58" s="72"/>
+      <c r="AJ58" s="72"/>
     </row>
     <row r="59" spans="1:36" ht="18" customHeight="1">
-      <c r="K59" s="4"/>
-      <c r="Y59" s="150"/>
-      <c r="Z59" s="150"/>
-      <c r="AA59" s="150"/>
-      <c r="AB59" s="161" t="s">
+      <c r="A59" s="51"/>
+      <c r="B59" s="52"/>
+      <c r="C59" s="52"/>
+      <c r="D59" s="52"/>
+      <c r="E59" s="52"/>
+      <c r="F59" s="52"/>
+      <c r="G59" s="52"/>
+      <c r="H59" s="52"/>
+      <c r="I59" s="52"/>
+      <c r="J59" s="52"/>
+      <c r="K59" s="52"/>
+      <c r="L59" s="52"/>
+      <c r="N59" s="52"/>
+      <c r="O59" s="52"/>
+      <c r="P59" s="52"/>
+      <c r="Q59" s="52"/>
+      <c r="R59" s="52"/>
+      <c r="S59" s="52"/>
+      <c r="T59" s="52"/>
+      <c r="U59" s="52"/>
+      <c r="V59" s="52"/>
+      <c r="W59" s="52"/>
+      <c r="X59" s="52"/>
+      <c r="Y59" s="72"/>
+      <c r="Z59" s="72"/>
+      <c r="AA59" s="72"/>
+      <c r="AB59" s="72"/>
+      <c r="AC59" s="72"/>
+      <c r="AD59" s="72"/>
+      <c r="AE59" s="72"/>
+      <c r="AF59" s="72"/>
+      <c r="AG59" s="72"/>
+      <c r="AH59" s="72"/>
+      <c r="AI59" s="72"/>
+      <c r="AJ59" s="72"/>
+    </row>
+    <row r="60" spans="1:36" ht="18" customHeight="1">
+      <c r="A60" s="72"/>
+      <c r="B60" s="72"/>
+      <c r="C60" s="72"/>
+      <c r="D60" s="72"/>
+      <c r="E60" s="72"/>
+      <c r="F60" s="72"/>
+      <c r="G60" s="72"/>
+      <c r="H60" s="72"/>
+      <c r="I60" s="72"/>
+      <c r="J60" s="72"/>
+      <c r="K60" s="72"/>
+      <c r="L60" s="72"/>
+      <c r="M60" s="72"/>
+      <c r="N60" s="72"/>
+      <c r="O60" s="72"/>
+      <c r="P60" s="72"/>
+      <c r="Q60" s="72"/>
+      <c r="R60" s="72"/>
+      <c r="S60" s="72"/>
+      <c r="T60" s="72"/>
+      <c r="U60" s="72"/>
+      <c r="V60" s="72"/>
+      <c r="W60" s="72"/>
+      <c r="X60" s="72"/>
+      <c r="Y60" s="72"/>
+      <c r="Z60" s="72"/>
+      <c r="AA60" s="72"/>
+      <c r="AB60" s="73"/>
+      <c r="AC60" s="73"/>
+      <c r="AD60" s="73"/>
+      <c r="AE60" s="73"/>
+      <c r="AF60" s="73"/>
+      <c r="AG60" s="73"/>
+      <c r="AH60" s="73"/>
+      <c r="AI60" s="73"/>
+      <c r="AJ60" s="73"/>
+    </row>
+    <row r="61" spans="1:36" ht="18" customHeight="1">
+      <c r="Y61" s="72"/>
+      <c r="Z61" s="72"/>
+      <c r="AA61" s="72"/>
+      <c r="AB61" s="71" t="s">
         <v>92</v>
       </c>
-      <c r="AC59" s="161"/>
-      <c r="AD59" s="161"/>
-      <c r="AE59" s="161"/>
-      <c r="AF59" s="161"/>
-      <c r="AG59" s="161"/>
-      <c r="AH59" s="161"/>
-      <c r="AI59" s="161"/>
-      <c r="AJ59" s="161"/>
+      <c r="AC61" s="71"/>
+      <c r="AD61" s="71"/>
+      <c r="AE61" s="71"/>
+      <c r="AF61" s="71"/>
+      <c r="AG61" s="71"/>
+      <c r="AH61" s="71"/>
+      <c r="AI61" s="71"/>
+      <c r="AJ61" s="71"/>
     </row>
-    <row r="60" spans="1:36" ht="16.5" customHeight="1"/>
-    <row r="61" spans="1:36" ht="18" hidden="1" customHeight="1"/>
-    <row r="62" spans="1:36" ht="18" hidden="1" customHeight="1"/>
+    <row r="62" spans="1:36" ht="16.5" customHeight="1"/>
     <row r="63" spans="1:36" ht="18" hidden="1" customHeight="1"/>
     <row r="64" spans="1:36" ht="18" hidden="1" customHeight="1"/>
     <row r="65" ht="18" hidden="1" customHeight="1"/>
@@ -10005,107 +10071,30 @@
     <row r="653" ht="18" hidden="1" customHeight="1"/>
     <row r="654" ht="18" hidden="1" customHeight="1"/>
     <row r="655" ht="18" hidden="1" customHeight="1"/>
+    <row r="656" ht="18" hidden="1" customHeight="1"/>
+    <row r="657" ht="18" hidden="1" customHeight="1"/>
+    <row r="658"/>
   </sheetData>
   <mergeCells count="133">
-    <mergeCell ref="AF44:AI44"/>
-    <mergeCell ref="T48:AA48"/>
-    <mergeCell ref="AF43:AI43"/>
-    <mergeCell ref="AB46:AF46"/>
-    <mergeCell ref="X45:Z45"/>
-    <mergeCell ref="AG47:AI47"/>
-    <mergeCell ref="W43:Z43"/>
-    <mergeCell ref="T49:V49"/>
-    <mergeCell ref="A27:AJ29"/>
-    <mergeCell ref="A36:R36"/>
-    <mergeCell ref="B45:I45"/>
-    <mergeCell ref="S41:AA41"/>
-    <mergeCell ref="AB59:AJ59"/>
-    <mergeCell ref="AB55:AJ58"/>
-    <mergeCell ref="AB54:AJ54"/>
-    <mergeCell ref="S46:AA46"/>
-    <mergeCell ref="AG46:AI46"/>
-    <mergeCell ref="AC51:AE51"/>
-    <mergeCell ref="T50:V50"/>
-    <mergeCell ref="W51:Y51"/>
-    <mergeCell ref="B54:L54"/>
-    <mergeCell ref="N54:X54"/>
-    <mergeCell ref="Y53:AA59"/>
-    <mergeCell ref="A58:X58"/>
-    <mergeCell ref="A53:A55"/>
-    <mergeCell ref="N53:X53"/>
-    <mergeCell ref="A52:M52"/>
-    <mergeCell ref="N52:AJ52"/>
-    <mergeCell ref="D51:H51"/>
-    <mergeCell ref="B48:I48"/>
-    <mergeCell ref="B53:L53"/>
-    <mergeCell ref="K50:R50"/>
-    <mergeCell ref="T51:V51"/>
-    <mergeCell ref="AB53:AJ53"/>
-    <mergeCell ref="W49:Y49"/>
-    <mergeCell ref="AC50:AJ50"/>
-    <mergeCell ref="B49:I49"/>
-    <mergeCell ref="AF42:AI42"/>
-    <mergeCell ref="A30:O30"/>
-    <mergeCell ref="B42:I42"/>
-    <mergeCell ref="AB41:AJ41"/>
-    <mergeCell ref="J41:R41"/>
-    <mergeCell ref="W42:Y42"/>
-    <mergeCell ref="A31:AJ35"/>
-    <mergeCell ref="A37:AJ40"/>
-    <mergeCell ref="B43:I43"/>
-    <mergeCell ref="AB45:AE45"/>
-    <mergeCell ref="J51:R51"/>
-    <mergeCell ref="B46:I46"/>
-    <mergeCell ref="AF45:AI45"/>
-    <mergeCell ref="AB47:AF47"/>
-    <mergeCell ref="AF51:AH51"/>
-    <mergeCell ref="AB48:AJ48"/>
-    <mergeCell ref="AC49:AJ49"/>
-    <mergeCell ref="B47:I47"/>
-    <mergeCell ref="B50:C50"/>
-    <mergeCell ref="D50:H50"/>
-    <mergeCell ref="K48:R48"/>
-    <mergeCell ref="K49:R49"/>
-    <mergeCell ref="S45:W45"/>
-    <mergeCell ref="T47:AA47"/>
-    <mergeCell ref="K46:R46"/>
-    <mergeCell ref="K47:R47"/>
-    <mergeCell ref="W50:Y50"/>
-    <mergeCell ref="K45:R45"/>
-    <mergeCell ref="B44:I44"/>
-    <mergeCell ref="K42:R42"/>
-    <mergeCell ref="AB44:AE44"/>
-    <mergeCell ref="S42:V42"/>
-    <mergeCell ref="S43:V43"/>
-    <mergeCell ref="S44:W44"/>
-    <mergeCell ref="X44:Z44"/>
-    <mergeCell ref="K44:R44"/>
-    <mergeCell ref="K43:R43"/>
-    <mergeCell ref="AB42:AE42"/>
-    <mergeCell ref="A5:B5"/>
-    <mergeCell ref="A6:B6"/>
-    <mergeCell ref="AD6:AF6"/>
-    <mergeCell ref="D9:R9"/>
-    <mergeCell ref="K7:O7"/>
-    <mergeCell ref="AB43:AE43"/>
-    <mergeCell ref="A25:AJ25"/>
-    <mergeCell ref="A22:AJ23"/>
-    <mergeCell ref="A17:T20"/>
-    <mergeCell ref="C5:I5"/>
-    <mergeCell ref="AF19:AG19"/>
-    <mergeCell ref="A41:I41"/>
-    <mergeCell ref="AI19:AJ19"/>
-    <mergeCell ref="A14:H14"/>
-    <mergeCell ref="I14:AJ14"/>
-    <mergeCell ref="AI17:AJ17"/>
-    <mergeCell ref="AF17:AG17"/>
-    <mergeCell ref="A15:AJ15"/>
-    <mergeCell ref="AF18:AG18"/>
-    <mergeCell ref="AA5:AJ5"/>
-    <mergeCell ref="V7:W7"/>
-    <mergeCell ref="AI18:AJ18"/>
-    <mergeCell ref="U16:AD16"/>
-    <mergeCell ref="AF7:AG7"/>
+    <mergeCell ref="B58:L58"/>
+    <mergeCell ref="N58:X58"/>
+    <mergeCell ref="Q2:Z2"/>
+    <mergeCell ref="Q3:Z3"/>
+    <mergeCell ref="A11:P11"/>
+    <mergeCell ref="K5:O5"/>
+    <mergeCell ref="K6:O6"/>
+    <mergeCell ref="P6:X6"/>
+    <mergeCell ref="A41:R41"/>
+    <mergeCell ref="A42:AJ43"/>
+    <mergeCell ref="AE16:AJ16"/>
+    <mergeCell ref="A16:T16"/>
+    <mergeCell ref="AD3:AJ3"/>
+    <mergeCell ref="Y6:AC6"/>
+    <mergeCell ref="Y5:Z5"/>
+    <mergeCell ref="P5:X5"/>
+    <mergeCell ref="AH6:AI6"/>
+    <mergeCell ref="AC7:AE7"/>
+    <mergeCell ref="AI7:AJ7"/>
     <mergeCell ref="C6:I6"/>
     <mergeCell ref="S8:W8"/>
     <mergeCell ref="A9:C9"/>
@@ -10121,25 +10110,105 @@
     <mergeCell ref="P7:R7"/>
     <mergeCell ref="X8:AJ8"/>
     <mergeCell ref="A10:AJ10"/>
-    <mergeCell ref="AE16:AJ16"/>
-    <mergeCell ref="A16:T16"/>
-    <mergeCell ref="AD3:AJ3"/>
-    <mergeCell ref="Y6:AC6"/>
-    <mergeCell ref="Y5:Z5"/>
-    <mergeCell ref="P5:X5"/>
-    <mergeCell ref="AH6:AI6"/>
-    <mergeCell ref="AC7:AE7"/>
-    <mergeCell ref="AI7:AJ7"/>
+    <mergeCell ref="A5:B5"/>
+    <mergeCell ref="A6:B6"/>
+    <mergeCell ref="AD6:AF6"/>
+    <mergeCell ref="D9:R9"/>
+    <mergeCell ref="K7:O7"/>
+    <mergeCell ref="AB46:AE46"/>
+    <mergeCell ref="A25:AJ25"/>
+    <mergeCell ref="A22:AJ23"/>
+    <mergeCell ref="A17:T20"/>
+    <mergeCell ref="C5:I5"/>
+    <mergeCell ref="AF19:AG19"/>
+    <mergeCell ref="A44:I44"/>
+    <mergeCell ref="AI19:AJ19"/>
+    <mergeCell ref="A14:H14"/>
+    <mergeCell ref="I14:AJ14"/>
+    <mergeCell ref="AI17:AJ17"/>
+    <mergeCell ref="AF17:AG17"/>
+    <mergeCell ref="A15:AJ15"/>
+    <mergeCell ref="AF18:AG18"/>
+    <mergeCell ref="AA5:AJ5"/>
+    <mergeCell ref="V7:W7"/>
+    <mergeCell ref="AI18:AJ18"/>
+    <mergeCell ref="U16:AD16"/>
+    <mergeCell ref="AF7:AG7"/>
+    <mergeCell ref="K45:R45"/>
+    <mergeCell ref="AB47:AE47"/>
+    <mergeCell ref="S45:V45"/>
+    <mergeCell ref="S46:V46"/>
+    <mergeCell ref="S47:W47"/>
+    <mergeCell ref="X47:Z47"/>
+    <mergeCell ref="K47:R47"/>
+    <mergeCell ref="K46:R46"/>
+    <mergeCell ref="AB45:AE45"/>
+    <mergeCell ref="J54:R54"/>
+    <mergeCell ref="B49:I49"/>
+    <mergeCell ref="AF48:AI48"/>
+    <mergeCell ref="AB50:AF50"/>
+    <mergeCell ref="AF54:AH54"/>
+    <mergeCell ref="AB51:AJ51"/>
+    <mergeCell ref="AC52:AJ52"/>
+    <mergeCell ref="B50:I50"/>
+    <mergeCell ref="B53:C53"/>
+    <mergeCell ref="D53:H53"/>
+    <mergeCell ref="K51:R51"/>
+    <mergeCell ref="K52:R52"/>
+    <mergeCell ref="S48:W48"/>
+    <mergeCell ref="T50:AA50"/>
+    <mergeCell ref="K49:R49"/>
+    <mergeCell ref="K50:R50"/>
+    <mergeCell ref="W53:Y53"/>
+    <mergeCell ref="K48:R48"/>
+    <mergeCell ref="AB61:AJ61"/>
+    <mergeCell ref="AB58:AJ60"/>
+    <mergeCell ref="AB57:AJ57"/>
+    <mergeCell ref="S49:AA49"/>
+    <mergeCell ref="AG49:AI49"/>
+    <mergeCell ref="AC54:AE54"/>
+    <mergeCell ref="T53:V53"/>
+    <mergeCell ref="W54:Y54"/>
+    <mergeCell ref="B57:L57"/>
+    <mergeCell ref="N57:X57"/>
+    <mergeCell ref="Y56:AA61"/>
+    <mergeCell ref="A60:X60"/>
+    <mergeCell ref="A56:A58"/>
+    <mergeCell ref="N56:X56"/>
+    <mergeCell ref="A55:M55"/>
+    <mergeCell ref="N55:AJ55"/>
+    <mergeCell ref="D54:H54"/>
+    <mergeCell ref="B51:I51"/>
     <mergeCell ref="B56:L56"/>
-    <mergeCell ref="N56:X56"/>
-    <mergeCell ref="B55:L55"/>
-    <mergeCell ref="N55:X55"/>
-    <mergeCell ref="Q2:Z2"/>
-    <mergeCell ref="Q3:Z3"/>
-    <mergeCell ref="A11:P11"/>
-    <mergeCell ref="K5:O5"/>
-    <mergeCell ref="K6:O6"/>
-    <mergeCell ref="P6:X6"/>
+    <mergeCell ref="K53:R53"/>
+    <mergeCell ref="T54:V54"/>
+    <mergeCell ref="AB56:AJ56"/>
+    <mergeCell ref="W52:Y52"/>
+    <mergeCell ref="AC53:AJ53"/>
+    <mergeCell ref="AF47:AI47"/>
+    <mergeCell ref="T51:AA51"/>
+    <mergeCell ref="AF46:AI46"/>
+    <mergeCell ref="AB49:AF49"/>
+    <mergeCell ref="X48:Z48"/>
+    <mergeCell ref="AG50:AI50"/>
+    <mergeCell ref="W46:Z46"/>
+    <mergeCell ref="T52:V52"/>
+    <mergeCell ref="A27:AJ29"/>
+    <mergeCell ref="A36:R36"/>
+    <mergeCell ref="B48:I48"/>
+    <mergeCell ref="S44:AA44"/>
+    <mergeCell ref="B52:I52"/>
+    <mergeCell ref="AF45:AI45"/>
+    <mergeCell ref="A30:O30"/>
+    <mergeCell ref="B45:I45"/>
+    <mergeCell ref="AB44:AJ44"/>
+    <mergeCell ref="J44:R44"/>
+    <mergeCell ref="W45:Y45"/>
+    <mergeCell ref="A31:AJ35"/>
+    <mergeCell ref="A37:AJ40"/>
+    <mergeCell ref="B46:I46"/>
+    <mergeCell ref="AB48:AE48"/>
+    <mergeCell ref="B47:I47"/>
   </mergeCells>
   <phoneticPr fontId="0" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -10708,72 +10777,6 @@
                   <from>
                     <xdr:col>0</xdr:col>
                     <xdr:colOff>53340</xdr:colOff>
-                    <xdr:row>41</xdr:row>
-                    <xdr:rowOff>30480</xdr:rowOff>
-                  </from>
-                  <to>
-                    <xdr:col>1</xdr:col>
-                    <xdr:colOff>91440</xdr:colOff>
-                    <xdr:row>42</xdr:row>
-                    <xdr:rowOff>15240</xdr:rowOff>
-                  </to>
-                </anchor>
-              </controlPr>
-            </control>
-          </mc:Choice>
-        </mc:AlternateContent>
-        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-          <mc:Choice Requires="x14">
-            <control shapeId="1147" r:id="rId30" name="Check Box 123">
-              <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
-                <anchor moveWithCells="1">
-                  <from>
-                    <xdr:col>0</xdr:col>
-                    <xdr:colOff>53340</xdr:colOff>
-                    <xdr:row>42</xdr:row>
-                    <xdr:rowOff>30480</xdr:rowOff>
-                  </from>
-                  <to>
-                    <xdr:col>1</xdr:col>
-                    <xdr:colOff>91440</xdr:colOff>
-                    <xdr:row>43</xdr:row>
-                    <xdr:rowOff>15240</xdr:rowOff>
-                  </to>
-                </anchor>
-              </controlPr>
-            </control>
-          </mc:Choice>
-        </mc:AlternateContent>
-        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-          <mc:Choice Requires="x14">
-            <control shapeId="1148" r:id="rId31" name="Check Box 124">
-              <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
-                <anchor moveWithCells="1">
-                  <from>
-                    <xdr:col>0</xdr:col>
-                    <xdr:colOff>53340</xdr:colOff>
-                    <xdr:row>43</xdr:row>
-                    <xdr:rowOff>30480</xdr:rowOff>
-                  </from>
-                  <to>
-                    <xdr:col>1</xdr:col>
-                    <xdr:colOff>91440</xdr:colOff>
-                    <xdr:row>44</xdr:row>
-                    <xdr:rowOff>15240</xdr:rowOff>
-                  </to>
-                </anchor>
-              </controlPr>
-            </control>
-          </mc:Choice>
-        </mc:AlternateContent>
-        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-          <mc:Choice Requires="x14">
-            <control shapeId="1149" r:id="rId32" name="Check Box 125">
-              <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
-                <anchor moveWithCells="1">
-                  <from>
-                    <xdr:col>0</xdr:col>
-                    <xdr:colOff>53340</xdr:colOff>
                     <xdr:row>44</xdr:row>
                     <xdr:rowOff>30480</xdr:rowOff>
                   </from>
@@ -10790,7 +10793,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
           <mc:Choice Requires="x14">
-            <control shapeId="1150" r:id="rId33" name="Check Box 126">
+            <control shapeId="1147" r:id="rId30" name="Check Box 123">
               <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -10812,7 +10815,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
           <mc:Choice Requires="x14">
-            <control shapeId="1151" r:id="rId34" name="Check Box 127">
+            <control shapeId="1148" r:id="rId31" name="Check Box 124">
               <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -10834,7 +10837,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
           <mc:Choice Requires="x14">
-            <control shapeId="1152" r:id="rId35" name="Check Box 128">
+            <control shapeId="1149" r:id="rId32" name="Check Box 125">
               <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -10856,7 +10859,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
           <mc:Choice Requires="x14">
-            <control shapeId="1153" r:id="rId36" name="Check Box 129">
+            <control shapeId="1150" r:id="rId33" name="Check Box 126">
               <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -10878,7 +10881,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
           <mc:Choice Requires="x14">
-            <control shapeId="1154" r:id="rId37" name="Check Box 130">
+            <control shapeId="1151" r:id="rId34" name="Check Box 127">
               <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -10900,19 +10903,19 @@
         </mc:AlternateContent>
         <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
           <mc:Choice Requires="x14">
-            <control shapeId="1164" r:id="rId38" name="Check Box 140">
+            <control shapeId="1152" r:id="rId35" name="Check Box 128">
               <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
-                    <xdr:col>9</xdr:col>
+                    <xdr:col>0</xdr:col>
                     <xdr:colOff>53340</xdr:colOff>
-                    <xdr:row>41</xdr:row>
+                    <xdr:row>50</xdr:row>
                     <xdr:rowOff>30480</xdr:rowOff>
                   </from>
                   <to>
-                    <xdr:col>10</xdr:col>
+                    <xdr:col>1</xdr:col>
                     <xdr:colOff>91440</xdr:colOff>
-                    <xdr:row>42</xdr:row>
+                    <xdr:row>51</xdr:row>
                     <xdr:rowOff>15240</xdr:rowOff>
                   </to>
                 </anchor>
@@ -10922,19 +10925,19 @@
         </mc:AlternateContent>
         <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
           <mc:Choice Requires="x14">
-            <control shapeId="1165" r:id="rId39" name="Check Box 141">
+            <control shapeId="1153" r:id="rId36" name="Check Box 129">
               <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
-                    <xdr:col>9</xdr:col>
+                    <xdr:col>0</xdr:col>
                     <xdr:colOff>53340</xdr:colOff>
-                    <xdr:row>42</xdr:row>
+                    <xdr:row>51</xdr:row>
                     <xdr:rowOff>30480</xdr:rowOff>
                   </from>
                   <to>
-                    <xdr:col>10</xdr:col>
+                    <xdr:col>1</xdr:col>
                     <xdr:colOff>91440</xdr:colOff>
-                    <xdr:row>43</xdr:row>
+                    <xdr:row>52</xdr:row>
                     <xdr:rowOff>15240</xdr:rowOff>
                   </to>
                 </anchor>
@@ -10944,19 +10947,19 @@
         </mc:AlternateContent>
         <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
           <mc:Choice Requires="x14">
-            <control shapeId="1166" r:id="rId40" name="Check Box 142">
+            <control shapeId="1154" r:id="rId37" name="Check Box 130">
               <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
-                    <xdr:col>9</xdr:col>
+                    <xdr:col>0</xdr:col>
                     <xdr:colOff>53340</xdr:colOff>
-                    <xdr:row>43</xdr:row>
+                    <xdr:row>52</xdr:row>
                     <xdr:rowOff>30480</xdr:rowOff>
                   </from>
                   <to>
-                    <xdr:col>10</xdr:col>
+                    <xdr:col>1</xdr:col>
                     <xdr:colOff>91440</xdr:colOff>
-                    <xdr:row>44</xdr:row>
+                    <xdr:row>53</xdr:row>
                     <xdr:rowOff>15240</xdr:rowOff>
                   </to>
                 </anchor>
@@ -10966,7 +10969,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
           <mc:Choice Requires="x14">
-            <control shapeId="1167" r:id="rId41" name="Check Box 143">
+            <control shapeId="1164" r:id="rId38" name="Check Box 140">
               <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -10988,7 +10991,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
           <mc:Choice Requires="x14">
-            <control shapeId="1168" r:id="rId42" name="Check Box 144">
+            <control shapeId="1165" r:id="rId39" name="Check Box 141">
               <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -11010,7 +11013,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
           <mc:Choice Requires="x14">
-            <control shapeId="1169" r:id="rId43" name="Check Box 145">
+            <control shapeId="1166" r:id="rId40" name="Check Box 142">
               <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -11032,7 +11035,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
           <mc:Choice Requires="x14">
-            <control shapeId="1170" r:id="rId44" name="Check Box 146">
+            <control shapeId="1167" r:id="rId41" name="Check Box 143">
               <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -11054,7 +11057,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
           <mc:Choice Requires="x14">
-            <control shapeId="1171" r:id="rId45" name="Check Box 147">
+            <control shapeId="1168" r:id="rId42" name="Check Box 144">
               <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -11076,7 +11079,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
           <mc:Choice Requires="x14">
-            <control shapeId="1172" r:id="rId46" name="Check Box 148">
+            <control shapeId="1169" r:id="rId43" name="Check Box 145">
               <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -11098,19 +11101,85 @@
         </mc:AlternateContent>
         <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
           <mc:Choice Requires="x14">
+            <control shapeId="1170" r:id="rId44" name="Check Box 146">
+              <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
+                <anchor moveWithCells="1">
+                  <from>
+                    <xdr:col>9</xdr:col>
+                    <xdr:colOff>53340</xdr:colOff>
+                    <xdr:row>50</xdr:row>
+                    <xdr:rowOff>30480</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>10</xdr:col>
+                    <xdr:colOff>91440</xdr:colOff>
+                    <xdr:row>51</xdr:row>
+                    <xdr:rowOff>15240</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
+        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+          <mc:Choice Requires="x14">
+            <control shapeId="1171" r:id="rId45" name="Check Box 147">
+              <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
+                <anchor moveWithCells="1">
+                  <from>
+                    <xdr:col>9</xdr:col>
+                    <xdr:colOff>53340</xdr:colOff>
+                    <xdr:row>51</xdr:row>
+                    <xdr:rowOff>30480</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>10</xdr:col>
+                    <xdr:colOff>91440</xdr:colOff>
+                    <xdr:row>52</xdr:row>
+                    <xdr:rowOff>15240</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
+        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+          <mc:Choice Requires="x14">
+            <control shapeId="1172" r:id="rId46" name="Check Box 148">
+              <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
+                <anchor moveWithCells="1">
+                  <from>
+                    <xdr:col>9</xdr:col>
+                    <xdr:colOff>53340</xdr:colOff>
+                    <xdr:row>52</xdr:row>
+                    <xdr:rowOff>30480</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>10</xdr:col>
+                    <xdr:colOff>91440</xdr:colOff>
+                    <xdr:row>53</xdr:row>
+                    <xdr:rowOff>15240</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
+        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+          <mc:Choice Requires="x14">
             <control shapeId="1173" r:id="rId47" name="Check Box 149">
               <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
                     <xdr:col>18</xdr:col>
                     <xdr:colOff>53340</xdr:colOff>
-                    <xdr:row>46</xdr:row>
+                    <xdr:row>49</xdr:row>
                     <xdr:rowOff>30480</xdr:rowOff>
                   </from>
                   <to>
                     <xdr:col>19</xdr:col>
                     <xdr:colOff>91440</xdr:colOff>
-                    <xdr:row>47</xdr:row>
+                    <xdr:row>50</xdr:row>
                     <xdr:rowOff>15240</xdr:rowOff>
                   </to>
                 </anchor>
@@ -11126,13 +11195,13 @@
                   <from>
                     <xdr:col>18</xdr:col>
                     <xdr:colOff>53340</xdr:colOff>
-                    <xdr:row>47</xdr:row>
+                    <xdr:row>50</xdr:row>
                     <xdr:rowOff>30480</xdr:rowOff>
                   </from>
                   <to>
                     <xdr:col>19</xdr:col>
                     <xdr:colOff>91440</xdr:colOff>
-                    <xdr:row>48</xdr:row>
+                    <xdr:row>51</xdr:row>
                     <xdr:rowOff>15240</xdr:rowOff>
                   </to>
                 </anchor>
@@ -11148,13 +11217,13 @@
                   <from>
                     <xdr:col>27</xdr:col>
                     <xdr:colOff>53340</xdr:colOff>
-                    <xdr:row>48</xdr:row>
+                    <xdr:row>51</xdr:row>
                     <xdr:rowOff>30480</xdr:rowOff>
                   </from>
                   <to>
                     <xdr:col>28</xdr:col>
                     <xdr:colOff>91440</xdr:colOff>
-                    <xdr:row>49</xdr:row>
+                    <xdr:row>52</xdr:row>
                     <xdr:rowOff>15240</xdr:rowOff>
                   </to>
                 </anchor>
@@ -11170,13 +11239,13 @@
                   <from>
                     <xdr:col>27</xdr:col>
                     <xdr:colOff>53340</xdr:colOff>
-                    <xdr:row>49</xdr:row>
+                    <xdr:row>52</xdr:row>
                     <xdr:rowOff>30480</xdr:rowOff>
                   </from>
                   <to>
                     <xdr:col>28</xdr:col>
                     <xdr:colOff>91440</xdr:colOff>
-                    <xdr:row>50</xdr:row>
+                    <xdr:row>53</xdr:row>
                     <xdr:rowOff>15240</xdr:rowOff>
                   </to>
                 </anchor>
@@ -11192,13 +11261,13 @@
                   <from>
                     <xdr:col>27</xdr:col>
                     <xdr:colOff>53340</xdr:colOff>
-                    <xdr:row>50</xdr:row>
+                    <xdr:row>53</xdr:row>
                     <xdr:rowOff>30480</xdr:rowOff>
                   </from>
                   <to>
                     <xdr:col>28</xdr:col>
                     <xdr:colOff>91440</xdr:colOff>
-                    <xdr:row>51</xdr:row>
+                    <xdr:row>54</xdr:row>
                     <xdr:rowOff>15240</xdr:rowOff>
                   </to>
                 </anchor>
@@ -11214,13 +11283,13 @@
                   <from>
                     <xdr:col>27</xdr:col>
                     <xdr:colOff>53340</xdr:colOff>
-                    <xdr:row>50</xdr:row>
+                    <xdr:row>53</xdr:row>
                     <xdr:rowOff>30480</xdr:rowOff>
                   </from>
                   <to>
                     <xdr:col>28</xdr:col>
                     <xdr:colOff>91440</xdr:colOff>
-                    <xdr:row>51</xdr:row>
+                    <xdr:row>54</xdr:row>
                     <xdr:rowOff>15240</xdr:rowOff>
                   </to>
                 </anchor>

--- a/backend_api/templates/container_report_template.xlsx
+++ b/backend_api/templates/container_report_template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Aaron Avila\Documents\ERP-SOM\backend_api\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{856E49EC-9204-4212-AF38-2E1771F849C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B50C4B53-0046-4AB3-8DD1-1262CCC48CD2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-1125" windowWidth="29040" windowHeight="15720" xr2:uid="{253FFB1B-D348-46B1-A532-0D44566D2FFD}"/>
   </bookViews>
@@ -568,7 +568,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="A44" authorId="1" shapeId="0" xr:uid="{30443301-1091-4C06-A3FA-E580BF54C74F}">
+    <comment ref="A43" authorId="1" shapeId="0" xr:uid="{30443301-1091-4C06-A3FA-E580BF54C74F}">
       <text>
         <r>
           <rPr>
@@ -583,7 +583,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="J44" authorId="1" shapeId="0" xr:uid="{36F2176C-C319-4967-9E8E-785489AA45AB}">
+    <comment ref="J43" authorId="1" shapeId="0" xr:uid="{36F2176C-C319-4967-9E8E-785489AA45AB}">
       <text>
         <r>
           <rPr>
@@ -597,7 +597,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="S44" authorId="1" shapeId="0" xr:uid="{EF231990-56B0-421A-BEF2-559550D4982B}">
+    <comment ref="S43" authorId="1" shapeId="0" xr:uid="{EF231990-56B0-421A-BEF2-559550D4982B}">
       <text>
         <r>
           <rPr>
@@ -611,7 +611,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AB44" authorId="1" shapeId="0" xr:uid="{9FC68C20-EF51-47CB-9CBA-1D201D3580EF}">
+    <comment ref="AB43" authorId="1" shapeId="0" xr:uid="{9FC68C20-EF51-47CB-9CBA-1D201D3580EF}">
       <text>
         <r>
           <rPr>
@@ -625,7 +625,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="S49" authorId="1" shapeId="0" xr:uid="{0D5099D2-C3D8-4CDE-BD1E-0AFB08D17C30}">
+    <comment ref="S48" authorId="1" shapeId="0" xr:uid="{0D5099D2-C3D8-4CDE-BD1E-0AFB08D17C30}">
       <text>
         <r>
           <rPr>
@@ -699,7 +699,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AB51" authorId="1" shapeId="0" xr:uid="{703412D1-5D8A-439E-A61F-D30F4F1283CB}">
+    <comment ref="AB50" authorId="1" shapeId="0" xr:uid="{703412D1-5D8A-439E-A61F-D30F4F1283CB}">
       <text>
         <r>
           <rPr>
@@ -713,7 +713,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="A55" authorId="1" shapeId="0" xr:uid="{ACCFB67C-ADAC-4F00-A332-CC4D5E296E84}">
+    <comment ref="A54" authorId="1" shapeId="0" xr:uid="{ACCFB67C-ADAC-4F00-A332-CC4D5E296E84}">
       <text>
         <r>
           <rPr>
@@ -727,7 +727,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AB56" authorId="1" shapeId="0" xr:uid="{FC59D6ED-F95D-44F3-88C3-22174703430C}">
+    <comment ref="AB55" authorId="1" shapeId="0" xr:uid="{FC59D6ED-F95D-44F3-88C3-22174703430C}">
       <text>
         <r>
           <rPr>
@@ -741,7 +741,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AB58" authorId="1" shapeId="0" xr:uid="{59D1CEF0-0C19-4AF8-B701-BE6BB6391D05}">
+    <comment ref="AB57" authorId="1" shapeId="0" xr:uid="{59D1CEF0-0C19-4AF8-B701-BE6BB6391D05}">
       <text>
         <r>
           <rPr>
@@ -1428,7 +1428,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="167">
+  <cellXfs count="164">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -1553,26 +1553,323 @@
       <alignment horizontal="left"/>
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="8" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="9" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="6" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="2" borderId="9" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="2" borderId="6" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="2" borderId="7" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="4" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="165" fontId="13" fillId="0" borderId="8" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="14" fontId="13" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="2" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="3" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="4" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="5" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="3" fontId="13" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="13" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="9" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="6" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="6" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="6" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="4" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="4" fontId="13" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
     <xf numFmtId="4" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="4" fontId="13" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right"/>
-      <protection locked="0"/>
-    </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
       <protection locked="0"/>
@@ -1601,74 +1898,6 @@
       <alignment horizontal="left" vertical="top" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="9" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="6" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="4" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
@@ -1677,10 +1906,6 @@
     </xf>
     <xf numFmtId="0" fontId="22" fillId="2" borderId="9" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="13" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -1702,253 +1927,16 @@
       <alignment horizontal="left" vertical="top" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="3" fontId="13" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="top" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="top" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="2" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="3" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="4" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="5" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top"/>
-      <protection locked="0"/>
-    </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="3" fontId="13" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="9" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="6" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="6" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="6" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="165" fontId="13" fillId="0" borderId="8" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="2" borderId="9" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="2" borderId="6" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="2" borderId="7" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="4" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="8" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
+      <alignment vertical="top" wrapText="1"/>
       <protection locked="0"/>
     </xf>
   </cellXfs>
@@ -2170,13 +2158,13 @@
     <xdr:from>
       <xdr:col>29</xdr:col>
       <xdr:colOff>114300</xdr:colOff>
-      <xdr:row>57</xdr:row>
+      <xdr:row>56</xdr:row>
       <xdr:rowOff>190500</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>32</xdr:col>
       <xdr:colOff>960120</xdr:colOff>
-      <xdr:row>59</xdr:row>
+      <xdr:row>58</xdr:row>
       <xdr:rowOff>190500</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -2251,9 +2239,9 @@
         </xdr:from>
         <xdr:to>
           <xdr:col>1</xdr:col>
-          <xdr:colOff>57150</xdr:colOff>
+          <xdr:colOff>53340</xdr:colOff>
           <xdr:row>12</xdr:row>
-          <xdr:rowOff>19050</xdr:rowOff>
+          <xdr:rowOff>15240</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -2318,9 +2306,9 @@
         </xdr:from>
         <xdr:to>
           <xdr:col>1</xdr:col>
-          <xdr:colOff>57150</xdr:colOff>
+          <xdr:colOff>53340</xdr:colOff>
           <xdr:row>13</xdr:row>
-          <xdr:rowOff>19050</xdr:rowOff>
+          <xdr:rowOff>15240</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -2385,9 +2373,9 @@
         </xdr:from>
         <xdr:to>
           <xdr:col>5</xdr:col>
-          <xdr:colOff>57150</xdr:colOff>
+          <xdr:colOff>53340</xdr:colOff>
           <xdr:row>12</xdr:row>
-          <xdr:rowOff>19050</xdr:rowOff>
+          <xdr:rowOff>15240</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -2452,9 +2440,9 @@
         </xdr:from>
         <xdr:to>
           <xdr:col>5</xdr:col>
-          <xdr:colOff>57150</xdr:colOff>
+          <xdr:colOff>53340</xdr:colOff>
           <xdr:row>13</xdr:row>
-          <xdr:rowOff>19050</xdr:rowOff>
+          <xdr:rowOff>15240</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -2519,9 +2507,9 @@
         </xdr:from>
         <xdr:to>
           <xdr:col>8</xdr:col>
-          <xdr:colOff>400050</xdr:colOff>
+          <xdr:colOff>396240</xdr:colOff>
           <xdr:row>12</xdr:row>
-          <xdr:rowOff>19050</xdr:rowOff>
+          <xdr:rowOff>15240</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -2586,9 +2574,9 @@
         </xdr:from>
         <xdr:to>
           <xdr:col>8</xdr:col>
-          <xdr:colOff>400050</xdr:colOff>
+          <xdr:colOff>396240</xdr:colOff>
           <xdr:row>13</xdr:row>
-          <xdr:rowOff>19050</xdr:rowOff>
+          <xdr:rowOff>15240</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -2653,9 +2641,9 @@
         </xdr:from>
         <xdr:to>
           <xdr:col>14</xdr:col>
-          <xdr:colOff>57150</xdr:colOff>
+          <xdr:colOff>53340</xdr:colOff>
           <xdr:row>12</xdr:row>
-          <xdr:rowOff>19050</xdr:rowOff>
+          <xdr:rowOff>15240</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -2720,9 +2708,9 @@
         </xdr:from>
         <xdr:to>
           <xdr:col>14</xdr:col>
-          <xdr:colOff>57150</xdr:colOff>
+          <xdr:colOff>53340</xdr:colOff>
           <xdr:row>13</xdr:row>
-          <xdr:rowOff>19050</xdr:rowOff>
+          <xdr:rowOff>15240</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -2787,9 +2775,9 @@
         </xdr:from>
         <xdr:to>
           <xdr:col>17</xdr:col>
-          <xdr:colOff>57150</xdr:colOff>
+          <xdr:colOff>53340</xdr:colOff>
           <xdr:row>12</xdr:row>
-          <xdr:rowOff>19050</xdr:rowOff>
+          <xdr:rowOff>15240</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -2854,9 +2842,9 @@
         </xdr:from>
         <xdr:to>
           <xdr:col>17</xdr:col>
-          <xdr:colOff>57150</xdr:colOff>
+          <xdr:colOff>53340</xdr:colOff>
           <xdr:row>13</xdr:row>
-          <xdr:rowOff>19050</xdr:rowOff>
+          <xdr:rowOff>15240</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -2921,9 +2909,9 @@
         </xdr:from>
         <xdr:to>
           <xdr:col>23</xdr:col>
-          <xdr:colOff>57150</xdr:colOff>
+          <xdr:colOff>53340</xdr:colOff>
           <xdr:row>12</xdr:row>
-          <xdr:rowOff>19050</xdr:rowOff>
+          <xdr:rowOff>15240</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -2988,9 +2976,9 @@
         </xdr:from>
         <xdr:to>
           <xdr:col>23</xdr:col>
-          <xdr:colOff>57150</xdr:colOff>
+          <xdr:colOff>53340</xdr:colOff>
           <xdr:row>13</xdr:row>
-          <xdr:rowOff>19050</xdr:rowOff>
+          <xdr:rowOff>15240</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -3055,9 +3043,9 @@
         </xdr:from>
         <xdr:to>
           <xdr:col>28</xdr:col>
-          <xdr:colOff>57150</xdr:colOff>
+          <xdr:colOff>53340</xdr:colOff>
           <xdr:row>12</xdr:row>
-          <xdr:rowOff>19050</xdr:rowOff>
+          <xdr:rowOff>15240</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -3122,9 +3110,9 @@
         </xdr:from>
         <xdr:to>
           <xdr:col>28</xdr:col>
-          <xdr:colOff>57150</xdr:colOff>
+          <xdr:colOff>53340</xdr:colOff>
           <xdr:row>13</xdr:row>
-          <xdr:rowOff>19050</xdr:rowOff>
+          <xdr:rowOff>15240</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -3191,7 +3179,7 @@
           <xdr:col>32</xdr:col>
           <xdr:colOff>342900</xdr:colOff>
           <xdr:row>12</xdr:row>
-          <xdr:rowOff>19050</xdr:rowOff>
+          <xdr:rowOff>15240</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -3258,7 +3246,7 @@
           <xdr:col>32</xdr:col>
           <xdr:colOff>342900</xdr:colOff>
           <xdr:row>13</xdr:row>
-          <xdr:rowOff>19050</xdr:rowOff>
+          <xdr:rowOff>15240</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -3323,9 +3311,9 @@
         </xdr:from>
         <xdr:to>
           <xdr:col>21</xdr:col>
-          <xdr:colOff>95250</xdr:colOff>
+          <xdr:colOff>91440</xdr:colOff>
           <xdr:row>17</xdr:row>
-          <xdr:rowOff>19050</xdr:rowOff>
+          <xdr:rowOff>15240</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -3390,9 +3378,9 @@
         </xdr:from>
         <xdr:to>
           <xdr:col>21</xdr:col>
-          <xdr:colOff>95250</xdr:colOff>
+          <xdr:colOff>91440</xdr:colOff>
           <xdr:row>18</xdr:row>
-          <xdr:rowOff>19050</xdr:rowOff>
+          <xdr:rowOff>15240</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -3457,9 +3445,9 @@
         </xdr:from>
         <xdr:to>
           <xdr:col>21</xdr:col>
-          <xdr:colOff>95250</xdr:colOff>
+          <xdr:colOff>91440</xdr:colOff>
           <xdr:row>19</xdr:row>
-          <xdr:rowOff>19050</xdr:rowOff>
+          <xdr:rowOff>15240</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -3524,9 +3512,9 @@
         </xdr:from>
         <xdr:to>
           <xdr:col>25</xdr:col>
-          <xdr:colOff>95250</xdr:colOff>
+          <xdr:colOff>91440</xdr:colOff>
           <xdr:row>17</xdr:row>
-          <xdr:rowOff>19050</xdr:rowOff>
+          <xdr:rowOff>15240</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -3591,9 +3579,9 @@
         </xdr:from>
         <xdr:to>
           <xdr:col>25</xdr:col>
-          <xdr:colOff>95250</xdr:colOff>
+          <xdr:colOff>91440</xdr:colOff>
           <xdr:row>18</xdr:row>
-          <xdr:rowOff>19050</xdr:rowOff>
+          <xdr:rowOff>15240</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -3658,9 +3646,9 @@
         </xdr:from>
         <xdr:to>
           <xdr:col>25</xdr:col>
-          <xdr:colOff>95250</xdr:colOff>
+          <xdr:colOff>91440</xdr:colOff>
           <xdr:row>19</xdr:row>
-          <xdr:rowOff>19050</xdr:rowOff>
+          <xdr:rowOff>15240</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -3725,9 +3713,9 @@
         </xdr:from>
         <xdr:to>
           <xdr:col>28</xdr:col>
-          <xdr:colOff>95250</xdr:colOff>
+          <xdr:colOff>91440</xdr:colOff>
           <xdr:row>17</xdr:row>
-          <xdr:rowOff>19050</xdr:rowOff>
+          <xdr:rowOff>15240</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -3792,9 +3780,9 @@
         </xdr:from>
         <xdr:to>
           <xdr:col>28</xdr:col>
-          <xdr:colOff>95250</xdr:colOff>
+          <xdr:colOff>91440</xdr:colOff>
           <xdr:row>18</xdr:row>
-          <xdr:rowOff>19050</xdr:rowOff>
+          <xdr:rowOff>15240</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -3859,9 +3847,9 @@
         </xdr:from>
         <xdr:to>
           <xdr:col>28</xdr:col>
-          <xdr:colOff>95250</xdr:colOff>
+          <xdr:colOff>91440</xdr:colOff>
           <xdr:row>19</xdr:row>
-          <xdr:rowOff>19050</xdr:rowOff>
+          <xdr:rowOff>15240</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -3921,14 +3909,14 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>53340</xdr:colOff>
-          <xdr:row>44</xdr:row>
+          <xdr:row>43</xdr:row>
           <xdr:rowOff>30480</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>1</xdr:col>
-          <xdr:colOff>95250</xdr:colOff>
-          <xdr:row>45</xdr:row>
-          <xdr:rowOff>19050</xdr:rowOff>
+          <xdr:colOff>91440</xdr:colOff>
+          <xdr:row>44</xdr:row>
+          <xdr:rowOff>15240</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -3988,14 +3976,14 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>53340</xdr:colOff>
-          <xdr:row>45</xdr:row>
+          <xdr:row>44</xdr:row>
           <xdr:rowOff>30480</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>1</xdr:col>
-          <xdr:colOff>95250</xdr:colOff>
-          <xdr:row>46</xdr:row>
-          <xdr:rowOff>19050</xdr:rowOff>
+          <xdr:colOff>91440</xdr:colOff>
+          <xdr:row>45</xdr:row>
+          <xdr:rowOff>15240</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -4055,14 +4043,14 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>53340</xdr:colOff>
-          <xdr:row>46</xdr:row>
+          <xdr:row>45</xdr:row>
           <xdr:rowOff>30480</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>1</xdr:col>
-          <xdr:colOff>95250</xdr:colOff>
-          <xdr:row>47</xdr:row>
-          <xdr:rowOff>19050</xdr:rowOff>
+          <xdr:colOff>91440</xdr:colOff>
+          <xdr:row>46</xdr:row>
+          <xdr:rowOff>15240</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -4122,14 +4110,14 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>53340</xdr:colOff>
-          <xdr:row>47</xdr:row>
+          <xdr:row>46</xdr:row>
           <xdr:rowOff>30480</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>1</xdr:col>
-          <xdr:colOff>95250</xdr:colOff>
-          <xdr:row>48</xdr:row>
-          <xdr:rowOff>19050</xdr:rowOff>
+          <xdr:colOff>91440</xdr:colOff>
+          <xdr:row>47</xdr:row>
+          <xdr:rowOff>15240</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -4189,14 +4177,14 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>53340</xdr:colOff>
-          <xdr:row>48</xdr:row>
+          <xdr:row>47</xdr:row>
           <xdr:rowOff>30480</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>1</xdr:col>
-          <xdr:colOff>95250</xdr:colOff>
-          <xdr:row>49</xdr:row>
-          <xdr:rowOff>19050</xdr:rowOff>
+          <xdr:colOff>91440</xdr:colOff>
+          <xdr:row>48</xdr:row>
+          <xdr:rowOff>15240</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -4256,14 +4244,14 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>53340</xdr:colOff>
-          <xdr:row>49</xdr:row>
+          <xdr:row>48</xdr:row>
           <xdr:rowOff>30480</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>1</xdr:col>
-          <xdr:colOff>95250</xdr:colOff>
-          <xdr:row>50</xdr:row>
-          <xdr:rowOff>19050</xdr:rowOff>
+          <xdr:colOff>91440</xdr:colOff>
+          <xdr:row>49</xdr:row>
+          <xdr:rowOff>15240</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -4323,14 +4311,14 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>53340</xdr:colOff>
-          <xdr:row>50</xdr:row>
+          <xdr:row>49</xdr:row>
           <xdr:rowOff>30480</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>1</xdr:col>
-          <xdr:colOff>95250</xdr:colOff>
-          <xdr:row>51</xdr:row>
-          <xdr:rowOff>19050</xdr:rowOff>
+          <xdr:colOff>91440</xdr:colOff>
+          <xdr:row>50</xdr:row>
+          <xdr:rowOff>15240</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -4390,14 +4378,14 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>53340</xdr:colOff>
-          <xdr:row>51</xdr:row>
+          <xdr:row>50</xdr:row>
           <xdr:rowOff>30480</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>1</xdr:col>
-          <xdr:colOff>95250</xdr:colOff>
-          <xdr:row>52</xdr:row>
-          <xdr:rowOff>19050</xdr:rowOff>
+          <xdr:colOff>91440</xdr:colOff>
+          <xdr:row>51</xdr:row>
+          <xdr:rowOff>15240</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -4457,14 +4445,14 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>53340</xdr:colOff>
-          <xdr:row>52</xdr:row>
+          <xdr:row>51</xdr:row>
           <xdr:rowOff>30480</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>1</xdr:col>
-          <xdr:colOff>95250</xdr:colOff>
-          <xdr:row>53</xdr:row>
-          <xdr:rowOff>19050</xdr:rowOff>
+          <xdr:colOff>91440</xdr:colOff>
+          <xdr:row>52</xdr:row>
+          <xdr:rowOff>15240</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -4524,14 +4512,14 @@
         <xdr:from>
           <xdr:col>9</xdr:col>
           <xdr:colOff>53340</xdr:colOff>
-          <xdr:row>44</xdr:row>
+          <xdr:row>43</xdr:row>
           <xdr:rowOff>30480</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>10</xdr:col>
-          <xdr:colOff>95250</xdr:colOff>
-          <xdr:row>45</xdr:row>
-          <xdr:rowOff>19050</xdr:rowOff>
+          <xdr:colOff>91440</xdr:colOff>
+          <xdr:row>44</xdr:row>
+          <xdr:rowOff>15240</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -4591,14 +4579,14 @@
         <xdr:from>
           <xdr:col>9</xdr:col>
           <xdr:colOff>53340</xdr:colOff>
-          <xdr:row>45</xdr:row>
+          <xdr:row>44</xdr:row>
           <xdr:rowOff>30480</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>10</xdr:col>
-          <xdr:colOff>95250</xdr:colOff>
-          <xdr:row>46</xdr:row>
-          <xdr:rowOff>19050</xdr:rowOff>
+          <xdr:colOff>91440</xdr:colOff>
+          <xdr:row>45</xdr:row>
+          <xdr:rowOff>15240</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -4658,14 +4646,14 @@
         <xdr:from>
           <xdr:col>9</xdr:col>
           <xdr:colOff>53340</xdr:colOff>
-          <xdr:row>46</xdr:row>
+          <xdr:row>45</xdr:row>
           <xdr:rowOff>30480</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>10</xdr:col>
-          <xdr:colOff>95250</xdr:colOff>
-          <xdr:row>47</xdr:row>
-          <xdr:rowOff>19050</xdr:rowOff>
+          <xdr:colOff>91440</xdr:colOff>
+          <xdr:row>46</xdr:row>
+          <xdr:rowOff>15240</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -4725,14 +4713,14 @@
         <xdr:from>
           <xdr:col>9</xdr:col>
           <xdr:colOff>53340</xdr:colOff>
-          <xdr:row>47</xdr:row>
+          <xdr:row>46</xdr:row>
           <xdr:rowOff>30480</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>10</xdr:col>
-          <xdr:colOff>95250</xdr:colOff>
-          <xdr:row>48</xdr:row>
-          <xdr:rowOff>19050</xdr:rowOff>
+          <xdr:colOff>91440</xdr:colOff>
+          <xdr:row>47</xdr:row>
+          <xdr:rowOff>15240</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -4792,14 +4780,14 @@
         <xdr:from>
           <xdr:col>9</xdr:col>
           <xdr:colOff>53340</xdr:colOff>
-          <xdr:row>48</xdr:row>
+          <xdr:row>47</xdr:row>
           <xdr:rowOff>30480</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>10</xdr:col>
-          <xdr:colOff>95250</xdr:colOff>
-          <xdr:row>49</xdr:row>
-          <xdr:rowOff>19050</xdr:rowOff>
+          <xdr:colOff>91440</xdr:colOff>
+          <xdr:row>48</xdr:row>
+          <xdr:rowOff>15240</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -4859,14 +4847,14 @@
         <xdr:from>
           <xdr:col>9</xdr:col>
           <xdr:colOff>53340</xdr:colOff>
-          <xdr:row>49</xdr:row>
+          <xdr:row>48</xdr:row>
           <xdr:rowOff>30480</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>10</xdr:col>
-          <xdr:colOff>95250</xdr:colOff>
-          <xdr:row>50</xdr:row>
-          <xdr:rowOff>19050</xdr:rowOff>
+          <xdr:colOff>91440</xdr:colOff>
+          <xdr:row>49</xdr:row>
+          <xdr:rowOff>15240</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -4926,14 +4914,14 @@
         <xdr:from>
           <xdr:col>9</xdr:col>
           <xdr:colOff>53340</xdr:colOff>
-          <xdr:row>50</xdr:row>
+          <xdr:row>49</xdr:row>
           <xdr:rowOff>30480</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>10</xdr:col>
-          <xdr:colOff>95250</xdr:colOff>
-          <xdr:row>51</xdr:row>
-          <xdr:rowOff>19050</xdr:rowOff>
+          <xdr:colOff>91440</xdr:colOff>
+          <xdr:row>50</xdr:row>
+          <xdr:rowOff>15240</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -4993,14 +4981,14 @@
         <xdr:from>
           <xdr:col>9</xdr:col>
           <xdr:colOff>53340</xdr:colOff>
-          <xdr:row>51</xdr:row>
+          <xdr:row>50</xdr:row>
           <xdr:rowOff>30480</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>10</xdr:col>
-          <xdr:colOff>95250</xdr:colOff>
-          <xdr:row>52</xdr:row>
-          <xdr:rowOff>19050</xdr:rowOff>
+          <xdr:colOff>91440</xdr:colOff>
+          <xdr:row>51</xdr:row>
+          <xdr:rowOff>15240</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -5060,14 +5048,14 @@
         <xdr:from>
           <xdr:col>9</xdr:col>
           <xdr:colOff>53340</xdr:colOff>
-          <xdr:row>52</xdr:row>
+          <xdr:row>51</xdr:row>
           <xdr:rowOff>30480</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>10</xdr:col>
-          <xdr:colOff>95250</xdr:colOff>
-          <xdr:row>53</xdr:row>
-          <xdr:rowOff>19050</xdr:rowOff>
+          <xdr:colOff>91440</xdr:colOff>
+          <xdr:row>52</xdr:row>
+          <xdr:rowOff>15240</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -5127,14 +5115,14 @@
         <xdr:from>
           <xdr:col>18</xdr:col>
           <xdr:colOff>53340</xdr:colOff>
-          <xdr:row>49</xdr:row>
+          <xdr:row>48</xdr:row>
           <xdr:rowOff>30480</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>19</xdr:col>
-          <xdr:colOff>95250</xdr:colOff>
-          <xdr:row>50</xdr:row>
-          <xdr:rowOff>19050</xdr:rowOff>
+          <xdr:colOff>91440</xdr:colOff>
+          <xdr:row>49</xdr:row>
+          <xdr:rowOff>15240</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -5194,14 +5182,14 @@
         <xdr:from>
           <xdr:col>18</xdr:col>
           <xdr:colOff>53340</xdr:colOff>
-          <xdr:row>50</xdr:row>
+          <xdr:row>49</xdr:row>
           <xdr:rowOff>30480</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>19</xdr:col>
-          <xdr:colOff>95250</xdr:colOff>
-          <xdr:row>51</xdr:row>
-          <xdr:rowOff>19050</xdr:rowOff>
+          <xdr:colOff>91440</xdr:colOff>
+          <xdr:row>50</xdr:row>
+          <xdr:rowOff>15240</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -5261,14 +5249,14 @@
         <xdr:from>
           <xdr:col>27</xdr:col>
           <xdr:colOff>53340</xdr:colOff>
-          <xdr:row>51</xdr:row>
+          <xdr:row>50</xdr:row>
           <xdr:rowOff>30480</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>28</xdr:col>
-          <xdr:colOff>95250</xdr:colOff>
-          <xdr:row>52</xdr:row>
-          <xdr:rowOff>19050</xdr:rowOff>
+          <xdr:colOff>91440</xdr:colOff>
+          <xdr:row>51</xdr:row>
+          <xdr:rowOff>15240</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -5328,14 +5316,14 @@
         <xdr:from>
           <xdr:col>27</xdr:col>
           <xdr:colOff>53340</xdr:colOff>
-          <xdr:row>52</xdr:row>
+          <xdr:row>51</xdr:row>
           <xdr:rowOff>30480</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>28</xdr:col>
-          <xdr:colOff>95250</xdr:colOff>
-          <xdr:row>53</xdr:row>
-          <xdr:rowOff>19050</xdr:rowOff>
+          <xdr:colOff>91440</xdr:colOff>
+          <xdr:row>52</xdr:row>
+          <xdr:rowOff>15240</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -5395,14 +5383,14 @@
         <xdr:from>
           <xdr:col>27</xdr:col>
           <xdr:colOff>53340</xdr:colOff>
-          <xdr:row>53</xdr:row>
+          <xdr:row>52</xdr:row>
           <xdr:rowOff>30480</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>28</xdr:col>
-          <xdr:colOff>95250</xdr:colOff>
-          <xdr:row>54</xdr:row>
-          <xdr:rowOff>19050</xdr:rowOff>
+          <xdr:colOff>91440</xdr:colOff>
+          <xdr:row>53</xdr:row>
+          <xdr:rowOff>15240</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -5460,13 +5448,13 @@
     <xdr:from>
       <xdr:col>22</xdr:col>
       <xdr:colOff>106680</xdr:colOff>
-      <xdr:row>51</xdr:row>
+      <xdr:row>50</xdr:row>
       <xdr:rowOff>213360</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>24</xdr:col>
       <xdr:colOff>228600</xdr:colOff>
-      <xdr:row>51</xdr:row>
+      <xdr:row>50</xdr:row>
       <xdr:rowOff>213360</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -5514,13 +5502,13 @@
     <xdr:from>
       <xdr:col>22</xdr:col>
       <xdr:colOff>121920</xdr:colOff>
-      <xdr:row>52</xdr:row>
+      <xdr:row>51</xdr:row>
       <xdr:rowOff>213360</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>25</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>52</xdr:row>
+      <xdr:row>51</xdr:row>
       <xdr:rowOff>213360</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -5568,13 +5556,13 @@
     <xdr:from>
       <xdr:col>22</xdr:col>
       <xdr:colOff>121920</xdr:colOff>
-      <xdr:row>53</xdr:row>
+      <xdr:row>52</xdr:row>
       <xdr:rowOff>213360</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>25</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>53</xdr:row>
+      <xdr:row>52</xdr:row>
       <xdr:rowOff>213360</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -5622,13 +5610,13 @@
     <xdr:from>
       <xdr:col>23</xdr:col>
       <xdr:colOff>91440</xdr:colOff>
-      <xdr:row>47</xdr:row>
+      <xdr:row>46</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>25</xdr:col>
       <xdr:colOff>220980</xdr:colOff>
-      <xdr:row>47</xdr:row>
+      <xdr:row>46</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -5676,13 +5664,13 @@
     <xdr:from>
       <xdr:col>23</xdr:col>
       <xdr:colOff>106680</xdr:colOff>
-      <xdr:row>47</xdr:row>
+      <xdr:row>46</xdr:row>
       <xdr:rowOff>213360</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>25</xdr:col>
       <xdr:colOff>228600</xdr:colOff>
-      <xdr:row>47</xdr:row>
+      <xdr:row>46</xdr:row>
       <xdr:rowOff>213360</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -5730,13 +5718,13 @@
     <xdr:from>
       <xdr:col>22</xdr:col>
       <xdr:colOff>91440</xdr:colOff>
-      <xdr:row>45</xdr:row>
+      <xdr:row>44</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>25</xdr:col>
       <xdr:colOff>259080</xdr:colOff>
-      <xdr:row>45</xdr:row>
+      <xdr:row>44</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -5784,13 +5772,13 @@
     <xdr:from>
       <xdr:col>32</xdr:col>
       <xdr:colOff>106680</xdr:colOff>
-      <xdr:row>48</xdr:row>
+      <xdr:row>47</xdr:row>
       <xdr:rowOff>213360</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>34</xdr:col>
       <xdr:colOff>228600</xdr:colOff>
-      <xdr:row>48</xdr:row>
+      <xdr:row>47</xdr:row>
       <xdr:rowOff>213360</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -5838,13 +5826,13 @@
     <xdr:from>
       <xdr:col>32</xdr:col>
       <xdr:colOff>106680</xdr:colOff>
-      <xdr:row>49</xdr:row>
+      <xdr:row>48</xdr:row>
       <xdr:rowOff>213360</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>34</xdr:col>
       <xdr:colOff>228600</xdr:colOff>
-      <xdr:row>49</xdr:row>
+      <xdr:row>48</xdr:row>
       <xdr:rowOff>213360</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -5892,13 +5880,13 @@
     <xdr:from>
       <xdr:col>30</xdr:col>
       <xdr:colOff>205740</xdr:colOff>
-      <xdr:row>45</xdr:row>
+      <xdr:row>44</xdr:row>
       <xdr:rowOff>213360</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>35</xdr:col>
       <xdr:colOff>53340</xdr:colOff>
-      <xdr:row>45</xdr:row>
+      <xdr:row>44</xdr:row>
       <xdr:rowOff>213360</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -5946,13 +5934,13 @@
     <xdr:from>
       <xdr:col>30</xdr:col>
       <xdr:colOff>205740</xdr:colOff>
-      <xdr:row>44</xdr:row>
+      <xdr:row>43</xdr:row>
       <xdr:rowOff>213360</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>35</xdr:col>
       <xdr:colOff>53340</xdr:colOff>
-      <xdr:row>44</xdr:row>
+      <xdr:row>43</xdr:row>
       <xdr:rowOff>213360</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -6000,13 +5988,13 @@
     <xdr:from>
       <xdr:col>30</xdr:col>
       <xdr:colOff>205740</xdr:colOff>
-      <xdr:row>46</xdr:row>
+      <xdr:row>45</xdr:row>
       <xdr:rowOff>213360</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>35</xdr:col>
       <xdr:colOff>53340</xdr:colOff>
-      <xdr:row>46</xdr:row>
+      <xdr:row>45</xdr:row>
       <xdr:rowOff>213360</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -6054,13 +6042,13 @@
     <xdr:from>
       <xdr:col>31</xdr:col>
       <xdr:colOff>121920</xdr:colOff>
-      <xdr:row>53</xdr:row>
+      <xdr:row>52</xdr:row>
       <xdr:rowOff>213360</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>34</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>53</xdr:row>
+      <xdr:row>52</xdr:row>
       <xdr:rowOff>213360</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -6108,13 +6096,13 @@
     <xdr:from>
       <xdr:col>30</xdr:col>
       <xdr:colOff>205740</xdr:colOff>
-      <xdr:row>47</xdr:row>
+      <xdr:row>46</xdr:row>
       <xdr:rowOff>213360</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>35</xdr:col>
       <xdr:colOff>53340</xdr:colOff>
-      <xdr:row>47</xdr:row>
+      <xdr:row>46</xdr:row>
       <xdr:rowOff>213360</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -6162,13 +6150,13 @@
     <xdr:from>
       <xdr:col>2</xdr:col>
       <xdr:colOff>220980</xdr:colOff>
-      <xdr:row>53</xdr:row>
+      <xdr:row>52</xdr:row>
       <xdr:rowOff>213360</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
       <xdr:colOff>7620</xdr:colOff>
-      <xdr:row>53</xdr:row>
+      <xdr:row>52</xdr:row>
       <xdr:rowOff>213360</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -6380,14 +6368,14 @@
         <xdr:from>
           <xdr:col>27</xdr:col>
           <xdr:colOff>53340</xdr:colOff>
-          <xdr:row>53</xdr:row>
+          <xdr:row>52</xdr:row>
           <xdr:rowOff>30480</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>28</xdr:col>
-          <xdr:colOff>95250</xdr:colOff>
-          <xdr:row>54</xdr:row>
-          <xdr:rowOff>19050</xdr:rowOff>
+          <xdr:colOff>91440</xdr:colOff>
+          <xdr:row>53</xdr:row>
+          <xdr:rowOff>15240</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -6519,13 +6507,13 @@
     <xdr:from>
       <xdr:col>25</xdr:col>
       <xdr:colOff>114423</xdr:colOff>
-      <xdr:row>56</xdr:row>
+      <xdr:row>55</xdr:row>
       <xdr:rowOff>117311</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>27</xdr:col>
       <xdr:colOff>243963</xdr:colOff>
-      <xdr:row>59</xdr:row>
+      <xdr:row>58</xdr:row>
       <xdr:rowOff>78514</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -6603,13 +6591,13 @@
     <xdr:from>
       <xdr:col>21</xdr:col>
       <xdr:colOff>167640</xdr:colOff>
-      <xdr:row>46</xdr:row>
+      <xdr:row>45</xdr:row>
       <xdr:rowOff>7620</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>25</xdr:col>
       <xdr:colOff>121920</xdr:colOff>
-      <xdr:row>46</xdr:row>
+      <xdr:row>45</xdr:row>
       <xdr:rowOff>7620</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -7050,18 +7038,18 @@
       <c r="N2" s="31"/>
       <c r="O2" s="38"/>
       <c r="P2" s="38"/>
-      <c r="Q2" s="154" t="s">
+      <c r="Q2" s="54" t="s">
         <v>98</v>
       </c>
-      <c r="R2" s="154"/>
-      <c r="S2" s="154"/>
-      <c r="T2" s="154"/>
-      <c r="U2" s="154"/>
-      <c r="V2" s="154"/>
-      <c r="W2" s="154"/>
-      <c r="X2" s="154"/>
-      <c r="Y2" s="154"/>
-      <c r="Z2" s="154"/>
+      <c r="R2" s="54"/>
+      <c r="S2" s="54"/>
+      <c r="T2" s="54"/>
+      <c r="U2" s="54"/>
+      <c r="V2" s="54"/>
+      <c r="W2" s="54"/>
+      <c r="X2" s="54"/>
+      <c r="Y2" s="54"/>
+      <c r="Z2" s="54"/>
       <c r="AA2" s="38"/>
       <c r="AB2" s="38"/>
       <c r="AC2" s="38"/>
@@ -7087,28 +7075,28 @@
       <c r="K3" s="1"/>
       <c r="M3" s="31"/>
       <c r="N3" s="31"/>
-      <c r="Q3" s="155"/>
-      <c r="R3" s="155"/>
-      <c r="S3" s="155"/>
-      <c r="T3" s="155"/>
-      <c r="U3" s="155"/>
-      <c r="V3" s="155"/>
-      <c r="W3" s="155"/>
-      <c r="X3" s="155"/>
-      <c r="Y3" s="155"/>
-      <c r="Z3" s="155"/>
+      <c r="Q3" s="55"/>
+      <c r="R3" s="55"/>
+      <c r="S3" s="55"/>
+      <c r="T3" s="55"/>
+      <c r="U3" s="55"/>
+      <c r="V3" s="55"/>
+      <c r="W3" s="55"/>
+      <c r="X3" s="55"/>
+      <c r="Y3" s="55"/>
+      <c r="Z3" s="55"/>
       <c r="AA3" s="37"/>
       <c r="AB3" s="50" t="s">
         <v>95</v>
       </c>
       <c r="AC3" s="48"/>
-      <c r="AD3" s="150"/>
-      <c r="AE3" s="151"/>
-      <c r="AF3" s="151"/>
-      <c r="AG3" s="151"/>
-      <c r="AH3" s="151"/>
-      <c r="AI3" s="151"/>
-      <c r="AJ3" s="151"/>
+      <c r="AD3" s="70"/>
+      <c r="AE3" s="71"/>
+      <c r="AF3" s="71"/>
+      <c r="AG3" s="71"/>
+      <c r="AH3" s="71"/>
+      <c r="AI3" s="71"/>
+      <c r="AJ3" s="71"/>
     </row>
     <row r="4" spans="1:36" ht="18" customHeight="1">
       <c r="A4" s="30"/>
@@ -7139,304 +7127,304 @@
       </c>
     </row>
     <row r="5" spans="1:36" ht="18" customHeight="1">
-      <c r="A5" s="57" t="s">
+      <c r="A5" s="78" t="s">
         <v>85</v>
       </c>
-      <c r="B5" s="57"/>
-      <c r="C5" s="85"/>
-      <c r="D5" s="85"/>
-      <c r="E5" s="85"/>
-      <c r="F5" s="85"/>
-      <c r="G5" s="85"/>
-      <c r="H5" s="85"/>
-      <c r="I5" s="85"/>
+      <c r="B5" s="78"/>
+      <c r="C5" s="102"/>
+      <c r="D5" s="102"/>
+      <c r="E5" s="102"/>
+      <c r="F5" s="102"/>
+      <c r="G5" s="102"/>
+      <c r="H5" s="102"/>
+      <c r="I5" s="102"/>
       <c r="J5" s="35"/>
-      <c r="K5" s="109" t="s">
+      <c r="K5" s="59" t="s">
         <v>0</v>
       </c>
-      <c r="L5" s="109"/>
-      <c r="M5" s="109"/>
-      <c r="N5" s="109"/>
-      <c r="O5" s="109"/>
-      <c r="P5" s="152"/>
-      <c r="Q5" s="153"/>
-      <c r="R5" s="153"/>
-      <c r="S5" s="153"/>
-      <c r="T5" s="153"/>
-      <c r="U5" s="153"/>
-      <c r="V5" s="153"/>
-      <c r="W5" s="153"/>
-      <c r="X5" s="153"/>
-      <c r="Y5" s="109" t="s">
+      <c r="L5" s="59"/>
+      <c r="M5" s="59"/>
+      <c r="N5" s="59"/>
+      <c r="O5" s="59"/>
+      <c r="P5" s="72"/>
+      <c r="Q5" s="73"/>
+      <c r="R5" s="73"/>
+      <c r="S5" s="73"/>
+      <c r="T5" s="73"/>
+      <c r="U5" s="73"/>
+      <c r="V5" s="73"/>
+      <c r="W5" s="73"/>
+      <c r="X5" s="73"/>
+      <c r="Y5" s="59" t="s">
         <v>48</v>
       </c>
-      <c r="Z5" s="109"/>
-      <c r="AA5" s="85"/>
-      <c r="AB5" s="85"/>
-      <c r="AC5" s="85"/>
-      <c r="AD5" s="85"/>
-      <c r="AE5" s="85"/>
-      <c r="AF5" s="85"/>
-      <c r="AG5" s="85"/>
-      <c r="AH5" s="85"/>
-      <c r="AI5" s="85"/>
-      <c r="AJ5" s="85"/>
+      <c r="Z5" s="59"/>
+      <c r="AA5" s="102"/>
+      <c r="AB5" s="102"/>
+      <c r="AC5" s="102"/>
+      <c r="AD5" s="102"/>
+      <c r="AE5" s="102"/>
+      <c r="AF5" s="102"/>
+      <c r="AG5" s="102"/>
+      <c r="AH5" s="102"/>
+      <c r="AI5" s="102"/>
+      <c r="AJ5" s="102"/>
     </row>
     <row r="6" spans="1:36" ht="18" customHeight="1">
-      <c r="A6" s="57" t="s">
+      <c r="A6" s="78" t="s">
         <v>1</v>
       </c>
-      <c r="B6" s="57"/>
-      <c r="C6" s="138"/>
-      <c r="D6" s="138"/>
-      <c r="E6" s="138"/>
-      <c r="F6" s="138"/>
-      <c r="G6" s="138"/>
-      <c r="H6" s="138"/>
-      <c r="I6" s="138"/>
+      <c r="B6" s="78"/>
+      <c r="C6" s="76"/>
+      <c r="D6" s="76"/>
+      <c r="E6" s="76"/>
+      <c r="F6" s="76"/>
+      <c r="G6" s="76"/>
+      <c r="H6" s="76"/>
+      <c r="I6" s="76"/>
       <c r="J6" s="35"/>
-      <c r="K6" s="109" t="s">
+      <c r="K6" s="59" t="s">
         <v>2</v>
       </c>
-      <c r="L6" s="109"/>
-      <c r="M6" s="109"/>
-      <c r="N6" s="109"/>
-      <c r="O6" s="109"/>
-      <c r="P6" s="159"/>
-      <c r="Q6" s="160"/>
-      <c r="R6" s="160"/>
-      <c r="S6" s="160"/>
-      <c r="T6" s="160"/>
-      <c r="U6" s="160"/>
-      <c r="V6" s="160"/>
-      <c r="W6" s="160"/>
-      <c r="X6" s="160"/>
-      <c r="Y6" s="109" t="s">
+      <c r="L6" s="59"/>
+      <c r="M6" s="59"/>
+      <c r="N6" s="59"/>
+      <c r="O6" s="59"/>
+      <c r="P6" s="60"/>
+      <c r="Q6" s="61"/>
+      <c r="R6" s="61"/>
+      <c r="S6" s="61"/>
+      <c r="T6" s="61"/>
+      <c r="U6" s="61"/>
+      <c r="V6" s="61"/>
+      <c r="W6" s="61"/>
+      <c r="X6" s="61"/>
+      <c r="Y6" s="59" t="s">
         <v>88</v>
       </c>
-      <c r="Z6" s="109"/>
-      <c r="AA6" s="109"/>
-      <c r="AB6" s="109"/>
-      <c r="AC6" s="109"/>
-      <c r="AD6" s="90"/>
-      <c r="AE6" s="90"/>
-      <c r="AF6" s="90"/>
+      <c r="Z6" s="59"/>
+      <c r="AA6" s="59"/>
+      <c r="AB6" s="59"/>
+      <c r="AC6" s="59"/>
+      <c r="AD6" s="75"/>
+      <c r="AE6" s="75"/>
+      <c r="AF6" s="75"/>
       <c r="AG6" s="44"/>
-      <c r="AH6" s="134"/>
-      <c r="AI6" s="134"/>
+      <c r="AH6" s="74"/>
+      <c r="AI6" s="74"/>
       <c r="AJ6" s="44"/>
     </row>
     <row r="7" spans="1:36" ht="18" customHeight="1">
-      <c r="A7" s="57" t="s">
+      <c r="A7" s="78" t="s">
         <v>3</v>
       </c>
-      <c r="B7" s="57"/>
-      <c r="C7" s="138"/>
-      <c r="D7" s="138"/>
-      <c r="E7" s="138"/>
-      <c r="F7" s="138"/>
-      <c r="G7" s="138"/>
-      <c r="H7" s="138"/>
-      <c r="I7" s="138"/>
+      <c r="B7" s="78"/>
+      <c r="C7" s="76"/>
+      <c r="D7" s="76"/>
+      <c r="E7" s="76"/>
+      <c r="F7" s="76"/>
+      <c r="G7" s="76"/>
+      <c r="H7" s="76"/>
+      <c r="I7" s="76"/>
       <c r="J7" s="35"/>
-      <c r="K7" s="109" t="s">
+      <c r="K7" s="59" t="s">
         <v>89</v>
       </c>
-      <c r="L7" s="109"/>
-      <c r="M7" s="109"/>
-      <c r="N7" s="109"/>
-      <c r="O7" s="109"/>
-      <c r="P7" s="90"/>
-      <c r="Q7" s="90"/>
-      <c r="R7" s="90"/>
-      <c r="S7" s="134"/>
-      <c r="T7" s="134"/>
+      <c r="L7" s="59"/>
+      <c r="M7" s="59"/>
+      <c r="N7" s="59"/>
+      <c r="O7" s="59"/>
+      <c r="P7" s="75"/>
+      <c r="Q7" s="75"/>
+      <c r="R7" s="75"/>
+      <c r="S7" s="74"/>
+      <c r="T7" s="74"/>
       <c r="U7" s="39" t="s">
         <v>4</v>
       </c>
-      <c r="V7" s="134"/>
-      <c r="W7" s="134"/>
-      <c r="X7" s="109" t="s">
+      <c r="V7" s="74"/>
+      <c r="W7" s="74"/>
+      <c r="X7" s="59" t="s">
         <v>90</v>
       </c>
-      <c r="Y7" s="109"/>
-      <c r="Z7" s="109"/>
-      <c r="AA7" s="109"/>
-      <c r="AB7" s="109"/>
-      <c r="AC7" s="90"/>
-      <c r="AD7" s="90"/>
-      <c r="AE7" s="90"/>
-      <c r="AF7" s="134"/>
-      <c r="AG7" s="134"/>
+      <c r="Y7" s="59"/>
+      <c r="Z7" s="59"/>
+      <c r="AA7" s="59"/>
+      <c r="AB7" s="59"/>
+      <c r="AC7" s="75"/>
+      <c r="AD7" s="75"/>
+      <c r="AE7" s="75"/>
+      <c r="AF7" s="74"/>
+      <c r="AG7" s="74"/>
       <c r="AH7" s="39" t="s">
         <v>4</v>
       </c>
-      <c r="AI7" s="134"/>
-      <c r="AJ7" s="134"/>
+      <c r="AI7" s="74"/>
+      <c r="AJ7" s="74"/>
     </row>
     <row r="8" spans="1:36" ht="18" customHeight="1">
-      <c r="A8" s="97" t="s">
+      <c r="A8" s="84" t="s">
         <v>5</v>
       </c>
-      <c r="B8" s="97"/>
-      <c r="C8" s="97"/>
-      <c r="D8" s="80"/>
-      <c r="E8" s="80"/>
-      <c r="F8" s="80"/>
-      <c r="G8" s="80"/>
-      <c r="H8" s="80"/>
-      <c r="I8" s="80"/>
-      <c r="J8" s="80"/>
-      <c r="K8" s="80"/>
-      <c r="L8" s="80"/>
-      <c r="M8" s="80"/>
-      <c r="N8" s="80"/>
-      <c r="O8" s="80"/>
-      <c r="P8" s="80"/>
-      <c r="Q8" s="80"/>
-      <c r="R8" s="80"/>
-      <c r="S8" s="139" t="s">
+      <c r="B8" s="84"/>
+      <c r="C8" s="84"/>
+      <c r="D8" s="53"/>
+      <c r="E8" s="53"/>
+      <c r="F8" s="53"/>
+      <c r="G8" s="53"/>
+      <c r="H8" s="53"/>
+      <c r="I8" s="53"/>
+      <c r="J8" s="53"/>
+      <c r="K8" s="53"/>
+      <c r="L8" s="53"/>
+      <c r="M8" s="53"/>
+      <c r="N8" s="53"/>
+      <c r="O8" s="53"/>
+      <c r="P8" s="53"/>
+      <c r="Q8" s="53"/>
+      <c r="R8" s="53"/>
+      <c r="S8" s="77" t="s">
         <v>49</v>
       </c>
-      <c r="T8" s="139"/>
-      <c r="U8" s="109"/>
-      <c r="V8" s="139"/>
-      <c r="W8" s="139"/>
-      <c r="X8" s="80"/>
-      <c r="Y8" s="80"/>
-      <c r="Z8" s="80"/>
-      <c r="AA8" s="80"/>
-      <c r="AB8" s="80"/>
-      <c r="AC8" s="80"/>
-      <c r="AD8" s="80"/>
-      <c r="AE8" s="80"/>
-      <c r="AF8" s="80"/>
-      <c r="AG8" s="80"/>
-      <c r="AH8" s="80"/>
-      <c r="AI8" s="80"/>
-      <c r="AJ8" s="80"/>
+      <c r="T8" s="77"/>
+      <c r="U8" s="59"/>
+      <c r="V8" s="77"/>
+      <c r="W8" s="77"/>
+      <c r="X8" s="53"/>
+      <c r="Y8" s="53"/>
+      <c r="Z8" s="53"/>
+      <c r="AA8" s="53"/>
+      <c r="AB8" s="53"/>
+      <c r="AC8" s="53"/>
+      <c r="AD8" s="53"/>
+      <c r="AE8" s="53"/>
+      <c r="AF8" s="53"/>
+      <c r="AG8" s="53"/>
+      <c r="AH8" s="53"/>
+      <c r="AI8" s="53"/>
+      <c r="AJ8" s="53"/>
     </row>
     <row r="9" spans="1:36" ht="26.4" customHeight="1">
-      <c r="A9" s="57" t="s">
+      <c r="A9" s="78" t="s">
         <v>6</v>
       </c>
-      <c r="B9" s="57"/>
-      <c r="C9" s="57"/>
-      <c r="D9" s="108"/>
-      <c r="E9" s="108"/>
-      <c r="F9" s="108"/>
-      <c r="G9" s="108"/>
-      <c r="H9" s="108"/>
-      <c r="I9" s="108"/>
-      <c r="J9" s="108"/>
-      <c r="K9" s="108"/>
-      <c r="L9" s="108"/>
-      <c r="M9" s="108"/>
-      <c r="N9" s="108"/>
-      <c r="O9" s="108"/>
-      <c r="P9" s="108"/>
-      <c r="Q9" s="108"/>
-      <c r="R9" s="108"/>
-      <c r="S9" s="109" t="s">
+      <c r="B9" s="78"/>
+      <c r="C9" s="78"/>
+      <c r="D9" s="80"/>
+      <c r="E9" s="80"/>
+      <c r="F9" s="80"/>
+      <c r="G9" s="80"/>
+      <c r="H9" s="80"/>
+      <c r="I9" s="80"/>
+      <c r="J9" s="80"/>
+      <c r="K9" s="80"/>
+      <c r="L9" s="80"/>
+      <c r="M9" s="80"/>
+      <c r="N9" s="80"/>
+      <c r="O9" s="80"/>
+      <c r="P9" s="80"/>
+      <c r="Q9" s="80"/>
+      <c r="R9" s="80"/>
+      <c r="S9" s="59" t="s">
         <v>50</v>
       </c>
-      <c r="T9" s="109"/>
-      <c r="U9" s="109"/>
-      <c r="V9" s="109"/>
-      <c r="W9" s="109"/>
-      <c r="X9" s="140"/>
-      <c r="Y9" s="108"/>
-      <c r="Z9" s="108"/>
-      <c r="AA9" s="108"/>
-      <c r="AB9" s="108"/>
-      <c r="AC9" s="108"/>
-      <c r="AD9" s="108"/>
-      <c r="AE9" s="108"/>
-      <c r="AF9" s="108"/>
-      <c r="AG9" s="108"/>
-      <c r="AH9" s="108"/>
-      <c r="AI9" s="108"/>
-      <c r="AJ9" s="108"/>
+      <c r="T9" s="59"/>
+      <c r="U9" s="59"/>
+      <c r="V9" s="59"/>
+      <c r="W9" s="59"/>
+      <c r="X9" s="79"/>
+      <c r="Y9" s="80"/>
+      <c r="Z9" s="80"/>
+      <c r="AA9" s="80"/>
+      <c r="AB9" s="80"/>
+      <c r="AC9" s="80"/>
+      <c r="AD9" s="80"/>
+      <c r="AE9" s="80"/>
+      <c r="AF9" s="80"/>
+      <c r="AG9" s="80"/>
+      <c r="AH9" s="80"/>
+      <c r="AI9" s="80"/>
+      <c r="AJ9" s="80"/>
     </row>
     <row r="10" spans="1:36" ht="5.25" customHeight="1">
-      <c r="A10" s="73"/>
-      <c r="B10" s="73"/>
-      <c r="C10" s="73"/>
-      <c r="D10" s="73"/>
-      <c r="E10" s="73"/>
-      <c r="F10" s="73"/>
-      <c r="G10" s="73"/>
-      <c r="H10" s="73"/>
-      <c r="I10" s="73"/>
-      <c r="J10" s="73"/>
-      <c r="K10" s="73"/>
-      <c r="L10" s="73"/>
-      <c r="M10" s="73"/>
-      <c r="N10" s="73"/>
-      <c r="O10" s="73"/>
-      <c r="P10" s="73"/>
-      <c r="Q10" s="73"/>
-      <c r="R10" s="73"/>
-      <c r="S10" s="73"/>
-      <c r="T10" s="73"/>
-      <c r="U10" s="73"/>
-      <c r="V10" s="73"/>
-      <c r="W10" s="73"/>
-      <c r="X10" s="73"/>
-      <c r="Y10" s="73"/>
-      <c r="Z10" s="73"/>
-      <c r="AA10" s="73"/>
-      <c r="AB10" s="73"/>
-      <c r="AC10" s="73"/>
-      <c r="AD10" s="73"/>
-      <c r="AE10" s="73"/>
-      <c r="AF10" s="73"/>
-      <c r="AG10" s="73"/>
-      <c r="AH10" s="73"/>
-      <c r="AI10" s="73"/>
-      <c r="AJ10" s="73"/>
+      <c r="A10" s="85"/>
+      <c r="B10" s="85"/>
+      <c r="C10" s="85"/>
+      <c r="D10" s="85"/>
+      <c r="E10" s="85"/>
+      <c r="F10" s="85"/>
+      <c r="G10" s="85"/>
+      <c r="H10" s="85"/>
+      <c r="I10" s="85"/>
+      <c r="J10" s="85"/>
+      <c r="K10" s="85"/>
+      <c r="L10" s="85"/>
+      <c r="M10" s="85"/>
+      <c r="N10" s="85"/>
+      <c r="O10" s="85"/>
+      <c r="P10" s="85"/>
+      <c r="Q10" s="85"/>
+      <c r="R10" s="85"/>
+      <c r="S10" s="85"/>
+      <c r="T10" s="85"/>
+      <c r="U10" s="85"/>
+      <c r="V10" s="85"/>
+      <c r="W10" s="85"/>
+      <c r="X10" s="85"/>
+      <c r="Y10" s="85"/>
+      <c r="Z10" s="85"/>
+      <c r="AA10" s="85"/>
+      <c r="AB10" s="85"/>
+      <c r="AC10" s="85"/>
+      <c r="AD10" s="85"/>
+      <c r="AE10" s="85"/>
+      <c r="AF10" s="85"/>
+      <c r="AG10" s="85"/>
+      <c r="AH10" s="85"/>
+      <c r="AI10" s="85"/>
+      <c r="AJ10" s="85"/>
     </row>
     <row r="11" spans="1:36" ht="14.25" customHeight="1">
-      <c r="A11" s="156" t="s">
+      <c r="A11" s="56" t="s">
         <v>7</v>
       </c>
-      <c r="B11" s="157"/>
-      <c r="C11" s="157"/>
-      <c r="D11" s="157"/>
-      <c r="E11" s="157"/>
-      <c r="F11" s="157"/>
-      <c r="G11" s="157"/>
-      <c r="H11" s="157"/>
-      <c r="I11" s="157"/>
-      <c r="J11" s="157"/>
-      <c r="K11" s="157"/>
-      <c r="L11" s="157"/>
-      <c r="M11" s="157"/>
-      <c r="N11" s="157"/>
-      <c r="O11" s="157"/>
-      <c r="P11" s="158"/>
-      <c r="Q11" s="141" t="s">
+      <c r="B11" s="57"/>
+      <c r="C11" s="57"/>
+      <c r="D11" s="57"/>
+      <c r="E11" s="57"/>
+      <c r="F11" s="57"/>
+      <c r="G11" s="57"/>
+      <c r="H11" s="57"/>
+      <c r="I11" s="57"/>
+      <c r="J11" s="57"/>
+      <c r="K11" s="57"/>
+      <c r="L11" s="57"/>
+      <c r="M11" s="57"/>
+      <c r="N11" s="57"/>
+      <c r="O11" s="57"/>
+      <c r="P11" s="58"/>
+      <c r="Q11" s="81" t="s">
         <v>8</v>
       </c>
-      <c r="R11" s="142"/>
-      <c r="S11" s="142"/>
-      <c r="T11" s="142"/>
-      <c r="U11" s="142"/>
-      <c r="V11" s="142"/>
-      <c r="W11" s="142"/>
-      <c r="X11" s="142"/>
-      <c r="Y11" s="142"/>
-      <c r="Z11" s="142"/>
-      <c r="AA11" s="142"/>
-      <c r="AB11" s="142"/>
-      <c r="AC11" s="142"/>
-      <c r="AD11" s="142"/>
-      <c r="AE11" s="142"/>
-      <c r="AF11" s="142"/>
-      <c r="AG11" s="142"/>
-      <c r="AH11" s="142"/>
-      <c r="AI11" s="142"/>
-      <c r="AJ11" s="143"/>
+      <c r="R11" s="82"/>
+      <c r="S11" s="82"/>
+      <c r="T11" s="82"/>
+      <c r="U11" s="82"/>
+      <c r="V11" s="82"/>
+      <c r="W11" s="82"/>
+      <c r="X11" s="82"/>
+      <c r="Y11" s="82"/>
+      <c r="Z11" s="82"/>
+      <c r="AA11" s="82"/>
+      <c r="AB11" s="82"/>
+      <c r="AC11" s="82"/>
+      <c r="AD11" s="82"/>
+      <c r="AE11" s="82"/>
+      <c r="AF11" s="82"/>
+      <c r="AG11" s="82"/>
+      <c r="AH11" s="82"/>
+      <c r="AI11" s="82"/>
+      <c r="AJ11" s="83"/>
     </row>
     <row r="12" spans="1:36" ht="18" customHeight="1">
       <c r="A12" s="2"/>
@@ -7545,150 +7533,150 @@
       <c r="AJ13" s="23"/>
     </row>
     <row r="14" spans="1:36" ht="16.5" customHeight="1">
-      <c r="A14" s="126" t="s">
+      <c r="A14" s="108" t="s">
         <v>86</v>
       </c>
-      <c r="B14" s="127"/>
-      <c r="C14" s="127"/>
-      <c r="D14" s="127"/>
-      <c r="E14" s="127"/>
-      <c r="F14" s="127"/>
-      <c r="G14" s="127"/>
-      <c r="H14" s="127"/>
-      <c r="I14" s="128"/>
-      <c r="J14" s="129"/>
-      <c r="K14" s="129"/>
-      <c r="L14" s="129"/>
-      <c r="M14" s="129"/>
-      <c r="N14" s="129"/>
-      <c r="O14" s="129"/>
-      <c r="P14" s="129"/>
-      <c r="Q14" s="129"/>
-      <c r="R14" s="129"/>
-      <c r="S14" s="129"/>
-      <c r="T14" s="129"/>
-      <c r="U14" s="129"/>
-      <c r="V14" s="129"/>
-      <c r="W14" s="129"/>
-      <c r="X14" s="129"/>
-      <c r="Y14" s="129"/>
-      <c r="Z14" s="129"/>
-      <c r="AA14" s="129"/>
-      <c r="AB14" s="129"/>
-      <c r="AC14" s="129"/>
-      <c r="AD14" s="129"/>
-      <c r="AE14" s="129"/>
-      <c r="AF14" s="129"/>
-      <c r="AG14" s="129"/>
-      <c r="AH14" s="129"/>
-      <c r="AI14" s="129"/>
-      <c r="AJ14" s="130"/>
+      <c r="B14" s="109"/>
+      <c r="C14" s="109"/>
+      <c r="D14" s="109"/>
+      <c r="E14" s="109"/>
+      <c r="F14" s="109"/>
+      <c r="G14" s="109"/>
+      <c r="H14" s="109"/>
+      <c r="I14" s="110"/>
+      <c r="J14" s="111"/>
+      <c r="K14" s="111"/>
+      <c r="L14" s="111"/>
+      <c r="M14" s="111"/>
+      <c r="N14" s="111"/>
+      <c r="O14" s="111"/>
+      <c r="P14" s="111"/>
+      <c r="Q14" s="111"/>
+      <c r="R14" s="111"/>
+      <c r="S14" s="111"/>
+      <c r="T14" s="111"/>
+      <c r="U14" s="111"/>
+      <c r="V14" s="111"/>
+      <c r="W14" s="111"/>
+      <c r="X14" s="111"/>
+      <c r="Y14" s="111"/>
+      <c r="Z14" s="111"/>
+      <c r="AA14" s="111"/>
+      <c r="AB14" s="111"/>
+      <c r="AC14" s="111"/>
+      <c r="AD14" s="111"/>
+      <c r="AE14" s="111"/>
+      <c r="AF14" s="111"/>
+      <c r="AG14" s="111"/>
+      <c r="AH14" s="111"/>
+      <c r="AI14" s="111"/>
+      <c r="AJ14" s="112"/>
     </row>
     <row r="15" spans="1:36" ht="3" customHeight="1">
-      <c r="A15" s="131">
+      <c r="A15" s="113">
         <v>2</v>
       </c>
-      <c r="B15" s="132"/>
-      <c r="C15" s="132"/>
-      <c r="D15" s="132"/>
-      <c r="E15" s="132"/>
-      <c r="F15" s="132"/>
-      <c r="G15" s="132"/>
-      <c r="H15" s="132"/>
-      <c r="I15" s="132"/>
-      <c r="J15" s="132"/>
-      <c r="K15" s="132"/>
-      <c r="L15" s="132"/>
-      <c r="M15" s="132"/>
-      <c r="N15" s="132"/>
-      <c r="O15" s="132"/>
-      <c r="P15" s="132"/>
-      <c r="Q15" s="132"/>
-      <c r="R15" s="132"/>
-      <c r="S15" s="132"/>
-      <c r="T15" s="132"/>
-      <c r="U15" s="132"/>
-      <c r="V15" s="132"/>
-      <c r="W15" s="132"/>
-      <c r="X15" s="132"/>
-      <c r="Y15" s="132"/>
-      <c r="Z15" s="132"/>
-      <c r="AA15" s="132"/>
-      <c r="AB15" s="132"/>
-      <c r="AC15" s="132"/>
-      <c r="AD15" s="132"/>
-      <c r="AE15" s="132"/>
-      <c r="AF15" s="132"/>
-      <c r="AG15" s="132"/>
-      <c r="AH15" s="132"/>
-      <c r="AI15" s="132"/>
-      <c r="AJ15" s="133"/>
+      <c r="B15" s="114"/>
+      <c r="C15" s="114"/>
+      <c r="D15" s="114"/>
+      <c r="E15" s="114"/>
+      <c r="F15" s="114"/>
+      <c r="G15" s="114"/>
+      <c r="H15" s="114"/>
+      <c r="I15" s="114"/>
+      <c r="J15" s="114"/>
+      <c r="K15" s="114"/>
+      <c r="L15" s="114"/>
+      <c r="M15" s="114"/>
+      <c r="N15" s="114"/>
+      <c r="O15" s="114"/>
+      <c r="P15" s="114"/>
+      <c r="Q15" s="114"/>
+      <c r="R15" s="114"/>
+      <c r="S15" s="114"/>
+      <c r="T15" s="114"/>
+      <c r="U15" s="114"/>
+      <c r="V15" s="114"/>
+      <c r="W15" s="114"/>
+      <c r="X15" s="114"/>
+      <c r="Y15" s="114"/>
+      <c r="Z15" s="114"/>
+      <c r="AA15" s="114"/>
+      <c r="AB15" s="114"/>
+      <c r="AC15" s="114"/>
+      <c r="AD15" s="114"/>
+      <c r="AE15" s="114"/>
+      <c r="AF15" s="114"/>
+      <c r="AG15" s="114"/>
+      <c r="AH15" s="114"/>
+      <c r="AI15" s="114"/>
+      <c r="AJ15" s="115"/>
     </row>
     <row r="16" spans="1:36" ht="12.75" customHeight="1">
-      <c r="A16" s="147" t="s">
+      <c r="A16" s="67" t="s">
         <v>9</v>
       </c>
-      <c r="B16" s="148"/>
-      <c r="C16" s="148"/>
-      <c r="D16" s="148"/>
-      <c r="E16" s="148"/>
-      <c r="F16" s="148"/>
-      <c r="G16" s="148"/>
-      <c r="H16" s="148"/>
-      <c r="I16" s="148"/>
-      <c r="J16" s="148"/>
-      <c r="K16" s="148"/>
-      <c r="L16" s="148"/>
-      <c r="M16" s="148"/>
-      <c r="N16" s="148"/>
-      <c r="O16" s="148"/>
-      <c r="P16" s="148"/>
-      <c r="Q16" s="148"/>
-      <c r="R16" s="148"/>
-      <c r="S16" s="148"/>
-      <c r="T16" s="149"/>
-      <c r="U16" s="135" t="s">
+      <c r="B16" s="68"/>
+      <c r="C16" s="68"/>
+      <c r="D16" s="68"/>
+      <c r="E16" s="68"/>
+      <c r="F16" s="68"/>
+      <c r="G16" s="68"/>
+      <c r="H16" s="68"/>
+      <c r="I16" s="68"/>
+      <c r="J16" s="68"/>
+      <c r="K16" s="68"/>
+      <c r="L16" s="68"/>
+      <c r="M16" s="68"/>
+      <c r="N16" s="68"/>
+      <c r="O16" s="68"/>
+      <c r="P16" s="68"/>
+      <c r="Q16" s="68"/>
+      <c r="R16" s="68"/>
+      <c r="S16" s="68"/>
+      <c r="T16" s="69"/>
+      <c r="U16" s="116" t="s">
         <v>73</v>
       </c>
-      <c r="V16" s="136"/>
-      <c r="W16" s="136"/>
-      <c r="X16" s="136"/>
-      <c r="Y16" s="136"/>
-      <c r="Z16" s="136"/>
-      <c r="AA16" s="136"/>
-      <c r="AB16" s="136"/>
-      <c r="AC16" s="136"/>
-      <c r="AD16" s="137"/>
-      <c r="AE16" s="144" t="s">
+      <c r="V16" s="117"/>
+      <c r="W16" s="117"/>
+      <c r="X16" s="117"/>
+      <c r="Y16" s="117"/>
+      <c r="Z16" s="117"/>
+      <c r="AA16" s="117"/>
+      <c r="AB16" s="117"/>
+      <c r="AC16" s="117"/>
+      <c r="AD16" s="118"/>
+      <c r="AE16" s="64" t="s">
         <v>10</v>
       </c>
-      <c r="AF16" s="145"/>
-      <c r="AG16" s="145"/>
-      <c r="AH16" s="145"/>
-      <c r="AI16" s="145"/>
-      <c r="AJ16" s="146"/>
+      <c r="AF16" s="65"/>
+      <c r="AG16" s="65"/>
+      <c r="AH16" s="65"/>
+      <c r="AI16" s="65"/>
+      <c r="AJ16" s="66"/>
     </row>
     <row r="17" spans="1:36" ht="18" customHeight="1">
-      <c r="A17" s="119"/>
-      <c r="B17" s="120"/>
-      <c r="C17" s="120"/>
-      <c r="D17" s="120"/>
-      <c r="E17" s="120"/>
-      <c r="F17" s="120"/>
-      <c r="G17" s="120"/>
-      <c r="H17" s="120"/>
-      <c r="I17" s="120"/>
-      <c r="J17" s="120"/>
-      <c r="K17" s="120"/>
-      <c r="L17" s="120"/>
-      <c r="M17" s="120"/>
-      <c r="N17" s="120"/>
-      <c r="O17" s="120"/>
-      <c r="P17" s="120"/>
-      <c r="Q17" s="120"/>
-      <c r="R17" s="120"/>
-      <c r="S17" s="120"/>
-      <c r="T17" s="121"/>
+      <c r="A17" s="96"/>
+      <c r="B17" s="97"/>
+      <c r="C17" s="97"/>
+      <c r="D17" s="97"/>
+      <c r="E17" s="97"/>
+      <c r="F17" s="97"/>
+      <c r="G17" s="97"/>
+      <c r="H17" s="97"/>
+      <c r="I17" s="97"/>
+      <c r="J17" s="97"/>
+      <c r="K17" s="97"/>
+      <c r="L17" s="97"/>
+      <c r="M17" s="97"/>
+      <c r="N17" s="97"/>
+      <c r="O17" s="97"/>
+      <c r="P17" s="97"/>
+      <c r="Q17" s="97"/>
+      <c r="R17" s="97"/>
+      <c r="S17" s="97"/>
+      <c r="T17" s="98"/>
       <c r="U17" s="25"/>
       <c r="V17" s="17" t="s">
         <v>64</v>
@@ -7704,32 +7692,32 @@
       <c r="AE17" s="14" t="s">
         <v>11</v>
       </c>
-      <c r="AF17" s="101"/>
-      <c r="AG17" s="101"/>
-      <c r="AI17" s="101"/>
-      <c r="AJ17" s="125"/>
+      <c r="AF17" s="103"/>
+      <c r="AG17" s="103"/>
+      <c r="AI17" s="103"/>
+      <c r="AJ17" s="107"/>
     </row>
     <row r="18" spans="1:36" ht="18" customHeight="1">
-      <c r="A18" s="119"/>
-      <c r="B18" s="120"/>
-      <c r="C18" s="120"/>
-      <c r="D18" s="120"/>
-      <c r="E18" s="120"/>
-      <c r="F18" s="120"/>
-      <c r="G18" s="120"/>
-      <c r="H18" s="120"/>
-      <c r="I18" s="120"/>
-      <c r="J18" s="120"/>
-      <c r="K18" s="120"/>
-      <c r="L18" s="120"/>
-      <c r="M18" s="120"/>
-      <c r="N18" s="120"/>
-      <c r="O18" s="120"/>
-      <c r="P18" s="120"/>
-      <c r="Q18" s="120"/>
-      <c r="R18" s="120"/>
-      <c r="S18" s="120"/>
-      <c r="T18" s="121"/>
+      <c r="A18" s="96"/>
+      <c r="B18" s="97"/>
+      <c r="C18" s="97"/>
+      <c r="D18" s="97"/>
+      <c r="E18" s="97"/>
+      <c r="F18" s="97"/>
+      <c r="G18" s="97"/>
+      <c r="H18" s="97"/>
+      <c r="I18" s="97"/>
+      <c r="J18" s="97"/>
+      <c r="K18" s="97"/>
+      <c r="L18" s="97"/>
+      <c r="M18" s="97"/>
+      <c r="N18" s="97"/>
+      <c r="O18" s="97"/>
+      <c r="P18" s="97"/>
+      <c r="Q18" s="97"/>
+      <c r="R18" s="97"/>
+      <c r="S18" s="97"/>
+      <c r="T18" s="98"/>
       <c r="U18" s="26"/>
       <c r="V18" s="17" t="s">
         <v>65</v>
@@ -7745,32 +7733,32 @@
       <c r="AE18" s="14" t="s">
         <v>12</v>
       </c>
-      <c r="AF18" s="101"/>
-      <c r="AG18" s="101"/>
-      <c r="AI18" s="101"/>
-      <c r="AJ18" s="125"/>
+      <c r="AF18" s="103"/>
+      <c r="AG18" s="103"/>
+      <c r="AI18" s="103"/>
+      <c r="AJ18" s="107"/>
     </row>
     <row r="19" spans="1:36" ht="18" customHeight="1">
-      <c r="A19" s="119"/>
-      <c r="B19" s="120"/>
-      <c r="C19" s="120"/>
-      <c r="D19" s="120"/>
-      <c r="E19" s="120"/>
-      <c r="F19" s="120"/>
-      <c r="G19" s="120"/>
-      <c r="H19" s="120"/>
-      <c r="I19" s="120"/>
-      <c r="J19" s="120"/>
-      <c r="K19" s="120"/>
-      <c r="L19" s="120"/>
-      <c r="M19" s="120"/>
-      <c r="N19" s="120"/>
-      <c r="O19" s="120"/>
-      <c r="P19" s="120"/>
-      <c r="Q19" s="120"/>
-      <c r="R19" s="120"/>
-      <c r="S19" s="120"/>
-      <c r="T19" s="121"/>
+      <c r="A19" s="96"/>
+      <c r="B19" s="97"/>
+      <c r="C19" s="97"/>
+      <c r="D19" s="97"/>
+      <c r="E19" s="97"/>
+      <c r="F19" s="97"/>
+      <c r="G19" s="97"/>
+      <c r="H19" s="97"/>
+      <c r="I19" s="97"/>
+      <c r="J19" s="97"/>
+      <c r="K19" s="97"/>
+      <c r="L19" s="97"/>
+      <c r="M19" s="97"/>
+      <c r="N19" s="97"/>
+      <c r="O19" s="97"/>
+      <c r="P19" s="97"/>
+      <c r="Q19" s="97"/>
+      <c r="R19" s="97"/>
+      <c r="S19" s="97"/>
+      <c r="T19" s="98"/>
       <c r="U19" s="26"/>
       <c r="V19" s="17" t="s">
         <v>66</v>
@@ -7786,32 +7774,32 @@
       <c r="AE19" s="14" t="s">
         <v>13</v>
       </c>
-      <c r="AF19" s="101"/>
-      <c r="AG19" s="101"/>
-      <c r="AI19" s="101"/>
-      <c r="AJ19" s="125"/>
+      <c r="AF19" s="103"/>
+      <c r="AG19" s="103"/>
+      <c r="AI19" s="103"/>
+      <c r="AJ19" s="107"/>
     </row>
     <row r="20" spans="1:36" ht="3.75" customHeight="1">
-      <c r="A20" s="122"/>
-      <c r="B20" s="123"/>
-      <c r="C20" s="123"/>
-      <c r="D20" s="123"/>
-      <c r="E20" s="123"/>
-      <c r="F20" s="123"/>
-      <c r="G20" s="123"/>
-      <c r="H20" s="123"/>
-      <c r="I20" s="123"/>
-      <c r="J20" s="123"/>
-      <c r="K20" s="123"/>
-      <c r="L20" s="123"/>
-      <c r="M20" s="123"/>
-      <c r="N20" s="123"/>
-      <c r="O20" s="123"/>
-      <c r="P20" s="123"/>
-      <c r="Q20" s="123"/>
-      <c r="R20" s="123"/>
-      <c r="S20" s="123"/>
-      <c r="T20" s="124"/>
+      <c r="A20" s="99"/>
+      <c r="B20" s="100"/>
+      <c r="C20" s="100"/>
+      <c r="D20" s="100"/>
+      <c r="E20" s="100"/>
+      <c r="F20" s="100"/>
+      <c r="G20" s="100"/>
+      <c r="H20" s="100"/>
+      <c r="I20" s="100"/>
+      <c r="J20" s="100"/>
+      <c r="K20" s="100"/>
+      <c r="L20" s="100"/>
+      <c r="M20" s="100"/>
+      <c r="N20" s="100"/>
+      <c r="O20" s="100"/>
+      <c r="P20" s="100"/>
+      <c r="Q20" s="100"/>
+      <c r="R20" s="100"/>
+      <c r="S20" s="100"/>
+      <c r="T20" s="101"/>
       <c r="U20" s="27"/>
       <c r="V20" s="16"/>
       <c r="W20" s="7"/>
@@ -7870,80 +7858,80 @@
       <c r="AJ21" s="47"/>
     </row>
     <row r="22" spans="1:36" ht="16.5" customHeight="1">
-      <c r="A22" s="113"/>
-      <c r="B22" s="114"/>
-      <c r="C22" s="114"/>
-      <c r="D22" s="114"/>
-      <c r="E22" s="114"/>
-      <c r="F22" s="114"/>
-      <c r="G22" s="114"/>
-      <c r="H22" s="114"/>
-      <c r="I22" s="114"/>
-      <c r="J22" s="114"/>
-      <c r="K22" s="114"/>
-      <c r="L22" s="114"/>
-      <c r="M22" s="114"/>
-      <c r="N22" s="114"/>
-      <c r="O22" s="114"/>
-      <c r="P22" s="114"/>
-      <c r="Q22" s="114"/>
-      <c r="R22" s="114"/>
-      <c r="S22" s="114"/>
-      <c r="T22" s="114"/>
-      <c r="U22" s="114"/>
-      <c r="V22" s="114"/>
-      <c r="W22" s="114"/>
-      <c r="X22" s="114"/>
-      <c r="Y22" s="114"/>
-      <c r="Z22" s="114"/>
-      <c r="AA22" s="114"/>
-      <c r="AB22" s="114"/>
-      <c r="AC22" s="114"/>
-      <c r="AD22" s="114"/>
-      <c r="AE22" s="114"/>
-      <c r="AF22" s="114"/>
-      <c r="AG22" s="114"/>
-      <c r="AH22" s="114"/>
-      <c r="AI22" s="114"/>
-      <c r="AJ22" s="115"/>
+      <c r="A22" s="90"/>
+      <c r="B22" s="91"/>
+      <c r="C22" s="91"/>
+      <c r="D22" s="91"/>
+      <c r="E22" s="91"/>
+      <c r="F22" s="91"/>
+      <c r="G22" s="91"/>
+      <c r="H22" s="91"/>
+      <c r="I22" s="91"/>
+      <c r="J22" s="91"/>
+      <c r="K22" s="91"/>
+      <c r="L22" s="91"/>
+      <c r="M22" s="91"/>
+      <c r="N22" s="91"/>
+      <c r="O22" s="91"/>
+      <c r="P22" s="91"/>
+      <c r="Q22" s="91"/>
+      <c r="R22" s="91"/>
+      <c r="S22" s="91"/>
+      <c r="T22" s="91"/>
+      <c r="U22" s="91"/>
+      <c r="V22" s="91"/>
+      <c r="W22" s="91"/>
+      <c r="X22" s="91"/>
+      <c r="Y22" s="91"/>
+      <c r="Z22" s="91"/>
+      <c r="AA22" s="91"/>
+      <c r="AB22" s="91"/>
+      <c r="AC22" s="91"/>
+      <c r="AD22" s="91"/>
+      <c r="AE22" s="91"/>
+      <c r="AF22" s="91"/>
+      <c r="AG22" s="91"/>
+      <c r="AH22" s="91"/>
+      <c r="AI22" s="91"/>
+      <c r="AJ22" s="92"/>
     </row>
     <row r="23" spans="1:36" ht="16.5" customHeight="1">
-      <c r="A23" s="116"/>
-      <c r="B23" s="117"/>
-      <c r="C23" s="117"/>
-      <c r="D23" s="117"/>
-      <c r="E23" s="117"/>
-      <c r="F23" s="117"/>
-      <c r="G23" s="117"/>
-      <c r="H23" s="117"/>
-      <c r="I23" s="117"/>
-      <c r="J23" s="117"/>
-      <c r="K23" s="117"/>
-      <c r="L23" s="117"/>
-      <c r="M23" s="117"/>
-      <c r="N23" s="117"/>
-      <c r="O23" s="117"/>
-      <c r="P23" s="117"/>
-      <c r="Q23" s="117"/>
-      <c r="R23" s="117"/>
-      <c r="S23" s="117"/>
-      <c r="T23" s="117"/>
-      <c r="U23" s="117"/>
-      <c r="V23" s="117"/>
-      <c r="W23" s="117"/>
-      <c r="X23" s="117"/>
-      <c r="Y23" s="117"/>
-      <c r="Z23" s="117"/>
-      <c r="AA23" s="117"/>
-      <c r="AB23" s="117"/>
-      <c r="AC23" s="117"/>
-      <c r="AD23" s="117"/>
-      <c r="AE23" s="117"/>
-      <c r="AF23" s="117"/>
-      <c r="AG23" s="117"/>
-      <c r="AH23" s="117"/>
-      <c r="AI23" s="117"/>
-      <c r="AJ23" s="118"/>
+      <c r="A23" s="93"/>
+      <c r="B23" s="94"/>
+      <c r="C23" s="94"/>
+      <c r="D23" s="94"/>
+      <c r="E23" s="94"/>
+      <c r="F23" s="94"/>
+      <c r="G23" s="94"/>
+      <c r="H23" s="94"/>
+      <c r="I23" s="94"/>
+      <c r="J23" s="94"/>
+      <c r="K23" s="94"/>
+      <c r="L23" s="94"/>
+      <c r="M23" s="94"/>
+      <c r="N23" s="94"/>
+      <c r="O23" s="94"/>
+      <c r="P23" s="94"/>
+      <c r="Q23" s="94"/>
+      <c r="R23" s="94"/>
+      <c r="S23" s="94"/>
+      <c r="T23" s="94"/>
+      <c r="U23" s="94"/>
+      <c r="V23" s="94"/>
+      <c r="W23" s="94"/>
+      <c r="X23" s="94"/>
+      <c r="Y23" s="94"/>
+      <c r="Z23" s="94"/>
+      <c r="AA23" s="94"/>
+      <c r="AB23" s="94"/>
+      <c r="AC23" s="94"/>
+      <c r="AD23" s="94"/>
+      <c r="AE23" s="94"/>
+      <c r="AF23" s="94"/>
+      <c r="AG23" s="94"/>
+      <c r="AH23" s="94"/>
+      <c r="AI23" s="94"/>
+      <c r="AJ23" s="95"/>
     </row>
     <row r="24" spans="1:36" ht="12.75" customHeight="1">
       <c r="A24" s="46" t="s">
@@ -7986,42 +7974,42 @@
       <c r="AJ24" s="47"/>
     </row>
     <row r="25" spans="1:36" ht="18" customHeight="1">
-      <c r="A25" s="110"/>
-      <c r="B25" s="111"/>
-      <c r="C25" s="111"/>
-      <c r="D25" s="111"/>
-      <c r="E25" s="111"/>
-      <c r="F25" s="111"/>
-      <c r="G25" s="111"/>
-      <c r="H25" s="111"/>
-      <c r="I25" s="111"/>
-      <c r="J25" s="111"/>
-      <c r="K25" s="111"/>
-      <c r="L25" s="111"/>
-      <c r="M25" s="111"/>
-      <c r="N25" s="111"/>
-      <c r="O25" s="111"/>
-      <c r="P25" s="111"/>
-      <c r="Q25" s="111"/>
-      <c r="R25" s="111"/>
-      <c r="S25" s="111"/>
-      <c r="T25" s="111"/>
-      <c r="U25" s="111"/>
-      <c r="V25" s="111"/>
-      <c r="W25" s="111"/>
-      <c r="X25" s="111"/>
-      <c r="Y25" s="111"/>
-      <c r="Z25" s="111"/>
-      <c r="AA25" s="111"/>
-      <c r="AB25" s="111"/>
-      <c r="AC25" s="111"/>
-      <c r="AD25" s="111"/>
-      <c r="AE25" s="111"/>
-      <c r="AF25" s="111"/>
-      <c r="AG25" s="111"/>
-      <c r="AH25" s="111"/>
-      <c r="AI25" s="111"/>
-      <c r="AJ25" s="112"/>
+      <c r="A25" s="87"/>
+      <c r="B25" s="88"/>
+      <c r="C25" s="88"/>
+      <c r="D25" s="88"/>
+      <c r="E25" s="88"/>
+      <c r="F25" s="88"/>
+      <c r="G25" s="88"/>
+      <c r="H25" s="88"/>
+      <c r="I25" s="88"/>
+      <c r="J25" s="88"/>
+      <c r="K25" s="88"/>
+      <c r="L25" s="88"/>
+      <c r="M25" s="88"/>
+      <c r="N25" s="88"/>
+      <c r="O25" s="88"/>
+      <c r="P25" s="88"/>
+      <c r="Q25" s="88"/>
+      <c r="R25" s="88"/>
+      <c r="S25" s="88"/>
+      <c r="T25" s="88"/>
+      <c r="U25" s="88"/>
+      <c r="V25" s="88"/>
+      <c r="W25" s="88"/>
+      <c r="X25" s="88"/>
+      <c r="Y25" s="88"/>
+      <c r="Z25" s="88"/>
+      <c r="AA25" s="88"/>
+      <c r="AB25" s="88"/>
+      <c r="AC25" s="88"/>
+      <c r="AD25" s="88"/>
+      <c r="AE25" s="88"/>
+      <c r="AF25" s="88"/>
+      <c r="AG25" s="88"/>
+      <c r="AH25" s="88"/>
+      <c r="AI25" s="88"/>
+      <c r="AJ25" s="89"/>
     </row>
     <row r="26" spans="1:36" ht="12.75" customHeight="1">
       <c r="A26" s="46" t="s">
@@ -8064,137 +8052,137 @@
       <c r="AJ26" s="47"/>
     </row>
     <row r="27" spans="1:36" ht="15" customHeight="1">
-      <c r="A27" s="59"/>
-      <c r="B27" s="60"/>
-      <c r="C27" s="60"/>
-      <c r="D27" s="60"/>
-      <c r="E27" s="60"/>
-      <c r="F27" s="60"/>
-      <c r="G27" s="60"/>
-      <c r="H27" s="60"/>
-      <c r="I27" s="60"/>
-      <c r="J27" s="60"/>
-      <c r="K27" s="60"/>
-      <c r="L27" s="60"/>
-      <c r="M27" s="60"/>
-      <c r="N27" s="60"/>
-      <c r="O27" s="60"/>
-      <c r="P27" s="60"/>
-      <c r="Q27" s="60"/>
-      <c r="R27" s="60"/>
-      <c r="S27" s="60"/>
-      <c r="T27" s="60"/>
-      <c r="U27" s="60"/>
-      <c r="V27" s="60"/>
-      <c r="W27" s="60"/>
-      <c r="X27" s="60"/>
-      <c r="Y27" s="60"/>
-      <c r="Z27" s="60"/>
-      <c r="AA27" s="60"/>
-      <c r="AB27" s="60"/>
-      <c r="AC27" s="60"/>
-      <c r="AD27" s="60"/>
-      <c r="AE27" s="60"/>
-      <c r="AF27" s="60"/>
-      <c r="AG27" s="60"/>
-      <c r="AH27" s="60"/>
-      <c r="AI27" s="60"/>
-      <c r="AJ27" s="61"/>
+      <c r="A27" s="146"/>
+      <c r="B27" s="147"/>
+      <c r="C27" s="147"/>
+      <c r="D27" s="147"/>
+      <c r="E27" s="147"/>
+      <c r="F27" s="147"/>
+      <c r="G27" s="147"/>
+      <c r="H27" s="147"/>
+      <c r="I27" s="147"/>
+      <c r="J27" s="147"/>
+      <c r="K27" s="147"/>
+      <c r="L27" s="147"/>
+      <c r="M27" s="147"/>
+      <c r="N27" s="147"/>
+      <c r="O27" s="147"/>
+      <c r="P27" s="147"/>
+      <c r="Q27" s="147"/>
+      <c r="R27" s="147"/>
+      <c r="S27" s="147"/>
+      <c r="T27" s="147"/>
+      <c r="U27" s="147"/>
+      <c r="V27" s="147"/>
+      <c r="W27" s="147"/>
+      <c r="X27" s="147"/>
+      <c r="Y27" s="147"/>
+      <c r="Z27" s="147"/>
+      <c r="AA27" s="147"/>
+      <c r="AB27" s="147"/>
+      <c r="AC27" s="147"/>
+      <c r="AD27" s="147"/>
+      <c r="AE27" s="147"/>
+      <c r="AF27" s="147"/>
+      <c r="AG27" s="147"/>
+      <c r="AH27" s="147"/>
+      <c r="AI27" s="147"/>
+      <c r="AJ27" s="148"/>
     </row>
     <row r="28" spans="1:36" ht="15" customHeight="1">
-      <c r="A28" s="62"/>
-      <c r="B28" s="60"/>
-      <c r="C28" s="60"/>
-      <c r="D28" s="60"/>
-      <c r="E28" s="60"/>
-      <c r="F28" s="60"/>
-      <c r="G28" s="60"/>
-      <c r="H28" s="60"/>
-      <c r="I28" s="60"/>
-      <c r="J28" s="60"/>
-      <c r="K28" s="60"/>
-      <c r="L28" s="60"/>
-      <c r="M28" s="60"/>
-      <c r="N28" s="60"/>
-      <c r="O28" s="60"/>
-      <c r="P28" s="60"/>
-      <c r="Q28" s="60"/>
-      <c r="R28" s="60"/>
-      <c r="S28" s="60"/>
-      <c r="T28" s="60"/>
-      <c r="U28" s="60"/>
-      <c r="V28" s="60"/>
-      <c r="W28" s="60"/>
-      <c r="X28" s="60"/>
-      <c r="Y28" s="60"/>
-      <c r="Z28" s="60"/>
-      <c r="AA28" s="60"/>
-      <c r="AB28" s="60"/>
-      <c r="AC28" s="60"/>
-      <c r="AD28" s="60"/>
-      <c r="AE28" s="60"/>
-      <c r="AF28" s="60"/>
-      <c r="AG28" s="60"/>
-      <c r="AH28" s="60"/>
-      <c r="AI28" s="60"/>
-      <c r="AJ28" s="61"/>
+      <c r="A28" s="149"/>
+      <c r="B28" s="147"/>
+      <c r="C28" s="147"/>
+      <c r="D28" s="147"/>
+      <c r="E28" s="147"/>
+      <c r="F28" s="147"/>
+      <c r="G28" s="147"/>
+      <c r="H28" s="147"/>
+      <c r="I28" s="147"/>
+      <c r="J28" s="147"/>
+      <c r="K28" s="147"/>
+      <c r="L28" s="147"/>
+      <c r="M28" s="147"/>
+      <c r="N28" s="147"/>
+      <c r="O28" s="147"/>
+      <c r="P28" s="147"/>
+      <c r="Q28" s="147"/>
+      <c r="R28" s="147"/>
+      <c r="S28" s="147"/>
+      <c r="T28" s="147"/>
+      <c r="U28" s="147"/>
+      <c r="V28" s="147"/>
+      <c r="W28" s="147"/>
+      <c r="X28" s="147"/>
+      <c r="Y28" s="147"/>
+      <c r="Z28" s="147"/>
+      <c r="AA28" s="147"/>
+      <c r="AB28" s="147"/>
+      <c r="AC28" s="147"/>
+      <c r="AD28" s="147"/>
+      <c r="AE28" s="147"/>
+      <c r="AF28" s="147"/>
+      <c r="AG28" s="147"/>
+      <c r="AH28" s="147"/>
+      <c r="AI28" s="147"/>
+      <c r="AJ28" s="148"/>
     </row>
     <row r="29" spans="1:36" ht="217.2" customHeight="1">
-      <c r="A29" s="63"/>
-      <c r="B29" s="64"/>
-      <c r="C29" s="64"/>
-      <c r="D29" s="64"/>
-      <c r="E29" s="64"/>
-      <c r="F29" s="64"/>
-      <c r="G29" s="64"/>
-      <c r="H29" s="64"/>
-      <c r="I29" s="64"/>
-      <c r="J29" s="64"/>
-      <c r="K29" s="64"/>
-      <c r="L29" s="64"/>
-      <c r="M29" s="64"/>
-      <c r="N29" s="64"/>
-      <c r="O29" s="64"/>
-      <c r="P29" s="64"/>
-      <c r="Q29" s="64"/>
-      <c r="R29" s="64"/>
-      <c r="S29" s="64"/>
-      <c r="T29" s="64"/>
-      <c r="U29" s="64"/>
-      <c r="V29" s="64"/>
-      <c r="W29" s="64"/>
-      <c r="X29" s="64"/>
-      <c r="Y29" s="64"/>
-      <c r="Z29" s="64"/>
-      <c r="AA29" s="64"/>
-      <c r="AB29" s="64"/>
-      <c r="AC29" s="64"/>
-      <c r="AD29" s="64"/>
-      <c r="AE29" s="64"/>
-      <c r="AF29" s="64"/>
-      <c r="AG29" s="64"/>
-      <c r="AH29" s="64"/>
-      <c r="AI29" s="64"/>
-      <c r="AJ29" s="65"/>
+      <c r="A29" s="150"/>
+      <c r="B29" s="151"/>
+      <c r="C29" s="151"/>
+      <c r="D29" s="151"/>
+      <c r="E29" s="151"/>
+      <c r="F29" s="151"/>
+      <c r="G29" s="151"/>
+      <c r="H29" s="151"/>
+      <c r="I29" s="151"/>
+      <c r="J29" s="151"/>
+      <c r="K29" s="151"/>
+      <c r="L29" s="151"/>
+      <c r="M29" s="151"/>
+      <c r="N29" s="151"/>
+      <c r="O29" s="151"/>
+      <c r="P29" s="151"/>
+      <c r="Q29" s="151"/>
+      <c r="R29" s="151"/>
+      <c r="S29" s="151"/>
+      <c r="T29" s="151"/>
+      <c r="U29" s="151"/>
+      <c r="V29" s="151"/>
+      <c r="W29" s="151"/>
+      <c r="X29" s="151"/>
+      <c r="Y29" s="151"/>
+      <c r="Z29" s="151"/>
+      <c r="AA29" s="151"/>
+      <c r="AB29" s="151"/>
+      <c r="AC29" s="151"/>
+      <c r="AD29" s="151"/>
+      <c r="AE29" s="151"/>
+      <c r="AF29" s="151"/>
+      <c r="AG29" s="151"/>
+      <c r="AH29" s="151"/>
+      <c r="AI29" s="151"/>
+      <c r="AJ29" s="152"/>
     </row>
     <row r="30" spans="1:36" ht="12.75" customHeight="1">
-      <c r="A30" s="87" t="s">
+      <c r="A30" s="153" t="s">
         <v>17</v>
       </c>
-      <c r="B30" s="88"/>
-      <c r="C30" s="88"/>
-      <c r="D30" s="88"/>
-      <c r="E30" s="88"/>
-      <c r="F30" s="88"/>
-      <c r="G30" s="88"/>
-      <c r="H30" s="88"/>
-      <c r="I30" s="88"/>
-      <c r="J30" s="88"/>
-      <c r="K30" s="88"/>
-      <c r="L30" s="88"/>
-      <c r="M30" s="88"/>
-      <c r="N30" s="88"/>
-      <c r="O30" s="88"/>
+      <c r="B30" s="154"/>
+      <c r="C30" s="154"/>
+      <c r="D30" s="154"/>
+      <c r="E30" s="154"/>
+      <c r="F30" s="154"/>
+      <c r="G30" s="154"/>
+      <c r="H30" s="154"/>
+      <c r="I30" s="154"/>
+      <c r="J30" s="154"/>
+      <c r="K30" s="154"/>
+      <c r="L30" s="154"/>
+      <c r="M30" s="154"/>
+      <c r="N30" s="154"/>
+      <c r="O30" s="154"/>
       <c r="P30" s="41"/>
       <c r="Q30" s="41"/>
       <c r="R30" s="41"/>
@@ -8218,216 +8206,216 @@
       <c r="AJ30" s="42"/>
     </row>
     <row r="31" spans="1:36" ht="16.5" customHeight="1">
-      <c r="A31" s="59"/>
-      <c r="B31" s="91"/>
-      <c r="C31" s="91"/>
-      <c r="D31" s="91"/>
-      <c r="E31" s="91"/>
-      <c r="F31" s="91"/>
-      <c r="G31" s="91"/>
-      <c r="H31" s="91"/>
-      <c r="I31" s="91"/>
-      <c r="J31" s="91"/>
-      <c r="K31" s="91"/>
-      <c r="L31" s="91"/>
-      <c r="M31" s="91"/>
-      <c r="N31" s="91"/>
-      <c r="O31" s="91"/>
-      <c r="P31" s="91"/>
-      <c r="Q31" s="91"/>
-      <c r="R31" s="91"/>
-      <c r="S31" s="91"/>
-      <c r="T31" s="91"/>
-      <c r="U31" s="91"/>
-      <c r="V31" s="91"/>
-      <c r="W31" s="91"/>
-      <c r="X31" s="91"/>
-      <c r="Y31" s="91"/>
-      <c r="Z31" s="91"/>
-      <c r="AA31" s="91"/>
-      <c r="AB31" s="91"/>
-      <c r="AC31" s="91"/>
-      <c r="AD31" s="91"/>
-      <c r="AE31" s="91"/>
-      <c r="AF31" s="91"/>
-      <c r="AG31" s="91"/>
-      <c r="AH31" s="91"/>
-      <c r="AI31" s="91"/>
-      <c r="AJ31" s="92"/>
+      <c r="A31" s="146"/>
+      <c r="B31" s="156"/>
+      <c r="C31" s="156"/>
+      <c r="D31" s="156"/>
+      <c r="E31" s="156"/>
+      <c r="F31" s="156"/>
+      <c r="G31" s="156"/>
+      <c r="H31" s="156"/>
+      <c r="I31" s="156"/>
+      <c r="J31" s="156"/>
+      <c r="K31" s="156"/>
+      <c r="L31" s="156"/>
+      <c r="M31" s="156"/>
+      <c r="N31" s="156"/>
+      <c r="O31" s="156"/>
+      <c r="P31" s="156"/>
+      <c r="Q31" s="156"/>
+      <c r="R31" s="156"/>
+      <c r="S31" s="156"/>
+      <c r="T31" s="156"/>
+      <c r="U31" s="156"/>
+      <c r="V31" s="156"/>
+      <c r="W31" s="156"/>
+      <c r="X31" s="156"/>
+      <c r="Y31" s="156"/>
+      <c r="Z31" s="156"/>
+      <c r="AA31" s="156"/>
+      <c r="AB31" s="156"/>
+      <c r="AC31" s="156"/>
+      <c r="AD31" s="156"/>
+      <c r="AE31" s="156"/>
+      <c r="AF31" s="156"/>
+      <c r="AG31" s="156"/>
+      <c r="AH31" s="156"/>
+      <c r="AI31" s="156"/>
+      <c r="AJ31" s="157"/>
     </row>
     <row r="32" spans="1:36" ht="16.5" customHeight="1">
-      <c r="A32" s="59"/>
-      <c r="B32" s="91"/>
-      <c r="C32" s="91"/>
-      <c r="D32" s="91"/>
-      <c r="E32" s="91"/>
-      <c r="F32" s="91"/>
-      <c r="G32" s="91"/>
-      <c r="H32" s="91"/>
-      <c r="I32" s="91"/>
-      <c r="J32" s="91"/>
-      <c r="K32" s="91"/>
-      <c r="L32" s="91"/>
-      <c r="M32" s="91"/>
-      <c r="N32" s="91"/>
-      <c r="O32" s="91"/>
-      <c r="P32" s="91"/>
-      <c r="Q32" s="91"/>
-      <c r="R32" s="91"/>
-      <c r="S32" s="91"/>
-      <c r="T32" s="91"/>
-      <c r="U32" s="91"/>
-      <c r="V32" s="91"/>
-      <c r="W32" s="91"/>
-      <c r="X32" s="91"/>
-      <c r="Y32" s="91"/>
-      <c r="Z32" s="91"/>
-      <c r="AA32" s="91"/>
-      <c r="AB32" s="91"/>
-      <c r="AC32" s="91"/>
-      <c r="AD32" s="91"/>
-      <c r="AE32" s="91"/>
-      <c r="AF32" s="91"/>
-      <c r="AG32" s="91"/>
-      <c r="AH32" s="91"/>
-      <c r="AI32" s="91"/>
-      <c r="AJ32" s="92"/>
+      <c r="A32" s="146"/>
+      <c r="B32" s="156"/>
+      <c r="C32" s="156"/>
+      <c r="D32" s="156"/>
+      <c r="E32" s="156"/>
+      <c r="F32" s="156"/>
+      <c r="G32" s="156"/>
+      <c r="H32" s="156"/>
+      <c r="I32" s="156"/>
+      <c r="J32" s="156"/>
+      <c r="K32" s="156"/>
+      <c r="L32" s="156"/>
+      <c r="M32" s="156"/>
+      <c r="N32" s="156"/>
+      <c r="O32" s="156"/>
+      <c r="P32" s="156"/>
+      <c r="Q32" s="156"/>
+      <c r="R32" s="156"/>
+      <c r="S32" s="156"/>
+      <c r="T32" s="156"/>
+      <c r="U32" s="156"/>
+      <c r="V32" s="156"/>
+      <c r="W32" s="156"/>
+      <c r="X32" s="156"/>
+      <c r="Y32" s="156"/>
+      <c r="Z32" s="156"/>
+      <c r="AA32" s="156"/>
+      <c r="AB32" s="156"/>
+      <c r="AC32" s="156"/>
+      <c r="AD32" s="156"/>
+      <c r="AE32" s="156"/>
+      <c r="AF32" s="156"/>
+      <c r="AG32" s="156"/>
+      <c r="AH32" s="156"/>
+      <c r="AI32" s="156"/>
+      <c r="AJ32" s="157"/>
     </row>
     <row r="33" spans="1:36" ht="16.5" customHeight="1">
-      <c r="A33" s="59"/>
-      <c r="B33" s="91"/>
-      <c r="C33" s="91"/>
-      <c r="D33" s="91"/>
-      <c r="E33" s="91"/>
-      <c r="F33" s="91"/>
-      <c r="G33" s="91"/>
-      <c r="H33" s="91"/>
-      <c r="I33" s="91"/>
-      <c r="J33" s="91"/>
-      <c r="K33" s="91"/>
-      <c r="L33" s="91"/>
-      <c r="M33" s="91"/>
-      <c r="N33" s="91"/>
-      <c r="O33" s="91"/>
-      <c r="P33" s="91"/>
-      <c r="Q33" s="91"/>
-      <c r="R33" s="91"/>
-      <c r="S33" s="91"/>
-      <c r="T33" s="91"/>
-      <c r="U33" s="91"/>
-      <c r="V33" s="91"/>
-      <c r="W33" s="91"/>
-      <c r="X33" s="91"/>
-      <c r="Y33" s="91"/>
-      <c r="Z33" s="91"/>
-      <c r="AA33" s="91"/>
-      <c r="AB33" s="91"/>
-      <c r="AC33" s="91"/>
-      <c r="AD33" s="91"/>
-      <c r="AE33" s="91"/>
-      <c r="AF33" s="91"/>
-      <c r="AG33" s="91"/>
-      <c r="AH33" s="91"/>
-      <c r="AI33" s="91"/>
-      <c r="AJ33" s="92"/>
+      <c r="A33" s="146"/>
+      <c r="B33" s="156"/>
+      <c r="C33" s="156"/>
+      <c r="D33" s="156"/>
+      <c r="E33" s="156"/>
+      <c r="F33" s="156"/>
+      <c r="G33" s="156"/>
+      <c r="H33" s="156"/>
+      <c r="I33" s="156"/>
+      <c r="J33" s="156"/>
+      <c r="K33" s="156"/>
+      <c r="L33" s="156"/>
+      <c r="M33" s="156"/>
+      <c r="N33" s="156"/>
+      <c r="O33" s="156"/>
+      <c r="P33" s="156"/>
+      <c r="Q33" s="156"/>
+      <c r="R33" s="156"/>
+      <c r="S33" s="156"/>
+      <c r="T33" s="156"/>
+      <c r="U33" s="156"/>
+      <c r="V33" s="156"/>
+      <c r="W33" s="156"/>
+      <c r="X33" s="156"/>
+      <c r="Y33" s="156"/>
+      <c r="Z33" s="156"/>
+      <c r="AA33" s="156"/>
+      <c r="AB33" s="156"/>
+      <c r="AC33" s="156"/>
+      <c r="AD33" s="156"/>
+      <c r="AE33" s="156"/>
+      <c r="AF33" s="156"/>
+      <c r="AG33" s="156"/>
+      <c r="AH33" s="156"/>
+      <c r="AI33" s="156"/>
+      <c r="AJ33" s="157"/>
     </row>
     <row r="34" spans="1:36" ht="61.8" customHeight="1">
-      <c r="A34" s="59"/>
-      <c r="B34" s="91"/>
-      <c r="C34" s="91"/>
-      <c r="D34" s="91"/>
-      <c r="E34" s="91"/>
-      <c r="F34" s="91"/>
-      <c r="G34" s="91"/>
-      <c r="H34" s="91"/>
-      <c r="I34" s="91"/>
-      <c r="J34" s="91"/>
-      <c r="K34" s="91"/>
-      <c r="L34" s="91"/>
-      <c r="M34" s="91"/>
-      <c r="N34" s="91"/>
-      <c r="O34" s="91"/>
-      <c r="P34" s="91"/>
-      <c r="Q34" s="91"/>
-      <c r="R34" s="91"/>
-      <c r="S34" s="91"/>
-      <c r="T34" s="91"/>
-      <c r="U34" s="91"/>
-      <c r="V34" s="91"/>
-      <c r="W34" s="91"/>
-      <c r="X34" s="91"/>
-      <c r="Y34" s="91"/>
-      <c r="Z34" s="91"/>
-      <c r="AA34" s="91"/>
-      <c r="AB34" s="91"/>
-      <c r="AC34" s="91"/>
-      <c r="AD34" s="91"/>
-      <c r="AE34" s="91"/>
-      <c r="AF34" s="91"/>
-      <c r="AG34" s="91"/>
-      <c r="AH34" s="91"/>
-      <c r="AI34" s="91"/>
-      <c r="AJ34" s="92"/>
+      <c r="A34" s="146"/>
+      <c r="B34" s="156"/>
+      <c r="C34" s="156"/>
+      <c r="D34" s="156"/>
+      <c r="E34" s="156"/>
+      <c r="F34" s="156"/>
+      <c r="G34" s="156"/>
+      <c r="H34" s="156"/>
+      <c r="I34" s="156"/>
+      <c r="J34" s="156"/>
+      <c r="K34" s="156"/>
+      <c r="L34" s="156"/>
+      <c r="M34" s="156"/>
+      <c r="N34" s="156"/>
+      <c r="O34" s="156"/>
+      <c r="P34" s="156"/>
+      <c r="Q34" s="156"/>
+      <c r="R34" s="156"/>
+      <c r="S34" s="156"/>
+      <c r="T34" s="156"/>
+      <c r="U34" s="156"/>
+      <c r="V34" s="156"/>
+      <c r="W34" s="156"/>
+      <c r="X34" s="156"/>
+      <c r="Y34" s="156"/>
+      <c r="Z34" s="156"/>
+      <c r="AA34" s="156"/>
+      <c r="AB34" s="156"/>
+      <c r="AC34" s="156"/>
+      <c r="AD34" s="156"/>
+      <c r="AE34" s="156"/>
+      <c r="AF34" s="156"/>
+      <c r="AG34" s="156"/>
+      <c r="AH34" s="156"/>
+      <c r="AI34" s="156"/>
+      <c r="AJ34" s="157"/>
     </row>
     <row r="35" spans="1:36" ht="13.2" customHeight="1">
-      <c r="A35" s="93"/>
-      <c r="B35" s="94"/>
-      <c r="C35" s="94"/>
-      <c r="D35" s="94"/>
-      <c r="E35" s="94"/>
-      <c r="F35" s="94"/>
-      <c r="G35" s="94"/>
-      <c r="H35" s="94"/>
-      <c r="I35" s="94"/>
-      <c r="J35" s="94"/>
-      <c r="K35" s="94"/>
-      <c r="L35" s="94"/>
-      <c r="M35" s="94"/>
-      <c r="N35" s="94"/>
-      <c r="O35" s="94"/>
-      <c r="P35" s="94"/>
-      <c r="Q35" s="94"/>
-      <c r="R35" s="94"/>
-      <c r="S35" s="94"/>
-      <c r="T35" s="94"/>
-      <c r="U35" s="94"/>
-      <c r="V35" s="94"/>
-      <c r="W35" s="94"/>
-      <c r="X35" s="94"/>
-      <c r="Y35" s="94"/>
-      <c r="Z35" s="94"/>
-      <c r="AA35" s="94"/>
-      <c r="AB35" s="94"/>
-      <c r="AC35" s="94"/>
-      <c r="AD35" s="94"/>
-      <c r="AE35" s="94"/>
-      <c r="AF35" s="94"/>
-      <c r="AG35" s="94"/>
-      <c r="AH35" s="94"/>
-      <c r="AI35" s="94"/>
-      <c r="AJ35" s="95"/>
+      <c r="A35" s="158"/>
+      <c r="B35" s="159"/>
+      <c r="C35" s="159"/>
+      <c r="D35" s="159"/>
+      <c r="E35" s="159"/>
+      <c r="F35" s="159"/>
+      <c r="G35" s="159"/>
+      <c r="H35" s="159"/>
+      <c r="I35" s="159"/>
+      <c r="J35" s="159"/>
+      <c r="K35" s="159"/>
+      <c r="L35" s="159"/>
+      <c r="M35" s="159"/>
+      <c r="N35" s="159"/>
+      <c r="O35" s="159"/>
+      <c r="P35" s="159"/>
+      <c r="Q35" s="159"/>
+      <c r="R35" s="159"/>
+      <c r="S35" s="159"/>
+      <c r="T35" s="159"/>
+      <c r="U35" s="159"/>
+      <c r="V35" s="159"/>
+      <c r="W35" s="159"/>
+      <c r="X35" s="159"/>
+      <c r="Y35" s="159"/>
+      <c r="Z35" s="159"/>
+      <c r="AA35" s="159"/>
+      <c r="AB35" s="159"/>
+      <c r="AC35" s="159"/>
+      <c r="AD35" s="159"/>
+      <c r="AE35" s="159"/>
+      <c r="AF35" s="159"/>
+      <c r="AG35" s="159"/>
+      <c r="AH35" s="159"/>
+      <c r="AI35" s="159"/>
+      <c r="AJ35" s="160"/>
     </row>
     <row r="36" spans="1:36" ht="13.5" customHeight="1">
-      <c r="A36" s="66" t="s">
+      <c r="A36" s="62" t="s">
         <v>94</v>
       </c>
-      <c r="B36" s="67"/>
-      <c r="C36" s="67"/>
-      <c r="D36" s="67"/>
-      <c r="E36" s="67"/>
-      <c r="F36" s="67"/>
-      <c r="G36" s="67"/>
-      <c r="H36" s="67"/>
-      <c r="I36" s="67"/>
-      <c r="J36" s="67"/>
-      <c r="K36" s="67"/>
-      <c r="L36" s="67"/>
-      <c r="M36" s="67"/>
-      <c r="N36" s="67"/>
-      <c r="O36" s="67"/>
-      <c r="P36" s="67"/>
-      <c r="Q36" s="67"/>
-      <c r="R36" s="67"/>
+      <c r="B36" s="63"/>
+      <c r="C36" s="63"/>
+      <c r="D36" s="63"/>
+      <c r="E36" s="63"/>
+      <c r="F36" s="63"/>
+      <c r="G36" s="63"/>
+      <c r="H36" s="63"/>
+      <c r="I36" s="63"/>
+      <c r="J36" s="63"/>
+      <c r="K36" s="63"/>
+      <c r="L36" s="63"/>
+      <c r="M36" s="63"/>
+      <c r="N36" s="63"/>
+      <c r="O36" s="63"/>
+      <c r="P36" s="63"/>
+      <c r="Q36" s="63"/>
+      <c r="R36" s="63"/>
       <c r="S36" s="40"/>
       <c r="T36" s="40"/>
       <c r="U36" s="40"/>
@@ -8448,178 +8436,178 @@
       <c r="AJ36" s="43"/>
     </row>
     <row r="37" spans="1:36" ht="14.25" customHeight="1">
-      <c r="A37" s="59"/>
-      <c r="B37" s="91"/>
-      <c r="C37" s="91"/>
-      <c r="D37" s="91"/>
-      <c r="E37" s="91"/>
-      <c r="F37" s="91"/>
-      <c r="G37" s="91"/>
-      <c r="H37" s="91"/>
-      <c r="I37" s="91"/>
-      <c r="J37" s="91"/>
-      <c r="K37" s="91"/>
-      <c r="L37" s="91"/>
-      <c r="M37" s="91"/>
-      <c r="N37" s="91"/>
-      <c r="O37" s="91"/>
-      <c r="P37" s="91"/>
-      <c r="Q37" s="91"/>
-      <c r="R37" s="91"/>
-      <c r="S37" s="91"/>
-      <c r="T37" s="91"/>
-      <c r="U37" s="91"/>
-      <c r="V37" s="91"/>
-      <c r="W37" s="91"/>
-      <c r="X37" s="91"/>
-      <c r="Y37" s="91"/>
-      <c r="Z37" s="91"/>
-      <c r="AA37" s="91"/>
-      <c r="AB37" s="91"/>
-      <c r="AC37" s="91"/>
-      <c r="AD37" s="91"/>
-      <c r="AE37" s="91"/>
-      <c r="AF37" s="91"/>
-      <c r="AG37" s="91"/>
-      <c r="AH37" s="91"/>
-      <c r="AI37" s="91"/>
-      <c r="AJ37" s="92"/>
+      <c r="A37" s="146"/>
+      <c r="B37" s="156"/>
+      <c r="C37" s="156"/>
+      <c r="D37" s="156"/>
+      <c r="E37" s="156"/>
+      <c r="F37" s="156"/>
+      <c r="G37" s="156"/>
+      <c r="H37" s="156"/>
+      <c r="I37" s="156"/>
+      <c r="J37" s="156"/>
+      <c r="K37" s="156"/>
+      <c r="L37" s="156"/>
+      <c r="M37" s="156"/>
+      <c r="N37" s="156"/>
+      <c r="O37" s="156"/>
+      <c r="P37" s="156"/>
+      <c r="Q37" s="156"/>
+      <c r="R37" s="156"/>
+      <c r="S37" s="156"/>
+      <c r="T37" s="156"/>
+      <c r="U37" s="156"/>
+      <c r="V37" s="156"/>
+      <c r="W37" s="156"/>
+      <c r="X37" s="156"/>
+      <c r="Y37" s="156"/>
+      <c r="Z37" s="156"/>
+      <c r="AA37" s="156"/>
+      <c r="AB37" s="156"/>
+      <c r="AC37" s="156"/>
+      <c r="AD37" s="156"/>
+      <c r="AE37" s="156"/>
+      <c r="AF37" s="156"/>
+      <c r="AG37" s="156"/>
+      <c r="AH37" s="156"/>
+      <c r="AI37" s="156"/>
+      <c r="AJ37" s="157"/>
     </row>
     <row r="38" spans="1:36" ht="14.25" customHeight="1">
-      <c r="A38" s="59"/>
-      <c r="B38" s="91"/>
-      <c r="C38" s="91"/>
-      <c r="D38" s="91"/>
-      <c r="E38" s="91"/>
-      <c r="F38" s="91"/>
-      <c r="G38" s="91"/>
-      <c r="H38" s="91"/>
-      <c r="I38" s="91"/>
-      <c r="J38" s="91"/>
-      <c r="K38" s="91"/>
-      <c r="L38" s="91"/>
-      <c r="M38" s="91"/>
-      <c r="N38" s="91"/>
-      <c r="O38" s="91"/>
-      <c r="P38" s="91"/>
-      <c r="Q38" s="91"/>
-      <c r="R38" s="91"/>
-      <c r="S38" s="91"/>
-      <c r="T38" s="91"/>
-      <c r="U38" s="91"/>
-      <c r="V38" s="91"/>
-      <c r="W38" s="91"/>
-      <c r="X38" s="91"/>
-      <c r="Y38" s="91"/>
-      <c r="Z38" s="91"/>
-      <c r="AA38" s="91"/>
-      <c r="AB38" s="91"/>
-      <c r="AC38" s="91"/>
-      <c r="AD38" s="91"/>
-      <c r="AE38" s="91"/>
-      <c r="AF38" s="91"/>
-      <c r="AG38" s="91"/>
-      <c r="AH38" s="91"/>
-      <c r="AI38" s="91"/>
-      <c r="AJ38" s="92"/>
+      <c r="A38" s="146"/>
+      <c r="B38" s="156"/>
+      <c r="C38" s="156"/>
+      <c r="D38" s="156"/>
+      <c r="E38" s="156"/>
+      <c r="F38" s="156"/>
+      <c r="G38" s="156"/>
+      <c r="H38" s="156"/>
+      <c r="I38" s="156"/>
+      <c r="J38" s="156"/>
+      <c r="K38" s="156"/>
+      <c r="L38" s="156"/>
+      <c r="M38" s="156"/>
+      <c r="N38" s="156"/>
+      <c r="O38" s="156"/>
+      <c r="P38" s="156"/>
+      <c r="Q38" s="156"/>
+      <c r="R38" s="156"/>
+      <c r="S38" s="156"/>
+      <c r="T38" s="156"/>
+      <c r="U38" s="156"/>
+      <c r="V38" s="156"/>
+      <c r="W38" s="156"/>
+      <c r="X38" s="156"/>
+      <c r="Y38" s="156"/>
+      <c r="Z38" s="156"/>
+      <c r="AA38" s="156"/>
+      <c r="AB38" s="156"/>
+      <c r="AC38" s="156"/>
+      <c r="AD38" s="156"/>
+      <c r="AE38" s="156"/>
+      <c r="AF38" s="156"/>
+      <c r="AG38" s="156"/>
+      <c r="AH38" s="156"/>
+      <c r="AI38" s="156"/>
+      <c r="AJ38" s="157"/>
     </row>
     <row r="39" spans="1:36" ht="27.6" customHeight="1">
-      <c r="A39" s="59"/>
-      <c r="B39" s="91"/>
-      <c r="C39" s="91"/>
-      <c r="D39" s="91"/>
-      <c r="E39" s="91"/>
-      <c r="F39" s="91"/>
-      <c r="G39" s="91"/>
-      <c r="H39" s="91"/>
-      <c r="I39" s="91"/>
-      <c r="J39" s="91"/>
-      <c r="K39" s="91"/>
-      <c r="L39" s="91"/>
-      <c r="M39" s="91"/>
-      <c r="N39" s="91"/>
-      <c r="O39" s="91"/>
-      <c r="P39" s="91"/>
-      <c r="Q39" s="91"/>
-      <c r="R39" s="91"/>
-      <c r="S39" s="91"/>
-      <c r="T39" s="91"/>
-      <c r="U39" s="91"/>
-      <c r="V39" s="91"/>
-      <c r="W39" s="91"/>
-      <c r="X39" s="91"/>
-      <c r="Y39" s="91"/>
-      <c r="Z39" s="91"/>
-      <c r="AA39" s="91"/>
-      <c r="AB39" s="91"/>
-      <c r="AC39" s="91"/>
-      <c r="AD39" s="91"/>
-      <c r="AE39" s="91"/>
-      <c r="AF39" s="91"/>
-      <c r="AG39" s="91"/>
-      <c r="AH39" s="91"/>
-      <c r="AI39" s="91"/>
-      <c r="AJ39" s="92"/>
+      <c r="A39" s="146"/>
+      <c r="B39" s="156"/>
+      <c r="C39" s="156"/>
+      <c r="D39" s="156"/>
+      <c r="E39" s="156"/>
+      <c r="F39" s="156"/>
+      <c r="G39" s="156"/>
+      <c r="H39" s="156"/>
+      <c r="I39" s="156"/>
+      <c r="J39" s="156"/>
+      <c r="K39" s="156"/>
+      <c r="L39" s="156"/>
+      <c r="M39" s="156"/>
+      <c r="N39" s="156"/>
+      <c r="O39" s="156"/>
+      <c r="P39" s="156"/>
+      <c r="Q39" s="156"/>
+      <c r="R39" s="156"/>
+      <c r="S39" s="156"/>
+      <c r="T39" s="156"/>
+      <c r="U39" s="156"/>
+      <c r="V39" s="156"/>
+      <c r="W39" s="156"/>
+      <c r="X39" s="156"/>
+      <c r="Y39" s="156"/>
+      <c r="Z39" s="156"/>
+      <c r="AA39" s="156"/>
+      <c r="AB39" s="156"/>
+      <c r="AC39" s="156"/>
+      <c r="AD39" s="156"/>
+      <c r="AE39" s="156"/>
+      <c r="AF39" s="156"/>
+      <c r="AG39" s="156"/>
+      <c r="AH39" s="156"/>
+      <c r="AI39" s="156"/>
+      <c r="AJ39" s="157"/>
     </row>
     <row r="40" spans="1:36" ht="16.8" customHeight="1">
-      <c r="A40" s="59"/>
-      <c r="B40" s="91"/>
-      <c r="C40" s="91"/>
-      <c r="D40" s="91"/>
-      <c r="E40" s="91"/>
-      <c r="F40" s="91"/>
-      <c r="G40" s="91"/>
-      <c r="H40" s="91"/>
-      <c r="I40" s="91"/>
-      <c r="J40" s="91"/>
-      <c r="K40" s="91"/>
-      <c r="L40" s="91"/>
-      <c r="M40" s="91"/>
-      <c r="N40" s="91"/>
-      <c r="O40" s="91"/>
-      <c r="P40" s="91"/>
-      <c r="Q40" s="91"/>
-      <c r="R40" s="91"/>
-      <c r="S40" s="91"/>
-      <c r="T40" s="91"/>
-      <c r="U40" s="91"/>
-      <c r="V40" s="91"/>
-      <c r="W40" s="91"/>
-      <c r="X40" s="91"/>
-      <c r="Y40" s="91"/>
-      <c r="Z40" s="91"/>
-      <c r="AA40" s="91"/>
-      <c r="AB40" s="91"/>
-      <c r="AC40" s="91"/>
-      <c r="AD40" s="91"/>
-      <c r="AE40" s="91"/>
-      <c r="AF40" s="91"/>
-      <c r="AG40" s="91"/>
-      <c r="AH40" s="91"/>
-      <c r="AI40" s="91"/>
-      <c r="AJ40" s="92"/>
+      <c r="A40" s="146"/>
+      <c r="B40" s="156"/>
+      <c r="C40" s="156"/>
+      <c r="D40" s="156"/>
+      <c r="E40" s="156"/>
+      <c r="F40" s="156"/>
+      <c r="G40" s="156"/>
+      <c r="H40" s="156"/>
+      <c r="I40" s="156"/>
+      <c r="J40" s="156"/>
+      <c r="K40" s="156"/>
+      <c r="L40" s="156"/>
+      <c r="M40" s="156"/>
+      <c r="N40" s="156"/>
+      <c r="O40" s="156"/>
+      <c r="P40" s="156"/>
+      <c r="Q40" s="156"/>
+      <c r="R40" s="156"/>
+      <c r="S40" s="156"/>
+      <c r="T40" s="156"/>
+      <c r="U40" s="156"/>
+      <c r="V40" s="156"/>
+      <c r="W40" s="156"/>
+      <c r="X40" s="156"/>
+      <c r="Y40" s="156"/>
+      <c r="Z40" s="156"/>
+      <c r="AA40" s="156"/>
+      <c r="AB40" s="156"/>
+      <c r="AC40" s="156"/>
+      <c r="AD40" s="156"/>
+      <c r="AE40" s="156"/>
+      <c r="AF40" s="156"/>
+      <c r="AG40" s="156"/>
+      <c r="AH40" s="156"/>
+      <c r="AI40" s="156"/>
+      <c r="AJ40" s="157"/>
     </row>
     <row r="41" spans="1:36" ht="16.8" customHeight="1">
-      <c r="A41" s="66" t="s">
+      <c r="A41" s="62" t="s">
         <v>100</v>
       </c>
-      <c r="B41" s="67"/>
-      <c r="C41" s="67"/>
-      <c r="D41" s="67"/>
-      <c r="E41" s="67"/>
-      <c r="F41" s="67"/>
-      <c r="G41" s="67"/>
-      <c r="H41" s="67"/>
-      <c r="I41" s="67"/>
-      <c r="J41" s="67"/>
-      <c r="K41" s="67"/>
-      <c r="L41" s="67"/>
-      <c r="M41" s="67"/>
-      <c r="N41" s="67"/>
-      <c r="O41" s="67"/>
-      <c r="P41" s="67"/>
-      <c r="Q41" s="67"/>
-      <c r="R41" s="67"/>
+      <c r="B41" s="63"/>
+      <c r="C41" s="63"/>
+      <c r="D41" s="63"/>
+      <c r="E41" s="63"/>
+      <c r="F41" s="63"/>
+      <c r="G41" s="63"/>
+      <c r="H41" s="63"/>
+      <c r="I41" s="63"/>
+      <c r="J41" s="63"/>
+      <c r="K41" s="63"/>
+      <c r="L41" s="63"/>
+      <c r="M41" s="63"/>
+      <c r="N41" s="63"/>
+      <c r="O41" s="63"/>
+      <c r="P41" s="63"/>
+      <c r="Q41" s="63"/>
+      <c r="R41" s="63"/>
       <c r="S41" s="40"/>
       <c r="T41" s="40"/>
       <c r="U41" s="40"/>
@@ -8677,807 +8665,770 @@
       <c r="AI42" s="162"/>
       <c r="AJ42" s="163"/>
     </row>
-    <row r="43" spans="1:36" ht="16.8" customHeight="1">
-      <c r="A43" s="164"/>
-      <c r="B43" s="165"/>
-      <c r="C43" s="165"/>
-      <c r="D43" s="165"/>
-      <c r="E43" s="165"/>
-      <c r="F43" s="165"/>
-      <c r="G43" s="165"/>
-      <c r="H43" s="165"/>
-      <c r="I43" s="165"/>
-      <c r="J43" s="165"/>
-      <c r="K43" s="165"/>
-      <c r="L43" s="165"/>
-      <c r="M43" s="165"/>
-      <c r="N43" s="165"/>
-      <c r="O43" s="165"/>
-      <c r="P43" s="165"/>
-      <c r="Q43" s="165"/>
-      <c r="R43" s="165"/>
-      <c r="S43" s="165"/>
-      <c r="T43" s="165"/>
-      <c r="U43" s="165"/>
-      <c r="V43" s="165"/>
-      <c r="W43" s="165"/>
-      <c r="X43" s="165"/>
-      <c r="Y43" s="165"/>
-      <c r="Z43" s="165"/>
-      <c r="AA43" s="165"/>
-      <c r="AB43" s="165"/>
-      <c r="AC43" s="165"/>
-      <c r="AD43" s="165"/>
-      <c r="AE43" s="165"/>
-      <c r="AF43" s="165"/>
-      <c r="AG43" s="165"/>
-      <c r="AH43" s="165"/>
-      <c r="AI43" s="165"/>
-      <c r="AJ43" s="166"/>
-    </row>
-    <row r="44" spans="1:36" ht="17.25" customHeight="1">
-      <c r="A44" s="68" t="s">
+    <row r="43" spans="1:36" ht="17.25" customHeight="1">
+      <c r="A43" s="104" t="s">
         <v>18</v>
       </c>
-      <c r="B44" s="69"/>
-      <c r="C44" s="69"/>
-      <c r="D44" s="69"/>
-      <c r="E44" s="69"/>
-      <c r="F44" s="69"/>
-      <c r="G44" s="69"/>
-      <c r="H44" s="69"/>
-      <c r="I44" s="70"/>
-      <c r="J44" s="68" t="s">
+      <c r="B43" s="105"/>
+      <c r="C43" s="105"/>
+      <c r="D43" s="105"/>
+      <c r="E43" s="105"/>
+      <c r="F43" s="105"/>
+      <c r="G43" s="105"/>
+      <c r="H43" s="105"/>
+      <c r="I43" s="106"/>
+      <c r="J43" s="104" t="s">
         <v>19</v>
       </c>
-      <c r="K44" s="69"/>
-      <c r="L44" s="69"/>
-      <c r="M44" s="69"/>
-      <c r="N44" s="69"/>
-      <c r="O44" s="69"/>
-      <c r="P44" s="69"/>
-      <c r="Q44" s="69"/>
-      <c r="R44" s="70"/>
-      <c r="S44" s="68" t="s">
+      <c r="K43" s="105"/>
+      <c r="L43" s="105"/>
+      <c r="M43" s="105"/>
+      <c r="N43" s="105"/>
+      <c r="O43" s="105"/>
+      <c r="P43" s="105"/>
+      <c r="Q43" s="105"/>
+      <c r="R43" s="106"/>
+      <c r="S43" s="104" t="s">
         <v>77</v>
       </c>
-      <c r="T44" s="69"/>
-      <c r="U44" s="69"/>
-      <c r="V44" s="69"/>
-      <c r="W44" s="69"/>
-      <c r="X44" s="69"/>
-      <c r="Y44" s="69"/>
-      <c r="Z44" s="69"/>
-      <c r="AA44" s="70"/>
-      <c r="AB44" s="89" t="s">
+      <c r="T43" s="105"/>
+      <c r="U43" s="105"/>
+      <c r="V43" s="105"/>
+      <c r="W43" s="105"/>
+      <c r="X43" s="105"/>
+      <c r="Y43" s="105"/>
+      <c r="Z43" s="105"/>
+      <c r="AA43" s="106"/>
+      <c r="AB43" s="155" t="s">
         <v>91</v>
       </c>
-      <c r="AC44" s="69"/>
-      <c r="AD44" s="69"/>
-      <c r="AE44" s="69"/>
-      <c r="AF44" s="69"/>
-      <c r="AG44" s="69"/>
-      <c r="AH44" s="69"/>
-      <c r="AI44" s="69"/>
-      <c r="AJ44" s="70"/>
+      <c r="AC43" s="105"/>
+      <c r="AD43" s="105"/>
+      <c r="AE43" s="105"/>
+      <c r="AF43" s="105"/>
+      <c r="AG43" s="105"/>
+      <c r="AH43" s="105"/>
+      <c r="AI43" s="105"/>
+      <c r="AJ43" s="106"/>
+    </row>
+    <row r="44" spans="1:36" ht="18" customHeight="1">
+      <c r="A44" s="2"/>
+      <c r="B44" s="119" t="s">
+        <v>21</v>
+      </c>
+      <c r="C44" s="119"/>
+      <c r="D44" s="119"/>
+      <c r="E44" s="119"/>
+      <c r="F44" s="119"/>
+      <c r="G44" s="119"/>
+      <c r="H44" s="119"/>
+      <c r="I44" s="120"/>
+      <c r="J44" s="10"/>
+      <c r="K44" s="119" t="s">
+        <v>22</v>
+      </c>
+      <c r="L44" s="119"/>
+      <c r="M44" s="119"/>
+      <c r="N44" s="119"/>
+      <c r="O44" s="119"/>
+      <c r="P44" s="119"/>
+      <c r="Q44" s="119"/>
+      <c r="R44" s="120"/>
+      <c r="S44" s="86" t="s">
+        <v>81</v>
+      </c>
+      <c r="T44" s="84"/>
+      <c r="U44" s="84"/>
+      <c r="V44" s="84"/>
+      <c r="W44" s="75"/>
+      <c r="X44" s="75"/>
+      <c r="Y44" s="75"/>
+      <c r="Z44" s="49"/>
+      <c r="AA44" s="4"/>
+      <c r="AB44" s="121" t="s">
+        <v>82</v>
+      </c>
+      <c r="AC44" s="78"/>
+      <c r="AD44" s="78"/>
+      <c r="AE44" s="78"/>
+      <c r="AF44" s="126"/>
+      <c r="AG44" s="126"/>
+      <c r="AH44" s="126"/>
+      <c r="AI44" s="126"/>
+      <c r="AJ44" s="4"/>
     </row>
     <row r="45" spans="1:36" ht="18" customHeight="1">
       <c r="A45" s="2"/>
-      <c r="B45" s="54" t="s">
-        <v>21</v>
+      <c r="B45" s="119" t="s">
+        <v>24</v>
       </c>
-      <c r="C45" s="54"/>
-      <c r="D45" s="54"/>
-      <c r="E45" s="54"/>
-      <c r="F45" s="54"/>
-      <c r="G45" s="54"/>
-      <c r="H45" s="54"/>
-      <c r="I45" s="55"/>
+      <c r="C45" s="119"/>
+      <c r="D45" s="119"/>
+      <c r="E45" s="119"/>
+      <c r="F45" s="119"/>
+      <c r="G45" s="119"/>
+      <c r="H45" s="119"/>
+      <c r="I45" s="120"/>
       <c r="J45" s="10"/>
-      <c r="K45" s="54" t="s">
-        <v>22</v>
+      <c r="K45" s="119" t="s">
+        <v>25</v>
       </c>
-      <c r="L45" s="54"/>
-      <c r="M45" s="54"/>
-      <c r="N45" s="54"/>
-      <c r="O45" s="54"/>
-      <c r="P45" s="54"/>
-      <c r="Q45" s="54"/>
-      <c r="R45" s="55"/>
-      <c r="S45" s="96" t="s">
+      <c r="L45" s="119"/>
+      <c r="M45" s="119"/>
+      <c r="N45" s="119"/>
+      <c r="O45" s="119"/>
+      <c r="P45" s="119"/>
+      <c r="Q45" s="119"/>
+      <c r="R45" s="120"/>
+      <c r="S45" s="86" t="s">
+        <v>80</v>
+      </c>
+      <c r="T45" s="84"/>
+      <c r="U45" s="84"/>
+      <c r="V45" s="84"/>
+      <c r="W45" s="145"/>
+      <c r="X45" s="145"/>
+      <c r="Y45" s="145"/>
+      <c r="Z45" s="145"/>
+      <c r="AA45" s="4"/>
+      <c r="AB45" s="86" t="s">
         <v>81</v>
       </c>
-      <c r="T45" s="97"/>
-      <c r="U45" s="97"/>
-      <c r="V45" s="97"/>
-      <c r="W45" s="90"/>
-      <c r="X45" s="90"/>
-      <c r="Y45" s="90"/>
-      <c r="Z45" s="49"/>
-      <c r="AA45" s="4"/>
-      <c r="AB45" s="56" t="s">
-        <v>82</v>
-      </c>
-      <c r="AC45" s="57"/>
-      <c r="AD45" s="57"/>
-      <c r="AE45" s="57"/>
-      <c r="AF45" s="86"/>
-      <c r="AG45" s="86"/>
-      <c r="AH45" s="86"/>
-      <c r="AI45" s="86"/>
+      <c r="AC45" s="84"/>
+      <c r="AD45" s="84"/>
+      <c r="AE45" s="84"/>
+      <c r="AF45" s="145"/>
+      <c r="AG45" s="145"/>
+      <c r="AH45" s="145"/>
+      <c r="AI45" s="145"/>
       <c r="AJ45" s="4"/>
     </row>
     <row r="46" spans="1:36" ht="18" customHeight="1">
       <c r="A46" s="2"/>
-      <c r="B46" s="54" t="s">
-        <v>24</v>
+      <c r="B46" s="119" t="s">
+        <v>27</v>
       </c>
-      <c r="C46" s="54"/>
-      <c r="D46" s="54"/>
-      <c r="E46" s="54"/>
-      <c r="F46" s="54"/>
-      <c r="G46" s="54"/>
-      <c r="H46" s="54"/>
-      <c r="I46" s="55"/>
+      <c r="C46" s="119"/>
+      <c r="D46" s="119"/>
+      <c r="E46" s="119"/>
+      <c r="F46" s="119"/>
+      <c r="G46" s="119"/>
+      <c r="H46" s="119"/>
+      <c r="I46" s="120"/>
       <c r="J46" s="10"/>
-      <c r="K46" s="54" t="s">
-        <v>25</v>
+      <c r="K46" s="119" t="s">
+        <v>28</v>
       </c>
-      <c r="L46" s="54"/>
-      <c r="M46" s="54"/>
-      <c r="N46" s="54"/>
-      <c r="O46" s="54"/>
-      <c r="P46" s="54"/>
-      <c r="Q46" s="54"/>
-      <c r="R46" s="55"/>
-      <c r="S46" s="96" t="s">
+      <c r="L46" s="119"/>
+      <c r="M46" s="119"/>
+      <c r="N46" s="119"/>
+      <c r="O46" s="119"/>
+      <c r="P46" s="119"/>
+      <c r="Q46" s="119"/>
+      <c r="R46" s="120"/>
+      <c r="S46" s="121" t="s">
+        <v>78</v>
+      </c>
+      <c r="T46" s="78"/>
+      <c r="U46" s="78"/>
+      <c r="V46" s="78"/>
+      <c r="W46" s="78"/>
+      <c r="X46" s="122"/>
+      <c r="Y46" s="122"/>
+      <c r="Z46" s="122"/>
+      <c r="AA46" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="AB46" s="86" t="s">
         <v>80</v>
       </c>
-      <c r="T46" s="97"/>
-      <c r="U46" s="97"/>
-      <c r="V46" s="97"/>
-      <c r="W46" s="53"/>
-      <c r="X46" s="53"/>
-      <c r="Y46" s="53"/>
-      <c r="Z46" s="53"/>
-      <c r="AA46" s="4"/>
-      <c r="AB46" s="96" t="s">
-        <v>81</v>
-      </c>
-      <c r="AC46" s="97"/>
-      <c r="AD46" s="97"/>
-      <c r="AE46" s="97"/>
-      <c r="AF46" s="53"/>
-      <c r="AG46" s="53"/>
-      <c r="AH46" s="53"/>
-      <c r="AI46" s="53"/>
+      <c r="AC46" s="84"/>
+      <c r="AD46" s="84"/>
+      <c r="AE46" s="84"/>
+      <c r="AF46" s="145"/>
+      <c r="AG46" s="145"/>
+      <c r="AH46" s="145"/>
+      <c r="AI46" s="145"/>
       <c r="AJ46" s="4"/>
     </row>
     <row r="47" spans="1:36" ht="18" customHeight="1">
       <c r="A47" s="2"/>
-      <c r="B47" s="54" t="s">
-        <v>27</v>
+      <c r="B47" s="119" t="s">
+        <v>87</v>
       </c>
-      <c r="C47" s="54"/>
-      <c r="D47" s="54"/>
-      <c r="E47" s="54"/>
-      <c r="F47" s="54"/>
-      <c r="G47" s="54"/>
-      <c r="H47" s="54"/>
-      <c r="I47" s="55"/>
+      <c r="C47" s="119"/>
+      <c r="D47" s="119"/>
+      <c r="E47" s="119"/>
+      <c r="F47" s="119"/>
+      <c r="G47" s="119"/>
+      <c r="H47" s="119"/>
+      <c r="I47" s="120"/>
       <c r="J47" s="10"/>
-      <c r="K47" s="54" t="s">
-        <v>28</v>
+      <c r="K47" s="119" t="s">
+        <v>31</v>
       </c>
-      <c r="L47" s="54"/>
-      <c r="M47" s="54"/>
-      <c r="N47" s="54"/>
-      <c r="O47" s="54"/>
-      <c r="P47" s="54"/>
-      <c r="Q47" s="54"/>
-      <c r="R47" s="55"/>
-      <c r="S47" s="56" t="s">
-        <v>78</v>
+      <c r="L47" s="119"/>
+      <c r="M47" s="119"/>
+      <c r="N47" s="119"/>
+      <c r="O47" s="119"/>
+      <c r="P47" s="119"/>
+      <c r="Q47" s="119"/>
+      <c r="R47" s="120"/>
+      <c r="S47" s="123" t="s">
+        <v>79</v>
       </c>
-      <c r="T47" s="57"/>
-      <c r="U47" s="57"/>
-      <c r="V47" s="57"/>
-      <c r="W47" s="57"/>
-      <c r="X47" s="78"/>
-      <c r="Y47" s="78"/>
-      <c r="Z47" s="78"/>
-      <c r="AA47" s="12" t="s">
+      <c r="T47" s="124"/>
+      <c r="U47" s="124"/>
+      <c r="V47" s="124"/>
+      <c r="W47" s="124"/>
+      <c r="X47" s="140"/>
+      <c r="Y47" s="140"/>
+      <c r="Z47" s="140"/>
+      <c r="AA47" s="33" t="s">
         <v>30</v>
       </c>
-      <c r="AB47" s="96" t="s">
-        <v>80</v>
+      <c r="AB47" s="86" t="s">
+        <v>83</v>
       </c>
-      <c r="AC47" s="97"/>
-      <c r="AD47" s="97"/>
-      <c r="AE47" s="97"/>
-      <c r="AF47" s="53"/>
-      <c r="AG47" s="53"/>
-      <c r="AH47" s="53"/>
-      <c r="AI47" s="53"/>
+      <c r="AC47" s="84"/>
+      <c r="AD47" s="84"/>
+      <c r="AE47" s="84"/>
+      <c r="AF47" s="126"/>
+      <c r="AG47" s="126"/>
+      <c r="AH47" s="126"/>
+      <c r="AI47" s="126"/>
       <c r="AJ47" s="4"/>
     </row>
     <row r="48" spans="1:36" ht="18" customHeight="1">
-      <c r="A48" s="2"/>
-      <c r="B48" s="54" t="s">
-        <v>87</v>
+      <c r="A48" s="34"/>
+      <c r="B48" s="119" t="s">
+        <v>33</v>
       </c>
-      <c r="C48" s="54"/>
-      <c r="D48" s="54"/>
-      <c r="E48" s="54"/>
-      <c r="F48" s="54"/>
-      <c r="G48" s="54"/>
-      <c r="H48" s="54"/>
-      <c r="I48" s="55"/>
+      <c r="C48" s="119"/>
+      <c r="D48" s="119"/>
+      <c r="E48" s="119"/>
+      <c r="F48" s="119"/>
+      <c r="G48" s="119"/>
+      <c r="H48" s="119"/>
+      <c r="I48" s="120"/>
       <c r="J48" s="10"/>
-      <c r="K48" s="54" t="s">
-        <v>31</v>
+      <c r="K48" s="119" t="s">
+        <v>34</v>
       </c>
-      <c r="L48" s="54"/>
-      <c r="M48" s="54"/>
-      <c r="N48" s="54"/>
-      <c r="O48" s="54"/>
-      <c r="P48" s="54"/>
-      <c r="Q48" s="54"/>
-      <c r="R48" s="55"/>
-      <c r="S48" s="98" t="s">
+      <c r="L48" s="119"/>
+      <c r="M48" s="119"/>
+      <c r="N48" s="119"/>
+      <c r="O48" s="119"/>
+      <c r="P48" s="119"/>
+      <c r="Q48" s="119"/>
+      <c r="R48" s="120"/>
+      <c r="S48" s="136" t="s">
+        <v>20</v>
+      </c>
+      <c r="T48" s="137"/>
+      <c r="U48" s="137"/>
+      <c r="V48" s="137"/>
+      <c r="W48" s="137"/>
+      <c r="X48" s="137"/>
+      <c r="Y48" s="137"/>
+      <c r="Z48" s="137"/>
+      <c r="AA48" s="138"/>
+      <c r="AB48" s="121" t="s">
+        <v>78</v>
+      </c>
+      <c r="AC48" s="78"/>
+      <c r="AD48" s="78"/>
+      <c r="AE48" s="78"/>
+      <c r="AF48" s="78"/>
+      <c r="AG48" s="122"/>
+      <c r="AH48" s="122"/>
+      <c r="AI48" s="122"/>
+      <c r="AJ48" s="12" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="49" spans="1:36" ht="18" customHeight="1">
+      <c r="A49" s="10"/>
+      <c r="B49" s="119" t="s">
+        <v>74</v>
+      </c>
+      <c r="C49" s="119"/>
+      <c r="D49" s="119"/>
+      <c r="E49" s="119"/>
+      <c r="F49" s="119"/>
+      <c r="G49" s="119"/>
+      <c r="H49" s="119"/>
+      <c r="I49" s="120"/>
+      <c r="J49" s="10"/>
+      <c r="K49" s="119" t="s">
+        <v>37</v>
+      </c>
+      <c r="L49" s="119"/>
+      <c r="M49" s="119"/>
+      <c r="N49" s="119"/>
+      <c r="O49" s="119"/>
+      <c r="P49" s="119"/>
+      <c r="Q49" s="119"/>
+      <c r="R49" s="120"/>
+      <c r="S49" s="10"/>
+      <c r="T49" s="119" t="s">
+        <v>23</v>
+      </c>
+      <c r="U49" s="119"/>
+      <c r="V49" s="119"/>
+      <c r="W49" s="119"/>
+      <c r="X49" s="119"/>
+      <c r="Y49" s="119"/>
+      <c r="Z49" s="119"/>
+      <c r="AA49" s="120"/>
+      <c r="AB49" s="123" t="s">
         <v>79</v>
       </c>
-      <c r="T48" s="99"/>
-      <c r="U48" s="99"/>
-      <c r="V48" s="99"/>
-      <c r="W48" s="99"/>
-      <c r="X48" s="58"/>
-      <c r="Y48" s="58"/>
-      <c r="Z48" s="58"/>
-      <c r="AA48" s="33" t="s">
-        <v>30</v>
-      </c>
-      <c r="AB48" s="96" t="s">
-        <v>83</v>
-      </c>
-      <c r="AC48" s="97"/>
-      <c r="AD48" s="97"/>
-      <c r="AE48" s="97"/>
-      <c r="AF48" s="86"/>
-      <c r="AG48" s="86"/>
-      <c r="AH48" s="86"/>
-      <c r="AI48" s="86"/>
-      <c r="AJ48" s="4"/>
-    </row>
-    <row r="49" spans="1:36" ht="18" customHeight="1">
-      <c r="A49" s="34"/>
-      <c r="B49" s="54" t="s">
-        <v>33</v>
-      </c>
-      <c r="C49" s="54"/>
-      <c r="D49" s="54"/>
-      <c r="E49" s="54"/>
-      <c r="F49" s="54"/>
-      <c r="G49" s="54"/>
-      <c r="H49" s="54"/>
-      <c r="I49" s="55"/>
-      <c r="J49" s="10"/>
-      <c r="K49" s="54" t="s">
-        <v>34</v>
-      </c>
-      <c r="L49" s="54"/>
-      <c r="M49" s="54"/>
-      <c r="N49" s="54"/>
-      <c r="O49" s="54"/>
-      <c r="P49" s="54"/>
-      <c r="Q49" s="54"/>
-      <c r="R49" s="55"/>
-      <c r="S49" s="75" t="s">
-        <v>20</v>
-      </c>
-      <c r="T49" s="76"/>
-      <c r="U49" s="76"/>
-      <c r="V49" s="76"/>
-      <c r="W49" s="76"/>
-      <c r="X49" s="76"/>
-      <c r="Y49" s="76"/>
-      <c r="Z49" s="76"/>
-      <c r="AA49" s="77"/>
-      <c r="AB49" s="56" t="s">
-        <v>78</v>
-      </c>
-      <c r="AC49" s="57"/>
-      <c r="AD49" s="57"/>
-      <c r="AE49" s="57"/>
-      <c r="AF49" s="57"/>
-      <c r="AG49" s="78"/>
-      <c r="AH49" s="78"/>
-      <c r="AI49" s="78"/>
-      <c r="AJ49" s="12" t="s">
+      <c r="AC49" s="124"/>
+      <c r="AD49" s="124"/>
+      <c r="AE49" s="124"/>
+      <c r="AF49" s="124"/>
+      <c r="AG49" s="140"/>
+      <c r="AH49" s="140"/>
+      <c r="AI49" s="140"/>
+      <c r="AJ49" s="33" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="50" spans="1:36" ht="18" customHeight="1">
       <c r="A50" s="10"/>
-      <c r="B50" s="54" t="s">
-        <v>74</v>
+      <c r="B50" s="119" t="s">
+        <v>75</v>
       </c>
-      <c r="C50" s="54"/>
-      <c r="D50" s="54"/>
-      <c r="E50" s="54"/>
-      <c r="F50" s="54"/>
-      <c r="G50" s="54"/>
-      <c r="H50" s="54"/>
-      <c r="I50" s="55"/>
+      <c r="C50" s="119"/>
+      <c r="D50" s="119"/>
+      <c r="E50" s="119"/>
+      <c r="F50" s="119"/>
+      <c r="G50" s="119"/>
+      <c r="H50" s="119"/>
+      <c r="I50" s="120"/>
       <c r="J50" s="10"/>
-      <c r="K50" s="54" t="s">
-        <v>37</v>
+      <c r="K50" s="119" t="s">
+        <v>39</v>
       </c>
-      <c r="L50" s="54"/>
-      <c r="M50" s="54"/>
-      <c r="N50" s="54"/>
-      <c r="O50" s="54"/>
-      <c r="P50" s="54"/>
-      <c r="Q50" s="54"/>
-      <c r="R50" s="55"/>
+      <c r="L50" s="119"/>
+      <c r="M50" s="119"/>
+      <c r="N50" s="119"/>
+      <c r="O50" s="119"/>
+      <c r="P50" s="119"/>
+      <c r="Q50" s="119"/>
+      <c r="R50" s="120"/>
       <c r="S50" s="10"/>
-      <c r="T50" s="54" t="s">
-        <v>23</v>
+      <c r="T50" s="119" t="s">
+        <v>26</v>
       </c>
-      <c r="U50" s="54"/>
-      <c r="V50" s="54"/>
-      <c r="W50" s="54"/>
-      <c r="X50" s="54"/>
-      <c r="Y50" s="54"/>
-      <c r="Z50" s="54"/>
-      <c r="AA50" s="55"/>
-      <c r="AB50" s="98" t="s">
-        <v>79</v>
+      <c r="U50" s="119"/>
+      <c r="V50" s="119"/>
+      <c r="W50" s="119"/>
+      <c r="X50" s="119"/>
+      <c r="Y50" s="119"/>
+      <c r="Z50" s="119"/>
+      <c r="AA50" s="120"/>
+      <c r="AB50" s="127" t="s">
+        <v>38</v>
       </c>
-      <c r="AC50" s="99"/>
-      <c r="AD50" s="99"/>
-      <c r="AE50" s="99"/>
-      <c r="AF50" s="99"/>
-      <c r="AG50" s="58"/>
-      <c r="AH50" s="58"/>
-      <c r="AI50" s="58"/>
-      <c r="AJ50" s="33" t="s">
-        <v>30</v>
-      </c>
+      <c r="AC50" s="128"/>
+      <c r="AD50" s="128"/>
+      <c r="AE50" s="128"/>
+      <c r="AF50" s="128"/>
+      <c r="AG50" s="128"/>
+      <c r="AH50" s="128"/>
+      <c r="AI50" s="128"/>
+      <c r="AJ50" s="129"/>
     </row>
     <row r="51" spans="1:36" ht="18" customHeight="1">
       <c r="A51" s="10"/>
-      <c r="B51" s="54" t="s">
-        <v>75</v>
+      <c r="B51" s="119" t="s">
+        <v>40</v>
       </c>
-      <c r="C51" s="54"/>
-      <c r="D51" s="54"/>
-      <c r="E51" s="54"/>
-      <c r="F51" s="54"/>
-      <c r="G51" s="54"/>
-      <c r="H51" s="54"/>
-      <c r="I51" s="55"/>
+      <c r="C51" s="119"/>
+      <c r="D51" s="119"/>
+      <c r="E51" s="119"/>
+      <c r="F51" s="119"/>
+      <c r="G51" s="119"/>
+      <c r="H51" s="119"/>
+      <c r="I51" s="120"/>
       <c r="J51" s="10"/>
-      <c r="K51" s="54" t="s">
-        <v>39</v>
+      <c r="K51" s="119" t="s">
+        <v>41</v>
       </c>
-      <c r="L51" s="54"/>
-      <c r="M51" s="54"/>
-      <c r="N51" s="54"/>
-      <c r="O51" s="54"/>
-      <c r="P51" s="54"/>
-      <c r="Q51" s="54"/>
-      <c r="R51" s="55"/>
+      <c r="L51" s="119"/>
+      <c r="M51" s="119"/>
+      <c r="N51" s="119"/>
+      <c r="O51" s="119"/>
+      <c r="P51" s="119"/>
+      <c r="Q51" s="119"/>
+      <c r="R51" s="120"/>
       <c r="S51" s="10"/>
-      <c r="T51" s="54" t="s">
-        <v>26</v>
+      <c r="T51" s="119" t="s">
+        <v>29</v>
       </c>
-      <c r="U51" s="54"/>
-      <c r="V51" s="54"/>
-      <c r="W51" s="54"/>
-      <c r="X51" s="54"/>
-      <c r="Y51" s="54"/>
-      <c r="Z51" s="54"/>
-      <c r="AA51" s="55"/>
-      <c r="AB51" s="102" t="s">
-        <v>38</v>
+      <c r="U51" s="119"/>
+      <c r="V51" s="119"/>
+      <c r="W51" s="122"/>
+      <c r="X51" s="122"/>
+      <c r="Y51" s="122"/>
+      <c r="Z51" s="3" t="s">
+        <v>30</v>
       </c>
-      <c r="AC51" s="103"/>
-      <c r="AD51" s="103"/>
-      <c r="AE51" s="103"/>
-      <c r="AF51" s="103"/>
-      <c r="AG51" s="103"/>
-      <c r="AH51" s="103"/>
-      <c r="AI51" s="103"/>
-      <c r="AJ51" s="104"/>
+      <c r="AA51" s="4"/>
+      <c r="AB51" s="10"/>
+      <c r="AC51" s="130" t="s">
+        <v>76</v>
+      </c>
+      <c r="AD51" s="130"/>
+      <c r="AE51" s="130"/>
+      <c r="AF51" s="130"/>
+      <c r="AG51" s="130"/>
+      <c r="AH51" s="130"/>
+      <c r="AI51" s="130"/>
+      <c r="AJ51" s="131"/>
     </row>
     <row r="52" spans="1:36" ht="18" customHeight="1">
       <c r="A52" s="10"/>
-      <c r="B52" s="54" t="s">
-        <v>40</v>
+      <c r="B52" s="119" t="s">
+        <v>43</v>
       </c>
-      <c r="C52" s="54"/>
-      <c r="D52" s="54"/>
-      <c r="E52" s="54"/>
-      <c r="F52" s="54"/>
-      <c r="G52" s="54"/>
-      <c r="H52" s="54"/>
-      <c r="I52" s="55"/>
+      <c r="C52" s="119"/>
+      <c r="D52" s="132"/>
+      <c r="E52" s="132"/>
+      <c r="F52" s="132"/>
+      <c r="G52" s="132"/>
+      <c r="H52" s="132"/>
+      <c r="I52" s="4"/>
       <c r="J52" s="10"/>
-      <c r="K52" s="54" t="s">
-        <v>41</v>
+      <c r="K52" s="119" t="s">
+        <v>44</v>
       </c>
-      <c r="L52" s="54"/>
-      <c r="M52" s="54"/>
-      <c r="N52" s="54"/>
-      <c r="O52" s="54"/>
-      <c r="P52" s="54"/>
-      <c r="Q52" s="54"/>
-      <c r="R52" s="55"/>
+      <c r="L52" s="119"/>
+      <c r="M52" s="119"/>
+      <c r="N52" s="119"/>
+      <c r="O52" s="119"/>
+      <c r="P52" s="119"/>
+      <c r="Q52" s="119"/>
+      <c r="R52" s="120"/>
       <c r="S52" s="10"/>
-      <c r="T52" s="54" t="s">
-        <v>29</v>
+      <c r="T52" s="119" t="s">
+        <v>32</v>
       </c>
-      <c r="U52" s="54"/>
-      <c r="V52" s="54"/>
-      <c r="W52" s="78"/>
-      <c r="X52" s="78"/>
-      <c r="Y52" s="78"/>
+      <c r="U52" s="119"/>
+      <c r="V52" s="119"/>
+      <c r="W52" s="122"/>
+      <c r="X52" s="122"/>
+      <c r="Y52" s="122"/>
       <c r="Z52" s="3" t="s">
         <v>30</v>
       </c>
       <c r="AA52" s="4"/>
       <c r="AB52" s="10"/>
-      <c r="AC52" s="105" t="s">
-        <v>76</v>
+      <c r="AC52" s="119" t="s">
+        <v>42</v>
       </c>
-      <c r="AD52" s="105"/>
-      <c r="AE52" s="105"/>
-      <c r="AF52" s="105"/>
-      <c r="AG52" s="105"/>
-      <c r="AH52" s="105"/>
-      <c r="AI52" s="105"/>
-      <c r="AJ52" s="106"/>
+      <c r="AD52" s="119"/>
+      <c r="AE52" s="119"/>
+      <c r="AF52" s="119"/>
+      <c r="AG52" s="119"/>
+      <c r="AH52" s="119"/>
+      <c r="AI52" s="119"/>
+      <c r="AJ52" s="120"/>
     </row>
     <row r="53" spans="1:36" ht="18" customHeight="1">
-      <c r="A53" s="10"/>
-      <c r="B53" s="54" t="s">
-        <v>43</v>
+      <c r="A53" s="13"/>
+      <c r="B53" s="7"/>
+      <c r="C53" s="7"/>
+      <c r="D53" s="143"/>
+      <c r="E53" s="143"/>
+      <c r="F53" s="143"/>
+      <c r="G53" s="143"/>
+      <c r="H53" s="143"/>
+      <c r="I53" s="8"/>
+      <c r="J53" s="123"/>
+      <c r="K53" s="124"/>
+      <c r="L53" s="124"/>
+      <c r="M53" s="124"/>
+      <c r="N53" s="124"/>
+      <c r="O53" s="124"/>
+      <c r="P53" s="124"/>
+      <c r="Q53" s="124"/>
+      <c r="R53" s="125"/>
+      <c r="S53" s="13"/>
+      <c r="T53" s="139" t="s">
+        <v>35</v>
       </c>
-      <c r="C53" s="54"/>
-      <c r="D53" s="107"/>
-      <c r="E53" s="107"/>
-      <c r="F53" s="107"/>
-      <c r="G53" s="107"/>
-      <c r="H53" s="107"/>
-      <c r="I53" s="4"/>
-      <c r="J53" s="10"/>
-      <c r="K53" s="54" t="s">
-        <v>44</v>
+      <c r="U53" s="139"/>
+      <c r="V53" s="139"/>
+      <c r="W53" s="140"/>
+      <c r="X53" s="140"/>
+      <c r="Y53" s="140"/>
+      <c r="Z53" s="6" t="s">
+        <v>36</v>
       </c>
-      <c r="L53" s="54"/>
-      <c r="M53" s="54"/>
-      <c r="N53" s="54"/>
-      <c r="O53" s="54"/>
-      <c r="P53" s="54"/>
-      <c r="Q53" s="54"/>
-      <c r="R53" s="55"/>
-      <c r="S53" s="10"/>
-      <c r="T53" s="54" t="s">
-        <v>32</v>
+      <c r="AA53" s="8"/>
+      <c r="AB53" s="13"/>
+      <c r="AC53" s="139" t="s">
+        <v>45</v>
       </c>
-      <c r="U53" s="54"/>
-      <c r="V53" s="54"/>
-      <c r="W53" s="78"/>
-      <c r="X53" s="78"/>
-      <c r="Y53" s="78"/>
-      <c r="Z53" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="AA53" s="4"/>
-      <c r="AB53" s="10"/>
-      <c r="AC53" s="54" t="s">
-        <v>42</v>
-      </c>
-      <c r="AD53" s="54"/>
-      <c r="AE53" s="54"/>
-      <c r="AF53" s="54"/>
-      <c r="AG53" s="54"/>
-      <c r="AH53" s="54"/>
-      <c r="AI53" s="54"/>
-      <c r="AJ53" s="55"/>
+      <c r="AD53" s="139"/>
+      <c r="AE53" s="139"/>
+      <c r="AF53" s="103"/>
+      <c r="AG53" s="103"/>
+      <c r="AH53" s="103"/>
+      <c r="AI53" s="7"/>
+      <c r="AJ53" s="8"/>
     </row>
     <row r="54" spans="1:36" ht="18" customHeight="1">
-      <c r="A54" s="13"/>
-      <c r="B54" s="7"/>
-      <c r="C54" s="7"/>
-      <c r="D54" s="83"/>
-      <c r="E54" s="83"/>
-      <c r="F54" s="83"/>
-      <c r="G54" s="83"/>
-      <c r="H54" s="83"/>
-      <c r="I54" s="8"/>
-      <c r="J54" s="98"/>
-      <c r="K54" s="99"/>
-      <c r="L54" s="99"/>
-      <c r="M54" s="99"/>
-      <c r="N54" s="99"/>
-      <c r="O54" s="99"/>
-      <c r="P54" s="99"/>
-      <c r="Q54" s="99"/>
-      <c r="R54" s="100"/>
-      <c r="S54" s="13"/>
-      <c r="T54" s="79" t="s">
-        <v>35</v>
+      <c r="A54" s="141" t="s">
+        <v>46</v>
       </c>
-      <c r="U54" s="79"/>
-      <c r="V54" s="79"/>
-      <c r="W54" s="58"/>
-      <c r="X54" s="58"/>
-      <c r="Y54" s="58"/>
-      <c r="Z54" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="AA54" s="8"/>
-      <c r="AB54" s="13"/>
-      <c r="AC54" s="79" t="s">
-        <v>45</v>
-      </c>
-      <c r="AD54" s="79"/>
-      <c r="AE54" s="79"/>
-      <c r="AF54" s="101"/>
-      <c r="AG54" s="101"/>
-      <c r="AH54" s="101"/>
-      <c r="AI54" s="7"/>
-      <c r="AJ54" s="8"/>
+      <c r="B54" s="141"/>
+      <c r="C54" s="141"/>
+      <c r="D54" s="141"/>
+      <c r="E54" s="141"/>
+      <c r="F54" s="141"/>
+      <c r="G54" s="141"/>
+      <c r="H54" s="141"/>
+      <c r="I54" s="141"/>
+      <c r="J54" s="141"/>
+      <c r="K54" s="141"/>
+      <c r="L54" s="141"/>
+      <c r="M54" s="141"/>
+      <c r="N54" s="142"/>
+      <c r="O54" s="142"/>
+      <c r="P54" s="142"/>
+      <c r="Q54" s="142"/>
+      <c r="R54" s="142"/>
+      <c r="S54" s="142"/>
+      <c r="T54" s="142"/>
+      <c r="U54" s="142"/>
+      <c r="V54" s="142"/>
+      <c r="W54" s="142"/>
+      <c r="X54" s="142"/>
+      <c r="Y54" s="142"/>
+      <c r="Z54" s="142"/>
+      <c r="AA54" s="142"/>
+      <c r="AB54" s="142"/>
+      <c r="AC54" s="142"/>
+      <c r="AD54" s="142"/>
+      <c r="AE54" s="142"/>
+      <c r="AF54" s="142"/>
+      <c r="AG54" s="142"/>
+      <c r="AH54" s="142"/>
+      <c r="AI54" s="142"/>
+      <c r="AJ54" s="142"/>
     </row>
     <row r="55" spans="1:36" ht="18" customHeight="1">
-      <c r="A55" s="81" t="s">
-        <v>46</v>
+      <c r="A55" s="134"/>
+      <c r="B55" s="53"/>
+      <c r="C55" s="53"/>
+      <c r="D55" s="53"/>
+      <c r="E55" s="53"/>
+      <c r="F55" s="53"/>
+      <c r="G55" s="53"/>
+      <c r="H55" s="53"/>
+      <c r="I55" s="53"/>
+      <c r="J55" s="53"/>
+      <c r="K55" s="53"/>
+      <c r="L55" s="53"/>
+      <c r="N55" s="53"/>
+      <c r="O55" s="53"/>
+      <c r="P55" s="53"/>
+      <c r="Q55" s="53"/>
+      <c r="R55" s="53"/>
+      <c r="S55" s="53"/>
+      <c r="T55" s="53"/>
+      <c r="U55" s="53"/>
+      <c r="V55" s="53"/>
+      <c r="W55" s="53"/>
+      <c r="X55" s="53"/>
+      <c r="Y55" s="134"/>
+      <c r="Z55" s="134"/>
+      <c r="AA55" s="134"/>
+      <c r="AB55" s="144" t="s">
+        <v>93</v>
       </c>
-      <c r="B55" s="81"/>
-      <c r="C55" s="81"/>
-      <c r="D55" s="81"/>
-      <c r="E55" s="81"/>
-      <c r="F55" s="81"/>
-      <c r="G55" s="81"/>
-      <c r="H55" s="81"/>
-      <c r="I55" s="81"/>
-      <c r="J55" s="81"/>
-      <c r="K55" s="81"/>
-      <c r="L55" s="81"/>
-      <c r="M55" s="81"/>
-      <c r="N55" s="82"/>
-      <c r="O55" s="82"/>
-      <c r="P55" s="82"/>
-      <c r="Q55" s="82"/>
-      <c r="R55" s="82"/>
-      <c r="S55" s="82"/>
-      <c r="T55" s="82"/>
-      <c r="U55" s="82"/>
-      <c r="V55" s="82"/>
-      <c r="W55" s="82"/>
-      <c r="X55" s="82"/>
-      <c r="Y55" s="82"/>
-      <c r="Z55" s="82"/>
-      <c r="AA55" s="82"/>
-      <c r="AB55" s="82"/>
-      <c r="AC55" s="82"/>
-      <c r="AD55" s="82"/>
-      <c r="AE55" s="82"/>
-      <c r="AF55" s="82"/>
-      <c r="AG55" s="82"/>
-      <c r="AH55" s="82"/>
-      <c r="AI55" s="82"/>
-      <c r="AJ55" s="82"/>
+      <c r="AC55" s="102"/>
+      <c r="AD55" s="102"/>
+      <c r="AE55" s="102"/>
+      <c r="AF55" s="102"/>
+      <c r="AG55" s="102"/>
+      <c r="AH55" s="102"/>
+      <c r="AI55" s="102"/>
+      <c r="AJ55" s="102"/>
     </row>
     <row r="56" spans="1:36" ht="18" customHeight="1">
-      <c r="A56" s="72"/>
-      <c r="B56" s="80"/>
-      <c r="C56" s="80"/>
-      <c r="D56" s="80"/>
-      <c r="E56" s="80"/>
-      <c r="F56" s="80"/>
-      <c r="G56" s="80"/>
-      <c r="H56" s="80"/>
-      <c r="I56" s="80"/>
-      <c r="J56" s="80"/>
-      <c r="K56" s="80"/>
-      <c r="L56" s="80"/>
-      <c r="N56" s="80"/>
-      <c r="O56" s="80"/>
-      <c r="P56" s="80"/>
-      <c r="Q56" s="80"/>
-      <c r="R56" s="80"/>
-      <c r="S56" s="80"/>
-      <c r="T56" s="80"/>
-      <c r="U56" s="80"/>
-      <c r="V56" s="80"/>
-      <c r="W56" s="80"/>
-      <c r="X56" s="80"/>
-      <c r="Y56" s="72"/>
-      <c r="Z56" s="72"/>
-      <c r="AA56" s="72"/>
-      <c r="AB56" s="84" t="s">
-        <v>93</v>
+      <c r="A56" s="134"/>
+      <c r="B56" s="53"/>
+      <c r="C56" s="53"/>
+      <c r="D56" s="53"/>
+      <c r="E56" s="53"/>
+      <c r="F56" s="53"/>
+      <c r="G56" s="53"/>
+      <c r="H56" s="53"/>
+      <c r="I56" s="53"/>
+      <c r="J56" s="53"/>
+      <c r="K56" s="53"/>
+      <c r="L56" s="53"/>
+      <c r="N56" s="53"/>
+      <c r="O56" s="53"/>
+      <c r="P56" s="53"/>
+      <c r="Q56" s="53"/>
+      <c r="R56" s="53"/>
+      <c r="S56" s="53"/>
+      <c r="T56" s="53"/>
+      <c r="U56" s="53"/>
+      <c r="V56" s="53"/>
+      <c r="W56" s="53"/>
+      <c r="X56" s="53"/>
+      <c r="Y56" s="134"/>
+      <c r="Z56" s="134"/>
+      <c r="AA56" s="134"/>
+      <c r="AB56" s="135" t="s">
+        <v>47</v>
       </c>
-      <c r="AC56" s="85"/>
-      <c r="AD56" s="85"/>
-      <c r="AE56" s="85"/>
-      <c r="AF56" s="85"/>
-      <c r="AG56" s="85"/>
-      <c r="AH56" s="85"/>
-      <c r="AI56" s="85"/>
-      <c r="AJ56" s="85"/>
+      <c r="AC56" s="135"/>
+      <c r="AD56" s="135"/>
+      <c r="AE56" s="135"/>
+      <c r="AF56" s="135"/>
+      <c r="AG56" s="135"/>
+      <c r="AH56" s="135"/>
+      <c r="AI56" s="135"/>
+      <c r="AJ56" s="135"/>
     </row>
     <row r="57" spans="1:36" ht="18" customHeight="1">
-      <c r="A57" s="72"/>
-      <c r="B57" s="80"/>
-      <c r="C57" s="80"/>
-      <c r="D57" s="80"/>
-      <c r="E57" s="80"/>
-      <c r="F57" s="80"/>
-      <c r="G57" s="80"/>
-      <c r="H57" s="80"/>
-      <c r="I57" s="80"/>
-      <c r="J57" s="80"/>
-      <c r="K57" s="80"/>
-      <c r="L57" s="80"/>
-      <c r="N57" s="80"/>
-      <c r="O57" s="80"/>
-      <c r="P57" s="80"/>
-      <c r="Q57" s="80"/>
-      <c r="R57" s="80"/>
-      <c r="S57" s="80"/>
-      <c r="T57" s="80"/>
-      <c r="U57" s="80"/>
-      <c r="V57" s="80"/>
-      <c r="W57" s="80"/>
-      <c r="X57" s="80"/>
-      <c r="Y57" s="72"/>
-      <c r="Z57" s="72"/>
-      <c r="AA57" s="72"/>
-      <c r="AB57" s="74" t="s">
-        <v>47</v>
-      </c>
-      <c r="AC57" s="74"/>
-      <c r="AD57" s="74"/>
-      <c r="AE57" s="74"/>
-      <c r="AF57" s="74"/>
-      <c r="AG57" s="74"/>
-      <c r="AH57" s="74"/>
-      <c r="AI57" s="74"/>
-      <c r="AJ57" s="74"/>
+      <c r="A57" s="134"/>
+      <c r="B57" s="53"/>
+      <c r="C57" s="53"/>
+      <c r="D57" s="53"/>
+      <c r="E57" s="53"/>
+      <c r="F57" s="53"/>
+      <c r="G57" s="53"/>
+      <c r="H57" s="53"/>
+      <c r="I57" s="53"/>
+      <c r="J57" s="53"/>
+      <c r="K57" s="53"/>
+      <c r="L57" s="53"/>
+      <c r="N57" s="53"/>
+      <c r="O57" s="53"/>
+      <c r="P57" s="53"/>
+      <c r="Q57" s="53"/>
+      <c r="R57" s="53"/>
+      <c r="S57" s="53"/>
+      <c r="T57" s="53"/>
+      <c r="U57" s="53"/>
+      <c r="V57" s="53"/>
+      <c r="W57" s="53"/>
+      <c r="X57" s="53"/>
+      <c r="Y57" s="134"/>
+      <c r="Z57" s="134"/>
+      <c r="AA57" s="134"/>
+      <c r="AB57" s="134"/>
+      <c r="AC57" s="134"/>
+      <c r="AD57" s="134"/>
+      <c r="AE57" s="134"/>
+      <c r="AF57" s="134"/>
+      <c r="AG57" s="134"/>
+      <c r="AH57" s="134"/>
+      <c r="AI57" s="134"/>
+      <c r="AJ57" s="134"/>
     </row>
     <row r="58" spans="1:36" ht="18" customHeight="1">
-      <c r="A58" s="72"/>
-      <c r="B58" s="80"/>
-      <c r="C58" s="80"/>
-      <c r="D58" s="80"/>
-      <c r="E58" s="80"/>
-      <c r="F58" s="80"/>
-      <c r="G58" s="80"/>
-      <c r="H58" s="80"/>
-      <c r="I58" s="80"/>
-      <c r="J58" s="80"/>
-      <c r="K58" s="80"/>
-      <c r="L58" s="80"/>
-      <c r="N58" s="80"/>
-      <c r="O58" s="80"/>
-      <c r="P58" s="80"/>
-      <c r="Q58" s="80"/>
-      <c r="R58" s="80"/>
-      <c r="S58" s="80"/>
-      <c r="T58" s="80"/>
-      <c r="U58" s="80"/>
-      <c r="V58" s="80"/>
-      <c r="W58" s="80"/>
-      <c r="X58" s="80"/>
-      <c r="Y58" s="72"/>
-      <c r="Z58" s="72"/>
-      <c r="AA58" s="72"/>
-      <c r="AB58" s="72"/>
-      <c r="AC58" s="72"/>
-      <c r="AD58" s="72"/>
-      <c r="AE58" s="72"/>
-      <c r="AF58" s="72"/>
-      <c r="AG58" s="72"/>
-      <c r="AH58" s="72"/>
-      <c r="AI58" s="72"/>
-      <c r="AJ58" s="72"/>
+      <c r="A58" s="51"/>
+      <c r="B58" s="52"/>
+      <c r="C58" s="52"/>
+      <c r="D58" s="52"/>
+      <c r="E58" s="52"/>
+      <c r="F58" s="52"/>
+      <c r="G58" s="52"/>
+      <c r="H58" s="52"/>
+      <c r="I58" s="52"/>
+      <c r="J58" s="52"/>
+      <c r="K58" s="52"/>
+      <c r="L58" s="52"/>
+      <c r="N58" s="52"/>
+      <c r="O58" s="52"/>
+      <c r="P58" s="52"/>
+      <c r="Q58" s="52"/>
+      <c r="R58" s="52"/>
+      <c r="S58" s="52"/>
+      <c r="T58" s="52"/>
+      <c r="U58" s="52"/>
+      <c r="V58" s="52"/>
+      <c r="W58" s="52"/>
+      <c r="X58" s="52"/>
+      <c r="Y58" s="134"/>
+      <c r="Z58" s="134"/>
+      <c r="AA58" s="134"/>
+      <c r="AB58" s="134"/>
+      <c r="AC58" s="134"/>
+      <c r="AD58" s="134"/>
+      <c r="AE58" s="134"/>
+      <c r="AF58" s="134"/>
+      <c r="AG58" s="134"/>
+      <c r="AH58" s="134"/>
+      <c r="AI58" s="134"/>
+      <c r="AJ58" s="134"/>
     </row>
     <row r="59" spans="1:36" ht="18" customHeight="1">
-      <c r="A59" s="51"/>
-      <c r="B59" s="52"/>
-      <c r="C59" s="52"/>
-      <c r="D59" s="52"/>
-      <c r="E59" s="52"/>
-      <c r="F59" s="52"/>
-      <c r="G59" s="52"/>
-      <c r="H59" s="52"/>
-      <c r="I59" s="52"/>
-      <c r="J59" s="52"/>
-      <c r="K59" s="52"/>
-      <c r="L59" s="52"/>
-      <c r="N59" s="52"/>
-      <c r="O59" s="52"/>
-      <c r="P59" s="52"/>
-      <c r="Q59" s="52"/>
-      <c r="R59" s="52"/>
-      <c r="S59" s="52"/>
-      <c r="T59" s="52"/>
-      <c r="U59" s="52"/>
-      <c r="V59" s="52"/>
-      <c r="W59" s="52"/>
-      <c r="X59" s="52"/>
-      <c r="Y59" s="72"/>
-      <c r="Z59" s="72"/>
-      <c r="AA59" s="72"/>
-      <c r="AB59" s="72"/>
-      <c r="AC59" s="72"/>
-      <c r="AD59" s="72"/>
-      <c r="AE59" s="72"/>
-      <c r="AF59" s="72"/>
-      <c r="AG59" s="72"/>
-      <c r="AH59" s="72"/>
-      <c r="AI59" s="72"/>
-      <c r="AJ59" s="72"/>
+      <c r="A59" s="134"/>
+      <c r="B59" s="134"/>
+      <c r="C59" s="134"/>
+      <c r="D59" s="134"/>
+      <c r="E59" s="134"/>
+      <c r="F59" s="134"/>
+      <c r="G59" s="134"/>
+      <c r="H59" s="134"/>
+      <c r="I59" s="134"/>
+      <c r="J59" s="134"/>
+      <c r="K59" s="134"/>
+      <c r="L59" s="134"/>
+      <c r="M59" s="134"/>
+      <c r="N59" s="134"/>
+      <c r="O59" s="134"/>
+      <c r="P59" s="134"/>
+      <c r="Q59" s="134"/>
+      <c r="R59" s="134"/>
+      <c r="S59" s="134"/>
+      <c r="T59" s="134"/>
+      <c r="U59" s="134"/>
+      <c r="V59" s="134"/>
+      <c r="W59" s="134"/>
+      <c r="X59" s="134"/>
+      <c r="Y59" s="134"/>
+      <c r="Z59" s="134"/>
+      <c r="AA59" s="134"/>
+      <c r="AB59" s="85"/>
+      <c r="AC59" s="85"/>
+      <c r="AD59" s="85"/>
+      <c r="AE59" s="85"/>
+      <c r="AF59" s="85"/>
+      <c r="AG59" s="85"/>
+      <c r="AH59" s="85"/>
+      <c r="AI59" s="85"/>
+      <c r="AJ59" s="85"/>
     </row>
     <row r="60" spans="1:36" ht="18" customHeight="1">
-      <c r="A60" s="72"/>
-      <c r="B60" s="72"/>
-      <c r="C60" s="72"/>
-      <c r="D60" s="72"/>
-      <c r="E60" s="72"/>
-      <c r="F60" s="72"/>
-      <c r="G60" s="72"/>
-      <c r="H60" s="72"/>
-      <c r="I60" s="72"/>
-      <c r="J60" s="72"/>
-      <c r="K60" s="72"/>
-      <c r="L60" s="72"/>
-      <c r="M60" s="72"/>
-      <c r="N60" s="72"/>
-      <c r="O60" s="72"/>
-      <c r="P60" s="72"/>
-      <c r="Q60" s="72"/>
-      <c r="R60" s="72"/>
-      <c r="S60" s="72"/>
-      <c r="T60" s="72"/>
-      <c r="U60" s="72"/>
-      <c r="V60" s="72"/>
-      <c r="W60" s="72"/>
-      <c r="X60" s="72"/>
-      <c r="Y60" s="72"/>
-      <c r="Z60" s="72"/>
-      <c r="AA60" s="72"/>
-      <c r="AB60" s="73"/>
-      <c r="AC60" s="73"/>
-      <c r="AD60" s="73"/>
-      <c r="AE60" s="73"/>
-      <c r="AF60" s="73"/>
-      <c r="AG60" s="73"/>
-      <c r="AH60" s="73"/>
-      <c r="AI60" s="73"/>
-      <c r="AJ60" s="73"/>
-    </row>
-    <row r="61" spans="1:36" ht="18" customHeight="1">
-      <c r="Y61" s="72"/>
-      <c r="Z61" s="72"/>
-      <c r="AA61" s="72"/>
-      <c r="AB61" s="71" t="s">
+      <c r="Y60" s="134"/>
+      <c r="Z60" s="134"/>
+      <c r="AA60" s="134"/>
+      <c r="AB60" s="133" t="s">
         <v>92</v>
       </c>
-      <c r="AC61" s="71"/>
-      <c r="AD61" s="71"/>
-      <c r="AE61" s="71"/>
-      <c r="AF61" s="71"/>
-      <c r="AG61" s="71"/>
-      <c r="AH61" s="71"/>
-      <c r="AI61" s="71"/>
-      <c r="AJ61" s="71"/>
+      <c r="AC60" s="133"/>
+      <c r="AD60" s="133"/>
+      <c r="AE60" s="133"/>
+      <c r="AF60" s="133"/>
+      <c r="AG60" s="133"/>
+      <c r="AH60" s="133"/>
+      <c r="AI60" s="133"/>
+      <c r="AJ60" s="133"/>
     </row>
-    <row r="62" spans="1:36" ht="16.5" customHeight="1"/>
+    <row r="61" spans="1:36" ht="16.5" customHeight="1"/>
+    <row r="62" spans="1:36" ht="18" hidden="1" customHeight="1"/>
     <row r="63" spans="1:36" ht="18" hidden="1" customHeight="1"/>
     <row r="64" spans="1:36" ht="18" hidden="1" customHeight="1"/>
     <row r="65" ht="18" hidden="1" customHeight="1"/>
@@ -10072,12 +10023,121 @@
     <row r="654" ht="18" hidden="1" customHeight="1"/>
     <row r="655" ht="18" hidden="1" customHeight="1"/>
     <row r="656" ht="18" hidden="1" customHeight="1"/>
-    <row r="657" ht="18" hidden="1" customHeight="1"/>
+    <row r="657"/>
     <row r="658"/>
   </sheetData>
-  <mergeCells count="133">
-    <mergeCell ref="B58:L58"/>
-    <mergeCell ref="N58:X58"/>
+  <mergeCells count="132">
+    <mergeCell ref="AF46:AI46"/>
+    <mergeCell ref="T50:AA50"/>
+    <mergeCell ref="AF45:AI45"/>
+    <mergeCell ref="AB48:AF48"/>
+    <mergeCell ref="X47:Z47"/>
+    <mergeCell ref="AG49:AI49"/>
+    <mergeCell ref="W45:Z45"/>
+    <mergeCell ref="T51:V51"/>
+    <mergeCell ref="A27:AJ29"/>
+    <mergeCell ref="A36:R36"/>
+    <mergeCell ref="B47:I47"/>
+    <mergeCell ref="S43:AA43"/>
+    <mergeCell ref="B51:I51"/>
+    <mergeCell ref="AF44:AI44"/>
+    <mergeCell ref="A30:O30"/>
+    <mergeCell ref="B44:I44"/>
+    <mergeCell ref="AB43:AJ43"/>
+    <mergeCell ref="J43:R43"/>
+    <mergeCell ref="W44:Y44"/>
+    <mergeCell ref="A31:AJ35"/>
+    <mergeCell ref="A37:AJ40"/>
+    <mergeCell ref="B45:I45"/>
+    <mergeCell ref="AB47:AE47"/>
+    <mergeCell ref="B46:I46"/>
+    <mergeCell ref="AB60:AJ60"/>
+    <mergeCell ref="AB57:AJ59"/>
+    <mergeCell ref="AB56:AJ56"/>
+    <mergeCell ref="S48:AA48"/>
+    <mergeCell ref="AG48:AI48"/>
+    <mergeCell ref="AC53:AE53"/>
+    <mergeCell ref="T52:V52"/>
+    <mergeCell ref="W53:Y53"/>
+    <mergeCell ref="B56:L56"/>
+    <mergeCell ref="N56:X56"/>
+    <mergeCell ref="Y55:AA60"/>
+    <mergeCell ref="A59:X59"/>
+    <mergeCell ref="A55:A57"/>
+    <mergeCell ref="N55:X55"/>
+    <mergeCell ref="A54:M54"/>
+    <mergeCell ref="N54:AJ54"/>
+    <mergeCell ref="D53:H53"/>
+    <mergeCell ref="B50:I50"/>
+    <mergeCell ref="B55:L55"/>
+    <mergeCell ref="K52:R52"/>
+    <mergeCell ref="T53:V53"/>
+    <mergeCell ref="AB55:AJ55"/>
+    <mergeCell ref="W51:Y51"/>
+    <mergeCell ref="AC52:AJ52"/>
+    <mergeCell ref="J53:R53"/>
+    <mergeCell ref="B48:I48"/>
+    <mergeCell ref="AF47:AI47"/>
+    <mergeCell ref="AB49:AF49"/>
+    <mergeCell ref="AF53:AH53"/>
+    <mergeCell ref="AB50:AJ50"/>
+    <mergeCell ref="AC51:AJ51"/>
+    <mergeCell ref="B49:I49"/>
+    <mergeCell ref="B52:C52"/>
+    <mergeCell ref="D52:H52"/>
+    <mergeCell ref="K50:R50"/>
+    <mergeCell ref="K51:R51"/>
+    <mergeCell ref="S47:W47"/>
+    <mergeCell ref="T49:AA49"/>
+    <mergeCell ref="K48:R48"/>
+    <mergeCell ref="K49:R49"/>
+    <mergeCell ref="W52:Y52"/>
+    <mergeCell ref="K47:R47"/>
+    <mergeCell ref="K44:R44"/>
+    <mergeCell ref="AB46:AE46"/>
+    <mergeCell ref="S44:V44"/>
+    <mergeCell ref="S45:V45"/>
+    <mergeCell ref="S46:W46"/>
+    <mergeCell ref="X46:Z46"/>
+    <mergeCell ref="K46:R46"/>
+    <mergeCell ref="K45:R45"/>
+    <mergeCell ref="AB44:AE44"/>
+    <mergeCell ref="A5:B5"/>
+    <mergeCell ref="A6:B6"/>
+    <mergeCell ref="AD6:AF6"/>
+    <mergeCell ref="D9:R9"/>
+    <mergeCell ref="K7:O7"/>
+    <mergeCell ref="AB45:AE45"/>
+    <mergeCell ref="A25:AJ25"/>
+    <mergeCell ref="A22:AJ23"/>
+    <mergeCell ref="A17:T20"/>
+    <mergeCell ref="C5:I5"/>
+    <mergeCell ref="AF19:AG19"/>
+    <mergeCell ref="A43:I43"/>
+    <mergeCell ref="AI19:AJ19"/>
+    <mergeCell ref="A14:H14"/>
+    <mergeCell ref="I14:AJ14"/>
+    <mergeCell ref="AI17:AJ17"/>
+    <mergeCell ref="AF17:AG17"/>
+    <mergeCell ref="A15:AJ15"/>
+    <mergeCell ref="AF18:AG18"/>
+    <mergeCell ref="AA5:AJ5"/>
+    <mergeCell ref="V7:W7"/>
+    <mergeCell ref="AI18:AJ18"/>
+    <mergeCell ref="U16:AD16"/>
+    <mergeCell ref="AF7:AG7"/>
+    <mergeCell ref="S9:W9"/>
+    <mergeCell ref="A7:B7"/>
+    <mergeCell ref="Q11:AJ11"/>
+    <mergeCell ref="C7:I7"/>
+    <mergeCell ref="D8:R8"/>
+    <mergeCell ref="A8:C8"/>
+    <mergeCell ref="S7:T7"/>
+    <mergeCell ref="P7:R7"/>
+    <mergeCell ref="X8:AJ8"/>
+    <mergeCell ref="A10:AJ10"/>
+    <mergeCell ref="B57:L57"/>
+    <mergeCell ref="N57:X57"/>
     <mergeCell ref="Q2:Z2"/>
     <mergeCell ref="Q3:Z3"/>
     <mergeCell ref="A11:P11"/>
@@ -10085,7 +10145,6 @@
     <mergeCell ref="K6:O6"/>
     <mergeCell ref="P6:X6"/>
     <mergeCell ref="A41:R41"/>
-    <mergeCell ref="A42:AJ43"/>
     <mergeCell ref="AE16:AJ16"/>
     <mergeCell ref="A16:T16"/>
     <mergeCell ref="AD3:AJ3"/>
@@ -10100,115 +10159,6 @@
     <mergeCell ref="A9:C9"/>
     <mergeCell ref="X9:AJ9"/>
     <mergeCell ref="X7:AB7"/>
-    <mergeCell ref="S9:W9"/>
-    <mergeCell ref="A7:B7"/>
-    <mergeCell ref="Q11:AJ11"/>
-    <mergeCell ref="C7:I7"/>
-    <mergeCell ref="D8:R8"/>
-    <mergeCell ref="A8:C8"/>
-    <mergeCell ref="S7:T7"/>
-    <mergeCell ref="P7:R7"/>
-    <mergeCell ref="X8:AJ8"/>
-    <mergeCell ref="A10:AJ10"/>
-    <mergeCell ref="A5:B5"/>
-    <mergeCell ref="A6:B6"/>
-    <mergeCell ref="AD6:AF6"/>
-    <mergeCell ref="D9:R9"/>
-    <mergeCell ref="K7:O7"/>
-    <mergeCell ref="AB46:AE46"/>
-    <mergeCell ref="A25:AJ25"/>
-    <mergeCell ref="A22:AJ23"/>
-    <mergeCell ref="A17:T20"/>
-    <mergeCell ref="C5:I5"/>
-    <mergeCell ref="AF19:AG19"/>
-    <mergeCell ref="A44:I44"/>
-    <mergeCell ref="AI19:AJ19"/>
-    <mergeCell ref="A14:H14"/>
-    <mergeCell ref="I14:AJ14"/>
-    <mergeCell ref="AI17:AJ17"/>
-    <mergeCell ref="AF17:AG17"/>
-    <mergeCell ref="A15:AJ15"/>
-    <mergeCell ref="AF18:AG18"/>
-    <mergeCell ref="AA5:AJ5"/>
-    <mergeCell ref="V7:W7"/>
-    <mergeCell ref="AI18:AJ18"/>
-    <mergeCell ref="U16:AD16"/>
-    <mergeCell ref="AF7:AG7"/>
-    <mergeCell ref="K45:R45"/>
-    <mergeCell ref="AB47:AE47"/>
-    <mergeCell ref="S45:V45"/>
-    <mergeCell ref="S46:V46"/>
-    <mergeCell ref="S47:W47"/>
-    <mergeCell ref="X47:Z47"/>
-    <mergeCell ref="K47:R47"/>
-    <mergeCell ref="K46:R46"/>
-    <mergeCell ref="AB45:AE45"/>
-    <mergeCell ref="J54:R54"/>
-    <mergeCell ref="B49:I49"/>
-    <mergeCell ref="AF48:AI48"/>
-    <mergeCell ref="AB50:AF50"/>
-    <mergeCell ref="AF54:AH54"/>
-    <mergeCell ref="AB51:AJ51"/>
-    <mergeCell ref="AC52:AJ52"/>
-    <mergeCell ref="B50:I50"/>
-    <mergeCell ref="B53:C53"/>
-    <mergeCell ref="D53:H53"/>
-    <mergeCell ref="K51:R51"/>
-    <mergeCell ref="K52:R52"/>
-    <mergeCell ref="S48:W48"/>
-    <mergeCell ref="T50:AA50"/>
-    <mergeCell ref="K49:R49"/>
-    <mergeCell ref="K50:R50"/>
-    <mergeCell ref="W53:Y53"/>
-    <mergeCell ref="K48:R48"/>
-    <mergeCell ref="AB61:AJ61"/>
-    <mergeCell ref="AB58:AJ60"/>
-    <mergeCell ref="AB57:AJ57"/>
-    <mergeCell ref="S49:AA49"/>
-    <mergeCell ref="AG49:AI49"/>
-    <mergeCell ref="AC54:AE54"/>
-    <mergeCell ref="T53:V53"/>
-    <mergeCell ref="W54:Y54"/>
-    <mergeCell ref="B57:L57"/>
-    <mergeCell ref="N57:X57"/>
-    <mergeCell ref="Y56:AA61"/>
-    <mergeCell ref="A60:X60"/>
-    <mergeCell ref="A56:A58"/>
-    <mergeCell ref="N56:X56"/>
-    <mergeCell ref="A55:M55"/>
-    <mergeCell ref="N55:AJ55"/>
-    <mergeCell ref="D54:H54"/>
-    <mergeCell ref="B51:I51"/>
-    <mergeCell ref="B56:L56"/>
-    <mergeCell ref="K53:R53"/>
-    <mergeCell ref="T54:V54"/>
-    <mergeCell ref="AB56:AJ56"/>
-    <mergeCell ref="W52:Y52"/>
-    <mergeCell ref="AC53:AJ53"/>
-    <mergeCell ref="AF47:AI47"/>
-    <mergeCell ref="T51:AA51"/>
-    <mergeCell ref="AF46:AI46"/>
-    <mergeCell ref="AB49:AF49"/>
-    <mergeCell ref="X48:Z48"/>
-    <mergeCell ref="AG50:AI50"/>
-    <mergeCell ref="W46:Z46"/>
-    <mergeCell ref="T52:V52"/>
-    <mergeCell ref="A27:AJ29"/>
-    <mergeCell ref="A36:R36"/>
-    <mergeCell ref="B48:I48"/>
-    <mergeCell ref="S44:AA44"/>
-    <mergeCell ref="B52:I52"/>
-    <mergeCell ref="AF45:AI45"/>
-    <mergeCell ref="A30:O30"/>
-    <mergeCell ref="B45:I45"/>
-    <mergeCell ref="AB44:AJ44"/>
-    <mergeCell ref="J44:R44"/>
-    <mergeCell ref="W45:Y45"/>
-    <mergeCell ref="A31:AJ35"/>
-    <mergeCell ref="A37:AJ40"/>
-    <mergeCell ref="B46:I46"/>
-    <mergeCell ref="AB48:AE48"/>
-    <mergeCell ref="B47:I47"/>
   </mergeCells>
   <phoneticPr fontId="0" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -10777,6 +10727,28 @@
                   <from>
                     <xdr:col>0</xdr:col>
                     <xdr:colOff>53340</xdr:colOff>
+                    <xdr:row>43</xdr:row>
+                    <xdr:rowOff>30480</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>1</xdr:col>
+                    <xdr:colOff>91440</xdr:colOff>
+                    <xdr:row>44</xdr:row>
+                    <xdr:rowOff>15240</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
+        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+          <mc:Choice Requires="x14">
+            <control shapeId="1147" r:id="rId30" name="Check Box 123">
+              <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
+                <anchor moveWithCells="1">
+                  <from>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>53340</xdr:colOff>
                     <xdr:row>44</xdr:row>
                     <xdr:rowOff>30480</xdr:rowOff>
                   </from>
@@ -10793,7 +10765,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
           <mc:Choice Requires="x14">
-            <control shapeId="1147" r:id="rId30" name="Check Box 123">
+            <control shapeId="1148" r:id="rId31" name="Check Box 124">
               <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -10815,7 +10787,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
           <mc:Choice Requires="x14">
-            <control shapeId="1148" r:id="rId31" name="Check Box 124">
+            <control shapeId="1149" r:id="rId32" name="Check Box 125">
               <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -10837,7 +10809,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
           <mc:Choice Requires="x14">
-            <control shapeId="1149" r:id="rId32" name="Check Box 125">
+            <control shapeId="1150" r:id="rId33" name="Check Box 126">
               <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -10859,7 +10831,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
           <mc:Choice Requires="x14">
-            <control shapeId="1150" r:id="rId33" name="Check Box 126">
+            <control shapeId="1151" r:id="rId34" name="Check Box 127">
               <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -10881,7 +10853,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
           <mc:Choice Requires="x14">
-            <control shapeId="1151" r:id="rId34" name="Check Box 127">
+            <control shapeId="1152" r:id="rId35" name="Check Box 128">
               <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -10903,7 +10875,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
           <mc:Choice Requires="x14">
-            <control shapeId="1152" r:id="rId35" name="Check Box 128">
+            <control shapeId="1153" r:id="rId36" name="Check Box 129">
               <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -10925,7 +10897,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
           <mc:Choice Requires="x14">
-            <control shapeId="1153" r:id="rId36" name="Check Box 129">
+            <control shapeId="1154" r:id="rId37" name="Check Box 130">
               <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -10947,19 +10919,19 @@
         </mc:AlternateContent>
         <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
           <mc:Choice Requires="x14">
-            <control shapeId="1154" r:id="rId37" name="Check Box 130">
+            <control shapeId="1164" r:id="rId38" name="Check Box 140">
               <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
-                    <xdr:col>0</xdr:col>
+                    <xdr:col>9</xdr:col>
                     <xdr:colOff>53340</xdr:colOff>
-                    <xdr:row>52</xdr:row>
+                    <xdr:row>43</xdr:row>
                     <xdr:rowOff>30480</xdr:rowOff>
                   </from>
                   <to>
-                    <xdr:col>1</xdr:col>
+                    <xdr:col>10</xdr:col>
                     <xdr:colOff>91440</xdr:colOff>
-                    <xdr:row>53</xdr:row>
+                    <xdr:row>44</xdr:row>
                     <xdr:rowOff>15240</xdr:rowOff>
                   </to>
                 </anchor>
@@ -10969,7 +10941,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
           <mc:Choice Requires="x14">
-            <control shapeId="1164" r:id="rId38" name="Check Box 140">
+            <control shapeId="1165" r:id="rId39" name="Check Box 141">
               <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -10991,7 +10963,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
           <mc:Choice Requires="x14">
-            <control shapeId="1165" r:id="rId39" name="Check Box 141">
+            <control shapeId="1166" r:id="rId40" name="Check Box 142">
               <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -11013,7 +10985,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
           <mc:Choice Requires="x14">
-            <control shapeId="1166" r:id="rId40" name="Check Box 142">
+            <control shapeId="1167" r:id="rId41" name="Check Box 143">
               <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -11035,7 +11007,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
           <mc:Choice Requires="x14">
-            <control shapeId="1167" r:id="rId41" name="Check Box 143">
+            <control shapeId="1168" r:id="rId42" name="Check Box 144">
               <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -11057,7 +11029,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
           <mc:Choice Requires="x14">
-            <control shapeId="1168" r:id="rId42" name="Check Box 144">
+            <control shapeId="1169" r:id="rId43" name="Check Box 145">
               <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -11079,7 +11051,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
           <mc:Choice Requires="x14">
-            <control shapeId="1169" r:id="rId43" name="Check Box 145">
+            <control shapeId="1170" r:id="rId44" name="Check Box 146">
               <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -11101,7 +11073,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
           <mc:Choice Requires="x14">
-            <control shapeId="1170" r:id="rId44" name="Check Box 146">
+            <control shapeId="1171" r:id="rId45" name="Check Box 147">
               <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -11123,7 +11095,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
           <mc:Choice Requires="x14">
-            <control shapeId="1171" r:id="rId45" name="Check Box 147">
+            <control shapeId="1172" r:id="rId46" name="Check Box 148">
               <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -11145,19 +11117,19 @@
         </mc:AlternateContent>
         <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
           <mc:Choice Requires="x14">
-            <control shapeId="1172" r:id="rId46" name="Check Box 148">
+            <control shapeId="1173" r:id="rId47" name="Check Box 149">
               <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
-                    <xdr:col>9</xdr:col>
+                    <xdr:col>18</xdr:col>
                     <xdr:colOff>53340</xdr:colOff>
-                    <xdr:row>52</xdr:row>
+                    <xdr:row>48</xdr:row>
                     <xdr:rowOff>30480</xdr:rowOff>
                   </from>
                   <to>
-                    <xdr:col>10</xdr:col>
+                    <xdr:col>19</xdr:col>
                     <xdr:colOff>91440</xdr:colOff>
-                    <xdr:row>53</xdr:row>
+                    <xdr:row>49</xdr:row>
                     <xdr:rowOff>15240</xdr:rowOff>
                   </to>
                 </anchor>
@@ -11167,7 +11139,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
           <mc:Choice Requires="x14">
-            <control shapeId="1173" r:id="rId47" name="Check Box 149">
+            <control shapeId="1174" r:id="rId48" name="Check Box 150">
               <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -11189,17 +11161,17 @@
         </mc:AlternateContent>
         <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
           <mc:Choice Requires="x14">
-            <control shapeId="1174" r:id="rId48" name="Check Box 150">
+            <control shapeId="1179" r:id="rId49" name="Check Box 155">
               <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
-                    <xdr:col>18</xdr:col>
+                    <xdr:col>27</xdr:col>
                     <xdr:colOff>53340</xdr:colOff>
                     <xdr:row>50</xdr:row>
                     <xdr:rowOff>30480</xdr:rowOff>
                   </from>
                   <to>
-                    <xdr:col>19</xdr:col>
+                    <xdr:col>28</xdr:col>
                     <xdr:colOff>91440</xdr:colOff>
                     <xdr:row>51</xdr:row>
                     <xdr:rowOff>15240</xdr:rowOff>
@@ -11211,7 +11183,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
           <mc:Choice Requires="x14">
-            <control shapeId="1179" r:id="rId49" name="Check Box 155">
+            <control shapeId="1180" r:id="rId50" name="Check Box 156">
               <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -11233,7 +11205,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
           <mc:Choice Requires="x14">
-            <control shapeId="1180" r:id="rId50" name="Check Box 156">
+            <control shapeId="1181" r:id="rId51" name="Check Box 157">
               <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -11255,41 +11227,19 @@
         </mc:AlternateContent>
         <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
           <mc:Choice Requires="x14">
-            <control shapeId="1181" r:id="rId51" name="Check Box 157">
-              <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
-                <anchor moveWithCells="1">
-                  <from>
-                    <xdr:col>27</xdr:col>
-                    <xdr:colOff>53340</xdr:colOff>
-                    <xdr:row>53</xdr:row>
-                    <xdr:rowOff>30480</xdr:rowOff>
-                  </from>
-                  <to>
-                    <xdr:col>28</xdr:col>
-                    <xdr:colOff>91440</xdr:colOff>
-                    <xdr:row>54</xdr:row>
-                    <xdr:rowOff>15240</xdr:rowOff>
-                  </to>
-                </anchor>
-              </controlPr>
-            </control>
-          </mc:Choice>
-        </mc:AlternateContent>
-        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-          <mc:Choice Requires="x14">
             <control shapeId="1261" r:id="rId52" name="Check Box 237">
               <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
                     <xdr:col>27</xdr:col>
                     <xdr:colOff>53340</xdr:colOff>
-                    <xdr:row>53</xdr:row>
+                    <xdr:row>52</xdr:row>
                     <xdr:rowOff>30480</xdr:rowOff>
                   </from>
                   <to>
                     <xdr:col>28</xdr:col>
                     <xdr:colOff>91440</xdr:colOff>
-                    <xdr:row>54</xdr:row>
+                    <xdr:row>53</xdr:row>
                     <xdr:rowOff>15240</xdr:rowOff>
                   </to>
                 </anchor>

--- a/backend_api/templates/container_report_template.xlsx
+++ b/backend_api/templates/container_report_template.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Aaron Avila\Documents\ERP-SOM\backend_api\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B50C4B53-0046-4AB3-8DD1-1262CCC48CD2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3D99A33F-2005-457D-AACA-A833B8C17C15}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-1125" windowWidth="29040" windowHeight="15720" xr2:uid="{253FFB1B-D348-46B1-A532-0D44566D2FFD}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{253FFB1B-D348-46B1-A532-0D44566D2FFD}"/>
   </bookViews>
   <sheets>
     <sheet name="DRY CARGO" sheetId="1" r:id="rId1"/>
@@ -760,7 +760,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="101">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="100">
   <si>
     <t xml:space="preserve">  INSP. PLACE</t>
   </si>
@@ -1100,9 +1100,6 @@
     <t xml:space="preserve"> </t>
   </si>
   <si>
-    <t>DRY CONTAINER</t>
-  </si>
-  <si>
     <t>LEAKING</t>
   </si>
   <si>
@@ -1553,6 +1550,81 @@
       <alignment horizontal="left"/>
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="2" borderId="9" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="2" borderId="6" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="2" borderId="7" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="4" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="165" fontId="13" fillId="0" borderId="8" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="14" fontId="13" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+      <protection locked="0"/>
+    </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left"/>
       <protection locked="0"/>
@@ -1572,9 +1644,6 @@
     <xf numFmtId="0" fontId="6" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="26" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
       <protection locked="0"/>
@@ -1589,66 +1658,6 @@
     <xf numFmtId="0" fontId="7" fillId="2" borderId="6" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="2" borderId="9" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="2" borderId="6" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="2" borderId="7" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="4" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="165" fontId="13" fillId="0" borderId="8" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="14" fontId="13" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left"/>
-      <protection locked="0"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1925,18 +1934,6 @@
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="top" wrapText="1"/>
       <protection locked="0"/>
     </xf>
   </cellXfs>
@@ -7000,9 +6997,12 @@
     <col min="1" max="8" width="4" customWidth="1"/>
     <col min="9" max="9" width="12.44140625" customWidth="1"/>
     <col min="10" max="13" width="4" customWidth="1"/>
-    <col min="16" max="16" width="4" customWidth="1"/>
+    <col min="16" max="16" width="10.5546875" customWidth="1"/>
+    <col min="22" max="22" width="12" customWidth="1"/>
+    <col min="29" max="29" width="11.44140625" customWidth="1"/>
     <col min="31" max="31" width="2.88671875" bestFit="1" customWidth="1"/>
     <col min="32" max="33" width="12.33203125" customWidth="1"/>
+    <col min="35" max="35" width="11.77734375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:36" ht="18" customHeight="1">
@@ -7038,18 +7038,16 @@
       <c r="N2" s="31"/>
       <c r="O2" s="38"/>
       <c r="P2" s="38"/>
-      <c r="Q2" s="54" t="s">
-        <v>98</v>
-      </c>
-      <c r="R2" s="54"/>
-      <c r="S2" s="54"/>
-      <c r="T2" s="54"/>
-      <c r="U2" s="54"/>
-      <c r="V2" s="54"/>
-      <c r="W2" s="54"/>
-      <c r="X2" s="54"/>
-      <c r="Y2" s="54"/>
-      <c r="Z2" s="54"/>
+      <c r="Q2" s="75"/>
+      <c r="R2" s="75"/>
+      <c r="S2" s="75"/>
+      <c r="T2" s="75"/>
+      <c r="U2" s="75"/>
+      <c r="V2" s="75"/>
+      <c r="W2" s="75"/>
+      <c r="X2" s="75"/>
+      <c r="Y2" s="75"/>
+      <c r="Z2" s="75"/>
       <c r="AA2" s="38"/>
       <c r="AB2" s="38"/>
       <c r="AC2" s="38"/>
@@ -7075,28 +7073,28 @@
       <c r="K3" s="1"/>
       <c r="M3" s="31"/>
       <c r="N3" s="31"/>
-      <c r="Q3" s="55"/>
-      <c r="R3" s="55"/>
-      <c r="S3" s="55"/>
-      <c r="T3" s="55"/>
-      <c r="U3" s="55"/>
-      <c r="V3" s="55"/>
-      <c r="W3" s="55"/>
-      <c r="X3" s="55"/>
-      <c r="Y3" s="55"/>
-      <c r="Z3" s="55"/>
+      <c r="Q3" s="76"/>
+      <c r="R3" s="76"/>
+      <c r="S3" s="76"/>
+      <c r="T3" s="76"/>
+      <c r="U3" s="76"/>
+      <c r="V3" s="76"/>
+      <c r="W3" s="76"/>
+      <c r="X3" s="76"/>
+      <c r="Y3" s="76"/>
+      <c r="Z3" s="76"/>
       <c r="AA3" s="37"/>
       <c r="AB3" s="50" t="s">
         <v>95</v>
       </c>
       <c r="AC3" s="48"/>
-      <c r="AD3" s="70"/>
-      <c r="AE3" s="71"/>
-      <c r="AF3" s="71"/>
-      <c r="AG3" s="71"/>
-      <c r="AH3" s="71"/>
-      <c r="AI3" s="71"/>
-      <c r="AJ3" s="71"/>
+      <c r="AD3" s="62"/>
+      <c r="AE3" s="63"/>
+      <c r="AF3" s="63"/>
+      <c r="AG3" s="63"/>
+      <c r="AH3" s="63"/>
+      <c r="AI3" s="63"/>
+      <c r="AJ3" s="63"/>
     </row>
     <row r="4" spans="1:36" ht="18" customHeight="1">
       <c r="A4" s="30"/>
@@ -7127,304 +7125,304 @@
       </c>
     </row>
     <row r="5" spans="1:36" ht="18" customHeight="1">
-      <c r="A5" s="78" t="s">
+      <c r="A5" s="71" t="s">
         <v>85</v>
       </c>
-      <c r="B5" s="78"/>
-      <c r="C5" s="102"/>
-      <c r="D5" s="102"/>
-      <c r="E5" s="102"/>
-      <c r="F5" s="102"/>
-      <c r="G5" s="102"/>
-      <c r="H5" s="102"/>
-      <c r="I5" s="102"/>
+      <c r="B5" s="71"/>
+      <c r="C5" s="105"/>
+      <c r="D5" s="105"/>
+      <c r="E5" s="105"/>
+      <c r="F5" s="105"/>
+      <c r="G5" s="105"/>
+      <c r="H5" s="105"/>
+      <c r="I5" s="105"/>
       <c r="J5" s="35"/>
-      <c r="K5" s="59" t="s">
+      <c r="K5" s="64" t="s">
         <v>0</v>
       </c>
-      <c r="L5" s="59"/>
-      <c r="M5" s="59"/>
-      <c r="N5" s="59"/>
-      <c r="O5" s="59"/>
-      <c r="P5" s="72"/>
-      <c r="Q5" s="73"/>
-      <c r="R5" s="73"/>
-      <c r="S5" s="73"/>
-      <c r="T5" s="73"/>
-      <c r="U5" s="73"/>
-      <c r="V5" s="73"/>
-      <c r="W5" s="73"/>
-      <c r="X5" s="73"/>
-      <c r="Y5" s="59" t="s">
+      <c r="L5" s="64"/>
+      <c r="M5" s="64"/>
+      <c r="N5" s="64"/>
+      <c r="O5" s="64"/>
+      <c r="P5" s="65"/>
+      <c r="Q5" s="66"/>
+      <c r="R5" s="66"/>
+      <c r="S5" s="66"/>
+      <c r="T5" s="66"/>
+      <c r="U5" s="66"/>
+      <c r="V5" s="66"/>
+      <c r="W5" s="66"/>
+      <c r="X5" s="66"/>
+      <c r="Y5" s="64" t="s">
         <v>48</v>
       </c>
-      <c r="Z5" s="59"/>
-      <c r="AA5" s="102"/>
-      <c r="AB5" s="102"/>
-      <c r="AC5" s="102"/>
-      <c r="AD5" s="102"/>
-      <c r="AE5" s="102"/>
-      <c r="AF5" s="102"/>
-      <c r="AG5" s="102"/>
-      <c r="AH5" s="102"/>
-      <c r="AI5" s="102"/>
-      <c r="AJ5" s="102"/>
+      <c r="Z5" s="64"/>
+      <c r="AA5" s="105"/>
+      <c r="AB5" s="105"/>
+      <c r="AC5" s="105"/>
+      <c r="AD5" s="105"/>
+      <c r="AE5" s="105"/>
+      <c r="AF5" s="105"/>
+      <c r="AG5" s="105"/>
+      <c r="AH5" s="105"/>
+      <c r="AI5" s="105"/>
+      <c r="AJ5" s="105"/>
     </row>
     <row r="6" spans="1:36" ht="18" customHeight="1">
-      <c r="A6" s="78" t="s">
+      <c r="A6" s="71" t="s">
         <v>1</v>
       </c>
-      <c r="B6" s="78"/>
-      <c r="C6" s="76"/>
-      <c r="D6" s="76"/>
-      <c r="E6" s="76"/>
-      <c r="F6" s="76"/>
-      <c r="G6" s="76"/>
-      <c r="H6" s="76"/>
-      <c r="I6" s="76"/>
+      <c r="B6" s="71"/>
+      <c r="C6" s="69"/>
+      <c r="D6" s="69"/>
+      <c r="E6" s="69"/>
+      <c r="F6" s="69"/>
+      <c r="G6" s="69"/>
+      <c r="H6" s="69"/>
+      <c r="I6" s="69"/>
       <c r="J6" s="35"/>
-      <c r="K6" s="59" t="s">
+      <c r="K6" s="64" t="s">
         <v>2</v>
       </c>
-      <c r="L6" s="59"/>
-      <c r="M6" s="59"/>
-      <c r="N6" s="59"/>
-      <c r="O6" s="59"/>
-      <c r="P6" s="60"/>
-      <c r="Q6" s="61"/>
-      <c r="R6" s="61"/>
-      <c r="S6" s="61"/>
-      <c r="T6" s="61"/>
-      <c r="U6" s="61"/>
-      <c r="V6" s="61"/>
-      <c r="W6" s="61"/>
-      <c r="X6" s="61"/>
-      <c r="Y6" s="59" t="s">
+      <c r="L6" s="64"/>
+      <c r="M6" s="64"/>
+      <c r="N6" s="64"/>
+      <c r="O6" s="64"/>
+      <c r="P6" s="80"/>
+      <c r="Q6" s="81"/>
+      <c r="R6" s="81"/>
+      <c r="S6" s="81"/>
+      <c r="T6" s="81"/>
+      <c r="U6" s="81"/>
+      <c r="V6" s="81"/>
+      <c r="W6" s="81"/>
+      <c r="X6" s="81"/>
+      <c r="Y6" s="64" t="s">
         <v>88</v>
       </c>
-      <c r="Z6" s="59"/>
-      <c r="AA6" s="59"/>
-      <c r="AB6" s="59"/>
-      <c r="AC6" s="59"/>
-      <c r="AD6" s="75"/>
-      <c r="AE6" s="75"/>
-      <c r="AF6" s="75"/>
+      <c r="Z6" s="64"/>
+      <c r="AA6" s="64"/>
+      <c r="AB6" s="64"/>
+      <c r="AC6" s="64"/>
+      <c r="AD6" s="68"/>
+      <c r="AE6" s="68"/>
+      <c r="AF6" s="68"/>
       <c r="AG6" s="44"/>
-      <c r="AH6" s="74"/>
-      <c r="AI6" s="74"/>
+      <c r="AH6" s="67"/>
+      <c r="AI6" s="67"/>
       <c r="AJ6" s="44"/>
     </row>
     <row r="7" spans="1:36" ht="18" customHeight="1">
-      <c r="A7" s="78" t="s">
+      <c r="A7" s="71" t="s">
         <v>3</v>
       </c>
-      <c r="B7" s="78"/>
-      <c r="C7" s="76"/>
-      <c r="D7" s="76"/>
-      <c r="E7" s="76"/>
-      <c r="F7" s="76"/>
-      <c r="G7" s="76"/>
-      <c r="H7" s="76"/>
-      <c r="I7" s="76"/>
+      <c r="B7" s="71"/>
+      <c r="C7" s="69"/>
+      <c r="D7" s="69"/>
+      <c r="E7" s="69"/>
+      <c r="F7" s="69"/>
+      <c r="G7" s="69"/>
+      <c r="H7" s="69"/>
+      <c r="I7" s="69"/>
       <c r="J7" s="35"/>
-      <c r="K7" s="59" t="s">
+      <c r="K7" s="64" t="s">
         <v>89</v>
       </c>
-      <c r="L7" s="59"/>
-      <c r="M7" s="59"/>
-      <c r="N7" s="59"/>
-      <c r="O7" s="59"/>
-      <c r="P7" s="75"/>
-      <c r="Q7" s="75"/>
-      <c r="R7" s="75"/>
-      <c r="S7" s="74"/>
-      <c r="T7" s="74"/>
+      <c r="L7" s="64"/>
+      <c r="M7" s="64"/>
+      <c r="N7" s="64"/>
+      <c r="O7" s="64"/>
+      <c r="P7" s="68"/>
+      <c r="Q7" s="68"/>
+      <c r="R7" s="68"/>
+      <c r="S7" s="67"/>
+      <c r="T7" s="67"/>
       <c r="U7" s="39" t="s">
         <v>4</v>
       </c>
-      <c r="V7" s="74"/>
-      <c r="W7" s="74"/>
-      <c r="X7" s="59" t="s">
+      <c r="V7" s="67"/>
+      <c r="W7" s="67"/>
+      <c r="X7" s="64" t="s">
         <v>90</v>
       </c>
-      <c r="Y7" s="59"/>
-      <c r="Z7" s="59"/>
-      <c r="AA7" s="59"/>
-      <c r="AB7" s="59"/>
-      <c r="AC7" s="75"/>
-      <c r="AD7" s="75"/>
-      <c r="AE7" s="75"/>
-      <c r="AF7" s="74"/>
-      <c r="AG7" s="74"/>
+      <c r="Y7" s="64"/>
+      <c r="Z7" s="64"/>
+      <c r="AA7" s="64"/>
+      <c r="AB7" s="64"/>
+      <c r="AC7" s="68"/>
+      <c r="AD7" s="68"/>
+      <c r="AE7" s="68"/>
+      <c r="AF7" s="67"/>
+      <c r="AG7" s="67"/>
       <c r="AH7" s="39" t="s">
         <v>4</v>
       </c>
-      <c r="AI7" s="74"/>
-      <c r="AJ7" s="74"/>
+      <c r="AI7" s="67"/>
+      <c r="AJ7" s="67"/>
     </row>
     <row r="8" spans="1:36" ht="18" customHeight="1">
-      <c r="A8" s="84" t="s">
+      <c r="A8" s="87" t="s">
         <v>5</v>
       </c>
-      <c r="B8" s="84"/>
-      <c r="C8" s="84"/>
-      <c r="D8" s="53"/>
-      <c r="E8" s="53"/>
-      <c r="F8" s="53"/>
-      <c r="G8" s="53"/>
-      <c r="H8" s="53"/>
-      <c r="I8" s="53"/>
-      <c r="J8" s="53"/>
-      <c r="K8" s="53"/>
-      <c r="L8" s="53"/>
-      <c r="M8" s="53"/>
-      <c r="N8" s="53"/>
-      <c r="O8" s="53"/>
-      <c r="P8" s="53"/>
-      <c r="Q8" s="53"/>
-      <c r="R8" s="53"/>
-      <c r="S8" s="77" t="s">
+      <c r="B8" s="87"/>
+      <c r="C8" s="87"/>
+      <c r="D8" s="74"/>
+      <c r="E8" s="74"/>
+      <c r="F8" s="74"/>
+      <c r="G8" s="74"/>
+      <c r="H8" s="74"/>
+      <c r="I8" s="74"/>
+      <c r="J8" s="74"/>
+      <c r="K8" s="74"/>
+      <c r="L8" s="74"/>
+      <c r="M8" s="74"/>
+      <c r="N8" s="74"/>
+      <c r="O8" s="74"/>
+      <c r="P8" s="74"/>
+      <c r="Q8" s="74"/>
+      <c r="R8" s="74"/>
+      <c r="S8" s="70" t="s">
         <v>49</v>
       </c>
-      <c r="T8" s="77"/>
-      <c r="U8" s="59"/>
-      <c r="V8" s="77"/>
-      <c r="W8" s="77"/>
-      <c r="X8" s="53"/>
-      <c r="Y8" s="53"/>
-      <c r="Z8" s="53"/>
-      <c r="AA8" s="53"/>
-      <c r="AB8" s="53"/>
-      <c r="AC8" s="53"/>
-      <c r="AD8" s="53"/>
-      <c r="AE8" s="53"/>
-      <c r="AF8" s="53"/>
-      <c r="AG8" s="53"/>
-      <c r="AH8" s="53"/>
-      <c r="AI8" s="53"/>
-      <c r="AJ8" s="53"/>
+      <c r="T8" s="70"/>
+      <c r="U8" s="64"/>
+      <c r="V8" s="70"/>
+      <c r="W8" s="70"/>
+      <c r="X8" s="74"/>
+      <c r="Y8" s="74"/>
+      <c r="Z8" s="74"/>
+      <c r="AA8" s="74"/>
+      <c r="AB8" s="74"/>
+      <c r="AC8" s="74"/>
+      <c r="AD8" s="74"/>
+      <c r="AE8" s="74"/>
+      <c r="AF8" s="74"/>
+      <c r="AG8" s="74"/>
+      <c r="AH8" s="74"/>
+      <c r="AI8" s="74"/>
+      <c r="AJ8" s="74"/>
     </row>
     <row r="9" spans="1:36" ht="26.4" customHeight="1">
-      <c r="A9" s="78" t="s">
+      <c r="A9" s="71" t="s">
         <v>6</v>
       </c>
-      <c r="B9" s="78"/>
-      <c r="C9" s="78"/>
-      <c r="D9" s="80"/>
-      <c r="E9" s="80"/>
-      <c r="F9" s="80"/>
-      <c r="G9" s="80"/>
-      <c r="H9" s="80"/>
-      <c r="I9" s="80"/>
-      <c r="J9" s="80"/>
-      <c r="K9" s="80"/>
-      <c r="L9" s="80"/>
-      <c r="M9" s="80"/>
-      <c r="N9" s="80"/>
-      <c r="O9" s="80"/>
-      <c r="P9" s="80"/>
-      <c r="Q9" s="80"/>
-      <c r="R9" s="80"/>
-      <c r="S9" s="59" t="s">
+      <c r="B9" s="71"/>
+      <c r="C9" s="71"/>
+      <c r="D9" s="73"/>
+      <c r="E9" s="73"/>
+      <c r="F9" s="73"/>
+      <c r="G9" s="73"/>
+      <c r="H9" s="73"/>
+      <c r="I9" s="73"/>
+      <c r="J9" s="73"/>
+      <c r="K9" s="73"/>
+      <c r="L9" s="73"/>
+      <c r="M9" s="73"/>
+      <c r="N9" s="73"/>
+      <c r="O9" s="73"/>
+      <c r="P9" s="73"/>
+      <c r="Q9" s="73"/>
+      <c r="R9" s="73"/>
+      <c r="S9" s="64" t="s">
         <v>50</v>
       </c>
-      <c r="T9" s="59"/>
-      <c r="U9" s="59"/>
-      <c r="V9" s="59"/>
-      <c r="W9" s="59"/>
-      <c r="X9" s="79"/>
-      <c r="Y9" s="80"/>
-      <c r="Z9" s="80"/>
-      <c r="AA9" s="80"/>
-      <c r="AB9" s="80"/>
-      <c r="AC9" s="80"/>
-      <c r="AD9" s="80"/>
-      <c r="AE9" s="80"/>
-      <c r="AF9" s="80"/>
-      <c r="AG9" s="80"/>
-      <c r="AH9" s="80"/>
-      <c r="AI9" s="80"/>
-      <c r="AJ9" s="80"/>
+      <c r="T9" s="64"/>
+      <c r="U9" s="64"/>
+      <c r="V9" s="64"/>
+      <c r="W9" s="64"/>
+      <c r="X9" s="72"/>
+      <c r="Y9" s="73"/>
+      <c r="Z9" s="73"/>
+      <c r="AA9" s="73"/>
+      <c r="AB9" s="73"/>
+      <c r="AC9" s="73"/>
+      <c r="AD9" s="73"/>
+      <c r="AE9" s="73"/>
+      <c r="AF9" s="73"/>
+      <c r="AG9" s="73"/>
+      <c r="AH9" s="73"/>
+      <c r="AI9" s="73"/>
+      <c r="AJ9" s="73"/>
     </row>
     <row r="10" spans="1:36" ht="5.25" customHeight="1">
-      <c r="A10" s="85"/>
-      <c r="B10" s="85"/>
-      <c r="C10" s="85"/>
-      <c r="D10" s="85"/>
-      <c r="E10" s="85"/>
-      <c r="F10" s="85"/>
-      <c r="G10" s="85"/>
-      <c r="H10" s="85"/>
-      <c r="I10" s="85"/>
-      <c r="J10" s="85"/>
-      <c r="K10" s="85"/>
-      <c r="L10" s="85"/>
-      <c r="M10" s="85"/>
-      <c r="N10" s="85"/>
-      <c r="O10" s="85"/>
-      <c r="P10" s="85"/>
-      <c r="Q10" s="85"/>
-      <c r="R10" s="85"/>
-      <c r="S10" s="85"/>
-      <c r="T10" s="85"/>
-      <c r="U10" s="85"/>
-      <c r="V10" s="85"/>
-      <c r="W10" s="85"/>
-      <c r="X10" s="85"/>
-      <c r="Y10" s="85"/>
-      <c r="Z10" s="85"/>
-      <c r="AA10" s="85"/>
-      <c r="AB10" s="85"/>
-      <c r="AC10" s="85"/>
-      <c r="AD10" s="85"/>
-      <c r="AE10" s="85"/>
-      <c r="AF10" s="85"/>
-      <c r="AG10" s="85"/>
-      <c r="AH10" s="85"/>
-      <c r="AI10" s="85"/>
-      <c r="AJ10" s="85"/>
+      <c r="A10" s="88"/>
+      <c r="B10" s="88"/>
+      <c r="C10" s="88"/>
+      <c r="D10" s="88"/>
+      <c r="E10" s="88"/>
+      <c r="F10" s="88"/>
+      <c r="G10" s="88"/>
+      <c r="H10" s="88"/>
+      <c r="I10" s="88"/>
+      <c r="J10" s="88"/>
+      <c r="K10" s="88"/>
+      <c r="L10" s="88"/>
+      <c r="M10" s="88"/>
+      <c r="N10" s="88"/>
+      <c r="O10" s="88"/>
+      <c r="P10" s="88"/>
+      <c r="Q10" s="88"/>
+      <c r="R10" s="88"/>
+      <c r="S10" s="88"/>
+      <c r="T10" s="88"/>
+      <c r="U10" s="88"/>
+      <c r="V10" s="88"/>
+      <c r="W10" s="88"/>
+      <c r="X10" s="88"/>
+      <c r="Y10" s="88"/>
+      <c r="Z10" s="88"/>
+      <c r="AA10" s="88"/>
+      <c r="AB10" s="88"/>
+      <c r="AC10" s="88"/>
+      <c r="AD10" s="88"/>
+      <c r="AE10" s="88"/>
+      <c r="AF10" s="88"/>
+      <c r="AG10" s="88"/>
+      <c r="AH10" s="88"/>
+      <c r="AI10" s="88"/>
+      <c r="AJ10" s="88"/>
     </row>
     <row r="11" spans="1:36" ht="14.25" customHeight="1">
-      <c r="A11" s="56" t="s">
+      <c r="A11" s="77" t="s">
         <v>7</v>
       </c>
-      <c r="B11" s="57"/>
-      <c r="C11" s="57"/>
-      <c r="D11" s="57"/>
-      <c r="E11" s="57"/>
-      <c r="F11" s="57"/>
-      <c r="G11" s="57"/>
-      <c r="H11" s="57"/>
-      <c r="I11" s="57"/>
-      <c r="J11" s="57"/>
-      <c r="K11" s="57"/>
-      <c r="L11" s="57"/>
-      <c r="M11" s="57"/>
-      <c r="N11" s="57"/>
-      <c r="O11" s="57"/>
-      <c r="P11" s="58"/>
-      <c r="Q11" s="81" t="s">
+      <c r="B11" s="78"/>
+      <c r="C11" s="78"/>
+      <c r="D11" s="78"/>
+      <c r="E11" s="78"/>
+      <c r="F11" s="78"/>
+      <c r="G11" s="78"/>
+      <c r="H11" s="78"/>
+      <c r="I11" s="78"/>
+      <c r="J11" s="78"/>
+      <c r="K11" s="78"/>
+      <c r="L11" s="78"/>
+      <c r="M11" s="78"/>
+      <c r="N11" s="78"/>
+      <c r="O11" s="78"/>
+      <c r="P11" s="79"/>
+      <c r="Q11" s="84" t="s">
         <v>8</v>
       </c>
-      <c r="R11" s="82"/>
-      <c r="S11" s="82"/>
-      <c r="T11" s="82"/>
-      <c r="U11" s="82"/>
-      <c r="V11" s="82"/>
-      <c r="W11" s="82"/>
-      <c r="X11" s="82"/>
-      <c r="Y11" s="82"/>
-      <c r="Z11" s="82"/>
-      <c r="AA11" s="82"/>
-      <c r="AB11" s="82"/>
-      <c r="AC11" s="82"/>
-      <c r="AD11" s="82"/>
-      <c r="AE11" s="82"/>
-      <c r="AF11" s="82"/>
-      <c r="AG11" s="82"/>
-      <c r="AH11" s="82"/>
-      <c r="AI11" s="82"/>
-      <c r="AJ11" s="83"/>
+      <c r="R11" s="85"/>
+      <c r="S11" s="85"/>
+      <c r="T11" s="85"/>
+      <c r="U11" s="85"/>
+      <c r="V11" s="85"/>
+      <c r="W11" s="85"/>
+      <c r="X11" s="85"/>
+      <c r="Y11" s="85"/>
+      <c r="Z11" s="85"/>
+      <c r="AA11" s="85"/>
+      <c r="AB11" s="85"/>
+      <c r="AC11" s="85"/>
+      <c r="AD11" s="85"/>
+      <c r="AE11" s="85"/>
+      <c r="AF11" s="85"/>
+      <c r="AG11" s="85"/>
+      <c r="AH11" s="85"/>
+      <c r="AI11" s="85"/>
+      <c r="AJ11" s="86"/>
     </row>
     <row r="12" spans="1:36" ht="18" customHeight="1">
       <c r="A12" s="2"/>
@@ -7467,7 +7465,7 @@
       <c r="AA12" s="17"/>
       <c r="AB12" s="17"/>
       <c r="AC12" s="17" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="AD12" s="17"/>
       <c r="AE12" s="17"/>
@@ -7533,150 +7531,150 @@
       <c r="AJ13" s="23"/>
     </row>
     <row r="14" spans="1:36" ht="16.5" customHeight="1">
-      <c r="A14" s="108" t="s">
+      <c r="A14" s="111" t="s">
         <v>86</v>
       </c>
-      <c r="B14" s="109"/>
-      <c r="C14" s="109"/>
-      <c r="D14" s="109"/>
-      <c r="E14" s="109"/>
-      <c r="F14" s="109"/>
-      <c r="G14" s="109"/>
-      <c r="H14" s="109"/>
-      <c r="I14" s="110"/>
-      <c r="J14" s="111"/>
-      <c r="K14" s="111"/>
-      <c r="L14" s="111"/>
-      <c r="M14" s="111"/>
-      <c r="N14" s="111"/>
-      <c r="O14" s="111"/>
-      <c r="P14" s="111"/>
-      <c r="Q14" s="111"/>
-      <c r="R14" s="111"/>
-      <c r="S14" s="111"/>
-      <c r="T14" s="111"/>
-      <c r="U14" s="111"/>
-      <c r="V14" s="111"/>
-      <c r="W14" s="111"/>
-      <c r="X14" s="111"/>
-      <c r="Y14" s="111"/>
-      <c r="Z14" s="111"/>
-      <c r="AA14" s="111"/>
-      <c r="AB14" s="111"/>
-      <c r="AC14" s="111"/>
-      <c r="AD14" s="111"/>
-      <c r="AE14" s="111"/>
-      <c r="AF14" s="111"/>
-      <c r="AG14" s="111"/>
-      <c r="AH14" s="111"/>
-      <c r="AI14" s="111"/>
-      <c r="AJ14" s="112"/>
+      <c r="B14" s="112"/>
+      <c r="C14" s="112"/>
+      <c r="D14" s="112"/>
+      <c r="E14" s="112"/>
+      <c r="F14" s="112"/>
+      <c r="G14" s="112"/>
+      <c r="H14" s="112"/>
+      <c r="I14" s="113"/>
+      <c r="J14" s="114"/>
+      <c r="K14" s="114"/>
+      <c r="L14" s="114"/>
+      <c r="M14" s="114"/>
+      <c r="N14" s="114"/>
+      <c r="O14" s="114"/>
+      <c r="P14" s="114"/>
+      <c r="Q14" s="114"/>
+      <c r="R14" s="114"/>
+      <c r="S14" s="114"/>
+      <c r="T14" s="114"/>
+      <c r="U14" s="114"/>
+      <c r="V14" s="114"/>
+      <c r="W14" s="114"/>
+      <c r="X14" s="114"/>
+      <c r="Y14" s="114"/>
+      <c r="Z14" s="114"/>
+      <c r="AA14" s="114"/>
+      <c r="AB14" s="114"/>
+      <c r="AC14" s="114"/>
+      <c r="AD14" s="114"/>
+      <c r="AE14" s="114"/>
+      <c r="AF14" s="114"/>
+      <c r="AG14" s="114"/>
+      <c r="AH14" s="114"/>
+      <c r="AI14" s="114"/>
+      <c r="AJ14" s="115"/>
     </row>
     <row r="15" spans="1:36" ht="3" customHeight="1">
-      <c r="A15" s="113">
+      <c r="A15" s="116">
         <v>2</v>
       </c>
-      <c r="B15" s="114"/>
-      <c r="C15" s="114"/>
-      <c r="D15" s="114"/>
-      <c r="E15" s="114"/>
-      <c r="F15" s="114"/>
-      <c r="G15" s="114"/>
-      <c r="H15" s="114"/>
-      <c r="I15" s="114"/>
-      <c r="J15" s="114"/>
-      <c r="K15" s="114"/>
-      <c r="L15" s="114"/>
-      <c r="M15" s="114"/>
-      <c r="N15" s="114"/>
-      <c r="O15" s="114"/>
-      <c r="P15" s="114"/>
-      <c r="Q15" s="114"/>
-      <c r="R15" s="114"/>
-      <c r="S15" s="114"/>
-      <c r="T15" s="114"/>
-      <c r="U15" s="114"/>
-      <c r="V15" s="114"/>
-      <c r="W15" s="114"/>
-      <c r="X15" s="114"/>
-      <c r="Y15" s="114"/>
-      <c r="Z15" s="114"/>
-      <c r="AA15" s="114"/>
-      <c r="AB15" s="114"/>
-      <c r="AC15" s="114"/>
-      <c r="AD15" s="114"/>
-      <c r="AE15" s="114"/>
-      <c r="AF15" s="114"/>
-      <c r="AG15" s="114"/>
-      <c r="AH15" s="114"/>
-      <c r="AI15" s="114"/>
-      <c r="AJ15" s="115"/>
+      <c r="B15" s="117"/>
+      <c r="C15" s="117"/>
+      <c r="D15" s="117"/>
+      <c r="E15" s="117"/>
+      <c r="F15" s="117"/>
+      <c r="G15" s="117"/>
+      <c r="H15" s="117"/>
+      <c r="I15" s="117"/>
+      <c r="J15" s="117"/>
+      <c r="K15" s="117"/>
+      <c r="L15" s="117"/>
+      <c r="M15" s="117"/>
+      <c r="N15" s="117"/>
+      <c r="O15" s="117"/>
+      <c r="P15" s="117"/>
+      <c r="Q15" s="117"/>
+      <c r="R15" s="117"/>
+      <c r="S15" s="117"/>
+      <c r="T15" s="117"/>
+      <c r="U15" s="117"/>
+      <c r="V15" s="117"/>
+      <c r="W15" s="117"/>
+      <c r="X15" s="117"/>
+      <c r="Y15" s="117"/>
+      <c r="Z15" s="117"/>
+      <c r="AA15" s="117"/>
+      <c r="AB15" s="117"/>
+      <c r="AC15" s="117"/>
+      <c r="AD15" s="117"/>
+      <c r="AE15" s="117"/>
+      <c r="AF15" s="117"/>
+      <c r="AG15" s="117"/>
+      <c r="AH15" s="117"/>
+      <c r="AI15" s="117"/>
+      <c r="AJ15" s="118"/>
     </row>
     <row r="16" spans="1:36" ht="12.75" customHeight="1">
-      <c r="A16" s="67" t="s">
+      <c r="A16" s="59" t="s">
         <v>9</v>
       </c>
-      <c r="B16" s="68"/>
-      <c r="C16" s="68"/>
-      <c r="D16" s="68"/>
-      <c r="E16" s="68"/>
-      <c r="F16" s="68"/>
-      <c r="G16" s="68"/>
-      <c r="H16" s="68"/>
-      <c r="I16" s="68"/>
-      <c r="J16" s="68"/>
-      <c r="K16" s="68"/>
-      <c r="L16" s="68"/>
-      <c r="M16" s="68"/>
-      <c r="N16" s="68"/>
-      <c r="O16" s="68"/>
-      <c r="P16" s="68"/>
-      <c r="Q16" s="68"/>
-      <c r="R16" s="68"/>
-      <c r="S16" s="68"/>
-      <c r="T16" s="69"/>
-      <c r="U16" s="116" t="s">
+      <c r="B16" s="60"/>
+      <c r="C16" s="60"/>
+      <c r="D16" s="60"/>
+      <c r="E16" s="60"/>
+      <c r="F16" s="60"/>
+      <c r="G16" s="60"/>
+      <c r="H16" s="60"/>
+      <c r="I16" s="60"/>
+      <c r="J16" s="60"/>
+      <c r="K16" s="60"/>
+      <c r="L16" s="60"/>
+      <c r="M16" s="60"/>
+      <c r="N16" s="60"/>
+      <c r="O16" s="60"/>
+      <c r="P16" s="60"/>
+      <c r="Q16" s="60"/>
+      <c r="R16" s="60"/>
+      <c r="S16" s="60"/>
+      <c r="T16" s="61"/>
+      <c r="U16" s="119" t="s">
         <v>73</v>
       </c>
-      <c r="V16" s="117"/>
-      <c r="W16" s="117"/>
-      <c r="X16" s="117"/>
-      <c r="Y16" s="117"/>
-      <c r="Z16" s="117"/>
-      <c r="AA16" s="117"/>
-      <c r="AB16" s="117"/>
-      <c r="AC16" s="117"/>
-      <c r="AD16" s="118"/>
-      <c r="AE16" s="64" t="s">
+      <c r="V16" s="120"/>
+      <c r="W16" s="120"/>
+      <c r="X16" s="120"/>
+      <c r="Y16" s="120"/>
+      <c r="Z16" s="120"/>
+      <c r="AA16" s="120"/>
+      <c r="AB16" s="120"/>
+      <c r="AC16" s="120"/>
+      <c r="AD16" s="121"/>
+      <c r="AE16" s="56" t="s">
         <v>10</v>
       </c>
-      <c r="AF16" s="65"/>
-      <c r="AG16" s="65"/>
-      <c r="AH16" s="65"/>
-      <c r="AI16" s="65"/>
-      <c r="AJ16" s="66"/>
+      <c r="AF16" s="57"/>
+      <c r="AG16" s="57"/>
+      <c r="AH16" s="57"/>
+      <c r="AI16" s="57"/>
+      <c r="AJ16" s="58"/>
     </row>
     <row r="17" spans="1:36" ht="18" customHeight="1">
-      <c r="A17" s="96"/>
-      <c r="B17" s="97"/>
-      <c r="C17" s="97"/>
-      <c r="D17" s="97"/>
-      <c r="E17" s="97"/>
-      <c r="F17" s="97"/>
-      <c r="G17" s="97"/>
-      <c r="H17" s="97"/>
-      <c r="I17" s="97"/>
-      <c r="J17" s="97"/>
-      <c r="K17" s="97"/>
-      <c r="L17" s="97"/>
-      <c r="M17" s="97"/>
-      <c r="N17" s="97"/>
-      <c r="O17" s="97"/>
-      <c r="P17" s="97"/>
-      <c r="Q17" s="97"/>
-      <c r="R17" s="97"/>
-      <c r="S17" s="97"/>
-      <c r="T17" s="98"/>
+      <c r="A17" s="99"/>
+      <c r="B17" s="100"/>
+      <c r="C17" s="100"/>
+      <c r="D17" s="100"/>
+      <c r="E17" s="100"/>
+      <c r="F17" s="100"/>
+      <c r="G17" s="100"/>
+      <c r="H17" s="100"/>
+      <c r="I17" s="100"/>
+      <c r="J17" s="100"/>
+      <c r="K17" s="100"/>
+      <c r="L17" s="100"/>
+      <c r="M17" s="100"/>
+      <c r="N17" s="100"/>
+      <c r="O17" s="100"/>
+      <c r="P17" s="100"/>
+      <c r="Q17" s="100"/>
+      <c r="R17" s="100"/>
+      <c r="S17" s="100"/>
+      <c r="T17" s="101"/>
       <c r="U17" s="25"/>
       <c r="V17" s="17" t="s">
         <v>64</v>
@@ -7692,32 +7690,32 @@
       <c r="AE17" s="14" t="s">
         <v>11</v>
       </c>
-      <c r="AF17" s="103"/>
-      <c r="AG17" s="103"/>
-      <c r="AI17" s="103"/>
-      <c r="AJ17" s="107"/>
+      <c r="AF17" s="106"/>
+      <c r="AG17" s="106"/>
+      <c r="AI17" s="106"/>
+      <c r="AJ17" s="110"/>
     </row>
     <row r="18" spans="1:36" ht="18" customHeight="1">
-      <c r="A18" s="96"/>
-      <c r="B18" s="97"/>
-      <c r="C18" s="97"/>
-      <c r="D18" s="97"/>
-      <c r="E18" s="97"/>
-      <c r="F18" s="97"/>
-      <c r="G18" s="97"/>
-      <c r="H18" s="97"/>
-      <c r="I18" s="97"/>
-      <c r="J18" s="97"/>
-      <c r="K18" s="97"/>
-      <c r="L18" s="97"/>
-      <c r="M18" s="97"/>
-      <c r="N18" s="97"/>
-      <c r="O18" s="97"/>
-      <c r="P18" s="97"/>
-      <c r="Q18" s="97"/>
-      <c r="R18" s="97"/>
-      <c r="S18" s="97"/>
-      <c r="T18" s="98"/>
+      <c r="A18" s="99"/>
+      <c r="B18" s="100"/>
+      <c r="C18" s="100"/>
+      <c r="D18" s="100"/>
+      <c r="E18" s="100"/>
+      <c r="F18" s="100"/>
+      <c r="G18" s="100"/>
+      <c r="H18" s="100"/>
+      <c r="I18" s="100"/>
+      <c r="J18" s="100"/>
+      <c r="K18" s="100"/>
+      <c r="L18" s="100"/>
+      <c r="M18" s="100"/>
+      <c r="N18" s="100"/>
+      <c r="O18" s="100"/>
+      <c r="P18" s="100"/>
+      <c r="Q18" s="100"/>
+      <c r="R18" s="100"/>
+      <c r="S18" s="100"/>
+      <c r="T18" s="101"/>
       <c r="U18" s="26"/>
       <c r="V18" s="17" t="s">
         <v>65</v>
@@ -7733,32 +7731,32 @@
       <c r="AE18" s="14" t="s">
         <v>12</v>
       </c>
-      <c r="AF18" s="103"/>
-      <c r="AG18" s="103"/>
-      <c r="AI18" s="103"/>
-      <c r="AJ18" s="107"/>
+      <c r="AF18" s="106"/>
+      <c r="AG18" s="106"/>
+      <c r="AI18" s="106"/>
+      <c r="AJ18" s="110"/>
     </row>
     <row r="19" spans="1:36" ht="18" customHeight="1">
-      <c r="A19" s="96"/>
-      <c r="B19" s="97"/>
-      <c r="C19" s="97"/>
-      <c r="D19" s="97"/>
-      <c r="E19" s="97"/>
-      <c r="F19" s="97"/>
-      <c r="G19" s="97"/>
-      <c r="H19" s="97"/>
-      <c r="I19" s="97"/>
-      <c r="J19" s="97"/>
-      <c r="K19" s="97"/>
-      <c r="L19" s="97"/>
-      <c r="M19" s="97"/>
-      <c r="N19" s="97"/>
-      <c r="O19" s="97"/>
-      <c r="P19" s="97"/>
-      <c r="Q19" s="97"/>
-      <c r="R19" s="97"/>
-      <c r="S19" s="97"/>
-      <c r="T19" s="98"/>
+      <c r="A19" s="99"/>
+      <c r="B19" s="100"/>
+      <c r="C19" s="100"/>
+      <c r="D19" s="100"/>
+      <c r="E19" s="100"/>
+      <c r="F19" s="100"/>
+      <c r="G19" s="100"/>
+      <c r="H19" s="100"/>
+      <c r="I19" s="100"/>
+      <c r="J19" s="100"/>
+      <c r="K19" s="100"/>
+      <c r="L19" s="100"/>
+      <c r="M19" s="100"/>
+      <c r="N19" s="100"/>
+      <c r="O19" s="100"/>
+      <c r="P19" s="100"/>
+      <c r="Q19" s="100"/>
+      <c r="R19" s="100"/>
+      <c r="S19" s="100"/>
+      <c r="T19" s="101"/>
       <c r="U19" s="26"/>
       <c r="V19" s="17" t="s">
         <v>66</v>
@@ -7774,32 +7772,32 @@
       <c r="AE19" s="14" t="s">
         <v>13</v>
       </c>
-      <c r="AF19" s="103"/>
-      <c r="AG19" s="103"/>
-      <c r="AI19" s="103"/>
-      <c r="AJ19" s="107"/>
+      <c r="AF19" s="106"/>
+      <c r="AG19" s="106"/>
+      <c r="AI19" s="106"/>
+      <c r="AJ19" s="110"/>
     </row>
     <row r="20" spans="1:36" ht="3.75" customHeight="1">
-      <c r="A20" s="99"/>
-      <c r="B20" s="100"/>
-      <c r="C20" s="100"/>
-      <c r="D20" s="100"/>
-      <c r="E20" s="100"/>
-      <c r="F20" s="100"/>
-      <c r="G20" s="100"/>
-      <c r="H20" s="100"/>
-      <c r="I20" s="100"/>
-      <c r="J20" s="100"/>
-      <c r="K20" s="100"/>
-      <c r="L20" s="100"/>
-      <c r="M20" s="100"/>
-      <c r="N20" s="100"/>
-      <c r="O20" s="100"/>
-      <c r="P20" s="100"/>
-      <c r="Q20" s="100"/>
-      <c r="R20" s="100"/>
-      <c r="S20" s="100"/>
-      <c r="T20" s="101"/>
+      <c r="A20" s="102"/>
+      <c r="B20" s="103"/>
+      <c r="C20" s="103"/>
+      <c r="D20" s="103"/>
+      <c r="E20" s="103"/>
+      <c r="F20" s="103"/>
+      <c r="G20" s="103"/>
+      <c r="H20" s="103"/>
+      <c r="I20" s="103"/>
+      <c r="J20" s="103"/>
+      <c r="K20" s="103"/>
+      <c r="L20" s="103"/>
+      <c r="M20" s="103"/>
+      <c r="N20" s="103"/>
+      <c r="O20" s="103"/>
+      <c r="P20" s="103"/>
+      <c r="Q20" s="103"/>
+      <c r="R20" s="103"/>
+      <c r="S20" s="103"/>
+      <c r="T20" s="104"/>
       <c r="U20" s="27"/>
       <c r="V20" s="16"/>
       <c r="W20" s="7"/>
@@ -7858,80 +7856,80 @@
       <c r="AJ21" s="47"/>
     </row>
     <row r="22" spans="1:36" ht="16.5" customHeight="1">
-      <c r="A22" s="90"/>
-      <c r="B22" s="91"/>
-      <c r="C22" s="91"/>
-      <c r="D22" s="91"/>
-      <c r="E22" s="91"/>
-      <c r="F22" s="91"/>
-      <c r="G22" s="91"/>
-      <c r="H22" s="91"/>
-      <c r="I22" s="91"/>
-      <c r="J22" s="91"/>
-      <c r="K22" s="91"/>
-      <c r="L22" s="91"/>
-      <c r="M22" s="91"/>
-      <c r="N22" s="91"/>
-      <c r="O22" s="91"/>
-      <c r="P22" s="91"/>
-      <c r="Q22" s="91"/>
-      <c r="R22" s="91"/>
-      <c r="S22" s="91"/>
-      <c r="T22" s="91"/>
-      <c r="U22" s="91"/>
-      <c r="V22" s="91"/>
-      <c r="W22" s="91"/>
-      <c r="X22" s="91"/>
-      <c r="Y22" s="91"/>
-      <c r="Z22" s="91"/>
-      <c r="AA22" s="91"/>
-      <c r="AB22" s="91"/>
-      <c r="AC22" s="91"/>
-      <c r="AD22" s="91"/>
-      <c r="AE22" s="91"/>
-      <c r="AF22" s="91"/>
-      <c r="AG22" s="91"/>
-      <c r="AH22" s="91"/>
-      <c r="AI22" s="91"/>
-      <c r="AJ22" s="92"/>
+      <c r="A22" s="93"/>
+      <c r="B22" s="94"/>
+      <c r="C22" s="94"/>
+      <c r="D22" s="94"/>
+      <c r="E22" s="94"/>
+      <c r="F22" s="94"/>
+      <c r="G22" s="94"/>
+      <c r="H22" s="94"/>
+      <c r="I22" s="94"/>
+      <c r="J22" s="94"/>
+      <c r="K22" s="94"/>
+      <c r="L22" s="94"/>
+      <c r="M22" s="94"/>
+      <c r="N22" s="94"/>
+      <c r="O22" s="94"/>
+      <c r="P22" s="94"/>
+      <c r="Q22" s="94"/>
+      <c r="R22" s="94"/>
+      <c r="S22" s="94"/>
+      <c r="T22" s="94"/>
+      <c r="U22" s="94"/>
+      <c r="V22" s="94"/>
+      <c r="W22" s="94"/>
+      <c r="X22" s="94"/>
+      <c r="Y22" s="94"/>
+      <c r="Z22" s="94"/>
+      <c r="AA22" s="94"/>
+      <c r="AB22" s="94"/>
+      <c r="AC22" s="94"/>
+      <c r="AD22" s="94"/>
+      <c r="AE22" s="94"/>
+      <c r="AF22" s="94"/>
+      <c r="AG22" s="94"/>
+      <c r="AH22" s="94"/>
+      <c r="AI22" s="94"/>
+      <c r="AJ22" s="95"/>
     </row>
     <row r="23" spans="1:36" ht="16.5" customHeight="1">
-      <c r="A23" s="93"/>
-      <c r="B23" s="94"/>
-      <c r="C23" s="94"/>
-      <c r="D23" s="94"/>
-      <c r="E23" s="94"/>
-      <c r="F23" s="94"/>
-      <c r="G23" s="94"/>
-      <c r="H23" s="94"/>
-      <c r="I23" s="94"/>
-      <c r="J23" s="94"/>
-      <c r="K23" s="94"/>
-      <c r="L23" s="94"/>
-      <c r="M23" s="94"/>
-      <c r="N23" s="94"/>
-      <c r="O23" s="94"/>
-      <c r="P23" s="94"/>
-      <c r="Q23" s="94"/>
-      <c r="R23" s="94"/>
-      <c r="S23" s="94"/>
-      <c r="T23" s="94"/>
-      <c r="U23" s="94"/>
-      <c r="V23" s="94"/>
-      <c r="W23" s="94"/>
-      <c r="X23" s="94"/>
-      <c r="Y23" s="94"/>
-      <c r="Z23" s="94"/>
-      <c r="AA23" s="94"/>
-      <c r="AB23" s="94"/>
-      <c r="AC23" s="94"/>
-      <c r="AD23" s="94"/>
-      <c r="AE23" s="94"/>
-      <c r="AF23" s="94"/>
-      <c r="AG23" s="94"/>
-      <c r="AH23" s="94"/>
-      <c r="AI23" s="94"/>
-      <c r="AJ23" s="95"/>
+      <c r="A23" s="96"/>
+      <c r="B23" s="97"/>
+      <c r="C23" s="97"/>
+      <c r="D23" s="97"/>
+      <c r="E23" s="97"/>
+      <c r="F23" s="97"/>
+      <c r="G23" s="97"/>
+      <c r="H23" s="97"/>
+      <c r="I23" s="97"/>
+      <c r="J23" s="97"/>
+      <c r="K23" s="97"/>
+      <c r="L23" s="97"/>
+      <c r="M23" s="97"/>
+      <c r="N23" s="97"/>
+      <c r="O23" s="97"/>
+      <c r="P23" s="97"/>
+      <c r="Q23" s="97"/>
+      <c r="R23" s="97"/>
+      <c r="S23" s="97"/>
+      <c r="T23" s="97"/>
+      <c r="U23" s="97"/>
+      <c r="V23" s="97"/>
+      <c r="W23" s="97"/>
+      <c r="X23" s="97"/>
+      <c r="Y23" s="97"/>
+      <c r="Z23" s="97"/>
+      <c r="AA23" s="97"/>
+      <c r="AB23" s="97"/>
+      <c r="AC23" s="97"/>
+      <c r="AD23" s="97"/>
+      <c r="AE23" s="97"/>
+      <c r="AF23" s="97"/>
+      <c r="AG23" s="97"/>
+      <c r="AH23" s="97"/>
+      <c r="AI23" s="97"/>
+      <c r="AJ23" s="98"/>
     </row>
     <row r="24" spans="1:36" ht="12.75" customHeight="1">
       <c r="A24" s="46" t="s">
@@ -7974,42 +7972,42 @@
       <c r="AJ24" s="47"/>
     </row>
     <row r="25" spans="1:36" ht="18" customHeight="1">
-      <c r="A25" s="87"/>
-      <c r="B25" s="88"/>
-      <c r="C25" s="88"/>
-      <c r="D25" s="88"/>
-      <c r="E25" s="88"/>
-      <c r="F25" s="88"/>
-      <c r="G25" s="88"/>
-      <c r="H25" s="88"/>
-      <c r="I25" s="88"/>
-      <c r="J25" s="88"/>
-      <c r="K25" s="88"/>
-      <c r="L25" s="88"/>
-      <c r="M25" s="88"/>
-      <c r="N25" s="88"/>
-      <c r="O25" s="88"/>
-      <c r="P25" s="88"/>
-      <c r="Q25" s="88"/>
-      <c r="R25" s="88"/>
-      <c r="S25" s="88"/>
-      <c r="T25" s="88"/>
-      <c r="U25" s="88"/>
-      <c r="V25" s="88"/>
-      <c r="W25" s="88"/>
-      <c r="X25" s="88"/>
-      <c r="Y25" s="88"/>
-      <c r="Z25" s="88"/>
-      <c r="AA25" s="88"/>
-      <c r="AB25" s="88"/>
-      <c r="AC25" s="88"/>
-      <c r="AD25" s="88"/>
-      <c r="AE25" s="88"/>
-      <c r="AF25" s="88"/>
-      <c r="AG25" s="88"/>
-      <c r="AH25" s="88"/>
-      <c r="AI25" s="88"/>
-      <c r="AJ25" s="89"/>
+      <c r="A25" s="90"/>
+      <c r="B25" s="91"/>
+      <c r="C25" s="91"/>
+      <c r="D25" s="91"/>
+      <c r="E25" s="91"/>
+      <c r="F25" s="91"/>
+      <c r="G25" s="91"/>
+      <c r="H25" s="91"/>
+      <c r="I25" s="91"/>
+      <c r="J25" s="91"/>
+      <c r="K25" s="91"/>
+      <c r="L25" s="91"/>
+      <c r="M25" s="91"/>
+      <c r="N25" s="91"/>
+      <c r="O25" s="91"/>
+      <c r="P25" s="91"/>
+      <c r="Q25" s="91"/>
+      <c r="R25" s="91"/>
+      <c r="S25" s="91"/>
+      <c r="T25" s="91"/>
+      <c r="U25" s="91"/>
+      <c r="V25" s="91"/>
+      <c r="W25" s="91"/>
+      <c r="X25" s="91"/>
+      <c r="Y25" s="91"/>
+      <c r="Z25" s="91"/>
+      <c r="AA25" s="91"/>
+      <c r="AB25" s="91"/>
+      <c r="AC25" s="91"/>
+      <c r="AD25" s="91"/>
+      <c r="AE25" s="91"/>
+      <c r="AF25" s="91"/>
+      <c r="AG25" s="91"/>
+      <c r="AH25" s="91"/>
+      <c r="AI25" s="91"/>
+      <c r="AJ25" s="92"/>
     </row>
     <row r="26" spans="1:36" ht="12.75" customHeight="1">
       <c r="A26" s="46" t="s">
@@ -8052,137 +8050,137 @@
       <c r="AJ26" s="47"/>
     </row>
     <row r="27" spans="1:36" ht="15" customHeight="1">
-      <c r="A27" s="146"/>
-      <c r="B27" s="147"/>
-      <c r="C27" s="147"/>
-      <c r="D27" s="147"/>
-      <c r="E27" s="147"/>
-      <c r="F27" s="147"/>
-      <c r="G27" s="147"/>
-      <c r="H27" s="147"/>
-      <c r="I27" s="147"/>
-      <c r="J27" s="147"/>
-      <c r="K27" s="147"/>
-      <c r="L27" s="147"/>
-      <c r="M27" s="147"/>
-      <c r="N27" s="147"/>
-      <c r="O27" s="147"/>
-      <c r="P27" s="147"/>
-      <c r="Q27" s="147"/>
-      <c r="R27" s="147"/>
-      <c r="S27" s="147"/>
-      <c r="T27" s="147"/>
-      <c r="U27" s="147"/>
-      <c r="V27" s="147"/>
-      <c r="W27" s="147"/>
-      <c r="X27" s="147"/>
-      <c r="Y27" s="147"/>
-      <c r="Z27" s="147"/>
-      <c r="AA27" s="147"/>
-      <c r="AB27" s="147"/>
-      <c r="AC27" s="147"/>
-      <c r="AD27" s="147"/>
-      <c r="AE27" s="147"/>
-      <c r="AF27" s="147"/>
-      <c r="AG27" s="147"/>
-      <c r="AH27" s="147"/>
-      <c r="AI27" s="147"/>
-      <c r="AJ27" s="148"/>
+      <c r="A27" s="149"/>
+      <c r="B27" s="150"/>
+      <c r="C27" s="150"/>
+      <c r="D27" s="150"/>
+      <c r="E27" s="150"/>
+      <c r="F27" s="150"/>
+      <c r="G27" s="150"/>
+      <c r="H27" s="150"/>
+      <c r="I27" s="150"/>
+      <c r="J27" s="150"/>
+      <c r="K27" s="150"/>
+      <c r="L27" s="150"/>
+      <c r="M27" s="150"/>
+      <c r="N27" s="150"/>
+      <c r="O27" s="150"/>
+      <c r="P27" s="150"/>
+      <c r="Q27" s="150"/>
+      <c r="R27" s="150"/>
+      <c r="S27" s="150"/>
+      <c r="T27" s="150"/>
+      <c r="U27" s="150"/>
+      <c r="V27" s="150"/>
+      <c r="W27" s="150"/>
+      <c r="X27" s="150"/>
+      <c r="Y27" s="150"/>
+      <c r="Z27" s="150"/>
+      <c r="AA27" s="150"/>
+      <c r="AB27" s="150"/>
+      <c r="AC27" s="150"/>
+      <c r="AD27" s="150"/>
+      <c r="AE27" s="150"/>
+      <c r="AF27" s="150"/>
+      <c r="AG27" s="150"/>
+      <c r="AH27" s="150"/>
+      <c r="AI27" s="150"/>
+      <c r="AJ27" s="151"/>
     </row>
     <row r="28" spans="1:36" ht="15" customHeight="1">
-      <c r="A28" s="149"/>
-      <c r="B28" s="147"/>
-      <c r="C28" s="147"/>
-      <c r="D28" s="147"/>
-      <c r="E28" s="147"/>
-      <c r="F28" s="147"/>
-      <c r="G28" s="147"/>
-      <c r="H28" s="147"/>
-      <c r="I28" s="147"/>
-      <c r="J28" s="147"/>
-      <c r="K28" s="147"/>
-      <c r="L28" s="147"/>
-      <c r="M28" s="147"/>
-      <c r="N28" s="147"/>
-      <c r="O28" s="147"/>
-      <c r="P28" s="147"/>
-      <c r="Q28" s="147"/>
-      <c r="R28" s="147"/>
-      <c r="S28" s="147"/>
-      <c r="T28" s="147"/>
-      <c r="U28" s="147"/>
-      <c r="V28" s="147"/>
-      <c r="W28" s="147"/>
-      <c r="X28" s="147"/>
-      <c r="Y28" s="147"/>
-      <c r="Z28" s="147"/>
-      <c r="AA28" s="147"/>
-      <c r="AB28" s="147"/>
-      <c r="AC28" s="147"/>
-      <c r="AD28" s="147"/>
-      <c r="AE28" s="147"/>
-      <c r="AF28" s="147"/>
-      <c r="AG28" s="147"/>
-      <c r="AH28" s="147"/>
-      <c r="AI28" s="147"/>
-      <c r="AJ28" s="148"/>
+      <c r="A28" s="152"/>
+      <c r="B28" s="150"/>
+      <c r="C28" s="150"/>
+      <c r="D28" s="150"/>
+      <c r="E28" s="150"/>
+      <c r="F28" s="150"/>
+      <c r="G28" s="150"/>
+      <c r="H28" s="150"/>
+      <c r="I28" s="150"/>
+      <c r="J28" s="150"/>
+      <c r="K28" s="150"/>
+      <c r="L28" s="150"/>
+      <c r="M28" s="150"/>
+      <c r="N28" s="150"/>
+      <c r="O28" s="150"/>
+      <c r="P28" s="150"/>
+      <c r="Q28" s="150"/>
+      <c r="R28" s="150"/>
+      <c r="S28" s="150"/>
+      <c r="T28" s="150"/>
+      <c r="U28" s="150"/>
+      <c r="V28" s="150"/>
+      <c r="W28" s="150"/>
+      <c r="X28" s="150"/>
+      <c r="Y28" s="150"/>
+      <c r="Z28" s="150"/>
+      <c r="AA28" s="150"/>
+      <c r="AB28" s="150"/>
+      <c r="AC28" s="150"/>
+      <c r="AD28" s="150"/>
+      <c r="AE28" s="150"/>
+      <c r="AF28" s="150"/>
+      <c r="AG28" s="150"/>
+      <c r="AH28" s="150"/>
+      <c r="AI28" s="150"/>
+      <c r="AJ28" s="151"/>
     </row>
     <row r="29" spans="1:36" ht="217.2" customHeight="1">
-      <c r="A29" s="150"/>
-      <c r="B29" s="151"/>
-      <c r="C29" s="151"/>
-      <c r="D29" s="151"/>
-      <c r="E29" s="151"/>
-      <c r="F29" s="151"/>
-      <c r="G29" s="151"/>
-      <c r="H29" s="151"/>
-      <c r="I29" s="151"/>
-      <c r="J29" s="151"/>
-      <c r="K29" s="151"/>
-      <c r="L29" s="151"/>
-      <c r="M29" s="151"/>
-      <c r="N29" s="151"/>
-      <c r="O29" s="151"/>
-      <c r="P29" s="151"/>
-      <c r="Q29" s="151"/>
-      <c r="R29" s="151"/>
-      <c r="S29" s="151"/>
-      <c r="T29" s="151"/>
-      <c r="U29" s="151"/>
-      <c r="V29" s="151"/>
-      <c r="W29" s="151"/>
-      <c r="X29" s="151"/>
-      <c r="Y29" s="151"/>
-      <c r="Z29" s="151"/>
-      <c r="AA29" s="151"/>
-      <c r="AB29" s="151"/>
-      <c r="AC29" s="151"/>
-      <c r="AD29" s="151"/>
-      <c r="AE29" s="151"/>
-      <c r="AF29" s="151"/>
-      <c r="AG29" s="151"/>
-      <c r="AH29" s="151"/>
-      <c r="AI29" s="151"/>
-      <c r="AJ29" s="152"/>
+      <c r="A29" s="153"/>
+      <c r="B29" s="154"/>
+      <c r="C29" s="154"/>
+      <c r="D29" s="154"/>
+      <c r="E29" s="154"/>
+      <c r="F29" s="154"/>
+      <c r="G29" s="154"/>
+      <c r="H29" s="154"/>
+      <c r="I29" s="154"/>
+      <c r="J29" s="154"/>
+      <c r="K29" s="154"/>
+      <c r="L29" s="154"/>
+      <c r="M29" s="154"/>
+      <c r="N29" s="154"/>
+      <c r="O29" s="154"/>
+      <c r="P29" s="154"/>
+      <c r="Q29" s="154"/>
+      <c r="R29" s="154"/>
+      <c r="S29" s="154"/>
+      <c r="T29" s="154"/>
+      <c r="U29" s="154"/>
+      <c r="V29" s="154"/>
+      <c r="W29" s="154"/>
+      <c r="X29" s="154"/>
+      <c r="Y29" s="154"/>
+      <c r="Z29" s="154"/>
+      <c r="AA29" s="154"/>
+      <c r="AB29" s="154"/>
+      <c r="AC29" s="154"/>
+      <c r="AD29" s="154"/>
+      <c r="AE29" s="154"/>
+      <c r="AF29" s="154"/>
+      <c r="AG29" s="154"/>
+      <c r="AH29" s="154"/>
+      <c r="AI29" s="154"/>
+      <c r="AJ29" s="155"/>
     </row>
     <row r="30" spans="1:36" ht="12.75" customHeight="1">
-      <c r="A30" s="153" t="s">
+      <c r="A30" s="156" t="s">
         <v>17</v>
       </c>
-      <c r="B30" s="154"/>
-      <c r="C30" s="154"/>
-      <c r="D30" s="154"/>
-      <c r="E30" s="154"/>
-      <c r="F30" s="154"/>
-      <c r="G30" s="154"/>
-      <c r="H30" s="154"/>
-      <c r="I30" s="154"/>
-      <c r="J30" s="154"/>
-      <c r="K30" s="154"/>
-      <c r="L30" s="154"/>
-      <c r="M30" s="154"/>
-      <c r="N30" s="154"/>
-      <c r="O30" s="154"/>
+      <c r="B30" s="157"/>
+      <c r="C30" s="157"/>
+      <c r="D30" s="157"/>
+      <c r="E30" s="157"/>
+      <c r="F30" s="157"/>
+      <c r="G30" s="157"/>
+      <c r="H30" s="157"/>
+      <c r="I30" s="157"/>
+      <c r="J30" s="157"/>
+      <c r="K30" s="157"/>
+      <c r="L30" s="157"/>
+      <c r="M30" s="157"/>
+      <c r="N30" s="157"/>
+      <c r="O30" s="157"/>
       <c r="P30" s="41"/>
       <c r="Q30" s="41"/>
       <c r="R30" s="41"/>
@@ -8206,216 +8204,216 @@
       <c r="AJ30" s="42"/>
     </row>
     <row r="31" spans="1:36" ht="16.5" customHeight="1">
-      <c r="A31" s="146"/>
-      <c r="B31" s="156"/>
-      <c r="C31" s="156"/>
-      <c r="D31" s="156"/>
-      <c r="E31" s="156"/>
-      <c r="F31" s="156"/>
-      <c r="G31" s="156"/>
-      <c r="H31" s="156"/>
-      <c r="I31" s="156"/>
-      <c r="J31" s="156"/>
-      <c r="K31" s="156"/>
-      <c r="L31" s="156"/>
-      <c r="M31" s="156"/>
-      <c r="N31" s="156"/>
-      <c r="O31" s="156"/>
-      <c r="P31" s="156"/>
-      <c r="Q31" s="156"/>
-      <c r="R31" s="156"/>
-      <c r="S31" s="156"/>
-      <c r="T31" s="156"/>
-      <c r="U31" s="156"/>
-      <c r="V31" s="156"/>
-      <c r="W31" s="156"/>
-      <c r="X31" s="156"/>
-      <c r="Y31" s="156"/>
-      <c r="Z31" s="156"/>
-      <c r="AA31" s="156"/>
-      <c r="AB31" s="156"/>
-      <c r="AC31" s="156"/>
-      <c r="AD31" s="156"/>
-      <c r="AE31" s="156"/>
-      <c r="AF31" s="156"/>
-      <c r="AG31" s="156"/>
-      <c r="AH31" s="156"/>
-      <c r="AI31" s="156"/>
-      <c r="AJ31" s="157"/>
+      <c r="A31" s="149"/>
+      <c r="B31" s="159"/>
+      <c r="C31" s="159"/>
+      <c r="D31" s="159"/>
+      <c r="E31" s="159"/>
+      <c r="F31" s="159"/>
+      <c r="G31" s="159"/>
+      <c r="H31" s="159"/>
+      <c r="I31" s="159"/>
+      <c r="J31" s="159"/>
+      <c r="K31" s="159"/>
+      <c r="L31" s="159"/>
+      <c r="M31" s="159"/>
+      <c r="N31" s="159"/>
+      <c r="O31" s="159"/>
+      <c r="P31" s="159"/>
+      <c r="Q31" s="159"/>
+      <c r="R31" s="159"/>
+      <c r="S31" s="159"/>
+      <c r="T31" s="159"/>
+      <c r="U31" s="159"/>
+      <c r="V31" s="159"/>
+      <c r="W31" s="159"/>
+      <c r="X31" s="159"/>
+      <c r="Y31" s="159"/>
+      <c r="Z31" s="159"/>
+      <c r="AA31" s="159"/>
+      <c r="AB31" s="159"/>
+      <c r="AC31" s="159"/>
+      <c r="AD31" s="159"/>
+      <c r="AE31" s="159"/>
+      <c r="AF31" s="159"/>
+      <c r="AG31" s="159"/>
+      <c r="AH31" s="159"/>
+      <c r="AI31" s="159"/>
+      <c r="AJ31" s="160"/>
     </row>
     <row r="32" spans="1:36" ht="16.5" customHeight="1">
-      <c r="A32" s="146"/>
-      <c r="B32" s="156"/>
-      <c r="C32" s="156"/>
-      <c r="D32" s="156"/>
-      <c r="E32" s="156"/>
-      <c r="F32" s="156"/>
-      <c r="G32" s="156"/>
-      <c r="H32" s="156"/>
-      <c r="I32" s="156"/>
-      <c r="J32" s="156"/>
-      <c r="K32" s="156"/>
-      <c r="L32" s="156"/>
-      <c r="M32" s="156"/>
-      <c r="N32" s="156"/>
-      <c r="O32" s="156"/>
-      <c r="P32" s="156"/>
-      <c r="Q32" s="156"/>
-      <c r="R32" s="156"/>
-      <c r="S32" s="156"/>
-      <c r="T32" s="156"/>
-      <c r="U32" s="156"/>
-      <c r="V32" s="156"/>
-      <c r="W32" s="156"/>
-      <c r="X32" s="156"/>
-      <c r="Y32" s="156"/>
-      <c r="Z32" s="156"/>
-      <c r="AA32" s="156"/>
-      <c r="AB32" s="156"/>
-      <c r="AC32" s="156"/>
-      <c r="AD32" s="156"/>
-      <c r="AE32" s="156"/>
-      <c r="AF32" s="156"/>
-      <c r="AG32" s="156"/>
-      <c r="AH32" s="156"/>
-      <c r="AI32" s="156"/>
-      <c r="AJ32" s="157"/>
+      <c r="A32" s="149"/>
+      <c r="B32" s="159"/>
+      <c r="C32" s="159"/>
+      <c r="D32" s="159"/>
+      <c r="E32" s="159"/>
+      <c r="F32" s="159"/>
+      <c r="G32" s="159"/>
+      <c r="H32" s="159"/>
+      <c r="I32" s="159"/>
+      <c r="J32" s="159"/>
+      <c r="K32" s="159"/>
+      <c r="L32" s="159"/>
+      <c r="M32" s="159"/>
+      <c r="N32" s="159"/>
+      <c r="O32" s="159"/>
+      <c r="P32" s="159"/>
+      <c r="Q32" s="159"/>
+      <c r="R32" s="159"/>
+      <c r="S32" s="159"/>
+      <c r="T32" s="159"/>
+      <c r="U32" s="159"/>
+      <c r="V32" s="159"/>
+      <c r="W32" s="159"/>
+      <c r="X32" s="159"/>
+      <c r="Y32" s="159"/>
+      <c r="Z32" s="159"/>
+      <c r="AA32" s="159"/>
+      <c r="AB32" s="159"/>
+      <c r="AC32" s="159"/>
+      <c r="AD32" s="159"/>
+      <c r="AE32" s="159"/>
+      <c r="AF32" s="159"/>
+      <c r="AG32" s="159"/>
+      <c r="AH32" s="159"/>
+      <c r="AI32" s="159"/>
+      <c r="AJ32" s="160"/>
     </row>
     <row r="33" spans="1:36" ht="16.5" customHeight="1">
-      <c r="A33" s="146"/>
-      <c r="B33" s="156"/>
-      <c r="C33" s="156"/>
-      <c r="D33" s="156"/>
-      <c r="E33" s="156"/>
-      <c r="F33" s="156"/>
-      <c r="G33" s="156"/>
-      <c r="H33" s="156"/>
-      <c r="I33" s="156"/>
-      <c r="J33" s="156"/>
-      <c r="K33" s="156"/>
-      <c r="L33" s="156"/>
-      <c r="M33" s="156"/>
-      <c r="N33" s="156"/>
-      <c r="O33" s="156"/>
-      <c r="P33" s="156"/>
-      <c r="Q33" s="156"/>
-      <c r="R33" s="156"/>
-      <c r="S33" s="156"/>
-      <c r="T33" s="156"/>
-      <c r="U33" s="156"/>
-      <c r="V33" s="156"/>
-      <c r="W33" s="156"/>
-      <c r="X33" s="156"/>
-      <c r="Y33" s="156"/>
-      <c r="Z33" s="156"/>
-      <c r="AA33" s="156"/>
-      <c r="AB33" s="156"/>
-      <c r="AC33" s="156"/>
-      <c r="AD33" s="156"/>
-      <c r="AE33" s="156"/>
-      <c r="AF33" s="156"/>
-      <c r="AG33" s="156"/>
-      <c r="AH33" s="156"/>
-      <c r="AI33" s="156"/>
-      <c r="AJ33" s="157"/>
+      <c r="A33" s="149"/>
+      <c r="B33" s="159"/>
+      <c r="C33" s="159"/>
+      <c r="D33" s="159"/>
+      <c r="E33" s="159"/>
+      <c r="F33" s="159"/>
+      <c r="G33" s="159"/>
+      <c r="H33" s="159"/>
+      <c r="I33" s="159"/>
+      <c r="J33" s="159"/>
+      <c r="K33" s="159"/>
+      <c r="L33" s="159"/>
+      <c r="M33" s="159"/>
+      <c r="N33" s="159"/>
+      <c r="O33" s="159"/>
+      <c r="P33" s="159"/>
+      <c r="Q33" s="159"/>
+      <c r="R33" s="159"/>
+      <c r="S33" s="159"/>
+      <c r="T33" s="159"/>
+      <c r="U33" s="159"/>
+      <c r="V33" s="159"/>
+      <c r="W33" s="159"/>
+      <c r="X33" s="159"/>
+      <c r="Y33" s="159"/>
+      <c r="Z33" s="159"/>
+      <c r="AA33" s="159"/>
+      <c r="AB33" s="159"/>
+      <c r="AC33" s="159"/>
+      <c r="AD33" s="159"/>
+      <c r="AE33" s="159"/>
+      <c r="AF33" s="159"/>
+      <c r="AG33" s="159"/>
+      <c r="AH33" s="159"/>
+      <c r="AI33" s="159"/>
+      <c r="AJ33" s="160"/>
     </row>
     <row r="34" spans="1:36" ht="61.8" customHeight="1">
-      <c r="A34" s="146"/>
-      <c r="B34" s="156"/>
-      <c r="C34" s="156"/>
-      <c r="D34" s="156"/>
-      <c r="E34" s="156"/>
-      <c r="F34" s="156"/>
-      <c r="G34" s="156"/>
-      <c r="H34" s="156"/>
-      <c r="I34" s="156"/>
-      <c r="J34" s="156"/>
-      <c r="K34" s="156"/>
-      <c r="L34" s="156"/>
-      <c r="M34" s="156"/>
-      <c r="N34" s="156"/>
-      <c r="O34" s="156"/>
-      <c r="P34" s="156"/>
-      <c r="Q34" s="156"/>
-      <c r="R34" s="156"/>
-      <c r="S34" s="156"/>
-      <c r="T34" s="156"/>
-      <c r="U34" s="156"/>
-      <c r="V34" s="156"/>
-      <c r="W34" s="156"/>
-      <c r="X34" s="156"/>
-      <c r="Y34" s="156"/>
-      <c r="Z34" s="156"/>
-      <c r="AA34" s="156"/>
-      <c r="AB34" s="156"/>
-      <c r="AC34" s="156"/>
-      <c r="AD34" s="156"/>
-      <c r="AE34" s="156"/>
-      <c r="AF34" s="156"/>
-      <c r="AG34" s="156"/>
-      <c r="AH34" s="156"/>
-      <c r="AI34" s="156"/>
-      <c r="AJ34" s="157"/>
+      <c r="A34" s="149"/>
+      <c r="B34" s="159"/>
+      <c r="C34" s="159"/>
+      <c r="D34" s="159"/>
+      <c r="E34" s="159"/>
+      <c r="F34" s="159"/>
+      <c r="G34" s="159"/>
+      <c r="H34" s="159"/>
+      <c r="I34" s="159"/>
+      <c r="J34" s="159"/>
+      <c r="K34" s="159"/>
+      <c r="L34" s="159"/>
+      <c r="M34" s="159"/>
+      <c r="N34" s="159"/>
+      <c r="O34" s="159"/>
+      <c r="P34" s="159"/>
+      <c r="Q34" s="159"/>
+      <c r="R34" s="159"/>
+      <c r="S34" s="159"/>
+      <c r="T34" s="159"/>
+      <c r="U34" s="159"/>
+      <c r="V34" s="159"/>
+      <c r="W34" s="159"/>
+      <c r="X34" s="159"/>
+      <c r="Y34" s="159"/>
+      <c r="Z34" s="159"/>
+      <c r="AA34" s="159"/>
+      <c r="AB34" s="159"/>
+      <c r="AC34" s="159"/>
+      <c r="AD34" s="159"/>
+      <c r="AE34" s="159"/>
+      <c r="AF34" s="159"/>
+      <c r="AG34" s="159"/>
+      <c r="AH34" s="159"/>
+      <c r="AI34" s="159"/>
+      <c r="AJ34" s="160"/>
     </row>
     <row r="35" spans="1:36" ht="13.2" customHeight="1">
-      <c r="A35" s="158"/>
-      <c r="B35" s="159"/>
-      <c r="C35" s="159"/>
-      <c r="D35" s="159"/>
-      <c r="E35" s="159"/>
-      <c r="F35" s="159"/>
-      <c r="G35" s="159"/>
-      <c r="H35" s="159"/>
-      <c r="I35" s="159"/>
-      <c r="J35" s="159"/>
-      <c r="K35" s="159"/>
-      <c r="L35" s="159"/>
-      <c r="M35" s="159"/>
-      <c r="N35" s="159"/>
-      <c r="O35" s="159"/>
-      <c r="P35" s="159"/>
-      <c r="Q35" s="159"/>
-      <c r="R35" s="159"/>
-      <c r="S35" s="159"/>
-      <c r="T35" s="159"/>
-      <c r="U35" s="159"/>
-      <c r="V35" s="159"/>
-      <c r="W35" s="159"/>
-      <c r="X35" s="159"/>
-      <c r="Y35" s="159"/>
-      <c r="Z35" s="159"/>
-      <c r="AA35" s="159"/>
-      <c r="AB35" s="159"/>
-      <c r="AC35" s="159"/>
-      <c r="AD35" s="159"/>
-      <c r="AE35" s="159"/>
-      <c r="AF35" s="159"/>
-      <c r="AG35" s="159"/>
-      <c r="AH35" s="159"/>
-      <c r="AI35" s="159"/>
-      <c r="AJ35" s="160"/>
+      <c r="A35" s="161"/>
+      <c r="B35" s="162"/>
+      <c r="C35" s="162"/>
+      <c r="D35" s="162"/>
+      <c r="E35" s="162"/>
+      <c r="F35" s="162"/>
+      <c r="G35" s="162"/>
+      <c r="H35" s="162"/>
+      <c r="I35" s="162"/>
+      <c r="J35" s="162"/>
+      <c r="K35" s="162"/>
+      <c r="L35" s="162"/>
+      <c r="M35" s="162"/>
+      <c r="N35" s="162"/>
+      <c r="O35" s="162"/>
+      <c r="P35" s="162"/>
+      <c r="Q35" s="162"/>
+      <c r="R35" s="162"/>
+      <c r="S35" s="162"/>
+      <c r="T35" s="162"/>
+      <c r="U35" s="162"/>
+      <c r="V35" s="162"/>
+      <c r="W35" s="162"/>
+      <c r="X35" s="162"/>
+      <c r="Y35" s="162"/>
+      <c r="Z35" s="162"/>
+      <c r="AA35" s="162"/>
+      <c r="AB35" s="162"/>
+      <c r="AC35" s="162"/>
+      <c r="AD35" s="162"/>
+      <c r="AE35" s="162"/>
+      <c r="AF35" s="162"/>
+      <c r="AG35" s="162"/>
+      <c r="AH35" s="162"/>
+      <c r="AI35" s="162"/>
+      <c r="AJ35" s="163"/>
     </row>
     <row r="36" spans="1:36" ht="13.5" customHeight="1">
-      <c r="A36" s="62" t="s">
+      <c r="A36" s="82" t="s">
         <v>94</v>
       </c>
-      <c r="B36" s="63"/>
-      <c r="C36" s="63"/>
-      <c r="D36" s="63"/>
-      <c r="E36" s="63"/>
-      <c r="F36" s="63"/>
-      <c r="G36" s="63"/>
-      <c r="H36" s="63"/>
-      <c r="I36" s="63"/>
-      <c r="J36" s="63"/>
-      <c r="K36" s="63"/>
-      <c r="L36" s="63"/>
-      <c r="M36" s="63"/>
-      <c r="N36" s="63"/>
-      <c r="O36" s="63"/>
-      <c r="P36" s="63"/>
-      <c r="Q36" s="63"/>
-      <c r="R36" s="63"/>
+      <c r="B36" s="83"/>
+      <c r="C36" s="83"/>
+      <c r="D36" s="83"/>
+      <c r="E36" s="83"/>
+      <c r="F36" s="83"/>
+      <c r="G36" s="83"/>
+      <c r="H36" s="83"/>
+      <c r="I36" s="83"/>
+      <c r="J36" s="83"/>
+      <c r="K36" s="83"/>
+      <c r="L36" s="83"/>
+      <c r="M36" s="83"/>
+      <c r="N36" s="83"/>
+      <c r="O36" s="83"/>
+      <c r="P36" s="83"/>
+      <c r="Q36" s="83"/>
+      <c r="R36" s="83"/>
       <c r="S36" s="40"/>
       <c r="T36" s="40"/>
       <c r="U36" s="40"/>
@@ -8436,178 +8434,178 @@
       <c r="AJ36" s="43"/>
     </row>
     <row r="37" spans="1:36" ht="14.25" customHeight="1">
-      <c r="A37" s="146"/>
-      <c r="B37" s="156"/>
-      <c r="C37" s="156"/>
-      <c r="D37" s="156"/>
-      <c r="E37" s="156"/>
-      <c r="F37" s="156"/>
-      <c r="G37" s="156"/>
-      <c r="H37" s="156"/>
-      <c r="I37" s="156"/>
-      <c r="J37" s="156"/>
-      <c r="K37" s="156"/>
-      <c r="L37" s="156"/>
-      <c r="M37" s="156"/>
-      <c r="N37" s="156"/>
-      <c r="O37" s="156"/>
-      <c r="P37" s="156"/>
-      <c r="Q37" s="156"/>
-      <c r="R37" s="156"/>
-      <c r="S37" s="156"/>
-      <c r="T37" s="156"/>
-      <c r="U37" s="156"/>
-      <c r="V37" s="156"/>
-      <c r="W37" s="156"/>
-      <c r="X37" s="156"/>
-      <c r="Y37" s="156"/>
-      <c r="Z37" s="156"/>
-      <c r="AA37" s="156"/>
-      <c r="AB37" s="156"/>
-      <c r="AC37" s="156"/>
-      <c r="AD37" s="156"/>
-      <c r="AE37" s="156"/>
-      <c r="AF37" s="156"/>
-      <c r="AG37" s="156"/>
-      <c r="AH37" s="156"/>
-      <c r="AI37" s="156"/>
-      <c r="AJ37" s="157"/>
+      <c r="A37" s="149"/>
+      <c r="B37" s="159"/>
+      <c r="C37" s="159"/>
+      <c r="D37" s="159"/>
+      <c r="E37" s="159"/>
+      <c r="F37" s="159"/>
+      <c r="G37" s="159"/>
+      <c r="H37" s="159"/>
+      <c r="I37" s="159"/>
+      <c r="J37" s="159"/>
+      <c r="K37" s="159"/>
+      <c r="L37" s="159"/>
+      <c r="M37" s="159"/>
+      <c r="N37" s="159"/>
+      <c r="O37" s="159"/>
+      <c r="P37" s="159"/>
+      <c r="Q37" s="159"/>
+      <c r="R37" s="159"/>
+      <c r="S37" s="159"/>
+      <c r="T37" s="159"/>
+      <c r="U37" s="159"/>
+      <c r="V37" s="159"/>
+      <c r="W37" s="159"/>
+      <c r="X37" s="159"/>
+      <c r="Y37" s="159"/>
+      <c r="Z37" s="159"/>
+      <c r="AA37" s="159"/>
+      <c r="AB37" s="159"/>
+      <c r="AC37" s="159"/>
+      <c r="AD37" s="159"/>
+      <c r="AE37" s="159"/>
+      <c r="AF37" s="159"/>
+      <c r="AG37" s="159"/>
+      <c r="AH37" s="159"/>
+      <c r="AI37" s="159"/>
+      <c r="AJ37" s="160"/>
     </row>
     <row r="38" spans="1:36" ht="14.25" customHeight="1">
-      <c r="A38" s="146"/>
-      <c r="B38" s="156"/>
-      <c r="C38" s="156"/>
-      <c r="D38" s="156"/>
-      <c r="E38" s="156"/>
-      <c r="F38" s="156"/>
-      <c r="G38" s="156"/>
-      <c r="H38" s="156"/>
-      <c r="I38" s="156"/>
-      <c r="J38" s="156"/>
-      <c r="K38" s="156"/>
-      <c r="L38" s="156"/>
-      <c r="M38" s="156"/>
-      <c r="N38" s="156"/>
-      <c r="O38" s="156"/>
-      <c r="P38" s="156"/>
-      <c r="Q38" s="156"/>
-      <c r="R38" s="156"/>
-      <c r="S38" s="156"/>
-      <c r="T38" s="156"/>
-      <c r="U38" s="156"/>
-      <c r="V38" s="156"/>
-      <c r="W38" s="156"/>
-      <c r="X38" s="156"/>
-      <c r="Y38" s="156"/>
-      <c r="Z38" s="156"/>
-      <c r="AA38" s="156"/>
-      <c r="AB38" s="156"/>
-      <c r="AC38" s="156"/>
-      <c r="AD38" s="156"/>
-      <c r="AE38" s="156"/>
-      <c r="AF38" s="156"/>
-      <c r="AG38" s="156"/>
-      <c r="AH38" s="156"/>
-      <c r="AI38" s="156"/>
-      <c r="AJ38" s="157"/>
+      <c r="A38" s="149"/>
+      <c r="B38" s="159"/>
+      <c r="C38" s="159"/>
+      <c r="D38" s="159"/>
+      <c r="E38" s="159"/>
+      <c r="F38" s="159"/>
+      <c r="G38" s="159"/>
+      <c r="H38" s="159"/>
+      <c r="I38" s="159"/>
+      <c r="J38" s="159"/>
+      <c r="K38" s="159"/>
+      <c r="L38" s="159"/>
+      <c r="M38" s="159"/>
+      <c r="N38" s="159"/>
+      <c r="O38" s="159"/>
+      <c r="P38" s="159"/>
+      <c r="Q38" s="159"/>
+      <c r="R38" s="159"/>
+      <c r="S38" s="159"/>
+      <c r="T38" s="159"/>
+      <c r="U38" s="159"/>
+      <c r="V38" s="159"/>
+      <c r="W38" s="159"/>
+      <c r="X38" s="159"/>
+      <c r="Y38" s="159"/>
+      <c r="Z38" s="159"/>
+      <c r="AA38" s="159"/>
+      <c r="AB38" s="159"/>
+      <c r="AC38" s="159"/>
+      <c r="AD38" s="159"/>
+      <c r="AE38" s="159"/>
+      <c r="AF38" s="159"/>
+      <c r="AG38" s="159"/>
+      <c r="AH38" s="159"/>
+      <c r="AI38" s="159"/>
+      <c r="AJ38" s="160"/>
     </row>
     <row r="39" spans="1:36" ht="27.6" customHeight="1">
-      <c r="A39" s="146"/>
-      <c r="B39" s="156"/>
-      <c r="C39" s="156"/>
-      <c r="D39" s="156"/>
-      <c r="E39" s="156"/>
-      <c r="F39" s="156"/>
-      <c r="G39" s="156"/>
-      <c r="H39" s="156"/>
-      <c r="I39" s="156"/>
-      <c r="J39" s="156"/>
-      <c r="K39" s="156"/>
-      <c r="L39" s="156"/>
-      <c r="M39" s="156"/>
-      <c r="N39" s="156"/>
-      <c r="O39" s="156"/>
-      <c r="P39" s="156"/>
-      <c r="Q39" s="156"/>
-      <c r="R39" s="156"/>
-      <c r="S39" s="156"/>
-      <c r="T39" s="156"/>
-      <c r="U39" s="156"/>
-      <c r="V39" s="156"/>
-      <c r="W39" s="156"/>
-      <c r="X39" s="156"/>
-      <c r="Y39" s="156"/>
-      <c r="Z39" s="156"/>
-      <c r="AA39" s="156"/>
-      <c r="AB39" s="156"/>
-      <c r="AC39" s="156"/>
-      <c r="AD39" s="156"/>
-      <c r="AE39" s="156"/>
-      <c r="AF39" s="156"/>
-      <c r="AG39" s="156"/>
-      <c r="AH39" s="156"/>
-      <c r="AI39" s="156"/>
-      <c r="AJ39" s="157"/>
+      <c r="A39" s="149"/>
+      <c r="B39" s="159"/>
+      <c r="C39" s="159"/>
+      <c r="D39" s="159"/>
+      <c r="E39" s="159"/>
+      <c r="F39" s="159"/>
+      <c r="G39" s="159"/>
+      <c r="H39" s="159"/>
+      <c r="I39" s="159"/>
+      <c r="J39" s="159"/>
+      <c r="K39" s="159"/>
+      <c r="L39" s="159"/>
+      <c r="M39" s="159"/>
+      <c r="N39" s="159"/>
+      <c r="O39" s="159"/>
+      <c r="P39" s="159"/>
+      <c r="Q39" s="159"/>
+      <c r="R39" s="159"/>
+      <c r="S39" s="159"/>
+      <c r="T39" s="159"/>
+      <c r="U39" s="159"/>
+      <c r="V39" s="159"/>
+      <c r="W39" s="159"/>
+      <c r="X39" s="159"/>
+      <c r="Y39" s="159"/>
+      <c r="Z39" s="159"/>
+      <c r="AA39" s="159"/>
+      <c r="AB39" s="159"/>
+      <c r="AC39" s="159"/>
+      <c r="AD39" s="159"/>
+      <c r="AE39" s="159"/>
+      <c r="AF39" s="159"/>
+      <c r="AG39" s="159"/>
+      <c r="AH39" s="159"/>
+      <c r="AI39" s="159"/>
+      <c r="AJ39" s="160"/>
     </row>
     <row r="40" spans="1:36" ht="16.8" customHeight="1">
-      <c r="A40" s="146"/>
-      <c r="B40" s="156"/>
-      <c r="C40" s="156"/>
-      <c r="D40" s="156"/>
-      <c r="E40" s="156"/>
-      <c r="F40" s="156"/>
-      <c r="G40" s="156"/>
-      <c r="H40" s="156"/>
-      <c r="I40" s="156"/>
-      <c r="J40" s="156"/>
-      <c r="K40" s="156"/>
-      <c r="L40" s="156"/>
-      <c r="M40" s="156"/>
-      <c r="N40" s="156"/>
-      <c r="O40" s="156"/>
-      <c r="P40" s="156"/>
-      <c r="Q40" s="156"/>
-      <c r="R40" s="156"/>
-      <c r="S40" s="156"/>
-      <c r="T40" s="156"/>
-      <c r="U40" s="156"/>
-      <c r="V40" s="156"/>
-      <c r="W40" s="156"/>
-      <c r="X40" s="156"/>
-      <c r="Y40" s="156"/>
-      <c r="Z40" s="156"/>
-      <c r="AA40" s="156"/>
-      <c r="AB40" s="156"/>
-      <c r="AC40" s="156"/>
-      <c r="AD40" s="156"/>
-      <c r="AE40" s="156"/>
-      <c r="AF40" s="156"/>
-      <c r="AG40" s="156"/>
-      <c r="AH40" s="156"/>
-      <c r="AI40" s="156"/>
-      <c r="AJ40" s="157"/>
+      <c r="A40" s="149"/>
+      <c r="B40" s="159"/>
+      <c r="C40" s="159"/>
+      <c r="D40" s="159"/>
+      <c r="E40" s="159"/>
+      <c r="F40" s="159"/>
+      <c r="G40" s="159"/>
+      <c r="H40" s="159"/>
+      <c r="I40" s="159"/>
+      <c r="J40" s="159"/>
+      <c r="K40" s="159"/>
+      <c r="L40" s="159"/>
+      <c r="M40" s="159"/>
+      <c r="N40" s="159"/>
+      <c r="O40" s="159"/>
+      <c r="P40" s="159"/>
+      <c r="Q40" s="159"/>
+      <c r="R40" s="159"/>
+      <c r="S40" s="159"/>
+      <c r="T40" s="159"/>
+      <c r="U40" s="159"/>
+      <c r="V40" s="159"/>
+      <c r="W40" s="159"/>
+      <c r="X40" s="159"/>
+      <c r="Y40" s="159"/>
+      <c r="Z40" s="159"/>
+      <c r="AA40" s="159"/>
+      <c r="AB40" s="159"/>
+      <c r="AC40" s="159"/>
+      <c r="AD40" s="159"/>
+      <c r="AE40" s="159"/>
+      <c r="AF40" s="159"/>
+      <c r="AG40" s="159"/>
+      <c r="AH40" s="159"/>
+      <c r="AI40" s="159"/>
+      <c r="AJ40" s="160"/>
     </row>
     <row r="41" spans="1:36" ht="16.8" customHeight="1">
-      <c r="A41" s="62" t="s">
-        <v>100</v>
+      <c r="A41" s="82" t="s">
+        <v>99</v>
       </c>
-      <c r="B41" s="63"/>
-      <c r="C41" s="63"/>
-      <c r="D41" s="63"/>
-      <c r="E41" s="63"/>
-      <c r="F41" s="63"/>
-      <c r="G41" s="63"/>
-      <c r="H41" s="63"/>
-      <c r="I41" s="63"/>
-      <c r="J41" s="63"/>
-      <c r="K41" s="63"/>
-      <c r="L41" s="63"/>
-      <c r="M41" s="63"/>
-      <c r="N41" s="63"/>
-      <c r="O41" s="63"/>
-      <c r="P41" s="63"/>
-      <c r="Q41" s="63"/>
-      <c r="R41" s="63"/>
+      <c r="B41" s="83"/>
+      <c r="C41" s="83"/>
+      <c r="D41" s="83"/>
+      <c r="E41" s="83"/>
+      <c r="F41" s="83"/>
+      <c r="G41" s="83"/>
+      <c r="H41" s="83"/>
+      <c r="I41" s="83"/>
+      <c r="J41" s="83"/>
+      <c r="K41" s="83"/>
+      <c r="L41" s="83"/>
+      <c r="M41" s="83"/>
+      <c r="N41" s="83"/>
+      <c r="O41" s="83"/>
+      <c r="P41" s="83"/>
+      <c r="Q41" s="83"/>
+      <c r="R41" s="83"/>
       <c r="S41" s="40"/>
       <c r="T41" s="40"/>
       <c r="U41" s="40"/>
@@ -8628,713 +8626,713 @@
       <c r="AJ41" s="43"/>
     </row>
     <row r="42" spans="1:36" ht="16.8" customHeight="1">
-      <c r="A42" s="161"/>
-      <c r="B42" s="162"/>
-      <c r="C42" s="162"/>
-      <c r="D42" s="162"/>
-      <c r="E42" s="162"/>
-      <c r="F42" s="162"/>
-      <c r="G42" s="162"/>
-      <c r="H42" s="162"/>
-      <c r="I42" s="162"/>
-      <c r="J42" s="162"/>
-      <c r="K42" s="162"/>
-      <c r="L42" s="162"/>
-      <c r="M42" s="162"/>
-      <c r="N42" s="162"/>
-      <c r="O42" s="162"/>
-      <c r="P42" s="162"/>
-      <c r="Q42" s="162"/>
-      <c r="R42" s="162"/>
-      <c r="S42" s="162"/>
-      <c r="T42" s="162"/>
-      <c r="U42" s="162"/>
-      <c r="V42" s="162"/>
-      <c r="W42" s="162"/>
-      <c r="X42" s="162"/>
-      <c r="Y42" s="162"/>
-      <c r="Z42" s="162"/>
-      <c r="AA42" s="162"/>
-      <c r="AB42" s="162"/>
-      <c r="AC42" s="162"/>
-      <c r="AD42" s="162"/>
-      <c r="AE42" s="162"/>
-      <c r="AF42" s="162"/>
-      <c r="AG42" s="162"/>
-      <c r="AH42" s="162"/>
-      <c r="AI42" s="162"/>
-      <c r="AJ42" s="163"/>
+      <c r="A42" s="53"/>
+      <c r="B42" s="54"/>
+      <c r="C42" s="54"/>
+      <c r="D42" s="54"/>
+      <c r="E42" s="54"/>
+      <c r="F42" s="54"/>
+      <c r="G42" s="54"/>
+      <c r="H42" s="54"/>
+      <c r="I42" s="54"/>
+      <c r="J42" s="54"/>
+      <c r="K42" s="54"/>
+      <c r="L42" s="54"/>
+      <c r="M42" s="54"/>
+      <c r="N42" s="54"/>
+      <c r="O42" s="54"/>
+      <c r="P42" s="54"/>
+      <c r="Q42" s="54"/>
+      <c r="R42" s="54"/>
+      <c r="S42" s="54"/>
+      <c r="T42" s="54"/>
+      <c r="U42" s="54"/>
+      <c r="V42" s="54"/>
+      <c r="W42" s="54"/>
+      <c r="X42" s="54"/>
+      <c r="Y42" s="54"/>
+      <c r="Z42" s="54"/>
+      <c r="AA42" s="54"/>
+      <c r="AB42" s="54"/>
+      <c r="AC42" s="54"/>
+      <c r="AD42" s="54"/>
+      <c r="AE42" s="54"/>
+      <c r="AF42" s="54"/>
+      <c r="AG42" s="54"/>
+      <c r="AH42" s="54"/>
+      <c r="AI42" s="54"/>
+      <c r="AJ42" s="55"/>
     </row>
     <row r="43" spans="1:36" ht="17.25" customHeight="1">
-      <c r="A43" s="104" t="s">
+      <c r="A43" s="107" t="s">
         <v>18</v>
       </c>
-      <c r="B43" s="105"/>
-      <c r="C43" s="105"/>
-      <c r="D43" s="105"/>
-      <c r="E43" s="105"/>
-      <c r="F43" s="105"/>
-      <c r="G43" s="105"/>
-      <c r="H43" s="105"/>
-      <c r="I43" s="106"/>
-      <c r="J43" s="104" t="s">
+      <c r="B43" s="108"/>
+      <c r="C43" s="108"/>
+      <c r="D43" s="108"/>
+      <c r="E43" s="108"/>
+      <c r="F43" s="108"/>
+      <c r="G43" s="108"/>
+      <c r="H43" s="108"/>
+      <c r="I43" s="109"/>
+      <c r="J43" s="107" t="s">
         <v>19</v>
       </c>
-      <c r="K43" s="105"/>
-      <c r="L43" s="105"/>
-      <c r="M43" s="105"/>
-      <c r="N43" s="105"/>
-      <c r="O43" s="105"/>
-      <c r="P43" s="105"/>
-      <c r="Q43" s="105"/>
-      <c r="R43" s="106"/>
-      <c r="S43" s="104" t="s">
+      <c r="K43" s="108"/>
+      <c r="L43" s="108"/>
+      <c r="M43" s="108"/>
+      <c r="N43" s="108"/>
+      <c r="O43" s="108"/>
+      <c r="P43" s="108"/>
+      <c r="Q43" s="108"/>
+      <c r="R43" s="109"/>
+      <c r="S43" s="107" t="s">
         <v>77</v>
       </c>
-      <c r="T43" s="105"/>
-      <c r="U43" s="105"/>
-      <c r="V43" s="105"/>
-      <c r="W43" s="105"/>
-      <c r="X43" s="105"/>
-      <c r="Y43" s="105"/>
-      <c r="Z43" s="105"/>
-      <c r="AA43" s="106"/>
-      <c r="AB43" s="155" t="s">
+      <c r="T43" s="108"/>
+      <c r="U43" s="108"/>
+      <c r="V43" s="108"/>
+      <c r="W43" s="108"/>
+      <c r="X43" s="108"/>
+      <c r="Y43" s="108"/>
+      <c r="Z43" s="108"/>
+      <c r="AA43" s="109"/>
+      <c r="AB43" s="158" t="s">
         <v>91</v>
       </c>
-      <c r="AC43" s="105"/>
-      <c r="AD43" s="105"/>
-      <c r="AE43" s="105"/>
-      <c r="AF43" s="105"/>
-      <c r="AG43" s="105"/>
-      <c r="AH43" s="105"/>
-      <c r="AI43" s="105"/>
-      <c r="AJ43" s="106"/>
+      <c r="AC43" s="108"/>
+      <c r="AD43" s="108"/>
+      <c r="AE43" s="108"/>
+      <c r="AF43" s="108"/>
+      <c r="AG43" s="108"/>
+      <c r="AH43" s="108"/>
+      <c r="AI43" s="108"/>
+      <c r="AJ43" s="109"/>
     </row>
     <row r="44" spans="1:36" ht="18" customHeight="1">
       <c r="A44" s="2"/>
-      <c r="B44" s="119" t="s">
+      <c r="B44" s="122" t="s">
         <v>21</v>
       </c>
-      <c r="C44" s="119"/>
-      <c r="D44" s="119"/>
-      <c r="E44" s="119"/>
-      <c r="F44" s="119"/>
-      <c r="G44" s="119"/>
-      <c r="H44" s="119"/>
-      <c r="I44" s="120"/>
+      <c r="C44" s="122"/>
+      <c r="D44" s="122"/>
+      <c r="E44" s="122"/>
+      <c r="F44" s="122"/>
+      <c r="G44" s="122"/>
+      <c r="H44" s="122"/>
+      <c r="I44" s="123"/>
       <c r="J44" s="10"/>
-      <c r="K44" s="119" t="s">
+      <c r="K44" s="122" t="s">
         <v>22</v>
       </c>
-      <c r="L44" s="119"/>
-      <c r="M44" s="119"/>
-      <c r="N44" s="119"/>
-      <c r="O44" s="119"/>
-      <c r="P44" s="119"/>
-      <c r="Q44" s="119"/>
-      <c r="R44" s="120"/>
-      <c r="S44" s="86" t="s">
+      <c r="L44" s="122"/>
+      <c r="M44" s="122"/>
+      <c r="N44" s="122"/>
+      <c r="O44" s="122"/>
+      <c r="P44" s="122"/>
+      <c r="Q44" s="122"/>
+      <c r="R44" s="123"/>
+      <c r="S44" s="89" t="s">
         <v>81</v>
       </c>
-      <c r="T44" s="84"/>
-      <c r="U44" s="84"/>
-      <c r="V44" s="84"/>
-      <c r="W44" s="75"/>
-      <c r="X44" s="75"/>
-      <c r="Y44" s="75"/>
+      <c r="T44" s="87"/>
+      <c r="U44" s="87"/>
+      <c r="V44" s="87"/>
+      <c r="W44" s="68"/>
+      <c r="X44" s="68"/>
+      <c r="Y44" s="68"/>
       <c r="Z44" s="49"/>
       <c r="AA44" s="4"/>
-      <c r="AB44" s="121" t="s">
+      <c r="AB44" s="124" t="s">
         <v>82</v>
       </c>
-      <c r="AC44" s="78"/>
-      <c r="AD44" s="78"/>
-      <c r="AE44" s="78"/>
-      <c r="AF44" s="126"/>
-      <c r="AG44" s="126"/>
-      <c r="AH44" s="126"/>
-      <c r="AI44" s="126"/>
+      <c r="AC44" s="71"/>
+      <c r="AD44" s="71"/>
+      <c r="AE44" s="71"/>
+      <c r="AF44" s="129"/>
+      <c r="AG44" s="129"/>
+      <c r="AH44" s="129"/>
+      <c r="AI44" s="129"/>
       <c r="AJ44" s="4"/>
     </row>
     <row r="45" spans="1:36" ht="18" customHeight="1">
       <c r="A45" s="2"/>
-      <c r="B45" s="119" t="s">
+      <c r="B45" s="122" t="s">
         <v>24</v>
       </c>
-      <c r="C45" s="119"/>
-      <c r="D45" s="119"/>
-      <c r="E45" s="119"/>
-      <c r="F45" s="119"/>
-      <c r="G45" s="119"/>
-      <c r="H45" s="119"/>
-      <c r="I45" s="120"/>
+      <c r="C45" s="122"/>
+      <c r="D45" s="122"/>
+      <c r="E45" s="122"/>
+      <c r="F45" s="122"/>
+      <c r="G45" s="122"/>
+      <c r="H45" s="122"/>
+      <c r="I45" s="123"/>
       <c r="J45" s="10"/>
-      <c r="K45" s="119" t="s">
+      <c r="K45" s="122" t="s">
         <v>25</v>
       </c>
-      <c r="L45" s="119"/>
-      <c r="M45" s="119"/>
-      <c r="N45" s="119"/>
-      <c r="O45" s="119"/>
-      <c r="P45" s="119"/>
-      <c r="Q45" s="119"/>
-      <c r="R45" s="120"/>
-      <c r="S45" s="86" t="s">
+      <c r="L45" s="122"/>
+      <c r="M45" s="122"/>
+      <c r="N45" s="122"/>
+      <c r="O45" s="122"/>
+      <c r="P45" s="122"/>
+      <c r="Q45" s="122"/>
+      <c r="R45" s="123"/>
+      <c r="S45" s="89" t="s">
         <v>80</v>
       </c>
-      <c r="T45" s="84"/>
-      <c r="U45" s="84"/>
-      <c r="V45" s="84"/>
-      <c r="W45" s="145"/>
-      <c r="X45" s="145"/>
-      <c r="Y45" s="145"/>
-      <c r="Z45" s="145"/>
+      <c r="T45" s="87"/>
+      <c r="U45" s="87"/>
+      <c r="V45" s="87"/>
+      <c r="W45" s="148"/>
+      <c r="X45" s="148"/>
+      <c r="Y45" s="148"/>
+      <c r="Z45" s="148"/>
       <c r="AA45" s="4"/>
-      <c r="AB45" s="86" t="s">
+      <c r="AB45" s="89" t="s">
         <v>81</v>
       </c>
-      <c r="AC45" s="84"/>
-      <c r="AD45" s="84"/>
-      <c r="AE45" s="84"/>
-      <c r="AF45" s="145"/>
-      <c r="AG45" s="145"/>
-      <c r="AH45" s="145"/>
-      <c r="AI45" s="145"/>
+      <c r="AC45" s="87"/>
+      <c r="AD45" s="87"/>
+      <c r="AE45" s="87"/>
+      <c r="AF45" s="148"/>
+      <c r="AG45" s="148"/>
+      <c r="AH45" s="148"/>
+      <c r="AI45" s="148"/>
       <c r="AJ45" s="4"/>
     </row>
     <row r="46" spans="1:36" ht="18" customHeight="1">
       <c r="A46" s="2"/>
-      <c r="B46" s="119" t="s">
+      <c r="B46" s="122" t="s">
         <v>27</v>
       </c>
-      <c r="C46" s="119"/>
-      <c r="D46" s="119"/>
-      <c r="E46" s="119"/>
-      <c r="F46" s="119"/>
-      <c r="G46" s="119"/>
-      <c r="H46" s="119"/>
-      <c r="I46" s="120"/>
+      <c r="C46" s="122"/>
+      <c r="D46" s="122"/>
+      <c r="E46" s="122"/>
+      <c r="F46" s="122"/>
+      <c r="G46" s="122"/>
+      <c r="H46" s="122"/>
+      <c r="I46" s="123"/>
       <c r="J46" s="10"/>
-      <c r="K46" s="119" t="s">
+      <c r="K46" s="122" t="s">
         <v>28</v>
       </c>
-      <c r="L46" s="119"/>
-      <c r="M46" s="119"/>
-      <c r="N46" s="119"/>
-      <c r="O46" s="119"/>
-      <c r="P46" s="119"/>
-      <c r="Q46" s="119"/>
-      <c r="R46" s="120"/>
-      <c r="S46" s="121" t="s">
+      <c r="L46" s="122"/>
+      <c r="M46" s="122"/>
+      <c r="N46" s="122"/>
+      <c r="O46" s="122"/>
+      <c r="P46" s="122"/>
+      <c r="Q46" s="122"/>
+      <c r="R46" s="123"/>
+      <c r="S46" s="124" t="s">
         <v>78</v>
       </c>
-      <c r="T46" s="78"/>
-      <c r="U46" s="78"/>
-      <c r="V46" s="78"/>
-      <c r="W46" s="78"/>
-      <c r="X46" s="122"/>
-      <c r="Y46" s="122"/>
-      <c r="Z46" s="122"/>
+      <c r="T46" s="71"/>
+      <c r="U46" s="71"/>
+      <c r="V46" s="71"/>
+      <c r="W46" s="71"/>
+      <c r="X46" s="125"/>
+      <c r="Y46" s="125"/>
+      <c r="Z46" s="125"/>
       <c r="AA46" s="12" t="s">
         <v>30</v>
       </c>
-      <c r="AB46" s="86" t="s">
+      <c r="AB46" s="89" t="s">
         <v>80</v>
       </c>
-      <c r="AC46" s="84"/>
-      <c r="AD46" s="84"/>
-      <c r="AE46" s="84"/>
-      <c r="AF46" s="145"/>
-      <c r="AG46" s="145"/>
-      <c r="AH46" s="145"/>
-      <c r="AI46" s="145"/>
+      <c r="AC46" s="87"/>
+      <c r="AD46" s="87"/>
+      <c r="AE46" s="87"/>
+      <c r="AF46" s="148"/>
+      <c r="AG46" s="148"/>
+      <c r="AH46" s="148"/>
+      <c r="AI46" s="148"/>
       <c r="AJ46" s="4"/>
     </row>
     <row r="47" spans="1:36" ht="18" customHeight="1">
       <c r="A47" s="2"/>
-      <c r="B47" s="119" t="s">
+      <c r="B47" s="122" t="s">
         <v>87</v>
       </c>
-      <c r="C47" s="119"/>
-      <c r="D47" s="119"/>
-      <c r="E47" s="119"/>
-      <c r="F47" s="119"/>
-      <c r="G47" s="119"/>
-      <c r="H47" s="119"/>
-      <c r="I47" s="120"/>
+      <c r="C47" s="122"/>
+      <c r="D47" s="122"/>
+      <c r="E47" s="122"/>
+      <c r="F47" s="122"/>
+      <c r="G47" s="122"/>
+      <c r="H47" s="122"/>
+      <c r="I47" s="123"/>
       <c r="J47" s="10"/>
-      <c r="K47" s="119" t="s">
+      <c r="K47" s="122" t="s">
         <v>31</v>
       </c>
-      <c r="L47" s="119"/>
-      <c r="M47" s="119"/>
-      <c r="N47" s="119"/>
-      <c r="O47" s="119"/>
-      <c r="P47" s="119"/>
-      <c r="Q47" s="119"/>
-      <c r="R47" s="120"/>
-      <c r="S47" s="123" t="s">
+      <c r="L47" s="122"/>
+      <c r="M47" s="122"/>
+      <c r="N47" s="122"/>
+      <c r="O47" s="122"/>
+      <c r="P47" s="122"/>
+      <c r="Q47" s="122"/>
+      <c r="R47" s="123"/>
+      <c r="S47" s="126" t="s">
         <v>79</v>
       </c>
-      <c r="T47" s="124"/>
-      <c r="U47" s="124"/>
-      <c r="V47" s="124"/>
-      <c r="W47" s="124"/>
-      <c r="X47" s="140"/>
-      <c r="Y47" s="140"/>
-      <c r="Z47" s="140"/>
+      <c r="T47" s="127"/>
+      <c r="U47" s="127"/>
+      <c r="V47" s="127"/>
+      <c r="W47" s="127"/>
+      <c r="X47" s="143"/>
+      <c r="Y47" s="143"/>
+      <c r="Z47" s="143"/>
       <c r="AA47" s="33" t="s">
         <v>30</v>
       </c>
-      <c r="AB47" s="86" t="s">
+      <c r="AB47" s="89" t="s">
         <v>83</v>
       </c>
-      <c r="AC47" s="84"/>
-      <c r="AD47" s="84"/>
-      <c r="AE47" s="84"/>
-      <c r="AF47" s="126"/>
-      <c r="AG47" s="126"/>
-      <c r="AH47" s="126"/>
-      <c r="AI47" s="126"/>
+      <c r="AC47" s="87"/>
+      <c r="AD47" s="87"/>
+      <c r="AE47" s="87"/>
+      <c r="AF47" s="129"/>
+      <c r="AG47" s="129"/>
+      <c r="AH47" s="129"/>
+      <c r="AI47" s="129"/>
       <c r="AJ47" s="4"/>
     </row>
     <row r="48" spans="1:36" ht="18" customHeight="1">
       <c r="A48" s="34"/>
-      <c r="B48" s="119" t="s">
+      <c r="B48" s="122" t="s">
         <v>33</v>
       </c>
-      <c r="C48" s="119"/>
-      <c r="D48" s="119"/>
-      <c r="E48" s="119"/>
-      <c r="F48" s="119"/>
-      <c r="G48" s="119"/>
-      <c r="H48" s="119"/>
-      <c r="I48" s="120"/>
+      <c r="C48" s="122"/>
+      <c r="D48" s="122"/>
+      <c r="E48" s="122"/>
+      <c r="F48" s="122"/>
+      <c r="G48" s="122"/>
+      <c r="H48" s="122"/>
+      <c r="I48" s="123"/>
       <c r="J48" s="10"/>
-      <c r="K48" s="119" t="s">
+      <c r="K48" s="122" t="s">
         <v>34</v>
       </c>
-      <c r="L48" s="119"/>
-      <c r="M48" s="119"/>
-      <c r="N48" s="119"/>
-      <c r="O48" s="119"/>
-      <c r="P48" s="119"/>
-      <c r="Q48" s="119"/>
-      <c r="R48" s="120"/>
-      <c r="S48" s="136" t="s">
+      <c r="L48" s="122"/>
+      <c r="M48" s="122"/>
+      <c r="N48" s="122"/>
+      <c r="O48" s="122"/>
+      <c r="P48" s="122"/>
+      <c r="Q48" s="122"/>
+      <c r="R48" s="123"/>
+      <c r="S48" s="139" t="s">
         <v>20</v>
       </c>
-      <c r="T48" s="137"/>
-      <c r="U48" s="137"/>
-      <c r="V48" s="137"/>
-      <c r="W48" s="137"/>
-      <c r="X48" s="137"/>
-      <c r="Y48" s="137"/>
-      <c r="Z48" s="137"/>
-      <c r="AA48" s="138"/>
-      <c r="AB48" s="121" t="s">
+      <c r="T48" s="140"/>
+      <c r="U48" s="140"/>
+      <c r="V48" s="140"/>
+      <c r="W48" s="140"/>
+      <c r="X48" s="140"/>
+      <c r="Y48" s="140"/>
+      <c r="Z48" s="140"/>
+      <c r="AA48" s="141"/>
+      <c r="AB48" s="124" t="s">
         <v>78</v>
       </c>
-      <c r="AC48" s="78"/>
-      <c r="AD48" s="78"/>
-      <c r="AE48" s="78"/>
-      <c r="AF48" s="78"/>
-      <c r="AG48" s="122"/>
-      <c r="AH48" s="122"/>
-      <c r="AI48" s="122"/>
+      <c r="AC48" s="71"/>
+      <c r="AD48" s="71"/>
+      <c r="AE48" s="71"/>
+      <c r="AF48" s="71"/>
+      <c r="AG48" s="125"/>
+      <c r="AH48" s="125"/>
+      <c r="AI48" s="125"/>
       <c r="AJ48" s="12" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="49" spans="1:36" ht="18" customHeight="1">
       <c r="A49" s="10"/>
-      <c r="B49" s="119" t="s">
+      <c r="B49" s="122" t="s">
         <v>74</v>
       </c>
-      <c r="C49" s="119"/>
-      <c r="D49" s="119"/>
-      <c r="E49" s="119"/>
-      <c r="F49" s="119"/>
-      <c r="G49" s="119"/>
-      <c r="H49" s="119"/>
-      <c r="I49" s="120"/>
+      <c r="C49" s="122"/>
+      <c r="D49" s="122"/>
+      <c r="E49" s="122"/>
+      <c r="F49" s="122"/>
+      <c r="G49" s="122"/>
+      <c r="H49" s="122"/>
+      <c r="I49" s="123"/>
       <c r="J49" s="10"/>
-      <c r="K49" s="119" t="s">
+      <c r="K49" s="122" t="s">
         <v>37</v>
       </c>
-      <c r="L49" s="119"/>
-      <c r="M49" s="119"/>
-      <c r="N49" s="119"/>
-      <c r="O49" s="119"/>
-      <c r="P49" s="119"/>
-      <c r="Q49" s="119"/>
-      <c r="R49" s="120"/>
+      <c r="L49" s="122"/>
+      <c r="M49" s="122"/>
+      <c r="N49" s="122"/>
+      <c r="O49" s="122"/>
+      <c r="P49" s="122"/>
+      <c r="Q49" s="122"/>
+      <c r="R49" s="123"/>
       <c r="S49" s="10"/>
-      <c r="T49" s="119" t="s">
+      <c r="T49" s="122" t="s">
         <v>23</v>
       </c>
-      <c r="U49" s="119"/>
-      <c r="V49" s="119"/>
-      <c r="W49" s="119"/>
-      <c r="X49" s="119"/>
-      <c r="Y49" s="119"/>
-      <c r="Z49" s="119"/>
-      <c r="AA49" s="120"/>
-      <c r="AB49" s="123" t="s">
+      <c r="U49" s="122"/>
+      <c r="V49" s="122"/>
+      <c r="W49" s="122"/>
+      <c r="X49" s="122"/>
+      <c r="Y49" s="122"/>
+      <c r="Z49" s="122"/>
+      <c r="AA49" s="123"/>
+      <c r="AB49" s="126" t="s">
         <v>79</v>
       </c>
-      <c r="AC49" s="124"/>
-      <c r="AD49" s="124"/>
-      <c r="AE49" s="124"/>
-      <c r="AF49" s="124"/>
-      <c r="AG49" s="140"/>
-      <c r="AH49" s="140"/>
-      <c r="AI49" s="140"/>
+      <c r="AC49" s="127"/>
+      <c r="AD49" s="127"/>
+      <c r="AE49" s="127"/>
+      <c r="AF49" s="127"/>
+      <c r="AG49" s="143"/>
+      <c r="AH49" s="143"/>
+      <c r="AI49" s="143"/>
       <c r="AJ49" s="33" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="50" spans="1:36" ht="18" customHeight="1">
       <c r="A50" s="10"/>
-      <c r="B50" s="119" t="s">
+      <c r="B50" s="122" t="s">
         <v>75</v>
       </c>
-      <c r="C50" s="119"/>
-      <c r="D50" s="119"/>
-      <c r="E50" s="119"/>
-      <c r="F50" s="119"/>
-      <c r="G50" s="119"/>
-      <c r="H50" s="119"/>
-      <c r="I50" s="120"/>
+      <c r="C50" s="122"/>
+      <c r="D50" s="122"/>
+      <c r="E50" s="122"/>
+      <c r="F50" s="122"/>
+      <c r="G50" s="122"/>
+      <c r="H50" s="122"/>
+      <c r="I50" s="123"/>
       <c r="J50" s="10"/>
-      <c r="K50" s="119" t="s">
+      <c r="K50" s="122" t="s">
         <v>39</v>
       </c>
-      <c r="L50" s="119"/>
-      <c r="M50" s="119"/>
-      <c r="N50" s="119"/>
-      <c r="O50" s="119"/>
-      <c r="P50" s="119"/>
-      <c r="Q50" s="119"/>
-      <c r="R50" s="120"/>
+      <c r="L50" s="122"/>
+      <c r="M50" s="122"/>
+      <c r="N50" s="122"/>
+      <c r="O50" s="122"/>
+      <c r="P50" s="122"/>
+      <c r="Q50" s="122"/>
+      <c r="R50" s="123"/>
       <c r="S50" s="10"/>
-      <c r="T50" s="119" t="s">
+      <c r="T50" s="122" t="s">
         <v>26</v>
       </c>
-      <c r="U50" s="119"/>
-      <c r="V50" s="119"/>
-      <c r="W50" s="119"/>
-      <c r="X50" s="119"/>
-      <c r="Y50" s="119"/>
-      <c r="Z50" s="119"/>
-      <c r="AA50" s="120"/>
-      <c r="AB50" s="127" t="s">
+      <c r="U50" s="122"/>
+      <c r="V50" s="122"/>
+      <c r="W50" s="122"/>
+      <c r="X50" s="122"/>
+      <c r="Y50" s="122"/>
+      <c r="Z50" s="122"/>
+      <c r="AA50" s="123"/>
+      <c r="AB50" s="130" t="s">
         <v>38</v>
       </c>
-      <c r="AC50" s="128"/>
-      <c r="AD50" s="128"/>
-      <c r="AE50" s="128"/>
-      <c r="AF50" s="128"/>
-      <c r="AG50" s="128"/>
-      <c r="AH50" s="128"/>
-      <c r="AI50" s="128"/>
-      <c r="AJ50" s="129"/>
+      <c r="AC50" s="131"/>
+      <c r="AD50" s="131"/>
+      <c r="AE50" s="131"/>
+      <c r="AF50" s="131"/>
+      <c r="AG50" s="131"/>
+      <c r="AH50" s="131"/>
+      <c r="AI50" s="131"/>
+      <c r="AJ50" s="132"/>
     </row>
     <row r="51" spans="1:36" ht="18" customHeight="1">
       <c r="A51" s="10"/>
-      <c r="B51" s="119" t="s">
+      <c r="B51" s="122" t="s">
         <v>40</v>
       </c>
-      <c r="C51" s="119"/>
-      <c r="D51" s="119"/>
-      <c r="E51" s="119"/>
-      <c r="F51" s="119"/>
-      <c r="G51" s="119"/>
-      <c r="H51" s="119"/>
-      <c r="I51" s="120"/>
+      <c r="C51" s="122"/>
+      <c r="D51" s="122"/>
+      <c r="E51" s="122"/>
+      <c r="F51" s="122"/>
+      <c r="G51" s="122"/>
+      <c r="H51" s="122"/>
+      <c r="I51" s="123"/>
       <c r="J51" s="10"/>
-      <c r="K51" s="119" t="s">
+      <c r="K51" s="122" t="s">
         <v>41</v>
       </c>
-      <c r="L51" s="119"/>
-      <c r="M51" s="119"/>
-      <c r="N51" s="119"/>
-      <c r="O51" s="119"/>
-      <c r="P51" s="119"/>
-      <c r="Q51" s="119"/>
-      <c r="R51" s="120"/>
+      <c r="L51" s="122"/>
+      <c r="M51" s="122"/>
+      <c r="N51" s="122"/>
+      <c r="O51" s="122"/>
+      <c r="P51" s="122"/>
+      <c r="Q51" s="122"/>
+      <c r="R51" s="123"/>
       <c r="S51" s="10"/>
-      <c r="T51" s="119" t="s">
+      <c r="T51" s="122" t="s">
         <v>29</v>
       </c>
-      <c r="U51" s="119"/>
-      <c r="V51" s="119"/>
-      <c r="W51" s="122"/>
-      <c r="X51" s="122"/>
-      <c r="Y51" s="122"/>
+      <c r="U51" s="122"/>
+      <c r="V51" s="122"/>
+      <c r="W51" s="125"/>
+      <c r="X51" s="125"/>
+      <c r="Y51" s="125"/>
       <c r="Z51" s="3" t="s">
         <v>30</v>
       </c>
       <c r="AA51" s="4"/>
       <c r="AB51" s="10"/>
-      <c r="AC51" s="130" t="s">
+      <c r="AC51" s="133" t="s">
         <v>76</v>
       </c>
-      <c r="AD51" s="130"/>
-      <c r="AE51" s="130"/>
-      <c r="AF51" s="130"/>
-      <c r="AG51" s="130"/>
-      <c r="AH51" s="130"/>
-      <c r="AI51" s="130"/>
-      <c r="AJ51" s="131"/>
+      <c r="AD51" s="133"/>
+      <c r="AE51" s="133"/>
+      <c r="AF51" s="133"/>
+      <c r="AG51" s="133"/>
+      <c r="AH51" s="133"/>
+      <c r="AI51" s="133"/>
+      <c r="AJ51" s="134"/>
     </row>
     <row r="52" spans="1:36" ht="18" customHeight="1">
       <c r="A52" s="10"/>
-      <c r="B52" s="119" t="s">
+      <c r="B52" s="122" t="s">
         <v>43</v>
       </c>
-      <c r="C52" s="119"/>
-      <c r="D52" s="132"/>
-      <c r="E52" s="132"/>
-      <c r="F52" s="132"/>
-      <c r="G52" s="132"/>
-      <c r="H52" s="132"/>
+      <c r="C52" s="122"/>
+      <c r="D52" s="135"/>
+      <c r="E52" s="135"/>
+      <c r="F52" s="135"/>
+      <c r="G52" s="135"/>
+      <c r="H52" s="135"/>
       <c r="I52" s="4"/>
       <c r="J52" s="10"/>
-      <c r="K52" s="119" t="s">
+      <c r="K52" s="122" t="s">
         <v>44</v>
       </c>
-      <c r="L52" s="119"/>
-      <c r="M52" s="119"/>
-      <c r="N52" s="119"/>
-      <c r="O52" s="119"/>
-      <c r="P52" s="119"/>
-      <c r="Q52" s="119"/>
-      <c r="R52" s="120"/>
+      <c r="L52" s="122"/>
+      <c r="M52" s="122"/>
+      <c r="N52" s="122"/>
+      <c r="O52" s="122"/>
+      <c r="P52" s="122"/>
+      <c r="Q52" s="122"/>
+      <c r="R52" s="123"/>
       <c r="S52" s="10"/>
-      <c r="T52" s="119" t="s">
+      <c r="T52" s="122" t="s">
         <v>32</v>
       </c>
-      <c r="U52" s="119"/>
-      <c r="V52" s="119"/>
-      <c r="W52" s="122"/>
-      <c r="X52" s="122"/>
-      <c r="Y52" s="122"/>
+      <c r="U52" s="122"/>
+      <c r="V52" s="122"/>
+      <c r="W52" s="125"/>
+      <c r="X52" s="125"/>
+      <c r="Y52" s="125"/>
       <c r="Z52" s="3" t="s">
         <v>30</v>
       </c>
       <c r="AA52" s="4"/>
       <c r="AB52" s="10"/>
-      <c r="AC52" s="119" t="s">
+      <c r="AC52" s="122" t="s">
         <v>42</v>
       </c>
-      <c r="AD52" s="119"/>
-      <c r="AE52" s="119"/>
-      <c r="AF52" s="119"/>
-      <c r="AG52" s="119"/>
-      <c r="AH52" s="119"/>
-      <c r="AI52" s="119"/>
-      <c r="AJ52" s="120"/>
+      <c r="AD52" s="122"/>
+      <c r="AE52" s="122"/>
+      <c r="AF52" s="122"/>
+      <c r="AG52" s="122"/>
+      <c r="AH52" s="122"/>
+      <c r="AI52" s="122"/>
+      <c r="AJ52" s="123"/>
     </row>
     <row r="53" spans="1:36" ht="18" customHeight="1">
       <c r="A53" s="13"/>
       <c r="B53" s="7"/>
       <c r="C53" s="7"/>
-      <c r="D53" s="143"/>
-      <c r="E53" s="143"/>
-      <c r="F53" s="143"/>
-      <c r="G53" s="143"/>
-      <c r="H53" s="143"/>
+      <c r="D53" s="146"/>
+      <c r="E53" s="146"/>
+      <c r="F53" s="146"/>
+      <c r="G53" s="146"/>
+      <c r="H53" s="146"/>
       <c r="I53" s="8"/>
-      <c r="J53" s="123"/>
-      <c r="K53" s="124"/>
-      <c r="L53" s="124"/>
-      <c r="M53" s="124"/>
-      <c r="N53" s="124"/>
-      <c r="O53" s="124"/>
-      <c r="P53" s="124"/>
-      <c r="Q53" s="124"/>
-      <c r="R53" s="125"/>
+      <c r="J53" s="126"/>
+      <c r="K53" s="127"/>
+      <c r="L53" s="127"/>
+      <c r="M53" s="127"/>
+      <c r="N53" s="127"/>
+      <c r="O53" s="127"/>
+      <c r="P53" s="127"/>
+      <c r="Q53" s="127"/>
+      <c r="R53" s="128"/>
       <c r="S53" s="13"/>
-      <c r="T53" s="139" t="s">
+      <c r="T53" s="142" t="s">
         <v>35</v>
       </c>
-      <c r="U53" s="139"/>
-      <c r="V53" s="139"/>
-      <c r="W53" s="140"/>
-      <c r="X53" s="140"/>
-      <c r="Y53" s="140"/>
+      <c r="U53" s="142"/>
+      <c r="V53" s="142"/>
+      <c r="W53" s="143"/>
+      <c r="X53" s="143"/>
+      <c r="Y53" s="143"/>
       <c r="Z53" s="6" t="s">
         <v>36</v>
       </c>
       <c r="AA53" s="8"/>
       <c r="AB53" s="13"/>
-      <c r="AC53" s="139" t="s">
+      <c r="AC53" s="142" t="s">
         <v>45</v>
       </c>
-      <c r="AD53" s="139"/>
-      <c r="AE53" s="139"/>
-      <c r="AF53" s="103"/>
-      <c r="AG53" s="103"/>
-      <c r="AH53" s="103"/>
+      <c r="AD53" s="142"/>
+      <c r="AE53" s="142"/>
+      <c r="AF53" s="106"/>
+      <c r="AG53" s="106"/>
+      <c r="AH53" s="106"/>
       <c r="AI53" s="7"/>
       <c r="AJ53" s="8"/>
     </row>
     <row r="54" spans="1:36" ht="18" customHeight="1">
-      <c r="A54" s="141" t="s">
+      <c r="A54" s="144" t="s">
         <v>46</v>
       </c>
-      <c r="B54" s="141"/>
-      <c r="C54" s="141"/>
-      <c r="D54" s="141"/>
-      <c r="E54" s="141"/>
-      <c r="F54" s="141"/>
-      <c r="G54" s="141"/>
-      <c r="H54" s="141"/>
-      <c r="I54" s="141"/>
-      <c r="J54" s="141"/>
-      <c r="K54" s="141"/>
-      <c r="L54" s="141"/>
-      <c r="M54" s="141"/>
-      <c r="N54" s="142"/>
-      <c r="O54" s="142"/>
-      <c r="P54" s="142"/>
-      <c r="Q54" s="142"/>
-      <c r="R54" s="142"/>
-      <c r="S54" s="142"/>
-      <c r="T54" s="142"/>
-      <c r="U54" s="142"/>
-      <c r="V54" s="142"/>
-      <c r="W54" s="142"/>
-      <c r="X54" s="142"/>
-      <c r="Y54" s="142"/>
-      <c r="Z54" s="142"/>
-      <c r="AA54" s="142"/>
-      <c r="AB54" s="142"/>
-      <c r="AC54" s="142"/>
-      <c r="AD54" s="142"/>
-      <c r="AE54" s="142"/>
-      <c r="AF54" s="142"/>
-      <c r="AG54" s="142"/>
-      <c r="AH54" s="142"/>
-      <c r="AI54" s="142"/>
-      <c r="AJ54" s="142"/>
+      <c r="B54" s="144"/>
+      <c r="C54" s="144"/>
+      <c r="D54" s="144"/>
+      <c r="E54" s="144"/>
+      <c r="F54" s="144"/>
+      <c r="G54" s="144"/>
+      <c r="H54" s="144"/>
+      <c r="I54" s="144"/>
+      <c r="J54" s="144"/>
+      <c r="K54" s="144"/>
+      <c r="L54" s="144"/>
+      <c r="M54" s="144"/>
+      <c r="N54" s="145"/>
+      <c r="O54" s="145"/>
+      <c r="P54" s="145"/>
+      <c r="Q54" s="145"/>
+      <c r="R54" s="145"/>
+      <c r="S54" s="145"/>
+      <c r="T54" s="145"/>
+      <c r="U54" s="145"/>
+      <c r="V54" s="145"/>
+      <c r="W54" s="145"/>
+      <c r="X54" s="145"/>
+      <c r="Y54" s="145"/>
+      <c r="Z54" s="145"/>
+      <c r="AA54" s="145"/>
+      <c r="AB54" s="145"/>
+      <c r="AC54" s="145"/>
+      <c r="AD54" s="145"/>
+      <c r="AE54" s="145"/>
+      <c r="AF54" s="145"/>
+      <c r="AG54" s="145"/>
+      <c r="AH54" s="145"/>
+      <c r="AI54" s="145"/>
+      <c r="AJ54" s="145"/>
     </row>
     <row r="55" spans="1:36" ht="18" customHeight="1">
-      <c r="A55" s="134"/>
-      <c r="B55" s="53"/>
-      <c r="C55" s="53"/>
-      <c r="D55" s="53"/>
-      <c r="E55" s="53"/>
-      <c r="F55" s="53"/>
-      <c r="G55" s="53"/>
-      <c r="H55" s="53"/>
-      <c r="I55" s="53"/>
-      <c r="J55" s="53"/>
-      <c r="K55" s="53"/>
-      <c r="L55" s="53"/>
-      <c r="N55" s="53"/>
-      <c r="O55" s="53"/>
-      <c r="P55" s="53"/>
-      <c r="Q55" s="53"/>
-      <c r="R55" s="53"/>
-      <c r="S55" s="53"/>
-      <c r="T55" s="53"/>
-      <c r="U55" s="53"/>
-      <c r="V55" s="53"/>
-      <c r="W55" s="53"/>
-      <c r="X55" s="53"/>
-      <c r="Y55" s="134"/>
-      <c r="Z55" s="134"/>
-      <c r="AA55" s="134"/>
-      <c r="AB55" s="144" t="s">
+      <c r="A55" s="137"/>
+      <c r="B55" s="74"/>
+      <c r="C55" s="74"/>
+      <c r="D55" s="74"/>
+      <c r="E55" s="74"/>
+      <c r="F55" s="74"/>
+      <c r="G55" s="74"/>
+      <c r="H55" s="74"/>
+      <c r="I55" s="74"/>
+      <c r="J55" s="74"/>
+      <c r="K55" s="74"/>
+      <c r="L55" s="74"/>
+      <c r="N55" s="74"/>
+      <c r="O55" s="74"/>
+      <c r="P55" s="74"/>
+      <c r="Q55" s="74"/>
+      <c r="R55" s="74"/>
+      <c r="S55" s="74"/>
+      <c r="T55" s="74"/>
+      <c r="U55" s="74"/>
+      <c r="V55" s="74"/>
+      <c r="W55" s="74"/>
+      <c r="X55" s="74"/>
+      <c r="Y55" s="137"/>
+      <c r="Z55" s="137"/>
+      <c r="AA55" s="137"/>
+      <c r="AB55" s="147" t="s">
         <v>93</v>
       </c>
-      <c r="AC55" s="102"/>
-      <c r="AD55" s="102"/>
-      <c r="AE55" s="102"/>
-      <c r="AF55" s="102"/>
-      <c r="AG55" s="102"/>
-      <c r="AH55" s="102"/>
-      <c r="AI55" s="102"/>
-      <c r="AJ55" s="102"/>
+      <c r="AC55" s="105"/>
+      <c r="AD55" s="105"/>
+      <c r="AE55" s="105"/>
+      <c r="AF55" s="105"/>
+      <c r="AG55" s="105"/>
+      <c r="AH55" s="105"/>
+      <c r="AI55" s="105"/>
+      <c r="AJ55" s="105"/>
     </row>
     <row r="56" spans="1:36" ht="18" customHeight="1">
-      <c r="A56" s="134"/>
-      <c r="B56" s="53"/>
-      <c r="C56" s="53"/>
-      <c r="D56" s="53"/>
-      <c r="E56" s="53"/>
-      <c r="F56" s="53"/>
-      <c r="G56" s="53"/>
-      <c r="H56" s="53"/>
-      <c r="I56" s="53"/>
-      <c r="J56" s="53"/>
-      <c r="K56" s="53"/>
-      <c r="L56" s="53"/>
-      <c r="N56" s="53"/>
-      <c r="O56" s="53"/>
-      <c r="P56" s="53"/>
-      <c r="Q56" s="53"/>
-      <c r="R56" s="53"/>
-      <c r="S56" s="53"/>
-      <c r="T56" s="53"/>
-      <c r="U56" s="53"/>
-      <c r="V56" s="53"/>
-      <c r="W56" s="53"/>
-      <c r="X56" s="53"/>
-      <c r="Y56" s="134"/>
-      <c r="Z56" s="134"/>
-      <c r="AA56" s="134"/>
-      <c r="AB56" s="135" t="s">
+      <c r="A56" s="137"/>
+      <c r="B56" s="74"/>
+      <c r="C56" s="74"/>
+      <c r="D56" s="74"/>
+      <c r="E56" s="74"/>
+      <c r="F56" s="74"/>
+      <c r="G56" s="74"/>
+      <c r="H56" s="74"/>
+      <c r="I56" s="74"/>
+      <c r="J56" s="74"/>
+      <c r="K56" s="74"/>
+      <c r="L56" s="74"/>
+      <c r="N56" s="74"/>
+      <c r="O56" s="74"/>
+      <c r="P56" s="74"/>
+      <c r="Q56" s="74"/>
+      <c r="R56" s="74"/>
+      <c r="S56" s="74"/>
+      <c r="T56" s="74"/>
+      <c r="U56" s="74"/>
+      <c r="V56" s="74"/>
+      <c r="W56" s="74"/>
+      <c r="X56" s="74"/>
+      <c r="Y56" s="137"/>
+      <c r="Z56" s="137"/>
+      <c r="AA56" s="137"/>
+      <c r="AB56" s="138" t="s">
         <v>47</v>
       </c>
-      <c r="AC56" s="135"/>
-      <c r="AD56" s="135"/>
-      <c r="AE56" s="135"/>
-      <c r="AF56" s="135"/>
-      <c r="AG56" s="135"/>
-      <c r="AH56" s="135"/>
-      <c r="AI56" s="135"/>
-      <c r="AJ56" s="135"/>
+      <c r="AC56" s="138"/>
+      <c r="AD56" s="138"/>
+      <c r="AE56" s="138"/>
+      <c r="AF56" s="138"/>
+      <c r="AG56" s="138"/>
+      <c r="AH56" s="138"/>
+      <c r="AI56" s="138"/>
+      <c r="AJ56" s="138"/>
     </row>
     <row r="57" spans="1:36" ht="18" customHeight="1">
-      <c r="A57" s="134"/>
-      <c r="B57" s="53"/>
-      <c r="C57" s="53"/>
-      <c r="D57" s="53"/>
-      <c r="E57" s="53"/>
-      <c r="F57" s="53"/>
-      <c r="G57" s="53"/>
-      <c r="H57" s="53"/>
-      <c r="I57" s="53"/>
-      <c r="J57" s="53"/>
-      <c r="K57" s="53"/>
-      <c r="L57" s="53"/>
-      <c r="N57" s="53"/>
-      <c r="O57" s="53"/>
-      <c r="P57" s="53"/>
-      <c r="Q57" s="53"/>
-      <c r="R57" s="53"/>
-      <c r="S57" s="53"/>
-      <c r="T57" s="53"/>
-      <c r="U57" s="53"/>
-      <c r="V57" s="53"/>
-      <c r="W57" s="53"/>
-      <c r="X57" s="53"/>
-      <c r="Y57" s="134"/>
-      <c r="Z57" s="134"/>
-      <c r="AA57" s="134"/>
-      <c r="AB57" s="134"/>
-      <c r="AC57" s="134"/>
-      <c r="AD57" s="134"/>
-      <c r="AE57" s="134"/>
-      <c r="AF57" s="134"/>
-      <c r="AG57" s="134"/>
-      <c r="AH57" s="134"/>
-      <c r="AI57" s="134"/>
-      <c r="AJ57" s="134"/>
+      <c r="A57" s="137"/>
+      <c r="B57" s="74"/>
+      <c r="C57" s="74"/>
+      <c r="D57" s="74"/>
+      <c r="E57" s="74"/>
+      <c r="F57" s="74"/>
+      <c r="G57" s="74"/>
+      <c r="H57" s="74"/>
+      <c r="I57" s="74"/>
+      <c r="J57" s="74"/>
+      <c r="K57" s="74"/>
+      <c r="L57" s="74"/>
+      <c r="N57" s="74"/>
+      <c r="O57" s="74"/>
+      <c r="P57" s="74"/>
+      <c r="Q57" s="74"/>
+      <c r="R57" s="74"/>
+      <c r="S57" s="74"/>
+      <c r="T57" s="74"/>
+      <c r="U57" s="74"/>
+      <c r="V57" s="74"/>
+      <c r="W57" s="74"/>
+      <c r="X57" s="74"/>
+      <c r="Y57" s="137"/>
+      <c r="Z57" s="137"/>
+      <c r="AA57" s="137"/>
+      <c r="AB57" s="137"/>
+      <c r="AC57" s="137"/>
+      <c r="AD57" s="137"/>
+      <c r="AE57" s="137"/>
+      <c r="AF57" s="137"/>
+      <c r="AG57" s="137"/>
+      <c r="AH57" s="137"/>
+      <c r="AI57" s="137"/>
+      <c r="AJ57" s="137"/>
     </row>
     <row r="58" spans="1:36" ht="18" customHeight="1">
       <c r="A58" s="51"/>
@@ -9360,72 +9358,72 @@
       <c r="V58" s="52"/>
       <c r="W58" s="52"/>
       <c r="X58" s="52"/>
-      <c r="Y58" s="134"/>
-      <c r="Z58" s="134"/>
-      <c r="AA58" s="134"/>
-      <c r="AB58" s="134"/>
-      <c r="AC58" s="134"/>
-      <c r="AD58" s="134"/>
-      <c r="AE58" s="134"/>
-      <c r="AF58" s="134"/>
-      <c r="AG58" s="134"/>
-      <c r="AH58" s="134"/>
-      <c r="AI58" s="134"/>
-      <c r="AJ58" s="134"/>
+      <c r="Y58" s="137"/>
+      <c r="Z58" s="137"/>
+      <c r="AA58" s="137"/>
+      <c r="AB58" s="137"/>
+      <c r="AC58" s="137"/>
+      <c r="AD58" s="137"/>
+      <c r="AE58" s="137"/>
+      <c r="AF58" s="137"/>
+      <c r="AG58" s="137"/>
+      <c r="AH58" s="137"/>
+      <c r="AI58" s="137"/>
+      <c r="AJ58" s="137"/>
     </row>
     <row r="59" spans="1:36" ht="18" customHeight="1">
-      <c r="A59" s="134"/>
-      <c r="B59" s="134"/>
-      <c r="C59" s="134"/>
-      <c r="D59" s="134"/>
-      <c r="E59" s="134"/>
-      <c r="F59" s="134"/>
-      <c r="G59" s="134"/>
-      <c r="H59" s="134"/>
-      <c r="I59" s="134"/>
-      <c r="J59" s="134"/>
-      <c r="K59" s="134"/>
-      <c r="L59" s="134"/>
-      <c r="M59" s="134"/>
-      <c r="N59" s="134"/>
-      <c r="O59" s="134"/>
-      <c r="P59" s="134"/>
-      <c r="Q59" s="134"/>
-      <c r="R59" s="134"/>
-      <c r="S59" s="134"/>
-      <c r="T59" s="134"/>
-      <c r="U59" s="134"/>
-      <c r="V59" s="134"/>
-      <c r="W59" s="134"/>
-      <c r="X59" s="134"/>
-      <c r="Y59" s="134"/>
-      <c r="Z59" s="134"/>
-      <c r="AA59" s="134"/>
-      <c r="AB59" s="85"/>
-      <c r="AC59" s="85"/>
-      <c r="AD59" s="85"/>
-      <c r="AE59" s="85"/>
-      <c r="AF59" s="85"/>
-      <c r="AG59" s="85"/>
-      <c r="AH59" s="85"/>
-      <c r="AI59" s="85"/>
-      <c r="AJ59" s="85"/>
+      <c r="A59" s="137"/>
+      <c r="B59" s="137"/>
+      <c r="C59" s="137"/>
+      <c r="D59" s="137"/>
+      <c r="E59" s="137"/>
+      <c r="F59" s="137"/>
+      <c r="G59" s="137"/>
+      <c r="H59" s="137"/>
+      <c r="I59" s="137"/>
+      <c r="J59" s="137"/>
+      <c r="K59" s="137"/>
+      <c r="L59" s="137"/>
+      <c r="M59" s="137"/>
+      <c r="N59" s="137"/>
+      <c r="O59" s="137"/>
+      <c r="P59" s="137"/>
+      <c r="Q59" s="137"/>
+      <c r="R59" s="137"/>
+      <c r="S59" s="137"/>
+      <c r="T59" s="137"/>
+      <c r="U59" s="137"/>
+      <c r="V59" s="137"/>
+      <c r="W59" s="137"/>
+      <c r="X59" s="137"/>
+      <c r="Y59" s="137"/>
+      <c r="Z59" s="137"/>
+      <c r="AA59" s="137"/>
+      <c r="AB59" s="88"/>
+      <c r="AC59" s="88"/>
+      <c r="AD59" s="88"/>
+      <c r="AE59" s="88"/>
+      <c r="AF59" s="88"/>
+      <c r="AG59" s="88"/>
+      <c r="AH59" s="88"/>
+      <c r="AI59" s="88"/>
+      <c r="AJ59" s="88"/>
     </row>
     <row r="60" spans="1:36" ht="18" customHeight="1">
-      <c r="Y60" s="134"/>
-      <c r="Z60" s="134"/>
-      <c r="AA60" s="134"/>
-      <c r="AB60" s="133" t="s">
+      <c r="Y60" s="137"/>
+      <c r="Z60" s="137"/>
+      <c r="AA60" s="137"/>
+      <c r="AB60" s="136" t="s">
         <v>92</v>
       </c>
-      <c r="AC60" s="133"/>
-      <c r="AD60" s="133"/>
-      <c r="AE60" s="133"/>
-      <c r="AF60" s="133"/>
-      <c r="AG60" s="133"/>
-      <c r="AH60" s="133"/>
-      <c r="AI60" s="133"/>
-      <c r="AJ60" s="133"/>
+      <c r="AC60" s="136"/>
+      <c r="AD60" s="136"/>
+      <c r="AE60" s="136"/>
+      <c r="AF60" s="136"/>
+      <c r="AG60" s="136"/>
+      <c r="AH60" s="136"/>
+      <c r="AI60" s="136"/>
+      <c r="AJ60" s="136"/>
     </row>
     <row r="61" spans="1:36" ht="16.5" customHeight="1"/>
     <row r="62" spans="1:36" ht="18" hidden="1" customHeight="1"/>
@@ -10075,7 +10073,6 @@
     <mergeCell ref="AB55:AJ55"/>
     <mergeCell ref="W51:Y51"/>
     <mergeCell ref="AC52:AJ52"/>
-    <mergeCell ref="J53:R53"/>
     <mergeCell ref="B48:I48"/>
     <mergeCell ref="AF47:AI47"/>
     <mergeCell ref="AB49:AF49"/>
@@ -10093,7 +10090,6 @@
     <mergeCell ref="K49:R49"/>
     <mergeCell ref="W52:Y52"/>
     <mergeCell ref="K47:R47"/>
-    <mergeCell ref="K44:R44"/>
     <mergeCell ref="AB46:AE46"/>
     <mergeCell ref="S44:V44"/>
     <mergeCell ref="S45:V45"/>
@@ -10102,11 +10098,7 @@
     <mergeCell ref="K46:R46"/>
     <mergeCell ref="K45:R45"/>
     <mergeCell ref="AB44:AE44"/>
-    <mergeCell ref="A5:B5"/>
-    <mergeCell ref="A6:B6"/>
-    <mergeCell ref="AD6:AF6"/>
-    <mergeCell ref="D9:R9"/>
-    <mergeCell ref="K7:O7"/>
+    <mergeCell ref="J53:R53"/>
     <mergeCell ref="AB45:AE45"/>
     <mergeCell ref="A25:AJ25"/>
     <mergeCell ref="A22:AJ23"/>
@@ -10126,6 +10118,16 @@
     <mergeCell ref="AI18:AJ18"/>
     <mergeCell ref="U16:AD16"/>
     <mergeCell ref="AF7:AG7"/>
+    <mergeCell ref="K44:R44"/>
+    <mergeCell ref="B57:L57"/>
+    <mergeCell ref="N57:X57"/>
+    <mergeCell ref="Q2:Z2"/>
+    <mergeCell ref="Q3:Z3"/>
+    <mergeCell ref="A11:P11"/>
+    <mergeCell ref="K5:O5"/>
+    <mergeCell ref="K6:O6"/>
+    <mergeCell ref="P6:X6"/>
+    <mergeCell ref="A41:R41"/>
     <mergeCell ref="S9:W9"/>
     <mergeCell ref="A7:B7"/>
     <mergeCell ref="Q11:AJ11"/>
@@ -10136,15 +10138,11 @@
     <mergeCell ref="P7:R7"/>
     <mergeCell ref="X8:AJ8"/>
     <mergeCell ref="A10:AJ10"/>
-    <mergeCell ref="B57:L57"/>
-    <mergeCell ref="N57:X57"/>
-    <mergeCell ref="Q2:Z2"/>
-    <mergeCell ref="Q3:Z3"/>
-    <mergeCell ref="A11:P11"/>
-    <mergeCell ref="K5:O5"/>
-    <mergeCell ref="K6:O6"/>
-    <mergeCell ref="P6:X6"/>
-    <mergeCell ref="A41:R41"/>
+    <mergeCell ref="A5:B5"/>
+    <mergeCell ref="A6:B6"/>
+    <mergeCell ref="AD6:AF6"/>
+    <mergeCell ref="D9:R9"/>
+    <mergeCell ref="K7:O7"/>
     <mergeCell ref="AE16:AJ16"/>
     <mergeCell ref="A16:T16"/>
     <mergeCell ref="AD3:AJ3"/>
@@ -10161,8 +10159,9 @@
     <mergeCell ref="X7:AB7"/>
   </mergeCells>
   <phoneticPr fontId="0" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup scale="77" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
+  <printOptions horizontalCentered="1"/>
+  <pageMargins left="0.70866141732283472" right="0.70866141732283472" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
+  <pageSetup paperSize="9" scale="77" orientation="landscape" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
   <headerFooter alignWithMargins="0"/>
   <drawing r:id="rId2"/>
   <legacyDrawing r:id="rId3"/>

--- a/backend_api/templates/container_report_template.xlsx
+++ b/backend_api/templates/container_report_template.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Aaron Avila\Documents\ERP-SOM\backend_api\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3D99A33F-2005-457D-AACA-A833B8C17C15}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2CA2A823-9724-484E-89AF-79C1879E1766}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{253FFB1B-D348-46B1-A532-0D44566D2FFD}"/>
+    <workbookView xWindow="-28920" yWindow="-1125" windowWidth="29040" windowHeight="15720" xr2:uid="{253FFB1B-D348-46B1-A532-0D44566D2FFD}"/>
   </bookViews>
   <sheets>
     <sheet name="DRY CARGO" sheetId="1" r:id="rId1"/>
@@ -1562,6 +1562,339 @@
       <alignment vertical="top" wrapText="1"/>
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="4" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="4" fontId="13" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="9" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="6" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="2" borderId="9" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="13" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="3" fontId="13" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="2" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="3" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="4" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="5" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="3" fontId="13" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="9" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="6" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="6" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="6" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="165" fontId="13" fillId="0" borderId="8" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="8" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+      <protection locked="0"/>
+    </xf>
     <xf numFmtId="0" fontId="22" fillId="2" borderId="9" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1588,9 +1921,6 @@
       <alignment horizontal="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="26" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
       <protection locked="0"/>
@@ -1599,341 +1929,11 @@
       <alignment horizontal="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="165" fontId="13" fillId="0" borderId="8" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="14" fontId="13" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="8" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="9" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="6" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="2" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="3" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="4" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="5" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="3" fontId="13" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="13" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="9" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="6" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="6" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="6" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="4" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="4" fontId="13" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="4" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="2" borderId="9" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
       <protection locked="0"/>
     </xf>
   </cellXfs>
@@ -2236,9 +2236,9 @@
         </xdr:from>
         <xdr:to>
           <xdr:col>1</xdr:col>
-          <xdr:colOff>53340</xdr:colOff>
+          <xdr:colOff>57150</xdr:colOff>
           <xdr:row>12</xdr:row>
-          <xdr:rowOff>15240</xdr:rowOff>
+          <xdr:rowOff>19050</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -2303,9 +2303,9 @@
         </xdr:from>
         <xdr:to>
           <xdr:col>1</xdr:col>
-          <xdr:colOff>53340</xdr:colOff>
+          <xdr:colOff>57150</xdr:colOff>
           <xdr:row>13</xdr:row>
-          <xdr:rowOff>15240</xdr:rowOff>
+          <xdr:rowOff>19050</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -2370,9 +2370,9 @@
         </xdr:from>
         <xdr:to>
           <xdr:col>5</xdr:col>
-          <xdr:colOff>53340</xdr:colOff>
+          <xdr:colOff>97155</xdr:colOff>
           <xdr:row>12</xdr:row>
-          <xdr:rowOff>15240</xdr:rowOff>
+          <xdr:rowOff>19050</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -2437,9 +2437,9 @@
         </xdr:from>
         <xdr:to>
           <xdr:col>5</xdr:col>
-          <xdr:colOff>53340</xdr:colOff>
+          <xdr:colOff>97155</xdr:colOff>
           <xdr:row>13</xdr:row>
-          <xdr:rowOff>15240</xdr:rowOff>
+          <xdr:rowOff>19050</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -2503,10 +2503,10 @@
           <xdr:rowOff>30480</xdr:rowOff>
         </xdr:from>
         <xdr:to>
-          <xdr:col>8</xdr:col>
-          <xdr:colOff>396240</xdr:colOff>
+          <xdr:col>9</xdr:col>
+          <xdr:colOff>133350</xdr:colOff>
           <xdr:row>12</xdr:row>
-          <xdr:rowOff>15240</xdr:rowOff>
+          <xdr:rowOff>19050</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -2570,10 +2570,10 @@
           <xdr:rowOff>7620</xdr:rowOff>
         </xdr:from>
         <xdr:to>
-          <xdr:col>8</xdr:col>
-          <xdr:colOff>396240</xdr:colOff>
+          <xdr:col>9</xdr:col>
+          <xdr:colOff>133350</xdr:colOff>
           <xdr:row>13</xdr:row>
-          <xdr:rowOff>15240</xdr:rowOff>
+          <xdr:rowOff>19050</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -2638,9 +2638,9 @@
         </xdr:from>
         <xdr:to>
           <xdr:col>14</xdr:col>
-          <xdr:colOff>53340</xdr:colOff>
+          <xdr:colOff>57150</xdr:colOff>
           <xdr:row>12</xdr:row>
-          <xdr:rowOff>15240</xdr:rowOff>
+          <xdr:rowOff>19050</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -2705,9 +2705,9 @@
         </xdr:from>
         <xdr:to>
           <xdr:col>14</xdr:col>
-          <xdr:colOff>53340</xdr:colOff>
+          <xdr:colOff>57150</xdr:colOff>
           <xdr:row>13</xdr:row>
-          <xdr:rowOff>15240</xdr:rowOff>
+          <xdr:rowOff>19050</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -2772,9 +2772,9 @@
         </xdr:from>
         <xdr:to>
           <xdr:col>17</xdr:col>
-          <xdr:colOff>53340</xdr:colOff>
+          <xdr:colOff>57150</xdr:colOff>
           <xdr:row>12</xdr:row>
-          <xdr:rowOff>15240</xdr:rowOff>
+          <xdr:rowOff>19050</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -2839,9 +2839,9 @@
         </xdr:from>
         <xdr:to>
           <xdr:col>17</xdr:col>
-          <xdr:colOff>53340</xdr:colOff>
+          <xdr:colOff>57150</xdr:colOff>
           <xdr:row>13</xdr:row>
-          <xdr:rowOff>15240</xdr:rowOff>
+          <xdr:rowOff>19050</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -2906,9 +2906,9 @@
         </xdr:from>
         <xdr:to>
           <xdr:col>23</xdr:col>
-          <xdr:colOff>53340</xdr:colOff>
+          <xdr:colOff>57150</xdr:colOff>
           <xdr:row>12</xdr:row>
-          <xdr:rowOff>15240</xdr:rowOff>
+          <xdr:rowOff>19050</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -2973,9 +2973,9 @@
         </xdr:from>
         <xdr:to>
           <xdr:col>23</xdr:col>
-          <xdr:colOff>53340</xdr:colOff>
+          <xdr:colOff>57150</xdr:colOff>
           <xdr:row>13</xdr:row>
-          <xdr:rowOff>15240</xdr:rowOff>
+          <xdr:rowOff>19050</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -3040,9 +3040,9 @@
         </xdr:from>
         <xdr:to>
           <xdr:col>28</xdr:col>
-          <xdr:colOff>53340</xdr:colOff>
+          <xdr:colOff>57150</xdr:colOff>
           <xdr:row>12</xdr:row>
-          <xdr:rowOff>15240</xdr:rowOff>
+          <xdr:rowOff>19050</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -3107,9 +3107,9 @@
         </xdr:from>
         <xdr:to>
           <xdr:col>28</xdr:col>
-          <xdr:colOff>53340</xdr:colOff>
+          <xdr:colOff>57150</xdr:colOff>
           <xdr:row>13</xdr:row>
-          <xdr:rowOff>15240</xdr:rowOff>
+          <xdr:rowOff>19050</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -3176,7 +3176,7 @@
           <xdr:col>32</xdr:col>
           <xdr:colOff>342900</xdr:colOff>
           <xdr:row>12</xdr:row>
-          <xdr:rowOff>15240</xdr:rowOff>
+          <xdr:rowOff>19050</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -3243,7 +3243,7 @@
           <xdr:col>32</xdr:col>
           <xdr:colOff>342900</xdr:colOff>
           <xdr:row>13</xdr:row>
-          <xdr:rowOff>15240</xdr:rowOff>
+          <xdr:rowOff>19050</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -3308,9 +3308,9 @@
         </xdr:from>
         <xdr:to>
           <xdr:col>21</xdr:col>
-          <xdr:colOff>91440</xdr:colOff>
+          <xdr:colOff>95250</xdr:colOff>
           <xdr:row>17</xdr:row>
-          <xdr:rowOff>15240</xdr:rowOff>
+          <xdr:rowOff>19050</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -3375,9 +3375,9 @@
         </xdr:from>
         <xdr:to>
           <xdr:col>21</xdr:col>
-          <xdr:colOff>91440</xdr:colOff>
+          <xdr:colOff>95250</xdr:colOff>
           <xdr:row>18</xdr:row>
-          <xdr:rowOff>15240</xdr:rowOff>
+          <xdr:rowOff>19050</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -3442,9 +3442,9 @@
         </xdr:from>
         <xdr:to>
           <xdr:col>21</xdr:col>
-          <xdr:colOff>91440</xdr:colOff>
+          <xdr:colOff>95250</xdr:colOff>
           <xdr:row>19</xdr:row>
-          <xdr:rowOff>15240</xdr:rowOff>
+          <xdr:rowOff>19050</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -3509,9 +3509,9 @@
         </xdr:from>
         <xdr:to>
           <xdr:col>25</xdr:col>
-          <xdr:colOff>91440</xdr:colOff>
+          <xdr:colOff>95250</xdr:colOff>
           <xdr:row>17</xdr:row>
-          <xdr:rowOff>15240</xdr:rowOff>
+          <xdr:rowOff>19050</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -3576,9 +3576,9 @@
         </xdr:from>
         <xdr:to>
           <xdr:col>25</xdr:col>
-          <xdr:colOff>91440</xdr:colOff>
+          <xdr:colOff>95250</xdr:colOff>
           <xdr:row>18</xdr:row>
-          <xdr:rowOff>15240</xdr:rowOff>
+          <xdr:rowOff>19050</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -3643,9 +3643,9 @@
         </xdr:from>
         <xdr:to>
           <xdr:col>25</xdr:col>
-          <xdr:colOff>91440</xdr:colOff>
+          <xdr:colOff>95250</xdr:colOff>
           <xdr:row>19</xdr:row>
-          <xdr:rowOff>15240</xdr:rowOff>
+          <xdr:rowOff>19050</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -3710,9 +3710,9 @@
         </xdr:from>
         <xdr:to>
           <xdr:col>28</xdr:col>
-          <xdr:colOff>91440</xdr:colOff>
+          <xdr:colOff>95250</xdr:colOff>
           <xdr:row>17</xdr:row>
-          <xdr:rowOff>15240</xdr:rowOff>
+          <xdr:rowOff>19050</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -3777,9 +3777,9 @@
         </xdr:from>
         <xdr:to>
           <xdr:col>28</xdr:col>
-          <xdr:colOff>91440</xdr:colOff>
+          <xdr:colOff>95250</xdr:colOff>
           <xdr:row>18</xdr:row>
-          <xdr:rowOff>15240</xdr:rowOff>
+          <xdr:rowOff>19050</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -3844,9 +3844,9 @@
         </xdr:from>
         <xdr:to>
           <xdr:col>28</xdr:col>
-          <xdr:colOff>91440</xdr:colOff>
+          <xdr:colOff>95250</xdr:colOff>
           <xdr:row>19</xdr:row>
-          <xdr:rowOff>15240</xdr:rowOff>
+          <xdr:rowOff>19050</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -3911,9 +3911,9 @@
         </xdr:from>
         <xdr:to>
           <xdr:col>1</xdr:col>
-          <xdr:colOff>91440</xdr:colOff>
+          <xdr:colOff>95250</xdr:colOff>
           <xdr:row>44</xdr:row>
-          <xdr:rowOff>15240</xdr:rowOff>
+          <xdr:rowOff>19050</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -3978,9 +3978,9 @@
         </xdr:from>
         <xdr:to>
           <xdr:col>1</xdr:col>
-          <xdr:colOff>91440</xdr:colOff>
+          <xdr:colOff>95250</xdr:colOff>
           <xdr:row>45</xdr:row>
-          <xdr:rowOff>15240</xdr:rowOff>
+          <xdr:rowOff>19050</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -4045,9 +4045,9 @@
         </xdr:from>
         <xdr:to>
           <xdr:col>1</xdr:col>
-          <xdr:colOff>91440</xdr:colOff>
+          <xdr:colOff>95250</xdr:colOff>
           <xdr:row>46</xdr:row>
-          <xdr:rowOff>15240</xdr:rowOff>
+          <xdr:rowOff>19050</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -4112,9 +4112,9 @@
         </xdr:from>
         <xdr:to>
           <xdr:col>1</xdr:col>
-          <xdr:colOff>91440</xdr:colOff>
+          <xdr:colOff>95250</xdr:colOff>
           <xdr:row>47</xdr:row>
-          <xdr:rowOff>15240</xdr:rowOff>
+          <xdr:rowOff>19050</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -4179,9 +4179,9 @@
         </xdr:from>
         <xdr:to>
           <xdr:col>1</xdr:col>
-          <xdr:colOff>91440</xdr:colOff>
+          <xdr:colOff>95250</xdr:colOff>
           <xdr:row>48</xdr:row>
-          <xdr:rowOff>15240</xdr:rowOff>
+          <xdr:rowOff>19050</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -4246,9 +4246,9 @@
         </xdr:from>
         <xdr:to>
           <xdr:col>1</xdr:col>
-          <xdr:colOff>91440</xdr:colOff>
+          <xdr:colOff>95250</xdr:colOff>
           <xdr:row>49</xdr:row>
-          <xdr:rowOff>15240</xdr:rowOff>
+          <xdr:rowOff>19050</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -4313,9 +4313,9 @@
         </xdr:from>
         <xdr:to>
           <xdr:col>1</xdr:col>
-          <xdr:colOff>91440</xdr:colOff>
+          <xdr:colOff>95250</xdr:colOff>
           <xdr:row>50</xdr:row>
-          <xdr:rowOff>15240</xdr:rowOff>
+          <xdr:rowOff>19050</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -4380,9 +4380,9 @@
         </xdr:from>
         <xdr:to>
           <xdr:col>1</xdr:col>
-          <xdr:colOff>91440</xdr:colOff>
+          <xdr:colOff>95250</xdr:colOff>
           <xdr:row>51</xdr:row>
-          <xdr:rowOff>15240</xdr:rowOff>
+          <xdr:rowOff>19050</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -4447,9 +4447,9 @@
         </xdr:from>
         <xdr:to>
           <xdr:col>1</xdr:col>
-          <xdr:colOff>91440</xdr:colOff>
+          <xdr:colOff>95250</xdr:colOff>
           <xdr:row>52</xdr:row>
-          <xdr:rowOff>15240</xdr:rowOff>
+          <xdr:rowOff>19050</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -4514,9 +4514,9 @@
         </xdr:from>
         <xdr:to>
           <xdr:col>10</xdr:col>
-          <xdr:colOff>91440</xdr:colOff>
+          <xdr:colOff>171450</xdr:colOff>
           <xdr:row>44</xdr:row>
-          <xdr:rowOff>15240</xdr:rowOff>
+          <xdr:rowOff>19050</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -4581,9 +4581,9 @@
         </xdr:from>
         <xdr:to>
           <xdr:col>10</xdr:col>
-          <xdr:colOff>91440</xdr:colOff>
+          <xdr:colOff>171450</xdr:colOff>
           <xdr:row>45</xdr:row>
-          <xdr:rowOff>15240</xdr:rowOff>
+          <xdr:rowOff>19050</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -4648,9 +4648,9 @@
         </xdr:from>
         <xdr:to>
           <xdr:col>10</xdr:col>
-          <xdr:colOff>91440</xdr:colOff>
+          <xdr:colOff>171450</xdr:colOff>
           <xdr:row>46</xdr:row>
-          <xdr:rowOff>15240</xdr:rowOff>
+          <xdr:rowOff>19050</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -4715,9 +4715,9 @@
         </xdr:from>
         <xdr:to>
           <xdr:col>10</xdr:col>
-          <xdr:colOff>91440</xdr:colOff>
+          <xdr:colOff>171450</xdr:colOff>
           <xdr:row>47</xdr:row>
-          <xdr:rowOff>15240</xdr:rowOff>
+          <xdr:rowOff>19050</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -4782,9 +4782,9 @@
         </xdr:from>
         <xdr:to>
           <xdr:col>10</xdr:col>
-          <xdr:colOff>91440</xdr:colOff>
+          <xdr:colOff>171450</xdr:colOff>
           <xdr:row>48</xdr:row>
-          <xdr:rowOff>15240</xdr:rowOff>
+          <xdr:rowOff>19050</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -4849,9 +4849,9 @@
         </xdr:from>
         <xdr:to>
           <xdr:col>10</xdr:col>
-          <xdr:colOff>91440</xdr:colOff>
+          <xdr:colOff>171450</xdr:colOff>
           <xdr:row>49</xdr:row>
-          <xdr:rowOff>15240</xdr:rowOff>
+          <xdr:rowOff>19050</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -4916,9 +4916,9 @@
         </xdr:from>
         <xdr:to>
           <xdr:col>10</xdr:col>
-          <xdr:colOff>91440</xdr:colOff>
+          <xdr:colOff>171450</xdr:colOff>
           <xdr:row>50</xdr:row>
-          <xdr:rowOff>15240</xdr:rowOff>
+          <xdr:rowOff>19050</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -4983,9 +4983,9 @@
         </xdr:from>
         <xdr:to>
           <xdr:col>10</xdr:col>
-          <xdr:colOff>91440</xdr:colOff>
+          <xdr:colOff>171450</xdr:colOff>
           <xdr:row>51</xdr:row>
-          <xdr:rowOff>15240</xdr:rowOff>
+          <xdr:rowOff>19050</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -5050,9 +5050,9 @@
         </xdr:from>
         <xdr:to>
           <xdr:col>10</xdr:col>
-          <xdr:colOff>91440</xdr:colOff>
+          <xdr:colOff>171450</xdr:colOff>
           <xdr:row>52</xdr:row>
-          <xdr:rowOff>15240</xdr:rowOff>
+          <xdr:rowOff>19050</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -5117,9 +5117,9 @@
         </xdr:from>
         <xdr:to>
           <xdr:col>19</xdr:col>
-          <xdr:colOff>91440</xdr:colOff>
+          <xdr:colOff>95250</xdr:colOff>
           <xdr:row>49</xdr:row>
-          <xdr:rowOff>15240</xdr:rowOff>
+          <xdr:rowOff>19050</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -5184,9 +5184,9 @@
         </xdr:from>
         <xdr:to>
           <xdr:col>19</xdr:col>
-          <xdr:colOff>91440</xdr:colOff>
+          <xdr:colOff>95250</xdr:colOff>
           <xdr:row>50</xdr:row>
-          <xdr:rowOff>15240</xdr:rowOff>
+          <xdr:rowOff>19050</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -5251,9 +5251,9 @@
         </xdr:from>
         <xdr:to>
           <xdr:col>28</xdr:col>
-          <xdr:colOff>91440</xdr:colOff>
+          <xdr:colOff>95250</xdr:colOff>
           <xdr:row>51</xdr:row>
-          <xdr:rowOff>15240</xdr:rowOff>
+          <xdr:rowOff>19050</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -5318,9 +5318,9 @@
         </xdr:from>
         <xdr:to>
           <xdr:col>28</xdr:col>
-          <xdr:colOff>91440</xdr:colOff>
+          <xdr:colOff>95250</xdr:colOff>
           <xdr:row>52</xdr:row>
-          <xdr:rowOff>15240</xdr:rowOff>
+          <xdr:rowOff>19050</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -5385,9 +5385,9 @@
         </xdr:from>
         <xdr:to>
           <xdr:col>28</xdr:col>
-          <xdr:colOff>91440</xdr:colOff>
+          <xdr:colOff>95250</xdr:colOff>
           <xdr:row>53</xdr:row>
-          <xdr:rowOff>15240</xdr:rowOff>
+          <xdr:rowOff>19050</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -6370,9 +6370,9 @@
         </xdr:from>
         <xdr:to>
           <xdr:col>28</xdr:col>
-          <xdr:colOff>91440</xdr:colOff>
+          <xdr:colOff>95250</xdr:colOff>
           <xdr:row>53</xdr:row>
-          <xdr:rowOff>15240</xdr:rowOff>
+          <xdr:rowOff>19050</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -6994,14 +6994,25 @@
   <dimension ref="A1:AJ658"/>
   <sheetFormatPr defaultColWidth="4" defaultRowHeight="13.2" zeroHeight="1"/>
   <cols>
-    <col min="1" max="8" width="4" customWidth="1"/>
-    <col min="9" max="9" width="12.44140625" customWidth="1"/>
-    <col min="10" max="13" width="4" customWidth="1"/>
-    <col min="16" max="16" width="10.5546875" customWidth="1"/>
+    <col min="1" max="2" width="4" customWidth="1"/>
+    <col min="3" max="3" width="1.109375" customWidth="1"/>
+    <col min="4" max="4" width="4" customWidth="1"/>
+    <col min="5" max="5" width="3.33203125" customWidth="1"/>
+    <col min="6" max="6" width="2.5546875" customWidth="1"/>
+    <col min="7" max="7" width="2.44140625" customWidth="1"/>
+    <col min="8" max="8" width="4.6640625" customWidth="1"/>
+    <col min="9" max="9" width="4" customWidth="1"/>
+    <col min="10" max="10" width="3" customWidth="1"/>
+    <col min="11" max="11" width="4" customWidth="1"/>
+    <col min="12" max="12" width="2.5546875" customWidth="1"/>
+    <col min="13" max="13" width="0.109375" customWidth="1"/>
+    <col min="15" max="15" width="7" customWidth="1"/>
+    <col min="16" max="16" width="11.109375" customWidth="1"/>
     <col min="22" max="22" width="12" customWidth="1"/>
     <col min="29" max="29" width="11.44140625" customWidth="1"/>
     <col min="31" max="31" width="2.88671875" bestFit="1" customWidth="1"/>
-    <col min="32" max="33" width="12.33203125" customWidth="1"/>
+    <col min="32" max="32" width="5.21875" customWidth="1"/>
+    <col min="33" max="33" width="12.33203125" customWidth="1"/>
     <col min="35" max="35" width="11.77734375" customWidth="1"/>
   </cols>
   <sheetData>
@@ -7038,16 +7049,16 @@
       <c r="N2" s="31"/>
       <c r="O2" s="38"/>
       <c r="P2" s="38"/>
-      <c r="Q2" s="75"/>
-      <c r="R2" s="75"/>
-      <c r="S2" s="75"/>
-      <c r="T2" s="75"/>
-      <c r="U2" s="75"/>
-      <c r="V2" s="75"/>
-      <c r="W2" s="75"/>
-      <c r="X2" s="75"/>
-      <c r="Y2" s="75"/>
-      <c r="Z2" s="75"/>
+      <c r="Q2" s="139"/>
+      <c r="R2" s="139"/>
+      <c r="S2" s="139"/>
+      <c r="T2" s="139"/>
+      <c r="U2" s="139"/>
+      <c r="V2" s="139"/>
+      <c r="W2" s="139"/>
+      <c r="X2" s="139"/>
+      <c r="Y2" s="139"/>
+      <c r="Z2" s="139"/>
       <c r="AA2" s="38"/>
       <c r="AB2" s="38"/>
       <c r="AC2" s="38"/>
@@ -7073,28 +7084,28 @@
       <c r="K3" s="1"/>
       <c r="M3" s="31"/>
       <c r="N3" s="31"/>
-      <c r="Q3" s="76"/>
-      <c r="R3" s="76"/>
-      <c r="S3" s="76"/>
-      <c r="T3" s="76"/>
-      <c r="U3" s="76"/>
-      <c r="V3" s="76"/>
-      <c r="W3" s="76"/>
-      <c r="X3" s="76"/>
-      <c r="Y3" s="76"/>
-      <c r="Z3" s="76"/>
+      <c r="Q3" s="140"/>
+      <c r="R3" s="140"/>
+      <c r="S3" s="140"/>
+      <c r="T3" s="140"/>
+      <c r="U3" s="140"/>
+      <c r="V3" s="140"/>
+      <c r="W3" s="140"/>
+      <c r="X3" s="140"/>
+      <c r="Y3" s="140"/>
+      <c r="Z3" s="140"/>
       <c r="AA3" s="37"/>
       <c r="AB3" s="50" t="s">
         <v>95</v>
       </c>
       <c r="AC3" s="48"/>
-      <c r="AD3" s="62"/>
-      <c r="AE3" s="63"/>
-      <c r="AF3" s="63"/>
-      <c r="AG3" s="63"/>
-      <c r="AH3" s="63"/>
-      <c r="AI3" s="63"/>
-      <c r="AJ3" s="63"/>
+      <c r="AD3" s="158"/>
+      <c r="AE3" s="159"/>
+      <c r="AF3" s="159"/>
+      <c r="AG3" s="159"/>
+      <c r="AH3" s="159"/>
+      <c r="AI3" s="159"/>
+      <c r="AJ3" s="159"/>
     </row>
     <row r="4" spans="1:36" ht="18" customHeight="1">
       <c r="A4" s="30"/>
@@ -7125,224 +7136,224 @@
       </c>
     </row>
     <row r="5" spans="1:36" ht="18" customHeight="1">
-      <c r="A5" s="71" t="s">
+      <c r="A5" s="60" t="s">
         <v>85</v>
       </c>
-      <c r="B5" s="71"/>
-      <c r="C5" s="105"/>
-      <c r="D5" s="105"/>
-      <c r="E5" s="105"/>
-      <c r="F5" s="105"/>
-      <c r="G5" s="105"/>
-      <c r="H5" s="105"/>
-      <c r="I5" s="105"/>
+      <c r="B5" s="60"/>
+      <c r="C5" s="100"/>
+      <c r="D5" s="100"/>
+      <c r="E5" s="100"/>
+      <c r="F5" s="100"/>
+      <c r="G5" s="100"/>
+      <c r="H5" s="100"/>
+      <c r="I5" s="100"/>
       <c r="J5" s="35"/>
-      <c r="K5" s="64" t="s">
+      <c r="K5" s="144" t="s">
         <v>0</v>
       </c>
-      <c r="L5" s="64"/>
-      <c r="M5" s="64"/>
-      <c r="N5" s="64"/>
-      <c r="O5" s="64"/>
-      <c r="P5" s="65"/>
-      <c r="Q5" s="66"/>
-      <c r="R5" s="66"/>
-      <c r="S5" s="66"/>
-      <c r="T5" s="66"/>
-      <c r="U5" s="66"/>
-      <c r="V5" s="66"/>
-      <c r="W5" s="66"/>
-      <c r="X5" s="66"/>
-      <c r="Y5" s="64" t="s">
+      <c r="L5" s="144"/>
+      <c r="M5" s="144"/>
+      <c r="N5" s="144"/>
+      <c r="O5" s="144"/>
+      <c r="P5" s="160"/>
+      <c r="Q5" s="161"/>
+      <c r="R5" s="161"/>
+      <c r="S5" s="161"/>
+      <c r="T5" s="161"/>
+      <c r="U5" s="161"/>
+      <c r="V5" s="161"/>
+      <c r="W5" s="161"/>
+      <c r="X5" s="161"/>
+      <c r="Y5" s="144" t="s">
         <v>48</v>
       </c>
-      <c r="Z5" s="64"/>
-      <c r="AA5" s="105"/>
-      <c r="AB5" s="105"/>
-      <c r="AC5" s="105"/>
-      <c r="AD5" s="105"/>
-      <c r="AE5" s="105"/>
-      <c r="AF5" s="105"/>
-      <c r="AG5" s="105"/>
-      <c r="AH5" s="105"/>
-      <c r="AI5" s="105"/>
-      <c r="AJ5" s="105"/>
+      <c r="Z5" s="144"/>
+      <c r="AA5" s="100"/>
+      <c r="AB5" s="100"/>
+      <c r="AC5" s="100"/>
+      <c r="AD5" s="100"/>
+      <c r="AE5" s="100"/>
+      <c r="AF5" s="100"/>
+      <c r="AG5" s="100"/>
+      <c r="AH5" s="100"/>
+      <c r="AI5" s="100"/>
+      <c r="AJ5" s="100"/>
     </row>
     <row r="6" spans="1:36" ht="18" customHeight="1">
-      <c r="A6" s="71" t="s">
+      <c r="A6" s="60" t="s">
         <v>1</v>
       </c>
-      <c r="B6" s="71"/>
-      <c r="C6" s="69"/>
-      <c r="D6" s="69"/>
-      <c r="E6" s="69"/>
-      <c r="F6" s="69"/>
-      <c r="G6" s="69"/>
-      <c r="H6" s="69"/>
-      <c r="I6" s="69"/>
+      <c r="B6" s="60"/>
+      <c r="C6" s="150"/>
+      <c r="D6" s="150"/>
+      <c r="E6" s="150"/>
+      <c r="F6" s="150"/>
+      <c r="G6" s="150"/>
+      <c r="H6" s="150"/>
+      <c r="I6" s="150"/>
       <c r="J6" s="35"/>
-      <c r="K6" s="64" t="s">
+      <c r="K6" s="144" t="s">
         <v>2</v>
       </c>
-      <c r="L6" s="64"/>
-      <c r="M6" s="64"/>
-      <c r="N6" s="64"/>
-      <c r="O6" s="64"/>
-      <c r="P6" s="80"/>
-      <c r="Q6" s="81"/>
-      <c r="R6" s="81"/>
-      <c r="S6" s="81"/>
-      <c r="T6" s="81"/>
-      <c r="U6" s="81"/>
-      <c r="V6" s="81"/>
-      <c r="W6" s="81"/>
-      <c r="X6" s="81"/>
-      <c r="Y6" s="64" t="s">
+      <c r="L6" s="144"/>
+      <c r="M6" s="144"/>
+      <c r="N6" s="144"/>
+      <c r="O6" s="144"/>
+      <c r="P6" s="145"/>
+      <c r="Q6" s="146"/>
+      <c r="R6" s="146"/>
+      <c r="S6" s="146"/>
+      <c r="T6" s="146"/>
+      <c r="U6" s="146"/>
+      <c r="V6" s="146"/>
+      <c r="W6" s="146"/>
+      <c r="X6" s="146"/>
+      <c r="Y6" s="144" t="s">
         <v>88</v>
       </c>
-      <c r="Z6" s="64"/>
-      <c r="AA6" s="64"/>
-      <c r="AB6" s="64"/>
-      <c r="AC6" s="64"/>
-      <c r="AD6" s="68"/>
-      <c r="AE6" s="68"/>
-      <c r="AF6" s="68"/>
+      <c r="Z6" s="144"/>
+      <c r="AA6" s="144"/>
+      <c r="AB6" s="144"/>
+      <c r="AC6" s="144"/>
+      <c r="AD6" s="78"/>
+      <c r="AE6" s="78"/>
+      <c r="AF6" s="78"/>
       <c r="AG6" s="44"/>
-      <c r="AH6" s="67"/>
-      <c r="AI6" s="67"/>
+      <c r="AH6" s="135"/>
+      <c r="AI6" s="135"/>
       <c r="AJ6" s="44"/>
     </row>
     <row r="7" spans="1:36" ht="18" customHeight="1">
-      <c r="A7" s="71" t="s">
+      <c r="A7" s="60" t="s">
         <v>3</v>
       </c>
-      <c r="B7" s="71"/>
-      <c r="C7" s="69"/>
-      <c r="D7" s="69"/>
-      <c r="E7" s="69"/>
-      <c r="F7" s="69"/>
-      <c r="G7" s="69"/>
-      <c r="H7" s="69"/>
-      <c r="I7" s="69"/>
+      <c r="B7" s="60"/>
+      <c r="C7" s="150"/>
+      <c r="D7" s="150"/>
+      <c r="E7" s="150"/>
+      <c r="F7" s="150"/>
+      <c r="G7" s="150"/>
+      <c r="H7" s="150"/>
+      <c r="I7" s="150"/>
       <c r="J7" s="35"/>
-      <c r="K7" s="64" t="s">
+      <c r="K7" s="144" t="s">
         <v>89</v>
       </c>
-      <c r="L7" s="64"/>
-      <c r="M7" s="64"/>
-      <c r="N7" s="64"/>
-      <c r="O7" s="64"/>
-      <c r="P7" s="68"/>
-      <c r="Q7" s="68"/>
-      <c r="R7" s="68"/>
-      <c r="S7" s="67"/>
-      <c r="T7" s="67"/>
+      <c r="L7" s="144"/>
+      <c r="M7" s="144"/>
+      <c r="N7" s="144"/>
+      <c r="O7" s="144"/>
+      <c r="P7" s="78"/>
+      <c r="Q7" s="78"/>
+      <c r="R7" s="78"/>
+      <c r="S7" s="135"/>
+      <c r="T7" s="135"/>
       <c r="U7" s="39" t="s">
         <v>4</v>
       </c>
-      <c r="V7" s="67"/>
-      <c r="W7" s="67"/>
-      <c r="X7" s="64" t="s">
+      <c r="V7" s="135"/>
+      <c r="W7" s="135"/>
+      <c r="X7" s="144" t="s">
         <v>90</v>
       </c>
-      <c r="Y7" s="64"/>
-      <c r="Z7" s="64"/>
-      <c r="AA7" s="64"/>
-      <c r="AB7" s="64"/>
-      <c r="AC7" s="68"/>
-      <c r="AD7" s="68"/>
-      <c r="AE7" s="68"/>
-      <c r="AF7" s="67"/>
-      <c r="AG7" s="67"/>
+      <c r="Y7" s="144"/>
+      <c r="Z7" s="144"/>
+      <c r="AA7" s="144"/>
+      <c r="AB7" s="144"/>
+      <c r="AC7" s="78"/>
+      <c r="AD7" s="78"/>
+      <c r="AE7" s="78"/>
+      <c r="AF7" s="135"/>
+      <c r="AG7" s="135"/>
       <c r="AH7" s="39" t="s">
         <v>4</v>
       </c>
-      <c r="AI7" s="67"/>
-      <c r="AJ7" s="67"/>
+      <c r="AI7" s="135"/>
+      <c r="AJ7" s="135"/>
     </row>
     <row r="8" spans="1:36" ht="18" customHeight="1">
-      <c r="A8" s="87" t="s">
+      <c r="A8" s="85" t="s">
         <v>5</v>
       </c>
-      <c r="B8" s="87"/>
-      <c r="C8" s="87"/>
-      <c r="D8" s="74"/>
-      <c r="E8" s="74"/>
-      <c r="F8" s="74"/>
-      <c r="G8" s="74"/>
-      <c r="H8" s="74"/>
-      <c r="I8" s="74"/>
-      <c r="J8" s="74"/>
-      <c r="K8" s="74"/>
-      <c r="L8" s="74"/>
-      <c r="M8" s="74"/>
-      <c r="N8" s="74"/>
-      <c r="O8" s="74"/>
-      <c r="P8" s="74"/>
-      <c r="Q8" s="74"/>
-      <c r="R8" s="74"/>
-      <c r="S8" s="70" t="s">
+      <c r="B8" s="85"/>
+      <c r="C8" s="85"/>
+      <c r="D8" s="95"/>
+      <c r="E8" s="95"/>
+      <c r="F8" s="95"/>
+      <c r="G8" s="95"/>
+      <c r="H8" s="95"/>
+      <c r="I8" s="95"/>
+      <c r="J8" s="95"/>
+      <c r="K8" s="95"/>
+      <c r="L8" s="95"/>
+      <c r="M8" s="95"/>
+      <c r="N8" s="95"/>
+      <c r="O8" s="95"/>
+      <c r="P8" s="95"/>
+      <c r="Q8" s="95"/>
+      <c r="R8" s="95"/>
+      <c r="S8" s="162" t="s">
         <v>49</v>
       </c>
-      <c r="T8" s="70"/>
-      <c r="U8" s="64"/>
-      <c r="V8" s="70"/>
-      <c r="W8" s="70"/>
-      <c r="X8" s="74"/>
-      <c r="Y8" s="74"/>
-      <c r="Z8" s="74"/>
-      <c r="AA8" s="74"/>
-      <c r="AB8" s="74"/>
-      <c r="AC8" s="74"/>
-      <c r="AD8" s="74"/>
-      <c r="AE8" s="74"/>
-      <c r="AF8" s="74"/>
-      <c r="AG8" s="74"/>
-      <c r="AH8" s="74"/>
-      <c r="AI8" s="74"/>
-      <c r="AJ8" s="74"/>
+      <c r="T8" s="162"/>
+      <c r="U8" s="144"/>
+      <c r="V8" s="162"/>
+      <c r="W8" s="162"/>
+      <c r="X8" s="95"/>
+      <c r="Y8" s="95"/>
+      <c r="Z8" s="95"/>
+      <c r="AA8" s="95"/>
+      <c r="AB8" s="95"/>
+      <c r="AC8" s="95"/>
+      <c r="AD8" s="95"/>
+      <c r="AE8" s="95"/>
+      <c r="AF8" s="95"/>
+      <c r="AG8" s="95"/>
+      <c r="AH8" s="95"/>
+      <c r="AI8" s="95"/>
+      <c r="AJ8" s="95"/>
     </row>
     <row r="9" spans="1:36" ht="26.4" customHeight="1">
-      <c r="A9" s="71" t="s">
+      <c r="A9" s="60" t="s">
         <v>6</v>
       </c>
-      <c r="B9" s="71"/>
-      <c r="C9" s="71"/>
-      <c r="D9" s="73"/>
-      <c r="E9" s="73"/>
-      <c r="F9" s="73"/>
-      <c r="G9" s="73"/>
-      <c r="H9" s="73"/>
-      <c r="I9" s="73"/>
-      <c r="J9" s="73"/>
-      <c r="K9" s="73"/>
-      <c r="L9" s="73"/>
-      <c r="M9" s="73"/>
-      <c r="N9" s="73"/>
-      <c r="O9" s="73"/>
-      <c r="P9" s="73"/>
-      <c r="Q9" s="73"/>
-      <c r="R9" s="73"/>
-      <c r="S9" s="64" t="s">
+      <c r="B9" s="60"/>
+      <c r="C9" s="60"/>
+      <c r="D9" s="151"/>
+      <c r="E9" s="151"/>
+      <c r="F9" s="151"/>
+      <c r="G9" s="151"/>
+      <c r="H9" s="151"/>
+      <c r="I9" s="151"/>
+      <c r="J9" s="151"/>
+      <c r="K9" s="151"/>
+      <c r="L9" s="151"/>
+      <c r="M9" s="151"/>
+      <c r="N9" s="151"/>
+      <c r="O9" s="151"/>
+      <c r="P9" s="151"/>
+      <c r="Q9" s="151"/>
+      <c r="R9" s="151"/>
+      <c r="S9" s="144" t="s">
         <v>50</v>
       </c>
-      <c r="T9" s="64"/>
-      <c r="U9" s="64"/>
-      <c r="V9" s="64"/>
-      <c r="W9" s="64"/>
-      <c r="X9" s="72"/>
-      <c r="Y9" s="73"/>
-      <c r="Z9" s="73"/>
-      <c r="AA9" s="73"/>
-      <c r="AB9" s="73"/>
-      <c r="AC9" s="73"/>
-      <c r="AD9" s="73"/>
-      <c r="AE9" s="73"/>
-      <c r="AF9" s="73"/>
-      <c r="AG9" s="73"/>
-      <c r="AH9" s="73"/>
-      <c r="AI9" s="73"/>
-      <c r="AJ9" s="73"/>
+      <c r="T9" s="144"/>
+      <c r="U9" s="144"/>
+      <c r="V9" s="144"/>
+      <c r="W9" s="144"/>
+      <c r="X9" s="163"/>
+      <c r="Y9" s="151"/>
+      <c r="Z9" s="151"/>
+      <c r="AA9" s="151"/>
+      <c r="AB9" s="151"/>
+      <c r="AC9" s="151"/>
+      <c r="AD9" s="151"/>
+      <c r="AE9" s="151"/>
+      <c r="AF9" s="151"/>
+      <c r="AG9" s="151"/>
+      <c r="AH9" s="151"/>
+      <c r="AI9" s="151"/>
+      <c r="AJ9" s="151"/>
     </row>
     <row r="10" spans="1:36" ht="5.25" customHeight="1">
       <c r="A10" s="88"/>
@@ -7383,46 +7394,46 @@
       <c r="AJ10" s="88"/>
     </row>
     <row r="11" spans="1:36" ht="14.25" customHeight="1">
-      <c r="A11" s="77" t="s">
+      <c r="A11" s="141" t="s">
         <v>7</v>
       </c>
-      <c r="B11" s="78"/>
-      <c r="C11" s="78"/>
-      <c r="D11" s="78"/>
-      <c r="E11" s="78"/>
-      <c r="F11" s="78"/>
-      <c r="G11" s="78"/>
-      <c r="H11" s="78"/>
-      <c r="I11" s="78"/>
-      <c r="J11" s="78"/>
-      <c r="K11" s="78"/>
-      <c r="L11" s="78"/>
-      <c r="M11" s="78"/>
-      <c r="N11" s="78"/>
-      <c r="O11" s="78"/>
-      <c r="P11" s="79"/>
-      <c r="Q11" s="84" t="s">
+      <c r="B11" s="142"/>
+      <c r="C11" s="142"/>
+      <c r="D11" s="142"/>
+      <c r="E11" s="142"/>
+      <c r="F11" s="142"/>
+      <c r="G11" s="142"/>
+      <c r="H11" s="142"/>
+      <c r="I11" s="142"/>
+      <c r="J11" s="142"/>
+      <c r="K11" s="142"/>
+      <c r="L11" s="142"/>
+      <c r="M11" s="142"/>
+      <c r="N11" s="142"/>
+      <c r="O11" s="142"/>
+      <c r="P11" s="143"/>
+      <c r="Q11" s="147" t="s">
         <v>8</v>
       </c>
-      <c r="R11" s="85"/>
-      <c r="S11" s="85"/>
-      <c r="T11" s="85"/>
-      <c r="U11" s="85"/>
-      <c r="V11" s="85"/>
-      <c r="W11" s="85"/>
-      <c r="X11" s="85"/>
-      <c r="Y11" s="85"/>
-      <c r="Z11" s="85"/>
-      <c r="AA11" s="85"/>
-      <c r="AB11" s="85"/>
-      <c r="AC11" s="85"/>
-      <c r="AD11" s="85"/>
-      <c r="AE11" s="85"/>
-      <c r="AF11" s="85"/>
-      <c r="AG11" s="85"/>
-      <c r="AH11" s="85"/>
-      <c r="AI11" s="85"/>
-      <c r="AJ11" s="86"/>
+      <c r="R11" s="148"/>
+      <c r="S11" s="148"/>
+      <c r="T11" s="148"/>
+      <c r="U11" s="148"/>
+      <c r="V11" s="148"/>
+      <c r="W11" s="148"/>
+      <c r="X11" s="148"/>
+      <c r="Y11" s="148"/>
+      <c r="Z11" s="148"/>
+      <c r="AA11" s="148"/>
+      <c r="AB11" s="148"/>
+      <c r="AC11" s="148"/>
+      <c r="AD11" s="148"/>
+      <c r="AE11" s="148"/>
+      <c r="AF11" s="148"/>
+      <c r="AG11" s="148"/>
+      <c r="AH11" s="148"/>
+      <c r="AI11" s="148"/>
+      <c r="AJ11" s="149"/>
     </row>
     <row r="12" spans="1:36" ht="18" customHeight="1">
       <c r="A12" s="2"/>
@@ -7531,150 +7542,150 @@
       <c r="AJ13" s="23"/>
     </row>
     <row r="14" spans="1:36" ht="16.5" customHeight="1">
-      <c r="A14" s="111" t="s">
+      <c r="A14" s="127" t="s">
         <v>86</v>
       </c>
-      <c r="B14" s="112"/>
-      <c r="C14" s="112"/>
-      <c r="D14" s="112"/>
-      <c r="E14" s="112"/>
-      <c r="F14" s="112"/>
-      <c r="G14" s="112"/>
-      <c r="H14" s="112"/>
-      <c r="I14" s="113"/>
-      <c r="J14" s="114"/>
-      <c r="K14" s="114"/>
-      <c r="L14" s="114"/>
-      <c r="M14" s="114"/>
-      <c r="N14" s="114"/>
-      <c r="O14" s="114"/>
-      <c r="P14" s="114"/>
-      <c r="Q14" s="114"/>
-      <c r="R14" s="114"/>
-      <c r="S14" s="114"/>
-      <c r="T14" s="114"/>
-      <c r="U14" s="114"/>
-      <c r="V14" s="114"/>
-      <c r="W14" s="114"/>
-      <c r="X14" s="114"/>
-      <c r="Y14" s="114"/>
-      <c r="Z14" s="114"/>
-      <c r="AA14" s="114"/>
-      <c r="AB14" s="114"/>
-      <c r="AC14" s="114"/>
-      <c r="AD14" s="114"/>
-      <c r="AE14" s="114"/>
-      <c r="AF14" s="114"/>
-      <c r="AG14" s="114"/>
-      <c r="AH14" s="114"/>
-      <c r="AI14" s="114"/>
-      <c r="AJ14" s="115"/>
+      <c r="B14" s="128"/>
+      <c r="C14" s="128"/>
+      <c r="D14" s="128"/>
+      <c r="E14" s="128"/>
+      <c r="F14" s="128"/>
+      <c r="G14" s="128"/>
+      <c r="H14" s="128"/>
+      <c r="I14" s="129"/>
+      <c r="J14" s="130"/>
+      <c r="K14" s="130"/>
+      <c r="L14" s="130"/>
+      <c r="M14" s="130"/>
+      <c r="N14" s="130"/>
+      <c r="O14" s="130"/>
+      <c r="P14" s="130"/>
+      <c r="Q14" s="130"/>
+      <c r="R14" s="130"/>
+      <c r="S14" s="130"/>
+      <c r="T14" s="130"/>
+      <c r="U14" s="130"/>
+      <c r="V14" s="130"/>
+      <c r="W14" s="130"/>
+      <c r="X14" s="130"/>
+      <c r="Y14" s="130"/>
+      <c r="Z14" s="130"/>
+      <c r="AA14" s="130"/>
+      <c r="AB14" s="130"/>
+      <c r="AC14" s="130"/>
+      <c r="AD14" s="130"/>
+      <c r="AE14" s="130"/>
+      <c r="AF14" s="130"/>
+      <c r="AG14" s="130"/>
+      <c r="AH14" s="130"/>
+      <c r="AI14" s="130"/>
+      <c r="AJ14" s="131"/>
     </row>
     <row r="15" spans="1:36" ht="3" customHeight="1">
-      <c r="A15" s="116">
+      <c r="A15" s="132">
         <v>2</v>
       </c>
-      <c r="B15" s="117"/>
-      <c r="C15" s="117"/>
-      <c r="D15" s="117"/>
-      <c r="E15" s="117"/>
-      <c r="F15" s="117"/>
-      <c r="G15" s="117"/>
-      <c r="H15" s="117"/>
-      <c r="I15" s="117"/>
-      <c r="J15" s="117"/>
-      <c r="K15" s="117"/>
-      <c r="L15" s="117"/>
-      <c r="M15" s="117"/>
-      <c r="N15" s="117"/>
-      <c r="O15" s="117"/>
-      <c r="P15" s="117"/>
-      <c r="Q15" s="117"/>
-      <c r="R15" s="117"/>
-      <c r="S15" s="117"/>
-      <c r="T15" s="117"/>
-      <c r="U15" s="117"/>
-      <c r="V15" s="117"/>
-      <c r="W15" s="117"/>
-      <c r="X15" s="117"/>
-      <c r="Y15" s="117"/>
-      <c r="Z15" s="117"/>
-      <c r="AA15" s="117"/>
-      <c r="AB15" s="117"/>
-      <c r="AC15" s="117"/>
-      <c r="AD15" s="117"/>
-      <c r="AE15" s="117"/>
-      <c r="AF15" s="117"/>
-      <c r="AG15" s="117"/>
-      <c r="AH15" s="117"/>
-      <c r="AI15" s="117"/>
-      <c r="AJ15" s="118"/>
+      <c r="B15" s="133"/>
+      <c r="C15" s="133"/>
+      <c r="D15" s="133"/>
+      <c r="E15" s="133"/>
+      <c r="F15" s="133"/>
+      <c r="G15" s="133"/>
+      <c r="H15" s="133"/>
+      <c r="I15" s="133"/>
+      <c r="J15" s="133"/>
+      <c r="K15" s="133"/>
+      <c r="L15" s="133"/>
+      <c r="M15" s="133"/>
+      <c r="N15" s="133"/>
+      <c r="O15" s="133"/>
+      <c r="P15" s="133"/>
+      <c r="Q15" s="133"/>
+      <c r="R15" s="133"/>
+      <c r="S15" s="133"/>
+      <c r="T15" s="133"/>
+      <c r="U15" s="133"/>
+      <c r="V15" s="133"/>
+      <c r="W15" s="133"/>
+      <c r="X15" s="133"/>
+      <c r="Y15" s="133"/>
+      <c r="Z15" s="133"/>
+      <c r="AA15" s="133"/>
+      <c r="AB15" s="133"/>
+      <c r="AC15" s="133"/>
+      <c r="AD15" s="133"/>
+      <c r="AE15" s="133"/>
+      <c r="AF15" s="133"/>
+      <c r="AG15" s="133"/>
+      <c r="AH15" s="133"/>
+      <c r="AI15" s="133"/>
+      <c r="AJ15" s="134"/>
     </row>
     <row r="16" spans="1:36" ht="12.75" customHeight="1">
-      <c r="A16" s="59" t="s">
+      <c r="A16" s="155" t="s">
         <v>9</v>
       </c>
-      <c r="B16" s="60"/>
-      <c r="C16" s="60"/>
-      <c r="D16" s="60"/>
-      <c r="E16" s="60"/>
-      <c r="F16" s="60"/>
-      <c r="G16" s="60"/>
-      <c r="H16" s="60"/>
-      <c r="I16" s="60"/>
-      <c r="J16" s="60"/>
-      <c r="K16" s="60"/>
-      <c r="L16" s="60"/>
-      <c r="M16" s="60"/>
-      <c r="N16" s="60"/>
-      <c r="O16" s="60"/>
-      <c r="P16" s="60"/>
-      <c r="Q16" s="60"/>
-      <c r="R16" s="60"/>
-      <c r="S16" s="60"/>
-      <c r="T16" s="61"/>
-      <c r="U16" s="119" t="s">
+      <c r="B16" s="156"/>
+      <c r="C16" s="156"/>
+      <c r="D16" s="156"/>
+      <c r="E16" s="156"/>
+      <c r="F16" s="156"/>
+      <c r="G16" s="156"/>
+      <c r="H16" s="156"/>
+      <c r="I16" s="156"/>
+      <c r="J16" s="156"/>
+      <c r="K16" s="156"/>
+      <c r="L16" s="156"/>
+      <c r="M16" s="156"/>
+      <c r="N16" s="156"/>
+      <c r="O16" s="156"/>
+      <c r="P16" s="156"/>
+      <c r="Q16" s="156"/>
+      <c r="R16" s="156"/>
+      <c r="S16" s="156"/>
+      <c r="T16" s="157"/>
+      <c r="U16" s="136" t="s">
         <v>73</v>
       </c>
-      <c r="V16" s="120"/>
-      <c r="W16" s="120"/>
-      <c r="X16" s="120"/>
-      <c r="Y16" s="120"/>
-      <c r="Z16" s="120"/>
-      <c r="AA16" s="120"/>
-      <c r="AB16" s="120"/>
-      <c r="AC16" s="120"/>
-      <c r="AD16" s="121"/>
-      <c r="AE16" s="56" t="s">
+      <c r="V16" s="137"/>
+      <c r="W16" s="137"/>
+      <c r="X16" s="137"/>
+      <c r="Y16" s="137"/>
+      <c r="Z16" s="137"/>
+      <c r="AA16" s="137"/>
+      <c r="AB16" s="137"/>
+      <c r="AC16" s="137"/>
+      <c r="AD16" s="138"/>
+      <c r="AE16" s="152" t="s">
         <v>10</v>
       </c>
-      <c r="AF16" s="57"/>
-      <c r="AG16" s="57"/>
-      <c r="AH16" s="57"/>
-      <c r="AI16" s="57"/>
-      <c r="AJ16" s="58"/>
+      <c r="AF16" s="153"/>
+      <c r="AG16" s="153"/>
+      <c r="AH16" s="153"/>
+      <c r="AI16" s="153"/>
+      <c r="AJ16" s="154"/>
     </row>
     <row r="17" spans="1:36" ht="18" customHeight="1">
-      <c r="A17" s="99"/>
-      <c r="B17" s="100"/>
-      <c r="C17" s="100"/>
-      <c r="D17" s="100"/>
-      <c r="E17" s="100"/>
-      <c r="F17" s="100"/>
-      <c r="G17" s="100"/>
-      <c r="H17" s="100"/>
-      <c r="I17" s="100"/>
-      <c r="J17" s="100"/>
-      <c r="K17" s="100"/>
-      <c r="L17" s="100"/>
-      <c r="M17" s="100"/>
-      <c r="N17" s="100"/>
-      <c r="O17" s="100"/>
-      <c r="P17" s="100"/>
-      <c r="Q17" s="100"/>
-      <c r="R17" s="100"/>
-      <c r="S17" s="100"/>
-      <c r="T17" s="101"/>
+      <c r="A17" s="120"/>
+      <c r="B17" s="121"/>
+      <c r="C17" s="121"/>
+      <c r="D17" s="121"/>
+      <c r="E17" s="121"/>
+      <c r="F17" s="121"/>
+      <c r="G17" s="121"/>
+      <c r="H17" s="121"/>
+      <c r="I17" s="121"/>
+      <c r="J17" s="121"/>
+      <c r="K17" s="121"/>
+      <c r="L17" s="121"/>
+      <c r="M17" s="121"/>
+      <c r="N17" s="121"/>
+      <c r="O17" s="121"/>
+      <c r="P17" s="121"/>
+      <c r="Q17" s="121"/>
+      <c r="R17" s="121"/>
+      <c r="S17" s="121"/>
+      <c r="T17" s="122"/>
       <c r="U17" s="25"/>
       <c r="V17" s="17" t="s">
         <v>64</v>
@@ -7690,32 +7701,32 @@
       <c r="AE17" s="14" t="s">
         <v>11</v>
       </c>
-      <c r="AF17" s="106"/>
-      <c r="AG17" s="106"/>
-      <c r="AI17" s="106"/>
-      <c r="AJ17" s="110"/>
+      <c r="AF17" s="103"/>
+      <c r="AG17" s="103"/>
+      <c r="AI17" s="103"/>
+      <c r="AJ17" s="126"/>
     </row>
     <row r="18" spans="1:36" ht="18" customHeight="1">
-      <c r="A18" s="99"/>
-      <c r="B18" s="100"/>
-      <c r="C18" s="100"/>
-      <c r="D18" s="100"/>
-      <c r="E18" s="100"/>
-      <c r="F18" s="100"/>
-      <c r="G18" s="100"/>
-      <c r="H18" s="100"/>
-      <c r="I18" s="100"/>
-      <c r="J18" s="100"/>
-      <c r="K18" s="100"/>
-      <c r="L18" s="100"/>
-      <c r="M18" s="100"/>
-      <c r="N18" s="100"/>
-      <c r="O18" s="100"/>
-      <c r="P18" s="100"/>
-      <c r="Q18" s="100"/>
-      <c r="R18" s="100"/>
-      <c r="S18" s="100"/>
-      <c r="T18" s="101"/>
+      <c r="A18" s="120"/>
+      <c r="B18" s="121"/>
+      <c r="C18" s="121"/>
+      <c r="D18" s="121"/>
+      <c r="E18" s="121"/>
+      <c r="F18" s="121"/>
+      <c r="G18" s="121"/>
+      <c r="H18" s="121"/>
+      <c r="I18" s="121"/>
+      <c r="J18" s="121"/>
+      <c r="K18" s="121"/>
+      <c r="L18" s="121"/>
+      <c r="M18" s="121"/>
+      <c r="N18" s="121"/>
+      <c r="O18" s="121"/>
+      <c r="P18" s="121"/>
+      <c r="Q18" s="121"/>
+      <c r="R18" s="121"/>
+      <c r="S18" s="121"/>
+      <c r="T18" s="122"/>
       <c r="U18" s="26"/>
       <c r="V18" s="17" t="s">
         <v>65</v>
@@ -7731,32 +7742,32 @@
       <c r="AE18" s="14" t="s">
         <v>12</v>
       </c>
-      <c r="AF18" s="106"/>
-      <c r="AG18" s="106"/>
-      <c r="AI18" s="106"/>
-      <c r="AJ18" s="110"/>
+      <c r="AF18" s="103"/>
+      <c r="AG18" s="103"/>
+      <c r="AI18" s="103"/>
+      <c r="AJ18" s="126"/>
     </row>
     <row r="19" spans="1:36" ht="18" customHeight="1">
-      <c r="A19" s="99"/>
-      <c r="B19" s="100"/>
-      <c r="C19" s="100"/>
-      <c r="D19" s="100"/>
-      <c r="E19" s="100"/>
-      <c r="F19" s="100"/>
-      <c r="G19" s="100"/>
-      <c r="H19" s="100"/>
-      <c r="I19" s="100"/>
-      <c r="J19" s="100"/>
-      <c r="K19" s="100"/>
-      <c r="L19" s="100"/>
-      <c r="M19" s="100"/>
-      <c r="N19" s="100"/>
-      <c r="O19" s="100"/>
-      <c r="P19" s="100"/>
-      <c r="Q19" s="100"/>
-      <c r="R19" s="100"/>
-      <c r="S19" s="100"/>
-      <c r="T19" s="101"/>
+      <c r="A19" s="120"/>
+      <c r="B19" s="121"/>
+      <c r="C19" s="121"/>
+      <c r="D19" s="121"/>
+      <c r="E19" s="121"/>
+      <c r="F19" s="121"/>
+      <c r="G19" s="121"/>
+      <c r="H19" s="121"/>
+      <c r="I19" s="121"/>
+      <c r="J19" s="121"/>
+      <c r="K19" s="121"/>
+      <c r="L19" s="121"/>
+      <c r="M19" s="121"/>
+      <c r="N19" s="121"/>
+      <c r="O19" s="121"/>
+      <c r="P19" s="121"/>
+      <c r="Q19" s="121"/>
+      <c r="R19" s="121"/>
+      <c r="S19" s="121"/>
+      <c r="T19" s="122"/>
       <c r="U19" s="26"/>
       <c r="V19" s="17" t="s">
         <v>66</v>
@@ -7772,32 +7783,32 @@
       <c r="AE19" s="14" t="s">
         <v>13</v>
       </c>
-      <c r="AF19" s="106"/>
-      <c r="AG19" s="106"/>
-      <c r="AI19" s="106"/>
-      <c r="AJ19" s="110"/>
+      <c r="AF19" s="103"/>
+      <c r="AG19" s="103"/>
+      <c r="AI19" s="103"/>
+      <c r="AJ19" s="126"/>
     </row>
     <row r="20" spans="1:36" ht="3.75" customHeight="1">
-      <c r="A20" s="102"/>
-      <c r="B20" s="103"/>
-      <c r="C20" s="103"/>
-      <c r="D20" s="103"/>
-      <c r="E20" s="103"/>
-      <c r="F20" s="103"/>
-      <c r="G20" s="103"/>
-      <c r="H20" s="103"/>
-      <c r="I20" s="103"/>
-      <c r="J20" s="103"/>
-      <c r="K20" s="103"/>
-      <c r="L20" s="103"/>
-      <c r="M20" s="103"/>
-      <c r="N20" s="103"/>
-      <c r="O20" s="103"/>
-      <c r="P20" s="103"/>
-      <c r="Q20" s="103"/>
-      <c r="R20" s="103"/>
-      <c r="S20" s="103"/>
-      <c r="T20" s="104"/>
+      <c r="A20" s="123"/>
+      <c r="B20" s="124"/>
+      <c r="C20" s="124"/>
+      <c r="D20" s="124"/>
+      <c r="E20" s="124"/>
+      <c r="F20" s="124"/>
+      <c r="G20" s="124"/>
+      <c r="H20" s="124"/>
+      <c r="I20" s="124"/>
+      <c r="J20" s="124"/>
+      <c r="K20" s="124"/>
+      <c r="L20" s="124"/>
+      <c r="M20" s="124"/>
+      <c r="N20" s="124"/>
+      <c r="O20" s="124"/>
+      <c r="P20" s="124"/>
+      <c r="Q20" s="124"/>
+      <c r="R20" s="124"/>
+      <c r="S20" s="124"/>
+      <c r="T20" s="125"/>
       <c r="U20" s="27"/>
       <c r="V20" s="16"/>
       <c r="W20" s="7"/>
@@ -7856,80 +7867,80 @@
       <c r="AJ21" s="47"/>
     </row>
     <row r="22" spans="1:36" ht="16.5" customHeight="1">
-      <c r="A22" s="93"/>
-      <c r="B22" s="94"/>
-      <c r="C22" s="94"/>
-      <c r="D22" s="94"/>
-      <c r="E22" s="94"/>
-      <c r="F22" s="94"/>
-      <c r="G22" s="94"/>
-      <c r="H22" s="94"/>
-      <c r="I22" s="94"/>
-      <c r="J22" s="94"/>
-      <c r="K22" s="94"/>
-      <c r="L22" s="94"/>
-      <c r="M22" s="94"/>
-      <c r="N22" s="94"/>
-      <c r="O22" s="94"/>
-      <c r="P22" s="94"/>
-      <c r="Q22" s="94"/>
-      <c r="R22" s="94"/>
-      <c r="S22" s="94"/>
-      <c r="T22" s="94"/>
-      <c r="U22" s="94"/>
-      <c r="V22" s="94"/>
-      <c r="W22" s="94"/>
-      <c r="X22" s="94"/>
-      <c r="Y22" s="94"/>
-      <c r="Z22" s="94"/>
-      <c r="AA22" s="94"/>
-      <c r="AB22" s="94"/>
-      <c r="AC22" s="94"/>
-      <c r="AD22" s="94"/>
-      <c r="AE22" s="94"/>
-      <c r="AF22" s="94"/>
-      <c r="AG22" s="94"/>
-      <c r="AH22" s="94"/>
-      <c r="AI22" s="94"/>
-      <c r="AJ22" s="95"/>
+      <c r="A22" s="114"/>
+      <c r="B22" s="115"/>
+      <c r="C22" s="115"/>
+      <c r="D22" s="115"/>
+      <c r="E22" s="115"/>
+      <c r="F22" s="115"/>
+      <c r="G22" s="115"/>
+      <c r="H22" s="115"/>
+      <c r="I22" s="115"/>
+      <c r="J22" s="115"/>
+      <c r="K22" s="115"/>
+      <c r="L22" s="115"/>
+      <c r="M22" s="115"/>
+      <c r="N22" s="115"/>
+      <c r="O22" s="115"/>
+      <c r="P22" s="115"/>
+      <c r="Q22" s="115"/>
+      <c r="R22" s="115"/>
+      <c r="S22" s="115"/>
+      <c r="T22" s="115"/>
+      <c r="U22" s="115"/>
+      <c r="V22" s="115"/>
+      <c r="W22" s="115"/>
+      <c r="X22" s="115"/>
+      <c r="Y22" s="115"/>
+      <c r="Z22" s="115"/>
+      <c r="AA22" s="115"/>
+      <c r="AB22" s="115"/>
+      <c r="AC22" s="115"/>
+      <c r="AD22" s="115"/>
+      <c r="AE22" s="115"/>
+      <c r="AF22" s="115"/>
+      <c r="AG22" s="115"/>
+      <c r="AH22" s="115"/>
+      <c r="AI22" s="115"/>
+      <c r="AJ22" s="116"/>
     </row>
     <row r="23" spans="1:36" ht="16.5" customHeight="1">
-      <c r="A23" s="96"/>
-      <c r="B23" s="97"/>
-      <c r="C23" s="97"/>
-      <c r="D23" s="97"/>
-      <c r="E23" s="97"/>
-      <c r="F23" s="97"/>
-      <c r="G23" s="97"/>
-      <c r="H23" s="97"/>
-      <c r="I23" s="97"/>
-      <c r="J23" s="97"/>
-      <c r="K23" s="97"/>
-      <c r="L23" s="97"/>
-      <c r="M23" s="97"/>
-      <c r="N23" s="97"/>
-      <c r="O23" s="97"/>
-      <c r="P23" s="97"/>
-      <c r="Q23" s="97"/>
-      <c r="R23" s="97"/>
-      <c r="S23" s="97"/>
-      <c r="T23" s="97"/>
-      <c r="U23" s="97"/>
-      <c r="V23" s="97"/>
-      <c r="W23" s="97"/>
-      <c r="X23" s="97"/>
-      <c r="Y23" s="97"/>
-      <c r="Z23" s="97"/>
-      <c r="AA23" s="97"/>
-      <c r="AB23" s="97"/>
-      <c r="AC23" s="97"/>
-      <c r="AD23" s="97"/>
-      <c r="AE23" s="97"/>
-      <c r="AF23" s="97"/>
-      <c r="AG23" s="97"/>
-      <c r="AH23" s="97"/>
-      <c r="AI23" s="97"/>
-      <c r="AJ23" s="98"/>
+      <c r="A23" s="117"/>
+      <c r="B23" s="118"/>
+      <c r="C23" s="118"/>
+      <c r="D23" s="118"/>
+      <c r="E23" s="118"/>
+      <c r="F23" s="118"/>
+      <c r="G23" s="118"/>
+      <c r="H23" s="118"/>
+      <c r="I23" s="118"/>
+      <c r="J23" s="118"/>
+      <c r="K23" s="118"/>
+      <c r="L23" s="118"/>
+      <c r="M23" s="118"/>
+      <c r="N23" s="118"/>
+      <c r="O23" s="118"/>
+      <c r="P23" s="118"/>
+      <c r="Q23" s="118"/>
+      <c r="R23" s="118"/>
+      <c r="S23" s="118"/>
+      <c r="T23" s="118"/>
+      <c r="U23" s="118"/>
+      <c r="V23" s="118"/>
+      <c r="W23" s="118"/>
+      <c r="X23" s="118"/>
+      <c r="Y23" s="118"/>
+      <c r="Z23" s="118"/>
+      <c r="AA23" s="118"/>
+      <c r="AB23" s="118"/>
+      <c r="AC23" s="118"/>
+      <c r="AD23" s="118"/>
+      <c r="AE23" s="118"/>
+      <c r="AF23" s="118"/>
+      <c r="AG23" s="118"/>
+      <c r="AH23" s="118"/>
+      <c r="AI23" s="118"/>
+      <c r="AJ23" s="119"/>
     </row>
     <row r="24" spans="1:36" ht="12.75" customHeight="1">
       <c r="A24" s="46" t="s">
@@ -7972,42 +7983,42 @@
       <c r="AJ24" s="47"/>
     </row>
     <row r="25" spans="1:36" ht="18" customHeight="1">
-      <c r="A25" s="90"/>
-      <c r="B25" s="91"/>
-      <c r="C25" s="91"/>
-      <c r="D25" s="91"/>
-      <c r="E25" s="91"/>
-      <c r="F25" s="91"/>
-      <c r="G25" s="91"/>
-      <c r="H25" s="91"/>
-      <c r="I25" s="91"/>
-      <c r="J25" s="91"/>
-      <c r="K25" s="91"/>
-      <c r="L25" s="91"/>
-      <c r="M25" s="91"/>
-      <c r="N25" s="91"/>
-      <c r="O25" s="91"/>
-      <c r="P25" s="91"/>
-      <c r="Q25" s="91"/>
-      <c r="R25" s="91"/>
-      <c r="S25" s="91"/>
-      <c r="T25" s="91"/>
-      <c r="U25" s="91"/>
-      <c r="V25" s="91"/>
-      <c r="W25" s="91"/>
-      <c r="X25" s="91"/>
-      <c r="Y25" s="91"/>
-      <c r="Z25" s="91"/>
-      <c r="AA25" s="91"/>
-      <c r="AB25" s="91"/>
-      <c r="AC25" s="91"/>
-      <c r="AD25" s="91"/>
-      <c r="AE25" s="91"/>
-      <c r="AF25" s="91"/>
-      <c r="AG25" s="91"/>
-      <c r="AH25" s="91"/>
-      <c r="AI25" s="91"/>
-      <c r="AJ25" s="92"/>
+      <c r="A25" s="111"/>
+      <c r="B25" s="112"/>
+      <c r="C25" s="112"/>
+      <c r="D25" s="112"/>
+      <c r="E25" s="112"/>
+      <c r="F25" s="112"/>
+      <c r="G25" s="112"/>
+      <c r="H25" s="112"/>
+      <c r="I25" s="112"/>
+      <c r="J25" s="112"/>
+      <c r="K25" s="112"/>
+      <c r="L25" s="112"/>
+      <c r="M25" s="112"/>
+      <c r="N25" s="112"/>
+      <c r="O25" s="112"/>
+      <c r="P25" s="112"/>
+      <c r="Q25" s="112"/>
+      <c r="R25" s="112"/>
+      <c r="S25" s="112"/>
+      <c r="T25" s="112"/>
+      <c r="U25" s="112"/>
+      <c r="V25" s="112"/>
+      <c r="W25" s="112"/>
+      <c r="X25" s="112"/>
+      <c r="Y25" s="112"/>
+      <c r="Z25" s="112"/>
+      <c r="AA25" s="112"/>
+      <c r="AB25" s="112"/>
+      <c r="AC25" s="112"/>
+      <c r="AD25" s="112"/>
+      <c r="AE25" s="112"/>
+      <c r="AF25" s="112"/>
+      <c r="AG25" s="112"/>
+      <c r="AH25" s="112"/>
+      <c r="AI25" s="112"/>
+      <c r="AJ25" s="113"/>
     </row>
     <row r="26" spans="1:36" ht="12.75" customHeight="1">
       <c r="A26" s="46" t="s">
@@ -8050,137 +8061,137 @@
       <c r="AJ26" s="47"/>
     </row>
     <row r="27" spans="1:36" ht="15" customHeight="1">
-      <c r="A27" s="149"/>
-      <c r="B27" s="150"/>
-      <c r="C27" s="150"/>
-      <c r="D27" s="150"/>
-      <c r="E27" s="150"/>
-      <c r="F27" s="150"/>
-      <c r="G27" s="150"/>
-      <c r="H27" s="150"/>
-      <c r="I27" s="150"/>
-      <c r="J27" s="150"/>
-      <c r="K27" s="150"/>
-      <c r="L27" s="150"/>
-      <c r="M27" s="150"/>
-      <c r="N27" s="150"/>
-      <c r="O27" s="150"/>
-      <c r="P27" s="150"/>
-      <c r="Q27" s="150"/>
-      <c r="R27" s="150"/>
-      <c r="S27" s="150"/>
-      <c r="T27" s="150"/>
-      <c r="U27" s="150"/>
-      <c r="V27" s="150"/>
-      <c r="W27" s="150"/>
-      <c r="X27" s="150"/>
-      <c r="Y27" s="150"/>
-      <c r="Z27" s="150"/>
-      <c r="AA27" s="150"/>
-      <c r="AB27" s="150"/>
-      <c r="AC27" s="150"/>
-      <c r="AD27" s="150"/>
-      <c r="AE27" s="150"/>
-      <c r="AF27" s="150"/>
-      <c r="AG27" s="150"/>
-      <c r="AH27" s="150"/>
-      <c r="AI27" s="150"/>
-      <c r="AJ27" s="151"/>
+      <c r="A27" s="62"/>
+      <c r="B27" s="63"/>
+      <c r="C27" s="63"/>
+      <c r="D27" s="63"/>
+      <c r="E27" s="63"/>
+      <c r="F27" s="63"/>
+      <c r="G27" s="63"/>
+      <c r="H27" s="63"/>
+      <c r="I27" s="63"/>
+      <c r="J27" s="63"/>
+      <c r="K27" s="63"/>
+      <c r="L27" s="63"/>
+      <c r="M27" s="63"/>
+      <c r="N27" s="63"/>
+      <c r="O27" s="63"/>
+      <c r="P27" s="63"/>
+      <c r="Q27" s="63"/>
+      <c r="R27" s="63"/>
+      <c r="S27" s="63"/>
+      <c r="T27" s="63"/>
+      <c r="U27" s="63"/>
+      <c r="V27" s="63"/>
+      <c r="W27" s="63"/>
+      <c r="X27" s="63"/>
+      <c r="Y27" s="63"/>
+      <c r="Z27" s="63"/>
+      <c r="AA27" s="63"/>
+      <c r="AB27" s="63"/>
+      <c r="AC27" s="63"/>
+      <c r="AD27" s="63"/>
+      <c r="AE27" s="63"/>
+      <c r="AF27" s="63"/>
+      <c r="AG27" s="63"/>
+      <c r="AH27" s="63"/>
+      <c r="AI27" s="63"/>
+      <c r="AJ27" s="64"/>
     </row>
     <row r="28" spans="1:36" ht="15" customHeight="1">
-      <c r="A28" s="152"/>
-      <c r="B28" s="150"/>
-      <c r="C28" s="150"/>
-      <c r="D28" s="150"/>
-      <c r="E28" s="150"/>
-      <c r="F28" s="150"/>
-      <c r="G28" s="150"/>
-      <c r="H28" s="150"/>
-      <c r="I28" s="150"/>
-      <c r="J28" s="150"/>
-      <c r="K28" s="150"/>
-      <c r="L28" s="150"/>
-      <c r="M28" s="150"/>
-      <c r="N28" s="150"/>
-      <c r="O28" s="150"/>
-      <c r="P28" s="150"/>
-      <c r="Q28" s="150"/>
-      <c r="R28" s="150"/>
-      <c r="S28" s="150"/>
-      <c r="T28" s="150"/>
-      <c r="U28" s="150"/>
-      <c r="V28" s="150"/>
-      <c r="W28" s="150"/>
-      <c r="X28" s="150"/>
-      <c r="Y28" s="150"/>
-      <c r="Z28" s="150"/>
-      <c r="AA28" s="150"/>
-      <c r="AB28" s="150"/>
-      <c r="AC28" s="150"/>
-      <c r="AD28" s="150"/>
-      <c r="AE28" s="150"/>
-      <c r="AF28" s="150"/>
-      <c r="AG28" s="150"/>
-      <c r="AH28" s="150"/>
-      <c r="AI28" s="150"/>
-      <c r="AJ28" s="151"/>
+      <c r="A28" s="65"/>
+      <c r="B28" s="63"/>
+      <c r="C28" s="63"/>
+      <c r="D28" s="63"/>
+      <c r="E28" s="63"/>
+      <c r="F28" s="63"/>
+      <c r="G28" s="63"/>
+      <c r="H28" s="63"/>
+      <c r="I28" s="63"/>
+      <c r="J28" s="63"/>
+      <c r="K28" s="63"/>
+      <c r="L28" s="63"/>
+      <c r="M28" s="63"/>
+      <c r="N28" s="63"/>
+      <c r="O28" s="63"/>
+      <c r="P28" s="63"/>
+      <c r="Q28" s="63"/>
+      <c r="R28" s="63"/>
+      <c r="S28" s="63"/>
+      <c r="T28" s="63"/>
+      <c r="U28" s="63"/>
+      <c r="V28" s="63"/>
+      <c r="W28" s="63"/>
+      <c r="X28" s="63"/>
+      <c r="Y28" s="63"/>
+      <c r="Z28" s="63"/>
+      <c r="AA28" s="63"/>
+      <c r="AB28" s="63"/>
+      <c r="AC28" s="63"/>
+      <c r="AD28" s="63"/>
+      <c r="AE28" s="63"/>
+      <c r="AF28" s="63"/>
+      <c r="AG28" s="63"/>
+      <c r="AH28" s="63"/>
+      <c r="AI28" s="63"/>
+      <c r="AJ28" s="64"/>
     </row>
-    <row r="29" spans="1:36" ht="217.2" customHeight="1">
-      <c r="A29" s="153"/>
-      <c r="B29" s="154"/>
-      <c r="C29" s="154"/>
-      <c r="D29" s="154"/>
-      <c r="E29" s="154"/>
-      <c r="F29" s="154"/>
-      <c r="G29" s="154"/>
-      <c r="H29" s="154"/>
-      <c r="I29" s="154"/>
-      <c r="J29" s="154"/>
-      <c r="K29" s="154"/>
-      <c r="L29" s="154"/>
-      <c r="M29" s="154"/>
-      <c r="N29" s="154"/>
-      <c r="O29" s="154"/>
-      <c r="P29" s="154"/>
-      <c r="Q29" s="154"/>
-      <c r="R29" s="154"/>
-      <c r="S29" s="154"/>
-      <c r="T29" s="154"/>
-      <c r="U29" s="154"/>
-      <c r="V29" s="154"/>
-      <c r="W29" s="154"/>
-      <c r="X29" s="154"/>
-      <c r="Y29" s="154"/>
-      <c r="Z29" s="154"/>
-      <c r="AA29" s="154"/>
-      <c r="AB29" s="154"/>
-      <c r="AC29" s="154"/>
-      <c r="AD29" s="154"/>
-      <c r="AE29" s="154"/>
-      <c r="AF29" s="154"/>
-      <c r="AG29" s="154"/>
-      <c r="AH29" s="154"/>
-      <c r="AI29" s="154"/>
-      <c r="AJ29" s="155"/>
+    <row r="29" spans="1:36" ht="100.8" customHeight="1">
+      <c r="A29" s="66"/>
+      <c r="B29" s="67"/>
+      <c r="C29" s="67"/>
+      <c r="D29" s="67"/>
+      <c r="E29" s="67"/>
+      <c r="F29" s="67"/>
+      <c r="G29" s="67"/>
+      <c r="H29" s="67"/>
+      <c r="I29" s="67"/>
+      <c r="J29" s="67"/>
+      <c r="K29" s="67"/>
+      <c r="L29" s="67"/>
+      <c r="M29" s="67"/>
+      <c r="N29" s="67"/>
+      <c r="O29" s="67"/>
+      <c r="P29" s="67"/>
+      <c r="Q29" s="67"/>
+      <c r="R29" s="67"/>
+      <c r="S29" s="67"/>
+      <c r="T29" s="67"/>
+      <c r="U29" s="67"/>
+      <c r="V29" s="67"/>
+      <c r="W29" s="67"/>
+      <c r="X29" s="67"/>
+      <c r="Y29" s="67"/>
+      <c r="Z29" s="67"/>
+      <c r="AA29" s="67"/>
+      <c r="AB29" s="67"/>
+      <c r="AC29" s="67"/>
+      <c r="AD29" s="67"/>
+      <c r="AE29" s="67"/>
+      <c r="AF29" s="67"/>
+      <c r="AG29" s="67"/>
+      <c r="AH29" s="67"/>
+      <c r="AI29" s="67"/>
+      <c r="AJ29" s="68"/>
     </row>
     <row r="30" spans="1:36" ht="12.75" customHeight="1">
-      <c r="A30" s="156" t="s">
+      <c r="A30" s="75" t="s">
         <v>17</v>
       </c>
-      <c r="B30" s="157"/>
-      <c r="C30" s="157"/>
-      <c r="D30" s="157"/>
-      <c r="E30" s="157"/>
-      <c r="F30" s="157"/>
-      <c r="G30" s="157"/>
-      <c r="H30" s="157"/>
-      <c r="I30" s="157"/>
-      <c r="J30" s="157"/>
-      <c r="K30" s="157"/>
-      <c r="L30" s="157"/>
-      <c r="M30" s="157"/>
-      <c r="N30" s="157"/>
-      <c r="O30" s="157"/>
+      <c r="B30" s="76"/>
+      <c r="C30" s="76"/>
+      <c r="D30" s="76"/>
+      <c r="E30" s="76"/>
+      <c r="F30" s="76"/>
+      <c r="G30" s="76"/>
+      <c r="H30" s="76"/>
+      <c r="I30" s="76"/>
+      <c r="J30" s="76"/>
+      <c r="K30" s="76"/>
+      <c r="L30" s="76"/>
+      <c r="M30" s="76"/>
+      <c r="N30" s="76"/>
+      <c r="O30" s="76"/>
       <c r="P30" s="41"/>
       <c r="Q30" s="41"/>
       <c r="R30" s="41"/>
@@ -8204,216 +8215,216 @@
       <c r="AJ30" s="42"/>
     </row>
     <row r="31" spans="1:36" ht="16.5" customHeight="1">
-      <c r="A31" s="149"/>
-      <c r="B31" s="159"/>
-      <c r="C31" s="159"/>
-      <c r="D31" s="159"/>
-      <c r="E31" s="159"/>
-      <c r="F31" s="159"/>
-      <c r="G31" s="159"/>
-      <c r="H31" s="159"/>
-      <c r="I31" s="159"/>
-      <c r="J31" s="159"/>
-      <c r="K31" s="159"/>
-      <c r="L31" s="159"/>
-      <c r="M31" s="159"/>
-      <c r="N31" s="159"/>
-      <c r="O31" s="159"/>
-      <c r="P31" s="159"/>
-      <c r="Q31" s="159"/>
-      <c r="R31" s="159"/>
-      <c r="S31" s="159"/>
-      <c r="T31" s="159"/>
-      <c r="U31" s="159"/>
-      <c r="V31" s="159"/>
-      <c r="W31" s="159"/>
-      <c r="X31" s="159"/>
-      <c r="Y31" s="159"/>
-      <c r="Z31" s="159"/>
-      <c r="AA31" s="159"/>
-      <c r="AB31" s="159"/>
-      <c r="AC31" s="159"/>
-      <c r="AD31" s="159"/>
-      <c r="AE31" s="159"/>
-      <c r="AF31" s="159"/>
-      <c r="AG31" s="159"/>
-      <c r="AH31" s="159"/>
-      <c r="AI31" s="159"/>
-      <c r="AJ31" s="160"/>
+      <c r="A31" s="62"/>
+      <c r="B31" s="79"/>
+      <c r="C31" s="79"/>
+      <c r="D31" s="79"/>
+      <c r="E31" s="79"/>
+      <c r="F31" s="79"/>
+      <c r="G31" s="79"/>
+      <c r="H31" s="79"/>
+      <c r="I31" s="79"/>
+      <c r="J31" s="79"/>
+      <c r="K31" s="79"/>
+      <c r="L31" s="79"/>
+      <c r="M31" s="79"/>
+      <c r="N31" s="79"/>
+      <c r="O31" s="79"/>
+      <c r="P31" s="79"/>
+      <c r="Q31" s="79"/>
+      <c r="R31" s="79"/>
+      <c r="S31" s="79"/>
+      <c r="T31" s="79"/>
+      <c r="U31" s="79"/>
+      <c r="V31" s="79"/>
+      <c r="W31" s="79"/>
+      <c r="X31" s="79"/>
+      <c r="Y31" s="79"/>
+      <c r="Z31" s="79"/>
+      <c r="AA31" s="79"/>
+      <c r="AB31" s="79"/>
+      <c r="AC31" s="79"/>
+      <c r="AD31" s="79"/>
+      <c r="AE31" s="79"/>
+      <c r="AF31" s="79"/>
+      <c r="AG31" s="79"/>
+      <c r="AH31" s="79"/>
+      <c r="AI31" s="79"/>
+      <c r="AJ31" s="80"/>
     </row>
     <row r="32" spans="1:36" ht="16.5" customHeight="1">
-      <c r="A32" s="149"/>
-      <c r="B32" s="159"/>
-      <c r="C32" s="159"/>
-      <c r="D32" s="159"/>
-      <c r="E32" s="159"/>
-      <c r="F32" s="159"/>
-      <c r="G32" s="159"/>
-      <c r="H32" s="159"/>
-      <c r="I32" s="159"/>
-      <c r="J32" s="159"/>
-      <c r="K32" s="159"/>
-      <c r="L32" s="159"/>
-      <c r="M32" s="159"/>
-      <c r="N32" s="159"/>
-      <c r="O32" s="159"/>
-      <c r="P32" s="159"/>
-      <c r="Q32" s="159"/>
-      <c r="R32" s="159"/>
-      <c r="S32" s="159"/>
-      <c r="T32" s="159"/>
-      <c r="U32" s="159"/>
-      <c r="V32" s="159"/>
-      <c r="W32" s="159"/>
-      <c r="X32" s="159"/>
-      <c r="Y32" s="159"/>
-      <c r="Z32" s="159"/>
-      <c r="AA32" s="159"/>
-      <c r="AB32" s="159"/>
-      <c r="AC32" s="159"/>
-      <c r="AD32" s="159"/>
-      <c r="AE32" s="159"/>
-      <c r="AF32" s="159"/>
-      <c r="AG32" s="159"/>
-      <c r="AH32" s="159"/>
-      <c r="AI32" s="159"/>
-      <c r="AJ32" s="160"/>
+      <c r="A32" s="62"/>
+      <c r="B32" s="79"/>
+      <c r="C32" s="79"/>
+      <c r="D32" s="79"/>
+      <c r="E32" s="79"/>
+      <c r="F32" s="79"/>
+      <c r="G32" s="79"/>
+      <c r="H32" s="79"/>
+      <c r="I32" s="79"/>
+      <c r="J32" s="79"/>
+      <c r="K32" s="79"/>
+      <c r="L32" s="79"/>
+      <c r="M32" s="79"/>
+      <c r="N32" s="79"/>
+      <c r="O32" s="79"/>
+      <c r="P32" s="79"/>
+      <c r="Q32" s="79"/>
+      <c r="R32" s="79"/>
+      <c r="S32" s="79"/>
+      <c r="T32" s="79"/>
+      <c r="U32" s="79"/>
+      <c r="V32" s="79"/>
+      <c r="W32" s="79"/>
+      <c r="X32" s="79"/>
+      <c r="Y32" s="79"/>
+      <c r="Z32" s="79"/>
+      <c r="AA32" s="79"/>
+      <c r="AB32" s="79"/>
+      <c r="AC32" s="79"/>
+      <c r="AD32" s="79"/>
+      <c r="AE32" s="79"/>
+      <c r="AF32" s="79"/>
+      <c r="AG32" s="79"/>
+      <c r="AH32" s="79"/>
+      <c r="AI32" s="79"/>
+      <c r="AJ32" s="80"/>
     </row>
     <row r="33" spans="1:36" ht="16.5" customHeight="1">
-      <c r="A33" s="149"/>
-      <c r="B33" s="159"/>
-      <c r="C33" s="159"/>
-      <c r="D33" s="159"/>
-      <c r="E33" s="159"/>
-      <c r="F33" s="159"/>
-      <c r="G33" s="159"/>
-      <c r="H33" s="159"/>
-      <c r="I33" s="159"/>
-      <c r="J33" s="159"/>
-      <c r="K33" s="159"/>
-      <c r="L33" s="159"/>
-      <c r="M33" s="159"/>
-      <c r="N33" s="159"/>
-      <c r="O33" s="159"/>
-      <c r="P33" s="159"/>
-      <c r="Q33" s="159"/>
-      <c r="R33" s="159"/>
-      <c r="S33" s="159"/>
-      <c r="T33" s="159"/>
-      <c r="U33" s="159"/>
-      <c r="V33" s="159"/>
-      <c r="W33" s="159"/>
-      <c r="X33" s="159"/>
-      <c r="Y33" s="159"/>
-      <c r="Z33" s="159"/>
-      <c r="AA33" s="159"/>
-      <c r="AB33" s="159"/>
-      <c r="AC33" s="159"/>
-      <c r="AD33" s="159"/>
-      <c r="AE33" s="159"/>
-      <c r="AF33" s="159"/>
-      <c r="AG33" s="159"/>
-      <c r="AH33" s="159"/>
-      <c r="AI33" s="159"/>
-      <c r="AJ33" s="160"/>
+      <c r="A33" s="62"/>
+      <c r="B33" s="79"/>
+      <c r="C33" s="79"/>
+      <c r="D33" s="79"/>
+      <c r="E33" s="79"/>
+      <c r="F33" s="79"/>
+      <c r="G33" s="79"/>
+      <c r="H33" s="79"/>
+      <c r="I33" s="79"/>
+      <c r="J33" s="79"/>
+      <c r="K33" s="79"/>
+      <c r="L33" s="79"/>
+      <c r="M33" s="79"/>
+      <c r="N33" s="79"/>
+      <c r="O33" s="79"/>
+      <c r="P33" s="79"/>
+      <c r="Q33" s="79"/>
+      <c r="R33" s="79"/>
+      <c r="S33" s="79"/>
+      <c r="T33" s="79"/>
+      <c r="U33" s="79"/>
+      <c r="V33" s="79"/>
+      <c r="W33" s="79"/>
+      <c r="X33" s="79"/>
+      <c r="Y33" s="79"/>
+      <c r="Z33" s="79"/>
+      <c r="AA33" s="79"/>
+      <c r="AB33" s="79"/>
+      <c r="AC33" s="79"/>
+      <c r="AD33" s="79"/>
+      <c r="AE33" s="79"/>
+      <c r="AF33" s="79"/>
+      <c r="AG33" s="79"/>
+      <c r="AH33" s="79"/>
+      <c r="AI33" s="79"/>
+      <c r="AJ33" s="80"/>
     </row>
     <row r="34" spans="1:36" ht="61.8" customHeight="1">
-      <c r="A34" s="149"/>
-      <c r="B34" s="159"/>
-      <c r="C34" s="159"/>
-      <c r="D34" s="159"/>
-      <c r="E34" s="159"/>
-      <c r="F34" s="159"/>
-      <c r="G34" s="159"/>
-      <c r="H34" s="159"/>
-      <c r="I34" s="159"/>
-      <c r="J34" s="159"/>
-      <c r="K34" s="159"/>
-      <c r="L34" s="159"/>
-      <c r="M34" s="159"/>
-      <c r="N34" s="159"/>
-      <c r="O34" s="159"/>
-      <c r="P34" s="159"/>
-      <c r="Q34" s="159"/>
-      <c r="R34" s="159"/>
-      <c r="S34" s="159"/>
-      <c r="T34" s="159"/>
-      <c r="U34" s="159"/>
-      <c r="V34" s="159"/>
-      <c r="W34" s="159"/>
-      <c r="X34" s="159"/>
-      <c r="Y34" s="159"/>
-      <c r="Z34" s="159"/>
-      <c r="AA34" s="159"/>
-      <c r="AB34" s="159"/>
-      <c r="AC34" s="159"/>
-      <c r="AD34" s="159"/>
-      <c r="AE34" s="159"/>
-      <c r="AF34" s="159"/>
-      <c r="AG34" s="159"/>
-      <c r="AH34" s="159"/>
-      <c r="AI34" s="159"/>
-      <c r="AJ34" s="160"/>
+      <c r="A34" s="62"/>
+      <c r="B34" s="79"/>
+      <c r="C34" s="79"/>
+      <c r="D34" s="79"/>
+      <c r="E34" s="79"/>
+      <c r="F34" s="79"/>
+      <c r="G34" s="79"/>
+      <c r="H34" s="79"/>
+      <c r="I34" s="79"/>
+      <c r="J34" s="79"/>
+      <c r="K34" s="79"/>
+      <c r="L34" s="79"/>
+      <c r="M34" s="79"/>
+      <c r="N34" s="79"/>
+      <c r="O34" s="79"/>
+      <c r="P34" s="79"/>
+      <c r="Q34" s="79"/>
+      <c r="R34" s="79"/>
+      <c r="S34" s="79"/>
+      <c r="T34" s="79"/>
+      <c r="U34" s="79"/>
+      <c r="V34" s="79"/>
+      <c r="W34" s="79"/>
+      <c r="X34" s="79"/>
+      <c r="Y34" s="79"/>
+      <c r="Z34" s="79"/>
+      <c r="AA34" s="79"/>
+      <c r="AB34" s="79"/>
+      <c r="AC34" s="79"/>
+      <c r="AD34" s="79"/>
+      <c r="AE34" s="79"/>
+      <c r="AF34" s="79"/>
+      <c r="AG34" s="79"/>
+      <c r="AH34" s="79"/>
+      <c r="AI34" s="79"/>
+      <c r="AJ34" s="80"/>
     </row>
     <row r="35" spans="1:36" ht="13.2" customHeight="1">
-      <c r="A35" s="161"/>
-      <c r="B35" s="162"/>
-      <c r="C35" s="162"/>
-      <c r="D35" s="162"/>
-      <c r="E35" s="162"/>
-      <c r="F35" s="162"/>
-      <c r="G35" s="162"/>
-      <c r="H35" s="162"/>
-      <c r="I35" s="162"/>
-      <c r="J35" s="162"/>
-      <c r="K35" s="162"/>
-      <c r="L35" s="162"/>
-      <c r="M35" s="162"/>
-      <c r="N35" s="162"/>
-      <c r="O35" s="162"/>
-      <c r="P35" s="162"/>
-      <c r="Q35" s="162"/>
-      <c r="R35" s="162"/>
-      <c r="S35" s="162"/>
-      <c r="T35" s="162"/>
-      <c r="U35" s="162"/>
-      <c r="V35" s="162"/>
-      <c r="W35" s="162"/>
-      <c r="X35" s="162"/>
-      <c r="Y35" s="162"/>
-      <c r="Z35" s="162"/>
-      <c r="AA35" s="162"/>
-      <c r="AB35" s="162"/>
-      <c r="AC35" s="162"/>
-      <c r="AD35" s="162"/>
-      <c r="AE35" s="162"/>
-      <c r="AF35" s="162"/>
-      <c r="AG35" s="162"/>
-      <c r="AH35" s="162"/>
-      <c r="AI35" s="162"/>
-      <c r="AJ35" s="163"/>
+      <c r="A35" s="81"/>
+      <c r="B35" s="82"/>
+      <c r="C35" s="82"/>
+      <c r="D35" s="82"/>
+      <c r="E35" s="82"/>
+      <c r="F35" s="82"/>
+      <c r="G35" s="82"/>
+      <c r="H35" s="82"/>
+      <c r="I35" s="82"/>
+      <c r="J35" s="82"/>
+      <c r="K35" s="82"/>
+      <c r="L35" s="82"/>
+      <c r="M35" s="82"/>
+      <c r="N35" s="82"/>
+      <c r="O35" s="82"/>
+      <c r="P35" s="82"/>
+      <c r="Q35" s="82"/>
+      <c r="R35" s="82"/>
+      <c r="S35" s="82"/>
+      <c r="T35" s="82"/>
+      <c r="U35" s="82"/>
+      <c r="V35" s="82"/>
+      <c r="W35" s="82"/>
+      <c r="X35" s="82"/>
+      <c r="Y35" s="82"/>
+      <c r="Z35" s="82"/>
+      <c r="AA35" s="82"/>
+      <c r="AB35" s="82"/>
+      <c r="AC35" s="82"/>
+      <c r="AD35" s="82"/>
+      <c r="AE35" s="82"/>
+      <c r="AF35" s="82"/>
+      <c r="AG35" s="82"/>
+      <c r="AH35" s="82"/>
+      <c r="AI35" s="82"/>
+      <c r="AJ35" s="83"/>
     </row>
     <row r="36" spans="1:36" ht="13.5" customHeight="1">
-      <c r="A36" s="82" t="s">
+      <c r="A36" s="69" t="s">
         <v>94</v>
       </c>
-      <c r="B36" s="83"/>
-      <c r="C36" s="83"/>
-      <c r="D36" s="83"/>
-      <c r="E36" s="83"/>
-      <c r="F36" s="83"/>
-      <c r="G36" s="83"/>
-      <c r="H36" s="83"/>
-      <c r="I36" s="83"/>
-      <c r="J36" s="83"/>
-      <c r="K36" s="83"/>
-      <c r="L36" s="83"/>
-      <c r="M36" s="83"/>
-      <c r="N36" s="83"/>
-      <c r="O36" s="83"/>
-      <c r="P36" s="83"/>
-      <c r="Q36" s="83"/>
-      <c r="R36" s="83"/>
+      <c r="B36" s="70"/>
+      <c r="C36" s="70"/>
+      <c r="D36" s="70"/>
+      <c r="E36" s="70"/>
+      <c r="F36" s="70"/>
+      <c r="G36" s="70"/>
+      <c r="H36" s="70"/>
+      <c r="I36" s="70"/>
+      <c r="J36" s="70"/>
+      <c r="K36" s="70"/>
+      <c r="L36" s="70"/>
+      <c r="M36" s="70"/>
+      <c r="N36" s="70"/>
+      <c r="O36" s="70"/>
+      <c r="P36" s="70"/>
+      <c r="Q36" s="70"/>
+      <c r="R36" s="70"/>
       <c r="S36" s="40"/>
       <c r="T36" s="40"/>
       <c r="U36" s="40"/>
@@ -8434,178 +8445,178 @@
       <c r="AJ36" s="43"/>
     </row>
     <row r="37" spans="1:36" ht="14.25" customHeight="1">
-      <c r="A37" s="149"/>
-      <c r="B37" s="159"/>
-      <c r="C37" s="159"/>
-      <c r="D37" s="159"/>
-      <c r="E37" s="159"/>
-      <c r="F37" s="159"/>
-      <c r="G37" s="159"/>
-      <c r="H37" s="159"/>
-      <c r="I37" s="159"/>
-      <c r="J37" s="159"/>
-      <c r="K37" s="159"/>
-      <c r="L37" s="159"/>
-      <c r="M37" s="159"/>
-      <c r="N37" s="159"/>
-      <c r="O37" s="159"/>
-      <c r="P37" s="159"/>
-      <c r="Q37" s="159"/>
-      <c r="R37" s="159"/>
-      <c r="S37" s="159"/>
-      <c r="T37" s="159"/>
-      <c r="U37" s="159"/>
-      <c r="V37" s="159"/>
-      <c r="W37" s="159"/>
-      <c r="X37" s="159"/>
-      <c r="Y37" s="159"/>
-      <c r="Z37" s="159"/>
-      <c r="AA37" s="159"/>
-      <c r="AB37" s="159"/>
-      <c r="AC37" s="159"/>
-      <c r="AD37" s="159"/>
-      <c r="AE37" s="159"/>
-      <c r="AF37" s="159"/>
-      <c r="AG37" s="159"/>
-      <c r="AH37" s="159"/>
-      <c r="AI37" s="159"/>
-      <c r="AJ37" s="160"/>
+      <c r="A37" s="62"/>
+      <c r="B37" s="79"/>
+      <c r="C37" s="79"/>
+      <c r="D37" s="79"/>
+      <c r="E37" s="79"/>
+      <c r="F37" s="79"/>
+      <c r="G37" s="79"/>
+      <c r="H37" s="79"/>
+      <c r="I37" s="79"/>
+      <c r="J37" s="79"/>
+      <c r="K37" s="79"/>
+      <c r="L37" s="79"/>
+      <c r="M37" s="79"/>
+      <c r="N37" s="79"/>
+      <c r="O37" s="79"/>
+      <c r="P37" s="79"/>
+      <c r="Q37" s="79"/>
+      <c r="R37" s="79"/>
+      <c r="S37" s="79"/>
+      <c r="T37" s="79"/>
+      <c r="U37" s="79"/>
+      <c r="V37" s="79"/>
+      <c r="W37" s="79"/>
+      <c r="X37" s="79"/>
+      <c r="Y37" s="79"/>
+      <c r="Z37" s="79"/>
+      <c r="AA37" s="79"/>
+      <c r="AB37" s="79"/>
+      <c r="AC37" s="79"/>
+      <c r="AD37" s="79"/>
+      <c r="AE37" s="79"/>
+      <c r="AF37" s="79"/>
+      <c r="AG37" s="79"/>
+      <c r="AH37" s="79"/>
+      <c r="AI37" s="79"/>
+      <c r="AJ37" s="80"/>
     </row>
     <row r="38" spans="1:36" ht="14.25" customHeight="1">
-      <c r="A38" s="149"/>
-      <c r="B38" s="159"/>
-      <c r="C38" s="159"/>
-      <c r="D38" s="159"/>
-      <c r="E38" s="159"/>
-      <c r="F38" s="159"/>
-      <c r="G38" s="159"/>
-      <c r="H38" s="159"/>
-      <c r="I38" s="159"/>
-      <c r="J38" s="159"/>
-      <c r="K38" s="159"/>
-      <c r="L38" s="159"/>
-      <c r="M38" s="159"/>
-      <c r="N38" s="159"/>
-      <c r="O38" s="159"/>
-      <c r="P38" s="159"/>
-      <c r="Q38" s="159"/>
-      <c r="R38" s="159"/>
-      <c r="S38" s="159"/>
-      <c r="T38" s="159"/>
-      <c r="U38" s="159"/>
-      <c r="V38" s="159"/>
-      <c r="W38" s="159"/>
-      <c r="X38" s="159"/>
-      <c r="Y38" s="159"/>
-      <c r="Z38" s="159"/>
-      <c r="AA38" s="159"/>
-      <c r="AB38" s="159"/>
-      <c r="AC38" s="159"/>
-      <c r="AD38" s="159"/>
-      <c r="AE38" s="159"/>
-      <c r="AF38" s="159"/>
-      <c r="AG38" s="159"/>
-      <c r="AH38" s="159"/>
-      <c r="AI38" s="159"/>
-      <c r="AJ38" s="160"/>
+      <c r="A38" s="62"/>
+      <c r="B38" s="79"/>
+      <c r="C38" s="79"/>
+      <c r="D38" s="79"/>
+      <c r="E38" s="79"/>
+      <c r="F38" s="79"/>
+      <c r="G38" s="79"/>
+      <c r="H38" s="79"/>
+      <c r="I38" s="79"/>
+      <c r="J38" s="79"/>
+      <c r="K38" s="79"/>
+      <c r="L38" s="79"/>
+      <c r="M38" s="79"/>
+      <c r="N38" s="79"/>
+      <c r="O38" s="79"/>
+      <c r="P38" s="79"/>
+      <c r="Q38" s="79"/>
+      <c r="R38" s="79"/>
+      <c r="S38" s="79"/>
+      <c r="T38" s="79"/>
+      <c r="U38" s="79"/>
+      <c r="V38" s="79"/>
+      <c r="W38" s="79"/>
+      <c r="X38" s="79"/>
+      <c r="Y38" s="79"/>
+      <c r="Z38" s="79"/>
+      <c r="AA38" s="79"/>
+      <c r="AB38" s="79"/>
+      <c r="AC38" s="79"/>
+      <c r="AD38" s="79"/>
+      <c r="AE38" s="79"/>
+      <c r="AF38" s="79"/>
+      <c r="AG38" s="79"/>
+      <c r="AH38" s="79"/>
+      <c r="AI38" s="79"/>
+      <c r="AJ38" s="80"/>
     </row>
     <row r="39" spans="1:36" ht="27.6" customHeight="1">
-      <c r="A39" s="149"/>
-      <c r="B39" s="159"/>
-      <c r="C39" s="159"/>
-      <c r="D39" s="159"/>
-      <c r="E39" s="159"/>
-      <c r="F39" s="159"/>
-      <c r="G39" s="159"/>
-      <c r="H39" s="159"/>
-      <c r="I39" s="159"/>
-      <c r="J39" s="159"/>
-      <c r="K39" s="159"/>
-      <c r="L39" s="159"/>
-      <c r="M39" s="159"/>
-      <c r="N39" s="159"/>
-      <c r="O39" s="159"/>
-      <c r="P39" s="159"/>
-      <c r="Q39" s="159"/>
-      <c r="R39" s="159"/>
-      <c r="S39" s="159"/>
-      <c r="T39" s="159"/>
-      <c r="U39" s="159"/>
-      <c r="V39" s="159"/>
-      <c r="W39" s="159"/>
-      <c r="X39" s="159"/>
-      <c r="Y39" s="159"/>
-      <c r="Z39" s="159"/>
-      <c r="AA39" s="159"/>
-      <c r="AB39" s="159"/>
-      <c r="AC39" s="159"/>
-      <c r="AD39" s="159"/>
-      <c r="AE39" s="159"/>
-      <c r="AF39" s="159"/>
-      <c r="AG39" s="159"/>
-      <c r="AH39" s="159"/>
-      <c r="AI39" s="159"/>
-      <c r="AJ39" s="160"/>
+      <c r="A39" s="62"/>
+      <c r="B39" s="79"/>
+      <c r="C39" s="79"/>
+      <c r="D39" s="79"/>
+      <c r="E39" s="79"/>
+      <c r="F39" s="79"/>
+      <c r="G39" s="79"/>
+      <c r="H39" s="79"/>
+      <c r="I39" s="79"/>
+      <c r="J39" s="79"/>
+      <c r="K39" s="79"/>
+      <c r="L39" s="79"/>
+      <c r="M39" s="79"/>
+      <c r="N39" s="79"/>
+      <c r="O39" s="79"/>
+      <c r="P39" s="79"/>
+      <c r="Q39" s="79"/>
+      <c r="R39" s="79"/>
+      <c r="S39" s="79"/>
+      <c r="T39" s="79"/>
+      <c r="U39" s="79"/>
+      <c r="V39" s="79"/>
+      <c r="W39" s="79"/>
+      <c r="X39" s="79"/>
+      <c r="Y39" s="79"/>
+      <c r="Z39" s="79"/>
+      <c r="AA39" s="79"/>
+      <c r="AB39" s="79"/>
+      <c r="AC39" s="79"/>
+      <c r="AD39" s="79"/>
+      <c r="AE39" s="79"/>
+      <c r="AF39" s="79"/>
+      <c r="AG39" s="79"/>
+      <c r="AH39" s="79"/>
+      <c r="AI39" s="79"/>
+      <c r="AJ39" s="80"/>
     </row>
     <row r="40" spans="1:36" ht="16.8" customHeight="1">
-      <c r="A40" s="149"/>
-      <c r="B40" s="159"/>
-      <c r="C40" s="159"/>
-      <c r="D40" s="159"/>
-      <c r="E40" s="159"/>
-      <c r="F40" s="159"/>
-      <c r="G40" s="159"/>
-      <c r="H40" s="159"/>
-      <c r="I40" s="159"/>
-      <c r="J40" s="159"/>
-      <c r="K40" s="159"/>
-      <c r="L40" s="159"/>
-      <c r="M40" s="159"/>
-      <c r="N40" s="159"/>
-      <c r="O40" s="159"/>
-      <c r="P40" s="159"/>
-      <c r="Q40" s="159"/>
-      <c r="R40" s="159"/>
-      <c r="S40" s="159"/>
-      <c r="T40" s="159"/>
-      <c r="U40" s="159"/>
-      <c r="V40" s="159"/>
-      <c r="W40" s="159"/>
-      <c r="X40" s="159"/>
-      <c r="Y40" s="159"/>
-      <c r="Z40" s="159"/>
-      <c r="AA40" s="159"/>
-      <c r="AB40" s="159"/>
-      <c r="AC40" s="159"/>
-      <c r="AD40" s="159"/>
-      <c r="AE40" s="159"/>
-      <c r="AF40" s="159"/>
-      <c r="AG40" s="159"/>
-      <c r="AH40" s="159"/>
-      <c r="AI40" s="159"/>
-      <c r="AJ40" s="160"/>
+      <c r="A40" s="62"/>
+      <c r="B40" s="79"/>
+      <c r="C40" s="79"/>
+      <c r="D40" s="79"/>
+      <c r="E40" s="79"/>
+      <c r="F40" s="79"/>
+      <c r="G40" s="79"/>
+      <c r="H40" s="79"/>
+      <c r="I40" s="79"/>
+      <c r="J40" s="79"/>
+      <c r="K40" s="79"/>
+      <c r="L40" s="79"/>
+      <c r="M40" s="79"/>
+      <c r="N40" s="79"/>
+      <c r="O40" s="79"/>
+      <c r="P40" s="79"/>
+      <c r="Q40" s="79"/>
+      <c r="R40" s="79"/>
+      <c r="S40" s="79"/>
+      <c r="T40" s="79"/>
+      <c r="U40" s="79"/>
+      <c r="V40" s="79"/>
+      <c r="W40" s="79"/>
+      <c r="X40" s="79"/>
+      <c r="Y40" s="79"/>
+      <c r="Z40" s="79"/>
+      <c r="AA40" s="79"/>
+      <c r="AB40" s="79"/>
+      <c r="AC40" s="79"/>
+      <c r="AD40" s="79"/>
+      <c r="AE40" s="79"/>
+      <c r="AF40" s="79"/>
+      <c r="AG40" s="79"/>
+      <c r="AH40" s="79"/>
+      <c r="AI40" s="79"/>
+      <c r="AJ40" s="80"/>
     </row>
     <row r="41" spans="1:36" ht="16.8" customHeight="1">
-      <c r="A41" s="82" t="s">
+      <c r="A41" s="69" t="s">
         <v>99</v>
       </c>
-      <c r="B41" s="83"/>
-      <c r="C41" s="83"/>
-      <c r="D41" s="83"/>
-      <c r="E41" s="83"/>
-      <c r="F41" s="83"/>
-      <c r="G41" s="83"/>
-      <c r="H41" s="83"/>
-      <c r="I41" s="83"/>
-      <c r="J41" s="83"/>
-      <c r="K41" s="83"/>
-      <c r="L41" s="83"/>
-      <c r="M41" s="83"/>
-      <c r="N41" s="83"/>
-      <c r="O41" s="83"/>
-      <c r="P41" s="83"/>
-      <c r="Q41" s="83"/>
-      <c r="R41" s="83"/>
+      <c r="B41" s="70"/>
+      <c r="C41" s="70"/>
+      <c r="D41" s="70"/>
+      <c r="E41" s="70"/>
+      <c r="F41" s="70"/>
+      <c r="G41" s="70"/>
+      <c r="H41" s="70"/>
+      <c r="I41" s="70"/>
+      <c r="J41" s="70"/>
+      <c r="K41" s="70"/>
+      <c r="L41" s="70"/>
+      <c r="M41" s="70"/>
+      <c r="N41" s="70"/>
+      <c r="O41" s="70"/>
+      <c r="P41" s="70"/>
+      <c r="Q41" s="70"/>
+      <c r="R41" s="70"/>
       <c r="S41" s="40"/>
       <c r="T41" s="40"/>
       <c r="U41" s="40"/>
@@ -8664,675 +8675,675 @@
       <c r="AJ42" s="55"/>
     </row>
     <row r="43" spans="1:36" ht="17.25" customHeight="1">
-      <c r="A43" s="107" t="s">
+      <c r="A43" s="71" t="s">
         <v>18</v>
       </c>
-      <c r="B43" s="108"/>
-      <c r="C43" s="108"/>
-      <c r="D43" s="108"/>
-      <c r="E43" s="108"/>
-      <c r="F43" s="108"/>
-      <c r="G43" s="108"/>
-      <c r="H43" s="108"/>
-      <c r="I43" s="109"/>
-      <c r="J43" s="107" t="s">
+      <c r="B43" s="72"/>
+      <c r="C43" s="72"/>
+      <c r="D43" s="72"/>
+      <c r="E43" s="72"/>
+      <c r="F43" s="72"/>
+      <c r="G43" s="72"/>
+      <c r="H43" s="72"/>
+      <c r="I43" s="73"/>
+      <c r="J43" s="71" t="s">
         <v>19</v>
       </c>
-      <c r="K43" s="108"/>
-      <c r="L43" s="108"/>
-      <c r="M43" s="108"/>
-      <c r="N43" s="108"/>
-      <c r="O43" s="108"/>
-      <c r="P43" s="108"/>
-      <c r="Q43" s="108"/>
-      <c r="R43" s="109"/>
-      <c r="S43" s="107" t="s">
+      <c r="K43" s="72"/>
+      <c r="L43" s="72"/>
+      <c r="M43" s="72"/>
+      <c r="N43" s="72"/>
+      <c r="O43" s="72"/>
+      <c r="P43" s="72"/>
+      <c r="Q43" s="72"/>
+      <c r="R43" s="73"/>
+      <c r="S43" s="71" t="s">
         <v>77</v>
       </c>
-      <c r="T43" s="108"/>
-      <c r="U43" s="108"/>
-      <c r="V43" s="108"/>
-      <c r="W43" s="108"/>
-      <c r="X43" s="108"/>
-      <c r="Y43" s="108"/>
-      <c r="Z43" s="108"/>
-      <c r="AA43" s="109"/>
-      <c r="AB43" s="158" t="s">
+      <c r="T43" s="72"/>
+      <c r="U43" s="72"/>
+      <c r="V43" s="72"/>
+      <c r="W43" s="72"/>
+      <c r="X43" s="72"/>
+      <c r="Y43" s="72"/>
+      <c r="Z43" s="72"/>
+      <c r="AA43" s="73"/>
+      <c r="AB43" s="77" t="s">
         <v>91</v>
       </c>
-      <c r="AC43" s="108"/>
-      <c r="AD43" s="108"/>
-      <c r="AE43" s="108"/>
-      <c r="AF43" s="108"/>
-      <c r="AG43" s="108"/>
-      <c r="AH43" s="108"/>
-      <c r="AI43" s="108"/>
-      <c r="AJ43" s="109"/>
+      <c r="AC43" s="72"/>
+      <c r="AD43" s="72"/>
+      <c r="AE43" s="72"/>
+      <c r="AF43" s="72"/>
+      <c r="AG43" s="72"/>
+      <c r="AH43" s="72"/>
+      <c r="AI43" s="72"/>
+      <c r="AJ43" s="73"/>
     </row>
     <row r="44" spans="1:36" ht="18" customHeight="1">
       <c r="A44" s="2"/>
-      <c r="B44" s="122" t="s">
+      <c r="B44" s="57" t="s">
         <v>21</v>
       </c>
-      <c r="C44" s="122"/>
-      <c r="D44" s="122"/>
-      <c r="E44" s="122"/>
-      <c r="F44" s="122"/>
-      <c r="G44" s="122"/>
-      <c r="H44" s="122"/>
-      <c r="I44" s="123"/>
+      <c r="C44" s="57"/>
+      <c r="D44" s="57"/>
+      <c r="E44" s="57"/>
+      <c r="F44" s="57"/>
+      <c r="G44" s="57"/>
+      <c r="H44" s="57"/>
+      <c r="I44" s="58"/>
       <c r="J44" s="10"/>
-      <c r="K44" s="122" t="s">
+      <c r="K44" s="57" t="s">
         <v>22</v>
       </c>
-      <c r="L44" s="122"/>
-      <c r="M44" s="122"/>
-      <c r="N44" s="122"/>
-      <c r="O44" s="122"/>
-      <c r="P44" s="122"/>
-      <c r="Q44" s="122"/>
-      <c r="R44" s="123"/>
-      <c r="S44" s="89" t="s">
+      <c r="L44" s="57"/>
+      <c r="M44" s="57"/>
+      <c r="N44" s="57"/>
+      <c r="O44" s="57"/>
+      <c r="P44" s="57"/>
+      <c r="Q44" s="57"/>
+      <c r="R44" s="58"/>
+      <c r="S44" s="84" t="s">
         <v>81</v>
       </c>
-      <c r="T44" s="87"/>
-      <c r="U44" s="87"/>
-      <c r="V44" s="87"/>
-      <c r="W44" s="68"/>
-      <c r="X44" s="68"/>
-      <c r="Y44" s="68"/>
+      <c r="T44" s="85"/>
+      <c r="U44" s="85"/>
+      <c r="V44" s="85"/>
+      <c r="W44" s="78"/>
+      <c r="X44" s="78"/>
+      <c r="Y44" s="78"/>
       <c r="Z44" s="49"/>
       <c r="AA44" s="4"/>
-      <c r="AB44" s="124" t="s">
+      <c r="AB44" s="59" t="s">
         <v>82</v>
       </c>
-      <c r="AC44" s="71"/>
-      <c r="AD44" s="71"/>
-      <c r="AE44" s="71"/>
-      <c r="AF44" s="129"/>
-      <c r="AG44" s="129"/>
-      <c r="AH44" s="129"/>
-      <c r="AI44" s="129"/>
+      <c r="AC44" s="60"/>
+      <c r="AD44" s="60"/>
+      <c r="AE44" s="60"/>
+      <c r="AF44" s="74"/>
+      <c r="AG44" s="74"/>
+      <c r="AH44" s="74"/>
+      <c r="AI44" s="74"/>
       <c r="AJ44" s="4"/>
     </row>
     <row r="45" spans="1:36" ht="18" customHeight="1">
       <c r="A45" s="2"/>
-      <c r="B45" s="122" t="s">
+      <c r="B45" s="57" t="s">
         <v>24</v>
       </c>
-      <c r="C45" s="122"/>
-      <c r="D45" s="122"/>
-      <c r="E45" s="122"/>
-      <c r="F45" s="122"/>
-      <c r="G45" s="122"/>
-      <c r="H45" s="122"/>
-      <c r="I45" s="123"/>
+      <c r="C45" s="57"/>
+      <c r="D45" s="57"/>
+      <c r="E45" s="57"/>
+      <c r="F45" s="57"/>
+      <c r="G45" s="57"/>
+      <c r="H45" s="57"/>
+      <c r="I45" s="58"/>
       <c r="J45" s="10"/>
-      <c r="K45" s="122" t="s">
+      <c r="K45" s="57" t="s">
         <v>25</v>
       </c>
-      <c r="L45" s="122"/>
-      <c r="M45" s="122"/>
-      <c r="N45" s="122"/>
-      <c r="O45" s="122"/>
-      <c r="P45" s="122"/>
-      <c r="Q45" s="122"/>
-      <c r="R45" s="123"/>
-      <c r="S45" s="89" t="s">
+      <c r="L45" s="57"/>
+      <c r="M45" s="57"/>
+      <c r="N45" s="57"/>
+      <c r="O45" s="57"/>
+      <c r="P45" s="57"/>
+      <c r="Q45" s="57"/>
+      <c r="R45" s="58"/>
+      <c r="S45" s="84" t="s">
         <v>80</v>
       </c>
-      <c r="T45" s="87"/>
-      <c r="U45" s="87"/>
-      <c r="V45" s="87"/>
-      <c r="W45" s="148"/>
-      <c r="X45" s="148"/>
-      <c r="Y45" s="148"/>
-      <c r="Z45" s="148"/>
+      <c r="T45" s="85"/>
+      <c r="U45" s="85"/>
+      <c r="V45" s="85"/>
+      <c r="W45" s="56"/>
+      <c r="X45" s="56"/>
+      <c r="Y45" s="56"/>
+      <c r="Z45" s="56"/>
       <c r="AA45" s="4"/>
-      <c r="AB45" s="89" t="s">
+      <c r="AB45" s="84" t="s">
         <v>81</v>
       </c>
-      <c r="AC45" s="87"/>
-      <c r="AD45" s="87"/>
-      <c r="AE45" s="87"/>
-      <c r="AF45" s="148"/>
-      <c r="AG45" s="148"/>
-      <c r="AH45" s="148"/>
-      <c r="AI45" s="148"/>
+      <c r="AC45" s="85"/>
+      <c r="AD45" s="85"/>
+      <c r="AE45" s="85"/>
+      <c r="AF45" s="56"/>
+      <c r="AG45" s="56"/>
+      <c r="AH45" s="56"/>
+      <c r="AI45" s="56"/>
       <c r="AJ45" s="4"/>
     </row>
     <row r="46" spans="1:36" ht="18" customHeight="1">
       <c r="A46" s="2"/>
-      <c r="B46" s="122" t="s">
+      <c r="B46" s="57" t="s">
         <v>27</v>
       </c>
-      <c r="C46" s="122"/>
-      <c r="D46" s="122"/>
-      <c r="E46" s="122"/>
-      <c r="F46" s="122"/>
-      <c r="G46" s="122"/>
-      <c r="H46" s="122"/>
-      <c r="I46" s="123"/>
+      <c r="C46" s="57"/>
+      <c r="D46" s="57"/>
+      <c r="E46" s="57"/>
+      <c r="F46" s="57"/>
+      <c r="G46" s="57"/>
+      <c r="H46" s="57"/>
+      <c r="I46" s="58"/>
       <c r="J46" s="10"/>
-      <c r="K46" s="122" t="s">
+      <c r="K46" s="57" t="s">
         <v>28</v>
       </c>
-      <c r="L46" s="122"/>
-      <c r="M46" s="122"/>
-      <c r="N46" s="122"/>
-      <c r="O46" s="122"/>
-      <c r="P46" s="122"/>
-      <c r="Q46" s="122"/>
-      <c r="R46" s="123"/>
-      <c r="S46" s="124" t="s">
+      <c r="L46" s="57"/>
+      <c r="M46" s="57"/>
+      <c r="N46" s="57"/>
+      <c r="O46" s="57"/>
+      <c r="P46" s="57"/>
+      <c r="Q46" s="57"/>
+      <c r="R46" s="58"/>
+      <c r="S46" s="59" t="s">
         <v>78</v>
       </c>
-      <c r="T46" s="71"/>
-      <c r="U46" s="71"/>
-      <c r="V46" s="71"/>
-      <c r="W46" s="71"/>
-      <c r="X46" s="125"/>
-      <c r="Y46" s="125"/>
-      <c r="Z46" s="125"/>
+      <c r="T46" s="60"/>
+      <c r="U46" s="60"/>
+      <c r="V46" s="60"/>
+      <c r="W46" s="60"/>
+      <c r="X46" s="93"/>
+      <c r="Y46" s="93"/>
+      <c r="Z46" s="93"/>
       <c r="AA46" s="12" t="s">
         <v>30</v>
       </c>
-      <c r="AB46" s="89" t="s">
+      <c r="AB46" s="84" t="s">
         <v>80</v>
       </c>
-      <c r="AC46" s="87"/>
-      <c r="AD46" s="87"/>
-      <c r="AE46" s="87"/>
-      <c r="AF46" s="148"/>
-      <c r="AG46" s="148"/>
-      <c r="AH46" s="148"/>
-      <c r="AI46" s="148"/>
+      <c r="AC46" s="85"/>
+      <c r="AD46" s="85"/>
+      <c r="AE46" s="85"/>
+      <c r="AF46" s="56"/>
+      <c r="AG46" s="56"/>
+      <c r="AH46" s="56"/>
+      <c r="AI46" s="56"/>
       <c r="AJ46" s="4"/>
     </row>
     <row r="47" spans="1:36" ht="18" customHeight="1">
       <c r="A47" s="2"/>
-      <c r="B47" s="122" t="s">
+      <c r="B47" s="57" t="s">
         <v>87</v>
       </c>
-      <c r="C47" s="122"/>
-      <c r="D47" s="122"/>
-      <c r="E47" s="122"/>
-      <c r="F47" s="122"/>
-      <c r="G47" s="122"/>
-      <c r="H47" s="122"/>
-      <c r="I47" s="123"/>
+      <c r="C47" s="57"/>
+      <c r="D47" s="57"/>
+      <c r="E47" s="57"/>
+      <c r="F47" s="57"/>
+      <c r="G47" s="57"/>
+      <c r="H47" s="57"/>
+      <c r="I47" s="58"/>
       <c r="J47" s="10"/>
-      <c r="K47" s="122" t="s">
+      <c r="K47" s="57" t="s">
         <v>31</v>
       </c>
-      <c r="L47" s="122"/>
-      <c r="M47" s="122"/>
-      <c r="N47" s="122"/>
-      <c r="O47" s="122"/>
-      <c r="P47" s="122"/>
-      <c r="Q47" s="122"/>
-      <c r="R47" s="123"/>
-      <c r="S47" s="126" t="s">
+      <c r="L47" s="57"/>
+      <c r="M47" s="57"/>
+      <c r="N47" s="57"/>
+      <c r="O47" s="57"/>
+      <c r="P47" s="57"/>
+      <c r="Q47" s="57"/>
+      <c r="R47" s="58"/>
+      <c r="S47" s="101" t="s">
         <v>79</v>
       </c>
-      <c r="T47" s="127"/>
-      <c r="U47" s="127"/>
-      <c r="V47" s="127"/>
-      <c r="W47" s="127"/>
-      <c r="X47" s="143"/>
-      <c r="Y47" s="143"/>
-      <c r="Z47" s="143"/>
+      <c r="T47" s="102"/>
+      <c r="U47" s="102"/>
+      <c r="V47" s="102"/>
+      <c r="W47" s="102"/>
+      <c r="X47" s="61"/>
+      <c r="Y47" s="61"/>
+      <c r="Z47" s="61"/>
       <c r="AA47" s="33" t="s">
         <v>30</v>
       </c>
-      <c r="AB47" s="89" t="s">
+      <c r="AB47" s="84" t="s">
         <v>83</v>
       </c>
-      <c r="AC47" s="87"/>
-      <c r="AD47" s="87"/>
-      <c r="AE47" s="87"/>
-      <c r="AF47" s="129"/>
-      <c r="AG47" s="129"/>
-      <c r="AH47" s="129"/>
-      <c r="AI47" s="129"/>
+      <c r="AC47" s="85"/>
+      <c r="AD47" s="85"/>
+      <c r="AE47" s="85"/>
+      <c r="AF47" s="74"/>
+      <c r="AG47" s="74"/>
+      <c r="AH47" s="74"/>
+      <c r="AI47" s="74"/>
       <c r="AJ47" s="4"/>
     </row>
     <row r="48" spans="1:36" ht="18" customHeight="1">
       <c r="A48" s="34"/>
-      <c r="B48" s="122" t="s">
+      <c r="B48" s="57" t="s">
         <v>33</v>
       </c>
-      <c r="C48" s="122"/>
-      <c r="D48" s="122"/>
-      <c r="E48" s="122"/>
-      <c r="F48" s="122"/>
-      <c r="G48" s="122"/>
-      <c r="H48" s="122"/>
-      <c r="I48" s="123"/>
+      <c r="C48" s="57"/>
+      <c r="D48" s="57"/>
+      <c r="E48" s="57"/>
+      <c r="F48" s="57"/>
+      <c r="G48" s="57"/>
+      <c r="H48" s="57"/>
+      <c r="I48" s="58"/>
       <c r="J48" s="10"/>
-      <c r="K48" s="122" t="s">
+      <c r="K48" s="57" t="s">
         <v>34</v>
       </c>
-      <c r="L48" s="122"/>
-      <c r="M48" s="122"/>
-      <c r="N48" s="122"/>
-      <c r="O48" s="122"/>
-      <c r="P48" s="122"/>
-      <c r="Q48" s="122"/>
-      <c r="R48" s="123"/>
-      <c r="S48" s="139" t="s">
+      <c r="L48" s="57"/>
+      <c r="M48" s="57"/>
+      <c r="N48" s="57"/>
+      <c r="O48" s="57"/>
+      <c r="P48" s="57"/>
+      <c r="Q48" s="57"/>
+      <c r="R48" s="58"/>
+      <c r="S48" s="90" t="s">
         <v>20</v>
       </c>
-      <c r="T48" s="140"/>
-      <c r="U48" s="140"/>
-      <c r="V48" s="140"/>
-      <c r="W48" s="140"/>
-      <c r="X48" s="140"/>
-      <c r="Y48" s="140"/>
-      <c r="Z48" s="140"/>
-      <c r="AA48" s="141"/>
-      <c r="AB48" s="124" t="s">
+      <c r="T48" s="91"/>
+      <c r="U48" s="91"/>
+      <c r="V48" s="91"/>
+      <c r="W48" s="91"/>
+      <c r="X48" s="91"/>
+      <c r="Y48" s="91"/>
+      <c r="Z48" s="91"/>
+      <c r="AA48" s="92"/>
+      <c r="AB48" s="59" t="s">
         <v>78</v>
       </c>
-      <c r="AC48" s="71"/>
-      <c r="AD48" s="71"/>
-      <c r="AE48" s="71"/>
-      <c r="AF48" s="71"/>
-      <c r="AG48" s="125"/>
-      <c r="AH48" s="125"/>
-      <c r="AI48" s="125"/>
+      <c r="AC48" s="60"/>
+      <c r="AD48" s="60"/>
+      <c r="AE48" s="60"/>
+      <c r="AF48" s="60"/>
+      <c r="AG48" s="93"/>
+      <c r="AH48" s="93"/>
+      <c r="AI48" s="93"/>
       <c r="AJ48" s="12" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="49" spans="1:36" ht="18" customHeight="1">
       <c r="A49" s="10"/>
-      <c r="B49" s="122" t="s">
+      <c r="B49" s="57" t="s">
         <v>74</v>
       </c>
-      <c r="C49" s="122"/>
-      <c r="D49" s="122"/>
-      <c r="E49" s="122"/>
-      <c r="F49" s="122"/>
-      <c r="G49" s="122"/>
-      <c r="H49" s="122"/>
-      <c r="I49" s="123"/>
+      <c r="C49" s="57"/>
+      <c r="D49" s="57"/>
+      <c r="E49" s="57"/>
+      <c r="F49" s="57"/>
+      <c r="G49" s="57"/>
+      <c r="H49" s="57"/>
+      <c r="I49" s="58"/>
       <c r="J49" s="10"/>
-      <c r="K49" s="122" t="s">
+      <c r="K49" s="57" t="s">
         <v>37</v>
       </c>
-      <c r="L49" s="122"/>
-      <c r="M49" s="122"/>
-      <c r="N49" s="122"/>
-      <c r="O49" s="122"/>
-      <c r="P49" s="122"/>
-      <c r="Q49" s="122"/>
-      <c r="R49" s="123"/>
+      <c r="L49" s="57"/>
+      <c r="M49" s="57"/>
+      <c r="N49" s="57"/>
+      <c r="O49" s="57"/>
+      <c r="P49" s="57"/>
+      <c r="Q49" s="57"/>
+      <c r="R49" s="58"/>
       <c r="S49" s="10"/>
-      <c r="T49" s="122" t="s">
+      <c r="T49" s="57" t="s">
         <v>23</v>
       </c>
-      <c r="U49" s="122"/>
-      <c r="V49" s="122"/>
-      <c r="W49" s="122"/>
-      <c r="X49" s="122"/>
-      <c r="Y49" s="122"/>
-      <c r="Z49" s="122"/>
-      <c r="AA49" s="123"/>
-      <c r="AB49" s="126" t="s">
+      <c r="U49" s="57"/>
+      <c r="V49" s="57"/>
+      <c r="W49" s="57"/>
+      <c r="X49" s="57"/>
+      <c r="Y49" s="57"/>
+      <c r="Z49" s="57"/>
+      <c r="AA49" s="58"/>
+      <c r="AB49" s="101" t="s">
         <v>79</v>
       </c>
-      <c r="AC49" s="127"/>
-      <c r="AD49" s="127"/>
-      <c r="AE49" s="127"/>
-      <c r="AF49" s="127"/>
-      <c r="AG49" s="143"/>
-      <c r="AH49" s="143"/>
-      <c r="AI49" s="143"/>
+      <c r="AC49" s="102"/>
+      <c r="AD49" s="102"/>
+      <c r="AE49" s="102"/>
+      <c r="AF49" s="102"/>
+      <c r="AG49" s="61"/>
+      <c r="AH49" s="61"/>
+      <c r="AI49" s="61"/>
       <c r="AJ49" s="33" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="50" spans="1:36" ht="18" customHeight="1">
       <c r="A50" s="10"/>
-      <c r="B50" s="122" t="s">
+      <c r="B50" s="57" t="s">
         <v>75</v>
       </c>
-      <c r="C50" s="122"/>
-      <c r="D50" s="122"/>
-      <c r="E50" s="122"/>
-      <c r="F50" s="122"/>
-      <c r="G50" s="122"/>
-      <c r="H50" s="122"/>
-      <c r="I50" s="123"/>
+      <c r="C50" s="57"/>
+      <c r="D50" s="57"/>
+      <c r="E50" s="57"/>
+      <c r="F50" s="57"/>
+      <c r="G50" s="57"/>
+      <c r="H50" s="57"/>
+      <c r="I50" s="58"/>
       <c r="J50" s="10"/>
-      <c r="K50" s="122" t="s">
+      <c r="K50" s="57" t="s">
         <v>39</v>
       </c>
-      <c r="L50" s="122"/>
-      <c r="M50" s="122"/>
-      <c r="N50" s="122"/>
-      <c r="O50" s="122"/>
-      <c r="P50" s="122"/>
-      <c r="Q50" s="122"/>
-      <c r="R50" s="123"/>
+      <c r="L50" s="57"/>
+      <c r="M50" s="57"/>
+      <c r="N50" s="57"/>
+      <c r="O50" s="57"/>
+      <c r="P50" s="57"/>
+      <c r="Q50" s="57"/>
+      <c r="R50" s="58"/>
       <c r="S50" s="10"/>
-      <c r="T50" s="122" t="s">
+      <c r="T50" s="57" t="s">
         <v>26</v>
       </c>
-      <c r="U50" s="122"/>
-      <c r="V50" s="122"/>
-      <c r="W50" s="122"/>
-      <c r="X50" s="122"/>
-      <c r="Y50" s="122"/>
-      <c r="Z50" s="122"/>
-      <c r="AA50" s="123"/>
-      <c r="AB50" s="130" t="s">
+      <c r="U50" s="57"/>
+      <c r="V50" s="57"/>
+      <c r="W50" s="57"/>
+      <c r="X50" s="57"/>
+      <c r="Y50" s="57"/>
+      <c r="Z50" s="57"/>
+      <c r="AA50" s="58"/>
+      <c r="AB50" s="104" t="s">
         <v>38</v>
       </c>
-      <c r="AC50" s="131"/>
-      <c r="AD50" s="131"/>
-      <c r="AE50" s="131"/>
-      <c r="AF50" s="131"/>
-      <c r="AG50" s="131"/>
-      <c r="AH50" s="131"/>
-      <c r="AI50" s="131"/>
-      <c r="AJ50" s="132"/>
+      <c r="AC50" s="105"/>
+      <c r="AD50" s="105"/>
+      <c r="AE50" s="105"/>
+      <c r="AF50" s="105"/>
+      <c r="AG50" s="105"/>
+      <c r="AH50" s="105"/>
+      <c r="AI50" s="105"/>
+      <c r="AJ50" s="106"/>
     </row>
     <row r="51" spans="1:36" ht="18" customHeight="1">
       <c r="A51" s="10"/>
-      <c r="B51" s="122" t="s">
+      <c r="B51" s="57" t="s">
         <v>40</v>
       </c>
-      <c r="C51" s="122"/>
-      <c r="D51" s="122"/>
-      <c r="E51" s="122"/>
-      <c r="F51" s="122"/>
-      <c r="G51" s="122"/>
-      <c r="H51" s="122"/>
-      <c r="I51" s="123"/>
+      <c r="C51" s="57"/>
+      <c r="D51" s="57"/>
+      <c r="E51" s="57"/>
+      <c r="F51" s="57"/>
+      <c r="G51" s="57"/>
+      <c r="H51" s="57"/>
+      <c r="I51" s="58"/>
       <c r="J51" s="10"/>
-      <c r="K51" s="122" t="s">
+      <c r="K51" s="57" t="s">
         <v>41</v>
       </c>
-      <c r="L51" s="122"/>
-      <c r="M51" s="122"/>
-      <c r="N51" s="122"/>
-      <c r="O51" s="122"/>
-      <c r="P51" s="122"/>
-      <c r="Q51" s="122"/>
-      <c r="R51" s="123"/>
+      <c r="L51" s="57"/>
+      <c r="M51" s="57"/>
+      <c r="N51" s="57"/>
+      <c r="O51" s="57"/>
+      <c r="P51" s="57"/>
+      <c r="Q51" s="57"/>
+      <c r="R51" s="58"/>
       <c r="S51" s="10"/>
-      <c r="T51" s="122" t="s">
+      <c r="T51" s="57" t="s">
         <v>29</v>
       </c>
-      <c r="U51" s="122"/>
-      <c r="V51" s="122"/>
-      <c r="W51" s="125"/>
-      <c r="X51" s="125"/>
-      <c r="Y51" s="125"/>
+      <c r="U51" s="57"/>
+      <c r="V51" s="57"/>
+      <c r="W51" s="93"/>
+      <c r="X51" s="93"/>
+      <c r="Y51" s="93"/>
       <c r="Z51" s="3" t="s">
         <v>30</v>
       </c>
       <c r="AA51" s="4"/>
       <c r="AB51" s="10"/>
-      <c r="AC51" s="133" t="s">
+      <c r="AC51" s="107" t="s">
         <v>76</v>
       </c>
-      <c r="AD51" s="133"/>
-      <c r="AE51" s="133"/>
-      <c r="AF51" s="133"/>
-      <c r="AG51" s="133"/>
-      <c r="AH51" s="133"/>
-      <c r="AI51" s="133"/>
-      <c r="AJ51" s="134"/>
+      <c r="AD51" s="107"/>
+      <c r="AE51" s="107"/>
+      <c r="AF51" s="107"/>
+      <c r="AG51" s="107"/>
+      <c r="AH51" s="107"/>
+      <c r="AI51" s="107"/>
+      <c r="AJ51" s="108"/>
     </row>
     <row r="52" spans="1:36" ht="18" customHeight="1">
       <c r="A52" s="10"/>
-      <c r="B52" s="122" t="s">
+      <c r="B52" s="57" t="s">
         <v>43</v>
       </c>
-      <c r="C52" s="122"/>
-      <c r="D52" s="135"/>
-      <c r="E52" s="135"/>
-      <c r="F52" s="135"/>
-      <c r="G52" s="135"/>
-      <c r="H52" s="135"/>
+      <c r="C52" s="57"/>
+      <c r="D52" s="109"/>
+      <c r="E52" s="109"/>
+      <c r="F52" s="109"/>
+      <c r="G52" s="109"/>
+      <c r="H52" s="109"/>
       <c r="I52" s="4"/>
       <c r="J52" s="10"/>
-      <c r="K52" s="122" t="s">
+      <c r="K52" s="57" t="s">
         <v>44</v>
       </c>
-      <c r="L52" s="122"/>
-      <c r="M52" s="122"/>
-      <c r="N52" s="122"/>
-      <c r="O52" s="122"/>
-      <c r="P52" s="122"/>
-      <c r="Q52" s="122"/>
-      <c r="R52" s="123"/>
+      <c r="L52" s="57"/>
+      <c r="M52" s="57"/>
+      <c r="N52" s="57"/>
+      <c r="O52" s="57"/>
+      <c r="P52" s="57"/>
+      <c r="Q52" s="57"/>
+      <c r="R52" s="58"/>
       <c r="S52" s="10"/>
-      <c r="T52" s="122" t="s">
+      <c r="T52" s="57" t="s">
         <v>32</v>
       </c>
-      <c r="U52" s="122"/>
-      <c r="V52" s="122"/>
-      <c r="W52" s="125"/>
-      <c r="X52" s="125"/>
-      <c r="Y52" s="125"/>
+      <c r="U52" s="57"/>
+      <c r="V52" s="57"/>
+      <c r="W52" s="93"/>
+      <c r="X52" s="93"/>
+      <c r="Y52" s="93"/>
       <c r="Z52" s="3" t="s">
         <v>30</v>
       </c>
       <c r="AA52" s="4"/>
       <c r="AB52" s="10"/>
-      <c r="AC52" s="122" t="s">
+      <c r="AC52" s="57" t="s">
         <v>42</v>
       </c>
-      <c r="AD52" s="122"/>
-      <c r="AE52" s="122"/>
-      <c r="AF52" s="122"/>
-      <c r="AG52" s="122"/>
-      <c r="AH52" s="122"/>
-      <c r="AI52" s="122"/>
-      <c r="AJ52" s="123"/>
+      <c r="AD52" s="57"/>
+      <c r="AE52" s="57"/>
+      <c r="AF52" s="57"/>
+      <c r="AG52" s="57"/>
+      <c r="AH52" s="57"/>
+      <c r="AI52" s="57"/>
+      <c r="AJ52" s="58"/>
     </row>
     <row r="53" spans="1:36" ht="18" customHeight="1">
       <c r="A53" s="13"/>
       <c r="B53" s="7"/>
       <c r="C53" s="7"/>
-      <c r="D53" s="146"/>
-      <c r="E53" s="146"/>
-      <c r="F53" s="146"/>
-      <c r="G53" s="146"/>
-      <c r="H53" s="146"/>
+      <c r="D53" s="98"/>
+      <c r="E53" s="98"/>
+      <c r="F53" s="98"/>
+      <c r="G53" s="98"/>
+      <c r="H53" s="98"/>
       <c r="I53" s="8"/>
-      <c r="J53" s="126"/>
-      <c r="K53" s="127"/>
-      <c r="L53" s="127"/>
-      <c r="M53" s="127"/>
-      <c r="N53" s="127"/>
-      <c r="O53" s="127"/>
-      <c r="P53" s="127"/>
-      <c r="Q53" s="127"/>
-      <c r="R53" s="128"/>
+      <c r="J53" s="101"/>
+      <c r="K53" s="102"/>
+      <c r="L53" s="102"/>
+      <c r="M53" s="102"/>
+      <c r="N53" s="102"/>
+      <c r="O53" s="102"/>
+      <c r="P53" s="102"/>
+      <c r="Q53" s="102"/>
+      <c r="R53" s="110"/>
       <c r="S53" s="13"/>
-      <c r="T53" s="142" t="s">
+      <c r="T53" s="94" t="s">
         <v>35</v>
       </c>
-      <c r="U53" s="142"/>
-      <c r="V53" s="142"/>
-      <c r="W53" s="143"/>
-      <c r="X53" s="143"/>
-      <c r="Y53" s="143"/>
+      <c r="U53" s="94"/>
+      <c r="V53" s="94"/>
+      <c r="W53" s="61"/>
+      <c r="X53" s="61"/>
+      <c r="Y53" s="61"/>
       <c r="Z53" s="6" t="s">
         <v>36</v>
       </c>
       <c r="AA53" s="8"/>
       <c r="AB53" s="13"/>
-      <c r="AC53" s="142" t="s">
+      <c r="AC53" s="94" t="s">
         <v>45</v>
       </c>
-      <c r="AD53" s="142"/>
-      <c r="AE53" s="142"/>
-      <c r="AF53" s="106"/>
-      <c r="AG53" s="106"/>
-      <c r="AH53" s="106"/>
+      <c r="AD53" s="94"/>
+      <c r="AE53" s="94"/>
+      <c r="AF53" s="103"/>
+      <c r="AG53" s="103"/>
+      <c r="AH53" s="103"/>
       <c r="AI53" s="7"/>
       <c r="AJ53" s="8"/>
     </row>
     <row r="54" spans="1:36" ht="18" customHeight="1">
-      <c r="A54" s="144" t="s">
+      <c r="A54" s="96" t="s">
         <v>46</v>
       </c>
-      <c r="B54" s="144"/>
-      <c r="C54" s="144"/>
-      <c r="D54" s="144"/>
-      <c r="E54" s="144"/>
-      <c r="F54" s="144"/>
-      <c r="G54" s="144"/>
-      <c r="H54" s="144"/>
-      <c r="I54" s="144"/>
-      <c r="J54" s="144"/>
-      <c r="K54" s="144"/>
-      <c r="L54" s="144"/>
-      <c r="M54" s="144"/>
-      <c r="N54" s="145"/>
-      <c r="O54" s="145"/>
-      <c r="P54" s="145"/>
-      <c r="Q54" s="145"/>
-      <c r="R54" s="145"/>
-      <c r="S54" s="145"/>
-      <c r="T54" s="145"/>
-      <c r="U54" s="145"/>
-      <c r="V54" s="145"/>
-      <c r="W54" s="145"/>
-      <c r="X54" s="145"/>
-      <c r="Y54" s="145"/>
-      <c r="Z54" s="145"/>
-      <c r="AA54" s="145"/>
-      <c r="AB54" s="145"/>
-      <c r="AC54" s="145"/>
-      <c r="AD54" s="145"/>
-      <c r="AE54" s="145"/>
-      <c r="AF54" s="145"/>
-      <c r="AG54" s="145"/>
-      <c r="AH54" s="145"/>
-      <c r="AI54" s="145"/>
-      <c r="AJ54" s="145"/>
+      <c r="B54" s="96"/>
+      <c r="C54" s="96"/>
+      <c r="D54" s="96"/>
+      <c r="E54" s="96"/>
+      <c r="F54" s="96"/>
+      <c r="G54" s="96"/>
+      <c r="H54" s="96"/>
+      <c r="I54" s="96"/>
+      <c r="J54" s="96"/>
+      <c r="K54" s="96"/>
+      <c r="L54" s="96"/>
+      <c r="M54" s="96"/>
+      <c r="N54" s="97"/>
+      <c r="O54" s="97"/>
+      <c r="P54" s="97"/>
+      <c r="Q54" s="97"/>
+      <c r="R54" s="97"/>
+      <c r="S54" s="97"/>
+      <c r="T54" s="97"/>
+      <c r="U54" s="97"/>
+      <c r="V54" s="97"/>
+      <c r="W54" s="97"/>
+      <c r="X54" s="97"/>
+      <c r="Y54" s="97"/>
+      <c r="Z54" s="97"/>
+      <c r="AA54" s="97"/>
+      <c r="AB54" s="97"/>
+      <c r="AC54" s="97"/>
+      <c r="AD54" s="97"/>
+      <c r="AE54" s="97"/>
+      <c r="AF54" s="97"/>
+      <c r="AG54" s="97"/>
+      <c r="AH54" s="97"/>
+      <c r="AI54" s="97"/>
+      <c r="AJ54" s="97"/>
     </row>
     <row r="55" spans="1:36" ht="18" customHeight="1">
-      <c r="A55" s="137"/>
-      <c r="B55" s="74"/>
-      <c r="C55" s="74"/>
-      <c r="D55" s="74"/>
-      <c r="E55" s="74"/>
-      <c r="F55" s="74"/>
-      <c r="G55" s="74"/>
-      <c r="H55" s="74"/>
-      <c r="I55" s="74"/>
-      <c r="J55" s="74"/>
-      <c r="K55" s="74"/>
-      <c r="L55" s="74"/>
-      <c r="N55" s="74"/>
-      <c r="O55" s="74"/>
-      <c r="P55" s="74"/>
-      <c r="Q55" s="74"/>
-      <c r="R55" s="74"/>
-      <c r="S55" s="74"/>
-      <c r="T55" s="74"/>
-      <c r="U55" s="74"/>
-      <c r="V55" s="74"/>
-      <c r="W55" s="74"/>
-      <c r="X55" s="74"/>
-      <c r="Y55" s="137"/>
-      <c r="Z55" s="137"/>
-      <c r="AA55" s="137"/>
-      <c r="AB55" s="147" t="s">
+      <c r="A55" s="87"/>
+      <c r="B55" s="95"/>
+      <c r="C55" s="95"/>
+      <c r="D55" s="95"/>
+      <c r="E55" s="95"/>
+      <c r="F55" s="95"/>
+      <c r="G55" s="95"/>
+      <c r="H55" s="95"/>
+      <c r="I55" s="95"/>
+      <c r="J55" s="95"/>
+      <c r="K55" s="95"/>
+      <c r="L55" s="95"/>
+      <c r="N55" s="95"/>
+      <c r="O55" s="95"/>
+      <c r="P55" s="95"/>
+      <c r="Q55" s="95"/>
+      <c r="R55" s="95"/>
+      <c r="S55" s="95"/>
+      <c r="T55" s="95"/>
+      <c r="U55" s="95"/>
+      <c r="V55" s="95"/>
+      <c r="W55" s="95"/>
+      <c r="X55" s="95"/>
+      <c r="Y55" s="87"/>
+      <c r="Z55" s="87"/>
+      <c r="AA55" s="87"/>
+      <c r="AB55" s="99" t="s">
         <v>93</v>
       </c>
-      <c r="AC55" s="105"/>
-      <c r="AD55" s="105"/>
-      <c r="AE55" s="105"/>
-      <c r="AF55" s="105"/>
-      <c r="AG55" s="105"/>
-      <c r="AH55" s="105"/>
-      <c r="AI55" s="105"/>
-      <c r="AJ55" s="105"/>
+      <c r="AC55" s="100"/>
+      <c r="AD55" s="100"/>
+      <c r="AE55" s="100"/>
+      <c r="AF55" s="100"/>
+      <c r="AG55" s="100"/>
+      <c r="AH55" s="100"/>
+      <c r="AI55" s="100"/>
+      <c r="AJ55" s="100"/>
     </row>
     <row r="56" spans="1:36" ht="18" customHeight="1">
-      <c r="A56" s="137"/>
-      <c r="B56" s="74"/>
-      <c r="C56" s="74"/>
-      <c r="D56" s="74"/>
-      <c r="E56" s="74"/>
-      <c r="F56" s="74"/>
-      <c r="G56" s="74"/>
-      <c r="H56" s="74"/>
-      <c r="I56" s="74"/>
-      <c r="J56" s="74"/>
-      <c r="K56" s="74"/>
-      <c r="L56" s="74"/>
-      <c r="N56" s="74"/>
-      <c r="O56" s="74"/>
-      <c r="P56" s="74"/>
-      <c r="Q56" s="74"/>
-      <c r="R56" s="74"/>
-      <c r="S56" s="74"/>
-      <c r="T56" s="74"/>
-      <c r="U56" s="74"/>
-      <c r="V56" s="74"/>
-      <c r="W56" s="74"/>
-      <c r="X56" s="74"/>
-      <c r="Y56" s="137"/>
-      <c r="Z56" s="137"/>
-      <c r="AA56" s="137"/>
-      <c r="AB56" s="138" t="s">
+      <c r="A56" s="87"/>
+      <c r="B56" s="95"/>
+      <c r="C56" s="95"/>
+      <c r="D56" s="95"/>
+      <c r="E56" s="95"/>
+      <c r="F56" s="95"/>
+      <c r="G56" s="95"/>
+      <c r="H56" s="95"/>
+      <c r="I56" s="95"/>
+      <c r="J56" s="95"/>
+      <c r="K56" s="95"/>
+      <c r="L56" s="95"/>
+      <c r="N56" s="95"/>
+      <c r="O56" s="95"/>
+      <c r="P56" s="95"/>
+      <c r="Q56" s="95"/>
+      <c r="R56" s="95"/>
+      <c r="S56" s="95"/>
+      <c r="T56" s="95"/>
+      <c r="U56" s="95"/>
+      <c r="V56" s="95"/>
+      <c r="W56" s="95"/>
+      <c r="X56" s="95"/>
+      <c r="Y56" s="87"/>
+      <c r="Z56" s="87"/>
+      <c r="AA56" s="87"/>
+      <c r="AB56" s="89" t="s">
         <v>47</v>
       </c>
-      <c r="AC56" s="138"/>
-      <c r="AD56" s="138"/>
-      <c r="AE56" s="138"/>
-      <c r="AF56" s="138"/>
-      <c r="AG56" s="138"/>
-      <c r="AH56" s="138"/>
-      <c r="AI56" s="138"/>
-      <c r="AJ56" s="138"/>
+      <c r="AC56" s="89"/>
+      <c r="AD56" s="89"/>
+      <c r="AE56" s="89"/>
+      <c r="AF56" s="89"/>
+      <c r="AG56" s="89"/>
+      <c r="AH56" s="89"/>
+      <c r="AI56" s="89"/>
+      <c r="AJ56" s="89"/>
     </row>
     <row r="57" spans="1:36" ht="18" customHeight="1">
-      <c r="A57" s="137"/>
-      <c r="B57" s="74"/>
-      <c r="C57" s="74"/>
-      <c r="D57" s="74"/>
-      <c r="E57" s="74"/>
-      <c r="F57" s="74"/>
-      <c r="G57" s="74"/>
-      <c r="H57" s="74"/>
-      <c r="I57" s="74"/>
-      <c r="J57" s="74"/>
-      <c r="K57" s="74"/>
-      <c r="L57" s="74"/>
-      <c r="N57" s="74"/>
-      <c r="O57" s="74"/>
-      <c r="P57" s="74"/>
-      <c r="Q57" s="74"/>
-      <c r="R57" s="74"/>
-      <c r="S57" s="74"/>
-      <c r="T57" s="74"/>
-      <c r="U57" s="74"/>
-      <c r="V57" s="74"/>
-      <c r="W57" s="74"/>
-      <c r="X57" s="74"/>
-      <c r="Y57" s="137"/>
-      <c r="Z57" s="137"/>
-      <c r="AA57" s="137"/>
-      <c r="AB57" s="137"/>
-      <c r="AC57" s="137"/>
-      <c r="AD57" s="137"/>
-      <c r="AE57" s="137"/>
-      <c r="AF57" s="137"/>
-      <c r="AG57" s="137"/>
-      <c r="AH57" s="137"/>
-      <c r="AI57" s="137"/>
-      <c r="AJ57" s="137"/>
+      <c r="A57" s="87"/>
+      <c r="B57" s="95"/>
+      <c r="C57" s="95"/>
+      <c r="D57" s="95"/>
+      <c r="E57" s="95"/>
+      <c r="F57" s="95"/>
+      <c r="G57" s="95"/>
+      <c r="H57" s="95"/>
+      <c r="I57" s="95"/>
+      <c r="J57" s="95"/>
+      <c r="K57" s="95"/>
+      <c r="L57" s="95"/>
+      <c r="N57" s="95"/>
+      <c r="O57" s="95"/>
+      <c r="P57" s="95"/>
+      <c r="Q57" s="95"/>
+      <c r="R57" s="95"/>
+      <c r="S57" s="95"/>
+      <c r="T57" s="95"/>
+      <c r="U57" s="95"/>
+      <c r="V57" s="95"/>
+      <c r="W57" s="95"/>
+      <c r="X57" s="95"/>
+      <c r="Y57" s="87"/>
+      <c r="Z57" s="87"/>
+      <c r="AA57" s="87"/>
+      <c r="AB57" s="87"/>
+      <c r="AC57" s="87"/>
+      <c r="AD57" s="87"/>
+      <c r="AE57" s="87"/>
+      <c r="AF57" s="87"/>
+      <c r="AG57" s="87"/>
+      <c r="AH57" s="87"/>
+      <c r="AI57" s="87"/>
+      <c r="AJ57" s="87"/>
     </row>
     <row r="58" spans="1:36" ht="18" customHeight="1">
       <c r="A58" s="51"/>
@@ -9358,47 +9369,47 @@
       <c r="V58" s="52"/>
       <c r="W58" s="52"/>
       <c r="X58" s="52"/>
-      <c r="Y58" s="137"/>
-      <c r="Z58" s="137"/>
-      <c r="AA58" s="137"/>
-      <c r="AB58" s="137"/>
-      <c r="AC58" s="137"/>
-      <c r="AD58" s="137"/>
-      <c r="AE58" s="137"/>
-      <c r="AF58" s="137"/>
-      <c r="AG58" s="137"/>
-      <c r="AH58" s="137"/>
-      <c r="AI58" s="137"/>
-      <c r="AJ58" s="137"/>
+      <c r="Y58" s="87"/>
+      <c r="Z58" s="87"/>
+      <c r="AA58" s="87"/>
+      <c r="AB58" s="87"/>
+      <c r="AC58" s="87"/>
+      <c r="AD58" s="87"/>
+      <c r="AE58" s="87"/>
+      <c r="AF58" s="87"/>
+      <c r="AG58" s="87"/>
+      <c r="AH58" s="87"/>
+      <c r="AI58" s="87"/>
+      <c r="AJ58" s="87"/>
     </row>
     <row r="59" spans="1:36" ht="18" customHeight="1">
-      <c r="A59" s="137"/>
-      <c r="B59" s="137"/>
-      <c r="C59" s="137"/>
-      <c r="D59" s="137"/>
-      <c r="E59" s="137"/>
-      <c r="F59" s="137"/>
-      <c r="G59" s="137"/>
-      <c r="H59" s="137"/>
-      <c r="I59" s="137"/>
-      <c r="J59" s="137"/>
-      <c r="K59" s="137"/>
-      <c r="L59" s="137"/>
-      <c r="M59" s="137"/>
-      <c r="N59" s="137"/>
-      <c r="O59" s="137"/>
-      <c r="P59" s="137"/>
-      <c r="Q59" s="137"/>
-      <c r="R59" s="137"/>
-      <c r="S59" s="137"/>
-      <c r="T59" s="137"/>
-      <c r="U59" s="137"/>
-      <c r="V59" s="137"/>
-      <c r="W59" s="137"/>
-      <c r="X59" s="137"/>
-      <c r="Y59" s="137"/>
-      <c r="Z59" s="137"/>
-      <c r="AA59" s="137"/>
+      <c r="A59" s="87"/>
+      <c r="B59" s="87"/>
+      <c r="C59" s="87"/>
+      <c r="D59" s="87"/>
+      <c r="E59" s="87"/>
+      <c r="F59" s="87"/>
+      <c r="G59" s="87"/>
+      <c r="H59" s="87"/>
+      <c r="I59" s="87"/>
+      <c r="J59" s="87"/>
+      <c r="K59" s="87"/>
+      <c r="L59" s="87"/>
+      <c r="M59" s="87"/>
+      <c r="N59" s="87"/>
+      <c r="O59" s="87"/>
+      <c r="P59" s="87"/>
+      <c r="Q59" s="87"/>
+      <c r="R59" s="87"/>
+      <c r="S59" s="87"/>
+      <c r="T59" s="87"/>
+      <c r="U59" s="87"/>
+      <c r="V59" s="87"/>
+      <c r="W59" s="87"/>
+      <c r="X59" s="87"/>
+      <c r="Y59" s="87"/>
+      <c r="Z59" s="87"/>
+      <c r="AA59" s="87"/>
       <c r="AB59" s="88"/>
       <c r="AC59" s="88"/>
       <c r="AD59" s="88"/>
@@ -9410,20 +9421,20 @@
       <c r="AJ59" s="88"/>
     </row>
     <row r="60" spans="1:36" ht="18" customHeight="1">
-      <c r="Y60" s="137"/>
-      <c r="Z60" s="137"/>
-      <c r="AA60" s="137"/>
-      <c r="AB60" s="136" t="s">
+      <c r="Y60" s="87"/>
+      <c r="Z60" s="87"/>
+      <c r="AA60" s="87"/>
+      <c r="AB60" s="86" t="s">
         <v>92</v>
       </c>
-      <c r="AC60" s="136"/>
-      <c r="AD60" s="136"/>
-      <c r="AE60" s="136"/>
-      <c r="AF60" s="136"/>
-      <c r="AG60" s="136"/>
-      <c r="AH60" s="136"/>
-      <c r="AI60" s="136"/>
-      <c r="AJ60" s="136"/>
+      <c r="AC60" s="86"/>
+      <c r="AD60" s="86"/>
+      <c r="AE60" s="86"/>
+      <c r="AF60" s="86"/>
+      <c r="AG60" s="86"/>
+      <c r="AH60" s="86"/>
+      <c r="AI60" s="86"/>
+      <c r="AJ60" s="86"/>
     </row>
     <row r="61" spans="1:36" ht="16.5" customHeight="1"/>
     <row r="62" spans="1:36" ht="18" hidden="1" customHeight="1"/>
@@ -10025,6 +10036,114 @@
     <row r="658"/>
   </sheetData>
   <mergeCells count="132">
+    <mergeCell ref="AD3:AJ3"/>
+    <mergeCell ref="Y6:AC6"/>
+    <mergeCell ref="Y5:Z5"/>
+    <mergeCell ref="P5:X5"/>
+    <mergeCell ref="AH6:AI6"/>
+    <mergeCell ref="AC7:AE7"/>
+    <mergeCell ref="AI7:AJ7"/>
+    <mergeCell ref="C6:I6"/>
+    <mergeCell ref="S8:W8"/>
+    <mergeCell ref="X7:AB7"/>
+    <mergeCell ref="B57:L57"/>
+    <mergeCell ref="N57:X57"/>
+    <mergeCell ref="Q2:Z2"/>
+    <mergeCell ref="Q3:Z3"/>
+    <mergeCell ref="A11:P11"/>
+    <mergeCell ref="K5:O5"/>
+    <mergeCell ref="K6:O6"/>
+    <mergeCell ref="P6:X6"/>
+    <mergeCell ref="A41:R41"/>
+    <mergeCell ref="S9:W9"/>
+    <mergeCell ref="A7:B7"/>
+    <mergeCell ref="Q11:AJ11"/>
+    <mergeCell ref="C7:I7"/>
+    <mergeCell ref="D8:R8"/>
+    <mergeCell ref="A8:C8"/>
+    <mergeCell ref="S7:T7"/>
+    <mergeCell ref="P7:R7"/>
+    <mergeCell ref="X8:AJ8"/>
+    <mergeCell ref="A10:AJ10"/>
+    <mergeCell ref="A5:B5"/>
+    <mergeCell ref="A6:B6"/>
+    <mergeCell ref="AD6:AF6"/>
+    <mergeCell ref="D9:R9"/>
+    <mergeCell ref="K7:O7"/>
+    <mergeCell ref="A25:AJ25"/>
+    <mergeCell ref="A22:AJ23"/>
+    <mergeCell ref="A17:T20"/>
+    <mergeCell ref="C5:I5"/>
+    <mergeCell ref="AF19:AG19"/>
+    <mergeCell ref="A43:I43"/>
+    <mergeCell ref="AI19:AJ19"/>
+    <mergeCell ref="A14:H14"/>
+    <mergeCell ref="I14:AJ14"/>
+    <mergeCell ref="AI17:AJ17"/>
+    <mergeCell ref="AF17:AG17"/>
+    <mergeCell ref="A15:AJ15"/>
+    <mergeCell ref="AF18:AG18"/>
+    <mergeCell ref="AA5:AJ5"/>
+    <mergeCell ref="V7:W7"/>
+    <mergeCell ref="AI18:AJ18"/>
+    <mergeCell ref="U16:AD16"/>
+    <mergeCell ref="AF7:AG7"/>
+    <mergeCell ref="AE16:AJ16"/>
+    <mergeCell ref="A16:T16"/>
+    <mergeCell ref="A9:C9"/>
+    <mergeCell ref="X9:AJ9"/>
+    <mergeCell ref="AB46:AE46"/>
+    <mergeCell ref="S44:V44"/>
+    <mergeCell ref="S45:V45"/>
+    <mergeCell ref="S46:W46"/>
+    <mergeCell ref="X46:Z46"/>
+    <mergeCell ref="K46:R46"/>
+    <mergeCell ref="K45:R45"/>
+    <mergeCell ref="AB44:AE44"/>
+    <mergeCell ref="J53:R53"/>
+    <mergeCell ref="AB45:AE45"/>
+    <mergeCell ref="K44:R44"/>
+    <mergeCell ref="B48:I48"/>
+    <mergeCell ref="AF47:AI47"/>
+    <mergeCell ref="AB49:AF49"/>
+    <mergeCell ref="AF53:AH53"/>
+    <mergeCell ref="AB50:AJ50"/>
+    <mergeCell ref="AC51:AJ51"/>
+    <mergeCell ref="B49:I49"/>
+    <mergeCell ref="B52:C52"/>
+    <mergeCell ref="D52:H52"/>
+    <mergeCell ref="K50:R50"/>
+    <mergeCell ref="K51:R51"/>
+    <mergeCell ref="S47:W47"/>
+    <mergeCell ref="T49:AA49"/>
+    <mergeCell ref="K48:R48"/>
+    <mergeCell ref="K49:R49"/>
+    <mergeCell ref="W52:Y52"/>
+    <mergeCell ref="K47:R47"/>
+    <mergeCell ref="AB60:AJ60"/>
+    <mergeCell ref="AB57:AJ59"/>
+    <mergeCell ref="AB56:AJ56"/>
+    <mergeCell ref="S48:AA48"/>
+    <mergeCell ref="AG48:AI48"/>
+    <mergeCell ref="AC53:AE53"/>
+    <mergeCell ref="T52:V52"/>
+    <mergeCell ref="W53:Y53"/>
+    <mergeCell ref="B56:L56"/>
+    <mergeCell ref="N56:X56"/>
+    <mergeCell ref="Y55:AA60"/>
+    <mergeCell ref="A59:X59"/>
+    <mergeCell ref="A55:A57"/>
+    <mergeCell ref="N55:X55"/>
+    <mergeCell ref="A54:M54"/>
+    <mergeCell ref="N54:AJ54"/>
+    <mergeCell ref="D53:H53"/>
+    <mergeCell ref="B50:I50"/>
+    <mergeCell ref="B55:L55"/>
+    <mergeCell ref="K52:R52"/>
+    <mergeCell ref="T53:V53"/>
+    <mergeCell ref="AB55:AJ55"/>
+    <mergeCell ref="W51:Y51"/>
+    <mergeCell ref="AC52:AJ52"/>
     <mergeCell ref="AF46:AI46"/>
     <mergeCell ref="T50:AA50"/>
     <mergeCell ref="AF45:AI45"/>
@@ -10049,114 +10168,6 @@
     <mergeCell ref="B45:I45"/>
     <mergeCell ref="AB47:AE47"/>
     <mergeCell ref="B46:I46"/>
-    <mergeCell ref="AB60:AJ60"/>
-    <mergeCell ref="AB57:AJ59"/>
-    <mergeCell ref="AB56:AJ56"/>
-    <mergeCell ref="S48:AA48"/>
-    <mergeCell ref="AG48:AI48"/>
-    <mergeCell ref="AC53:AE53"/>
-    <mergeCell ref="T52:V52"/>
-    <mergeCell ref="W53:Y53"/>
-    <mergeCell ref="B56:L56"/>
-    <mergeCell ref="N56:X56"/>
-    <mergeCell ref="Y55:AA60"/>
-    <mergeCell ref="A59:X59"/>
-    <mergeCell ref="A55:A57"/>
-    <mergeCell ref="N55:X55"/>
-    <mergeCell ref="A54:M54"/>
-    <mergeCell ref="N54:AJ54"/>
-    <mergeCell ref="D53:H53"/>
-    <mergeCell ref="B50:I50"/>
-    <mergeCell ref="B55:L55"/>
-    <mergeCell ref="K52:R52"/>
-    <mergeCell ref="T53:V53"/>
-    <mergeCell ref="AB55:AJ55"/>
-    <mergeCell ref="W51:Y51"/>
-    <mergeCell ref="AC52:AJ52"/>
-    <mergeCell ref="B48:I48"/>
-    <mergeCell ref="AF47:AI47"/>
-    <mergeCell ref="AB49:AF49"/>
-    <mergeCell ref="AF53:AH53"/>
-    <mergeCell ref="AB50:AJ50"/>
-    <mergeCell ref="AC51:AJ51"/>
-    <mergeCell ref="B49:I49"/>
-    <mergeCell ref="B52:C52"/>
-    <mergeCell ref="D52:H52"/>
-    <mergeCell ref="K50:R50"/>
-    <mergeCell ref="K51:R51"/>
-    <mergeCell ref="S47:W47"/>
-    <mergeCell ref="T49:AA49"/>
-    <mergeCell ref="K48:R48"/>
-    <mergeCell ref="K49:R49"/>
-    <mergeCell ref="W52:Y52"/>
-    <mergeCell ref="K47:R47"/>
-    <mergeCell ref="AB46:AE46"/>
-    <mergeCell ref="S44:V44"/>
-    <mergeCell ref="S45:V45"/>
-    <mergeCell ref="S46:W46"/>
-    <mergeCell ref="X46:Z46"/>
-    <mergeCell ref="K46:R46"/>
-    <mergeCell ref="K45:R45"/>
-    <mergeCell ref="AB44:AE44"/>
-    <mergeCell ref="J53:R53"/>
-    <mergeCell ref="AB45:AE45"/>
-    <mergeCell ref="A25:AJ25"/>
-    <mergeCell ref="A22:AJ23"/>
-    <mergeCell ref="A17:T20"/>
-    <mergeCell ref="C5:I5"/>
-    <mergeCell ref="AF19:AG19"/>
-    <mergeCell ref="A43:I43"/>
-    <mergeCell ref="AI19:AJ19"/>
-    <mergeCell ref="A14:H14"/>
-    <mergeCell ref="I14:AJ14"/>
-    <mergeCell ref="AI17:AJ17"/>
-    <mergeCell ref="AF17:AG17"/>
-    <mergeCell ref="A15:AJ15"/>
-    <mergeCell ref="AF18:AG18"/>
-    <mergeCell ref="AA5:AJ5"/>
-    <mergeCell ref="V7:W7"/>
-    <mergeCell ref="AI18:AJ18"/>
-    <mergeCell ref="U16:AD16"/>
-    <mergeCell ref="AF7:AG7"/>
-    <mergeCell ref="K44:R44"/>
-    <mergeCell ref="B57:L57"/>
-    <mergeCell ref="N57:X57"/>
-    <mergeCell ref="Q2:Z2"/>
-    <mergeCell ref="Q3:Z3"/>
-    <mergeCell ref="A11:P11"/>
-    <mergeCell ref="K5:O5"/>
-    <mergeCell ref="K6:O6"/>
-    <mergeCell ref="P6:X6"/>
-    <mergeCell ref="A41:R41"/>
-    <mergeCell ref="S9:W9"/>
-    <mergeCell ref="A7:B7"/>
-    <mergeCell ref="Q11:AJ11"/>
-    <mergeCell ref="C7:I7"/>
-    <mergeCell ref="D8:R8"/>
-    <mergeCell ref="A8:C8"/>
-    <mergeCell ref="S7:T7"/>
-    <mergeCell ref="P7:R7"/>
-    <mergeCell ref="X8:AJ8"/>
-    <mergeCell ref="A10:AJ10"/>
-    <mergeCell ref="A5:B5"/>
-    <mergeCell ref="A6:B6"/>
-    <mergeCell ref="AD6:AF6"/>
-    <mergeCell ref="D9:R9"/>
-    <mergeCell ref="K7:O7"/>
-    <mergeCell ref="AE16:AJ16"/>
-    <mergeCell ref="A16:T16"/>
-    <mergeCell ref="AD3:AJ3"/>
-    <mergeCell ref="Y6:AC6"/>
-    <mergeCell ref="Y5:Z5"/>
-    <mergeCell ref="P5:X5"/>
-    <mergeCell ref="AH6:AI6"/>
-    <mergeCell ref="AC7:AE7"/>
-    <mergeCell ref="AI7:AJ7"/>
-    <mergeCell ref="C6:I6"/>
-    <mergeCell ref="S8:W8"/>
-    <mergeCell ref="A9:C9"/>
-    <mergeCell ref="X9:AJ9"/>
-    <mergeCell ref="X7:AB7"/>
   </mergeCells>
   <phoneticPr fontId="0" type="noConversion"/>
   <printOptions horizontalCentered="1"/>
@@ -10225,7 +10236,7 @@
                   </from>
                   <to>
                     <xdr:col>5</xdr:col>
-                    <xdr:colOff>53340</xdr:colOff>
+                    <xdr:colOff>99060</xdr:colOff>
                     <xdr:row>12</xdr:row>
                     <xdr:rowOff>15240</xdr:rowOff>
                   </to>
@@ -10247,7 +10258,7 @@
                   </from>
                   <to>
                     <xdr:col>5</xdr:col>
-                    <xdr:colOff>53340</xdr:colOff>
+                    <xdr:colOff>99060</xdr:colOff>
                     <xdr:row>13</xdr:row>
                     <xdr:rowOff>15240</xdr:rowOff>
                   </to>
@@ -10268,8 +10279,8 @@
                     <xdr:rowOff>30480</xdr:rowOff>
                   </from>
                   <to>
-                    <xdr:col>8</xdr:col>
-                    <xdr:colOff>396240</xdr:colOff>
+                    <xdr:col>9</xdr:col>
+                    <xdr:colOff>121920</xdr:colOff>
                     <xdr:row>12</xdr:row>
                     <xdr:rowOff>15240</xdr:rowOff>
                   </to>
@@ -10290,8 +10301,8 @@
                     <xdr:rowOff>7620</xdr:rowOff>
                   </from>
                   <to>
-                    <xdr:col>8</xdr:col>
-                    <xdr:colOff>396240</xdr:colOff>
+                    <xdr:col>9</xdr:col>
+                    <xdr:colOff>121920</xdr:colOff>
                     <xdr:row>13</xdr:row>
                     <xdr:rowOff>15240</xdr:rowOff>
                   </to>
@@ -10929,7 +10940,7 @@
                   </from>
                   <to>
                     <xdr:col>10</xdr:col>
-                    <xdr:colOff>91440</xdr:colOff>
+                    <xdr:colOff>160020</xdr:colOff>
                     <xdr:row>44</xdr:row>
                     <xdr:rowOff>15240</xdr:rowOff>
                   </to>
@@ -10951,7 +10962,7 @@
                   </from>
                   <to>
                     <xdr:col>10</xdr:col>
-                    <xdr:colOff>91440</xdr:colOff>
+                    <xdr:colOff>160020</xdr:colOff>
                     <xdr:row>45</xdr:row>
                     <xdr:rowOff>15240</xdr:rowOff>
                   </to>
@@ -10973,7 +10984,7 @@
                   </from>
                   <to>
                     <xdr:col>10</xdr:col>
-                    <xdr:colOff>91440</xdr:colOff>
+                    <xdr:colOff>160020</xdr:colOff>
                     <xdr:row>46</xdr:row>
                     <xdr:rowOff>15240</xdr:rowOff>
                   </to>
@@ -10995,7 +11006,7 @@
                   </from>
                   <to>
                     <xdr:col>10</xdr:col>
-                    <xdr:colOff>91440</xdr:colOff>
+                    <xdr:colOff>160020</xdr:colOff>
                     <xdr:row>47</xdr:row>
                     <xdr:rowOff>15240</xdr:rowOff>
                   </to>
@@ -11017,7 +11028,7 @@
                   </from>
                   <to>
                     <xdr:col>10</xdr:col>
-                    <xdr:colOff>91440</xdr:colOff>
+                    <xdr:colOff>160020</xdr:colOff>
                     <xdr:row>48</xdr:row>
                     <xdr:rowOff>15240</xdr:rowOff>
                   </to>
@@ -11039,7 +11050,7 @@
                   </from>
                   <to>
                     <xdr:col>10</xdr:col>
-                    <xdr:colOff>91440</xdr:colOff>
+                    <xdr:colOff>160020</xdr:colOff>
                     <xdr:row>49</xdr:row>
                     <xdr:rowOff>15240</xdr:rowOff>
                   </to>
@@ -11061,7 +11072,7 @@
                   </from>
                   <to>
                     <xdr:col>10</xdr:col>
-                    <xdr:colOff>91440</xdr:colOff>
+                    <xdr:colOff>160020</xdr:colOff>
                     <xdr:row>50</xdr:row>
                     <xdr:rowOff>15240</xdr:rowOff>
                   </to>
@@ -11083,7 +11094,7 @@
                   </from>
                   <to>
                     <xdr:col>10</xdr:col>
-                    <xdr:colOff>91440</xdr:colOff>
+                    <xdr:colOff>160020</xdr:colOff>
                     <xdr:row>51</xdr:row>
                     <xdr:rowOff>15240</xdr:rowOff>
                   </to>
@@ -11105,7 +11116,7 @@
                   </from>
                   <to>
                     <xdr:col>10</xdr:col>
-                    <xdr:colOff>91440</xdr:colOff>
+                    <xdr:colOff>160020</xdr:colOff>
                     <xdr:row>52</xdr:row>
                     <xdr:rowOff>15240</xdr:rowOff>
                   </to>

--- a/backend_api/templates/container_report_template.xlsx
+++ b/backend_api/templates/container_report_template.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Aaron Avila\Documents\ERP-SOM\backend_api\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2CA2A823-9724-484E-89AF-79C1879E1766}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D6DD7CB7-A98A-4B70-9CC8-95C821D79277}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-1125" windowWidth="29040" windowHeight="15720" xr2:uid="{253FFB1B-D348-46B1-A532-0D44566D2FFD}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{253FFB1B-D348-46B1-A532-0D44566D2FFD}"/>
   </bookViews>
   <sheets>
     <sheet name="DRY CARGO" sheetId="1" r:id="rId1"/>
@@ -1425,7 +1425,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="164">
+  <cellXfs count="165">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -1936,6 +1936,7 @@
       <alignment horizontal="left" wrapText="1"/>
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -6995,7 +6996,7 @@
   <sheetFormatPr defaultColWidth="4" defaultRowHeight="13.2" zeroHeight="1"/>
   <cols>
     <col min="1" max="2" width="4" customWidth="1"/>
-    <col min="3" max="3" width="1.109375" customWidth="1"/>
+    <col min="3" max="3" width="3.5546875" customWidth="1"/>
     <col min="4" max="4" width="4" customWidth="1"/>
     <col min="5" max="5" width="3.33203125" customWidth="1"/>
     <col min="6" max="6" width="2.5546875" customWidth="1"/>
@@ -7009,7 +7010,7 @@
     <col min="15" max="15" width="7" customWidth="1"/>
     <col min="16" max="16" width="11.109375" customWidth="1"/>
     <col min="22" max="22" width="12" customWidth="1"/>
-    <col min="29" max="29" width="11.44140625" customWidth="1"/>
+    <col min="29" max="29" width="8.77734375" customWidth="1"/>
     <col min="31" max="31" width="2.88671875" bestFit="1" customWidth="1"/>
     <col min="32" max="32" width="5.21875" customWidth="1"/>
     <col min="33" max="33" width="12.33203125" customWidth="1"/>
@@ -7208,13 +7209,13 @@
       <c r="V6" s="146"/>
       <c r="W6" s="146"/>
       <c r="X6" s="146"/>
-      <c r="Y6" s="144" t="s">
+      <c r="Y6" s="164" t="s">
         <v>88</v>
       </c>
-      <c r="Z6" s="144"/>
-      <c r="AA6" s="144"/>
-      <c r="AB6" s="144"/>
-      <c r="AC6" s="144"/>
+      <c r="Z6" s="164"/>
+      <c r="AA6" s="164"/>
+      <c r="AB6" s="164"/>
+      <c r="AC6" s="164"/>
       <c r="AD6" s="78"/>
       <c r="AE6" s="78"/>
       <c r="AF6" s="78"/>
@@ -10035,9 +10036,8 @@
     <row r="657"/>
     <row r="658"/>
   </sheetData>
-  <mergeCells count="132">
+  <mergeCells count="131">
     <mergeCell ref="AD3:AJ3"/>
-    <mergeCell ref="Y6:AC6"/>
     <mergeCell ref="Y5:Z5"/>
     <mergeCell ref="P5:X5"/>
     <mergeCell ref="AH6:AI6"/>

--- a/backend_api/templates/container_report_template.xlsx
+++ b/backend_api/templates/container_report_template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Aaron Avila\Documents\ERP-SOM\backend_api\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D6DD7CB7-A98A-4B70-9CC8-95C821D79277}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{A2125F2B-319E-4DCB-8DE4-F8C7A6B063DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{253FFB1B-D348-46B1-A532-0D44566D2FFD}"/>
   </bookViews>
@@ -1562,26 +1562,324 @@
       <alignment vertical="top" wrapText="1"/>
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="4" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="165" fontId="13" fillId="0" borderId="8" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="14" fontId="13" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="8" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="9" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="6" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="2" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="3" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="4" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="5" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="3" fontId="13" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="13" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="9" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="6" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="6" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="6" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="2" borderId="9" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="2" borderId="6" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="2" borderId="7" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="4" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="4" fontId="13" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
     <xf numFmtId="4" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="4" fontId="13" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right"/>
-      <protection locked="0"/>
-    </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
       <protection locked="0"/>
@@ -1610,25 +1908,6 @@
       <alignment horizontal="left" vertical="top" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="9" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="6" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
@@ -1637,10 +1916,6 @@
     </xf>
     <xf numFmtId="0" fontId="22" fillId="2" borderId="9" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="13" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -1662,281 +1937,6 @@
       <alignment horizontal="left" vertical="top" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="4" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="3" fontId="13" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="2" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="3" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="4" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="5" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="3" fontId="13" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="9" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="6" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="6" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="6" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="165" fontId="13" fillId="0" borderId="8" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="8" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="2" borderId="9" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="2" borderId="6" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="2" borderId="7" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="4" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2236,10 +2236,10 @@
           <xdr:rowOff>30480</xdr:rowOff>
         </xdr:from>
         <xdr:to>
-          <xdr:col>1</xdr:col>
-          <xdr:colOff>57150</xdr:colOff>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>327660</xdr:colOff>
           <xdr:row>12</xdr:row>
-          <xdr:rowOff>19050</xdr:rowOff>
+          <xdr:rowOff>15240</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -2303,10 +2303,10 @@
           <xdr:rowOff>7620</xdr:rowOff>
         </xdr:from>
         <xdr:to>
-          <xdr:col>1</xdr:col>
-          <xdr:colOff>57150</xdr:colOff>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>327660</xdr:colOff>
           <xdr:row>13</xdr:row>
-          <xdr:rowOff>19050</xdr:rowOff>
+          <xdr:rowOff>15240</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -2370,10 +2370,10 @@
           <xdr:rowOff>30480</xdr:rowOff>
         </xdr:from>
         <xdr:to>
-          <xdr:col>5</xdr:col>
-          <xdr:colOff>97155</xdr:colOff>
+          <xdr:col>4</xdr:col>
+          <xdr:colOff>327660</xdr:colOff>
           <xdr:row>12</xdr:row>
-          <xdr:rowOff>19050</xdr:rowOff>
+          <xdr:rowOff>15240</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -2437,10 +2437,10 @@
           <xdr:rowOff>7620</xdr:rowOff>
         </xdr:from>
         <xdr:to>
-          <xdr:col>5</xdr:col>
-          <xdr:colOff>97155</xdr:colOff>
+          <xdr:col>4</xdr:col>
+          <xdr:colOff>327660</xdr:colOff>
           <xdr:row>13</xdr:row>
-          <xdr:rowOff>19050</xdr:rowOff>
+          <xdr:rowOff>15240</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -2504,10 +2504,10 @@
           <xdr:rowOff>30480</xdr:rowOff>
         </xdr:from>
         <xdr:to>
-          <xdr:col>9</xdr:col>
-          <xdr:colOff>133350</xdr:colOff>
+          <xdr:col>8</xdr:col>
+          <xdr:colOff>396240</xdr:colOff>
           <xdr:row>12</xdr:row>
-          <xdr:rowOff>19050</xdr:rowOff>
+          <xdr:rowOff>15240</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -2571,10 +2571,10 @@
           <xdr:rowOff>7620</xdr:rowOff>
         </xdr:from>
         <xdr:to>
-          <xdr:col>9</xdr:col>
-          <xdr:colOff>133350</xdr:colOff>
+          <xdr:col>8</xdr:col>
+          <xdr:colOff>396240</xdr:colOff>
           <xdr:row>13</xdr:row>
-          <xdr:rowOff>19050</xdr:rowOff>
+          <xdr:rowOff>15240</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -2638,10 +2638,10 @@
           <xdr:rowOff>30480</xdr:rowOff>
         </xdr:from>
         <xdr:to>
-          <xdr:col>14</xdr:col>
-          <xdr:colOff>57150</xdr:colOff>
+          <xdr:col>13</xdr:col>
+          <xdr:colOff>327660</xdr:colOff>
           <xdr:row>12</xdr:row>
-          <xdr:rowOff>19050</xdr:rowOff>
+          <xdr:rowOff>15240</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -2705,10 +2705,10 @@
           <xdr:rowOff>7620</xdr:rowOff>
         </xdr:from>
         <xdr:to>
-          <xdr:col>14</xdr:col>
-          <xdr:colOff>57150</xdr:colOff>
+          <xdr:col>13</xdr:col>
+          <xdr:colOff>327660</xdr:colOff>
           <xdr:row>13</xdr:row>
-          <xdr:rowOff>19050</xdr:rowOff>
+          <xdr:rowOff>15240</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -2773,9 +2773,9 @@
         </xdr:from>
         <xdr:to>
           <xdr:col>17</xdr:col>
-          <xdr:colOff>57150</xdr:colOff>
+          <xdr:colOff>53340</xdr:colOff>
           <xdr:row>12</xdr:row>
-          <xdr:rowOff>19050</xdr:rowOff>
+          <xdr:rowOff>15240</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -2840,9 +2840,9 @@
         </xdr:from>
         <xdr:to>
           <xdr:col>17</xdr:col>
-          <xdr:colOff>57150</xdr:colOff>
+          <xdr:colOff>53340</xdr:colOff>
           <xdr:row>13</xdr:row>
-          <xdr:rowOff>19050</xdr:rowOff>
+          <xdr:rowOff>15240</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -2907,9 +2907,9 @@
         </xdr:from>
         <xdr:to>
           <xdr:col>23</xdr:col>
-          <xdr:colOff>57150</xdr:colOff>
+          <xdr:colOff>53340</xdr:colOff>
           <xdr:row>12</xdr:row>
-          <xdr:rowOff>19050</xdr:rowOff>
+          <xdr:rowOff>15240</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -2974,9 +2974,9 @@
         </xdr:from>
         <xdr:to>
           <xdr:col>23</xdr:col>
-          <xdr:colOff>57150</xdr:colOff>
+          <xdr:colOff>53340</xdr:colOff>
           <xdr:row>13</xdr:row>
-          <xdr:rowOff>19050</xdr:rowOff>
+          <xdr:rowOff>15240</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -3041,9 +3041,9 @@
         </xdr:from>
         <xdr:to>
           <xdr:col>28</xdr:col>
-          <xdr:colOff>57150</xdr:colOff>
+          <xdr:colOff>53340</xdr:colOff>
           <xdr:row>12</xdr:row>
-          <xdr:rowOff>19050</xdr:rowOff>
+          <xdr:rowOff>15240</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -3108,9 +3108,9 @@
         </xdr:from>
         <xdr:to>
           <xdr:col>28</xdr:col>
-          <xdr:colOff>57150</xdr:colOff>
+          <xdr:colOff>53340</xdr:colOff>
           <xdr:row>13</xdr:row>
-          <xdr:rowOff>19050</xdr:rowOff>
+          <xdr:rowOff>15240</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -3177,7 +3177,7 @@
           <xdr:col>32</xdr:col>
           <xdr:colOff>342900</xdr:colOff>
           <xdr:row>12</xdr:row>
-          <xdr:rowOff>19050</xdr:rowOff>
+          <xdr:rowOff>15240</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -3244,7 +3244,7 @@
           <xdr:col>32</xdr:col>
           <xdr:colOff>342900</xdr:colOff>
           <xdr:row>13</xdr:row>
-          <xdr:rowOff>19050</xdr:rowOff>
+          <xdr:rowOff>15240</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -3309,9 +3309,9 @@
         </xdr:from>
         <xdr:to>
           <xdr:col>21</xdr:col>
-          <xdr:colOff>95250</xdr:colOff>
+          <xdr:colOff>91440</xdr:colOff>
           <xdr:row>17</xdr:row>
-          <xdr:rowOff>19050</xdr:rowOff>
+          <xdr:rowOff>15240</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -3376,9 +3376,9 @@
         </xdr:from>
         <xdr:to>
           <xdr:col>21</xdr:col>
-          <xdr:colOff>95250</xdr:colOff>
+          <xdr:colOff>91440</xdr:colOff>
           <xdr:row>18</xdr:row>
-          <xdr:rowOff>19050</xdr:rowOff>
+          <xdr:rowOff>15240</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -3443,9 +3443,9 @@
         </xdr:from>
         <xdr:to>
           <xdr:col>21</xdr:col>
-          <xdr:colOff>95250</xdr:colOff>
+          <xdr:colOff>91440</xdr:colOff>
           <xdr:row>19</xdr:row>
-          <xdr:rowOff>19050</xdr:rowOff>
+          <xdr:rowOff>15240</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -3510,9 +3510,9 @@
         </xdr:from>
         <xdr:to>
           <xdr:col>25</xdr:col>
-          <xdr:colOff>95250</xdr:colOff>
+          <xdr:colOff>91440</xdr:colOff>
           <xdr:row>17</xdr:row>
-          <xdr:rowOff>19050</xdr:rowOff>
+          <xdr:rowOff>15240</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -3577,9 +3577,9 @@
         </xdr:from>
         <xdr:to>
           <xdr:col>25</xdr:col>
-          <xdr:colOff>95250</xdr:colOff>
+          <xdr:colOff>91440</xdr:colOff>
           <xdr:row>18</xdr:row>
-          <xdr:rowOff>19050</xdr:rowOff>
+          <xdr:rowOff>15240</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -3644,9 +3644,9 @@
         </xdr:from>
         <xdr:to>
           <xdr:col>25</xdr:col>
-          <xdr:colOff>95250</xdr:colOff>
+          <xdr:colOff>91440</xdr:colOff>
           <xdr:row>19</xdr:row>
-          <xdr:rowOff>19050</xdr:rowOff>
+          <xdr:rowOff>15240</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -3711,9 +3711,9 @@
         </xdr:from>
         <xdr:to>
           <xdr:col>28</xdr:col>
-          <xdr:colOff>95250</xdr:colOff>
+          <xdr:colOff>91440</xdr:colOff>
           <xdr:row>17</xdr:row>
-          <xdr:rowOff>19050</xdr:rowOff>
+          <xdr:rowOff>15240</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -3778,9 +3778,9 @@
         </xdr:from>
         <xdr:to>
           <xdr:col>28</xdr:col>
-          <xdr:colOff>95250</xdr:colOff>
+          <xdr:colOff>91440</xdr:colOff>
           <xdr:row>18</xdr:row>
-          <xdr:rowOff>19050</xdr:rowOff>
+          <xdr:rowOff>15240</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -3845,9 +3845,9 @@
         </xdr:from>
         <xdr:to>
           <xdr:col>28</xdr:col>
-          <xdr:colOff>95250</xdr:colOff>
+          <xdr:colOff>91440</xdr:colOff>
           <xdr:row>19</xdr:row>
-          <xdr:rowOff>19050</xdr:rowOff>
+          <xdr:rowOff>15240</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -3911,10 +3911,10 @@
           <xdr:rowOff>30480</xdr:rowOff>
         </xdr:from>
         <xdr:to>
-          <xdr:col>1</xdr:col>
-          <xdr:colOff>95250</xdr:colOff>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>365760</xdr:colOff>
           <xdr:row>44</xdr:row>
-          <xdr:rowOff>19050</xdr:rowOff>
+          <xdr:rowOff>15240</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -3978,10 +3978,10 @@
           <xdr:rowOff>30480</xdr:rowOff>
         </xdr:from>
         <xdr:to>
-          <xdr:col>1</xdr:col>
-          <xdr:colOff>95250</xdr:colOff>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>365760</xdr:colOff>
           <xdr:row>45</xdr:row>
-          <xdr:rowOff>19050</xdr:rowOff>
+          <xdr:rowOff>15240</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -4045,10 +4045,10 @@
           <xdr:rowOff>30480</xdr:rowOff>
         </xdr:from>
         <xdr:to>
-          <xdr:col>1</xdr:col>
-          <xdr:colOff>95250</xdr:colOff>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>365760</xdr:colOff>
           <xdr:row>46</xdr:row>
-          <xdr:rowOff>19050</xdr:rowOff>
+          <xdr:rowOff>15240</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -4112,10 +4112,10 @@
           <xdr:rowOff>30480</xdr:rowOff>
         </xdr:from>
         <xdr:to>
-          <xdr:col>1</xdr:col>
-          <xdr:colOff>95250</xdr:colOff>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>365760</xdr:colOff>
           <xdr:row>47</xdr:row>
-          <xdr:rowOff>19050</xdr:rowOff>
+          <xdr:rowOff>15240</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -4179,10 +4179,10 @@
           <xdr:rowOff>30480</xdr:rowOff>
         </xdr:from>
         <xdr:to>
-          <xdr:col>1</xdr:col>
-          <xdr:colOff>95250</xdr:colOff>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>365760</xdr:colOff>
           <xdr:row>48</xdr:row>
-          <xdr:rowOff>19050</xdr:rowOff>
+          <xdr:rowOff>15240</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -4246,10 +4246,10 @@
           <xdr:rowOff>30480</xdr:rowOff>
         </xdr:from>
         <xdr:to>
-          <xdr:col>1</xdr:col>
-          <xdr:colOff>95250</xdr:colOff>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>365760</xdr:colOff>
           <xdr:row>49</xdr:row>
-          <xdr:rowOff>19050</xdr:rowOff>
+          <xdr:rowOff>15240</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -4313,10 +4313,10 @@
           <xdr:rowOff>30480</xdr:rowOff>
         </xdr:from>
         <xdr:to>
-          <xdr:col>1</xdr:col>
-          <xdr:colOff>95250</xdr:colOff>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>365760</xdr:colOff>
           <xdr:row>50</xdr:row>
-          <xdr:rowOff>19050</xdr:rowOff>
+          <xdr:rowOff>15240</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -4380,10 +4380,10 @@
           <xdr:rowOff>30480</xdr:rowOff>
         </xdr:from>
         <xdr:to>
-          <xdr:col>1</xdr:col>
-          <xdr:colOff>95250</xdr:colOff>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>365760</xdr:colOff>
           <xdr:row>51</xdr:row>
-          <xdr:rowOff>19050</xdr:rowOff>
+          <xdr:rowOff>15240</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -4447,10 +4447,10 @@
           <xdr:rowOff>30480</xdr:rowOff>
         </xdr:from>
         <xdr:to>
-          <xdr:col>1</xdr:col>
-          <xdr:colOff>95250</xdr:colOff>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>365760</xdr:colOff>
           <xdr:row>52</xdr:row>
-          <xdr:rowOff>19050</xdr:rowOff>
+          <xdr:rowOff>15240</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -4515,9 +4515,9 @@
         </xdr:from>
         <xdr:to>
           <xdr:col>10</xdr:col>
-          <xdr:colOff>171450</xdr:colOff>
+          <xdr:colOff>160020</xdr:colOff>
           <xdr:row>44</xdr:row>
-          <xdr:rowOff>19050</xdr:rowOff>
+          <xdr:rowOff>15240</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -4582,9 +4582,9 @@
         </xdr:from>
         <xdr:to>
           <xdr:col>10</xdr:col>
-          <xdr:colOff>171450</xdr:colOff>
+          <xdr:colOff>160020</xdr:colOff>
           <xdr:row>45</xdr:row>
-          <xdr:rowOff>19050</xdr:rowOff>
+          <xdr:rowOff>15240</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -4649,9 +4649,9 @@
         </xdr:from>
         <xdr:to>
           <xdr:col>10</xdr:col>
-          <xdr:colOff>171450</xdr:colOff>
+          <xdr:colOff>160020</xdr:colOff>
           <xdr:row>46</xdr:row>
-          <xdr:rowOff>19050</xdr:rowOff>
+          <xdr:rowOff>15240</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -4716,9 +4716,9 @@
         </xdr:from>
         <xdr:to>
           <xdr:col>10</xdr:col>
-          <xdr:colOff>171450</xdr:colOff>
+          <xdr:colOff>160020</xdr:colOff>
           <xdr:row>47</xdr:row>
-          <xdr:rowOff>19050</xdr:rowOff>
+          <xdr:rowOff>15240</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -4783,9 +4783,9 @@
         </xdr:from>
         <xdr:to>
           <xdr:col>10</xdr:col>
-          <xdr:colOff>171450</xdr:colOff>
+          <xdr:colOff>160020</xdr:colOff>
           <xdr:row>48</xdr:row>
-          <xdr:rowOff>19050</xdr:rowOff>
+          <xdr:rowOff>15240</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -4850,9 +4850,9 @@
         </xdr:from>
         <xdr:to>
           <xdr:col>10</xdr:col>
-          <xdr:colOff>171450</xdr:colOff>
+          <xdr:colOff>160020</xdr:colOff>
           <xdr:row>49</xdr:row>
-          <xdr:rowOff>19050</xdr:rowOff>
+          <xdr:rowOff>15240</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -4917,9 +4917,9 @@
         </xdr:from>
         <xdr:to>
           <xdr:col>10</xdr:col>
-          <xdr:colOff>171450</xdr:colOff>
+          <xdr:colOff>160020</xdr:colOff>
           <xdr:row>50</xdr:row>
-          <xdr:rowOff>19050</xdr:rowOff>
+          <xdr:rowOff>15240</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -4984,9 +4984,9 @@
         </xdr:from>
         <xdr:to>
           <xdr:col>10</xdr:col>
-          <xdr:colOff>171450</xdr:colOff>
+          <xdr:colOff>160020</xdr:colOff>
           <xdr:row>51</xdr:row>
-          <xdr:rowOff>19050</xdr:rowOff>
+          <xdr:rowOff>15240</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -5051,9 +5051,9 @@
         </xdr:from>
         <xdr:to>
           <xdr:col>10</xdr:col>
-          <xdr:colOff>171450</xdr:colOff>
+          <xdr:colOff>160020</xdr:colOff>
           <xdr:row>52</xdr:row>
-          <xdr:rowOff>19050</xdr:rowOff>
+          <xdr:rowOff>15240</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -5118,9 +5118,9 @@
         </xdr:from>
         <xdr:to>
           <xdr:col>19</xdr:col>
-          <xdr:colOff>95250</xdr:colOff>
+          <xdr:colOff>91440</xdr:colOff>
           <xdr:row>49</xdr:row>
-          <xdr:rowOff>19050</xdr:rowOff>
+          <xdr:rowOff>15240</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -5185,9 +5185,9 @@
         </xdr:from>
         <xdr:to>
           <xdr:col>19</xdr:col>
-          <xdr:colOff>95250</xdr:colOff>
+          <xdr:colOff>91440</xdr:colOff>
           <xdr:row>50</xdr:row>
-          <xdr:rowOff>19050</xdr:rowOff>
+          <xdr:rowOff>15240</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -5252,9 +5252,9 @@
         </xdr:from>
         <xdr:to>
           <xdr:col>28</xdr:col>
-          <xdr:colOff>95250</xdr:colOff>
+          <xdr:colOff>91440</xdr:colOff>
           <xdr:row>51</xdr:row>
-          <xdr:rowOff>19050</xdr:rowOff>
+          <xdr:rowOff>15240</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -5319,9 +5319,9 @@
         </xdr:from>
         <xdr:to>
           <xdr:col>28</xdr:col>
-          <xdr:colOff>95250</xdr:colOff>
+          <xdr:colOff>91440</xdr:colOff>
           <xdr:row>52</xdr:row>
-          <xdr:rowOff>19050</xdr:rowOff>
+          <xdr:rowOff>15240</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -5386,9 +5386,9 @@
         </xdr:from>
         <xdr:to>
           <xdr:col>28</xdr:col>
-          <xdr:colOff>95250</xdr:colOff>
+          <xdr:colOff>91440</xdr:colOff>
           <xdr:row>53</xdr:row>
-          <xdr:rowOff>19050</xdr:rowOff>
+          <xdr:rowOff>15240</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -6371,9 +6371,9 @@
         </xdr:from>
         <xdr:to>
           <xdr:col>28</xdr:col>
-          <xdr:colOff>95250</xdr:colOff>
+          <xdr:colOff>91440</xdr:colOff>
           <xdr:row>53</xdr:row>
-          <xdr:rowOff>19050</xdr:rowOff>
+          <xdr:rowOff>15240</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -6995,18 +6995,20 @@
   <dimension ref="A1:AJ658"/>
   <sheetFormatPr defaultColWidth="4" defaultRowHeight="13.2" zeroHeight="1"/>
   <cols>
-    <col min="1" max="2" width="4" customWidth="1"/>
+    <col min="1" max="1" width="6.109375" customWidth="1"/>
+    <col min="2" max="2" width="4" customWidth="1"/>
     <col min="3" max="3" width="3.5546875" customWidth="1"/>
     <col min="4" max="4" width="4" customWidth="1"/>
-    <col min="5" max="5" width="3.33203125" customWidth="1"/>
+    <col min="5" max="5" width="6.109375" customWidth="1"/>
     <col min="6" max="6" width="2.5546875" customWidth="1"/>
     <col min="7" max="7" width="2.44140625" customWidth="1"/>
     <col min="8" max="8" width="4.6640625" customWidth="1"/>
-    <col min="9" max="9" width="4" customWidth="1"/>
+    <col min="9" max="9" width="6.44140625" customWidth="1"/>
     <col min="10" max="10" width="3" customWidth="1"/>
     <col min="11" max="11" width="4" customWidth="1"/>
     <col min="12" max="12" width="2.5546875" customWidth="1"/>
     <col min="13" max="13" width="0.109375" customWidth="1"/>
+    <col min="14" max="14" width="6.21875" customWidth="1"/>
     <col min="15" max="15" width="7" customWidth="1"/>
     <col min="16" max="16" width="11.109375" customWidth="1"/>
     <col min="22" max="22" width="12" customWidth="1"/>
@@ -7050,16 +7052,16 @@
       <c r="N2" s="31"/>
       <c r="O2" s="38"/>
       <c r="P2" s="38"/>
-      <c r="Q2" s="139"/>
-      <c r="R2" s="139"/>
-      <c r="S2" s="139"/>
-      <c r="T2" s="139"/>
-      <c r="U2" s="139"/>
-      <c r="V2" s="139"/>
-      <c r="W2" s="139"/>
-      <c r="X2" s="139"/>
-      <c r="Y2" s="139"/>
-      <c r="Z2" s="139"/>
+      <c r="Q2" s="67"/>
+      <c r="R2" s="67"/>
+      <c r="S2" s="67"/>
+      <c r="T2" s="67"/>
+      <c r="U2" s="67"/>
+      <c r="V2" s="67"/>
+      <c r="W2" s="67"/>
+      <c r="X2" s="67"/>
+      <c r="Y2" s="67"/>
+      <c r="Z2" s="67"/>
       <c r="AA2" s="38"/>
       <c r="AB2" s="38"/>
       <c r="AC2" s="38"/>
@@ -7085,28 +7087,28 @@
       <c r="K3" s="1"/>
       <c r="M3" s="31"/>
       <c r="N3" s="31"/>
-      <c r="Q3" s="140"/>
-      <c r="R3" s="140"/>
-      <c r="S3" s="140"/>
-      <c r="T3" s="140"/>
-      <c r="U3" s="140"/>
-      <c r="V3" s="140"/>
-      <c r="W3" s="140"/>
-      <c r="X3" s="140"/>
-      <c r="Y3" s="140"/>
-      <c r="Z3" s="140"/>
+      <c r="Q3" s="68"/>
+      <c r="R3" s="68"/>
+      <c r="S3" s="68"/>
+      <c r="T3" s="68"/>
+      <c r="U3" s="68"/>
+      <c r="V3" s="68"/>
+      <c r="W3" s="68"/>
+      <c r="X3" s="68"/>
+      <c r="Y3" s="68"/>
+      <c r="Z3" s="68"/>
       <c r="AA3" s="37"/>
       <c r="AB3" s="50" t="s">
         <v>95</v>
       </c>
       <c r="AC3" s="48"/>
-      <c r="AD3" s="158"/>
-      <c r="AE3" s="159"/>
-      <c r="AF3" s="159"/>
-      <c r="AG3" s="159"/>
-      <c r="AH3" s="159"/>
-      <c r="AI3" s="159"/>
-      <c r="AJ3" s="159"/>
+      <c r="AD3" s="57"/>
+      <c r="AE3" s="58"/>
+      <c r="AF3" s="58"/>
+      <c r="AG3" s="58"/>
+      <c r="AH3" s="58"/>
+      <c r="AI3" s="58"/>
+      <c r="AJ3" s="58"/>
     </row>
     <row r="4" spans="1:36" ht="18" customHeight="1">
       <c r="A4" s="30"/>
@@ -7137,304 +7139,304 @@
       </c>
     </row>
     <row r="5" spans="1:36" ht="18" customHeight="1">
-      <c r="A5" s="60" t="s">
+      <c r="A5" s="76" t="s">
         <v>85</v>
       </c>
-      <c r="B5" s="60"/>
-      <c r="C5" s="100"/>
-      <c r="D5" s="100"/>
-      <c r="E5" s="100"/>
-      <c r="F5" s="100"/>
-      <c r="G5" s="100"/>
-      <c r="H5" s="100"/>
-      <c r="I5" s="100"/>
+      <c r="B5" s="76"/>
+      <c r="C5" s="98"/>
+      <c r="D5" s="98"/>
+      <c r="E5" s="98"/>
+      <c r="F5" s="98"/>
+      <c r="G5" s="98"/>
+      <c r="H5" s="98"/>
+      <c r="I5" s="98"/>
       <c r="J5" s="35"/>
-      <c r="K5" s="144" t="s">
+      <c r="K5" s="59" t="s">
         <v>0</v>
       </c>
-      <c r="L5" s="144"/>
-      <c r="M5" s="144"/>
-      <c r="N5" s="144"/>
-      <c r="O5" s="144"/>
-      <c r="P5" s="160"/>
-      <c r="Q5" s="161"/>
-      <c r="R5" s="161"/>
-      <c r="S5" s="161"/>
-      <c r="T5" s="161"/>
-      <c r="U5" s="161"/>
-      <c r="V5" s="161"/>
-      <c r="W5" s="161"/>
-      <c r="X5" s="161"/>
-      <c r="Y5" s="144" t="s">
+      <c r="L5" s="59"/>
+      <c r="M5" s="59"/>
+      <c r="N5" s="59"/>
+      <c r="O5" s="59"/>
+      <c r="P5" s="60"/>
+      <c r="Q5" s="61"/>
+      <c r="R5" s="61"/>
+      <c r="S5" s="61"/>
+      <c r="T5" s="61"/>
+      <c r="U5" s="61"/>
+      <c r="V5" s="61"/>
+      <c r="W5" s="61"/>
+      <c r="X5" s="61"/>
+      <c r="Y5" s="59" t="s">
         <v>48</v>
       </c>
-      <c r="Z5" s="144"/>
-      <c r="AA5" s="100"/>
-      <c r="AB5" s="100"/>
-      <c r="AC5" s="100"/>
-      <c r="AD5" s="100"/>
-      <c r="AE5" s="100"/>
-      <c r="AF5" s="100"/>
-      <c r="AG5" s="100"/>
-      <c r="AH5" s="100"/>
-      <c r="AI5" s="100"/>
-      <c r="AJ5" s="100"/>
+      <c r="Z5" s="59"/>
+      <c r="AA5" s="98"/>
+      <c r="AB5" s="98"/>
+      <c r="AC5" s="98"/>
+      <c r="AD5" s="98"/>
+      <c r="AE5" s="98"/>
+      <c r="AF5" s="98"/>
+      <c r="AG5" s="98"/>
+      <c r="AH5" s="98"/>
+      <c r="AI5" s="98"/>
+      <c r="AJ5" s="98"/>
     </row>
     <row r="6" spans="1:36" ht="18" customHeight="1">
-      <c r="A6" s="60" t="s">
+      <c r="A6" s="76" t="s">
         <v>1</v>
       </c>
-      <c r="B6" s="60"/>
-      <c r="C6" s="150"/>
-      <c r="D6" s="150"/>
-      <c r="E6" s="150"/>
-      <c r="F6" s="150"/>
-      <c r="G6" s="150"/>
-      <c r="H6" s="150"/>
-      <c r="I6" s="150"/>
+      <c r="B6" s="76"/>
+      <c r="C6" s="64"/>
+      <c r="D6" s="64"/>
+      <c r="E6" s="64"/>
+      <c r="F6" s="64"/>
+      <c r="G6" s="64"/>
+      <c r="H6" s="64"/>
+      <c r="I6" s="64"/>
       <c r="J6" s="35"/>
-      <c r="K6" s="144" t="s">
+      <c r="K6" s="59" t="s">
         <v>2</v>
       </c>
-      <c r="L6" s="144"/>
-      <c r="M6" s="144"/>
-      <c r="N6" s="144"/>
-      <c r="O6" s="144"/>
-      <c r="P6" s="145"/>
-      <c r="Q6" s="146"/>
-      <c r="R6" s="146"/>
-      <c r="S6" s="146"/>
-      <c r="T6" s="146"/>
-      <c r="U6" s="146"/>
-      <c r="V6" s="146"/>
-      <c r="W6" s="146"/>
-      <c r="X6" s="146"/>
-      <c r="Y6" s="164" t="s">
+      <c r="L6" s="59"/>
+      <c r="M6" s="59"/>
+      <c r="N6" s="59"/>
+      <c r="O6" s="59"/>
+      <c r="P6" s="72"/>
+      <c r="Q6" s="73"/>
+      <c r="R6" s="73"/>
+      <c r="S6" s="73"/>
+      <c r="T6" s="73"/>
+      <c r="U6" s="73"/>
+      <c r="V6" s="73"/>
+      <c r="W6" s="73"/>
+      <c r="X6" s="73"/>
+      <c r="Y6" s="56" t="s">
         <v>88</v>
       </c>
-      <c r="Z6" s="164"/>
-      <c r="AA6" s="164"/>
-      <c r="AB6" s="164"/>
-      <c r="AC6" s="164"/>
-      <c r="AD6" s="78"/>
-      <c r="AE6" s="78"/>
-      <c r="AF6" s="78"/>
+      <c r="Z6" s="56"/>
+      <c r="AA6" s="56"/>
+      <c r="AB6" s="56"/>
+      <c r="AC6" s="56"/>
+      <c r="AD6" s="63"/>
+      <c r="AE6" s="63"/>
+      <c r="AF6" s="63"/>
       <c r="AG6" s="44"/>
-      <c r="AH6" s="135"/>
-      <c r="AI6" s="135"/>
+      <c r="AH6" s="62"/>
+      <c r="AI6" s="62"/>
       <c r="AJ6" s="44"/>
     </row>
     <row r="7" spans="1:36" ht="18" customHeight="1">
-      <c r="A7" s="60" t="s">
+      <c r="A7" s="76" t="s">
         <v>3</v>
       </c>
-      <c r="B7" s="60"/>
-      <c r="C7" s="150"/>
-      <c r="D7" s="150"/>
-      <c r="E7" s="150"/>
-      <c r="F7" s="150"/>
-      <c r="G7" s="150"/>
-      <c r="H7" s="150"/>
-      <c r="I7" s="150"/>
+      <c r="B7" s="76"/>
+      <c r="C7" s="64"/>
+      <c r="D7" s="64"/>
+      <c r="E7" s="64"/>
+      <c r="F7" s="64"/>
+      <c r="G7" s="64"/>
+      <c r="H7" s="64"/>
+      <c r="I7" s="64"/>
       <c r="J7" s="35"/>
-      <c r="K7" s="144" t="s">
+      <c r="K7" s="59" t="s">
         <v>89</v>
       </c>
-      <c r="L7" s="144"/>
-      <c r="M7" s="144"/>
-      <c r="N7" s="144"/>
-      <c r="O7" s="144"/>
-      <c r="P7" s="78"/>
-      <c r="Q7" s="78"/>
-      <c r="R7" s="78"/>
-      <c r="S7" s="135"/>
-      <c r="T7" s="135"/>
+      <c r="L7" s="59"/>
+      <c r="M7" s="59"/>
+      <c r="N7" s="59"/>
+      <c r="O7" s="59"/>
+      <c r="P7" s="63"/>
+      <c r="Q7" s="63"/>
+      <c r="R7" s="63"/>
+      <c r="S7" s="62"/>
+      <c r="T7" s="62"/>
       <c r="U7" s="39" t="s">
         <v>4</v>
       </c>
-      <c r="V7" s="135"/>
-      <c r="W7" s="135"/>
-      <c r="X7" s="144" t="s">
+      <c r="V7" s="62"/>
+      <c r="W7" s="62"/>
+      <c r="X7" s="59" t="s">
         <v>90</v>
       </c>
-      <c r="Y7" s="144"/>
-      <c r="Z7" s="144"/>
-      <c r="AA7" s="144"/>
-      <c r="AB7" s="144"/>
-      <c r="AC7" s="78"/>
-      <c r="AD7" s="78"/>
-      <c r="AE7" s="78"/>
-      <c r="AF7" s="135"/>
-      <c r="AG7" s="135"/>
+      <c r="Y7" s="59"/>
+      <c r="Z7" s="59"/>
+      <c r="AA7" s="59"/>
+      <c r="AB7" s="59"/>
+      <c r="AC7" s="63"/>
+      <c r="AD7" s="63"/>
+      <c r="AE7" s="63"/>
+      <c r="AF7" s="62"/>
+      <c r="AG7" s="62"/>
       <c r="AH7" s="39" t="s">
         <v>4</v>
       </c>
-      <c r="AI7" s="135"/>
-      <c r="AJ7" s="135"/>
+      <c r="AI7" s="62"/>
+      <c r="AJ7" s="62"/>
     </row>
     <row r="8" spans="1:36" ht="18" customHeight="1">
-      <c r="A8" s="85" t="s">
+      <c r="A8" s="80" t="s">
         <v>5</v>
       </c>
-      <c r="B8" s="85"/>
-      <c r="C8" s="85"/>
-      <c r="D8" s="95"/>
-      <c r="E8" s="95"/>
-      <c r="F8" s="95"/>
-      <c r="G8" s="95"/>
-      <c r="H8" s="95"/>
-      <c r="I8" s="95"/>
-      <c r="J8" s="95"/>
-      <c r="K8" s="95"/>
-      <c r="L8" s="95"/>
-      <c r="M8" s="95"/>
-      <c r="N8" s="95"/>
-      <c r="O8" s="95"/>
-      <c r="P8" s="95"/>
-      <c r="Q8" s="95"/>
-      <c r="R8" s="95"/>
-      <c r="S8" s="162" t="s">
+      <c r="B8" s="80"/>
+      <c r="C8" s="80"/>
+      <c r="D8" s="66"/>
+      <c r="E8" s="66"/>
+      <c r="F8" s="66"/>
+      <c r="G8" s="66"/>
+      <c r="H8" s="66"/>
+      <c r="I8" s="66"/>
+      <c r="J8" s="66"/>
+      <c r="K8" s="66"/>
+      <c r="L8" s="66"/>
+      <c r="M8" s="66"/>
+      <c r="N8" s="66"/>
+      <c r="O8" s="66"/>
+      <c r="P8" s="66"/>
+      <c r="Q8" s="66"/>
+      <c r="R8" s="66"/>
+      <c r="S8" s="65" t="s">
         <v>49</v>
       </c>
-      <c r="T8" s="162"/>
-      <c r="U8" s="144"/>
-      <c r="V8" s="162"/>
-      <c r="W8" s="162"/>
-      <c r="X8" s="95"/>
-      <c r="Y8" s="95"/>
-      <c r="Z8" s="95"/>
-      <c r="AA8" s="95"/>
-      <c r="AB8" s="95"/>
-      <c r="AC8" s="95"/>
-      <c r="AD8" s="95"/>
-      <c r="AE8" s="95"/>
-      <c r="AF8" s="95"/>
-      <c r="AG8" s="95"/>
-      <c r="AH8" s="95"/>
-      <c r="AI8" s="95"/>
-      <c r="AJ8" s="95"/>
+      <c r="T8" s="65"/>
+      <c r="U8" s="59"/>
+      <c r="V8" s="65"/>
+      <c r="W8" s="65"/>
+      <c r="X8" s="66"/>
+      <c r="Y8" s="66"/>
+      <c r="Z8" s="66"/>
+      <c r="AA8" s="66"/>
+      <c r="AB8" s="66"/>
+      <c r="AC8" s="66"/>
+      <c r="AD8" s="66"/>
+      <c r="AE8" s="66"/>
+      <c r="AF8" s="66"/>
+      <c r="AG8" s="66"/>
+      <c r="AH8" s="66"/>
+      <c r="AI8" s="66"/>
+      <c r="AJ8" s="66"/>
     </row>
     <row r="9" spans="1:36" ht="26.4" customHeight="1">
-      <c r="A9" s="60" t="s">
+      <c r="A9" s="76" t="s">
         <v>6</v>
       </c>
-      <c r="B9" s="60"/>
-      <c r="C9" s="60"/>
-      <c r="D9" s="151"/>
-      <c r="E9" s="151"/>
-      <c r="F9" s="151"/>
-      <c r="G9" s="151"/>
-      <c r="H9" s="151"/>
-      <c r="I9" s="151"/>
-      <c r="J9" s="151"/>
-      <c r="K9" s="151"/>
-      <c r="L9" s="151"/>
-      <c r="M9" s="151"/>
-      <c r="N9" s="151"/>
-      <c r="O9" s="151"/>
-      <c r="P9" s="151"/>
-      <c r="Q9" s="151"/>
-      <c r="R9" s="151"/>
-      <c r="S9" s="144" t="s">
+      <c r="B9" s="76"/>
+      <c r="C9" s="76"/>
+      <c r="D9" s="82"/>
+      <c r="E9" s="82"/>
+      <c r="F9" s="82"/>
+      <c r="G9" s="82"/>
+      <c r="H9" s="82"/>
+      <c r="I9" s="82"/>
+      <c r="J9" s="82"/>
+      <c r="K9" s="82"/>
+      <c r="L9" s="82"/>
+      <c r="M9" s="82"/>
+      <c r="N9" s="82"/>
+      <c r="O9" s="82"/>
+      <c r="P9" s="82"/>
+      <c r="Q9" s="82"/>
+      <c r="R9" s="82"/>
+      <c r="S9" s="59" t="s">
         <v>50</v>
       </c>
-      <c r="T9" s="144"/>
-      <c r="U9" s="144"/>
-      <c r="V9" s="144"/>
-      <c r="W9" s="144"/>
-      <c r="X9" s="163"/>
-      <c r="Y9" s="151"/>
-      <c r="Z9" s="151"/>
-      <c r="AA9" s="151"/>
-      <c r="AB9" s="151"/>
-      <c r="AC9" s="151"/>
-      <c r="AD9" s="151"/>
-      <c r="AE9" s="151"/>
-      <c r="AF9" s="151"/>
-      <c r="AG9" s="151"/>
-      <c r="AH9" s="151"/>
-      <c r="AI9" s="151"/>
-      <c r="AJ9" s="151"/>
+      <c r="T9" s="59"/>
+      <c r="U9" s="59"/>
+      <c r="V9" s="59"/>
+      <c r="W9" s="59"/>
+      <c r="X9" s="121"/>
+      <c r="Y9" s="82"/>
+      <c r="Z9" s="82"/>
+      <c r="AA9" s="82"/>
+      <c r="AB9" s="82"/>
+      <c r="AC9" s="82"/>
+      <c r="AD9" s="82"/>
+      <c r="AE9" s="82"/>
+      <c r="AF9" s="82"/>
+      <c r="AG9" s="82"/>
+      <c r="AH9" s="82"/>
+      <c r="AI9" s="82"/>
+      <c r="AJ9" s="82"/>
     </row>
     <row r="10" spans="1:36" ht="5.25" customHeight="1">
-      <c r="A10" s="88"/>
-      <c r="B10" s="88"/>
-      <c r="C10" s="88"/>
-      <c r="D10" s="88"/>
-      <c r="E10" s="88"/>
-      <c r="F10" s="88"/>
-      <c r="G10" s="88"/>
-      <c r="H10" s="88"/>
-      <c r="I10" s="88"/>
-      <c r="J10" s="88"/>
-      <c r="K10" s="88"/>
-      <c r="L10" s="88"/>
-      <c r="M10" s="88"/>
-      <c r="N10" s="88"/>
-      <c r="O10" s="88"/>
-      <c r="P10" s="88"/>
-      <c r="Q10" s="88"/>
-      <c r="R10" s="88"/>
-      <c r="S10" s="88"/>
-      <c r="T10" s="88"/>
-      <c r="U10" s="88"/>
-      <c r="V10" s="88"/>
-      <c r="W10" s="88"/>
-      <c r="X10" s="88"/>
-      <c r="Y10" s="88"/>
-      <c r="Z10" s="88"/>
-      <c r="AA10" s="88"/>
-      <c r="AB10" s="88"/>
-      <c r="AC10" s="88"/>
-      <c r="AD10" s="88"/>
-      <c r="AE10" s="88"/>
-      <c r="AF10" s="88"/>
-      <c r="AG10" s="88"/>
-      <c r="AH10" s="88"/>
-      <c r="AI10" s="88"/>
-      <c r="AJ10" s="88"/>
+      <c r="A10" s="81"/>
+      <c r="B10" s="81"/>
+      <c r="C10" s="81"/>
+      <c r="D10" s="81"/>
+      <c r="E10" s="81"/>
+      <c r="F10" s="81"/>
+      <c r="G10" s="81"/>
+      <c r="H10" s="81"/>
+      <c r="I10" s="81"/>
+      <c r="J10" s="81"/>
+      <c r="K10" s="81"/>
+      <c r="L10" s="81"/>
+      <c r="M10" s="81"/>
+      <c r="N10" s="81"/>
+      <c r="O10" s="81"/>
+      <c r="P10" s="81"/>
+      <c r="Q10" s="81"/>
+      <c r="R10" s="81"/>
+      <c r="S10" s="81"/>
+      <c r="T10" s="81"/>
+      <c r="U10" s="81"/>
+      <c r="V10" s="81"/>
+      <c r="W10" s="81"/>
+      <c r="X10" s="81"/>
+      <c r="Y10" s="81"/>
+      <c r="Z10" s="81"/>
+      <c r="AA10" s="81"/>
+      <c r="AB10" s="81"/>
+      <c r="AC10" s="81"/>
+      <c r="AD10" s="81"/>
+      <c r="AE10" s="81"/>
+      <c r="AF10" s="81"/>
+      <c r="AG10" s="81"/>
+      <c r="AH10" s="81"/>
+      <c r="AI10" s="81"/>
+      <c r="AJ10" s="81"/>
     </row>
     <row r="11" spans="1:36" ht="14.25" customHeight="1">
-      <c r="A11" s="141" t="s">
+      <c r="A11" s="69" t="s">
         <v>7</v>
       </c>
-      <c r="B11" s="142"/>
-      <c r="C11" s="142"/>
-      <c r="D11" s="142"/>
-      <c r="E11" s="142"/>
-      <c r="F11" s="142"/>
-      <c r="G11" s="142"/>
-      <c r="H11" s="142"/>
-      <c r="I11" s="142"/>
-      <c r="J11" s="142"/>
-      <c r="K11" s="142"/>
-      <c r="L11" s="142"/>
-      <c r="M11" s="142"/>
-      <c r="N11" s="142"/>
-      <c r="O11" s="142"/>
-      <c r="P11" s="143"/>
-      <c r="Q11" s="147" t="s">
+      <c r="B11" s="70"/>
+      <c r="C11" s="70"/>
+      <c r="D11" s="70"/>
+      <c r="E11" s="70"/>
+      <c r="F11" s="70"/>
+      <c r="G11" s="70"/>
+      <c r="H11" s="70"/>
+      <c r="I11" s="70"/>
+      <c r="J11" s="70"/>
+      <c r="K11" s="70"/>
+      <c r="L11" s="70"/>
+      <c r="M11" s="70"/>
+      <c r="N11" s="70"/>
+      <c r="O11" s="70"/>
+      <c r="P11" s="71"/>
+      <c r="Q11" s="77" t="s">
         <v>8</v>
       </c>
-      <c r="R11" s="148"/>
-      <c r="S11" s="148"/>
-      <c r="T11" s="148"/>
-      <c r="U11" s="148"/>
-      <c r="V11" s="148"/>
-      <c r="W11" s="148"/>
-      <c r="X11" s="148"/>
-      <c r="Y11" s="148"/>
-      <c r="Z11" s="148"/>
-      <c r="AA11" s="148"/>
-      <c r="AB11" s="148"/>
-      <c r="AC11" s="148"/>
-      <c r="AD11" s="148"/>
-      <c r="AE11" s="148"/>
-      <c r="AF11" s="148"/>
-      <c r="AG11" s="148"/>
-      <c r="AH11" s="148"/>
-      <c r="AI11" s="148"/>
-      <c r="AJ11" s="149"/>
+      <c r="R11" s="78"/>
+      <c r="S11" s="78"/>
+      <c r="T11" s="78"/>
+      <c r="U11" s="78"/>
+      <c r="V11" s="78"/>
+      <c r="W11" s="78"/>
+      <c r="X11" s="78"/>
+      <c r="Y11" s="78"/>
+      <c r="Z11" s="78"/>
+      <c r="AA11" s="78"/>
+      <c r="AB11" s="78"/>
+      <c r="AC11" s="78"/>
+      <c r="AD11" s="78"/>
+      <c r="AE11" s="78"/>
+      <c r="AF11" s="78"/>
+      <c r="AG11" s="78"/>
+      <c r="AH11" s="78"/>
+      <c r="AI11" s="78"/>
+      <c r="AJ11" s="79"/>
     </row>
     <row r="12" spans="1:36" ht="18" customHeight="1">
       <c r="A12" s="2"/>
@@ -7543,150 +7545,150 @@
       <c r="AJ13" s="23"/>
     </row>
     <row r="14" spans="1:36" ht="16.5" customHeight="1">
-      <c r="A14" s="127" t="s">
+      <c r="A14" s="104" t="s">
         <v>86</v>
       </c>
-      <c r="B14" s="128"/>
-      <c r="C14" s="128"/>
-      <c r="D14" s="128"/>
-      <c r="E14" s="128"/>
-      <c r="F14" s="128"/>
-      <c r="G14" s="128"/>
-      <c r="H14" s="128"/>
-      <c r="I14" s="129"/>
-      <c r="J14" s="130"/>
-      <c r="K14" s="130"/>
-      <c r="L14" s="130"/>
-      <c r="M14" s="130"/>
-      <c r="N14" s="130"/>
-      <c r="O14" s="130"/>
-      <c r="P14" s="130"/>
-      <c r="Q14" s="130"/>
-      <c r="R14" s="130"/>
-      <c r="S14" s="130"/>
-      <c r="T14" s="130"/>
-      <c r="U14" s="130"/>
-      <c r="V14" s="130"/>
-      <c r="W14" s="130"/>
-      <c r="X14" s="130"/>
-      <c r="Y14" s="130"/>
-      <c r="Z14" s="130"/>
-      <c r="AA14" s="130"/>
-      <c r="AB14" s="130"/>
-      <c r="AC14" s="130"/>
-      <c r="AD14" s="130"/>
-      <c r="AE14" s="130"/>
-      <c r="AF14" s="130"/>
-      <c r="AG14" s="130"/>
-      <c r="AH14" s="130"/>
-      <c r="AI14" s="130"/>
-      <c r="AJ14" s="131"/>
+      <c r="B14" s="105"/>
+      <c r="C14" s="105"/>
+      <c r="D14" s="105"/>
+      <c r="E14" s="105"/>
+      <c r="F14" s="105"/>
+      <c r="G14" s="105"/>
+      <c r="H14" s="105"/>
+      <c r="I14" s="106"/>
+      <c r="J14" s="107"/>
+      <c r="K14" s="107"/>
+      <c r="L14" s="107"/>
+      <c r="M14" s="107"/>
+      <c r="N14" s="107"/>
+      <c r="O14" s="107"/>
+      <c r="P14" s="107"/>
+      <c r="Q14" s="107"/>
+      <c r="R14" s="107"/>
+      <c r="S14" s="107"/>
+      <c r="T14" s="107"/>
+      <c r="U14" s="107"/>
+      <c r="V14" s="107"/>
+      <c r="W14" s="107"/>
+      <c r="X14" s="107"/>
+      <c r="Y14" s="107"/>
+      <c r="Z14" s="107"/>
+      <c r="AA14" s="107"/>
+      <c r="AB14" s="107"/>
+      <c r="AC14" s="107"/>
+      <c r="AD14" s="107"/>
+      <c r="AE14" s="107"/>
+      <c r="AF14" s="107"/>
+      <c r="AG14" s="107"/>
+      <c r="AH14" s="107"/>
+      <c r="AI14" s="107"/>
+      <c r="AJ14" s="108"/>
     </row>
     <row r="15" spans="1:36" ht="3" customHeight="1">
-      <c r="A15" s="132">
+      <c r="A15" s="109">
         <v>2</v>
       </c>
-      <c r="B15" s="133"/>
-      <c r="C15" s="133"/>
-      <c r="D15" s="133"/>
-      <c r="E15" s="133"/>
-      <c r="F15" s="133"/>
-      <c r="G15" s="133"/>
-      <c r="H15" s="133"/>
-      <c r="I15" s="133"/>
-      <c r="J15" s="133"/>
-      <c r="K15" s="133"/>
-      <c r="L15" s="133"/>
-      <c r="M15" s="133"/>
-      <c r="N15" s="133"/>
-      <c r="O15" s="133"/>
-      <c r="P15" s="133"/>
-      <c r="Q15" s="133"/>
-      <c r="R15" s="133"/>
-      <c r="S15" s="133"/>
-      <c r="T15" s="133"/>
-      <c r="U15" s="133"/>
-      <c r="V15" s="133"/>
-      <c r="W15" s="133"/>
-      <c r="X15" s="133"/>
-      <c r="Y15" s="133"/>
-      <c r="Z15" s="133"/>
-      <c r="AA15" s="133"/>
-      <c r="AB15" s="133"/>
-      <c r="AC15" s="133"/>
-      <c r="AD15" s="133"/>
-      <c r="AE15" s="133"/>
-      <c r="AF15" s="133"/>
-      <c r="AG15" s="133"/>
-      <c r="AH15" s="133"/>
-      <c r="AI15" s="133"/>
-      <c r="AJ15" s="134"/>
+      <c r="B15" s="110"/>
+      <c r="C15" s="110"/>
+      <c r="D15" s="110"/>
+      <c r="E15" s="110"/>
+      <c r="F15" s="110"/>
+      <c r="G15" s="110"/>
+      <c r="H15" s="110"/>
+      <c r="I15" s="110"/>
+      <c r="J15" s="110"/>
+      <c r="K15" s="110"/>
+      <c r="L15" s="110"/>
+      <c r="M15" s="110"/>
+      <c r="N15" s="110"/>
+      <c r="O15" s="110"/>
+      <c r="P15" s="110"/>
+      <c r="Q15" s="110"/>
+      <c r="R15" s="110"/>
+      <c r="S15" s="110"/>
+      <c r="T15" s="110"/>
+      <c r="U15" s="110"/>
+      <c r="V15" s="110"/>
+      <c r="W15" s="110"/>
+      <c r="X15" s="110"/>
+      <c r="Y15" s="110"/>
+      <c r="Z15" s="110"/>
+      <c r="AA15" s="110"/>
+      <c r="AB15" s="110"/>
+      <c r="AC15" s="110"/>
+      <c r="AD15" s="110"/>
+      <c r="AE15" s="110"/>
+      <c r="AF15" s="110"/>
+      <c r="AG15" s="110"/>
+      <c r="AH15" s="110"/>
+      <c r="AI15" s="110"/>
+      <c r="AJ15" s="111"/>
     </row>
     <row r="16" spans="1:36" ht="12.75" customHeight="1">
-      <c r="A16" s="155" t="s">
+      <c r="A16" s="118" t="s">
         <v>9</v>
       </c>
-      <c r="B16" s="156"/>
-      <c r="C16" s="156"/>
-      <c r="D16" s="156"/>
-      <c r="E16" s="156"/>
-      <c r="F16" s="156"/>
-      <c r="G16" s="156"/>
-      <c r="H16" s="156"/>
-      <c r="I16" s="156"/>
-      <c r="J16" s="156"/>
-      <c r="K16" s="156"/>
-      <c r="L16" s="156"/>
-      <c r="M16" s="156"/>
-      <c r="N16" s="156"/>
-      <c r="O16" s="156"/>
-      <c r="P16" s="156"/>
-      <c r="Q16" s="156"/>
-      <c r="R16" s="156"/>
-      <c r="S16" s="156"/>
-      <c r="T16" s="157"/>
-      <c r="U16" s="136" t="s">
+      <c r="B16" s="119"/>
+      <c r="C16" s="119"/>
+      <c r="D16" s="119"/>
+      <c r="E16" s="119"/>
+      <c r="F16" s="119"/>
+      <c r="G16" s="119"/>
+      <c r="H16" s="119"/>
+      <c r="I16" s="119"/>
+      <c r="J16" s="119"/>
+      <c r="K16" s="119"/>
+      <c r="L16" s="119"/>
+      <c r="M16" s="119"/>
+      <c r="N16" s="119"/>
+      <c r="O16" s="119"/>
+      <c r="P16" s="119"/>
+      <c r="Q16" s="119"/>
+      <c r="R16" s="119"/>
+      <c r="S16" s="119"/>
+      <c r="T16" s="120"/>
+      <c r="U16" s="112" t="s">
         <v>73</v>
       </c>
-      <c r="V16" s="137"/>
-      <c r="W16" s="137"/>
-      <c r="X16" s="137"/>
-      <c r="Y16" s="137"/>
-      <c r="Z16" s="137"/>
-      <c r="AA16" s="137"/>
-      <c r="AB16" s="137"/>
-      <c r="AC16" s="137"/>
-      <c r="AD16" s="138"/>
-      <c r="AE16" s="152" t="s">
+      <c r="V16" s="113"/>
+      <c r="W16" s="113"/>
+      <c r="X16" s="113"/>
+      <c r="Y16" s="113"/>
+      <c r="Z16" s="113"/>
+      <c r="AA16" s="113"/>
+      <c r="AB16" s="113"/>
+      <c r="AC16" s="113"/>
+      <c r="AD16" s="114"/>
+      <c r="AE16" s="115" t="s">
         <v>10</v>
       </c>
-      <c r="AF16" s="153"/>
-      <c r="AG16" s="153"/>
-      <c r="AH16" s="153"/>
-      <c r="AI16" s="153"/>
-      <c r="AJ16" s="154"/>
+      <c r="AF16" s="116"/>
+      <c r="AG16" s="116"/>
+      <c r="AH16" s="116"/>
+      <c r="AI16" s="116"/>
+      <c r="AJ16" s="117"/>
     </row>
     <row r="17" spans="1:36" ht="18" customHeight="1">
-      <c r="A17" s="120"/>
-      <c r="B17" s="121"/>
-      <c r="C17" s="121"/>
-      <c r="D17" s="121"/>
-      <c r="E17" s="121"/>
-      <c r="F17" s="121"/>
-      <c r="G17" s="121"/>
-      <c r="H17" s="121"/>
-      <c r="I17" s="121"/>
-      <c r="J17" s="121"/>
-      <c r="K17" s="121"/>
-      <c r="L17" s="121"/>
-      <c r="M17" s="121"/>
-      <c r="N17" s="121"/>
-      <c r="O17" s="121"/>
-      <c r="P17" s="121"/>
-      <c r="Q17" s="121"/>
-      <c r="R17" s="121"/>
-      <c r="S17" s="121"/>
-      <c r="T17" s="122"/>
+      <c r="A17" s="92"/>
+      <c r="B17" s="93"/>
+      <c r="C17" s="93"/>
+      <c r="D17" s="93"/>
+      <c r="E17" s="93"/>
+      <c r="F17" s="93"/>
+      <c r="G17" s="93"/>
+      <c r="H17" s="93"/>
+      <c r="I17" s="93"/>
+      <c r="J17" s="93"/>
+      <c r="K17" s="93"/>
+      <c r="L17" s="93"/>
+      <c r="M17" s="93"/>
+      <c r="N17" s="93"/>
+      <c r="O17" s="93"/>
+      <c r="P17" s="93"/>
+      <c r="Q17" s="93"/>
+      <c r="R17" s="93"/>
+      <c r="S17" s="93"/>
+      <c r="T17" s="94"/>
       <c r="U17" s="25"/>
       <c r="V17" s="17" t="s">
         <v>64</v>
@@ -7702,32 +7704,32 @@
       <c r="AE17" s="14" t="s">
         <v>11</v>
       </c>
-      <c r="AF17" s="103"/>
-      <c r="AG17" s="103"/>
-      <c r="AI17" s="103"/>
-      <c r="AJ17" s="126"/>
+      <c r="AF17" s="99"/>
+      <c r="AG17" s="99"/>
+      <c r="AI17" s="99"/>
+      <c r="AJ17" s="103"/>
     </row>
     <row r="18" spans="1:36" ht="18" customHeight="1">
-      <c r="A18" s="120"/>
-      <c r="B18" s="121"/>
-      <c r="C18" s="121"/>
-      <c r="D18" s="121"/>
-      <c r="E18" s="121"/>
-      <c r="F18" s="121"/>
-      <c r="G18" s="121"/>
-      <c r="H18" s="121"/>
-      <c r="I18" s="121"/>
-      <c r="J18" s="121"/>
-      <c r="K18" s="121"/>
-      <c r="L18" s="121"/>
-      <c r="M18" s="121"/>
-      <c r="N18" s="121"/>
-      <c r="O18" s="121"/>
-      <c r="P18" s="121"/>
-      <c r="Q18" s="121"/>
-      <c r="R18" s="121"/>
-      <c r="S18" s="121"/>
-      <c r="T18" s="122"/>
+      <c r="A18" s="92"/>
+      <c r="B18" s="93"/>
+      <c r="C18" s="93"/>
+      <c r="D18" s="93"/>
+      <c r="E18" s="93"/>
+      <c r="F18" s="93"/>
+      <c r="G18" s="93"/>
+      <c r="H18" s="93"/>
+      <c r="I18" s="93"/>
+      <c r="J18" s="93"/>
+      <c r="K18" s="93"/>
+      <c r="L18" s="93"/>
+      <c r="M18" s="93"/>
+      <c r="N18" s="93"/>
+      <c r="O18" s="93"/>
+      <c r="P18" s="93"/>
+      <c r="Q18" s="93"/>
+      <c r="R18" s="93"/>
+      <c r="S18" s="93"/>
+      <c r="T18" s="94"/>
       <c r="U18" s="26"/>
       <c r="V18" s="17" t="s">
         <v>65</v>
@@ -7743,32 +7745,32 @@
       <c r="AE18" s="14" t="s">
         <v>12</v>
       </c>
-      <c r="AF18" s="103"/>
-      <c r="AG18" s="103"/>
-      <c r="AI18" s="103"/>
-      <c r="AJ18" s="126"/>
+      <c r="AF18" s="99"/>
+      <c r="AG18" s="99"/>
+      <c r="AI18" s="99"/>
+      <c r="AJ18" s="103"/>
     </row>
     <row r="19" spans="1:36" ht="18" customHeight="1">
-      <c r="A19" s="120"/>
-      <c r="B19" s="121"/>
-      <c r="C19" s="121"/>
-      <c r="D19" s="121"/>
-      <c r="E19" s="121"/>
-      <c r="F19" s="121"/>
-      <c r="G19" s="121"/>
-      <c r="H19" s="121"/>
-      <c r="I19" s="121"/>
-      <c r="J19" s="121"/>
-      <c r="K19" s="121"/>
-      <c r="L19" s="121"/>
-      <c r="M19" s="121"/>
-      <c r="N19" s="121"/>
-      <c r="O19" s="121"/>
-      <c r="P19" s="121"/>
-      <c r="Q19" s="121"/>
-      <c r="R19" s="121"/>
-      <c r="S19" s="121"/>
-      <c r="T19" s="122"/>
+      <c r="A19" s="92"/>
+      <c r="B19" s="93"/>
+      <c r="C19" s="93"/>
+      <c r="D19" s="93"/>
+      <c r="E19" s="93"/>
+      <c r="F19" s="93"/>
+      <c r="G19" s="93"/>
+      <c r="H19" s="93"/>
+      <c r="I19" s="93"/>
+      <c r="J19" s="93"/>
+      <c r="K19" s="93"/>
+      <c r="L19" s="93"/>
+      <c r="M19" s="93"/>
+      <c r="N19" s="93"/>
+      <c r="O19" s="93"/>
+      <c r="P19" s="93"/>
+      <c r="Q19" s="93"/>
+      <c r="R19" s="93"/>
+      <c r="S19" s="93"/>
+      <c r="T19" s="94"/>
       <c r="U19" s="26"/>
       <c r="V19" s="17" t="s">
         <v>66</v>
@@ -7784,32 +7786,32 @@
       <c r="AE19" s="14" t="s">
         <v>13</v>
       </c>
-      <c r="AF19" s="103"/>
-      <c r="AG19" s="103"/>
-      <c r="AI19" s="103"/>
-      <c r="AJ19" s="126"/>
+      <c r="AF19" s="99"/>
+      <c r="AG19" s="99"/>
+      <c r="AI19" s="99"/>
+      <c r="AJ19" s="103"/>
     </row>
     <row r="20" spans="1:36" ht="3.75" customHeight="1">
-      <c r="A20" s="123"/>
-      <c r="B20" s="124"/>
-      <c r="C20" s="124"/>
-      <c r="D20" s="124"/>
-      <c r="E20" s="124"/>
-      <c r="F20" s="124"/>
-      <c r="G20" s="124"/>
-      <c r="H20" s="124"/>
-      <c r="I20" s="124"/>
-      <c r="J20" s="124"/>
-      <c r="K20" s="124"/>
-      <c r="L20" s="124"/>
-      <c r="M20" s="124"/>
-      <c r="N20" s="124"/>
-      <c r="O20" s="124"/>
-      <c r="P20" s="124"/>
-      <c r="Q20" s="124"/>
-      <c r="R20" s="124"/>
-      <c r="S20" s="124"/>
-      <c r="T20" s="125"/>
+      <c r="A20" s="95"/>
+      <c r="B20" s="96"/>
+      <c r="C20" s="96"/>
+      <c r="D20" s="96"/>
+      <c r="E20" s="96"/>
+      <c r="F20" s="96"/>
+      <c r="G20" s="96"/>
+      <c r="H20" s="96"/>
+      <c r="I20" s="96"/>
+      <c r="J20" s="96"/>
+      <c r="K20" s="96"/>
+      <c r="L20" s="96"/>
+      <c r="M20" s="96"/>
+      <c r="N20" s="96"/>
+      <c r="O20" s="96"/>
+      <c r="P20" s="96"/>
+      <c r="Q20" s="96"/>
+      <c r="R20" s="96"/>
+      <c r="S20" s="96"/>
+      <c r="T20" s="97"/>
       <c r="U20" s="27"/>
       <c r="V20" s="16"/>
       <c r="W20" s="7"/>
@@ -7868,80 +7870,80 @@
       <c r="AJ21" s="47"/>
     </row>
     <row r="22" spans="1:36" ht="16.5" customHeight="1">
-      <c r="A22" s="114"/>
-      <c r="B22" s="115"/>
-      <c r="C22" s="115"/>
-      <c r="D22" s="115"/>
-      <c r="E22" s="115"/>
-      <c r="F22" s="115"/>
-      <c r="G22" s="115"/>
-      <c r="H22" s="115"/>
-      <c r="I22" s="115"/>
-      <c r="J22" s="115"/>
-      <c r="K22" s="115"/>
-      <c r="L22" s="115"/>
-      <c r="M22" s="115"/>
-      <c r="N22" s="115"/>
-      <c r="O22" s="115"/>
-      <c r="P22" s="115"/>
-      <c r="Q22" s="115"/>
-      <c r="R22" s="115"/>
-      <c r="S22" s="115"/>
-      <c r="T22" s="115"/>
-      <c r="U22" s="115"/>
-      <c r="V22" s="115"/>
-      <c r="W22" s="115"/>
-      <c r="X22" s="115"/>
-      <c r="Y22" s="115"/>
-      <c r="Z22" s="115"/>
-      <c r="AA22" s="115"/>
-      <c r="AB22" s="115"/>
-      <c r="AC22" s="115"/>
-      <c r="AD22" s="115"/>
-      <c r="AE22" s="115"/>
-      <c r="AF22" s="115"/>
-      <c r="AG22" s="115"/>
-      <c r="AH22" s="115"/>
-      <c r="AI22" s="115"/>
-      <c r="AJ22" s="116"/>
+      <c r="A22" s="86"/>
+      <c r="B22" s="87"/>
+      <c r="C22" s="87"/>
+      <c r="D22" s="87"/>
+      <c r="E22" s="87"/>
+      <c r="F22" s="87"/>
+      <c r="G22" s="87"/>
+      <c r="H22" s="87"/>
+      <c r="I22" s="87"/>
+      <c r="J22" s="87"/>
+      <c r="K22" s="87"/>
+      <c r="L22" s="87"/>
+      <c r="M22" s="87"/>
+      <c r="N22" s="87"/>
+      <c r="O22" s="87"/>
+      <c r="P22" s="87"/>
+      <c r="Q22" s="87"/>
+      <c r="R22" s="87"/>
+      <c r="S22" s="87"/>
+      <c r="T22" s="87"/>
+      <c r="U22" s="87"/>
+      <c r="V22" s="87"/>
+      <c r="W22" s="87"/>
+      <c r="X22" s="87"/>
+      <c r="Y22" s="87"/>
+      <c r="Z22" s="87"/>
+      <c r="AA22" s="87"/>
+      <c r="AB22" s="87"/>
+      <c r="AC22" s="87"/>
+      <c r="AD22" s="87"/>
+      <c r="AE22" s="87"/>
+      <c r="AF22" s="87"/>
+      <c r="AG22" s="87"/>
+      <c r="AH22" s="87"/>
+      <c r="AI22" s="87"/>
+      <c r="AJ22" s="88"/>
     </row>
     <row r="23" spans="1:36" ht="16.5" customHeight="1">
-      <c r="A23" s="117"/>
-      <c r="B23" s="118"/>
-      <c r="C23" s="118"/>
-      <c r="D23" s="118"/>
-      <c r="E23" s="118"/>
-      <c r="F23" s="118"/>
-      <c r="G23" s="118"/>
-      <c r="H23" s="118"/>
-      <c r="I23" s="118"/>
-      <c r="J23" s="118"/>
-      <c r="K23" s="118"/>
-      <c r="L23" s="118"/>
-      <c r="M23" s="118"/>
-      <c r="N23" s="118"/>
-      <c r="O23" s="118"/>
-      <c r="P23" s="118"/>
-      <c r="Q23" s="118"/>
-      <c r="R23" s="118"/>
-      <c r="S23" s="118"/>
-      <c r="T23" s="118"/>
-      <c r="U23" s="118"/>
-      <c r="V23" s="118"/>
-      <c r="W23" s="118"/>
-      <c r="X23" s="118"/>
-      <c r="Y23" s="118"/>
-      <c r="Z23" s="118"/>
-      <c r="AA23" s="118"/>
-      <c r="AB23" s="118"/>
-      <c r="AC23" s="118"/>
-      <c r="AD23" s="118"/>
-      <c r="AE23" s="118"/>
-      <c r="AF23" s="118"/>
-      <c r="AG23" s="118"/>
-      <c r="AH23" s="118"/>
-      <c r="AI23" s="118"/>
-      <c r="AJ23" s="119"/>
+      <c r="A23" s="89"/>
+      <c r="B23" s="90"/>
+      <c r="C23" s="90"/>
+      <c r="D23" s="90"/>
+      <c r="E23" s="90"/>
+      <c r="F23" s="90"/>
+      <c r="G23" s="90"/>
+      <c r="H23" s="90"/>
+      <c r="I23" s="90"/>
+      <c r="J23" s="90"/>
+      <c r="K23" s="90"/>
+      <c r="L23" s="90"/>
+      <c r="M23" s="90"/>
+      <c r="N23" s="90"/>
+      <c r="O23" s="90"/>
+      <c r="P23" s="90"/>
+      <c r="Q23" s="90"/>
+      <c r="R23" s="90"/>
+      <c r="S23" s="90"/>
+      <c r="T23" s="90"/>
+      <c r="U23" s="90"/>
+      <c r="V23" s="90"/>
+      <c r="W23" s="90"/>
+      <c r="X23" s="90"/>
+      <c r="Y23" s="90"/>
+      <c r="Z23" s="90"/>
+      <c r="AA23" s="90"/>
+      <c r="AB23" s="90"/>
+      <c r="AC23" s="90"/>
+      <c r="AD23" s="90"/>
+      <c r="AE23" s="90"/>
+      <c r="AF23" s="90"/>
+      <c r="AG23" s="90"/>
+      <c r="AH23" s="90"/>
+      <c r="AI23" s="90"/>
+      <c r="AJ23" s="91"/>
     </row>
     <row r="24" spans="1:36" ht="12.75" customHeight="1">
       <c r="A24" s="46" t="s">
@@ -7984,42 +7986,42 @@
       <c r="AJ24" s="47"/>
     </row>
     <row r="25" spans="1:36" ht="18" customHeight="1">
-      <c r="A25" s="111"/>
-      <c r="B25" s="112"/>
-      <c r="C25" s="112"/>
-      <c r="D25" s="112"/>
-      <c r="E25" s="112"/>
-      <c r="F25" s="112"/>
-      <c r="G25" s="112"/>
-      <c r="H25" s="112"/>
-      <c r="I25" s="112"/>
-      <c r="J25" s="112"/>
-      <c r="K25" s="112"/>
-      <c r="L25" s="112"/>
-      <c r="M25" s="112"/>
-      <c r="N25" s="112"/>
-      <c r="O25" s="112"/>
-      <c r="P25" s="112"/>
-      <c r="Q25" s="112"/>
-      <c r="R25" s="112"/>
-      <c r="S25" s="112"/>
-      <c r="T25" s="112"/>
-      <c r="U25" s="112"/>
-      <c r="V25" s="112"/>
-      <c r="W25" s="112"/>
-      <c r="X25" s="112"/>
-      <c r="Y25" s="112"/>
-      <c r="Z25" s="112"/>
-      <c r="AA25" s="112"/>
-      <c r="AB25" s="112"/>
-      <c r="AC25" s="112"/>
-      <c r="AD25" s="112"/>
-      <c r="AE25" s="112"/>
-      <c r="AF25" s="112"/>
-      <c r="AG25" s="112"/>
-      <c r="AH25" s="112"/>
-      <c r="AI25" s="112"/>
-      <c r="AJ25" s="113"/>
+      <c r="A25" s="83"/>
+      <c r="B25" s="84"/>
+      <c r="C25" s="84"/>
+      <c r="D25" s="84"/>
+      <c r="E25" s="84"/>
+      <c r="F25" s="84"/>
+      <c r="G25" s="84"/>
+      <c r="H25" s="84"/>
+      <c r="I25" s="84"/>
+      <c r="J25" s="84"/>
+      <c r="K25" s="84"/>
+      <c r="L25" s="84"/>
+      <c r="M25" s="84"/>
+      <c r="N25" s="84"/>
+      <c r="O25" s="84"/>
+      <c r="P25" s="84"/>
+      <c r="Q25" s="84"/>
+      <c r="R25" s="84"/>
+      <c r="S25" s="84"/>
+      <c r="T25" s="84"/>
+      <c r="U25" s="84"/>
+      <c r="V25" s="84"/>
+      <c r="W25" s="84"/>
+      <c r="X25" s="84"/>
+      <c r="Y25" s="84"/>
+      <c r="Z25" s="84"/>
+      <c r="AA25" s="84"/>
+      <c r="AB25" s="84"/>
+      <c r="AC25" s="84"/>
+      <c r="AD25" s="84"/>
+      <c r="AE25" s="84"/>
+      <c r="AF25" s="84"/>
+      <c r="AG25" s="84"/>
+      <c r="AH25" s="84"/>
+      <c r="AI25" s="84"/>
+      <c r="AJ25" s="85"/>
     </row>
     <row r="26" spans="1:36" ht="12.75" customHeight="1">
       <c r="A26" s="46" t="s">
@@ -8062,137 +8064,137 @@
       <c r="AJ26" s="47"/>
     </row>
     <row r="27" spans="1:36" ht="15" customHeight="1">
-      <c r="A27" s="62"/>
-      <c r="B27" s="63"/>
-      <c r="C27" s="63"/>
-      <c r="D27" s="63"/>
-      <c r="E27" s="63"/>
-      <c r="F27" s="63"/>
-      <c r="G27" s="63"/>
-      <c r="H27" s="63"/>
-      <c r="I27" s="63"/>
-      <c r="J27" s="63"/>
-      <c r="K27" s="63"/>
-      <c r="L27" s="63"/>
-      <c r="M27" s="63"/>
-      <c r="N27" s="63"/>
-      <c r="O27" s="63"/>
-      <c r="P27" s="63"/>
-      <c r="Q27" s="63"/>
-      <c r="R27" s="63"/>
-      <c r="S27" s="63"/>
-      <c r="T27" s="63"/>
-      <c r="U27" s="63"/>
-      <c r="V27" s="63"/>
-      <c r="W27" s="63"/>
-      <c r="X27" s="63"/>
-      <c r="Y27" s="63"/>
-      <c r="Z27" s="63"/>
-      <c r="AA27" s="63"/>
-      <c r="AB27" s="63"/>
-      <c r="AC27" s="63"/>
-      <c r="AD27" s="63"/>
-      <c r="AE27" s="63"/>
-      <c r="AF27" s="63"/>
-      <c r="AG27" s="63"/>
-      <c r="AH27" s="63"/>
-      <c r="AI27" s="63"/>
-      <c r="AJ27" s="64"/>
+      <c r="A27" s="150"/>
+      <c r="B27" s="151"/>
+      <c r="C27" s="151"/>
+      <c r="D27" s="151"/>
+      <c r="E27" s="151"/>
+      <c r="F27" s="151"/>
+      <c r="G27" s="151"/>
+      <c r="H27" s="151"/>
+      <c r="I27" s="151"/>
+      <c r="J27" s="151"/>
+      <c r="K27" s="151"/>
+      <c r="L27" s="151"/>
+      <c r="M27" s="151"/>
+      <c r="N27" s="151"/>
+      <c r="O27" s="151"/>
+      <c r="P27" s="151"/>
+      <c r="Q27" s="151"/>
+      <c r="R27" s="151"/>
+      <c r="S27" s="151"/>
+      <c r="T27" s="151"/>
+      <c r="U27" s="151"/>
+      <c r="V27" s="151"/>
+      <c r="W27" s="151"/>
+      <c r="X27" s="151"/>
+      <c r="Y27" s="151"/>
+      <c r="Z27" s="151"/>
+      <c r="AA27" s="151"/>
+      <c r="AB27" s="151"/>
+      <c r="AC27" s="151"/>
+      <c r="AD27" s="151"/>
+      <c r="AE27" s="151"/>
+      <c r="AF27" s="151"/>
+      <c r="AG27" s="151"/>
+      <c r="AH27" s="151"/>
+      <c r="AI27" s="151"/>
+      <c r="AJ27" s="152"/>
     </row>
     <row r="28" spans="1:36" ht="15" customHeight="1">
-      <c r="A28" s="65"/>
-      <c r="B28" s="63"/>
-      <c r="C28" s="63"/>
-      <c r="D28" s="63"/>
-      <c r="E28" s="63"/>
-      <c r="F28" s="63"/>
-      <c r="G28" s="63"/>
-      <c r="H28" s="63"/>
-      <c r="I28" s="63"/>
-      <c r="J28" s="63"/>
-      <c r="K28" s="63"/>
-      <c r="L28" s="63"/>
-      <c r="M28" s="63"/>
-      <c r="N28" s="63"/>
-      <c r="O28" s="63"/>
-      <c r="P28" s="63"/>
-      <c r="Q28" s="63"/>
-      <c r="R28" s="63"/>
-      <c r="S28" s="63"/>
-      <c r="T28" s="63"/>
-      <c r="U28" s="63"/>
-      <c r="V28" s="63"/>
-      <c r="W28" s="63"/>
-      <c r="X28" s="63"/>
-      <c r="Y28" s="63"/>
-      <c r="Z28" s="63"/>
-      <c r="AA28" s="63"/>
-      <c r="AB28" s="63"/>
-      <c r="AC28" s="63"/>
-      <c r="AD28" s="63"/>
-      <c r="AE28" s="63"/>
-      <c r="AF28" s="63"/>
-      <c r="AG28" s="63"/>
-      <c r="AH28" s="63"/>
-      <c r="AI28" s="63"/>
-      <c r="AJ28" s="64"/>
+      <c r="A28" s="153"/>
+      <c r="B28" s="151"/>
+      <c r="C28" s="151"/>
+      <c r="D28" s="151"/>
+      <c r="E28" s="151"/>
+      <c r="F28" s="151"/>
+      <c r="G28" s="151"/>
+      <c r="H28" s="151"/>
+      <c r="I28" s="151"/>
+      <c r="J28" s="151"/>
+      <c r="K28" s="151"/>
+      <c r="L28" s="151"/>
+      <c r="M28" s="151"/>
+      <c r="N28" s="151"/>
+      <c r="O28" s="151"/>
+      <c r="P28" s="151"/>
+      <c r="Q28" s="151"/>
+      <c r="R28" s="151"/>
+      <c r="S28" s="151"/>
+      <c r="T28" s="151"/>
+      <c r="U28" s="151"/>
+      <c r="V28" s="151"/>
+      <c r="W28" s="151"/>
+      <c r="X28" s="151"/>
+      <c r="Y28" s="151"/>
+      <c r="Z28" s="151"/>
+      <c r="AA28" s="151"/>
+      <c r="AB28" s="151"/>
+      <c r="AC28" s="151"/>
+      <c r="AD28" s="151"/>
+      <c r="AE28" s="151"/>
+      <c r="AF28" s="151"/>
+      <c r="AG28" s="151"/>
+      <c r="AH28" s="151"/>
+      <c r="AI28" s="151"/>
+      <c r="AJ28" s="152"/>
     </row>
     <row r="29" spans="1:36" ht="100.8" customHeight="1">
-      <c r="A29" s="66"/>
-      <c r="B29" s="67"/>
-      <c r="C29" s="67"/>
-      <c r="D29" s="67"/>
-      <c r="E29" s="67"/>
-      <c r="F29" s="67"/>
-      <c r="G29" s="67"/>
-      <c r="H29" s="67"/>
-      <c r="I29" s="67"/>
-      <c r="J29" s="67"/>
-      <c r="K29" s="67"/>
-      <c r="L29" s="67"/>
-      <c r="M29" s="67"/>
-      <c r="N29" s="67"/>
-      <c r="O29" s="67"/>
-      <c r="P29" s="67"/>
-      <c r="Q29" s="67"/>
-      <c r="R29" s="67"/>
-      <c r="S29" s="67"/>
-      <c r="T29" s="67"/>
-      <c r="U29" s="67"/>
-      <c r="V29" s="67"/>
-      <c r="W29" s="67"/>
-      <c r="X29" s="67"/>
-      <c r="Y29" s="67"/>
-      <c r="Z29" s="67"/>
-      <c r="AA29" s="67"/>
-      <c r="AB29" s="67"/>
-      <c r="AC29" s="67"/>
-      <c r="AD29" s="67"/>
-      <c r="AE29" s="67"/>
-      <c r="AF29" s="67"/>
-      <c r="AG29" s="67"/>
-      <c r="AH29" s="67"/>
-      <c r="AI29" s="67"/>
-      <c r="AJ29" s="68"/>
+      <c r="A29" s="154"/>
+      <c r="B29" s="155"/>
+      <c r="C29" s="155"/>
+      <c r="D29" s="155"/>
+      <c r="E29" s="155"/>
+      <c r="F29" s="155"/>
+      <c r="G29" s="155"/>
+      <c r="H29" s="155"/>
+      <c r="I29" s="155"/>
+      <c r="J29" s="155"/>
+      <c r="K29" s="155"/>
+      <c r="L29" s="155"/>
+      <c r="M29" s="155"/>
+      <c r="N29" s="155"/>
+      <c r="O29" s="155"/>
+      <c r="P29" s="155"/>
+      <c r="Q29" s="155"/>
+      <c r="R29" s="155"/>
+      <c r="S29" s="155"/>
+      <c r="T29" s="155"/>
+      <c r="U29" s="155"/>
+      <c r="V29" s="155"/>
+      <c r="W29" s="155"/>
+      <c r="X29" s="155"/>
+      <c r="Y29" s="155"/>
+      <c r="Z29" s="155"/>
+      <c r="AA29" s="155"/>
+      <c r="AB29" s="155"/>
+      <c r="AC29" s="155"/>
+      <c r="AD29" s="155"/>
+      <c r="AE29" s="155"/>
+      <c r="AF29" s="155"/>
+      <c r="AG29" s="155"/>
+      <c r="AH29" s="155"/>
+      <c r="AI29" s="155"/>
+      <c r="AJ29" s="156"/>
     </row>
     <row r="30" spans="1:36" ht="12.75" customHeight="1">
-      <c r="A30" s="75" t="s">
+      <c r="A30" s="157" t="s">
         <v>17</v>
       </c>
-      <c r="B30" s="76"/>
-      <c r="C30" s="76"/>
-      <c r="D30" s="76"/>
-      <c r="E30" s="76"/>
-      <c r="F30" s="76"/>
-      <c r="G30" s="76"/>
-      <c r="H30" s="76"/>
-      <c r="I30" s="76"/>
-      <c r="J30" s="76"/>
-      <c r="K30" s="76"/>
-      <c r="L30" s="76"/>
-      <c r="M30" s="76"/>
-      <c r="N30" s="76"/>
-      <c r="O30" s="76"/>
+      <c r="B30" s="158"/>
+      <c r="C30" s="158"/>
+      <c r="D30" s="158"/>
+      <c r="E30" s="158"/>
+      <c r="F30" s="158"/>
+      <c r="G30" s="158"/>
+      <c r="H30" s="158"/>
+      <c r="I30" s="158"/>
+      <c r="J30" s="158"/>
+      <c r="K30" s="158"/>
+      <c r="L30" s="158"/>
+      <c r="M30" s="158"/>
+      <c r="N30" s="158"/>
+      <c r="O30" s="158"/>
       <c r="P30" s="41"/>
       <c r="Q30" s="41"/>
       <c r="R30" s="41"/>
@@ -8216,216 +8218,216 @@
       <c r="AJ30" s="42"/>
     </row>
     <row r="31" spans="1:36" ht="16.5" customHeight="1">
-      <c r="A31" s="62"/>
-      <c r="B31" s="79"/>
-      <c r="C31" s="79"/>
-      <c r="D31" s="79"/>
-      <c r="E31" s="79"/>
-      <c r="F31" s="79"/>
-      <c r="G31" s="79"/>
-      <c r="H31" s="79"/>
-      <c r="I31" s="79"/>
-      <c r="J31" s="79"/>
-      <c r="K31" s="79"/>
-      <c r="L31" s="79"/>
-      <c r="M31" s="79"/>
-      <c r="N31" s="79"/>
-      <c r="O31" s="79"/>
-      <c r="P31" s="79"/>
-      <c r="Q31" s="79"/>
-      <c r="R31" s="79"/>
-      <c r="S31" s="79"/>
-      <c r="T31" s="79"/>
-      <c r="U31" s="79"/>
-      <c r="V31" s="79"/>
-      <c r="W31" s="79"/>
-      <c r="X31" s="79"/>
-      <c r="Y31" s="79"/>
-      <c r="Z31" s="79"/>
-      <c r="AA31" s="79"/>
-      <c r="AB31" s="79"/>
-      <c r="AC31" s="79"/>
-      <c r="AD31" s="79"/>
-      <c r="AE31" s="79"/>
-      <c r="AF31" s="79"/>
-      <c r="AG31" s="79"/>
-      <c r="AH31" s="79"/>
-      <c r="AI31" s="79"/>
-      <c r="AJ31" s="80"/>
+      <c r="A31" s="150"/>
+      <c r="B31" s="160"/>
+      <c r="C31" s="160"/>
+      <c r="D31" s="160"/>
+      <c r="E31" s="160"/>
+      <c r="F31" s="160"/>
+      <c r="G31" s="160"/>
+      <c r="H31" s="160"/>
+      <c r="I31" s="160"/>
+      <c r="J31" s="160"/>
+      <c r="K31" s="160"/>
+      <c r="L31" s="160"/>
+      <c r="M31" s="160"/>
+      <c r="N31" s="160"/>
+      <c r="O31" s="160"/>
+      <c r="P31" s="160"/>
+      <c r="Q31" s="160"/>
+      <c r="R31" s="160"/>
+      <c r="S31" s="160"/>
+      <c r="T31" s="160"/>
+      <c r="U31" s="160"/>
+      <c r="V31" s="160"/>
+      <c r="W31" s="160"/>
+      <c r="X31" s="160"/>
+      <c r="Y31" s="160"/>
+      <c r="Z31" s="160"/>
+      <c r="AA31" s="160"/>
+      <c r="AB31" s="160"/>
+      <c r="AC31" s="160"/>
+      <c r="AD31" s="160"/>
+      <c r="AE31" s="160"/>
+      <c r="AF31" s="160"/>
+      <c r="AG31" s="160"/>
+      <c r="AH31" s="160"/>
+      <c r="AI31" s="160"/>
+      <c r="AJ31" s="161"/>
     </row>
     <row r="32" spans="1:36" ht="16.5" customHeight="1">
-      <c r="A32" s="62"/>
-      <c r="B32" s="79"/>
-      <c r="C32" s="79"/>
-      <c r="D32" s="79"/>
-      <c r="E32" s="79"/>
-      <c r="F32" s="79"/>
-      <c r="G32" s="79"/>
-      <c r="H32" s="79"/>
-      <c r="I32" s="79"/>
-      <c r="J32" s="79"/>
-      <c r="K32" s="79"/>
-      <c r="L32" s="79"/>
-      <c r="M32" s="79"/>
-      <c r="N32" s="79"/>
-      <c r="O32" s="79"/>
-      <c r="P32" s="79"/>
-      <c r="Q32" s="79"/>
-      <c r="R32" s="79"/>
-      <c r="S32" s="79"/>
-      <c r="T32" s="79"/>
-      <c r="U32" s="79"/>
-      <c r="V32" s="79"/>
-      <c r="W32" s="79"/>
-      <c r="X32" s="79"/>
-      <c r="Y32" s="79"/>
-      <c r="Z32" s="79"/>
-      <c r="AA32" s="79"/>
-      <c r="AB32" s="79"/>
-      <c r="AC32" s="79"/>
-      <c r="AD32" s="79"/>
-      <c r="AE32" s="79"/>
-      <c r="AF32" s="79"/>
-      <c r="AG32" s="79"/>
-      <c r="AH32" s="79"/>
-      <c r="AI32" s="79"/>
-      <c r="AJ32" s="80"/>
+      <c r="A32" s="150"/>
+      <c r="B32" s="160"/>
+      <c r="C32" s="160"/>
+      <c r="D32" s="160"/>
+      <c r="E32" s="160"/>
+      <c r="F32" s="160"/>
+      <c r="G32" s="160"/>
+      <c r="H32" s="160"/>
+      <c r="I32" s="160"/>
+      <c r="J32" s="160"/>
+      <c r="K32" s="160"/>
+      <c r="L32" s="160"/>
+      <c r="M32" s="160"/>
+      <c r="N32" s="160"/>
+      <c r="O32" s="160"/>
+      <c r="P32" s="160"/>
+      <c r="Q32" s="160"/>
+      <c r="R32" s="160"/>
+      <c r="S32" s="160"/>
+      <c r="T32" s="160"/>
+      <c r="U32" s="160"/>
+      <c r="V32" s="160"/>
+      <c r="W32" s="160"/>
+      <c r="X32" s="160"/>
+      <c r="Y32" s="160"/>
+      <c r="Z32" s="160"/>
+      <c r="AA32" s="160"/>
+      <c r="AB32" s="160"/>
+      <c r="AC32" s="160"/>
+      <c r="AD32" s="160"/>
+      <c r="AE32" s="160"/>
+      <c r="AF32" s="160"/>
+      <c r="AG32" s="160"/>
+      <c r="AH32" s="160"/>
+      <c r="AI32" s="160"/>
+      <c r="AJ32" s="161"/>
     </row>
     <row r="33" spans="1:36" ht="16.5" customHeight="1">
-      <c r="A33" s="62"/>
-      <c r="B33" s="79"/>
-      <c r="C33" s="79"/>
-      <c r="D33" s="79"/>
-      <c r="E33" s="79"/>
-      <c r="F33" s="79"/>
-      <c r="G33" s="79"/>
-      <c r="H33" s="79"/>
-      <c r="I33" s="79"/>
-      <c r="J33" s="79"/>
-      <c r="K33" s="79"/>
-      <c r="L33" s="79"/>
-      <c r="M33" s="79"/>
-      <c r="N33" s="79"/>
-      <c r="O33" s="79"/>
-      <c r="P33" s="79"/>
-      <c r="Q33" s="79"/>
-      <c r="R33" s="79"/>
-      <c r="S33" s="79"/>
-      <c r="T33" s="79"/>
-      <c r="U33" s="79"/>
-      <c r="V33" s="79"/>
-      <c r="W33" s="79"/>
-      <c r="X33" s="79"/>
-      <c r="Y33" s="79"/>
-      <c r="Z33" s="79"/>
-      <c r="AA33" s="79"/>
-      <c r="AB33" s="79"/>
-      <c r="AC33" s="79"/>
-      <c r="AD33" s="79"/>
-      <c r="AE33" s="79"/>
-      <c r="AF33" s="79"/>
-      <c r="AG33" s="79"/>
-      <c r="AH33" s="79"/>
-      <c r="AI33" s="79"/>
-      <c r="AJ33" s="80"/>
+      <c r="A33" s="150"/>
+      <c r="B33" s="160"/>
+      <c r="C33" s="160"/>
+      <c r="D33" s="160"/>
+      <c r="E33" s="160"/>
+      <c r="F33" s="160"/>
+      <c r="G33" s="160"/>
+      <c r="H33" s="160"/>
+      <c r="I33" s="160"/>
+      <c r="J33" s="160"/>
+      <c r="K33" s="160"/>
+      <c r="L33" s="160"/>
+      <c r="M33" s="160"/>
+      <c r="N33" s="160"/>
+      <c r="O33" s="160"/>
+      <c r="P33" s="160"/>
+      <c r="Q33" s="160"/>
+      <c r="R33" s="160"/>
+      <c r="S33" s="160"/>
+      <c r="T33" s="160"/>
+      <c r="U33" s="160"/>
+      <c r="V33" s="160"/>
+      <c r="W33" s="160"/>
+      <c r="X33" s="160"/>
+      <c r="Y33" s="160"/>
+      <c r="Z33" s="160"/>
+      <c r="AA33" s="160"/>
+      <c r="AB33" s="160"/>
+      <c r="AC33" s="160"/>
+      <c r="AD33" s="160"/>
+      <c r="AE33" s="160"/>
+      <c r="AF33" s="160"/>
+      <c r="AG33" s="160"/>
+      <c r="AH33" s="160"/>
+      <c r="AI33" s="160"/>
+      <c r="AJ33" s="161"/>
     </row>
     <row r="34" spans="1:36" ht="61.8" customHeight="1">
-      <c r="A34" s="62"/>
-      <c r="B34" s="79"/>
-      <c r="C34" s="79"/>
-      <c r="D34" s="79"/>
-      <c r="E34" s="79"/>
-      <c r="F34" s="79"/>
-      <c r="G34" s="79"/>
-      <c r="H34" s="79"/>
-      <c r="I34" s="79"/>
-      <c r="J34" s="79"/>
-      <c r="K34" s="79"/>
-      <c r="L34" s="79"/>
-      <c r="M34" s="79"/>
-      <c r="N34" s="79"/>
-      <c r="O34" s="79"/>
-      <c r="P34" s="79"/>
-      <c r="Q34" s="79"/>
-      <c r="R34" s="79"/>
-      <c r="S34" s="79"/>
-      <c r="T34" s="79"/>
-      <c r="U34" s="79"/>
-      <c r="V34" s="79"/>
-      <c r="W34" s="79"/>
-      <c r="X34" s="79"/>
-      <c r="Y34" s="79"/>
-      <c r="Z34" s="79"/>
-      <c r="AA34" s="79"/>
-      <c r="AB34" s="79"/>
-      <c r="AC34" s="79"/>
-      <c r="AD34" s="79"/>
-      <c r="AE34" s="79"/>
-      <c r="AF34" s="79"/>
-      <c r="AG34" s="79"/>
-      <c r="AH34" s="79"/>
-      <c r="AI34" s="79"/>
-      <c r="AJ34" s="80"/>
+      <c r="A34" s="150"/>
+      <c r="B34" s="160"/>
+      <c r="C34" s="160"/>
+      <c r="D34" s="160"/>
+      <c r="E34" s="160"/>
+      <c r="F34" s="160"/>
+      <c r="G34" s="160"/>
+      <c r="H34" s="160"/>
+      <c r="I34" s="160"/>
+      <c r="J34" s="160"/>
+      <c r="K34" s="160"/>
+      <c r="L34" s="160"/>
+      <c r="M34" s="160"/>
+      <c r="N34" s="160"/>
+      <c r="O34" s="160"/>
+      <c r="P34" s="160"/>
+      <c r="Q34" s="160"/>
+      <c r="R34" s="160"/>
+      <c r="S34" s="160"/>
+      <c r="T34" s="160"/>
+      <c r="U34" s="160"/>
+      <c r="V34" s="160"/>
+      <c r="W34" s="160"/>
+      <c r="X34" s="160"/>
+      <c r="Y34" s="160"/>
+      <c r="Z34" s="160"/>
+      <c r="AA34" s="160"/>
+      <c r="AB34" s="160"/>
+      <c r="AC34" s="160"/>
+      <c r="AD34" s="160"/>
+      <c r="AE34" s="160"/>
+      <c r="AF34" s="160"/>
+      <c r="AG34" s="160"/>
+      <c r="AH34" s="160"/>
+      <c r="AI34" s="160"/>
+      <c r="AJ34" s="161"/>
     </row>
     <row r="35" spans="1:36" ht="13.2" customHeight="1">
-      <c r="A35" s="81"/>
-      <c r="B35" s="82"/>
-      <c r="C35" s="82"/>
-      <c r="D35" s="82"/>
-      <c r="E35" s="82"/>
-      <c r="F35" s="82"/>
-      <c r="G35" s="82"/>
-      <c r="H35" s="82"/>
-      <c r="I35" s="82"/>
-      <c r="J35" s="82"/>
-      <c r="K35" s="82"/>
-      <c r="L35" s="82"/>
-      <c r="M35" s="82"/>
-      <c r="N35" s="82"/>
-      <c r="O35" s="82"/>
-      <c r="P35" s="82"/>
-      <c r="Q35" s="82"/>
-      <c r="R35" s="82"/>
-      <c r="S35" s="82"/>
-      <c r="T35" s="82"/>
-      <c r="U35" s="82"/>
-      <c r="V35" s="82"/>
-      <c r="W35" s="82"/>
-      <c r="X35" s="82"/>
-      <c r="Y35" s="82"/>
-      <c r="Z35" s="82"/>
-      <c r="AA35" s="82"/>
-      <c r="AB35" s="82"/>
-      <c r="AC35" s="82"/>
-      <c r="AD35" s="82"/>
-      <c r="AE35" s="82"/>
-      <c r="AF35" s="82"/>
-      <c r="AG35" s="82"/>
-      <c r="AH35" s="82"/>
-      <c r="AI35" s="82"/>
-      <c r="AJ35" s="83"/>
+      <c r="A35" s="162"/>
+      <c r="B35" s="163"/>
+      <c r="C35" s="163"/>
+      <c r="D35" s="163"/>
+      <c r="E35" s="163"/>
+      <c r="F35" s="163"/>
+      <c r="G35" s="163"/>
+      <c r="H35" s="163"/>
+      <c r="I35" s="163"/>
+      <c r="J35" s="163"/>
+      <c r="K35" s="163"/>
+      <c r="L35" s="163"/>
+      <c r="M35" s="163"/>
+      <c r="N35" s="163"/>
+      <c r="O35" s="163"/>
+      <c r="P35" s="163"/>
+      <c r="Q35" s="163"/>
+      <c r="R35" s="163"/>
+      <c r="S35" s="163"/>
+      <c r="T35" s="163"/>
+      <c r="U35" s="163"/>
+      <c r="V35" s="163"/>
+      <c r="W35" s="163"/>
+      <c r="X35" s="163"/>
+      <c r="Y35" s="163"/>
+      <c r="Z35" s="163"/>
+      <c r="AA35" s="163"/>
+      <c r="AB35" s="163"/>
+      <c r="AC35" s="163"/>
+      <c r="AD35" s="163"/>
+      <c r="AE35" s="163"/>
+      <c r="AF35" s="163"/>
+      <c r="AG35" s="163"/>
+      <c r="AH35" s="163"/>
+      <c r="AI35" s="163"/>
+      <c r="AJ35" s="164"/>
     </row>
     <row r="36" spans="1:36" ht="13.5" customHeight="1">
-      <c r="A36" s="69" t="s">
+      <c r="A36" s="74" t="s">
         <v>94</v>
       </c>
-      <c r="B36" s="70"/>
-      <c r="C36" s="70"/>
-      <c r="D36" s="70"/>
-      <c r="E36" s="70"/>
-      <c r="F36" s="70"/>
-      <c r="G36" s="70"/>
-      <c r="H36" s="70"/>
-      <c r="I36" s="70"/>
-      <c r="J36" s="70"/>
-      <c r="K36" s="70"/>
-      <c r="L36" s="70"/>
-      <c r="M36" s="70"/>
-      <c r="N36" s="70"/>
-      <c r="O36" s="70"/>
-      <c r="P36" s="70"/>
-      <c r="Q36" s="70"/>
-      <c r="R36" s="70"/>
+      <c r="B36" s="75"/>
+      <c r="C36" s="75"/>
+      <c r="D36" s="75"/>
+      <c r="E36" s="75"/>
+      <c r="F36" s="75"/>
+      <c r="G36" s="75"/>
+      <c r="H36" s="75"/>
+      <c r="I36" s="75"/>
+      <c r="J36" s="75"/>
+      <c r="K36" s="75"/>
+      <c r="L36" s="75"/>
+      <c r="M36" s="75"/>
+      <c r="N36" s="75"/>
+      <c r="O36" s="75"/>
+      <c r="P36" s="75"/>
+      <c r="Q36" s="75"/>
+      <c r="R36" s="75"/>
       <c r="S36" s="40"/>
       <c r="T36" s="40"/>
       <c r="U36" s="40"/>
@@ -8446,178 +8448,178 @@
       <c r="AJ36" s="43"/>
     </row>
     <row r="37" spans="1:36" ht="14.25" customHeight="1">
-      <c r="A37" s="62"/>
-      <c r="B37" s="79"/>
-      <c r="C37" s="79"/>
-      <c r="D37" s="79"/>
-      <c r="E37" s="79"/>
-      <c r="F37" s="79"/>
-      <c r="G37" s="79"/>
-      <c r="H37" s="79"/>
-      <c r="I37" s="79"/>
-      <c r="J37" s="79"/>
-      <c r="K37" s="79"/>
-      <c r="L37" s="79"/>
-      <c r="M37" s="79"/>
-      <c r="N37" s="79"/>
-      <c r="O37" s="79"/>
-      <c r="P37" s="79"/>
-      <c r="Q37" s="79"/>
-      <c r="R37" s="79"/>
-      <c r="S37" s="79"/>
-      <c r="T37" s="79"/>
-      <c r="U37" s="79"/>
-      <c r="V37" s="79"/>
-      <c r="W37" s="79"/>
-      <c r="X37" s="79"/>
-      <c r="Y37" s="79"/>
-      <c r="Z37" s="79"/>
-      <c r="AA37" s="79"/>
-      <c r="AB37" s="79"/>
-      <c r="AC37" s="79"/>
-      <c r="AD37" s="79"/>
-      <c r="AE37" s="79"/>
-      <c r="AF37" s="79"/>
-      <c r="AG37" s="79"/>
-      <c r="AH37" s="79"/>
-      <c r="AI37" s="79"/>
-      <c r="AJ37" s="80"/>
+      <c r="A37" s="150"/>
+      <c r="B37" s="160"/>
+      <c r="C37" s="160"/>
+      <c r="D37" s="160"/>
+      <c r="E37" s="160"/>
+      <c r="F37" s="160"/>
+      <c r="G37" s="160"/>
+      <c r="H37" s="160"/>
+      <c r="I37" s="160"/>
+      <c r="J37" s="160"/>
+      <c r="K37" s="160"/>
+      <c r="L37" s="160"/>
+      <c r="M37" s="160"/>
+      <c r="N37" s="160"/>
+      <c r="O37" s="160"/>
+      <c r="P37" s="160"/>
+      <c r="Q37" s="160"/>
+      <c r="R37" s="160"/>
+      <c r="S37" s="160"/>
+      <c r="T37" s="160"/>
+      <c r="U37" s="160"/>
+      <c r="V37" s="160"/>
+      <c r="W37" s="160"/>
+      <c r="X37" s="160"/>
+      <c r="Y37" s="160"/>
+      <c r="Z37" s="160"/>
+      <c r="AA37" s="160"/>
+      <c r="AB37" s="160"/>
+      <c r="AC37" s="160"/>
+      <c r="AD37" s="160"/>
+      <c r="AE37" s="160"/>
+      <c r="AF37" s="160"/>
+      <c r="AG37" s="160"/>
+      <c r="AH37" s="160"/>
+      <c r="AI37" s="160"/>
+      <c r="AJ37" s="161"/>
     </row>
     <row r="38" spans="1:36" ht="14.25" customHeight="1">
-      <c r="A38" s="62"/>
-      <c r="B38" s="79"/>
-      <c r="C38" s="79"/>
-      <c r="D38" s="79"/>
-      <c r="E38" s="79"/>
-      <c r="F38" s="79"/>
-      <c r="G38" s="79"/>
-      <c r="H38" s="79"/>
-      <c r="I38" s="79"/>
-      <c r="J38" s="79"/>
-      <c r="K38" s="79"/>
-      <c r="L38" s="79"/>
-      <c r="M38" s="79"/>
-      <c r="N38" s="79"/>
-      <c r="O38" s="79"/>
-      <c r="P38" s="79"/>
-      <c r="Q38" s="79"/>
-      <c r="R38" s="79"/>
-      <c r="S38" s="79"/>
-      <c r="T38" s="79"/>
-      <c r="U38" s="79"/>
-      <c r="V38" s="79"/>
-      <c r="W38" s="79"/>
-      <c r="X38" s="79"/>
-      <c r="Y38" s="79"/>
-      <c r="Z38" s="79"/>
-      <c r="AA38" s="79"/>
-      <c r="AB38" s="79"/>
-      <c r="AC38" s="79"/>
-      <c r="AD38" s="79"/>
-      <c r="AE38" s="79"/>
-      <c r="AF38" s="79"/>
-      <c r="AG38" s="79"/>
-      <c r="AH38" s="79"/>
-      <c r="AI38" s="79"/>
-      <c r="AJ38" s="80"/>
+      <c r="A38" s="150"/>
+      <c r="B38" s="160"/>
+      <c r="C38" s="160"/>
+      <c r="D38" s="160"/>
+      <c r="E38" s="160"/>
+      <c r="F38" s="160"/>
+      <c r="G38" s="160"/>
+      <c r="H38" s="160"/>
+      <c r="I38" s="160"/>
+      <c r="J38" s="160"/>
+      <c r="K38" s="160"/>
+      <c r="L38" s="160"/>
+      <c r="M38" s="160"/>
+      <c r="N38" s="160"/>
+      <c r="O38" s="160"/>
+      <c r="P38" s="160"/>
+      <c r="Q38" s="160"/>
+      <c r="R38" s="160"/>
+      <c r="S38" s="160"/>
+      <c r="T38" s="160"/>
+      <c r="U38" s="160"/>
+      <c r="V38" s="160"/>
+      <c r="W38" s="160"/>
+      <c r="X38" s="160"/>
+      <c r="Y38" s="160"/>
+      <c r="Z38" s="160"/>
+      <c r="AA38" s="160"/>
+      <c r="AB38" s="160"/>
+      <c r="AC38" s="160"/>
+      <c r="AD38" s="160"/>
+      <c r="AE38" s="160"/>
+      <c r="AF38" s="160"/>
+      <c r="AG38" s="160"/>
+      <c r="AH38" s="160"/>
+      <c r="AI38" s="160"/>
+      <c r="AJ38" s="161"/>
     </row>
     <row r="39" spans="1:36" ht="27.6" customHeight="1">
-      <c r="A39" s="62"/>
-      <c r="B39" s="79"/>
-      <c r="C39" s="79"/>
-      <c r="D39" s="79"/>
-      <c r="E39" s="79"/>
-      <c r="F39" s="79"/>
-      <c r="G39" s="79"/>
-      <c r="H39" s="79"/>
-      <c r="I39" s="79"/>
-      <c r="J39" s="79"/>
-      <c r="K39" s="79"/>
-      <c r="L39" s="79"/>
-      <c r="M39" s="79"/>
-      <c r="N39" s="79"/>
-      <c r="O39" s="79"/>
-      <c r="P39" s="79"/>
-      <c r="Q39" s="79"/>
-      <c r="R39" s="79"/>
-      <c r="S39" s="79"/>
-      <c r="T39" s="79"/>
-      <c r="U39" s="79"/>
-      <c r="V39" s="79"/>
-      <c r="W39" s="79"/>
-      <c r="X39" s="79"/>
-      <c r="Y39" s="79"/>
-      <c r="Z39" s="79"/>
-      <c r="AA39" s="79"/>
-      <c r="AB39" s="79"/>
-      <c r="AC39" s="79"/>
-      <c r="AD39" s="79"/>
-      <c r="AE39" s="79"/>
-      <c r="AF39" s="79"/>
-      <c r="AG39" s="79"/>
-      <c r="AH39" s="79"/>
-      <c r="AI39" s="79"/>
-      <c r="AJ39" s="80"/>
+      <c r="A39" s="150"/>
+      <c r="B39" s="160"/>
+      <c r="C39" s="160"/>
+      <c r="D39" s="160"/>
+      <c r="E39" s="160"/>
+      <c r="F39" s="160"/>
+      <c r="G39" s="160"/>
+      <c r="H39" s="160"/>
+      <c r="I39" s="160"/>
+      <c r="J39" s="160"/>
+      <c r="K39" s="160"/>
+      <c r="L39" s="160"/>
+      <c r="M39" s="160"/>
+      <c r="N39" s="160"/>
+      <c r="O39" s="160"/>
+      <c r="P39" s="160"/>
+      <c r="Q39" s="160"/>
+      <c r="R39" s="160"/>
+      <c r="S39" s="160"/>
+      <c r="T39" s="160"/>
+      <c r="U39" s="160"/>
+      <c r="V39" s="160"/>
+      <c r="W39" s="160"/>
+      <c r="X39" s="160"/>
+      <c r="Y39" s="160"/>
+      <c r="Z39" s="160"/>
+      <c r="AA39" s="160"/>
+      <c r="AB39" s="160"/>
+      <c r="AC39" s="160"/>
+      <c r="AD39" s="160"/>
+      <c r="AE39" s="160"/>
+      <c r="AF39" s="160"/>
+      <c r="AG39" s="160"/>
+      <c r="AH39" s="160"/>
+      <c r="AI39" s="160"/>
+      <c r="AJ39" s="161"/>
     </row>
     <row r="40" spans="1:36" ht="16.8" customHeight="1">
-      <c r="A40" s="62"/>
-      <c r="B40" s="79"/>
-      <c r="C40" s="79"/>
-      <c r="D40" s="79"/>
-      <c r="E40" s="79"/>
-      <c r="F40" s="79"/>
-      <c r="G40" s="79"/>
-      <c r="H40" s="79"/>
-      <c r="I40" s="79"/>
-      <c r="J40" s="79"/>
-      <c r="K40" s="79"/>
-      <c r="L40" s="79"/>
-      <c r="M40" s="79"/>
-      <c r="N40" s="79"/>
-      <c r="O40" s="79"/>
-      <c r="P40" s="79"/>
-      <c r="Q40" s="79"/>
-      <c r="R40" s="79"/>
-      <c r="S40" s="79"/>
-      <c r="T40" s="79"/>
-      <c r="U40" s="79"/>
-      <c r="V40" s="79"/>
-      <c r="W40" s="79"/>
-      <c r="X40" s="79"/>
-      <c r="Y40" s="79"/>
-      <c r="Z40" s="79"/>
-      <c r="AA40" s="79"/>
-      <c r="AB40" s="79"/>
-      <c r="AC40" s="79"/>
-      <c r="AD40" s="79"/>
-      <c r="AE40" s="79"/>
-      <c r="AF40" s="79"/>
-      <c r="AG40" s="79"/>
-      <c r="AH40" s="79"/>
-      <c r="AI40" s="79"/>
-      <c r="AJ40" s="80"/>
+      <c r="A40" s="150"/>
+      <c r="B40" s="160"/>
+      <c r="C40" s="160"/>
+      <c r="D40" s="160"/>
+      <c r="E40" s="160"/>
+      <c r="F40" s="160"/>
+      <c r="G40" s="160"/>
+      <c r="H40" s="160"/>
+      <c r="I40" s="160"/>
+      <c r="J40" s="160"/>
+      <c r="K40" s="160"/>
+      <c r="L40" s="160"/>
+      <c r="M40" s="160"/>
+      <c r="N40" s="160"/>
+      <c r="O40" s="160"/>
+      <c r="P40" s="160"/>
+      <c r="Q40" s="160"/>
+      <c r="R40" s="160"/>
+      <c r="S40" s="160"/>
+      <c r="T40" s="160"/>
+      <c r="U40" s="160"/>
+      <c r="V40" s="160"/>
+      <c r="W40" s="160"/>
+      <c r="X40" s="160"/>
+      <c r="Y40" s="160"/>
+      <c r="Z40" s="160"/>
+      <c r="AA40" s="160"/>
+      <c r="AB40" s="160"/>
+      <c r="AC40" s="160"/>
+      <c r="AD40" s="160"/>
+      <c r="AE40" s="160"/>
+      <c r="AF40" s="160"/>
+      <c r="AG40" s="160"/>
+      <c r="AH40" s="160"/>
+      <c r="AI40" s="160"/>
+      <c r="AJ40" s="161"/>
     </row>
     <row r="41" spans="1:36" ht="16.8" customHeight="1">
-      <c r="A41" s="69" t="s">
+      <c r="A41" s="74" t="s">
         <v>99</v>
       </c>
-      <c r="B41" s="70"/>
-      <c r="C41" s="70"/>
-      <c r="D41" s="70"/>
-      <c r="E41" s="70"/>
-      <c r="F41" s="70"/>
-      <c r="G41" s="70"/>
-      <c r="H41" s="70"/>
-      <c r="I41" s="70"/>
-      <c r="J41" s="70"/>
-      <c r="K41" s="70"/>
-      <c r="L41" s="70"/>
-      <c r="M41" s="70"/>
-      <c r="N41" s="70"/>
-      <c r="O41" s="70"/>
-      <c r="P41" s="70"/>
-      <c r="Q41" s="70"/>
-      <c r="R41" s="70"/>
+      <c r="B41" s="75"/>
+      <c r="C41" s="75"/>
+      <c r="D41" s="75"/>
+      <c r="E41" s="75"/>
+      <c r="F41" s="75"/>
+      <c r="G41" s="75"/>
+      <c r="H41" s="75"/>
+      <c r="I41" s="75"/>
+      <c r="J41" s="75"/>
+      <c r="K41" s="75"/>
+      <c r="L41" s="75"/>
+      <c r="M41" s="75"/>
+      <c r="N41" s="75"/>
+      <c r="O41" s="75"/>
+      <c r="P41" s="75"/>
+      <c r="Q41" s="75"/>
+      <c r="R41" s="75"/>
       <c r="S41" s="40"/>
       <c r="T41" s="40"/>
       <c r="U41" s="40"/>
@@ -8676,675 +8678,675 @@
       <c r="AJ42" s="55"/>
     </row>
     <row r="43" spans="1:36" ht="17.25" customHeight="1">
-      <c r="A43" s="71" t="s">
+      <c r="A43" s="100" t="s">
         <v>18</v>
       </c>
-      <c r="B43" s="72"/>
-      <c r="C43" s="72"/>
-      <c r="D43" s="72"/>
-      <c r="E43" s="72"/>
-      <c r="F43" s="72"/>
-      <c r="G43" s="72"/>
-      <c r="H43" s="72"/>
-      <c r="I43" s="73"/>
-      <c r="J43" s="71" t="s">
+      <c r="B43" s="101"/>
+      <c r="C43" s="101"/>
+      <c r="D43" s="101"/>
+      <c r="E43" s="101"/>
+      <c r="F43" s="101"/>
+      <c r="G43" s="101"/>
+      <c r="H43" s="101"/>
+      <c r="I43" s="102"/>
+      <c r="J43" s="100" t="s">
         <v>19</v>
       </c>
-      <c r="K43" s="72"/>
-      <c r="L43" s="72"/>
-      <c r="M43" s="72"/>
-      <c r="N43" s="72"/>
-      <c r="O43" s="72"/>
-      <c r="P43" s="72"/>
-      <c r="Q43" s="72"/>
-      <c r="R43" s="73"/>
-      <c r="S43" s="71" t="s">
+      <c r="K43" s="101"/>
+      <c r="L43" s="101"/>
+      <c r="M43" s="101"/>
+      <c r="N43" s="101"/>
+      <c r="O43" s="101"/>
+      <c r="P43" s="101"/>
+      <c r="Q43" s="101"/>
+      <c r="R43" s="102"/>
+      <c r="S43" s="100" t="s">
         <v>77</v>
       </c>
-      <c r="T43" s="72"/>
-      <c r="U43" s="72"/>
-      <c r="V43" s="72"/>
-      <c r="W43" s="72"/>
-      <c r="X43" s="72"/>
-      <c r="Y43" s="72"/>
-      <c r="Z43" s="72"/>
-      <c r="AA43" s="73"/>
-      <c r="AB43" s="77" t="s">
+      <c r="T43" s="101"/>
+      <c r="U43" s="101"/>
+      <c r="V43" s="101"/>
+      <c r="W43" s="101"/>
+      <c r="X43" s="101"/>
+      <c r="Y43" s="101"/>
+      <c r="Z43" s="101"/>
+      <c r="AA43" s="102"/>
+      <c r="AB43" s="159" t="s">
         <v>91</v>
       </c>
-      <c r="AC43" s="72"/>
-      <c r="AD43" s="72"/>
-      <c r="AE43" s="72"/>
-      <c r="AF43" s="72"/>
-      <c r="AG43" s="72"/>
-      <c r="AH43" s="72"/>
-      <c r="AI43" s="72"/>
-      <c r="AJ43" s="73"/>
+      <c r="AC43" s="101"/>
+      <c r="AD43" s="101"/>
+      <c r="AE43" s="101"/>
+      <c r="AF43" s="101"/>
+      <c r="AG43" s="101"/>
+      <c r="AH43" s="101"/>
+      <c r="AI43" s="101"/>
+      <c r="AJ43" s="102"/>
     </row>
     <row r="44" spans="1:36" ht="18" customHeight="1">
       <c r="A44" s="2"/>
-      <c r="B44" s="57" t="s">
+      <c r="B44" s="125" t="s">
         <v>21</v>
       </c>
-      <c r="C44" s="57"/>
-      <c r="D44" s="57"/>
-      <c r="E44" s="57"/>
-      <c r="F44" s="57"/>
-      <c r="G44" s="57"/>
-      <c r="H44" s="57"/>
-      <c r="I44" s="58"/>
+      <c r="C44" s="125"/>
+      <c r="D44" s="125"/>
+      <c r="E44" s="125"/>
+      <c r="F44" s="125"/>
+      <c r="G44" s="125"/>
+      <c r="H44" s="125"/>
+      <c r="I44" s="126"/>
       <c r="J44" s="10"/>
-      <c r="K44" s="57" t="s">
+      <c r="K44" s="125" t="s">
         <v>22</v>
       </c>
-      <c r="L44" s="57"/>
-      <c r="M44" s="57"/>
-      <c r="N44" s="57"/>
-      <c r="O44" s="57"/>
-      <c r="P44" s="57"/>
-      <c r="Q44" s="57"/>
-      <c r="R44" s="58"/>
-      <c r="S44" s="84" t="s">
+      <c r="L44" s="125"/>
+      <c r="M44" s="125"/>
+      <c r="N44" s="125"/>
+      <c r="O44" s="125"/>
+      <c r="P44" s="125"/>
+      <c r="Q44" s="125"/>
+      <c r="R44" s="126"/>
+      <c r="S44" s="122" t="s">
         <v>81</v>
       </c>
-      <c r="T44" s="85"/>
-      <c r="U44" s="85"/>
-      <c r="V44" s="85"/>
-      <c r="W44" s="78"/>
-      <c r="X44" s="78"/>
-      <c r="Y44" s="78"/>
+      <c r="T44" s="80"/>
+      <c r="U44" s="80"/>
+      <c r="V44" s="80"/>
+      <c r="W44" s="63"/>
+      <c r="X44" s="63"/>
+      <c r="Y44" s="63"/>
       <c r="Z44" s="49"/>
       <c r="AA44" s="4"/>
-      <c r="AB44" s="59" t="s">
+      <c r="AB44" s="123" t="s">
         <v>82</v>
       </c>
-      <c r="AC44" s="60"/>
-      <c r="AD44" s="60"/>
-      <c r="AE44" s="60"/>
-      <c r="AF44" s="74"/>
-      <c r="AG44" s="74"/>
-      <c r="AH44" s="74"/>
-      <c r="AI44" s="74"/>
+      <c r="AC44" s="76"/>
+      <c r="AD44" s="76"/>
+      <c r="AE44" s="76"/>
+      <c r="AF44" s="130"/>
+      <c r="AG44" s="130"/>
+      <c r="AH44" s="130"/>
+      <c r="AI44" s="130"/>
       <c r="AJ44" s="4"/>
     </row>
     <row r="45" spans="1:36" ht="18" customHeight="1">
       <c r="A45" s="2"/>
-      <c r="B45" s="57" t="s">
+      <c r="B45" s="125" t="s">
         <v>24</v>
       </c>
-      <c r="C45" s="57"/>
-      <c r="D45" s="57"/>
-      <c r="E45" s="57"/>
-      <c r="F45" s="57"/>
-      <c r="G45" s="57"/>
-      <c r="H45" s="57"/>
-      <c r="I45" s="58"/>
+      <c r="C45" s="125"/>
+      <c r="D45" s="125"/>
+      <c r="E45" s="125"/>
+      <c r="F45" s="125"/>
+      <c r="G45" s="125"/>
+      <c r="H45" s="125"/>
+      <c r="I45" s="126"/>
       <c r="J45" s="10"/>
-      <c r="K45" s="57" t="s">
+      <c r="K45" s="125" t="s">
         <v>25</v>
       </c>
-      <c r="L45" s="57"/>
-      <c r="M45" s="57"/>
-      <c r="N45" s="57"/>
-      <c r="O45" s="57"/>
-      <c r="P45" s="57"/>
-      <c r="Q45" s="57"/>
-      <c r="R45" s="58"/>
-      <c r="S45" s="84" t="s">
+      <c r="L45" s="125"/>
+      <c r="M45" s="125"/>
+      <c r="N45" s="125"/>
+      <c r="O45" s="125"/>
+      <c r="P45" s="125"/>
+      <c r="Q45" s="125"/>
+      <c r="R45" s="126"/>
+      <c r="S45" s="122" t="s">
         <v>80</v>
       </c>
-      <c r="T45" s="85"/>
-      <c r="U45" s="85"/>
-      <c r="V45" s="85"/>
-      <c r="W45" s="56"/>
-      <c r="X45" s="56"/>
-      <c r="Y45" s="56"/>
-      <c r="Z45" s="56"/>
+      <c r="T45" s="80"/>
+      <c r="U45" s="80"/>
+      <c r="V45" s="80"/>
+      <c r="W45" s="149"/>
+      <c r="X45" s="149"/>
+      <c r="Y45" s="149"/>
+      <c r="Z45" s="149"/>
       <c r="AA45" s="4"/>
-      <c r="AB45" s="84" t="s">
+      <c r="AB45" s="122" t="s">
         <v>81</v>
       </c>
-      <c r="AC45" s="85"/>
-      <c r="AD45" s="85"/>
-      <c r="AE45" s="85"/>
-      <c r="AF45" s="56"/>
-      <c r="AG45" s="56"/>
-      <c r="AH45" s="56"/>
-      <c r="AI45" s="56"/>
+      <c r="AC45" s="80"/>
+      <c r="AD45" s="80"/>
+      <c r="AE45" s="80"/>
+      <c r="AF45" s="149"/>
+      <c r="AG45" s="149"/>
+      <c r="AH45" s="149"/>
+      <c r="AI45" s="149"/>
       <c r="AJ45" s="4"/>
     </row>
     <row r="46" spans="1:36" ht="18" customHeight="1">
       <c r="A46" s="2"/>
-      <c r="B46" s="57" t="s">
+      <c r="B46" s="125" t="s">
         <v>27</v>
       </c>
-      <c r="C46" s="57"/>
-      <c r="D46" s="57"/>
-      <c r="E46" s="57"/>
-      <c r="F46" s="57"/>
-      <c r="G46" s="57"/>
-      <c r="H46" s="57"/>
-      <c r="I46" s="58"/>
+      <c r="C46" s="125"/>
+      <c r="D46" s="125"/>
+      <c r="E46" s="125"/>
+      <c r="F46" s="125"/>
+      <c r="G46" s="125"/>
+      <c r="H46" s="125"/>
+      <c r="I46" s="126"/>
       <c r="J46" s="10"/>
-      <c r="K46" s="57" t="s">
+      <c r="K46" s="125" t="s">
         <v>28</v>
       </c>
-      <c r="L46" s="57"/>
-      <c r="M46" s="57"/>
-      <c r="N46" s="57"/>
-      <c r="O46" s="57"/>
-      <c r="P46" s="57"/>
-      <c r="Q46" s="57"/>
-      <c r="R46" s="58"/>
-      <c r="S46" s="59" t="s">
+      <c r="L46" s="125"/>
+      <c r="M46" s="125"/>
+      <c r="N46" s="125"/>
+      <c r="O46" s="125"/>
+      <c r="P46" s="125"/>
+      <c r="Q46" s="125"/>
+      <c r="R46" s="126"/>
+      <c r="S46" s="123" t="s">
         <v>78</v>
       </c>
-      <c r="T46" s="60"/>
-      <c r="U46" s="60"/>
-      <c r="V46" s="60"/>
-      <c r="W46" s="60"/>
-      <c r="X46" s="93"/>
-      <c r="Y46" s="93"/>
-      <c r="Z46" s="93"/>
+      <c r="T46" s="76"/>
+      <c r="U46" s="76"/>
+      <c r="V46" s="76"/>
+      <c r="W46" s="76"/>
+      <c r="X46" s="124"/>
+      <c r="Y46" s="124"/>
+      <c r="Z46" s="124"/>
       <c r="AA46" s="12" t="s">
         <v>30</v>
       </c>
-      <c r="AB46" s="84" t="s">
+      <c r="AB46" s="122" t="s">
         <v>80</v>
       </c>
-      <c r="AC46" s="85"/>
-      <c r="AD46" s="85"/>
-      <c r="AE46" s="85"/>
-      <c r="AF46" s="56"/>
-      <c r="AG46" s="56"/>
-      <c r="AH46" s="56"/>
-      <c r="AI46" s="56"/>
+      <c r="AC46" s="80"/>
+      <c r="AD46" s="80"/>
+      <c r="AE46" s="80"/>
+      <c r="AF46" s="149"/>
+      <c r="AG46" s="149"/>
+      <c r="AH46" s="149"/>
+      <c r="AI46" s="149"/>
       <c r="AJ46" s="4"/>
     </row>
     <row r="47" spans="1:36" ht="18" customHeight="1">
       <c r="A47" s="2"/>
-      <c r="B47" s="57" t="s">
+      <c r="B47" s="125" t="s">
         <v>87</v>
       </c>
-      <c r="C47" s="57"/>
-      <c r="D47" s="57"/>
-      <c r="E47" s="57"/>
-      <c r="F47" s="57"/>
-      <c r="G47" s="57"/>
-      <c r="H47" s="57"/>
-      <c r="I47" s="58"/>
+      <c r="C47" s="125"/>
+      <c r="D47" s="125"/>
+      <c r="E47" s="125"/>
+      <c r="F47" s="125"/>
+      <c r="G47" s="125"/>
+      <c r="H47" s="125"/>
+      <c r="I47" s="126"/>
       <c r="J47" s="10"/>
-      <c r="K47" s="57" t="s">
+      <c r="K47" s="125" t="s">
         <v>31</v>
       </c>
-      <c r="L47" s="57"/>
-      <c r="M47" s="57"/>
-      <c r="N47" s="57"/>
-      <c r="O47" s="57"/>
-      <c r="P47" s="57"/>
-      <c r="Q47" s="57"/>
-      <c r="R47" s="58"/>
-      <c r="S47" s="101" t="s">
+      <c r="L47" s="125"/>
+      <c r="M47" s="125"/>
+      <c r="N47" s="125"/>
+      <c r="O47" s="125"/>
+      <c r="P47" s="125"/>
+      <c r="Q47" s="125"/>
+      <c r="R47" s="126"/>
+      <c r="S47" s="127" t="s">
         <v>79</v>
       </c>
-      <c r="T47" s="102"/>
-      <c r="U47" s="102"/>
-      <c r="V47" s="102"/>
-      <c r="W47" s="102"/>
-      <c r="X47" s="61"/>
-      <c r="Y47" s="61"/>
-      <c r="Z47" s="61"/>
+      <c r="T47" s="128"/>
+      <c r="U47" s="128"/>
+      <c r="V47" s="128"/>
+      <c r="W47" s="128"/>
+      <c r="X47" s="144"/>
+      <c r="Y47" s="144"/>
+      <c r="Z47" s="144"/>
       <c r="AA47" s="33" t="s">
         <v>30</v>
       </c>
-      <c r="AB47" s="84" t="s">
+      <c r="AB47" s="122" t="s">
         <v>83</v>
       </c>
-      <c r="AC47" s="85"/>
-      <c r="AD47" s="85"/>
-      <c r="AE47" s="85"/>
-      <c r="AF47" s="74"/>
-      <c r="AG47" s="74"/>
-      <c r="AH47" s="74"/>
-      <c r="AI47" s="74"/>
+      <c r="AC47" s="80"/>
+      <c r="AD47" s="80"/>
+      <c r="AE47" s="80"/>
+      <c r="AF47" s="130"/>
+      <c r="AG47" s="130"/>
+      <c r="AH47" s="130"/>
+      <c r="AI47" s="130"/>
       <c r="AJ47" s="4"/>
     </row>
     <row r="48" spans="1:36" ht="18" customHeight="1">
       <c r="A48" s="34"/>
-      <c r="B48" s="57" t="s">
+      <c r="B48" s="125" t="s">
         <v>33</v>
       </c>
-      <c r="C48" s="57"/>
-      <c r="D48" s="57"/>
-      <c r="E48" s="57"/>
-      <c r="F48" s="57"/>
-      <c r="G48" s="57"/>
-      <c r="H48" s="57"/>
-      <c r="I48" s="58"/>
+      <c r="C48" s="125"/>
+      <c r="D48" s="125"/>
+      <c r="E48" s="125"/>
+      <c r="F48" s="125"/>
+      <c r="G48" s="125"/>
+      <c r="H48" s="125"/>
+      <c r="I48" s="126"/>
       <c r="J48" s="10"/>
-      <c r="K48" s="57" t="s">
+      <c r="K48" s="125" t="s">
         <v>34</v>
       </c>
-      <c r="L48" s="57"/>
-      <c r="M48" s="57"/>
-      <c r="N48" s="57"/>
-      <c r="O48" s="57"/>
-      <c r="P48" s="57"/>
-      <c r="Q48" s="57"/>
-      <c r="R48" s="58"/>
-      <c r="S48" s="90" t="s">
+      <c r="L48" s="125"/>
+      <c r="M48" s="125"/>
+      <c r="N48" s="125"/>
+      <c r="O48" s="125"/>
+      <c r="P48" s="125"/>
+      <c r="Q48" s="125"/>
+      <c r="R48" s="126"/>
+      <c r="S48" s="140" t="s">
         <v>20</v>
       </c>
-      <c r="T48" s="91"/>
-      <c r="U48" s="91"/>
-      <c r="V48" s="91"/>
-      <c r="W48" s="91"/>
-      <c r="X48" s="91"/>
-      <c r="Y48" s="91"/>
-      <c r="Z48" s="91"/>
-      <c r="AA48" s="92"/>
-      <c r="AB48" s="59" t="s">
+      <c r="T48" s="141"/>
+      <c r="U48" s="141"/>
+      <c r="V48" s="141"/>
+      <c r="W48" s="141"/>
+      <c r="X48" s="141"/>
+      <c r="Y48" s="141"/>
+      <c r="Z48" s="141"/>
+      <c r="AA48" s="142"/>
+      <c r="AB48" s="123" t="s">
         <v>78</v>
       </c>
-      <c r="AC48" s="60"/>
-      <c r="AD48" s="60"/>
-      <c r="AE48" s="60"/>
-      <c r="AF48" s="60"/>
-      <c r="AG48" s="93"/>
-      <c r="AH48" s="93"/>
-      <c r="AI48" s="93"/>
+      <c r="AC48" s="76"/>
+      <c r="AD48" s="76"/>
+      <c r="AE48" s="76"/>
+      <c r="AF48" s="76"/>
+      <c r="AG48" s="124"/>
+      <c r="AH48" s="124"/>
+      <c r="AI48" s="124"/>
       <c r="AJ48" s="12" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="49" spans="1:36" ht="18" customHeight="1">
       <c r="A49" s="10"/>
-      <c r="B49" s="57" t="s">
+      <c r="B49" s="125" t="s">
         <v>74</v>
       </c>
-      <c r="C49" s="57"/>
-      <c r="D49" s="57"/>
-      <c r="E49" s="57"/>
-      <c r="F49" s="57"/>
-      <c r="G49" s="57"/>
-      <c r="H49" s="57"/>
-      <c r="I49" s="58"/>
+      <c r="C49" s="125"/>
+      <c r="D49" s="125"/>
+      <c r="E49" s="125"/>
+      <c r="F49" s="125"/>
+      <c r="G49" s="125"/>
+      <c r="H49" s="125"/>
+      <c r="I49" s="126"/>
       <c r="J49" s="10"/>
-      <c r="K49" s="57" t="s">
+      <c r="K49" s="125" t="s">
         <v>37</v>
       </c>
-      <c r="L49" s="57"/>
-      <c r="M49" s="57"/>
-      <c r="N49" s="57"/>
-      <c r="O49" s="57"/>
-      <c r="P49" s="57"/>
-      <c r="Q49" s="57"/>
-      <c r="R49" s="58"/>
+      <c r="L49" s="125"/>
+      <c r="M49" s="125"/>
+      <c r="N49" s="125"/>
+      <c r="O49" s="125"/>
+      <c r="P49" s="125"/>
+      <c r="Q49" s="125"/>
+      <c r="R49" s="126"/>
       <c r="S49" s="10"/>
-      <c r="T49" s="57" t="s">
+      <c r="T49" s="125" t="s">
         <v>23</v>
       </c>
-      <c r="U49" s="57"/>
-      <c r="V49" s="57"/>
-      <c r="W49" s="57"/>
-      <c r="X49" s="57"/>
-      <c r="Y49" s="57"/>
-      <c r="Z49" s="57"/>
-      <c r="AA49" s="58"/>
-      <c r="AB49" s="101" t="s">
+      <c r="U49" s="125"/>
+      <c r="V49" s="125"/>
+      <c r="W49" s="125"/>
+      <c r="X49" s="125"/>
+      <c r="Y49" s="125"/>
+      <c r="Z49" s="125"/>
+      <c r="AA49" s="126"/>
+      <c r="AB49" s="127" t="s">
         <v>79</v>
       </c>
-      <c r="AC49" s="102"/>
-      <c r="AD49" s="102"/>
-      <c r="AE49" s="102"/>
-      <c r="AF49" s="102"/>
-      <c r="AG49" s="61"/>
-      <c r="AH49" s="61"/>
-      <c r="AI49" s="61"/>
+      <c r="AC49" s="128"/>
+      <c r="AD49" s="128"/>
+      <c r="AE49" s="128"/>
+      <c r="AF49" s="128"/>
+      <c r="AG49" s="144"/>
+      <c r="AH49" s="144"/>
+      <c r="AI49" s="144"/>
       <c r="AJ49" s="33" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="50" spans="1:36" ht="18" customHeight="1">
       <c r="A50" s="10"/>
-      <c r="B50" s="57" t="s">
+      <c r="B50" s="125" t="s">
         <v>75</v>
       </c>
-      <c r="C50" s="57"/>
-      <c r="D50" s="57"/>
-      <c r="E50" s="57"/>
-      <c r="F50" s="57"/>
-      <c r="G50" s="57"/>
-      <c r="H50" s="57"/>
-      <c r="I50" s="58"/>
+      <c r="C50" s="125"/>
+      <c r="D50" s="125"/>
+      <c r="E50" s="125"/>
+      <c r="F50" s="125"/>
+      <c r="G50" s="125"/>
+      <c r="H50" s="125"/>
+      <c r="I50" s="126"/>
       <c r="J50" s="10"/>
-      <c r="K50" s="57" t="s">
+      <c r="K50" s="125" t="s">
         <v>39</v>
       </c>
-      <c r="L50" s="57"/>
-      <c r="M50" s="57"/>
-      <c r="N50" s="57"/>
-      <c r="O50" s="57"/>
-      <c r="P50" s="57"/>
-      <c r="Q50" s="57"/>
-      <c r="R50" s="58"/>
+      <c r="L50" s="125"/>
+      <c r="M50" s="125"/>
+      <c r="N50" s="125"/>
+      <c r="O50" s="125"/>
+      <c r="P50" s="125"/>
+      <c r="Q50" s="125"/>
+      <c r="R50" s="126"/>
       <c r="S50" s="10"/>
-      <c r="T50" s="57" t="s">
+      <c r="T50" s="125" t="s">
         <v>26</v>
       </c>
-      <c r="U50" s="57"/>
-      <c r="V50" s="57"/>
-      <c r="W50" s="57"/>
-      <c r="X50" s="57"/>
-      <c r="Y50" s="57"/>
-      <c r="Z50" s="57"/>
-      <c r="AA50" s="58"/>
-      <c r="AB50" s="104" t="s">
+      <c r="U50" s="125"/>
+      <c r="V50" s="125"/>
+      <c r="W50" s="125"/>
+      <c r="X50" s="125"/>
+      <c r="Y50" s="125"/>
+      <c r="Z50" s="125"/>
+      <c r="AA50" s="126"/>
+      <c r="AB50" s="131" t="s">
         <v>38</v>
       </c>
-      <c r="AC50" s="105"/>
-      <c r="AD50" s="105"/>
-      <c r="AE50" s="105"/>
-      <c r="AF50" s="105"/>
-      <c r="AG50" s="105"/>
-      <c r="AH50" s="105"/>
-      <c r="AI50" s="105"/>
-      <c r="AJ50" s="106"/>
+      <c r="AC50" s="132"/>
+      <c r="AD50" s="132"/>
+      <c r="AE50" s="132"/>
+      <c r="AF50" s="132"/>
+      <c r="AG50" s="132"/>
+      <c r="AH50" s="132"/>
+      <c r="AI50" s="132"/>
+      <c r="AJ50" s="133"/>
     </row>
     <row r="51" spans="1:36" ht="18" customHeight="1">
       <c r="A51" s="10"/>
-      <c r="B51" s="57" t="s">
+      <c r="B51" s="125" t="s">
         <v>40</v>
       </c>
-      <c r="C51" s="57"/>
-      <c r="D51" s="57"/>
-      <c r="E51" s="57"/>
-      <c r="F51" s="57"/>
-      <c r="G51" s="57"/>
-      <c r="H51" s="57"/>
-      <c r="I51" s="58"/>
+      <c r="C51" s="125"/>
+      <c r="D51" s="125"/>
+      <c r="E51" s="125"/>
+      <c r="F51" s="125"/>
+      <c r="G51" s="125"/>
+      <c r="H51" s="125"/>
+      <c r="I51" s="126"/>
       <c r="J51" s="10"/>
-      <c r="K51" s="57" t="s">
+      <c r="K51" s="125" t="s">
         <v>41</v>
       </c>
-      <c r="L51" s="57"/>
-      <c r="M51" s="57"/>
-      <c r="N51" s="57"/>
-      <c r="O51" s="57"/>
-      <c r="P51" s="57"/>
-      <c r="Q51" s="57"/>
-      <c r="R51" s="58"/>
+      <c r="L51" s="125"/>
+      <c r="M51" s="125"/>
+      <c r="N51" s="125"/>
+      <c r="O51" s="125"/>
+      <c r="P51" s="125"/>
+      <c r="Q51" s="125"/>
+      <c r="R51" s="126"/>
       <c r="S51" s="10"/>
-      <c r="T51" s="57" t="s">
+      <c r="T51" s="125" t="s">
         <v>29</v>
       </c>
-      <c r="U51" s="57"/>
-      <c r="V51" s="57"/>
-      <c r="W51" s="93"/>
-      <c r="X51" s="93"/>
-      <c r="Y51" s="93"/>
+      <c r="U51" s="125"/>
+      <c r="V51" s="125"/>
+      <c r="W51" s="124"/>
+      <c r="X51" s="124"/>
+      <c r="Y51" s="124"/>
       <c r="Z51" s="3" t="s">
         <v>30</v>
       </c>
       <c r="AA51" s="4"/>
       <c r="AB51" s="10"/>
-      <c r="AC51" s="107" t="s">
+      <c r="AC51" s="134" t="s">
         <v>76</v>
       </c>
-      <c r="AD51" s="107"/>
-      <c r="AE51" s="107"/>
-      <c r="AF51" s="107"/>
-      <c r="AG51" s="107"/>
-      <c r="AH51" s="107"/>
-      <c r="AI51" s="107"/>
-      <c r="AJ51" s="108"/>
+      <c r="AD51" s="134"/>
+      <c r="AE51" s="134"/>
+      <c r="AF51" s="134"/>
+      <c r="AG51" s="134"/>
+      <c r="AH51" s="134"/>
+      <c r="AI51" s="134"/>
+      <c r="AJ51" s="135"/>
     </row>
     <row r="52" spans="1:36" ht="18" customHeight="1">
       <c r="A52" s="10"/>
-      <c r="B52" s="57" t="s">
+      <c r="B52" s="125" t="s">
         <v>43</v>
       </c>
-      <c r="C52" s="57"/>
-      <c r="D52" s="109"/>
-      <c r="E52" s="109"/>
-      <c r="F52" s="109"/>
-      <c r="G52" s="109"/>
-      <c r="H52" s="109"/>
+      <c r="C52" s="125"/>
+      <c r="D52" s="136"/>
+      <c r="E52" s="136"/>
+      <c r="F52" s="136"/>
+      <c r="G52" s="136"/>
+      <c r="H52" s="136"/>
       <c r="I52" s="4"/>
       <c r="J52" s="10"/>
-      <c r="K52" s="57" t="s">
+      <c r="K52" s="125" t="s">
         <v>44</v>
       </c>
-      <c r="L52" s="57"/>
-      <c r="M52" s="57"/>
-      <c r="N52" s="57"/>
-      <c r="O52" s="57"/>
-      <c r="P52" s="57"/>
-      <c r="Q52" s="57"/>
-      <c r="R52" s="58"/>
+      <c r="L52" s="125"/>
+      <c r="M52" s="125"/>
+      <c r="N52" s="125"/>
+      <c r="O52" s="125"/>
+      <c r="P52" s="125"/>
+      <c r="Q52" s="125"/>
+      <c r="R52" s="126"/>
       <c r="S52" s="10"/>
-      <c r="T52" s="57" t="s">
+      <c r="T52" s="125" t="s">
         <v>32</v>
       </c>
-      <c r="U52" s="57"/>
-      <c r="V52" s="57"/>
-      <c r="W52" s="93"/>
-      <c r="X52" s="93"/>
-      <c r="Y52" s="93"/>
+      <c r="U52" s="125"/>
+      <c r="V52" s="125"/>
+      <c r="W52" s="124"/>
+      <c r="X52" s="124"/>
+      <c r="Y52" s="124"/>
       <c r="Z52" s="3" t="s">
         <v>30</v>
       </c>
       <c r="AA52" s="4"/>
       <c r="AB52" s="10"/>
-      <c r="AC52" s="57" t="s">
+      <c r="AC52" s="125" t="s">
         <v>42</v>
       </c>
-      <c r="AD52" s="57"/>
-      <c r="AE52" s="57"/>
-      <c r="AF52" s="57"/>
-      <c r="AG52" s="57"/>
-      <c r="AH52" s="57"/>
-      <c r="AI52" s="57"/>
-      <c r="AJ52" s="58"/>
+      <c r="AD52" s="125"/>
+      <c r="AE52" s="125"/>
+      <c r="AF52" s="125"/>
+      <c r="AG52" s="125"/>
+      <c r="AH52" s="125"/>
+      <c r="AI52" s="125"/>
+      <c r="AJ52" s="126"/>
     </row>
     <row r="53" spans="1:36" ht="18" customHeight="1">
       <c r="A53" s="13"/>
       <c r="B53" s="7"/>
       <c r="C53" s="7"/>
-      <c r="D53" s="98"/>
-      <c r="E53" s="98"/>
-      <c r="F53" s="98"/>
-      <c r="G53" s="98"/>
-      <c r="H53" s="98"/>
+      <c r="D53" s="147"/>
+      <c r="E53" s="147"/>
+      <c r="F53" s="147"/>
+      <c r="G53" s="147"/>
+      <c r="H53" s="147"/>
       <c r="I53" s="8"/>
-      <c r="J53" s="101"/>
-      <c r="K53" s="102"/>
-      <c r="L53" s="102"/>
-      <c r="M53" s="102"/>
-      <c r="N53" s="102"/>
-      <c r="O53" s="102"/>
-      <c r="P53" s="102"/>
-      <c r="Q53" s="102"/>
-      <c r="R53" s="110"/>
+      <c r="J53" s="127"/>
+      <c r="K53" s="128"/>
+      <c r="L53" s="128"/>
+      <c r="M53" s="128"/>
+      <c r="N53" s="128"/>
+      <c r="O53" s="128"/>
+      <c r="P53" s="128"/>
+      <c r="Q53" s="128"/>
+      <c r="R53" s="129"/>
       <c r="S53" s="13"/>
-      <c r="T53" s="94" t="s">
+      <c r="T53" s="143" t="s">
         <v>35</v>
       </c>
-      <c r="U53" s="94"/>
-      <c r="V53" s="94"/>
-      <c r="W53" s="61"/>
-      <c r="X53" s="61"/>
-      <c r="Y53" s="61"/>
+      <c r="U53" s="143"/>
+      <c r="V53" s="143"/>
+      <c r="W53" s="144"/>
+      <c r="X53" s="144"/>
+      <c r="Y53" s="144"/>
       <c r="Z53" s="6" t="s">
         <v>36</v>
       </c>
       <c r="AA53" s="8"/>
       <c r="AB53" s="13"/>
-      <c r="AC53" s="94" t="s">
+      <c r="AC53" s="143" t="s">
         <v>45</v>
       </c>
-      <c r="AD53" s="94"/>
-      <c r="AE53" s="94"/>
-      <c r="AF53" s="103"/>
-      <c r="AG53" s="103"/>
-      <c r="AH53" s="103"/>
+      <c r="AD53" s="143"/>
+      <c r="AE53" s="143"/>
+      <c r="AF53" s="99"/>
+      <c r="AG53" s="99"/>
+      <c r="AH53" s="99"/>
       <c r="AI53" s="7"/>
       <c r="AJ53" s="8"/>
     </row>
     <row r="54" spans="1:36" ht="18" customHeight="1">
-      <c r="A54" s="96" t="s">
+      <c r="A54" s="145" t="s">
         <v>46</v>
       </c>
-      <c r="B54" s="96"/>
-      <c r="C54" s="96"/>
-      <c r="D54" s="96"/>
-      <c r="E54" s="96"/>
-      <c r="F54" s="96"/>
-      <c r="G54" s="96"/>
-      <c r="H54" s="96"/>
-      <c r="I54" s="96"/>
-      <c r="J54" s="96"/>
-      <c r="K54" s="96"/>
-      <c r="L54" s="96"/>
-      <c r="M54" s="96"/>
-      <c r="N54" s="97"/>
-      <c r="O54" s="97"/>
-      <c r="P54" s="97"/>
-      <c r="Q54" s="97"/>
-      <c r="R54" s="97"/>
-      <c r="S54" s="97"/>
-      <c r="T54" s="97"/>
-      <c r="U54" s="97"/>
-      <c r="V54" s="97"/>
-      <c r="W54" s="97"/>
-      <c r="X54" s="97"/>
-      <c r="Y54" s="97"/>
-      <c r="Z54" s="97"/>
-      <c r="AA54" s="97"/>
-      <c r="AB54" s="97"/>
-      <c r="AC54" s="97"/>
-      <c r="AD54" s="97"/>
-      <c r="AE54" s="97"/>
-      <c r="AF54" s="97"/>
-      <c r="AG54" s="97"/>
-      <c r="AH54" s="97"/>
-      <c r="AI54" s="97"/>
-      <c r="AJ54" s="97"/>
+      <c r="B54" s="145"/>
+      <c r="C54" s="145"/>
+      <c r="D54" s="145"/>
+      <c r="E54" s="145"/>
+      <c r="F54" s="145"/>
+      <c r="G54" s="145"/>
+      <c r="H54" s="145"/>
+      <c r="I54" s="145"/>
+      <c r="J54" s="145"/>
+      <c r="K54" s="145"/>
+      <c r="L54" s="145"/>
+      <c r="M54" s="145"/>
+      <c r="N54" s="146"/>
+      <c r="O54" s="146"/>
+      <c r="P54" s="146"/>
+      <c r="Q54" s="146"/>
+      <c r="R54" s="146"/>
+      <c r="S54" s="146"/>
+      <c r="T54" s="146"/>
+      <c r="U54" s="146"/>
+      <c r="V54" s="146"/>
+      <c r="W54" s="146"/>
+      <c r="X54" s="146"/>
+      <c r="Y54" s="146"/>
+      <c r="Z54" s="146"/>
+      <c r="AA54" s="146"/>
+      <c r="AB54" s="146"/>
+      <c r="AC54" s="146"/>
+      <c r="AD54" s="146"/>
+      <c r="AE54" s="146"/>
+      <c r="AF54" s="146"/>
+      <c r="AG54" s="146"/>
+      <c r="AH54" s="146"/>
+      <c r="AI54" s="146"/>
+      <c r="AJ54" s="146"/>
     </row>
     <row r="55" spans="1:36" ht="18" customHeight="1">
-      <c r="A55" s="87"/>
-      <c r="B55" s="95"/>
-      <c r="C55" s="95"/>
-      <c r="D55" s="95"/>
-      <c r="E55" s="95"/>
-      <c r="F55" s="95"/>
-      <c r="G55" s="95"/>
-      <c r="H55" s="95"/>
-      <c r="I55" s="95"/>
-      <c r="J55" s="95"/>
-      <c r="K55" s="95"/>
-      <c r="L55" s="95"/>
-      <c r="N55" s="95"/>
-      <c r="O55" s="95"/>
-      <c r="P55" s="95"/>
-      <c r="Q55" s="95"/>
-      <c r="R55" s="95"/>
-      <c r="S55" s="95"/>
-      <c r="T55" s="95"/>
-      <c r="U55" s="95"/>
-      <c r="V55" s="95"/>
-      <c r="W55" s="95"/>
-      <c r="X55" s="95"/>
-      <c r="Y55" s="87"/>
-      <c r="Z55" s="87"/>
-      <c r="AA55" s="87"/>
-      <c r="AB55" s="99" t="s">
+      <c r="A55" s="138"/>
+      <c r="B55" s="66"/>
+      <c r="C55" s="66"/>
+      <c r="D55" s="66"/>
+      <c r="E55" s="66"/>
+      <c r="F55" s="66"/>
+      <c r="G55" s="66"/>
+      <c r="H55" s="66"/>
+      <c r="I55" s="66"/>
+      <c r="J55" s="66"/>
+      <c r="K55" s="66"/>
+      <c r="L55" s="66"/>
+      <c r="N55" s="66"/>
+      <c r="O55" s="66"/>
+      <c r="P55" s="66"/>
+      <c r="Q55" s="66"/>
+      <c r="R55" s="66"/>
+      <c r="S55" s="66"/>
+      <c r="T55" s="66"/>
+      <c r="U55" s="66"/>
+      <c r="V55" s="66"/>
+      <c r="W55" s="66"/>
+      <c r="X55" s="66"/>
+      <c r="Y55" s="138"/>
+      <c r="Z55" s="138"/>
+      <c r="AA55" s="138"/>
+      <c r="AB55" s="148" t="s">
         <v>93</v>
       </c>
-      <c r="AC55" s="100"/>
-      <c r="AD55" s="100"/>
-      <c r="AE55" s="100"/>
-      <c r="AF55" s="100"/>
-      <c r="AG55" s="100"/>
-      <c r="AH55" s="100"/>
-      <c r="AI55" s="100"/>
-      <c r="AJ55" s="100"/>
+      <c r="AC55" s="98"/>
+      <c r="AD55" s="98"/>
+      <c r="AE55" s="98"/>
+      <c r="AF55" s="98"/>
+      <c r="AG55" s="98"/>
+      <c r="AH55" s="98"/>
+      <c r="AI55" s="98"/>
+      <c r="AJ55" s="98"/>
     </row>
     <row r="56" spans="1:36" ht="18" customHeight="1">
-      <c r="A56" s="87"/>
-      <c r="B56" s="95"/>
-      <c r="C56" s="95"/>
-      <c r="D56" s="95"/>
-      <c r="E56" s="95"/>
-      <c r="F56" s="95"/>
-      <c r="G56" s="95"/>
-      <c r="H56" s="95"/>
-      <c r="I56" s="95"/>
-      <c r="J56" s="95"/>
-      <c r="K56" s="95"/>
-      <c r="L56" s="95"/>
-      <c r="N56" s="95"/>
-      <c r="O56" s="95"/>
-      <c r="P56" s="95"/>
-      <c r="Q56" s="95"/>
-      <c r="R56" s="95"/>
-      <c r="S56" s="95"/>
-      <c r="T56" s="95"/>
-      <c r="U56" s="95"/>
-      <c r="V56" s="95"/>
-      <c r="W56" s="95"/>
-      <c r="X56" s="95"/>
-      <c r="Y56" s="87"/>
-      <c r="Z56" s="87"/>
-      <c r="AA56" s="87"/>
-      <c r="AB56" s="89" t="s">
+      <c r="A56" s="138"/>
+      <c r="B56" s="66"/>
+      <c r="C56" s="66"/>
+      <c r="D56" s="66"/>
+      <c r="E56" s="66"/>
+      <c r="F56" s="66"/>
+      <c r="G56" s="66"/>
+      <c r="H56" s="66"/>
+      <c r="I56" s="66"/>
+      <c r="J56" s="66"/>
+      <c r="K56" s="66"/>
+      <c r="L56" s="66"/>
+      <c r="N56" s="66"/>
+      <c r="O56" s="66"/>
+      <c r="P56" s="66"/>
+      <c r="Q56" s="66"/>
+      <c r="R56" s="66"/>
+      <c r="S56" s="66"/>
+      <c r="T56" s="66"/>
+      <c r="U56" s="66"/>
+      <c r="V56" s="66"/>
+      <c r="W56" s="66"/>
+      <c r="X56" s="66"/>
+      <c r="Y56" s="138"/>
+      <c r="Z56" s="138"/>
+      <c r="AA56" s="138"/>
+      <c r="AB56" s="139" t="s">
         <v>47</v>
       </c>
-      <c r="AC56" s="89"/>
-      <c r="AD56" s="89"/>
-      <c r="AE56" s="89"/>
-      <c r="AF56" s="89"/>
-      <c r="AG56" s="89"/>
-      <c r="AH56" s="89"/>
-      <c r="AI56" s="89"/>
-      <c r="AJ56" s="89"/>
+      <c r="AC56" s="139"/>
+      <c r="AD56" s="139"/>
+      <c r="AE56" s="139"/>
+      <c r="AF56" s="139"/>
+      <c r="AG56" s="139"/>
+      <c r="AH56" s="139"/>
+      <c r="AI56" s="139"/>
+      <c r="AJ56" s="139"/>
     </row>
     <row r="57" spans="1:36" ht="18" customHeight="1">
-      <c r="A57" s="87"/>
-      <c r="B57" s="95"/>
-      <c r="C57" s="95"/>
-      <c r="D57" s="95"/>
-      <c r="E57" s="95"/>
-      <c r="F57" s="95"/>
-      <c r="G57" s="95"/>
-      <c r="H57" s="95"/>
-      <c r="I57" s="95"/>
-      <c r="J57" s="95"/>
-      <c r="K57" s="95"/>
-      <c r="L57" s="95"/>
-      <c r="N57" s="95"/>
-      <c r="O57" s="95"/>
-      <c r="P57" s="95"/>
-      <c r="Q57" s="95"/>
-      <c r="R57" s="95"/>
-      <c r="S57" s="95"/>
-      <c r="T57" s="95"/>
-      <c r="U57" s="95"/>
-      <c r="V57" s="95"/>
-      <c r="W57" s="95"/>
-      <c r="X57" s="95"/>
-      <c r="Y57" s="87"/>
-      <c r="Z57" s="87"/>
-      <c r="AA57" s="87"/>
-      <c r="AB57" s="87"/>
-      <c r="AC57" s="87"/>
-      <c r="AD57" s="87"/>
-      <c r="AE57" s="87"/>
-      <c r="AF57" s="87"/>
-      <c r="AG57" s="87"/>
-      <c r="AH57" s="87"/>
-      <c r="AI57" s="87"/>
-      <c r="AJ57" s="87"/>
+      <c r="A57" s="138"/>
+      <c r="B57" s="66"/>
+      <c r="C57" s="66"/>
+      <c r="D57" s="66"/>
+      <c r="E57" s="66"/>
+      <c r="F57" s="66"/>
+      <c r="G57" s="66"/>
+      <c r="H57" s="66"/>
+      <c r="I57" s="66"/>
+      <c r="J57" s="66"/>
+      <c r="K57" s="66"/>
+      <c r="L57" s="66"/>
+      <c r="N57" s="66"/>
+      <c r="O57" s="66"/>
+      <c r="P57" s="66"/>
+      <c r="Q57" s="66"/>
+      <c r="R57" s="66"/>
+      <c r="S57" s="66"/>
+      <c r="T57" s="66"/>
+      <c r="U57" s="66"/>
+      <c r="V57" s="66"/>
+      <c r="W57" s="66"/>
+      <c r="X57" s="66"/>
+      <c r="Y57" s="138"/>
+      <c r="Z57" s="138"/>
+      <c r="AA57" s="138"/>
+      <c r="AB57" s="138"/>
+      <c r="AC57" s="138"/>
+      <c r="AD57" s="138"/>
+      <c r="AE57" s="138"/>
+      <c r="AF57" s="138"/>
+      <c r="AG57" s="138"/>
+      <c r="AH57" s="138"/>
+      <c r="AI57" s="138"/>
+      <c r="AJ57" s="138"/>
     </row>
     <row r="58" spans="1:36" ht="18" customHeight="1">
       <c r="A58" s="51"/>
@@ -9370,72 +9372,72 @@
       <c r="V58" s="52"/>
       <c r="W58" s="52"/>
       <c r="X58" s="52"/>
-      <c r="Y58" s="87"/>
-      <c r="Z58" s="87"/>
-      <c r="AA58" s="87"/>
-      <c r="AB58" s="87"/>
-      <c r="AC58" s="87"/>
-      <c r="AD58" s="87"/>
-      <c r="AE58" s="87"/>
-      <c r="AF58" s="87"/>
-      <c r="AG58" s="87"/>
-      <c r="AH58" s="87"/>
-      <c r="AI58" s="87"/>
-      <c r="AJ58" s="87"/>
+      <c r="Y58" s="138"/>
+      <c r="Z58" s="138"/>
+      <c r="AA58" s="138"/>
+      <c r="AB58" s="138"/>
+      <c r="AC58" s="138"/>
+      <c r="AD58" s="138"/>
+      <c r="AE58" s="138"/>
+      <c r="AF58" s="138"/>
+      <c r="AG58" s="138"/>
+      <c r="AH58" s="138"/>
+      <c r="AI58" s="138"/>
+      <c r="AJ58" s="138"/>
     </row>
     <row r="59" spans="1:36" ht="18" customHeight="1">
-      <c r="A59" s="87"/>
-      <c r="B59" s="87"/>
-      <c r="C59" s="87"/>
-      <c r="D59" s="87"/>
-      <c r="E59" s="87"/>
-      <c r="F59" s="87"/>
-      <c r="G59" s="87"/>
-      <c r="H59" s="87"/>
-      <c r="I59" s="87"/>
-      <c r="J59" s="87"/>
-      <c r="K59" s="87"/>
-      <c r="L59" s="87"/>
-      <c r="M59" s="87"/>
-      <c r="N59" s="87"/>
-      <c r="O59" s="87"/>
-      <c r="P59" s="87"/>
-      <c r="Q59" s="87"/>
-      <c r="R59" s="87"/>
-      <c r="S59" s="87"/>
-      <c r="T59" s="87"/>
-      <c r="U59" s="87"/>
-      <c r="V59" s="87"/>
-      <c r="W59" s="87"/>
-      <c r="X59" s="87"/>
-      <c r="Y59" s="87"/>
-      <c r="Z59" s="87"/>
-      <c r="AA59" s="87"/>
-      <c r="AB59" s="88"/>
-      <c r="AC59" s="88"/>
-      <c r="AD59" s="88"/>
-      <c r="AE59" s="88"/>
-      <c r="AF59" s="88"/>
-      <c r="AG59" s="88"/>
-      <c r="AH59" s="88"/>
-      <c r="AI59" s="88"/>
-      <c r="AJ59" s="88"/>
+      <c r="A59" s="138"/>
+      <c r="B59" s="138"/>
+      <c r="C59" s="138"/>
+      <c r="D59" s="138"/>
+      <c r="E59" s="138"/>
+      <c r="F59" s="138"/>
+      <c r="G59" s="138"/>
+      <c r="H59" s="138"/>
+      <c r="I59" s="138"/>
+      <c r="J59" s="138"/>
+      <c r="K59" s="138"/>
+      <c r="L59" s="138"/>
+      <c r="M59" s="138"/>
+      <c r="N59" s="138"/>
+      <c r="O59" s="138"/>
+      <c r="P59" s="138"/>
+      <c r="Q59" s="138"/>
+      <c r="R59" s="138"/>
+      <c r="S59" s="138"/>
+      <c r="T59" s="138"/>
+      <c r="U59" s="138"/>
+      <c r="V59" s="138"/>
+      <c r="W59" s="138"/>
+      <c r="X59" s="138"/>
+      <c r="Y59" s="138"/>
+      <c r="Z59" s="138"/>
+      <c r="AA59" s="138"/>
+      <c r="AB59" s="81"/>
+      <c r="AC59" s="81"/>
+      <c r="AD59" s="81"/>
+      <c r="AE59" s="81"/>
+      <c r="AF59" s="81"/>
+      <c r="AG59" s="81"/>
+      <c r="AH59" s="81"/>
+      <c r="AI59" s="81"/>
+      <c r="AJ59" s="81"/>
     </row>
     <row r="60" spans="1:36" ht="18" customHeight="1">
-      <c r="Y60" s="87"/>
-      <c r="Z60" s="87"/>
-      <c r="AA60" s="87"/>
-      <c r="AB60" s="86" t="s">
+      <c r="Y60" s="138"/>
+      <c r="Z60" s="138"/>
+      <c r="AA60" s="138"/>
+      <c r="AB60" s="137" t="s">
         <v>92</v>
       </c>
-      <c r="AC60" s="86"/>
-      <c r="AD60" s="86"/>
-      <c r="AE60" s="86"/>
-      <c r="AF60" s="86"/>
-      <c r="AG60" s="86"/>
-      <c r="AH60" s="86"/>
-      <c r="AI60" s="86"/>
-      <c r="AJ60" s="86"/>
+      <c r="AC60" s="137"/>
+      <c r="AD60" s="137"/>
+      <c r="AE60" s="137"/>
+      <c r="AF60" s="137"/>
+      <c r="AG60" s="137"/>
+      <c r="AH60" s="137"/>
+      <c r="AI60" s="137"/>
+      <c r="AJ60" s="137"/>
     </row>
     <row r="61" spans="1:36" ht="16.5" customHeight="1"/>
     <row r="62" spans="1:36" ht="18" hidden="1" customHeight="1"/>
@@ -10037,15 +10039,104 @@
     <row r="658"/>
   </sheetData>
   <mergeCells count="131">
-    <mergeCell ref="AD3:AJ3"/>
-    <mergeCell ref="Y5:Z5"/>
-    <mergeCell ref="P5:X5"/>
-    <mergeCell ref="AH6:AI6"/>
-    <mergeCell ref="AC7:AE7"/>
-    <mergeCell ref="AI7:AJ7"/>
-    <mergeCell ref="C6:I6"/>
-    <mergeCell ref="S8:W8"/>
-    <mergeCell ref="X7:AB7"/>
+    <mergeCell ref="AF46:AI46"/>
+    <mergeCell ref="T50:AA50"/>
+    <mergeCell ref="AF45:AI45"/>
+    <mergeCell ref="AB48:AF48"/>
+    <mergeCell ref="X47:Z47"/>
+    <mergeCell ref="AG49:AI49"/>
+    <mergeCell ref="W45:Z45"/>
+    <mergeCell ref="T51:V51"/>
+    <mergeCell ref="A27:AJ29"/>
+    <mergeCell ref="A36:R36"/>
+    <mergeCell ref="B47:I47"/>
+    <mergeCell ref="S43:AA43"/>
+    <mergeCell ref="B51:I51"/>
+    <mergeCell ref="AF44:AI44"/>
+    <mergeCell ref="A30:O30"/>
+    <mergeCell ref="B44:I44"/>
+    <mergeCell ref="AB43:AJ43"/>
+    <mergeCell ref="J43:R43"/>
+    <mergeCell ref="W44:Y44"/>
+    <mergeCell ref="A31:AJ35"/>
+    <mergeCell ref="A37:AJ40"/>
+    <mergeCell ref="B45:I45"/>
+    <mergeCell ref="AB47:AE47"/>
+    <mergeCell ref="B46:I46"/>
+    <mergeCell ref="AB60:AJ60"/>
+    <mergeCell ref="AB57:AJ59"/>
+    <mergeCell ref="AB56:AJ56"/>
+    <mergeCell ref="S48:AA48"/>
+    <mergeCell ref="AG48:AI48"/>
+    <mergeCell ref="AC53:AE53"/>
+    <mergeCell ref="T52:V52"/>
+    <mergeCell ref="W53:Y53"/>
+    <mergeCell ref="B56:L56"/>
+    <mergeCell ref="N56:X56"/>
+    <mergeCell ref="Y55:AA60"/>
+    <mergeCell ref="A59:X59"/>
+    <mergeCell ref="A55:A57"/>
+    <mergeCell ref="N55:X55"/>
+    <mergeCell ref="A54:M54"/>
+    <mergeCell ref="N54:AJ54"/>
+    <mergeCell ref="D53:H53"/>
+    <mergeCell ref="B50:I50"/>
+    <mergeCell ref="B55:L55"/>
+    <mergeCell ref="K52:R52"/>
+    <mergeCell ref="T53:V53"/>
+    <mergeCell ref="AB55:AJ55"/>
+    <mergeCell ref="W51:Y51"/>
+    <mergeCell ref="AC52:AJ52"/>
+    <mergeCell ref="B48:I48"/>
+    <mergeCell ref="AF47:AI47"/>
+    <mergeCell ref="AB49:AF49"/>
+    <mergeCell ref="AF53:AH53"/>
+    <mergeCell ref="AB50:AJ50"/>
+    <mergeCell ref="AC51:AJ51"/>
+    <mergeCell ref="B49:I49"/>
+    <mergeCell ref="B52:C52"/>
+    <mergeCell ref="D52:H52"/>
+    <mergeCell ref="K50:R50"/>
+    <mergeCell ref="K51:R51"/>
+    <mergeCell ref="S47:W47"/>
+    <mergeCell ref="T49:AA49"/>
+    <mergeCell ref="K48:R48"/>
+    <mergeCell ref="K49:R49"/>
+    <mergeCell ref="W52:Y52"/>
+    <mergeCell ref="K47:R47"/>
+    <mergeCell ref="AB46:AE46"/>
+    <mergeCell ref="S44:V44"/>
+    <mergeCell ref="S45:V45"/>
+    <mergeCell ref="S46:W46"/>
+    <mergeCell ref="X46:Z46"/>
+    <mergeCell ref="K46:R46"/>
+    <mergeCell ref="K45:R45"/>
+    <mergeCell ref="AB44:AE44"/>
+    <mergeCell ref="J53:R53"/>
+    <mergeCell ref="AB45:AE45"/>
+    <mergeCell ref="K44:R44"/>
+    <mergeCell ref="A25:AJ25"/>
+    <mergeCell ref="A22:AJ23"/>
+    <mergeCell ref="A17:T20"/>
+    <mergeCell ref="C5:I5"/>
+    <mergeCell ref="AF19:AG19"/>
+    <mergeCell ref="A43:I43"/>
+    <mergeCell ref="AI19:AJ19"/>
+    <mergeCell ref="A14:H14"/>
+    <mergeCell ref="I14:AJ14"/>
+    <mergeCell ref="AI17:AJ17"/>
+    <mergeCell ref="AF17:AG17"/>
+    <mergeCell ref="A15:AJ15"/>
+    <mergeCell ref="AF18:AG18"/>
+    <mergeCell ref="AA5:AJ5"/>
+    <mergeCell ref="V7:W7"/>
+    <mergeCell ref="AI18:AJ18"/>
+    <mergeCell ref="U16:AD16"/>
+    <mergeCell ref="AF7:AG7"/>
+    <mergeCell ref="AE16:AJ16"/>
+    <mergeCell ref="A16:T16"/>
+    <mergeCell ref="A9:C9"/>
+    <mergeCell ref="X9:AJ9"/>
     <mergeCell ref="B57:L57"/>
     <mergeCell ref="N57:X57"/>
     <mergeCell ref="Q2:Z2"/>
@@ -10070,104 +10161,15 @@
     <mergeCell ref="AD6:AF6"/>
     <mergeCell ref="D9:R9"/>
     <mergeCell ref="K7:O7"/>
-    <mergeCell ref="A25:AJ25"/>
-    <mergeCell ref="A22:AJ23"/>
-    <mergeCell ref="A17:T20"/>
-    <mergeCell ref="C5:I5"/>
-    <mergeCell ref="AF19:AG19"/>
-    <mergeCell ref="A43:I43"/>
-    <mergeCell ref="AI19:AJ19"/>
-    <mergeCell ref="A14:H14"/>
-    <mergeCell ref="I14:AJ14"/>
-    <mergeCell ref="AI17:AJ17"/>
-    <mergeCell ref="AF17:AG17"/>
-    <mergeCell ref="A15:AJ15"/>
-    <mergeCell ref="AF18:AG18"/>
-    <mergeCell ref="AA5:AJ5"/>
-    <mergeCell ref="V7:W7"/>
-    <mergeCell ref="AI18:AJ18"/>
-    <mergeCell ref="U16:AD16"/>
-    <mergeCell ref="AF7:AG7"/>
-    <mergeCell ref="AE16:AJ16"/>
-    <mergeCell ref="A16:T16"/>
-    <mergeCell ref="A9:C9"/>
-    <mergeCell ref="X9:AJ9"/>
-    <mergeCell ref="AB46:AE46"/>
-    <mergeCell ref="S44:V44"/>
-    <mergeCell ref="S45:V45"/>
-    <mergeCell ref="S46:W46"/>
-    <mergeCell ref="X46:Z46"/>
-    <mergeCell ref="K46:R46"/>
-    <mergeCell ref="K45:R45"/>
-    <mergeCell ref="AB44:AE44"/>
-    <mergeCell ref="J53:R53"/>
-    <mergeCell ref="AB45:AE45"/>
-    <mergeCell ref="K44:R44"/>
-    <mergeCell ref="B48:I48"/>
-    <mergeCell ref="AF47:AI47"/>
-    <mergeCell ref="AB49:AF49"/>
-    <mergeCell ref="AF53:AH53"/>
-    <mergeCell ref="AB50:AJ50"/>
-    <mergeCell ref="AC51:AJ51"/>
-    <mergeCell ref="B49:I49"/>
-    <mergeCell ref="B52:C52"/>
-    <mergeCell ref="D52:H52"/>
-    <mergeCell ref="K50:R50"/>
-    <mergeCell ref="K51:R51"/>
-    <mergeCell ref="S47:W47"/>
-    <mergeCell ref="T49:AA49"/>
-    <mergeCell ref="K48:R48"/>
-    <mergeCell ref="K49:R49"/>
-    <mergeCell ref="W52:Y52"/>
-    <mergeCell ref="K47:R47"/>
-    <mergeCell ref="AB60:AJ60"/>
-    <mergeCell ref="AB57:AJ59"/>
-    <mergeCell ref="AB56:AJ56"/>
-    <mergeCell ref="S48:AA48"/>
-    <mergeCell ref="AG48:AI48"/>
-    <mergeCell ref="AC53:AE53"/>
-    <mergeCell ref="T52:V52"/>
-    <mergeCell ref="W53:Y53"/>
-    <mergeCell ref="B56:L56"/>
-    <mergeCell ref="N56:X56"/>
-    <mergeCell ref="Y55:AA60"/>
-    <mergeCell ref="A59:X59"/>
-    <mergeCell ref="A55:A57"/>
-    <mergeCell ref="N55:X55"/>
-    <mergeCell ref="A54:M54"/>
-    <mergeCell ref="N54:AJ54"/>
-    <mergeCell ref="D53:H53"/>
-    <mergeCell ref="B50:I50"/>
-    <mergeCell ref="B55:L55"/>
-    <mergeCell ref="K52:R52"/>
-    <mergeCell ref="T53:V53"/>
-    <mergeCell ref="AB55:AJ55"/>
-    <mergeCell ref="W51:Y51"/>
-    <mergeCell ref="AC52:AJ52"/>
-    <mergeCell ref="AF46:AI46"/>
-    <mergeCell ref="T50:AA50"/>
-    <mergeCell ref="AF45:AI45"/>
-    <mergeCell ref="AB48:AF48"/>
-    <mergeCell ref="X47:Z47"/>
-    <mergeCell ref="AG49:AI49"/>
-    <mergeCell ref="W45:Z45"/>
-    <mergeCell ref="T51:V51"/>
-    <mergeCell ref="A27:AJ29"/>
-    <mergeCell ref="A36:R36"/>
-    <mergeCell ref="B47:I47"/>
-    <mergeCell ref="S43:AA43"/>
-    <mergeCell ref="B51:I51"/>
-    <mergeCell ref="AF44:AI44"/>
-    <mergeCell ref="A30:O30"/>
-    <mergeCell ref="B44:I44"/>
-    <mergeCell ref="AB43:AJ43"/>
-    <mergeCell ref="J43:R43"/>
-    <mergeCell ref="W44:Y44"/>
-    <mergeCell ref="A31:AJ35"/>
-    <mergeCell ref="A37:AJ40"/>
-    <mergeCell ref="B45:I45"/>
-    <mergeCell ref="AB47:AE47"/>
-    <mergeCell ref="B46:I46"/>
+    <mergeCell ref="AD3:AJ3"/>
+    <mergeCell ref="Y5:Z5"/>
+    <mergeCell ref="P5:X5"/>
+    <mergeCell ref="AH6:AI6"/>
+    <mergeCell ref="AC7:AE7"/>
+    <mergeCell ref="AI7:AJ7"/>
+    <mergeCell ref="C6:I6"/>
+    <mergeCell ref="S8:W8"/>
+    <mergeCell ref="X7:AB7"/>
   </mergeCells>
   <phoneticPr fontId="0" type="noConversion"/>
   <printOptions horizontalCentered="1"/>
@@ -10191,8 +10193,8 @@
                     <xdr:rowOff>30480</xdr:rowOff>
                   </from>
                   <to>
-                    <xdr:col>1</xdr:col>
-                    <xdr:colOff>53340</xdr:colOff>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>327660</xdr:colOff>
                     <xdr:row>12</xdr:row>
                     <xdr:rowOff>15240</xdr:rowOff>
                   </to>
@@ -10213,8 +10215,8 @@
                     <xdr:rowOff>7620</xdr:rowOff>
                   </from>
                   <to>
-                    <xdr:col>1</xdr:col>
-                    <xdr:colOff>53340</xdr:colOff>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>327660</xdr:colOff>
                     <xdr:row>13</xdr:row>
                     <xdr:rowOff>15240</xdr:rowOff>
                   </to>
@@ -10235,8 +10237,8 @@
                     <xdr:rowOff>30480</xdr:rowOff>
                   </from>
                   <to>
-                    <xdr:col>5</xdr:col>
-                    <xdr:colOff>99060</xdr:colOff>
+                    <xdr:col>4</xdr:col>
+                    <xdr:colOff>327660</xdr:colOff>
                     <xdr:row>12</xdr:row>
                     <xdr:rowOff>15240</xdr:rowOff>
                   </to>
@@ -10257,8 +10259,8 @@
                     <xdr:rowOff>7620</xdr:rowOff>
                   </from>
                   <to>
-                    <xdr:col>5</xdr:col>
-                    <xdr:colOff>99060</xdr:colOff>
+                    <xdr:col>4</xdr:col>
+                    <xdr:colOff>327660</xdr:colOff>
                     <xdr:row>13</xdr:row>
                     <xdr:rowOff>15240</xdr:rowOff>
                   </to>
@@ -10279,8 +10281,8 @@
                     <xdr:rowOff>30480</xdr:rowOff>
                   </from>
                   <to>
-                    <xdr:col>9</xdr:col>
-                    <xdr:colOff>121920</xdr:colOff>
+                    <xdr:col>8</xdr:col>
+                    <xdr:colOff>396240</xdr:colOff>
                     <xdr:row>12</xdr:row>
                     <xdr:rowOff>15240</xdr:rowOff>
                   </to>
@@ -10301,8 +10303,8 @@
                     <xdr:rowOff>7620</xdr:rowOff>
                   </from>
                   <to>
-                    <xdr:col>9</xdr:col>
-                    <xdr:colOff>121920</xdr:colOff>
+                    <xdr:col>8</xdr:col>
+                    <xdr:colOff>396240</xdr:colOff>
                     <xdr:row>13</xdr:row>
                     <xdr:rowOff>15240</xdr:rowOff>
                   </to>
@@ -10323,8 +10325,8 @@
                     <xdr:rowOff>30480</xdr:rowOff>
                   </from>
                   <to>
-                    <xdr:col>14</xdr:col>
-                    <xdr:colOff>53340</xdr:colOff>
+                    <xdr:col>13</xdr:col>
+                    <xdr:colOff>327660</xdr:colOff>
                     <xdr:row>12</xdr:row>
                     <xdr:rowOff>15240</xdr:rowOff>
                   </to>
@@ -10345,8 +10347,8 @@
                     <xdr:rowOff>7620</xdr:rowOff>
                   </from>
                   <to>
-                    <xdr:col>14</xdr:col>
-                    <xdr:colOff>53340</xdr:colOff>
+                    <xdr:col>13</xdr:col>
+                    <xdr:colOff>327660</xdr:colOff>
                     <xdr:row>13</xdr:row>
                     <xdr:rowOff>15240</xdr:rowOff>
                   </to>
@@ -10741,8 +10743,8 @@
                     <xdr:rowOff>30480</xdr:rowOff>
                   </from>
                   <to>
-                    <xdr:col>1</xdr:col>
-                    <xdr:colOff>91440</xdr:colOff>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>365760</xdr:colOff>
                     <xdr:row>44</xdr:row>
                     <xdr:rowOff>15240</xdr:rowOff>
                   </to>
@@ -10763,8 +10765,8 @@
                     <xdr:rowOff>30480</xdr:rowOff>
                   </from>
                   <to>
-                    <xdr:col>1</xdr:col>
-                    <xdr:colOff>91440</xdr:colOff>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>365760</xdr:colOff>
                     <xdr:row>45</xdr:row>
                     <xdr:rowOff>15240</xdr:rowOff>
                   </to>
@@ -10785,8 +10787,8 @@
                     <xdr:rowOff>30480</xdr:rowOff>
                   </from>
                   <to>
-                    <xdr:col>1</xdr:col>
-                    <xdr:colOff>91440</xdr:colOff>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>365760</xdr:colOff>
                     <xdr:row>46</xdr:row>
                     <xdr:rowOff>15240</xdr:rowOff>
                   </to>
@@ -10807,8 +10809,8 @@
                     <xdr:rowOff>30480</xdr:rowOff>
                   </from>
                   <to>
-                    <xdr:col>1</xdr:col>
-                    <xdr:colOff>91440</xdr:colOff>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>365760</xdr:colOff>
                     <xdr:row>47</xdr:row>
                     <xdr:rowOff>15240</xdr:rowOff>
                   </to>
@@ -10829,8 +10831,8 @@
                     <xdr:rowOff>30480</xdr:rowOff>
                   </from>
                   <to>
-                    <xdr:col>1</xdr:col>
-                    <xdr:colOff>91440</xdr:colOff>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>365760</xdr:colOff>
                     <xdr:row>48</xdr:row>
                     <xdr:rowOff>15240</xdr:rowOff>
                   </to>
@@ -10851,8 +10853,8 @@
                     <xdr:rowOff>30480</xdr:rowOff>
                   </from>
                   <to>
-                    <xdr:col>1</xdr:col>
-                    <xdr:colOff>91440</xdr:colOff>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>365760</xdr:colOff>
                     <xdr:row>49</xdr:row>
                     <xdr:rowOff>15240</xdr:rowOff>
                   </to>
@@ -10873,8 +10875,8 @@
                     <xdr:rowOff>30480</xdr:rowOff>
                   </from>
                   <to>
-                    <xdr:col>1</xdr:col>
-                    <xdr:colOff>91440</xdr:colOff>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>365760</xdr:colOff>
                     <xdr:row>50</xdr:row>
                     <xdr:rowOff>15240</xdr:rowOff>
                   </to>
@@ -10895,8 +10897,8 @@
                     <xdr:rowOff>30480</xdr:rowOff>
                   </from>
                   <to>
-                    <xdr:col>1</xdr:col>
-                    <xdr:colOff>91440</xdr:colOff>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>365760</xdr:colOff>
                     <xdr:row>51</xdr:row>
                     <xdr:rowOff>15240</xdr:rowOff>
                   </to>
@@ -10917,8 +10919,8 @@
                     <xdr:rowOff>30480</xdr:rowOff>
                   </from>
                   <to>
-                    <xdr:col>1</xdr:col>
-                    <xdr:colOff>91440</xdr:colOff>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>365760</xdr:colOff>
                     <xdr:row>52</xdr:row>
                     <xdr:rowOff>15240</xdr:rowOff>
                   </to>

--- a/backend_api/templates/container_report_template.xlsx
+++ b/backend_api/templates/container_report_template.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Aaron Avila\Documents\ERP-SOM\backend_api\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{A2125F2B-319E-4DCB-8DE4-F8C7A6B063DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7B26B275-840D-436D-B3AC-DF2073B79FBE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{253FFB1B-D348-46B1-A532-0D44566D2FFD}"/>
+    <workbookView xWindow="-28920" yWindow="-1125" windowWidth="29040" windowHeight="15720" xr2:uid="{253FFB1B-D348-46B1-A532-0D44566D2FFD}"/>
   </bookViews>
   <sheets>
     <sheet name="DRY CARGO" sheetId="1" r:id="rId1"/>
@@ -1425,7 +1425,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="165">
+  <cellXfs count="167">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -1563,6 +1563,361 @@
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
+    <xf numFmtId="4" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="4" fontId="13" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="9" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="6" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="2" borderId="9" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="13" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="3" fontId="13" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="2" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="3" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="4" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="5" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="3" fontId="13" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="9" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="6" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="6" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="6" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="165" fontId="13" fillId="0" borderId="8" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="2" borderId="9" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="2" borderId="6" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="2" borderId="7" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="8" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
     <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
       <protection locked="0"/>
@@ -1571,9 +1926,6 @@
       <alignment horizontal="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="26" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
       <protection locked="0"/>
@@ -1582,360 +1934,14 @@
       <alignment horizontal="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="165" fontId="13" fillId="0" borderId="8" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="14" fontId="13" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left"/>
+    <xf numFmtId="14" fontId="13" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="8" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="8" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="9" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="6" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="2" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="3" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="4" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="5" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="3" fontId="13" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="13" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="9" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="6" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="6" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="6" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="2" borderId="9" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="2" borderId="6" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="2" borderId="7" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="4" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="4" fontId="13" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="4" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="2" borderId="9" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2237,7 +2243,7 @@
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
-          <xdr:colOff>327660</xdr:colOff>
+          <xdr:colOff>320040</xdr:colOff>
           <xdr:row>12</xdr:row>
           <xdr:rowOff>15240</xdr:rowOff>
         </xdr:to>
@@ -2304,7 +2310,7 @@
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
-          <xdr:colOff>327660</xdr:colOff>
+          <xdr:colOff>320040</xdr:colOff>
           <xdr:row>13</xdr:row>
           <xdr:rowOff>15240</xdr:rowOff>
         </xdr:to>
@@ -2371,7 +2377,7 @@
         </xdr:from>
         <xdr:to>
           <xdr:col>4</xdr:col>
-          <xdr:colOff>327660</xdr:colOff>
+          <xdr:colOff>320040</xdr:colOff>
           <xdr:row>12</xdr:row>
           <xdr:rowOff>15240</xdr:rowOff>
         </xdr:to>
@@ -2438,7 +2444,7 @@
         </xdr:from>
         <xdr:to>
           <xdr:col>4</xdr:col>
-          <xdr:colOff>327660</xdr:colOff>
+          <xdr:colOff>320040</xdr:colOff>
           <xdr:row>13</xdr:row>
           <xdr:rowOff>15240</xdr:rowOff>
         </xdr:to>
@@ -2639,7 +2645,7 @@
         </xdr:from>
         <xdr:to>
           <xdr:col>13</xdr:col>
-          <xdr:colOff>327660</xdr:colOff>
+          <xdr:colOff>320040</xdr:colOff>
           <xdr:row>12</xdr:row>
           <xdr:rowOff>15240</xdr:rowOff>
         </xdr:to>
@@ -2706,7 +2712,7 @@
         </xdr:from>
         <xdr:to>
           <xdr:col>13</xdr:col>
-          <xdr:colOff>327660</xdr:colOff>
+          <xdr:colOff>320040</xdr:colOff>
           <xdr:row>13</xdr:row>
           <xdr:rowOff>15240</xdr:rowOff>
         </xdr:to>
@@ -3912,7 +3918,7 @@
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
-          <xdr:colOff>365760</xdr:colOff>
+          <xdr:colOff>358140</xdr:colOff>
           <xdr:row>44</xdr:row>
           <xdr:rowOff>15240</xdr:rowOff>
         </xdr:to>
@@ -3979,7 +3985,7 @@
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
-          <xdr:colOff>365760</xdr:colOff>
+          <xdr:colOff>358140</xdr:colOff>
           <xdr:row>45</xdr:row>
           <xdr:rowOff>15240</xdr:rowOff>
         </xdr:to>
@@ -4046,7 +4052,7 @@
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
-          <xdr:colOff>365760</xdr:colOff>
+          <xdr:colOff>358140</xdr:colOff>
           <xdr:row>46</xdr:row>
           <xdr:rowOff>15240</xdr:rowOff>
         </xdr:to>
@@ -4113,7 +4119,7 @@
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
-          <xdr:colOff>365760</xdr:colOff>
+          <xdr:colOff>358140</xdr:colOff>
           <xdr:row>47</xdr:row>
           <xdr:rowOff>15240</xdr:rowOff>
         </xdr:to>
@@ -4180,7 +4186,7 @@
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
-          <xdr:colOff>365760</xdr:colOff>
+          <xdr:colOff>358140</xdr:colOff>
           <xdr:row>48</xdr:row>
           <xdr:rowOff>15240</xdr:rowOff>
         </xdr:to>
@@ -4247,7 +4253,7 @@
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
-          <xdr:colOff>365760</xdr:colOff>
+          <xdr:colOff>358140</xdr:colOff>
           <xdr:row>49</xdr:row>
           <xdr:rowOff>15240</xdr:rowOff>
         </xdr:to>
@@ -4314,7 +4320,7 @@
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
-          <xdr:colOff>365760</xdr:colOff>
+          <xdr:colOff>358140</xdr:colOff>
           <xdr:row>50</xdr:row>
           <xdr:rowOff>15240</xdr:rowOff>
         </xdr:to>
@@ -4381,7 +4387,7 @@
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
-          <xdr:colOff>365760</xdr:colOff>
+          <xdr:colOff>358140</xdr:colOff>
           <xdr:row>51</xdr:row>
           <xdr:rowOff>15240</xdr:rowOff>
         </xdr:to>
@@ -4448,7 +4454,7 @@
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
-          <xdr:colOff>365760</xdr:colOff>
+          <xdr:colOff>358140</xdr:colOff>
           <xdr:row>52</xdr:row>
           <xdr:rowOff>15240</xdr:rowOff>
         </xdr:to>
@@ -4515,7 +4521,7 @@
         </xdr:from>
         <xdr:to>
           <xdr:col>10</xdr:col>
-          <xdr:colOff>160020</xdr:colOff>
+          <xdr:colOff>163830</xdr:colOff>
           <xdr:row>44</xdr:row>
           <xdr:rowOff>15240</xdr:rowOff>
         </xdr:to>
@@ -4582,7 +4588,7 @@
         </xdr:from>
         <xdr:to>
           <xdr:col>10</xdr:col>
-          <xdr:colOff>160020</xdr:colOff>
+          <xdr:colOff>163830</xdr:colOff>
           <xdr:row>45</xdr:row>
           <xdr:rowOff>15240</xdr:rowOff>
         </xdr:to>
@@ -4649,7 +4655,7 @@
         </xdr:from>
         <xdr:to>
           <xdr:col>10</xdr:col>
-          <xdr:colOff>160020</xdr:colOff>
+          <xdr:colOff>163830</xdr:colOff>
           <xdr:row>46</xdr:row>
           <xdr:rowOff>15240</xdr:rowOff>
         </xdr:to>
@@ -4716,7 +4722,7 @@
         </xdr:from>
         <xdr:to>
           <xdr:col>10</xdr:col>
-          <xdr:colOff>160020</xdr:colOff>
+          <xdr:colOff>163830</xdr:colOff>
           <xdr:row>47</xdr:row>
           <xdr:rowOff>15240</xdr:rowOff>
         </xdr:to>
@@ -4783,7 +4789,7 @@
         </xdr:from>
         <xdr:to>
           <xdr:col>10</xdr:col>
-          <xdr:colOff>160020</xdr:colOff>
+          <xdr:colOff>163830</xdr:colOff>
           <xdr:row>48</xdr:row>
           <xdr:rowOff>15240</xdr:rowOff>
         </xdr:to>
@@ -4850,7 +4856,7 @@
         </xdr:from>
         <xdr:to>
           <xdr:col>10</xdr:col>
-          <xdr:colOff>160020</xdr:colOff>
+          <xdr:colOff>163830</xdr:colOff>
           <xdr:row>49</xdr:row>
           <xdr:rowOff>15240</xdr:rowOff>
         </xdr:to>
@@ -4917,7 +4923,7 @@
         </xdr:from>
         <xdr:to>
           <xdr:col>10</xdr:col>
-          <xdr:colOff>160020</xdr:colOff>
+          <xdr:colOff>163830</xdr:colOff>
           <xdr:row>50</xdr:row>
           <xdr:rowOff>15240</xdr:rowOff>
         </xdr:to>
@@ -4984,7 +4990,7 @@
         </xdr:from>
         <xdr:to>
           <xdr:col>10</xdr:col>
-          <xdr:colOff>160020</xdr:colOff>
+          <xdr:colOff>163830</xdr:colOff>
           <xdr:row>51</xdr:row>
           <xdr:rowOff>15240</xdr:rowOff>
         </xdr:to>
@@ -5051,7 +5057,7 @@
         </xdr:from>
         <xdr:to>
           <xdr:col>10</xdr:col>
-          <xdr:colOff>160020</xdr:colOff>
+          <xdr:colOff>163830</xdr:colOff>
           <xdr:row>52</xdr:row>
           <xdr:rowOff>15240</xdr:rowOff>
         </xdr:to>
@@ -7052,16 +7058,16 @@
       <c r="N2" s="31"/>
       <c r="O2" s="38"/>
       <c r="P2" s="38"/>
-      <c r="Q2" s="67"/>
-      <c r="R2" s="67"/>
-      <c r="S2" s="67"/>
-      <c r="T2" s="67"/>
-      <c r="U2" s="67"/>
-      <c r="V2" s="67"/>
-      <c r="W2" s="67"/>
-      <c r="X2" s="67"/>
-      <c r="Y2" s="67"/>
-      <c r="Z2" s="67"/>
+      <c r="Q2" s="148"/>
+      <c r="R2" s="148"/>
+      <c r="S2" s="148"/>
+      <c r="T2" s="148"/>
+      <c r="U2" s="148"/>
+      <c r="V2" s="148"/>
+      <c r="W2" s="148"/>
+      <c r="X2" s="148"/>
+      <c r="Y2" s="148"/>
+      <c r="Z2" s="148"/>
       <c r="AA2" s="38"/>
       <c r="AB2" s="38"/>
       <c r="AC2" s="38"/>
@@ -7087,28 +7093,28 @@
       <c r="K3" s="1"/>
       <c r="M3" s="31"/>
       <c r="N3" s="31"/>
-      <c r="Q3" s="68"/>
-      <c r="R3" s="68"/>
-      <c r="S3" s="68"/>
-      <c r="T3" s="68"/>
-      <c r="U3" s="68"/>
-      <c r="V3" s="68"/>
-      <c r="W3" s="68"/>
-      <c r="X3" s="68"/>
-      <c r="Y3" s="68"/>
-      <c r="Z3" s="68"/>
+      <c r="Q3" s="149"/>
+      <c r="R3" s="149"/>
+      <c r="S3" s="149"/>
+      <c r="T3" s="149"/>
+      <c r="U3" s="149"/>
+      <c r="V3" s="149"/>
+      <c r="W3" s="149"/>
+      <c r="X3" s="149"/>
+      <c r="Y3" s="149"/>
+      <c r="Z3" s="149"/>
       <c r="AA3" s="37"/>
       <c r="AB3" s="50" t="s">
         <v>95</v>
       </c>
       <c r="AC3" s="48"/>
-      <c r="AD3" s="57"/>
-      <c r="AE3" s="58"/>
-      <c r="AF3" s="58"/>
-      <c r="AG3" s="58"/>
-      <c r="AH3" s="58"/>
-      <c r="AI3" s="58"/>
-      <c r="AJ3" s="58"/>
+      <c r="AD3" s="160"/>
+      <c r="AE3" s="161"/>
+      <c r="AF3" s="161"/>
+      <c r="AG3" s="161"/>
+      <c r="AH3" s="161"/>
+      <c r="AI3" s="161"/>
+      <c r="AJ3" s="161"/>
     </row>
     <row r="4" spans="1:36" ht="18" customHeight="1">
       <c r="A4" s="30"/>
@@ -7139,304 +7145,304 @@
       </c>
     </row>
     <row r="5" spans="1:36" ht="18" customHeight="1">
-      <c r="A5" s="76" t="s">
+      <c r="A5" s="61" t="s">
         <v>85</v>
       </c>
-      <c r="B5" s="76"/>
-      <c r="C5" s="98"/>
-      <c r="D5" s="98"/>
-      <c r="E5" s="98"/>
-      <c r="F5" s="98"/>
-      <c r="G5" s="98"/>
-      <c r="H5" s="98"/>
-      <c r="I5" s="98"/>
+      <c r="B5" s="61"/>
+      <c r="C5" s="101"/>
+      <c r="D5" s="101"/>
+      <c r="E5" s="101"/>
+      <c r="F5" s="101"/>
+      <c r="G5" s="101"/>
+      <c r="H5" s="101"/>
+      <c r="I5" s="101"/>
       <c r="J5" s="35"/>
-      <c r="K5" s="59" t="s">
+      <c r="K5" s="153" t="s">
         <v>0</v>
       </c>
-      <c r="L5" s="59"/>
-      <c r="M5" s="59"/>
-      <c r="N5" s="59"/>
-      <c r="O5" s="59"/>
-      <c r="P5" s="60"/>
-      <c r="Q5" s="61"/>
-      <c r="R5" s="61"/>
-      <c r="S5" s="61"/>
-      <c r="T5" s="61"/>
-      <c r="U5" s="61"/>
-      <c r="V5" s="61"/>
-      <c r="W5" s="61"/>
-      <c r="X5" s="61"/>
-      <c r="Y5" s="59" t="s">
+      <c r="L5" s="153"/>
+      <c r="M5" s="153"/>
+      <c r="N5" s="153"/>
+      <c r="O5" s="153"/>
+      <c r="P5" s="162"/>
+      <c r="Q5" s="163"/>
+      <c r="R5" s="163"/>
+      <c r="S5" s="163"/>
+      <c r="T5" s="163"/>
+      <c r="U5" s="163"/>
+      <c r="V5" s="163"/>
+      <c r="W5" s="163"/>
+      <c r="X5" s="163"/>
+      <c r="Y5" s="153" t="s">
         <v>48</v>
       </c>
-      <c r="Z5" s="59"/>
-      <c r="AA5" s="98"/>
-      <c r="AB5" s="98"/>
-      <c r="AC5" s="98"/>
-      <c r="AD5" s="98"/>
-      <c r="AE5" s="98"/>
-      <c r="AF5" s="98"/>
-      <c r="AG5" s="98"/>
-      <c r="AH5" s="98"/>
-      <c r="AI5" s="98"/>
-      <c r="AJ5" s="98"/>
+      <c r="Z5" s="153"/>
+      <c r="AA5" s="101"/>
+      <c r="AB5" s="101"/>
+      <c r="AC5" s="101"/>
+      <c r="AD5" s="101"/>
+      <c r="AE5" s="101"/>
+      <c r="AF5" s="101"/>
+      <c r="AG5" s="101"/>
+      <c r="AH5" s="101"/>
+      <c r="AI5" s="101"/>
+      <c r="AJ5" s="101"/>
     </row>
     <row r="6" spans="1:36" ht="18" customHeight="1">
-      <c r="A6" s="76" t="s">
+      <c r="A6" s="61" t="s">
         <v>1</v>
       </c>
-      <c r="B6" s="76"/>
-      <c r="C6" s="64"/>
-      <c r="D6" s="64"/>
-      <c r="E6" s="64"/>
-      <c r="F6" s="64"/>
-      <c r="G6" s="64"/>
-      <c r="H6" s="64"/>
-      <c r="I6" s="64"/>
+      <c r="B6" s="61"/>
+      <c r="C6" s="159"/>
+      <c r="D6" s="159"/>
+      <c r="E6" s="159"/>
+      <c r="F6" s="159"/>
+      <c r="G6" s="159"/>
+      <c r="H6" s="159"/>
+      <c r="I6" s="159"/>
       <c r="J6" s="35"/>
-      <c r="K6" s="59" t="s">
+      <c r="K6" s="153" t="s">
         <v>2</v>
       </c>
-      <c r="L6" s="59"/>
-      <c r="M6" s="59"/>
-      <c r="N6" s="59"/>
-      <c r="O6" s="59"/>
-      <c r="P6" s="72"/>
-      <c r="Q6" s="73"/>
-      <c r="R6" s="73"/>
-      <c r="S6" s="73"/>
-      <c r="T6" s="73"/>
-      <c r="U6" s="73"/>
-      <c r="V6" s="73"/>
-      <c r="W6" s="73"/>
-      <c r="X6" s="73"/>
+      <c r="L6" s="153"/>
+      <c r="M6" s="153"/>
+      <c r="N6" s="153"/>
+      <c r="O6" s="153"/>
+      <c r="P6" s="154"/>
+      <c r="Q6" s="155"/>
+      <c r="R6" s="155"/>
+      <c r="S6" s="155"/>
+      <c r="T6" s="155"/>
+      <c r="U6" s="155"/>
+      <c r="V6" s="155"/>
+      <c r="W6" s="155"/>
+      <c r="X6" s="155"/>
       <c r="Y6" s="56" t="s">
         <v>88</v>
       </c>
       <c r="Z6" s="56"/>
       <c r="AA6" s="56"/>
       <c r="AB6" s="56"/>
-      <c r="AC6" s="56"/>
-      <c r="AD6" s="63"/>
-      <c r="AE6" s="63"/>
-      <c r="AF6" s="63"/>
+      <c r="AC6" s="166"/>
+      <c r="AD6" s="166"/>
+      <c r="AE6" s="165"/>
+      <c r="AF6" s="165"/>
       <c r="AG6" s="44"/>
-      <c r="AH6" s="62"/>
-      <c r="AI6" s="62"/>
+      <c r="AH6" s="136"/>
+      <c r="AI6" s="136"/>
       <c r="AJ6" s="44"/>
     </row>
     <row r="7" spans="1:36" ht="18" customHeight="1">
-      <c r="A7" s="76" t="s">
+      <c r="A7" s="61" t="s">
         <v>3</v>
       </c>
-      <c r="B7" s="76"/>
-      <c r="C7" s="64"/>
-      <c r="D7" s="64"/>
-      <c r="E7" s="64"/>
-      <c r="F7" s="64"/>
-      <c r="G7" s="64"/>
-      <c r="H7" s="64"/>
-      <c r="I7" s="64"/>
+      <c r="B7" s="61"/>
+      <c r="C7" s="159"/>
+      <c r="D7" s="159"/>
+      <c r="E7" s="159"/>
+      <c r="F7" s="159"/>
+      <c r="G7" s="159"/>
+      <c r="H7" s="159"/>
+      <c r="I7" s="159"/>
       <c r="J7" s="35"/>
-      <c r="K7" s="59" t="s">
+      <c r="K7" s="153" t="s">
         <v>89</v>
       </c>
-      <c r="L7" s="59"/>
-      <c r="M7" s="59"/>
-      <c r="N7" s="59"/>
-      <c r="O7" s="59"/>
-      <c r="P7" s="63"/>
-      <c r="Q7" s="63"/>
-      <c r="R7" s="63"/>
-      <c r="S7" s="62"/>
-      <c r="T7" s="62"/>
+      <c r="L7" s="153"/>
+      <c r="M7" s="153"/>
+      <c r="N7" s="153"/>
+      <c r="O7" s="153"/>
+      <c r="P7" s="79"/>
+      <c r="Q7" s="79"/>
+      <c r="R7" s="79"/>
+      <c r="S7" s="136"/>
+      <c r="T7" s="136"/>
       <c r="U7" s="39" t="s">
         <v>4</v>
       </c>
-      <c r="V7" s="62"/>
-      <c r="W7" s="62"/>
-      <c r="X7" s="59" t="s">
+      <c r="V7" s="136"/>
+      <c r="W7" s="136"/>
+      <c r="X7" s="153" t="s">
         <v>90</v>
       </c>
-      <c r="Y7" s="59"/>
-      <c r="Z7" s="59"/>
-      <c r="AA7" s="59"/>
-      <c r="AB7" s="59"/>
-      <c r="AC7" s="63"/>
-      <c r="AD7" s="63"/>
-      <c r="AE7" s="63"/>
-      <c r="AF7" s="62"/>
-      <c r="AG7" s="62"/>
+      <c r="Y7" s="153"/>
+      <c r="Z7" s="153"/>
+      <c r="AA7" s="153"/>
+      <c r="AB7" s="153"/>
+      <c r="AC7" s="79"/>
+      <c r="AD7" s="79"/>
+      <c r="AE7" s="79"/>
+      <c r="AF7" s="136"/>
+      <c r="AG7" s="136"/>
       <c r="AH7" s="39" t="s">
         <v>4</v>
       </c>
-      <c r="AI7" s="62"/>
-      <c r="AJ7" s="62"/>
+      <c r="AI7" s="136"/>
+      <c r="AJ7" s="136"/>
     </row>
     <row r="8" spans="1:36" ht="18" customHeight="1">
-      <c r="A8" s="80" t="s">
+      <c r="A8" s="86" t="s">
         <v>5</v>
       </c>
-      <c r="B8" s="80"/>
-      <c r="C8" s="80"/>
-      <c r="D8" s="66"/>
-      <c r="E8" s="66"/>
-      <c r="F8" s="66"/>
-      <c r="G8" s="66"/>
-      <c r="H8" s="66"/>
-      <c r="I8" s="66"/>
-      <c r="J8" s="66"/>
-      <c r="K8" s="66"/>
-      <c r="L8" s="66"/>
-      <c r="M8" s="66"/>
-      <c r="N8" s="66"/>
-      <c r="O8" s="66"/>
-      <c r="P8" s="66"/>
-      <c r="Q8" s="66"/>
-      <c r="R8" s="66"/>
-      <c r="S8" s="65" t="s">
+      <c r="B8" s="86"/>
+      <c r="C8" s="86"/>
+      <c r="D8" s="96"/>
+      <c r="E8" s="96"/>
+      <c r="F8" s="96"/>
+      <c r="G8" s="96"/>
+      <c r="H8" s="96"/>
+      <c r="I8" s="96"/>
+      <c r="J8" s="96"/>
+      <c r="K8" s="96"/>
+      <c r="L8" s="96"/>
+      <c r="M8" s="96"/>
+      <c r="N8" s="96"/>
+      <c r="O8" s="96"/>
+      <c r="P8" s="96"/>
+      <c r="Q8" s="96"/>
+      <c r="R8" s="96"/>
+      <c r="S8" s="164" t="s">
         <v>49</v>
       </c>
-      <c r="T8" s="65"/>
-      <c r="U8" s="59"/>
-      <c r="V8" s="65"/>
-      <c r="W8" s="65"/>
-      <c r="X8" s="66"/>
-      <c r="Y8" s="66"/>
-      <c r="Z8" s="66"/>
-      <c r="AA8" s="66"/>
-      <c r="AB8" s="66"/>
-      <c r="AC8" s="66"/>
-      <c r="AD8" s="66"/>
-      <c r="AE8" s="66"/>
-      <c r="AF8" s="66"/>
-      <c r="AG8" s="66"/>
-      <c r="AH8" s="66"/>
-      <c r="AI8" s="66"/>
-      <c r="AJ8" s="66"/>
+      <c r="T8" s="164"/>
+      <c r="U8" s="153"/>
+      <c r="V8" s="164"/>
+      <c r="W8" s="164"/>
+      <c r="X8" s="96"/>
+      <c r="Y8" s="96"/>
+      <c r="Z8" s="96"/>
+      <c r="AA8" s="96"/>
+      <c r="AB8" s="96"/>
+      <c r="AC8" s="96"/>
+      <c r="AD8" s="96"/>
+      <c r="AE8" s="96"/>
+      <c r="AF8" s="96"/>
+      <c r="AG8" s="96"/>
+      <c r="AH8" s="96"/>
+      <c r="AI8" s="96"/>
+      <c r="AJ8" s="96"/>
     </row>
     <row r="9" spans="1:36" ht="26.4" customHeight="1">
-      <c r="A9" s="76" t="s">
+      <c r="A9" s="61" t="s">
         <v>6</v>
       </c>
-      <c r="B9" s="76"/>
-      <c r="C9" s="76"/>
-      <c r="D9" s="82"/>
-      <c r="E9" s="82"/>
-      <c r="F9" s="82"/>
-      <c r="G9" s="82"/>
-      <c r="H9" s="82"/>
-      <c r="I9" s="82"/>
-      <c r="J9" s="82"/>
-      <c r="K9" s="82"/>
-      <c r="L9" s="82"/>
-      <c r="M9" s="82"/>
-      <c r="N9" s="82"/>
-      <c r="O9" s="82"/>
-      <c r="P9" s="82"/>
-      <c r="Q9" s="82"/>
-      <c r="R9" s="82"/>
-      <c r="S9" s="59" t="s">
+      <c r="B9" s="61"/>
+      <c r="C9" s="61"/>
+      <c r="D9" s="147"/>
+      <c r="E9" s="147"/>
+      <c r="F9" s="147"/>
+      <c r="G9" s="147"/>
+      <c r="H9" s="147"/>
+      <c r="I9" s="147"/>
+      <c r="J9" s="147"/>
+      <c r="K9" s="147"/>
+      <c r="L9" s="147"/>
+      <c r="M9" s="147"/>
+      <c r="N9" s="147"/>
+      <c r="O9" s="147"/>
+      <c r="P9" s="147"/>
+      <c r="Q9" s="147"/>
+      <c r="R9" s="147"/>
+      <c r="S9" s="153" t="s">
         <v>50</v>
       </c>
-      <c r="T9" s="59"/>
-      <c r="U9" s="59"/>
-      <c r="V9" s="59"/>
-      <c r="W9" s="59"/>
-      <c r="X9" s="121"/>
-      <c r="Y9" s="82"/>
-      <c r="Z9" s="82"/>
-      <c r="AA9" s="82"/>
-      <c r="AB9" s="82"/>
-      <c r="AC9" s="82"/>
-      <c r="AD9" s="82"/>
-      <c r="AE9" s="82"/>
-      <c r="AF9" s="82"/>
-      <c r="AG9" s="82"/>
-      <c r="AH9" s="82"/>
-      <c r="AI9" s="82"/>
-      <c r="AJ9" s="82"/>
+      <c r="T9" s="153"/>
+      <c r="U9" s="153"/>
+      <c r="V9" s="153"/>
+      <c r="W9" s="153"/>
+      <c r="X9" s="146"/>
+      <c r="Y9" s="147"/>
+      <c r="Z9" s="147"/>
+      <c r="AA9" s="147"/>
+      <c r="AB9" s="147"/>
+      <c r="AC9" s="147"/>
+      <c r="AD9" s="147"/>
+      <c r="AE9" s="147"/>
+      <c r="AF9" s="147"/>
+      <c r="AG9" s="147"/>
+      <c r="AH9" s="147"/>
+      <c r="AI9" s="147"/>
+      <c r="AJ9" s="147"/>
     </row>
     <row r="10" spans="1:36" ht="5.25" customHeight="1">
-      <c r="A10" s="81"/>
-      <c r="B10" s="81"/>
-      <c r="C10" s="81"/>
-      <c r="D10" s="81"/>
-      <c r="E10" s="81"/>
-      <c r="F10" s="81"/>
-      <c r="G10" s="81"/>
-      <c r="H10" s="81"/>
-      <c r="I10" s="81"/>
-      <c r="J10" s="81"/>
-      <c r="K10" s="81"/>
-      <c r="L10" s="81"/>
-      <c r="M10" s="81"/>
-      <c r="N10" s="81"/>
-      <c r="O10" s="81"/>
-      <c r="P10" s="81"/>
-      <c r="Q10" s="81"/>
-      <c r="R10" s="81"/>
-      <c r="S10" s="81"/>
-      <c r="T10" s="81"/>
-      <c r="U10" s="81"/>
-      <c r="V10" s="81"/>
-      <c r="W10" s="81"/>
-      <c r="X10" s="81"/>
-      <c r="Y10" s="81"/>
-      <c r="Z10" s="81"/>
-      <c r="AA10" s="81"/>
-      <c r="AB10" s="81"/>
-      <c r="AC10" s="81"/>
-      <c r="AD10" s="81"/>
-      <c r="AE10" s="81"/>
-      <c r="AF10" s="81"/>
-      <c r="AG10" s="81"/>
-      <c r="AH10" s="81"/>
-      <c r="AI10" s="81"/>
-      <c r="AJ10" s="81"/>
+      <c r="A10" s="89"/>
+      <c r="B10" s="89"/>
+      <c r="C10" s="89"/>
+      <c r="D10" s="89"/>
+      <c r="E10" s="89"/>
+      <c r="F10" s="89"/>
+      <c r="G10" s="89"/>
+      <c r="H10" s="89"/>
+      <c r="I10" s="89"/>
+      <c r="J10" s="89"/>
+      <c r="K10" s="89"/>
+      <c r="L10" s="89"/>
+      <c r="M10" s="89"/>
+      <c r="N10" s="89"/>
+      <c r="O10" s="89"/>
+      <c r="P10" s="89"/>
+      <c r="Q10" s="89"/>
+      <c r="R10" s="89"/>
+      <c r="S10" s="89"/>
+      <c r="T10" s="89"/>
+      <c r="U10" s="89"/>
+      <c r="V10" s="89"/>
+      <c r="W10" s="89"/>
+      <c r="X10" s="89"/>
+      <c r="Y10" s="89"/>
+      <c r="Z10" s="89"/>
+      <c r="AA10" s="89"/>
+      <c r="AB10" s="89"/>
+      <c r="AC10" s="89"/>
+      <c r="AD10" s="89"/>
+      <c r="AE10" s="89"/>
+      <c r="AF10" s="89"/>
+      <c r="AG10" s="89"/>
+      <c r="AH10" s="89"/>
+      <c r="AI10" s="89"/>
+      <c r="AJ10" s="89"/>
     </row>
     <row r="11" spans="1:36" ht="14.25" customHeight="1">
-      <c r="A11" s="69" t="s">
+      <c r="A11" s="150" t="s">
         <v>7</v>
       </c>
-      <c r="B11" s="70"/>
-      <c r="C11" s="70"/>
-      <c r="D11" s="70"/>
-      <c r="E11" s="70"/>
-      <c r="F11" s="70"/>
-      <c r="G11" s="70"/>
-      <c r="H11" s="70"/>
-      <c r="I11" s="70"/>
-      <c r="J11" s="70"/>
-      <c r="K11" s="70"/>
-      <c r="L11" s="70"/>
-      <c r="M11" s="70"/>
-      <c r="N11" s="70"/>
-      <c r="O11" s="70"/>
-      <c r="P11" s="71"/>
-      <c r="Q11" s="77" t="s">
+      <c r="B11" s="151"/>
+      <c r="C11" s="151"/>
+      <c r="D11" s="151"/>
+      <c r="E11" s="151"/>
+      <c r="F11" s="151"/>
+      <c r="G11" s="151"/>
+      <c r="H11" s="151"/>
+      <c r="I11" s="151"/>
+      <c r="J11" s="151"/>
+      <c r="K11" s="151"/>
+      <c r="L11" s="151"/>
+      <c r="M11" s="151"/>
+      <c r="N11" s="151"/>
+      <c r="O11" s="151"/>
+      <c r="P11" s="152"/>
+      <c r="Q11" s="156" t="s">
         <v>8</v>
       </c>
-      <c r="R11" s="78"/>
-      <c r="S11" s="78"/>
-      <c r="T11" s="78"/>
-      <c r="U11" s="78"/>
-      <c r="V11" s="78"/>
-      <c r="W11" s="78"/>
-      <c r="X11" s="78"/>
-      <c r="Y11" s="78"/>
-      <c r="Z11" s="78"/>
-      <c r="AA11" s="78"/>
-      <c r="AB11" s="78"/>
-      <c r="AC11" s="78"/>
-      <c r="AD11" s="78"/>
-      <c r="AE11" s="78"/>
-      <c r="AF11" s="78"/>
-      <c r="AG11" s="78"/>
-      <c r="AH11" s="78"/>
-      <c r="AI11" s="78"/>
-      <c r="AJ11" s="79"/>
+      <c r="R11" s="157"/>
+      <c r="S11" s="157"/>
+      <c r="T11" s="157"/>
+      <c r="U11" s="157"/>
+      <c r="V11" s="157"/>
+      <c r="W11" s="157"/>
+      <c r="X11" s="157"/>
+      <c r="Y11" s="157"/>
+      <c r="Z11" s="157"/>
+      <c r="AA11" s="157"/>
+      <c r="AB11" s="157"/>
+      <c r="AC11" s="157"/>
+      <c r="AD11" s="157"/>
+      <c r="AE11" s="157"/>
+      <c r="AF11" s="157"/>
+      <c r="AG11" s="157"/>
+      <c r="AH11" s="157"/>
+      <c r="AI11" s="157"/>
+      <c r="AJ11" s="158"/>
     </row>
     <row r="12" spans="1:36" ht="18" customHeight="1">
       <c r="A12" s="2"/>
@@ -7545,150 +7551,150 @@
       <c r="AJ13" s="23"/>
     </row>
     <row r="14" spans="1:36" ht="16.5" customHeight="1">
-      <c r="A14" s="104" t="s">
+      <c r="A14" s="128" t="s">
         <v>86</v>
       </c>
-      <c r="B14" s="105"/>
-      <c r="C14" s="105"/>
-      <c r="D14" s="105"/>
-      <c r="E14" s="105"/>
-      <c r="F14" s="105"/>
-      <c r="G14" s="105"/>
-      <c r="H14" s="105"/>
-      <c r="I14" s="106"/>
-      <c r="J14" s="107"/>
-      <c r="K14" s="107"/>
-      <c r="L14" s="107"/>
-      <c r="M14" s="107"/>
-      <c r="N14" s="107"/>
-      <c r="O14" s="107"/>
-      <c r="P14" s="107"/>
-      <c r="Q14" s="107"/>
-      <c r="R14" s="107"/>
-      <c r="S14" s="107"/>
-      <c r="T14" s="107"/>
-      <c r="U14" s="107"/>
-      <c r="V14" s="107"/>
-      <c r="W14" s="107"/>
-      <c r="X14" s="107"/>
-      <c r="Y14" s="107"/>
-      <c r="Z14" s="107"/>
-      <c r="AA14" s="107"/>
-      <c r="AB14" s="107"/>
-      <c r="AC14" s="107"/>
-      <c r="AD14" s="107"/>
-      <c r="AE14" s="107"/>
-      <c r="AF14" s="107"/>
-      <c r="AG14" s="107"/>
-      <c r="AH14" s="107"/>
-      <c r="AI14" s="107"/>
-      <c r="AJ14" s="108"/>
+      <c r="B14" s="129"/>
+      <c r="C14" s="129"/>
+      <c r="D14" s="129"/>
+      <c r="E14" s="129"/>
+      <c r="F14" s="129"/>
+      <c r="G14" s="129"/>
+      <c r="H14" s="129"/>
+      <c r="I14" s="130"/>
+      <c r="J14" s="131"/>
+      <c r="K14" s="131"/>
+      <c r="L14" s="131"/>
+      <c r="M14" s="131"/>
+      <c r="N14" s="131"/>
+      <c r="O14" s="131"/>
+      <c r="P14" s="131"/>
+      <c r="Q14" s="131"/>
+      <c r="R14" s="131"/>
+      <c r="S14" s="131"/>
+      <c r="T14" s="131"/>
+      <c r="U14" s="131"/>
+      <c r="V14" s="131"/>
+      <c r="W14" s="131"/>
+      <c r="X14" s="131"/>
+      <c r="Y14" s="131"/>
+      <c r="Z14" s="131"/>
+      <c r="AA14" s="131"/>
+      <c r="AB14" s="131"/>
+      <c r="AC14" s="131"/>
+      <c r="AD14" s="131"/>
+      <c r="AE14" s="131"/>
+      <c r="AF14" s="131"/>
+      <c r="AG14" s="131"/>
+      <c r="AH14" s="131"/>
+      <c r="AI14" s="131"/>
+      <c r="AJ14" s="132"/>
     </row>
     <row r="15" spans="1:36" ht="3" customHeight="1">
-      <c r="A15" s="109">
+      <c r="A15" s="133">
         <v>2</v>
       </c>
-      <c r="B15" s="110"/>
-      <c r="C15" s="110"/>
-      <c r="D15" s="110"/>
-      <c r="E15" s="110"/>
-      <c r="F15" s="110"/>
-      <c r="G15" s="110"/>
-      <c r="H15" s="110"/>
-      <c r="I15" s="110"/>
-      <c r="J15" s="110"/>
-      <c r="K15" s="110"/>
-      <c r="L15" s="110"/>
-      <c r="M15" s="110"/>
-      <c r="N15" s="110"/>
-      <c r="O15" s="110"/>
-      <c r="P15" s="110"/>
-      <c r="Q15" s="110"/>
-      <c r="R15" s="110"/>
-      <c r="S15" s="110"/>
-      <c r="T15" s="110"/>
-      <c r="U15" s="110"/>
-      <c r="V15" s="110"/>
-      <c r="W15" s="110"/>
-      <c r="X15" s="110"/>
-      <c r="Y15" s="110"/>
-      <c r="Z15" s="110"/>
-      <c r="AA15" s="110"/>
-      <c r="AB15" s="110"/>
-      <c r="AC15" s="110"/>
-      <c r="AD15" s="110"/>
-      <c r="AE15" s="110"/>
-      <c r="AF15" s="110"/>
-      <c r="AG15" s="110"/>
-      <c r="AH15" s="110"/>
-      <c r="AI15" s="110"/>
-      <c r="AJ15" s="111"/>
+      <c r="B15" s="134"/>
+      <c r="C15" s="134"/>
+      <c r="D15" s="134"/>
+      <c r="E15" s="134"/>
+      <c r="F15" s="134"/>
+      <c r="G15" s="134"/>
+      <c r="H15" s="134"/>
+      <c r="I15" s="134"/>
+      <c r="J15" s="134"/>
+      <c r="K15" s="134"/>
+      <c r="L15" s="134"/>
+      <c r="M15" s="134"/>
+      <c r="N15" s="134"/>
+      <c r="O15" s="134"/>
+      <c r="P15" s="134"/>
+      <c r="Q15" s="134"/>
+      <c r="R15" s="134"/>
+      <c r="S15" s="134"/>
+      <c r="T15" s="134"/>
+      <c r="U15" s="134"/>
+      <c r="V15" s="134"/>
+      <c r="W15" s="134"/>
+      <c r="X15" s="134"/>
+      <c r="Y15" s="134"/>
+      <c r="Z15" s="134"/>
+      <c r="AA15" s="134"/>
+      <c r="AB15" s="134"/>
+      <c r="AC15" s="134"/>
+      <c r="AD15" s="134"/>
+      <c r="AE15" s="134"/>
+      <c r="AF15" s="134"/>
+      <c r="AG15" s="134"/>
+      <c r="AH15" s="134"/>
+      <c r="AI15" s="134"/>
+      <c r="AJ15" s="135"/>
     </row>
     <row r="16" spans="1:36" ht="12.75" customHeight="1">
-      <c r="A16" s="118" t="s">
+      <c r="A16" s="143" t="s">
         <v>9</v>
       </c>
-      <c r="B16" s="119"/>
-      <c r="C16" s="119"/>
-      <c r="D16" s="119"/>
-      <c r="E16" s="119"/>
-      <c r="F16" s="119"/>
-      <c r="G16" s="119"/>
-      <c r="H16" s="119"/>
-      <c r="I16" s="119"/>
-      <c r="J16" s="119"/>
-      <c r="K16" s="119"/>
-      <c r="L16" s="119"/>
-      <c r="M16" s="119"/>
-      <c r="N16" s="119"/>
-      <c r="O16" s="119"/>
-      <c r="P16" s="119"/>
-      <c r="Q16" s="119"/>
-      <c r="R16" s="119"/>
-      <c r="S16" s="119"/>
-      <c r="T16" s="120"/>
-      <c r="U16" s="112" t="s">
+      <c r="B16" s="144"/>
+      <c r="C16" s="144"/>
+      <c r="D16" s="144"/>
+      <c r="E16" s="144"/>
+      <c r="F16" s="144"/>
+      <c r="G16" s="144"/>
+      <c r="H16" s="144"/>
+      <c r="I16" s="144"/>
+      <c r="J16" s="144"/>
+      <c r="K16" s="144"/>
+      <c r="L16" s="144"/>
+      <c r="M16" s="144"/>
+      <c r="N16" s="144"/>
+      <c r="O16" s="144"/>
+      <c r="P16" s="144"/>
+      <c r="Q16" s="144"/>
+      <c r="R16" s="144"/>
+      <c r="S16" s="144"/>
+      <c r="T16" s="145"/>
+      <c r="U16" s="137" t="s">
         <v>73</v>
       </c>
-      <c r="V16" s="113"/>
-      <c r="W16" s="113"/>
-      <c r="X16" s="113"/>
-      <c r="Y16" s="113"/>
-      <c r="Z16" s="113"/>
-      <c r="AA16" s="113"/>
-      <c r="AB16" s="113"/>
-      <c r="AC16" s="113"/>
-      <c r="AD16" s="114"/>
-      <c r="AE16" s="115" t="s">
+      <c r="V16" s="138"/>
+      <c r="W16" s="138"/>
+      <c r="X16" s="138"/>
+      <c r="Y16" s="138"/>
+      <c r="Z16" s="138"/>
+      <c r="AA16" s="138"/>
+      <c r="AB16" s="138"/>
+      <c r="AC16" s="138"/>
+      <c r="AD16" s="139"/>
+      <c r="AE16" s="140" t="s">
         <v>10</v>
       </c>
-      <c r="AF16" s="116"/>
-      <c r="AG16" s="116"/>
-      <c r="AH16" s="116"/>
-      <c r="AI16" s="116"/>
-      <c r="AJ16" s="117"/>
+      <c r="AF16" s="141"/>
+      <c r="AG16" s="141"/>
+      <c r="AH16" s="141"/>
+      <c r="AI16" s="141"/>
+      <c r="AJ16" s="142"/>
     </row>
     <row r="17" spans="1:36" ht="18" customHeight="1">
-      <c r="A17" s="92"/>
-      <c r="B17" s="93"/>
-      <c r="C17" s="93"/>
-      <c r="D17" s="93"/>
-      <c r="E17" s="93"/>
-      <c r="F17" s="93"/>
-      <c r="G17" s="93"/>
-      <c r="H17" s="93"/>
-      <c r="I17" s="93"/>
-      <c r="J17" s="93"/>
-      <c r="K17" s="93"/>
-      <c r="L17" s="93"/>
-      <c r="M17" s="93"/>
-      <c r="N17" s="93"/>
-      <c r="O17" s="93"/>
-      <c r="P17" s="93"/>
-      <c r="Q17" s="93"/>
-      <c r="R17" s="93"/>
-      <c r="S17" s="93"/>
-      <c r="T17" s="94"/>
+      <c r="A17" s="121"/>
+      <c r="B17" s="122"/>
+      <c r="C17" s="122"/>
+      <c r="D17" s="122"/>
+      <c r="E17" s="122"/>
+      <c r="F17" s="122"/>
+      <c r="G17" s="122"/>
+      <c r="H17" s="122"/>
+      <c r="I17" s="122"/>
+      <c r="J17" s="122"/>
+      <c r="K17" s="122"/>
+      <c r="L17" s="122"/>
+      <c r="M17" s="122"/>
+      <c r="N17" s="122"/>
+      <c r="O17" s="122"/>
+      <c r="P17" s="122"/>
+      <c r="Q17" s="122"/>
+      <c r="R17" s="122"/>
+      <c r="S17" s="122"/>
+      <c r="T17" s="123"/>
       <c r="U17" s="25"/>
       <c r="V17" s="17" t="s">
         <v>64</v>
@@ -7704,32 +7710,32 @@
       <c r="AE17" s="14" t="s">
         <v>11</v>
       </c>
-      <c r="AF17" s="99"/>
-      <c r="AG17" s="99"/>
-      <c r="AI17" s="99"/>
-      <c r="AJ17" s="103"/>
+      <c r="AF17" s="104"/>
+      <c r="AG17" s="104"/>
+      <c r="AI17" s="104"/>
+      <c r="AJ17" s="127"/>
     </row>
     <row r="18" spans="1:36" ht="18" customHeight="1">
-      <c r="A18" s="92"/>
-      <c r="B18" s="93"/>
-      <c r="C18" s="93"/>
-      <c r="D18" s="93"/>
-      <c r="E18" s="93"/>
-      <c r="F18" s="93"/>
-      <c r="G18" s="93"/>
-      <c r="H18" s="93"/>
-      <c r="I18" s="93"/>
-      <c r="J18" s="93"/>
-      <c r="K18" s="93"/>
-      <c r="L18" s="93"/>
-      <c r="M18" s="93"/>
-      <c r="N18" s="93"/>
-      <c r="O18" s="93"/>
-      <c r="P18" s="93"/>
-      <c r="Q18" s="93"/>
-      <c r="R18" s="93"/>
-      <c r="S18" s="93"/>
-      <c r="T18" s="94"/>
+      <c r="A18" s="121"/>
+      <c r="B18" s="122"/>
+      <c r="C18" s="122"/>
+      <c r="D18" s="122"/>
+      <c r="E18" s="122"/>
+      <c r="F18" s="122"/>
+      <c r="G18" s="122"/>
+      <c r="H18" s="122"/>
+      <c r="I18" s="122"/>
+      <c r="J18" s="122"/>
+      <c r="K18" s="122"/>
+      <c r="L18" s="122"/>
+      <c r="M18" s="122"/>
+      <c r="N18" s="122"/>
+      <c r="O18" s="122"/>
+      <c r="P18" s="122"/>
+      <c r="Q18" s="122"/>
+      <c r="R18" s="122"/>
+      <c r="S18" s="122"/>
+      <c r="T18" s="123"/>
       <c r="U18" s="26"/>
       <c r="V18" s="17" t="s">
         <v>65</v>
@@ -7745,32 +7751,32 @@
       <c r="AE18" s="14" t="s">
         <v>12</v>
       </c>
-      <c r="AF18" s="99"/>
-      <c r="AG18" s="99"/>
-      <c r="AI18" s="99"/>
-      <c r="AJ18" s="103"/>
+      <c r="AF18" s="104"/>
+      <c r="AG18" s="104"/>
+      <c r="AI18" s="104"/>
+      <c r="AJ18" s="127"/>
     </row>
     <row r="19" spans="1:36" ht="18" customHeight="1">
-      <c r="A19" s="92"/>
-      <c r="B19" s="93"/>
-      <c r="C19" s="93"/>
-      <c r="D19" s="93"/>
-      <c r="E19" s="93"/>
-      <c r="F19" s="93"/>
-      <c r="G19" s="93"/>
-      <c r="H19" s="93"/>
-      <c r="I19" s="93"/>
-      <c r="J19" s="93"/>
-      <c r="K19" s="93"/>
-      <c r="L19" s="93"/>
-      <c r="M19" s="93"/>
-      <c r="N19" s="93"/>
-      <c r="O19" s="93"/>
-      <c r="P19" s="93"/>
-      <c r="Q19" s="93"/>
-      <c r="R19" s="93"/>
-      <c r="S19" s="93"/>
-      <c r="T19" s="94"/>
+      <c r="A19" s="121"/>
+      <c r="B19" s="122"/>
+      <c r="C19" s="122"/>
+      <c r="D19" s="122"/>
+      <c r="E19" s="122"/>
+      <c r="F19" s="122"/>
+      <c r="G19" s="122"/>
+      <c r="H19" s="122"/>
+      <c r="I19" s="122"/>
+      <c r="J19" s="122"/>
+      <c r="K19" s="122"/>
+      <c r="L19" s="122"/>
+      <c r="M19" s="122"/>
+      <c r="N19" s="122"/>
+      <c r="O19" s="122"/>
+      <c r="P19" s="122"/>
+      <c r="Q19" s="122"/>
+      <c r="R19" s="122"/>
+      <c r="S19" s="122"/>
+      <c r="T19" s="123"/>
       <c r="U19" s="26"/>
       <c r="V19" s="17" t="s">
         <v>66</v>
@@ -7786,32 +7792,32 @@
       <c r="AE19" s="14" t="s">
         <v>13</v>
       </c>
-      <c r="AF19" s="99"/>
-      <c r="AG19" s="99"/>
-      <c r="AI19" s="99"/>
-      <c r="AJ19" s="103"/>
+      <c r="AF19" s="104"/>
+      <c r="AG19" s="104"/>
+      <c r="AI19" s="104"/>
+      <c r="AJ19" s="127"/>
     </row>
     <row r="20" spans="1:36" ht="3.75" customHeight="1">
-      <c r="A20" s="95"/>
-      <c r="B20" s="96"/>
-      <c r="C20" s="96"/>
-      <c r="D20" s="96"/>
-      <c r="E20" s="96"/>
-      <c r="F20" s="96"/>
-      <c r="G20" s="96"/>
-      <c r="H20" s="96"/>
-      <c r="I20" s="96"/>
-      <c r="J20" s="96"/>
-      <c r="K20" s="96"/>
-      <c r="L20" s="96"/>
-      <c r="M20" s="96"/>
-      <c r="N20" s="96"/>
-      <c r="O20" s="96"/>
-      <c r="P20" s="96"/>
-      <c r="Q20" s="96"/>
-      <c r="R20" s="96"/>
-      <c r="S20" s="96"/>
-      <c r="T20" s="97"/>
+      <c r="A20" s="124"/>
+      <c r="B20" s="125"/>
+      <c r="C20" s="125"/>
+      <c r="D20" s="125"/>
+      <c r="E20" s="125"/>
+      <c r="F20" s="125"/>
+      <c r="G20" s="125"/>
+      <c r="H20" s="125"/>
+      <c r="I20" s="125"/>
+      <c r="J20" s="125"/>
+      <c r="K20" s="125"/>
+      <c r="L20" s="125"/>
+      <c r="M20" s="125"/>
+      <c r="N20" s="125"/>
+      <c r="O20" s="125"/>
+      <c r="P20" s="125"/>
+      <c r="Q20" s="125"/>
+      <c r="R20" s="125"/>
+      <c r="S20" s="125"/>
+      <c r="T20" s="126"/>
       <c r="U20" s="27"/>
       <c r="V20" s="16"/>
       <c r="W20" s="7"/>
@@ -7870,80 +7876,80 @@
       <c r="AJ21" s="47"/>
     </row>
     <row r="22" spans="1:36" ht="16.5" customHeight="1">
-      <c r="A22" s="86"/>
-      <c r="B22" s="87"/>
-      <c r="C22" s="87"/>
-      <c r="D22" s="87"/>
-      <c r="E22" s="87"/>
-      <c r="F22" s="87"/>
-      <c r="G22" s="87"/>
-      <c r="H22" s="87"/>
-      <c r="I22" s="87"/>
-      <c r="J22" s="87"/>
-      <c r="K22" s="87"/>
-      <c r="L22" s="87"/>
-      <c r="M22" s="87"/>
-      <c r="N22" s="87"/>
-      <c r="O22" s="87"/>
-      <c r="P22" s="87"/>
-      <c r="Q22" s="87"/>
-      <c r="R22" s="87"/>
-      <c r="S22" s="87"/>
-      <c r="T22" s="87"/>
-      <c r="U22" s="87"/>
-      <c r="V22" s="87"/>
-      <c r="W22" s="87"/>
-      <c r="X22" s="87"/>
-      <c r="Y22" s="87"/>
-      <c r="Z22" s="87"/>
-      <c r="AA22" s="87"/>
-      <c r="AB22" s="87"/>
-      <c r="AC22" s="87"/>
-      <c r="AD22" s="87"/>
-      <c r="AE22" s="87"/>
-      <c r="AF22" s="87"/>
-      <c r="AG22" s="87"/>
-      <c r="AH22" s="87"/>
-      <c r="AI22" s="87"/>
-      <c r="AJ22" s="88"/>
+      <c r="A22" s="115"/>
+      <c r="B22" s="116"/>
+      <c r="C22" s="116"/>
+      <c r="D22" s="116"/>
+      <c r="E22" s="116"/>
+      <c r="F22" s="116"/>
+      <c r="G22" s="116"/>
+      <c r="H22" s="116"/>
+      <c r="I22" s="116"/>
+      <c r="J22" s="116"/>
+      <c r="K22" s="116"/>
+      <c r="L22" s="116"/>
+      <c r="M22" s="116"/>
+      <c r="N22" s="116"/>
+      <c r="O22" s="116"/>
+      <c r="P22" s="116"/>
+      <c r="Q22" s="116"/>
+      <c r="R22" s="116"/>
+      <c r="S22" s="116"/>
+      <c r="T22" s="116"/>
+      <c r="U22" s="116"/>
+      <c r="V22" s="116"/>
+      <c r="W22" s="116"/>
+      <c r="X22" s="116"/>
+      <c r="Y22" s="116"/>
+      <c r="Z22" s="116"/>
+      <c r="AA22" s="116"/>
+      <c r="AB22" s="116"/>
+      <c r="AC22" s="116"/>
+      <c r="AD22" s="116"/>
+      <c r="AE22" s="116"/>
+      <c r="AF22" s="116"/>
+      <c r="AG22" s="116"/>
+      <c r="AH22" s="116"/>
+      <c r="AI22" s="116"/>
+      <c r="AJ22" s="117"/>
     </row>
     <row r="23" spans="1:36" ht="16.5" customHeight="1">
-      <c r="A23" s="89"/>
-      <c r="B23" s="90"/>
-      <c r="C23" s="90"/>
-      <c r="D23" s="90"/>
-      <c r="E23" s="90"/>
-      <c r="F23" s="90"/>
-      <c r="G23" s="90"/>
-      <c r="H23" s="90"/>
-      <c r="I23" s="90"/>
-      <c r="J23" s="90"/>
-      <c r="K23" s="90"/>
-      <c r="L23" s="90"/>
-      <c r="M23" s="90"/>
-      <c r="N23" s="90"/>
-      <c r="O23" s="90"/>
-      <c r="P23" s="90"/>
-      <c r="Q23" s="90"/>
-      <c r="R23" s="90"/>
-      <c r="S23" s="90"/>
-      <c r="T23" s="90"/>
-      <c r="U23" s="90"/>
-      <c r="V23" s="90"/>
-      <c r="W23" s="90"/>
-      <c r="X23" s="90"/>
-      <c r="Y23" s="90"/>
-      <c r="Z23" s="90"/>
-      <c r="AA23" s="90"/>
-      <c r="AB23" s="90"/>
-      <c r="AC23" s="90"/>
-      <c r="AD23" s="90"/>
-      <c r="AE23" s="90"/>
-      <c r="AF23" s="90"/>
-      <c r="AG23" s="90"/>
-      <c r="AH23" s="90"/>
-      <c r="AI23" s="90"/>
-      <c r="AJ23" s="91"/>
+      <c r="A23" s="118"/>
+      <c r="B23" s="119"/>
+      <c r="C23" s="119"/>
+      <c r="D23" s="119"/>
+      <c r="E23" s="119"/>
+      <c r="F23" s="119"/>
+      <c r="G23" s="119"/>
+      <c r="H23" s="119"/>
+      <c r="I23" s="119"/>
+      <c r="J23" s="119"/>
+      <c r="K23" s="119"/>
+      <c r="L23" s="119"/>
+      <c r="M23" s="119"/>
+      <c r="N23" s="119"/>
+      <c r="O23" s="119"/>
+      <c r="P23" s="119"/>
+      <c r="Q23" s="119"/>
+      <c r="R23" s="119"/>
+      <c r="S23" s="119"/>
+      <c r="T23" s="119"/>
+      <c r="U23" s="119"/>
+      <c r="V23" s="119"/>
+      <c r="W23" s="119"/>
+      <c r="X23" s="119"/>
+      <c r="Y23" s="119"/>
+      <c r="Z23" s="119"/>
+      <c r="AA23" s="119"/>
+      <c r="AB23" s="119"/>
+      <c r="AC23" s="119"/>
+      <c r="AD23" s="119"/>
+      <c r="AE23" s="119"/>
+      <c r="AF23" s="119"/>
+      <c r="AG23" s="119"/>
+      <c r="AH23" s="119"/>
+      <c r="AI23" s="119"/>
+      <c r="AJ23" s="120"/>
     </row>
     <row r="24" spans="1:36" ht="12.75" customHeight="1">
       <c r="A24" s="46" t="s">
@@ -7986,42 +7992,42 @@
       <c r="AJ24" s="47"/>
     </row>
     <row r="25" spans="1:36" ht="18" customHeight="1">
-      <c r="A25" s="83"/>
-      <c r="B25" s="84"/>
-      <c r="C25" s="84"/>
-      <c r="D25" s="84"/>
-      <c r="E25" s="84"/>
-      <c r="F25" s="84"/>
-      <c r="G25" s="84"/>
-      <c r="H25" s="84"/>
-      <c r="I25" s="84"/>
-      <c r="J25" s="84"/>
-      <c r="K25" s="84"/>
-      <c r="L25" s="84"/>
-      <c r="M25" s="84"/>
-      <c r="N25" s="84"/>
-      <c r="O25" s="84"/>
-      <c r="P25" s="84"/>
-      <c r="Q25" s="84"/>
-      <c r="R25" s="84"/>
-      <c r="S25" s="84"/>
-      <c r="T25" s="84"/>
-      <c r="U25" s="84"/>
-      <c r="V25" s="84"/>
-      <c r="W25" s="84"/>
-      <c r="X25" s="84"/>
-      <c r="Y25" s="84"/>
-      <c r="Z25" s="84"/>
-      <c r="AA25" s="84"/>
-      <c r="AB25" s="84"/>
-      <c r="AC25" s="84"/>
-      <c r="AD25" s="84"/>
-      <c r="AE25" s="84"/>
-      <c r="AF25" s="84"/>
-      <c r="AG25" s="84"/>
-      <c r="AH25" s="84"/>
-      <c r="AI25" s="84"/>
-      <c r="AJ25" s="85"/>
+      <c r="A25" s="112"/>
+      <c r="B25" s="113"/>
+      <c r="C25" s="113"/>
+      <c r="D25" s="113"/>
+      <c r="E25" s="113"/>
+      <c r="F25" s="113"/>
+      <c r="G25" s="113"/>
+      <c r="H25" s="113"/>
+      <c r="I25" s="113"/>
+      <c r="J25" s="113"/>
+      <c r="K25" s="113"/>
+      <c r="L25" s="113"/>
+      <c r="M25" s="113"/>
+      <c r="N25" s="113"/>
+      <c r="O25" s="113"/>
+      <c r="P25" s="113"/>
+      <c r="Q25" s="113"/>
+      <c r="R25" s="113"/>
+      <c r="S25" s="113"/>
+      <c r="T25" s="113"/>
+      <c r="U25" s="113"/>
+      <c r="V25" s="113"/>
+      <c r="W25" s="113"/>
+      <c r="X25" s="113"/>
+      <c r="Y25" s="113"/>
+      <c r="Z25" s="113"/>
+      <c r="AA25" s="113"/>
+      <c r="AB25" s="113"/>
+      <c r="AC25" s="113"/>
+      <c r="AD25" s="113"/>
+      <c r="AE25" s="113"/>
+      <c r="AF25" s="113"/>
+      <c r="AG25" s="113"/>
+      <c r="AH25" s="113"/>
+      <c r="AI25" s="113"/>
+      <c r="AJ25" s="114"/>
     </row>
     <row r="26" spans="1:36" ht="12.75" customHeight="1">
       <c r="A26" s="46" t="s">
@@ -8064,137 +8070,137 @@
       <c r="AJ26" s="47"/>
     </row>
     <row r="27" spans="1:36" ht="15" customHeight="1">
-      <c r="A27" s="150"/>
-      <c r="B27" s="151"/>
-      <c r="C27" s="151"/>
-      <c r="D27" s="151"/>
-      <c r="E27" s="151"/>
-      <c r="F27" s="151"/>
-      <c r="G27" s="151"/>
-      <c r="H27" s="151"/>
-      <c r="I27" s="151"/>
-      <c r="J27" s="151"/>
-      <c r="K27" s="151"/>
-      <c r="L27" s="151"/>
-      <c r="M27" s="151"/>
-      <c r="N27" s="151"/>
-      <c r="O27" s="151"/>
-      <c r="P27" s="151"/>
-      <c r="Q27" s="151"/>
-      <c r="R27" s="151"/>
-      <c r="S27" s="151"/>
-      <c r="T27" s="151"/>
-      <c r="U27" s="151"/>
-      <c r="V27" s="151"/>
-      <c r="W27" s="151"/>
-      <c r="X27" s="151"/>
-      <c r="Y27" s="151"/>
-      <c r="Z27" s="151"/>
-      <c r="AA27" s="151"/>
-      <c r="AB27" s="151"/>
-      <c r="AC27" s="151"/>
-      <c r="AD27" s="151"/>
-      <c r="AE27" s="151"/>
-      <c r="AF27" s="151"/>
-      <c r="AG27" s="151"/>
-      <c r="AH27" s="151"/>
-      <c r="AI27" s="151"/>
-      <c r="AJ27" s="152"/>
+      <c r="A27" s="63"/>
+      <c r="B27" s="64"/>
+      <c r="C27" s="64"/>
+      <c r="D27" s="64"/>
+      <c r="E27" s="64"/>
+      <c r="F27" s="64"/>
+      <c r="G27" s="64"/>
+      <c r="H27" s="64"/>
+      <c r="I27" s="64"/>
+      <c r="J27" s="64"/>
+      <c r="K27" s="64"/>
+      <c r="L27" s="64"/>
+      <c r="M27" s="64"/>
+      <c r="N27" s="64"/>
+      <c r="O27" s="64"/>
+      <c r="P27" s="64"/>
+      <c r="Q27" s="64"/>
+      <c r="R27" s="64"/>
+      <c r="S27" s="64"/>
+      <c r="T27" s="64"/>
+      <c r="U27" s="64"/>
+      <c r="V27" s="64"/>
+      <c r="W27" s="64"/>
+      <c r="X27" s="64"/>
+      <c r="Y27" s="64"/>
+      <c r="Z27" s="64"/>
+      <c r="AA27" s="64"/>
+      <c r="AB27" s="64"/>
+      <c r="AC27" s="64"/>
+      <c r="AD27" s="64"/>
+      <c r="AE27" s="64"/>
+      <c r="AF27" s="64"/>
+      <c r="AG27" s="64"/>
+      <c r="AH27" s="64"/>
+      <c r="AI27" s="64"/>
+      <c r="AJ27" s="65"/>
     </row>
     <row r="28" spans="1:36" ht="15" customHeight="1">
-      <c r="A28" s="153"/>
-      <c r="B28" s="151"/>
-      <c r="C28" s="151"/>
-      <c r="D28" s="151"/>
-      <c r="E28" s="151"/>
-      <c r="F28" s="151"/>
-      <c r="G28" s="151"/>
-      <c r="H28" s="151"/>
-      <c r="I28" s="151"/>
-      <c r="J28" s="151"/>
-      <c r="K28" s="151"/>
-      <c r="L28" s="151"/>
-      <c r="M28" s="151"/>
-      <c r="N28" s="151"/>
-      <c r="O28" s="151"/>
-      <c r="P28" s="151"/>
-      <c r="Q28" s="151"/>
-      <c r="R28" s="151"/>
-      <c r="S28" s="151"/>
-      <c r="T28" s="151"/>
-      <c r="U28" s="151"/>
-      <c r="V28" s="151"/>
-      <c r="W28" s="151"/>
-      <c r="X28" s="151"/>
-      <c r="Y28" s="151"/>
-      <c r="Z28" s="151"/>
-      <c r="AA28" s="151"/>
-      <c r="AB28" s="151"/>
-      <c r="AC28" s="151"/>
-      <c r="AD28" s="151"/>
-      <c r="AE28" s="151"/>
-      <c r="AF28" s="151"/>
-      <c r="AG28" s="151"/>
-      <c r="AH28" s="151"/>
-      <c r="AI28" s="151"/>
-      <c r="AJ28" s="152"/>
+      <c r="A28" s="66"/>
+      <c r="B28" s="64"/>
+      <c r="C28" s="64"/>
+      <c r="D28" s="64"/>
+      <c r="E28" s="64"/>
+      <c r="F28" s="64"/>
+      <c r="G28" s="64"/>
+      <c r="H28" s="64"/>
+      <c r="I28" s="64"/>
+      <c r="J28" s="64"/>
+      <c r="K28" s="64"/>
+      <c r="L28" s="64"/>
+      <c r="M28" s="64"/>
+      <c r="N28" s="64"/>
+      <c r="O28" s="64"/>
+      <c r="P28" s="64"/>
+      <c r="Q28" s="64"/>
+      <c r="R28" s="64"/>
+      <c r="S28" s="64"/>
+      <c r="T28" s="64"/>
+      <c r="U28" s="64"/>
+      <c r="V28" s="64"/>
+      <c r="W28" s="64"/>
+      <c r="X28" s="64"/>
+      <c r="Y28" s="64"/>
+      <c r="Z28" s="64"/>
+      <c r="AA28" s="64"/>
+      <c r="AB28" s="64"/>
+      <c r="AC28" s="64"/>
+      <c r="AD28" s="64"/>
+      <c r="AE28" s="64"/>
+      <c r="AF28" s="64"/>
+      <c r="AG28" s="64"/>
+      <c r="AH28" s="64"/>
+      <c r="AI28" s="64"/>
+      <c r="AJ28" s="65"/>
     </row>
     <row r="29" spans="1:36" ht="100.8" customHeight="1">
-      <c r="A29" s="154"/>
-      <c r="B29" s="155"/>
-      <c r="C29" s="155"/>
-      <c r="D29" s="155"/>
-      <c r="E29" s="155"/>
-      <c r="F29" s="155"/>
-      <c r="G29" s="155"/>
-      <c r="H29" s="155"/>
-      <c r="I29" s="155"/>
-      <c r="J29" s="155"/>
-      <c r="K29" s="155"/>
-      <c r="L29" s="155"/>
-      <c r="M29" s="155"/>
-      <c r="N29" s="155"/>
-      <c r="O29" s="155"/>
-      <c r="P29" s="155"/>
-      <c r="Q29" s="155"/>
-      <c r="R29" s="155"/>
-      <c r="S29" s="155"/>
-      <c r="T29" s="155"/>
-      <c r="U29" s="155"/>
-      <c r="V29" s="155"/>
-      <c r="W29" s="155"/>
-      <c r="X29" s="155"/>
-      <c r="Y29" s="155"/>
-      <c r="Z29" s="155"/>
-      <c r="AA29" s="155"/>
-      <c r="AB29" s="155"/>
-      <c r="AC29" s="155"/>
-      <c r="AD29" s="155"/>
-      <c r="AE29" s="155"/>
-      <c r="AF29" s="155"/>
-      <c r="AG29" s="155"/>
-      <c r="AH29" s="155"/>
-      <c r="AI29" s="155"/>
-      <c r="AJ29" s="156"/>
+      <c r="A29" s="67"/>
+      <c r="B29" s="68"/>
+      <c r="C29" s="68"/>
+      <c r="D29" s="68"/>
+      <c r="E29" s="68"/>
+      <c r="F29" s="68"/>
+      <c r="G29" s="68"/>
+      <c r="H29" s="68"/>
+      <c r="I29" s="68"/>
+      <c r="J29" s="68"/>
+      <c r="K29" s="68"/>
+      <c r="L29" s="68"/>
+      <c r="M29" s="68"/>
+      <c r="N29" s="68"/>
+      <c r="O29" s="68"/>
+      <c r="P29" s="68"/>
+      <c r="Q29" s="68"/>
+      <c r="R29" s="68"/>
+      <c r="S29" s="68"/>
+      <c r="T29" s="68"/>
+      <c r="U29" s="68"/>
+      <c r="V29" s="68"/>
+      <c r="W29" s="68"/>
+      <c r="X29" s="68"/>
+      <c r="Y29" s="68"/>
+      <c r="Z29" s="68"/>
+      <c r="AA29" s="68"/>
+      <c r="AB29" s="68"/>
+      <c r="AC29" s="68"/>
+      <c r="AD29" s="68"/>
+      <c r="AE29" s="68"/>
+      <c r="AF29" s="68"/>
+      <c r="AG29" s="68"/>
+      <c r="AH29" s="68"/>
+      <c r="AI29" s="68"/>
+      <c r="AJ29" s="69"/>
     </row>
     <row r="30" spans="1:36" ht="12.75" customHeight="1">
-      <c r="A30" s="157" t="s">
+      <c r="A30" s="76" t="s">
         <v>17</v>
       </c>
-      <c r="B30" s="158"/>
-      <c r="C30" s="158"/>
-      <c r="D30" s="158"/>
-      <c r="E30" s="158"/>
-      <c r="F30" s="158"/>
-      <c r="G30" s="158"/>
-      <c r="H30" s="158"/>
-      <c r="I30" s="158"/>
-      <c r="J30" s="158"/>
-      <c r="K30" s="158"/>
-      <c r="L30" s="158"/>
-      <c r="M30" s="158"/>
-      <c r="N30" s="158"/>
-      <c r="O30" s="158"/>
+      <c r="B30" s="77"/>
+      <c r="C30" s="77"/>
+      <c r="D30" s="77"/>
+      <c r="E30" s="77"/>
+      <c r="F30" s="77"/>
+      <c r="G30" s="77"/>
+      <c r="H30" s="77"/>
+      <c r="I30" s="77"/>
+      <c r="J30" s="77"/>
+      <c r="K30" s="77"/>
+      <c r="L30" s="77"/>
+      <c r="M30" s="77"/>
+      <c r="N30" s="77"/>
+      <c r="O30" s="77"/>
       <c r="P30" s="41"/>
       <c r="Q30" s="41"/>
       <c r="R30" s="41"/>
@@ -8218,216 +8224,216 @@
       <c r="AJ30" s="42"/>
     </row>
     <row r="31" spans="1:36" ht="16.5" customHeight="1">
-      <c r="A31" s="150"/>
-      <c r="B31" s="160"/>
-      <c r="C31" s="160"/>
-      <c r="D31" s="160"/>
-      <c r="E31" s="160"/>
-      <c r="F31" s="160"/>
-      <c r="G31" s="160"/>
-      <c r="H31" s="160"/>
-      <c r="I31" s="160"/>
-      <c r="J31" s="160"/>
-      <c r="K31" s="160"/>
-      <c r="L31" s="160"/>
-      <c r="M31" s="160"/>
-      <c r="N31" s="160"/>
-      <c r="O31" s="160"/>
-      <c r="P31" s="160"/>
-      <c r="Q31" s="160"/>
-      <c r="R31" s="160"/>
-      <c r="S31" s="160"/>
-      <c r="T31" s="160"/>
-      <c r="U31" s="160"/>
-      <c r="V31" s="160"/>
-      <c r="W31" s="160"/>
-      <c r="X31" s="160"/>
-      <c r="Y31" s="160"/>
-      <c r="Z31" s="160"/>
-      <c r="AA31" s="160"/>
-      <c r="AB31" s="160"/>
-      <c r="AC31" s="160"/>
-      <c r="AD31" s="160"/>
-      <c r="AE31" s="160"/>
-      <c r="AF31" s="160"/>
-      <c r="AG31" s="160"/>
-      <c r="AH31" s="160"/>
-      <c r="AI31" s="160"/>
-      <c r="AJ31" s="161"/>
+      <c r="A31" s="63"/>
+      <c r="B31" s="80"/>
+      <c r="C31" s="80"/>
+      <c r="D31" s="80"/>
+      <c r="E31" s="80"/>
+      <c r="F31" s="80"/>
+      <c r="G31" s="80"/>
+      <c r="H31" s="80"/>
+      <c r="I31" s="80"/>
+      <c r="J31" s="80"/>
+      <c r="K31" s="80"/>
+      <c r="L31" s="80"/>
+      <c r="M31" s="80"/>
+      <c r="N31" s="80"/>
+      <c r="O31" s="80"/>
+      <c r="P31" s="80"/>
+      <c r="Q31" s="80"/>
+      <c r="R31" s="80"/>
+      <c r="S31" s="80"/>
+      <c r="T31" s="80"/>
+      <c r="U31" s="80"/>
+      <c r="V31" s="80"/>
+      <c r="W31" s="80"/>
+      <c r="X31" s="80"/>
+      <c r="Y31" s="80"/>
+      <c r="Z31" s="80"/>
+      <c r="AA31" s="80"/>
+      <c r="AB31" s="80"/>
+      <c r="AC31" s="80"/>
+      <c r="AD31" s="80"/>
+      <c r="AE31" s="80"/>
+      <c r="AF31" s="80"/>
+      <c r="AG31" s="80"/>
+      <c r="AH31" s="80"/>
+      <c r="AI31" s="80"/>
+      <c r="AJ31" s="81"/>
     </row>
     <row r="32" spans="1:36" ht="16.5" customHeight="1">
-      <c r="A32" s="150"/>
-      <c r="B32" s="160"/>
-      <c r="C32" s="160"/>
-      <c r="D32" s="160"/>
-      <c r="E32" s="160"/>
-      <c r="F32" s="160"/>
-      <c r="G32" s="160"/>
-      <c r="H32" s="160"/>
-      <c r="I32" s="160"/>
-      <c r="J32" s="160"/>
-      <c r="K32" s="160"/>
-      <c r="L32" s="160"/>
-      <c r="M32" s="160"/>
-      <c r="N32" s="160"/>
-      <c r="O32" s="160"/>
-      <c r="P32" s="160"/>
-      <c r="Q32" s="160"/>
-      <c r="R32" s="160"/>
-      <c r="S32" s="160"/>
-      <c r="T32" s="160"/>
-      <c r="U32" s="160"/>
-      <c r="V32" s="160"/>
-      <c r="W32" s="160"/>
-      <c r="X32" s="160"/>
-      <c r="Y32" s="160"/>
-      <c r="Z32" s="160"/>
-      <c r="AA32" s="160"/>
-      <c r="AB32" s="160"/>
-      <c r="AC32" s="160"/>
-      <c r="AD32" s="160"/>
-      <c r="AE32" s="160"/>
-      <c r="AF32" s="160"/>
-      <c r="AG32" s="160"/>
-      <c r="AH32" s="160"/>
-      <c r="AI32" s="160"/>
-      <c r="AJ32" s="161"/>
+      <c r="A32" s="63"/>
+      <c r="B32" s="80"/>
+      <c r="C32" s="80"/>
+      <c r="D32" s="80"/>
+      <c r="E32" s="80"/>
+      <c r="F32" s="80"/>
+      <c r="G32" s="80"/>
+      <c r="H32" s="80"/>
+      <c r="I32" s="80"/>
+      <c r="J32" s="80"/>
+      <c r="K32" s="80"/>
+      <c r="L32" s="80"/>
+      <c r="M32" s="80"/>
+      <c r="N32" s="80"/>
+      <c r="O32" s="80"/>
+      <c r="P32" s="80"/>
+      <c r="Q32" s="80"/>
+      <c r="R32" s="80"/>
+      <c r="S32" s="80"/>
+      <c r="T32" s="80"/>
+      <c r="U32" s="80"/>
+      <c r="V32" s="80"/>
+      <c r="W32" s="80"/>
+      <c r="X32" s="80"/>
+      <c r="Y32" s="80"/>
+      <c r="Z32" s="80"/>
+      <c r="AA32" s="80"/>
+      <c r="AB32" s="80"/>
+      <c r="AC32" s="80"/>
+      <c r="AD32" s="80"/>
+      <c r="AE32" s="80"/>
+      <c r="AF32" s="80"/>
+      <c r="AG32" s="80"/>
+      <c r="AH32" s="80"/>
+      <c r="AI32" s="80"/>
+      <c r="AJ32" s="81"/>
     </row>
     <row r="33" spans="1:36" ht="16.5" customHeight="1">
-      <c r="A33" s="150"/>
-      <c r="B33" s="160"/>
-      <c r="C33" s="160"/>
-      <c r="D33" s="160"/>
-      <c r="E33" s="160"/>
-      <c r="F33" s="160"/>
-      <c r="G33" s="160"/>
-      <c r="H33" s="160"/>
-      <c r="I33" s="160"/>
-      <c r="J33" s="160"/>
-      <c r="K33" s="160"/>
-      <c r="L33" s="160"/>
-      <c r="M33" s="160"/>
-      <c r="N33" s="160"/>
-      <c r="O33" s="160"/>
-      <c r="P33" s="160"/>
-      <c r="Q33" s="160"/>
-      <c r="R33" s="160"/>
-      <c r="S33" s="160"/>
-      <c r="T33" s="160"/>
-      <c r="U33" s="160"/>
-      <c r="V33" s="160"/>
-      <c r="W33" s="160"/>
-      <c r="X33" s="160"/>
-      <c r="Y33" s="160"/>
-      <c r="Z33" s="160"/>
-      <c r="AA33" s="160"/>
-      <c r="AB33" s="160"/>
-      <c r="AC33" s="160"/>
-      <c r="AD33" s="160"/>
-      <c r="AE33" s="160"/>
-      <c r="AF33" s="160"/>
-      <c r="AG33" s="160"/>
-      <c r="AH33" s="160"/>
-      <c r="AI33" s="160"/>
-      <c r="AJ33" s="161"/>
+      <c r="A33" s="63"/>
+      <c r="B33" s="80"/>
+      <c r="C33" s="80"/>
+      <c r="D33" s="80"/>
+      <c r="E33" s="80"/>
+      <c r="F33" s="80"/>
+      <c r="G33" s="80"/>
+      <c r="H33" s="80"/>
+      <c r="I33" s="80"/>
+      <c r="J33" s="80"/>
+      <c r="K33" s="80"/>
+      <c r="L33" s="80"/>
+      <c r="M33" s="80"/>
+      <c r="N33" s="80"/>
+      <c r="O33" s="80"/>
+      <c r="P33" s="80"/>
+      <c r="Q33" s="80"/>
+      <c r="R33" s="80"/>
+      <c r="S33" s="80"/>
+      <c r="T33" s="80"/>
+      <c r="U33" s="80"/>
+      <c r="V33" s="80"/>
+      <c r="W33" s="80"/>
+      <c r="X33" s="80"/>
+      <c r="Y33" s="80"/>
+      <c r="Z33" s="80"/>
+      <c r="AA33" s="80"/>
+      <c r="AB33" s="80"/>
+      <c r="AC33" s="80"/>
+      <c r="AD33" s="80"/>
+      <c r="AE33" s="80"/>
+      <c r="AF33" s="80"/>
+      <c r="AG33" s="80"/>
+      <c r="AH33" s="80"/>
+      <c r="AI33" s="80"/>
+      <c r="AJ33" s="81"/>
     </row>
     <row r="34" spans="1:36" ht="61.8" customHeight="1">
-      <c r="A34" s="150"/>
-      <c r="B34" s="160"/>
-      <c r="C34" s="160"/>
-      <c r="D34" s="160"/>
-      <c r="E34" s="160"/>
-      <c r="F34" s="160"/>
-      <c r="G34" s="160"/>
-      <c r="H34" s="160"/>
-      <c r="I34" s="160"/>
-      <c r="J34" s="160"/>
-      <c r="K34" s="160"/>
-      <c r="L34" s="160"/>
-      <c r="M34" s="160"/>
-      <c r="N34" s="160"/>
-      <c r="O34" s="160"/>
-      <c r="P34" s="160"/>
-      <c r="Q34" s="160"/>
-      <c r="R34" s="160"/>
-      <c r="S34" s="160"/>
-      <c r="T34" s="160"/>
-      <c r="U34" s="160"/>
-      <c r="V34" s="160"/>
-      <c r="W34" s="160"/>
-      <c r="X34" s="160"/>
-      <c r="Y34" s="160"/>
-      <c r="Z34" s="160"/>
-      <c r="AA34" s="160"/>
-      <c r="AB34" s="160"/>
-      <c r="AC34" s="160"/>
-      <c r="AD34" s="160"/>
-      <c r="AE34" s="160"/>
-      <c r="AF34" s="160"/>
-      <c r="AG34" s="160"/>
-      <c r="AH34" s="160"/>
-      <c r="AI34" s="160"/>
-      <c r="AJ34" s="161"/>
+      <c r="A34" s="63"/>
+      <c r="B34" s="80"/>
+      <c r="C34" s="80"/>
+      <c r="D34" s="80"/>
+      <c r="E34" s="80"/>
+      <c r="F34" s="80"/>
+      <c r="G34" s="80"/>
+      <c r="H34" s="80"/>
+      <c r="I34" s="80"/>
+      <c r="J34" s="80"/>
+      <c r="K34" s="80"/>
+      <c r="L34" s="80"/>
+      <c r="M34" s="80"/>
+      <c r="N34" s="80"/>
+      <c r="O34" s="80"/>
+      <c r="P34" s="80"/>
+      <c r="Q34" s="80"/>
+      <c r="R34" s="80"/>
+      <c r="S34" s="80"/>
+      <c r="T34" s="80"/>
+      <c r="U34" s="80"/>
+      <c r="V34" s="80"/>
+      <c r="W34" s="80"/>
+      <c r="X34" s="80"/>
+      <c r="Y34" s="80"/>
+      <c r="Z34" s="80"/>
+      <c r="AA34" s="80"/>
+      <c r="AB34" s="80"/>
+      <c r="AC34" s="80"/>
+      <c r="AD34" s="80"/>
+      <c r="AE34" s="80"/>
+      <c r="AF34" s="80"/>
+      <c r="AG34" s="80"/>
+      <c r="AH34" s="80"/>
+      <c r="AI34" s="80"/>
+      <c r="AJ34" s="81"/>
     </row>
     <row r="35" spans="1:36" ht="13.2" customHeight="1">
-      <c r="A35" s="162"/>
-      <c r="B35" s="163"/>
-      <c r="C35" s="163"/>
-      <c r="D35" s="163"/>
-      <c r="E35" s="163"/>
-      <c r="F35" s="163"/>
-      <c r="G35" s="163"/>
-      <c r="H35" s="163"/>
-      <c r="I35" s="163"/>
-      <c r="J35" s="163"/>
-      <c r="K35" s="163"/>
-      <c r="L35" s="163"/>
-      <c r="M35" s="163"/>
-      <c r="N35" s="163"/>
-      <c r="O35" s="163"/>
-      <c r="P35" s="163"/>
-      <c r="Q35" s="163"/>
-      <c r="R35" s="163"/>
-      <c r="S35" s="163"/>
-      <c r="T35" s="163"/>
-      <c r="U35" s="163"/>
-      <c r="V35" s="163"/>
-      <c r="W35" s="163"/>
-      <c r="X35" s="163"/>
-      <c r="Y35" s="163"/>
-      <c r="Z35" s="163"/>
-      <c r="AA35" s="163"/>
-      <c r="AB35" s="163"/>
-      <c r="AC35" s="163"/>
-      <c r="AD35" s="163"/>
-      <c r="AE35" s="163"/>
-      <c r="AF35" s="163"/>
-      <c r="AG35" s="163"/>
-      <c r="AH35" s="163"/>
-      <c r="AI35" s="163"/>
-      <c r="AJ35" s="164"/>
+      <c r="A35" s="82"/>
+      <c r="B35" s="83"/>
+      <c r="C35" s="83"/>
+      <c r="D35" s="83"/>
+      <c r="E35" s="83"/>
+      <c r="F35" s="83"/>
+      <c r="G35" s="83"/>
+      <c r="H35" s="83"/>
+      <c r="I35" s="83"/>
+      <c r="J35" s="83"/>
+      <c r="K35" s="83"/>
+      <c r="L35" s="83"/>
+      <c r="M35" s="83"/>
+      <c r="N35" s="83"/>
+      <c r="O35" s="83"/>
+      <c r="P35" s="83"/>
+      <c r="Q35" s="83"/>
+      <c r="R35" s="83"/>
+      <c r="S35" s="83"/>
+      <c r="T35" s="83"/>
+      <c r="U35" s="83"/>
+      <c r="V35" s="83"/>
+      <c r="W35" s="83"/>
+      <c r="X35" s="83"/>
+      <c r="Y35" s="83"/>
+      <c r="Z35" s="83"/>
+      <c r="AA35" s="83"/>
+      <c r="AB35" s="83"/>
+      <c r="AC35" s="83"/>
+      <c r="AD35" s="83"/>
+      <c r="AE35" s="83"/>
+      <c r="AF35" s="83"/>
+      <c r="AG35" s="83"/>
+      <c r="AH35" s="83"/>
+      <c r="AI35" s="83"/>
+      <c r="AJ35" s="84"/>
     </row>
     <row r="36" spans="1:36" ht="13.5" customHeight="1">
-      <c r="A36" s="74" t="s">
+      <c r="A36" s="70" t="s">
         <v>94</v>
       </c>
-      <c r="B36" s="75"/>
-      <c r="C36" s="75"/>
-      <c r="D36" s="75"/>
-      <c r="E36" s="75"/>
-      <c r="F36" s="75"/>
-      <c r="G36" s="75"/>
-      <c r="H36" s="75"/>
-      <c r="I36" s="75"/>
-      <c r="J36" s="75"/>
-      <c r="K36" s="75"/>
-      <c r="L36" s="75"/>
-      <c r="M36" s="75"/>
-      <c r="N36" s="75"/>
-      <c r="O36" s="75"/>
-      <c r="P36" s="75"/>
-      <c r="Q36" s="75"/>
-      <c r="R36" s="75"/>
+      <c r="B36" s="71"/>
+      <c r="C36" s="71"/>
+      <c r="D36" s="71"/>
+      <c r="E36" s="71"/>
+      <c r="F36" s="71"/>
+      <c r="G36" s="71"/>
+      <c r="H36" s="71"/>
+      <c r="I36" s="71"/>
+      <c r="J36" s="71"/>
+      <c r="K36" s="71"/>
+      <c r="L36" s="71"/>
+      <c r="M36" s="71"/>
+      <c r="N36" s="71"/>
+      <c r="O36" s="71"/>
+      <c r="P36" s="71"/>
+      <c r="Q36" s="71"/>
+      <c r="R36" s="71"/>
       <c r="S36" s="40"/>
       <c r="T36" s="40"/>
       <c r="U36" s="40"/>
@@ -8448,178 +8454,178 @@
       <c r="AJ36" s="43"/>
     </row>
     <row r="37" spans="1:36" ht="14.25" customHeight="1">
-      <c r="A37" s="150"/>
-      <c r="B37" s="160"/>
-      <c r="C37" s="160"/>
-      <c r="D37" s="160"/>
-      <c r="E37" s="160"/>
-      <c r="F37" s="160"/>
-      <c r="G37" s="160"/>
-      <c r="H37" s="160"/>
-      <c r="I37" s="160"/>
-      <c r="J37" s="160"/>
-      <c r="K37" s="160"/>
-      <c r="L37" s="160"/>
-      <c r="M37" s="160"/>
-      <c r="N37" s="160"/>
-      <c r="O37" s="160"/>
-      <c r="P37" s="160"/>
-      <c r="Q37" s="160"/>
-      <c r="R37" s="160"/>
-      <c r="S37" s="160"/>
-      <c r="T37" s="160"/>
-      <c r="U37" s="160"/>
-      <c r="V37" s="160"/>
-      <c r="W37" s="160"/>
-      <c r="X37" s="160"/>
-      <c r="Y37" s="160"/>
-      <c r="Z37" s="160"/>
-      <c r="AA37" s="160"/>
-      <c r="AB37" s="160"/>
-      <c r="AC37" s="160"/>
-      <c r="AD37" s="160"/>
-      <c r="AE37" s="160"/>
-      <c r="AF37" s="160"/>
-      <c r="AG37" s="160"/>
-      <c r="AH37" s="160"/>
-      <c r="AI37" s="160"/>
-      <c r="AJ37" s="161"/>
+      <c r="A37" s="63"/>
+      <c r="B37" s="80"/>
+      <c r="C37" s="80"/>
+      <c r="D37" s="80"/>
+      <c r="E37" s="80"/>
+      <c r="F37" s="80"/>
+      <c r="G37" s="80"/>
+      <c r="H37" s="80"/>
+      <c r="I37" s="80"/>
+      <c r="J37" s="80"/>
+      <c r="K37" s="80"/>
+      <c r="L37" s="80"/>
+      <c r="M37" s="80"/>
+      <c r="N37" s="80"/>
+      <c r="O37" s="80"/>
+      <c r="P37" s="80"/>
+      <c r="Q37" s="80"/>
+      <c r="R37" s="80"/>
+      <c r="S37" s="80"/>
+      <c r="T37" s="80"/>
+      <c r="U37" s="80"/>
+      <c r="V37" s="80"/>
+      <c r="W37" s="80"/>
+      <c r="X37" s="80"/>
+      <c r="Y37" s="80"/>
+      <c r="Z37" s="80"/>
+      <c r="AA37" s="80"/>
+      <c r="AB37" s="80"/>
+      <c r="AC37" s="80"/>
+      <c r="AD37" s="80"/>
+      <c r="AE37" s="80"/>
+      <c r="AF37" s="80"/>
+      <c r="AG37" s="80"/>
+      <c r="AH37" s="80"/>
+      <c r="AI37" s="80"/>
+      <c r="AJ37" s="81"/>
     </row>
     <row r="38" spans="1:36" ht="14.25" customHeight="1">
-      <c r="A38" s="150"/>
-      <c r="B38" s="160"/>
-      <c r="C38" s="160"/>
-      <c r="D38" s="160"/>
-      <c r="E38" s="160"/>
-      <c r="F38" s="160"/>
-      <c r="G38" s="160"/>
-      <c r="H38" s="160"/>
-      <c r="I38" s="160"/>
-      <c r="J38" s="160"/>
-      <c r="K38" s="160"/>
-      <c r="L38" s="160"/>
-      <c r="M38" s="160"/>
-      <c r="N38" s="160"/>
-      <c r="O38" s="160"/>
-      <c r="P38" s="160"/>
-      <c r="Q38" s="160"/>
-      <c r="R38" s="160"/>
-      <c r="S38" s="160"/>
-      <c r="T38" s="160"/>
-      <c r="U38" s="160"/>
-      <c r="V38" s="160"/>
-      <c r="W38" s="160"/>
-      <c r="X38" s="160"/>
-      <c r="Y38" s="160"/>
-      <c r="Z38" s="160"/>
-      <c r="AA38" s="160"/>
-      <c r="AB38" s="160"/>
-      <c r="AC38" s="160"/>
-      <c r="AD38" s="160"/>
-      <c r="AE38" s="160"/>
-      <c r="AF38" s="160"/>
-      <c r="AG38" s="160"/>
-      <c r="AH38" s="160"/>
-      <c r="AI38" s="160"/>
-      <c r="AJ38" s="161"/>
+      <c r="A38" s="63"/>
+      <c r="B38" s="80"/>
+      <c r="C38" s="80"/>
+      <c r="D38" s="80"/>
+      <c r="E38" s="80"/>
+      <c r="F38" s="80"/>
+      <c r="G38" s="80"/>
+      <c r="H38" s="80"/>
+      <c r="I38" s="80"/>
+      <c r="J38" s="80"/>
+      <c r="K38" s="80"/>
+      <c r="L38" s="80"/>
+      <c r="M38" s="80"/>
+      <c r="N38" s="80"/>
+      <c r="O38" s="80"/>
+      <c r="P38" s="80"/>
+      <c r="Q38" s="80"/>
+      <c r="R38" s="80"/>
+      <c r="S38" s="80"/>
+      <c r="T38" s="80"/>
+      <c r="U38" s="80"/>
+      <c r="V38" s="80"/>
+      <c r="W38" s="80"/>
+      <c r="X38" s="80"/>
+      <c r="Y38" s="80"/>
+      <c r="Z38" s="80"/>
+      <c r="AA38" s="80"/>
+      <c r="AB38" s="80"/>
+      <c r="AC38" s="80"/>
+      <c r="AD38" s="80"/>
+      <c r="AE38" s="80"/>
+      <c r="AF38" s="80"/>
+      <c r="AG38" s="80"/>
+      <c r="AH38" s="80"/>
+      <c r="AI38" s="80"/>
+      <c r="AJ38" s="81"/>
     </row>
     <row r="39" spans="1:36" ht="27.6" customHeight="1">
-      <c r="A39" s="150"/>
-      <c r="B39" s="160"/>
-      <c r="C39" s="160"/>
-      <c r="D39" s="160"/>
-      <c r="E39" s="160"/>
-      <c r="F39" s="160"/>
-      <c r="G39" s="160"/>
-      <c r="H39" s="160"/>
-      <c r="I39" s="160"/>
-      <c r="J39" s="160"/>
-      <c r="K39" s="160"/>
-      <c r="L39" s="160"/>
-      <c r="M39" s="160"/>
-      <c r="N39" s="160"/>
-      <c r="O39" s="160"/>
-      <c r="P39" s="160"/>
-      <c r="Q39" s="160"/>
-      <c r="R39" s="160"/>
-      <c r="S39" s="160"/>
-      <c r="T39" s="160"/>
-      <c r="U39" s="160"/>
-      <c r="V39" s="160"/>
-      <c r="W39" s="160"/>
-      <c r="X39" s="160"/>
-      <c r="Y39" s="160"/>
-      <c r="Z39" s="160"/>
-      <c r="AA39" s="160"/>
-      <c r="AB39" s="160"/>
-      <c r="AC39" s="160"/>
-      <c r="AD39" s="160"/>
-      <c r="AE39" s="160"/>
-      <c r="AF39" s="160"/>
-      <c r="AG39" s="160"/>
-      <c r="AH39" s="160"/>
-      <c r="AI39" s="160"/>
-      <c r="AJ39" s="161"/>
+      <c r="A39" s="63"/>
+      <c r="B39" s="80"/>
+      <c r="C39" s="80"/>
+      <c r="D39" s="80"/>
+      <c r="E39" s="80"/>
+      <c r="F39" s="80"/>
+      <c r="G39" s="80"/>
+      <c r="H39" s="80"/>
+      <c r="I39" s="80"/>
+      <c r="J39" s="80"/>
+      <c r="K39" s="80"/>
+      <c r="L39" s="80"/>
+      <c r="M39" s="80"/>
+      <c r="N39" s="80"/>
+      <c r="O39" s="80"/>
+      <c r="P39" s="80"/>
+      <c r="Q39" s="80"/>
+      <c r="R39" s="80"/>
+      <c r="S39" s="80"/>
+      <c r="T39" s="80"/>
+      <c r="U39" s="80"/>
+      <c r="V39" s="80"/>
+      <c r="W39" s="80"/>
+      <c r="X39" s="80"/>
+      <c r="Y39" s="80"/>
+      <c r="Z39" s="80"/>
+      <c r="AA39" s="80"/>
+      <c r="AB39" s="80"/>
+      <c r="AC39" s="80"/>
+      <c r="AD39" s="80"/>
+      <c r="AE39" s="80"/>
+      <c r="AF39" s="80"/>
+      <c r="AG39" s="80"/>
+      <c r="AH39" s="80"/>
+      <c r="AI39" s="80"/>
+      <c r="AJ39" s="81"/>
     </row>
     <row r="40" spans="1:36" ht="16.8" customHeight="1">
-      <c r="A40" s="150"/>
-      <c r="B40" s="160"/>
-      <c r="C40" s="160"/>
-      <c r="D40" s="160"/>
-      <c r="E40" s="160"/>
-      <c r="F40" s="160"/>
-      <c r="G40" s="160"/>
-      <c r="H40" s="160"/>
-      <c r="I40" s="160"/>
-      <c r="J40" s="160"/>
-      <c r="K40" s="160"/>
-      <c r="L40" s="160"/>
-      <c r="M40" s="160"/>
-      <c r="N40" s="160"/>
-      <c r="O40" s="160"/>
-      <c r="P40" s="160"/>
-      <c r="Q40" s="160"/>
-      <c r="R40" s="160"/>
-      <c r="S40" s="160"/>
-      <c r="T40" s="160"/>
-      <c r="U40" s="160"/>
-      <c r="V40" s="160"/>
-      <c r="W40" s="160"/>
-      <c r="X40" s="160"/>
-      <c r="Y40" s="160"/>
-      <c r="Z40" s="160"/>
-      <c r="AA40" s="160"/>
-      <c r="AB40" s="160"/>
-      <c r="AC40" s="160"/>
-      <c r="AD40" s="160"/>
-      <c r="AE40" s="160"/>
-      <c r="AF40" s="160"/>
-      <c r="AG40" s="160"/>
-      <c r="AH40" s="160"/>
-      <c r="AI40" s="160"/>
-      <c r="AJ40" s="161"/>
+      <c r="A40" s="63"/>
+      <c r="B40" s="80"/>
+      <c r="C40" s="80"/>
+      <c r="D40" s="80"/>
+      <c r="E40" s="80"/>
+      <c r="F40" s="80"/>
+      <c r="G40" s="80"/>
+      <c r="H40" s="80"/>
+      <c r="I40" s="80"/>
+      <c r="J40" s="80"/>
+      <c r="K40" s="80"/>
+      <c r="L40" s="80"/>
+      <c r="M40" s="80"/>
+      <c r="N40" s="80"/>
+      <c r="O40" s="80"/>
+      <c r="P40" s="80"/>
+      <c r="Q40" s="80"/>
+      <c r="R40" s="80"/>
+      <c r="S40" s="80"/>
+      <c r="T40" s="80"/>
+      <c r="U40" s="80"/>
+      <c r="V40" s="80"/>
+      <c r="W40" s="80"/>
+      <c r="X40" s="80"/>
+      <c r="Y40" s="80"/>
+      <c r="Z40" s="80"/>
+      <c r="AA40" s="80"/>
+      <c r="AB40" s="80"/>
+      <c r="AC40" s="80"/>
+      <c r="AD40" s="80"/>
+      <c r="AE40" s="80"/>
+      <c r="AF40" s="80"/>
+      <c r="AG40" s="80"/>
+      <c r="AH40" s="80"/>
+      <c r="AI40" s="80"/>
+      <c r="AJ40" s="81"/>
     </row>
     <row r="41" spans="1:36" ht="16.8" customHeight="1">
-      <c r="A41" s="74" t="s">
+      <c r="A41" s="70" t="s">
         <v>99</v>
       </c>
-      <c r="B41" s="75"/>
-      <c r="C41" s="75"/>
-      <c r="D41" s="75"/>
-      <c r="E41" s="75"/>
-      <c r="F41" s="75"/>
-      <c r="G41" s="75"/>
-      <c r="H41" s="75"/>
-      <c r="I41" s="75"/>
-      <c r="J41" s="75"/>
-      <c r="K41" s="75"/>
-      <c r="L41" s="75"/>
-      <c r="M41" s="75"/>
-      <c r="N41" s="75"/>
-      <c r="O41" s="75"/>
-      <c r="P41" s="75"/>
-      <c r="Q41" s="75"/>
-      <c r="R41" s="75"/>
+      <c r="B41" s="71"/>
+      <c r="C41" s="71"/>
+      <c r="D41" s="71"/>
+      <c r="E41" s="71"/>
+      <c r="F41" s="71"/>
+      <c r="G41" s="71"/>
+      <c r="H41" s="71"/>
+      <c r="I41" s="71"/>
+      <c r="J41" s="71"/>
+      <c r="K41" s="71"/>
+      <c r="L41" s="71"/>
+      <c r="M41" s="71"/>
+      <c r="N41" s="71"/>
+      <c r="O41" s="71"/>
+      <c r="P41" s="71"/>
+      <c r="Q41" s="71"/>
+      <c r="R41" s="71"/>
       <c r="S41" s="40"/>
       <c r="T41" s="40"/>
       <c r="U41" s="40"/>
@@ -8678,675 +8684,675 @@
       <c r="AJ42" s="55"/>
     </row>
     <row r="43" spans="1:36" ht="17.25" customHeight="1">
-      <c r="A43" s="100" t="s">
+      <c r="A43" s="72" t="s">
         <v>18</v>
       </c>
-      <c r="B43" s="101"/>
-      <c r="C43" s="101"/>
-      <c r="D43" s="101"/>
-      <c r="E43" s="101"/>
-      <c r="F43" s="101"/>
-      <c r="G43" s="101"/>
-      <c r="H43" s="101"/>
-      <c r="I43" s="102"/>
-      <c r="J43" s="100" t="s">
+      <c r="B43" s="73"/>
+      <c r="C43" s="73"/>
+      <c r="D43" s="73"/>
+      <c r="E43" s="73"/>
+      <c r="F43" s="73"/>
+      <c r="G43" s="73"/>
+      <c r="H43" s="73"/>
+      <c r="I43" s="74"/>
+      <c r="J43" s="72" t="s">
         <v>19</v>
       </c>
-      <c r="K43" s="101"/>
-      <c r="L43" s="101"/>
-      <c r="M43" s="101"/>
-      <c r="N43" s="101"/>
-      <c r="O43" s="101"/>
-      <c r="P43" s="101"/>
-      <c r="Q43" s="101"/>
-      <c r="R43" s="102"/>
-      <c r="S43" s="100" t="s">
+      <c r="K43" s="73"/>
+      <c r="L43" s="73"/>
+      <c r="M43" s="73"/>
+      <c r="N43" s="73"/>
+      <c r="O43" s="73"/>
+      <c r="P43" s="73"/>
+      <c r="Q43" s="73"/>
+      <c r="R43" s="74"/>
+      <c r="S43" s="72" t="s">
         <v>77</v>
       </c>
-      <c r="T43" s="101"/>
-      <c r="U43" s="101"/>
-      <c r="V43" s="101"/>
-      <c r="W43" s="101"/>
-      <c r="X43" s="101"/>
-      <c r="Y43" s="101"/>
-      <c r="Z43" s="101"/>
-      <c r="AA43" s="102"/>
-      <c r="AB43" s="159" t="s">
+      <c r="T43" s="73"/>
+      <c r="U43" s="73"/>
+      <c r="V43" s="73"/>
+      <c r="W43" s="73"/>
+      <c r="X43" s="73"/>
+      <c r="Y43" s="73"/>
+      <c r="Z43" s="73"/>
+      <c r="AA43" s="74"/>
+      <c r="AB43" s="78" t="s">
         <v>91</v>
       </c>
-      <c r="AC43" s="101"/>
-      <c r="AD43" s="101"/>
-      <c r="AE43" s="101"/>
-      <c r="AF43" s="101"/>
-      <c r="AG43" s="101"/>
-      <c r="AH43" s="101"/>
-      <c r="AI43" s="101"/>
-      <c r="AJ43" s="102"/>
+      <c r="AC43" s="73"/>
+      <c r="AD43" s="73"/>
+      <c r="AE43" s="73"/>
+      <c r="AF43" s="73"/>
+      <c r="AG43" s="73"/>
+      <c r="AH43" s="73"/>
+      <c r="AI43" s="73"/>
+      <c r="AJ43" s="74"/>
     </row>
     <row r="44" spans="1:36" ht="18" customHeight="1">
       <c r="A44" s="2"/>
-      <c r="B44" s="125" t="s">
+      <c r="B44" s="58" t="s">
         <v>21</v>
       </c>
-      <c r="C44" s="125"/>
-      <c r="D44" s="125"/>
-      <c r="E44" s="125"/>
-      <c r="F44" s="125"/>
-      <c r="G44" s="125"/>
-      <c r="H44" s="125"/>
-      <c r="I44" s="126"/>
+      <c r="C44" s="58"/>
+      <c r="D44" s="58"/>
+      <c r="E44" s="58"/>
+      <c r="F44" s="58"/>
+      <c r="G44" s="58"/>
+      <c r="H44" s="58"/>
+      <c r="I44" s="59"/>
       <c r="J44" s="10"/>
-      <c r="K44" s="125" t="s">
+      <c r="K44" s="58" t="s">
         <v>22</v>
       </c>
-      <c r="L44" s="125"/>
-      <c r="M44" s="125"/>
-      <c r="N44" s="125"/>
-      <c r="O44" s="125"/>
-      <c r="P44" s="125"/>
-      <c r="Q44" s="125"/>
-      <c r="R44" s="126"/>
-      <c r="S44" s="122" t="s">
+      <c r="L44" s="58"/>
+      <c r="M44" s="58"/>
+      <c r="N44" s="58"/>
+      <c r="O44" s="58"/>
+      <c r="P44" s="58"/>
+      <c r="Q44" s="58"/>
+      <c r="R44" s="59"/>
+      <c r="S44" s="85" t="s">
         <v>81</v>
       </c>
-      <c r="T44" s="80"/>
-      <c r="U44" s="80"/>
-      <c r="V44" s="80"/>
-      <c r="W44" s="63"/>
-      <c r="X44" s="63"/>
-      <c r="Y44" s="63"/>
+      <c r="T44" s="86"/>
+      <c r="U44" s="86"/>
+      <c r="V44" s="86"/>
+      <c r="W44" s="79"/>
+      <c r="X44" s="79"/>
+      <c r="Y44" s="79"/>
       <c r="Z44" s="49"/>
       <c r="AA44" s="4"/>
-      <c r="AB44" s="123" t="s">
+      <c r="AB44" s="60" t="s">
         <v>82</v>
       </c>
-      <c r="AC44" s="76"/>
-      <c r="AD44" s="76"/>
-      <c r="AE44" s="76"/>
-      <c r="AF44" s="130"/>
-      <c r="AG44" s="130"/>
-      <c r="AH44" s="130"/>
-      <c r="AI44" s="130"/>
+      <c r="AC44" s="61"/>
+      <c r="AD44" s="61"/>
+      <c r="AE44" s="61"/>
+      <c r="AF44" s="75"/>
+      <c r="AG44" s="75"/>
+      <c r="AH44" s="75"/>
+      <c r="AI44" s="75"/>
       <c r="AJ44" s="4"/>
     </row>
     <row r="45" spans="1:36" ht="18" customHeight="1">
       <c r="A45" s="2"/>
-      <c r="B45" s="125" t="s">
+      <c r="B45" s="58" t="s">
         <v>24</v>
       </c>
-      <c r="C45" s="125"/>
-      <c r="D45" s="125"/>
-      <c r="E45" s="125"/>
-      <c r="F45" s="125"/>
-      <c r="G45" s="125"/>
-      <c r="H45" s="125"/>
-      <c r="I45" s="126"/>
+      <c r="C45" s="58"/>
+      <c r="D45" s="58"/>
+      <c r="E45" s="58"/>
+      <c r="F45" s="58"/>
+      <c r="G45" s="58"/>
+      <c r="H45" s="58"/>
+      <c r="I45" s="59"/>
       <c r="J45" s="10"/>
-      <c r="K45" s="125" t="s">
+      <c r="K45" s="58" t="s">
         <v>25</v>
       </c>
-      <c r="L45" s="125"/>
-      <c r="M45" s="125"/>
-      <c r="N45" s="125"/>
-      <c r="O45" s="125"/>
-      <c r="P45" s="125"/>
-      <c r="Q45" s="125"/>
-      <c r="R45" s="126"/>
-      <c r="S45" s="122" t="s">
+      <c r="L45" s="58"/>
+      <c r="M45" s="58"/>
+      <c r="N45" s="58"/>
+      <c r="O45" s="58"/>
+      <c r="P45" s="58"/>
+      <c r="Q45" s="58"/>
+      <c r="R45" s="59"/>
+      <c r="S45" s="85" t="s">
         <v>80</v>
       </c>
-      <c r="T45" s="80"/>
-      <c r="U45" s="80"/>
-      <c r="V45" s="80"/>
-      <c r="W45" s="149"/>
-      <c r="X45" s="149"/>
-      <c r="Y45" s="149"/>
-      <c r="Z45" s="149"/>
+      <c r="T45" s="86"/>
+      <c r="U45" s="86"/>
+      <c r="V45" s="86"/>
+      <c r="W45" s="57"/>
+      <c r="X45" s="57"/>
+      <c r="Y45" s="57"/>
+      <c r="Z45" s="57"/>
       <c r="AA45" s="4"/>
-      <c r="AB45" s="122" t="s">
+      <c r="AB45" s="85" t="s">
         <v>81</v>
       </c>
-      <c r="AC45" s="80"/>
-      <c r="AD45" s="80"/>
-      <c r="AE45" s="80"/>
-      <c r="AF45" s="149"/>
-      <c r="AG45" s="149"/>
-      <c r="AH45" s="149"/>
-      <c r="AI45" s="149"/>
+      <c r="AC45" s="86"/>
+      <c r="AD45" s="86"/>
+      <c r="AE45" s="86"/>
+      <c r="AF45" s="57"/>
+      <c r="AG45" s="57"/>
+      <c r="AH45" s="57"/>
+      <c r="AI45" s="57"/>
       <c r="AJ45" s="4"/>
     </row>
     <row r="46" spans="1:36" ht="18" customHeight="1">
       <c r="A46" s="2"/>
-      <c r="B46" s="125" t="s">
+      <c r="B46" s="58" t="s">
         <v>27</v>
       </c>
-      <c r="C46" s="125"/>
-      <c r="D46" s="125"/>
-      <c r="E46" s="125"/>
-      <c r="F46" s="125"/>
-      <c r="G46" s="125"/>
-      <c r="H46" s="125"/>
-      <c r="I46" s="126"/>
+      <c r="C46" s="58"/>
+      <c r="D46" s="58"/>
+      <c r="E46" s="58"/>
+      <c r="F46" s="58"/>
+      <c r="G46" s="58"/>
+      <c r="H46" s="58"/>
+      <c r="I46" s="59"/>
       <c r="J46" s="10"/>
-      <c r="K46" s="125" t="s">
+      <c r="K46" s="58" t="s">
         <v>28</v>
       </c>
-      <c r="L46" s="125"/>
-      <c r="M46" s="125"/>
-      <c r="N46" s="125"/>
-      <c r="O46" s="125"/>
-      <c r="P46" s="125"/>
-      <c r="Q46" s="125"/>
-      <c r="R46" s="126"/>
-      <c r="S46" s="123" t="s">
+      <c r="L46" s="58"/>
+      <c r="M46" s="58"/>
+      <c r="N46" s="58"/>
+      <c r="O46" s="58"/>
+      <c r="P46" s="58"/>
+      <c r="Q46" s="58"/>
+      <c r="R46" s="59"/>
+      <c r="S46" s="60" t="s">
         <v>78</v>
       </c>
-      <c r="T46" s="76"/>
-      <c r="U46" s="76"/>
-      <c r="V46" s="76"/>
-      <c r="W46" s="76"/>
-      <c r="X46" s="124"/>
-      <c r="Y46" s="124"/>
-      <c r="Z46" s="124"/>
+      <c r="T46" s="61"/>
+      <c r="U46" s="61"/>
+      <c r="V46" s="61"/>
+      <c r="W46" s="61"/>
+      <c r="X46" s="94"/>
+      <c r="Y46" s="94"/>
+      <c r="Z46" s="94"/>
       <c r="AA46" s="12" t="s">
         <v>30</v>
       </c>
-      <c r="AB46" s="122" t="s">
+      <c r="AB46" s="85" t="s">
         <v>80</v>
       </c>
-      <c r="AC46" s="80"/>
-      <c r="AD46" s="80"/>
-      <c r="AE46" s="80"/>
-      <c r="AF46" s="149"/>
-      <c r="AG46" s="149"/>
-      <c r="AH46" s="149"/>
-      <c r="AI46" s="149"/>
+      <c r="AC46" s="86"/>
+      <c r="AD46" s="86"/>
+      <c r="AE46" s="86"/>
+      <c r="AF46" s="57"/>
+      <c r="AG46" s="57"/>
+      <c r="AH46" s="57"/>
+      <c r="AI46" s="57"/>
       <c r="AJ46" s="4"/>
     </row>
     <row r="47" spans="1:36" ht="18" customHeight="1">
       <c r="A47" s="2"/>
-      <c r="B47" s="125" t="s">
+      <c r="B47" s="58" t="s">
         <v>87</v>
       </c>
-      <c r="C47" s="125"/>
-      <c r="D47" s="125"/>
-      <c r="E47" s="125"/>
-      <c r="F47" s="125"/>
-      <c r="G47" s="125"/>
-      <c r="H47" s="125"/>
-      <c r="I47" s="126"/>
+      <c r="C47" s="58"/>
+      <c r="D47" s="58"/>
+      <c r="E47" s="58"/>
+      <c r="F47" s="58"/>
+      <c r="G47" s="58"/>
+      <c r="H47" s="58"/>
+      <c r="I47" s="59"/>
       <c r="J47" s="10"/>
-      <c r="K47" s="125" t="s">
+      <c r="K47" s="58" t="s">
         <v>31</v>
       </c>
-      <c r="L47" s="125"/>
-      <c r="M47" s="125"/>
-      <c r="N47" s="125"/>
-      <c r="O47" s="125"/>
-      <c r="P47" s="125"/>
-      <c r="Q47" s="125"/>
-      <c r="R47" s="126"/>
-      <c r="S47" s="127" t="s">
+      <c r="L47" s="58"/>
+      <c r="M47" s="58"/>
+      <c r="N47" s="58"/>
+      <c r="O47" s="58"/>
+      <c r="P47" s="58"/>
+      <c r="Q47" s="58"/>
+      <c r="R47" s="59"/>
+      <c r="S47" s="102" t="s">
         <v>79</v>
       </c>
-      <c r="T47" s="128"/>
-      <c r="U47" s="128"/>
-      <c r="V47" s="128"/>
-      <c r="W47" s="128"/>
-      <c r="X47" s="144"/>
-      <c r="Y47" s="144"/>
-      <c r="Z47" s="144"/>
+      <c r="T47" s="103"/>
+      <c r="U47" s="103"/>
+      <c r="V47" s="103"/>
+      <c r="W47" s="103"/>
+      <c r="X47" s="62"/>
+      <c r="Y47" s="62"/>
+      <c r="Z47" s="62"/>
       <c r="AA47" s="33" t="s">
         <v>30</v>
       </c>
-      <c r="AB47" s="122" t="s">
+      <c r="AB47" s="85" t="s">
         <v>83</v>
       </c>
-      <c r="AC47" s="80"/>
-      <c r="AD47" s="80"/>
-      <c r="AE47" s="80"/>
-      <c r="AF47" s="130"/>
-      <c r="AG47" s="130"/>
-      <c r="AH47" s="130"/>
-      <c r="AI47" s="130"/>
+      <c r="AC47" s="86"/>
+      <c r="AD47" s="86"/>
+      <c r="AE47" s="86"/>
+      <c r="AF47" s="75"/>
+      <c r="AG47" s="75"/>
+      <c r="AH47" s="75"/>
+      <c r="AI47" s="75"/>
       <c r="AJ47" s="4"/>
     </row>
     <row r="48" spans="1:36" ht="18" customHeight="1">
       <c r="A48" s="34"/>
-      <c r="B48" s="125" t="s">
+      <c r="B48" s="58" t="s">
         <v>33</v>
       </c>
-      <c r="C48" s="125"/>
-      <c r="D48" s="125"/>
-      <c r="E48" s="125"/>
-      <c r="F48" s="125"/>
-      <c r="G48" s="125"/>
-      <c r="H48" s="125"/>
-      <c r="I48" s="126"/>
+      <c r="C48" s="58"/>
+      <c r="D48" s="58"/>
+      <c r="E48" s="58"/>
+      <c r="F48" s="58"/>
+      <c r="G48" s="58"/>
+      <c r="H48" s="58"/>
+      <c r="I48" s="59"/>
       <c r="J48" s="10"/>
-      <c r="K48" s="125" t="s">
+      <c r="K48" s="58" t="s">
         <v>34</v>
       </c>
-      <c r="L48" s="125"/>
-      <c r="M48" s="125"/>
-      <c r="N48" s="125"/>
-      <c r="O48" s="125"/>
-      <c r="P48" s="125"/>
-      <c r="Q48" s="125"/>
-      <c r="R48" s="126"/>
-      <c r="S48" s="140" t="s">
+      <c r="L48" s="58"/>
+      <c r="M48" s="58"/>
+      <c r="N48" s="58"/>
+      <c r="O48" s="58"/>
+      <c r="P48" s="58"/>
+      <c r="Q48" s="58"/>
+      <c r="R48" s="59"/>
+      <c r="S48" s="91" t="s">
         <v>20</v>
       </c>
-      <c r="T48" s="141"/>
-      <c r="U48" s="141"/>
-      <c r="V48" s="141"/>
-      <c r="W48" s="141"/>
-      <c r="X48" s="141"/>
-      <c r="Y48" s="141"/>
-      <c r="Z48" s="141"/>
-      <c r="AA48" s="142"/>
-      <c r="AB48" s="123" t="s">
+      <c r="T48" s="92"/>
+      <c r="U48" s="92"/>
+      <c r="V48" s="92"/>
+      <c r="W48" s="92"/>
+      <c r="X48" s="92"/>
+      <c r="Y48" s="92"/>
+      <c r="Z48" s="92"/>
+      <c r="AA48" s="93"/>
+      <c r="AB48" s="60" t="s">
         <v>78</v>
       </c>
-      <c r="AC48" s="76"/>
-      <c r="AD48" s="76"/>
-      <c r="AE48" s="76"/>
-      <c r="AF48" s="76"/>
-      <c r="AG48" s="124"/>
-      <c r="AH48" s="124"/>
-      <c r="AI48" s="124"/>
+      <c r="AC48" s="61"/>
+      <c r="AD48" s="61"/>
+      <c r="AE48" s="61"/>
+      <c r="AF48" s="61"/>
+      <c r="AG48" s="94"/>
+      <c r="AH48" s="94"/>
+      <c r="AI48" s="94"/>
       <c r="AJ48" s="12" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="49" spans="1:36" ht="18" customHeight="1">
       <c r="A49" s="10"/>
-      <c r="B49" s="125" t="s">
+      <c r="B49" s="58" t="s">
         <v>74</v>
       </c>
-      <c r="C49" s="125"/>
-      <c r="D49" s="125"/>
-      <c r="E49" s="125"/>
-      <c r="F49" s="125"/>
-      <c r="G49" s="125"/>
-      <c r="H49" s="125"/>
-      <c r="I49" s="126"/>
+      <c r="C49" s="58"/>
+      <c r="D49" s="58"/>
+      <c r="E49" s="58"/>
+      <c r="F49" s="58"/>
+      <c r="G49" s="58"/>
+      <c r="H49" s="58"/>
+      <c r="I49" s="59"/>
       <c r="J49" s="10"/>
-      <c r="K49" s="125" t="s">
+      <c r="K49" s="58" t="s">
         <v>37</v>
       </c>
-      <c r="L49" s="125"/>
-      <c r="M49" s="125"/>
-      <c r="N49" s="125"/>
-      <c r="O49" s="125"/>
-      <c r="P49" s="125"/>
-      <c r="Q49" s="125"/>
-      <c r="R49" s="126"/>
+      <c r="L49" s="58"/>
+      <c r="M49" s="58"/>
+      <c r="N49" s="58"/>
+      <c r="O49" s="58"/>
+      <c r="P49" s="58"/>
+      <c r="Q49" s="58"/>
+      <c r="R49" s="59"/>
       <c r="S49" s="10"/>
-      <c r="T49" s="125" t="s">
+      <c r="T49" s="58" t="s">
         <v>23</v>
       </c>
-      <c r="U49" s="125"/>
-      <c r="V49" s="125"/>
-      <c r="W49" s="125"/>
-      <c r="X49" s="125"/>
-      <c r="Y49" s="125"/>
-      <c r="Z49" s="125"/>
-      <c r="AA49" s="126"/>
-      <c r="AB49" s="127" t="s">
+      <c r="U49" s="58"/>
+      <c r="V49" s="58"/>
+      <c r="W49" s="58"/>
+      <c r="X49" s="58"/>
+      <c r="Y49" s="58"/>
+      <c r="Z49" s="58"/>
+      <c r="AA49" s="59"/>
+      <c r="AB49" s="102" t="s">
         <v>79</v>
       </c>
-      <c r="AC49" s="128"/>
-      <c r="AD49" s="128"/>
-      <c r="AE49" s="128"/>
-      <c r="AF49" s="128"/>
-      <c r="AG49" s="144"/>
-      <c r="AH49" s="144"/>
-      <c r="AI49" s="144"/>
+      <c r="AC49" s="103"/>
+      <c r="AD49" s="103"/>
+      <c r="AE49" s="103"/>
+      <c r="AF49" s="103"/>
+      <c r="AG49" s="62"/>
+      <c r="AH49" s="62"/>
+      <c r="AI49" s="62"/>
       <c r="AJ49" s="33" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="50" spans="1:36" ht="18" customHeight="1">
       <c r="A50" s="10"/>
-      <c r="B50" s="125" t="s">
+      <c r="B50" s="58" t="s">
         <v>75</v>
       </c>
-      <c r="C50" s="125"/>
-      <c r="D50" s="125"/>
-      <c r="E50" s="125"/>
-      <c r="F50" s="125"/>
-      <c r="G50" s="125"/>
-      <c r="H50" s="125"/>
-      <c r="I50" s="126"/>
+      <c r="C50" s="58"/>
+      <c r="D50" s="58"/>
+      <c r="E50" s="58"/>
+      <c r="F50" s="58"/>
+      <c r="G50" s="58"/>
+      <c r="H50" s="58"/>
+      <c r="I50" s="59"/>
       <c r="J50" s="10"/>
-      <c r="K50" s="125" t="s">
+      <c r="K50" s="58" t="s">
         <v>39</v>
       </c>
-      <c r="L50" s="125"/>
-      <c r="M50" s="125"/>
-      <c r="N50" s="125"/>
-      <c r="O50" s="125"/>
-      <c r="P50" s="125"/>
-      <c r="Q50" s="125"/>
-      <c r="R50" s="126"/>
+      <c r="L50" s="58"/>
+      <c r="M50" s="58"/>
+      <c r="N50" s="58"/>
+      <c r="O50" s="58"/>
+      <c r="P50" s="58"/>
+      <c r="Q50" s="58"/>
+      <c r="R50" s="59"/>
       <c r="S50" s="10"/>
-      <c r="T50" s="125" t="s">
+      <c r="T50" s="58" t="s">
         <v>26</v>
       </c>
-      <c r="U50" s="125"/>
-      <c r="V50" s="125"/>
-      <c r="W50" s="125"/>
-      <c r="X50" s="125"/>
-      <c r="Y50" s="125"/>
-      <c r="Z50" s="125"/>
-      <c r="AA50" s="126"/>
-      <c r="AB50" s="131" t="s">
+      <c r="U50" s="58"/>
+      <c r="V50" s="58"/>
+      <c r="W50" s="58"/>
+      <c r="X50" s="58"/>
+      <c r="Y50" s="58"/>
+      <c r="Z50" s="58"/>
+      <c r="AA50" s="59"/>
+      <c r="AB50" s="105" t="s">
         <v>38</v>
       </c>
-      <c r="AC50" s="132"/>
-      <c r="AD50" s="132"/>
-      <c r="AE50" s="132"/>
-      <c r="AF50" s="132"/>
-      <c r="AG50" s="132"/>
-      <c r="AH50" s="132"/>
-      <c r="AI50" s="132"/>
-      <c r="AJ50" s="133"/>
+      <c r="AC50" s="106"/>
+      <c r="AD50" s="106"/>
+      <c r="AE50" s="106"/>
+      <c r="AF50" s="106"/>
+      <c r="AG50" s="106"/>
+      <c r="AH50" s="106"/>
+      <c r="AI50" s="106"/>
+      <c r="AJ50" s="107"/>
     </row>
     <row r="51" spans="1:36" ht="18" customHeight="1">
       <c r="A51" s="10"/>
-      <c r="B51" s="125" t="s">
+      <c r="B51" s="58" t="s">
         <v>40</v>
       </c>
-      <c r="C51" s="125"/>
-      <c r="D51" s="125"/>
-      <c r="E51" s="125"/>
-      <c r="F51" s="125"/>
-      <c r="G51" s="125"/>
-      <c r="H51" s="125"/>
-      <c r="I51" s="126"/>
+      <c r="C51" s="58"/>
+      <c r="D51" s="58"/>
+      <c r="E51" s="58"/>
+      <c r="F51" s="58"/>
+      <c r="G51" s="58"/>
+      <c r="H51" s="58"/>
+      <c r="I51" s="59"/>
       <c r="J51" s="10"/>
-      <c r="K51" s="125" t="s">
+      <c r="K51" s="58" t="s">
         <v>41</v>
       </c>
-      <c r="L51" s="125"/>
-      <c r="M51" s="125"/>
-      <c r="N51" s="125"/>
-      <c r="O51" s="125"/>
-      <c r="P51" s="125"/>
-      <c r="Q51" s="125"/>
-      <c r="R51" s="126"/>
+      <c r="L51" s="58"/>
+      <c r="M51" s="58"/>
+      <c r="N51" s="58"/>
+      <c r="O51" s="58"/>
+      <c r="P51" s="58"/>
+      <c r="Q51" s="58"/>
+      <c r="R51" s="59"/>
       <c r="S51" s="10"/>
-      <c r="T51" s="125" t="s">
+      <c r="T51" s="58" t="s">
         <v>29</v>
       </c>
-      <c r="U51" s="125"/>
-      <c r="V51" s="125"/>
-      <c r="W51" s="124"/>
-      <c r="X51" s="124"/>
-      <c r="Y51" s="124"/>
+      <c r="U51" s="58"/>
+      <c r="V51" s="58"/>
+      <c r="W51" s="94"/>
+      <c r="X51" s="94"/>
+      <c r="Y51" s="94"/>
       <c r="Z51" s="3" t="s">
         <v>30</v>
       </c>
       <c r="AA51" s="4"/>
       <c r="AB51" s="10"/>
-      <c r="AC51" s="134" t="s">
+      <c r="AC51" s="108" t="s">
         <v>76</v>
       </c>
-      <c r="AD51" s="134"/>
-      <c r="AE51" s="134"/>
-      <c r="AF51" s="134"/>
-      <c r="AG51" s="134"/>
-      <c r="AH51" s="134"/>
-      <c r="AI51" s="134"/>
-      <c r="AJ51" s="135"/>
+      <c r="AD51" s="108"/>
+      <c r="AE51" s="108"/>
+      <c r="AF51" s="108"/>
+      <c r="AG51" s="108"/>
+      <c r="AH51" s="108"/>
+      <c r="AI51" s="108"/>
+      <c r="AJ51" s="109"/>
     </row>
     <row r="52" spans="1:36" ht="18" customHeight="1">
       <c r="A52" s="10"/>
-      <c r="B52" s="125" t="s">
+      <c r="B52" s="58" t="s">
         <v>43</v>
       </c>
-      <c r="C52" s="125"/>
-      <c r="D52" s="136"/>
-      <c r="E52" s="136"/>
-      <c r="F52" s="136"/>
-      <c r="G52" s="136"/>
-      <c r="H52" s="136"/>
+      <c r="C52" s="58"/>
+      <c r="D52" s="110"/>
+      <c r="E52" s="110"/>
+      <c r="F52" s="110"/>
+      <c r="G52" s="110"/>
+      <c r="H52" s="110"/>
       <c r="I52" s="4"/>
       <c r="J52" s="10"/>
-      <c r="K52" s="125" t="s">
+      <c r="K52" s="58" t="s">
         <v>44</v>
       </c>
-      <c r="L52" s="125"/>
-      <c r="M52" s="125"/>
-      <c r="N52" s="125"/>
-      <c r="O52" s="125"/>
-      <c r="P52" s="125"/>
-      <c r="Q52" s="125"/>
-      <c r="R52" s="126"/>
+      <c r="L52" s="58"/>
+      <c r="M52" s="58"/>
+      <c r="N52" s="58"/>
+      <c r="O52" s="58"/>
+      <c r="P52" s="58"/>
+      <c r="Q52" s="58"/>
+      <c r="R52" s="59"/>
       <c r="S52" s="10"/>
-      <c r="T52" s="125" t="s">
+      <c r="T52" s="58" t="s">
         <v>32</v>
       </c>
-      <c r="U52" s="125"/>
-      <c r="V52" s="125"/>
-      <c r="W52" s="124"/>
-      <c r="X52" s="124"/>
-      <c r="Y52" s="124"/>
+      <c r="U52" s="58"/>
+      <c r="V52" s="58"/>
+      <c r="W52" s="94"/>
+      <c r="X52" s="94"/>
+      <c r="Y52" s="94"/>
       <c r="Z52" s="3" t="s">
         <v>30</v>
       </c>
       <c r="AA52" s="4"/>
       <c r="AB52" s="10"/>
-      <c r="AC52" s="125" t="s">
+      <c r="AC52" s="58" t="s">
         <v>42</v>
       </c>
-      <c r="AD52" s="125"/>
-      <c r="AE52" s="125"/>
-      <c r="AF52" s="125"/>
-      <c r="AG52" s="125"/>
-      <c r="AH52" s="125"/>
-      <c r="AI52" s="125"/>
-      <c r="AJ52" s="126"/>
+      <c r="AD52" s="58"/>
+      <c r="AE52" s="58"/>
+      <c r="AF52" s="58"/>
+      <c r="AG52" s="58"/>
+      <c r="AH52" s="58"/>
+      <c r="AI52" s="58"/>
+      <c r="AJ52" s="59"/>
     </row>
     <row r="53" spans="1:36" ht="18" customHeight="1">
       <c r="A53" s="13"/>
       <c r="B53" s="7"/>
       <c r="C53" s="7"/>
-      <c r="D53" s="147"/>
-      <c r="E53" s="147"/>
-      <c r="F53" s="147"/>
-      <c r="G53" s="147"/>
-      <c r="H53" s="147"/>
+      <c r="D53" s="99"/>
+      <c r="E53" s="99"/>
+      <c r="F53" s="99"/>
+      <c r="G53" s="99"/>
+      <c r="H53" s="99"/>
       <c r="I53" s="8"/>
-      <c r="J53" s="127"/>
-      <c r="K53" s="128"/>
-      <c r="L53" s="128"/>
-      <c r="M53" s="128"/>
-      <c r="N53" s="128"/>
-      <c r="O53" s="128"/>
-      <c r="P53" s="128"/>
-      <c r="Q53" s="128"/>
-      <c r="R53" s="129"/>
+      <c r="J53" s="102"/>
+      <c r="K53" s="103"/>
+      <c r="L53" s="103"/>
+      <c r="M53" s="103"/>
+      <c r="N53" s="103"/>
+      <c r="O53" s="103"/>
+      <c r="P53" s="103"/>
+      <c r="Q53" s="103"/>
+      <c r="R53" s="111"/>
       <c r="S53" s="13"/>
-      <c r="T53" s="143" t="s">
+      <c r="T53" s="95" t="s">
         <v>35</v>
       </c>
-      <c r="U53" s="143"/>
-      <c r="V53" s="143"/>
-      <c r="W53" s="144"/>
-      <c r="X53" s="144"/>
-      <c r="Y53" s="144"/>
+      <c r="U53" s="95"/>
+      <c r="V53" s="95"/>
+      <c r="W53" s="62"/>
+      <c r="X53" s="62"/>
+      <c r="Y53" s="62"/>
       <c r="Z53" s="6" t="s">
         <v>36</v>
       </c>
       <c r="AA53" s="8"/>
       <c r="AB53" s="13"/>
-      <c r="AC53" s="143" t="s">
+      <c r="AC53" s="95" t="s">
         <v>45</v>
       </c>
-      <c r="AD53" s="143"/>
-      <c r="AE53" s="143"/>
-      <c r="AF53" s="99"/>
-      <c r="AG53" s="99"/>
-      <c r="AH53" s="99"/>
+      <c r="AD53" s="95"/>
+      <c r="AE53" s="95"/>
+      <c r="AF53" s="104"/>
+      <c r="AG53" s="104"/>
+      <c r="AH53" s="104"/>
       <c r="AI53" s="7"/>
       <c r="AJ53" s="8"/>
     </row>
     <row r="54" spans="1:36" ht="18" customHeight="1">
-      <c r="A54" s="145" t="s">
+      <c r="A54" s="97" t="s">
         <v>46</v>
       </c>
-      <c r="B54" s="145"/>
-      <c r="C54" s="145"/>
-      <c r="D54" s="145"/>
-      <c r="E54" s="145"/>
-      <c r="F54" s="145"/>
-      <c r="G54" s="145"/>
-      <c r="H54" s="145"/>
-      <c r="I54" s="145"/>
-      <c r="J54" s="145"/>
-      <c r="K54" s="145"/>
-      <c r="L54" s="145"/>
-      <c r="M54" s="145"/>
-      <c r="N54" s="146"/>
-      <c r="O54" s="146"/>
-      <c r="P54" s="146"/>
-      <c r="Q54" s="146"/>
-      <c r="R54" s="146"/>
-      <c r="S54" s="146"/>
-      <c r="T54" s="146"/>
-      <c r="U54" s="146"/>
-      <c r="V54" s="146"/>
-      <c r="W54" s="146"/>
-      <c r="X54" s="146"/>
-      <c r="Y54" s="146"/>
-      <c r="Z54" s="146"/>
-      <c r="AA54" s="146"/>
-      <c r="AB54" s="146"/>
-      <c r="AC54" s="146"/>
-      <c r="AD54" s="146"/>
-      <c r="AE54" s="146"/>
-      <c r="AF54" s="146"/>
-      <c r="AG54" s="146"/>
-      <c r="AH54" s="146"/>
-      <c r="AI54" s="146"/>
-      <c r="AJ54" s="146"/>
+      <c r="B54" s="97"/>
+      <c r="C54" s="97"/>
+      <c r="D54" s="97"/>
+      <c r="E54" s="97"/>
+      <c r="F54" s="97"/>
+      <c r="G54" s="97"/>
+      <c r="H54" s="97"/>
+      <c r="I54" s="97"/>
+      <c r="J54" s="97"/>
+      <c r="K54" s="97"/>
+      <c r="L54" s="97"/>
+      <c r="M54" s="97"/>
+      <c r="N54" s="98"/>
+      <c r="O54" s="98"/>
+      <c r="P54" s="98"/>
+      <c r="Q54" s="98"/>
+      <c r="R54" s="98"/>
+      <c r="S54" s="98"/>
+      <c r="T54" s="98"/>
+      <c r="U54" s="98"/>
+      <c r="V54" s="98"/>
+      <c r="W54" s="98"/>
+      <c r="X54" s="98"/>
+      <c r="Y54" s="98"/>
+      <c r="Z54" s="98"/>
+      <c r="AA54" s="98"/>
+      <c r="AB54" s="98"/>
+      <c r="AC54" s="98"/>
+      <c r="AD54" s="98"/>
+      <c r="AE54" s="98"/>
+      <c r="AF54" s="98"/>
+      <c r="AG54" s="98"/>
+      <c r="AH54" s="98"/>
+      <c r="AI54" s="98"/>
+      <c r="AJ54" s="98"/>
     </row>
     <row r="55" spans="1:36" ht="18" customHeight="1">
-      <c r="A55" s="138"/>
-      <c r="B55" s="66"/>
-      <c r="C55" s="66"/>
-      <c r="D55" s="66"/>
-      <c r="E55" s="66"/>
-      <c r="F55" s="66"/>
-      <c r="G55" s="66"/>
-      <c r="H55" s="66"/>
-      <c r="I55" s="66"/>
-      <c r="J55" s="66"/>
-      <c r="K55" s="66"/>
-      <c r="L55" s="66"/>
-      <c r="N55" s="66"/>
-      <c r="O55" s="66"/>
-      <c r="P55" s="66"/>
-      <c r="Q55" s="66"/>
-      <c r="R55" s="66"/>
-      <c r="S55" s="66"/>
-      <c r="T55" s="66"/>
-      <c r="U55" s="66"/>
-      <c r="V55" s="66"/>
-      <c r="W55" s="66"/>
-      <c r="X55" s="66"/>
-      <c r="Y55" s="138"/>
-      <c r="Z55" s="138"/>
-      <c r="AA55" s="138"/>
-      <c r="AB55" s="148" t="s">
+      <c r="A55" s="88"/>
+      <c r="B55" s="96"/>
+      <c r="C55" s="96"/>
+      <c r="D55" s="96"/>
+      <c r="E55" s="96"/>
+      <c r="F55" s="96"/>
+      <c r="G55" s="96"/>
+      <c r="H55" s="96"/>
+      <c r="I55" s="96"/>
+      <c r="J55" s="96"/>
+      <c r="K55" s="96"/>
+      <c r="L55" s="96"/>
+      <c r="N55" s="96"/>
+      <c r="O55" s="96"/>
+      <c r="P55" s="96"/>
+      <c r="Q55" s="96"/>
+      <c r="R55" s="96"/>
+      <c r="S55" s="96"/>
+      <c r="T55" s="96"/>
+      <c r="U55" s="96"/>
+      <c r="V55" s="96"/>
+      <c r="W55" s="96"/>
+      <c r="X55" s="96"/>
+      <c r="Y55" s="88"/>
+      <c r="Z55" s="88"/>
+      <c r="AA55" s="88"/>
+      <c r="AB55" s="100" t="s">
         <v>93</v>
       </c>
-      <c r="AC55" s="98"/>
-      <c r="AD55" s="98"/>
-      <c r="AE55" s="98"/>
-      <c r="AF55" s="98"/>
-      <c r="AG55" s="98"/>
-      <c r="AH55" s="98"/>
-      <c r="AI55" s="98"/>
-      <c r="AJ55" s="98"/>
+      <c r="AC55" s="101"/>
+      <c r="AD55" s="101"/>
+      <c r="AE55" s="101"/>
+      <c r="AF55" s="101"/>
+      <c r="AG55" s="101"/>
+      <c r="AH55" s="101"/>
+      <c r="AI55" s="101"/>
+      <c r="AJ55" s="101"/>
     </row>
     <row r="56" spans="1:36" ht="18" customHeight="1">
-      <c r="A56" s="138"/>
-      <c r="B56" s="66"/>
-      <c r="C56" s="66"/>
-      <c r="D56" s="66"/>
-      <c r="E56" s="66"/>
-      <c r="F56" s="66"/>
-      <c r="G56" s="66"/>
-      <c r="H56" s="66"/>
-      <c r="I56" s="66"/>
-      <c r="J56" s="66"/>
-      <c r="K56" s="66"/>
-      <c r="L56" s="66"/>
-      <c r="N56" s="66"/>
-      <c r="O56" s="66"/>
-      <c r="P56" s="66"/>
-      <c r="Q56" s="66"/>
-      <c r="R56" s="66"/>
-      <c r="S56" s="66"/>
-      <c r="T56" s="66"/>
-      <c r="U56" s="66"/>
-      <c r="V56" s="66"/>
-      <c r="W56" s="66"/>
-      <c r="X56" s="66"/>
-      <c r="Y56" s="138"/>
-      <c r="Z56" s="138"/>
-      <c r="AA56" s="138"/>
-      <c r="AB56" s="139" t="s">
+      <c r="A56" s="88"/>
+      <c r="B56" s="96"/>
+      <c r="C56" s="96"/>
+      <c r="D56" s="96"/>
+      <c r="E56" s="96"/>
+      <c r="F56" s="96"/>
+      <c r="G56" s="96"/>
+      <c r="H56" s="96"/>
+      <c r="I56" s="96"/>
+      <c r="J56" s="96"/>
+      <c r="K56" s="96"/>
+      <c r="L56" s="96"/>
+      <c r="N56" s="96"/>
+      <c r="O56" s="96"/>
+      <c r="P56" s="96"/>
+      <c r="Q56" s="96"/>
+      <c r="R56" s="96"/>
+      <c r="S56" s="96"/>
+      <c r="T56" s="96"/>
+      <c r="U56" s="96"/>
+      <c r="V56" s="96"/>
+      <c r="W56" s="96"/>
+      <c r="X56" s="96"/>
+      <c r="Y56" s="88"/>
+      <c r="Z56" s="88"/>
+      <c r="AA56" s="88"/>
+      <c r="AB56" s="90" t="s">
         <v>47</v>
       </c>
-      <c r="AC56" s="139"/>
-      <c r="AD56" s="139"/>
-      <c r="AE56" s="139"/>
-      <c r="AF56" s="139"/>
-      <c r="AG56" s="139"/>
-      <c r="AH56" s="139"/>
-      <c r="AI56" s="139"/>
-      <c r="AJ56" s="139"/>
+      <c r="AC56" s="90"/>
+      <c r="AD56" s="90"/>
+      <c r="AE56" s="90"/>
+      <c r="AF56" s="90"/>
+      <c r="AG56" s="90"/>
+      <c r="AH56" s="90"/>
+      <c r="AI56" s="90"/>
+      <c r="AJ56" s="90"/>
     </row>
     <row r="57" spans="1:36" ht="18" customHeight="1">
-      <c r="A57" s="138"/>
-      <c r="B57" s="66"/>
-      <c r="C57" s="66"/>
-      <c r="D57" s="66"/>
-      <c r="E57" s="66"/>
-      <c r="F57" s="66"/>
-      <c r="G57" s="66"/>
-      <c r="H57" s="66"/>
-      <c r="I57" s="66"/>
-      <c r="J57" s="66"/>
-      <c r="K57" s="66"/>
-      <c r="L57" s="66"/>
-      <c r="N57" s="66"/>
-      <c r="O57" s="66"/>
-      <c r="P57" s="66"/>
-      <c r="Q57" s="66"/>
-      <c r="R57" s="66"/>
-      <c r="S57" s="66"/>
-      <c r="T57" s="66"/>
-      <c r="U57" s="66"/>
-      <c r="V57" s="66"/>
-      <c r="W57" s="66"/>
-      <c r="X57" s="66"/>
-      <c r="Y57" s="138"/>
-      <c r="Z57" s="138"/>
-      <c r="AA57" s="138"/>
-      <c r="AB57" s="138"/>
-      <c r="AC57" s="138"/>
-      <c r="AD57" s="138"/>
-      <c r="AE57" s="138"/>
-      <c r="AF57" s="138"/>
-      <c r="AG57" s="138"/>
-      <c r="AH57" s="138"/>
-      <c r="AI57" s="138"/>
-      <c r="AJ57" s="138"/>
+      <c r="A57" s="88"/>
+      <c r="B57" s="96"/>
+      <c r="C57" s="96"/>
+      <c r="D57" s="96"/>
+      <c r="E57" s="96"/>
+      <c r="F57" s="96"/>
+      <c r="G57" s="96"/>
+      <c r="H57" s="96"/>
+      <c r="I57" s="96"/>
+      <c r="J57" s="96"/>
+      <c r="K57" s="96"/>
+      <c r="L57" s="96"/>
+      <c r="N57" s="96"/>
+      <c r="O57" s="96"/>
+      <c r="P57" s="96"/>
+      <c r="Q57" s="96"/>
+      <c r="R57" s="96"/>
+      <c r="S57" s="96"/>
+      <c r="T57" s="96"/>
+      <c r="U57" s="96"/>
+      <c r="V57" s="96"/>
+      <c r="W57" s="96"/>
+      <c r="X57" s="96"/>
+      <c r="Y57" s="88"/>
+      <c r="Z57" s="88"/>
+      <c r="AA57" s="88"/>
+      <c r="AB57" s="88"/>
+      <c r="AC57" s="88"/>
+      <c r="AD57" s="88"/>
+      <c r="AE57" s="88"/>
+      <c r="AF57" s="88"/>
+      <c r="AG57" s="88"/>
+      <c r="AH57" s="88"/>
+      <c r="AI57" s="88"/>
+      <c r="AJ57" s="88"/>
     </row>
     <row r="58" spans="1:36" ht="18" customHeight="1">
       <c r="A58" s="51"/>
@@ -9372,72 +9378,72 @@
       <c r="V58" s="52"/>
       <c r="W58" s="52"/>
       <c r="X58" s="52"/>
-      <c r="Y58" s="138"/>
-      <c r="Z58" s="138"/>
-      <c r="AA58" s="138"/>
-      <c r="AB58" s="138"/>
-      <c r="AC58" s="138"/>
-      <c r="AD58" s="138"/>
-      <c r="AE58" s="138"/>
-      <c r="AF58" s="138"/>
-      <c r="AG58" s="138"/>
-      <c r="AH58" s="138"/>
-      <c r="AI58" s="138"/>
-      <c r="AJ58" s="138"/>
+      <c r="Y58" s="88"/>
+      <c r="Z58" s="88"/>
+      <c r="AA58" s="88"/>
+      <c r="AB58" s="88"/>
+      <c r="AC58" s="88"/>
+      <c r="AD58" s="88"/>
+      <c r="AE58" s="88"/>
+      <c r="AF58" s="88"/>
+      <c r="AG58" s="88"/>
+      <c r="AH58" s="88"/>
+      <c r="AI58" s="88"/>
+      <c r="AJ58" s="88"/>
     </row>
     <row r="59" spans="1:36" ht="18" customHeight="1">
-      <c r="A59" s="138"/>
-      <c r="B59" s="138"/>
-      <c r="C59" s="138"/>
-      <c r="D59" s="138"/>
-      <c r="E59" s="138"/>
-      <c r="F59" s="138"/>
-      <c r="G59" s="138"/>
-      <c r="H59" s="138"/>
-      <c r="I59" s="138"/>
-      <c r="J59" s="138"/>
-      <c r="K59" s="138"/>
-      <c r="L59" s="138"/>
-      <c r="M59" s="138"/>
-      <c r="N59" s="138"/>
-      <c r="O59" s="138"/>
-      <c r="P59" s="138"/>
-      <c r="Q59" s="138"/>
-      <c r="R59" s="138"/>
-      <c r="S59" s="138"/>
-      <c r="T59" s="138"/>
-      <c r="U59" s="138"/>
-      <c r="V59" s="138"/>
-      <c r="W59" s="138"/>
-      <c r="X59" s="138"/>
-      <c r="Y59" s="138"/>
-      <c r="Z59" s="138"/>
-      <c r="AA59" s="138"/>
-      <c r="AB59" s="81"/>
-      <c r="AC59" s="81"/>
-      <c r="AD59" s="81"/>
-      <c r="AE59" s="81"/>
-      <c r="AF59" s="81"/>
-      <c r="AG59" s="81"/>
-      <c r="AH59" s="81"/>
-      <c r="AI59" s="81"/>
-      <c r="AJ59" s="81"/>
+      <c r="A59" s="88"/>
+      <c r="B59" s="88"/>
+      <c r="C59" s="88"/>
+      <c r="D59" s="88"/>
+      <c r="E59" s="88"/>
+      <c r="F59" s="88"/>
+      <c r="G59" s="88"/>
+      <c r="H59" s="88"/>
+      <c r="I59" s="88"/>
+      <c r="J59" s="88"/>
+      <c r="K59" s="88"/>
+      <c r="L59" s="88"/>
+      <c r="M59" s="88"/>
+      <c r="N59" s="88"/>
+      <c r="O59" s="88"/>
+      <c r="P59" s="88"/>
+      <c r="Q59" s="88"/>
+      <c r="R59" s="88"/>
+      <c r="S59" s="88"/>
+      <c r="T59" s="88"/>
+      <c r="U59" s="88"/>
+      <c r="V59" s="88"/>
+      <c r="W59" s="88"/>
+      <c r="X59" s="88"/>
+      <c r="Y59" s="88"/>
+      <c r="Z59" s="88"/>
+      <c r="AA59" s="88"/>
+      <c r="AB59" s="89"/>
+      <c r="AC59" s="89"/>
+      <c r="AD59" s="89"/>
+      <c r="AE59" s="89"/>
+      <c r="AF59" s="89"/>
+      <c r="AG59" s="89"/>
+      <c r="AH59" s="89"/>
+      <c r="AI59" s="89"/>
+      <c r="AJ59" s="89"/>
     </row>
     <row r="60" spans="1:36" ht="18" customHeight="1">
-      <c r="Y60" s="138"/>
-      <c r="Z60" s="138"/>
-      <c r="AA60" s="138"/>
-      <c r="AB60" s="137" t="s">
+      <c r="Y60" s="88"/>
+      <c r="Z60" s="88"/>
+      <c r="AA60" s="88"/>
+      <c r="AB60" s="87" t="s">
         <v>92</v>
       </c>
-      <c r="AC60" s="137"/>
-      <c r="AD60" s="137"/>
-      <c r="AE60" s="137"/>
-      <c r="AF60" s="137"/>
-      <c r="AG60" s="137"/>
-      <c r="AH60" s="137"/>
-      <c r="AI60" s="137"/>
-      <c r="AJ60" s="137"/>
+      <c r="AC60" s="87"/>
+      <c r="AD60" s="87"/>
+      <c r="AE60" s="87"/>
+      <c r="AF60" s="87"/>
+      <c r="AG60" s="87"/>
+      <c r="AH60" s="87"/>
+      <c r="AI60" s="87"/>
+      <c r="AJ60" s="87"/>
     </row>
     <row r="61" spans="1:36" ht="16.5" customHeight="1"/>
     <row r="62" spans="1:36" ht="18" hidden="1" customHeight="1"/>
@@ -10039,6 +10045,113 @@
     <row r="658"/>
   </sheetData>
   <mergeCells count="131">
+    <mergeCell ref="AD3:AJ3"/>
+    <mergeCell ref="Y5:Z5"/>
+    <mergeCell ref="P5:X5"/>
+    <mergeCell ref="AH6:AI6"/>
+    <mergeCell ref="AC7:AE7"/>
+    <mergeCell ref="AI7:AJ7"/>
+    <mergeCell ref="C6:I6"/>
+    <mergeCell ref="S8:W8"/>
+    <mergeCell ref="X7:AB7"/>
+    <mergeCell ref="AC6:AD6"/>
+    <mergeCell ref="B57:L57"/>
+    <mergeCell ref="N57:X57"/>
+    <mergeCell ref="Q2:Z2"/>
+    <mergeCell ref="Q3:Z3"/>
+    <mergeCell ref="A11:P11"/>
+    <mergeCell ref="K5:O5"/>
+    <mergeCell ref="K6:O6"/>
+    <mergeCell ref="P6:X6"/>
+    <mergeCell ref="A41:R41"/>
+    <mergeCell ref="S9:W9"/>
+    <mergeCell ref="A7:B7"/>
+    <mergeCell ref="Q11:AJ11"/>
+    <mergeCell ref="C7:I7"/>
+    <mergeCell ref="D8:R8"/>
+    <mergeCell ref="A8:C8"/>
+    <mergeCell ref="S7:T7"/>
+    <mergeCell ref="P7:R7"/>
+    <mergeCell ref="X8:AJ8"/>
+    <mergeCell ref="A10:AJ10"/>
+    <mergeCell ref="A5:B5"/>
+    <mergeCell ref="A6:B6"/>
+    <mergeCell ref="D9:R9"/>
+    <mergeCell ref="K7:O7"/>
+    <mergeCell ref="A25:AJ25"/>
+    <mergeCell ref="A22:AJ23"/>
+    <mergeCell ref="A17:T20"/>
+    <mergeCell ref="C5:I5"/>
+    <mergeCell ref="AF19:AG19"/>
+    <mergeCell ref="A43:I43"/>
+    <mergeCell ref="AI19:AJ19"/>
+    <mergeCell ref="A14:H14"/>
+    <mergeCell ref="I14:AJ14"/>
+    <mergeCell ref="AI17:AJ17"/>
+    <mergeCell ref="AF17:AG17"/>
+    <mergeCell ref="A15:AJ15"/>
+    <mergeCell ref="AF18:AG18"/>
+    <mergeCell ref="AA5:AJ5"/>
+    <mergeCell ref="V7:W7"/>
+    <mergeCell ref="AI18:AJ18"/>
+    <mergeCell ref="U16:AD16"/>
+    <mergeCell ref="AF7:AG7"/>
+    <mergeCell ref="AE16:AJ16"/>
+    <mergeCell ref="A16:T16"/>
+    <mergeCell ref="A9:C9"/>
+    <mergeCell ref="X9:AJ9"/>
+    <mergeCell ref="AB46:AE46"/>
+    <mergeCell ref="S44:V44"/>
+    <mergeCell ref="S45:V45"/>
+    <mergeCell ref="S46:W46"/>
+    <mergeCell ref="X46:Z46"/>
+    <mergeCell ref="K46:R46"/>
+    <mergeCell ref="K45:R45"/>
+    <mergeCell ref="AB44:AE44"/>
+    <mergeCell ref="J53:R53"/>
+    <mergeCell ref="AB45:AE45"/>
+    <mergeCell ref="K44:R44"/>
+    <mergeCell ref="B48:I48"/>
+    <mergeCell ref="AF47:AI47"/>
+    <mergeCell ref="AB49:AF49"/>
+    <mergeCell ref="AF53:AH53"/>
+    <mergeCell ref="AB50:AJ50"/>
+    <mergeCell ref="AC51:AJ51"/>
+    <mergeCell ref="B49:I49"/>
+    <mergeCell ref="B52:C52"/>
+    <mergeCell ref="D52:H52"/>
+    <mergeCell ref="K50:R50"/>
+    <mergeCell ref="K51:R51"/>
+    <mergeCell ref="S47:W47"/>
+    <mergeCell ref="T49:AA49"/>
+    <mergeCell ref="K48:R48"/>
+    <mergeCell ref="K49:R49"/>
+    <mergeCell ref="W52:Y52"/>
+    <mergeCell ref="K47:R47"/>
+    <mergeCell ref="AB60:AJ60"/>
+    <mergeCell ref="AB57:AJ59"/>
+    <mergeCell ref="AB56:AJ56"/>
+    <mergeCell ref="S48:AA48"/>
+    <mergeCell ref="AG48:AI48"/>
+    <mergeCell ref="AC53:AE53"/>
+    <mergeCell ref="T52:V52"/>
+    <mergeCell ref="W53:Y53"/>
+    <mergeCell ref="B56:L56"/>
+    <mergeCell ref="N56:X56"/>
+    <mergeCell ref="Y55:AA60"/>
+    <mergeCell ref="A59:X59"/>
+    <mergeCell ref="A55:A57"/>
+    <mergeCell ref="N55:X55"/>
+    <mergeCell ref="A54:M54"/>
+    <mergeCell ref="N54:AJ54"/>
+    <mergeCell ref="D53:H53"/>
+    <mergeCell ref="B50:I50"/>
+    <mergeCell ref="B55:L55"/>
+    <mergeCell ref="K52:R52"/>
+    <mergeCell ref="T53:V53"/>
+    <mergeCell ref="AB55:AJ55"/>
+    <mergeCell ref="W51:Y51"/>
+    <mergeCell ref="AC52:AJ52"/>
     <mergeCell ref="AF46:AI46"/>
     <mergeCell ref="T50:AA50"/>
     <mergeCell ref="AF45:AI45"/>
@@ -10063,113 +10176,6 @@
     <mergeCell ref="B45:I45"/>
     <mergeCell ref="AB47:AE47"/>
     <mergeCell ref="B46:I46"/>
-    <mergeCell ref="AB60:AJ60"/>
-    <mergeCell ref="AB57:AJ59"/>
-    <mergeCell ref="AB56:AJ56"/>
-    <mergeCell ref="S48:AA48"/>
-    <mergeCell ref="AG48:AI48"/>
-    <mergeCell ref="AC53:AE53"/>
-    <mergeCell ref="T52:V52"/>
-    <mergeCell ref="W53:Y53"/>
-    <mergeCell ref="B56:L56"/>
-    <mergeCell ref="N56:X56"/>
-    <mergeCell ref="Y55:AA60"/>
-    <mergeCell ref="A59:X59"/>
-    <mergeCell ref="A55:A57"/>
-    <mergeCell ref="N55:X55"/>
-    <mergeCell ref="A54:M54"/>
-    <mergeCell ref="N54:AJ54"/>
-    <mergeCell ref="D53:H53"/>
-    <mergeCell ref="B50:I50"/>
-    <mergeCell ref="B55:L55"/>
-    <mergeCell ref="K52:R52"/>
-    <mergeCell ref="T53:V53"/>
-    <mergeCell ref="AB55:AJ55"/>
-    <mergeCell ref="W51:Y51"/>
-    <mergeCell ref="AC52:AJ52"/>
-    <mergeCell ref="B48:I48"/>
-    <mergeCell ref="AF47:AI47"/>
-    <mergeCell ref="AB49:AF49"/>
-    <mergeCell ref="AF53:AH53"/>
-    <mergeCell ref="AB50:AJ50"/>
-    <mergeCell ref="AC51:AJ51"/>
-    <mergeCell ref="B49:I49"/>
-    <mergeCell ref="B52:C52"/>
-    <mergeCell ref="D52:H52"/>
-    <mergeCell ref="K50:R50"/>
-    <mergeCell ref="K51:R51"/>
-    <mergeCell ref="S47:W47"/>
-    <mergeCell ref="T49:AA49"/>
-    <mergeCell ref="K48:R48"/>
-    <mergeCell ref="K49:R49"/>
-    <mergeCell ref="W52:Y52"/>
-    <mergeCell ref="K47:R47"/>
-    <mergeCell ref="AB46:AE46"/>
-    <mergeCell ref="S44:V44"/>
-    <mergeCell ref="S45:V45"/>
-    <mergeCell ref="S46:W46"/>
-    <mergeCell ref="X46:Z46"/>
-    <mergeCell ref="K46:R46"/>
-    <mergeCell ref="K45:R45"/>
-    <mergeCell ref="AB44:AE44"/>
-    <mergeCell ref="J53:R53"/>
-    <mergeCell ref="AB45:AE45"/>
-    <mergeCell ref="K44:R44"/>
-    <mergeCell ref="A25:AJ25"/>
-    <mergeCell ref="A22:AJ23"/>
-    <mergeCell ref="A17:T20"/>
-    <mergeCell ref="C5:I5"/>
-    <mergeCell ref="AF19:AG19"/>
-    <mergeCell ref="A43:I43"/>
-    <mergeCell ref="AI19:AJ19"/>
-    <mergeCell ref="A14:H14"/>
-    <mergeCell ref="I14:AJ14"/>
-    <mergeCell ref="AI17:AJ17"/>
-    <mergeCell ref="AF17:AG17"/>
-    <mergeCell ref="A15:AJ15"/>
-    <mergeCell ref="AF18:AG18"/>
-    <mergeCell ref="AA5:AJ5"/>
-    <mergeCell ref="V7:W7"/>
-    <mergeCell ref="AI18:AJ18"/>
-    <mergeCell ref="U16:AD16"/>
-    <mergeCell ref="AF7:AG7"/>
-    <mergeCell ref="AE16:AJ16"/>
-    <mergeCell ref="A16:T16"/>
-    <mergeCell ref="A9:C9"/>
-    <mergeCell ref="X9:AJ9"/>
-    <mergeCell ref="B57:L57"/>
-    <mergeCell ref="N57:X57"/>
-    <mergeCell ref="Q2:Z2"/>
-    <mergeCell ref="Q3:Z3"/>
-    <mergeCell ref="A11:P11"/>
-    <mergeCell ref="K5:O5"/>
-    <mergeCell ref="K6:O6"/>
-    <mergeCell ref="P6:X6"/>
-    <mergeCell ref="A41:R41"/>
-    <mergeCell ref="S9:W9"/>
-    <mergeCell ref="A7:B7"/>
-    <mergeCell ref="Q11:AJ11"/>
-    <mergeCell ref="C7:I7"/>
-    <mergeCell ref="D8:R8"/>
-    <mergeCell ref="A8:C8"/>
-    <mergeCell ref="S7:T7"/>
-    <mergeCell ref="P7:R7"/>
-    <mergeCell ref="X8:AJ8"/>
-    <mergeCell ref="A10:AJ10"/>
-    <mergeCell ref="A5:B5"/>
-    <mergeCell ref="A6:B6"/>
-    <mergeCell ref="AD6:AF6"/>
-    <mergeCell ref="D9:R9"/>
-    <mergeCell ref="K7:O7"/>
-    <mergeCell ref="AD3:AJ3"/>
-    <mergeCell ref="Y5:Z5"/>
-    <mergeCell ref="P5:X5"/>
-    <mergeCell ref="AH6:AI6"/>
-    <mergeCell ref="AC7:AE7"/>
-    <mergeCell ref="AI7:AJ7"/>
-    <mergeCell ref="C6:I6"/>
-    <mergeCell ref="S8:W8"/>
-    <mergeCell ref="X7:AB7"/>
   </mergeCells>
   <phoneticPr fontId="0" type="noConversion"/>
   <printOptions horizontalCentered="1"/>

--- a/backend_api/templates/container_report_template.xlsx
+++ b/backend_api/templates/container_report_template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Aaron Avila\Documents\ERP-SOM\backend_api\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7B26B275-840D-436D-B3AC-DF2073B79FBE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FE6AAC90-F041-4099-8E87-E019DBF1C341}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-1125" windowWidth="29040" windowHeight="15720" xr2:uid="{253FFB1B-D348-46B1-A532-0D44566D2FFD}"/>
   </bookViews>
@@ -256,20 +256,6 @@
             <family val="2"/>
           </rPr>
           <t>Fecha en que se inicia la Inspección</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="S7" authorId="0" shapeId="0" xr:uid="{14F5F057-6659-46AD-8C09-DF5BB6769F86}">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="8"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>Hora en que se inicia la Inspección</t>
         </r>
       </text>
     </comment>
@@ -1425,7 +1411,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="167">
+  <cellXfs count="168">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -1563,26 +1549,326 @@
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
+    <xf numFmtId="14" fontId="13" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="4" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="165" fontId="13" fillId="0" borderId="8" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="14" fontId="13" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="8" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="9" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="6" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="2" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="3" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="4" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="5" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="3" fontId="13" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="13" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="9" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="6" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="6" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="6" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="2" borderId="9" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="2" borderId="6" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="2" borderId="7" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="4" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="4" fontId="13" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
     <xf numFmtId="4" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="4" fontId="13" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right"/>
-      <protection locked="0"/>
-    </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
       <protection locked="0"/>
@@ -1611,25 +1897,6 @@
       <alignment horizontal="left" vertical="top" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="9" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="6" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
@@ -1638,10 +1905,6 @@
     </xf>
     <xf numFmtId="0" fontId="22" fillId="2" borderId="9" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="13" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -1663,285 +1926,11 @@
       <alignment horizontal="left" vertical="top" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="4" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right"/>
+    <xf numFmtId="165" fontId="13" fillId="0" borderId="8" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="3" fontId="13" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="2" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="3" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="4" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="5" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="3" fontId="13" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="9" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="6" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="6" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="6" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="165" fontId="13" fillId="0" borderId="8" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="2" borderId="9" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="2" borderId="6" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="2" borderId="7" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="8" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="4" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="14" fontId="13" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="8" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2242,8 +2231,8 @@
           <xdr:rowOff>30480</xdr:rowOff>
         </xdr:from>
         <xdr:to>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>320040</xdr:colOff>
+          <xdr:col>1</xdr:col>
+          <xdr:colOff>91440</xdr:colOff>
           <xdr:row>12</xdr:row>
           <xdr:rowOff>15240</xdr:rowOff>
         </xdr:to>
@@ -2309,8 +2298,8 @@
           <xdr:rowOff>7620</xdr:rowOff>
         </xdr:from>
         <xdr:to>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>320040</xdr:colOff>
+          <xdr:col>1</xdr:col>
+          <xdr:colOff>91440</xdr:colOff>
           <xdr:row>13</xdr:row>
           <xdr:rowOff>15240</xdr:rowOff>
         </xdr:to>
@@ -2376,8 +2365,8 @@
           <xdr:rowOff>30480</xdr:rowOff>
         </xdr:from>
         <xdr:to>
-          <xdr:col>4</xdr:col>
-          <xdr:colOff>320040</xdr:colOff>
+          <xdr:col>5</xdr:col>
+          <xdr:colOff>40005</xdr:colOff>
           <xdr:row>12</xdr:row>
           <xdr:rowOff>15240</xdr:rowOff>
         </xdr:to>
@@ -2443,8 +2432,8 @@
           <xdr:rowOff>7620</xdr:rowOff>
         </xdr:from>
         <xdr:to>
-          <xdr:col>4</xdr:col>
-          <xdr:colOff>320040</xdr:colOff>
+          <xdr:col>5</xdr:col>
+          <xdr:colOff>40005</xdr:colOff>
           <xdr:row>13</xdr:row>
           <xdr:rowOff>15240</xdr:rowOff>
         </xdr:to>
@@ -2510,8 +2499,8 @@
           <xdr:rowOff>30480</xdr:rowOff>
         </xdr:from>
         <xdr:to>
-          <xdr:col>8</xdr:col>
-          <xdr:colOff>396240</xdr:colOff>
+          <xdr:col>9</xdr:col>
+          <xdr:colOff>112395</xdr:colOff>
           <xdr:row>12</xdr:row>
           <xdr:rowOff>15240</xdr:rowOff>
         </xdr:to>
@@ -2577,8 +2566,8 @@
           <xdr:rowOff>7620</xdr:rowOff>
         </xdr:from>
         <xdr:to>
-          <xdr:col>8</xdr:col>
-          <xdr:colOff>396240</xdr:colOff>
+          <xdr:col>9</xdr:col>
+          <xdr:colOff>112395</xdr:colOff>
           <xdr:row>13</xdr:row>
           <xdr:rowOff>15240</xdr:rowOff>
         </xdr:to>
@@ -2644,8 +2633,8 @@
           <xdr:rowOff>30480</xdr:rowOff>
         </xdr:from>
         <xdr:to>
-          <xdr:col>13</xdr:col>
-          <xdr:colOff>320040</xdr:colOff>
+          <xdr:col>14</xdr:col>
+          <xdr:colOff>53340</xdr:colOff>
           <xdr:row>12</xdr:row>
           <xdr:rowOff>15240</xdr:rowOff>
         </xdr:to>
@@ -2711,8 +2700,8 @@
           <xdr:rowOff>7620</xdr:rowOff>
         </xdr:from>
         <xdr:to>
-          <xdr:col>13</xdr:col>
-          <xdr:colOff>320040</xdr:colOff>
+          <xdr:col>14</xdr:col>
+          <xdr:colOff>53340</xdr:colOff>
           <xdr:row>13</xdr:row>
           <xdr:rowOff>15240</xdr:rowOff>
         </xdr:to>
@@ -3917,8 +3906,8 @@
           <xdr:rowOff>30480</xdr:rowOff>
         </xdr:from>
         <xdr:to>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>358140</xdr:colOff>
+          <xdr:col>1</xdr:col>
+          <xdr:colOff>129540</xdr:colOff>
           <xdr:row>44</xdr:row>
           <xdr:rowOff>15240</xdr:rowOff>
         </xdr:to>
@@ -3984,8 +3973,8 @@
           <xdr:rowOff>30480</xdr:rowOff>
         </xdr:from>
         <xdr:to>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>358140</xdr:colOff>
+          <xdr:col>1</xdr:col>
+          <xdr:colOff>129540</xdr:colOff>
           <xdr:row>45</xdr:row>
           <xdr:rowOff>15240</xdr:rowOff>
         </xdr:to>
@@ -4051,8 +4040,8 @@
           <xdr:rowOff>30480</xdr:rowOff>
         </xdr:from>
         <xdr:to>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>358140</xdr:colOff>
+          <xdr:col>1</xdr:col>
+          <xdr:colOff>129540</xdr:colOff>
           <xdr:row>46</xdr:row>
           <xdr:rowOff>15240</xdr:rowOff>
         </xdr:to>
@@ -4118,8 +4107,8 @@
           <xdr:rowOff>30480</xdr:rowOff>
         </xdr:from>
         <xdr:to>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>358140</xdr:colOff>
+          <xdr:col>1</xdr:col>
+          <xdr:colOff>129540</xdr:colOff>
           <xdr:row>47</xdr:row>
           <xdr:rowOff>15240</xdr:rowOff>
         </xdr:to>
@@ -4185,8 +4174,8 @@
           <xdr:rowOff>30480</xdr:rowOff>
         </xdr:from>
         <xdr:to>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>358140</xdr:colOff>
+          <xdr:col>1</xdr:col>
+          <xdr:colOff>129540</xdr:colOff>
           <xdr:row>48</xdr:row>
           <xdr:rowOff>15240</xdr:rowOff>
         </xdr:to>
@@ -4252,8 +4241,8 @@
           <xdr:rowOff>30480</xdr:rowOff>
         </xdr:from>
         <xdr:to>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>358140</xdr:colOff>
+          <xdr:col>1</xdr:col>
+          <xdr:colOff>129540</xdr:colOff>
           <xdr:row>49</xdr:row>
           <xdr:rowOff>15240</xdr:rowOff>
         </xdr:to>
@@ -4319,8 +4308,8 @@
           <xdr:rowOff>30480</xdr:rowOff>
         </xdr:from>
         <xdr:to>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>358140</xdr:colOff>
+          <xdr:col>1</xdr:col>
+          <xdr:colOff>129540</xdr:colOff>
           <xdr:row>50</xdr:row>
           <xdr:rowOff>15240</xdr:rowOff>
         </xdr:to>
@@ -4386,8 +4375,8 @@
           <xdr:rowOff>30480</xdr:rowOff>
         </xdr:from>
         <xdr:to>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>358140</xdr:colOff>
+          <xdr:col>1</xdr:col>
+          <xdr:colOff>129540</xdr:colOff>
           <xdr:row>51</xdr:row>
           <xdr:rowOff>15240</xdr:rowOff>
         </xdr:to>
@@ -4453,8 +4442,8 @@
           <xdr:rowOff>30480</xdr:rowOff>
         </xdr:from>
         <xdr:to>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>358140</xdr:colOff>
+          <xdr:col>1</xdr:col>
+          <xdr:colOff>129540</xdr:colOff>
           <xdr:row>52</xdr:row>
           <xdr:rowOff>15240</xdr:rowOff>
         </xdr:to>
@@ -4521,7 +4510,7 @@
         </xdr:from>
         <xdr:to>
           <xdr:col>10</xdr:col>
-          <xdr:colOff>163830</xdr:colOff>
+          <xdr:colOff>171450</xdr:colOff>
           <xdr:row>44</xdr:row>
           <xdr:rowOff>15240</xdr:rowOff>
         </xdr:to>
@@ -4588,7 +4577,7 @@
         </xdr:from>
         <xdr:to>
           <xdr:col>10</xdr:col>
-          <xdr:colOff>163830</xdr:colOff>
+          <xdr:colOff>171450</xdr:colOff>
           <xdr:row>45</xdr:row>
           <xdr:rowOff>15240</xdr:rowOff>
         </xdr:to>
@@ -4655,7 +4644,7 @@
         </xdr:from>
         <xdr:to>
           <xdr:col>10</xdr:col>
-          <xdr:colOff>163830</xdr:colOff>
+          <xdr:colOff>171450</xdr:colOff>
           <xdr:row>46</xdr:row>
           <xdr:rowOff>15240</xdr:rowOff>
         </xdr:to>
@@ -4722,7 +4711,7 @@
         </xdr:from>
         <xdr:to>
           <xdr:col>10</xdr:col>
-          <xdr:colOff>163830</xdr:colOff>
+          <xdr:colOff>171450</xdr:colOff>
           <xdr:row>47</xdr:row>
           <xdr:rowOff>15240</xdr:rowOff>
         </xdr:to>
@@ -4789,7 +4778,7 @@
         </xdr:from>
         <xdr:to>
           <xdr:col>10</xdr:col>
-          <xdr:colOff>163830</xdr:colOff>
+          <xdr:colOff>171450</xdr:colOff>
           <xdr:row>48</xdr:row>
           <xdr:rowOff>15240</xdr:rowOff>
         </xdr:to>
@@ -4856,7 +4845,7 @@
         </xdr:from>
         <xdr:to>
           <xdr:col>10</xdr:col>
-          <xdr:colOff>163830</xdr:colOff>
+          <xdr:colOff>171450</xdr:colOff>
           <xdr:row>49</xdr:row>
           <xdr:rowOff>15240</xdr:rowOff>
         </xdr:to>
@@ -4923,7 +4912,7 @@
         </xdr:from>
         <xdr:to>
           <xdr:col>10</xdr:col>
-          <xdr:colOff>163830</xdr:colOff>
+          <xdr:colOff>171450</xdr:colOff>
           <xdr:row>50</xdr:row>
           <xdr:rowOff>15240</xdr:rowOff>
         </xdr:to>
@@ -4990,7 +4979,7 @@
         </xdr:from>
         <xdr:to>
           <xdr:col>10</xdr:col>
-          <xdr:colOff>163830</xdr:colOff>
+          <xdr:colOff>171450</xdr:colOff>
           <xdr:row>51</xdr:row>
           <xdr:rowOff>15240</xdr:rowOff>
         </xdr:to>
@@ -5057,7 +5046,7 @@
         </xdr:from>
         <xdr:to>
           <xdr:col>10</xdr:col>
-          <xdr:colOff>163830</xdr:colOff>
+          <xdr:colOff>171450</xdr:colOff>
           <xdr:row>52</xdr:row>
           <xdr:rowOff>15240</xdr:rowOff>
         </xdr:to>
@@ -7001,27 +6990,27 @@
   <dimension ref="A1:AJ658"/>
   <sheetFormatPr defaultColWidth="4" defaultRowHeight="13.2" zeroHeight="1"/>
   <cols>
-    <col min="1" max="1" width="6.109375" customWidth="1"/>
-    <col min="2" max="2" width="4" customWidth="1"/>
-    <col min="3" max="3" width="3.5546875" customWidth="1"/>
+    <col min="1" max="1" width="3.44140625" customWidth="1"/>
+    <col min="2" max="2" width="3" customWidth="1"/>
+    <col min="3" max="3" width="3.6640625" customWidth="1"/>
     <col min="4" max="4" width="4" customWidth="1"/>
-    <col min="5" max="5" width="6.109375" customWidth="1"/>
+    <col min="5" max="5" width="4.109375" customWidth="1"/>
     <col min="6" max="6" width="2.5546875" customWidth="1"/>
     <col min="7" max="7" width="2.44140625" customWidth="1"/>
     <col min="8" max="8" width="4.6640625" customWidth="1"/>
-    <col min="9" max="9" width="6.44140625" customWidth="1"/>
+    <col min="9" max="9" width="4.109375" customWidth="1"/>
     <col min="10" max="10" width="3" customWidth="1"/>
     <col min="11" max="11" width="4" customWidth="1"/>
     <col min="12" max="12" width="2.5546875" customWidth="1"/>
     <col min="13" max="13" width="0.109375" customWidth="1"/>
-    <col min="14" max="14" width="6.21875" customWidth="1"/>
+    <col min="14" max="14" width="3.88671875" customWidth="1"/>
     <col min="15" max="15" width="7" customWidth="1"/>
-    <col min="16" max="16" width="11.109375" customWidth="1"/>
+    <col min="16" max="16" width="8.5546875" customWidth="1"/>
     <col min="22" max="22" width="12" customWidth="1"/>
-    <col min="29" max="29" width="8.77734375" customWidth="1"/>
+    <col min="29" max="29" width="10.5546875" customWidth="1"/>
     <col min="31" max="31" width="2.88671875" bestFit="1" customWidth="1"/>
     <col min="32" max="32" width="5.21875" customWidth="1"/>
-    <col min="33" max="33" width="12.33203125" customWidth="1"/>
+    <col min="33" max="33" width="9.5546875" customWidth="1"/>
     <col min="35" max="35" width="11.77734375" customWidth="1"/>
   </cols>
   <sheetData>
@@ -7058,16 +7047,16 @@
       <c r="N2" s="31"/>
       <c r="O2" s="38"/>
       <c r="P2" s="38"/>
-      <c r="Q2" s="148"/>
-      <c r="R2" s="148"/>
-      <c r="S2" s="148"/>
-      <c r="T2" s="148"/>
-      <c r="U2" s="148"/>
-      <c r="V2" s="148"/>
-      <c r="W2" s="148"/>
-      <c r="X2" s="148"/>
-      <c r="Y2" s="148"/>
-      <c r="Z2" s="148"/>
+      <c r="Q2" s="68"/>
+      <c r="R2" s="68"/>
+      <c r="S2" s="68"/>
+      <c r="T2" s="68"/>
+      <c r="U2" s="68"/>
+      <c r="V2" s="68"/>
+      <c r="W2" s="68"/>
+      <c r="X2" s="68"/>
+      <c r="Y2" s="68"/>
+      <c r="Z2" s="68"/>
       <c r="AA2" s="38"/>
       <c r="AB2" s="38"/>
       <c r="AC2" s="38"/>
@@ -7093,28 +7082,28 @@
       <c r="K3" s="1"/>
       <c r="M3" s="31"/>
       <c r="N3" s="31"/>
-      <c r="Q3" s="149"/>
-      <c r="R3" s="149"/>
-      <c r="S3" s="149"/>
-      <c r="T3" s="149"/>
-      <c r="U3" s="149"/>
-      <c r="V3" s="149"/>
-      <c r="W3" s="149"/>
-      <c r="X3" s="149"/>
-      <c r="Y3" s="149"/>
-      <c r="Z3" s="149"/>
+      <c r="Q3" s="69"/>
+      <c r="R3" s="69"/>
+      <c r="S3" s="69"/>
+      <c r="T3" s="69"/>
+      <c r="U3" s="69"/>
+      <c r="V3" s="69"/>
+      <c r="W3" s="69"/>
+      <c r="X3" s="69"/>
+      <c r="Y3" s="69"/>
+      <c r="Z3" s="69"/>
       <c r="AA3" s="37"/>
       <c r="AB3" s="50" t="s">
         <v>95</v>
       </c>
       <c r="AC3" s="48"/>
-      <c r="AD3" s="160"/>
-      <c r="AE3" s="161"/>
-      <c r="AF3" s="161"/>
-      <c r="AG3" s="161"/>
-      <c r="AH3" s="161"/>
-      <c r="AI3" s="161"/>
-      <c r="AJ3" s="161"/>
+      <c r="AD3" s="58"/>
+      <c r="AE3" s="59"/>
+      <c r="AF3" s="59"/>
+      <c r="AG3" s="59"/>
+      <c r="AH3" s="59"/>
+      <c r="AI3" s="59"/>
+      <c r="AJ3" s="59"/>
     </row>
     <row r="4" spans="1:36" ht="18" customHeight="1">
       <c r="A4" s="30"/>
@@ -7145,304 +7134,304 @@
       </c>
     </row>
     <row r="5" spans="1:36" ht="18" customHeight="1">
-      <c r="A5" s="61" t="s">
+      <c r="A5" s="77" t="s">
         <v>85</v>
       </c>
-      <c r="B5" s="61"/>
-      <c r="C5" s="101"/>
-      <c r="D5" s="101"/>
-      <c r="E5" s="101"/>
-      <c r="F5" s="101"/>
-      <c r="G5" s="101"/>
-      <c r="H5" s="101"/>
-      <c r="I5" s="101"/>
+      <c r="B5" s="77"/>
+      <c r="C5" s="99"/>
+      <c r="D5" s="99"/>
+      <c r="E5" s="99"/>
+      <c r="F5" s="99"/>
+      <c r="G5" s="99"/>
+      <c r="H5" s="99"/>
+      <c r="I5" s="99"/>
       <c r="J5" s="35"/>
-      <c r="K5" s="153" t="s">
+      <c r="K5" s="60" t="s">
         <v>0</v>
       </c>
-      <c r="L5" s="153"/>
-      <c r="M5" s="153"/>
-      <c r="N5" s="153"/>
-      <c r="O5" s="153"/>
-      <c r="P5" s="162"/>
-      <c r="Q5" s="163"/>
-      <c r="R5" s="163"/>
-      <c r="S5" s="163"/>
-      <c r="T5" s="163"/>
-      <c r="U5" s="163"/>
-      <c r="V5" s="163"/>
-      <c r="W5" s="163"/>
-      <c r="X5" s="163"/>
-      <c r="Y5" s="153" t="s">
+      <c r="L5" s="60"/>
+      <c r="M5" s="60"/>
+      <c r="N5" s="60"/>
+      <c r="O5" s="60"/>
+      <c r="P5" s="61"/>
+      <c r="Q5" s="62"/>
+      <c r="R5" s="62"/>
+      <c r="S5" s="62"/>
+      <c r="T5" s="62"/>
+      <c r="U5" s="62"/>
+      <c r="V5" s="62"/>
+      <c r="W5" s="62"/>
+      <c r="X5" s="62"/>
+      <c r="Y5" s="60" t="s">
         <v>48</v>
       </c>
-      <c r="Z5" s="153"/>
-      <c r="AA5" s="101"/>
-      <c r="AB5" s="101"/>
-      <c r="AC5" s="101"/>
-      <c r="AD5" s="101"/>
-      <c r="AE5" s="101"/>
-      <c r="AF5" s="101"/>
-      <c r="AG5" s="101"/>
-      <c r="AH5" s="101"/>
-      <c r="AI5" s="101"/>
-      <c r="AJ5" s="101"/>
+      <c r="Z5" s="60"/>
+      <c r="AA5" s="99"/>
+      <c r="AB5" s="99"/>
+      <c r="AC5" s="99"/>
+      <c r="AD5" s="99"/>
+      <c r="AE5" s="99"/>
+      <c r="AF5" s="99"/>
+      <c r="AG5" s="99"/>
+      <c r="AH5" s="99"/>
+      <c r="AI5" s="99"/>
+      <c r="AJ5" s="99"/>
     </row>
     <row r="6" spans="1:36" ht="18" customHeight="1">
-      <c r="A6" s="61" t="s">
+      <c r="A6" s="77" t="s">
         <v>1</v>
       </c>
-      <c r="B6" s="61"/>
-      <c r="C6" s="159"/>
-      <c r="D6" s="159"/>
-      <c r="E6" s="159"/>
-      <c r="F6" s="159"/>
-      <c r="G6" s="159"/>
-      <c r="H6" s="159"/>
-      <c r="I6" s="159"/>
+      <c r="B6" s="77"/>
+      <c r="C6" s="65"/>
+      <c r="D6" s="65"/>
+      <c r="E6" s="65"/>
+      <c r="F6" s="65"/>
+      <c r="G6" s="65"/>
+      <c r="H6" s="65"/>
+      <c r="I6" s="65"/>
       <c r="J6" s="35"/>
-      <c r="K6" s="153" t="s">
+      <c r="K6" s="60" t="s">
         <v>2</v>
       </c>
-      <c r="L6" s="153"/>
-      <c r="M6" s="153"/>
-      <c r="N6" s="153"/>
-      <c r="O6" s="153"/>
-      <c r="P6" s="154"/>
-      <c r="Q6" s="155"/>
-      <c r="R6" s="155"/>
-      <c r="S6" s="155"/>
-      <c r="T6" s="155"/>
-      <c r="U6" s="155"/>
-      <c r="V6" s="155"/>
-      <c r="W6" s="155"/>
-      <c r="X6" s="155"/>
+      <c r="L6" s="60"/>
+      <c r="M6" s="60"/>
+      <c r="N6" s="60"/>
+      <c r="O6" s="60"/>
+      <c r="P6" s="73"/>
+      <c r="Q6" s="74"/>
+      <c r="R6" s="74"/>
+      <c r="S6" s="74"/>
+      <c r="T6" s="74"/>
+      <c r="U6" s="74"/>
+      <c r="V6" s="74"/>
+      <c r="W6" s="74"/>
+      <c r="X6" s="74"/>
       <c r="Y6" s="56" t="s">
         <v>88</v>
       </c>
       <c r="Z6" s="56"/>
       <c r="AA6" s="56"/>
       <c r="AB6" s="56"/>
-      <c r="AC6" s="166"/>
-      <c r="AD6" s="166"/>
-      <c r="AE6" s="165"/>
-      <c r="AF6" s="165"/>
+      <c r="AC6" s="167"/>
+      <c r="AD6" s="167"/>
+      <c r="AE6" s="57"/>
+      <c r="AF6" s="57"/>
       <c r="AG6" s="44"/>
-      <c r="AH6" s="136"/>
-      <c r="AI6" s="136"/>
+      <c r="AH6" s="166"/>
+      <c r="AI6" s="166"/>
       <c r="AJ6" s="44"/>
     </row>
     <row r="7" spans="1:36" ht="18" customHeight="1">
-      <c r="A7" s="61" t="s">
+      <c r="A7" s="77" t="s">
         <v>3</v>
       </c>
-      <c r="B7" s="61"/>
-      <c r="C7" s="159"/>
-      <c r="D7" s="159"/>
-      <c r="E7" s="159"/>
-      <c r="F7" s="159"/>
-      <c r="G7" s="159"/>
-      <c r="H7" s="159"/>
-      <c r="I7" s="159"/>
+      <c r="B7" s="77"/>
+      <c r="C7" s="65"/>
+      <c r="D7" s="65"/>
+      <c r="E7" s="65"/>
+      <c r="F7" s="65"/>
+      <c r="G7" s="65"/>
+      <c r="H7" s="65"/>
+      <c r="I7" s="65"/>
       <c r="J7" s="35"/>
-      <c r="K7" s="153" t="s">
+      <c r="K7" s="60" t="s">
         <v>89</v>
       </c>
-      <c r="L7" s="153"/>
-      <c r="M7" s="153"/>
-      <c r="N7" s="153"/>
-      <c r="O7" s="153"/>
-      <c r="P7" s="79"/>
-      <c r="Q7" s="79"/>
-      <c r="R7" s="79"/>
-      <c r="S7" s="136"/>
-      <c r="T7" s="136"/>
+      <c r="L7" s="60"/>
+      <c r="M7" s="60"/>
+      <c r="N7" s="60"/>
+      <c r="O7" s="60"/>
+      <c r="P7" s="63"/>
+      <c r="Q7" s="63"/>
+      <c r="R7" s="63"/>
+      <c r="S7" s="63"/>
+      <c r="T7" s="63"/>
       <c r="U7" s="39" t="s">
         <v>4</v>
       </c>
-      <c r="V7" s="136"/>
-      <c r="W7" s="136"/>
-      <c r="X7" s="153" t="s">
+      <c r="V7" s="63"/>
+      <c r="W7" s="63"/>
+      <c r="X7" s="60" t="s">
         <v>90</v>
       </c>
-      <c r="Y7" s="153"/>
-      <c r="Z7" s="153"/>
-      <c r="AA7" s="153"/>
-      <c r="AB7" s="153"/>
-      <c r="AC7" s="79"/>
-      <c r="AD7" s="79"/>
-      <c r="AE7" s="79"/>
-      <c r="AF7" s="136"/>
-      <c r="AG7" s="136"/>
+      <c r="Y7" s="60"/>
+      <c r="Z7" s="60"/>
+      <c r="AA7" s="60"/>
+      <c r="AB7" s="60"/>
+      <c r="AC7" s="167"/>
+      <c r="AD7" s="167"/>
+      <c r="AE7" s="167"/>
+      <c r="AF7" s="166"/>
+      <c r="AG7" s="166"/>
       <c r="AH7" s="39" t="s">
         <v>4</v>
       </c>
-      <c r="AI7" s="136"/>
-      <c r="AJ7" s="136"/>
+      <c r="AI7" s="63"/>
+      <c r="AJ7" s="63"/>
     </row>
     <row r="8" spans="1:36" ht="18" customHeight="1">
-      <c r="A8" s="86" t="s">
+      <c r="A8" s="81" t="s">
         <v>5</v>
       </c>
-      <c r="B8" s="86"/>
-      <c r="C8" s="86"/>
-      <c r="D8" s="96"/>
-      <c r="E8" s="96"/>
-      <c r="F8" s="96"/>
-      <c r="G8" s="96"/>
-      <c r="H8" s="96"/>
-      <c r="I8" s="96"/>
-      <c r="J8" s="96"/>
-      <c r="K8" s="96"/>
-      <c r="L8" s="96"/>
-      <c r="M8" s="96"/>
-      <c r="N8" s="96"/>
-      <c r="O8" s="96"/>
-      <c r="P8" s="96"/>
-      <c r="Q8" s="96"/>
-      <c r="R8" s="96"/>
-      <c r="S8" s="164" t="s">
+      <c r="B8" s="81"/>
+      <c r="C8" s="81"/>
+      <c r="D8" s="67"/>
+      <c r="E8" s="67"/>
+      <c r="F8" s="67"/>
+      <c r="G8" s="67"/>
+      <c r="H8" s="67"/>
+      <c r="I8" s="67"/>
+      <c r="J8" s="67"/>
+      <c r="K8" s="67"/>
+      <c r="L8" s="67"/>
+      <c r="M8" s="67"/>
+      <c r="N8" s="67"/>
+      <c r="O8" s="67"/>
+      <c r="P8" s="67"/>
+      <c r="Q8" s="67"/>
+      <c r="R8" s="67"/>
+      <c r="S8" s="66" t="s">
         <v>49</v>
       </c>
-      <c r="T8" s="164"/>
-      <c r="U8" s="153"/>
-      <c r="V8" s="164"/>
-      <c r="W8" s="164"/>
-      <c r="X8" s="96"/>
-      <c r="Y8" s="96"/>
-      <c r="Z8" s="96"/>
-      <c r="AA8" s="96"/>
-      <c r="AB8" s="96"/>
-      <c r="AC8" s="96"/>
-      <c r="AD8" s="96"/>
-      <c r="AE8" s="96"/>
-      <c r="AF8" s="96"/>
-      <c r="AG8" s="96"/>
-      <c r="AH8" s="96"/>
-      <c r="AI8" s="96"/>
-      <c r="AJ8" s="96"/>
+      <c r="T8" s="66"/>
+      <c r="U8" s="60"/>
+      <c r="V8" s="66"/>
+      <c r="W8" s="66"/>
+      <c r="X8" s="67"/>
+      <c r="Y8" s="67"/>
+      <c r="Z8" s="67"/>
+      <c r="AA8" s="67"/>
+      <c r="AB8" s="67"/>
+      <c r="AC8" s="67"/>
+      <c r="AD8" s="67"/>
+      <c r="AE8" s="67"/>
+      <c r="AF8" s="67"/>
+      <c r="AG8" s="67"/>
+      <c r="AH8" s="67"/>
+      <c r="AI8" s="67"/>
+      <c r="AJ8" s="67"/>
     </row>
     <row r="9" spans="1:36" ht="26.4" customHeight="1">
-      <c r="A9" s="61" t="s">
+      <c r="A9" s="77" t="s">
         <v>6</v>
       </c>
-      <c r="B9" s="61"/>
-      <c r="C9" s="61"/>
-      <c r="D9" s="147"/>
-      <c r="E9" s="147"/>
-      <c r="F9" s="147"/>
-      <c r="G9" s="147"/>
-      <c r="H9" s="147"/>
-      <c r="I9" s="147"/>
-      <c r="J9" s="147"/>
-      <c r="K9" s="147"/>
-      <c r="L9" s="147"/>
-      <c r="M9" s="147"/>
-      <c r="N9" s="147"/>
-      <c r="O9" s="147"/>
-      <c r="P9" s="147"/>
-      <c r="Q9" s="147"/>
-      <c r="R9" s="147"/>
-      <c r="S9" s="153" t="s">
+      <c r="B9" s="77"/>
+      <c r="C9" s="77"/>
+      <c r="D9" s="83"/>
+      <c r="E9" s="83"/>
+      <c r="F9" s="83"/>
+      <c r="G9" s="83"/>
+      <c r="H9" s="83"/>
+      <c r="I9" s="83"/>
+      <c r="J9" s="83"/>
+      <c r="K9" s="83"/>
+      <c r="L9" s="83"/>
+      <c r="M9" s="83"/>
+      <c r="N9" s="83"/>
+      <c r="O9" s="83"/>
+      <c r="P9" s="83"/>
+      <c r="Q9" s="83"/>
+      <c r="R9" s="83"/>
+      <c r="S9" s="60" t="s">
         <v>50</v>
       </c>
-      <c r="T9" s="153"/>
-      <c r="U9" s="153"/>
-      <c r="V9" s="153"/>
-      <c r="W9" s="153"/>
-      <c r="X9" s="146"/>
-      <c r="Y9" s="147"/>
-      <c r="Z9" s="147"/>
-      <c r="AA9" s="147"/>
-      <c r="AB9" s="147"/>
-      <c r="AC9" s="147"/>
-      <c r="AD9" s="147"/>
-      <c r="AE9" s="147"/>
-      <c r="AF9" s="147"/>
-      <c r="AG9" s="147"/>
-      <c r="AH9" s="147"/>
-      <c r="AI9" s="147"/>
-      <c r="AJ9" s="147"/>
+      <c r="T9" s="60"/>
+      <c r="U9" s="60"/>
+      <c r="V9" s="60"/>
+      <c r="W9" s="60"/>
+      <c r="X9" s="122"/>
+      <c r="Y9" s="83"/>
+      <c r="Z9" s="83"/>
+      <c r="AA9" s="83"/>
+      <c r="AB9" s="83"/>
+      <c r="AC9" s="83"/>
+      <c r="AD9" s="83"/>
+      <c r="AE9" s="83"/>
+      <c r="AF9" s="83"/>
+      <c r="AG9" s="83"/>
+      <c r="AH9" s="83"/>
+      <c r="AI9" s="83"/>
+      <c r="AJ9" s="83"/>
     </row>
     <row r="10" spans="1:36" ht="5.25" customHeight="1">
-      <c r="A10" s="89"/>
-      <c r="B10" s="89"/>
-      <c r="C10" s="89"/>
-      <c r="D10" s="89"/>
-      <c r="E10" s="89"/>
-      <c r="F10" s="89"/>
-      <c r="G10" s="89"/>
-      <c r="H10" s="89"/>
-      <c r="I10" s="89"/>
-      <c r="J10" s="89"/>
-      <c r="K10" s="89"/>
-      <c r="L10" s="89"/>
-      <c r="M10" s="89"/>
-      <c r="N10" s="89"/>
-      <c r="O10" s="89"/>
-      <c r="P10" s="89"/>
-      <c r="Q10" s="89"/>
-      <c r="R10" s="89"/>
-      <c r="S10" s="89"/>
-      <c r="T10" s="89"/>
-      <c r="U10" s="89"/>
-      <c r="V10" s="89"/>
-      <c r="W10" s="89"/>
-      <c r="X10" s="89"/>
-      <c r="Y10" s="89"/>
-      <c r="Z10" s="89"/>
-      <c r="AA10" s="89"/>
-      <c r="AB10" s="89"/>
-      <c r="AC10" s="89"/>
-      <c r="AD10" s="89"/>
-      <c r="AE10" s="89"/>
-      <c r="AF10" s="89"/>
-      <c r="AG10" s="89"/>
-      <c r="AH10" s="89"/>
-      <c r="AI10" s="89"/>
-      <c r="AJ10" s="89"/>
+      <c r="A10" s="82"/>
+      <c r="B10" s="82"/>
+      <c r="C10" s="82"/>
+      <c r="D10" s="82"/>
+      <c r="E10" s="82"/>
+      <c r="F10" s="82"/>
+      <c r="G10" s="82"/>
+      <c r="H10" s="82"/>
+      <c r="I10" s="82"/>
+      <c r="J10" s="82"/>
+      <c r="K10" s="82"/>
+      <c r="L10" s="82"/>
+      <c r="M10" s="82"/>
+      <c r="N10" s="82"/>
+      <c r="O10" s="82"/>
+      <c r="P10" s="82"/>
+      <c r="Q10" s="82"/>
+      <c r="R10" s="82"/>
+      <c r="S10" s="82"/>
+      <c r="T10" s="82"/>
+      <c r="U10" s="82"/>
+      <c r="V10" s="82"/>
+      <c r="W10" s="82"/>
+      <c r="X10" s="82"/>
+      <c r="Y10" s="82"/>
+      <c r="Z10" s="82"/>
+      <c r="AA10" s="82"/>
+      <c r="AB10" s="82"/>
+      <c r="AC10" s="82"/>
+      <c r="AD10" s="82"/>
+      <c r="AE10" s="82"/>
+      <c r="AF10" s="82"/>
+      <c r="AG10" s="82"/>
+      <c r="AH10" s="82"/>
+      <c r="AI10" s="82"/>
+      <c r="AJ10" s="82"/>
     </row>
     <row r="11" spans="1:36" ht="14.25" customHeight="1">
-      <c r="A11" s="150" t="s">
+      <c r="A11" s="70" t="s">
         <v>7</v>
       </c>
-      <c r="B11" s="151"/>
-      <c r="C11" s="151"/>
-      <c r="D11" s="151"/>
-      <c r="E11" s="151"/>
-      <c r="F11" s="151"/>
-      <c r="G11" s="151"/>
-      <c r="H11" s="151"/>
-      <c r="I11" s="151"/>
-      <c r="J11" s="151"/>
-      <c r="K11" s="151"/>
-      <c r="L11" s="151"/>
-      <c r="M11" s="151"/>
-      <c r="N11" s="151"/>
-      <c r="O11" s="151"/>
-      <c r="P11" s="152"/>
-      <c r="Q11" s="156" t="s">
+      <c r="B11" s="71"/>
+      <c r="C11" s="71"/>
+      <c r="D11" s="71"/>
+      <c r="E11" s="71"/>
+      <c r="F11" s="71"/>
+      <c r="G11" s="71"/>
+      <c r="H11" s="71"/>
+      <c r="I11" s="71"/>
+      <c r="J11" s="71"/>
+      <c r="K11" s="71"/>
+      <c r="L11" s="71"/>
+      <c r="M11" s="71"/>
+      <c r="N11" s="71"/>
+      <c r="O11" s="71"/>
+      <c r="P11" s="72"/>
+      <c r="Q11" s="78" t="s">
         <v>8</v>
       </c>
-      <c r="R11" s="157"/>
-      <c r="S11" s="157"/>
-      <c r="T11" s="157"/>
-      <c r="U11" s="157"/>
-      <c r="V11" s="157"/>
-      <c r="W11" s="157"/>
-      <c r="X11" s="157"/>
-      <c r="Y11" s="157"/>
-      <c r="Z11" s="157"/>
-      <c r="AA11" s="157"/>
-      <c r="AB11" s="157"/>
-      <c r="AC11" s="157"/>
-      <c r="AD11" s="157"/>
-      <c r="AE11" s="157"/>
-      <c r="AF11" s="157"/>
-      <c r="AG11" s="157"/>
-      <c r="AH11" s="157"/>
-      <c r="AI11" s="157"/>
-      <c r="AJ11" s="158"/>
+      <c r="R11" s="79"/>
+      <c r="S11" s="79"/>
+      <c r="T11" s="79"/>
+      <c r="U11" s="79"/>
+      <c r="V11" s="79"/>
+      <c r="W11" s="79"/>
+      <c r="X11" s="79"/>
+      <c r="Y11" s="79"/>
+      <c r="Z11" s="79"/>
+      <c r="AA11" s="79"/>
+      <c r="AB11" s="79"/>
+      <c r="AC11" s="79"/>
+      <c r="AD11" s="79"/>
+      <c r="AE11" s="79"/>
+      <c r="AF11" s="79"/>
+      <c r="AG11" s="79"/>
+      <c r="AH11" s="79"/>
+      <c r="AI11" s="79"/>
+      <c r="AJ11" s="80"/>
     </row>
     <row r="12" spans="1:36" ht="18" customHeight="1">
       <c r="A12" s="2"/>
@@ -7551,150 +7540,150 @@
       <c r="AJ13" s="23"/>
     </row>
     <row r="14" spans="1:36" ht="16.5" customHeight="1">
-      <c r="A14" s="128" t="s">
+      <c r="A14" s="105" t="s">
         <v>86</v>
       </c>
-      <c r="B14" s="129"/>
-      <c r="C14" s="129"/>
-      <c r="D14" s="129"/>
-      <c r="E14" s="129"/>
-      <c r="F14" s="129"/>
-      <c r="G14" s="129"/>
-      <c r="H14" s="129"/>
-      <c r="I14" s="130"/>
-      <c r="J14" s="131"/>
-      <c r="K14" s="131"/>
-      <c r="L14" s="131"/>
-      <c r="M14" s="131"/>
-      <c r="N14" s="131"/>
-      <c r="O14" s="131"/>
-      <c r="P14" s="131"/>
-      <c r="Q14" s="131"/>
-      <c r="R14" s="131"/>
-      <c r="S14" s="131"/>
-      <c r="T14" s="131"/>
-      <c r="U14" s="131"/>
-      <c r="V14" s="131"/>
-      <c r="W14" s="131"/>
-      <c r="X14" s="131"/>
-      <c r="Y14" s="131"/>
-      <c r="Z14" s="131"/>
-      <c r="AA14" s="131"/>
-      <c r="AB14" s="131"/>
-      <c r="AC14" s="131"/>
-      <c r="AD14" s="131"/>
-      <c r="AE14" s="131"/>
-      <c r="AF14" s="131"/>
-      <c r="AG14" s="131"/>
-      <c r="AH14" s="131"/>
-      <c r="AI14" s="131"/>
-      <c r="AJ14" s="132"/>
+      <c r="B14" s="106"/>
+      <c r="C14" s="106"/>
+      <c r="D14" s="106"/>
+      <c r="E14" s="106"/>
+      <c r="F14" s="106"/>
+      <c r="G14" s="106"/>
+      <c r="H14" s="106"/>
+      <c r="I14" s="107"/>
+      <c r="J14" s="108"/>
+      <c r="K14" s="108"/>
+      <c r="L14" s="108"/>
+      <c r="M14" s="108"/>
+      <c r="N14" s="108"/>
+      <c r="O14" s="108"/>
+      <c r="P14" s="108"/>
+      <c r="Q14" s="108"/>
+      <c r="R14" s="108"/>
+      <c r="S14" s="108"/>
+      <c r="T14" s="108"/>
+      <c r="U14" s="108"/>
+      <c r="V14" s="108"/>
+      <c r="W14" s="108"/>
+      <c r="X14" s="108"/>
+      <c r="Y14" s="108"/>
+      <c r="Z14" s="108"/>
+      <c r="AA14" s="108"/>
+      <c r="AB14" s="108"/>
+      <c r="AC14" s="108"/>
+      <c r="AD14" s="108"/>
+      <c r="AE14" s="108"/>
+      <c r="AF14" s="108"/>
+      <c r="AG14" s="108"/>
+      <c r="AH14" s="108"/>
+      <c r="AI14" s="108"/>
+      <c r="AJ14" s="109"/>
     </row>
     <row r="15" spans="1:36" ht="3" customHeight="1">
-      <c r="A15" s="133">
+      <c r="A15" s="110">
         <v>2</v>
       </c>
-      <c r="B15" s="134"/>
-      <c r="C15" s="134"/>
-      <c r="D15" s="134"/>
-      <c r="E15" s="134"/>
-      <c r="F15" s="134"/>
-      <c r="G15" s="134"/>
-      <c r="H15" s="134"/>
-      <c r="I15" s="134"/>
-      <c r="J15" s="134"/>
-      <c r="K15" s="134"/>
-      <c r="L15" s="134"/>
-      <c r="M15" s="134"/>
-      <c r="N15" s="134"/>
-      <c r="O15" s="134"/>
-      <c r="P15" s="134"/>
-      <c r="Q15" s="134"/>
-      <c r="R15" s="134"/>
-      <c r="S15" s="134"/>
-      <c r="T15" s="134"/>
-      <c r="U15" s="134"/>
-      <c r="V15" s="134"/>
-      <c r="W15" s="134"/>
-      <c r="X15" s="134"/>
-      <c r="Y15" s="134"/>
-      <c r="Z15" s="134"/>
-      <c r="AA15" s="134"/>
-      <c r="AB15" s="134"/>
-      <c r="AC15" s="134"/>
-      <c r="AD15" s="134"/>
-      <c r="AE15" s="134"/>
-      <c r="AF15" s="134"/>
-      <c r="AG15" s="134"/>
-      <c r="AH15" s="134"/>
-      <c r="AI15" s="134"/>
-      <c r="AJ15" s="135"/>
+      <c r="B15" s="111"/>
+      <c r="C15" s="111"/>
+      <c r="D15" s="111"/>
+      <c r="E15" s="111"/>
+      <c r="F15" s="111"/>
+      <c r="G15" s="111"/>
+      <c r="H15" s="111"/>
+      <c r="I15" s="111"/>
+      <c r="J15" s="111"/>
+      <c r="K15" s="111"/>
+      <c r="L15" s="111"/>
+      <c r="M15" s="111"/>
+      <c r="N15" s="111"/>
+      <c r="O15" s="111"/>
+      <c r="P15" s="111"/>
+      <c r="Q15" s="111"/>
+      <c r="R15" s="111"/>
+      <c r="S15" s="111"/>
+      <c r="T15" s="111"/>
+      <c r="U15" s="111"/>
+      <c r="V15" s="111"/>
+      <c r="W15" s="111"/>
+      <c r="X15" s="111"/>
+      <c r="Y15" s="111"/>
+      <c r="Z15" s="111"/>
+      <c r="AA15" s="111"/>
+      <c r="AB15" s="111"/>
+      <c r="AC15" s="111"/>
+      <c r="AD15" s="111"/>
+      <c r="AE15" s="111"/>
+      <c r="AF15" s="111"/>
+      <c r="AG15" s="111"/>
+      <c r="AH15" s="111"/>
+      <c r="AI15" s="111"/>
+      <c r="AJ15" s="112"/>
     </row>
     <row r="16" spans="1:36" ht="12.75" customHeight="1">
-      <c r="A16" s="143" t="s">
+      <c r="A16" s="119" t="s">
         <v>9</v>
       </c>
-      <c r="B16" s="144"/>
-      <c r="C16" s="144"/>
-      <c r="D16" s="144"/>
-      <c r="E16" s="144"/>
-      <c r="F16" s="144"/>
-      <c r="G16" s="144"/>
-      <c r="H16" s="144"/>
-      <c r="I16" s="144"/>
-      <c r="J16" s="144"/>
-      <c r="K16" s="144"/>
-      <c r="L16" s="144"/>
-      <c r="M16" s="144"/>
-      <c r="N16" s="144"/>
-      <c r="O16" s="144"/>
-      <c r="P16" s="144"/>
-      <c r="Q16" s="144"/>
-      <c r="R16" s="144"/>
-      <c r="S16" s="144"/>
-      <c r="T16" s="145"/>
-      <c r="U16" s="137" t="s">
+      <c r="B16" s="120"/>
+      <c r="C16" s="120"/>
+      <c r="D16" s="120"/>
+      <c r="E16" s="120"/>
+      <c r="F16" s="120"/>
+      <c r="G16" s="120"/>
+      <c r="H16" s="120"/>
+      <c r="I16" s="120"/>
+      <c r="J16" s="120"/>
+      <c r="K16" s="120"/>
+      <c r="L16" s="120"/>
+      <c r="M16" s="120"/>
+      <c r="N16" s="120"/>
+      <c r="O16" s="120"/>
+      <c r="P16" s="120"/>
+      <c r="Q16" s="120"/>
+      <c r="R16" s="120"/>
+      <c r="S16" s="120"/>
+      <c r="T16" s="121"/>
+      <c r="U16" s="113" t="s">
         <v>73</v>
       </c>
-      <c r="V16" s="138"/>
-      <c r="W16" s="138"/>
-      <c r="X16" s="138"/>
-      <c r="Y16" s="138"/>
-      <c r="Z16" s="138"/>
-      <c r="AA16" s="138"/>
-      <c r="AB16" s="138"/>
-      <c r="AC16" s="138"/>
-      <c r="AD16" s="139"/>
-      <c r="AE16" s="140" t="s">
+      <c r="V16" s="114"/>
+      <c r="W16" s="114"/>
+      <c r="X16" s="114"/>
+      <c r="Y16" s="114"/>
+      <c r="Z16" s="114"/>
+      <c r="AA16" s="114"/>
+      <c r="AB16" s="114"/>
+      <c r="AC16" s="114"/>
+      <c r="AD16" s="115"/>
+      <c r="AE16" s="116" t="s">
         <v>10</v>
       </c>
-      <c r="AF16" s="141"/>
-      <c r="AG16" s="141"/>
-      <c r="AH16" s="141"/>
-      <c r="AI16" s="141"/>
-      <c r="AJ16" s="142"/>
+      <c r="AF16" s="117"/>
+      <c r="AG16" s="117"/>
+      <c r="AH16" s="117"/>
+      <c r="AI16" s="117"/>
+      <c r="AJ16" s="118"/>
     </row>
     <row r="17" spans="1:36" ht="18" customHeight="1">
-      <c r="A17" s="121"/>
-      <c r="B17" s="122"/>
-      <c r="C17" s="122"/>
-      <c r="D17" s="122"/>
-      <c r="E17" s="122"/>
-      <c r="F17" s="122"/>
-      <c r="G17" s="122"/>
-      <c r="H17" s="122"/>
-      <c r="I17" s="122"/>
-      <c r="J17" s="122"/>
-      <c r="K17" s="122"/>
-      <c r="L17" s="122"/>
-      <c r="M17" s="122"/>
-      <c r="N17" s="122"/>
-      <c r="O17" s="122"/>
-      <c r="P17" s="122"/>
-      <c r="Q17" s="122"/>
-      <c r="R17" s="122"/>
-      <c r="S17" s="122"/>
-      <c r="T17" s="123"/>
+      <c r="A17" s="93"/>
+      <c r="B17" s="94"/>
+      <c r="C17" s="94"/>
+      <c r="D17" s="94"/>
+      <c r="E17" s="94"/>
+      <c r="F17" s="94"/>
+      <c r="G17" s="94"/>
+      <c r="H17" s="94"/>
+      <c r="I17" s="94"/>
+      <c r="J17" s="94"/>
+      <c r="K17" s="94"/>
+      <c r="L17" s="94"/>
+      <c r="M17" s="94"/>
+      <c r="N17" s="94"/>
+      <c r="O17" s="94"/>
+      <c r="P17" s="94"/>
+      <c r="Q17" s="94"/>
+      <c r="R17" s="94"/>
+      <c r="S17" s="94"/>
+      <c r="T17" s="95"/>
       <c r="U17" s="25"/>
       <c r="V17" s="17" t="s">
         <v>64</v>
@@ -7710,32 +7699,32 @@
       <c r="AE17" s="14" t="s">
         <v>11</v>
       </c>
-      <c r="AF17" s="104"/>
-      <c r="AG17" s="104"/>
-      <c r="AI17" s="104"/>
-      <c r="AJ17" s="127"/>
+      <c r="AF17" s="100"/>
+      <c r="AG17" s="100"/>
+      <c r="AI17" s="100"/>
+      <c r="AJ17" s="104"/>
     </row>
     <row r="18" spans="1:36" ht="18" customHeight="1">
-      <c r="A18" s="121"/>
-      <c r="B18" s="122"/>
-      <c r="C18" s="122"/>
-      <c r="D18" s="122"/>
-      <c r="E18" s="122"/>
-      <c r="F18" s="122"/>
-      <c r="G18" s="122"/>
-      <c r="H18" s="122"/>
-      <c r="I18" s="122"/>
-      <c r="J18" s="122"/>
-      <c r="K18" s="122"/>
-      <c r="L18" s="122"/>
-      <c r="M18" s="122"/>
-      <c r="N18" s="122"/>
-      <c r="O18" s="122"/>
-      <c r="P18" s="122"/>
-      <c r="Q18" s="122"/>
-      <c r="R18" s="122"/>
-      <c r="S18" s="122"/>
-      <c r="T18" s="123"/>
+      <c r="A18" s="93"/>
+      <c r="B18" s="94"/>
+      <c r="C18" s="94"/>
+      <c r="D18" s="94"/>
+      <c r="E18" s="94"/>
+      <c r="F18" s="94"/>
+      <c r="G18" s="94"/>
+      <c r="H18" s="94"/>
+      <c r="I18" s="94"/>
+      <c r="J18" s="94"/>
+      <c r="K18" s="94"/>
+      <c r="L18" s="94"/>
+      <c r="M18" s="94"/>
+      <c r="N18" s="94"/>
+      <c r="O18" s="94"/>
+      <c r="P18" s="94"/>
+      <c r="Q18" s="94"/>
+      <c r="R18" s="94"/>
+      <c r="S18" s="94"/>
+      <c r="T18" s="95"/>
       <c r="U18" s="26"/>
       <c r="V18" s="17" t="s">
         <v>65</v>
@@ -7751,32 +7740,32 @@
       <c r="AE18" s="14" t="s">
         <v>12</v>
       </c>
-      <c r="AF18" s="104"/>
-      <c r="AG18" s="104"/>
-      <c r="AI18" s="104"/>
-      <c r="AJ18" s="127"/>
+      <c r="AF18" s="100"/>
+      <c r="AG18" s="100"/>
+      <c r="AI18" s="100"/>
+      <c r="AJ18" s="104"/>
     </row>
     <row r="19" spans="1:36" ht="18" customHeight="1">
-      <c r="A19" s="121"/>
-      <c r="B19" s="122"/>
-      <c r="C19" s="122"/>
-      <c r="D19" s="122"/>
-      <c r="E19" s="122"/>
-      <c r="F19" s="122"/>
-      <c r="G19" s="122"/>
-      <c r="H19" s="122"/>
-      <c r="I19" s="122"/>
-      <c r="J19" s="122"/>
-      <c r="K19" s="122"/>
-      <c r="L19" s="122"/>
-      <c r="M19" s="122"/>
-      <c r="N19" s="122"/>
-      <c r="O19" s="122"/>
-      <c r="P19" s="122"/>
-      <c r="Q19" s="122"/>
-      <c r="R19" s="122"/>
-      <c r="S19" s="122"/>
-      <c r="T19" s="123"/>
+      <c r="A19" s="93"/>
+      <c r="B19" s="94"/>
+      <c r="C19" s="94"/>
+      <c r="D19" s="94"/>
+      <c r="E19" s="94"/>
+      <c r="F19" s="94"/>
+      <c r="G19" s="94"/>
+      <c r="H19" s="94"/>
+      <c r="I19" s="94"/>
+      <c r="J19" s="94"/>
+      <c r="K19" s="94"/>
+      <c r="L19" s="94"/>
+      <c r="M19" s="94"/>
+      <c r="N19" s="94"/>
+      <c r="O19" s="94"/>
+      <c r="P19" s="94"/>
+      <c r="Q19" s="94"/>
+      <c r="R19" s="94"/>
+      <c r="S19" s="94"/>
+      <c r="T19" s="95"/>
       <c r="U19" s="26"/>
       <c r="V19" s="17" t="s">
         <v>66</v>
@@ -7792,32 +7781,32 @@
       <c r="AE19" s="14" t="s">
         <v>13</v>
       </c>
-      <c r="AF19" s="104"/>
-      <c r="AG19" s="104"/>
-      <c r="AI19" s="104"/>
-      <c r="AJ19" s="127"/>
+      <c r="AF19" s="100"/>
+      <c r="AG19" s="100"/>
+      <c r="AI19" s="100"/>
+      <c r="AJ19" s="104"/>
     </row>
     <row r="20" spans="1:36" ht="3.75" customHeight="1">
-      <c r="A20" s="124"/>
-      <c r="B20" s="125"/>
-      <c r="C20" s="125"/>
-      <c r="D20" s="125"/>
-      <c r="E20" s="125"/>
-      <c r="F20" s="125"/>
-      <c r="G20" s="125"/>
-      <c r="H20" s="125"/>
-      <c r="I20" s="125"/>
-      <c r="J20" s="125"/>
-      <c r="K20" s="125"/>
-      <c r="L20" s="125"/>
-      <c r="M20" s="125"/>
-      <c r="N20" s="125"/>
-      <c r="O20" s="125"/>
-      <c r="P20" s="125"/>
-      <c r="Q20" s="125"/>
-      <c r="R20" s="125"/>
-      <c r="S20" s="125"/>
-      <c r="T20" s="126"/>
+      <c r="A20" s="96"/>
+      <c r="B20" s="97"/>
+      <c r="C20" s="97"/>
+      <c r="D20" s="97"/>
+      <c r="E20" s="97"/>
+      <c r="F20" s="97"/>
+      <c r="G20" s="97"/>
+      <c r="H20" s="97"/>
+      <c r="I20" s="97"/>
+      <c r="J20" s="97"/>
+      <c r="K20" s="97"/>
+      <c r="L20" s="97"/>
+      <c r="M20" s="97"/>
+      <c r="N20" s="97"/>
+      <c r="O20" s="97"/>
+      <c r="P20" s="97"/>
+      <c r="Q20" s="97"/>
+      <c r="R20" s="97"/>
+      <c r="S20" s="97"/>
+      <c r="T20" s="98"/>
       <c r="U20" s="27"/>
       <c r="V20" s="16"/>
       <c r="W20" s="7"/>
@@ -7876,80 +7865,80 @@
       <c r="AJ21" s="47"/>
     </row>
     <row r="22" spans="1:36" ht="16.5" customHeight="1">
-      <c r="A22" s="115"/>
-      <c r="B22" s="116"/>
-      <c r="C22" s="116"/>
-      <c r="D22" s="116"/>
-      <c r="E22" s="116"/>
-      <c r="F22" s="116"/>
-      <c r="G22" s="116"/>
-      <c r="H22" s="116"/>
-      <c r="I22" s="116"/>
-      <c r="J22" s="116"/>
-      <c r="K22" s="116"/>
-      <c r="L22" s="116"/>
-      <c r="M22" s="116"/>
-      <c r="N22" s="116"/>
-      <c r="O22" s="116"/>
-      <c r="P22" s="116"/>
-      <c r="Q22" s="116"/>
-      <c r="R22" s="116"/>
-      <c r="S22" s="116"/>
-      <c r="T22" s="116"/>
-      <c r="U22" s="116"/>
-      <c r="V22" s="116"/>
-      <c r="W22" s="116"/>
-      <c r="X22" s="116"/>
-      <c r="Y22" s="116"/>
-      <c r="Z22" s="116"/>
-      <c r="AA22" s="116"/>
-      <c r="AB22" s="116"/>
-      <c r="AC22" s="116"/>
-      <c r="AD22" s="116"/>
-      <c r="AE22" s="116"/>
-      <c r="AF22" s="116"/>
-      <c r="AG22" s="116"/>
-      <c r="AH22" s="116"/>
-      <c r="AI22" s="116"/>
-      <c r="AJ22" s="117"/>
+      <c r="A22" s="87"/>
+      <c r="B22" s="88"/>
+      <c r="C22" s="88"/>
+      <c r="D22" s="88"/>
+      <c r="E22" s="88"/>
+      <c r="F22" s="88"/>
+      <c r="G22" s="88"/>
+      <c r="H22" s="88"/>
+      <c r="I22" s="88"/>
+      <c r="J22" s="88"/>
+      <c r="K22" s="88"/>
+      <c r="L22" s="88"/>
+      <c r="M22" s="88"/>
+      <c r="N22" s="88"/>
+      <c r="O22" s="88"/>
+      <c r="P22" s="88"/>
+      <c r="Q22" s="88"/>
+      <c r="R22" s="88"/>
+      <c r="S22" s="88"/>
+      <c r="T22" s="88"/>
+      <c r="U22" s="88"/>
+      <c r="V22" s="88"/>
+      <c r="W22" s="88"/>
+      <c r="X22" s="88"/>
+      <c r="Y22" s="88"/>
+      <c r="Z22" s="88"/>
+      <c r="AA22" s="88"/>
+      <c r="AB22" s="88"/>
+      <c r="AC22" s="88"/>
+      <c r="AD22" s="88"/>
+      <c r="AE22" s="88"/>
+      <c r="AF22" s="88"/>
+      <c r="AG22" s="88"/>
+      <c r="AH22" s="88"/>
+      <c r="AI22" s="88"/>
+      <c r="AJ22" s="89"/>
     </row>
     <row r="23" spans="1:36" ht="16.5" customHeight="1">
-      <c r="A23" s="118"/>
-      <c r="B23" s="119"/>
-      <c r="C23" s="119"/>
-      <c r="D23" s="119"/>
-      <c r="E23" s="119"/>
-      <c r="F23" s="119"/>
-      <c r="G23" s="119"/>
-      <c r="H23" s="119"/>
-      <c r="I23" s="119"/>
-      <c r="J23" s="119"/>
-      <c r="K23" s="119"/>
-      <c r="L23" s="119"/>
-      <c r="M23" s="119"/>
-      <c r="N23" s="119"/>
-      <c r="O23" s="119"/>
-      <c r="P23" s="119"/>
-      <c r="Q23" s="119"/>
-      <c r="R23" s="119"/>
-      <c r="S23" s="119"/>
-      <c r="T23" s="119"/>
-      <c r="U23" s="119"/>
-      <c r="V23" s="119"/>
-      <c r="W23" s="119"/>
-      <c r="X23" s="119"/>
-      <c r="Y23" s="119"/>
-      <c r="Z23" s="119"/>
-      <c r="AA23" s="119"/>
-      <c r="AB23" s="119"/>
-      <c r="AC23" s="119"/>
-      <c r="AD23" s="119"/>
-      <c r="AE23" s="119"/>
-      <c r="AF23" s="119"/>
-      <c r="AG23" s="119"/>
-      <c r="AH23" s="119"/>
-      <c r="AI23" s="119"/>
-      <c r="AJ23" s="120"/>
+      <c r="A23" s="90"/>
+      <c r="B23" s="91"/>
+      <c r="C23" s="91"/>
+      <c r="D23" s="91"/>
+      <c r="E23" s="91"/>
+      <c r="F23" s="91"/>
+      <c r="G23" s="91"/>
+      <c r="H23" s="91"/>
+      <c r="I23" s="91"/>
+      <c r="J23" s="91"/>
+      <c r="K23" s="91"/>
+      <c r="L23" s="91"/>
+      <c r="M23" s="91"/>
+      <c r="N23" s="91"/>
+      <c r="O23" s="91"/>
+      <c r="P23" s="91"/>
+      <c r="Q23" s="91"/>
+      <c r="R23" s="91"/>
+      <c r="S23" s="91"/>
+      <c r="T23" s="91"/>
+      <c r="U23" s="91"/>
+      <c r="V23" s="91"/>
+      <c r="W23" s="91"/>
+      <c r="X23" s="91"/>
+      <c r="Y23" s="91"/>
+      <c r="Z23" s="91"/>
+      <c r="AA23" s="91"/>
+      <c r="AB23" s="91"/>
+      <c r="AC23" s="91"/>
+      <c r="AD23" s="91"/>
+      <c r="AE23" s="91"/>
+      <c r="AF23" s="91"/>
+      <c r="AG23" s="91"/>
+      <c r="AH23" s="91"/>
+      <c r="AI23" s="91"/>
+      <c r="AJ23" s="92"/>
     </row>
     <row r="24" spans="1:36" ht="12.75" customHeight="1">
       <c r="A24" s="46" t="s">
@@ -7992,42 +7981,42 @@
       <c r="AJ24" s="47"/>
     </row>
     <row r="25" spans="1:36" ht="18" customHeight="1">
-      <c r="A25" s="112"/>
-      <c r="B25" s="113"/>
-      <c r="C25" s="113"/>
-      <c r="D25" s="113"/>
-      <c r="E25" s="113"/>
-      <c r="F25" s="113"/>
-      <c r="G25" s="113"/>
-      <c r="H25" s="113"/>
-      <c r="I25" s="113"/>
-      <c r="J25" s="113"/>
-      <c r="K25" s="113"/>
-      <c r="L25" s="113"/>
-      <c r="M25" s="113"/>
-      <c r="N25" s="113"/>
-      <c r="O25" s="113"/>
-      <c r="P25" s="113"/>
-      <c r="Q25" s="113"/>
-      <c r="R25" s="113"/>
-      <c r="S25" s="113"/>
-      <c r="T25" s="113"/>
-      <c r="U25" s="113"/>
-      <c r="V25" s="113"/>
-      <c r="W25" s="113"/>
-      <c r="X25" s="113"/>
-      <c r="Y25" s="113"/>
-      <c r="Z25" s="113"/>
-      <c r="AA25" s="113"/>
-      <c r="AB25" s="113"/>
-      <c r="AC25" s="113"/>
-      <c r="AD25" s="113"/>
-      <c r="AE25" s="113"/>
-      <c r="AF25" s="113"/>
-      <c r="AG25" s="113"/>
-      <c r="AH25" s="113"/>
-      <c r="AI25" s="113"/>
-      <c r="AJ25" s="114"/>
+      <c r="A25" s="84"/>
+      <c r="B25" s="85"/>
+      <c r="C25" s="85"/>
+      <c r="D25" s="85"/>
+      <c r="E25" s="85"/>
+      <c r="F25" s="85"/>
+      <c r="G25" s="85"/>
+      <c r="H25" s="85"/>
+      <c r="I25" s="85"/>
+      <c r="J25" s="85"/>
+      <c r="K25" s="85"/>
+      <c r="L25" s="85"/>
+      <c r="M25" s="85"/>
+      <c r="N25" s="85"/>
+      <c r="O25" s="85"/>
+      <c r="P25" s="85"/>
+      <c r="Q25" s="85"/>
+      <c r="R25" s="85"/>
+      <c r="S25" s="85"/>
+      <c r="T25" s="85"/>
+      <c r="U25" s="85"/>
+      <c r="V25" s="85"/>
+      <c r="W25" s="85"/>
+      <c r="X25" s="85"/>
+      <c r="Y25" s="85"/>
+      <c r="Z25" s="85"/>
+      <c r="AA25" s="85"/>
+      <c r="AB25" s="85"/>
+      <c r="AC25" s="85"/>
+      <c r="AD25" s="85"/>
+      <c r="AE25" s="85"/>
+      <c r="AF25" s="85"/>
+      <c r="AG25" s="85"/>
+      <c r="AH25" s="85"/>
+      <c r="AI25" s="85"/>
+      <c r="AJ25" s="86"/>
     </row>
     <row r="26" spans="1:36" ht="12.75" customHeight="1">
       <c r="A26" s="46" t="s">
@@ -8070,137 +8059,137 @@
       <c r="AJ26" s="47"/>
     </row>
     <row r="27" spans="1:36" ht="15" customHeight="1">
-      <c r="A27" s="63"/>
-      <c r="B27" s="64"/>
-      <c r="C27" s="64"/>
-      <c r="D27" s="64"/>
-      <c r="E27" s="64"/>
-      <c r="F27" s="64"/>
-      <c r="G27" s="64"/>
-      <c r="H27" s="64"/>
-      <c r="I27" s="64"/>
-      <c r="J27" s="64"/>
-      <c r="K27" s="64"/>
-      <c r="L27" s="64"/>
-      <c r="M27" s="64"/>
-      <c r="N27" s="64"/>
-      <c r="O27" s="64"/>
-      <c r="P27" s="64"/>
-      <c r="Q27" s="64"/>
-      <c r="R27" s="64"/>
-      <c r="S27" s="64"/>
-      <c r="T27" s="64"/>
-      <c r="U27" s="64"/>
-      <c r="V27" s="64"/>
-      <c r="W27" s="64"/>
-      <c r="X27" s="64"/>
-      <c r="Y27" s="64"/>
-      <c r="Z27" s="64"/>
-      <c r="AA27" s="64"/>
-      <c r="AB27" s="64"/>
-      <c r="AC27" s="64"/>
-      <c r="AD27" s="64"/>
-      <c r="AE27" s="64"/>
-      <c r="AF27" s="64"/>
-      <c r="AG27" s="64"/>
-      <c r="AH27" s="64"/>
-      <c r="AI27" s="64"/>
-      <c r="AJ27" s="65"/>
+      <c r="A27" s="151"/>
+      <c r="B27" s="152"/>
+      <c r="C27" s="152"/>
+      <c r="D27" s="152"/>
+      <c r="E27" s="152"/>
+      <c r="F27" s="152"/>
+      <c r="G27" s="152"/>
+      <c r="H27" s="152"/>
+      <c r="I27" s="152"/>
+      <c r="J27" s="152"/>
+      <c r="K27" s="152"/>
+      <c r="L27" s="152"/>
+      <c r="M27" s="152"/>
+      <c r="N27" s="152"/>
+      <c r="O27" s="152"/>
+      <c r="P27" s="152"/>
+      <c r="Q27" s="152"/>
+      <c r="R27" s="152"/>
+      <c r="S27" s="152"/>
+      <c r="T27" s="152"/>
+      <c r="U27" s="152"/>
+      <c r="V27" s="152"/>
+      <c r="W27" s="152"/>
+      <c r="X27" s="152"/>
+      <c r="Y27" s="152"/>
+      <c r="Z27" s="152"/>
+      <c r="AA27" s="152"/>
+      <c r="AB27" s="152"/>
+      <c r="AC27" s="152"/>
+      <c r="AD27" s="152"/>
+      <c r="AE27" s="152"/>
+      <c r="AF27" s="152"/>
+      <c r="AG27" s="152"/>
+      <c r="AH27" s="152"/>
+      <c r="AI27" s="152"/>
+      <c r="AJ27" s="153"/>
     </row>
     <row r="28" spans="1:36" ht="15" customHeight="1">
-      <c r="A28" s="66"/>
-      <c r="B28" s="64"/>
-      <c r="C28" s="64"/>
-      <c r="D28" s="64"/>
-      <c r="E28" s="64"/>
-      <c r="F28" s="64"/>
-      <c r="G28" s="64"/>
-      <c r="H28" s="64"/>
-      <c r="I28" s="64"/>
-      <c r="J28" s="64"/>
-      <c r="K28" s="64"/>
-      <c r="L28" s="64"/>
-      <c r="M28" s="64"/>
-      <c r="N28" s="64"/>
-      <c r="O28" s="64"/>
-      <c r="P28" s="64"/>
-      <c r="Q28" s="64"/>
-      <c r="R28" s="64"/>
-      <c r="S28" s="64"/>
-      <c r="T28" s="64"/>
-      <c r="U28" s="64"/>
-      <c r="V28" s="64"/>
-      <c r="W28" s="64"/>
-      <c r="X28" s="64"/>
-      <c r="Y28" s="64"/>
-      <c r="Z28" s="64"/>
-      <c r="AA28" s="64"/>
-      <c r="AB28" s="64"/>
-      <c r="AC28" s="64"/>
-      <c r="AD28" s="64"/>
-      <c r="AE28" s="64"/>
-      <c r="AF28" s="64"/>
-      <c r="AG28" s="64"/>
-      <c r="AH28" s="64"/>
-      <c r="AI28" s="64"/>
-      <c r="AJ28" s="65"/>
+      <c r="A28" s="154"/>
+      <c r="B28" s="152"/>
+      <c r="C28" s="152"/>
+      <c r="D28" s="152"/>
+      <c r="E28" s="152"/>
+      <c r="F28" s="152"/>
+      <c r="G28" s="152"/>
+      <c r="H28" s="152"/>
+      <c r="I28" s="152"/>
+      <c r="J28" s="152"/>
+      <c r="K28" s="152"/>
+      <c r="L28" s="152"/>
+      <c r="M28" s="152"/>
+      <c r="N28" s="152"/>
+      <c r="O28" s="152"/>
+      <c r="P28" s="152"/>
+      <c r="Q28" s="152"/>
+      <c r="R28" s="152"/>
+      <c r="S28" s="152"/>
+      <c r="T28" s="152"/>
+      <c r="U28" s="152"/>
+      <c r="V28" s="152"/>
+      <c r="W28" s="152"/>
+      <c r="X28" s="152"/>
+      <c r="Y28" s="152"/>
+      <c r="Z28" s="152"/>
+      <c r="AA28" s="152"/>
+      <c r="AB28" s="152"/>
+      <c r="AC28" s="152"/>
+      <c r="AD28" s="152"/>
+      <c r="AE28" s="152"/>
+      <c r="AF28" s="152"/>
+      <c r="AG28" s="152"/>
+      <c r="AH28" s="152"/>
+      <c r="AI28" s="152"/>
+      <c r="AJ28" s="153"/>
     </row>
     <row r="29" spans="1:36" ht="100.8" customHeight="1">
-      <c r="A29" s="67"/>
-      <c r="B29" s="68"/>
-      <c r="C29" s="68"/>
-      <c r="D29" s="68"/>
-      <c r="E29" s="68"/>
-      <c r="F29" s="68"/>
-      <c r="G29" s="68"/>
-      <c r="H29" s="68"/>
-      <c r="I29" s="68"/>
-      <c r="J29" s="68"/>
-      <c r="K29" s="68"/>
-      <c r="L29" s="68"/>
-      <c r="M29" s="68"/>
-      <c r="N29" s="68"/>
-      <c r="O29" s="68"/>
-      <c r="P29" s="68"/>
-      <c r="Q29" s="68"/>
-      <c r="R29" s="68"/>
-      <c r="S29" s="68"/>
-      <c r="T29" s="68"/>
-      <c r="U29" s="68"/>
-      <c r="V29" s="68"/>
-      <c r="W29" s="68"/>
-      <c r="X29" s="68"/>
-      <c r="Y29" s="68"/>
-      <c r="Z29" s="68"/>
-      <c r="AA29" s="68"/>
-      <c r="AB29" s="68"/>
-      <c r="AC29" s="68"/>
-      <c r="AD29" s="68"/>
-      <c r="AE29" s="68"/>
-      <c r="AF29" s="68"/>
-      <c r="AG29" s="68"/>
-      <c r="AH29" s="68"/>
-      <c r="AI29" s="68"/>
-      <c r="AJ29" s="69"/>
+      <c r="A29" s="155"/>
+      <c r="B29" s="156"/>
+      <c r="C29" s="156"/>
+      <c r="D29" s="156"/>
+      <c r="E29" s="156"/>
+      <c r="F29" s="156"/>
+      <c r="G29" s="156"/>
+      <c r="H29" s="156"/>
+      <c r="I29" s="156"/>
+      <c r="J29" s="156"/>
+      <c r="K29" s="156"/>
+      <c r="L29" s="156"/>
+      <c r="M29" s="156"/>
+      <c r="N29" s="156"/>
+      <c r="O29" s="156"/>
+      <c r="P29" s="156"/>
+      <c r="Q29" s="156"/>
+      <c r="R29" s="156"/>
+      <c r="S29" s="156"/>
+      <c r="T29" s="156"/>
+      <c r="U29" s="156"/>
+      <c r="V29" s="156"/>
+      <c r="W29" s="156"/>
+      <c r="X29" s="156"/>
+      <c r="Y29" s="156"/>
+      <c r="Z29" s="156"/>
+      <c r="AA29" s="156"/>
+      <c r="AB29" s="156"/>
+      <c r="AC29" s="156"/>
+      <c r="AD29" s="156"/>
+      <c r="AE29" s="156"/>
+      <c r="AF29" s="156"/>
+      <c r="AG29" s="156"/>
+      <c r="AH29" s="156"/>
+      <c r="AI29" s="156"/>
+      <c r="AJ29" s="157"/>
     </row>
     <row r="30" spans="1:36" ht="12.75" customHeight="1">
-      <c r="A30" s="76" t="s">
+      <c r="A30" s="158" t="s">
         <v>17</v>
       </c>
-      <c r="B30" s="77"/>
-      <c r="C30" s="77"/>
-      <c r="D30" s="77"/>
-      <c r="E30" s="77"/>
-      <c r="F30" s="77"/>
-      <c r="G30" s="77"/>
-      <c r="H30" s="77"/>
-      <c r="I30" s="77"/>
-      <c r="J30" s="77"/>
-      <c r="K30" s="77"/>
-      <c r="L30" s="77"/>
-      <c r="M30" s="77"/>
-      <c r="N30" s="77"/>
-      <c r="O30" s="77"/>
+      <c r="B30" s="159"/>
+      <c r="C30" s="159"/>
+      <c r="D30" s="159"/>
+      <c r="E30" s="159"/>
+      <c r="F30" s="159"/>
+      <c r="G30" s="159"/>
+      <c r="H30" s="159"/>
+      <c r="I30" s="159"/>
+      <c r="J30" s="159"/>
+      <c r="K30" s="159"/>
+      <c r="L30" s="159"/>
+      <c r="M30" s="159"/>
+      <c r="N30" s="159"/>
+      <c r="O30" s="159"/>
       <c r="P30" s="41"/>
       <c r="Q30" s="41"/>
       <c r="R30" s="41"/>
@@ -8224,216 +8213,216 @@
       <c r="AJ30" s="42"/>
     </row>
     <row r="31" spans="1:36" ht="16.5" customHeight="1">
-      <c r="A31" s="63"/>
-      <c r="B31" s="80"/>
-      <c r="C31" s="80"/>
-      <c r="D31" s="80"/>
-      <c r="E31" s="80"/>
-      <c r="F31" s="80"/>
-      <c r="G31" s="80"/>
-      <c r="H31" s="80"/>
-      <c r="I31" s="80"/>
-      <c r="J31" s="80"/>
-      <c r="K31" s="80"/>
-      <c r="L31" s="80"/>
-      <c r="M31" s="80"/>
-      <c r="N31" s="80"/>
-      <c r="O31" s="80"/>
-      <c r="P31" s="80"/>
-      <c r="Q31" s="80"/>
-      <c r="R31" s="80"/>
-      <c r="S31" s="80"/>
-      <c r="T31" s="80"/>
-      <c r="U31" s="80"/>
-      <c r="V31" s="80"/>
-      <c r="W31" s="80"/>
-      <c r="X31" s="80"/>
-      <c r="Y31" s="80"/>
-      <c r="Z31" s="80"/>
-      <c r="AA31" s="80"/>
-      <c r="AB31" s="80"/>
-      <c r="AC31" s="80"/>
-      <c r="AD31" s="80"/>
-      <c r="AE31" s="80"/>
-      <c r="AF31" s="80"/>
-      <c r="AG31" s="80"/>
-      <c r="AH31" s="80"/>
-      <c r="AI31" s="80"/>
-      <c r="AJ31" s="81"/>
+      <c r="A31" s="151"/>
+      <c r="B31" s="161"/>
+      <c r="C31" s="161"/>
+      <c r="D31" s="161"/>
+      <c r="E31" s="161"/>
+      <c r="F31" s="161"/>
+      <c r="G31" s="161"/>
+      <c r="H31" s="161"/>
+      <c r="I31" s="161"/>
+      <c r="J31" s="161"/>
+      <c r="K31" s="161"/>
+      <c r="L31" s="161"/>
+      <c r="M31" s="161"/>
+      <c r="N31" s="161"/>
+      <c r="O31" s="161"/>
+      <c r="P31" s="161"/>
+      <c r="Q31" s="161"/>
+      <c r="R31" s="161"/>
+      <c r="S31" s="161"/>
+      <c r="T31" s="161"/>
+      <c r="U31" s="161"/>
+      <c r="V31" s="161"/>
+      <c r="W31" s="161"/>
+      <c r="X31" s="161"/>
+      <c r="Y31" s="161"/>
+      <c r="Z31" s="161"/>
+      <c r="AA31" s="161"/>
+      <c r="AB31" s="161"/>
+      <c r="AC31" s="161"/>
+      <c r="AD31" s="161"/>
+      <c r="AE31" s="161"/>
+      <c r="AF31" s="161"/>
+      <c r="AG31" s="161"/>
+      <c r="AH31" s="161"/>
+      <c r="AI31" s="161"/>
+      <c r="AJ31" s="162"/>
     </row>
     <row r="32" spans="1:36" ht="16.5" customHeight="1">
-      <c r="A32" s="63"/>
-      <c r="B32" s="80"/>
-      <c r="C32" s="80"/>
-      <c r="D32" s="80"/>
-      <c r="E32" s="80"/>
-      <c r="F32" s="80"/>
-      <c r="G32" s="80"/>
-      <c r="H32" s="80"/>
-      <c r="I32" s="80"/>
-      <c r="J32" s="80"/>
-      <c r="K32" s="80"/>
-      <c r="L32" s="80"/>
-      <c r="M32" s="80"/>
-      <c r="N32" s="80"/>
-      <c r="O32" s="80"/>
-      <c r="P32" s="80"/>
-      <c r="Q32" s="80"/>
-      <c r="R32" s="80"/>
-      <c r="S32" s="80"/>
-      <c r="T32" s="80"/>
-      <c r="U32" s="80"/>
-      <c r="V32" s="80"/>
-      <c r="W32" s="80"/>
-      <c r="X32" s="80"/>
-      <c r="Y32" s="80"/>
-      <c r="Z32" s="80"/>
-      <c r="AA32" s="80"/>
-      <c r="AB32" s="80"/>
-      <c r="AC32" s="80"/>
-      <c r="AD32" s="80"/>
-      <c r="AE32" s="80"/>
-      <c r="AF32" s="80"/>
-      <c r="AG32" s="80"/>
-      <c r="AH32" s="80"/>
-      <c r="AI32" s="80"/>
-      <c r="AJ32" s="81"/>
+      <c r="A32" s="151"/>
+      <c r="B32" s="161"/>
+      <c r="C32" s="161"/>
+      <c r="D32" s="161"/>
+      <c r="E32" s="161"/>
+      <c r="F32" s="161"/>
+      <c r="G32" s="161"/>
+      <c r="H32" s="161"/>
+      <c r="I32" s="161"/>
+      <c r="J32" s="161"/>
+      <c r="K32" s="161"/>
+      <c r="L32" s="161"/>
+      <c r="M32" s="161"/>
+      <c r="N32" s="161"/>
+      <c r="O32" s="161"/>
+      <c r="P32" s="161"/>
+      <c r="Q32" s="161"/>
+      <c r="R32" s="161"/>
+      <c r="S32" s="161"/>
+      <c r="T32" s="161"/>
+      <c r="U32" s="161"/>
+      <c r="V32" s="161"/>
+      <c r="W32" s="161"/>
+      <c r="X32" s="161"/>
+      <c r="Y32" s="161"/>
+      <c r="Z32" s="161"/>
+      <c r="AA32" s="161"/>
+      <c r="AB32" s="161"/>
+      <c r="AC32" s="161"/>
+      <c r="AD32" s="161"/>
+      <c r="AE32" s="161"/>
+      <c r="AF32" s="161"/>
+      <c r="AG32" s="161"/>
+      <c r="AH32" s="161"/>
+      <c r="AI32" s="161"/>
+      <c r="AJ32" s="162"/>
     </row>
     <row r="33" spans="1:36" ht="16.5" customHeight="1">
-      <c r="A33" s="63"/>
-      <c r="B33" s="80"/>
-      <c r="C33" s="80"/>
-      <c r="D33" s="80"/>
-      <c r="E33" s="80"/>
-      <c r="F33" s="80"/>
-      <c r="G33" s="80"/>
-      <c r="H33" s="80"/>
-      <c r="I33" s="80"/>
-      <c r="J33" s="80"/>
-      <c r="K33" s="80"/>
-      <c r="L33" s="80"/>
-      <c r="M33" s="80"/>
-      <c r="N33" s="80"/>
-      <c r="O33" s="80"/>
-      <c r="P33" s="80"/>
-      <c r="Q33" s="80"/>
-      <c r="R33" s="80"/>
-      <c r="S33" s="80"/>
-      <c r="T33" s="80"/>
-      <c r="U33" s="80"/>
-      <c r="V33" s="80"/>
-      <c r="W33" s="80"/>
-      <c r="X33" s="80"/>
-      <c r="Y33" s="80"/>
-      <c r="Z33" s="80"/>
-      <c r="AA33" s="80"/>
-      <c r="AB33" s="80"/>
-      <c r="AC33" s="80"/>
-      <c r="AD33" s="80"/>
-      <c r="AE33" s="80"/>
-      <c r="AF33" s="80"/>
-      <c r="AG33" s="80"/>
-      <c r="AH33" s="80"/>
-      <c r="AI33" s="80"/>
-      <c r="AJ33" s="81"/>
+      <c r="A33" s="151"/>
+      <c r="B33" s="161"/>
+      <c r="C33" s="161"/>
+      <c r="D33" s="161"/>
+      <c r="E33" s="161"/>
+      <c r="F33" s="161"/>
+      <c r="G33" s="161"/>
+      <c r="H33" s="161"/>
+      <c r="I33" s="161"/>
+      <c r="J33" s="161"/>
+      <c r="K33" s="161"/>
+      <c r="L33" s="161"/>
+      <c r="M33" s="161"/>
+      <c r="N33" s="161"/>
+      <c r="O33" s="161"/>
+      <c r="P33" s="161"/>
+      <c r="Q33" s="161"/>
+      <c r="R33" s="161"/>
+      <c r="S33" s="161"/>
+      <c r="T33" s="161"/>
+      <c r="U33" s="161"/>
+      <c r="V33" s="161"/>
+      <c r="W33" s="161"/>
+      <c r="X33" s="161"/>
+      <c r="Y33" s="161"/>
+      <c r="Z33" s="161"/>
+      <c r="AA33" s="161"/>
+      <c r="AB33" s="161"/>
+      <c r="AC33" s="161"/>
+      <c r="AD33" s="161"/>
+      <c r="AE33" s="161"/>
+      <c r="AF33" s="161"/>
+      <c r="AG33" s="161"/>
+      <c r="AH33" s="161"/>
+      <c r="AI33" s="161"/>
+      <c r="AJ33" s="162"/>
     </row>
     <row r="34" spans="1:36" ht="61.8" customHeight="1">
-      <c r="A34" s="63"/>
-      <c r="B34" s="80"/>
-      <c r="C34" s="80"/>
-      <c r="D34" s="80"/>
-      <c r="E34" s="80"/>
-      <c r="F34" s="80"/>
-      <c r="G34" s="80"/>
-      <c r="H34" s="80"/>
-      <c r="I34" s="80"/>
-      <c r="J34" s="80"/>
-      <c r="K34" s="80"/>
-      <c r="L34" s="80"/>
-      <c r="M34" s="80"/>
-      <c r="N34" s="80"/>
-      <c r="O34" s="80"/>
-      <c r="P34" s="80"/>
-      <c r="Q34" s="80"/>
-      <c r="R34" s="80"/>
-      <c r="S34" s="80"/>
-      <c r="T34" s="80"/>
-      <c r="U34" s="80"/>
-      <c r="V34" s="80"/>
-      <c r="W34" s="80"/>
-      <c r="X34" s="80"/>
-      <c r="Y34" s="80"/>
-      <c r="Z34" s="80"/>
-      <c r="AA34" s="80"/>
-      <c r="AB34" s="80"/>
-      <c r="AC34" s="80"/>
-      <c r="AD34" s="80"/>
-      <c r="AE34" s="80"/>
-      <c r="AF34" s="80"/>
-      <c r="AG34" s="80"/>
-      <c r="AH34" s="80"/>
-      <c r="AI34" s="80"/>
-      <c r="AJ34" s="81"/>
+      <c r="A34" s="151"/>
+      <c r="B34" s="161"/>
+      <c r="C34" s="161"/>
+      <c r="D34" s="161"/>
+      <c r="E34" s="161"/>
+      <c r="F34" s="161"/>
+      <c r="G34" s="161"/>
+      <c r="H34" s="161"/>
+      <c r="I34" s="161"/>
+      <c r="J34" s="161"/>
+      <c r="K34" s="161"/>
+      <c r="L34" s="161"/>
+      <c r="M34" s="161"/>
+      <c r="N34" s="161"/>
+      <c r="O34" s="161"/>
+      <c r="P34" s="161"/>
+      <c r="Q34" s="161"/>
+      <c r="R34" s="161"/>
+      <c r="S34" s="161"/>
+      <c r="T34" s="161"/>
+      <c r="U34" s="161"/>
+      <c r="V34" s="161"/>
+      <c r="W34" s="161"/>
+      <c r="X34" s="161"/>
+      <c r="Y34" s="161"/>
+      <c r="Z34" s="161"/>
+      <c r="AA34" s="161"/>
+      <c r="AB34" s="161"/>
+      <c r="AC34" s="161"/>
+      <c r="AD34" s="161"/>
+      <c r="AE34" s="161"/>
+      <c r="AF34" s="161"/>
+      <c r="AG34" s="161"/>
+      <c r="AH34" s="161"/>
+      <c r="AI34" s="161"/>
+      <c r="AJ34" s="162"/>
     </row>
     <row r="35" spans="1:36" ht="13.2" customHeight="1">
-      <c r="A35" s="82"/>
-      <c r="B35" s="83"/>
-      <c r="C35" s="83"/>
-      <c r="D35" s="83"/>
-      <c r="E35" s="83"/>
-      <c r="F35" s="83"/>
-      <c r="G35" s="83"/>
-      <c r="H35" s="83"/>
-      <c r="I35" s="83"/>
-      <c r="J35" s="83"/>
-      <c r="K35" s="83"/>
-      <c r="L35" s="83"/>
-      <c r="M35" s="83"/>
-      <c r="N35" s="83"/>
-      <c r="O35" s="83"/>
-      <c r="P35" s="83"/>
-      <c r="Q35" s="83"/>
-      <c r="R35" s="83"/>
-      <c r="S35" s="83"/>
-      <c r="T35" s="83"/>
-      <c r="U35" s="83"/>
-      <c r="V35" s="83"/>
-      <c r="W35" s="83"/>
-      <c r="X35" s="83"/>
-      <c r="Y35" s="83"/>
-      <c r="Z35" s="83"/>
-      <c r="AA35" s="83"/>
-      <c r="AB35" s="83"/>
-      <c r="AC35" s="83"/>
-      <c r="AD35" s="83"/>
-      <c r="AE35" s="83"/>
-      <c r="AF35" s="83"/>
-      <c r="AG35" s="83"/>
-      <c r="AH35" s="83"/>
-      <c r="AI35" s="83"/>
-      <c r="AJ35" s="84"/>
+      <c r="A35" s="163"/>
+      <c r="B35" s="164"/>
+      <c r="C35" s="164"/>
+      <c r="D35" s="164"/>
+      <c r="E35" s="164"/>
+      <c r="F35" s="164"/>
+      <c r="G35" s="164"/>
+      <c r="H35" s="164"/>
+      <c r="I35" s="164"/>
+      <c r="J35" s="164"/>
+      <c r="K35" s="164"/>
+      <c r="L35" s="164"/>
+      <c r="M35" s="164"/>
+      <c r="N35" s="164"/>
+      <c r="O35" s="164"/>
+      <c r="P35" s="164"/>
+      <c r="Q35" s="164"/>
+      <c r="R35" s="164"/>
+      <c r="S35" s="164"/>
+      <c r="T35" s="164"/>
+      <c r="U35" s="164"/>
+      <c r="V35" s="164"/>
+      <c r="W35" s="164"/>
+      <c r="X35" s="164"/>
+      <c r="Y35" s="164"/>
+      <c r="Z35" s="164"/>
+      <c r="AA35" s="164"/>
+      <c r="AB35" s="164"/>
+      <c r="AC35" s="164"/>
+      <c r="AD35" s="164"/>
+      <c r="AE35" s="164"/>
+      <c r="AF35" s="164"/>
+      <c r="AG35" s="164"/>
+      <c r="AH35" s="164"/>
+      <c r="AI35" s="164"/>
+      <c r="AJ35" s="165"/>
     </row>
     <row r="36" spans="1:36" ht="13.5" customHeight="1">
-      <c r="A36" s="70" t="s">
+      <c r="A36" s="75" t="s">
         <v>94</v>
       </c>
-      <c r="B36" s="71"/>
-      <c r="C36" s="71"/>
-      <c r="D36" s="71"/>
-      <c r="E36" s="71"/>
-      <c r="F36" s="71"/>
-      <c r="G36" s="71"/>
-      <c r="H36" s="71"/>
-      <c r="I36" s="71"/>
-      <c r="J36" s="71"/>
-      <c r="K36" s="71"/>
-      <c r="L36" s="71"/>
-      <c r="M36" s="71"/>
-      <c r="N36" s="71"/>
-      <c r="O36" s="71"/>
-      <c r="P36" s="71"/>
-      <c r="Q36" s="71"/>
-      <c r="R36" s="71"/>
+      <c r="B36" s="76"/>
+      <c r="C36" s="76"/>
+      <c r="D36" s="76"/>
+      <c r="E36" s="76"/>
+      <c r="F36" s="76"/>
+      <c r="G36" s="76"/>
+      <c r="H36" s="76"/>
+      <c r="I36" s="76"/>
+      <c r="J36" s="76"/>
+      <c r="K36" s="76"/>
+      <c r="L36" s="76"/>
+      <c r="M36" s="76"/>
+      <c r="N36" s="76"/>
+      <c r="O36" s="76"/>
+      <c r="P36" s="76"/>
+      <c r="Q36" s="76"/>
+      <c r="R36" s="76"/>
       <c r="S36" s="40"/>
       <c r="T36" s="40"/>
       <c r="U36" s="40"/>
@@ -8454,178 +8443,178 @@
       <c r="AJ36" s="43"/>
     </row>
     <row r="37" spans="1:36" ht="14.25" customHeight="1">
-      <c r="A37" s="63"/>
-      <c r="B37" s="80"/>
-      <c r="C37" s="80"/>
-      <c r="D37" s="80"/>
-      <c r="E37" s="80"/>
-      <c r="F37" s="80"/>
-      <c r="G37" s="80"/>
-      <c r="H37" s="80"/>
-      <c r="I37" s="80"/>
-      <c r="J37" s="80"/>
-      <c r="K37" s="80"/>
-      <c r="L37" s="80"/>
-      <c r="M37" s="80"/>
-      <c r="N37" s="80"/>
-      <c r="O37" s="80"/>
-      <c r="P37" s="80"/>
-      <c r="Q37" s="80"/>
-      <c r="R37" s="80"/>
-      <c r="S37" s="80"/>
-      <c r="T37" s="80"/>
-      <c r="U37" s="80"/>
-      <c r="V37" s="80"/>
-      <c r="W37" s="80"/>
-      <c r="X37" s="80"/>
-      <c r="Y37" s="80"/>
-      <c r="Z37" s="80"/>
-      <c r="AA37" s="80"/>
-      <c r="AB37" s="80"/>
-      <c r="AC37" s="80"/>
-      <c r="AD37" s="80"/>
-      <c r="AE37" s="80"/>
-      <c r="AF37" s="80"/>
-      <c r="AG37" s="80"/>
-      <c r="AH37" s="80"/>
-      <c r="AI37" s="80"/>
-      <c r="AJ37" s="81"/>
+      <c r="A37" s="151"/>
+      <c r="B37" s="161"/>
+      <c r="C37" s="161"/>
+      <c r="D37" s="161"/>
+      <c r="E37" s="161"/>
+      <c r="F37" s="161"/>
+      <c r="G37" s="161"/>
+      <c r="H37" s="161"/>
+      <c r="I37" s="161"/>
+      <c r="J37" s="161"/>
+      <c r="K37" s="161"/>
+      <c r="L37" s="161"/>
+      <c r="M37" s="161"/>
+      <c r="N37" s="161"/>
+      <c r="O37" s="161"/>
+      <c r="P37" s="161"/>
+      <c r="Q37" s="161"/>
+      <c r="R37" s="161"/>
+      <c r="S37" s="161"/>
+      <c r="T37" s="161"/>
+      <c r="U37" s="161"/>
+      <c r="V37" s="161"/>
+      <c r="W37" s="161"/>
+      <c r="X37" s="161"/>
+      <c r="Y37" s="161"/>
+      <c r="Z37" s="161"/>
+      <c r="AA37" s="161"/>
+      <c r="AB37" s="161"/>
+      <c r="AC37" s="161"/>
+      <c r="AD37" s="161"/>
+      <c r="AE37" s="161"/>
+      <c r="AF37" s="161"/>
+      <c r="AG37" s="161"/>
+      <c r="AH37" s="161"/>
+      <c r="AI37" s="161"/>
+      <c r="AJ37" s="162"/>
     </row>
     <row r="38" spans="1:36" ht="14.25" customHeight="1">
-      <c r="A38" s="63"/>
-      <c r="B38" s="80"/>
-      <c r="C38" s="80"/>
-      <c r="D38" s="80"/>
-      <c r="E38" s="80"/>
-      <c r="F38" s="80"/>
-      <c r="G38" s="80"/>
-      <c r="H38" s="80"/>
-      <c r="I38" s="80"/>
-      <c r="J38" s="80"/>
-      <c r="K38" s="80"/>
-      <c r="L38" s="80"/>
-      <c r="M38" s="80"/>
-      <c r="N38" s="80"/>
-      <c r="O38" s="80"/>
-      <c r="P38" s="80"/>
-      <c r="Q38" s="80"/>
-      <c r="R38" s="80"/>
-      <c r="S38" s="80"/>
-      <c r="T38" s="80"/>
-      <c r="U38" s="80"/>
-      <c r="V38" s="80"/>
-      <c r="W38" s="80"/>
-      <c r="X38" s="80"/>
-      <c r="Y38" s="80"/>
-      <c r="Z38" s="80"/>
-      <c r="AA38" s="80"/>
-      <c r="AB38" s="80"/>
-      <c r="AC38" s="80"/>
-      <c r="AD38" s="80"/>
-      <c r="AE38" s="80"/>
-      <c r="AF38" s="80"/>
-      <c r="AG38" s="80"/>
-      <c r="AH38" s="80"/>
-      <c r="AI38" s="80"/>
-      <c r="AJ38" s="81"/>
+      <c r="A38" s="151"/>
+      <c r="B38" s="161"/>
+      <c r="C38" s="161"/>
+      <c r="D38" s="161"/>
+      <c r="E38" s="161"/>
+      <c r="F38" s="161"/>
+      <c r="G38" s="161"/>
+      <c r="H38" s="161"/>
+      <c r="I38" s="161"/>
+      <c r="J38" s="161"/>
+      <c r="K38" s="161"/>
+      <c r="L38" s="161"/>
+      <c r="M38" s="161"/>
+      <c r="N38" s="161"/>
+      <c r="O38" s="161"/>
+      <c r="P38" s="161"/>
+      <c r="Q38" s="161"/>
+      <c r="R38" s="161"/>
+      <c r="S38" s="161"/>
+      <c r="T38" s="161"/>
+      <c r="U38" s="161"/>
+      <c r="V38" s="161"/>
+      <c r="W38" s="161"/>
+      <c r="X38" s="161"/>
+      <c r="Y38" s="161"/>
+      <c r="Z38" s="161"/>
+      <c r="AA38" s="161"/>
+      <c r="AB38" s="161"/>
+      <c r="AC38" s="161"/>
+      <c r="AD38" s="161"/>
+      <c r="AE38" s="161"/>
+      <c r="AF38" s="161"/>
+      <c r="AG38" s="161"/>
+      <c r="AH38" s="161"/>
+      <c r="AI38" s="161"/>
+      <c r="AJ38" s="162"/>
     </row>
     <row r="39" spans="1:36" ht="27.6" customHeight="1">
-      <c r="A39" s="63"/>
-      <c r="B39" s="80"/>
-      <c r="C39" s="80"/>
-      <c r="D39" s="80"/>
-      <c r="E39" s="80"/>
-      <c r="F39" s="80"/>
-      <c r="G39" s="80"/>
-      <c r="H39" s="80"/>
-      <c r="I39" s="80"/>
-      <c r="J39" s="80"/>
-      <c r="K39" s="80"/>
-      <c r="L39" s="80"/>
-      <c r="M39" s="80"/>
-      <c r="N39" s="80"/>
-      <c r="O39" s="80"/>
-      <c r="P39" s="80"/>
-      <c r="Q39" s="80"/>
-      <c r="R39" s="80"/>
-      <c r="S39" s="80"/>
-      <c r="T39" s="80"/>
-      <c r="U39" s="80"/>
-      <c r="V39" s="80"/>
-      <c r="W39" s="80"/>
-      <c r="X39" s="80"/>
-      <c r="Y39" s="80"/>
-      <c r="Z39" s="80"/>
-      <c r="AA39" s="80"/>
-      <c r="AB39" s="80"/>
-      <c r="AC39" s="80"/>
-      <c r="AD39" s="80"/>
-      <c r="AE39" s="80"/>
-      <c r="AF39" s="80"/>
-      <c r="AG39" s="80"/>
-      <c r="AH39" s="80"/>
-      <c r="AI39" s="80"/>
-      <c r="AJ39" s="81"/>
+      <c r="A39" s="151"/>
+      <c r="B39" s="161"/>
+      <c r="C39" s="161"/>
+      <c r="D39" s="161"/>
+      <c r="E39" s="161"/>
+      <c r="F39" s="161"/>
+      <c r="G39" s="161"/>
+      <c r="H39" s="161"/>
+      <c r="I39" s="161"/>
+      <c r="J39" s="161"/>
+      <c r="K39" s="161"/>
+      <c r="L39" s="161"/>
+      <c r="M39" s="161"/>
+      <c r="N39" s="161"/>
+      <c r="O39" s="161"/>
+      <c r="P39" s="161"/>
+      <c r="Q39" s="161"/>
+      <c r="R39" s="161"/>
+      <c r="S39" s="161"/>
+      <c r="T39" s="161"/>
+      <c r="U39" s="161"/>
+      <c r="V39" s="161"/>
+      <c r="W39" s="161"/>
+      <c r="X39" s="161"/>
+      <c r="Y39" s="161"/>
+      <c r="Z39" s="161"/>
+      <c r="AA39" s="161"/>
+      <c r="AB39" s="161"/>
+      <c r="AC39" s="161"/>
+      <c r="AD39" s="161"/>
+      <c r="AE39" s="161"/>
+      <c r="AF39" s="161"/>
+      <c r="AG39" s="161"/>
+      <c r="AH39" s="161"/>
+      <c r="AI39" s="161"/>
+      <c r="AJ39" s="162"/>
     </row>
     <row r="40" spans="1:36" ht="16.8" customHeight="1">
-      <c r="A40" s="63"/>
-      <c r="B40" s="80"/>
-      <c r="C40" s="80"/>
-      <c r="D40" s="80"/>
-      <c r="E40" s="80"/>
-      <c r="F40" s="80"/>
-      <c r="G40" s="80"/>
-      <c r="H40" s="80"/>
-      <c r="I40" s="80"/>
-      <c r="J40" s="80"/>
-      <c r="K40" s="80"/>
-      <c r="L40" s="80"/>
-      <c r="M40" s="80"/>
-      <c r="N40" s="80"/>
-      <c r="O40" s="80"/>
-      <c r="P40" s="80"/>
-      <c r="Q40" s="80"/>
-      <c r="R40" s="80"/>
-      <c r="S40" s="80"/>
-      <c r="T40" s="80"/>
-      <c r="U40" s="80"/>
-      <c r="V40" s="80"/>
-      <c r="W40" s="80"/>
-      <c r="X40" s="80"/>
-      <c r="Y40" s="80"/>
-      <c r="Z40" s="80"/>
-      <c r="AA40" s="80"/>
-      <c r="AB40" s="80"/>
-      <c r="AC40" s="80"/>
-      <c r="AD40" s="80"/>
-      <c r="AE40" s="80"/>
-      <c r="AF40" s="80"/>
-      <c r="AG40" s="80"/>
-      <c r="AH40" s="80"/>
-      <c r="AI40" s="80"/>
-      <c r="AJ40" s="81"/>
+      <c r="A40" s="151"/>
+      <c r="B40" s="161"/>
+      <c r="C40" s="161"/>
+      <c r="D40" s="161"/>
+      <c r="E40" s="161"/>
+      <c r="F40" s="161"/>
+      <c r="G40" s="161"/>
+      <c r="H40" s="161"/>
+      <c r="I40" s="161"/>
+      <c r="J40" s="161"/>
+      <c r="K40" s="161"/>
+      <c r="L40" s="161"/>
+      <c r="M40" s="161"/>
+      <c r="N40" s="161"/>
+      <c r="O40" s="161"/>
+      <c r="P40" s="161"/>
+      <c r="Q40" s="161"/>
+      <c r="R40" s="161"/>
+      <c r="S40" s="161"/>
+      <c r="T40" s="161"/>
+      <c r="U40" s="161"/>
+      <c r="V40" s="161"/>
+      <c r="W40" s="161"/>
+      <c r="X40" s="161"/>
+      <c r="Y40" s="161"/>
+      <c r="Z40" s="161"/>
+      <c r="AA40" s="161"/>
+      <c r="AB40" s="161"/>
+      <c r="AC40" s="161"/>
+      <c r="AD40" s="161"/>
+      <c r="AE40" s="161"/>
+      <c r="AF40" s="161"/>
+      <c r="AG40" s="161"/>
+      <c r="AH40" s="161"/>
+      <c r="AI40" s="161"/>
+      <c r="AJ40" s="162"/>
     </row>
     <row r="41" spans="1:36" ht="16.8" customHeight="1">
-      <c r="A41" s="70" t="s">
+      <c r="A41" s="75" t="s">
         <v>99</v>
       </c>
-      <c r="B41" s="71"/>
-      <c r="C41" s="71"/>
-      <c r="D41" s="71"/>
-      <c r="E41" s="71"/>
-      <c r="F41" s="71"/>
-      <c r="G41" s="71"/>
-      <c r="H41" s="71"/>
-      <c r="I41" s="71"/>
-      <c r="J41" s="71"/>
-      <c r="K41" s="71"/>
-      <c r="L41" s="71"/>
-      <c r="M41" s="71"/>
-      <c r="N41" s="71"/>
-      <c r="O41" s="71"/>
-      <c r="P41" s="71"/>
-      <c r="Q41" s="71"/>
-      <c r="R41" s="71"/>
+      <c r="B41" s="76"/>
+      <c r="C41" s="76"/>
+      <c r="D41" s="76"/>
+      <c r="E41" s="76"/>
+      <c r="F41" s="76"/>
+      <c r="G41" s="76"/>
+      <c r="H41" s="76"/>
+      <c r="I41" s="76"/>
+      <c r="J41" s="76"/>
+      <c r="K41" s="76"/>
+      <c r="L41" s="76"/>
+      <c r="M41" s="76"/>
+      <c r="N41" s="76"/>
+      <c r="O41" s="76"/>
+      <c r="P41" s="76"/>
+      <c r="Q41" s="76"/>
+      <c r="R41" s="76"/>
       <c r="S41" s="40"/>
       <c r="T41" s="40"/>
       <c r="U41" s="40"/>
@@ -8684,675 +8673,675 @@
       <c r="AJ42" s="55"/>
     </row>
     <row r="43" spans="1:36" ht="17.25" customHeight="1">
-      <c r="A43" s="72" t="s">
+      <c r="A43" s="101" t="s">
         <v>18</v>
       </c>
-      <c r="B43" s="73"/>
-      <c r="C43" s="73"/>
-      <c r="D43" s="73"/>
-      <c r="E43" s="73"/>
-      <c r="F43" s="73"/>
-      <c r="G43" s="73"/>
-      <c r="H43" s="73"/>
-      <c r="I43" s="74"/>
-      <c r="J43" s="72" t="s">
+      <c r="B43" s="102"/>
+      <c r="C43" s="102"/>
+      <c r="D43" s="102"/>
+      <c r="E43" s="102"/>
+      <c r="F43" s="102"/>
+      <c r="G43" s="102"/>
+      <c r="H43" s="102"/>
+      <c r="I43" s="103"/>
+      <c r="J43" s="101" t="s">
         <v>19</v>
       </c>
-      <c r="K43" s="73"/>
-      <c r="L43" s="73"/>
-      <c r="M43" s="73"/>
-      <c r="N43" s="73"/>
-      <c r="O43" s="73"/>
-      <c r="P43" s="73"/>
-      <c r="Q43" s="73"/>
-      <c r="R43" s="74"/>
-      <c r="S43" s="72" t="s">
+      <c r="K43" s="102"/>
+      <c r="L43" s="102"/>
+      <c r="M43" s="102"/>
+      <c r="N43" s="102"/>
+      <c r="O43" s="102"/>
+      <c r="P43" s="102"/>
+      <c r="Q43" s="102"/>
+      <c r="R43" s="103"/>
+      <c r="S43" s="101" t="s">
         <v>77</v>
       </c>
-      <c r="T43" s="73"/>
-      <c r="U43" s="73"/>
-      <c r="V43" s="73"/>
-      <c r="W43" s="73"/>
-      <c r="X43" s="73"/>
-      <c r="Y43" s="73"/>
-      <c r="Z43" s="73"/>
-      <c r="AA43" s="74"/>
-      <c r="AB43" s="78" t="s">
+      <c r="T43" s="102"/>
+      <c r="U43" s="102"/>
+      <c r="V43" s="102"/>
+      <c r="W43" s="102"/>
+      <c r="X43" s="102"/>
+      <c r="Y43" s="102"/>
+      <c r="Z43" s="102"/>
+      <c r="AA43" s="103"/>
+      <c r="AB43" s="160" t="s">
         <v>91</v>
       </c>
-      <c r="AC43" s="73"/>
-      <c r="AD43" s="73"/>
-      <c r="AE43" s="73"/>
-      <c r="AF43" s="73"/>
-      <c r="AG43" s="73"/>
-      <c r="AH43" s="73"/>
-      <c r="AI43" s="73"/>
-      <c r="AJ43" s="74"/>
+      <c r="AC43" s="102"/>
+      <c r="AD43" s="102"/>
+      <c r="AE43" s="102"/>
+      <c r="AF43" s="102"/>
+      <c r="AG43" s="102"/>
+      <c r="AH43" s="102"/>
+      <c r="AI43" s="102"/>
+      <c r="AJ43" s="103"/>
     </row>
     <row r="44" spans="1:36" ht="18" customHeight="1">
       <c r="A44" s="2"/>
-      <c r="B44" s="58" t="s">
+      <c r="B44" s="126" t="s">
         <v>21</v>
       </c>
-      <c r="C44" s="58"/>
-      <c r="D44" s="58"/>
-      <c r="E44" s="58"/>
-      <c r="F44" s="58"/>
-      <c r="G44" s="58"/>
-      <c r="H44" s="58"/>
-      <c r="I44" s="59"/>
+      <c r="C44" s="126"/>
+      <c r="D44" s="126"/>
+      <c r="E44" s="126"/>
+      <c r="F44" s="126"/>
+      <c r="G44" s="126"/>
+      <c r="H44" s="126"/>
+      <c r="I44" s="127"/>
       <c r="J44" s="10"/>
-      <c r="K44" s="58" t="s">
+      <c r="K44" s="126" t="s">
         <v>22</v>
       </c>
-      <c r="L44" s="58"/>
-      <c r="M44" s="58"/>
-      <c r="N44" s="58"/>
-      <c r="O44" s="58"/>
-      <c r="P44" s="58"/>
-      <c r="Q44" s="58"/>
-      <c r="R44" s="59"/>
-      <c r="S44" s="85" t="s">
+      <c r="L44" s="126"/>
+      <c r="M44" s="126"/>
+      <c r="N44" s="126"/>
+      <c r="O44" s="126"/>
+      <c r="P44" s="126"/>
+      <c r="Q44" s="126"/>
+      <c r="R44" s="127"/>
+      <c r="S44" s="123" t="s">
         <v>81</v>
       </c>
-      <c r="T44" s="86"/>
-      <c r="U44" s="86"/>
-      <c r="V44" s="86"/>
-      <c r="W44" s="79"/>
-      <c r="X44" s="79"/>
-      <c r="Y44" s="79"/>
+      <c r="T44" s="81"/>
+      <c r="U44" s="81"/>
+      <c r="V44" s="81"/>
+      <c r="W44" s="64"/>
+      <c r="X44" s="64"/>
+      <c r="Y44" s="64"/>
       <c r="Z44" s="49"/>
       <c r="AA44" s="4"/>
-      <c r="AB44" s="60" t="s">
+      <c r="AB44" s="124" t="s">
         <v>82</v>
       </c>
-      <c r="AC44" s="61"/>
-      <c r="AD44" s="61"/>
-      <c r="AE44" s="61"/>
-      <c r="AF44" s="75"/>
-      <c r="AG44" s="75"/>
-      <c r="AH44" s="75"/>
-      <c r="AI44" s="75"/>
+      <c r="AC44" s="77"/>
+      <c r="AD44" s="77"/>
+      <c r="AE44" s="77"/>
+      <c r="AF44" s="131"/>
+      <c r="AG44" s="131"/>
+      <c r="AH44" s="131"/>
+      <c r="AI44" s="131"/>
       <c r="AJ44" s="4"/>
     </row>
     <row r="45" spans="1:36" ht="18" customHeight="1">
       <c r="A45" s="2"/>
-      <c r="B45" s="58" t="s">
+      <c r="B45" s="126" t="s">
         <v>24</v>
       </c>
-      <c r="C45" s="58"/>
-      <c r="D45" s="58"/>
-      <c r="E45" s="58"/>
-      <c r="F45" s="58"/>
-      <c r="G45" s="58"/>
-      <c r="H45" s="58"/>
-      <c r="I45" s="59"/>
+      <c r="C45" s="126"/>
+      <c r="D45" s="126"/>
+      <c r="E45" s="126"/>
+      <c r="F45" s="126"/>
+      <c r="G45" s="126"/>
+      <c r="H45" s="126"/>
+      <c r="I45" s="127"/>
       <c r="J45" s="10"/>
-      <c r="K45" s="58" t="s">
+      <c r="K45" s="126" t="s">
         <v>25</v>
       </c>
-      <c r="L45" s="58"/>
-      <c r="M45" s="58"/>
-      <c r="N45" s="58"/>
-      <c r="O45" s="58"/>
-      <c r="P45" s="58"/>
-      <c r="Q45" s="58"/>
-      <c r="R45" s="59"/>
-      <c r="S45" s="85" t="s">
+      <c r="L45" s="126"/>
+      <c r="M45" s="126"/>
+      <c r="N45" s="126"/>
+      <c r="O45" s="126"/>
+      <c r="P45" s="126"/>
+      <c r="Q45" s="126"/>
+      <c r="R45" s="127"/>
+      <c r="S45" s="123" t="s">
         <v>80</v>
       </c>
-      <c r="T45" s="86"/>
-      <c r="U45" s="86"/>
-      <c r="V45" s="86"/>
-      <c r="W45" s="57"/>
-      <c r="X45" s="57"/>
-      <c r="Y45" s="57"/>
-      <c r="Z45" s="57"/>
+      <c r="T45" s="81"/>
+      <c r="U45" s="81"/>
+      <c r="V45" s="81"/>
+      <c r="W45" s="150"/>
+      <c r="X45" s="150"/>
+      <c r="Y45" s="150"/>
+      <c r="Z45" s="150"/>
       <c r="AA45" s="4"/>
-      <c r="AB45" s="85" t="s">
+      <c r="AB45" s="123" t="s">
         <v>81</v>
       </c>
-      <c r="AC45" s="86"/>
-      <c r="AD45" s="86"/>
-      <c r="AE45" s="86"/>
-      <c r="AF45" s="57"/>
-      <c r="AG45" s="57"/>
-      <c r="AH45" s="57"/>
-      <c r="AI45" s="57"/>
+      <c r="AC45" s="81"/>
+      <c r="AD45" s="81"/>
+      <c r="AE45" s="81"/>
+      <c r="AF45" s="150"/>
+      <c r="AG45" s="150"/>
+      <c r="AH45" s="150"/>
+      <c r="AI45" s="150"/>
       <c r="AJ45" s="4"/>
     </row>
     <row r="46" spans="1:36" ht="18" customHeight="1">
       <c r="A46" s="2"/>
-      <c r="B46" s="58" t="s">
+      <c r="B46" s="126" t="s">
         <v>27</v>
       </c>
-      <c r="C46" s="58"/>
-      <c r="D46" s="58"/>
-      <c r="E46" s="58"/>
-      <c r="F46" s="58"/>
-      <c r="G46" s="58"/>
-      <c r="H46" s="58"/>
-      <c r="I46" s="59"/>
+      <c r="C46" s="126"/>
+      <c r="D46" s="126"/>
+      <c r="E46" s="126"/>
+      <c r="F46" s="126"/>
+      <c r="G46" s="126"/>
+      <c r="H46" s="126"/>
+      <c r="I46" s="127"/>
       <c r="J46" s="10"/>
-      <c r="K46" s="58" t="s">
+      <c r="K46" s="126" t="s">
         <v>28</v>
       </c>
-      <c r="L46" s="58"/>
-      <c r="M46" s="58"/>
-      <c r="N46" s="58"/>
-      <c r="O46" s="58"/>
-      <c r="P46" s="58"/>
-      <c r="Q46" s="58"/>
-      <c r="R46" s="59"/>
-      <c r="S46" s="60" t="s">
+      <c r="L46" s="126"/>
+      <c r="M46" s="126"/>
+      <c r="N46" s="126"/>
+      <c r="O46" s="126"/>
+      <c r="P46" s="126"/>
+      <c r="Q46" s="126"/>
+      <c r="R46" s="127"/>
+      <c r="S46" s="124" t="s">
         <v>78</v>
       </c>
-      <c r="T46" s="61"/>
-      <c r="U46" s="61"/>
-      <c r="V46" s="61"/>
-      <c r="W46" s="61"/>
-      <c r="X46" s="94"/>
-      <c r="Y46" s="94"/>
-      <c r="Z46" s="94"/>
+      <c r="T46" s="77"/>
+      <c r="U46" s="77"/>
+      <c r="V46" s="77"/>
+      <c r="W46" s="77"/>
+      <c r="X46" s="125"/>
+      <c r="Y46" s="125"/>
+      <c r="Z46" s="125"/>
       <c r="AA46" s="12" t="s">
         <v>30</v>
       </c>
-      <c r="AB46" s="85" t="s">
+      <c r="AB46" s="123" t="s">
         <v>80</v>
       </c>
-      <c r="AC46" s="86"/>
-      <c r="AD46" s="86"/>
-      <c r="AE46" s="86"/>
-      <c r="AF46" s="57"/>
-      <c r="AG46" s="57"/>
-      <c r="AH46" s="57"/>
-      <c r="AI46" s="57"/>
+      <c r="AC46" s="81"/>
+      <c r="AD46" s="81"/>
+      <c r="AE46" s="81"/>
+      <c r="AF46" s="150"/>
+      <c r="AG46" s="150"/>
+      <c r="AH46" s="150"/>
+      <c r="AI46" s="150"/>
       <c r="AJ46" s="4"/>
     </row>
     <row r="47" spans="1:36" ht="18" customHeight="1">
       <c r="A47" s="2"/>
-      <c r="B47" s="58" t="s">
+      <c r="B47" s="126" t="s">
         <v>87</v>
       </c>
-      <c r="C47" s="58"/>
-      <c r="D47" s="58"/>
-      <c r="E47" s="58"/>
-      <c r="F47" s="58"/>
-      <c r="G47" s="58"/>
-      <c r="H47" s="58"/>
-      <c r="I47" s="59"/>
+      <c r="C47" s="126"/>
+      <c r="D47" s="126"/>
+      <c r="E47" s="126"/>
+      <c r="F47" s="126"/>
+      <c r="G47" s="126"/>
+      <c r="H47" s="126"/>
+      <c r="I47" s="127"/>
       <c r="J47" s="10"/>
-      <c r="K47" s="58" t="s">
+      <c r="K47" s="126" t="s">
         <v>31</v>
       </c>
-      <c r="L47" s="58"/>
-      <c r="M47" s="58"/>
-      <c r="N47" s="58"/>
-      <c r="O47" s="58"/>
-      <c r="P47" s="58"/>
-      <c r="Q47" s="58"/>
-      <c r="R47" s="59"/>
-      <c r="S47" s="102" t="s">
+      <c r="L47" s="126"/>
+      <c r="M47" s="126"/>
+      <c r="N47" s="126"/>
+      <c r="O47" s="126"/>
+      <c r="P47" s="126"/>
+      <c r="Q47" s="126"/>
+      <c r="R47" s="127"/>
+      <c r="S47" s="128" t="s">
         <v>79</v>
       </c>
-      <c r="T47" s="103"/>
-      <c r="U47" s="103"/>
-      <c r="V47" s="103"/>
-      <c r="W47" s="103"/>
-      <c r="X47" s="62"/>
-      <c r="Y47" s="62"/>
-      <c r="Z47" s="62"/>
+      <c r="T47" s="129"/>
+      <c r="U47" s="129"/>
+      <c r="V47" s="129"/>
+      <c r="W47" s="129"/>
+      <c r="X47" s="145"/>
+      <c r="Y47" s="145"/>
+      <c r="Z47" s="145"/>
       <c r="AA47" s="33" t="s">
         <v>30</v>
       </c>
-      <c r="AB47" s="85" t="s">
+      <c r="AB47" s="123" t="s">
         <v>83</v>
       </c>
-      <c r="AC47" s="86"/>
-      <c r="AD47" s="86"/>
-      <c r="AE47" s="86"/>
-      <c r="AF47" s="75"/>
-      <c r="AG47" s="75"/>
-      <c r="AH47" s="75"/>
-      <c r="AI47" s="75"/>
+      <c r="AC47" s="81"/>
+      <c r="AD47" s="81"/>
+      <c r="AE47" s="81"/>
+      <c r="AF47" s="131"/>
+      <c r="AG47" s="131"/>
+      <c r="AH47" s="131"/>
+      <c r="AI47" s="131"/>
       <c r="AJ47" s="4"/>
     </row>
     <row r="48" spans="1:36" ht="18" customHeight="1">
       <c r="A48" s="34"/>
-      <c r="B48" s="58" t="s">
+      <c r="B48" s="126" t="s">
         <v>33</v>
       </c>
-      <c r="C48" s="58"/>
-      <c r="D48" s="58"/>
-      <c r="E48" s="58"/>
-      <c r="F48" s="58"/>
-      <c r="G48" s="58"/>
-      <c r="H48" s="58"/>
-      <c r="I48" s="59"/>
+      <c r="C48" s="126"/>
+      <c r="D48" s="126"/>
+      <c r="E48" s="126"/>
+      <c r="F48" s="126"/>
+      <c r="G48" s="126"/>
+      <c r="H48" s="126"/>
+      <c r="I48" s="127"/>
       <c r="J48" s="10"/>
-      <c r="K48" s="58" t="s">
+      <c r="K48" s="126" t="s">
         <v>34</v>
       </c>
-      <c r="L48" s="58"/>
-      <c r="M48" s="58"/>
-      <c r="N48" s="58"/>
-      <c r="O48" s="58"/>
-      <c r="P48" s="58"/>
-      <c r="Q48" s="58"/>
-      <c r="R48" s="59"/>
-      <c r="S48" s="91" t="s">
+      <c r="L48" s="126"/>
+      <c r="M48" s="126"/>
+      <c r="N48" s="126"/>
+      <c r="O48" s="126"/>
+      <c r="P48" s="126"/>
+      <c r="Q48" s="126"/>
+      <c r="R48" s="127"/>
+      <c r="S48" s="141" t="s">
         <v>20</v>
       </c>
-      <c r="T48" s="92"/>
-      <c r="U48" s="92"/>
-      <c r="V48" s="92"/>
-      <c r="W48" s="92"/>
-      <c r="X48" s="92"/>
-      <c r="Y48" s="92"/>
-      <c r="Z48" s="92"/>
-      <c r="AA48" s="93"/>
-      <c r="AB48" s="60" t="s">
+      <c r="T48" s="142"/>
+      <c r="U48" s="142"/>
+      <c r="V48" s="142"/>
+      <c r="W48" s="142"/>
+      <c r="X48" s="142"/>
+      <c r="Y48" s="142"/>
+      <c r="Z48" s="142"/>
+      <c r="AA48" s="143"/>
+      <c r="AB48" s="124" t="s">
         <v>78</v>
       </c>
-      <c r="AC48" s="61"/>
-      <c r="AD48" s="61"/>
-      <c r="AE48" s="61"/>
-      <c r="AF48" s="61"/>
-      <c r="AG48" s="94"/>
-      <c r="AH48" s="94"/>
-      <c r="AI48" s="94"/>
+      <c r="AC48" s="77"/>
+      <c r="AD48" s="77"/>
+      <c r="AE48" s="77"/>
+      <c r="AF48" s="77"/>
+      <c r="AG48" s="125"/>
+      <c r="AH48" s="125"/>
+      <c r="AI48" s="125"/>
       <c r="AJ48" s="12" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="49" spans="1:36" ht="18" customHeight="1">
       <c r="A49" s="10"/>
-      <c r="B49" s="58" t="s">
+      <c r="B49" s="126" t="s">
         <v>74</v>
       </c>
-      <c r="C49" s="58"/>
-      <c r="D49" s="58"/>
-      <c r="E49" s="58"/>
-      <c r="F49" s="58"/>
-      <c r="G49" s="58"/>
-      <c r="H49" s="58"/>
-      <c r="I49" s="59"/>
+      <c r="C49" s="126"/>
+      <c r="D49" s="126"/>
+      <c r="E49" s="126"/>
+      <c r="F49" s="126"/>
+      <c r="G49" s="126"/>
+      <c r="H49" s="126"/>
+      <c r="I49" s="127"/>
       <c r="J49" s="10"/>
-      <c r="K49" s="58" t="s">
+      <c r="K49" s="126" t="s">
         <v>37</v>
       </c>
-      <c r="L49" s="58"/>
-      <c r="M49" s="58"/>
-      <c r="N49" s="58"/>
-      <c r="O49" s="58"/>
-      <c r="P49" s="58"/>
-      <c r="Q49" s="58"/>
-      <c r="R49" s="59"/>
+      <c r="L49" s="126"/>
+      <c r="M49" s="126"/>
+      <c r="N49" s="126"/>
+      <c r="O49" s="126"/>
+      <c r="P49" s="126"/>
+      <c r="Q49" s="126"/>
+      <c r="R49" s="127"/>
       <c r="S49" s="10"/>
-      <c r="T49" s="58" t="s">
+      <c r="T49" s="126" t="s">
         <v>23</v>
       </c>
-      <c r="U49" s="58"/>
-      <c r="V49" s="58"/>
-      <c r="W49" s="58"/>
-      <c r="X49" s="58"/>
-      <c r="Y49" s="58"/>
-      <c r="Z49" s="58"/>
-      <c r="AA49" s="59"/>
-      <c r="AB49" s="102" t="s">
+      <c r="U49" s="126"/>
+      <c r="V49" s="126"/>
+      <c r="W49" s="126"/>
+      <c r="X49" s="126"/>
+      <c r="Y49" s="126"/>
+      <c r="Z49" s="126"/>
+      <c r="AA49" s="127"/>
+      <c r="AB49" s="128" t="s">
         <v>79</v>
       </c>
-      <c r="AC49" s="103"/>
-      <c r="AD49" s="103"/>
-      <c r="AE49" s="103"/>
-      <c r="AF49" s="103"/>
-      <c r="AG49" s="62"/>
-      <c r="AH49" s="62"/>
-      <c r="AI49" s="62"/>
+      <c r="AC49" s="129"/>
+      <c r="AD49" s="129"/>
+      <c r="AE49" s="129"/>
+      <c r="AF49" s="129"/>
+      <c r="AG49" s="145"/>
+      <c r="AH49" s="145"/>
+      <c r="AI49" s="145"/>
       <c r="AJ49" s="33" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="50" spans="1:36" ht="18" customHeight="1">
       <c r="A50" s="10"/>
-      <c r="B50" s="58" t="s">
+      <c r="B50" s="126" t="s">
         <v>75</v>
       </c>
-      <c r="C50" s="58"/>
-      <c r="D50" s="58"/>
-      <c r="E50" s="58"/>
-      <c r="F50" s="58"/>
-      <c r="G50" s="58"/>
-      <c r="H50" s="58"/>
-      <c r="I50" s="59"/>
+      <c r="C50" s="126"/>
+      <c r="D50" s="126"/>
+      <c r="E50" s="126"/>
+      <c r="F50" s="126"/>
+      <c r="G50" s="126"/>
+      <c r="H50" s="126"/>
+      <c r="I50" s="127"/>
       <c r="J50" s="10"/>
-      <c r="K50" s="58" t="s">
+      <c r="K50" s="126" t="s">
         <v>39</v>
       </c>
-      <c r="L50" s="58"/>
-      <c r="M50" s="58"/>
-      <c r="N50" s="58"/>
-      <c r="O50" s="58"/>
-      <c r="P50" s="58"/>
-      <c r="Q50" s="58"/>
-      <c r="R50" s="59"/>
+      <c r="L50" s="126"/>
+      <c r="M50" s="126"/>
+      <c r="N50" s="126"/>
+      <c r="O50" s="126"/>
+      <c r="P50" s="126"/>
+      <c r="Q50" s="126"/>
+      <c r="R50" s="127"/>
       <c r="S50" s="10"/>
-      <c r="T50" s="58" t="s">
+      <c r="T50" s="126" t="s">
         <v>26</v>
       </c>
-      <c r="U50" s="58"/>
-      <c r="V50" s="58"/>
-      <c r="W50" s="58"/>
-      <c r="X50" s="58"/>
-      <c r="Y50" s="58"/>
-      <c r="Z50" s="58"/>
-      <c r="AA50" s="59"/>
-      <c r="AB50" s="105" t="s">
+      <c r="U50" s="126"/>
+      <c r="V50" s="126"/>
+      <c r="W50" s="126"/>
+      <c r="X50" s="126"/>
+      <c r="Y50" s="126"/>
+      <c r="Z50" s="126"/>
+      <c r="AA50" s="127"/>
+      <c r="AB50" s="132" t="s">
         <v>38</v>
       </c>
-      <c r="AC50" s="106"/>
-      <c r="AD50" s="106"/>
-      <c r="AE50" s="106"/>
-      <c r="AF50" s="106"/>
-      <c r="AG50" s="106"/>
-      <c r="AH50" s="106"/>
-      <c r="AI50" s="106"/>
-      <c r="AJ50" s="107"/>
+      <c r="AC50" s="133"/>
+      <c r="AD50" s="133"/>
+      <c r="AE50" s="133"/>
+      <c r="AF50" s="133"/>
+      <c r="AG50" s="133"/>
+      <c r="AH50" s="133"/>
+      <c r="AI50" s="133"/>
+      <c r="AJ50" s="134"/>
     </row>
     <row r="51" spans="1:36" ht="18" customHeight="1">
       <c r="A51" s="10"/>
-      <c r="B51" s="58" t="s">
+      <c r="B51" s="126" t="s">
         <v>40</v>
       </c>
-      <c r="C51" s="58"/>
-      <c r="D51" s="58"/>
-      <c r="E51" s="58"/>
-      <c r="F51" s="58"/>
-      <c r="G51" s="58"/>
-      <c r="H51" s="58"/>
-      <c r="I51" s="59"/>
+      <c r="C51" s="126"/>
+      <c r="D51" s="126"/>
+      <c r="E51" s="126"/>
+      <c r="F51" s="126"/>
+      <c r="G51" s="126"/>
+      <c r="H51" s="126"/>
+      <c r="I51" s="127"/>
       <c r="J51" s="10"/>
-      <c r="K51" s="58" t="s">
+      <c r="K51" s="126" t="s">
         <v>41</v>
       </c>
-      <c r="L51" s="58"/>
-      <c r="M51" s="58"/>
-      <c r="N51" s="58"/>
-      <c r="O51" s="58"/>
-      <c r="P51" s="58"/>
-      <c r="Q51" s="58"/>
-      <c r="R51" s="59"/>
+      <c r="L51" s="126"/>
+      <c r="M51" s="126"/>
+      <c r="N51" s="126"/>
+      <c r="O51" s="126"/>
+      <c r="P51" s="126"/>
+      <c r="Q51" s="126"/>
+      <c r="R51" s="127"/>
       <c r="S51" s="10"/>
-      <c r="T51" s="58" t="s">
+      <c r="T51" s="126" t="s">
         <v>29</v>
       </c>
-      <c r="U51" s="58"/>
-      <c r="V51" s="58"/>
-      <c r="W51" s="94"/>
-      <c r="X51" s="94"/>
-      <c r="Y51" s="94"/>
+      <c r="U51" s="126"/>
+      <c r="V51" s="126"/>
+      <c r="W51" s="125"/>
+      <c r="X51" s="125"/>
+      <c r="Y51" s="125"/>
       <c r="Z51" s="3" t="s">
         <v>30</v>
       </c>
       <c r="AA51" s="4"/>
       <c r="AB51" s="10"/>
-      <c r="AC51" s="108" t="s">
+      <c r="AC51" s="135" t="s">
         <v>76</v>
       </c>
-      <c r="AD51" s="108"/>
-      <c r="AE51" s="108"/>
-      <c r="AF51" s="108"/>
-      <c r="AG51" s="108"/>
-      <c r="AH51" s="108"/>
-      <c r="AI51" s="108"/>
-      <c r="AJ51" s="109"/>
+      <c r="AD51" s="135"/>
+      <c r="AE51" s="135"/>
+      <c r="AF51" s="135"/>
+      <c r="AG51" s="135"/>
+      <c r="AH51" s="135"/>
+      <c r="AI51" s="135"/>
+      <c r="AJ51" s="136"/>
     </row>
     <row r="52" spans="1:36" ht="18" customHeight="1">
       <c r="A52" s="10"/>
-      <c r="B52" s="58" t="s">
+      <c r="B52" s="126" t="s">
         <v>43</v>
       </c>
-      <c r="C52" s="58"/>
-      <c r="D52" s="110"/>
-      <c r="E52" s="110"/>
-      <c r="F52" s="110"/>
-      <c r="G52" s="110"/>
-      <c r="H52" s="110"/>
+      <c r="C52" s="126"/>
+      <c r="D52" s="137"/>
+      <c r="E52" s="137"/>
+      <c r="F52" s="137"/>
+      <c r="G52" s="137"/>
+      <c r="H52" s="137"/>
       <c r="I52" s="4"/>
       <c r="J52" s="10"/>
-      <c r="K52" s="58" t="s">
+      <c r="K52" s="126" t="s">
         <v>44</v>
       </c>
-      <c r="L52" s="58"/>
-      <c r="M52" s="58"/>
-      <c r="N52" s="58"/>
-      <c r="O52" s="58"/>
-      <c r="P52" s="58"/>
-      <c r="Q52" s="58"/>
-      <c r="R52" s="59"/>
+      <c r="L52" s="126"/>
+      <c r="M52" s="126"/>
+      <c r="N52" s="126"/>
+      <c r="O52" s="126"/>
+      <c r="P52" s="126"/>
+      <c r="Q52" s="126"/>
+      <c r="R52" s="127"/>
       <c r="S52" s="10"/>
-      <c r="T52" s="58" t="s">
+      <c r="T52" s="126" t="s">
         <v>32</v>
       </c>
-      <c r="U52" s="58"/>
-      <c r="V52" s="58"/>
-      <c r="W52" s="94"/>
-      <c r="X52" s="94"/>
-      <c r="Y52" s="94"/>
+      <c r="U52" s="126"/>
+      <c r="V52" s="126"/>
+      <c r="W52" s="125"/>
+      <c r="X52" s="125"/>
+      <c r="Y52" s="125"/>
       <c r="Z52" s="3" t="s">
         <v>30</v>
       </c>
       <c r="AA52" s="4"/>
       <c r="AB52" s="10"/>
-      <c r="AC52" s="58" t="s">
+      <c r="AC52" s="126" t="s">
         <v>42</v>
       </c>
-      <c r="AD52" s="58"/>
-      <c r="AE52" s="58"/>
-      <c r="AF52" s="58"/>
-      <c r="AG52" s="58"/>
-      <c r="AH52" s="58"/>
-      <c r="AI52" s="58"/>
-      <c r="AJ52" s="59"/>
+      <c r="AD52" s="126"/>
+      <c r="AE52" s="126"/>
+      <c r="AF52" s="126"/>
+      <c r="AG52" s="126"/>
+      <c r="AH52" s="126"/>
+      <c r="AI52" s="126"/>
+      <c r="AJ52" s="127"/>
     </row>
     <row r="53" spans="1:36" ht="18" customHeight="1">
       <c r="A53" s="13"/>
       <c r="B53" s="7"/>
       <c r="C53" s="7"/>
-      <c r="D53" s="99"/>
-      <c r="E53" s="99"/>
-      <c r="F53" s="99"/>
-      <c r="G53" s="99"/>
-      <c r="H53" s="99"/>
+      <c r="D53" s="148"/>
+      <c r="E53" s="148"/>
+      <c r="F53" s="148"/>
+      <c r="G53" s="148"/>
+      <c r="H53" s="148"/>
       <c r="I53" s="8"/>
-      <c r="J53" s="102"/>
-      <c r="K53" s="103"/>
-      <c r="L53" s="103"/>
-      <c r="M53" s="103"/>
-      <c r="N53" s="103"/>
-      <c r="O53" s="103"/>
-      <c r="P53" s="103"/>
-      <c r="Q53" s="103"/>
-      <c r="R53" s="111"/>
+      <c r="J53" s="128"/>
+      <c r="K53" s="129"/>
+      <c r="L53" s="129"/>
+      <c r="M53" s="129"/>
+      <c r="N53" s="129"/>
+      <c r="O53" s="129"/>
+      <c r="P53" s="129"/>
+      <c r="Q53" s="129"/>
+      <c r="R53" s="130"/>
       <c r="S53" s="13"/>
-      <c r="T53" s="95" t="s">
+      <c r="T53" s="144" t="s">
         <v>35</v>
       </c>
-      <c r="U53" s="95"/>
-      <c r="V53" s="95"/>
-      <c r="W53" s="62"/>
-      <c r="X53" s="62"/>
-      <c r="Y53" s="62"/>
+      <c r="U53" s="144"/>
+      <c r="V53" s="144"/>
+      <c r="W53" s="145"/>
+      <c r="X53" s="145"/>
+      <c r="Y53" s="145"/>
       <c r="Z53" s="6" t="s">
         <v>36</v>
       </c>
       <c r="AA53" s="8"/>
       <c r="AB53" s="13"/>
-      <c r="AC53" s="95" t="s">
+      <c r="AC53" s="144" t="s">
         <v>45</v>
       </c>
-      <c r="AD53" s="95"/>
-      <c r="AE53" s="95"/>
-      <c r="AF53" s="104"/>
-      <c r="AG53" s="104"/>
-      <c r="AH53" s="104"/>
+      <c r="AD53" s="144"/>
+      <c r="AE53" s="144"/>
+      <c r="AF53" s="100"/>
+      <c r="AG53" s="100"/>
+      <c r="AH53" s="100"/>
       <c r="AI53" s="7"/>
       <c r="AJ53" s="8"/>
     </row>
     <row r="54" spans="1:36" ht="18" customHeight="1">
-      <c r="A54" s="97" t="s">
+      <c r="A54" s="146" t="s">
         <v>46</v>
       </c>
-      <c r="B54" s="97"/>
-      <c r="C54" s="97"/>
-      <c r="D54" s="97"/>
-      <c r="E54" s="97"/>
-      <c r="F54" s="97"/>
-      <c r="G54" s="97"/>
-      <c r="H54" s="97"/>
-      <c r="I54" s="97"/>
-      <c r="J54" s="97"/>
-      <c r="K54" s="97"/>
-      <c r="L54" s="97"/>
-      <c r="M54" s="97"/>
-      <c r="N54" s="98"/>
-      <c r="O54" s="98"/>
-      <c r="P54" s="98"/>
-      <c r="Q54" s="98"/>
-      <c r="R54" s="98"/>
-      <c r="S54" s="98"/>
-      <c r="T54" s="98"/>
-      <c r="U54" s="98"/>
-      <c r="V54" s="98"/>
-      <c r="W54" s="98"/>
-      <c r="X54" s="98"/>
-      <c r="Y54" s="98"/>
-      <c r="Z54" s="98"/>
-      <c r="AA54" s="98"/>
-      <c r="AB54" s="98"/>
-      <c r="AC54" s="98"/>
-      <c r="AD54" s="98"/>
-      <c r="AE54" s="98"/>
-      <c r="AF54" s="98"/>
-      <c r="AG54" s="98"/>
-      <c r="AH54" s="98"/>
-      <c r="AI54" s="98"/>
-      <c r="AJ54" s="98"/>
+      <c r="B54" s="146"/>
+      <c r="C54" s="146"/>
+      <c r="D54" s="146"/>
+      <c r="E54" s="146"/>
+      <c r="F54" s="146"/>
+      <c r="G54" s="146"/>
+      <c r="H54" s="146"/>
+      <c r="I54" s="146"/>
+      <c r="J54" s="146"/>
+      <c r="K54" s="146"/>
+      <c r="L54" s="146"/>
+      <c r="M54" s="146"/>
+      <c r="N54" s="147"/>
+      <c r="O54" s="147"/>
+      <c r="P54" s="147"/>
+      <c r="Q54" s="147"/>
+      <c r="R54" s="147"/>
+      <c r="S54" s="147"/>
+      <c r="T54" s="147"/>
+      <c r="U54" s="147"/>
+      <c r="V54" s="147"/>
+      <c r="W54" s="147"/>
+      <c r="X54" s="147"/>
+      <c r="Y54" s="147"/>
+      <c r="Z54" s="147"/>
+      <c r="AA54" s="147"/>
+      <c r="AB54" s="147"/>
+      <c r="AC54" s="147"/>
+      <c r="AD54" s="147"/>
+      <c r="AE54" s="147"/>
+      <c r="AF54" s="147"/>
+      <c r="AG54" s="147"/>
+      <c r="AH54" s="147"/>
+      <c r="AI54" s="147"/>
+      <c r="AJ54" s="147"/>
     </row>
     <row r="55" spans="1:36" ht="18" customHeight="1">
-      <c r="A55" s="88"/>
-      <c r="B55" s="96"/>
-      <c r="C55" s="96"/>
-      <c r="D55" s="96"/>
-      <c r="E55" s="96"/>
-      <c r="F55" s="96"/>
-      <c r="G55" s="96"/>
-      <c r="H55" s="96"/>
-      <c r="I55" s="96"/>
-      <c r="J55" s="96"/>
-      <c r="K55" s="96"/>
-      <c r="L55" s="96"/>
-      <c r="N55" s="96"/>
-      <c r="O55" s="96"/>
-      <c r="P55" s="96"/>
-      <c r="Q55" s="96"/>
-      <c r="R55" s="96"/>
-      <c r="S55" s="96"/>
-      <c r="T55" s="96"/>
-      <c r="U55" s="96"/>
-      <c r="V55" s="96"/>
-      <c r="W55" s="96"/>
-      <c r="X55" s="96"/>
-      <c r="Y55" s="88"/>
-      <c r="Z55" s="88"/>
-      <c r="AA55" s="88"/>
-      <c r="AB55" s="100" t="s">
+      <c r="A55" s="139"/>
+      <c r="B55" s="67"/>
+      <c r="C55" s="67"/>
+      <c r="D55" s="67"/>
+      <c r="E55" s="67"/>
+      <c r="F55" s="67"/>
+      <c r="G55" s="67"/>
+      <c r="H55" s="67"/>
+      <c r="I55" s="67"/>
+      <c r="J55" s="67"/>
+      <c r="K55" s="67"/>
+      <c r="L55" s="67"/>
+      <c r="N55" s="67"/>
+      <c r="O55" s="67"/>
+      <c r="P55" s="67"/>
+      <c r="Q55" s="67"/>
+      <c r="R55" s="67"/>
+      <c r="S55" s="67"/>
+      <c r="T55" s="67"/>
+      <c r="U55" s="67"/>
+      <c r="V55" s="67"/>
+      <c r="W55" s="67"/>
+      <c r="X55" s="67"/>
+      <c r="Y55" s="139"/>
+      <c r="Z55" s="139"/>
+      <c r="AA55" s="139"/>
+      <c r="AB55" s="149" t="s">
         <v>93</v>
       </c>
-      <c r="AC55" s="101"/>
-      <c r="AD55" s="101"/>
-      <c r="AE55" s="101"/>
-      <c r="AF55" s="101"/>
-      <c r="AG55" s="101"/>
-      <c r="AH55" s="101"/>
-      <c r="AI55" s="101"/>
-      <c r="AJ55" s="101"/>
+      <c r="AC55" s="99"/>
+      <c r="AD55" s="99"/>
+      <c r="AE55" s="99"/>
+      <c r="AF55" s="99"/>
+      <c r="AG55" s="99"/>
+      <c r="AH55" s="99"/>
+      <c r="AI55" s="99"/>
+      <c r="AJ55" s="99"/>
     </row>
     <row r="56" spans="1:36" ht="18" customHeight="1">
-      <c r="A56" s="88"/>
-      <c r="B56" s="96"/>
-      <c r="C56" s="96"/>
-      <c r="D56" s="96"/>
-      <c r="E56" s="96"/>
-      <c r="F56" s="96"/>
-      <c r="G56" s="96"/>
-      <c r="H56" s="96"/>
-      <c r="I56" s="96"/>
-      <c r="J56" s="96"/>
-      <c r="K56" s="96"/>
-      <c r="L56" s="96"/>
-      <c r="N56" s="96"/>
-      <c r="O56" s="96"/>
-      <c r="P56" s="96"/>
-      <c r="Q56" s="96"/>
-      <c r="R56" s="96"/>
-      <c r="S56" s="96"/>
-      <c r="T56" s="96"/>
-      <c r="U56" s="96"/>
-      <c r="V56" s="96"/>
-      <c r="W56" s="96"/>
-      <c r="X56" s="96"/>
-      <c r="Y56" s="88"/>
-      <c r="Z56" s="88"/>
-      <c r="AA56" s="88"/>
-      <c r="AB56" s="90" t="s">
+      <c r="A56" s="139"/>
+      <c r="B56" s="67"/>
+      <c r="C56" s="67"/>
+      <c r="D56" s="67"/>
+      <c r="E56" s="67"/>
+      <c r="F56" s="67"/>
+      <c r="G56" s="67"/>
+      <c r="H56" s="67"/>
+      <c r="I56" s="67"/>
+      <c r="J56" s="67"/>
+      <c r="K56" s="67"/>
+      <c r="L56" s="67"/>
+      <c r="N56" s="67"/>
+      <c r="O56" s="67"/>
+      <c r="P56" s="67"/>
+      <c r="Q56" s="67"/>
+      <c r="R56" s="67"/>
+      <c r="S56" s="67"/>
+      <c r="T56" s="67"/>
+      <c r="U56" s="67"/>
+      <c r="V56" s="67"/>
+      <c r="W56" s="67"/>
+      <c r="X56" s="67"/>
+      <c r="Y56" s="139"/>
+      <c r="Z56" s="139"/>
+      <c r="AA56" s="139"/>
+      <c r="AB56" s="140" t="s">
         <v>47</v>
       </c>
-      <c r="AC56" s="90"/>
-      <c r="AD56" s="90"/>
-      <c r="AE56" s="90"/>
-      <c r="AF56" s="90"/>
-      <c r="AG56" s="90"/>
-      <c r="AH56" s="90"/>
-      <c r="AI56" s="90"/>
-      <c r="AJ56" s="90"/>
+      <c r="AC56" s="140"/>
+      <c r="AD56" s="140"/>
+      <c r="AE56" s="140"/>
+      <c r="AF56" s="140"/>
+      <c r="AG56" s="140"/>
+      <c r="AH56" s="140"/>
+      <c r="AI56" s="140"/>
+      <c r="AJ56" s="140"/>
     </row>
     <row r="57" spans="1:36" ht="18" customHeight="1">
-      <c r="A57" s="88"/>
-      <c r="B57" s="96"/>
-      <c r="C57" s="96"/>
-      <c r="D57" s="96"/>
-      <c r="E57" s="96"/>
-      <c r="F57" s="96"/>
-      <c r="G57" s="96"/>
-      <c r="H57" s="96"/>
-      <c r="I57" s="96"/>
-      <c r="J57" s="96"/>
-      <c r="K57" s="96"/>
-      <c r="L57" s="96"/>
-      <c r="N57" s="96"/>
-      <c r="O57" s="96"/>
-      <c r="P57" s="96"/>
-      <c r="Q57" s="96"/>
-      <c r="R57" s="96"/>
-      <c r="S57" s="96"/>
-      <c r="T57" s="96"/>
-      <c r="U57" s="96"/>
-      <c r="V57" s="96"/>
-      <c r="W57" s="96"/>
-      <c r="X57" s="96"/>
-      <c r="Y57" s="88"/>
-      <c r="Z57" s="88"/>
-      <c r="AA57" s="88"/>
-      <c r="AB57" s="88"/>
-      <c r="AC57" s="88"/>
-      <c r="AD57" s="88"/>
-      <c r="AE57" s="88"/>
-      <c r="AF57" s="88"/>
-      <c r="AG57" s="88"/>
-      <c r="AH57" s="88"/>
-      <c r="AI57" s="88"/>
-      <c r="AJ57" s="88"/>
+      <c r="A57" s="139"/>
+      <c r="B57" s="67"/>
+      <c r="C57" s="67"/>
+      <c r="D57" s="67"/>
+      <c r="E57" s="67"/>
+      <c r="F57" s="67"/>
+      <c r="G57" s="67"/>
+      <c r="H57" s="67"/>
+      <c r="I57" s="67"/>
+      <c r="J57" s="67"/>
+      <c r="K57" s="67"/>
+      <c r="L57" s="67"/>
+      <c r="N57" s="67"/>
+      <c r="O57" s="67"/>
+      <c r="P57" s="67"/>
+      <c r="Q57" s="67"/>
+      <c r="R57" s="67"/>
+      <c r="S57" s="67"/>
+      <c r="T57" s="67"/>
+      <c r="U57" s="67"/>
+      <c r="V57" s="67"/>
+      <c r="W57" s="67"/>
+      <c r="X57" s="67"/>
+      <c r="Y57" s="139"/>
+      <c r="Z57" s="139"/>
+      <c r="AA57" s="139"/>
+      <c r="AB57" s="139"/>
+      <c r="AC57" s="139"/>
+      <c r="AD57" s="139"/>
+      <c r="AE57" s="139"/>
+      <c r="AF57" s="139"/>
+      <c r="AG57" s="139"/>
+      <c r="AH57" s="139"/>
+      <c r="AI57" s="139"/>
+      <c r="AJ57" s="139"/>
     </row>
     <row r="58" spans="1:36" ht="18" customHeight="1">
       <c r="A58" s="51"/>
@@ -9378,72 +9367,72 @@
       <c r="V58" s="52"/>
       <c r="W58" s="52"/>
       <c r="X58" s="52"/>
-      <c r="Y58" s="88"/>
-      <c r="Z58" s="88"/>
-      <c r="AA58" s="88"/>
-      <c r="AB58" s="88"/>
-      <c r="AC58" s="88"/>
-      <c r="AD58" s="88"/>
-      <c r="AE58" s="88"/>
-      <c r="AF58" s="88"/>
-      <c r="AG58" s="88"/>
-      <c r="AH58" s="88"/>
-      <c r="AI58" s="88"/>
-      <c r="AJ58" s="88"/>
+      <c r="Y58" s="139"/>
+      <c r="Z58" s="139"/>
+      <c r="AA58" s="139"/>
+      <c r="AB58" s="139"/>
+      <c r="AC58" s="139"/>
+      <c r="AD58" s="139"/>
+      <c r="AE58" s="139"/>
+      <c r="AF58" s="139"/>
+      <c r="AG58" s="139"/>
+      <c r="AH58" s="139"/>
+      <c r="AI58" s="139"/>
+      <c r="AJ58" s="139"/>
     </row>
     <row r="59" spans="1:36" ht="18" customHeight="1">
-      <c r="A59" s="88"/>
-      <c r="B59" s="88"/>
-      <c r="C59" s="88"/>
-      <c r="D59" s="88"/>
-      <c r="E59" s="88"/>
-      <c r="F59" s="88"/>
-      <c r="G59" s="88"/>
-      <c r="H59" s="88"/>
-      <c r="I59" s="88"/>
-      <c r="J59" s="88"/>
-      <c r="K59" s="88"/>
-      <c r="L59" s="88"/>
-      <c r="M59" s="88"/>
-      <c r="N59" s="88"/>
-      <c r="O59" s="88"/>
-      <c r="P59" s="88"/>
-      <c r="Q59" s="88"/>
-      <c r="R59" s="88"/>
-      <c r="S59" s="88"/>
-      <c r="T59" s="88"/>
-      <c r="U59" s="88"/>
-      <c r="V59" s="88"/>
-      <c r="W59" s="88"/>
-      <c r="X59" s="88"/>
-      <c r="Y59" s="88"/>
-      <c r="Z59" s="88"/>
-      <c r="AA59" s="88"/>
-      <c r="AB59" s="89"/>
-      <c r="AC59" s="89"/>
-      <c r="AD59" s="89"/>
-      <c r="AE59" s="89"/>
-      <c r="AF59" s="89"/>
-      <c r="AG59" s="89"/>
-      <c r="AH59" s="89"/>
-      <c r="AI59" s="89"/>
-      <c r="AJ59" s="89"/>
+      <c r="A59" s="139"/>
+      <c r="B59" s="139"/>
+      <c r="C59" s="139"/>
+      <c r="D59" s="139"/>
+      <c r="E59" s="139"/>
+      <c r="F59" s="139"/>
+      <c r="G59" s="139"/>
+      <c r="H59" s="139"/>
+      <c r="I59" s="139"/>
+      <c r="J59" s="139"/>
+      <c r="K59" s="139"/>
+      <c r="L59" s="139"/>
+      <c r="M59" s="139"/>
+      <c r="N59" s="139"/>
+      <c r="O59" s="139"/>
+      <c r="P59" s="139"/>
+      <c r="Q59" s="139"/>
+      <c r="R59" s="139"/>
+      <c r="S59" s="139"/>
+      <c r="T59" s="139"/>
+      <c r="U59" s="139"/>
+      <c r="V59" s="139"/>
+      <c r="W59" s="139"/>
+      <c r="X59" s="139"/>
+      <c r="Y59" s="139"/>
+      <c r="Z59" s="139"/>
+      <c r="AA59" s="139"/>
+      <c r="AB59" s="82"/>
+      <c r="AC59" s="82"/>
+      <c r="AD59" s="82"/>
+      <c r="AE59" s="82"/>
+      <c r="AF59" s="82"/>
+      <c r="AG59" s="82"/>
+      <c r="AH59" s="82"/>
+      <c r="AI59" s="82"/>
+      <c r="AJ59" s="82"/>
     </row>
     <row r="60" spans="1:36" ht="18" customHeight="1">
-      <c r="Y60" s="88"/>
-      <c r="Z60" s="88"/>
-      <c r="AA60" s="88"/>
-      <c r="AB60" s="87" t="s">
+      <c r="Y60" s="139"/>
+      <c r="Z60" s="139"/>
+      <c r="AA60" s="139"/>
+      <c r="AB60" s="138" t="s">
         <v>92</v>
       </c>
-      <c r="AC60" s="87"/>
-      <c r="AD60" s="87"/>
-      <c r="AE60" s="87"/>
-      <c r="AF60" s="87"/>
-      <c r="AG60" s="87"/>
-      <c r="AH60" s="87"/>
-      <c r="AI60" s="87"/>
-      <c r="AJ60" s="87"/>
+      <c r="AC60" s="138"/>
+      <c r="AD60" s="138"/>
+      <c r="AE60" s="138"/>
+      <c r="AF60" s="138"/>
+      <c r="AG60" s="138"/>
+      <c r="AH60" s="138"/>
+      <c r="AI60" s="138"/>
+      <c r="AJ60" s="138"/>
     </row>
     <row r="61" spans="1:36" ht="16.5" customHeight="1"/>
     <row r="62" spans="1:36" ht="18" hidden="1" customHeight="1"/>
@@ -10044,90 +10033,31 @@
     <row r="657"/>
     <row r="658"/>
   </sheetData>
-  <mergeCells count="131">
-    <mergeCell ref="AD3:AJ3"/>
-    <mergeCell ref="Y5:Z5"/>
-    <mergeCell ref="P5:X5"/>
-    <mergeCell ref="AH6:AI6"/>
-    <mergeCell ref="AC7:AE7"/>
-    <mergeCell ref="AI7:AJ7"/>
-    <mergeCell ref="C6:I6"/>
-    <mergeCell ref="S8:W8"/>
-    <mergeCell ref="X7:AB7"/>
-    <mergeCell ref="AC6:AD6"/>
-    <mergeCell ref="B57:L57"/>
-    <mergeCell ref="N57:X57"/>
-    <mergeCell ref="Q2:Z2"/>
-    <mergeCell ref="Q3:Z3"/>
-    <mergeCell ref="A11:P11"/>
-    <mergeCell ref="K5:O5"/>
-    <mergeCell ref="K6:O6"/>
-    <mergeCell ref="P6:X6"/>
-    <mergeCell ref="A41:R41"/>
-    <mergeCell ref="S9:W9"/>
-    <mergeCell ref="A7:B7"/>
-    <mergeCell ref="Q11:AJ11"/>
-    <mergeCell ref="C7:I7"/>
-    <mergeCell ref="D8:R8"/>
-    <mergeCell ref="A8:C8"/>
-    <mergeCell ref="S7:T7"/>
-    <mergeCell ref="P7:R7"/>
-    <mergeCell ref="X8:AJ8"/>
-    <mergeCell ref="A10:AJ10"/>
-    <mergeCell ref="A5:B5"/>
-    <mergeCell ref="A6:B6"/>
-    <mergeCell ref="D9:R9"/>
-    <mergeCell ref="K7:O7"/>
-    <mergeCell ref="A25:AJ25"/>
-    <mergeCell ref="A22:AJ23"/>
-    <mergeCell ref="A17:T20"/>
-    <mergeCell ref="C5:I5"/>
-    <mergeCell ref="AF19:AG19"/>
-    <mergeCell ref="A43:I43"/>
-    <mergeCell ref="AI19:AJ19"/>
-    <mergeCell ref="A14:H14"/>
-    <mergeCell ref="I14:AJ14"/>
-    <mergeCell ref="AI17:AJ17"/>
-    <mergeCell ref="AF17:AG17"/>
-    <mergeCell ref="A15:AJ15"/>
-    <mergeCell ref="AF18:AG18"/>
-    <mergeCell ref="AA5:AJ5"/>
-    <mergeCell ref="V7:W7"/>
-    <mergeCell ref="AI18:AJ18"/>
-    <mergeCell ref="U16:AD16"/>
-    <mergeCell ref="AF7:AG7"/>
-    <mergeCell ref="AE16:AJ16"/>
-    <mergeCell ref="A16:T16"/>
-    <mergeCell ref="A9:C9"/>
-    <mergeCell ref="X9:AJ9"/>
-    <mergeCell ref="AB46:AE46"/>
-    <mergeCell ref="S44:V44"/>
-    <mergeCell ref="S45:V45"/>
-    <mergeCell ref="S46:W46"/>
-    <mergeCell ref="X46:Z46"/>
-    <mergeCell ref="K46:R46"/>
-    <mergeCell ref="K45:R45"/>
-    <mergeCell ref="AB44:AE44"/>
-    <mergeCell ref="J53:R53"/>
-    <mergeCell ref="AB45:AE45"/>
-    <mergeCell ref="K44:R44"/>
-    <mergeCell ref="B48:I48"/>
-    <mergeCell ref="AF47:AI47"/>
-    <mergeCell ref="AB49:AF49"/>
-    <mergeCell ref="AF53:AH53"/>
-    <mergeCell ref="AB50:AJ50"/>
-    <mergeCell ref="AC51:AJ51"/>
-    <mergeCell ref="B49:I49"/>
-    <mergeCell ref="B52:C52"/>
-    <mergeCell ref="D52:H52"/>
-    <mergeCell ref="K50:R50"/>
-    <mergeCell ref="K51:R51"/>
-    <mergeCell ref="S47:W47"/>
-    <mergeCell ref="T49:AA49"/>
-    <mergeCell ref="K48:R48"/>
-    <mergeCell ref="K49:R49"/>
-    <mergeCell ref="W52:Y52"/>
-    <mergeCell ref="K47:R47"/>
+  <mergeCells count="126">
+    <mergeCell ref="AF46:AI46"/>
+    <mergeCell ref="T50:AA50"/>
+    <mergeCell ref="AF45:AI45"/>
+    <mergeCell ref="AB48:AF48"/>
+    <mergeCell ref="X47:Z47"/>
+    <mergeCell ref="AG49:AI49"/>
+    <mergeCell ref="W45:Z45"/>
+    <mergeCell ref="T51:V51"/>
+    <mergeCell ref="A27:AJ29"/>
+    <mergeCell ref="A36:R36"/>
+    <mergeCell ref="B47:I47"/>
+    <mergeCell ref="S43:AA43"/>
+    <mergeCell ref="B51:I51"/>
+    <mergeCell ref="AF44:AI44"/>
+    <mergeCell ref="A30:O30"/>
+    <mergeCell ref="B44:I44"/>
+    <mergeCell ref="AB43:AJ43"/>
+    <mergeCell ref="J43:R43"/>
+    <mergeCell ref="W44:Y44"/>
+    <mergeCell ref="A31:AJ35"/>
+    <mergeCell ref="A37:AJ40"/>
+    <mergeCell ref="B45:I45"/>
+    <mergeCell ref="AB47:AE47"/>
+    <mergeCell ref="B46:I46"/>
     <mergeCell ref="AB60:AJ60"/>
     <mergeCell ref="AB57:AJ59"/>
     <mergeCell ref="AB56:AJ56"/>
@@ -10152,30 +10082,84 @@
     <mergeCell ref="AB55:AJ55"/>
     <mergeCell ref="W51:Y51"/>
     <mergeCell ref="AC52:AJ52"/>
-    <mergeCell ref="AF46:AI46"/>
-    <mergeCell ref="T50:AA50"/>
-    <mergeCell ref="AF45:AI45"/>
-    <mergeCell ref="AB48:AF48"/>
-    <mergeCell ref="X47:Z47"/>
-    <mergeCell ref="AG49:AI49"/>
-    <mergeCell ref="W45:Z45"/>
-    <mergeCell ref="T51:V51"/>
-    <mergeCell ref="A27:AJ29"/>
-    <mergeCell ref="A36:R36"/>
-    <mergeCell ref="B47:I47"/>
-    <mergeCell ref="S43:AA43"/>
-    <mergeCell ref="B51:I51"/>
-    <mergeCell ref="AF44:AI44"/>
-    <mergeCell ref="A30:O30"/>
-    <mergeCell ref="B44:I44"/>
-    <mergeCell ref="AB43:AJ43"/>
-    <mergeCell ref="J43:R43"/>
-    <mergeCell ref="W44:Y44"/>
-    <mergeCell ref="A31:AJ35"/>
-    <mergeCell ref="A37:AJ40"/>
-    <mergeCell ref="B45:I45"/>
-    <mergeCell ref="AB47:AE47"/>
-    <mergeCell ref="B46:I46"/>
+    <mergeCell ref="B48:I48"/>
+    <mergeCell ref="AF47:AI47"/>
+    <mergeCell ref="AB49:AF49"/>
+    <mergeCell ref="AF53:AH53"/>
+    <mergeCell ref="AB50:AJ50"/>
+    <mergeCell ref="AC51:AJ51"/>
+    <mergeCell ref="B49:I49"/>
+    <mergeCell ref="B52:C52"/>
+    <mergeCell ref="D52:H52"/>
+    <mergeCell ref="K50:R50"/>
+    <mergeCell ref="K51:R51"/>
+    <mergeCell ref="S47:W47"/>
+    <mergeCell ref="T49:AA49"/>
+    <mergeCell ref="K48:R48"/>
+    <mergeCell ref="K49:R49"/>
+    <mergeCell ref="W52:Y52"/>
+    <mergeCell ref="K47:R47"/>
+    <mergeCell ref="AB46:AE46"/>
+    <mergeCell ref="S44:V44"/>
+    <mergeCell ref="S45:V45"/>
+    <mergeCell ref="S46:W46"/>
+    <mergeCell ref="X46:Z46"/>
+    <mergeCell ref="K46:R46"/>
+    <mergeCell ref="K45:R45"/>
+    <mergeCell ref="AB44:AE44"/>
+    <mergeCell ref="J53:R53"/>
+    <mergeCell ref="AB45:AE45"/>
+    <mergeCell ref="K44:R44"/>
+    <mergeCell ref="A22:AJ23"/>
+    <mergeCell ref="A17:T20"/>
+    <mergeCell ref="C5:I5"/>
+    <mergeCell ref="AF19:AG19"/>
+    <mergeCell ref="A43:I43"/>
+    <mergeCell ref="AI19:AJ19"/>
+    <mergeCell ref="A14:H14"/>
+    <mergeCell ref="I14:AJ14"/>
+    <mergeCell ref="AI17:AJ17"/>
+    <mergeCell ref="AF17:AG17"/>
+    <mergeCell ref="A15:AJ15"/>
+    <mergeCell ref="AF18:AG18"/>
+    <mergeCell ref="AA5:AJ5"/>
+    <mergeCell ref="V7:W7"/>
+    <mergeCell ref="AI18:AJ18"/>
+    <mergeCell ref="U16:AD16"/>
+    <mergeCell ref="AE16:AJ16"/>
+    <mergeCell ref="A16:T16"/>
+    <mergeCell ref="A9:C9"/>
+    <mergeCell ref="X9:AJ9"/>
+    <mergeCell ref="P7:T7"/>
+    <mergeCell ref="B57:L57"/>
+    <mergeCell ref="N57:X57"/>
+    <mergeCell ref="Q2:Z2"/>
+    <mergeCell ref="Q3:Z3"/>
+    <mergeCell ref="A11:P11"/>
+    <mergeCell ref="K5:O5"/>
+    <mergeCell ref="K6:O6"/>
+    <mergeCell ref="P6:X6"/>
+    <mergeCell ref="A41:R41"/>
+    <mergeCell ref="S9:W9"/>
+    <mergeCell ref="A7:B7"/>
+    <mergeCell ref="Q11:AJ11"/>
+    <mergeCell ref="C7:I7"/>
+    <mergeCell ref="D8:R8"/>
+    <mergeCell ref="A8:C8"/>
+    <mergeCell ref="X8:AJ8"/>
+    <mergeCell ref="A10:AJ10"/>
+    <mergeCell ref="A5:B5"/>
+    <mergeCell ref="A6:B6"/>
+    <mergeCell ref="D9:R9"/>
+    <mergeCell ref="K7:O7"/>
+    <mergeCell ref="A25:AJ25"/>
+    <mergeCell ref="AD3:AJ3"/>
+    <mergeCell ref="Y5:Z5"/>
+    <mergeCell ref="P5:X5"/>
+    <mergeCell ref="AI7:AJ7"/>
+    <mergeCell ref="C6:I6"/>
+    <mergeCell ref="S8:W8"/>
+    <mergeCell ref="X7:AB7"/>
   </mergeCells>
   <phoneticPr fontId="0" type="noConversion"/>
   <printOptions horizontalCentered="1"/>
@@ -10199,8 +10183,8 @@
                     <xdr:rowOff>30480</xdr:rowOff>
                   </from>
                   <to>
-                    <xdr:col>0</xdr:col>
-                    <xdr:colOff>327660</xdr:colOff>
+                    <xdr:col>1</xdr:col>
+                    <xdr:colOff>91440</xdr:colOff>
                     <xdr:row>12</xdr:row>
                     <xdr:rowOff>15240</xdr:rowOff>
                   </to>
@@ -10221,8 +10205,8 @@
                     <xdr:rowOff>7620</xdr:rowOff>
                   </from>
                   <to>
-                    <xdr:col>0</xdr:col>
-                    <xdr:colOff>327660</xdr:colOff>
+                    <xdr:col>1</xdr:col>
+                    <xdr:colOff>91440</xdr:colOff>
                     <xdr:row>13</xdr:row>
                     <xdr:rowOff>15240</xdr:rowOff>
                   </to>
@@ -10243,8 +10227,8 @@
                     <xdr:rowOff>30480</xdr:rowOff>
                   </from>
                   <to>
-                    <xdr:col>4</xdr:col>
-                    <xdr:colOff>327660</xdr:colOff>
+                    <xdr:col>5</xdr:col>
+                    <xdr:colOff>45720</xdr:colOff>
                     <xdr:row>12</xdr:row>
                     <xdr:rowOff>15240</xdr:rowOff>
                   </to>
@@ -10265,8 +10249,8 @@
                     <xdr:rowOff>7620</xdr:rowOff>
                   </from>
                   <to>
-                    <xdr:col>4</xdr:col>
-                    <xdr:colOff>327660</xdr:colOff>
+                    <xdr:col>5</xdr:col>
+                    <xdr:colOff>45720</xdr:colOff>
                     <xdr:row>13</xdr:row>
                     <xdr:rowOff>15240</xdr:rowOff>
                   </to>
@@ -10287,8 +10271,8 @@
                     <xdr:rowOff>30480</xdr:rowOff>
                   </from>
                   <to>
-                    <xdr:col>8</xdr:col>
-                    <xdr:colOff>396240</xdr:colOff>
+                    <xdr:col>9</xdr:col>
+                    <xdr:colOff>114300</xdr:colOff>
                     <xdr:row>12</xdr:row>
                     <xdr:rowOff>15240</xdr:rowOff>
                   </to>
@@ -10309,8 +10293,8 @@
                     <xdr:rowOff>7620</xdr:rowOff>
                   </from>
                   <to>
-                    <xdr:col>8</xdr:col>
-                    <xdr:colOff>396240</xdr:colOff>
+                    <xdr:col>9</xdr:col>
+                    <xdr:colOff>114300</xdr:colOff>
                     <xdr:row>13</xdr:row>
                     <xdr:rowOff>15240</xdr:rowOff>
                   </to>
@@ -10331,8 +10315,8 @@
                     <xdr:rowOff>30480</xdr:rowOff>
                   </from>
                   <to>
-                    <xdr:col>13</xdr:col>
-                    <xdr:colOff>327660</xdr:colOff>
+                    <xdr:col>14</xdr:col>
+                    <xdr:colOff>60960</xdr:colOff>
                     <xdr:row>12</xdr:row>
                     <xdr:rowOff>15240</xdr:rowOff>
                   </to>
@@ -10353,8 +10337,8 @@
                     <xdr:rowOff>7620</xdr:rowOff>
                   </from>
                   <to>
-                    <xdr:col>13</xdr:col>
-                    <xdr:colOff>327660</xdr:colOff>
+                    <xdr:col>14</xdr:col>
+                    <xdr:colOff>60960</xdr:colOff>
                     <xdr:row>13</xdr:row>
                     <xdr:rowOff>15240</xdr:rowOff>
                   </to>
@@ -10749,8 +10733,8 @@
                     <xdr:rowOff>30480</xdr:rowOff>
                   </from>
                   <to>
-                    <xdr:col>0</xdr:col>
-                    <xdr:colOff>365760</xdr:colOff>
+                    <xdr:col>1</xdr:col>
+                    <xdr:colOff>129540</xdr:colOff>
                     <xdr:row>44</xdr:row>
                     <xdr:rowOff>15240</xdr:rowOff>
                   </to>
@@ -10771,8 +10755,8 @@
                     <xdr:rowOff>30480</xdr:rowOff>
                   </from>
                   <to>
-                    <xdr:col>0</xdr:col>
-                    <xdr:colOff>365760</xdr:colOff>
+                    <xdr:col>1</xdr:col>
+                    <xdr:colOff>129540</xdr:colOff>
                     <xdr:row>45</xdr:row>
                     <xdr:rowOff>15240</xdr:rowOff>
                   </to>
@@ -10793,8 +10777,8 @@
                     <xdr:rowOff>30480</xdr:rowOff>
                   </from>
                   <to>
-                    <xdr:col>0</xdr:col>
-                    <xdr:colOff>365760</xdr:colOff>
+                    <xdr:col>1</xdr:col>
+                    <xdr:colOff>129540</xdr:colOff>
                     <xdr:row>46</xdr:row>
                     <xdr:rowOff>15240</xdr:rowOff>
                   </to>
@@ -10815,8 +10799,8 @@
                     <xdr:rowOff>30480</xdr:rowOff>
                   </from>
                   <to>
-                    <xdr:col>0</xdr:col>
-                    <xdr:colOff>365760</xdr:colOff>
+                    <xdr:col>1</xdr:col>
+                    <xdr:colOff>129540</xdr:colOff>
                     <xdr:row>47</xdr:row>
                     <xdr:rowOff>15240</xdr:rowOff>
                   </to>
@@ -10837,8 +10821,8 @@
                     <xdr:rowOff>30480</xdr:rowOff>
                   </from>
                   <to>
-                    <xdr:col>0</xdr:col>
-                    <xdr:colOff>365760</xdr:colOff>
+                    <xdr:col>1</xdr:col>
+                    <xdr:colOff>129540</xdr:colOff>
                     <xdr:row>48</xdr:row>
                     <xdr:rowOff>15240</xdr:rowOff>
                   </to>
@@ -10859,8 +10843,8 @@
                     <xdr:rowOff>30480</xdr:rowOff>
                   </from>
                   <to>
-                    <xdr:col>0</xdr:col>
-                    <xdr:colOff>365760</xdr:colOff>
+                    <xdr:col>1</xdr:col>
+                    <xdr:colOff>129540</xdr:colOff>
                     <xdr:row>49</xdr:row>
                     <xdr:rowOff>15240</xdr:rowOff>
                   </to>
@@ -10881,8 +10865,8 @@
                     <xdr:rowOff>30480</xdr:rowOff>
                   </from>
                   <to>
-                    <xdr:col>0</xdr:col>
-                    <xdr:colOff>365760</xdr:colOff>
+                    <xdr:col>1</xdr:col>
+                    <xdr:colOff>129540</xdr:colOff>
                     <xdr:row>50</xdr:row>
                     <xdr:rowOff>15240</xdr:rowOff>
                   </to>
@@ -10903,8 +10887,8 @@
                     <xdr:rowOff>30480</xdr:rowOff>
                   </from>
                   <to>
-                    <xdr:col>0</xdr:col>
-                    <xdr:colOff>365760</xdr:colOff>
+                    <xdr:col>1</xdr:col>
+                    <xdr:colOff>129540</xdr:colOff>
                     <xdr:row>51</xdr:row>
                     <xdr:rowOff>15240</xdr:rowOff>
                   </to>
@@ -10925,8 +10909,8 @@
                     <xdr:rowOff>30480</xdr:rowOff>
                   </from>
                   <to>
-                    <xdr:col>0</xdr:col>
-                    <xdr:colOff>365760</xdr:colOff>
+                    <xdr:col>1</xdr:col>
+                    <xdr:colOff>129540</xdr:colOff>
                     <xdr:row>52</xdr:row>
                     <xdr:rowOff>15240</xdr:rowOff>
                   </to>

--- a/backend_api/templates/container_report_template.xlsx
+++ b/backend_api/templates/container_report_template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Aaron Avila\Documents\ERP-SOM\backend_api\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FE6AAC90-F041-4099-8E87-E019DBF1C341}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6D9E4B4F-214D-4123-9BE6-96191302A10F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-1125" windowWidth="29040" windowHeight="15720" xr2:uid="{253FFB1B-D348-46B1-A532-0D44566D2FFD}"/>
   </bookViews>
@@ -1411,7 +1411,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="168">
+  <cellXfs count="169">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -1552,6 +1552,356 @@
     <xf numFmtId="14" fontId="13" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyProtection="1">
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="165" fontId="13" fillId="0" borderId="8" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="4" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="4" fontId="13" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="9" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="6" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="2" borderId="9" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="13" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="3" fontId="13" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="2" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="3" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="4" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="5" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="3" fontId="13" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="9" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="6" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="6" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="6" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="165" fontId="13" fillId="0" borderId="8" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="2" borderId="9" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="2" borderId="6" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="2" borderId="7" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
     <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
       <protection locked="0"/>
@@ -1560,9 +1910,6 @@
       <alignment horizontal="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="26" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
       <protection locked="0"/>
@@ -1571,365 +1918,23 @@
       <alignment horizontal="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="165" fontId="13" fillId="0" borderId="8" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="14" fontId="13" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
     <xf numFmtId="0" fontId="26" fillId="0" borderId="8" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="9" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="6" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="2" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="3" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="4" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="5" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="3" fontId="13" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="13" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="9" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="6" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="6" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="6" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="165" fontId="13" fillId="0" borderId="8" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="14" fontId="13" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="2" borderId="9" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="2" borderId="6" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="2" borderId="7" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="4" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="4" fontId="13" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="4" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="2" borderId="9" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="165" fontId="13" fillId="0" borderId="8" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="14" fontId="13" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <protection locked="0"/>
     </xf>
   </cellXfs>
@@ -2232,7 +2237,7 @@
         </xdr:from>
         <xdr:to>
           <xdr:col>1</xdr:col>
-          <xdr:colOff>91440</xdr:colOff>
+          <xdr:colOff>53340</xdr:colOff>
           <xdr:row>12</xdr:row>
           <xdr:rowOff>15240</xdr:rowOff>
         </xdr:to>
@@ -2299,7 +2304,7 @@
         </xdr:from>
         <xdr:to>
           <xdr:col>1</xdr:col>
-          <xdr:colOff>91440</xdr:colOff>
+          <xdr:colOff>53340</xdr:colOff>
           <xdr:row>13</xdr:row>
           <xdr:rowOff>15240</xdr:rowOff>
         </xdr:to>
@@ -2366,7 +2371,7 @@
         </xdr:from>
         <xdr:to>
           <xdr:col>5</xdr:col>
-          <xdr:colOff>40005</xdr:colOff>
+          <xdr:colOff>57150</xdr:colOff>
           <xdr:row>12</xdr:row>
           <xdr:rowOff>15240</xdr:rowOff>
         </xdr:to>
@@ -2433,7 +2438,7 @@
         </xdr:from>
         <xdr:to>
           <xdr:col>5</xdr:col>
-          <xdr:colOff>40005</xdr:colOff>
+          <xdr:colOff>57150</xdr:colOff>
           <xdr:row>13</xdr:row>
           <xdr:rowOff>15240</xdr:rowOff>
         </xdr:to>
@@ -2500,7 +2505,7 @@
         </xdr:from>
         <xdr:to>
           <xdr:col>9</xdr:col>
-          <xdr:colOff>112395</xdr:colOff>
+          <xdr:colOff>114300</xdr:colOff>
           <xdr:row>12</xdr:row>
           <xdr:rowOff>15240</xdr:rowOff>
         </xdr:to>
@@ -2567,7 +2572,7 @@
         </xdr:from>
         <xdr:to>
           <xdr:col>9</xdr:col>
-          <xdr:colOff>112395</xdr:colOff>
+          <xdr:colOff>114300</xdr:colOff>
           <xdr:row>13</xdr:row>
           <xdr:rowOff>15240</xdr:rowOff>
         </xdr:to>
@@ -3907,7 +3912,7 @@
         </xdr:from>
         <xdr:to>
           <xdr:col>1</xdr:col>
-          <xdr:colOff>129540</xdr:colOff>
+          <xdr:colOff>91440</xdr:colOff>
           <xdr:row>44</xdr:row>
           <xdr:rowOff>15240</xdr:rowOff>
         </xdr:to>
@@ -3974,7 +3979,7 @@
         </xdr:from>
         <xdr:to>
           <xdr:col>1</xdr:col>
-          <xdr:colOff>129540</xdr:colOff>
+          <xdr:colOff>91440</xdr:colOff>
           <xdr:row>45</xdr:row>
           <xdr:rowOff>15240</xdr:rowOff>
         </xdr:to>
@@ -4041,7 +4046,7 @@
         </xdr:from>
         <xdr:to>
           <xdr:col>1</xdr:col>
-          <xdr:colOff>129540</xdr:colOff>
+          <xdr:colOff>91440</xdr:colOff>
           <xdr:row>46</xdr:row>
           <xdr:rowOff>15240</xdr:rowOff>
         </xdr:to>
@@ -4108,7 +4113,7 @@
         </xdr:from>
         <xdr:to>
           <xdr:col>1</xdr:col>
-          <xdr:colOff>129540</xdr:colOff>
+          <xdr:colOff>91440</xdr:colOff>
           <xdr:row>47</xdr:row>
           <xdr:rowOff>15240</xdr:rowOff>
         </xdr:to>
@@ -4175,7 +4180,7 @@
         </xdr:from>
         <xdr:to>
           <xdr:col>1</xdr:col>
-          <xdr:colOff>129540</xdr:colOff>
+          <xdr:colOff>91440</xdr:colOff>
           <xdr:row>48</xdr:row>
           <xdr:rowOff>15240</xdr:rowOff>
         </xdr:to>
@@ -4242,7 +4247,7 @@
         </xdr:from>
         <xdr:to>
           <xdr:col>1</xdr:col>
-          <xdr:colOff>129540</xdr:colOff>
+          <xdr:colOff>91440</xdr:colOff>
           <xdr:row>49</xdr:row>
           <xdr:rowOff>15240</xdr:rowOff>
         </xdr:to>
@@ -4309,7 +4314,7 @@
         </xdr:from>
         <xdr:to>
           <xdr:col>1</xdr:col>
-          <xdr:colOff>129540</xdr:colOff>
+          <xdr:colOff>91440</xdr:colOff>
           <xdr:row>50</xdr:row>
           <xdr:rowOff>15240</xdr:rowOff>
         </xdr:to>
@@ -4376,7 +4381,7 @@
         </xdr:from>
         <xdr:to>
           <xdr:col>1</xdr:col>
-          <xdr:colOff>129540</xdr:colOff>
+          <xdr:colOff>91440</xdr:colOff>
           <xdr:row>51</xdr:row>
           <xdr:rowOff>15240</xdr:rowOff>
         </xdr:to>
@@ -4443,7 +4448,7 @@
         </xdr:from>
         <xdr:to>
           <xdr:col>1</xdr:col>
-          <xdr:colOff>129540</xdr:colOff>
+          <xdr:colOff>91440</xdr:colOff>
           <xdr:row>52</xdr:row>
           <xdr:rowOff>15240</xdr:rowOff>
         </xdr:to>
@@ -6990,7 +6995,7 @@
   <dimension ref="A1:AJ658"/>
   <sheetFormatPr defaultColWidth="4" defaultRowHeight="13.2" zeroHeight="1"/>
   <cols>
-    <col min="1" max="1" width="3.44140625" customWidth="1"/>
+    <col min="1" max="1" width="4.109375" customWidth="1"/>
     <col min="2" max="2" width="3" customWidth="1"/>
     <col min="3" max="3" width="3.6640625" customWidth="1"/>
     <col min="4" max="4" width="4" customWidth="1"/>
@@ -7001,13 +7006,13 @@
     <col min="9" max="9" width="4.109375" customWidth="1"/>
     <col min="10" max="10" width="3" customWidth="1"/>
     <col min="11" max="11" width="4" customWidth="1"/>
-    <col min="12" max="12" width="2.5546875" customWidth="1"/>
+    <col min="12" max="12" width="7.109375" customWidth="1"/>
     <col min="13" max="13" width="0.109375" customWidth="1"/>
     <col min="14" max="14" width="3.88671875" customWidth="1"/>
-    <col min="15" max="15" width="7" customWidth="1"/>
-    <col min="16" max="16" width="8.5546875" customWidth="1"/>
+    <col min="15" max="15" width="3.6640625" customWidth="1"/>
+    <col min="16" max="16" width="2.109375" customWidth="1"/>
     <col min="22" max="22" width="12" customWidth="1"/>
-    <col min="29" max="29" width="10.5546875" customWidth="1"/>
+    <col min="29" max="29" width="15.109375" customWidth="1"/>
     <col min="31" max="31" width="2.88671875" bestFit="1" customWidth="1"/>
     <col min="32" max="32" width="5.21875" customWidth="1"/>
     <col min="33" max="33" width="9.5546875" customWidth="1"/>
@@ -7047,16 +7052,16 @@
       <c r="N2" s="31"/>
       <c r="O2" s="38"/>
       <c r="P2" s="38"/>
-      <c r="Q2" s="68"/>
-      <c r="R2" s="68"/>
-      <c r="S2" s="68"/>
-      <c r="T2" s="68"/>
-      <c r="U2" s="68"/>
-      <c r="V2" s="68"/>
-      <c r="W2" s="68"/>
-      <c r="X2" s="68"/>
-      <c r="Y2" s="68"/>
-      <c r="Z2" s="68"/>
+      <c r="Q2" s="147"/>
+      <c r="R2" s="147"/>
+      <c r="S2" s="147"/>
+      <c r="T2" s="147"/>
+      <c r="U2" s="147"/>
+      <c r="V2" s="147"/>
+      <c r="W2" s="147"/>
+      <c r="X2" s="147"/>
+      <c r="Y2" s="147"/>
+      <c r="Z2" s="147"/>
       <c r="AA2" s="38"/>
       <c r="AB2" s="38"/>
       <c r="AC2" s="38"/>
@@ -7082,28 +7087,28 @@
       <c r="K3" s="1"/>
       <c r="M3" s="31"/>
       <c r="N3" s="31"/>
-      <c r="Q3" s="69"/>
-      <c r="R3" s="69"/>
-      <c r="S3" s="69"/>
-      <c r="T3" s="69"/>
-      <c r="U3" s="69"/>
-      <c r="V3" s="69"/>
-      <c r="W3" s="69"/>
-      <c r="X3" s="69"/>
-      <c r="Y3" s="69"/>
-      <c r="Z3" s="69"/>
+      <c r="Q3" s="148"/>
+      <c r="R3" s="148"/>
+      <c r="S3" s="148"/>
+      <c r="T3" s="148"/>
+      <c r="U3" s="148"/>
+      <c r="V3" s="148"/>
+      <c r="W3" s="148"/>
+      <c r="X3" s="148"/>
+      <c r="Y3" s="148"/>
+      <c r="Z3" s="148"/>
       <c r="AA3" s="37"/>
       <c r="AB3" s="50" t="s">
         <v>95</v>
       </c>
       <c r="AC3" s="48"/>
-      <c r="AD3" s="58"/>
-      <c r="AE3" s="59"/>
-      <c r="AF3" s="59"/>
-      <c r="AG3" s="59"/>
-      <c r="AH3" s="59"/>
-      <c r="AI3" s="59"/>
-      <c r="AJ3" s="59"/>
+      <c r="AD3" s="160"/>
+      <c r="AE3" s="161"/>
+      <c r="AF3" s="161"/>
+      <c r="AG3" s="161"/>
+      <c r="AH3" s="161"/>
+      <c r="AI3" s="161"/>
+      <c r="AJ3" s="161"/>
     </row>
     <row r="4" spans="1:36" ht="18" customHeight="1">
       <c r="A4" s="30"/>
@@ -7134,304 +7139,304 @@
       </c>
     </row>
     <row r="5" spans="1:36" ht="18" customHeight="1">
-      <c r="A5" s="77" t="s">
+      <c r="A5" s="63" t="s">
         <v>85</v>
       </c>
-      <c r="B5" s="77"/>
-      <c r="C5" s="99"/>
-      <c r="D5" s="99"/>
-      <c r="E5" s="99"/>
-      <c r="F5" s="99"/>
-      <c r="G5" s="99"/>
-      <c r="H5" s="99"/>
-      <c r="I5" s="99"/>
+      <c r="B5" s="63"/>
+      <c r="C5" s="103"/>
+      <c r="D5" s="103"/>
+      <c r="E5" s="103"/>
+      <c r="F5" s="103"/>
+      <c r="G5" s="103"/>
+      <c r="H5" s="103"/>
+      <c r="I5" s="103"/>
       <c r="J5" s="35"/>
-      <c r="K5" s="60" t="s">
+      <c r="K5" s="152" t="s">
         <v>0</v>
       </c>
-      <c r="L5" s="60"/>
-      <c r="M5" s="60"/>
-      <c r="N5" s="60"/>
-      <c r="O5" s="60"/>
-      <c r="P5" s="61"/>
-      <c r="Q5" s="62"/>
-      <c r="R5" s="62"/>
-      <c r="S5" s="62"/>
-      <c r="T5" s="62"/>
-      <c r="U5" s="62"/>
-      <c r="V5" s="62"/>
-      <c r="W5" s="62"/>
-      <c r="X5" s="62"/>
-      <c r="Y5" s="60" t="s">
+      <c r="L5" s="152"/>
+      <c r="M5" s="152"/>
+      <c r="N5" s="152"/>
+      <c r="O5" s="152"/>
+      <c r="P5" s="162"/>
+      <c r="Q5" s="163"/>
+      <c r="R5" s="163"/>
+      <c r="S5" s="163"/>
+      <c r="T5" s="163"/>
+      <c r="U5" s="163"/>
+      <c r="V5" s="163"/>
+      <c r="W5" s="163"/>
+      <c r="X5" s="163"/>
+      <c r="Y5" s="152" t="s">
         <v>48</v>
       </c>
-      <c r="Z5" s="60"/>
-      <c r="AA5" s="99"/>
-      <c r="AB5" s="99"/>
-      <c r="AC5" s="99"/>
-      <c r="AD5" s="99"/>
-      <c r="AE5" s="99"/>
-      <c r="AF5" s="99"/>
-      <c r="AG5" s="99"/>
-      <c r="AH5" s="99"/>
-      <c r="AI5" s="99"/>
-      <c r="AJ5" s="99"/>
+      <c r="Z5" s="152"/>
+      <c r="AA5" s="103"/>
+      <c r="AB5" s="103"/>
+      <c r="AC5" s="103"/>
+      <c r="AD5" s="103"/>
+      <c r="AE5" s="103"/>
+      <c r="AF5" s="103"/>
+      <c r="AG5" s="103"/>
+      <c r="AH5" s="103"/>
+      <c r="AI5" s="103"/>
+      <c r="AJ5" s="103"/>
     </row>
     <row r="6" spans="1:36" ht="18" customHeight="1">
-      <c r="A6" s="77" t="s">
+      <c r="A6" s="63" t="s">
         <v>1</v>
       </c>
-      <c r="B6" s="77"/>
-      <c r="C6" s="65"/>
-      <c r="D6" s="65"/>
-      <c r="E6" s="65"/>
-      <c r="F6" s="65"/>
-      <c r="G6" s="65"/>
-      <c r="H6" s="65"/>
-      <c r="I6" s="65"/>
+      <c r="B6" s="63"/>
+      <c r="C6" s="156"/>
+      <c r="D6" s="156"/>
+      <c r="E6" s="156"/>
+      <c r="F6" s="156"/>
+      <c r="G6" s="156"/>
+      <c r="H6" s="156"/>
+      <c r="I6" s="156"/>
       <c r="J6" s="35"/>
-      <c r="K6" s="60" t="s">
+      <c r="K6" s="152" t="s">
         <v>2</v>
       </c>
-      <c r="L6" s="60"/>
-      <c r="M6" s="60"/>
-      <c r="N6" s="60"/>
-      <c r="O6" s="60"/>
-      <c r="P6" s="73"/>
-      <c r="Q6" s="74"/>
-      <c r="R6" s="74"/>
-      <c r="S6" s="74"/>
-      <c r="T6" s="74"/>
-      <c r="U6" s="74"/>
-      <c r="V6" s="74"/>
-      <c r="W6" s="74"/>
-      <c r="X6" s="74"/>
+      <c r="L6" s="152"/>
+      <c r="M6" s="152"/>
+      <c r="N6" s="152"/>
+      <c r="O6" s="152"/>
+      <c r="P6" s="165"/>
+      <c r="Q6" s="166"/>
+      <c r="R6" s="166"/>
+      <c r="S6" s="166"/>
+      <c r="T6" s="166"/>
+      <c r="U6" s="166"/>
+      <c r="V6" s="166"/>
+      <c r="W6" s="166"/>
+      <c r="X6" s="166"/>
       <c r="Y6" s="56" t="s">
         <v>88</v>
       </c>
       <c r="Z6" s="56"/>
       <c r="AA6" s="56"/>
       <c r="AB6" s="56"/>
-      <c r="AC6" s="167"/>
-      <c r="AD6" s="167"/>
+      <c r="AC6" s="168"/>
+      <c r="AD6" s="57"/>
       <c r="AE6" s="57"/>
       <c r="AF6" s="57"/>
       <c r="AG6" s="44"/>
-      <c r="AH6" s="166"/>
-      <c r="AI6" s="166"/>
+      <c r="AH6" s="58"/>
+      <c r="AI6" s="58"/>
       <c r="AJ6" s="44"/>
     </row>
     <row r="7" spans="1:36" ht="18" customHeight="1">
-      <c r="A7" s="77" t="s">
+      <c r="A7" s="63" t="s">
         <v>3</v>
       </c>
-      <c r="B7" s="77"/>
-      <c r="C7" s="65"/>
-      <c r="D7" s="65"/>
-      <c r="E7" s="65"/>
-      <c r="F7" s="65"/>
-      <c r="G7" s="65"/>
-      <c r="H7" s="65"/>
-      <c r="I7" s="65"/>
+      <c r="B7" s="63"/>
+      <c r="C7" s="156"/>
+      <c r="D7" s="156"/>
+      <c r="E7" s="156"/>
+      <c r="F7" s="156"/>
+      <c r="G7" s="156"/>
+      <c r="H7" s="156"/>
+      <c r="I7" s="156"/>
       <c r="J7" s="35"/>
-      <c r="K7" s="60" t="s">
+      <c r="K7" s="152" t="s">
         <v>89</v>
       </c>
-      <c r="L7" s="60"/>
-      <c r="M7" s="60"/>
-      <c r="N7" s="60"/>
-      <c r="O7" s="60"/>
-      <c r="P7" s="63"/>
-      <c r="Q7" s="63"/>
-      <c r="R7" s="63"/>
-      <c r="S7" s="63"/>
-      <c r="T7" s="63"/>
+      <c r="L7" s="152"/>
+      <c r="M7" s="152"/>
+      <c r="N7" s="152"/>
+      <c r="O7" s="152"/>
+      <c r="P7" s="167"/>
+      <c r="Q7" s="167"/>
+      <c r="R7" s="167"/>
+      <c r="S7" s="167"/>
+      <c r="T7" s="167"/>
       <c r="U7" s="39" t="s">
         <v>4</v>
       </c>
-      <c r="V7" s="63"/>
-      <c r="W7" s="63"/>
-      <c r="X7" s="60" t="s">
+      <c r="V7" s="135"/>
+      <c r="W7" s="135"/>
+      <c r="X7" s="152" t="s">
         <v>90</v>
       </c>
-      <c r="Y7" s="60"/>
-      <c r="Z7" s="60"/>
-      <c r="AA7" s="60"/>
-      <c r="AB7" s="60"/>
-      <c r="AC7" s="167"/>
-      <c r="AD7" s="167"/>
-      <c r="AE7" s="167"/>
-      <c r="AF7" s="166"/>
-      <c r="AG7" s="166"/>
+      <c r="Y7" s="152"/>
+      <c r="Z7" s="152"/>
+      <c r="AA7" s="152"/>
+      <c r="AB7" s="152"/>
+      <c r="AC7" s="168"/>
+      <c r="AD7" s="57"/>
+      <c r="AE7" s="57"/>
+      <c r="AF7" s="58"/>
+      <c r="AG7" s="58"/>
       <c r="AH7" s="39" t="s">
         <v>4</v>
       </c>
-      <c r="AI7" s="63"/>
-      <c r="AJ7" s="63"/>
+      <c r="AI7" s="167"/>
+      <c r="AJ7" s="167"/>
     </row>
     <row r="8" spans="1:36" ht="18" customHeight="1">
-      <c r="A8" s="81" t="s">
+      <c r="A8" s="88" t="s">
         <v>5</v>
       </c>
-      <c r="B8" s="81"/>
-      <c r="C8" s="81"/>
-      <c r="D8" s="67"/>
-      <c r="E8" s="67"/>
-      <c r="F8" s="67"/>
-      <c r="G8" s="67"/>
-      <c r="H8" s="67"/>
-      <c r="I8" s="67"/>
-      <c r="J8" s="67"/>
-      <c r="K8" s="67"/>
-      <c r="L8" s="67"/>
-      <c r="M8" s="67"/>
-      <c r="N8" s="67"/>
-      <c r="O8" s="67"/>
-      <c r="P8" s="67"/>
-      <c r="Q8" s="67"/>
-      <c r="R8" s="67"/>
-      <c r="S8" s="66" t="s">
+      <c r="B8" s="88"/>
+      <c r="C8" s="88"/>
+      <c r="D8" s="98"/>
+      <c r="E8" s="98"/>
+      <c r="F8" s="98"/>
+      <c r="G8" s="98"/>
+      <c r="H8" s="98"/>
+      <c r="I8" s="98"/>
+      <c r="J8" s="98"/>
+      <c r="K8" s="98"/>
+      <c r="L8" s="98"/>
+      <c r="M8" s="98"/>
+      <c r="N8" s="98"/>
+      <c r="O8" s="98"/>
+      <c r="P8" s="98"/>
+      <c r="Q8" s="98"/>
+      <c r="R8" s="98"/>
+      <c r="S8" s="164" t="s">
         <v>49</v>
       </c>
-      <c r="T8" s="66"/>
-      <c r="U8" s="60"/>
-      <c r="V8" s="66"/>
-      <c r="W8" s="66"/>
-      <c r="X8" s="67"/>
-      <c r="Y8" s="67"/>
-      <c r="Z8" s="67"/>
-      <c r="AA8" s="67"/>
-      <c r="AB8" s="67"/>
-      <c r="AC8" s="67"/>
-      <c r="AD8" s="67"/>
-      <c r="AE8" s="67"/>
-      <c r="AF8" s="67"/>
-      <c r="AG8" s="67"/>
-      <c r="AH8" s="67"/>
-      <c r="AI8" s="67"/>
-      <c r="AJ8" s="67"/>
+      <c r="T8" s="164"/>
+      <c r="U8" s="152"/>
+      <c r="V8" s="164"/>
+      <c r="W8" s="164"/>
+      <c r="X8" s="98"/>
+      <c r="Y8" s="98"/>
+      <c r="Z8" s="98"/>
+      <c r="AA8" s="98"/>
+      <c r="AB8" s="98"/>
+      <c r="AC8" s="98"/>
+      <c r="AD8" s="98"/>
+      <c r="AE8" s="98"/>
+      <c r="AF8" s="98"/>
+      <c r="AG8" s="98"/>
+      <c r="AH8" s="98"/>
+      <c r="AI8" s="98"/>
+      <c r="AJ8" s="98"/>
     </row>
     <row r="9" spans="1:36" ht="26.4" customHeight="1">
-      <c r="A9" s="77" t="s">
+      <c r="A9" s="63" t="s">
         <v>6</v>
       </c>
-      <c r="B9" s="77"/>
-      <c r="C9" s="77"/>
-      <c r="D9" s="83"/>
-      <c r="E9" s="83"/>
-      <c r="F9" s="83"/>
-      <c r="G9" s="83"/>
-      <c r="H9" s="83"/>
-      <c r="I9" s="83"/>
-      <c r="J9" s="83"/>
-      <c r="K9" s="83"/>
-      <c r="L9" s="83"/>
-      <c r="M9" s="83"/>
-      <c r="N9" s="83"/>
-      <c r="O9" s="83"/>
-      <c r="P9" s="83"/>
-      <c r="Q9" s="83"/>
-      <c r="R9" s="83"/>
-      <c r="S9" s="60" t="s">
+      <c r="B9" s="63"/>
+      <c r="C9" s="63"/>
+      <c r="D9" s="146"/>
+      <c r="E9" s="146"/>
+      <c r="F9" s="146"/>
+      <c r="G9" s="146"/>
+      <c r="H9" s="146"/>
+      <c r="I9" s="146"/>
+      <c r="J9" s="146"/>
+      <c r="K9" s="146"/>
+      <c r="L9" s="146"/>
+      <c r="M9" s="146"/>
+      <c r="N9" s="146"/>
+      <c r="O9" s="146"/>
+      <c r="P9" s="146"/>
+      <c r="Q9" s="146"/>
+      <c r="R9" s="146"/>
+      <c r="S9" s="152" t="s">
         <v>50</v>
       </c>
-      <c r="T9" s="60"/>
-      <c r="U9" s="60"/>
-      <c r="V9" s="60"/>
-      <c r="W9" s="60"/>
-      <c r="X9" s="122"/>
-      <c r="Y9" s="83"/>
-      <c r="Z9" s="83"/>
-      <c r="AA9" s="83"/>
-      <c r="AB9" s="83"/>
-      <c r="AC9" s="83"/>
-      <c r="AD9" s="83"/>
-      <c r="AE9" s="83"/>
-      <c r="AF9" s="83"/>
-      <c r="AG9" s="83"/>
-      <c r="AH9" s="83"/>
-      <c r="AI9" s="83"/>
-      <c r="AJ9" s="83"/>
+      <c r="T9" s="152"/>
+      <c r="U9" s="152"/>
+      <c r="V9" s="152"/>
+      <c r="W9" s="152"/>
+      <c r="X9" s="145"/>
+      <c r="Y9" s="146"/>
+      <c r="Z9" s="146"/>
+      <c r="AA9" s="146"/>
+      <c r="AB9" s="146"/>
+      <c r="AC9" s="146"/>
+      <c r="AD9" s="146"/>
+      <c r="AE9" s="146"/>
+      <c r="AF9" s="146"/>
+      <c r="AG9" s="146"/>
+      <c r="AH9" s="146"/>
+      <c r="AI9" s="146"/>
+      <c r="AJ9" s="146"/>
     </row>
     <row r="10" spans="1:36" ht="5.25" customHeight="1">
-      <c r="A10" s="82"/>
-      <c r="B10" s="82"/>
-      <c r="C10" s="82"/>
-      <c r="D10" s="82"/>
-      <c r="E10" s="82"/>
-      <c r="F10" s="82"/>
-      <c r="G10" s="82"/>
-      <c r="H10" s="82"/>
-      <c r="I10" s="82"/>
-      <c r="J10" s="82"/>
-      <c r="K10" s="82"/>
-      <c r="L10" s="82"/>
-      <c r="M10" s="82"/>
-      <c r="N10" s="82"/>
-      <c r="O10" s="82"/>
-      <c r="P10" s="82"/>
-      <c r="Q10" s="82"/>
-      <c r="R10" s="82"/>
-      <c r="S10" s="82"/>
-      <c r="T10" s="82"/>
-      <c r="U10" s="82"/>
-      <c r="V10" s="82"/>
-      <c r="W10" s="82"/>
-      <c r="X10" s="82"/>
-      <c r="Y10" s="82"/>
-      <c r="Z10" s="82"/>
-      <c r="AA10" s="82"/>
-      <c r="AB10" s="82"/>
-      <c r="AC10" s="82"/>
-      <c r="AD10" s="82"/>
-      <c r="AE10" s="82"/>
-      <c r="AF10" s="82"/>
-      <c r="AG10" s="82"/>
-      <c r="AH10" s="82"/>
-      <c r="AI10" s="82"/>
-      <c r="AJ10" s="82"/>
+      <c r="A10" s="91"/>
+      <c r="B10" s="91"/>
+      <c r="C10" s="91"/>
+      <c r="D10" s="91"/>
+      <c r="E10" s="91"/>
+      <c r="F10" s="91"/>
+      <c r="G10" s="91"/>
+      <c r="H10" s="91"/>
+      <c r="I10" s="91"/>
+      <c r="J10" s="91"/>
+      <c r="K10" s="91"/>
+      <c r="L10" s="91"/>
+      <c r="M10" s="91"/>
+      <c r="N10" s="91"/>
+      <c r="O10" s="91"/>
+      <c r="P10" s="91"/>
+      <c r="Q10" s="91"/>
+      <c r="R10" s="91"/>
+      <c r="S10" s="91"/>
+      <c r="T10" s="91"/>
+      <c r="U10" s="91"/>
+      <c r="V10" s="91"/>
+      <c r="W10" s="91"/>
+      <c r="X10" s="91"/>
+      <c r="Y10" s="91"/>
+      <c r="Z10" s="91"/>
+      <c r="AA10" s="91"/>
+      <c r="AB10" s="91"/>
+      <c r="AC10" s="91"/>
+      <c r="AD10" s="91"/>
+      <c r="AE10" s="91"/>
+      <c r="AF10" s="91"/>
+      <c r="AG10" s="91"/>
+      <c r="AH10" s="91"/>
+      <c r="AI10" s="91"/>
+      <c r="AJ10" s="91"/>
     </row>
     <row r="11" spans="1:36" ht="14.25" customHeight="1">
-      <c r="A11" s="70" t="s">
+      <c r="A11" s="149" t="s">
         <v>7</v>
       </c>
-      <c r="B11" s="71"/>
-      <c r="C11" s="71"/>
-      <c r="D11" s="71"/>
-      <c r="E11" s="71"/>
-      <c r="F11" s="71"/>
-      <c r="G11" s="71"/>
-      <c r="H11" s="71"/>
-      <c r="I11" s="71"/>
-      <c r="J11" s="71"/>
-      <c r="K11" s="71"/>
-      <c r="L11" s="71"/>
-      <c r="M11" s="71"/>
-      <c r="N11" s="71"/>
-      <c r="O11" s="71"/>
-      <c r="P11" s="72"/>
-      <c r="Q11" s="78" t="s">
+      <c r="B11" s="150"/>
+      <c r="C11" s="150"/>
+      <c r="D11" s="150"/>
+      <c r="E11" s="150"/>
+      <c r="F11" s="150"/>
+      <c r="G11" s="150"/>
+      <c r="H11" s="150"/>
+      <c r="I11" s="150"/>
+      <c r="J11" s="150"/>
+      <c r="K11" s="150"/>
+      <c r="L11" s="150"/>
+      <c r="M11" s="150"/>
+      <c r="N11" s="150"/>
+      <c r="O11" s="150"/>
+      <c r="P11" s="151"/>
+      <c r="Q11" s="153" t="s">
         <v>8</v>
       </c>
-      <c r="R11" s="79"/>
-      <c r="S11" s="79"/>
-      <c r="T11" s="79"/>
-      <c r="U11" s="79"/>
-      <c r="V11" s="79"/>
-      <c r="W11" s="79"/>
-      <c r="X11" s="79"/>
-      <c r="Y11" s="79"/>
-      <c r="Z11" s="79"/>
-      <c r="AA11" s="79"/>
-      <c r="AB11" s="79"/>
-      <c r="AC11" s="79"/>
-      <c r="AD11" s="79"/>
-      <c r="AE11" s="79"/>
-      <c r="AF11" s="79"/>
-      <c r="AG11" s="79"/>
-      <c r="AH11" s="79"/>
-      <c r="AI11" s="79"/>
-      <c r="AJ11" s="80"/>
+      <c r="R11" s="154"/>
+      <c r="S11" s="154"/>
+      <c r="T11" s="154"/>
+      <c r="U11" s="154"/>
+      <c r="V11" s="154"/>
+      <c r="W11" s="154"/>
+      <c r="X11" s="154"/>
+      <c r="Y11" s="154"/>
+      <c r="Z11" s="154"/>
+      <c r="AA11" s="154"/>
+      <c r="AB11" s="154"/>
+      <c r="AC11" s="154"/>
+      <c r="AD11" s="154"/>
+      <c r="AE11" s="154"/>
+      <c r="AF11" s="154"/>
+      <c r="AG11" s="154"/>
+      <c r="AH11" s="154"/>
+      <c r="AI11" s="154"/>
+      <c r="AJ11" s="155"/>
     </row>
     <row r="12" spans="1:36" ht="18" customHeight="1">
       <c r="A12" s="2"/>
@@ -7540,150 +7545,150 @@
       <c r="AJ13" s="23"/>
     </row>
     <row r="14" spans="1:36" ht="16.5" customHeight="1">
-      <c r="A14" s="105" t="s">
+      <c r="A14" s="127" t="s">
         <v>86</v>
       </c>
-      <c r="B14" s="106"/>
-      <c r="C14" s="106"/>
-      <c r="D14" s="106"/>
-      <c r="E14" s="106"/>
-      <c r="F14" s="106"/>
-      <c r="G14" s="106"/>
-      <c r="H14" s="106"/>
-      <c r="I14" s="107"/>
-      <c r="J14" s="108"/>
-      <c r="K14" s="108"/>
-      <c r="L14" s="108"/>
-      <c r="M14" s="108"/>
-      <c r="N14" s="108"/>
-      <c r="O14" s="108"/>
-      <c r="P14" s="108"/>
-      <c r="Q14" s="108"/>
-      <c r="R14" s="108"/>
-      <c r="S14" s="108"/>
-      <c r="T14" s="108"/>
-      <c r="U14" s="108"/>
-      <c r="V14" s="108"/>
-      <c r="W14" s="108"/>
-      <c r="X14" s="108"/>
-      <c r="Y14" s="108"/>
-      <c r="Z14" s="108"/>
-      <c r="AA14" s="108"/>
-      <c r="AB14" s="108"/>
-      <c r="AC14" s="108"/>
-      <c r="AD14" s="108"/>
-      <c r="AE14" s="108"/>
-      <c r="AF14" s="108"/>
-      <c r="AG14" s="108"/>
-      <c r="AH14" s="108"/>
-      <c r="AI14" s="108"/>
-      <c r="AJ14" s="109"/>
+      <c r="B14" s="128"/>
+      <c r="C14" s="128"/>
+      <c r="D14" s="128"/>
+      <c r="E14" s="128"/>
+      <c r="F14" s="128"/>
+      <c r="G14" s="128"/>
+      <c r="H14" s="128"/>
+      <c r="I14" s="129"/>
+      <c r="J14" s="130"/>
+      <c r="K14" s="130"/>
+      <c r="L14" s="130"/>
+      <c r="M14" s="130"/>
+      <c r="N14" s="130"/>
+      <c r="O14" s="130"/>
+      <c r="P14" s="130"/>
+      <c r="Q14" s="130"/>
+      <c r="R14" s="130"/>
+      <c r="S14" s="130"/>
+      <c r="T14" s="130"/>
+      <c r="U14" s="130"/>
+      <c r="V14" s="130"/>
+      <c r="W14" s="130"/>
+      <c r="X14" s="130"/>
+      <c r="Y14" s="130"/>
+      <c r="Z14" s="130"/>
+      <c r="AA14" s="130"/>
+      <c r="AB14" s="130"/>
+      <c r="AC14" s="130"/>
+      <c r="AD14" s="130"/>
+      <c r="AE14" s="130"/>
+      <c r="AF14" s="130"/>
+      <c r="AG14" s="130"/>
+      <c r="AH14" s="130"/>
+      <c r="AI14" s="130"/>
+      <c r="AJ14" s="131"/>
     </row>
     <row r="15" spans="1:36" ht="3" customHeight="1">
-      <c r="A15" s="110">
+      <c r="A15" s="132">
         <v>2</v>
       </c>
-      <c r="B15" s="111"/>
-      <c r="C15" s="111"/>
-      <c r="D15" s="111"/>
-      <c r="E15" s="111"/>
-      <c r="F15" s="111"/>
-      <c r="G15" s="111"/>
-      <c r="H15" s="111"/>
-      <c r="I15" s="111"/>
-      <c r="J15" s="111"/>
-      <c r="K15" s="111"/>
-      <c r="L15" s="111"/>
-      <c r="M15" s="111"/>
-      <c r="N15" s="111"/>
-      <c r="O15" s="111"/>
-      <c r="P15" s="111"/>
-      <c r="Q15" s="111"/>
-      <c r="R15" s="111"/>
-      <c r="S15" s="111"/>
-      <c r="T15" s="111"/>
-      <c r="U15" s="111"/>
-      <c r="V15" s="111"/>
-      <c r="W15" s="111"/>
-      <c r="X15" s="111"/>
-      <c r="Y15" s="111"/>
-      <c r="Z15" s="111"/>
-      <c r="AA15" s="111"/>
-      <c r="AB15" s="111"/>
-      <c r="AC15" s="111"/>
-      <c r="AD15" s="111"/>
-      <c r="AE15" s="111"/>
-      <c r="AF15" s="111"/>
-      <c r="AG15" s="111"/>
-      <c r="AH15" s="111"/>
-      <c r="AI15" s="111"/>
-      <c r="AJ15" s="112"/>
+      <c r="B15" s="133"/>
+      <c r="C15" s="133"/>
+      <c r="D15" s="133"/>
+      <c r="E15" s="133"/>
+      <c r="F15" s="133"/>
+      <c r="G15" s="133"/>
+      <c r="H15" s="133"/>
+      <c r="I15" s="133"/>
+      <c r="J15" s="133"/>
+      <c r="K15" s="133"/>
+      <c r="L15" s="133"/>
+      <c r="M15" s="133"/>
+      <c r="N15" s="133"/>
+      <c r="O15" s="133"/>
+      <c r="P15" s="133"/>
+      <c r="Q15" s="133"/>
+      <c r="R15" s="133"/>
+      <c r="S15" s="133"/>
+      <c r="T15" s="133"/>
+      <c r="U15" s="133"/>
+      <c r="V15" s="133"/>
+      <c r="W15" s="133"/>
+      <c r="X15" s="133"/>
+      <c r="Y15" s="133"/>
+      <c r="Z15" s="133"/>
+      <c r="AA15" s="133"/>
+      <c r="AB15" s="133"/>
+      <c r="AC15" s="133"/>
+      <c r="AD15" s="133"/>
+      <c r="AE15" s="133"/>
+      <c r="AF15" s="133"/>
+      <c r="AG15" s="133"/>
+      <c r="AH15" s="133"/>
+      <c r="AI15" s="133"/>
+      <c r="AJ15" s="134"/>
     </row>
     <row r="16" spans="1:36" ht="12.75" customHeight="1">
-      <c r="A16" s="119" t="s">
+      <c r="A16" s="142" t="s">
         <v>9</v>
       </c>
-      <c r="B16" s="120"/>
-      <c r="C16" s="120"/>
-      <c r="D16" s="120"/>
-      <c r="E16" s="120"/>
-      <c r="F16" s="120"/>
-      <c r="G16" s="120"/>
-      <c r="H16" s="120"/>
-      <c r="I16" s="120"/>
-      <c r="J16" s="120"/>
-      <c r="K16" s="120"/>
-      <c r="L16" s="120"/>
-      <c r="M16" s="120"/>
-      <c r="N16" s="120"/>
-      <c r="O16" s="120"/>
-      <c r="P16" s="120"/>
-      <c r="Q16" s="120"/>
-      <c r="R16" s="120"/>
-      <c r="S16" s="120"/>
-      <c r="T16" s="121"/>
-      <c r="U16" s="113" t="s">
+      <c r="B16" s="143"/>
+      <c r="C16" s="143"/>
+      <c r="D16" s="143"/>
+      <c r="E16" s="143"/>
+      <c r="F16" s="143"/>
+      <c r="G16" s="143"/>
+      <c r="H16" s="143"/>
+      <c r="I16" s="143"/>
+      <c r="J16" s="143"/>
+      <c r="K16" s="143"/>
+      <c r="L16" s="143"/>
+      <c r="M16" s="143"/>
+      <c r="N16" s="143"/>
+      <c r="O16" s="143"/>
+      <c r="P16" s="143"/>
+      <c r="Q16" s="143"/>
+      <c r="R16" s="143"/>
+      <c r="S16" s="143"/>
+      <c r="T16" s="144"/>
+      <c r="U16" s="136" t="s">
         <v>73</v>
       </c>
-      <c r="V16" s="114"/>
-      <c r="W16" s="114"/>
-      <c r="X16" s="114"/>
-      <c r="Y16" s="114"/>
-      <c r="Z16" s="114"/>
-      <c r="AA16" s="114"/>
-      <c r="AB16" s="114"/>
-      <c r="AC16" s="114"/>
-      <c r="AD16" s="115"/>
-      <c r="AE16" s="116" t="s">
+      <c r="V16" s="137"/>
+      <c r="W16" s="137"/>
+      <c r="X16" s="137"/>
+      <c r="Y16" s="137"/>
+      <c r="Z16" s="137"/>
+      <c r="AA16" s="137"/>
+      <c r="AB16" s="137"/>
+      <c r="AC16" s="137"/>
+      <c r="AD16" s="138"/>
+      <c r="AE16" s="139" t="s">
         <v>10</v>
       </c>
-      <c r="AF16" s="117"/>
-      <c r="AG16" s="117"/>
-      <c r="AH16" s="117"/>
-      <c r="AI16" s="117"/>
-      <c r="AJ16" s="118"/>
+      <c r="AF16" s="140"/>
+      <c r="AG16" s="140"/>
+      <c r="AH16" s="140"/>
+      <c r="AI16" s="140"/>
+      <c r="AJ16" s="141"/>
     </row>
     <row r="17" spans="1:36" ht="18" customHeight="1">
-      <c r="A17" s="93"/>
-      <c r="B17" s="94"/>
-      <c r="C17" s="94"/>
-      <c r="D17" s="94"/>
-      <c r="E17" s="94"/>
-      <c r="F17" s="94"/>
-      <c r="G17" s="94"/>
-      <c r="H17" s="94"/>
-      <c r="I17" s="94"/>
-      <c r="J17" s="94"/>
-      <c r="K17" s="94"/>
-      <c r="L17" s="94"/>
-      <c r="M17" s="94"/>
-      <c r="N17" s="94"/>
-      <c r="O17" s="94"/>
-      <c r="P17" s="94"/>
-      <c r="Q17" s="94"/>
-      <c r="R17" s="94"/>
-      <c r="S17" s="94"/>
-      <c r="T17" s="95"/>
+      <c r="A17" s="120"/>
+      <c r="B17" s="121"/>
+      <c r="C17" s="121"/>
+      <c r="D17" s="121"/>
+      <c r="E17" s="121"/>
+      <c r="F17" s="121"/>
+      <c r="G17" s="121"/>
+      <c r="H17" s="121"/>
+      <c r="I17" s="121"/>
+      <c r="J17" s="121"/>
+      <c r="K17" s="121"/>
+      <c r="L17" s="121"/>
+      <c r="M17" s="121"/>
+      <c r="N17" s="121"/>
+      <c r="O17" s="121"/>
+      <c r="P17" s="121"/>
+      <c r="Q17" s="121"/>
+      <c r="R17" s="121"/>
+      <c r="S17" s="121"/>
+      <c r="T17" s="122"/>
       <c r="U17" s="25"/>
       <c r="V17" s="17" t="s">
         <v>64</v>
@@ -7699,32 +7704,32 @@
       <c r="AE17" s="14" t="s">
         <v>11</v>
       </c>
-      <c r="AF17" s="100"/>
-      <c r="AG17" s="100"/>
-      <c r="AI17" s="100"/>
-      <c r="AJ17" s="104"/>
+      <c r="AF17" s="106"/>
+      <c r="AG17" s="106"/>
+      <c r="AI17" s="106"/>
+      <c r="AJ17" s="126"/>
     </row>
     <row r="18" spans="1:36" ht="18" customHeight="1">
-      <c r="A18" s="93"/>
-      <c r="B18" s="94"/>
-      <c r="C18" s="94"/>
-      <c r="D18" s="94"/>
-      <c r="E18" s="94"/>
-      <c r="F18" s="94"/>
-      <c r="G18" s="94"/>
-      <c r="H18" s="94"/>
-      <c r="I18" s="94"/>
-      <c r="J18" s="94"/>
-      <c r="K18" s="94"/>
-      <c r="L18" s="94"/>
-      <c r="M18" s="94"/>
-      <c r="N18" s="94"/>
-      <c r="O18" s="94"/>
-      <c r="P18" s="94"/>
-      <c r="Q18" s="94"/>
-      <c r="R18" s="94"/>
-      <c r="S18" s="94"/>
-      <c r="T18" s="95"/>
+      <c r="A18" s="120"/>
+      <c r="B18" s="121"/>
+      <c r="C18" s="121"/>
+      <c r="D18" s="121"/>
+      <c r="E18" s="121"/>
+      <c r="F18" s="121"/>
+      <c r="G18" s="121"/>
+      <c r="H18" s="121"/>
+      <c r="I18" s="121"/>
+      <c r="J18" s="121"/>
+      <c r="K18" s="121"/>
+      <c r="L18" s="121"/>
+      <c r="M18" s="121"/>
+      <c r="N18" s="121"/>
+      <c r="O18" s="121"/>
+      <c r="P18" s="121"/>
+      <c r="Q18" s="121"/>
+      <c r="R18" s="121"/>
+      <c r="S18" s="121"/>
+      <c r="T18" s="122"/>
       <c r="U18" s="26"/>
       <c r="V18" s="17" t="s">
         <v>65</v>
@@ -7740,32 +7745,32 @@
       <c r="AE18" s="14" t="s">
         <v>12</v>
       </c>
-      <c r="AF18" s="100"/>
-      <c r="AG18" s="100"/>
-      <c r="AI18" s="100"/>
-      <c r="AJ18" s="104"/>
+      <c r="AF18" s="106"/>
+      <c r="AG18" s="106"/>
+      <c r="AI18" s="106"/>
+      <c r="AJ18" s="126"/>
     </row>
     <row r="19" spans="1:36" ht="18" customHeight="1">
-      <c r="A19" s="93"/>
-      <c r="B19" s="94"/>
-      <c r="C19" s="94"/>
-      <c r="D19" s="94"/>
-      <c r="E19" s="94"/>
-      <c r="F19" s="94"/>
-      <c r="G19" s="94"/>
-      <c r="H19" s="94"/>
-      <c r="I19" s="94"/>
-      <c r="J19" s="94"/>
-      <c r="K19" s="94"/>
-      <c r="L19" s="94"/>
-      <c r="M19" s="94"/>
-      <c r="N19" s="94"/>
-      <c r="O19" s="94"/>
-      <c r="P19" s="94"/>
-      <c r="Q19" s="94"/>
-      <c r="R19" s="94"/>
-      <c r="S19" s="94"/>
-      <c r="T19" s="95"/>
+      <c r="A19" s="120"/>
+      <c r="B19" s="121"/>
+      <c r="C19" s="121"/>
+      <c r="D19" s="121"/>
+      <c r="E19" s="121"/>
+      <c r="F19" s="121"/>
+      <c r="G19" s="121"/>
+      <c r="H19" s="121"/>
+      <c r="I19" s="121"/>
+      <c r="J19" s="121"/>
+      <c r="K19" s="121"/>
+      <c r="L19" s="121"/>
+      <c r="M19" s="121"/>
+      <c r="N19" s="121"/>
+      <c r="O19" s="121"/>
+      <c r="P19" s="121"/>
+      <c r="Q19" s="121"/>
+      <c r="R19" s="121"/>
+      <c r="S19" s="121"/>
+      <c r="T19" s="122"/>
       <c r="U19" s="26"/>
       <c r="V19" s="17" t="s">
         <v>66</v>
@@ -7781,32 +7786,32 @@
       <c r="AE19" s="14" t="s">
         <v>13</v>
       </c>
-      <c r="AF19" s="100"/>
-      <c r="AG19" s="100"/>
-      <c r="AI19" s="100"/>
-      <c r="AJ19" s="104"/>
+      <c r="AF19" s="106"/>
+      <c r="AG19" s="106"/>
+      <c r="AI19" s="106"/>
+      <c r="AJ19" s="126"/>
     </row>
     <row r="20" spans="1:36" ht="3.75" customHeight="1">
-      <c r="A20" s="96"/>
-      <c r="B20" s="97"/>
-      <c r="C20" s="97"/>
-      <c r="D20" s="97"/>
-      <c r="E20" s="97"/>
-      <c r="F20" s="97"/>
-      <c r="G20" s="97"/>
-      <c r="H20" s="97"/>
-      <c r="I20" s="97"/>
-      <c r="J20" s="97"/>
-      <c r="K20" s="97"/>
-      <c r="L20" s="97"/>
-      <c r="M20" s="97"/>
-      <c r="N20" s="97"/>
-      <c r="O20" s="97"/>
-      <c r="P20" s="97"/>
-      <c r="Q20" s="97"/>
-      <c r="R20" s="97"/>
-      <c r="S20" s="97"/>
-      <c r="T20" s="98"/>
+      <c r="A20" s="123"/>
+      <c r="B20" s="124"/>
+      <c r="C20" s="124"/>
+      <c r="D20" s="124"/>
+      <c r="E20" s="124"/>
+      <c r="F20" s="124"/>
+      <c r="G20" s="124"/>
+      <c r="H20" s="124"/>
+      <c r="I20" s="124"/>
+      <c r="J20" s="124"/>
+      <c r="K20" s="124"/>
+      <c r="L20" s="124"/>
+      <c r="M20" s="124"/>
+      <c r="N20" s="124"/>
+      <c r="O20" s="124"/>
+      <c r="P20" s="124"/>
+      <c r="Q20" s="124"/>
+      <c r="R20" s="124"/>
+      <c r="S20" s="124"/>
+      <c r="T20" s="125"/>
       <c r="U20" s="27"/>
       <c r="V20" s="16"/>
       <c r="W20" s="7"/>
@@ -7865,80 +7870,80 @@
       <c r="AJ21" s="47"/>
     </row>
     <row r="22" spans="1:36" ht="16.5" customHeight="1">
-      <c r="A22" s="87"/>
-      <c r="B22" s="88"/>
-      <c r="C22" s="88"/>
-      <c r="D22" s="88"/>
-      <c r="E22" s="88"/>
-      <c r="F22" s="88"/>
-      <c r="G22" s="88"/>
-      <c r="H22" s="88"/>
-      <c r="I22" s="88"/>
-      <c r="J22" s="88"/>
-      <c r="K22" s="88"/>
-      <c r="L22" s="88"/>
-      <c r="M22" s="88"/>
-      <c r="N22" s="88"/>
-      <c r="O22" s="88"/>
-      <c r="P22" s="88"/>
-      <c r="Q22" s="88"/>
-      <c r="R22" s="88"/>
-      <c r="S22" s="88"/>
-      <c r="T22" s="88"/>
-      <c r="U22" s="88"/>
-      <c r="V22" s="88"/>
-      <c r="W22" s="88"/>
-      <c r="X22" s="88"/>
-      <c r="Y22" s="88"/>
-      <c r="Z22" s="88"/>
-      <c r="AA22" s="88"/>
-      <c r="AB22" s="88"/>
-      <c r="AC22" s="88"/>
-      <c r="AD22" s="88"/>
-      <c r="AE22" s="88"/>
-      <c r="AF22" s="88"/>
-      <c r="AG22" s="88"/>
-      <c r="AH22" s="88"/>
-      <c r="AI22" s="88"/>
-      <c r="AJ22" s="89"/>
+      <c r="A22" s="114"/>
+      <c r="B22" s="115"/>
+      <c r="C22" s="115"/>
+      <c r="D22" s="115"/>
+      <c r="E22" s="115"/>
+      <c r="F22" s="115"/>
+      <c r="G22" s="115"/>
+      <c r="H22" s="115"/>
+      <c r="I22" s="115"/>
+      <c r="J22" s="115"/>
+      <c r="K22" s="115"/>
+      <c r="L22" s="115"/>
+      <c r="M22" s="115"/>
+      <c r="N22" s="115"/>
+      <c r="O22" s="115"/>
+      <c r="P22" s="115"/>
+      <c r="Q22" s="115"/>
+      <c r="R22" s="115"/>
+      <c r="S22" s="115"/>
+      <c r="T22" s="115"/>
+      <c r="U22" s="115"/>
+      <c r="V22" s="115"/>
+      <c r="W22" s="115"/>
+      <c r="X22" s="115"/>
+      <c r="Y22" s="115"/>
+      <c r="Z22" s="115"/>
+      <c r="AA22" s="115"/>
+      <c r="AB22" s="115"/>
+      <c r="AC22" s="115"/>
+      <c r="AD22" s="115"/>
+      <c r="AE22" s="115"/>
+      <c r="AF22" s="115"/>
+      <c r="AG22" s="115"/>
+      <c r="AH22" s="115"/>
+      <c r="AI22" s="115"/>
+      <c r="AJ22" s="116"/>
     </row>
     <row r="23" spans="1:36" ht="16.5" customHeight="1">
-      <c r="A23" s="90"/>
-      <c r="B23" s="91"/>
-      <c r="C23" s="91"/>
-      <c r="D23" s="91"/>
-      <c r="E23" s="91"/>
-      <c r="F23" s="91"/>
-      <c r="G23" s="91"/>
-      <c r="H23" s="91"/>
-      <c r="I23" s="91"/>
-      <c r="J23" s="91"/>
-      <c r="K23" s="91"/>
-      <c r="L23" s="91"/>
-      <c r="M23" s="91"/>
-      <c r="N23" s="91"/>
-      <c r="O23" s="91"/>
-      <c r="P23" s="91"/>
-      <c r="Q23" s="91"/>
-      <c r="R23" s="91"/>
-      <c r="S23" s="91"/>
-      <c r="T23" s="91"/>
-      <c r="U23" s="91"/>
-      <c r="V23" s="91"/>
-      <c r="W23" s="91"/>
-      <c r="X23" s="91"/>
-      <c r="Y23" s="91"/>
-      <c r="Z23" s="91"/>
-      <c r="AA23" s="91"/>
-      <c r="AB23" s="91"/>
-      <c r="AC23" s="91"/>
-      <c r="AD23" s="91"/>
-      <c r="AE23" s="91"/>
-      <c r="AF23" s="91"/>
-      <c r="AG23" s="91"/>
-      <c r="AH23" s="91"/>
-      <c r="AI23" s="91"/>
-      <c r="AJ23" s="92"/>
+      <c r="A23" s="117"/>
+      <c r="B23" s="118"/>
+      <c r="C23" s="118"/>
+      <c r="D23" s="118"/>
+      <c r="E23" s="118"/>
+      <c r="F23" s="118"/>
+      <c r="G23" s="118"/>
+      <c r="H23" s="118"/>
+      <c r="I23" s="118"/>
+      <c r="J23" s="118"/>
+      <c r="K23" s="118"/>
+      <c r="L23" s="118"/>
+      <c r="M23" s="118"/>
+      <c r="N23" s="118"/>
+      <c r="O23" s="118"/>
+      <c r="P23" s="118"/>
+      <c r="Q23" s="118"/>
+      <c r="R23" s="118"/>
+      <c r="S23" s="118"/>
+      <c r="T23" s="118"/>
+      <c r="U23" s="118"/>
+      <c r="V23" s="118"/>
+      <c r="W23" s="118"/>
+      <c r="X23" s="118"/>
+      <c r="Y23" s="118"/>
+      <c r="Z23" s="118"/>
+      <c r="AA23" s="118"/>
+      <c r="AB23" s="118"/>
+      <c r="AC23" s="118"/>
+      <c r="AD23" s="118"/>
+      <c r="AE23" s="118"/>
+      <c r="AF23" s="118"/>
+      <c r="AG23" s="118"/>
+      <c r="AH23" s="118"/>
+      <c r="AI23" s="118"/>
+      <c r="AJ23" s="119"/>
     </row>
     <row r="24" spans="1:36" ht="12.75" customHeight="1">
       <c r="A24" s="46" t="s">
@@ -7981,42 +7986,42 @@
       <c r="AJ24" s="47"/>
     </row>
     <row r="25" spans="1:36" ht="18" customHeight="1">
-      <c r="A25" s="84"/>
-      <c r="B25" s="85"/>
-      <c r="C25" s="85"/>
-      <c r="D25" s="85"/>
-      <c r="E25" s="85"/>
-      <c r="F25" s="85"/>
-      <c r="G25" s="85"/>
-      <c r="H25" s="85"/>
-      <c r="I25" s="85"/>
-      <c r="J25" s="85"/>
-      <c r="K25" s="85"/>
-      <c r="L25" s="85"/>
-      <c r="M25" s="85"/>
-      <c r="N25" s="85"/>
-      <c r="O25" s="85"/>
-      <c r="P25" s="85"/>
-      <c r="Q25" s="85"/>
-      <c r="R25" s="85"/>
-      <c r="S25" s="85"/>
-      <c r="T25" s="85"/>
-      <c r="U25" s="85"/>
-      <c r="V25" s="85"/>
-      <c r="W25" s="85"/>
-      <c r="X25" s="85"/>
-      <c r="Y25" s="85"/>
-      <c r="Z25" s="85"/>
-      <c r="AA25" s="85"/>
-      <c r="AB25" s="85"/>
-      <c r="AC25" s="85"/>
-      <c r="AD25" s="85"/>
-      <c r="AE25" s="85"/>
-      <c r="AF25" s="85"/>
-      <c r="AG25" s="85"/>
-      <c r="AH25" s="85"/>
-      <c r="AI25" s="85"/>
-      <c r="AJ25" s="86"/>
+      <c r="A25" s="157"/>
+      <c r="B25" s="158"/>
+      <c r="C25" s="158"/>
+      <c r="D25" s="158"/>
+      <c r="E25" s="158"/>
+      <c r="F25" s="158"/>
+      <c r="G25" s="158"/>
+      <c r="H25" s="158"/>
+      <c r="I25" s="158"/>
+      <c r="J25" s="158"/>
+      <c r="K25" s="158"/>
+      <c r="L25" s="158"/>
+      <c r="M25" s="158"/>
+      <c r="N25" s="158"/>
+      <c r="O25" s="158"/>
+      <c r="P25" s="158"/>
+      <c r="Q25" s="158"/>
+      <c r="R25" s="158"/>
+      <c r="S25" s="158"/>
+      <c r="T25" s="158"/>
+      <c r="U25" s="158"/>
+      <c r="V25" s="158"/>
+      <c r="W25" s="158"/>
+      <c r="X25" s="158"/>
+      <c r="Y25" s="158"/>
+      <c r="Z25" s="158"/>
+      <c r="AA25" s="158"/>
+      <c r="AB25" s="158"/>
+      <c r="AC25" s="158"/>
+      <c r="AD25" s="158"/>
+      <c r="AE25" s="158"/>
+      <c r="AF25" s="158"/>
+      <c r="AG25" s="158"/>
+      <c r="AH25" s="158"/>
+      <c r="AI25" s="158"/>
+      <c r="AJ25" s="159"/>
     </row>
     <row r="26" spans="1:36" ht="12.75" customHeight="1">
       <c r="A26" s="46" t="s">
@@ -8059,137 +8064,137 @@
       <c r="AJ26" s="47"/>
     </row>
     <row r="27" spans="1:36" ht="15" customHeight="1">
-      <c r="A27" s="151"/>
-      <c r="B27" s="152"/>
-      <c r="C27" s="152"/>
-      <c r="D27" s="152"/>
-      <c r="E27" s="152"/>
-      <c r="F27" s="152"/>
-      <c r="G27" s="152"/>
-      <c r="H27" s="152"/>
-      <c r="I27" s="152"/>
-      <c r="J27" s="152"/>
-      <c r="K27" s="152"/>
-      <c r="L27" s="152"/>
-      <c r="M27" s="152"/>
-      <c r="N27" s="152"/>
-      <c r="O27" s="152"/>
-      <c r="P27" s="152"/>
-      <c r="Q27" s="152"/>
-      <c r="R27" s="152"/>
-      <c r="S27" s="152"/>
-      <c r="T27" s="152"/>
-      <c r="U27" s="152"/>
-      <c r="V27" s="152"/>
-      <c r="W27" s="152"/>
-      <c r="X27" s="152"/>
-      <c r="Y27" s="152"/>
-      <c r="Z27" s="152"/>
-      <c r="AA27" s="152"/>
-      <c r="AB27" s="152"/>
-      <c r="AC27" s="152"/>
-      <c r="AD27" s="152"/>
-      <c r="AE27" s="152"/>
-      <c r="AF27" s="152"/>
-      <c r="AG27" s="152"/>
-      <c r="AH27" s="152"/>
-      <c r="AI27" s="152"/>
-      <c r="AJ27" s="153"/>
+      <c r="A27" s="65"/>
+      <c r="B27" s="66"/>
+      <c r="C27" s="66"/>
+      <c r="D27" s="66"/>
+      <c r="E27" s="66"/>
+      <c r="F27" s="66"/>
+      <c r="G27" s="66"/>
+      <c r="H27" s="66"/>
+      <c r="I27" s="66"/>
+      <c r="J27" s="66"/>
+      <c r="K27" s="66"/>
+      <c r="L27" s="66"/>
+      <c r="M27" s="66"/>
+      <c r="N27" s="66"/>
+      <c r="O27" s="66"/>
+      <c r="P27" s="66"/>
+      <c r="Q27" s="66"/>
+      <c r="R27" s="66"/>
+      <c r="S27" s="66"/>
+      <c r="T27" s="66"/>
+      <c r="U27" s="66"/>
+      <c r="V27" s="66"/>
+      <c r="W27" s="66"/>
+      <c r="X27" s="66"/>
+      <c r="Y27" s="66"/>
+      <c r="Z27" s="66"/>
+      <c r="AA27" s="66"/>
+      <c r="AB27" s="66"/>
+      <c r="AC27" s="66"/>
+      <c r="AD27" s="66"/>
+      <c r="AE27" s="66"/>
+      <c r="AF27" s="66"/>
+      <c r="AG27" s="66"/>
+      <c r="AH27" s="66"/>
+      <c r="AI27" s="66"/>
+      <c r="AJ27" s="67"/>
     </row>
     <row r="28" spans="1:36" ht="15" customHeight="1">
-      <c r="A28" s="154"/>
-      <c r="B28" s="152"/>
-      <c r="C28" s="152"/>
-      <c r="D28" s="152"/>
-      <c r="E28" s="152"/>
-      <c r="F28" s="152"/>
-      <c r="G28" s="152"/>
-      <c r="H28" s="152"/>
-      <c r="I28" s="152"/>
-      <c r="J28" s="152"/>
-      <c r="K28" s="152"/>
-      <c r="L28" s="152"/>
-      <c r="M28" s="152"/>
-      <c r="N28" s="152"/>
-      <c r="O28" s="152"/>
-      <c r="P28" s="152"/>
-      <c r="Q28" s="152"/>
-      <c r="R28" s="152"/>
-      <c r="S28" s="152"/>
-      <c r="T28" s="152"/>
-      <c r="U28" s="152"/>
-      <c r="V28" s="152"/>
-      <c r="W28" s="152"/>
-      <c r="X28" s="152"/>
-      <c r="Y28" s="152"/>
-      <c r="Z28" s="152"/>
-      <c r="AA28" s="152"/>
-      <c r="AB28" s="152"/>
-      <c r="AC28" s="152"/>
-      <c r="AD28" s="152"/>
-      <c r="AE28" s="152"/>
-      <c r="AF28" s="152"/>
-      <c r="AG28" s="152"/>
-      <c r="AH28" s="152"/>
-      <c r="AI28" s="152"/>
-      <c r="AJ28" s="153"/>
+      <c r="A28" s="68"/>
+      <c r="B28" s="66"/>
+      <c r="C28" s="66"/>
+      <c r="D28" s="66"/>
+      <c r="E28" s="66"/>
+      <c r="F28" s="66"/>
+      <c r="G28" s="66"/>
+      <c r="H28" s="66"/>
+      <c r="I28" s="66"/>
+      <c r="J28" s="66"/>
+      <c r="K28" s="66"/>
+      <c r="L28" s="66"/>
+      <c r="M28" s="66"/>
+      <c r="N28" s="66"/>
+      <c r="O28" s="66"/>
+      <c r="P28" s="66"/>
+      <c r="Q28" s="66"/>
+      <c r="R28" s="66"/>
+      <c r="S28" s="66"/>
+      <c r="T28" s="66"/>
+      <c r="U28" s="66"/>
+      <c r="V28" s="66"/>
+      <c r="W28" s="66"/>
+      <c r="X28" s="66"/>
+      <c r="Y28" s="66"/>
+      <c r="Z28" s="66"/>
+      <c r="AA28" s="66"/>
+      <c r="AB28" s="66"/>
+      <c r="AC28" s="66"/>
+      <c r="AD28" s="66"/>
+      <c r="AE28" s="66"/>
+      <c r="AF28" s="66"/>
+      <c r="AG28" s="66"/>
+      <c r="AH28" s="66"/>
+      <c r="AI28" s="66"/>
+      <c r="AJ28" s="67"/>
     </row>
     <row r="29" spans="1:36" ht="100.8" customHeight="1">
-      <c r="A29" s="155"/>
-      <c r="B29" s="156"/>
-      <c r="C29" s="156"/>
-      <c r="D29" s="156"/>
-      <c r="E29" s="156"/>
-      <c r="F29" s="156"/>
-      <c r="G29" s="156"/>
-      <c r="H29" s="156"/>
-      <c r="I29" s="156"/>
-      <c r="J29" s="156"/>
-      <c r="K29" s="156"/>
-      <c r="L29" s="156"/>
-      <c r="M29" s="156"/>
-      <c r="N29" s="156"/>
-      <c r="O29" s="156"/>
-      <c r="P29" s="156"/>
-      <c r="Q29" s="156"/>
-      <c r="R29" s="156"/>
-      <c r="S29" s="156"/>
-      <c r="T29" s="156"/>
-      <c r="U29" s="156"/>
-      <c r="V29" s="156"/>
-      <c r="W29" s="156"/>
-      <c r="X29" s="156"/>
-      <c r="Y29" s="156"/>
-      <c r="Z29" s="156"/>
-      <c r="AA29" s="156"/>
-      <c r="AB29" s="156"/>
-      <c r="AC29" s="156"/>
-      <c r="AD29" s="156"/>
-      <c r="AE29" s="156"/>
-      <c r="AF29" s="156"/>
-      <c r="AG29" s="156"/>
-      <c r="AH29" s="156"/>
-      <c r="AI29" s="156"/>
-      <c r="AJ29" s="157"/>
+      <c r="A29" s="69"/>
+      <c r="B29" s="70"/>
+      <c r="C29" s="70"/>
+      <c r="D29" s="70"/>
+      <c r="E29" s="70"/>
+      <c r="F29" s="70"/>
+      <c r="G29" s="70"/>
+      <c r="H29" s="70"/>
+      <c r="I29" s="70"/>
+      <c r="J29" s="70"/>
+      <c r="K29" s="70"/>
+      <c r="L29" s="70"/>
+      <c r="M29" s="70"/>
+      <c r="N29" s="70"/>
+      <c r="O29" s="70"/>
+      <c r="P29" s="70"/>
+      <c r="Q29" s="70"/>
+      <c r="R29" s="70"/>
+      <c r="S29" s="70"/>
+      <c r="T29" s="70"/>
+      <c r="U29" s="70"/>
+      <c r="V29" s="70"/>
+      <c r="W29" s="70"/>
+      <c r="X29" s="70"/>
+      <c r="Y29" s="70"/>
+      <c r="Z29" s="70"/>
+      <c r="AA29" s="70"/>
+      <c r="AB29" s="70"/>
+      <c r="AC29" s="70"/>
+      <c r="AD29" s="70"/>
+      <c r="AE29" s="70"/>
+      <c r="AF29" s="70"/>
+      <c r="AG29" s="70"/>
+      <c r="AH29" s="70"/>
+      <c r="AI29" s="70"/>
+      <c r="AJ29" s="71"/>
     </row>
     <row r="30" spans="1:36" ht="12.75" customHeight="1">
-      <c r="A30" s="158" t="s">
+      <c r="A30" s="78" t="s">
         <v>17</v>
       </c>
-      <c r="B30" s="159"/>
-      <c r="C30" s="159"/>
-      <c r="D30" s="159"/>
-      <c r="E30" s="159"/>
-      <c r="F30" s="159"/>
-      <c r="G30" s="159"/>
-      <c r="H30" s="159"/>
-      <c r="I30" s="159"/>
-      <c r="J30" s="159"/>
-      <c r="K30" s="159"/>
-      <c r="L30" s="159"/>
-      <c r="M30" s="159"/>
-      <c r="N30" s="159"/>
-      <c r="O30" s="159"/>
+      <c r="B30" s="79"/>
+      <c r="C30" s="79"/>
+      <c r="D30" s="79"/>
+      <c r="E30" s="79"/>
+      <c r="F30" s="79"/>
+      <c r="G30" s="79"/>
+      <c r="H30" s="79"/>
+      <c r="I30" s="79"/>
+      <c r="J30" s="79"/>
+      <c r="K30" s="79"/>
+      <c r="L30" s="79"/>
+      <c r="M30" s="79"/>
+      <c r="N30" s="79"/>
+      <c r="O30" s="79"/>
       <c r="P30" s="41"/>
       <c r="Q30" s="41"/>
       <c r="R30" s="41"/>
@@ -8213,216 +8218,216 @@
       <c r="AJ30" s="42"/>
     </row>
     <row r="31" spans="1:36" ht="16.5" customHeight="1">
-      <c r="A31" s="151"/>
-      <c r="B31" s="161"/>
-      <c r="C31" s="161"/>
-      <c r="D31" s="161"/>
-      <c r="E31" s="161"/>
-      <c r="F31" s="161"/>
-      <c r="G31" s="161"/>
-      <c r="H31" s="161"/>
-      <c r="I31" s="161"/>
-      <c r="J31" s="161"/>
-      <c r="K31" s="161"/>
-      <c r="L31" s="161"/>
-      <c r="M31" s="161"/>
-      <c r="N31" s="161"/>
-      <c r="O31" s="161"/>
-      <c r="P31" s="161"/>
-      <c r="Q31" s="161"/>
-      <c r="R31" s="161"/>
-      <c r="S31" s="161"/>
-      <c r="T31" s="161"/>
-      <c r="U31" s="161"/>
-      <c r="V31" s="161"/>
-      <c r="W31" s="161"/>
-      <c r="X31" s="161"/>
-      <c r="Y31" s="161"/>
-      <c r="Z31" s="161"/>
-      <c r="AA31" s="161"/>
-      <c r="AB31" s="161"/>
-      <c r="AC31" s="161"/>
-      <c r="AD31" s="161"/>
-      <c r="AE31" s="161"/>
-      <c r="AF31" s="161"/>
-      <c r="AG31" s="161"/>
-      <c r="AH31" s="161"/>
-      <c r="AI31" s="161"/>
-      <c r="AJ31" s="162"/>
+      <c r="A31" s="65"/>
+      <c r="B31" s="82"/>
+      <c r="C31" s="82"/>
+      <c r="D31" s="82"/>
+      <c r="E31" s="82"/>
+      <c r="F31" s="82"/>
+      <c r="G31" s="82"/>
+      <c r="H31" s="82"/>
+      <c r="I31" s="82"/>
+      <c r="J31" s="82"/>
+      <c r="K31" s="82"/>
+      <c r="L31" s="82"/>
+      <c r="M31" s="82"/>
+      <c r="N31" s="82"/>
+      <c r="O31" s="82"/>
+      <c r="P31" s="82"/>
+      <c r="Q31" s="82"/>
+      <c r="R31" s="82"/>
+      <c r="S31" s="82"/>
+      <c r="T31" s="82"/>
+      <c r="U31" s="82"/>
+      <c r="V31" s="82"/>
+      <c r="W31" s="82"/>
+      <c r="X31" s="82"/>
+      <c r="Y31" s="82"/>
+      <c r="Z31" s="82"/>
+      <c r="AA31" s="82"/>
+      <c r="AB31" s="82"/>
+      <c r="AC31" s="82"/>
+      <c r="AD31" s="82"/>
+      <c r="AE31" s="82"/>
+      <c r="AF31" s="82"/>
+      <c r="AG31" s="82"/>
+      <c r="AH31" s="82"/>
+      <c r="AI31" s="82"/>
+      <c r="AJ31" s="83"/>
     </row>
     <row r="32" spans="1:36" ht="16.5" customHeight="1">
-      <c r="A32" s="151"/>
-      <c r="B32" s="161"/>
-      <c r="C32" s="161"/>
-      <c r="D32" s="161"/>
-      <c r="E32" s="161"/>
-      <c r="F32" s="161"/>
-      <c r="G32" s="161"/>
-      <c r="H32" s="161"/>
-      <c r="I32" s="161"/>
-      <c r="J32" s="161"/>
-      <c r="K32" s="161"/>
-      <c r="L32" s="161"/>
-      <c r="M32" s="161"/>
-      <c r="N32" s="161"/>
-      <c r="O32" s="161"/>
-      <c r="P32" s="161"/>
-      <c r="Q32" s="161"/>
-      <c r="R32" s="161"/>
-      <c r="S32" s="161"/>
-      <c r="T32" s="161"/>
-      <c r="U32" s="161"/>
-      <c r="V32" s="161"/>
-      <c r="W32" s="161"/>
-      <c r="X32" s="161"/>
-      <c r="Y32" s="161"/>
-      <c r="Z32" s="161"/>
-      <c r="AA32" s="161"/>
-      <c r="AB32" s="161"/>
-      <c r="AC32" s="161"/>
-      <c r="AD32" s="161"/>
-      <c r="AE32" s="161"/>
-      <c r="AF32" s="161"/>
-      <c r="AG32" s="161"/>
-      <c r="AH32" s="161"/>
-      <c r="AI32" s="161"/>
-      <c r="AJ32" s="162"/>
+      <c r="A32" s="65"/>
+      <c r="B32" s="82"/>
+      <c r="C32" s="82"/>
+      <c r="D32" s="82"/>
+      <c r="E32" s="82"/>
+      <c r="F32" s="82"/>
+      <c r="G32" s="82"/>
+      <c r="H32" s="82"/>
+      <c r="I32" s="82"/>
+      <c r="J32" s="82"/>
+      <c r="K32" s="82"/>
+      <c r="L32" s="82"/>
+      <c r="M32" s="82"/>
+      <c r="N32" s="82"/>
+      <c r="O32" s="82"/>
+      <c r="P32" s="82"/>
+      <c r="Q32" s="82"/>
+      <c r="R32" s="82"/>
+      <c r="S32" s="82"/>
+      <c r="T32" s="82"/>
+      <c r="U32" s="82"/>
+      <c r="V32" s="82"/>
+      <c r="W32" s="82"/>
+      <c r="X32" s="82"/>
+      <c r="Y32" s="82"/>
+      <c r="Z32" s="82"/>
+      <c r="AA32" s="82"/>
+      <c r="AB32" s="82"/>
+      <c r="AC32" s="82"/>
+      <c r="AD32" s="82"/>
+      <c r="AE32" s="82"/>
+      <c r="AF32" s="82"/>
+      <c r="AG32" s="82"/>
+      <c r="AH32" s="82"/>
+      <c r="AI32" s="82"/>
+      <c r="AJ32" s="83"/>
     </row>
     <row r="33" spans="1:36" ht="16.5" customHeight="1">
-      <c r="A33" s="151"/>
-      <c r="B33" s="161"/>
-      <c r="C33" s="161"/>
-      <c r="D33" s="161"/>
-      <c r="E33" s="161"/>
-      <c r="F33" s="161"/>
-      <c r="G33" s="161"/>
-      <c r="H33" s="161"/>
-      <c r="I33" s="161"/>
-      <c r="J33" s="161"/>
-      <c r="K33" s="161"/>
-      <c r="L33" s="161"/>
-      <c r="M33" s="161"/>
-      <c r="N33" s="161"/>
-      <c r="O33" s="161"/>
-      <c r="P33" s="161"/>
-      <c r="Q33" s="161"/>
-      <c r="R33" s="161"/>
-      <c r="S33" s="161"/>
-      <c r="T33" s="161"/>
-      <c r="U33" s="161"/>
-      <c r="V33" s="161"/>
-      <c r="W33" s="161"/>
-      <c r="X33" s="161"/>
-      <c r="Y33" s="161"/>
-      <c r="Z33" s="161"/>
-      <c r="AA33" s="161"/>
-      <c r="AB33" s="161"/>
-      <c r="AC33" s="161"/>
-      <c r="AD33" s="161"/>
-      <c r="AE33" s="161"/>
-      <c r="AF33" s="161"/>
-      <c r="AG33" s="161"/>
-      <c r="AH33" s="161"/>
-      <c r="AI33" s="161"/>
-      <c r="AJ33" s="162"/>
+      <c r="A33" s="65"/>
+      <c r="B33" s="82"/>
+      <c r="C33" s="82"/>
+      <c r="D33" s="82"/>
+      <c r="E33" s="82"/>
+      <c r="F33" s="82"/>
+      <c r="G33" s="82"/>
+      <c r="H33" s="82"/>
+      <c r="I33" s="82"/>
+      <c r="J33" s="82"/>
+      <c r="K33" s="82"/>
+      <c r="L33" s="82"/>
+      <c r="M33" s="82"/>
+      <c r="N33" s="82"/>
+      <c r="O33" s="82"/>
+      <c r="P33" s="82"/>
+      <c r="Q33" s="82"/>
+      <c r="R33" s="82"/>
+      <c r="S33" s="82"/>
+      <c r="T33" s="82"/>
+      <c r="U33" s="82"/>
+      <c r="V33" s="82"/>
+      <c r="W33" s="82"/>
+      <c r="X33" s="82"/>
+      <c r="Y33" s="82"/>
+      <c r="Z33" s="82"/>
+      <c r="AA33" s="82"/>
+      <c r="AB33" s="82"/>
+      <c r="AC33" s="82"/>
+      <c r="AD33" s="82"/>
+      <c r="AE33" s="82"/>
+      <c r="AF33" s="82"/>
+      <c r="AG33" s="82"/>
+      <c r="AH33" s="82"/>
+      <c r="AI33" s="82"/>
+      <c r="AJ33" s="83"/>
     </row>
     <row r="34" spans="1:36" ht="61.8" customHeight="1">
-      <c r="A34" s="151"/>
-      <c r="B34" s="161"/>
-      <c r="C34" s="161"/>
-      <c r="D34" s="161"/>
-      <c r="E34" s="161"/>
-      <c r="F34" s="161"/>
-      <c r="G34" s="161"/>
-      <c r="H34" s="161"/>
-      <c r="I34" s="161"/>
-      <c r="J34" s="161"/>
-      <c r="K34" s="161"/>
-      <c r="L34" s="161"/>
-      <c r="M34" s="161"/>
-      <c r="N34" s="161"/>
-      <c r="O34" s="161"/>
-      <c r="P34" s="161"/>
-      <c r="Q34" s="161"/>
-      <c r="R34" s="161"/>
-      <c r="S34" s="161"/>
-      <c r="T34" s="161"/>
-      <c r="U34" s="161"/>
-      <c r="V34" s="161"/>
-      <c r="W34" s="161"/>
-      <c r="X34" s="161"/>
-      <c r="Y34" s="161"/>
-      <c r="Z34" s="161"/>
-      <c r="AA34" s="161"/>
-      <c r="AB34" s="161"/>
-      <c r="AC34" s="161"/>
-      <c r="AD34" s="161"/>
-      <c r="AE34" s="161"/>
-      <c r="AF34" s="161"/>
-      <c r="AG34" s="161"/>
-      <c r="AH34" s="161"/>
-      <c r="AI34" s="161"/>
-      <c r="AJ34" s="162"/>
+      <c r="A34" s="65"/>
+      <c r="B34" s="82"/>
+      <c r="C34" s="82"/>
+      <c r="D34" s="82"/>
+      <c r="E34" s="82"/>
+      <c r="F34" s="82"/>
+      <c r="G34" s="82"/>
+      <c r="H34" s="82"/>
+      <c r="I34" s="82"/>
+      <c r="J34" s="82"/>
+      <c r="K34" s="82"/>
+      <c r="L34" s="82"/>
+      <c r="M34" s="82"/>
+      <c r="N34" s="82"/>
+      <c r="O34" s="82"/>
+      <c r="P34" s="82"/>
+      <c r="Q34" s="82"/>
+      <c r="R34" s="82"/>
+      <c r="S34" s="82"/>
+      <c r="T34" s="82"/>
+      <c r="U34" s="82"/>
+      <c r="V34" s="82"/>
+      <c r="W34" s="82"/>
+      <c r="X34" s="82"/>
+      <c r="Y34" s="82"/>
+      <c r="Z34" s="82"/>
+      <c r="AA34" s="82"/>
+      <c r="AB34" s="82"/>
+      <c r="AC34" s="82"/>
+      <c r="AD34" s="82"/>
+      <c r="AE34" s="82"/>
+      <c r="AF34" s="82"/>
+      <c r="AG34" s="82"/>
+      <c r="AH34" s="82"/>
+      <c r="AI34" s="82"/>
+      <c r="AJ34" s="83"/>
     </row>
     <row r="35" spans="1:36" ht="13.2" customHeight="1">
-      <c r="A35" s="163"/>
-      <c r="B35" s="164"/>
-      <c r="C35" s="164"/>
-      <c r="D35" s="164"/>
-      <c r="E35" s="164"/>
-      <c r="F35" s="164"/>
-      <c r="G35" s="164"/>
-      <c r="H35" s="164"/>
-      <c r="I35" s="164"/>
-      <c r="J35" s="164"/>
-      <c r="K35" s="164"/>
-      <c r="L35" s="164"/>
-      <c r="M35" s="164"/>
-      <c r="N35" s="164"/>
-      <c r="O35" s="164"/>
-      <c r="P35" s="164"/>
-      <c r="Q35" s="164"/>
-      <c r="R35" s="164"/>
-      <c r="S35" s="164"/>
-      <c r="T35" s="164"/>
-      <c r="U35" s="164"/>
-      <c r="V35" s="164"/>
-      <c r="W35" s="164"/>
-      <c r="X35" s="164"/>
-      <c r="Y35" s="164"/>
-      <c r="Z35" s="164"/>
-      <c r="AA35" s="164"/>
-      <c r="AB35" s="164"/>
-      <c r="AC35" s="164"/>
-      <c r="AD35" s="164"/>
-      <c r="AE35" s="164"/>
-      <c r="AF35" s="164"/>
-      <c r="AG35" s="164"/>
-      <c r="AH35" s="164"/>
-      <c r="AI35" s="164"/>
-      <c r="AJ35" s="165"/>
+      <c r="A35" s="84"/>
+      <c r="B35" s="85"/>
+      <c r="C35" s="85"/>
+      <c r="D35" s="85"/>
+      <c r="E35" s="85"/>
+      <c r="F35" s="85"/>
+      <c r="G35" s="85"/>
+      <c r="H35" s="85"/>
+      <c r="I35" s="85"/>
+      <c r="J35" s="85"/>
+      <c r="K35" s="85"/>
+      <c r="L35" s="85"/>
+      <c r="M35" s="85"/>
+      <c r="N35" s="85"/>
+      <c r="O35" s="85"/>
+      <c r="P35" s="85"/>
+      <c r="Q35" s="85"/>
+      <c r="R35" s="85"/>
+      <c r="S35" s="85"/>
+      <c r="T35" s="85"/>
+      <c r="U35" s="85"/>
+      <c r="V35" s="85"/>
+      <c r="W35" s="85"/>
+      <c r="X35" s="85"/>
+      <c r="Y35" s="85"/>
+      <c r="Z35" s="85"/>
+      <c r="AA35" s="85"/>
+      <c r="AB35" s="85"/>
+      <c r="AC35" s="85"/>
+      <c r="AD35" s="85"/>
+      <c r="AE35" s="85"/>
+      <c r="AF35" s="85"/>
+      <c r="AG35" s="85"/>
+      <c r="AH35" s="85"/>
+      <c r="AI35" s="85"/>
+      <c r="AJ35" s="86"/>
     </row>
     <row r="36" spans="1:36" ht="13.5" customHeight="1">
-      <c r="A36" s="75" t="s">
+      <c r="A36" s="72" t="s">
         <v>94</v>
       </c>
-      <c r="B36" s="76"/>
-      <c r="C36" s="76"/>
-      <c r="D36" s="76"/>
-      <c r="E36" s="76"/>
-      <c r="F36" s="76"/>
-      <c r="G36" s="76"/>
-      <c r="H36" s="76"/>
-      <c r="I36" s="76"/>
-      <c r="J36" s="76"/>
-      <c r="K36" s="76"/>
-      <c r="L36" s="76"/>
-      <c r="M36" s="76"/>
-      <c r="N36" s="76"/>
-      <c r="O36" s="76"/>
-      <c r="P36" s="76"/>
-      <c r="Q36" s="76"/>
-      <c r="R36" s="76"/>
+      <c r="B36" s="73"/>
+      <c r="C36" s="73"/>
+      <c r="D36" s="73"/>
+      <c r="E36" s="73"/>
+      <c r="F36" s="73"/>
+      <c r="G36" s="73"/>
+      <c r="H36" s="73"/>
+      <c r="I36" s="73"/>
+      <c r="J36" s="73"/>
+      <c r="K36" s="73"/>
+      <c r="L36" s="73"/>
+      <c r="M36" s="73"/>
+      <c r="N36" s="73"/>
+      <c r="O36" s="73"/>
+      <c r="P36" s="73"/>
+      <c r="Q36" s="73"/>
+      <c r="R36" s="73"/>
       <c r="S36" s="40"/>
       <c r="T36" s="40"/>
       <c r="U36" s="40"/>
@@ -8443,178 +8448,178 @@
       <c r="AJ36" s="43"/>
     </row>
     <row r="37" spans="1:36" ht="14.25" customHeight="1">
-      <c r="A37" s="151"/>
-      <c r="B37" s="161"/>
-      <c r="C37" s="161"/>
-      <c r="D37" s="161"/>
-      <c r="E37" s="161"/>
-      <c r="F37" s="161"/>
-      <c r="G37" s="161"/>
-      <c r="H37" s="161"/>
-      <c r="I37" s="161"/>
-      <c r="J37" s="161"/>
-      <c r="K37" s="161"/>
-      <c r="L37" s="161"/>
-      <c r="M37" s="161"/>
-      <c r="N37" s="161"/>
-      <c r="O37" s="161"/>
-      <c r="P37" s="161"/>
-      <c r="Q37" s="161"/>
-      <c r="R37" s="161"/>
-      <c r="S37" s="161"/>
-      <c r="T37" s="161"/>
-      <c r="U37" s="161"/>
-      <c r="V37" s="161"/>
-      <c r="W37" s="161"/>
-      <c r="X37" s="161"/>
-      <c r="Y37" s="161"/>
-      <c r="Z37" s="161"/>
-      <c r="AA37" s="161"/>
-      <c r="AB37" s="161"/>
-      <c r="AC37" s="161"/>
-      <c r="AD37" s="161"/>
-      <c r="AE37" s="161"/>
-      <c r="AF37" s="161"/>
-      <c r="AG37" s="161"/>
-      <c r="AH37" s="161"/>
-      <c r="AI37" s="161"/>
-      <c r="AJ37" s="162"/>
+      <c r="A37" s="65"/>
+      <c r="B37" s="82"/>
+      <c r="C37" s="82"/>
+      <c r="D37" s="82"/>
+      <c r="E37" s="82"/>
+      <c r="F37" s="82"/>
+      <c r="G37" s="82"/>
+      <c r="H37" s="82"/>
+      <c r="I37" s="82"/>
+      <c r="J37" s="82"/>
+      <c r="K37" s="82"/>
+      <c r="L37" s="82"/>
+      <c r="M37" s="82"/>
+      <c r="N37" s="82"/>
+      <c r="O37" s="82"/>
+      <c r="P37" s="82"/>
+      <c r="Q37" s="82"/>
+      <c r="R37" s="82"/>
+      <c r="S37" s="82"/>
+      <c r="T37" s="82"/>
+      <c r="U37" s="82"/>
+      <c r="V37" s="82"/>
+      <c r="W37" s="82"/>
+      <c r="X37" s="82"/>
+      <c r="Y37" s="82"/>
+      <c r="Z37" s="82"/>
+      <c r="AA37" s="82"/>
+      <c r="AB37" s="82"/>
+      <c r="AC37" s="82"/>
+      <c r="AD37" s="82"/>
+      <c r="AE37" s="82"/>
+      <c r="AF37" s="82"/>
+      <c r="AG37" s="82"/>
+      <c r="AH37" s="82"/>
+      <c r="AI37" s="82"/>
+      <c r="AJ37" s="83"/>
     </row>
     <row r="38" spans="1:36" ht="14.25" customHeight="1">
-      <c r="A38" s="151"/>
-      <c r="B38" s="161"/>
-      <c r="C38" s="161"/>
-      <c r="D38" s="161"/>
-      <c r="E38" s="161"/>
-      <c r="F38" s="161"/>
-      <c r="G38" s="161"/>
-      <c r="H38" s="161"/>
-      <c r="I38" s="161"/>
-      <c r="J38" s="161"/>
-      <c r="K38" s="161"/>
-      <c r="L38" s="161"/>
-      <c r="M38" s="161"/>
-      <c r="N38" s="161"/>
-      <c r="O38" s="161"/>
-      <c r="P38" s="161"/>
-      <c r="Q38" s="161"/>
-      <c r="R38" s="161"/>
-      <c r="S38" s="161"/>
-      <c r="T38" s="161"/>
-      <c r="U38" s="161"/>
-      <c r="V38" s="161"/>
-      <c r="W38" s="161"/>
-      <c r="X38" s="161"/>
-      <c r="Y38" s="161"/>
-      <c r="Z38" s="161"/>
-      <c r="AA38" s="161"/>
-      <c r="AB38" s="161"/>
-      <c r="AC38" s="161"/>
-      <c r="AD38" s="161"/>
-      <c r="AE38" s="161"/>
-      <c r="AF38" s="161"/>
-      <c r="AG38" s="161"/>
-      <c r="AH38" s="161"/>
-      <c r="AI38" s="161"/>
-      <c r="AJ38" s="162"/>
+      <c r="A38" s="65"/>
+      <c r="B38" s="82"/>
+      <c r="C38" s="82"/>
+      <c r="D38" s="82"/>
+      <c r="E38" s="82"/>
+      <c r="F38" s="82"/>
+      <c r="G38" s="82"/>
+      <c r="H38" s="82"/>
+      <c r="I38" s="82"/>
+      <c r="J38" s="82"/>
+      <c r="K38" s="82"/>
+      <c r="L38" s="82"/>
+      <c r="M38" s="82"/>
+      <c r="N38" s="82"/>
+      <c r="O38" s="82"/>
+      <c r="P38" s="82"/>
+      <c r="Q38" s="82"/>
+      <c r="R38" s="82"/>
+      <c r="S38" s="82"/>
+      <c r="T38" s="82"/>
+      <c r="U38" s="82"/>
+      <c r="V38" s="82"/>
+      <c r="W38" s="82"/>
+      <c r="X38" s="82"/>
+      <c r="Y38" s="82"/>
+      <c r="Z38" s="82"/>
+      <c r="AA38" s="82"/>
+      <c r="AB38" s="82"/>
+      <c r="AC38" s="82"/>
+      <c r="AD38" s="82"/>
+      <c r="AE38" s="82"/>
+      <c r="AF38" s="82"/>
+      <c r="AG38" s="82"/>
+      <c r="AH38" s="82"/>
+      <c r="AI38" s="82"/>
+      <c r="AJ38" s="83"/>
     </row>
     <row r="39" spans="1:36" ht="27.6" customHeight="1">
-      <c r="A39" s="151"/>
-      <c r="B39" s="161"/>
-      <c r="C39" s="161"/>
-      <c r="D39" s="161"/>
-      <c r="E39" s="161"/>
-      <c r="F39" s="161"/>
-      <c r="G39" s="161"/>
-      <c r="H39" s="161"/>
-      <c r="I39" s="161"/>
-      <c r="J39" s="161"/>
-      <c r="K39" s="161"/>
-      <c r="L39" s="161"/>
-      <c r="M39" s="161"/>
-      <c r="N39" s="161"/>
-      <c r="O39" s="161"/>
-      <c r="P39" s="161"/>
-      <c r="Q39" s="161"/>
-      <c r="R39" s="161"/>
-      <c r="S39" s="161"/>
-      <c r="T39" s="161"/>
-      <c r="U39" s="161"/>
-      <c r="V39" s="161"/>
-      <c r="W39" s="161"/>
-      <c r="X39" s="161"/>
-      <c r="Y39" s="161"/>
-      <c r="Z39" s="161"/>
-      <c r="AA39" s="161"/>
-      <c r="AB39" s="161"/>
-      <c r="AC39" s="161"/>
-      <c r="AD39" s="161"/>
-      <c r="AE39" s="161"/>
-      <c r="AF39" s="161"/>
-      <c r="AG39" s="161"/>
-      <c r="AH39" s="161"/>
-      <c r="AI39" s="161"/>
-      <c r="AJ39" s="162"/>
+      <c r="A39" s="65"/>
+      <c r="B39" s="82"/>
+      <c r="C39" s="82"/>
+      <c r="D39" s="82"/>
+      <c r="E39" s="82"/>
+      <c r="F39" s="82"/>
+      <c r="G39" s="82"/>
+      <c r="H39" s="82"/>
+      <c r="I39" s="82"/>
+      <c r="J39" s="82"/>
+      <c r="K39" s="82"/>
+      <c r="L39" s="82"/>
+      <c r="M39" s="82"/>
+      <c r="N39" s="82"/>
+      <c r="O39" s="82"/>
+      <c r="P39" s="82"/>
+      <c r="Q39" s="82"/>
+      <c r="R39" s="82"/>
+      <c r="S39" s="82"/>
+      <c r="T39" s="82"/>
+      <c r="U39" s="82"/>
+      <c r="V39" s="82"/>
+      <c r="W39" s="82"/>
+      <c r="X39" s="82"/>
+      <c r="Y39" s="82"/>
+      <c r="Z39" s="82"/>
+      <c r="AA39" s="82"/>
+      <c r="AB39" s="82"/>
+      <c r="AC39" s="82"/>
+      <c r="AD39" s="82"/>
+      <c r="AE39" s="82"/>
+      <c r="AF39" s="82"/>
+      <c r="AG39" s="82"/>
+      <c r="AH39" s="82"/>
+      <c r="AI39" s="82"/>
+      <c r="AJ39" s="83"/>
     </row>
     <row r="40" spans="1:36" ht="16.8" customHeight="1">
-      <c r="A40" s="151"/>
-      <c r="B40" s="161"/>
-      <c r="C40" s="161"/>
-      <c r="D40" s="161"/>
-      <c r="E40" s="161"/>
-      <c r="F40" s="161"/>
-      <c r="G40" s="161"/>
-      <c r="H40" s="161"/>
-      <c r="I40" s="161"/>
-      <c r="J40" s="161"/>
-      <c r="K40" s="161"/>
-      <c r="L40" s="161"/>
-      <c r="M40" s="161"/>
-      <c r="N40" s="161"/>
-      <c r="O40" s="161"/>
-      <c r="P40" s="161"/>
-      <c r="Q40" s="161"/>
-      <c r="R40" s="161"/>
-      <c r="S40" s="161"/>
-      <c r="T40" s="161"/>
-      <c r="U40" s="161"/>
-      <c r="V40" s="161"/>
-      <c r="W40" s="161"/>
-      <c r="X40" s="161"/>
-      <c r="Y40" s="161"/>
-      <c r="Z40" s="161"/>
-      <c r="AA40" s="161"/>
-      <c r="AB40" s="161"/>
-      <c r="AC40" s="161"/>
-      <c r="AD40" s="161"/>
-      <c r="AE40" s="161"/>
-      <c r="AF40" s="161"/>
-      <c r="AG40" s="161"/>
-      <c r="AH40" s="161"/>
-      <c r="AI40" s="161"/>
-      <c r="AJ40" s="162"/>
+      <c r="A40" s="65"/>
+      <c r="B40" s="82"/>
+      <c r="C40" s="82"/>
+      <c r="D40" s="82"/>
+      <c r="E40" s="82"/>
+      <c r="F40" s="82"/>
+      <c r="G40" s="82"/>
+      <c r="H40" s="82"/>
+      <c r="I40" s="82"/>
+      <c r="J40" s="82"/>
+      <c r="K40" s="82"/>
+      <c r="L40" s="82"/>
+      <c r="M40" s="82"/>
+      <c r="N40" s="82"/>
+      <c r="O40" s="82"/>
+      <c r="P40" s="82"/>
+      <c r="Q40" s="82"/>
+      <c r="R40" s="82"/>
+      <c r="S40" s="82"/>
+      <c r="T40" s="82"/>
+      <c r="U40" s="82"/>
+      <c r="V40" s="82"/>
+      <c r="W40" s="82"/>
+      <c r="X40" s="82"/>
+      <c r="Y40" s="82"/>
+      <c r="Z40" s="82"/>
+      <c r="AA40" s="82"/>
+      <c r="AB40" s="82"/>
+      <c r="AC40" s="82"/>
+      <c r="AD40" s="82"/>
+      <c r="AE40" s="82"/>
+      <c r="AF40" s="82"/>
+      <c r="AG40" s="82"/>
+      <c r="AH40" s="82"/>
+      <c r="AI40" s="82"/>
+      <c r="AJ40" s="83"/>
     </row>
     <row r="41" spans="1:36" ht="16.8" customHeight="1">
-      <c r="A41" s="75" t="s">
+      <c r="A41" s="72" t="s">
         <v>99</v>
       </c>
-      <c r="B41" s="76"/>
-      <c r="C41" s="76"/>
-      <c r="D41" s="76"/>
-      <c r="E41" s="76"/>
-      <c r="F41" s="76"/>
-      <c r="G41" s="76"/>
-      <c r="H41" s="76"/>
-      <c r="I41" s="76"/>
-      <c r="J41" s="76"/>
-      <c r="K41" s="76"/>
-      <c r="L41" s="76"/>
-      <c r="M41" s="76"/>
-      <c r="N41" s="76"/>
-      <c r="O41" s="76"/>
-      <c r="P41" s="76"/>
-      <c r="Q41" s="76"/>
-      <c r="R41" s="76"/>
+      <c r="B41" s="73"/>
+      <c r="C41" s="73"/>
+      <c r="D41" s="73"/>
+      <c r="E41" s="73"/>
+      <c r="F41" s="73"/>
+      <c r="G41" s="73"/>
+      <c r="H41" s="73"/>
+      <c r="I41" s="73"/>
+      <c r="J41" s="73"/>
+      <c r="K41" s="73"/>
+      <c r="L41" s="73"/>
+      <c r="M41" s="73"/>
+      <c r="N41" s="73"/>
+      <c r="O41" s="73"/>
+      <c r="P41" s="73"/>
+      <c r="Q41" s="73"/>
+      <c r="R41" s="73"/>
       <c r="S41" s="40"/>
       <c r="T41" s="40"/>
       <c r="U41" s="40"/>
@@ -8673,675 +8678,675 @@
       <c r="AJ42" s="55"/>
     </row>
     <row r="43" spans="1:36" ht="17.25" customHeight="1">
-      <c r="A43" s="101" t="s">
+      <c r="A43" s="74" t="s">
         <v>18</v>
       </c>
-      <c r="B43" s="102"/>
-      <c r="C43" s="102"/>
-      <c r="D43" s="102"/>
-      <c r="E43" s="102"/>
-      <c r="F43" s="102"/>
-      <c r="G43" s="102"/>
-      <c r="H43" s="102"/>
-      <c r="I43" s="103"/>
-      <c r="J43" s="101" t="s">
+      <c r="B43" s="75"/>
+      <c r="C43" s="75"/>
+      <c r="D43" s="75"/>
+      <c r="E43" s="75"/>
+      <c r="F43" s="75"/>
+      <c r="G43" s="75"/>
+      <c r="H43" s="75"/>
+      <c r="I43" s="76"/>
+      <c r="J43" s="74" t="s">
         <v>19</v>
       </c>
-      <c r="K43" s="102"/>
-      <c r="L43" s="102"/>
-      <c r="M43" s="102"/>
-      <c r="N43" s="102"/>
-      <c r="O43" s="102"/>
-      <c r="P43" s="102"/>
-      <c r="Q43" s="102"/>
-      <c r="R43" s="103"/>
-      <c r="S43" s="101" t="s">
+      <c r="K43" s="75"/>
+      <c r="L43" s="75"/>
+      <c r="M43" s="75"/>
+      <c r="N43" s="75"/>
+      <c r="O43" s="75"/>
+      <c r="P43" s="75"/>
+      <c r="Q43" s="75"/>
+      <c r="R43" s="76"/>
+      <c r="S43" s="74" t="s">
         <v>77</v>
       </c>
-      <c r="T43" s="102"/>
-      <c r="U43" s="102"/>
-      <c r="V43" s="102"/>
-      <c r="W43" s="102"/>
-      <c r="X43" s="102"/>
-      <c r="Y43" s="102"/>
-      <c r="Z43" s="102"/>
-      <c r="AA43" s="103"/>
-      <c r="AB43" s="160" t="s">
+      <c r="T43" s="75"/>
+      <c r="U43" s="75"/>
+      <c r="V43" s="75"/>
+      <c r="W43" s="75"/>
+      <c r="X43" s="75"/>
+      <c r="Y43" s="75"/>
+      <c r="Z43" s="75"/>
+      <c r="AA43" s="76"/>
+      <c r="AB43" s="80" t="s">
         <v>91</v>
       </c>
-      <c r="AC43" s="102"/>
-      <c r="AD43" s="102"/>
-      <c r="AE43" s="102"/>
-      <c r="AF43" s="102"/>
-      <c r="AG43" s="102"/>
-      <c r="AH43" s="102"/>
-      <c r="AI43" s="102"/>
-      <c r="AJ43" s="103"/>
+      <c r="AC43" s="75"/>
+      <c r="AD43" s="75"/>
+      <c r="AE43" s="75"/>
+      <c r="AF43" s="75"/>
+      <c r="AG43" s="75"/>
+      <c r="AH43" s="75"/>
+      <c r="AI43" s="75"/>
+      <c r="AJ43" s="76"/>
     </row>
     <row r="44" spans="1:36" ht="18" customHeight="1">
       <c r="A44" s="2"/>
-      <c r="B44" s="126" t="s">
+      <c r="B44" s="60" t="s">
         <v>21</v>
       </c>
-      <c r="C44" s="126"/>
-      <c r="D44" s="126"/>
-      <c r="E44" s="126"/>
-      <c r="F44" s="126"/>
-      <c r="G44" s="126"/>
-      <c r="H44" s="126"/>
-      <c r="I44" s="127"/>
+      <c r="C44" s="60"/>
+      <c r="D44" s="60"/>
+      <c r="E44" s="60"/>
+      <c r="F44" s="60"/>
+      <c r="G44" s="60"/>
+      <c r="H44" s="60"/>
+      <c r="I44" s="61"/>
       <c r="J44" s="10"/>
-      <c r="K44" s="126" t="s">
+      <c r="K44" s="60" t="s">
         <v>22</v>
       </c>
-      <c r="L44" s="126"/>
-      <c r="M44" s="126"/>
-      <c r="N44" s="126"/>
-      <c r="O44" s="126"/>
-      <c r="P44" s="126"/>
-      <c r="Q44" s="126"/>
-      <c r="R44" s="127"/>
-      <c r="S44" s="123" t="s">
+      <c r="L44" s="60"/>
+      <c r="M44" s="60"/>
+      <c r="N44" s="60"/>
+      <c r="O44" s="60"/>
+      <c r="P44" s="60"/>
+      <c r="Q44" s="60"/>
+      <c r="R44" s="61"/>
+      <c r="S44" s="87" t="s">
         <v>81</v>
       </c>
-      <c r="T44" s="81"/>
-      <c r="U44" s="81"/>
-      <c r="V44" s="81"/>
-      <c r="W44" s="64"/>
-      <c r="X44" s="64"/>
-      <c r="Y44" s="64"/>
+      <c r="T44" s="88"/>
+      <c r="U44" s="88"/>
+      <c r="V44" s="88"/>
+      <c r="W44" s="81"/>
+      <c r="X44" s="81"/>
+      <c r="Y44" s="81"/>
       <c r="Z44" s="49"/>
       <c r="AA44" s="4"/>
-      <c r="AB44" s="124" t="s">
+      <c r="AB44" s="62" t="s">
         <v>82</v>
       </c>
-      <c r="AC44" s="77"/>
-      <c r="AD44" s="77"/>
-      <c r="AE44" s="77"/>
-      <c r="AF44" s="131"/>
-      <c r="AG44" s="131"/>
-      <c r="AH44" s="131"/>
-      <c r="AI44" s="131"/>
+      <c r="AC44" s="63"/>
+      <c r="AD44" s="63"/>
+      <c r="AE44" s="63"/>
+      <c r="AF44" s="77"/>
+      <c r="AG44" s="77"/>
+      <c r="AH44" s="77"/>
+      <c r="AI44" s="77"/>
       <c r="AJ44" s="4"/>
     </row>
     <row r="45" spans="1:36" ht="18" customHeight="1">
       <c r="A45" s="2"/>
-      <c r="B45" s="126" t="s">
+      <c r="B45" s="60" t="s">
         <v>24</v>
       </c>
-      <c r="C45" s="126"/>
-      <c r="D45" s="126"/>
-      <c r="E45" s="126"/>
-      <c r="F45" s="126"/>
-      <c r="G45" s="126"/>
-      <c r="H45" s="126"/>
-      <c r="I45" s="127"/>
+      <c r="C45" s="60"/>
+      <c r="D45" s="60"/>
+      <c r="E45" s="60"/>
+      <c r="F45" s="60"/>
+      <c r="G45" s="60"/>
+      <c r="H45" s="60"/>
+      <c r="I45" s="61"/>
       <c r="J45" s="10"/>
-      <c r="K45" s="126" t="s">
+      <c r="K45" s="60" t="s">
         <v>25</v>
       </c>
-      <c r="L45" s="126"/>
-      <c r="M45" s="126"/>
-      <c r="N45" s="126"/>
-      <c r="O45" s="126"/>
-      <c r="P45" s="126"/>
-      <c r="Q45" s="126"/>
-      <c r="R45" s="127"/>
-      <c r="S45" s="123" t="s">
+      <c r="L45" s="60"/>
+      <c r="M45" s="60"/>
+      <c r="N45" s="60"/>
+      <c r="O45" s="60"/>
+      <c r="P45" s="60"/>
+      <c r="Q45" s="60"/>
+      <c r="R45" s="61"/>
+      <c r="S45" s="87" t="s">
         <v>80</v>
       </c>
-      <c r="T45" s="81"/>
-      <c r="U45" s="81"/>
-      <c r="V45" s="81"/>
-      <c r="W45" s="150"/>
-      <c r="X45" s="150"/>
-      <c r="Y45" s="150"/>
-      <c r="Z45" s="150"/>
+      <c r="T45" s="88"/>
+      <c r="U45" s="88"/>
+      <c r="V45" s="88"/>
+      <c r="W45" s="59"/>
+      <c r="X45" s="59"/>
+      <c r="Y45" s="59"/>
+      <c r="Z45" s="59"/>
       <c r="AA45" s="4"/>
-      <c r="AB45" s="123" t="s">
+      <c r="AB45" s="87" t="s">
         <v>81</v>
       </c>
-      <c r="AC45" s="81"/>
-      <c r="AD45" s="81"/>
-      <c r="AE45" s="81"/>
-      <c r="AF45" s="150"/>
-      <c r="AG45" s="150"/>
-      <c r="AH45" s="150"/>
-      <c r="AI45" s="150"/>
+      <c r="AC45" s="88"/>
+      <c r="AD45" s="88"/>
+      <c r="AE45" s="88"/>
+      <c r="AF45" s="59"/>
+      <c r="AG45" s="59"/>
+      <c r="AH45" s="59"/>
+      <c r="AI45" s="59"/>
       <c r="AJ45" s="4"/>
     </row>
     <row r="46" spans="1:36" ht="18" customHeight="1">
       <c r="A46" s="2"/>
-      <c r="B46" s="126" t="s">
+      <c r="B46" s="60" t="s">
         <v>27</v>
       </c>
-      <c r="C46" s="126"/>
-      <c r="D46" s="126"/>
-      <c r="E46" s="126"/>
-      <c r="F46" s="126"/>
-      <c r="G46" s="126"/>
-      <c r="H46" s="126"/>
-      <c r="I46" s="127"/>
+      <c r="C46" s="60"/>
+      <c r="D46" s="60"/>
+      <c r="E46" s="60"/>
+      <c r="F46" s="60"/>
+      <c r="G46" s="60"/>
+      <c r="H46" s="60"/>
+      <c r="I46" s="61"/>
       <c r="J46" s="10"/>
-      <c r="K46" s="126" t="s">
+      <c r="K46" s="60" t="s">
         <v>28</v>
       </c>
-      <c r="L46" s="126"/>
-      <c r="M46" s="126"/>
-      <c r="N46" s="126"/>
-      <c r="O46" s="126"/>
-      <c r="P46" s="126"/>
-      <c r="Q46" s="126"/>
-      <c r="R46" s="127"/>
-      <c r="S46" s="124" t="s">
+      <c r="L46" s="60"/>
+      <c r="M46" s="60"/>
+      <c r="N46" s="60"/>
+      <c r="O46" s="60"/>
+      <c r="P46" s="60"/>
+      <c r="Q46" s="60"/>
+      <c r="R46" s="61"/>
+      <c r="S46" s="62" t="s">
         <v>78</v>
       </c>
-      <c r="T46" s="77"/>
-      <c r="U46" s="77"/>
-      <c r="V46" s="77"/>
-      <c r="W46" s="77"/>
-      <c r="X46" s="125"/>
-      <c r="Y46" s="125"/>
-      <c r="Z46" s="125"/>
+      <c r="T46" s="63"/>
+      <c r="U46" s="63"/>
+      <c r="V46" s="63"/>
+      <c r="W46" s="63"/>
+      <c r="X46" s="96"/>
+      <c r="Y46" s="96"/>
+      <c r="Z46" s="96"/>
       <c r="AA46" s="12" t="s">
         <v>30</v>
       </c>
-      <c r="AB46" s="123" t="s">
+      <c r="AB46" s="87" t="s">
         <v>80</v>
       </c>
-      <c r="AC46" s="81"/>
-      <c r="AD46" s="81"/>
-      <c r="AE46" s="81"/>
-      <c r="AF46" s="150"/>
-      <c r="AG46" s="150"/>
-      <c r="AH46" s="150"/>
-      <c r="AI46" s="150"/>
+      <c r="AC46" s="88"/>
+      <c r="AD46" s="88"/>
+      <c r="AE46" s="88"/>
+      <c r="AF46" s="59"/>
+      <c r="AG46" s="59"/>
+      <c r="AH46" s="59"/>
+      <c r="AI46" s="59"/>
       <c r="AJ46" s="4"/>
     </row>
     <row r="47" spans="1:36" ht="18" customHeight="1">
       <c r="A47" s="2"/>
-      <c r="B47" s="126" t="s">
+      <c r="B47" s="60" t="s">
         <v>87</v>
       </c>
-      <c r="C47" s="126"/>
-      <c r="D47" s="126"/>
-      <c r="E47" s="126"/>
-      <c r="F47" s="126"/>
-      <c r="G47" s="126"/>
-      <c r="H47" s="126"/>
-      <c r="I47" s="127"/>
+      <c r="C47" s="60"/>
+      <c r="D47" s="60"/>
+      <c r="E47" s="60"/>
+      <c r="F47" s="60"/>
+      <c r="G47" s="60"/>
+      <c r="H47" s="60"/>
+      <c r="I47" s="61"/>
       <c r="J47" s="10"/>
-      <c r="K47" s="126" t="s">
+      <c r="K47" s="60" t="s">
         <v>31</v>
       </c>
-      <c r="L47" s="126"/>
-      <c r="M47" s="126"/>
-      <c r="N47" s="126"/>
-      <c r="O47" s="126"/>
-      <c r="P47" s="126"/>
-      <c r="Q47" s="126"/>
-      <c r="R47" s="127"/>
-      <c r="S47" s="128" t="s">
+      <c r="L47" s="60"/>
+      <c r="M47" s="60"/>
+      <c r="N47" s="60"/>
+      <c r="O47" s="60"/>
+      <c r="P47" s="60"/>
+      <c r="Q47" s="60"/>
+      <c r="R47" s="61"/>
+      <c r="S47" s="104" t="s">
         <v>79</v>
       </c>
-      <c r="T47" s="129"/>
-      <c r="U47" s="129"/>
-      <c r="V47" s="129"/>
-      <c r="W47" s="129"/>
-      <c r="X47" s="145"/>
-      <c r="Y47" s="145"/>
-      <c r="Z47" s="145"/>
+      <c r="T47" s="105"/>
+      <c r="U47" s="105"/>
+      <c r="V47" s="105"/>
+      <c r="W47" s="105"/>
+      <c r="X47" s="64"/>
+      <c r="Y47" s="64"/>
+      <c r="Z47" s="64"/>
       <c r="AA47" s="33" t="s">
         <v>30</v>
       </c>
-      <c r="AB47" s="123" t="s">
+      <c r="AB47" s="87" t="s">
         <v>83</v>
       </c>
-      <c r="AC47" s="81"/>
-      <c r="AD47" s="81"/>
-      <c r="AE47" s="81"/>
-      <c r="AF47" s="131"/>
-      <c r="AG47" s="131"/>
-      <c r="AH47" s="131"/>
-      <c r="AI47" s="131"/>
+      <c r="AC47" s="88"/>
+      <c r="AD47" s="88"/>
+      <c r="AE47" s="88"/>
+      <c r="AF47" s="77"/>
+      <c r="AG47" s="77"/>
+      <c r="AH47" s="77"/>
+      <c r="AI47" s="77"/>
       <c r="AJ47" s="4"/>
     </row>
     <row r="48" spans="1:36" ht="18" customHeight="1">
       <c r="A48" s="34"/>
-      <c r="B48" s="126" t="s">
+      <c r="B48" s="60" t="s">
         <v>33</v>
       </c>
-      <c r="C48" s="126"/>
-      <c r="D48" s="126"/>
-      <c r="E48" s="126"/>
-      <c r="F48" s="126"/>
-      <c r="G48" s="126"/>
-      <c r="H48" s="126"/>
-      <c r="I48" s="127"/>
+      <c r="C48" s="60"/>
+      <c r="D48" s="60"/>
+      <c r="E48" s="60"/>
+      <c r="F48" s="60"/>
+      <c r="G48" s="60"/>
+      <c r="H48" s="60"/>
+      <c r="I48" s="61"/>
       <c r="J48" s="10"/>
-      <c r="K48" s="126" t="s">
+      <c r="K48" s="60" t="s">
         <v>34</v>
       </c>
-      <c r="L48" s="126"/>
-      <c r="M48" s="126"/>
-      <c r="N48" s="126"/>
-      <c r="O48" s="126"/>
-      <c r="P48" s="126"/>
-      <c r="Q48" s="126"/>
-      <c r="R48" s="127"/>
-      <c r="S48" s="141" t="s">
+      <c r="L48" s="60"/>
+      <c r="M48" s="60"/>
+      <c r="N48" s="60"/>
+      <c r="O48" s="60"/>
+      <c r="P48" s="60"/>
+      <c r="Q48" s="60"/>
+      <c r="R48" s="61"/>
+      <c r="S48" s="93" t="s">
         <v>20</v>
       </c>
-      <c r="T48" s="142"/>
-      <c r="U48" s="142"/>
-      <c r="V48" s="142"/>
-      <c r="W48" s="142"/>
-      <c r="X48" s="142"/>
-      <c r="Y48" s="142"/>
-      <c r="Z48" s="142"/>
-      <c r="AA48" s="143"/>
-      <c r="AB48" s="124" t="s">
+      <c r="T48" s="94"/>
+      <c r="U48" s="94"/>
+      <c r="V48" s="94"/>
+      <c r="W48" s="94"/>
+      <c r="X48" s="94"/>
+      <c r="Y48" s="94"/>
+      <c r="Z48" s="94"/>
+      <c r="AA48" s="95"/>
+      <c r="AB48" s="62" t="s">
         <v>78</v>
       </c>
-      <c r="AC48" s="77"/>
-      <c r="AD48" s="77"/>
-      <c r="AE48" s="77"/>
-      <c r="AF48" s="77"/>
-      <c r="AG48" s="125"/>
-      <c r="AH48" s="125"/>
-      <c r="AI48" s="125"/>
+      <c r="AC48" s="63"/>
+      <c r="AD48" s="63"/>
+      <c r="AE48" s="63"/>
+      <c r="AF48" s="63"/>
+      <c r="AG48" s="96"/>
+      <c r="AH48" s="96"/>
+      <c r="AI48" s="96"/>
       <c r="AJ48" s="12" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="49" spans="1:36" ht="18" customHeight="1">
       <c r="A49" s="10"/>
-      <c r="B49" s="126" t="s">
+      <c r="B49" s="60" t="s">
         <v>74</v>
       </c>
-      <c r="C49" s="126"/>
-      <c r="D49" s="126"/>
-      <c r="E49" s="126"/>
-      <c r="F49" s="126"/>
-      <c r="G49" s="126"/>
-      <c r="H49" s="126"/>
-      <c r="I49" s="127"/>
+      <c r="C49" s="60"/>
+      <c r="D49" s="60"/>
+      <c r="E49" s="60"/>
+      <c r="F49" s="60"/>
+      <c r="G49" s="60"/>
+      <c r="H49" s="60"/>
+      <c r="I49" s="61"/>
       <c r="J49" s="10"/>
-      <c r="K49" s="126" t="s">
+      <c r="K49" s="60" t="s">
         <v>37</v>
       </c>
-      <c r="L49" s="126"/>
-      <c r="M49" s="126"/>
-      <c r="N49" s="126"/>
-      <c r="O49" s="126"/>
-      <c r="P49" s="126"/>
-      <c r="Q49" s="126"/>
-      <c r="R49" s="127"/>
+      <c r="L49" s="60"/>
+      <c r="M49" s="60"/>
+      <c r="N49" s="60"/>
+      <c r="O49" s="60"/>
+      <c r="P49" s="60"/>
+      <c r="Q49" s="60"/>
+      <c r="R49" s="61"/>
       <c r="S49" s="10"/>
-      <c r="T49" s="126" t="s">
+      <c r="T49" s="60" t="s">
         <v>23</v>
       </c>
-      <c r="U49" s="126"/>
-      <c r="V49" s="126"/>
-      <c r="W49" s="126"/>
-      <c r="X49" s="126"/>
-      <c r="Y49" s="126"/>
-      <c r="Z49" s="126"/>
-      <c r="AA49" s="127"/>
-      <c r="AB49" s="128" t="s">
+      <c r="U49" s="60"/>
+      <c r="V49" s="60"/>
+      <c r="W49" s="60"/>
+      <c r="X49" s="60"/>
+      <c r="Y49" s="60"/>
+      <c r="Z49" s="60"/>
+      <c r="AA49" s="61"/>
+      <c r="AB49" s="104" t="s">
         <v>79</v>
       </c>
-      <c r="AC49" s="129"/>
-      <c r="AD49" s="129"/>
-      <c r="AE49" s="129"/>
-      <c r="AF49" s="129"/>
-      <c r="AG49" s="145"/>
-      <c r="AH49" s="145"/>
-      <c r="AI49" s="145"/>
+      <c r="AC49" s="105"/>
+      <c r="AD49" s="105"/>
+      <c r="AE49" s="105"/>
+      <c r="AF49" s="105"/>
+      <c r="AG49" s="64"/>
+      <c r="AH49" s="64"/>
+      <c r="AI49" s="64"/>
       <c r="AJ49" s="33" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="50" spans="1:36" ht="18" customHeight="1">
       <c r="A50" s="10"/>
-      <c r="B50" s="126" t="s">
+      <c r="B50" s="60" t="s">
         <v>75</v>
       </c>
-      <c r="C50" s="126"/>
-      <c r="D50" s="126"/>
-      <c r="E50" s="126"/>
-      <c r="F50" s="126"/>
-      <c r="G50" s="126"/>
-      <c r="H50" s="126"/>
-      <c r="I50" s="127"/>
+      <c r="C50" s="60"/>
+      <c r="D50" s="60"/>
+      <c r="E50" s="60"/>
+      <c r="F50" s="60"/>
+      <c r="G50" s="60"/>
+      <c r="H50" s="60"/>
+      <c r="I50" s="61"/>
       <c r="J50" s="10"/>
-      <c r="K50" s="126" t="s">
+      <c r="K50" s="60" t="s">
         <v>39</v>
       </c>
-      <c r="L50" s="126"/>
-      <c r="M50" s="126"/>
-      <c r="N50" s="126"/>
-      <c r="O50" s="126"/>
-      <c r="P50" s="126"/>
-      <c r="Q50" s="126"/>
-      <c r="R50" s="127"/>
+      <c r="L50" s="60"/>
+      <c r="M50" s="60"/>
+      <c r="N50" s="60"/>
+      <c r="O50" s="60"/>
+      <c r="P50" s="60"/>
+      <c r="Q50" s="60"/>
+      <c r="R50" s="61"/>
       <c r="S50" s="10"/>
-      <c r="T50" s="126" t="s">
+      <c r="T50" s="60" t="s">
         <v>26</v>
       </c>
-      <c r="U50" s="126"/>
-      <c r="V50" s="126"/>
-      <c r="W50" s="126"/>
-      <c r="X50" s="126"/>
-      <c r="Y50" s="126"/>
-      <c r="Z50" s="126"/>
-      <c r="AA50" s="127"/>
-      <c r="AB50" s="132" t="s">
+      <c r="U50" s="60"/>
+      <c r="V50" s="60"/>
+      <c r="W50" s="60"/>
+      <c r="X50" s="60"/>
+      <c r="Y50" s="60"/>
+      <c r="Z50" s="60"/>
+      <c r="AA50" s="61"/>
+      <c r="AB50" s="107" t="s">
         <v>38</v>
       </c>
-      <c r="AC50" s="133"/>
-      <c r="AD50" s="133"/>
-      <c r="AE50" s="133"/>
-      <c r="AF50" s="133"/>
-      <c r="AG50" s="133"/>
-      <c r="AH50" s="133"/>
-      <c r="AI50" s="133"/>
-      <c r="AJ50" s="134"/>
+      <c r="AC50" s="108"/>
+      <c r="AD50" s="108"/>
+      <c r="AE50" s="108"/>
+      <c r="AF50" s="108"/>
+      <c r="AG50" s="108"/>
+      <c r="AH50" s="108"/>
+      <c r="AI50" s="108"/>
+      <c r="AJ50" s="109"/>
     </row>
     <row r="51" spans="1:36" ht="18" customHeight="1">
       <c r="A51" s="10"/>
-      <c r="B51" s="126" t="s">
+      <c r="B51" s="60" t="s">
         <v>40</v>
       </c>
-      <c r="C51" s="126"/>
-      <c r="D51" s="126"/>
-      <c r="E51" s="126"/>
-      <c r="F51" s="126"/>
-      <c r="G51" s="126"/>
-      <c r="H51" s="126"/>
-      <c r="I51" s="127"/>
+      <c r="C51" s="60"/>
+      <c r="D51" s="60"/>
+      <c r="E51" s="60"/>
+      <c r="F51" s="60"/>
+      <c r="G51" s="60"/>
+      <c r="H51" s="60"/>
+      <c r="I51" s="61"/>
       <c r="J51" s="10"/>
-      <c r="K51" s="126" t="s">
+      <c r="K51" s="60" t="s">
         <v>41</v>
       </c>
-      <c r="L51" s="126"/>
-      <c r="M51" s="126"/>
-      <c r="N51" s="126"/>
-      <c r="O51" s="126"/>
-      <c r="P51" s="126"/>
-      <c r="Q51" s="126"/>
-      <c r="R51" s="127"/>
+      <c r="L51" s="60"/>
+      <c r="M51" s="60"/>
+      <c r="N51" s="60"/>
+      <c r="O51" s="60"/>
+      <c r="P51" s="60"/>
+      <c r="Q51" s="60"/>
+      <c r="R51" s="61"/>
       <c r="S51" s="10"/>
-      <c r="T51" s="126" t="s">
+      <c r="T51" s="60" t="s">
         <v>29</v>
       </c>
-      <c r="U51" s="126"/>
-      <c r="V51" s="126"/>
-      <c r="W51" s="125"/>
-      <c r="X51" s="125"/>
-      <c r="Y51" s="125"/>
+      <c r="U51" s="60"/>
+      <c r="V51" s="60"/>
+      <c r="W51" s="96"/>
+      <c r="X51" s="96"/>
+      <c r="Y51" s="96"/>
       <c r="Z51" s="3" t="s">
         <v>30</v>
       </c>
       <c r="AA51" s="4"/>
       <c r="AB51" s="10"/>
-      <c r="AC51" s="135" t="s">
+      <c r="AC51" s="110" t="s">
         <v>76</v>
       </c>
-      <c r="AD51" s="135"/>
-      <c r="AE51" s="135"/>
-      <c r="AF51" s="135"/>
-      <c r="AG51" s="135"/>
-      <c r="AH51" s="135"/>
-      <c r="AI51" s="135"/>
-      <c r="AJ51" s="136"/>
+      <c r="AD51" s="110"/>
+      <c r="AE51" s="110"/>
+      <c r="AF51" s="110"/>
+      <c r="AG51" s="110"/>
+      <c r="AH51" s="110"/>
+      <c r="AI51" s="110"/>
+      <c r="AJ51" s="111"/>
     </row>
     <row r="52" spans="1:36" ht="18" customHeight="1">
       <c r="A52" s="10"/>
-      <c r="B52" s="126" t="s">
+      <c r="B52" s="60" t="s">
         <v>43</v>
       </c>
-      <c r="C52" s="126"/>
-      <c r="D52" s="137"/>
-      <c r="E52" s="137"/>
-      <c r="F52" s="137"/>
-      <c r="G52" s="137"/>
-      <c r="H52" s="137"/>
+      <c r="C52" s="60"/>
+      <c r="D52" s="112"/>
+      <c r="E52" s="112"/>
+      <c r="F52" s="112"/>
+      <c r="G52" s="112"/>
+      <c r="H52" s="112"/>
       <c r="I52" s="4"/>
       <c r="J52" s="10"/>
-      <c r="K52" s="126" t="s">
+      <c r="K52" s="60" t="s">
         <v>44</v>
       </c>
-      <c r="L52" s="126"/>
-      <c r="M52" s="126"/>
-      <c r="N52" s="126"/>
-      <c r="O52" s="126"/>
-      <c r="P52" s="126"/>
-      <c r="Q52" s="126"/>
-      <c r="R52" s="127"/>
+      <c r="L52" s="60"/>
+      <c r="M52" s="60"/>
+      <c r="N52" s="60"/>
+      <c r="O52" s="60"/>
+      <c r="P52" s="60"/>
+      <c r="Q52" s="60"/>
+      <c r="R52" s="61"/>
       <c r="S52" s="10"/>
-      <c r="T52" s="126" t="s">
+      <c r="T52" s="60" t="s">
         <v>32</v>
       </c>
-      <c r="U52" s="126"/>
-      <c r="V52" s="126"/>
-      <c r="W52" s="125"/>
-      <c r="X52" s="125"/>
-      <c r="Y52" s="125"/>
+      <c r="U52" s="60"/>
+      <c r="V52" s="60"/>
+      <c r="W52" s="96"/>
+      <c r="X52" s="96"/>
+      <c r="Y52" s="96"/>
       <c r="Z52" s="3" t="s">
         <v>30</v>
       </c>
       <c r="AA52" s="4"/>
       <c r="AB52" s="10"/>
-      <c r="AC52" s="126" t="s">
+      <c r="AC52" s="60" t="s">
         <v>42</v>
       </c>
-      <c r="AD52" s="126"/>
-      <c r="AE52" s="126"/>
-      <c r="AF52" s="126"/>
-      <c r="AG52" s="126"/>
-      <c r="AH52" s="126"/>
-      <c r="AI52" s="126"/>
-      <c r="AJ52" s="127"/>
+      <c r="AD52" s="60"/>
+      <c r="AE52" s="60"/>
+      <c r="AF52" s="60"/>
+      <c r="AG52" s="60"/>
+      <c r="AH52" s="60"/>
+      <c r="AI52" s="60"/>
+      <c r="AJ52" s="61"/>
     </row>
     <row r="53" spans="1:36" ht="18" customHeight="1">
       <c r="A53" s="13"/>
       <c r="B53" s="7"/>
       <c r="C53" s="7"/>
-      <c r="D53" s="148"/>
-      <c r="E53" s="148"/>
-      <c r="F53" s="148"/>
-      <c r="G53" s="148"/>
-      <c r="H53" s="148"/>
+      <c r="D53" s="101"/>
+      <c r="E53" s="101"/>
+      <c r="F53" s="101"/>
+      <c r="G53" s="101"/>
+      <c r="H53" s="101"/>
       <c r="I53" s="8"/>
-      <c r="J53" s="128"/>
-      <c r="K53" s="129"/>
-      <c r="L53" s="129"/>
-      <c r="M53" s="129"/>
-      <c r="N53" s="129"/>
-      <c r="O53" s="129"/>
-      <c r="P53" s="129"/>
-      <c r="Q53" s="129"/>
-      <c r="R53" s="130"/>
+      <c r="J53" s="104"/>
+      <c r="K53" s="105"/>
+      <c r="L53" s="105"/>
+      <c r="M53" s="105"/>
+      <c r="N53" s="105"/>
+      <c r="O53" s="105"/>
+      <c r="P53" s="105"/>
+      <c r="Q53" s="105"/>
+      <c r="R53" s="113"/>
       <c r="S53" s="13"/>
-      <c r="T53" s="144" t="s">
+      <c r="T53" s="97" t="s">
         <v>35</v>
       </c>
-      <c r="U53" s="144"/>
-      <c r="V53" s="144"/>
-      <c r="W53" s="145"/>
-      <c r="X53" s="145"/>
-      <c r="Y53" s="145"/>
+      <c r="U53" s="97"/>
+      <c r="V53" s="97"/>
+      <c r="W53" s="64"/>
+      <c r="X53" s="64"/>
+      <c r="Y53" s="64"/>
       <c r="Z53" s="6" t="s">
         <v>36</v>
       </c>
       <c r="AA53" s="8"/>
       <c r="AB53" s="13"/>
-      <c r="AC53" s="144" t="s">
+      <c r="AC53" s="97" t="s">
         <v>45</v>
       </c>
-      <c r="AD53" s="144"/>
-      <c r="AE53" s="144"/>
-      <c r="AF53" s="100"/>
-      <c r="AG53" s="100"/>
-      <c r="AH53" s="100"/>
+      <c r="AD53" s="97"/>
+      <c r="AE53" s="97"/>
+      <c r="AF53" s="106"/>
+      <c r="AG53" s="106"/>
+      <c r="AH53" s="106"/>
       <c r="AI53" s="7"/>
       <c r="AJ53" s="8"/>
     </row>
     <row r="54" spans="1:36" ht="18" customHeight="1">
-      <c r="A54" s="146" t="s">
+      <c r="A54" s="99" t="s">
         <v>46</v>
       </c>
-      <c r="B54" s="146"/>
-      <c r="C54" s="146"/>
-      <c r="D54" s="146"/>
-      <c r="E54" s="146"/>
-      <c r="F54" s="146"/>
-      <c r="G54" s="146"/>
-      <c r="H54" s="146"/>
-      <c r="I54" s="146"/>
-      <c r="J54" s="146"/>
-      <c r="K54" s="146"/>
-      <c r="L54" s="146"/>
-      <c r="M54" s="146"/>
-      <c r="N54" s="147"/>
-      <c r="O54" s="147"/>
-      <c r="P54" s="147"/>
-      <c r="Q54" s="147"/>
-      <c r="R54" s="147"/>
-      <c r="S54" s="147"/>
-      <c r="T54" s="147"/>
-      <c r="U54" s="147"/>
-      <c r="V54" s="147"/>
-      <c r="W54" s="147"/>
-      <c r="X54" s="147"/>
-      <c r="Y54" s="147"/>
-      <c r="Z54" s="147"/>
-      <c r="AA54" s="147"/>
-      <c r="AB54" s="147"/>
-      <c r="AC54" s="147"/>
-      <c r="AD54" s="147"/>
-      <c r="AE54" s="147"/>
-      <c r="AF54" s="147"/>
-      <c r="AG54" s="147"/>
-      <c r="AH54" s="147"/>
-      <c r="AI54" s="147"/>
-      <c r="AJ54" s="147"/>
+      <c r="B54" s="99"/>
+      <c r="C54" s="99"/>
+      <c r="D54" s="99"/>
+      <c r="E54" s="99"/>
+      <c r="F54" s="99"/>
+      <c r="G54" s="99"/>
+      <c r="H54" s="99"/>
+      <c r="I54" s="99"/>
+      <c r="J54" s="99"/>
+      <c r="K54" s="99"/>
+      <c r="L54" s="99"/>
+      <c r="M54" s="99"/>
+      <c r="N54" s="100"/>
+      <c r="O54" s="100"/>
+      <c r="P54" s="100"/>
+      <c r="Q54" s="100"/>
+      <c r="R54" s="100"/>
+      <c r="S54" s="100"/>
+      <c r="T54" s="100"/>
+      <c r="U54" s="100"/>
+      <c r="V54" s="100"/>
+      <c r="W54" s="100"/>
+      <c r="X54" s="100"/>
+      <c r="Y54" s="100"/>
+      <c r="Z54" s="100"/>
+      <c r="AA54" s="100"/>
+      <c r="AB54" s="100"/>
+      <c r="AC54" s="100"/>
+      <c r="AD54" s="100"/>
+      <c r="AE54" s="100"/>
+      <c r="AF54" s="100"/>
+      <c r="AG54" s="100"/>
+      <c r="AH54" s="100"/>
+      <c r="AI54" s="100"/>
+      <c r="AJ54" s="100"/>
     </row>
     <row r="55" spans="1:36" ht="18" customHeight="1">
-      <c r="A55" s="139"/>
-      <c r="B55" s="67"/>
-      <c r="C55" s="67"/>
-      <c r="D55" s="67"/>
-      <c r="E55" s="67"/>
-      <c r="F55" s="67"/>
-      <c r="G55" s="67"/>
-      <c r="H55" s="67"/>
-      <c r="I55" s="67"/>
-      <c r="J55" s="67"/>
-      <c r="K55" s="67"/>
-      <c r="L55" s="67"/>
-      <c r="N55" s="67"/>
-      <c r="O55" s="67"/>
-      <c r="P55" s="67"/>
-      <c r="Q55" s="67"/>
-      <c r="R55" s="67"/>
-      <c r="S55" s="67"/>
-      <c r="T55" s="67"/>
-      <c r="U55" s="67"/>
-      <c r="V55" s="67"/>
-      <c r="W55" s="67"/>
-      <c r="X55" s="67"/>
-      <c r="Y55" s="139"/>
-      <c r="Z55" s="139"/>
-      <c r="AA55" s="139"/>
-      <c r="AB55" s="149" t="s">
+      <c r="A55" s="90"/>
+      <c r="B55" s="98"/>
+      <c r="C55" s="98"/>
+      <c r="D55" s="98"/>
+      <c r="E55" s="98"/>
+      <c r="F55" s="98"/>
+      <c r="G55" s="98"/>
+      <c r="H55" s="98"/>
+      <c r="I55" s="98"/>
+      <c r="J55" s="98"/>
+      <c r="K55" s="98"/>
+      <c r="L55" s="98"/>
+      <c r="N55" s="98"/>
+      <c r="O55" s="98"/>
+      <c r="P55" s="98"/>
+      <c r="Q55" s="98"/>
+      <c r="R55" s="98"/>
+      <c r="S55" s="98"/>
+      <c r="T55" s="98"/>
+      <c r="U55" s="98"/>
+      <c r="V55" s="98"/>
+      <c r="W55" s="98"/>
+      <c r="X55" s="98"/>
+      <c r="Y55" s="90"/>
+      <c r="Z55" s="90"/>
+      <c r="AA55" s="90"/>
+      <c r="AB55" s="102" t="s">
         <v>93</v>
       </c>
-      <c r="AC55" s="99"/>
-      <c r="AD55" s="99"/>
-      <c r="AE55" s="99"/>
-      <c r="AF55" s="99"/>
-      <c r="AG55" s="99"/>
-      <c r="AH55" s="99"/>
-      <c r="AI55" s="99"/>
-      <c r="AJ55" s="99"/>
+      <c r="AC55" s="103"/>
+      <c r="AD55" s="103"/>
+      <c r="AE55" s="103"/>
+      <c r="AF55" s="103"/>
+      <c r="AG55" s="103"/>
+      <c r="AH55" s="103"/>
+      <c r="AI55" s="103"/>
+      <c r="AJ55" s="103"/>
     </row>
     <row r="56" spans="1:36" ht="18" customHeight="1">
-      <c r="A56" s="139"/>
-      <c r="B56" s="67"/>
-      <c r="C56" s="67"/>
-      <c r="D56" s="67"/>
-      <c r="E56" s="67"/>
-      <c r="F56" s="67"/>
-      <c r="G56" s="67"/>
-      <c r="H56" s="67"/>
-      <c r="I56" s="67"/>
-      <c r="J56" s="67"/>
-      <c r="K56" s="67"/>
-      <c r="L56" s="67"/>
-      <c r="N56" s="67"/>
-      <c r="O56" s="67"/>
-      <c r="P56" s="67"/>
-      <c r="Q56" s="67"/>
-      <c r="R56" s="67"/>
-      <c r="S56" s="67"/>
-      <c r="T56" s="67"/>
-      <c r="U56" s="67"/>
-      <c r="V56" s="67"/>
-      <c r="W56" s="67"/>
-      <c r="X56" s="67"/>
-      <c r="Y56" s="139"/>
-      <c r="Z56" s="139"/>
-      <c r="AA56" s="139"/>
-      <c r="AB56" s="140" t="s">
+      <c r="A56" s="90"/>
+      <c r="B56" s="98"/>
+      <c r="C56" s="98"/>
+      <c r="D56" s="98"/>
+      <c r="E56" s="98"/>
+      <c r="F56" s="98"/>
+      <c r="G56" s="98"/>
+      <c r="H56" s="98"/>
+      <c r="I56" s="98"/>
+      <c r="J56" s="98"/>
+      <c r="K56" s="98"/>
+      <c r="L56" s="98"/>
+      <c r="N56" s="98"/>
+      <c r="O56" s="98"/>
+      <c r="P56" s="98"/>
+      <c r="Q56" s="98"/>
+      <c r="R56" s="98"/>
+      <c r="S56" s="98"/>
+      <c r="T56" s="98"/>
+      <c r="U56" s="98"/>
+      <c r="V56" s="98"/>
+      <c r="W56" s="98"/>
+      <c r="X56" s="98"/>
+      <c r="Y56" s="90"/>
+      <c r="Z56" s="90"/>
+      <c r="AA56" s="90"/>
+      <c r="AB56" s="92" t="s">
         <v>47</v>
       </c>
-      <c r="AC56" s="140"/>
-      <c r="AD56" s="140"/>
-      <c r="AE56" s="140"/>
-      <c r="AF56" s="140"/>
-      <c r="AG56" s="140"/>
-      <c r="AH56" s="140"/>
-      <c r="AI56" s="140"/>
-      <c r="AJ56" s="140"/>
+      <c r="AC56" s="92"/>
+      <c r="AD56" s="92"/>
+      <c r="AE56" s="92"/>
+      <c r="AF56" s="92"/>
+      <c r="AG56" s="92"/>
+      <c r="AH56" s="92"/>
+      <c r="AI56" s="92"/>
+      <c r="AJ56" s="92"/>
     </row>
     <row r="57" spans="1:36" ht="18" customHeight="1">
-      <c r="A57" s="139"/>
-      <c r="B57" s="67"/>
-      <c r="C57" s="67"/>
-      <c r="D57" s="67"/>
-      <c r="E57" s="67"/>
-      <c r="F57" s="67"/>
-      <c r="G57" s="67"/>
-      <c r="H57" s="67"/>
-      <c r="I57" s="67"/>
-      <c r="J57" s="67"/>
-      <c r="K57" s="67"/>
-      <c r="L57" s="67"/>
-      <c r="N57" s="67"/>
-      <c r="O57" s="67"/>
-      <c r="P57" s="67"/>
-      <c r="Q57" s="67"/>
-      <c r="R57" s="67"/>
-      <c r="S57" s="67"/>
-      <c r="T57" s="67"/>
-      <c r="U57" s="67"/>
-      <c r="V57" s="67"/>
-      <c r="W57" s="67"/>
-      <c r="X57" s="67"/>
-      <c r="Y57" s="139"/>
-      <c r="Z57" s="139"/>
-      <c r="AA57" s="139"/>
-      <c r="AB57" s="139"/>
-      <c r="AC57" s="139"/>
-      <c r="AD57" s="139"/>
-      <c r="AE57" s="139"/>
-      <c r="AF57" s="139"/>
-      <c r="AG57" s="139"/>
-      <c r="AH57" s="139"/>
-      <c r="AI57" s="139"/>
-      <c r="AJ57" s="139"/>
+      <c r="A57" s="90"/>
+      <c r="B57" s="98"/>
+      <c r="C57" s="98"/>
+      <c r="D57" s="98"/>
+      <c r="E57" s="98"/>
+      <c r="F57" s="98"/>
+      <c r="G57" s="98"/>
+      <c r="H57" s="98"/>
+      <c r="I57" s="98"/>
+      <c r="J57" s="98"/>
+      <c r="K57" s="98"/>
+      <c r="L57" s="98"/>
+      <c r="N57" s="98"/>
+      <c r="O57" s="98"/>
+      <c r="P57" s="98"/>
+      <c r="Q57" s="98"/>
+      <c r="R57" s="98"/>
+      <c r="S57" s="98"/>
+      <c r="T57" s="98"/>
+      <c r="U57" s="98"/>
+      <c r="V57" s="98"/>
+      <c r="W57" s="98"/>
+      <c r="X57" s="98"/>
+      <c r="Y57" s="90"/>
+      <c r="Z57" s="90"/>
+      <c r="AA57" s="90"/>
+      <c r="AB57" s="90"/>
+      <c r="AC57" s="90"/>
+      <c r="AD57" s="90"/>
+      <c r="AE57" s="90"/>
+      <c r="AF57" s="90"/>
+      <c r="AG57" s="90"/>
+      <c r="AH57" s="90"/>
+      <c r="AI57" s="90"/>
+      <c r="AJ57" s="90"/>
     </row>
     <row r="58" spans="1:36" ht="18" customHeight="1">
       <c r="A58" s="51"/>
@@ -9367,72 +9372,72 @@
       <c r="V58" s="52"/>
       <c r="W58" s="52"/>
       <c r="X58" s="52"/>
-      <c r="Y58" s="139"/>
-      <c r="Z58" s="139"/>
-      <c r="AA58" s="139"/>
-      <c r="AB58" s="139"/>
-      <c r="AC58" s="139"/>
-      <c r="AD58" s="139"/>
-      <c r="AE58" s="139"/>
-      <c r="AF58" s="139"/>
-      <c r="AG58" s="139"/>
-      <c r="AH58" s="139"/>
-      <c r="AI58" s="139"/>
-      <c r="AJ58" s="139"/>
+      <c r="Y58" s="90"/>
+      <c r="Z58" s="90"/>
+      <c r="AA58" s="90"/>
+      <c r="AB58" s="90"/>
+      <c r="AC58" s="90"/>
+      <c r="AD58" s="90"/>
+      <c r="AE58" s="90"/>
+      <c r="AF58" s="90"/>
+      <c r="AG58" s="90"/>
+      <c r="AH58" s="90"/>
+      <c r="AI58" s="90"/>
+      <c r="AJ58" s="90"/>
     </row>
     <row r="59" spans="1:36" ht="18" customHeight="1">
-      <c r="A59" s="139"/>
-      <c r="B59" s="139"/>
-      <c r="C59" s="139"/>
-      <c r="D59" s="139"/>
-      <c r="E59" s="139"/>
-      <c r="F59" s="139"/>
-      <c r="G59" s="139"/>
-      <c r="H59" s="139"/>
-      <c r="I59" s="139"/>
-      <c r="J59" s="139"/>
-      <c r="K59" s="139"/>
-      <c r="L59" s="139"/>
-      <c r="M59" s="139"/>
-      <c r="N59" s="139"/>
-      <c r="O59" s="139"/>
-      <c r="P59" s="139"/>
-      <c r="Q59" s="139"/>
-      <c r="R59" s="139"/>
-      <c r="S59" s="139"/>
-      <c r="T59" s="139"/>
-      <c r="U59" s="139"/>
-      <c r="V59" s="139"/>
-      <c r="W59" s="139"/>
-      <c r="X59" s="139"/>
-      <c r="Y59" s="139"/>
-      <c r="Z59" s="139"/>
-      <c r="AA59" s="139"/>
-      <c r="AB59" s="82"/>
-      <c r="AC59" s="82"/>
-      <c r="AD59" s="82"/>
-      <c r="AE59" s="82"/>
-      <c r="AF59" s="82"/>
-      <c r="AG59" s="82"/>
-      <c r="AH59" s="82"/>
-      <c r="AI59" s="82"/>
-      <c r="AJ59" s="82"/>
+      <c r="A59" s="90"/>
+      <c r="B59" s="90"/>
+      <c r="C59" s="90"/>
+      <c r="D59" s="90"/>
+      <c r="E59" s="90"/>
+      <c r="F59" s="90"/>
+      <c r="G59" s="90"/>
+      <c r="H59" s="90"/>
+      <c r="I59" s="90"/>
+      <c r="J59" s="90"/>
+      <c r="K59" s="90"/>
+      <c r="L59" s="90"/>
+      <c r="M59" s="90"/>
+      <c r="N59" s="90"/>
+      <c r="O59" s="90"/>
+      <c r="P59" s="90"/>
+      <c r="Q59" s="90"/>
+      <c r="R59" s="90"/>
+      <c r="S59" s="90"/>
+      <c r="T59" s="90"/>
+      <c r="U59" s="90"/>
+      <c r="V59" s="90"/>
+      <c r="W59" s="90"/>
+      <c r="X59" s="90"/>
+      <c r="Y59" s="90"/>
+      <c r="Z59" s="90"/>
+      <c r="AA59" s="90"/>
+      <c r="AB59" s="91"/>
+      <c r="AC59" s="91"/>
+      <c r="AD59" s="91"/>
+      <c r="AE59" s="91"/>
+      <c r="AF59" s="91"/>
+      <c r="AG59" s="91"/>
+      <c r="AH59" s="91"/>
+      <c r="AI59" s="91"/>
+      <c r="AJ59" s="91"/>
     </row>
     <row r="60" spans="1:36" ht="18" customHeight="1">
-      <c r="Y60" s="139"/>
-      <c r="Z60" s="139"/>
-      <c r="AA60" s="139"/>
-      <c r="AB60" s="138" t="s">
+      <c r="Y60" s="90"/>
+      <c r="Z60" s="90"/>
+      <c r="AA60" s="90"/>
+      <c r="AB60" s="89" t="s">
         <v>92</v>
       </c>
-      <c r="AC60" s="138"/>
-      <c r="AD60" s="138"/>
-      <c r="AE60" s="138"/>
-      <c r="AF60" s="138"/>
-      <c r="AG60" s="138"/>
-      <c r="AH60" s="138"/>
-      <c r="AI60" s="138"/>
-      <c r="AJ60" s="138"/>
+      <c r="AC60" s="89"/>
+      <c r="AD60" s="89"/>
+      <c r="AE60" s="89"/>
+      <c r="AF60" s="89"/>
+      <c r="AG60" s="89"/>
+      <c r="AH60" s="89"/>
+      <c r="AI60" s="89"/>
+      <c r="AJ60" s="89"/>
     </row>
     <row r="61" spans="1:36" ht="16.5" customHeight="1"/>
     <row r="62" spans="1:36" ht="18" hidden="1" customHeight="1"/>
@@ -10034,6 +10039,108 @@
     <row r="658"/>
   </sheetData>
   <mergeCells count="126">
+    <mergeCell ref="S8:W8"/>
+    <mergeCell ref="X7:AB7"/>
+    <mergeCell ref="B57:L57"/>
+    <mergeCell ref="N57:X57"/>
+    <mergeCell ref="Q2:Z2"/>
+    <mergeCell ref="Q3:Z3"/>
+    <mergeCell ref="A11:P11"/>
+    <mergeCell ref="K5:O5"/>
+    <mergeCell ref="K6:O6"/>
+    <mergeCell ref="P6:X6"/>
+    <mergeCell ref="A41:R41"/>
+    <mergeCell ref="S9:W9"/>
+    <mergeCell ref="A7:B7"/>
+    <mergeCell ref="Q11:AJ11"/>
+    <mergeCell ref="C7:I7"/>
+    <mergeCell ref="D8:R8"/>
+    <mergeCell ref="A8:C8"/>
+    <mergeCell ref="X8:AJ8"/>
+    <mergeCell ref="A10:AJ10"/>
+    <mergeCell ref="A5:B5"/>
+    <mergeCell ref="A6:B6"/>
+    <mergeCell ref="D9:R9"/>
+    <mergeCell ref="K7:O7"/>
+    <mergeCell ref="A25:AJ25"/>
+    <mergeCell ref="AD3:AJ3"/>
+    <mergeCell ref="Y5:Z5"/>
+    <mergeCell ref="A22:AJ23"/>
+    <mergeCell ref="A17:T20"/>
+    <mergeCell ref="C5:I5"/>
+    <mergeCell ref="AF19:AG19"/>
+    <mergeCell ref="A43:I43"/>
+    <mergeCell ref="AI19:AJ19"/>
+    <mergeCell ref="A14:H14"/>
+    <mergeCell ref="I14:AJ14"/>
+    <mergeCell ref="AI17:AJ17"/>
+    <mergeCell ref="AF17:AG17"/>
+    <mergeCell ref="A15:AJ15"/>
+    <mergeCell ref="AF18:AG18"/>
+    <mergeCell ref="AA5:AJ5"/>
+    <mergeCell ref="V7:W7"/>
+    <mergeCell ref="AI18:AJ18"/>
+    <mergeCell ref="U16:AD16"/>
+    <mergeCell ref="AE16:AJ16"/>
+    <mergeCell ref="A16:T16"/>
+    <mergeCell ref="A9:C9"/>
+    <mergeCell ref="X9:AJ9"/>
+    <mergeCell ref="P7:T7"/>
+    <mergeCell ref="P5:X5"/>
+    <mergeCell ref="AI7:AJ7"/>
+    <mergeCell ref="C6:I6"/>
+    <mergeCell ref="AB46:AE46"/>
+    <mergeCell ref="S44:V44"/>
+    <mergeCell ref="S45:V45"/>
+    <mergeCell ref="S46:W46"/>
+    <mergeCell ref="X46:Z46"/>
+    <mergeCell ref="K46:R46"/>
+    <mergeCell ref="K45:R45"/>
+    <mergeCell ref="AB44:AE44"/>
+    <mergeCell ref="J53:R53"/>
+    <mergeCell ref="AB45:AE45"/>
+    <mergeCell ref="K44:R44"/>
+    <mergeCell ref="B48:I48"/>
+    <mergeCell ref="AF47:AI47"/>
+    <mergeCell ref="AB49:AF49"/>
+    <mergeCell ref="AF53:AH53"/>
+    <mergeCell ref="AB50:AJ50"/>
+    <mergeCell ref="AC51:AJ51"/>
+    <mergeCell ref="B49:I49"/>
+    <mergeCell ref="B52:C52"/>
+    <mergeCell ref="D52:H52"/>
+    <mergeCell ref="K50:R50"/>
+    <mergeCell ref="K51:R51"/>
+    <mergeCell ref="S47:W47"/>
+    <mergeCell ref="T49:AA49"/>
+    <mergeCell ref="K48:R48"/>
+    <mergeCell ref="K49:R49"/>
+    <mergeCell ref="W52:Y52"/>
+    <mergeCell ref="K47:R47"/>
+    <mergeCell ref="AB60:AJ60"/>
+    <mergeCell ref="AB57:AJ59"/>
+    <mergeCell ref="AB56:AJ56"/>
+    <mergeCell ref="S48:AA48"/>
+    <mergeCell ref="AG48:AI48"/>
+    <mergeCell ref="AC53:AE53"/>
+    <mergeCell ref="T52:V52"/>
+    <mergeCell ref="W53:Y53"/>
+    <mergeCell ref="B56:L56"/>
+    <mergeCell ref="N56:X56"/>
+    <mergeCell ref="Y55:AA60"/>
+    <mergeCell ref="A59:X59"/>
+    <mergeCell ref="A55:A57"/>
+    <mergeCell ref="N55:X55"/>
+    <mergeCell ref="A54:M54"/>
+    <mergeCell ref="N54:AJ54"/>
+    <mergeCell ref="D53:H53"/>
+    <mergeCell ref="B50:I50"/>
+    <mergeCell ref="B55:L55"/>
+    <mergeCell ref="K52:R52"/>
+    <mergeCell ref="T53:V53"/>
+    <mergeCell ref="AB55:AJ55"/>
+    <mergeCell ref="W51:Y51"/>
+    <mergeCell ref="AC52:AJ52"/>
     <mergeCell ref="AF46:AI46"/>
     <mergeCell ref="T50:AA50"/>
     <mergeCell ref="AF45:AI45"/>
@@ -10058,108 +10165,6 @@
     <mergeCell ref="B45:I45"/>
     <mergeCell ref="AB47:AE47"/>
     <mergeCell ref="B46:I46"/>
-    <mergeCell ref="AB60:AJ60"/>
-    <mergeCell ref="AB57:AJ59"/>
-    <mergeCell ref="AB56:AJ56"/>
-    <mergeCell ref="S48:AA48"/>
-    <mergeCell ref="AG48:AI48"/>
-    <mergeCell ref="AC53:AE53"/>
-    <mergeCell ref="T52:V52"/>
-    <mergeCell ref="W53:Y53"/>
-    <mergeCell ref="B56:L56"/>
-    <mergeCell ref="N56:X56"/>
-    <mergeCell ref="Y55:AA60"/>
-    <mergeCell ref="A59:X59"/>
-    <mergeCell ref="A55:A57"/>
-    <mergeCell ref="N55:X55"/>
-    <mergeCell ref="A54:M54"/>
-    <mergeCell ref="N54:AJ54"/>
-    <mergeCell ref="D53:H53"/>
-    <mergeCell ref="B50:I50"/>
-    <mergeCell ref="B55:L55"/>
-    <mergeCell ref="K52:R52"/>
-    <mergeCell ref="T53:V53"/>
-    <mergeCell ref="AB55:AJ55"/>
-    <mergeCell ref="W51:Y51"/>
-    <mergeCell ref="AC52:AJ52"/>
-    <mergeCell ref="B48:I48"/>
-    <mergeCell ref="AF47:AI47"/>
-    <mergeCell ref="AB49:AF49"/>
-    <mergeCell ref="AF53:AH53"/>
-    <mergeCell ref="AB50:AJ50"/>
-    <mergeCell ref="AC51:AJ51"/>
-    <mergeCell ref="B49:I49"/>
-    <mergeCell ref="B52:C52"/>
-    <mergeCell ref="D52:H52"/>
-    <mergeCell ref="K50:R50"/>
-    <mergeCell ref="K51:R51"/>
-    <mergeCell ref="S47:W47"/>
-    <mergeCell ref="T49:AA49"/>
-    <mergeCell ref="K48:R48"/>
-    <mergeCell ref="K49:R49"/>
-    <mergeCell ref="W52:Y52"/>
-    <mergeCell ref="K47:R47"/>
-    <mergeCell ref="AB46:AE46"/>
-    <mergeCell ref="S44:V44"/>
-    <mergeCell ref="S45:V45"/>
-    <mergeCell ref="S46:W46"/>
-    <mergeCell ref="X46:Z46"/>
-    <mergeCell ref="K46:R46"/>
-    <mergeCell ref="K45:R45"/>
-    <mergeCell ref="AB44:AE44"/>
-    <mergeCell ref="J53:R53"/>
-    <mergeCell ref="AB45:AE45"/>
-    <mergeCell ref="K44:R44"/>
-    <mergeCell ref="A22:AJ23"/>
-    <mergeCell ref="A17:T20"/>
-    <mergeCell ref="C5:I5"/>
-    <mergeCell ref="AF19:AG19"/>
-    <mergeCell ref="A43:I43"/>
-    <mergeCell ref="AI19:AJ19"/>
-    <mergeCell ref="A14:H14"/>
-    <mergeCell ref="I14:AJ14"/>
-    <mergeCell ref="AI17:AJ17"/>
-    <mergeCell ref="AF17:AG17"/>
-    <mergeCell ref="A15:AJ15"/>
-    <mergeCell ref="AF18:AG18"/>
-    <mergeCell ref="AA5:AJ5"/>
-    <mergeCell ref="V7:W7"/>
-    <mergeCell ref="AI18:AJ18"/>
-    <mergeCell ref="U16:AD16"/>
-    <mergeCell ref="AE16:AJ16"/>
-    <mergeCell ref="A16:T16"/>
-    <mergeCell ref="A9:C9"/>
-    <mergeCell ref="X9:AJ9"/>
-    <mergeCell ref="P7:T7"/>
-    <mergeCell ref="B57:L57"/>
-    <mergeCell ref="N57:X57"/>
-    <mergeCell ref="Q2:Z2"/>
-    <mergeCell ref="Q3:Z3"/>
-    <mergeCell ref="A11:P11"/>
-    <mergeCell ref="K5:O5"/>
-    <mergeCell ref="K6:O6"/>
-    <mergeCell ref="P6:X6"/>
-    <mergeCell ref="A41:R41"/>
-    <mergeCell ref="S9:W9"/>
-    <mergeCell ref="A7:B7"/>
-    <mergeCell ref="Q11:AJ11"/>
-    <mergeCell ref="C7:I7"/>
-    <mergeCell ref="D8:R8"/>
-    <mergeCell ref="A8:C8"/>
-    <mergeCell ref="X8:AJ8"/>
-    <mergeCell ref="A10:AJ10"/>
-    <mergeCell ref="A5:B5"/>
-    <mergeCell ref="A6:B6"/>
-    <mergeCell ref="D9:R9"/>
-    <mergeCell ref="K7:O7"/>
-    <mergeCell ref="A25:AJ25"/>
-    <mergeCell ref="AD3:AJ3"/>
-    <mergeCell ref="Y5:Z5"/>
-    <mergeCell ref="P5:X5"/>
-    <mergeCell ref="AI7:AJ7"/>
-    <mergeCell ref="C6:I6"/>
-    <mergeCell ref="S8:W8"/>
-    <mergeCell ref="X7:AB7"/>
   </mergeCells>
   <phoneticPr fontId="0" type="noConversion"/>
   <printOptions horizontalCentered="1"/>
@@ -10184,7 +10189,7 @@
                   </from>
                   <to>
                     <xdr:col>1</xdr:col>
-                    <xdr:colOff>91440</xdr:colOff>
+                    <xdr:colOff>45720</xdr:colOff>
                     <xdr:row>12</xdr:row>
                     <xdr:rowOff>15240</xdr:rowOff>
                   </to>
@@ -10206,7 +10211,7 @@
                   </from>
                   <to>
                     <xdr:col>1</xdr:col>
-                    <xdr:colOff>91440</xdr:colOff>
+                    <xdr:colOff>45720</xdr:colOff>
                     <xdr:row>13</xdr:row>
                     <xdr:rowOff>15240</xdr:rowOff>
                   </to>
@@ -10734,7 +10739,7 @@
                   </from>
                   <to>
                     <xdr:col>1</xdr:col>
-                    <xdr:colOff>129540</xdr:colOff>
+                    <xdr:colOff>83820</xdr:colOff>
                     <xdr:row>44</xdr:row>
                     <xdr:rowOff>15240</xdr:rowOff>
                   </to>
@@ -10756,7 +10761,7 @@
                   </from>
                   <to>
                     <xdr:col>1</xdr:col>
-                    <xdr:colOff>129540</xdr:colOff>
+                    <xdr:colOff>83820</xdr:colOff>
                     <xdr:row>45</xdr:row>
                     <xdr:rowOff>15240</xdr:rowOff>
                   </to>
@@ -10778,7 +10783,7 @@
                   </from>
                   <to>
                     <xdr:col>1</xdr:col>
-                    <xdr:colOff>129540</xdr:colOff>
+                    <xdr:colOff>83820</xdr:colOff>
                     <xdr:row>46</xdr:row>
                     <xdr:rowOff>15240</xdr:rowOff>
                   </to>
@@ -10800,7 +10805,7 @@
                   </from>
                   <to>
                     <xdr:col>1</xdr:col>
-                    <xdr:colOff>129540</xdr:colOff>
+                    <xdr:colOff>83820</xdr:colOff>
                     <xdr:row>47</xdr:row>
                     <xdr:rowOff>15240</xdr:rowOff>
                   </to>
@@ -10822,7 +10827,7 @@
                   </from>
                   <to>
                     <xdr:col>1</xdr:col>
-                    <xdr:colOff>129540</xdr:colOff>
+                    <xdr:colOff>83820</xdr:colOff>
                     <xdr:row>48</xdr:row>
                     <xdr:rowOff>15240</xdr:rowOff>
                   </to>
@@ -10844,7 +10849,7 @@
                   </from>
                   <to>
                     <xdr:col>1</xdr:col>
-                    <xdr:colOff>129540</xdr:colOff>
+                    <xdr:colOff>83820</xdr:colOff>
                     <xdr:row>49</xdr:row>
                     <xdr:rowOff>15240</xdr:rowOff>
                   </to>
@@ -10866,7 +10871,7 @@
                   </from>
                   <to>
                     <xdr:col>1</xdr:col>
-                    <xdr:colOff>129540</xdr:colOff>
+                    <xdr:colOff>83820</xdr:colOff>
                     <xdr:row>50</xdr:row>
                     <xdr:rowOff>15240</xdr:rowOff>
                   </to>
@@ -10888,7 +10893,7 @@
                   </from>
                   <to>
                     <xdr:col>1</xdr:col>
-                    <xdr:colOff>129540</xdr:colOff>
+                    <xdr:colOff>83820</xdr:colOff>
                     <xdr:row>51</xdr:row>
                     <xdr:rowOff>15240</xdr:rowOff>
                   </to>
@@ -10910,7 +10915,7 @@
                   </from>
                   <to>
                     <xdr:col>1</xdr:col>
-                    <xdr:colOff>129540</xdr:colOff>
+                    <xdr:colOff>83820</xdr:colOff>
                     <xdr:row>52</xdr:row>
                     <xdr:rowOff>15240</xdr:rowOff>
                   </to>

--- a/backend_api/templates/container_report_template.xlsx
+++ b/backend_api/templates/container_report_template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Aaron Avila\Documents\ERP-SOM\backend_api\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6D9E4B4F-214D-4123-9BE6-96191302A10F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CAF798A8-DA6F-4DD5-B264-F1CD97FB3CC6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-1125" windowWidth="29040" windowHeight="15720" xr2:uid="{253FFB1B-D348-46B1-A532-0D44566D2FFD}"/>
   </bookViews>
@@ -1411,7 +1411,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="169">
+  <cellXfs count="176">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -1555,26 +1555,324 @@
     <xf numFmtId="165" fontId="13" fillId="0" borderId="8" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyProtection="1">
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="14" fontId="13" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="8" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="9" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="6" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="2" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="3" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="4" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="5" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="3" fontId="13" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="13" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="9" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="6" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="6" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="6" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="165" fontId="13" fillId="0" borderId="8" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="2" borderId="9" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="2" borderId="6" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="2" borderId="7" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="165" fontId="13" fillId="0" borderId="8" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="4" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="4" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="4" fontId="13" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
     <xf numFmtId="4" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="4" fontId="13" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right"/>
-      <protection locked="0"/>
-    </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
       <protection locked="0"/>
@@ -1603,25 +1901,6 @@
       <alignment horizontal="left" vertical="top" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="9" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="6" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
@@ -1655,286 +1934,16 @@
       <alignment horizontal="left" vertical="top" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="4" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="3" fontId="13" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="2" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="3" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="4" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="5" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="3" fontId="13" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="9" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="6" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="6" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="6" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="165" fontId="13" fillId="0" borderId="8" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="2" borderId="9" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="2" borderId="6" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="2" borderId="7" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="4" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="8" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="165" fontId="13" fillId="0" borderId="8" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="14" fontId="13" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left"/>
       <protection locked="0"/>
     </xf>
   </cellXfs>
@@ -2239,7 +2248,7 @@
           <xdr:col>1</xdr:col>
           <xdr:colOff>53340</xdr:colOff>
           <xdr:row>12</xdr:row>
-          <xdr:rowOff>15240</xdr:rowOff>
+          <xdr:rowOff>19050</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -2306,7 +2315,7 @@
           <xdr:col>1</xdr:col>
           <xdr:colOff>53340</xdr:colOff>
           <xdr:row>13</xdr:row>
-          <xdr:rowOff>15240</xdr:rowOff>
+          <xdr:rowOff>19050</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -2371,9 +2380,9 @@
         </xdr:from>
         <xdr:to>
           <xdr:col>5</xdr:col>
-          <xdr:colOff>57150</xdr:colOff>
+          <xdr:colOff>53340</xdr:colOff>
           <xdr:row>12</xdr:row>
-          <xdr:rowOff>15240</xdr:rowOff>
+          <xdr:rowOff>19050</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -2438,9 +2447,9 @@
         </xdr:from>
         <xdr:to>
           <xdr:col>5</xdr:col>
-          <xdr:colOff>57150</xdr:colOff>
+          <xdr:colOff>53340</xdr:colOff>
           <xdr:row>13</xdr:row>
-          <xdr:rowOff>15240</xdr:rowOff>
+          <xdr:rowOff>19050</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -2507,7 +2516,7 @@
           <xdr:col>9</xdr:col>
           <xdr:colOff>114300</xdr:colOff>
           <xdr:row>12</xdr:row>
-          <xdr:rowOff>15240</xdr:rowOff>
+          <xdr:rowOff>19050</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -2574,7 +2583,7 @@
           <xdr:col>9</xdr:col>
           <xdr:colOff>114300</xdr:colOff>
           <xdr:row>13</xdr:row>
-          <xdr:rowOff>15240</xdr:rowOff>
+          <xdr:rowOff>19050</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -2639,9 +2648,9 @@
         </xdr:from>
         <xdr:to>
           <xdr:col>14</xdr:col>
-          <xdr:colOff>53340</xdr:colOff>
+          <xdr:colOff>57150</xdr:colOff>
           <xdr:row>12</xdr:row>
-          <xdr:rowOff>15240</xdr:rowOff>
+          <xdr:rowOff>19050</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -2706,9 +2715,9 @@
         </xdr:from>
         <xdr:to>
           <xdr:col>14</xdr:col>
-          <xdr:colOff>53340</xdr:colOff>
+          <xdr:colOff>57150</xdr:colOff>
           <xdr:row>13</xdr:row>
-          <xdr:rowOff>15240</xdr:rowOff>
+          <xdr:rowOff>19050</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -2773,9 +2782,9 @@
         </xdr:from>
         <xdr:to>
           <xdr:col>17</xdr:col>
-          <xdr:colOff>53340</xdr:colOff>
+          <xdr:colOff>57150</xdr:colOff>
           <xdr:row>12</xdr:row>
-          <xdr:rowOff>15240</xdr:rowOff>
+          <xdr:rowOff>19050</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -2840,9 +2849,9 @@
         </xdr:from>
         <xdr:to>
           <xdr:col>17</xdr:col>
-          <xdr:colOff>53340</xdr:colOff>
+          <xdr:colOff>57150</xdr:colOff>
           <xdr:row>13</xdr:row>
-          <xdr:rowOff>15240</xdr:rowOff>
+          <xdr:rowOff>19050</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -2907,9 +2916,9 @@
         </xdr:from>
         <xdr:to>
           <xdr:col>23</xdr:col>
-          <xdr:colOff>53340</xdr:colOff>
+          <xdr:colOff>57150</xdr:colOff>
           <xdr:row>12</xdr:row>
-          <xdr:rowOff>15240</xdr:rowOff>
+          <xdr:rowOff>19050</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -2974,9 +2983,9 @@
         </xdr:from>
         <xdr:to>
           <xdr:col>23</xdr:col>
-          <xdr:colOff>53340</xdr:colOff>
+          <xdr:colOff>57150</xdr:colOff>
           <xdr:row>13</xdr:row>
-          <xdr:rowOff>15240</xdr:rowOff>
+          <xdr:rowOff>19050</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -3041,9 +3050,9 @@
         </xdr:from>
         <xdr:to>
           <xdr:col>28</xdr:col>
-          <xdr:colOff>53340</xdr:colOff>
+          <xdr:colOff>57150</xdr:colOff>
           <xdr:row>12</xdr:row>
-          <xdr:rowOff>15240</xdr:rowOff>
+          <xdr:rowOff>19050</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -3108,9 +3117,9 @@
         </xdr:from>
         <xdr:to>
           <xdr:col>28</xdr:col>
-          <xdr:colOff>53340</xdr:colOff>
+          <xdr:colOff>57150</xdr:colOff>
           <xdr:row>13</xdr:row>
-          <xdr:rowOff>15240</xdr:rowOff>
+          <xdr:rowOff>19050</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -3177,7 +3186,7 @@
           <xdr:col>32</xdr:col>
           <xdr:colOff>342900</xdr:colOff>
           <xdr:row>12</xdr:row>
-          <xdr:rowOff>15240</xdr:rowOff>
+          <xdr:rowOff>19050</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -3244,7 +3253,7 @@
           <xdr:col>32</xdr:col>
           <xdr:colOff>342900</xdr:colOff>
           <xdr:row>13</xdr:row>
-          <xdr:rowOff>15240</xdr:rowOff>
+          <xdr:rowOff>19050</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -3309,9 +3318,9 @@
         </xdr:from>
         <xdr:to>
           <xdr:col>21</xdr:col>
-          <xdr:colOff>91440</xdr:colOff>
+          <xdr:colOff>95250</xdr:colOff>
           <xdr:row>17</xdr:row>
-          <xdr:rowOff>15240</xdr:rowOff>
+          <xdr:rowOff>19050</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -3376,9 +3385,9 @@
         </xdr:from>
         <xdr:to>
           <xdr:col>21</xdr:col>
-          <xdr:colOff>91440</xdr:colOff>
+          <xdr:colOff>95250</xdr:colOff>
           <xdr:row>18</xdr:row>
-          <xdr:rowOff>15240</xdr:rowOff>
+          <xdr:rowOff>19050</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -3443,9 +3452,9 @@
         </xdr:from>
         <xdr:to>
           <xdr:col>21</xdr:col>
-          <xdr:colOff>91440</xdr:colOff>
+          <xdr:colOff>95250</xdr:colOff>
           <xdr:row>19</xdr:row>
-          <xdr:rowOff>15240</xdr:rowOff>
+          <xdr:rowOff>19050</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -3510,9 +3519,9 @@
         </xdr:from>
         <xdr:to>
           <xdr:col>25</xdr:col>
-          <xdr:colOff>91440</xdr:colOff>
+          <xdr:colOff>95250</xdr:colOff>
           <xdr:row>17</xdr:row>
-          <xdr:rowOff>15240</xdr:rowOff>
+          <xdr:rowOff>19050</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -3577,9 +3586,9 @@
         </xdr:from>
         <xdr:to>
           <xdr:col>25</xdr:col>
-          <xdr:colOff>91440</xdr:colOff>
+          <xdr:colOff>95250</xdr:colOff>
           <xdr:row>18</xdr:row>
-          <xdr:rowOff>15240</xdr:rowOff>
+          <xdr:rowOff>19050</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -3644,9 +3653,9 @@
         </xdr:from>
         <xdr:to>
           <xdr:col>25</xdr:col>
-          <xdr:colOff>91440</xdr:colOff>
+          <xdr:colOff>95250</xdr:colOff>
           <xdr:row>19</xdr:row>
-          <xdr:rowOff>15240</xdr:rowOff>
+          <xdr:rowOff>19050</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -3711,9 +3720,9 @@
         </xdr:from>
         <xdr:to>
           <xdr:col>28</xdr:col>
-          <xdr:colOff>91440</xdr:colOff>
+          <xdr:colOff>95250</xdr:colOff>
           <xdr:row>17</xdr:row>
-          <xdr:rowOff>15240</xdr:rowOff>
+          <xdr:rowOff>19050</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -3778,9 +3787,9 @@
         </xdr:from>
         <xdr:to>
           <xdr:col>28</xdr:col>
-          <xdr:colOff>91440</xdr:colOff>
+          <xdr:colOff>95250</xdr:colOff>
           <xdr:row>18</xdr:row>
-          <xdr:rowOff>15240</xdr:rowOff>
+          <xdr:rowOff>19050</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -3845,9 +3854,9 @@
         </xdr:from>
         <xdr:to>
           <xdr:col>28</xdr:col>
-          <xdr:colOff>91440</xdr:colOff>
+          <xdr:colOff>95250</xdr:colOff>
           <xdr:row>19</xdr:row>
-          <xdr:rowOff>15240</xdr:rowOff>
+          <xdr:rowOff>19050</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -3914,7 +3923,7 @@
           <xdr:col>1</xdr:col>
           <xdr:colOff>91440</xdr:colOff>
           <xdr:row>44</xdr:row>
-          <xdr:rowOff>15240</xdr:rowOff>
+          <xdr:rowOff>19050</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -3981,7 +3990,7 @@
           <xdr:col>1</xdr:col>
           <xdr:colOff>91440</xdr:colOff>
           <xdr:row>45</xdr:row>
-          <xdr:rowOff>15240</xdr:rowOff>
+          <xdr:rowOff>19050</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -4048,7 +4057,7 @@
           <xdr:col>1</xdr:col>
           <xdr:colOff>91440</xdr:colOff>
           <xdr:row>46</xdr:row>
-          <xdr:rowOff>15240</xdr:rowOff>
+          <xdr:rowOff>19050</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -4115,7 +4124,7 @@
           <xdr:col>1</xdr:col>
           <xdr:colOff>91440</xdr:colOff>
           <xdr:row>47</xdr:row>
-          <xdr:rowOff>15240</xdr:rowOff>
+          <xdr:rowOff>19050</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -4182,7 +4191,7 @@
           <xdr:col>1</xdr:col>
           <xdr:colOff>91440</xdr:colOff>
           <xdr:row>48</xdr:row>
-          <xdr:rowOff>15240</xdr:rowOff>
+          <xdr:rowOff>19050</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -4249,7 +4258,7 @@
           <xdr:col>1</xdr:col>
           <xdr:colOff>91440</xdr:colOff>
           <xdr:row>49</xdr:row>
-          <xdr:rowOff>15240</xdr:rowOff>
+          <xdr:rowOff>19050</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -4316,7 +4325,7 @@
           <xdr:col>1</xdr:col>
           <xdr:colOff>91440</xdr:colOff>
           <xdr:row>50</xdr:row>
-          <xdr:rowOff>15240</xdr:rowOff>
+          <xdr:rowOff>19050</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -4383,7 +4392,7 @@
           <xdr:col>1</xdr:col>
           <xdr:colOff>91440</xdr:colOff>
           <xdr:row>51</xdr:row>
-          <xdr:rowOff>15240</xdr:rowOff>
+          <xdr:rowOff>19050</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -4450,7 +4459,7 @@
           <xdr:col>1</xdr:col>
           <xdr:colOff>91440</xdr:colOff>
           <xdr:row>52</xdr:row>
-          <xdr:rowOff>15240</xdr:rowOff>
+          <xdr:rowOff>19050</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -4515,9 +4524,9 @@
         </xdr:from>
         <xdr:to>
           <xdr:col>10</xdr:col>
-          <xdr:colOff>171450</xdr:colOff>
+          <xdr:colOff>167640</xdr:colOff>
           <xdr:row>44</xdr:row>
-          <xdr:rowOff>15240</xdr:rowOff>
+          <xdr:rowOff>19050</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -4582,9 +4591,9 @@
         </xdr:from>
         <xdr:to>
           <xdr:col>10</xdr:col>
-          <xdr:colOff>171450</xdr:colOff>
+          <xdr:colOff>167640</xdr:colOff>
           <xdr:row>45</xdr:row>
-          <xdr:rowOff>15240</xdr:rowOff>
+          <xdr:rowOff>19050</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -4649,9 +4658,9 @@
         </xdr:from>
         <xdr:to>
           <xdr:col>10</xdr:col>
-          <xdr:colOff>171450</xdr:colOff>
+          <xdr:colOff>167640</xdr:colOff>
           <xdr:row>46</xdr:row>
-          <xdr:rowOff>15240</xdr:rowOff>
+          <xdr:rowOff>19050</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -4716,9 +4725,9 @@
         </xdr:from>
         <xdr:to>
           <xdr:col>10</xdr:col>
-          <xdr:colOff>171450</xdr:colOff>
+          <xdr:colOff>167640</xdr:colOff>
           <xdr:row>47</xdr:row>
-          <xdr:rowOff>15240</xdr:rowOff>
+          <xdr:rowOff>19050</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -4783,9 +4792,9 @@
         </xdr:from>
         <xdr:to>
           <xdr:col>10</xdr:col>
-          <xdr:colOff>171450</xdr:colOff>
+          <xdr:colOff>167640</xdr:colOff>
           <xdr:row>48</xdr:row>
-          <xdr:rowOff>15240</xdr:rowOff>
+          <xdr:rowOff>19050</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -4850,9 +4859,9 @@
         </xdr:from>
         <xdr:to>
           <xdr:col>10</xdr:col>
-          <xdr:colOff>171450</xdr:colOff>
+          <xdr:colOff>167640</xdr:colOff>
           <xdr:row>49</xdr:row>
-          <xdr:rowOff>15240</xdr:rowOff>
+          <xdr:rowOff>19050</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -4917,9 +4926,9 @@
         </xdr:from>
         <xdr:to>
           <xdr:col>10</xdr:col>
-          <xdr:colOff>171450</xdr:colOff>
+          <xdr:colOff>167640</xdr:colOff>
           <xdr:row>50</xdr:row>
-          <xdr:rowOff>15240</xdr:rowOff>
+          <xdr:rowOff>19050</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -4984,9 +4993,9 @@
         </xdr:from>
         <xdr:to>
           <xdr:col>10</xdr:col>
-          <xdr:colOff>171450</xdr:colOff>
+          <xdr:colOff>167640</xdr:colOff>
           <xdr:row>51</xdr:row>
-          <xdr:rowOff>15240</xdr:rowOff>
+          <xdr:rowOff>19050</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -5051,9 +5060,9 @@
         </xdr:from>
         <xdr:to>
           <xdr:col>10</xdr:col>
-          <xdr:colOff>171450</xdr:colOff>
+          <xdr:colOff>167640</xdr:colOff>
           <xdr:row>52</xdr:row>
-          <xdr:rowOff>15240</xdr:rowOff>
+          <xdr:rowOff>19050</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -5118,9 +5127,9 @@
         </xdr:from>
         <xdr:to>
           <xdr:col>19</xdr:col>
-          <xdr:colOff>91440</xdr:colOff>
+          <xdr:colOff>95250</xdr:colOff>
           <xdr:row>49</xdr:row>
-          <xdr:rowOff>15240</xdr:rowOff>
+          <xdr:rowOff>19050</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -5185,9 +5194,9 @@
         </xdr:from>
         <xdr:to>
           <xdr:col>19</xdr:col>
-          <xdr:colOff>91440</xdr:colOff>
+          <xdr:colOff>95250</xdr:colOff>
           <xdr:row>50</xdr:row>
-          <xdr:rowOff>15240</xdr:rowOff>
+          <xdr:rowOff>19050</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -5252,9 +5261,9 @@
         </xdr:from>
         <xdr:to>
           <xdr:col>28</xdr:col>
-          <xdr:colOff>91440</xdr:colOff>
+          <xdr:colOff>95250</xdr:colOff>
           <xdr:row>51</xdr:row>
-          <xdr:rowOff>15240</xdr:rowOff>
+          <xdr:rowOff>19050</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -5319,9 +5328,9 @@
         </xdr:from>
         <xdr:to>
           <xdr:col>28</xdr:col>
-          <xdr:colOff>91440</xdr:colOff>
+          <xdr:colOff>95250</xdr:colOff>
           <xdr:row>52</xdr:row>
-          <xdr:rowOff>15240</xdr:rowOff>
+          <xdr:rowOff>19050</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -5386,9 +5395,9 @@
         </xdr:from>
         <xdr:to>
           <xdr:col>28</xdr:col>
-          <xdr:colOff>91440</xdr:colOff>
+          <xdr:colOff>95250</xdr:colOff>
           <xdr:row>53</xdr:row>
-          <xdr:rowOff>15240</xdr:rowOff>
+          <xdr:rowOff>19050</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -6371,9 +6380,9 @@
         </xdr:from>
         <xdr:to>
           <xdr:col>28</xdr:col>
-          <xdr:colOff>91440</xdr:colOff>
+          <xdr:colOff>95250</xdr:colOff>
           <xdr:row>53</xdr:row>
-          <xdr:rowOff>15240</xdr:rowOff>
+          <xdr:rowOff>19050</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -7052,16 +7061,16 @@
       <c r="N2" s="31"/>
       <c r="O2" s="38"/>
       <c r="P2" s="38"/>
-      <c r="Q2" s="147"/>
-      <c r="R2" s="147"/>
-      <c r="S2" s="147"/>
-      <c r="T2" s="147"/>
-      <c r="U2" s="147"/>
-      <c r="V2" s="147"/>
-      <c r="W2" s="147"/>
-      <c r="X2" s="147"/>
-      <c r="Y2" s="147"/>
-      <c r="Z2" s="147"/>
+      <c r="Q2" s="62"/>
+      <c r="R2" s="62"/>
+      <c r="S2" s="62"/>
+      <c r="T2" s="62"/>
+      <c r="U2" s="62"/>
+      <c r="V2" s="62"/>
+      <c r="W2" s="62"/>
+      <c r="X2" s="62"/>
+      <c r="Y2" s="62"/>
+      <c r="Z2" s="62"/>
       <c r="AA2" s="38"/>
       <c r="AB2" s="38"/>
       <c r="AC2" s="38"/>
@@ -7087,28 +7096,28 @@
       <c r="K3" s="1"/>
       <c r="M3" s="31"/>
       <c r="N3" s="31"/>
-      <c r="Q3" s="148"/>
-      <c r="R3" s="148"/>
-      <c r="S3" s="148"/>
-      <c r="T3" s="148"/>
-      <c r="U3" s="148"/>
-      <c r="V3" s="148"/>
-      <c r="W3" s="148"/>
-      <c r="X3" s="148"/>
-      <c r="Y3" s="148"/>
-      <c r="Z3" s="148"/>
+      <c r="Q3" s="63"/>
+      <c r="R3" s="63"/>
+      <c r="S3" s="63"/>
+      <c r="T3" s="63"/>
+      <c r="U3" s="63"/>
+      <c r="V3" s="63"/>
+      <c r="W3" s="63"/>
+      <c r="X3" s="63"/>
+      <c r="Y3" s="63"/>
+      <c r="Z3" s="63"/>
       <c r="AA3" s="37"/>
       <c r="AB3" s="50" t="s">
         <v>95</v>
       </c>
       <c r="AC3" s="48"/>
-      <c r="AD3" s="160"/>
-      <c r="AE3" s="161"/>
-      <c r="AF3" s="161"/>
-      <c r="AG3" s="161"/>
-      <c r="AH3" s="161"/>
-      <c r="AI3" s="161"/>
-      <c r="AJ3" s="161"/>
+      <c r="AD3" s="82"/>
+      <c r="AE3" s="83"/>
+      <c r="AF3" s="83"/>
+      <c r="AG3" s="83"/>
+      <c r="AH3" s="83"/>
+      <c r="AI3" s="83"/>
+      <c r="AJ3" s="83"/>
     </row>
     <row r="4" spans="1:36" ht="18" customHeight="1">
       <c r="A4" s="30"/>
@@ -7139,85 +7148,85 @@
       </c>
     </row>
     <row r="5" spans="1:36" ht="18" customHeight="1">
-      <c r="A5" s="63" t="s">
+      <c r="A5" s="168" t="s">
         <v>85</v>
       </c>
-      <c r="B5" s="63"/>
-      <c r="C5" s="103"/>
-      <c r="D5" s="103"/>
-      <c r="E5" s="103"/>
-      <c r="F5" s="103"/>
-      <c r="G5" s="103"/>
-      <c r="H5" s="103"/>
-      <c r="I5" s="103"/>
+      <c r="B5" s="168"/>
+      <c r="C5" s="96"/>
+      <c r="D5" s="96"/>
+      <c r="E5" s="96"/>
+      <c r="F5" s="96"/>
+      <c r="G5" s="96"/>
+      <c r="H5" s="96"/>
+      <c r="I5" s="96"/>
       <c r="J5" s="35"/>
-      <c r="K5" s="152" t="s">
+      <c r="K5" s="60" t="s">
         <v>0</v>
       </c>
-      <c r="L5" s="152"/>
-      <c r="M5" s="152"/>
-      <c r="N5" s="152"/>
-      <c r="O5" s="152"/>
-      <c r="P5" s="162"/>
-      <c r="Q5" s="163"/>
-      <c r="R5" s="163"/>
-      <c r="S5" s="163"/>
-      <c r="T5" s="163"/>
-      <c r="U5" s="163"/>
-      <c r="V5" s="163"/>
-      <c r="W5" s="163"/>
-      <c r="X5" s="163"/>
-      <c r="Y5" s="152" t="s">
+      <c r="L5" s="60"/>
+      <c r="M5" s="60"/>
+      <c r="N5" s="60"/>
+      <c r="O5" s="60"/>
+      <c r="P5" s="122"/>
+      <c r="Q5" s="123"/>
+      <c r="R5" s="123"/>
+      <c r="S5" s="123"/>
+      <c r="T5" s="123"/>
+      <c r="U5" s="123"/>
+      <c r="V5" s="123"/>
+      <c r="W5" s="123"/>
+      <c r="X5" s="123"/>
+      <c r="Y5" s="60" t="s">
         <v>48</v>
       </c>
-      <c r="Z5" s="152"/>
-      <c r="AA5" s="103"/>
-      <c r="AB5" s="103"/>
-      <c r="AC5" s="103"/>
-      <c r="AD5" s="103"/>
-      <c r="AE5" s="103"/>
-      <c r="AF5" s="103"/>
-      <c r="AG5" s="103"/>
-      <c r="AH5" s="103"/>
-      <c r="AI5" s="103"/>
-      <c r="AJ5" s="103"/>
+      <c r="Z5" s="60"/>
+      <c r="AA5" s="96"/>
+      <c r="AB5" s="96"/>
+      <c r="AC5" s="96"/>
+      <c r="AD5" s="96"/>
+      <c r="AE5" s="96"/>
+      <c r="AF5" s="96"/>
+      <c r="AG5" s="96"/>
+      <c r="AH5" s="96"/>
+      <c r="AI5" s="96"/>
+      <c r="AJ5" s="96"/>
     </row>
     <row r="6" spans="1:36" ht="18" customHeight="1">
-      <c r="A6" s="63" t="s">
+      <c r="A6" s="168" t="s">
         <v>1</v>
       </c>
-      <c r="B6" s="63"/>
-      <c r="C6" s="156"/>
-      <c r="D6" s="156"/>
-      <c r="E6" s="156"/>
-      <c r="F6" s="156"/>
-      <c r="G6" s="156"/>
-      <c r="H6" s="156"/>
-      <c r="I6" s="156"/>
+      <c r="B6" s="168"/>
+      <c r="C6" s="75"/>
+      <c r="D6" s="75"/>
+      <c r="E6" s="75"/>
+      <c r="F6" s="75"/>
+      <c r="G6" s="75"/>
+      <c r="H6" s="75"/>
+      <c r="I6" s="75"/>
       <c r="J6" s="35"/>
-      <c r="K6" s="152" t="s">
+      <c r="K6" s="60" t="s">
         <v>2</v>
       </c>
-      <c r="L6" s="152"/>
-      <c r="M6" s="152"/>
-      <c r="N6" s="152"/>
-      <c r="O6" s="152"/>
-      <c r="P6" s="165"/>
-      <c r="Q6" s="166"/>
-      <c r="R6" s="166"/>
-      <c r="S6" s="166"/>
-      <c r="T6" s="166"/>
-      <c r="U6" s="166"/>
-      <c r="V6" s="166"/>
-      <c r="W6" s="166"/>
-      <c r="X6" s="166"/>
+      <c r="L6" s="60"/>
+      <c r="M6" s="60"/>
+      <c r="N6" s="60"/>
+      <c r="O6" s="60"/>
+      <c r="P6" s="67"/>
+      <c r="Q6" s="68"/>
+      <c r="R6" s="68"/>
+      <c r="S6" s="68"/>
+      <c r="T6" s="68"/>
+      <c r="U6" s="68"/>
+      <c r="V6" s="68"/>
+      <c r="W6" s="68"/>
+      <c r="X6" s="68"/>
       <c r="Y6" s="56" t="s">
         <v>88</v>
       </c>
       <c r="Z6" s="56"/>
       <c r="AA6" s="56"/>
       <c r="AB6" s="56"/>
-      <c r="AC6" s="168"/>
+      <c r="AC6" s="59"/>
       <c r="AD6" s="57"/>
       <c r="AE6" s="57"/>
       <c r="AF6" s="57"/>
@@ -7227,43 +7236,43 @@
       <c r="AJ6" s="44"/>
     </row>
     <row r="7" spans="1:36" ht="18" customHeight="1">
-      <c r="A7" s="63" t="s">
+      <c r="A7" s="168" t="s">
         <v>3</v>
       </c>
-      <c r="B7" s="63"/>
-      <c r="C7" s="156"/>
-      <c r="D7" s="156"/>
-      <c r="E7" s="156"/>
-      <c r="F7" s="156"/>
-      <c r="G7" s="156"/>
-      <c r="H7" s="156"/>
-      <c r="I7" s="156"/>
+      <c r="B7" s="168"/>
+      <c r="C7" s="75"/>
+      <c r="D7" s="75"/>
+      <c r="E7" s="75"/>
+      <c r="F7" s="75"/>
+      <c r="G7" s="75"/>
+      <c r="H7" s="75"/>
+      <c r="I7" s="75"/>
       <c r="J7" s="35"/>
-      <c r="K7" s="152" t="s">
+      <c r="K7" s="60" t="s">
         <v>89</v>
       </c>
-      <c r="L7" s="152"/>
-      <c r="M7" s="152"/>
-      <c r="N7" s="152"/>
-      <c r="O7" s="152"/>
-      <c r="P7" s="167"/>
-      <c r="Q7" s="167"/>
-      <c r="R7" s="167"/>
-      <c r="S7" s="167"/>
-      <c r="T7" s="167"/>
+      <c r="L7" s="60"/>
+      <c r="M7" s="60"/>
+      <c r="N7" s="60"/>
+      <c r="O7" s="60"/>
+      <c r="P7" s="121"/>
+      <c r="Q7" s="121"/>
+      <c r="R7" s="121"/>
+      <c r="S7" s="121"/>
+      <c r="T7" s="121"/>
       <c r="U7" s="39" t="s">
         <v>4</v>
       </c>
-      <c r="V7" s="135"/>
-      <c r="W7" s="135"/>
-      <c r="X7" s="152" t="s">
+      <c r="V7" s="110"/>
+      <c r="W7" s="110"/>
+      <c r="X7" s="60" t="s">
         <v>90</v>
       </c>
-      <c r="Y7" s="152"/>
-      <c r="Z7" s="152"/>
-      <c r="AA7" s="152"/>
-      <c r="AB7" s="152"/>
-      <c r="AC7" s="168"/>
+      <c r="Y7" s="60"/>
+      <c r="Z7" s="60"/>
+      <c r="AA7" s="60"/>
+      <c r="AB7" s="60"/>
+      <c r="AC7" s="59"/>
       <c r="AD7" s="57"/>
       <c r="AE7" s="57"/>
       <c r="AF7" s="58"/>
@@ -7271,172 +7280,172 @@
       <c r="AH7" s="39" t="s">
         <v>4</v>
       </c>
-      <c r="AI7" s="167"/>
-      <c r="AJ7" s="167"/>
+      <c r="AI7" s="121"/>
+      <c r="AJ7" s="121"/>
     </row>
     <row r="8" spans="1:36" ht="18" customHeight="1">
-      <c r="A8" s="88" t="s">
+      <c r="A8" s="169" t="s">
         <v>5</v>
       </c>
-      <c r="B8" s="88"/>
-      <c r="C8" s="88"/>
-      <c r="D8" s="98"/>
-      <c r="E8" s="98"/>
-      <c r="F8" s="98"/>
-      <c r="G8" s="98"/>
-      <c r="H8" s="98"/>
-      <c r="I8" s="98"/>
-      <c r="J8" s="98"/>
-      <c r="K8" s="98"/>
-      <c r="L8" s="98"/>
-      <c r="M8" s="98"/>
-      <c r="N8" s="98"/>
-      <c r="O8" s="98"/>
-      <c r="P8" s="98"/>
-      <c r="Q8" s="98"/>
-      <c r="R8" s="98"/>
-      <c r="S8" s="164" t="s">
+      <c r="B8" s="169"/>
+      <c r="C8" s="169"/>
+      <c r="D8" s="61"/>
+      <c r="E8" s="61"/>
+      <c r="F8" s="61"/>
+      <c r="G8" s="61"/>
+      <c r="H8" s="61"/>
+      <c r="I8" s="61"/>
+      <c r="J8" s="61"/>
+      <c r="K8" s="61"/>
+      <c r="L8" s="61"/>
+      <c r="M8" s="61"/>
+      <c r="N8" s="61"/>
+      <c r="O8" s="61"/>
+      <c r="P8" s="61"/>
+      <c r="Q8" s="61"/>
+      <c r="R8" s="61"/>
+      <c r="S8" s="170" t="s">
         <v>49</v>
       </c>
-      <c r="T8" s="164"/>
-      <c r="U8" s="152"/>
-      <c r="V8" s="164"/>
-      <c r="W8" s="164"/>
-      <c r="X8" s="98"/>
-      <c r="Y8" s="98"/>
-      <c r="Z8" s="98"/>
-      <c r="AA8" s="98"/>
-      <c r="AB8" s="98"/>
-      <c r="AC8" s="98"/>
-      <c r="AD8" s="98"/>
-      <c r="AE8" s="98"/>
-      <c r="AF8" s="98"/>
-      <c r="AG8" s="98"/>
-      <c r="AH8" s="98"/>
-      <c r="AI8" s="98"/>
-      <c r="AJ8" s="98"/>
+      <c r="T8" s="170"/>
+      <c r="U8" s="171"/>
+      <c r="V8" s="170"/>
+      <c r="W8" s="170"/>
+      <c r="X8" s="61"/>
+      <c r="Y8" s="61"/>
+      <c r="Z8" s="61"/>
+      <c r="AA8" s="61"/>
+      <c r="AB8" s="61"/>
+      <c r="AC8" s="61"/>
+      <c r="AD8" s="61"/>
+      <c r="AE8" s="61"/>
+      <c r="AF8" s="61"/>
+      <c r="AG8" s="61"/>
+      <c r="AH8" s="61"/>
+      <c r="AI8" s="61"/>
+      <c r="AJ8" s="61"/>
     </row>
     <row r="9" spans="1:36" ht="26.4" customHeight="1">
-      <c r="A9" s="63" t="s">
+      <c r="A9" s="168" t="s">
         <v>6</v>
       </c>
-      <c r="B9" s="63"/>
-      <c r="C9" s="63"/>
-      <c r="D9" s="146"/>
-      <c r="E9" s="146"/>
-      <c r="F9" s="146"/>
-      <c r="G9" s="146"/>
-      <c r="H9" s="146"/>
-      <c r="I9" s="146"/>
-      <c r="J9" s="146"/>
-      <c r="K9" s="146"/>
-      <c r="L9" s="146"/>
-      <c r="M9" s="146"/>
-      <c r="N9" s="146"/>
-      <c r="O9" s="146"/>
-      <c r="P9" s="146"/>
-      <c r="Q9" s="146"/>
-      <c r="R9" s="146"/>
-      <c r="S9" s="152" t="s">
+      <c r="B9" s="168"/>
+      <c r="C9" s="168"/>
+      <c r="D9" s="75"/>
+      <c r="E9" s="75"/>
+      <c r="F9" s="75"/>
+      <c r="G9" s="75"/>
+      <c r="H9" s="75"/>
+      <c r="I9" s="175"/>
+      <c r="J9" s="175"/>
+      <c r="K9" s="175"/>
+      <c r="L9" s="175"/>
+      <c r="M9" s="175"/>
+      <c r="N9" s="175"/>
+      <c r="O9" s="175"/>
+      <c r="P9" s="175"/>
+      <c r="Q9" s="175"/>
+      <c r="R9" s="175"/>
+      <c r="S9" s="171" t="s">
         <v>50</v>
       </c>
-      <c r="T9" s="152"/>
-      <c r="U9" s="152"/>
-      <c r="V9" s="152"/>
-      <c r="W9" s="152"/>
-      <c r="X9" s="145"/>
-      <c r="Y9" s="146"/>
-      <c r="Z9" s="146"/>
-      <c r="AA9" s="146"/>
-      <c r="AB9" s="146"/>
-      <c r="AC9" s="146"/>
-      <c r="AD9" s="146"/>
-      <c r="AE9" s="146"/>
-      <c r="AF9" s="146"/>
-      <c r="AG9" s="146"/>
-      <c r="AH9" s="146"/>
-      <c r="AI9" s="146"/>
-      <c r="AJ9" s="146"/>
+      <c r="T9" s="171"/>
+      <c r="U9" s="171"/>
+      <c r="V9" s="171"/>
+      <c r="W9" s="171"/>
+      <c r="X9" s="120"/>
+      <c r="Y9" s="78"/>
+      <c r="Z9" s="78"/>
+      <c r="AA9" s="78"/>
+      <c r="AB9" s="78"/>
+      <c r="AC9" s="78"/>
+      <c r="AD9" s="78"/>
+      <c r="AE9" s="78"/>
+      <c r="AF9" s="78"/>
+      <c r="AG9" s="78"/>
+      <c r="AH9" s="78"/>
+      <c r="AI9" s="78"/>
+      <c r="AJ9" s="78"/>
     </row>
     <row r="10" spans="1:36" ht="5.25" customHeight="1">
-      <c r="A10" s="91"/>
-      <c r="B10" s="91"/>
-      <c r="C10" s="91"/>
-      <c r="D10" s="91"/>
-      <c r="E10" s="91"/>
-      <c r="F10" s="91"/>
-      <c r="G10" s="91"/>
-      <c r="H10" s="91"/>
-      <c r="I10" s="91"/>
-      <c r="J10" s="91"/>
-      <c r="K10" s="91"/>
-      <c r="L10" s="91"/>
-      <c r="M10" s="91"/>
-      <c r="N10" s="91"/>
-      <c r="O10" s="91"/>
-      <c r="P10" s="91"/>
-      <c r="Q10" s="91"/>
-      <c r="R10" s="91"/>
-      <c r="S10" s="91"/>
-      <c r="T10" s="91"/>
-      <c r="U10" s="91"/>
-      <c r="V10" s="91"/>
-      <c r="W10" s="91"/>
-      <c r="X10" s="91"/>
-      <c r="Y10" s="91"/>
-      <c r="Z10" s="91"/>
-      <c r="AA10" s="91"/>
-      <c r="AB10" s="91"/>
-      <c r="AC10" s="91"/>
-      <c r="AD10" s="91"/>
-      <c r="AE10" s="91"/>
-      <c r="AF10" s="91"/>
-      <c r="AG10" s="91"/>
-      <c r="AH10" s="91"/>
-      <c r="AI10" s="91"/>
-      <c r="AJ10" s="91"/>
+      <c r="A10" s="77"/>
+      <c r="B10" s="77"/>
+      <c r="C10" s="77"/>
+      <c r="D10" s="77"/>
+      <c r="E10" s="77"/>
+      <c r="F10" s="77"/>
+      <c r="G10" s="77"/>
+      <c r="H10" s="77"/>
+      <c r="I10" s="77"/>
+      <c r="J10" s="77"/>
+      <c r="K10" s="77"/>
+      <c r="L10" s="77"/>
+      <c r="M10" s="77"/>
+      <c r="N10" s="77"/>
+      <c r="O10" s="77"/>
+      <c r="P10" s="77"/>
+      <c r="Q10" s="77"/>
+      <c r="R10" s="77"/>
+      <c r="S10" s="77"/>
+      <c r="T10" s="77"/>
+      <c r="U10" s="77"/>
+      <c r="V10" s="77"/>
+      <c r="W10" s="77"/>
+      <c r="X10" s="77"/>
+      <c r="Y10" s="77"/>
+      <c r="Z10" s="77"/>
+      <c r="AA10" s="77"/>
+      <c r="AB10" s="77"/>
+      <c r="AC10" s="77"/>
+      <c r="AD10" s="77"/>
+      <c r="AE10" s="77"/>
+      <c r="AF10" s="77"/>
+      <c r="AG10" s="77"/>
+      <c r="AH10" s="77"/>
+      <c r="AI10" s="77"/>
+      <c r="AJ10" s="77"/>
     </row>
     <row r="11" spans="1:36" ht="14.25" customHeight="1">
-      <c r="A11" s="149" t="s">
+      <c r="A11" s="64" t="s">
         <v>7</v>
       </c>
-      <c r="B11" s="150"/>
-      <c r="C11" s="150"/>
-      <c r="D11" s="150"/>
-      <c r="E11" s="150"/>
-      <c r="F11" s="150"/>
-      <c r="G11" s="150"/>
-      <c r="H11" s="150"/>
-      <c r="I11" s="150"/>
-      <c r="J11" s="150"/>
-      <c r="K11" s="150"/>
-      <c r="L11" s="150"/>
-      <c r="M11" s="150"/>
-      <c r="N11" s="150"/>
-      <c r="O11" s="150"/>
-      <c r="P11" s="151"/>
-      <c r="Q11" s="153" t="s">
+      <c r="B11" s="65"/>
+      <c r="C11" s="65"/>
+      <c r="D11" s="65"/>
+      <c r="E11" s="65"/>
+      <c r="F11" s="65"/>
+      <c r="G11" s="65"/>
+      <c r="H11" s="65"/>
+      <c r="I11" s="65"/>
+      <c r="J11" s="65"/>
+      <c r="K11" s="65"/>
+      <c r="L11" s="65"/>
+      <c r="M11" s="65"/>
+      <c r="N11" s="65"/>
+      <c r="O11" s="65"/>
+      <c r="P11" s="66"/>
+      <c r="Q11" s="72" t="s">
         <v>8</v>
       </c>
-      <c r="R11" s="154"/>
-      <c r="S11" s="154"/>
-      <c r="T11" s="154"/>
-      <c r="U11" s="154"/>
-      <c r="V11" s="154"/>
-      <c r="W11" s="154"/>
-      <c r="X11" s="154"/>
-      <c r="Y11" s="154"/>
-      <c r="Z11" s="154"/>
-      <c r="AA11" s="154"/>
-      <c r="AB11" s="154"/>
-      <c r="AC11" s="154"/>
-      <c r="AD11" s="154"/>
-      <c r="AE11" s="154"/>
-      <c r="AF11" s="154"/>
-      <c r="AG11" s="154"/>
-      <c r="AH11" s="154"/>
-      <c r="AI11" s="154"/>
-      <c r="AJ11" s="155"/>
+      <c r="R11" s="73"/>
+      <c r="S11" s="73"/>
+      <c r="T11" s="73"/>
+      <c r="U11" s="73"/>
+      <c r="V11" s="73"/>
+      <c r="W11" s="73"/>
+      <c r="X11" s="73"/>
+      <c r="Y11" s="73"/>
+      <c r="Z11" s="73"/>
+      <c r="AA11" s="73"/>
+      <c r="AB11" s="73"/>
+      <c r="AC11" s="73"/>
+      <c r="AD11" s="73"/>
+      <c r="AE11" s="73"/>
+      <c r="AF11" s="73"/>
+      <c r="AG11" s="73"/>
+      <c r="AH11" s="73"/>
+      <c r="AI11" s="73"/>
+      <c r="AJ11" s="74"/>
     </row>
     <row r="12" spans="1:36" ht="18" customHeight="1">
       <c r="A12" s="2"/>
@@ -7545,150 +7554,150 @@
       <c r="AJ13" s="23"/>
     </row>
     <row r="14" spans="1:36" ht="16.5" customHeight="1">
-      <c r="A14" s="127" t="s">
+      <c r="A14" s="102" t="s">
         <v>86</v>
       </c>
-      <c r="B14" s="128"/>
-      <c r="C14" s="128"/>
-      <c r="D14" s="128"/>
-      <c r="E14" s="128"/>
-      <c r="F14" s="128"/>
-      <c r="G14" s="128"/>
-      <c r="H14" s="128"/>
-      <c r="I14" s="129"/>
-      <c r="J14" s="130"/>
-      <c r="K14" s="130"/>
-      <c r="L14" s="130"/>
-      <c r="M14" s="130"/>
-      <c r="N14" s="130"/>
-      <c r="O14" s="130"/>
-      <c r="P14" s="130"/>
-      <c r="Q14" s="130"/>
-      <c r="R14" s="130"/>
-      <c r="S14" s="130"/>
-      <c r="T14" s="130"/>
-      <c r="U14" s="130"/>
-      <c r="V14" s="130"/>
-      <c r="W14" s="130"/>
-      <c r="X14" s="130"/>
-      <c r="Y14" s="130"/>
-      <c r="Z14" s="130"/>
-      <c r="AA14" s="130"/>
-      <c r="AB14" s="130"/>
-      <c r="AC14" s="130"/>
-      <c r="AD14" s="130"/>
-      <c r="AE14" s="130"/>
-      <c r="AF14" s="130"/>
-      <c r="AG14" s="130"/>
-      <c r="AH14" s="130"/>
-      <c r="AI14" s="130"/>
-      <c r="AJ14" s="131"/>
+      <c r="B14" s="103"/>
+      <c r="C14" s="103"/>
+      <c r="D14" s="103"/>
+      <c r="E14" s="103"/>
+      <c r="F14" s="103"/>
+      <c r="G14" s="103"/>
+      <c r="H14" s="103"/>
+      <c r="I14" s="104"/>
+      <c r="J14" s="105"/>
+      <c r="K14" s="105"/>
+      <c r="L14" s="105"/>
+      <c r="M14" s="105"/>
+      <c r="N14" s="105"/>
+      <c r="O14" s="105"/>
+      <c r="P14" s="105"/>
+      <c r="Q14" s="105"/>
+      <c r="R14" s="105"/>
+      <c r="S14" s="105"/>
+      <c r="T14" s="105"/>
+      <c r="U14" s="105"/>
+      <c r="V14" s="105"/>
+      <c r="W14" s="105"/>
+      <c r="X14" s="105"/>
+      <c r="Y14" s="105"/>
+      <c r="Z14" s="105"/>
+      <c r="AA14" s="105"/>
+      <c r="AB14" s="105"/>
+      <c r="AC14" s="105"/>
+      <c r="AD14" s="105"/>
+      <c r="AE14" s="105"/>
+      <c r="AF14" s="105"/>
+      <c r="AG14" s="105"/>
+      <c r="AH14" s="105"/>
+      <c r="AI14" s="105"/>
+      <c r="AJ14" s="106"/>
     </row>
     <row r="15" spans="1:36" ht="3" customHeight="1">
-      <c r="A15" s="132">
+      <c r="A15" s="107">
         <v>2</v>
       </c>
-      <c r="B15" s="133"/>
-      <c r="C15" s="133"/>
-      <c r="D15" s="133"/>
-      <c r="E15" s="133"/>
-      <c r="F15" s="133"/>
-      <c r="G15" s="133"/>
-      <c r="H15" s="133"/>
-      <c r="I15" s="133"/>
-      <c r="J15" s="133"/>
-      <c r="K15" s="133"/>
-      <c r="L15" s="133"/>
-      <c r="M15" s="133"/>
-      <c r="N15" s="133"/>
-      <c r="O15" s="133"/>
-      <c r="P15" s="133"/>
-      <c r="Q15" s="133"/>
-      <c r="R15" s="133"/>
-      <c r="S15" s="133"/>
-      <c r="T15" s="133"/>
-      <c r="U15" s="133"/>
-      <c r="V15" s="133"/>
-      <c r="W15" s="133"/>
-      <c r="X15" s="133"/>
-      <c r="Y15" s="133"/>
-      <c r="Z15" s="133"/>
-      <c r="AA15" s="133"/>
-      <c r="AB15" s="133"/>
-      <c r="AC15" s="133"/>
-      <c r="AD15" s="133"/>
-      <c r="AE15" s="133"/>
-      <c r="AF15" s="133"/>
-      <c r="AG15" s="133"/>
-      <c r="AH15" s="133"/>
-      <c r="AI15" s="133"/>
-      <c r="AJ15" s="134"/>
+      <c r="B15" s="108"/>
+      <c r="C15" s="108"/>
+      <c r="D15" s="108"/>
+      <c r="E15" s="108"/>
+      <c r="F15" s="108"/>
+      <c r="G15" s="108"/>
+      <c r="H15" s="108"/>
+      <c r="I15" s="108"/>
+      <c r="J15" s="108"/>
+      <c r="K15" s="108"/>
+      <c r="L15" s="108"/>
+      <c r="M15" s="108"/>
+      <c r="N15" s="108"/>
+      <c r="O15" s="108"/>
+      <c r="P15" s="108"/>
+      <c r="Q15" s="108"/>
+      <c r="R15" s="108"/>
+      <c r="S15" s="108"/>
+      <c r="T15" s="108"/>
+      <c r="U15" s="108"/>
+      <c r="V15" s="108"/>
+      <c r="W15" s="108"/>
+      <c r="X15" s="108"/>
+      <c r="Y15" s="108"/>
+      <c r="Z15" s="108"/>
+      <c r="AA15" s="108"/>
+      <c r="AB15" s="108"/>
+      <c r="AC15" s="108"/>
+      <c r="AD15" s="108"/>
+      <c r="AE15" s="108"/>
+      <c r="AF15" s="108"/>
+      <c r="AG15" s="108"/>
+      <c r="AH15" s="108"/>
+      <c r="AI15" s="108"/>
+      <c r="AJ15" s="109"/>
     </row>
     <row r="16" spans="1:36" ht="12.75" customHeight="1">
-      <c r="A16" s="142" t="s">
+      <c r="A16" s="117" t="s">
         <v>9</v>
       </c>
-      <c r="B16" s="143"/>
-      <c r="C16" s="143"/>
-      <c r="D16" s="143"/>
-      <c r="E16" s="143"/>
-      <c r="F16" s="143"/>
-      <c r="G16" s="143"/>
-      <c r="H16" s="143"/>
-      <c r="I16" s="143"/>
-      <c r="J16" s="143"/>
-      <c r="K16" s="143"/>
-      <c r="L16" s="143"/>
-      <c r="M16" s="143"/>
-      <c r="N16" s="143"/>
-      <c r="O16" s="143"/>
-      <c r="P16" s="143"/>
-      <c r="Q16" s="143"/>
-      <c r="R16" s="143"/>
-      <c r="S16" s="143"/>
-      <c r="T16" s="144"/>
-      <c r="U16" s="136" t="s">
+      <c r="B16" s="118"/>
+      <c r="C16" s="118"/>
+      <c r="D16" s="118"/>
+      <c r="E16" s="118"/>
+      <c r="F16" s="118"/>
+      <c r="G16" s="118"/>
+      <c r="H16" s="118"/>
+      <c r="I16" s="118"/>
+      <c r="J16" s="118"/>
+      <c r="K16" s="118"/>
+      <c r="L16" s="118"/>
+      <c r="M16" s="118"/>
+      <c r="N16" s="118"/>
+      <c r="O16" s="118"/>
+      <c r="P16" s="118"/>
+      <c r="Q16" s="118"/>
+      <c r="R16" s="118"/>
+      <c r="S16" s="118"/>
+      <c r="T16" s="119"/>
+      <c r="U16" s="111" t="s">
         <v>73</v>
       </c>
-      <c r="V16" s="137"/>
-      <c r="W16" s="137"/>
-      <c r="X16" s="137"/>
-      <c r="Y16" s="137"/>
-      <c r="Z16" s="137"/>
-      <c r="AA16" s="137"/>
-      <c r="AB16" s="137"/>
-      <c r="AC16" s="137"/>
-      <c r="AD16" s="138"/>
-      <c r="AE16" s="139" t="s">
+      <c r="V16" s="112"/>
+      <c r="W16" s="112"/>
+      <c r="X16" s="112"/>
+      <c r="Y16" s="112"/>
+      <c r="Z16" s="112"/>
+      <c r="AA16" s="112"/>
+      <c r="AB16" s="112"/>
+      <c r="AC16" s="112"/>
+      <c r="AD16" s="113"/>
+      <c r="AE16" s="114" t="s">
         <v>10</v>
       </c>
-      <c r="AF16" s="140"/>
-      <c r="AG16" s="140"/>
-      <c r="AH16" s="140"/>
-      <c r="AI16" s="140"/>
-      <c r="AJ16" s="141"/>
+      <c r="AF16" s="115"/>
+      <c r="AG16" s="115"/>
+      <c r="AH16" s="115"/>
+      <c r="AI16" s="115"/>
+      <c r="AJ16" s="116"/>
     </row>
     <row r="17" spans="1:36" ht="18" customHeight="1">
-      <c r="A17" s="120"/>
-      <c r="B17" s="121"/>
-      <c r="C17" s="121"/>
-      <c r="D17" s="121"/>
-      <c r="E17" s="121"/>
-      <c r="F17" s="121"/>
-      <c r="G17" s="121"/>
-      <c r="H17" s="121"/>
-      <c r="I17" s="121"/>
-      <c r="J17" s="121"/>
-      <c r="K17" s="121"/>
-      <c r="L17" s="121"/>
-      <c r="M17" s="121"/>
-      <c r="N17" s="121"/>
-      <c r="O17" s="121"/>
-      <c r="P17" s="121"/>
-      <c r="Q17" s="121"/>
-      <c r="R17" s="121"/>
-      <c r="S17" s="121"/>
-      <c r="T17" s="122"/>
+      <c r="A17" s="90"/>
+      <c r="B17" s="91"/>
+      <c r="C17" s="91"/>
+      <c r="D17" s="91"/>
+      <c r="E17" s="91"/>
+      <c r="F17" s="91"/>
+      <c r="G17" s="91"/>
+      <c r="H17" s="91"/>
+      <c r="I17" s="91"/>
+      <c r="J17" s="91"/>
+      <c r="K17" s="91"/>
+      <c r="L17" s="91"/>
+      <c r="M17" s="91"/>
+      <c r="N17" s="91"/>
+      <c r="O17" s="91"/>
+      <c r="P17" s="91"/>
+      <c r="Q17" s="91"/>
+      <c r="R17" s="91"/>
+      <c r="S17" s="91"/>
+      <c r="T17" s="92"/>
       <c r="U17" s="25"/>
       <c r="V17" s="17" t="s">
         <v>64</v>
@@ -7704,32 +7713,32 @@
       <c r="AE17" s="14" t="s">
         <v>11</v>
       </c>
-      <c r="AF17" s="106"/>
-      <c r="AG17" s="106"/>
-      <c r="AI17" s="106"/>
-      <c r="AJ17" s="126"/>
+      <c r="AF17" s="97"/>
+      <c r="AG17" s="97"/>
+      <c r="AI17" s="97"/>
+      <c r="AJ17" s="101"/>
     </row>
     <row r="18" spans="1:36" ht="18" customHeight="1">
-      <c r="A18" s="120"/>
-      <c r="B18" s="121"/>
-      <c r="C18" s="121"/>
-      <c r="D18" s="121"/>
-      <c r="E18" s="121"/>
-      <c r="F18" s="121"/>
-      <c r="G18" s="121"/>
-      <c r="H18" s="121"/>
-      <c r="I18" s="121"/>
-      <c r="J18" s="121"/>
-      <c r="K18" s="121"/>
-      <c r="L18" s="121"/>
-      <c r="M18" s="121"/>
-      <c r="N18" s="121"/>
-      <c r="O18" s="121"/>
-      <c r="P18" s="121"/>
-      <c r="Q18" s="121"/>
-      <c r="R18" s="121"/>
-      <c r="S18" s="121"/>
-      <c r="T18" s="122"/>
+      <c r="A18" s="90"/>
+      <c r="B18" s="91"/>
+      <c r="C18" s="91"/>
+      <c r="D18" s="91"/>
+      <c r="E18" s="91"/>
+      <c r="F18" s="91"/>
+      <c r="G18" s="91"/>
+      <c r="H18" s="91"/>
+      <c r="I18" s="91"/>
+      <c r="J18" s="91"/>
+      <c r="K18" s="91"/>
+      <c r="L18" s="91"/>
+      <c r="M18" s="91"/>
+      <c r="N18" s="91"/>
+      <c r="O18" s="91"/>
+      <c r="P18" s="91"/>
+      <c r="Q18" s="91"/>
+      <c r="R18" s="91"/>
+      <c r="S18" s="91"/>
+      <c r="T18" s="92"/>
       <c r="U18" s="26"/>
       <c r="V18" s="17" t="s">
         <v>65</v>
@@ -7745,32 +7754,32 @@
       <c r="AE18" s="14" t="s">
         <v>12</v>
       </c>
-      <c r="AF18" s="106"/>
-      <c r="AG18" s="106"/>
-      <c r="AI18" s="106"/>
-      <c r="AJ18" s="126"/>
+      <c r="AF18" s="97"/>
+      <c r="AG18" s="97"/>
+      <c r="AI18" s="97"/>
+      <c r="AJ18" s="101"/>
     </row>
     <row r="19" spans="1:36" ht="18" customHeight="1">
-      <c r="A19" s="120"/>
-      <c r="B19" s="121"/>
-      <c r="C19" s="121"/>
-      <c r="D19" s="121"/>
-      <c r="E19" s="121"/>
-      <c r="F19" s="121"/>
-      <c r="G19" s="121"/>
-      <c r="H19" s="121"/>
-      <c r="I19" s="121"/>
-      <c r="J19" s="121"/>
-      <c r="K19" s="121"/>
-      <c r="L19" s="121"/>
-      <c r="M19" s="121"/>
-      <c r="N19" s="121"/>
-      <c r="O19" s="121"/>
-      <c r="P19" s="121"/>
-      <c r="Q19" s="121"/>
-      <c r="R19" s="121"/>
-      <c r="S19" s="121"/>
-      <c r="T19" s="122"/>
+      <c r="A19" s="90"/>
+      <c r="B19" s="91"/>
+      <c r="C19" s="91"/>
+      <c r="D19" s="91"/>
+      <c r="E19" s="91"/>
+      <c r="F19" s="91"/>
+      <c r="G19" s="91"/>
+      <c r="H19" s="91"/>
+      <c r="I19" s="91"/>
+      <c r="J19" s="91"/>
+      <c r="K19" s="91"/>
+      <c r="L19" s="91"/>
+      <c r="M19" s="91"/>
+      <c r="N19" s="91"/>
+      <c r="O19" s="91"/>
+      <c r="P19" s="91"/>
+      <c r="Q19" s="91"/>
+      <c r="R19" s="91"/>
+      <c r="S19" s="91"/>
+      <c r="T19" s="92"/>
       <c r="U19" s="26"/>
       <c r="V19" s="17" t="s">
         <v>66</v>
@@ -7786,32 +7795,32 @@
       <c r="AE19" s="14" t="s">
         <v>13</v>
       </c>
-      <c r="AF19" s="106"/>
-      <c r="AG19" s="106"/>
-      <c r="AI19" s="106"/>
-      <c r="AJ19" s="126"/>
+      <c r="AF19" s="97"/>
+      <c r="AG19" s="97"/>
+      <c r="AI19" s="97"/>
+      <c r="AJ19" s="101"/>
     </row>
     <row r="20" spans="1:36" ht="3.75" customHeight="1">
-      <c r="A20" s="123"/>
-      <c r="B20" s="124"/>
-      <c r="C20" s="124"/>
-      <c r="D20" s="124"/>
-      <c r="E20" s="124"/>
-      <c r="F20" s="124"/>
-      <c r="G20" s="124"/>
-      <c r="H20" s="124"/>
-      <c r="I20" s="124"/>
-      <c r="J20" s="124"/>
-      <c r="K20" s="124"/>
-      <c r="L20" s="124"/>
-      <c r="M20" s="124"/>
-      <c r="N20" s="124"/>
-      <c r="O20" s="124"/>
-      <c r="P20" s="124"/>
-      <c r="Q20" s="124"/>
-      <c r="R20" s="124"/>
-      <c r="S20" s="124"/>
-      <c r="T20" s="125"/>
+      <c r="A20" s="93"/>
+      <c r="B20" s="94"/>
+      <c r="C20" s="94"/>
+      <c r="D20" s="94"/>
+      <c r="E20" s="94"/>
+      <c r="F20" s="94"/>
+      <c r="G20" s="94"/>
+      <c r="H20" s="94"/>
+      <c r="I20" s="94"/>
+      <c r="J20" s="94"/>
+      <c r="K20" s="94"/>
+      <c r="L20" s="94"/>
+      <c r="M20" s="94"/>
+      <c r="N20" s="94"/>
+      <c r="O20" s="94"/>
+      <c r="P20" s="94"/>
+      <c r="Q20" s="94"/>
+      <c r="R20" s="94"/>
+      <c r="S20" s="94"/>
+      <c r="T20" s="95"/>
       <c r="U20" s="27"/>
       <c r="V20" s="16"/>
       <c r="W20" s="7"/>
@@ -7870,80 +7879,80 @@
       <c r="AJ21" s="47"/>
     </row>
     <row r="22" spans="1:36" ht="16.5" customHeight="1">
-      <c r="A22" s="114"/>
-      <c r="B22" s="115"/>
-      <c r="C22" s="115"/>
-      <c r="D22" s="115"/>
-      <c r="E22" s="115"/>
-      <c r="F22" s="115"/>
-      <c r="G22" s="115"/>
-      <c r="H22" s="115"/>
-      <c r="I22" s="115"/>
-      <c r="J22" s="115"/>
-      <c r="K22" s="115"/>
-      <c r="L22" s="115"/>
-      <c r="M22" s="115"/>
-      <c r="N22" s="115"/>
-      <c r="O22" s="115"/>
-      <c r="P22" s="115"/>
-      <c r="Q22" s="115"/>
-      <c r="R22" s="115"/>
-      <c r="S22" s="115"/>
-      <c r="T22" s="115"/>
-      <c r="U22" s="115"/>
-      <c r="V22" s="115"/>
-      <c r="W22" s="115"/>
-      <c r="X22" s="115"/>
-      <c r="Y22" s="115"/>
-      <c r="Z22" s="115"/>
-      <c r="AA22" s="115"/>
-      <c r="AB22" s="115"/>
-      <c r="AC22" s="115"/>
-      <c r="AD22" s="115"/>
-      <c r="AE22" s="115"/>
-      <c r="AF22" s="115"/>
-      <c r="AG22" s="115"/>
-      <c r="AH22" s="115"/>
-      <c r="AI22" s="115"/>
-      <c r="AJ22" s="116"/>
+      <c r="A22" s="84"/>
+      <c r="B22" s="85"/>
+      <c r="C22" s="85"/>
+      <c r="D22" s="85"/>
+      <c r="E22" s="85"/>
+      <c r="F22" s="85"/>
+      <c r="G22" s="85"/>
+      <c r="H22" s="85"/>
+      <c r="I22" s="85"/>
+      <c r="J22" s="85"/>
+      <c r="K22" s="85"/>
+      <c r="L22" s="85"/>
+      <c r="M22" s="85"/>
+      <c r="N22" s="85"/>
+      <c r="O22" s="85"/>
+      <c r="P22" s="85"/>
+      <c r="Q22" s="85"/>
+      <c r="R22" s="85"/>
+      <c r="S22" s="85"/>
+      <c r="T22" s="85"/>
+      <c r="U22" s="85"/>
+      <c r="V22" s="85"/>
+      <c r="W22" s="85"/>
+      <c r="X22" s="85"/>
+      <c r="Y22" s="85"/>
+      <c r="Z22" s="85"/>
+      <c r="AA22" s="85"/>
+      <c r="AB22" s="85"/>
+      <c r="AC22" s="85"/>
+      <c r="AD22" s="85"/>
+      <c r="AE22" s="85"/>
+      <c r="AF22" s="85"/>
+      <c r="AG22" s="85"/>
+      <c r="AH22" s="85"/>
+      <c r="AI22" s="85"/>
+      <c r="AJ22" s="86"/>
     </row>
     <row r="23" spans="1:36" ht="16.5" customHeight="1">
-      <c r="A23" s="117"/>
-      <c r="B23" s="118"/>
-      <c r="C23" s="118"/>
-      <c r="D23" s="118"/>
-      <c r="E23" s="118"/>
-      <c r="F23" s="118"/>
-      <c r="G23" s="118"/>
-      <c r="H23" s="118"/>
-      <c r="I23" s="118"/>
-      <c r="J23" s="118"/>
-      <c r="K23" s="118"/>
-      <c r="L23" s="118"/>
-      <c r="M23" s="118"/>
-      <c r="N23" s="118"/>
-      <c r="O23" s="118"/>
-      <c r="P23" s="118"/>
-      <c r="Q23" s="118"/>
-      <c r="R23" s="118"/>
-      <c r="S23" s="118"/>
-      <c r="T23" s="118"/>
-      <c r="U23" s="118"/>
-      <c r="V23" s="118"/>
-      <c r="W23" s="118"/>
-      <c r="X23" s="118"/>
-      <c r="Y23" s="118"/>
-      <c r="Z23" s="118"/>
-      <c r="AA23" s="118"/>
-      <c r="AB23" s="118"/>
-      <c r="AC23" s="118"/>
-      <c r="AD23" s="118"/>
-      <c r="AE23" s="118"/>
-      <c r="AF23" s="118"/>
-      <c r="AG23" s="118"/>
-      <c r="AH23" s="118"/>
-      <c r="AI23" s="118"/>
-      <c r="AJ23" s="119"/>
+      <c r="A23" s="87"/>
+      <c r="B23" s="88"/>
+      <c r="C23" s="88"/>
+      <c r="D23" s="88"/>
+      <c r="E23" s="88"/>
+      <c r="F23" s="88"/>
+      <c r="G23" s="88"/>
+      <c r="H23" s="88"/>
+      <c r="I23" s="88"/>
+      <c r="J23" s="88"/>
+      <c r="K23" s="88"/>
+      <c r="L23" s="88"/>
+      <c r="M23" s="88"/>
+      <c r="N23" s="88"/>
+      <c r="O23" s="88"/>
+      <c r="P23" s="88"/>
+      <c r="Q23" s="88"/>
+      <c r="R23" s="88"/>
+      <c r="S23" s="88"/>
+      <c r="T23" s="88"/>
+      <c r="U23" s="88"/>
+      <c r="V23" s="88"/>
+      <c r="W23" s="88"/>
+      <c r="X23" s="88"/>
+      <c r="Y23" s="88"/>
+      <c r="Z23" s="88"/>
+      <c r="AA23" s="88"/>
+      <c r="AB23" s="88"/>
+      <c r="AC23" s="88"/>
+      <c r="AD23" s="88"/>
+      <c r="AE23" s="88"/>
+      <c r="AF23" s="88"/>
+      <c r="AG23" s="88"/>
+      <c r="AH23" s="88"/>
+      <c r="AI23" s="88"/>
+      <c r="AJ23" s="89"/>
     </row>
     <row r="24" spans="1:36" ht="12.75" customHeight="1">
       <c r="A24" s="46" t="s">
@@ -7986,42 +7995,42 @@
       <c r="AJ24" s="47"/>
     </row>
     <row r="25" spans="1:36" ht="18" customHeight="1">
-      <c r="A25" s="157"/>
-      <c r="B25" s="158"/>
-      <c r="C25" s="158"/>
-      <c r="D25" s="158"/>
-      <c r="E25" s="158"/>
-      <c r="F25" s="158"/>
-      <c r="G25" s="158"/>
-      <c r="H25" s="158"/>
-      <c r="I25" s="158"/>
-      <c r="J25" s="158"/>
-      <c r="K25" s="158"/>
-      <c r="L25" s="158"/>
-      <c r="M25" s="158"/>
-      <c r="N25" s="158"/>
-      <c r="O25" s="158"/>
-      <c r="P25" s="158"/>
-      <c r="Q25" s="158"/>
-      <c r="R25" s="158"/>
-      <c r="S25" s="158"/>
-      <c r="T25" s="158"/>
-      <c r="U25" s="158"/>
-      <c r="V25" s="158"/>
-      <c r="W25" s="158"/>
-      <c r="X25" s="158"/>
-      <c r="Y25" s="158"/>
-      <c r="Z25" s="158"/>
-      <c r="AA25" s="158"/>
-      <c r="AB25" s="158"/>
-      <c r="AC25" s="158"/>
-      <c r="AD25" s="158"/>
-      <c r="AE25" s="158"/>
-      <c r="AF25" s="158"/>
-      <c r="AG25" s="158"/>
-      <c r="AH25" s="158"/>
-      <c r="AI25" s="158"/>
-      <c r="AJ25" s="159"/>
+      <c r="A25" s="79"/>
+      <c r="B25" s="80"/>
+      <c r="C25" s="80"/>
+      <c r="D25" s="80"/>
+      <c r="E25" s="80"/>
+      <c r="F25" s="80"/>
+      <c r="G25" s="80"/>
+      <c r="H25" s="80"/>
+      <c r="I25" s="80"/>
+      <c r="J25" s="80"/>
+      <c r="K25" s="80"/>
+      <c r="L25" s="80"/>
+      <c r="M25" s="80"/>
+      <c r="N25" s="80"/>
+      <c r="O25" s="80"/>
+      <c r="P25" s="80"/>
+      <c r="Q25" s="80"/>
+      <c r="R25" s="80"/>
+      <c r="S25" s="80"/>
+      <c r="T25" s="80"/>
+      <c r="U25" s="80"/>
+      <c r="V25" s="80"/>
+      <c r="W25" s="80"/>
+      <c r="X25" s="80"/>
+      <c r="Y25" s="80"/>
+      <c r="Z25" s="80"/>
+      <c r="AA25" s="80"/>
+      <c r="AB25" s="80"/>
+      <c r="AC25" s="80"/>
+      <c r="AD25" s="80"/>
+      <c r="AE25" s="80"/>
+      <c r="AF25" s="80"/>
+      <c r="AG25" s="80"/>
+      <c r="AH25" s="80"/>
+      <c r="AI25" s="80"/>
+      <c r="AJ25" s="81"/>
     </row>
     <row r="26" spans="1:36" ht="12.75" customHeight="1">
       <c r="A26" s="46" t="s">
@@ -8064,137 +8073,137 @@
       <c r="AJ26" s="47"/>
     </row>
     <row r="27" spans="1:36" ht="15" customHeight="1">
-      <c r="A27" s="65"/>
-      <c r="B27" s="66"/>
-      <c r="C27" s="66"/>
-      <c r="D27" s="66"/>
-      <c r="E27" s="66"/>
-      <c r="F27" s="66"/>
-      <c r="G27" s="66"/>
-      <c r="H27" s="66"/>
-      <c r="I27" s="66"/>
-      <c r="J27" s="66"/>
-      <c r="K27" s="66"/>
-      <c r="L27" s="66"/>
-      <c r="M27" s="66"/>
-      <c r="N27" s="66"/>
-      <c r="O27" s="66"/>
-      <c r="P27" s="66"/>
-      <c r="Q27" s="66"/>
-      <c r="R27" s="66"/>
-      <c r="S27" s="66"/>
-      <c r="T27" s="66"/>
-      <c r="U27" s="66"/>
-      <c r="V27" s="66"/>
-      <c r="W27" s="66"/>
-      <c r="X27" s="66"/>
-      <c r="Y27" s="66"/>
-      <c r="Z27" s="66"/>
-      <c r="AA27" s="66"/>
-      <c r="AB27" s="66"/>
-      <c r="AC27" s="66"/>
-      <c r="AD27" s="66"/>
-      <c r="AE27" s="66"/>
-      <c r="AF27" s="66"/>
-      <c r="AG27" s="66"/>
-      <c r="AH27" s="66"/>
-      <c r="AI27" s="66"/>
-      <c r="AJ27" s="67"/>
+      <c r="A27" s="152"/>
+      <c r="B27" s="153"/>
+      <c r="C27" s="153"/>
+      <c r="D27" s="153"/>
+      <c r="E27" s="153"/>
+      <c r="F27" s="153"/>
+      <c r="G27" s="153"/>
+      <c r="H27" s="153"/>
+      <c r="I27" s="153"/>
+      <c r="J27" s="153"/>
+      <c r="K27" s="153"/>
+      <c r="L27" s="153"/>
+      <c r="M27" s="153"/>
+      <c r="N27" s="153"/>
+      <c r="O27" s="153"/>
+      <c r="P27" s="153"/>
+      <c r="Q27" s="153"/>
+      <c r="R27" s="153"/>
+      <c r="S27" s="153"/>
+      <c r="T27" s="153"/>
+      <c r="U27" s="153"/>
+      <c r="V27" s="153"/>
+      <c r="W27" s="153"/>
+      <c r="X27" s="153"/>
+      <c r="Y27" s="153"/>
+      <c r="Z27" s="153"/>
+      <c r="AA27" s="153"/>
+      <c r="AB27" s="153"/>
+      <c r="AC27" s="153"/>
+      <c r="AD27" s="153"/>
+      <c r="AE27" s="153"/>
+      <c r="AF27" s="153"/>
+      <c r="AG27" s="153"/>
+      <c r="AH27" s="153"/>
+      <c r="AI27" s="153"/>
+      <c r="AJ27" s="154"/>
     </row>
     <row r="28" spans="1:36" ht="15" customHeight="1">
-      <c r="A28" s="68"/>
-      <c r="B28" s="66"/>
-      <c r="C28" s="66"/>
-      <c r="D28" s="66"/>
-      <c r="E28" s="66"/>
-      <c r="F28" s="66"/>
-      <c r="G28" s="66"/>
-      <c r="H28" s="66"/>
-      <c r="I28" s="66"/>
-      <c r="J28" s="66"/>
-      <c r="K28" s="66"/>
-      <c r="L28" s="66"/>
-      <c r="M28" s="66"/>
-      <c r="N28" s="66"/>
-      <c r="O28" s="66"/>
-      <c r="P28" s="66"/>
-      <c r="Q28" s="66"/>
-      <c r="R28" s="66"/>
-      <c r="S28" s="66"/>
-      <c r="T28" s="66"/>
-      <c r="U28" s="66"/>
-      <c r="V28" s="66"/>
-      <c r="W28" s="66"/>
-      <c r="X28" s="66"/>
-      <c r="Y28" s="66"/>
-      <c r="Z28" s="66"/>
-      <c r="AA28" s="66"/>
-      <c r="AB28" s="66"/>
-      <c r="AC28" s="66"/>
-      <c r="AD28" s="66"/>
-      <c r="AE28" s="66"/>
-      <c r="AF28" s="66"/>
-      <c r="AG28" s="66"/>
-      <c r="AH28" s="66"/>
-      <c r="AI28" s="66"/>
-      <c r="AJ28" s="67"/>
+      <c r="A28" s="155"/>
+      <c r="B28" s="153"/>
+      <c r="C28" s="153"/>
+      <c r="D28" s="153"/>
+      <c r="E28" s="153"/>
+      <c r="F28" s="153"/>
+      <c r="G28" s="153"/>
+      <c r="H28" s="153"/>
+      <c r="I28" s="153"/>
+      <c r="J28" s="153"/>
+      <c r="K28" s="153"/>
+      <c r="L28" s="153"/>
+      <c r="M28" s="153"/>
+      <c r="N28" s="153"/>
+      <c r="O28" s="153"/>
+      <c r="P28" s="153"/>
+      <c r="Q28" s="153"/>
+      <c r="R28" s="153"/>
+      <c r="S28" s="153"/>
+      <c r="T28" s="153"/>
+      <c r="U28" s="153"/>
+      <c r="V28" s="153"/>
+      <c r="W28" s="153"/>
+      <c r="X28" s="153"/>
+      <c r="Y28" s="153"/>
+      <c r="Z28" s="153"/>
+      <c r="AA28" s="153"/>
+      <c r="AB28" s="153"/>
+      <c r="AC28" s="153"/>
+      <c r="AD28" s="153"/>
+      <c r="AE28" s="153"/>
+      <c r="AF28" s="153"/>
+      <c r="AG28" s="153"/>
+      <c r="AH28" s="153"/>
+      <c r="AI28" s="153"/>
+      <c r="AJ28" s="154"/>
     </row>
     <row r="29" spans="1:36" ht="100.8" customHeight="1">
-      <c r="A29" s="69"/>
-      <c r="B29" s="70"/>
-      <c r="C29" s="70"/>
-      <c r="D29" s="70"/>
-      <c r="E29" s="70"/>
-      <c r="F29" s="70"/>
-      <c r="G29" s="70"/>
-      <c r="H29" s="70"/>
-      <c r="I29" s="70"/>
-      <c r="J29" s="70"/>
-      <c r="K29" s="70"/>
-      <c r="L29" s="70"/>
-      <c r="M29" s="70"/>
-      <c r="N29" s="70"/>
-      <c r="O29" s="70"/>
-      <c r="P29" s="70"/>
-      <c r="Q29" s="70"/>
-      <c r="R29" s="70"/>
-      <c r="S29" s="70"/>
-      <c r="T29" s="70"/>
-      <c r="U29" s="70"/>
-      <c r="V29" s="70"/>
-      <c r="W29" s="70"/>
-      <c r="X29" s="70"/>
-      <c r="Y29" s="70"/>
-      <c r="Z29" s="70"/>
-      <c r="AA29" s="70"/>
-      <c r="AB29" s="70"/>
-      <c r="AC29" s="70"/>
-      <c r="AD29" s="70"/>
-      <c r="AE29" s="70"/>
-      <c r="AF29" s="70"/>
-      <c r="AG29" s="70"/>
-      <c r="AH29" s="70"/>
-      <c r="AI29" s="70"/>
-      <c r="AJ29" s="71"/>
+      <c r="A29" s="156"/>
+      <c r="B29" s="157"/>
+      <c r="C29" s="157"/>
+      <c r="D29" s="157"/>
+      <c r="E29" s="157"/>
+      <c r="F29" s="157"/>
+      <c r="G29" s="157"/>
+      <c r="H29" s="157"/>
+      <c r="I29" s="157"/>
+      <c r="J29" s="157"/>
+      <c r="K29" s="157"/>
+      <c r="L29" s="157"/>
+      <c r="M29" s="157"/>
+      <c r="N29" s="157"/>
+      <c r="O29" s="157"/>
+      <c r="P29" s="157"/>
+      <c r="Q29" s="157"/>
+      <c r="R29" s="157"/>
+      <c r="S29" s="157"/>
+      <c r="T29" s="157"/>
+      <c r="U29" s="157"/>
+      <c r="V29" s="157"/>
+      <c r="W29" s="157"/>
+      <c r="X29" s="157"/>
+      <c r="Y29" s="157"/>
+      <c r="Z29" s="157"/>
+      <c r="AA29" s="157"/>
+      <c r="AB29" s="157"/>
+      <c r="AC29" s="157"/>
+      <c r="AD29" s="157"/>
+      <c r="AE29" s="157"/>
+      <c r="AF29" s="157"/>
+      <c r="AG29" s="157"/>
+      <c r="AH29" s="157"/>
+      <c r="AI29" s="157"/>
+      <c r="AJ29" s="158"/>
     </row>
     <row r="30" spans="1:36" ht="12.75" customHeight="1">
-      <c r="A30" s="78" t="s">
+      <c r="A30" s="159" t="s">
         <v>17</v>
       </c>
-      <c r="B30" s="79"/>
-      <c r="C30" s="79"/>
-      <c r="D30" s="79"/>
-      <c r="E30" s="79"/>
-      <c r="F30" s="79"/>
-      <c r="G30" s="79"/>
-      <c r="H30" s="79"/>
-      <c r="I30" s="79"/>
-      <c r="J30" s="79"/>
-      <c r="K30" s="79"/>
-      <c r="L30" s="79"/>
-      <c r="M30" s="79"/>
-      <c r="N30" s="79"/>
-      <c r="O30" s="79"/>
+      <c r="B30" s="160"/>
+      <c r="C30" s="160"/>
+      <c r="D30" s="160"/>
+      <c r="E30" s="160"/>
+      <c r="F30" s="160"/>
+      <c r="G30" s="160"/>
+      <c r="H30" s="160"/>
+      <c r="I30" s="160"/>
+      <c r="J30" s="160"/>
+      <c r="K30" s="160"/>
+      <c r="L30" s="160"/>
+      <c r="M30" s="160"/>
+      <c r="N30" s="160"/>
+      <c r="O30" s="160"/>
       <c r="P30" s="41"/>
       <c r="Q30" s="41"/>
       <c r="R30" s="41"/>
@@ -8218,216 +8227,216 @@
       <c r="AJ30" s="42"/>
     </row>
     <row r="31" spans="1:36" ht="16.5" customHeight="1">
-      <c r="A31" s="65"/>
-      <c r="B31" s="82"/>
-      <c r="C31" s="82"/>
-      <c r="D31" s="82"/>
-      <c r="E31" s="82"/>
-      <c r="F31" s="82"/>
-      <c r="G31" s="82"/>
-      <c r="H31" s="82"/>
-      <c r="I31" s="82"/>
-      <c r="J31" s="82"/>
-      <c r="K31" s="82"/>
-      <c r="L31" s="82"/>
-      <c r="M31" s="82"/>
-      <c r="N31" s="82"/>
-      <c r="O31" s="82"/>
-      <c r="P31" s="82"/>
-      <c r="Q31" s="82"/>
-      <c r="R31" s="82"/>
-      <c r="S31" s="82"/>
-      <c r="T31" s="82"/>
-      <c r="U31" s="82"/>
-      <c r="V31" s="82"/>
-      <c r="W31" s="82"/>
-      <c r="X31" s="82"/>
-      <c r="Y31" s="82"/>
-      <c r="Z31" s="82"/>
-      <c r="AA31" s="82"/>
-      <c r="AB31" s="82"/>
-      <c r="AC31" s="82"/>
-      <c r="AD31" s="82"/>
-      <c r="AE31" s="82"/>
-      <c r="AF31" s="82"/>
-      <c r="AG31" s="82"/>
-      <c r="AH31" s="82"/>
-      <c r="AI31" s="82"/>
-      <c r="AJ31" s="83"/>
+      <c r="A31" s="152"/>
+      <c r="B31" s="163"/>
+      <c r="C31" s="163"/>
+      <c r="D31" s="163"/>
+      <c r="E31" s="163"/>
+      <c r="F31" s="163"/>
+      <c r="G31" s="163"/>
+      <c r="H31" s="163"/>
+      <c r="I31" s="163"/>
+      <c r="J31" s="163"/>
+      <c r="K31" s="163"/>
+      <c r="L31" s="163"/>
+      <c r="M31" s="163"/>
+      <c r="N31" s="163"/>
+      <c r="O31" s="163"/>
+      <c r="P31" s="163"/>
+      <c r="Q31" s="163"/>
+      <c r="R31" s="163"/>
+      <c r="S31" s="163"/>
+      <c r="T31" s="163"/>
+      <c r="U31" s="163"/>
+      <c r="V31" s="163"/>
+      <c r="W31" s="163"/>
+      <c r="X31" s="163"/>
+      <c r="Y31" s="163"/>
+      <c r="Z31" s="163"/>
+      <c r="AA31" s="163"/>
+      <c r="AB31" s="163"/>
+      <c r="AC31" s="163"/>
+      <c r="AD31" s="163"/>
+      <c r="AE31" s="163"/>
+      <c r="AF31" s="163"/>
+      <c r="AG31" s="163"/>
+      <c r="AH31" s="163"/>
+      <c r="AI31" s="163"/>
+      <c r="AJ31" s="164"/>
     </row>
     <row r="32" spans="1:36" ht="16.5" customHeight="1">
-      <c r="A32" s="65"/>
-      <c r="B32" s="82"/>
-      <c r="C32" s="82"/>
-      <c r="D32" s="82"/>
-      <c r="E32" s="82"/>
-      <c r="F32" s="82"/>
-      <c r="G32" s="82"/>
-      <c r="H32" s="82"/>
-      <c r="I32" s="82"/>
-      <c r="J32" s="82"/>
-      <c r="K32" s="82"/>
-      <c r="L32" s="82"/>
-      <c r="M32" s="82"/>
-      <c r="N32" s="82"/>
-      <c r="O32" s="82"/>
-      <c r="P32" s="82"/>
-      <c r="Q32" s="82"/>
-      <c r="R32" s="82"/>
-      <c r="S32" s="82"/>
-      <c r="T32" s="82"/>
-      <c r="U32" s="82"/>
-      <c r="V32" s="82"/>
-      <c r="W32" s="82"/>
-      <c r="X32" s="82"/>
-      <c r="Y32" s="82"/>
-      <c r="Z32" s="82"/>
-      <c r="AA32" s="82"/>
-      <c r="AB32" s="82"/>
-      <c r="AC32" s="82"/>
-      <c r="AD32" s="82"/>
-      <c r="AE32" s="82"/>
-      <c r="AF32" s="82"/>
-      <c r="AG32" s="82"/>
-      <c r="AH32" s="82"/>
-      <c r="AI32" s="82"/>
-      <c r="AJ32" s="83"/>
+      <c r="A32" s="152"/>
+      <c r="B32" s="163"/>
+      <c r="C32" s="163"/>
+      <c r="D32" s="163"/>
+      <c r="E32" s="163"/>
+      <c r="F32" s="163"/>
+      <c r="G32" s="163"/>
+      <c r="H32" s="163"/>
+      <c r="I32" s="163"/>
+      <c r="J32" s="163"/>
+      <c r="K32" s="163"/>
+      <c r="L32" s="163"/>
+      <c r="M32" s="163"/>
+      <c r="N32" s="163"/>
+      <c r="O32" s="163"/>
+      <c r="P32" s="163"/>
+      <c r="Q32" s="163"/>
+      <c r="R32" s="163"/>
+      <c r="S32" s="163"/>
+      <c r="T32" s="163"/>
+      <c r="U32" s="163"/>
+      <c r="V32" s="163"/>
+      <c r="W32" s="163"/>
+      <c r="X32" s="163"/>
+      <c r="Y32" s="163"/>
+      <c r="Z32" s="163"/>
+      <c r="AA32" s="163"/>
+      <c r="AB32" s="163"/>
+      <c r="AC32" s="163"/>
+      <c r="AD32" s="163"/>
+      <c r="AE32" s="163"/>
+      <c r="AF32" s="163"/>
+      <c r="AG32" s="163"/>
+      <c r="AH32" s="163"/>
+      <c r="AI32" s="163"/>
+      <c r="AJ32" s="164"/>
     </row>
     <row r="33" spans="1:36" ht="16.5" customHeight="1">
-      <c r="A33" s="65"/>
-      <c r="B33" s="82"/>
-      <c r="C33" s="82"/>
-      <c r="D33" s="82"/>
-      <c r="E33" s="82"/>
-      <c r="F33" s="82"/>
-      <c r="G33" s="82"/>
-      <c r="H33" s="82"/>
-      <c r="I33" s="82"/>
-      <c r="J33" s="82"/>
-      <c r="K33" s="82"/>
-      <c r="L33" s="82"/>
-      <c r="M33" s="82"/>
-      <c r="N33" s="82"/>
-      <c r="O33" s="82"/>
-      <c r="P33" s="82"/>
-      <c r="Q33" s="82"/>
-      <c r="R33" s="82"/>
-      <c r="S33" s="82"/>
-      <c r="T33" s="82"/>
-      <c r="U33" s="82"/>
-      <c r="V33" s="82"/>
-      <c r="W33" s="82"/>
-      <c r="X33" s="82"/>
-      <c r="Y33" s="82"/>
-      <c r="Z33" s="82"/>
-      <c r="AA33" s="82"/>
-      <c r="AB33" s="82"/>
-      <c r="AC33" s="82"/>
-      <c r="AD33" s="82"/>
-      <c r="AE33" s="82"/>
-      <c r="AF33" s="82"/>
-      <c r="AG33" s="82"/>
-      <c r="AH33" s="82"/>
-      <c r="AI33" s="82"/>
-      <c r="AJ33" s="83"/>
+      <c r="A33" s="152"/>
+      <c r="B33" s="163"/>
+      <c r="C33" s="163"/>
+      <c r="D33" s="163"/>
+      <c r="E33" s="163"/>
+      <c r="F33" s="163"/>
+      <c r="G33" s="163"/>
+      <c r="H33" s="163"/>
+      <c r="I33" s="163"/>
+      <c r="J33" s="163"/>
+      <c r="K33" s="163"/>
+      <c r="L33" s="163"/>
+      <c r="M33" s="163"/>
+      <c r="N33" s="163"/>
+      <c r="O33" s="163"/>
+      <c r="P33" s="163"/>
+      <c r="Q33" s="163"/>
+      <c r="R33" s="163"/>
+      <c r="S33" s="163"/>
+      <c r="T33" s="163"/>
+      <c r="U33" s="163"/>
+      <c r="V33" s="163"/>
+      <c r="W33" s="163"/>
+      <c r="X33" s="163"/>
+      <c r="Y33" s="163"/>
+      <c r="Z33" s="163"/>
+      <c r="AA33" s="163"/>
+      <c r="AB33" s="163"/>
+      <c r="AC33" s="163"/>
+      <c r="AD33" s="163"/>
+      <c r="AE33" s="163"/>
+      <c r="AF33" s="163"/>
+      <c r="AG33" s="163"/>
+      <c r="AH33" s="163"/>
+      <c r="AI33" s="163"/>
+      <c r="AJ33" s="164"/>
     </row>
     <row r="34" spans="1:36" ht="61.8" customHeight="1">
-      <c r="A34" s="65"/>
-      <c r="B34" s="82"/>
-      <c r="C34" s="82"/>
-      <c r="D34" s="82"/>
-      <c r="E34" s="82"/>
-      <c r="F34" s="82"/>
-      <c r="G34" s="82"/>
-      <c r="H34" s="82"/>
-      <c r="I34" s="82"/>
-      <c r="J34" s="82"/>
-      <c r="K34" s="82"/>
-      <c r="L34" s="82"/>
-      <c r="M34" s="82"/>
-      <c r="N34" s="82"/>
-      <c r="O34" s="82"/>
-      <c r="P34" s="82"/>
-      <c r="Q34" s="82"/>
-      <c r="R34" s="82"/>
-      <c r="S34" s="82"/>
-      <c r="T34" s="82"/>
-      <c r="U34" s="82"/>
-      <c r="V34" s="82"/>
-      <c r="W34" s="82"/>
-      <c r="X34" s="82"/>
-      <c r="Y34" s="82"/>
-      <c r="Z34" s="82"/>
-      <c r="AA34" s="82"/>
-      <c r="AB34" s="82"/>
-      <c r="AC34" s="82"/>
-      <c r="AD34" s="82"/>
-      <c r="AE34" s="82"/>
-      <c r="AF34" s="82"/>
-      <c r="AG34" s="82"/>
-      <c r="AH34" s="82"/>
-      <c r="AI34" s="82"/>
-      <c r="AJ34" s="83"/>
+      <c r="A34" s="152"/>
+      <c r="B34" s="163"/>
+      <c r="C34" s="163"/>
+      <c r="D34" s="163"/>
+      <c r="E34" s="163"/>
+      <c r="F34" s="163"/>
+      <c r="G34" s="163"/>
+      <c r="H34" s="163"/>
+      <c r="I34" s="163"/>
+      <c r="J34" s="163"/>
+      <c r="K34" s="163"/>
+      <c r="L34" s="163"/>
+      <c r="M34" s="163"/>
+      <c r="N34" s="163"/>
+      <c r="O34" s="163"/>
+      <c r="P34" s="163"/>
+      <c r="Q34" s="163"/>
+      <c r="R34" s="163"/>
+      <c r="S34" s="163"/>
+      <c r="T34" s="163"/>
+      <c r="U34" s="163"/>
+      <c r="V34" s="163"/>
+      <c r="W34" s="163"/>
+      <c r="X34" s="163"/>
+      <c r="Y34" s="163"/>
+      <c r="Z34" s="163"/>
+      <c r="AA34" s="163"/>
+      <c r="AB34" s="163"/>
+      <c r="AC34" s="163"/>
+      <c r="AD34" s="163"/>
+      <c r="AE34" s="163"/>
+      <c r="AF34" s="163"/>
+      <c r="AG34" s="163"/>
+      <c r="AH34" s="163"/>
+      <c r="AI34" s="163"/>
+      <c r="AJ34" s="164"/>
     </row>
     <row r="35" spans="1:36" ht="13.2" customHeight="1">
-      <c r="A35" s="84"/>
-      <c r="B35" s="85"/>
-      <c r="C35" s="85"/>
-      <c r="D35" s="85"/>
-      <c r="E35" s="85"/>
-      <c r="F35" s="85"/>
-      <c r="G35" s="85"/>
-      <c r="H35" s="85"/>
-      <c r="I35" s="85"/>
-      <c r="J35" s="85"/>
-      <c r="K35" s="85"/>
-      <c r="L35" s="85"/>
-      <c r="M35" s="85"/>
-      <c r="N35" s="85"/>
-      <c r="O35" s="85"/>
-      <c r="P35" s="85"/>
-      <c r="Q35" s="85"/>
-      <c r="R35" s="85"/>
-      <c r="S35" s="85"/>
-      <c r="T35" s="85"/>
-      <c r="U35" s="85"/>
-      <c r="V35" s="85"/>
-      <c r="W35" s="85"/>
-      <c r="X35" s="85"/>
-      <c r="Y35" s="85"/>
-      <c r="Z35" s="85"/>
-      <c r="AA35" s="85"/>
-      <c r="AB35" s="85"/>
-      <c r="AC35" s="85"/>
-      <c r="AD35" s="85"/>
-      <c r="AE35" s="85"/>
-      <c r="AF35" s="85"/>
-      <c r="AG35" s="85"/>
-      <c r="AH35" s="85"/>
-      <c r="AI35" s="85"/>
-      <c r="AJ35" s="86"/>
+      <c r="A35" s="165"/>
+      <c r="B35" s="166"/>
+      <c r="C35" s="166"/>
+      <c r="D35" s="166"/>
+      <c r="E35" s="166"/>
+      <c r="F35" s="166"/>
+      <c r="G35" s="166"/>
+      <c r="H35" s="166"/>
+      <c r="I35" s="166"/>
+      <c r="J35" s="166"/>
+      <c r="K35" s="166"/>
+      <c r="L35" s="166"/>
+      <c r="M35" s="166"/>
+      <c r="N35" s="166"/>
+      <c r="O35" s="166"/>
+      <c r="P35" s="166"/>
+      <c r="Q35" s="166"/>
+      <c r="R35" s="166"/>
+      <c r="S35" s="166"/>
+      <c r="T35" s="166"/>
+      <c r="U35" s="166"/>
+      <c r="V35" s="166"/>
+      <c r="W35" s="166"/>
+      <c r="X35" s="166"/>
+      <c r="Y35" s="166"/>
+      <c r="Z35" s="166"/>
+      <c r="AA35" s="166"/>
+      <c r="AB35" s="166"/>
+      <c r="AC35" s="166"/>
+      <c r="AD35" s="166"/>
+      <c r="AE35" s="166"/>
+      <c r="AF35" s="166"/>
+      <c r="AG35" s="166"/>
+      <c r="AH35" s="166"/>
+      <c r="AI35" s="166"/>
+      <c r="AJ35" s="167"/>
     </row>
     <row r="36" spans="1:36" ht="13.5" customHeight="1">
-      <c r="A36" s="72" t="s">
+      <c r="A36" s="69" t="s">
         <v>94</v>
       </c>
-      <c r="B36" s="73"/>
-      <c r="C36" s="73"/>
-      <c r="D36" s="73"/>
-      <c r="E36" s="73"/>
-      <c r="F36" s="73"/>
-      <c r="G36" s="73"/>
-      <c r="H36" s="73"/>
-      <c r="I36" s="73"/>
-      <c r="J36" s="73"/>
-      <c r="K36" s="73"/>
-      <c r="L36" s="73"/>
-      <c r="M36" s="73"/>
-      <c r="N36" s="73"/>
-      <c r="O36" s="73"/>
-      <c r="P36" s="73"/>
-      <c r="Q36" s="73"/>
-      <c r="R36" s="73"/>
+      <c r="B36" s="70"/>
+      <c r="C36" s="70"/>
+      <c r="D36" s="70"/>
+      <c r="E36" s="70"/>
+      <c r="F36" s="70"/>
+      <c r="G36" s="70"/>
+      <c r="H36" s="70"/>
+      <c r="I36" s="70"/>
+      <c r="J36" s="70"/>
+      <c r="K36" s="70"/>
+      <c r="L36" s="70"/>
+      <c r="M36" s="70"/>
+      <c r="N36" s="70"/>
+      <c r="O36" s="70"/>
+      <c r="P36" s="70"/>
+      <c r="Q36" s="70"/>
+      <c r="R36" s="70"/>
       <c r="S36" s="40"/>
       <c r="T36" s="40"/>
       <c r="U36" s="40"/>
@@ -8448,178 +8457,178 @@
       <c r="AJ36" s="43"/>
     </row>
     <row r="37" spans="1:36" ht="14.25" customHeight="1">
-      <c r="A37" s="65"/>
-      <c r="B37" s="82"/>
-      <c r="C37" s="82"/>
-      <c r="D37" s="82"/>
-      <c r="E37" s="82"/>
-      <c r="F37" s="82"/>
-      <c r="G37" s="82"/>
-      <c r="H37" s="82"/>
-      <c r="I37" s="82"/>
-      <c r="J37" s="82"/>
-      <c r="K37" s="82"/>
-      <c r="L37" s="82"/>
-      <c r="M37" s="82"/>
-      <c r="N37" s="82"/>
-      <c r="O37" s="82"/>
-      <c r="P37" s="82"/>
-      <c r="Q37" s="82"/>
-      <c r="R37" s="82"/>
-      <c r="S37" s="82"/>
-      <c r="T37" s="82"/>
-      <c r="U37" s="82"/>
-      <c r="V37" s="82"/>
-      <c r="W37" s="82"/>
-      <c r="X37" s="82"/>
-      <c r="Y37" s="82"/>
-      <c r="Z37" s="82"/>
-      <c r="AA37" s="82"/>
-      <c r="AB37" s="82"/>
-      <c r="AC37" s="82"/>
-      <c r="AD37" s="82"/>
-      <c r="AE37" s="82"/>
-      <c r="AF37" s="82"/>
-      <c r="AG37" s="82"/>
-      <c r="AH37" s="82"/>
-      <c r="AI37" s="82"/>
-      <c r="AJ37" s="83"/>
+      <c r="A37" s="152"/>
+      <c r="B37" s="163"/>
+      <c r="C37" s="163"/>
+      <c r="D37" s="163"/>
+      <c r="E37" s="163"/>
+      <c r="F37" s="163"/>
+      <c r="G37" s="163"/>
+      <c r="H37" s="163"/>
+      <c r="I37" s="163"/>
+      <c r="J37" s="163"/>
+      <c r="K37" s="163"/>
+      <c r="L37" s="163"/>
+      <c r="M37" s="163"/>
+      <c r="N37" s="163"/>
+      <c r="O37" s="163"/>
+      <c r="P37" s="163"/>
+      <c r="Q37" s="163"/>
+      <c r="R37" s="163"/>
+      <c r="S37" s="163"/>
+      <c r="T37" s="163"/>
+      <c r="U37" s="163"/>
+      <c r="V37" s="163"/>
+      <c r="W37" s="163"/>
+      <c r="X37" s="163"/>
+      <c r="Y37" s="163"/>
+      <c r="Z37" s="163"/>
+      <c r="AA37" s="163"/>
+      <c r="AB37" s="163"/>
+      <c r="AC37" s="163"/>
+      <c r="AD37" s="163"/>
+      <c r="AE37" s="163"/>
+      <c r="AF37" s="163"/>
+      <c r="AG37" s="163"/>
+      <c r="AH37" s="163"/>
+      <c r="AI37" s="163"/>
+      <c r="AJ37" s="164"/>
     </row>
     <row r="38" spans="1:36" ht="14.25" customHeight="1">
-      <c r="A38" s="65"/>
-      <c r="B38" s="82"/>
-      <c r="C38" s="82"/>
-      <c r="D38" s="82"/>
-      <c r="E38" s="82"/>
-      <c r="F38" s="82"/>
-      <c r="G38" s="82"/>
-      <c r="H38" s="82"/>
-      <c r="I38" s="82"/>
-      <c r="J38" s="82"/>
-      <c r="K38" s="82"/>
-      <c r="L38" s="82"/>
-      <c r="M38" s="82"/>
-      <c r="N38" s="82"/>
-      <c r="O38" s="82"/>
-      <c r="P38" s="82"/>
-      <c r="Q38" s="82"/>
-      <c r="R38" s="82"/>
-      <c r="S38" s="82"/>
-      <c r="T38" s="82"/>
-      <c r="U38" s="82"/>
-      <c r="V38" s="82"/>
-      <c r="W38" s="82"/>
-      <c r="X38" s="82"/>
-      <c r="Y38" s="82"/>
-      <c r="Z38" s="82"/>
-      <c r="AA38" s="82"/>
-      <c r="AB38" s="82"/>
-      <c r="AC38" s="82"/>
-      <c r="AD38" s="82"/>
-      <c r="AE38" s="82"/>
-      <c r="AF38" s="82"/>
-      <c r="AG38" s="82"/>
-      <c r="AH38" s="82"/>
-      <c r="AI38" s="82"/>
-      <c r="AJ38" s="83"/>
+      <c r="A38" s="152"/>
+      <c r="B38" s="163"/>
+      <c r="C38" s="163"/>
+      <c r="D38" s="163"/>
+      <c r="E38" s="163"/>
+      <c r="F38" s="163"/>
+      <c r="G38" s="163"/>
+      <c r="H38" s="163"/>
+      <c r="I38" s="163"/>
+      <c r="J38" s="163"/>
+      <c r="K38" s="163"/>
+      <c r="L38" s="163"/>
+      <c r="M38" s="163"/>
+      <c r="N38" s="163"/>
+      <c r="O38" s="163"/>
+      <c r="P38" s="163"/>
+      <c r="Q38" s="163"/>
+      <c r="R38" s="163"/>
+      <c r="S38" s="163"/>
+      <c r="T38" s="163"/>
+      <c r="U38" s="163"/>
+      <c r="V38" s="163"/>
+      <c r="W38" s="163"/>
+      <c r="X38" s="163"/>
+      <c r="Y38" s="163"/>
+      <c r="Z38" s="163"/>
+      <c r="AA38" s="163"/>
+      <c r="AB38" s="163"/>
+      <c r="AC38" s="163"/>
+      <c r="AD38" s="163"/>
+      <c r="AE38" s="163"/>
+      <c r="AF38" s="163"/>
+      <c r="AG38" s="163"/>
+      <c r="AH38" s="163"/>
+      <c r="AI38" s="163"/>
+      <c r="AJ38" s="164"/>
     </row>
     <row r="39" spans="1:36" ht="27.6" customHeight="1">
-      <c r="A39" s="65"/>
-      <c r="B39" s="82"/>
-      <c r="C39" s="82"/>
-      <c r="D39" s="82"/>
-      <c r="E39" s="82"/>
-      <c r="F39" s="82"/>
-      <c r="G39" s="82"/>
-      <c r="H39" s="82"/>
-      <c r="I39" s="82"/>
-      <c r="J39" s="82"/>
-      <c r="K39" s="82"/>
-      <c r="L39" s="82"/>
-      <c r="M39" s="82"/>
-      <c r="N39" s="82"/>
-      <c r="O39" s="82"/>
-      <c r="P39" s="82"/>
-      <c r="Q39" s="82"/>
-      <c r="R39" s="82"/>
-      <c r="S39" s="82"/>
-      <c r="T39" s="82"/>
-      <c r="U39" s="82"/>
-      <c r="V39" s="82"/>
-      <c r="W39" s="82"/>
-      <c r="X39" s="82"/>
-      <c r="Y39" s="82"/>
-      <c r="Z39" s="82"/>
-      <c r="AA39" s="82"/>
-      <c r="AB39" s="82"/>
-      <c r="AC39" s="82"/>
-      <c r="AD39" s="82"/>
-      <c r="AE39" s="82"/>
-      <c r="AF39" s="82"/>
-      <c r="AG39" s="82"/>
-      <c r="AH39" s="82"/>
-      <c r="AI39" s="82"/>
-      <c r="AJ39" s="83"/>
+      <c r="A39" s="152"/>
+      <c r="B39" s="163"/>
+      <c r="C39" s="163"/>
+      <c r="D39" s="163"/>
+      <c r="E39" s="163"/>
+      <c r="F39" s="163"/>
+      <c r="G39" s="163"/>
+      <c r="H39" s="163"/>
+      <c r="I39" s="163"/>
+      <c r="J39" s="163"/>
+      <c r="K39" s="163"/>
+      <c r="L39" s="163"/>
+      <c r="M39" s="163"/>
+      <c r="N39" s="163"/>
+      <c r="O39" s="163"/>
+      <c r="P39" s="163"/>
+      <c r="Q39" s="163"/>
+      <c r="R39" s="163"/>
+      <c r="S39" s="163"/>
+      <c r="T39" s="163"/>
+      <c r="U39" s="163"/>
+      <c r="V39" s="163"/>
+      <c r="W39" s="163"/>
+      <c r="X39" s="163"/>
+      <c r="Y39" s="163"/>
+      <c r="Z39" s="163"/>
+      <c r="AA39" s="163"/>
+      <c r="AB39" s="163"/>
+      <c r="AC39" s="163"/>
+      <c r="AD39" s="163"/>
+      <c r="AE39" s="163"/>
+      <c r="AF39" s="163"/>
+      <c r="AG39" s="163"/>
+      <c r="AH39" s="163"/>
+      <c r="AI39" s="163"/>
+      <c r="AJ39" s="164"/>
     </row>
     <row r="40" spans="1:36" ht="16.8" customHeight="1">
-      <c r="A40" s="65"/>
-      <c r="B40" s="82"/>
-      <c r="C40" s="82"/>
-      <c r="D40" s="82"/>
-      <c r="E40" s="82"/>
-      <c r="F40" s="82"/>
-      <c r="G40" s="82"/>
-      <c r="H40" s="82"/>
-      <c r="I40" s="82"/>
-      <c r="J40" s="82"/>
-      <c r="K40" s="82"/>
-      <c r="L40" s="82"/>
-      <c r="M40" s="82"/>
-      <c r="N40" s="82"/>
-      <c r="O40" s="82"/>
-      <c r="P40" s="82"/>
-      <c r="Q40" s="82"/>
-      <c r="R40" s="82"/>
-      <c r="S40" s="82"/>
-      <c r="T40" s="82"/>
-      <c r="U40" s="82"/>
-      <c r="V40" s="82"/>
-      <c r="W40" s="82"/>
-      <c r="X40" s="82"/>
-      <c r="Y40" s="82"/>
-      <c r="Z40" s="82"/>
-      <c r="AA40" s="82"/>
-      <c r="AB40" s="82"/>
-      <c r="AC40" s="82"/>
-      <c r="AD40" s="82"/>
-      <c r="AE40" s="82"/>
-      <c r="AF40" s="82"/>
-      <c r="AG40" s="82"/>
-      <c r="AH40" s="82"/>
-      <c r="AI40" s="82"/>
-      <c r="AJ40" s="83"/>
+      <c r="A40" s="152"/>
+      <c r="B40" s="163"/>
+      <c r="C40" s="163"/>
+      <c r="D40" s="163"/>
+      <c r="E40" s="163"/>
+      <c r="F40" s="163"/>
+      <c r="G40" s="163"/>
+      <c r="H40" s="163"/>
+      <c r="I40" s="163"/>
+      <c r="J40" s="163"/>
+      <c r="K40" s="163"/>
+      <c r="L40" s="163"/>
+      <c r="M40" s="163"/>
+      <c r="N40" s="163"/>
+      <c r="O40" s="163"/>
+      <c r="P40" s="163"/>
+      <c r="Q40" s="163"/>
+      <c r="R40" s="163"/>
+      <c r="S40" s="163"/>
+      <c r="T40" s="163"/>
+      <c r="U40" s="163"/>
+      <c r="V40" s="163"/>
+      <c r="W40" s="163"/>
+      <c r="X40" s="163"/>
+      <c r="Y40" s="163"/>
+      <c r="Z40" s="163"/>
+      <c r="AA40" s="163"/>
+      <c r="AB40" s="163"/>
+      <c r="AC40" s="163"/>
+      <c r="AD40" s="163"/>
+      <c r="AE40" s="163"/>
+      <c r="AF40" s="163"/>
+      <c r="AG40" s="163"/>
+      <c r="AH40" s="163"/>
+      <c r="AI40" s="163"/>
+      <c r="AJ40" s="164"/>
     </row>
     <row r="41" spans="1:36" ht="16.8" customHeight="1">
-      <c r="A41" s="72" t="s">
+      <c r="A41" s="69" t="s">
         <v>99</v>
       </c>
-      <c r="B41" s="73"/>
-      <c r="C41" s="73"/>
-      <c r="D41" s="73"/>
-      <c r="E41" s="73"/>
-      <c r="F41" s="73"/>
-      <c r="G41" s="73"/>
-      <c r="H41" s="73"/>
-      <c r="I41" s="73"/>
-      <c r="J41" s="73"/>
-      <c r="K41" s="73"/>
-      <c r="L41" s="73"/>
-      <c r="M41" s="73"/>
-      <c r="N41" s="73"/>
-      <c r="O41" s="73"/>
-      <c r="P41" s="73"/>
-      <c r="Q41" s="73"/>
-      <c r="R41" s="73"/>
+      <c r="B41" s="70"/>
+      <c r="C41" s="70"/>
+      <c r="D41" s="70"/>
+      <c r="E41" s="70"/>
+      <c r="F41" s="70"/>
+      <c r="G41" s="70"/>
+      <c r="H41" s="70"/>
+      <c r="I41" s="70"/>
+      <c r="J41" s="70"/>
+      <c r="K41" s="70"/>
+      <c r="L41" s="70"/>
+      <c r="M41" s="70"/>
+      <c r="N41" s="70"/>
+      <c r="O41" s="70"/>
+      <c r="P41" s="70"/>
+      <c r="Q41" s="70"/>
+      <c r="R41" s="70"/>
       <c r="S41" s="40"/>
       <c r="T41" s="40"/>
       <c r="U41" s="40"/>
@@ -8678,675 +8687,675 @@
       <c r="AJ42" s="55"/>
     </row>
     <row r="43" spans="1:36" ht="17.25" customHeight="1">
-      <c r="A43" s="74" t="s">
+      <c r="A43" s="98" t="s">
         <v>18</v>
       </c>
-      <c r="B43" s="75"/>
-      <c r="C43" s="75"/>
-      <c r="D43" s="75"/>
-      <c r="E43" s="75"/>
-      <c r="F43" s="75"/>
-      <c r="G43" s="75"/>
-      <c r="H43" s="75"/>
-      <c r="I43" s="76"/>
-      <c r="J43" s="74" t="s">
+      <c r="B43" s="99"/>
+      <c r="C43" s="99"/>
+      <c r="D43" s="99"/>
+      <c r="E43" s="99"/>
+      <c r="F43" s="99"/>
+      <c r="G43" s="99"/>
+      <c r="H43" s="99"/>
+      <c r="I43" s="100"/>
+      <c r="J43" s="98" t="s">
         <v>19</v>
       </c>
-      <c r="K43" s="75"/>
-      <c r="L43" s="75"/>
-      <c r="M43" s="75"/>
-      <c r="N43" s="75"/>
-      <c r="O43" s="75"/>
-      <c r="P43" s="75"/>
-      <c r="Q43" s="75"/>
-      <c r="R43" s="76"/>
-      <c r="S43" s="74" t="s">
+      <c r="K43" s="99"/>
+      <c r="L43" s="99"/>
+      <c r="M43" s="99"/>
+      <c r="N43" s="99"/>
+      <c r="O43" s="99"/>
+      <c r="P43" s="99"/>
+      <c r="Q43" s="99"/>
+      <c r="R43" s="100"/>
+      <c r="S43" s="98" t="s">
         <v>77</v>
       </c>
-      <c r="T43" s="75"/>
-      <c r="U43" s="75"/>
-      <c r="V43" s="75"/>
-      <c r="W43" s="75"/>
-      <c r="X43" s="75"/>
-      <c r="Y43" s="75"/>
-      <c r="Z43" s="75"/>
-      <c r="AA43" s="76"/>
-      <c r="AB43" s="80" t="s">
+      <c r="T43" s="99"/>
+      <c r="U43" s="99"/>
+      <c r="V43" s="99"/>
+      <c r="W43" s="99"/>
+      <c r="X43" s="99"/>
+      <c r="Y43" s="99"/>
+      <c r="Z43" s="99"/>
+      <c r="AA43" s="100"/>
+      <c r="AB43" s="161" t="s">
         <v>91</v>
       </c>
-      <c r="AC43" s="75"/>
-      <c r="AD43" s="75"/>
-      <c r="AE43" s="75"/>
-      <c r="AF43" s="75"/>
-      <c r="AG43" s="75"/>
-      <c r="AH43" s="75"/>
-      <c r="AI43" s="75"/>
-      <c r="AJ43" s="76"/>
+      <c r="AC43" s="99"/>
+      <c r="AD43" s="99"/>
+      <c r="AE43" s="99"/>
+      <c r="AF43" s="99"/>
+      <c r="AG43" s="99"/>
+      <c r="AH43" s="99"/>
+      <c r="AI43" s="99"/>
+      <c r="AJ43" s="100"/>
     </row>
     <row r="44" spans="1:36" ht="18" customHeight="1">
       <c r="A44" s="2"/>
-      <c r="B44" s="60" t="s">
+      <c r="B44" s="127" t="s">
         <v>21</v>
       </c>
-      <c r="C44" s="60"/>
-      <c r="D44" s="60"/>
-      <c r="E44" s="60"/>
-      <c r="F44" s="60"/>
-      <c r="G44" s="60"/>
-      <c r="H44" s="60"/>
-      <c r="I44" s="61"/>
+      <c r="C44" s="127"/>
+      <c r="D44" s="127"/>
+      <c r="E44" s="127"/>
+      <c r="F44" s="127"/>
+      <c r="G44" s="127"/>
+      <c r="H44" s="127"/>
+      <c r="I44" s="128"/>
       <c r="J44" s="10"/>
-      <c r="K44" s="60" t="s">
+      <c r="K44" s="172" t="s">
         <v>22</v>
       </c>
-      <c r="L44" s="60"/>
-      <c r="M44" s="60"/>
-      <c r="N44" s="60"/>
-      <c r="O44" s="60"/>
-      <c r="P44" s="60"/>
-      <c r="Q44" s="60"/>
-      <c r="R44" s="61"/>
-      <c r="S44" s="87" t="s">
+      <c r="L44" s="172"/>
+      <c r="M44" s="172"/>
+      <c r="N44" s="172"/>
+      <c r="O44" s="172"/>
+      <c r="P44" s="172"/>
+      <c r="Q44" s="172"/>
+      <c r="R44" s="173"/>
+      <c r="S44" s="124" t="s">
         <v>81</v>
       </c>
-      <c r="T44" s="88"/>
-      <c r="U44" s="88"/>
-      <c r="V44" s="88"/>
-      <c r="W44" s="81"/>
-      <c r="X44" s="81"/>
-      <c r="Y44" s="81"/>
+      <c r="T44" s="76"/>
+      <c r="U44" s="76"/>
+      <c r="V44" s="76"/>
+      <c r="W44" s="162"/>
+      <c r="X44" s="162"/>
+      <c r="Y44" s="162"/>
       <c r="Z44" s="49"/>
       <c r="AA44" s="4"/>
-      <c r="AB44" s="62" t="s">
+      <c r="AB44" s="125" t="s">
         <v>82</v>
       </c>
-      <c r="AC44" s="63"/>
-      <c r="AD44" s="63"/>
-      <c r="AE44" s="63"/>
-      <c r="AF44" s="77"/>
-      <c r="AG44" s="77"/>
-      <c r="AH44" s="77"/>
-      <c r="AI44" s="77"/>
+      <c r="AC44" s="71"/>
+      <c r="AD44" s="71"/>
+      <c r="AE44" s="71"/>
+      <c r="AF44" s="132"/>
+      <c r="AG44" s="132"/>
+      <c r="AH44" s="132"/>
+      <c r="AI44" s="132"/>
       <c r="AJ44" s="4"/>
     </row>
     <row r="45" spans="1:36" ht="18" customHeight="1">
       <c r="A45" s="2"/>
-      <c r="B45" s="60" t="s">
+      <c r="B45" s="127" t="s">
         <v>24</v>
       </c>
-      <c r="C45" s="60"/>
-      <c r="D45" s="60"/>
-      <c r="E45" s="60"/>
-      <c r="F45" s="60"/>
-      <c r="G45" s="60"/>
-      <c r="H45" s="60"/>
-      <c r="I45" s="61"/>
+      <c r="C45" s="127"/>
+      <c r="D45" s="127"/>
+      <c r="E45" s="127"/>
+      <c r="F45" s="127"/>
+      <c r="G45" s="127"/>
+      <c r="H45" s="127"/>
+      <c r="I45" s="128"/>
       <c r="J45" s="10"/>
-      <c r="K45" s="60" t="s">
+      <c r="K45" s="172" t="s">
         <v>25</v>
       </c>
-      <c r="L45" s="60"/>
-      <c r="M45" s="60"/>
-      <c r="N45" s="60"/>
-      <c r="O45" s="60"/>
-      <c r="P45" s="60"/>
-      <c r="Q45" s="60"/>
-      <c r="R45" s="61"/>
-      <c r="S45" s="87" t="s">
+      <c r="L45" s="172"/>
+      <c r="M45" s="172"/>
+      <c r="N45" s="172"/>
+      <c r="O45" s="172"/>
+      <c r="P45" s="172"/>
+      <c r="Q45" s="172"/>
+      <c r="R45" s="173"/>
+      <c r="S45" s="124" t="s">
         <v>80</v>
       </c>
-      <c r="T45" s="88"/>
-      <c r="U45" s="88"/>
-      <c r="V45" s="88"/>
-      <c r="W45" s="59"/>
-      <c r="X45" s="59"/>
-      <c r="Y45" s="59"/>
-      <c r="Z45" s="59"/>
+      <c r="T45" s="76"/>
+      <c r="U45" s="76"/>
+      <c r="V45" s="76"/>
+      <c r="W45" s="151"/>
+      <c r="X45" s="151"/>
+      <c r="Y45" s="151"/>
+      <c r="Z45" s="151"/>
       <c r="AA45" s="4"/>
-      <c r="AB45" s="87" t="s">
+      <c r="AB45" s="124" t="s">
         <v>81</v>
       </c>
-      <c r="AC45" s="88"/>
-      <c r="AD45" s="88"/>
-      <c r="AE45" s="88"/>
-      <c r="AF45" s="59"/>
-      <c r="AG45" s="59"/>
-      <c r="AH45" s="59"/>
-      <c r="AI45" s="59"/>
+      <c r="AC45" s="76"/>
+      <c r="AD45" s="76"/>
+      <c r="AE45" s="76"/>
+      <c r="AF45" s="151"/>
+      <c r="AG45" s="151"/>
+      <c r="AH45" s="151"/>
+      <c r="AI45" s="151"/>
       <c r="AJ45" s="4"/>
     </row>
     <row r="46" spans="1:36" ht="18" customHeight="1">
       <c r="A46" s="2"/>
-      <c r="B46" s="60" t="s">
+      <c r="B46" s="127" t="s">
         <v>27</v>
       </c>
-      <c r="C46" s="60"/>
-      <c r="D46" s="60"/>
-      <c r="E46" s="60"/>
-      <c r="F46" s="60"/>
-      <c r="G46" s="60"/>
-      <c r="H46" s="60"/>
-      <c r="I46" s="61"/>
+      <c r="C46" s="127"/>
+      <c r="D46" s="127"/>
+      <c r="E46" s="127"/>
+      <c r="F46" s="127"/>
+      <c r="G46" s="127"/>
+      <c r="H46" s="127"/>
+      <c r="I46" s="128"/>
       <c r="J46" s="10"/>
-      <c r="K46" s="60" t="s">
+      <c r="K46" s="172" t="s">
         <v>28</v>
       </c>
-      <c r="L46" s="60"/>
-      <c r="M46" s="60"/>
-      <c r="N46" s="60"/>
-      <c r="O46" s="60"/>
-      <c r="P46" s="60"/>
-      <c r="Q46" s="60"/>
-      <c r="R46" s="61"/>
-      <c r="S46" s="62" t="s">
+      <c r="L46" s="172"/>
+      <c r="M46" s="172"/>
+      <c r="N46" s="172"/>
+      <c r="O46" s="172"/>
+      <c r="P46" s="172"/>
+      <c r="Q46" s="172"/>
+      <c r="R46" s="173"/>
+      <c r="S46" s="125" t="s">
         <v>78</v>
       </c>
-      <c r="T46" s="63"/>
-      <c r="U46" s="63"/>
-      <c r="V46" s="63"/>
-      <c r="W46" s="63"/>
-      <c r="X46" s="96"/>
-      <c r="Y46" s="96"/>
-      <c r="Z46" s="96"/>
+      <c r="T46" s="71"/>
+      <c r="U46" s="71"/>
+      <c r="V46" s="71"/>
+      <c r="W46" s="71"/>
+      <c r="X46" s="126"/>
+      <c r="Y46" s="126"/>
+      <c r="Z46" s="126"/>
       <c r="AA46" s="12" t="s">
         <v>30</v>
       </c>
-      <c r="AB46" s="87" t="s">
+      <c r="AB46" s="124" t="s">
         <v>80</v>
       </c>
-      <c r="AC46" s="88"/>
-      <c r="AD46" s="88"/>
-      <c r="AE46" s="88"/>
-      <c r="AF46" s="59"/>
-      <c r="AG46" s="59"/>
-      <c r="AH46" s="59"/>
-      <c r="AI46" s="59"/>
+      <c r="AC46" s="76"/>
+      <c r="AD46" s="76"/>
+      <c r="AE46" s="76"/>
+      <c r="AF46" s="151"/>
+      <c r="AG46" s="151"/>
+      <c r="AH46" s="151"/>
+      <c r="AI46" s="151"/>
       <c r="AJ46" s="4"/>
     </row>
     <row r="47" spans="1:36" ht="18" customHeight="1">
       <c r="A47" s="2"/>
-      <c r="B47" s="60" t="s">
+      <c r="B47" s="127" t="s">
         <v>87</v>
       </c>
-      <c r="C47" s="60"/>
-      <c r="D47" s="60"/>
-      <c r="E47" s="60"/>
-      <c r="F47" s="60"/>
-      <c r="G47" s="60"/>
-      <c r="H47" s="60"/>
-      <c r="I47" s="61"/>
+      <c r="C47" s="127"/>
+      <c r="D47" s="127"/>
+      <c r="E47" s="127"/>
+      <c r="F47" s="127"/>
+      <c r="G47" s="127"/>
+      <c r="H47" s="127"/>
+      <c r="I47" s="128"/>
       <c r="J47" s="10"/>
-      <c r="K47" s="60" t="s">
+      <c r="K47" s="172" t="s">
         <v>31</v>
       </c>
-      <c r="L47" s="60"/>
-      <c r="M47" s="60"/>
-      <c r="N47" s="60"/>
-      <c r="O47" s="60"/>
-      <c r="P47" s="60"/>
-      <c r="Q47" s="60"/>
-      <c r="R47" s="61"/>
-      <c r="S47" s="104" t="s">
+      <c r="L47" s="172"/>
+      <c r="M47" s="172"/>
+      <c r="N47" s="172"/>
+      <c r="O47" s="172"/>
+      <c r="P47" s="172"/>
+      <c r="Q47" s="172"/>
+      <c r="R47" s="173"/>
+      <c r="S47" s="129" t="s">
         <v>79</v>
       </c>
-      <c r="T47" s="105"/>
-      <c r="U47" s="105"/>
-      <c r="V47" s="105"/>
-      <c r="W47" s="105"/>
-      <c r="X47" s="64"/>
-      <c r="Y47" s="64"/>
-      <c r="Z47" s="64"/>
+      <c r="T47" s="130"/>
+      <c r="U47" s="130"/>
+      <c r="V47" s="130"/>
+      <c r="W47" s="130"/>
+      <c r="X47" s="146"/>
+      <c r="Y47" s="146"/>
+      <c r="Z47" s="146"/>
       <c r="AA47" s="33" t="s">
         <v>30</v>
       </c>
-      <c r="AB47" s="87" t="s">
+      <c r="AB47" s="124" t="s">
         <v>83</v>
       </c>
-      <c r="AC47" s="88"/>
-      <c r="AD47" s="88"/>
-      <c r="AE47" s="88"/>
-      <c r="AF47" s="77"/>
-      <c r="AG47" s="77"/>
-      <c r="AH47" s="77"/>
-      <c r="AI47" s="77"/>
+      <c r="AC47" s="76"/>
+      <c r="AD47" s="76"/>
+      <c r="AE47" s="76"/>
+      <c r="AF47" s="132"/>
+      <c r="AG47" s="132"/>
+      <c r="AH47" s="132"/>
+      <c r="AI47" s="132"/>
       <c r="AJ47" s="4"/>
     </row>
     <row r="48" spans="1:36" ht="18" customHeight="1">
       <c r="A48" s="34"/>
-      <c r="B48" s="60" t="s">
+      <c r="B48" s="127" t="s">
         <v>33</v>
       </c>
-      <c r="C48" s="60"/>
-      <c r="D48" s="60"/>
-      <c r="E48" s="60"/>
-      <c r="F48" s="60"/>
-      <c r="G48" s="60"/>
-      <c r="H48" s="60"/>
-      <c r="I48" s="61"/>
+      <c r="C48" s="127"/>
+      <c r="D48" s="127"/>
+      <c r="E48" s="127"/>
+      <c r="F48" s="127"/>
+      <c r="G48" s="127"/>
+      <c r="H48" s="127"/>
+      <c r="I48" s="128"/>
       <c r="J48" s="10"/>
-      <c r="K48" s="60" t="s">
+      <c r="K48" s="172" t="s">
         <v>34</v>
       </c>
-      <c r="L48" s="60"/>
-      <c r="M48" s="60"/>
-      <c r="N48" s="60"/>
-      <c r="O48" s="60"/>
-      <c r="P48" s="60"/>
-      <c r="Q48" s="60"/>
-      <c r="R48" s="61"/>
-      <c r="S48" s="93" t="s">
+      <c r="L48" s="172"/>
+      <c r="M48" s="172"/>
+      <c r="N48" s="174"/>
+      <c r="O48" s="172"/>
+      <c r="P48" s="172"/>
+      <c r="Q48" s="172"/>
+      <c r="R48" s="173"/>
+      <c r="S48" s="142" t="s">
         <v>20</v>
       </c>
-      <c r="T48" s="94"/>
-      <c r="U48" s="94"/>
-      <c r="V48" s="94"/>
-      <c r="W48" s="94"/>
-      <c r="X48" s="94"/>
-      <c r="Y48" s="94"/>
-      <c r="Z48" s="94"/>
-      <c r="AA48" s="95"/>
-      <c r="AB48" s="62" t="s">
+      <c r="T48" s="143"/>
+      <c r="U48" s="143"/>
+      <c r="V48" s="143"/>
+      <c r="W48" s="143"/>
+      <c r="X48" s="143"/>
+      <c r="Y48" s="143"/>
+      <c r="Z48" s="143"/>
+      <c r="AA48" s="144"/>
+      <c r="AB48" s="125" t="s">
         <v>78</v>
       </c>
-      <c r="AC48" s="63"/>
-      <c r="AD48" s="63"/>
-      <c r="AE48" s="63"/>
-      <c r="AF48" s="63"/>
-      <c r="AG48" s="96"/>
-      <c r="AH48" s="96"/>
-      <c r="AI48" s="96"/>
+      <c r="AC48" s="71"/>
+      <c r="AD48" s="71"/>
+      <c r="AE48" s="71"/>
+      <c r="AF48" s="71"/>
+      <c r="AG48" s="126"/>
+      <c r="AH48" s="126"/>
+      <c r="AI48" s="126"/>
       <c r="AJ48" s="12" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="49" spans="1:36" ht="18" customHeight="1">
       <c r="A49" s="10"/>
-      <c r="B49" s="60" t="s">
+      <c r="B49" s="127" t="s">
         <v>74</v>
       </c>
-      <c r="C49" s="60"/>
-      <c r="D49" s="60"/>
-      <c r="E49" s="60"/>
-      <c r="F49" s="60"/>
-      <c r="G49" s="60"/>
-      <c r="H49" s="60"/>
-      <c r="I49" s="61"/>
+      <c r="C49" s="127"/>
+      <c r="D49" s="127"/>
+      <c r="E49" s="127"/>
+      <c r="F49" s="127"/>
+      <c r="G49" s="127"/>
+      <c r="H49" s="127"/>
+      <c r="I49" s="128"/>
       <c r="J49" s="10"/>
-      <c r="K49" s="60" t="s">
+      <c r="K49" s="172" t="s">
         <v>37</v>
       </c>
-      <c r="L49" s="60"/>
-      <c r="M49" s="60"/>
-      <c r="N49" s="60"/>
-      <c r="O49" s="60"/>
-      <c r="P49" s="60"/>
-      <c r="Q49" s="60"/>
-      <c r="R49" s="61"/>
+      <c r="L49" s="172"/>
+      <c r="M49" s="172"/>
+      <c r="N49" s="172"/>
+      <c r="O49" s="172"/>
+      <c r="P49" s="172"/>
+      <c r="Q49" s="172"/>
+      <c r="R49" s="173"/>
       <c r="S49" s="10"/>
-      <c r="T49" s="60" t="s">
+      <c r="T49" s="127" t="s">
         <v>23</v>
       </c>
-      <c r="U49" s="60"/>
-      <c r="V49" s="60"/>
-      <c r="W49" s="60"/>
-      <c r="X49" s="60"/>
-      <c r="Y49" s="60"/>
-      <c r="Z49" s="60"/>
-      <c r="AA49" s="61"/>
-      <c r="AB49" s="104" t="s">
+      <c r="U49" s="127"/>
+      <c r="V49" s="127"/>
+      <c r="W49" s="127"/>
+      <c r="X49" s="127"/>
+      <c r="Y49" s="127"/>
+      <c r="Z49" s="127"/>
+      <c r="AA49" s="128"/>
+      <c r="AB49" s="129" t="s">
         <v>79</v>
       </c>
-      <c r="AC49" s="105"/>
-      <c r="AD49" s="105"/>
-      <c r="AE49" s="105"/>
-      <c r="AF49" s="105"/>
-      <c r="AG49" s="64"/>
-      <c r="AH49" s="64"/>
-      <c r="AI49" s="64"/>
+      <c r="AC49" s="130"/>
+      <c r="AD49" s="130"/>
+      <c r="AE49" s="130"/>
+      <c r="AF49" s="130"/>
+      <c r="AG49" s="146"/>
+      <c r="AH49" s="146"/>
+      <c r="AI49" s="146"/>
       <c r="AJ49" s="33" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="50" spans="1:36" ht="18" customHeight="1">
       <c r="A50" s="10"/>
-      <c r="B50" s="60" t="s">
+      <c r="B50" s="127" t="s">
         <v>75</v>
       </c>
-      <c r="C50" s="60"/>
-      <c r="D50" s="60"/>
-      <c r="E50" s="60"/>
-      <c r="F50" s="60"/>
-      <c r="G50" s="60"/>
-      <c r="H50" s="60"/>
-      <c r="I50" s="61"/>
+      <c r="C50" s="127"/>
+      <c r="D50" s="127"/>
+      <c r="E50" s="127"/>
+      <c r="F50" s="127"/>
+      <c r="G50" s="127"/>
+      <c r="H50" s="127"/>
+      <c r="I50" s="128"/>
       <c r="J50" s="10"/>
-      <c r="K50" s="60" t="s">
+      <c r="K50" s="172" t="s">
         <v>39</v>
       </c>
-      <c r="L50" s="60"/>
-      <c r="M50" s="60"/>
-      <c r="N50" s="60"/>
-      <c r="O50" s="60"/>
-      <c r="P50" s="60"/>
-      <c r="Q50" s="60"/>
-      <c r="R50" s="61"/>
+      <c r="L50" s="172"/>
+      <c r="M50" s="172"/>
+      <c r="N50" s="172"/>
+      <c r="O50" s="172"/>
+      <c r="P50" s="172"/>
+      <c r="Q50" s="172"/>
+      <c r="R50" s="173"/>
       <c r="S50" s="10"/>
-      <c r="T50" s="60" t="s">
+      <c r="T50" s="127" t="s">
         <v>26</v>
       </c>
-      <c r="U50" s="60"/>
-      <c r="V50" s="60"/>
-      <c r="W50" s="60"/>
-      <c r="X50" s="60"/>
-      <c r="Y50" s="60"/>
-      <c r="Z50" s="60"/>
-      <c r="AA50" s="61"/>
-      <c r="AB50" s="107" t="s">
+      <c r="U50" s="127"/>
+      <c r="V50" s="127"/>
+      <c r="W50" s="127"/>
+      <c r="X50" s="127"/>
+      <c r="Y50" s="127"/>
+      <c r="Z50" s="127"/>
+      <c r="AA50" s="128"/>
+      <c r="AB50" s="133" t="s">
         <v>38</v>
       </c>
-      <c r="AC50" s="108"/>
-      <c r="AD50" s="108"/>
-      <c r="AE50" s="108"/>
-      <c r="AF50" s="108"/>
-      <c r="AG50" s="108"/>
-      <c r="AH50" s="108"/>
-      <c r="AI50" s="108"/>
-      <c r="AJ50" s="109"/>
+      <c r="AC50" s="134"/>
+      <c r="AD50" s="134"/>
+      <c r="AE50" s="134"/>
+      <c r="AF50" s="134"/>
+      <c r="AG50" s="134"/>
+      <c r="AH50" s="134"/>
+      <c r="AI50" s="134"/>
+      <c r="AJ50" s="135"/>
     </row>
     <row r="51" spans="1:36" ht="18" customHeight="1">
       <c r="A51" s="10"/>
-      <c r="B51" s="60" t="s">
+      <c r="B51" s="127" t="s">
         <v>40</v>
       </c>
-      <c r="C51" s="60"/>
-      <c r="D51" s="60"/>
-      <c r="E51" s="60"/>
-      <c r="F51" s="60"/>
-      <c r="G51" s="60"/>
-      <c r="H51" s="60"/>
-      <c r="I51" s="61"/>
+      <c r="C51" s="127"/>
+      <c r="D51" s="127"/>
+      <c r="E51" s="127"/>
+      <c r="F51" s="127"/>
+      <c r="G51" s="127"/>
+      <c r="H51" s="127"/>
+      <c r="I51" s="128"/>
       <c r="J51" s="10"/>
-      <c r="K51" s="60" t="s">
+      <c r="K51" s="172" t="s">
         <v>41</v>
       </c>
-      <c r="L51" s="60"/>
-      <c r="M51" s="60"/>
-      <c r="N51" s="60"/>
-      <c r="O51" s="60"/>
-      <c r="P51" s="60"/>
-      <c r="Q51" s="60"/>
-      <c r="R51" s="61"/>
+      <c r="L51" s="172"/>
+      <c r="M51" s="172"/>
+      <c r="N51" s="172"/>
+      <c r="O51" s="172"/>
+      <c r="P51" s="172"/>
+      <c r="Q51" s="172"/>
+      <c r="R51" s="173"/>
       <c r="S51" s="10"/>
-      <c r="T51" s="60" t="s">
+      <c r="T51" s="127" t="s">
         <v>29</v>
       </c>
-      <c r="U51" s="60"/>
-      <c r="V51" s="60"/>
-      <c r="W51" s="96"/>
-      <c r="X51" s="96"/>
-      <c r="Y51" s="96"/>
+      <c r="U51" s="127"/>
+      <c r="V51" s="127"/>
+      <c r="W51" s="126"/>
+      <c r="X51" s="126"/>
+      <c r="Y51" s="126"/>
       <c r="Z51" s="3" t="s">
         <v>30</v>
       </c>
       <c r="AA51" s="4"/>
       <c r="AB51" s="10"/>
-      <c r="AC51" s="110" t="s">
+      <c r="AC51" s="136" t="s">
         <v>76</v>
       </c>
-      <c r="AD51" s="110"/>
-      <c r="AE51" s="110"/>
-      <c r="AF51" s="110"/>
-      <c r="AG51" s="110"/>
-      <c r="AH51" s="110"/>
-      <c r="AI51" s="110"/>
-      <c r="AJ51" s="111"/>
+      <c r="AD51" s="136"/>
+      <c r="AE51" s="136"/>
+      <c r="AF51" s="136"/>
+      <c r="AG51" s="136"/>
+      <c r="AH51" s="136"/>
+      <c r="AI51" s="136"/>
+      <c r="AJ51" s="137"/>
     </row>
     <row r="52" spans="1:36" ht="18" customHeight="1">
       <c r="A52" s="10"/>
-      <c r="B52" s="60" t="s">
+      <c r="B52" s="127" t="s">
         <v>43</v>
       </c>
-      <c r="C52" s="60"/>
-      <c r="D52" s="112"/>
-      <c r="E52" s="112"/>
-      <c r="F52" s="112"/>
-      <c r="G52" s="112"/>
-      <c r="H52" s="112"/>
+      <c r="C52" s="127"/>
+      <c r="D52" s="138"/>
+      <c r="E52" s="138"/>
+      <c r="F52" s="138"/>
+      <c r="G52" s="138"/>
+      <c r="H52" s="138"/>
       <c r="I52" s="4"/>
       <c r="J52" s="10"/>
-      <c r="K52" s="60" t="s">
+      <c r="K52" s="172" t="s">
         <v>44</v>
       </c>
-      <c r="L52" s="60"/>
-      <c r="M52" s="60"/>
-      <c r="N52" s="60"/>
-      <c r="O52" s="60"/>
-      <c r="P52" s="60"/>
-      <c r="Q52" s="60"/>
-      <c r="R52" s="61"/>
+      <c r="L52" s="172"/>
+      <c r="M52" s="172"/>
+      <c r="N52" s="172"/>
+      <c r="O52" s="172"/>
+      <c r="P52" s="172"/>
+      <c r="Q52" s="172"/>
+      <c r="R52" s="173"/>
       <c r="S52" s="10"/>
-      <c r="T52" s="60" t="s">
+      <c r="T52" s="127" t="s">
         <v>32</v>
       </c>
-      <c r="U52" s="60"/>
-      <c r="V52" s="60"/>
-      <c r="W52" s="96"/>
-      <c r="X52" s="96"/>
-      <c r="Y52" s="96"/>
+      <c r="U52" s="127"/>
+      <c r="V52" s="127"/>
+      <c r="W52" s="126"/>
+      <c r="X52" s="126"/>
+      <c r="Y52" s="126"/>
       <c r="Z52" s="3" t="s">
         <v>30</v>
       </c>
       <c r="AA52" s="4"/>
       <c r="AB52" s="10"/>
-      <c r="AC52" s="60" t="s">
+      <c r="AC52" s="127" t="s">
         <v>42</v>
       </c>
-      <c r="AD52" s="60"/>
-      <c r="AE52" s="60"/>
-      <c r="AF52" s="60"/>
-      <c r="AG52" s="60"/>
-      <c r="AH52" s="60"/>
-      <c r="AI52" s="60"/>
-      <c r="AJ52" s="61"/>
+      <c r="AD52" s="127"/>
+      <c r="AE52" s="127"/>
+      <c r="AF52" s="127"/>
+      <c r="AG52" s="127"/>
+      <c r="AH52" s="127"/>
+      <c r="AI52" s="127"/>
+      <c r="AJ52" s="128"/>
     </row>
     <row r="53" spans="1:36" ht="18" customHeight="1">
       <c r="A53" s="13"/>
       <c r="B53" s="7"/>
       <c r="C53" s="7"/>
-      <c r="D53" s="101"/>
-      <c r="E53" s="101"/>
-      <c r="F53" s="101"/>
-      <c r="G53" s="101"/>
-      <c r="H53" s="101"/>
+      <c r="D53" s="149"/>
+      <c r="E53" s="149"/>
+      <c r="F53" s="149"/>
+      <c r="G53" s="149"/>
+      <c r="H53" s="149"/>
       <c r="I53" s="8"/>
-      <c r="J53" s="104"/>
-      <c r="K53" s="105"/>
-      <c r="L53" s="105"/>
-      <c r="M53" s="105"/>
-      <c r="N53" s="105"/>
-      <c r="O53" s="105"/>
-      <c r="P53" s="105"/>
-      <c r="Q53" s="105"/>
-      <c r="R53" s="113"/>
+      <c r="J53" s="129"/>
+      <c r="K53" s="130"/>
+      <c r="L53" s="130"/>
+      <c r="M53" s="130"/>
+      <c r="N53" s="130"/>
+      <c r="O53" s="130"/>
+      <c r="P53" s="130"/>
+      <c r="Q53" s="130"/>
+      <c r="R53" s="131"/>
       <c r="S53" s="13"/>
-      <c r="T53" s="97" t="s">
+      <c r="T53" s="145" t="s">
         <v>35</v>
       </c>
-      <c r="U53" s="97"/>
-      <c r="V53" s="97"/>
-      <c r="W53" s="64"/>
-      <c r="X53" s="64"/>
-      <c r="Y53" s="64"/>
+      <c r="U53" s="145"/>
+      <c r="V53" s="145"/>
+      <c r="W53" s="146"/>
+      <c r="X53" s="146"/>
+      <c r="Y53" s="146"/>
       <c r="Z53" s="6" t="s">
         <v>36</v>
       </c>
       <c r="AA53" s="8"/>
       <c r="AB53" s="13"/>
-      <c r="AC53" s="97" t="s">
+      <c r="AC53" s="145" t="s">
         <v>45</v>
       </c>
-      <c r="AD53" s="97"/>
-      <c r="AE53" s="97"/>
-      <c r="AF53" s="106"/>
-      <c r="AG53" s="106"/>
-      <c r="AH53" s="106"/>
+      <c r="AD53" s="145"/>
+      <c r="AE53" s="145"/>
+      <c r="AF53" s="97"/>
+      <c r="AG53" s="97"/>
+      <c r="AH53" s="97"/>
       <c r="AI53" s="7"/>
       <c r="AJ53" s="8"/>
     </row>
     <row r="54" spans="1:36" ht="18" customHeight="1">
-      <c r="A54" s="99" t="s">
+      <c r="A54" s="147" t="s">
         <v>46</v>
       </c>
-      <c r="B54" s="99"/>
-      <c r="C54" s="99"/>
-      <c r="D54" s="99"/>
-      <c r="E54" s="99"/>
-      <c r="F54" s="99"/>
-      <c r="G54" s="99"/>
-      <c r="H54" s="99"/>
-      <c r="I54" s="99"/>
-      <c r="J54" s="99"/>
-      <c r="K54" s="99"/>
-      <c r="L54" s="99"/>
-      <c r="M54" s="99"/>
-      <c r="N54" s="100"/>
-      <c r="O54" s="100"/>
-      <c r="P54" s="100"/>
-      <c r="Q54" s="100"/>
-      <c r="R54" s="100"/>
-      <c r="S54" s="100"/>
-      <c r="T54" s="100"/>
-      <c r="U54" s="100"/>
-      <c r="V54" s="100"/>
-      <c r="W54" s="100"/>
-      <c r="X54" s="100"/>
-      <c r="Y54" s="100"/>
-      <c r="Z54" s="100"/>
-      <c r="AA54" s="100"/>
-      <c r="AB54" s="100"/>
-      <c r="AC54" s="100"/>
-      <c r="AD54" s="100"/>
-      <c r="AE54" s="100"/>
-      <c r="AF54" s="100"/>
-      <c r="AG54" s="100"/>
-      <c r="AH54" s="100"/>
-      <c r="AI54" s="100"/>
-      <c r="AJ54" s="100"/>
+      <c r="B54" s="147"/>
+      <c r="C54" s="147"/>
+      <c r="D54" s="147"/>
+      <c r="E54" s="147"/>
+      <c r="F54" s="147"/>
+      <c r="G54" s="147"/>
+      <c r="H54" s="147"/>
+      <c r="I54" s="147"/>
+      <c r="J54" s="147"/>
+      <c r="K54" s="147"/>
+      <c r="L54" s="147"/>
+      <c r="M54" s="147"/>
+      <c r="N54" s="148"/>
+      <c r="O54" s="148"/>
+      <c r="P54" s="148"/>
+      <c r="Q54" s="148"/>
+      <c r="R54" s="148"/>
+      <c r="S54" s="148"/>
+      <c r="T54" s="148"/>
+      <c r="U54" s="148"/>
+      <c r="V54" s="148"/>
+      <c r="W54" s="148"/>
+      <c r="X54" s="148"/>
+      <c r="Y54" s="148"/>
+      <c r="Z54" s="148"/>
+      <c r="AA54" s="148"/>
+      <c r="AB54" s="148"/>
+      <c r="AC54" s="148"/>
+      <c r="AD54" s="148"/>
+      <c r="AE54" s="148"/>
+      <c r="AF54" s="148"/>
+      <c r="AG54" s="148"/>
+      <c r="AH54" s="148"/>
+      <c r="AI54" s="148"/>
+      <c r="AJ54" s="148"/>
     </row>
     <row r="55" spans="1:36" ht="18" customHeight="1">
-      <c r="A55" s="90"/>
-      <c r="B55" s="98"/>
-      <c r="C55" s="98"/>
-      <c r="D55" s="98"/>
-      <c r="E55" s="98"/>
-      <c r="F55" s="98"/>
-      <c r="G55" s="98"/>
-      <c r="H55" s="98"/>
-      <c r="I55" s="98"/>
-      <c r="J55" s="98"/>
-      <c r="K55" s="98"/>
-      <c r="L55" s="98"/>
-      <c r="N55" s="98"/>
-      <c r="O55" s="98"/>
-      <c r="P55" s="98"/>
-      <c r="Q55" s="98"/>
-      <c r="R55" s="98"/>
-      <c r="S55" s="98"/>
-      <c r="T55" s="98"/>
-      <c r="U55" s="98"/>
-      <c r="V55" s="98"/>
-      <c r="W55" s="98"/>
-      <c r="X55" s="98"/>
-      <c r="Y55" s="90"/>
-      <c r="Z55" s="90"/>
-      <c r="AA55" s="90"/>
-      <c r="AB55" s="102" t="s">
+      <c r="A55" s="140"/>
+      <c r="B55" s="61"/>
+      <c r="C55" s="61"/>
+      <c r="D55" s="61"/>
+      <c r="E55" s="61"/>
+      <c r="F55" s="61"/>
+      <c r="G55" s="61"/>
+      <c r="H55" s="61"/>
+      <c r="I55" s="61"/>
+      <c r="J55" s="61"/>
+      <c r="K55" s="61"/>
+      <c r="L55" s="61"/>
+      <c r="N55" s="61"/>
+      <c r="O55" s="61"/>
+      <c r="P55" s="61"/>
+      <c r="Q55" s="61"/>
+      <c r="R55" s="61"/>
+      <c r="S55" s="61"/>
+      <c r="T55" s="61"/>
+      <c r="U55" s="61"/>
+      <c r="V55" s="61"/>
+      <c r="W55" s="61"/>
+      <c r="X55" s="61"/>
+      <c r="Y55" s="140"/>
+      <c r="Z55" s="140"/>
+      <c r="AA55" s="140"/>
+      <c r="AB55" s="150" t="s">
         <v>93</v>
       </c>
-      <c r="AC55" s="103"/>
-      <c r="AD55" s="103"/>
-      <c r="AE55" s="103"/>
-      <c r="AF55" s="103"/>
-      <c r="AG55" s="103"/>
-      <c r="AH55" s="103"/>
-      <c r="AI55" s="103"/>
-      <c r="AJ55" s="103"/>
+      <c r="AC55" s="96"/>
+      <c r="AD55" s="96"/>
+      <c r="AE55" s="96"/>
+      <c r="AF55" s="96"/>
+      <c r="AG55" s="96"/>
+      <c r="AH55" s="96"/>
+      <c r="AI55" s="96"/>
+      <c r="AJ55" s="96"/>
     </row>
     <row r="56" spans="1:36" ht="18" customHeight="1">
-      <c r="A56" s="90"/>
-      <c r="B56" s="98"/>
-      <c r="C56" s="98"/>
-      <c r="D56" s="98"/>
-      <c r="E56" s="98"/>
-      <c r="F56" s="98"/>
-      <c r="G56" s="98"/>
-      <c r="H56" s="98"/>
-      <c r="I56" s="98"/>
-      <c r="J56" s="98"/>
-      <c r="K56" s="98"/>
-      <c r="L56" s="98"/>
-      <c r="N56" s="98"/>
-      <c r="O56" s="98"/>
-      <c r="P56" s="98"/>
-      <c r="Q56" s="98"/>
-      <c r="R56" s="98"/>
-      <c r="S56" s="98"/>
-      <c r="T56" s="98"/>
-      <c r="U56" s="98"/>
-      <c r="V56" s="98"/>
-      <c r="W56" s="98"/>
-      <c r="X56" s="98"/>
-      <c r="Y56" s="90"/>
-      <c r="Z56" s="90"/>
-      <c r="AA56" s="90"/>
-      <c r="AB56" s="92" t="s">
+      <c r="A56" s="140"/>
+      <c r="B56" s="61"/>
+      <c r="C56" s="61"/>
+      <c r="D56" s="61"/>
+      <c r="E56" s="61"/>
+      <c r="F56" s="61"/>
+      <c r="G56" s="61"/>
+      <c r="H56" s="61"/>
+      <c r="I56" s="61"/>
+      <c r="J56" s="61"/>
+      <c r="K56" s="61"/>
+      <c r="L56" s="61"/>
+      <c r="N56" s="61"/>
+      <c r="O56" s="61"/>
+      <c r="P56" s="61"/>
+      <c r="Q56" s="61"/>
+      <c r="R56" s="61"/>
+      <c r="S56" s="61"/>
+      <c r="T56" s="61"/>
+      <c r="U56" s="61"/>
+      <c r="V56" s="61"/>
+      <c r="W56" s="61"/>
+      <c r="X56" s="61"/>
+      <c r="Y56" s="140"/>
+      <c r="Z56" s="140"/>
+      <c r="AA56" s="140"/>
+      <c r="AB56" s="141" t="s">
         <v>47</v>
       </c>
-      <c r="AC56" s="92"/>
-      <c r="AD56" s="92"/>
-      <c r="AE56" s="92"/>
-      <c r="AF56" s="92"/>
-      <c r="AG56" s="92"/>
-      <c r="AH56" s="92"/>
-      <c r="AI56" s="92"/>
-      <c r="AJ56" s="92"/>
+      <c r="AC56" s="141"/>
+      <c r="AD56" s="141"/>
+      <c r="AE56" s="141"/>
+      <c r="AF56" s="141"/>
+      <c r="AG56" s="141"/>
+      <c r="AH56" s="141"/>
+      <c r="AI56" s="141"/>
+      <c r="AJ56" s="141"/>
     </row>
     <row r="57" spans="1:36" ht="18" customHeight="1">
-      <c r="A57" s="90"/>
-      <c r="B57" s="98"/>
-      <c r="C57" s="98"/>
-      <c r="D57" s="98"/>
-      <c r="E57" s="98"/>
-      <c r="F57" s="98"/>
-      <c r="G57" s="98"/>
-      <c r="H57" s="98"/>
-      <c r="I57" s="98"/>
-      <c r="J57" s="98"/>
-      <c r="K57" s="98"/>
-      <c r="L57" s="98"/>
-      <c r="N57" s="98"/>
-      <c r="O57" s="98"/>
-      <c r="P57" s="98"/>
-      <c r="Q57" s="98"/>
-      <c r="R57" s="98"/>
-      <c r="S57" s="98"/>
-      <c r="T57" s="98"/>
-      <c r="U57" s="98"/>
-      <c r="V57" s="98"/>
-      <c r="W57" s="98"/>
-      <c r="X57" s="98"/>
-      <c r="Y57" s="90"/>
-      <c r="Z57" s="90"/>
-      <c r="AA57" s="90"/>
-      <c r="AB57" s="90"/>
-      <c r="AC57" s="90"/>
-      <c r="AD57" s="90"/>
-      <c r="AE57" s="90"/>
-      <c r="AF57" s="90"/>
-      <c r="AG57" s="90"/>
-      <c r="AH57" s="90"/>
-      <c r="AI57" s="90"/>
-      <c r="AJ57" s="90"/>
+      <c r="A57" s="140"/>
+      <c r="B57" s="61"/>
+      <c r="C57" s="61"/>
+      <c r="D57" s="61"/>
+      <c r="E57" s="61"/>
+      <c r="F57" s="61"/>
+      <c r="G57" s="61"/>
+      <c r="H57" s="61"/>
+      <c r="I57" s="61"/>
+      <c r="J57" s="61"/>
+      <c r="K57" s="61"/>
+      <c r="L57" s="61"/>
+      <c r="N57" s="61"/>
+      <c r="O57" s="61"/>
+      <c r="P57" s="61"/>
+      <c r="Q57" s="61"/>
+      <c r="R57" s="61"/>
+      <c r="S57" s="61"/>
+      <c r="T57" s="61"/>
+      <c r="U57" s="61"/>
+      <c r="V57" s="61"/>
+      <c r="W57" s="61"/>
+      <c r="X57" s="61"/>
+      <c r="Y57" s="140"/>
+      <c r="Z57" s="140"/>
+      <c r="AA57" s="140"/>
+      <c r="AB57" s="140"/>
+      <c r="AC57" s="140"/>
+      <c r="AD57" s="140"/>
+      <c r="AE57" s="140"/>
+      <c r="AF57" s="140"/>
+      <c r="AG57" s="140"/>
+      <c r="AH57" s="140"/>
+      <c r="AI57" s="140"/>
+      <c r="AJ57" s="140"/>
     </row>
     <row r="58" spans="1:36" ht="18" customHeight="1">
       <c r="A58" s="51"/>
@@ -9372,72 +9381,72 @@
       <c r="V58" s="52"/>
       <c r="W58" s="52"/>
       <c r="X58" s="52"/>
-      <c r="Y58" s="90"/>
-      <c r="Z58" s="90"/>
-      <c r="AA58" s="90"/>
-      <c r="AB58" s="90"/>
-      <c r="AC58" s="90"/>
-      <c r="AD58" s="90"/>
-      <c r="AE58" s="90"/>
-      <c r="AF58" s="90"/>
-      <c r="AG58" s="90"/>
-      <c r="AH58" s="90"/>
-      <c r="AI58" s="90"/>
-      <c r="AJ58" s="90"/>
+      <c r="Y58" s="140"/>
+      <c r="Z58" s="140"/>
+      <c r="AA58" s="140"/>
+      <c r="AB58" s="140"/>
+      <c r="AC58" s="140"/>
+      <c r="AD58" s="140"/>
+      <c r="AE58" s="140"/>
+      <c r="AF58" s="140"/>
+      <c r="AG58" s="140"/>
+      <c r="AH58" s="140"/>
+      <c r="AI58" s="140"/>
+      <c r="AJ58" s="140"/>
     </row>
     <row r="59" spans="1:36" ht="18" customHeight="1">
-      <c r="A59" s="90"/>
-      <c r="B59" s="90"/>
-      <c r="C59" s="90"/>
-      <c r="D59" s="90"/>
-      <c r="E59" s="90"/>
-      <c r="F59" s="90"/>
-      <c r="G59" s="90"/>
-      <c r="H59" s="90"/>
-      <c r="I59" s="90"/>
-      <c r="J59" s="90"/>
-      <c r="K59" s="90"/>
-      <c r="L59" s="90"/>
-      <c r="M59" s="90"/>
-      <c r="N59" s="90"/>
-      <c r="O59" s="90"/>
-      <c r="P59" s="90"/>
-      <c r="Q59" s="90"/>
-      <c r="R59" s="90"/>
-      <c r="S59" s="90"/>
-      <c r="T59" s="90"/>
-      <c r="U59" s="90"/>
-      <c r="V59" s="90"/>
-      <c r="W59" s="90"/>
-      <c r="X59" s="90"/>
-      <c r="Y59" s="90"/>
-      <c r="Z59" s="90"/>
-      <c r="AA59" s="90"/>
-      <c r="AB59" s="91"/>
-      <c r="AC59" s="91"/>
-      <c r="AD59" s="91"/>
-      <c r="AE59" s="91"/>
-      <c r="AF59" s="91"/>
-      <c r="AG59" s="91"/>
-      <c r="AH59" s="91"/>
-      <c r="AI59" s="91"/>
-      <c r="AJ59" s="91"/>
+      <c r="A59" s="140"/>
+      <c r="B59" s="140"/>
+      <c r="C59" s="140"/>
+      <c r="D59" s="140"/>
+      <c r="E59" s="140"/>
+      <c r="F59" s="140"/>
+      <c r="G59" s="140"/>
+      <c r="H59" s="140"/>
+      <c r="I59" s="140"/>
+      <c r="J59" s="140"/>
+      <c r="K59" s="140"/>
+      <c r="L59" s="140"/>
+      <c r="M59" s="140"/>
+      <c r="N59" s="140"/>
+      <c r="O59" s="140"/>
+      <c r="P59" s="140"/>
+      <c r="Q59" s="140"/>
+      <c r="R59" s="140"/>
+      <c r="S59" s="140"/>
+      <c r="T59" s="140"/>
+      <c r="U59" s="140"/>
+      <c r="V59" s="140"/>
+      <c r="W59" s="140"/>
+      <c r="X59" s="140"/>
+      <c r="Y59" s="140"/>
+      <c r="Z59" s="140"/>
+      <c r="AA59" s="140"/>
+      <c r="AB59" s="77"/>
+      <c r="AC59" s="77"/>
+      <c r="AD59" s="77"/>
+      <c r="AE59" s="77"/>
+      <c r="AF59" s="77"/>
+      <c r="AG59" s="77"/>
+      <c r="AH59" s="77"/>
+      <c r="AI59" s="77"/>
+      <c r="AJ59" s="77"/>
     </row>
     <row r="60" spans="1:36" ht="18" customHeight="1">
-      <c r="Y60" s="90"/>
-      <c r="Z60" s="90"/>
-      <c r="AA60" s="90"/>
-      <c r="AB60" s="89" t="s">
+      <c r="Y60" s="140"/>
+      <c r="Z60" s="140"/>
+      <c r="AA60" s="140"/>
+      <c r="AB60" s="139" t="s">
         <v>92</v>
       </c>
-      <c r="AC60" s="89"/>
-      <c r="AD60" s="89"/>
-      <c r="AE60" s="89"/>
-      <c r="AF60" s="89"/>
-      <c r="AG60" s="89"/>
-      <c r="AH60" s="89"/>
-      <c r="AI60" s="89"/>
-      <c r="AJ60" s="89"/>
+      <c r="AC60" s="139"/>
+      <c r="AD60" s="139"/>
+      <c r="AE60" s="139"/>
+      <c r="AF60" s="139"/>
+      <c r="AG60" s="139"/>
+      <c r="AH60" s="139"/>
+      <c r="AI60" s="139"/>
+      <c r="AJ60" s="139"/>
     </row>
     <row r="61" spans="1:36" ht="16.5" customHeight="1"/>
     <row r="62" spans="1:36" ht="18" hidden="1" customHeight="1"/>
@@ -10038,31 +10047,77 @@
     <row r="657"/>
     <row r="658"/>
   </sheetData>
-  <mergeCells count="126">
-    <mergeCell ref="S8:W8"/>
-    <mergeCell ref="X7:AB7"/>
-    <mergeCell ref="B57:L57"/>
-    <mergeCell ref="N57:X57"/>
-    <mergeCell ref="Q2:Z2"/>
-    <mergeCell ref="Q3:Z3"/>
-    <mergeCell ref="A11:P11"/>
-    <mergeCell ref="K5:O5"/>
-    <mergeCell ref="K6:O6"/>
-    <mergeCell ref="P6:X6"/>
-    <mergeCell ref="A41:R41"/>
-    <mergeCell ref="S9:W9"/>
-    <mergeCell ref="A7:B7"/>
-    <mergeCell ref="Q11:AJ11"/>
-    <mergeCell ref="C7:I7"/>
-    <mergeCell ref="D8:R8"/>
-    <mergeCell ref="A8:C8"/>
-    <mergeCell ref="X8:AJ8"/>
-    <mergeCell ref="A10:AJ10"/>
-    <mergeCell ref="A5:B5"/>
-    <mergeCell ref="A6:B6"/>
-    <mergeCell ref="D9:R9"/>
-    <mergeCell ref="K7:O7"/>
-    <mergeCell ref="A25:AJ25"/>
+  <mergeCells count="110">
+    <mergeCell ref="X47:Z47"/>
+    <mergeCell ref="AG49:AI49"/>
+    <mergeCell ref="W45:Z45"/>
+    <mergeCell ref="T51:V51"/>
+    <mergeCell ref="A27:AJ29"/>
+    <mergeCell ref="A36:R36"/>
+    <mergeCell ref="B47:I47"/>
+    <mergeCell ref="S43:AA43"/>
+    <mergeCell ref="B51:I51"/>
+    <mergeCell ref="AF44:AI44"/>
+    <mergeCell ref="A30:O30"/>
+    <mergeCell ref="B44:I44"/>
+    <mergeCell ref="AB43:AJ43"/>
+    <mergeCell ref="J43:R43"/>
+    <mergeCell ref="W44:Y44"/>
+    <mergeCell ref="A31:AJ35"/>
+    <mergeCell ref="A37:AJ40"/>
+    <mergeCell ref="B45:I45"/>
+    <mergeCell ref="AB47:AE47"/>
+    <mergeCell ref="B46:I46"/>
+    <mergeCell ref="AB60:AJ60"/>
+    <mergeCell ref="AB57:AJ59"/>
+    <mergeCell ref="AB56:AJ56"/>
+    <mergeCell ref="S48:AA48"/>
+    <mergeCell ref="AG48:AI48"/>
+    <mergeCell ref="AC53:AE53"/>
+    <mergeCell ref="T52:V52"/>
+    <mergeCell ref="W53:Y53"/>
+    <mergeCell ref="B56:L56"/>
+    <mergeCell ref="N56:X56"/>
+    <mergeCell ref="Y55:AA60"/>
+    <mergeCell ref="A59:X59"/>
+    <mergeCell ref="A55:A57"/>
+    <mergeCell ref="N55:X55"/>
+    <mergeCell ref="A54:M54"/>
+    <mergeCell ref="N54:AJ54"/>
+    <mergeCell ref="D53:H53"/>
+    <mergeCell ref="B50:I50"/>
+    <mergeCell ref="B55:L55"/>
+    <mergeCell ref="T53:V53"/>
+    <mergeCell ref="AB55:AJ55"/>
+    <mergeCell ref="W51:Y51"/>
+    <mergeCell ref="AC52:AJ52"/>
+    <mergeCell ref="J53:R53"/>
+    <mergeCell ref="AB45:AE45"/>
+    <mergeCell ref="B48:I48"/>
+    <mergeCell ref="AF47:AI47"/>
+    <mergeCell ref="AB49:AF49"/>
+    <mergeCell ref="AF53:AH53"/>
+    <mergeCell ref="AB50:AJ50"/>
+    <mergeCell ref="AC51:AJ51"/>
+    <mergeCell ref="B49:I49"/>
+    <mergeCell ref="B52:C52"/>
+    <mergeCell ref="D52:H52"/>
+    <mergeCell ref="S47:W47"/>
+    <mergeCell ref="T49:AA49"/>
+    <mergeCell ref="W52:Y52"/>
+    <mergeCell ref="AF46:AI46"/>
+    <mergeCell ref="T50:AA50"/>
+    <mergeCell ref="AF45:AI45"/>
+    <mergeCell ref="AB48:AF48"/>
+    <mergeCell ref="AI7:AJ7"/>
+    <mergeCell ref="C6:I6"/>
+    <mergeCell ref="AB46:AE46"/>
+    <mergeCell ref="S44:V44"/>
+    <mergeCell ref="S45:V45"/>
+    <mergeCell ref="S46:W46"/>
+    <mergeCell ref="X46:Z46"/>
+    <mergeCell ref="AB44:AE44"/>
+    <mergeCell ref="D9:H9"/>
     <mergeCell ref="AD3:AJ3"/>
     <mergeCell ref="Y5:Z5"/>
     <mergeCell ref="A22:AJ23"/>
@@ -10083,88 +10138,26 @@
     <mergeCell ref="U16:AD16"/>
     <mergeCell ref="AE16:AJ16"/>
     <mergeCell ref="A16:T16"/>
-    <mergeCell ref="A9:C9"/>
     <mergeCell ref="X9:AJ9"/>
     <mergeCell ref="P7:T7"/>
     <mergeCell ref="P5:X5"/>
-    <mergeCell ref="AI7:AJ7"/>
-    <mergeCell ref="C6:I6"/>
-    <mergeCell ref="AB46:AE46"/>
-    <mergeCell ref="S44:V44"/>
-    <mergeCell ref="S45:V45"/>
-    <mergeCell ref="S46:W46"/>
-    <mergeCell ref="X46:Z46"/>
-    <mergeCell ref="K46:R46"/>
-    <mergeCell ref="K45:R45"/>
-    <mergeCell ref="AB44:AE44"/>
-    <mergeCell ref="J53:R53"/>
-    <mergeCell ref="AB45:AE45"/>
-    <mergeCell ref="K44:R44"/>
-    <mergeCell ref="B48:I48"/>
-    <mergeCell ref="AF47:AI47"/>
-    <mergeCell ref="AB49:AF49"/>
-    <mergeCell ref="AF53:AH53"/>
-    <mergeCell ref="AB50:AJ50"/>
-    <mergeCell ref="AC51:AJ51"/>
-    <mergeCell ref="B49:I49"/>
-    <mergeCell ref="B52:C52"/>
-    <mergeCell ref="D52:H52"/>
-    <mergeCell ref="K50:R50"/>
-    <mergeCell ref="K51:R51"/>
-    <mergeCell ref="S47:W47"/>
-    <mergeCell ref="T49:AA49"/>
-    <mergeCell ref="K48:R48"/>
-    <mergeCell ref="K49:R49"/>
-    <mergeCell ref="W52:Y52"/>
-    <mergeCell ref="K47:R47"/>
-    <mergeCell ref="AB60:AJ60"/>
-    <mergeCell ref="AB57:AJ59"/>
-    <mergeCell ref="AB56:AJ56"/>
-    <mergeCell ref="S48:AA48"/>
-    <mergeCell ref="AG48:AI48"/>
-    <mergeCell ref="AC53:AE53"/>
-    <mergeCell ref="T52:V52"/>
-    <mergeCell ref="W53:Y53"/>
-    <mergeCell ref="B56:L56"/>
-    <mergeCell ref="N56:X56"/>
-    <mergeCell ref="Y55:AA60"/>
-    <mergeCell ref="A59:X59"/>
-    <mergeCell ref="A55:A57"/>
-    <mergeCell ref="N55:X55"/>
-    <mergeCell ref="A54:M54"/>
-    <mergeCell ref="N54:AJ54"/>
-    <mergeCell ref="D53:H53"/>
-    <mergeCell ref="B50:I50"/>
-    <mergeCell ref="B55:L55"/>
-    <mergeCell ref="K52:R52"/>
-    <mergeCell ref="T53:V53"/>
-    <mergeCell ref="AB55:AJ55"/>
-    <mergeCell ref="W51:Y51"/>
-    <mergeCell ref="AC52:AJ52"/>
-    <mergeCell ref="AF46:AI46"/>
-    <mergeCell ref="T50:AA50"/>
-    <mergeCell ref="AF45:AI45"/>
-    <mergeCell ref="AB48:AF48"/>
-    <mergeCell ref="X47:Z47"/>
-    <mergeCell ref="AG49:AI49"/>
-    <mergeCell ref="W45:Z45"/>
-    <mergeCell ref="T51:V51"/>
-    <mergeCell ref="A27:AJ29"/>
-    <mergeCell ref="A36:R36"/>
-    <mergeCell ref="B47:I47"/>
-    <mergeCell ref="S43:AA43"/>
-    <mergeCell ref="B51:I51"/>
-    <mergeCell ref="AF44:AI44"/>
-    <mergeCell ref="A30:O30"/>
-    <mergeCell ref="B44:I44"/>
-    <mergeCell ref="AB43:AJ43"/>
-    <mergeCell ref="J43:R43"/>
-    <mergeCell ref="W44:Y44"/>
-    <mergeCell ref="A31:AJ35"/>
-    <mergeCell ref="A37:AJ40"/>
-    <mergeCell ref="B45:I45"/>
-    <mergeCell ref="AB47:AE47"/>
-    <mergeCell ref="B46:I46"/>
+    <mergeCell ref="X7:AB7"/>
+    <mergeCell ref="B57:L57"/>
+    <mergeCell ref="N57:X57"/>
+    <mergeCell ref="Q2:Z2"/>
+    <mergeCell ref="Q3:Z3"/>
+    <mergeCell ref="A11:P11"/>
+    <mergeCell ref="K5:O5"/>
+    <mergeCell ref="K6:O6"/>
+    <mergeCell ref="P6:X6"/>
+    <mergeCell ref="A41:R41"/>
+    <mergeCell ref="Q11:AJ11"/>
+    <mergeCell ref="C7:I7"/>
+    <mergeCell ref="D8:R8"/>
+    <mergeCell ref="X8:AJ8"/>
+    <mergeCell ref="A10:AJ10"/>
+    <mergeCell ref="K7:O7"/>
+    <mergeCell ref="A25:AJ25"/>
   </mergeCells>
   <phoneticPr fontId="0" type="noConversion"/>
   <printOptions horizontalCentered="1"/>

--- a/backend_api/templates/container_report_template.xlsx
+++ b/backend_api/templates/container_report_template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Aaron Avila\Documents\ERP-SOM\backend_api\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CAF798A8-DA6F-4DD5-B264-F1CD97FB3CC6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B6EF17F4-6005-40DD-ABD8-4A3DB26165A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-1125" windowWidth="29040" windowHeight="15720" xr2:uid="{253FFB1B-D348-46B1-A532-0D44566D2FFD}"/>
   </bookViews>
@@ -1100,7 +1100,7 @@
     <numFmt numFmtId="164" formatCode="dd\-mmm\-yyyy"/>
     <numFmt numFmtId="165" formatCode="h:mm;@"/>
   </numFmts>
-  <fonts count="31">
+  <fonts count="30">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -1251,11 +1251,6 @@
       <sz val="8"/>
       <color indexed="53"/>
       <name val="Tahoma"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <name val="Arial"/>
       <family val="2"/>
     </font>
     <font>
@@ -1411,7 +1406,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="176">
+  <cellXfs count="171">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -1520,15 +1515,10 @@
     <xf numFmtId="0" fontId="7" fillId="2" borderId="6" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="9" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="2" borderId="7" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="14" fontId="13" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left"/>
-      <protection locked="0"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1555,395 +1545,393 @@
     <xf numFmtId="165" fontId="13" fillId="0" borderId="8" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyProtection="1">
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="4" fontId="13" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="4" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="9" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="6" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="2" borderId="9" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="14" fontId="13" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="3" fontId="13" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="165" fontId="13" fillId="0" borderId="8" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left"/>
       <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="8" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="9" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="6" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="2" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="3" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="4" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="5" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="3" fontId="13" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="9" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="6" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="6" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="6" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="165" fontId="13" fillId="0" borderId="8" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="2" borderId="9" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="2" borderId="6" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="2" borderId="7" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" wrapText="1"/>
+      <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="4" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="8" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1" applyProtection="1">
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="2" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="3" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="4" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="5" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="3" fontId="13" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="13" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="9" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="6" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="6" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="6" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="165" fontId="13" fillId="0" borderId="8" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="2" borderId="9" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="2" borderId="6" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="2" borderId="7" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="165" fontId="13" fillId="0" borderId="8" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="4" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="4" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="4" fontId="13" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="4" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="2" borderId="9" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="14" fontId="13" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
   </cellXfs>
@@ -2246,9 +2234,9 @@
         </xdr:from>
         <xdr:to>
           <xdr:col>1</xdr:col>
-          <xdr:colOff>53340</xdr:colOff>
+          <xdr:colOff>57150</xdr:colOff>
           <xdr:row>12</xdr:row>
-          <xdr:rowOff>19050</xdr:rowOff>
+          <xdr:rowOff>15240</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -2313,9 +2301,9 @@
         </xdr:from>
         <xdr:to>
           <xdr:col>1</xdr:col>
-          <xdr:colOff>53340</xdr:colOff>
+          <xdr:colOff>57150</xdr:colOff>
           <xdr:row>13</xdr:row>
-          <xdr:rowOff>19050</xdr:rowOff>
+          <xdr:rowOff>15240</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -2380,9 +2368,9 @@
         </xdr:from>
         <xdr:to>
           <xdr:col>5</xdr:col>
-          <xdr:colOff>53340</xdr:colOff>
+          <xdr:colOff>57150</xdr:colOff>
           <xdr:row>12</xdr:row>
-          <xdr:rowOff>19050</xdr:rowOff>
+          <xdr:rowOff>15240</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -2447,9 +2435,9 @@
         </xdr:from>
         <xdr:to>
           <xdr:col>5</xdr:col>
-          <xdr:colOff>53340</xdr:colOff>
+          <xdr:colOff>57150</xdr:colOff>
           <xdr:row>13</xdr:row>
-          <xdr:rowOff>19050</xdr:rowOff>
+          <xdr:rowOff>15240</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -2516,7 +2504,7 @@
           <xdr:col>9</xdr:col>
           <xdr:colOff>114300</xdr:colOff>
           <xdr:row>12</xdr:row>
-          <xdr:rowOff>19050</xdr:rowOff>
+          <xdr:rowOff>15240</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -2583,7 +2571,7 @@
           <xdr:col>9</xdr:col>
           <xdr:colOff>114300</xdr:colOff>
           <xdr:row>13</xdr:row>
-          <xdr:rowOff>19050</xdr:rowOff>
+          <xdr:rowOff>15240</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -2648,9 +2636,9 @@
         </xdr:from>
         <xdr:to>
           <xdr:col>14</xdr:col>
-          <xdr:colOff>57150</xdr:colOff>
+          <xdr:colOff>53340</xdr:colOff>
           <xdr:row>12</xdr:row>
-          <xdr:rowOff>19050</xdr:rowOff>
+          <xdr:rowOff>15240</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -2715,9 +2703,9 @@
         </xdr:from>
         <xdr:to>
           <xdr:col>14</xdr:col>
-          <xdr:colOff>57150</xdr:colOff>
+          <xdr:colOff>53340</xdr:colOff>
           <xdr:row>13</xdr:row>
-          <xdr:rowOff>19050</xdr:rowOff>
+          <xdr:rowOff>15240</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -2782,9 +2770,9 @@
         </xdr:from>
         <xdr:to>
           <xdr:col>17</xdr:col>
-          <xdr:colOff>57150</xdr:colOff>
+          <xdr:colOff>53340</xdr:colOff>
           <xdr:row>12</xdr:row>
-          <xdr:rowOff>19050</xdr:rowOff>
+          <xdr:rowOff>15240</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -2849,9 +2837,9 @@
         </xdr:from>
         <xdr:to>
           <xdr:col>17</xdr:col>
-          <xdr:colOff>57150</xdr:colOff>
+          <xdr:colOff>53340</xdr:colOff>
           <xdr:row>13</xdr:row>
-          <xdr:rowOff>19050</xdr:rowOff>
+          <xdr:rowOff>15240</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -2916,9 +2904,9 @@
         </xdr:from>
         <xdr:to>
           <xdr:col>23</xdr:col>
-          <xdr:colOff>57150</xdr:colOff>
+          <xdr:colOff>53340</xdr:colOff>
           <xdr:row>12</xdr:row>
-          <xdr:rowOff>19050</xdr:rowOff>
+          <xdr:rowOff>15240</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -2983,9 +2971,9 @@
         </xdr:from>
         <xdr:to>
           <xdr:col>23</xdr:col>
-          <xdr:colOff>57150</xdr:colOff>
+          <xdr:colOff>53340</xdr:colOff>
           <xdr:row>13</xdr:row>
-          <xdr:rowOff>19050</xdr:rowOff>
+          <xdr:rowOff>15240</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -3050,9 +3038,9 @@
         </xdr:from>
         <xdr:to>
           <xdr:col>28</xdr:col>
-          <xdr:colOff>57150</xdr:colOff>
+          <xdr:colOff>53340</xdr:colOff>
           <xdr:row>12</xdr:row>
-          <xdr:rowOff>19050</xdr:rowOff>
+          <xdr:rowOff>15240</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -3117,9 +3105,9 @@
         </xdr:from>
         <xdr:to>
           <xdr:col>28</xdr:col>
-          <xdr:colOff>57150</xdr:colOff>
+          <xdr:colOff>53340</xdr:colOff>
           <xdr:row>13</xdr:row>
-          <xdr:rowOff>19050</xdr:rowOff>
+          <xdr:rowOff>15240</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -3186,7 +3174,7 @@
           <xdr:col>32</xdr:col>
           <xdr:colOff>342900</xdr:colOff>
           <xdr:row>12</xdr:row>
-          <xdr:rowOff>19050</xdr:rowOff>
+          <xdr:rowOff>15240</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -3253,7 +3241,7 @@
           <xdr:col>32</xdr:col>
           <xdr:colOff>342900</xdr:colOff>
           <xdr:row>13</xdr:row>
-          <xdr:rowOff>19050</xdr:rowOff>
+          <xdr:rowOff>15240</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -3318,9 +3306,9 @@
         </xdr:from>
         <xdr:to>
           <xdr:col>21</xdr:col>
-          <xdr:colOff>95250</xdr:colOff>
+          <xdr:colOff>91440</xdr:colOff>
           <xdr:row>17</xdr:row>
-          <xdr:rowOff>19050</xdr:rowOff>
+          <xdr:rowOff>15240</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -3385,9 +3373,9 @@
         </xdr:from>
         <xdr:to>
           <xdr:col>21</xdr:col>
-          <xdr:colOff>95250</xdr:colOff>
+          <xdr:colOff>91440</xdr:colOff>
           <xdr:row>18</xdr:row>
-          <xdr:rowOff>19050</xdr:rowOff>
+          <xdr:rowOff>15240</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -3452,9 +3440,9 @@
         </xdr:from>
         <xdr:to>
           <xdr:col>21</xdr:col>
-          <xdr:colOff>95250</xdr:colOff>
+          <xdr:colOff>91440</xdr:colOff>
           <xdr:row>19</xdr:row>
-          <xdr:rowOff>19050</xdr:rowOff>
+          <xdr:rowOff>15240</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -3519,9 +3507,9 @@
         </xdr:from>
         <xdr:to>
           <xdr:col>25</xdr:col>
-          <xdr:colOff>95250</xdr:colOff>
+          <xdr:colOff>91440</xdr:colOff>
           <xdr:row>17</xdr:row>
-          <xdr:rowOff>19050</xdr:rowOff>
+          <xdr:rowOff>15240</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -3586,9 +3574,9 @@
         </xdr:from>
         <xdr:to>
           <xdr:col>25</xdr:col>
-          <xdr:colOff>95250</xdr:colOff>
+          <xdr:colOff>91440</xdr:colOff>
           <xdr:row>18</xdr:row>
-          <xdr:rowOff>19050</xdr:rowOff>
+          <xdr:rowOff>15240</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -3653,9 +3641,9 @@
         </xdr:from>
         <xdr:to>
           <xdr:col>25</xdr:col>
-          <xdr:colOff>95250</xdr:colOff>
+          <xdr:colOff>91440</xdr:colOff>
           <xdr:row>19</xdr:row>
-          <xdr:rowOff>19050</xdr:rowOff>
+          <xdr:rowOff>15240</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -3720,9 +3708,9 @@
         </xdr:from>
         <xdr:to>
           <xdr:col>28</xdr:col>
-          <xdr:colOff>95250</xdr:colOff>
+          <xdr:colOff>91440</xdr:colOff>
           <xdr:row>17</xdr:row>
-          <xdr:rowOff>19050</xdr:rowOff>
+          <xdr:rowOff>15240</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -3787,9 +3775,9 @@
         </xdr:from>
         <xdr:to>
           <xdr:col>28</xdr:col>
-          <xdr:colOff>95250</xdr:colOff>
+          <xdr:colOff>91440</xdr:colOff>
           <xdr:row>18</xdr:row>
-          <xdr:rowOff>19050</xdr:rowOff>
+          <xdr:rowOff>15240</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -3854,9 +3842,9 @@
         </xdr:from>
         <xdr:to>
           <xdr:col>28</xdr:col>
-          <xdr:colOff>95250</xdr:colOff>
+          <xdr:colOff>91440</xdr:colOff>
           <xdr:row>19</xdr:row>
-          <xdr:rowOff>19050</xdr:rowOff>
+          <xdr:rowOff>15240</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -3921,9 +3909,9 @@
         </xdr:from>
         <xdr:to>
           <xdr:col>1</xdr:col>
-          <xdr:colOff>91440</xdr:colOff>
+          <xdr:colOff>95250</xdr:colOff>
           <xdr:row>44</xdr:row>
-          <xdr:rowOff>19050</xdr:rowOff>
+          <xdr:rowOff>15240</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -3988,9 +3976,9 @@
         </xdr:from>
         <xdr:to>
           <xdr:col>1</xdr:col>
-          <xdr:colOff>91440</xdr:colOff>
+          <xdr:colOff>95250</xdr:colOff>
           <xdr:row>45</xdr:row>
-          <xdr:rowOff>19050</xdr:rowOff>
+          <xdr:rowOff>15240</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -4055,9 +4043,9 @@
         </xdr:from>
         <xdr:to>
           <xdr:col>1</xdr:col>
-          <xdr:colOff>91440</xdr:colOff>
+          <xdr:colOff>95250</xdr:colOff>
           <xdr:row>46</xdr:row>
-          <xdr:rowOff>19050</xdr:rowOff>
+          <xdr:rowOff>15240</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -4122,9 +4110,9 @@
         </xdr:from>
         <xdr:to>
           <xdr:col>1</xdr:col>
-          <xdr:colOff>91440</xdr:colOff>
+          <xdr:colOff>95250</xdr:colOff>
           <xdr:row>47</xdr:row>
-          <xdr:rowOff>19050</xdr:rowOff>
+          <xdr:rowOff>15240</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -4189,9 +4177,9 @@
         </xdr:from>
         <xdr:to>
           <xdr:col>1</xdr:col>
-          <xdr:colOff>91440</xdr:colOff>
+          <xdr:colOff>95250</xdr:colOff>
           <xdr:row>48</xdr:row>
-          <xdr:rowOff>19050</xdr:rowOff>
+          <xdr:rowOff>15240</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -4256,9 +4244,9 @@
         </xdr:from>
         <xdr:to>
           <xdr:col>1</xdr:col>
-          <xdr:colOff>91440</xdr:colOff>
+          <xdr:colOff>95250</xdr:colOff>
           <xdr:row>49</xdr:row>
-          <xdr:rowOff>19050</xdr:rowOff>
+          <xdr:rowOff>15240</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -4323,9 +4311,9 @@
         </xdr:from>
         <xdr:to>
           <xdr:col>1</xdr:col>
-          <xdr:colOff>91440</xdr:colOff>
+          <xdr:colOff>95250</xdr:colOff>
           <xdr:row>50</xdr:row>
-          <xdr:rowOff>19050</xdr:rowOff>
+          <xdr:rowOff>15240</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -4390,9 +4378,9 @@
         </xdr:from>
         <xdr:to>
           <xdr:col>1</xdr:col>
-          <xdr:colOff>91440</xdr:colOff>
+          <xdr:colOff>95250</xdr:colOff>
           <xdr:row>51</xdr:row>
-          <xdr:rowOff>19050</xdr:rowOff>
+          <xdr:rowOff>15240</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -4457,9 +4445,9 @@
         </xdr:from>
         <xdr:to>
           <xdr:col>1</xdr:col>
-          <xdr:colOff>91440</xdr:colOff>
+          <xdr:colOff>95250</xdr:colOff>
           <xdr:row>52</xdr:row>
-          <xdr:rowOff>19050</xdr:rowOff>
+          <xdr:rowOff>15240</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -4524,9 +4512,9 @@
         </xdr:from>
         <xdr:to>
           <xdr:col>10</xdr:col>
-          <xdr:colOff>167640</xdr:colOff>
+          <xdr:colOff>171450</xdr:colOff>
           <xdr:row>44</xdr:row>
-          <xdr:rowOff>19050</xdr:rowOff>
+          <xdr:rowOff>15240</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -4591,9 +4579,9 @@
         </xdr:from>
         <xdr:to>
           <xdr:col>10</xdr:col>
-          <xdr:colOff>167640</xdr:colOff>
+          <xdr:colOff>171450</xdr:colOff>
           <xdr:row>45</xdr:row>
-          <xdr:rowOff>19050</xdr:rowOff>
+          <xdr:rowOff>15240</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -4658,9 +4646,9 @@
         </xdr:from>
         <xdr:to>
           <xdr:col>10</xdr:col>
-          <xdr:colOff>167640</xdr:colOff>
+          <xdr:colOff>171450</xdr:colOff>
           <xdr:row>46</xdr:row>
-          <xdr:rowOff>19050</xdr:rowOff>
+          <xdr:rowOff>15240</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -4725,9 +4713,9 @@
         </xdr:from>
         <xdr:to>
           <xdr:col>10</xdr:col>
-          <xdr:colOff>167640</xdr:colOff>
+          <xdr:colOff>171450</xdr:colOff>
           <xdr:row>47</xdr:row>
-          <xdr:rowOff>19050</xdr:rowOff>
+          <xdr:rowOff>15240</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -4792,9 +4780,9 @@
         </xdr:from>
         <xdr:to>
           <xdr:col>10</xdr:col>
-          <xdr:colOff>167640</xdr:colOff>
+          <xdr:colOff>171450</xdr:colOff>
           <xdr:row>48</xdr:row>
-          <xdr:rowOff>19050</xdr:rowOff>
+          <xdr:rowOff>15240</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -4859,9 +4847,9 @@
         </xdr:from>
         <xdr:to>
           <xdr:col>10</xdr:col>
-          <xdr:colOff>167640</xdr:colOff>
+          <xdr:colOff>171450</xdr:colOff>
           <xdr:row>49</xdr:row>
-          <xdr:rowOff>19050</xdr:rowOff>
+          <xdr:rowOff>15240</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -4926,9 +4914,9 @@
         </xdr:from>
         <xdr:to>
           <xdr:col>10</xdr:col>
-          <xdr:colOff>167640</xdr:colOff>
+          <xdr:colOff>171450</xdr:colOff>
           <xdr:row>50</xdr:row>
-          <xdr:rowOff>19050</xdr:rowOff>
+          <xdr:rowOff>15240</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -4993,9 +4981,9 @@
         </xdr:from>
         <xdr:to>
           <xdr:col>10</xdr:col>
-          <xdr:colOff>167640</xdr:colOff>
+          <xdr:colOff>171450</xdr:colOff>
           <xdr:row>51</xdr:row>
-          <xdr:rowOff>19050</xdr:rowOff>
+          <xdr:rowOff>15240</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -5060,9 +5048,9 @@
         </xdr:from>
         <xdr:to>
           <xdr:col>10</xdr:col>
-          <xdr:colOff>167640</xdr:colOff>
+          <xdr:colOff>171450</xdr:colOff>
           <xdr:row>52</xdr:row>
-          <xdr:rowOff>19050</xdr:rowOff>
+          <xdr:rowOff>15240</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -5127,9 +5115,9 @@
         </xdr:from>
         <xdr:to>
           <xdr:col>19</xdr:col>
-          <xdr:colOff>95250</xdr:colOff>
+          <xdr:colOff>91440</xdr:colOff>
           <xdr:row>49</xdr:row>
-          <xdr:rowOff>19050</xdr:rowOff>
+          <xdr:rowOff>15240</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -5194,9 +5182,9 @@
         </xdr:from>
         <xdr:to>
           <xdr:col>19</xdr:col>
-          <xdr:colOff>95250</xdr:colOff>
+          <xdr:colOff>91440</xdr:colOff>
           <xdr:row>50</xdr:row>
-          <xdr:rowOff>19050</xdr:rowOff>
+          <xdr:rowOff>15240</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -5261,9 +5249,9 @@
         </xdr:from>
         <xdr:to>
           <xdr:col>28</xdr:col>
-          <xdr:colOff>95250</xdr:colOff>
+          <xdr:colOff>91440</xdr:colOff>
           <xdr:row>51</xdr:row>
-          <xdr:rowOff>19050</xdr:rowOff>
+          <xdr:rowOff>15240</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -5328,9 +5316,9 @@
         </xdr:from>
         <xdr:to>
           <xdr:col>28</xdr:col>
-          <xdr:colOff>95250</xdr:colOff>
+          <xdr:colOff>91440</xdr:colOff>
           <xdr:row>52</xdr:row>
-          <xdr:rowOff>19050</xdr:rowOff>
+          <xdr:rowOff>15240</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -5395,9 +5383,9 @@
         </xdr:from>
         <xdr:to>
           <xdr:col>28</xdr:col>
-          <xdr:colOff>95250</xdr:colOff>
+          <xdr:colOff>91440</xdr:colOff>
           <xdr:row>53</xdr:row>
-          <xdr:rowOff>19050</xdr:rowOff>
+          <xdr:rowOff>15240</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -6380,9 +6368,9 @@
         </xdr:from>
         <xdr:to>
           <xdr:col>28</xdr:col>
-          <xdr:colOff>95250</xdr:colOff>
+          <xdr:colOff>91440</xdr:colOff>
           <xdr:row>53</xdr:row>
-          <xdr:rowOff>19050</xdr:rowOff>
+          <xdr:rowOff>15240</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -7061,16 +7049,16 @@
       <c r="N2" s="31"/>
       <c r="O2" s="38"/>
       <c r="P2" s="38"/>
-      <c r="Q2" s="62"/>
-      <c r="R2" s="62"/>
-      <c r="S2" s="62"/>
-      <c r="T2" s="62"/>
-      <c r="U2" s="62"/>
-      <c r="V2" s="62"/>
-      <c r="W2" s="62"/>
-      <c r="X2" s="62"/>
-      <c r="Y2" s="62"/>
-      <c r="Z2" s="62"/>
+      <c r="Q2" s="154"/>
+      <c r="R2" s="154"/>
+      <c r="S2" s="154"/>
+      <c r="T2" s="154"/>
+      <c r="U2" s="154"/>
+      <c r="V2" s="154"/>
+      <c r="W2" s="154"/>
+      <c r="X2" s="154"/>
+      <c r="Y2" s="154"/>
+      <c r="Z2" s="154"/>
       <c r="AA2" s="38"/>
       <c r="AB2" s="38"/>
       <c r="AC2" s="38"/>
@@ -7096,28 +7084,28 @@
       <c r="K3" s="1"/>
       <c r="M3" s="31"/>
       <c r="N3" s="31"/>
-      <c r="Q3" s="63"/>
-      <c r="R3" s="63"/>
-      <c r="S3" s="63"/>
-      <c r="T3" s="63"/>
-      <c r="U3" s="63"/>
-      <c r="V3" s="63"/>
-      <c r="W3" s="63"/>
-      <c r="X3" s="63"/>
-      <c r="Y3" s="63"/>
-      <c r="Z3" s="63"/>
+      <c r="Q3" s="155"/>
+      <c r="R3" s="155"/>
+      <c r="S3" s="155"/>
+      <c r="T3" s="155"/>
+      <c r="U3" s="155"/>
+      <c r="V3" s="155"/>
+      <c r="W3" s="155"/>
+      <c r="X3" s="155"/>
+      <c r="Y3" s="155"/>
+      <c r="Z3" s="155"/>
       <c r="AA3" s="37"/>
-      <c r="AB3" s="50" t="s">
+      <c r="AB3" s="169" t="s">
         <v>95</v>
       </c>
-      <c r="AC3" s="48"/>
-      <c r="AD3" s="82"/>
-      <c r="AE3" s="83"/>
-      <c r="AF3" s="83"/>
-      <c r="AG3" s="83"/>
-      <c r="AH3" s="83"/>
-      <c r="AI3" s="83"/>
-      <c r="AJ3" s="83"/>
+      <c r="AC3" s="169"/>
+      <c r="AD3" s="167"/>
+      <c r="AE3" s="168"/>
+      <c r="AF3" s="168"/>
+      <c r="AG3" s="168"/>
+      <c r="AH3" s="168"/>
+      <c r="AI3" s="168"/>
+      <c r="AJ3" s="168"/>
     </row>
     <row r="4" spans="1:36" ht="18" customHeight="1">
       <c r="A4" s="30"/>
@@ -7148,304 +7136,299 @@
       </c>
     </row>
     <row r="5" spans="1:36" ht="18" customHeight="1">
-      <c r="A5" s="168" t="s">
+      <c r="A5" t="s">
         <v>85</v>
       </c>
-      <c r="B5" s="168"/>
-      <c r="C5" s="96"/>
-      <c r="D5" s="96"/>
-      <c r="E5" s="96"/>
-      <c r="F5" s="96"/>
-      <c r="G5" s="96"/>
-      <c r="H5" s="96"/>
-      <c r="I5" s="96"/>
+      <c r="C5" s="103"/>
+      <c r="D5" s="103"/>
+      <c r="E5" s="103"/>
+      <c r="F5" s="103"/>
+      <c r="G5" s="103"/>
+      <c r="H5" s="103"/>
+      <c r="I5" s="103"/>
       <c r="J5" s="35"/>
-      <c r="K5" s="60" t="s">
+      <c r="K5" s="118" t="s">
         <v>0</v>
       </c>
-      <c r="L5" s="60"/>
-      <c r="M5" s="60"/>
-      <c r="N5" s="60"/>
-      <c r="O5" s="60"/>
-      <c r="P5" s="122"/>
-      <c r="Q5" s="123"/>
-      <c r="R5" s="123"/>
-      <c r="S5" s="123"/>
-      <c r="T5" s="123"/>
-      <c r="U5" s="123"/>
-      <c r="V5" s="123"/>
-      <c r="W5" s="123"/>
-      <c r="X5" s="123"/>
-      <c r="Y5" s="60" t="s">
+      <c r="L5" s="118"/>
+      <c r="M5" s="118"/>
+      <c r="N5" s="118"/>
+      <c r="O5" s="118"/>
+      <c r="P5" s="152"/>
+      <c r="Q5" s="153"/>
+      <c r="R5" s="153"/>
+      <c r="S5" s="153"/>
+      <c r="T5" s="153"/>
+      <c r="U5" s="153"/>
+      <c r="V5" s="153"/>
+      <c r="W5" s="153"/>
+      <c r="X5" s="153"/>
+      <c r="Y5" s="118" t="s">
         <v>48</v>
       </c>
-      <c r="Z5" s="60"/>
-      <c r="AA5" s="96"/>
-      <c r="AB5" s="96"/>
-      <c r="AC5" s="96"/>
-      <c r="AD5" s="96"/>
-      <c r="AE5" s="96"/>
-      <c r="AF5" s="96"/>
-      <c r="AG5" s="96"/>
-      <c r="AH5" s="96"/>
-      <c r="AI5" s="96"/>
-      <c r="AJ5" s="96"/>
+      <c r="Z5" s="118"/>
+      <c r="AA5" s="103"/>
+      <c r="AB5" s="103"/>
+      <c r="AC5" s="103"/>
+      <c r="AD5" s="103"/>
+      <c r="AE5" s="103"/>
+      <c r="AF5" s="103"/>
+      <c r="AG5" s="103"/>
+      <c r="AH5" s="103"/>
+      <c r="AI5" s="103"/>
+      <c r="AJ5" s="103"/>
     </row>
     <row r="6" spans="1:36" ht="18" customHeight="1">
-      <c r="A6" s="168" t="s">
+      <c r="A6" t="s">
         <v>1</v>
       </c>
-      <c r="B6" s="168"/>
-      <c r="C6" s="75"/>
-      <c r="D6" s="75"/>
-      <c r="E6" s="75"/>
-      <c r="F6" s="75"/>
-      <c r="G6" s="75"/>
-      <c r="H6" s="75"/>
-      <c r="I6" s="75"/>
+      <c r="C6" s="117"/>
+      <c r="D6" s="117"/>
+      <c r="E6" s="117"/>
+      <c r="F6" s="117"/>
+      <c r="G6" s="117"/>
+      <c r="H6" s="117"/>
+      <c r="I6" s="117"/>
       <c r="J6" s="35"/>
-      <c r="K6" s="60" t="s">
+      <c r="K6" s="118" t="s">
         <v>2</v>
       </c>
-      <c r="L6" s="60"/>
-      <c r="M6" s="60"/>
-      <c r="N6" s="60"/>
-      <c r="O6" s="60"/>
-      <c r="P6" s="67"/>
-      <c r="Q6" s="68"/>
-      <c r="R6" s="68"/>
-      <c r="S6" s="68"/>
-      <c r="T6" s="68"/>
-      <c r="U6" s="68"/>
-      <c r="V6" s="68"/>
-      <c r="W6" s="68"/>
-      <c r="X6" s="68"/>
-      <c r="Y6" s="56" t="s">
+      <c r="L6" s="118"/>
+      <c r="M6" s="118"/>
+      <c r="N6" s="118"/>
+      <c r="O6" s="118"/>
+      <c r="P6" s="159"/>
+      <c r="Q6" s="160"/>
+      <c r="R6" s="160"/>
+      <c r="S6" s="160"/>
+      <c r="T6" s="160"/>
+      <c r="U6" s="160"/>
+      <c r="V6" s="160"/>
+      <c r="W6" s="160"/>
+      <c r="X6" s="160"/>
+      <c r="Y6" s="54" t="s">
         <v>88</v>
       </c>
-      <c r="Z6" s="56"/>
-      <c r="AA6" s="56"/>
-      <c r="AB6" s="56"/>
-      <c r="AC6" s="59"/>
-      <c r="AD6" s="57"/>
-      <c r="AE6" s="57"/>
-      <c r="AF6" s="57"/>
+      <c r="Z6" s="54"/>
+      <c r="AA6" s="54"/>
+      <c r="AB6" s="54"/>
+      <c r="AC6" s="170"/>
+      <c r="AD6" s="170"/>
+      <c r="AE6" s="170"/>
+      <c r="AF6" s="55"/>
       <c r="AG6" s="44"/>
-      <c r="AH6" s="58"/>
-      <c r="AI6" s="58"/>
+      <c r="AH6" s="56"/>
+      <c r="AI6" s="56"/>
       <c r="AJ6" s="44"/>
     </row>
     <row r="7" spans="1:36" ht="18" customHeight="1">
-      <c r="A7" s="168" t="s">
+      <c r="A7" t="s">
         <v>3</v>
       </c>
-      <c r="B7" s="168"/>
-      <c r="C7" s="75"/>
-      <c r="D7" s="75"/>
-      <c r="E7" s="75"/>
-      <c r="F7" s="75"/>
-      <c r="G7" s="75"/>
-      <c r="H7" s="75"/>
-      <c r="I7" s="75"/>
+      <c r="C7" s="117"/>
+      <c r="D7" s="117"/>
+      <c r="E7" s="117"/>
+      <c r="F7" s="117"/>
+      <c r="G7" s="117"/>
+      <c r="H7" s="117"/>
+      <c r="I7" s="117"/>
       <c r="J7" s="35"/>
-      <c r="K7" s="60" t="s">
+      <c r="K7" s="118" t="s">
         <v>89</v>
       </c>
-      <c r="L7" s="60"/>
-      <c r="M7" s="60"/>
-      <c r="N7" s="60"/>
-      <c r="O7" s="60"/>
-      <c r="P7" s="121"/>
-      <c r="Q7" s="121"/>
-      <c r="R7" s="121"/>
-      <c r="S7" s="121"/>
-      <c r="T7" s="121"/>
+      <c r="L7" s="118"/>
+      <c r="M7" s="118"/>
+      <c r="N7" s="118"/>
+      <c r="O7" s="118"/>
+      <c r="P7" s="116"/>
+      <c r="Q7" s="116"/>
+      <c r="R7" s="116"/>
+      <c r="S7" s="116"/>
+      <c r="T7" s="116"/>
       <c r="U7" s="39" t="s">
         <v>4</v>
       </c>
-      <c r="V7" s="110"/>
-      <c r="W7" s="110"/>
-      <c r="X7" s="60" t="s">
+      <c r="V7" s="140"/>
+      <c r="W7" s="140"/>
+      <c r="X7" s="118" t="s">
         <v>90</v>
       </c>
-      <c r="Y7" s="60"/>
-      <c r="Z7" s="60"/>
-      <c r="AA7" s="60"/>
-      <c r="AB7" s="60"/>
-      <c r="AC7" s="59"/>
-      <c r="AD7" s="57"/>
-      <c r="AE7" s="57"/>
-      <c r="AF7" s="58"/>
-      <c r="AG7" s="58"/>
+      <c r="Y7" s="118"/>
+      <c r="Z7" s="118"/>
+      <c r="AA7" s="118"/>
+      <c r="AB7" s="118"/>
+      <c r="AC7" s="81"/>
+      <c r="AD7" s="81"/>
+      <c r="AE7" s="81"/>
+      <c r="AF7" s="56"/>
+      <c r="AG7" s="56"/>
       <c r="AH7" s="39" t="s">
         <v>4</v>
       </c>
-      <c r="AI7" s="121"/>
-      <c r="AJ7" s="121"/>
+      <c r="AI7" s="116"/>
+      <c r="AJ7" s="116"/>
     </row>
     <row r="8" spans="1:36" ht="18" customHeight="1">
-      <c r="A8" s="169" t="s">
+      <c r="A8" s="57" t="s">
         <v>5</v>
       </c>
-      <c r="B8" s="169"/>
-      <c r="C8" s="169"/>
-      <c r="D8" s="61"/>
-      <c r="E8" s="61"/>
-      <c r="F8" s="61"/>
-      <c r="G8" s="61"/>
-      <c r="H8" s="61"/>
-      <c r="I8" s="61"/>
-      <c r="J8" s="61"/>
-      <c r="K8" s="61"/>
-      <c r="L8" s="61"/>
-      <c r="M8" s="61"/>
-      <c r="N8" s="61"/>
-      <c r="O8" s="61"/>
-      <c r="P8" s="61"/>
-      <c r="Q8" s="61"/>
-      <c r="R8" s="61"/>
-      <c r="S8" s="170" t="s">
+      <c r="B8" s="57"/>
+      <c r="C8" s="57"/>
+      <c r="D8" s="98"/>
+      <c r="E8" s="98"/>
+      <c r="F8" s="98"/>
+      <c r="G8" s="98"/>
+      <c r="H8" s="98"/>
+      <c r="I8" s="98"/>
+      <c r="J8" s="98"/>
+      <c r="K8" s="98"/>
+      <c r="L8" s="98"/>
+      <c r="M8" s="98"/>
+      <c r="N8" s="98"/>
+      <c r="O8" s="98"/>
+      <c r="P8" s="98"/>
+      <c r="Q8" s="98"/>
+      <c r="R8" s="98"/>
+      <c r="S8" s="58" t="s">
         <v>49</v>
       </c>
-      <c r="T8" s="170"/>
-      <c r="U8" s="171"/>
-      <c r="V8" s="170"/>
-      <c r="W8" s="170"/>
-      <c r="X8" s="61"/>
-      <c r="Y8" s="61"/>
-      <c r="Z8" s="61"/>
-      <c r="AA8" s="61"/>
-      <c r="AB8" s="61"/>
-      <c r="AC8" s="61"/>
-      <c r="AD8" s="61"/>
-      <c r="AE8" s="61"/>
-      <c r="AF8" s="61"/>
-      <c r="AG8" s="61"/>
-      <c r="AH8" s="61"/>
-      <c r="AI8" s="61"/>
-      <c r="AJ8" s="61"/>
+      <c r="T8" s="58"/>
+      <c r="U8" s="54"/>
+      <c r="V8" s="58"/>
+      <c r="W8" s="58"/>
+      <c r="X8" s="98"/>
+      <c r="Y8" s="98"/>
+      <c r="Z8" s="98"/>
+      <c r="AA8" s="98"/>
+      <c r="AB8" s="98"/>
+      <c r="AC8" s="98"/>
+      <c r="AD8" s="98"/>
+      <c r="AE8" s="98"/>
+      <c r="AF8" s="98"/>
+      <c r="AG8" s="98"/>
+      <c r="AH8" s="98"/>
+      <c r="AI8" s="98"/>
+      <c r="AJ8" s="98"/>
     </row>
     <row r="9" spans="1:36" ht="26.4" customHeight="1">
-      <c r="A9" s="168" t="s">
+      <c r="A9" t="s">
         <v>6</v>
       </c>
-      <c r="B9" s="168"/>
-      <c r="C9" s="168"/>
-      <c r="D9" s="75"/>
-      <c r="E9" s="75"/>
-      <c r="F9" s="75"/>
-      <c r="G9" s="75"/>
-      <c r="H9" s="75"/>
-      <c r="I9" s="175"/>
-      <c r="J9" s="175"/>
-      <c r="K9" s="175"/>
-      <c r="L9" s="175"/>
-      <c r="M9" s="175"/>
-      <c r="N9" s="175"/>
-      <c r="O9" s="175"/>
-      <c r="P9" s="175"/>
-      <c r="Q9" s="175"/>
-      <c r="R9" s="175"/>
-      <c r="S9" s="171" t="s">
+      <c r="D9" s="117"/>
+      <c r="E9" s="117"/>
+      <c r="F9" s="117"/>
+      <c r="G9" s="117"/>
+      <c r="H9" s="117"/>
+      <c r="I9" s="60"/>
+      <c r="J9" s="60"/>
+      <c r="K9" s="60"/>
+      <c r="L9" s="60"/>
+      <c r="M9" s="60"/>
+      <c r="N9" s="60"/>
+      <c r="O9" s="60"/>
+      <c r="P9" s="60"/>
+      <c r="Q9" s="60"/>
+      <c r="R9" s="60"/>
+      <c r="S9" s="54" t="s">
         <v>50</v>
       </c>
-      <c r="T9" s="171"/>
-      <c r="U9" s="171"/>
-      <c r="V9" s="171"/>
-      <c r="W9" s="171"/>
-      <c r="X9" s="120"/>
-      <c r="Y9" s="78"/>
-      <c r="Z9" s="78"/>
-      <c r="AA9" s="78"/>
-      <c r="AB9" s="78"/>
-      <c r="AC9" s="78"/>
-      <c r="AD9" s="78"/>
-      <c r="AE9" s="78"/>
-      <c r="AF9" s="78"/>
-      <c r="AG9" s="78"/>
-      <c r="AH9" s="78"/>
-      <c r="AI9" s="78"/>
-      <c r="AJ9" s="78"/>
+      <c r="T9" s="54"/>
+      <c r="U9" s="54"/>
+      <c r="V9" s="54"/>
+      <c r="W9" s="54"/>
+      <c r="X9" s="150"/>
+      <c r="Y9" s="151"/>
+      <c r="Z9" s="151"/>
+      <c r="AA9" s="151"/>
+      <c r="AB9" s="151"/>
+      <c r="AC9" s="151"/>
+      <c r="AD9" s="151"/>
+      <c r="AE9" s="151"/>
+      <c r="AF9" s="151"/>
+      <c r="AG9" s="151"/>
+      <c r="AH9" s="151"/>
+      <c r="AI9" s="151"/>
+      <c r="AJ9" s="151"/>
     </row>
     <row r="10" spans="1:36" ht="5.25" customHeight="1">
-      <c r="A10" s="77"/>
-      <c r="B10" s="77"/>
-      <c r="C10" s="77"/>
-      <c r="D10" s="77"/>
-      <c r="E10" s="77"/>
-      <c r="F10" s="77"/>
-      <c r="G10" s="77"/>
-      <c r="H10" s="77"/>
-      <c r="I10" s="77"/>
-      <c r="J10" s="77"/>
-      <c r="K10" s="77"/>
-      <c r="L10" s="77"/>
-      <c r="M10" s="77"/>
-      <c r="N10" s="77"/>
-      <c r="O10" s="77"/>
-      <c r="P10" s="77"/>
-      <c r="Q10" s="77"/>
-      <c r="R10" s="77"/>
-      <c r="S10" s="77"/>
-      <c r="T10" s="77"/>
-      <c r="U10" s="77"/>
-      <c r="V10" s="77"/>
-      <c r="W10" s="77"/>
-      <c r="X10" s="77"/>
-      <c r="Y10" s="77"/>
-      <c r="Z10" s="77"/>
-      <c r="AA10" s="77"/>
-      <c r="AB10" s="77"/>
-      <c r="AC10" s="77"/>
-      <c r="AD10" s="77"/>
-      <c r="AE10" s="77"/>
-      <c r="AF10" s="77"/>
-      <c r="AG10" s="77"/>
-      <c r="AH10" s="77"/>
-      <c r="AI10" s="77"/>
-      <c r="AJ10" s="77"/>
+      <c r="A10" s="91"/>
+      <c r="B10" s="91"/>
+      <c r="C10" s="91"/>
+      <c r="D10" s="91"/>
+      <c r="E10" s="91"/>
+      <c r="F10" s="91"/>
+      <c r="G10" s="91"/>
+      <c r="H10" s="91"/>
+      <c r="I10" s="91"/>
+      <c r="J10" s="91"/>
+      <c r="K10" s="91"/>
+      <c r="L10" s="91"/>
+      <c r="M10" s="91"/>
+      <c r="N10" s="91"/>
+      <c r="O10" s="91"/>
+      <c r="P10" s="91"/>
+      <c r="Q10" s="91"/>
+      <c r="R10" s="91"/>
+      <c r="S10" s="91"/>
+      <c r="T10" s="91"/>
+      <c r="U10" s="91"/>
+      <c r="V10" s="91"/>
+      <c r="W10" s="91"/>
+      <c r="X10" s="91"/>
+      <c r="Y10" s="91"/>
+      <c r="Z10" s="91"/>
+      <c r="AA10" s="91"/>
+      <c r="AB10" s="91"/>
+      <c r="AC10" s="91"/>
+      <c r="AD10" s="91"/>
+      <c r="AE10" s="91"/>
+      <c r="AF10" s="91"/>
+      <c r="AG10" s="91"/>
+      <c r="AH10" s="91"/>
+      <c r="AI10" s="91"/>
+      <c r="AJ10" s="91"/>
     </row>
     <row r="11" spans="1:36" ht="14.25" customHeight="1">
-      <c r="A11" s="64" t="s">
+      <c r="A11" s="156" t="s">
         <v>7</v>
       </c>
-      <c r="B11" s="65"/>
-      <c r="C11" s="65"/>
-      <c r="D11" s="65"/>
-      <c r="E11" s="65"/>
-      <c r="F11" s="65"/>
-      <c r="G11" s="65"/>
-      <c r="H11" s="65"/>
-      <c r="I11" s="65"/>
-      <c r="J11" s="65"/>
-      <c r="K11" s="65"/>
-      <c r="L11" s="65"/>
-      <c r="M11" s="65"/>
-      <c r="N11" s="65"/>
-      <c r="O11" s="65"/>
-      <c r="P11" s="66"/>
-      <c r="Q11" s="72" t="s">
+      <c r="B11" s="157"/>
+      <c r="C11" s="157"/>
+      <c r="D11" s="157"/>
+      <c r="E11" s="157"/>
+      <c r="F11" s="157"/>
+      <c r="G11" s="157"/>
+      <c r="H11" s="157"/>
+      <c r="I11" s="157"/>
+      <c r="J11" s="157"/>
+      <c r="K11" s="157"/>
+      <c r="L11" s="157"/>
+      <c r="M11" s="157"/>
+      <c r="N11" s="157"/>
+      <c r="O11" s="157"/>
+      <c r="P11" s="158"/>
+      <c r="Q11" s="161" t="s">
         <v>8</v>
       </c>
-      <c r="R11" s="73"/>
-      <c r="S11" s="73"/>
-      <c r="T11" s="73"/>
-      <c r="U11" s="73"/>
-      <c r="V11" s="73"/>
-      <c r="W11" s="73"/>
-      <c r="X11" s="73"/>
-      <c r="Y11" s="73"/>
-      <c r="Z11" s="73"/>
-      <c r="AA11" s="73"/>
-      <c r="AB11" s="73"/>
-      <c r="AC11" s="73"/>
-      <c r="AD11" s="73"/>
-      <c r="AE11" s="73"/>
-      <c r="AF11" s="73"/>
-      <c r="AG11" s="73"/>
-      <c r="AH11" s="73"/>
-      <c r="AI11" s="73"/>
-      <c r="AJ11" s="74"/>
+      <c r="R11" s="162"/>
+      <c r="S11" s="162"/>
+      <c r="T11" s="162"/>
+      <c r="U11" s="162"/>
+      <c r="V11" s="162"/>
+      <c r="W11" s="162"/>
+      <c r="X11" s="162"/>
+      <c r="Y11" s="162"/>
+      <c r="Z11" s="162"/>
+      <c r="AA11" s="162"/>
+      <c r="AB11" s="162"/>
+      <c r="AC11" s="162"/>
+      <c r="AD11" s="162"/>
+      <c r="AE11" s="162"/>
+      <c r="AF11" s="162"/>
+      <c r="AG11" s="162"/>
+      <c r="AH11" s="162"/>
+      <c r="AI11" s="162"/>
+      <c r="AJ11" s="163"/>
     </row>
     <row r="12" spans="1:36" ht="18" customHeight="1">
       <c r="A12" s="2"/>
@@ -7554,150 +7537,150 @@
       <c r="AJ13" s="23"/>
     </row>
     <row r="14" spans="1:36" ht="16.5" customHeight="1">
-      <c r="A14" s="102" t="s">
+      <c r="A14" s="132" t="s">
         <v>86</v>
       </c>
-      <c r="B14" s="103"/>
-      <c r="C14" s="103"/>
-      <c r="D14" s="103"/>
-      <c r="E14" s="103"/>
-      <c r="F14" s="103"/>
-      <c r="G14" s="103"/>
-      <c r="H14" s="103"/>
-      <c r="I14" s="104"/>
-      <c r="J14" s="105"/>
-      <c r="K14" s="105"/>
-      <c r="L14" s="105"/>
-      <c r="M14" s="105"/>
-      <c r="N14" s="105"/>
-      <c r="O14" s="105"/>
-      <c r="P14" s="105"/>
-      <c r="Q14" s="105"/>
-      <c r="R14" s="105"/>
-      <c r="S14" s="105"/>
-      <c r="T14" s="105"/>
-      <c r="U14" s="105"/>
-      <c r="V14" s="105"/>
-      <c r="W14" s="105"/>
-      <c r="X14" s="105"/>
-      <c r="Y14" s="105"/>
-      <c r="Z14" s="105"/>
-      <c r="AA14" s="105"/>
-      <c r="AB14" s="105"/>
-      <c r="AC14" s="105"/>
-      <c r="AD14" s="105"/>
-      <c r="AE14" s="105"/>
-      <c r="AF14" s="105"/>
-      <c r="AG14" s="105"/>
-      <c r="AH14" s="105"/>
-      <c r="AI14" s="105"/>
-      <c r="AJ14" s="106"/>
+      <c r="B14" s="133"/>
+      <c r="C14" s="133"/>
+      <c r="D14" s="133"/>
+      <c r="E14" s="133"/>
+      <c r="F14" s="133"/>
+      <c r="G14" s="133"/>
+      <c r="H14" s="133"/>
+      <c r="I14" s="134"/>
+      <c r="J14" s="135"/>
+      <c r="K14" s="135"/>
+      <c r="L14" s="135"/>
+      <c r="M14" s="135"/>
+      <c r="N14" s="135"/>
+      <c r="O14" s="135"/>
+      <c r="P14" s="135"/>
+      <c r="Q14" s="135"/>
+      <c r="R14" s="135"/>
+      <c r="S14" s="135"/>
+      <c r="T14" s="135"/>
+      <c r="U14" s="135"/>
+      <c r="V14" s="135"/>
+      <c r="W14" s="135"/>
+      <c r="X14" s="135"/>
+      <c r="Y14" s="135"/>
+      <c r="Z14" s="135"/>
+      <c r="AA14" s="135"/>
+      <c r="AB14" s="135"/>
+      <c r="AC14" s="135"/>
+      <c r="AD14" s="135"/>
+      <c r="AE14" s="135"/>
+      <c r="AF14" s="135"/>
+      <c r="AG14" s="135"/>
+      <c r="AH14" s="135"/>
+      <c r="AI14" s="135"/>
+      <c r="AJ14" s="136"/>
     </row>
     <row r="15" spans="1:36" ht="3" customHeight="1">
-      <c r="A15" s="107">
+      <c r="A15" s="137">
         <v>2</v>
       </c>
-      <c r="B15" s="108"/>
-      <c r="C15" s="108"/>
-      <c r="D15" s="108"/>
-      <c r="E15" s="108"/>
-      <c r="F15" s="108"/>
-      <c r="G15" s="108"/>
-      <c r="H15" s="108"/>
-      <c r="I15" s="108"/>
-      <c r="J15" s="108"/>
-      <c r="K15" s="108"/>
-      <c r="L15" s="108"/>
-      <c r="M15" s="108"/>
-      <c r="N15" s="108"/>
-      <c r="O15" s="108"/>
-      <c r="P15" s="108"/>
-      <c r="Q15" s="108"/>
-      <c r="R15" s="108"/>
-      <c r="S15" s="108"/>
-      <c r="T15" s="108"/>
-      <c r="U15" s="108"/>
-      <c r="V15" s="108"/>
-      <c r="W15" s="108"/>
-      <c r="X15" s="108"/>
-      <c r="Y15" s="108"/>
-      <c r="Z15" s="108"/>
-      <c r="AA15" s="108"/>
-      <c r="AB15" s="108"/>
-      <c r="AC15" s="108"/>
-      <c r="AD15" s="108"/>
-      <c r="AE15" s="108"/>
-      <c r="AF15" s="108"/>
-      <c r="AG15" s="108"/>
-      <c r="AH15" s="108"/>
-      <c r="AI15" s="108"/>
-      <c r="AJ15" s="109"/>
+      <c r="B15" s="138"/>
+      <c r="C15" s="138"/>
+      <c r="D15" s="138"/>
+      <c r="E15" s="138"/>
+      <c r="F15" s="138"/>
+      <c r="G15" s="138"/>
+      <c r="H15" s="138"/>
+      <c r="I15" s="138"/>
+      <c r="J15" s="138"/>
+      <c r="K15" s="138"/>
+      <c r="L15" s="138"/>
+      <c r="M15" s="138"/>
+      <c r="N15" s="138"/>
+      <c r="O15" s="138"/>
+      <c r="P15" s="138"/>
+      <c r="Q15" s="138"/>
+      <c r="R15" s="138"/>
+      <c r="S15" s="138"/>
+      <c r="T15" s="138"/>
+      <c r="U15" s="138"/>
+      <c r="V15" s="138"/>
+      <c r="W15" s="138"/>
+      <c r="X15" s="138"/>
+      <c r="Y15" s="138"/>
+      <c r="Z15" s="138"/>
+      <c r="AA15" s="138"/>
+      <c r="AB15" s="138"/>
+      <c r="AC15" s="138"/>
+      <c r="AD15" s="138"/>
+      <c r="AE15" s="138"/>
+      <c r="AF15" s="138"/>
+      <c r="AG15" s="138"/>
+      <c r="AH15" s="138"/>
+      <c r="AI15" s="138"/>
+      <c r="AJ15" s="139"/>
     </row>
     <row r="16" spans="1:36" ht="12.75" customHeight="1">
-      <c r="A16" s="117" t="s">
+      <c r="A16" s="147" t="s">
         <v>9</v>
       </c>
-      <c r="B16" s="118"/>
-      <c r="C16" s="118"/>
-      <c r="D16" s="118"/>
-      <c r="E16" s="118"/>
-      <c r="F16" s="118"/>
-      <c r="G16" s="118"/>
-      <c r="H16" s="118"/>
-      <c r="I16" s="118"/>
-      <c r="J16" s="118"/>
-      <c r="K16" s="118"/>
-      <c r="L16" s="118"/>
-      <c r="M16" s="118"/>
-      <c r="N16" s="118"/>
-      <c r="O16" s="118"/>
-      <c r="P16" s="118"/>
-      <c r="Q16" s="118"/>
-      <c r="R16" s="118"/>
-      <c r="S16" s="118"/>
-      <c r="T16" s="119"/>
-      <c r="U16" s="111" t="s">
+      <c r="B16" s="148"/>
+      <c r="C16" s="148"/>
+      <c r="D16" s="148"/>
+      <c r="E16" s="148"/>
+      <c r="F16" s="148"/>
+      <c r="G16" s="148"/>
+      <c r="H16" s="148"/>
+      <c r="I16" s="148"/>
+      <c r="J16" s="148"/>
+      <c r="K16" s="148"/>
+      <c r="L16" s="148"/>
+      <c r="M16" s="148"/>
+      <c r="N16" s="148"/>
+      <c r="O16" s="148"/>
+      <c r="P16" s="148"/>
+      <c r="Q16" s="148"/>
+      <c r="R16" s="148"/>
+      <c r="S16" s="148"/>
+      <c r="T16" s="149"/>
+      <c r="U16" s="141" t="s">
         <v>73</v>
       </c>
-      <c r="V16" s="112"/>
-      <c r="W16" s="112"/>
-      <c r="X16" s="112"/>
-      <c r="Y16" s="112"/>
-      <c r="Z16" s="112"/>
-      <c r="AA16" s="112"/>
-      <c r="AB16" s="112"/>
-      <c r="AC16" s="112"/>
-      <c r="AD16" s="113"/>
-      <c r="AE16" s="114" t="s">
+      <c r="V16" s="142"/>
+      <c r="W16" s="142"/>
+      <c r="X16" s="142"/>
+      <c r="Y16" s="142"/>
+      <c r="Z16" s="142"/>
+      <c r="AA16" s="142"/>
+      <c r="AB16" s="142"/>
+      <c r="AC16" s="142"/>
+      <c r="AD16" s="143"/>
+      <c r="AE16" s="144" t="s">
         <v>10</v>
       </c>
-      <c r="AF16" s="115"/>
-      <c r="AG16" s="115"/>
-      <c r="AH16" s="115"/>
-      <c r="AI16" s="115"/>
-      <c r="AJ16" s="116"/>
+      <c r="AF16" s="145"/>
+      <c r="AG16" s="145"/>
+      <c r="AH16" s="145"/>
+      <c r="AI16" s="145"/>
+      <c r="AJ16" s="146"/>
     </row>
     <row r="17" spans="1:36" ht="18" customHeight="1">
-      <c r="A17" s="90"/>
-      <c r="B17" s="91"/>
-      <c r="C17" s="91"/>
-      <c r="D17" s="91"/>
-      <c r="E17" s="91"/>
-      <c r="F17" s="91"/>
-      <c r="G17" s="91"/>
-      <c r="H17" s="91"/>
-      <c r="I17" s="91"/>
-      <c r="J17" s="91"/>
-      <c r="K17" s="91"/>
-      <c r="L17" s="91"/>
-      <c r="M17" s="91"/>
-      <c r="N17" s="91"/>
-      <c r="O17" s="91"/>
-      <c r="P17" s="91"/>
-      <c r="Q17" s="91"/>
-      <c r="R17" s="91"/>
-      <c r="S17" s="91"/>
-      <c r="T17" s="92"/>
+      <c r="A17" s="125"/>
+      <c r="B17" s="126"/>
+      <c r="C17" s="126"/>
+      <c r="D17" s="126"/>
+      <c r="E17" s="126"/>
+      <c r="F17" s="126"/>
+      <c r="G17" s="126"/>
+      <c r="H17" s="126"/>
+      <c r="I17" s="126"/>
+      <c r="J17" s="126"/>
+      <c r="K17" s="126"/>
+      <c r="L17" s="126"/>
+      <c r="M17" s="126"/>
+      <c r="N17" s="126"/>
+      <c r="O17" s="126"/>
+      <c r="P17" s="126"/>
+      <c r="Q17" s="126"/>
+      <c r="R17" s="126"/>
+      <c r="S17" s="126"/>
+      <c r="T17" s="127"/>
       <c r="U17" s="25"/>
       <c r="V17" s="17" t="s">
         <v>64</v>
@@ -7713,32 +7696,32 @@
       <c r="AE17" s="14" t="s">
         <v>11</v>
       </c>
-      <c r="AF17" s="97"/>
-      <c r="AG17" s="97"/>
-      <c r="AI17" s="97"/>
-      <c r="AJ17" s="101"/>
+      <c r="AF17" s="107"/>
+      <c r="AG17" s="107"/>
+      <c r="AI17" s="107"/>
+      <c r="AJ17" s="131"/>
     </row>
     <row r="18" spans="1:36" ht="18" customHeight="1">
-      <c r="A18" s="90"/>
-      <c r="B18" s="91"/>
-      <c r="C18" s="91"/>
-      <c r="D18" s="91"/>
-      <c r="E18" s="91"/>
-      <c r="F18" s="91"/>
-      <c r="G18" s="91"/>
-      <c r="H18" s="91"/>
-      <c r="I18" s="91"/>
-      <c r="J18" s="91"/>
-      <c r="K18" s="91"/>
-      <c r="L18" s="91"/>
-      <c r="M18" s="91"/>
-      <c r="N18" s="91"/>
-      <c r="O18" s="91"/>
-      <c r="P18" s="91"/>
-      <c r="Q18" s="91"/>
-      <c r="R18" s="91"/>
-      <c r="S18" s="91"/>
-      <c r="T18" s="92"/>
+      <c r="A18" s="125"/>
+      <c r="B18" s="126"/>
+      <c r="C18" s="126"/>
+      <c r="D18" s="126"/>
+      <c r="E18" s="126"/>
+      <c r="F18" s="126"/>
+      <c r="G18" s="126"/>
+      <c r="H18" s="126"/>
+      <c r="I18" s="126"/>
+      <c r="J18" s="126"/>
+      <c r="K18" s="126"/>
+      <c r="L18" s="126"/>
+      <c r="M18" s="126"/>
+      <c r="N18" s="126"/>
+      <c r="O18" s="126"/>
+      <c r="P18" s="126"/>
+      <c r="Q18" s="126"/>
+      <c r="R18" s="126"/>
+      <c r="S18" s="126"/>
+      <c r="T18" s="127"/>
       <c r="U18" s="26"/>
       <c r="V18" s="17" t="s">
         <v>65</v>
@@ -7754,32 +7737,32 @@
       <c r="AE18" s="14" t="s">
         <v>12</v>
       </c>
-      <c r="AF18" s="97"/>
-      <c r="AG18" s="97"/>
-      <c r="AI18" s="97"/>
-      <c r="AJ18" s="101"/>
+      <c r="AF18" s="107"/>
+      <c r="AG18" s="107"/>
+      <c r="AI18" s="107"/>
+      <c r="AJ18" s="131"/>
     </row>
     <row r="19" spans="1:36" ht="18" customHeight="1">
-      <c r="A19" s="90"/>
-      <c r="B19" s="91"/>
-      <c r="C19" s="91"/>
-      <c r="D19" s="91"/>
-      <c r="E19" s="91"/>
-      <c r="F19" s="91"/>
-      <c r="G19" s="91"/>
-      <c r="H19" s="91"/>
-      <c r="I19" s="91"/>
-      <c r="J19" s="91"/>
-      <c r="K19" s="91"/>
-      <c r="L19" s="91"/>
-      <c r="M19" s="91"/>
-      <c r="N19" s="91"/>
-      <c r="O19" s="91"/>
-      <c r="P19" s="91"/>
-      <c r="Q19" s="91"/>
-      <c r="R19" s="91"/>
-      <c r="S19" s="91"/>
-      <c r="T19" s="92"/>
+      <c r="A19" s="125"/>
+      <c r="B19" s="126"/>
+      <c r="C19" s="126"/>
+      <c r="D19" s="126"/>
+      <c r="E19" s="126"/>
+      <c r="F19" s="126"/>
+      <c r="G19" s="126"/>
+      <c r="H19" s="126"/>
+      <c r="I19" s="126"/>
+      <c r="J19" s="126"/>
+      <c r="K19" s="126"/>
+      <c r="L19" s="126"/>
+      <c r="M19" s="126"/>
+      <c r="N19" s="126"/>
+      <c r="O19" s="126"/>
+      <c r="P19" s="126"/>
+      <c r="Q19" s="126"/>
+      <c r="R19" s="126"/>
+      <c r="S19" s="126"/>
+      <c r="T19" s="127"/>
       <c r="U19" s="26"/>
       <c r="V19" s="17" t="s">
         <v>66</v>
@@ -7795,32 +7778,32 @@
       <c r="AE19" s="14" t="s">
         <v>13</v>
       </c>
-      <c r="AF19" s="97"/>
-      <c r="AG19" s="97"/>
-      <c r="AI19" s="97"/>
-      <c r="AJ19" s="101"/>
+      <c r="AF19" s="107"/>
+      <c r="AG19" s="107"/>
+      <c r="AI19" s="107"/>
+      <c r="AJ19" s="131"/>
     </row>
     <row r="20" spans="1:36" ht="3.75" customHeight="1">
-      <c r="A20" s="93"/>
-      <c r="B20" s="94"/>
-      <c r="C20" s="94"/>
-      <c r="D20" s="94"/>
-      <c r="E20" s="94"/>
-      <c r="F20" s="94"/>
-      <c r="G20" s="94"/>
-      <c r="H20" s="94"/>
-      <c r="I20" s="94"/>
-      <c r="J20" s="94"/>
-      <c r="K20" s="94"/>
-      <c r="L20" s="94"/>
-      <c r="M20" s="94"/>
-      <c r="N20" s="94"/>
-      <c r="O20" s="94"/>
-      <c r="P20" s="94"/>
-      <c r="Q20" s="94"/>
-      <c r="R20" s="94"/>
-      <c r="S20" s="94"/>
-      <c r="T20" s="95"/>
+      <c r="A20" s="128"/>
+      <c r="B20" s="129"/>
+      <c r="C20" s="129"/>
+      <c r="D20" s="129"/>
+      <c r="E20" s="129"/>
+      <c r="F20" s="129"/>
+      <c r="G20" s="129"/>
+      <c r="H20" s="129"/>
+      <c r="I20" s="129"/>
+      <c r="J20" s="129"/>
+      <c r="K20" s="129"/>
+      <c r="L20" s="129"/>
+      <c r="M20" s="129"/>
+      <c r="N20" s="129"/>
+      <c r="O20" s="129"/>
+      <c r="P20" s="129"/>
+      <c r="Q20" s="129"/>
+      <c r="R20" s="129"/>
+      <c r="S20" s="129"/>
+      <c r="T20" s="130"/>
       <c r="U20" s="27"/>
       <c r="V20" s="16"/>
       <c r="W20" s="7"/>
@@ -7879,80 +7862,80 @@
       <c r="AJ21" s="47"/>
     </row>
     <row r="22" spans="1:36" ht="16.5" customHeight="1">
-      <c r="A22" s="84"/>
-      <c r="B22" s="85"/>
-      <c r="C22" s="85"/>
-      <c r="D22" s="85"/>
-      <c r="E22" s="85"/>
-      <c r="F22" s="85"/>
-      <c r="G22" s="85"/>
-      <c r="H22" s="85"/>
-      <c r="I22" s="85"/>
-      <c r="J22" s="85"/>
-      <c r="K22" s="85"/>
-      <c r="L22" s="85"/>
-      <c r="M22" s="85"/>
-      <c r="N22" s="85"/>
-      <c r="O22" s="85"/>
-      <c r="P22" s="85"/>
-      <c r="Q22" s="85"/>
-      <c r="R22" s="85"/>
-      <c r="S22" s="85"/>
-      <c r="T22" s="85"/>
-      <c r="U22" s="85"/>
-      <c r="V22" s="85"/>
-      <c r="W22" s="85"/>
-      <c r="X22" s="85"/>
-      <c r="Y22" s="85"/>
-      <c r="Z22" s="85"/>
-      <c r="AA22" s="85"/>
-      <c r="AB22" s="85"/>
-      <c r="AC22" s="85"/>
-      <c r="AD22" s="85"/>
-      <c r="AE22" s="85"/>
-      <c r="AF22" s="85"/>
-      <c r="AG22" s="85"/>
-      <c r="AH22" s="85"/>
-      <c r="AI22" s="85"/>
-      <c r="AJ22" s="86"/>
+      <c r="A22" s="119"/>
+      <c r="B22" s="120"/>
+      <c r="C22" s="120"/>
+      <c r="D22" s="120"/>
+      <c r="E22" s="120"/>
+      <c r="F22" s="120"/>
+      <c r="G22" s="120"/>
+      <c r="H22" s="120"/>
+      <c r="I22" s="120"/>
+      <c r="J22" s="120"/>
+      <c r="K22" s="120"/>
+      <c r="L22" s="120"/>
+      <c r="M22" s="120"/>
+      <c r="N22" s="120"/>
+      <c r="O22" s="120"/>
+      <c r="P22" s="120"/>
+      <c r="Q22" s="120"/>
+      <c r="R22" s="120"/>
+      <c r="S22" s="120"/>
+      <c r="T22" s="120"/>
+      <c r="U22" s="120"/>
+      <c r="V22" s="120"/>
+      <c r="W22" s="120"/>
+      <c r="X22" s="120"/>
+      <c r="Y22" s="120"/>
+      <c r="Z22" s="120"/>
+      <c r="AA22" s="120"/>
+      <c r="AB22" s="120"/>
+      <c r="AC22" s="120"/>
+      <c r="AD22" s="120"/>
+      <c r="AE22" s="120"/>
+      <c r="AF22" s="120"/>
+      <c r="AG22" s="120"/>
+      <c r="AH22" s="120"/>
+      <c r="AI22" s="120"/>
+      <c r="AJ22" s="121"/>
     </row>
     <row r="23" spans="1:36" ht="16.5" customHeight="1">
-      <c r="A23" s="87"/>
-      <c r="B23" s="88"/>
-      <c r="C23" s="88"/>
-      <c r="D23" s="88"/>
-      <c r="E23" s="88"/>
-      <c r="F23" s="88"/>
-      <c r="G23" s="88"/>
-      <c r="H23" s="88"/>
-      <c r="I23" s="88"/>
-      <c r="J23" s="88"/>
-      <c r="K23" s="88"/>
-      <c r="L23" s="88"/>
-      <c r="M23" s="88"/>
-      <c r="N23" s="88"/>
-      <c r="O23" s="88"/>
-      <c r="P23" s="88"/>
-      <c r="Q23" s="88"/>
-      <c r="R23" s="88"/>
-      <c r="S23" s="88"/>
-      <c r="T23" s="88"/>
-      <c r="U23" s="88"/>
-      <c r="V23" s="88"/>
-      <c r="W23" s="88"/>
-      <c r="X23" s="88"/>
-      <c r="Y23" s="88"/>
-      <c r="Z23" s="88"/>
-      <c r="AA23" s="88"/>
-      <c r="AB23" s="88"/>
-      <c r="AC23" s="88"/>
-      <c r="AD23" s="88"/>
-      <c r="AE23" s="88"/>
-      <c r="AF23" s="88"/>
-      <c r="AG23" s="88"/>
-      <c r="AH23" s="88"/>
-      <c r="AI23" s="88"/>
-      <c r="AJ23" s="89"/>
+      <c r="A23" s="122"/>
+      <c r="B23" s="123"/>
+      <c r="C23" s="123"/>
+      <c r="D23" s="123"/>
+      <c r="E23" s="123"/>
+      <c r="F23" s="123"/>
+      <c r="G23" s="123"/>
+      <c r="H23" s="123"/>
+      <c r="I23" s="123"/>
+      <c r="J23" s="123"/>
+      <c r="K23" s="123"/>
+      <c r="L23" s="123"/>
+      <c r="M23" s="123"/>
+      <c r="N23" s="123"/>
+      <c r="O23" s="123"/>
+      <c r="P23" s="123"/>
+      <c r="Q23" s="123"/>
+      <c r="R23" s="123"/>
+      <c r="S23" s="123"/>
+      <c r="T23" s="123"/>
+      <c r="U23" s="123"/>
+      <c r="V23" s="123"/>
+      <c r="W23" s="123"/>
+      <c r="X23" s="123"/>
+      <c r="Y23" s="123"/>
+      <c r="Z23" s="123"/>
+      <c r="AA23" s="123"/>
+      <c r="AB23" s="123"/>
+      <c r="AC23" s="123"/>
+      <c r="AD23" s="123"/>
+      <c r="AE23" s="123"/>
+      <c r="AF23" s="123"/>
+      <c r="AG23" s="123"/>
+      <c r="AH23" s="123"/>
+      <c r="AI23" s="123"/>
+      <c r="AJ23" s="124"/>
     </row>
     <row r="24" spans="1:36" ht="12.75" customHeight="1">
       <c r="A24" s="46" t="s">
@@ -7995,42 +7978,42 @@
       <c r="AJ24" s="47"/>
     </row>
     <row r="25" spans="1:36" ht="18" customHeight="1">
-      <c r="A25" s="79"/>
-      <c r="B25" s="80"/>
-      <c r="C25" s="80"/>
-      <c r="D25" s="80"/>
-      <c r="E25" s="80"/>
-      <c r="F25" s="80"/>
-      <c r="G25" s="80"/>
-      <c r="H25" s="80"/>
-      <c r="I25" s="80"/>
-      <c r="J25" s="80"/>
-      <c r="K25" s="80"/>
-      <c r="L25" s="80"/>
-      <c r="M25" s="80"/>
-      <c r="N25" s="80"/>
-      <c r="O25" s="80"/>
-      <c r="P25" s="80"/>
-      <c r="Q25" s="80"/>
-      <c r="R25" s="80"/>
-      <c r="S25" s="80"/>
-      <c r="T25" s="80"/>
-      <c r="U25" s="80"/>
-      <c r="V25" s="80"/>
-      <c r="W25" s="80"/>
-      <c r="X25" s="80"/>
-      <c r="Y25" s="80"/>
-      <c r="Z25" s="80"/>
-      <c r="AA25" s="80"/>
-      <c r="AB25" s="80"/>
-      <c r="AC25" s="80"/>
-      <c r="AD25" s="80"/>
-      <c r="AE25" s="80"/>
-      <c r="AF25" s="80"/>
-      <c r="AG25" s="80"/>
-      <c r="AH25" s="80"/>
-      <c r="AI25" s="80"/>
-      <c r="AJ25" s="81"/>
+      <c r="A25" s="164"/>
+      <c r="B25" s="165"/>
+      <c r="C25" s="165"/>
+      <c r="D25" s="165"/>
+      <c r="E25" s="165"/>
+      <c r="F25" s="165"/>
+      <c r="G25" s="165"/>
+      <c r="H25" s="165"/>
+      <c r="I25" s="165"/>
+      <c r="J25" s="165"/>
+      <c r="K25" s="165"/>
+      <c r="L25" s="165"/>
+      <c r="M25" s="165"/>
+      <c r="N25" s="165"/>
+      <c r="O25" s="165"/>
+      <c r="P25" s="165"/>
+      <c r="Q25" s="165"/>
+      <c r="R25" s="165"/>
+      <c r="S25" s="165"/>
+      <c r="T25" s="165"/>
+      <c r="U25" s="165"/>
+      <c r="V25" s="165"/>
+      <c r="W25" s="165"/>
+      <c r="X25" s="165"/>
+      <c r="Y25" s="165"/>
+      <c r="Z25" s="165"/>
+      <c r="AA25" s="165"/>
+      <c r="AB25" s="165"/>
+      <c r="AC25" s="165"/>
+      <c r="AD25" s="165"/>
+      <c r="AE25" s="165"/>
+      <c r="AF25" s="165"/>
+      <c r="AG25" s="165"/>
+      <c r="AH25" s="165"/>
+      <c r="AI25" s="165"/>
+      <c r="AJ25" s="166"/>
     </row>
     <row r="26" spans="1:36" ht="12.75" customHeight="1">
       <c r="A26" s="46" t="s">
@@ -8073,137 +8056,137 @@
       <c r="AJ26" s="47"/>
     </row>
     <row r="27" spans="1:36" ht="15" customHeight="1">
-      <c r="A27" s="152"/>
-      <c r="B27" s="153"/>
-      <c r="C27" s="153"/>
-      <c r="D27" s="153"/>
-      <c r="E27" s="153"/>
-      <c r="F27" s="153"/>
-      <c r="G27" s="153"/>
-      <c r="H27" s="153"/>
-      <c r="I27" s="153"/>
-      <c r="J27" s="153"/>
-      <c r="K27" s="153"/>
-      <c r="L27" s="153"/>
-      <c r="M27" s="153"/>
-      <c r="N27" s="153"/>
-      <c r="O27" s="153"/>
-      <c r="P27" s="153"/>
-      <c r="Q27" s="153"/>
-      <c r="R27" s="153"/>
-      <c r="S27" s="153"/>
-      <c r="T27" s="153"/>
-      <c r="U27" s="153"/>
-      <c r="V27" s="153"/>
-      <c r="W27" s="153"/>
-      <c r="X27" s="153"/>
-      <c r="Y27" s="153"/>
-      <c r="Z27" s="153"/>
-      <c r="AA27" s="153"/>
-      <c r="AB27" s="153"/>
-      <c r="AC27" s="153"/>
-      <c r="AD27" s="153"/>
-      <c r="AE27" s="153"/>
-      <c r="AF27" s="153"/>
-      <c r="AG27" s="153"/>
-      <c r="AH27" s="153"/>
-      <c r="AI27" s="153"/>
-      <c r="AJ27" s="154"/>
+      <c r="A27" s="64"/>
+      <c r="B27" s="65"/>
+      <c r="C27" s="65"/>
+      <c r="D27" s="65"/>
+      <c r="E27" s="65"/>
+      <c r="F27" s="65"/>
+      <c r="G27" s="65"/>
+      <c r="H27" s="65"/>
+      <c r="I27" s="65"/>
+      <c r="J27" s="65"/>
+      <c r="K27" s="65"/>
+      <c r="L27" s="65"/>
+      <c r="M27" s="65"/>
+      <c r="N27" s="65"/>
+      <c r="O27" s="65"/>
+      <c r="P27" s="65"/>
+      <c r="Q27" s="65"/>
+      <c r="R27" s="65"/>
+      <c r="S27" s="65"/>
+      <c r="T27" s="65"/>
+      <c r="U27" s="65"/>
+      <c r="V27" s="65"/>
+      <c r="W27" s="65"/>
+      <c r="X27" s="65"/>
+      <c r="Y27" s="65"/>
+      <c r="Z27" s="65"/>
+      <c r="AA27" s="65"/>
+      <c r="AB27" s="65"/>
+      <c r="AC27" s="65"/>
+      <c r="AD27" s="65"/>
+      <c r="AE27" s="65"/>
+      <c r="AF27" s="65"/>
+      <c r="AG27" s="65"/>
+      <c r="AH27" s="65"/>
+      <c r="AI27" s="65"/>
+      <c r="AJ27" s="66"/>
     </row>
     <row r="28" spans="1:36" ht="15" customHeight="1">
-      <c r="A28" s="155"/>
-      <c r="B28" s="153"/>
-      <c r="C28" s="153"/>
-      <c r="D28" s="153"/>
-      <c r="E28" s="153"/>
-      <c r="F28" s="153"/>
-      <c r="G28" s="153"/>
-      <c r="H28" s="153"/>
-      <c r="I28" s="153"/>
-      <c r="J28" s="153"/>
-      <c r="K28" s="153"/>
-      <c r="L28" s="153"/>
-      <c r="M28" s="153"/>
-      <c r="N28" s="153"/>
-      <c r="O28" s="153"/>
-      <c r="P28" s="153"/>
-      <c r="Q28" s="153"/>
-      <c r="R28" s="153"/>
-      <c r="S28" s="153"/>
-      <c r="T28" s="153"/>
-      <c r="U28" s="153"/>
-      <c r="V28" s="153"/>
-      <c r="W28" s="153"/>
-      <c r="X28" s="153"/>
-      <c r="Y28" s="153"/>
-      <c r="Z28" s="153"/>
-      <c r="AA28" s="153"/>
-      <c r="AB28" s="153"/>
-      <c r="AC28" s="153"/>
-      <c r="AD28" s="153"/>
-      <c r="AE28" s="153"/>
-      <c r="AF28" s="153"/>
-      <c r="AG28" s="153"/>
-      <c r="AH28" s="153"/>
-      <c r="AI28" s="153"/>
-      <c r="AJ28" s="154"/>
+      <c r="A28" s="67"/>
+      <c r="B28" s="65"/>
+      <c r="C28" s="65"/>
+      <c r="D28" s="65"/>
+      <c r="E28" s="65"/>
+      <c r="F28" s="65"/>
+      <c r="G28" s="65"/>
+      <c r="H28" s="65"/>
+      <c r="I28" s="65"/>
+      <c r="J28" s="65"/>
+      <c r="K28" s="65"/>
+      <c r="L28" s="65"/>
+      <c r="M28" s="65"/>
+      <c r="N28" s="65"/>
+      <c r="O28" s="65"/>
+      <c r="P28" s="65"/>
+      <c r="Q28" s="65"/>
+      <c r="R28" s="65"/>
+      <c r="S28" s="65"/>
+      <c r="T28" s="65"/>
+      <c r="U28" s="65"/>
+      <c r="V28" s="65"/>
+      <c r="W28" s="65"/>
+      <c r="X28" s="65"/>
+      <c r="Y28" s="65"/>
+      <c r="Z28" s="65"/>
+      <c r="AA28" s="65"/>
+      <c r="AB28" s="65"/>
+      <c r="AC28" s="65"/>
+      <c r="AD28" s="65"/>
+      <c r="AE28" s="65"/>
+      <c r="AF28" s="65"/>
+      <c r="AG28" s="65"/>
+      <c r="AH28" s="65"/>
+      <c r="AI28" s="65"/>
+      <c r="AJ28" s="66"/>
     </row>
     <row r="29" spans="1:36" ht="100.8" customHeight="1">
-      <c r="A29" s="156"/>
-      <c r="B29" s="157"/>
-      <c r="C29" s="157"/>
-      <c r="D29" s="157"/>
-      <c r="E29" s="157"/>
-      <c r="F29" s="157"/>
-      <c r="G29" s="157"/>
-      <c r="H29" s="157"/>
-      <c r="I29" s="157"/>
-      <c r="J29" s="157"/>
-      <c r="K29" s="157"/>
-      <c r="L29" s="157"/>
-      <c r="M29" s="157"/>
-      <c r="N29" s="157"/>
-      <c r="O29" s="157"/>
-      <c r="P29" s="157"/>
-      <c r="Q29" s="157"/>
-      <c r="R29" s="157"/>
-      <c r="S29" s="157"/>
-      <c r="T29" s="157"/>
-      <c r="U29" s="157"/>
-      <c r="V29" s="157"/>
-      <c r="W29" s="157"/>
-      <c r="X29" s="157"/>
-      <c r="Y29" s="157"/>
-      <c r="Z29" s="157"/>
-      <c r="AA29" s="157"/>
-      <c r="AB29" s="157"/>
-      <c r="AC29" s="157"/>
-      <c r="AD29" s="157"/>
-      <c r="AE29" s="157"/>
-      <c r="AF29" s="157"/>
-      <c r="AG29" s="157"/>
-      <c r="AH29" s="157"/>
-      <c r="AI29" s="157"/>
-      <c r="AJ29" s="158"/>
+      <c r="A29" s="68"/>
+      <c r="B29" s="69"/>
+      <c r="C29" s="69"/>
+      <c r="D29" s="69"/>
+      <c r="E29" s="69"/>
+      <c r="F29" s="69"/>
+      <c r="G29" s="69"/>
+      <c r="H29" s="69"/>
+      <c r="I29" s="69"/>
+      <c r="J29" s="69"/>
+      <c r="K29" s="69"/>
+      <c r="L29" s="69"/>
+      <c r="M29" s="69"/>
+      <c r="N29" s="69"/>
+      <c r="O29" s="69"/>
+      <c r="P29" s="69"/>
+      <c r="Q29" s="69"/>
+      <c r="R29" s="69"/>
+      <c r="S29" s="69"/>
+      <c r="T29" s="69"/>
+      <c r="U29" s="69"/>
+      <c r="V29" s="69"/>
+      <c r="W29" s="69"/>
+      <c r="X29" s="69"/>
+      <c r="Y29" s="69"/>
+      <c r="Z29" s="69"/>
+      <c r="AA29" s="69"/>
+      <c r="AB29" s="69"/>
+      <c r="AC29" s="69"/>
+      <c r="AD29" s="69"/>
+      <c r="AE29" s="69"/>
+      <c r="AF29" s="69"/>
+      <c r="AG29" s="69"/>
+      <c r="AH29" s="69"/>
+      <c r="AI29" s="69"/>
+      <c r="AJ29" s="70"/>
     </row>
     <row r="30" spans="1:36" ht="12.75" customHeight="1">
-      <c r="A30" s="159" t="s">
+      <c r="A30" s="78" t="s">
         <v>17</v>
       </c>
-      <c r="B30" s="160"/>
-      <c r="C30" s="160"/>
-      <c r="D30" s="160"/>
-      <c r="E30" s="160"/>
-      <c r="F30" s="160"/>
-      <c r="G30" s="160"/>
-      <c r="H30" s="160"/>
-      <c r="I30" s="160"/>
-      <c r="J30" s="160"/>
-      <c r="K30" s="160"/>
-      <c r="L30" s="160"/>
-      <c r="M30" s="160"/>
-      <c r="N30" s="160"/>
-      <c r="O30" s="160"/>
+      <c r="B30" s="79"/>
+      <c r="C30" s="79"/>
+      <c r="D30" s="79"/>
+      <c r="E30" s="79"/>
+      <c r="F30" s="79"/>
+      <c r="G30" s="79"/>
+      <c r="H30" s="79"/>
+      <c r="I30" s="79"/>
+      <c r="J30" s="79"/>
+      <c r="K30" s="79"/>
+      <c r="L30" s="79"/>
+      <c r="M30" s="79"/>
+      <c r="N30" s="79"/>
+      <c r="O30" s="79"/>
       <c r="P30" s="41"/>
       <c r="Q30" s="41"/>
       <c r="R30" s="41"/>
@@ -8227,216 +8210,216 @@
       <c r="AJ30" s="42"/>
     </row>
     <row r="31" spans="1:36" ht="16.5" customHeight="1">
-      <c r="A31" s="152"/>
-      <c r="B31" s="163"/>
-      <c r="C31" s="163"/>
-      <c r="D31" s="163"/>
-      <c r="E31" s="163"/>
-      <c r="F31" s="163"/>
-      <c r="G31" s="163"/>
-      <c r="H31" s="163"/>
-      <c r="I31" s="163"/>
-      <c r="J31" s="163"/>
-      <c r="K31" s="163"/>
-      <c r="L31" s="163"/>
-      <c r="M31" s="163"/>
-      <c r="N31" s="163"/>
-      <c r="O31" s="163"/>
-      <c r="P31" s="163"/>
-      <c r="Q31" s="163"/>
-      <c r="R31" s="163"/>
-      <c r="S31" s="163"/>
-      <c r="T31" s="163"/>
-      <c r="U31" s="163"/>
-      <c r="V31" s="163"/>
-      <c r="W31" s="163"/>
-      <c r="X31" s="163"/>
-      <c r="Y31" s="163"/>
-      <c r="Z31" s="163"/>
-      <c r="AA31" s="163"/>
-      <c r="AB31" s="163"/>
-      <c r="AC31" s="163"/>
-      <c r="AD31" s="163"/>
-      <c r="AE31" s="163"/>
-      <c r="AF31" s="163"/>
-      <c r="AG31" s="163"/>
-      <c r="AH31" s="163"/>
-      <c r="AI31" s="163"/>
-      <c r="AJ31" s="164"/>
+      <c r="A31" s="64"/>
+      <c r="B31" s="82"/>
+      <c r="C31" s="82"/>
+      <c r="D31" s="82"/>
+      <c r="E31" s="82"/>
+      <c r="F31" s="82"/>
+      <c r="G31" s="82"/>
+      <c r="H31" s="82"/>
+      <c r="I31" s="82"/>
+      <c r="J31" s="82"/>
+      <c r="K31" s="82"/>
+      <c r="L31" s="82"/>
+      <c r="M31" s="82"/>
+      <c r="N31" s="82"/>
+      <c r="O31" s="82"/>
+      <c r="P31" s="82"/>
+      <c r="Q31" s="82"/>
+      <c r="R31" s="82"/>
+      <c r="S31" s="82"/>
+      <c r="T31" s="82"/>
+      <c r="U31" s="82"/>
+      <c r="V31" s="82"/>
+      <c r="W31" s="82"/>
+      <c r="X31" s="82"/>
+      <c r="Y31" s="82"/>
+      <c r="Z31" s="82"/>
+      <c r="AA31" s="82"/>
+      <c r="AB31" s="82"/>
+      <c r="AC31" s="82"/>
+      <c r="AD31" s="82"/>
+      <c r="AE31" s="82"/>
+      <c r="AF31" s="82"/>
+      <c r="AG31" s="82"/>
+      <c r="AH31" s="82"/>
+      <c r="AI31" s="82"/>
+      <c r="AJ31" s="83"/>
     </row>
     <row r="32" spans="1:36" ht="16.5" customHeight="1">
-      <c r="A32" s="152"/>
-      <c r="B32" s="163"/>
-      <c r="C32" s="163"/>
-      <c r="D32" s="163"/>
-      <c r="E32" s="163"/>
-      <c r="F32" s="163"/>
-      <c r="G32" s="163"/>
-      <c r="H32" s="163"/>
-      <c r="I32" s="163"/>
-      <c r="J32" s="163"/>
-      <c r="K32" s="163"/>
-      <c r="L32" s="163"/>
-      <c r="M32" s="163"/>
-      <c r="N32" s="163"/>
-      <c r="O32" s="163"/>
-      <c r="P32" s="163"/>
-      <c r="Q32" s="163"/>
-      <c r="R32" s="163"/>
-      <c r="S32" s="163"/>
-      <c r="T32" s="163"/>
-      <c r="U32" s="163"/>
-      <c r="V32" s="163"/>
-      <c r="W32" s="163"/>
-      <c r="X32" s="163"/>
-      <c r="Y32" s="163"/>
-      <c r="Z32" s="163"/>
-      <c r="AA32" s="163"/>
-      <c r="AB32" s="163"/>
-      <c r="AC32" s="163"/>
-      <c r="AD32" s="163"/>
-      <c r="AE32" s="163"/>
-      <c r="AF32" s="163"/>
-      <c r="AG32" s="163"/>
-      <c r="AH32" s="163"/>
-      <c r="AI32" s="163"/>
-      <c r="AJ32" s="164"/>
+      <c r="A32" s="64"/>
+      <c r="B32" s="82"/>
+      <c r="C32" s="82"/>
+      <c r="D32" s="82"/>
+      <c r="E32" s="82"/>
+      <c r="F32" s="82"/>
+      <c r="G32" s="82"/>
+      <c r="H32" s="82"/>
+      <c r="I32" s="82"/>
+      <c r="J32" s="82"/>
+      <c r="K32" s="82"/>
+      <c r="L32" s="82"/>
+      <c r="M32" s="82"/>
+      <c r="N32" s="82"/>
+      <c r="O32" s="82"/>
+      <c r="P32" s="82"/>
+      <c r="Q32" s="82"/>
+      <c r="R32" s="82"/>
+      <c r="S32" s="82"/>
+      <c r="T32" s="82"/>
+      <c r="U32" s="82"/>
+      <c r="V32" s="82"/>
+      <c r="W32" s="82"/>
+      <c r="X32" s="82"/>
+      <c r="Y32" s="82"/>
+      <c r="Z32" s="82"/>
+      <c r="AA32" s="82"/>
+      <c r="AB32" s="82"/>
+      <c r="AC32" s="82"/>
+      <c r="AD32" s="82"/>
+      <c r="AE32" s="82"/>
+      <c r="AF32" s="82"/>
+      <c r="AG32" s="82"/>
+      <c r="AH32" s="82"/>
+      <c r="AI32" s="82"/>
+      <c r="AJ32" s="83"/>
     </row>
     <row r="33" spans="1:36" ht="16.5" customHeight="1">
-      <c r="A33" s="152"/>
-      <c r="B33" s="163"/>
-      <c r="C33" s="163"/>
-      <c r="D33" s="163"/>
-      <c r="E33" s="163"/>
-      <c r="F33" s="163"/>
-      <c r="G33" s="163"/>
-      <c r="H33" s="163"/>
-      <c r="I33" s="163"/>
-      <c r="J33" s="163"/>
-      <c r="K33" s="163"/>
-      <c r="L33" s="163"/>
-      <c r="M33" s="163"/>
-      <c r="N33" s="163"/>
-      <c r="O33" s="163"/>
-      <c r="P33" s="163"/>
-      <c r="Q33" s="163"/>
-      <c r="R33" s="163"/>
-      <c r="S33" s="163"/>
-      <c r="T33" s="163"/>
-      <c r="U33" s="163"/>
-      <c r="V33" s="163"/>
-      <c r="W33" s="163"/>
-      <c r="X33" s="163"/>
-      <c r="Y33" s="163"/>
-      <c r="Z33" s="163"/>
-      <c r="AA33" s="163"/>
-      <c r="AB33" s="163"/>
-      <c r="AC33" s="163"/>
-      <c r="AD33" s="163"/>
-      <c r="AE33" s="163"/>
-      <c r="AF33" s="163"/>
-      <c r="AG33" s="163"/>
-      <c r="AH33" s="163"/>
-      <c r="AI33" s="163"/>
-      <c r="AJ33" s="164"/>
+      <c r="A33" s="64"/>
+      <c r="B33" s="82"/>
+      <c r="C33" s="82"/>
+      <c r="D33" s="82"/>
+      <c r="E33" s="82"/>
+      <c r="F33" s="82"/>
+      <c r="G33" s="82"/>
+      <c r="H33" s="82"/>
+      <c r="I33" s="82"/>
+      <c r="J33" s="82"/>
+      <c r="K33" s="82"/>
+      <c r="L33" s="82"/>
+      <c r="M33" s="82"/>
+      <c r="N33" s="82"/>
+      <c r="O33" s="82"/>
+      <c r="P33" s="82"/>
+      <c r="Q33" s="82"/>
+      <c r="R33" s="82"/>
+      <c r="S33" s="82"/>
+      <c r="T33" s="82"/>
+      <c r="U33" s="82"/>
+      <c r="V33" s="82"/>
+      <c r="W33" s="82"/>
+      <c r="X33" s="82"/>
+      <c r="Y33" s="82"/>
+      <c r="Z33" s="82"/>
+      <c r="AA33" s="82"/>
+      <c r="AB33" s="82"/>
+      <c r="AC33" s="82"/>
+      <c r="AD33" s="82"/>
+      <c r="AE33" s="82"/>
+      <c r="AF33" s="82"/>
+      <c r="AG33" s="82"/>
+      <c r="AH33" s="82"/>
+      <c r="AI33" s="82"/>
+      <c r="AJ33" s="83"/>
     </row>
     <row r="34" spans="1:36" ht="61.8" customHeight="1">
-      <c r="A34" s="152"/>
-      <c r="B34" s="163"/>
-      <c r="C34" s="163"/>
-      <c r="D34" s="163"/>
-      <c r="E34" s="163"/>
-      <c r="F34" s="163"/>
-      <c r="G34" s="163"/>
-      <c r="H34" s="163"/>
-      <c r="I34" s="163"/>
-      <c r="J34" s="163"/>
-      <c r="K34" s="163"/>
-      <c r="L34" s="163"/>
-      <c r="M34" s="163"/>
-      <c r="N34" s="163"/>
-      <c r="O34" s="163"/>
-      <c r="P34" s="163"/>
-      <c r="Q34" s="163"/>
-      <c r="R34" s="163"/>
-      <c r="S34" s="163"/>
-      <c r="T34" s="163"/>
-      <c r="U34" s="163"/>
-      <c r="V34" s="163"/>
-      <c r="W34" s="163"/>
-      <c r="X34" s="163"/>
-      <c r="Y34" s="163"/>
-      <c r="Z34" s="163"/>
-      <c r="AA34" s="163"/>
-      <c r="AB34" s="163"/>
-      <c r="AC34" s="163"/>
-      <c r="AD34" s="163"/>
-      <c r="AE34" s="163"/>
-      <c r="AF34" s="163"/>
-      <c r="AG34" s="163"/>
-      <c r="AH34" s="163"/>
-      <c r="AI34" s="163"/>
-      <c r="AJ34" s="164"/>
+      <c r="A34" s="64"/>
+      <c r="B34" s="82"/>
+      <c r="C34" s="82"/>
+      <c r="D34" s="82"/>
+      <c r="E34" s="82"/>
+      <c r="F34" s="82"/>
+      <c r="G34" s="82"/>
+      <c r="H34" s="82"/>
+      <c r="I34" s="82"/>
+      <c r="J34" s="82"/>
+      <c r="K34" s="82"/>
+      <c r="L34" s="82"/>
+      <c r="M34" s="82"/>
+      <c r="N34" s="82"/>
+      <c r="O34" s="82"/>
+      <c r="P34" s="82"/>
+      <c r="Q34" s="82"/>
+      <c r="R34" s="82"/>
+      <c r="S34" s="82"/>
+      <c r="T34" s="82"/>
+      <c r="U34" s="82"/>
+      <c r="V34" s="82"/>
+      <c r="W34" s="82"/>
+      <c r="X34" s="82"/>
+      <c r="Y34" s="82"/>
+      <c r="Z34" s="82"/>
+      <c r="AA34" s="82"/>
+      <c r="AB34" s="82"/>
+      <c r="AC34" s="82"/>
+      <c r="AD34" s="82"/>
+      <c r="AE34" s="82"/>
+      <c r="AF34" s="82"/>
+      <c r="AG34" s="82"/>
+      <c r="AH34" s="82"/>
+      <c r="AI34" s="82"/>
+      <c r="AJ34" s="83"/>
     </row>
     <row r="35" spans="1:36" ht="13.2" customHeight="1">
-      <c r="A35" s="165"/>
-      <c r="B35" s="166"/>
-      <c r="C35" s="166"/>
-      <c r="D35" s="166"/>
-      <c r="E35" s="166"/>
-      <c r="F35" s="166"/>
-      <c r="G35" s="166"/>
-      <c r="H35" s="166"/>
-      <c r="I35" s="166"/>
-      <c r="J35" s="166"/>
-      <c r="K35" s="166"/>
-      <c r="L35" s="166"/>
-      <c r="M35" s="166"/>
-      <c r="N35" s="166"/>
-      <c r="O35" s="166"/>
-      <c r="P35" s="166"/>
-      <c r="Q35" s="166"/>
-      <c r="R35" s="166"/>
-      <c r="S35" s="166"/>
-      <c r="T35" s="166"/>
-      <c r="U35" s="166"/>
-      <c r="V35" s="166"/>
-      <c r="W35" s="166"/>
-      <c r="X35" s="166"/>
-      <c r="Y35" s="166"/>
-      <c r="Z35" s="166"/>
-      <c r="AA35" s="166"/>
-      <c r="AB35" s="166"/>
-      <c r="AC35" s="166"/>
-      <c r="AD35" s="166"/>
-      <c r="AE35" s="166"/>
-      <c r="AF35" s="166"/>
-      <c r="AG35" s="166"/>
-      <c r="AH35" s="166"/>
-      <c r="AI35" s="166"/>
-      <c r="AJ35" s="167"/>
+      <c r="A35" s="84"/>
+      <c r="B35" s="85"/>
+      <c r="C35" s="85"/>
+      <c r="D35" s="85"/>
+      <c r="E35" s="85"/>
+      <c r="F35" s="85"/>
+      <c r="G35" s="85"/>
+      <c r="H35" s="85"/>
+      <c r="I35" s="85"/>
+      <c r="J35" s="85"/>
+      <c r="K35" s="85"/>
+      <c r="L35" s="85"/>
+      <c r="M35" s="85"/>
+      <c r="N35" s="85"/>
+      <c r="O35" s="85"/>
+      <c r="P35" s="85"/>
+      <c r="Q35" s="85"/>
+      <c r="R35" s="85"/>
+      <c r="S35" s="85"/>
+      <c r="T35" s="85"/>
+      <c r="U35" s="85"/>
+      <c r="V35" s="85"/>
+      <c r="W35" s="85"/>
+      <c r="X35" s="85"/>
+      <c r="Y35" s="85"/>
+      <c r="Z35" s="85"/>
+      <c r="AA35" s="85"/>
+      <c r="AB35" s="85"/>
+      <c r="AC35" s="85"/>
+      <c r="AD35" s="85"/>
+      <c r="AE35" s="85"/>
+      <c r="AF35" s="85"/>
+      <c r="AG35" s="85"/>
+      <c r="AH35" s="85"/>
+      <c r="AI35" s="85"/>
+      <c r="AJ35" s="86"/>
     </row>
     <row r="36" spans="1:36" ht="13.5" customHeight="1">
-      <c r="A36" s="69" t="s">
+      <c r="A36" s="71" t="s">
         <v>94</v>
       </c>
-      <c r="B36" s="70"/>
-      <c r="C36" s="70"/>
-      <c r="D36" s="70"/>
-      <c r="E36" s="70"/>
-      <c r="F36" s="70"/>
-      <c r="G36" s="70"/>
-      <c r="H36" s="70"/>
-      <c r="I36" s="70"/>
-      <c r="J36" s="70"/>
-      <c r="K36" s="70"/>
-      <c r="L36" s="70"/>
-      <c r="M36" s="70"/>
-      <c r="N36" s="70"/>
-      <c r="O36" s="70"/>
-      <c r="P36" s="70"/>
-      <c r="Q36" s="70"/>
-      <c r="R36" s="70"/>
+      <c r="B36" s="72"/>
+      <c r="C36" s="72"/>
+      <c r="D36" s="72"/>
+      <c r="E36" s="72"/>
+      <c r="F36" s="72"/>
+      <c r="G36" s="72"/>
+      <c r="H36" s="72"/>
+      <c r="I36" s="72"/>
+      <c r="J36" s="72"/>
+      <c r="K36" s="72"/>
+      <c r="L36" s="72"/>
+      <c r="M36" s="72"/>
+      <c r="N36" s="72"/>
+      <c r="O36" s="72"/>
+      <c r="P36" s="72"/>
+      <c r="Q36" s="72"/>
+      <c r="R36" s="72"/>
       <c r="S36" s="40"/>
       <c r="T36" s="40"/>
       <c r="U36" s="40"/>
@@ -8457,178 +8440,178 @@
       <c r="AJ36" s="43"/>
     </row>
     <row r="37" spans="1:36" ht="14.25" customHeight="1">
-      <c r="A37" s="152"/>
-      <c r="B37" s="163"/>
-      <c r="C37" s="163"/>
-      <c r="D37" s="163"/>
-      <c r="E37" s="163"/>
-      <c r="F37" s="163"/>
-      <c r="G37" s="163"/>
-      <c r="H37" s="163"/>
-      <c r="I37" s="163"/>
-      <c r="J37" s="163"/>
-      <c r="K37" s="163"/>
-      <c r="L37" s="163"/>
-      <c r="M37" s="163"/>
-      <c r="N37" s="163"/>
-      <c r="O37" s="163"/>
-      <c r="P37" s="163"/>
-      <c r="Q37" s="163"/>
-      <c r="R37" s="163"/>
-      <c r="S37" s="163"/>
-      <c r="T37" s="163"/>
-      <c r="U37" s="163"/>
-      <c r="V37" s="163"/>
-      <c r="W37" s="163"/>
-      <c r="X37" s="163"/>
-      <c r="Y37" s="163"/>
-      <c r="Z37" s="163"/>
-      <c r="AA37" s="163"/>
-      <c r="AB37" s="163"/>
-      <c r="AC37" s="163"/>
-      <c r="AD37" s="163"/>
-      <c r="AE37" s="163"/>
-      <c r="AF37" s="163"/>
-      <c r="AG37" s="163"/>
-      <c r="AH37" s="163"/>
-      <c r="AI37" s="163"/>
-      <c r="AJ37" s="164"/>
+      <c r="A37" s="64"/>
+      <c r="B37" s="82"/>
+      <c r="C37" s="82"/>
+      <c r="D37" s="82"/>
+      <c r="E37" s="82"/>
+      <c r="F37" s="82"/>
+      <c r="G37" s="82"/>
+      <c r="H37" s="82"/>
+      <c r="I37" s="82"/>
+      <c r="J37" s="82"/>
+      <c r="K37" s="82"/>
+      <c r="L37" s="82"/>
+      <c r="M37" s="82"/>
+      <c r="N37" s="82"/>
+      <c r="O37" s="82"/>
+      <c r="P37" s="82"/>
+      <c r="Q37" s="82"/>
+      <c r="R37" s="82"/>
+      <c r="S37" s="82"/>
+      <c r="T37" s="82"/>
+      <c r="U37" s="82"/>
+      <c r="V37" s="82"/>
+      <c r="W37" s="82"/>
+      <c r="X37" s="82"/>
+      <c r="Y37" s="82"/>
+      <c r="Z37" s="82"/>
+      <c r="AA37" s="82"/>
+      <c r="AB37" s="82"/>
+      <c r="AC37" s="82"/>
+      <c r="AD37" s="82"/>
+      <c r="AE37" s="82"/>
+      <c r="AF37" s="82"/>
+      <c r="AG37" s="82"/>
+      <c r="AH37" s="82"/>
+      <c r="AI37" s="82"/>
+      <c r="AJ37" s="83"/>
     </row>
     <row r="38" spans="1:36" ht="14.25" customHeight="1">
-      <c r="A38" s="152"/>
-      <c r="B38" s="163"/>
-      <c r="C38" s="163"/>
-      <c r="D38" s="163"/>
-      <c r="E38" s="163"/>
-      <c r="F38" s="163"/>
-      <c r="G38" s="163"/>
-      <c r="H38" s="163"/>
-      <c r="I38" s="163"/>
-      <c r="J38" s="163"/>
-      <c r="K38" s="163"/>
-      <c r="L38" s="163"/>
-      <c r="M38" s="163"/>
-      <c r="N38" s="163"/>
-      <c r="O38" s="163"/>
-      <c r="P38" s="163"/>
-      <c r="Q38" s="163"/>
-      <c r="R38" s="163"/>
-      <c r="S38" s="163"/>
-      <c r="T38" s="163"/>
-      <c r="U38" s="163"/>
-      <c r="V38" s="163"/>
-      <c r="W38" s="163"/>
-      <c r="X38" s="163"/>
-      <c r="Y38" s="163"/>
-      <c r="Z38" s="163"/>
-      <c r="AA38" s="163"/>
-      <c r="AB38" s="163"/>
-      <c r="AC38" s="163"/>
-      <c r="AD38" s="163"/>
-      <c r="AE38" s="163"/>
-      <c r="AF38" s="163"/>
-      <c r="AG38" s="163"/>
-      <c r="AH38" s="163"/>
-      <c r="AI38" s="163"/>
-      <c r="AJ38" s="164"/>
+      <c r="A38" s="64"/>
+      <c r="B38" s="82"/>
+      <c r="C38" s="82"/>
+      <c r="D38" s="82"/>
+      <c r="E38" s="82"/>
+      <c r="F38" s="82"/>
+      <c r="G38" s="82"/>
+      <c r="H38" s="82"/>
+      <c r="I38" s="82"/>
+      <c r="J38" s="82"/>
+      <c r="K38" s="82"/>
+      <c r="L38" s="82"/>
+      <c r="M38" s="82"/>
+      <c r="N38" s="82"/>
+      <c r="O38" s="82"/>
+      <c r="P38" s="82"/>
+      <c r="Q38" s="82"/>
+      <c r="R38" s="82"/>
+      <c r="S38" s="82"/>
+      <c r="T38" s="82"/>
+      <c r="U38" s="82"/>
+      <c r="V38" s="82"/>
+      <c r="W38" s="82"/>
+      <c r="X38" s="82"/>
+      <c r="Y38" s="82"/>
+      <c r="Z38" s="82"/>
+      <c r="AA38" s="82"/>
+      <c r="AB38" s="82"/>
+      <c r="AC38" s="82"/>
+      <c r="AD38" s="82"/>
+      <c r="AE38" s="82"/>
+      <c r="AF38" s="82"/>
+      <c r="AG38" s="82"/>
+      <c r="AH38" s="82"/>
+      <c r="AI38" s="82"/>
+      <c r="AJ38" s="83"/>
     </row>
     <row r="39" spans="1:36" ht="27.6" customHeight="1">
-      <c r="A39" s="152"/>
-      <c r="B39" s="163"/>
-      <c r="C39" s="163"/>
-      <c r="D39" s="163"/>
-      <c r="E39" s="163"/>
-      <c r="F39" s="163"/>
-      <c r="G39" s="163"/>
-      <c r="H39" s="163"/>
-      <c r="I39" s="163"/>
-      <c r="J39" s="163"/>
-      <c r="K39" s="163"/>
-      <c r="L39" s="163"/>
-      <c r="M39" s="163"/>
-      <c r="N39" s="163"/>
-      <c r="O39" s="163"/>
-      <c r="P39" s="163"/>
-      <c r="Q39" s="163"/>
-      <c r="R39" s="163"/>
-      <c r="S39" s="163"/>
-      <c r="T39" s="163"/>
-      <c r="U39" s="163"/>
-      <c r="V39" s="163"/>
-      <c r="W39" s="163"/>
-      <c r="X39" s="163"/>
-      <c r="Y39" s="163"/>
-      <c r="Z39" s="163"/>
-      <c r="AA39" s="163"/>
-      <c r="AB39" s="163"/>
-      <c r="AC39" s="163"/>
-      <c r="AD39" s="163"/>
-      <c r="AE39" s="163"/>
-      <c r="AF39" s="163"/>
-      <c r="AG39" s="163"/>
-      <c r="AH39" s="163"/>
-      <c r="AI39" s="163"/>
-      <c r="AJ39" s="164"/>
+      <c r="A39" s="64"/>
+      <c r="B39" s="82"/>
+      <c r="C39" s="82"/>
+      <c r="D39" s="82"/>
+      <c r="E39" s="82"/>
+      <c r="F39" s="82"/>
+      <c r="G39" s="82"/>
+      <c r="H39" s="82"/>
+      <c r="I39" s="82"/>
+      <c r="J39" s="82"/>
+      <c r="K39" s="82"/>
+      <c r="L39" s="82"/>
+      <c r="M39" s="82"/>
+      <c r="N39" s="82"/>
+      <c r="O39" s="82"/>
+      <c r="P39" s="82"/>
+      <c r="Q39" s="82"/>
+      <c r="R39" s="82"/>
+      <c r="S39" s="82"/>
+      <c r="T39" s="82"/>
+      <c r="U39" s="82"/>
+      <c r="V39" s="82"/>
+      <c r="W39" s="82"/>
+      <c r="X39" s="82"/>
+      <c r="Y39" s="82"/>
+      <c r="Z39" s="82"/>
+      <c r="AA39" s="82"/>
+      <c r="AB39" s="82"/>
+      <c r="AC39" s="82"/>
+      <c r="AD39" s="82"/>
+      <c r="AE39" s="82"/>
+      <c r="AF39" s="82"/>
+      <c r="AG39" s="82"/>
+      <c r="AH39" s="82"/>
+      <c r="AI39" s="82"/>
+      <c r="AJ39" s="83"/>
     </row>
     <row r="40" spans="1:36" ht="16.8" customHeight="1">
-      <c r="A40" s="152"/>
-      <c r="B40" s="163"/>
-      <c r="C40" s="163"/>
-      <c r="D40" s="163"/>
-      <c r="E40" s="163"/>
-      <c r="F40" s="163"/>
-      <c r="G40" s="163"/>
-      <c r="H40" s="163"/>
-      <c r="I40" s="163"/>
-      <c r="J40" s="163"/>
-      <c r="K40" s="163"/>
-      <c r="L40" s="163"/>
-      <c r="M40" s="163"/>
-      <c r="N40" s="163"/>
-      <c r="O40" s="163"/>
-      <c r="P40" s="163"/>
-      <c r="Q40" s="163"/>
-      <c r="R40" s="163"/>
-      <c r="S40" s="163"/>
-      <c r="T40" s="163"/>
-      <c r="U40" s="163"/>
-      <c r="V40" s="163"/>
-      <c r="W40" s="163"/>
-      <c r="X40" s="163"/>
-      <c r="Y40" s="163"/>
-      <c r="Z40" s="163"/>
-      <c r="AA40" s="163"/>
-      <c r="AB40" s="163"/>
-      <c r="AC40" s="163"/>
-      <c r="AD40" s="163"/>
-      <c r="AE40" s="163"/>
-      <c r="AF40" s="163"/>
-      <c r="AG40" s="163"/>
-      <c r="AH40" s="163"/>
-      <c r="AI40" s="163"/>
-      <c r="AJ40" s="164"/>
+      <c r="A40" s="64"/>
+      <c r="B40" s="82"/>
+      <c r="C40" s="82"/>
+      <c r="D40" s="82"/>
+      <c r="E40" s="82"/>
+      <c r="F40" s="82"/>
+      <c r="G40" s="82"/>
+      <c r="H40" s="82"/>
+      <c r="I40" s="82"/>
+      <c r="J40" s="82"/>
+      <c r="K40" s="82"/>
+      <c r="L40" s="82"/>
+      <c r="M40" s="82"/>
+      <c r="N40" s="82"/>
+      <c r="O40" s="82"/>
+      <c r="P40" s="82"/>
+      <c r="Q40" s="82"/>
+      <c r="R40" s="82"/>
+      <c r="S40" s="82"/>
+      <c r="T40" s="82"/>
+      <c r="U40" s="82"/>
+      <c r="V40" s="82"/>
+      <c r="W40" s="82"/>
+      <c r="X40" s="82"/>
+      <c r="Y40" s="82"/>
+      <c r="Z40" s="82"/>
+      <c r="AA40" s="82"/>
+      <c r="AB40" s="82"/>
+      <c r="AC40" s="82"/>
+      <c r="AD40" s="82"/>
+      <c r="AE40" s="82"/>
+      <c r="AF40" s="82"/>
+      <c r="AG40" s="82"/>
+      <c r="AH40" s="82"/>
+      <c r="AI40" s="82"/>
+      <c r="AJ40" s="83"/>
     </row>
     <row r="41" spans="1:36" ht="16.8" customHeight="1">
-      <c r="A41" s="69" t="s">
+      <c r="A41" s="71" t="s">
         <v>99</v>
       </c>
-      <c r="B41" s="70"/>
-      <c r="C41" s="70"/>
-      <c r="D41" s="70"/>
-      <c r="E41" s="70"/>
-      <c r="F41" s="70"/>
-      <c r="G41" s="70"/>
-      <c r="H41" s="70"/>
-      <c r="I41" s="70"/>
-      <c r="J41" s="70"/>
-      <c r="K41" s="70"/>
-      <c r="L41" s="70"/>
-      <c r="M41" s="70"/>
-      <c r="N41" s="70"/>
-      <c r="O41" s="70"/>
-      <c r="P41" s="70"/>
-      <c r="Q41" s="70"/>
-      <c r="R41" s="70"/>
+      <c r="B41" s="72"/>
+      <c r="C41" s="72"/>
+      <c r="D41" s="72"/>
+      <c r="E41" s="72"/>
+      <c r="F41" s="72"/>
+      <c r="G41" s="72"/>
+      <c r="H41" s="72"/>
+      <c r="I41" s="72"/>
+      <c r="J41" s="72"/>
+      <c r="K41" s="72"/>
+      <c r="L41" s="72"/>
+      <c r="M41" s="72"/>
+      <c r="N41" s="72"/>
+      <c r="O41" s="72"/>
+      <c r="P41" s="72"/>
+      <c r="Q41" s="72"/>
+      <c r="R41" s="72"/>
       <c r="S41" s="40"/>
       <c r="T41" s="40"/>
       <c r="U41" s="40"/>
@@ -8649,804 +8632,804 @@
       <c r="AJ41" s="43"/>
     </row>
     <row r="42" spans="1:36" ht="16.8" customHeight="1">
-      <c r="A42" s="53"/>
-      <c r="B42" s="54"/>
-      <c r="C42" s="54"/>
-      <c r="D42" s="54"/>
-      <c r="E42" s="54"/>
-      <c r="F42" s="54"/>
-      <c r="G42" s="54"/>
-      <c r="H42" s="54"/>
-      <c r="I42" s="54"/>
-      <c r="J42" s="54"/>
-      <c r="K42" s="54"/>
-      <c r="L42" s="54"/>
-      <c r="M42" s="54"/>
-      <c r="N42" s="54"/>
-      <c r="O42" s="54"/>
-      <c r="P42" s="54"/>
-      <c r="Q42" s="54"/>
-      <c r="R42" s="54"/>
-      <c r="S42" s="54"/>
-      <c r="T42" s="54"/>
-      <c r="U42" s="54"/>
-      <c r="V42" s="54"/>
-      <c r="W42" s="54"/>
-      <c r="X42" s="54"/>
-      <c r="Y42" s="54"/>
-      <c r="Z42" s="54"/>
-      <c r="AA42" s="54"/>
-      <c r="AB42" s="54"/>
-      <c r="AC42" s="54"/>
-      <c r="AD42" s="54"/>
-      <c r="AE42" s="54"/>
-      <c r="AF42" s="54"/>
-      <c r="AG42" s="54"/>
-      <c r="AH42" s="54"/>
-      <c r="AI42" s="54"/>
-      <c r="AJ42" s="55"/>
+      <c r="A42" s="51"/>
+      <c r="B42" s="52"/>
+      <c r="C42" s="52"/>
+      <c r="D42" s="52"/>
+      <c r="E42" s="52"/>
+      <c r="F42" s="52"/>
+      <c r="G42" s="52"/>
+      <c r="H42" s="52"/>
+      <c r="I42" s="52"/>
+      <c r="J42" s="52"/>
+      <c r="K42" s="52"/>
+      <c r="L42" s="52"/>
+      <c r="M42" s="52"/>
+      <c r="N42" s="52"/>
+      <c r="O42" s="52"/>
+      <c r="P42" s="52"/>
+      <c r="Q42" s="52"/>
+      <c r="R42" s="52"/>
+      <c r="S42" s="52"/>
+      <c r="T42" s="52"/>
+      <c r="U42" s="52"/>
+      <c r="V42" s="52"/>
+      <c r="W42" s="52"/>
+      <c r="X42" s="52"/>
+      <c r="Y42" s="52"/>
+      <c r="Z42" s="52"/>
+      <c r="AA42" s="52"/>
+      <c r="AB42" s="52"/>
+      <c r="AC42" s="52"/>
+      <c r="AD42" s="52"/>
+      <c r="AE42" s="52"/>
+      <c r="AF42" s="52"/>
+      <c r="AG42" s="52"/>
+      <c r="AH42" s="52"/>
+      <c r="AI42" s="52"/>
+      <c r="AJ42" s="53"/>
     </row>
     <row r="43" spans="1:36" ht="17.25" customHeight="1">
-      <c r="A43" s="98" t="s">
+      <c r="A43" s="74" t="s">
         <v>18</v>
       </c>
-      <c r="B43" s="99"/>
-      <c r="C43" s="99"/>
-      <c r="D43" s="99"/>
-      <c r="E43" s="99"/>
-      <c r="F43" s="99"/>
-      <c r="G43" s="99"/>
-      <c r="H43" s="99"/>
-      <c r="I43" s="100"/>
-      <c r="J43" s="98" t="s">
+      <c r="B43" s="75"/>
+      <c r="C43" s="75"/>
+      <c r="D43" s="75"/>
+      <c r="E43" s="75"/>
+      <c r="F43" s="75"/>
+      <c r="G43" s="75"/>
+      <c r="H43" s="75"/>
+      <c r="I43" s="76"/>
+      <c r="J43" s="74" t="s">
         <v>19</v>
       </c>
-      <c r="K43" s="99"/>
-      <c r="L43" s="99"/>
-      <c r="M43" s="99"/>
-      <c r="N43" s="99"/>
-      <c r="O43" s="99"/>
-      <c r="P43" s="99"/>
-      <c r="Q43" s="99"/>
-      <c r="R43" s="100"/>
-      <c r="S43" s="98" t="s">
+      <c r="K43" s="75"/>
+      <c r="L43" s="75"/>
+      <c r="M43" s="75"/>
+      <c r="N43" s="75"/>
+      <c r="O43" s="75"/>
+      <c r="P43" s="75"/>
+      <c r="Q43" s="75"/>
+      <c r="R43" s="76"/>
+      <c r="S43" s="74" t="s">
         <v>77</v>
       </c>
-      <c r="T43" s="99"/>
-      <c r="U43" s="99"/>
-      <c r="V43" s="99"/>
-      <c r="W43" s="99"/>
-      <c r="X43" s="99"/>
-      <c r="Y43" s="99"/>
-      <c r="Z43" s="99"/>
-      <c r="AA43" s="100"/>
-      <c r="AB43" s="161" t="s">
+      <c r="T43" s="75"/>
+      <c r="U43" s="75"/>
+      <c r="V43" s="75"/>
+      <c r="W43" s="75"/>
+      <c r="X43" s="75"/>
+      <c r="Y43" s="75"/>
+      <c r="Z43" s="75"/>
+      <c r="AA43" s="76"/>
+      <c r="AB43" s="80" t="s">
         <v>91</v>
       </c>
-      <c r="AC43" s="99"/>
-      <c r="AD43" s="99"/>
-      <c r="AE43" s="99"/>
-      <c r="AF43" s="99"/>
-      <c r="AG43" s="99"/>
-      <c r="AH43" s="99"/>
-      <c r="AI43" s="99"/>
-      <c r="AJ43" s="100"/>
+      <c r="AC43" s="75"/>
+      <c r="AD43" s="75"/>
+      <c r="AE43" s="75"/>
+      <c r="AF43" s="75"/>
+      <c r="AG43" s="75"/>
+      <c r="AH43" s="75"/>
+      <c r="AI43" s="75"/>
+      <c r="AJ43" s="76"/>
     </row>
     <row r="44" spans="1:36" ht="18" customHeight="1">
       <c r="A44" s="2"/>
-      <c r="B44" s="127" t="s">
+      <c r="B44" s="63" t="s">
         <v>21</v>
       </c>
-      <c r="C44" s="127"/>
-      <c r="D44" s="127"/>
-      <c r="E44" s="127"/>
-      <c r="F44" s="127"/>
-      <c r="G44" s="127"/>
-      <c r="H44" s="127"/>
-      <c r="I44" s="128"/>
+      <c r="C44" s="63"/>
+      <c r="D44" s="63"/>
+      <c r="E44" s="63"/>
+      <c r="F44" s="63"/>
+      <c r="G44" s="63"/>
+      <c r="H44" s="63"/>
+      <c r="I44" s="73"/>
       <c r="J44" s="10"/>
-      <c r="K44" s="172" t="s">
+      <c r="K44" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="L44" s="172"/>
-      <c r="M44" s="172"/>
-      <c r="N44" s="172"/>
-      <c r="O44" s="172"/>
-      <c r="P44" s="172"/>
-      <c r="Q44" s="172"/>
-      <c r="R44" s="173"/>
-      <c r="S44" s="124" t="s">
+      <c r="L44" s="3"/>
+      <c r="M44" s="3"/>
+      <c r="N44" s="3"/>
+      <c r="O44" s="3"/>
+      <c r="P44" s="3"/>
+      <c r="Q44" s="3"/>
+      <c r="R44" s="12"/>
+      <c r="S44" s="87" t="s">
         <v>81</v>
       </c>
-      <c r="T44" s="76"/>
-      <c r="U44" s="76"/>
-      <c r="V44" s="76"/>
-      <c r="W44" s="162"/>
-      <c r="X44" s="162"/>
-      <c r="Y44" s="162"/>
-      <c r="Z44" s="49"/>
+      <c r="T44" s="88"/>
+      <c r="U44" s="88"/>
+      <c r="V44" s="88"/>
+      <c r="W44" s="81"/>
+      <c r="X44" s="81"/>
+      <c r="Y44" s="81"/>
+      <c r="Z44" s="48"/>
       <c r="AA44" s="4"/>
-      <c r="AB44" s="125" t="s">
+      <c r="AB44" s="114" t="s">
         <v>82</v>
       </c>
-      <c r="AC44" s="71"/>
-      <c r="AD44" s="71"/>
-      <c r="AE44" s="71"/>
-      <c r="AF44" s="132"/>
-      <c r="AG44" s="132"/>
-      <c r="AH44" s="132"/>
-      <c r="AI44" s="132"/>
+      <c r="AC44" s="115"/>
+      <c r="AD44" s="115"/>
+      <c r="AE44" s="115"/>
+      <c r="AF44" s="77"/>
+      <c r="AG44" s="77"/>
+      <c r="AH44" s="77"/>
+      <c r="AI44" s="77"/>
       <c r="AJ44" s="4"/>
     </row>
     <row r="45" spans="1:36" ht="18" customHeight="1">
       <c r="A45" s="2"/>
-      <c r="B45" s="127" t="s">
+      <c r="B45" s="63" t="s">
         <v>24</v>
       </c>
-      <c r="C45" s="127"/>
-      <c r="D45" s="127"/>
-      <c r="E45" s="127"/>
-      <c r="F45" s="127"/>
-      <c r="G45" s="127"/>
-      <c r="H45" s="127"/>
-      <c r="I45" s="128"/>
+      <c r="C45" s="63"/>
+      <c r="D45" s="63"/>
+      <c r="E45" s="63"/>
+      <c r="F45" s="63"/>
+      <c r="G45" s="63"/>
+      <c r="H45" s="63"/>
+      <c r="I45" s="73"/>
       <c r="J45" s="10"/>
-      <c r="K45" s="172" t="s">
+      <c r="K45" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="L45" s="172"/>
-      <c r="M45" s="172"/>
-      <c r="N45" s="172"/>
-      <c r="O45" s="172"/>
-      <c r="P45" s="172"/>
-      <c r="Q45" s="172"/>
-      <c r="R45" s="173"/>
-      <c r="S45" s="124" t="s">
+      <c r="L45" s="3"/>
+      <c r="M45" s="3"/>
+      <c r="N45" s="3"/>
+      <c r="O45" s="3"/>
+      <c r="P45" s="3"/>
+      <c r="Q45" s="3"/>
+      <c r="R45" s="12"/>
+      <c r="S45" s="87" t="s">
         <v>80</v>
       </c>
-      <c r="T45" s="76"/>
-      <c r="U45" s="76"/>
-      <c r="V45" s="76"/>
-      <c r="W45" s="151"/>
-      <c r="X45" s="151"/>
-      <c r="Y45" s="151"/>
-      <c r="Z45" s="151"/>
+      <c r="T45" s="88"/>
+      <c r="U45" s="88"/>
+      <c r="V45" s="88"/>
+      <c r="W45" s="62"/>
+      <c r="X45" s="62"/>
+      <c r="Y45" s="62"/>
+      <c r="Z45" s="62"/>
       <c r="AA45" s="4"/>
-      <c r="AB45" s="124" t="s">
+      <c r="AB45" s="87" t="s">
         <v>81</v>
       </c>
-      <c r="AC45" s="76"/>
-      <c r="AD45" s="76"/>
-      <c r="AE45" s="76"/>
-      <c r="AF45" s="151"/>
-      <c r="AG45" s="151"/>
-      <c r="AH45" s="151"/>
-      <c r="AI45" s="151"/>
+      <c r="AC45" s="88"/>
+      <c r="AD45" s="88"/>
+      <c r="AE45" s="88"/>
+      <c r="AF45" s="62"/>
+      <c r="AG45" s="62"/>
+      <c r="AH45" s="62"/>
+      <c r="AI45" s="62"/>
       <c r="AJ45" s="4"/>
     </row>
     <row r="46" spans="1:36" ht="18" customHeight="1">
       <c r="A46" s="2"/>
-      <c r="B46" s="127" t="s">
+      <c r="B46" s="63" t="s">
         <v>27</v>
       </c>
-      <c r="C46" s="127"/>
-      <c r="D46" s="127"/>
-      <c r="E46" s="127"/>
-      <c r="F46" s="127"/>
-      <c r="G46" s="127"/>
-      <c r="H46" s="127"/>
-      <c r="I46" s="128"/>
+      <c r="C46" s="63"/>
+      <c r="D46" s="63"/>
+      <c r="E46" s="63"/>
+      <c r="F46" s="63"/>
+      <c r="G46" s="63"/>
+      <c r="H46" s="63"/>
+      <c r="I46" s="73"/>
       <c r="J46" s="10"/>
-      <c r="K46" s="172" t="s">
+      <c r="K46" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="L46" s="172"/>
-      <c r="M46" s="172"/>
-      <c r="N46" s="172"/>
-      <c r="O46" s="172"/>
-      <c r="P46" s="172"/>
-      <c r="Q46" s="172"/>
-      <c r="R46" s="173"/>
-      <c r="S46" s="125" t="s">
+      <c r="L46" s="3"/>
+      <c r="M46" s="3"/>
+      <c r="N46" s="3"/>
+      <c r="O46" s="3"/>
+      <c r="P46" s="3"/>
+      <c r="Q46" s="3"/>
+      <c r="R46" s="12"/>
+      <c r="S46" s="114" t="s">
         <v>78</v>
       </c>
-      <c r="T46" s="71"/>
-      <c r="U46" s="71"/>
-      <c r="V46" s="71"/>
-      <c r="W46" s="71"/>
-      <c r="X46" s="126"/>
-      <c r="Y46" s="126"/>
-      <c r="Z46" s="126"/>
+      <c r="T46" s="115"/>
+      <c r="U46" s="115"/>
+      <c r="V46" s="115"/>
+      <c r="W46" s="115"/>
+      <c r="X46" s="96"/>
+      <c r="Y46" s="96"/>
+      <c r="Z46" s="96"/>
       <c r="AA46" s="12" t="s">
         <v>30</v>
       </c>
-      <c r="AB46" s="124" t="s">
+      <c r="AB46" s="87" t="s">
         <v>80</v>
       </c>
-      <c r="AC46" s="76"/>
-      <c r="AD46" s="76"/>
-      <c r="AE46" s="76"/>
-      <c r="AF46" s="151"/>
-      <c r="AG46" s="151"/>
-      <c r="AH46" s="151"/>
-      <c r="AI46" s="151"/>
+      <c r="AC46" s="88"/>
+      <c r="AD46" s="88"/>
+      <c r="AE46" s="88"/>
+      <c r="AF46" s="62"/>
+      <c r="AG46" s="62"/>
+      <c r="AH46" s="62"/>
+      <c r="AI46" s="62"/>
       <c r="AJ46" s="4"/>
     </row>
     <row r="47" spans="1:36" ht="18" customHeight="1">
       <c r="A47" s="2"/>
-      <c r="B47" s="127" t="s">
+      <c r="B47" s="63" t="s">
         <v>87</v>
       </c>
-      <c r="C47" s="127"/>
-      <c r="D47" s="127"/>
-      <c r="E47" s="127"/>
-      <c r="F47" s="127"/>
-      <c r="G47" s="127"/>
-      <c r="H47" s="127"/>
-      <c r="I47" s="128"/>
+      <c r="C47" s="63"/>
+      <c r="D47" s="63"/>
+      <c r="E47" s="63"/>
+      <c r="F47" s="63"/>
+      <c r="G47" s="63"/>
+      <c r="H47" s="63"/>
+      <c r="I47" s="73"/>
       <c r="J47" s="10"/>
-      <c r="K47" s="172" t="s">
+      <c r="K47" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="L47" s="172"/>
-      <c r="M47" s="172"/>
-      <c r="N47" s="172"/>
-      <c r="O47" s="172"/>
-      <c r="P47" s="172"/>
-      <c r="Q47" s="172"/>
-      <c r="R47" s="173"/>
-      <c r="S47" s="129" t="s">
+      <c r="L47" s="3"/>
+      <c r="M47" s="3"/>
+      <c r="N47" s="3"/>
+      <c r="O47" s="3"/>
+      <c r="P47" s="3"/>
+      <c r="Q47" s="3"/>
+      <c r="R47" s="12"/>
+      <c r="S47" s="104" t="s">
         <v>79</v>
       </c>
-      <c r="T47" s="130"/>
-      <c r="U47" s="130"/>
-      <c r="V47" s="130"/>
-      <c r="W47" s="130"/>
-      <c r="X47" s="146"/>
-      <c r="Y47" s="146"/>
-      <c r="Z47" s="146"/>
+      <c r="T47" s="105"/>
+      <c r="U47" s="105"/>
+      <c r="V47" s="105"/>
+      <c r="W47" s="105"/>
+      <c r="X47" s="61"/>
+      <c r="Y47" s="61"/>
+      <c r="Z47" s="61"/>
       <c r="AA47" s="33" t="s">
         <v>30</v>
       </c>
-      <c r="AB47" s="124" t="s">
+      <c r="AB47" s="87" t="s">
         <v>83</v>
       </c>
-      <c r="AC47" s="76"/>
-      <c r="AD47" s="76"/>
-      <c r="AE47" s="76"/>
-      <c r="AF47" s="132"/>
-      <c r="AG47" s="132"/>
-      <c r="AH47" s="132"/>
-      <c r="AI47" s="132"/>
+      <c r="AC47" s="88"/>
+      <c r="AD47" s="88"/>
+      <c r="AE47" s="88"/>
+      <c r="AF47" s="77"/>
+      <c r="AG47" s="77"/>
+      <c r="AH47" s="77"/>
+      <c r="AI47" s="77"/>
       <c r="AJ47" s="4"/>
     </row>
     <row r="48" spans="1:36" ht="18" customHeight="1">
       <c r="A48" s="34"/>
-      <c r="B48" s="127" t="s">
+      <c r="B48" s="63" t="s">
         <v>33</v>
       </c>
-      <c r="C48" s="127"/>
-      <c r="D48" s="127"/>
-      <c r="E48" s="127"/>
-      <c r="F48" s="127"/>
-      <c r="G48" s="127"/>
-      <c r="H48" s="127"/>
-      <c r="I48" s="128"/>
+      <c r="C48" s="63"/>
+      <c r="D48" s="63"/>
+      <c r="E48" s="63"/>
+      <c r="F48" s="63"/>
+      <c r="G48" s="63"/>
+      <c r="H48" s="63"/>
+      <c r="I48" s="73"/>
       <c r="J48" s="10"/>
-      <c r="K48" s="172" t="s">
+      <c r="K48" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="L48" s="172"/>
-      <c r="M48" s="172"/>
-      <c r="N48" s="174"/>
-      <c r="O48" s="172"/>
-      <c r="P48" s="172"/>
-      <c r="Q48" s="172"/>
-      <c r="R48" s="173"/>
-      <c r="S48" s="142" t="s">
+      <c r="L48" s="3"/>
+      <c r="M48" s="3"/>
+      <c r="N48" s="59"/>
+      <c r="O48" s="3"/>
+      <c r="P48" s="3"/>
+      <c r="Q48" s="3"/>
+      <c r="R48" s="12"/>
+      <c r="S48" s="93" t="s">
         <v>20</v>
       </c>
-      <c r="T48" s="143"/>
-      <c r="U48" s="143"/>
-      <c r="V48" s="143"/>
-      <c r="W48" s="143"/>
-      <c r="X48" s="143"/>
-      <c r="Y48" s="143"/>
-      <c r="Z48" s="143"/>
-      <c r="AA48" s="144"/>
-      <c r="AB48" s="125" t="s">
+      <c r="T48" s="94"/>
+      <c r="U48" s="94"/>
+      <c r="V48" s="94"/>
+      <c r="W48" s="94"/>
+      <c r="X48" s="94"/>
+      <c r="Y48" s="94"/>
+      <c r="Z48" s="94"/>
+      <c r="AA48" s="95"/>
+      <c r="AB48" s="114" t="s">
         <v>78</v>
       </c>
-      <c r="AC48" s="71"/>
-      <c r="AD48" s="71"/>
-      <c r="AE48" s="71"/>
-      <c r="AF48" s="71"/>
-      <c r="AG48" s="126"/>
-      <c r="AH48" s="126"/>
-      <c r="AI48" s="126"/>
+      <c r="AC48" s="115"/>
+      <c r="AD48" s="115"/>
+      <c r="AE48" s="115"/>
+      <c r="AF48" s="115"/>
+      <c r="AG48" s="96"/>
+      <c r="AH48" s="96"/>
+      <c r="AI48" s="96"/>
       <c r="AJ48" s="12" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="49" spans="1:36" ht="18" customHeight="1">
       <c r="A49" s="10"/>
-      <c r="B49" s="127" t="s">
+      <c r="B49" s="63" t="s">
         <v>74</v>
       </c>
-      <c r="C49" s="127"/>
-      <c r="D49" s="127"/>
-      <c r="E49" s="127"/>
-      <c r="F49" s="127"/>
-      <c r="G49" s="127"/>
-      <c r="H49" s="127"/>
-      <c r="I49" s="128"/>
+      <c r="C49" s="63"/>
+      <c r="D49" s="63"/>
+      <c r="E49" s="63"/>
+      <c r="F49" s="63"/>
+      <c r="G49" s="63"/>
+      <c r="H49" s="63"/>
+      <c r="I49" s="73"/>
       <c r="J49" s="10"/>
-      <c r="K49" s="172" t="s">
+      <c r="K49" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="L49" s="172"/>
-      <c r="M49" s="172"/>
-      <c r="N49" s="172"/>
-      <c r="O49" s="172"/>
-      <c r="P49" s="172"/>
-      <c r="Q49" s="172"/>
-      <c r="R49" s="173"/>
+      <c r="L49" s="3"/>
+      <c r="M49" s="3"/>
+      <c r="N49" s="3"/>
+      <c r="O49" s="3"/>
+      <c r="P49" s="3"/>
+      <c r="Q49" s="3"/>
+      <c r="R49" s="12"/>
       <c r="S49" s="10"/>
-      <c r="T49" s="127" t="s">
+      <c r="T49" s="63" t="s">
         <v>23</v>
       </c>
-      <c r="U49" s="127"/>
-      <c r="V49" s="127"/>
-      <c r="W49" s="127"/>
-      <c r="X49" s="127"/>
-      <c r="Y49" s="127"/>
-      <c r="Z49" s="127"/>
-      <c r="AA49" s="128"/>
-      <c r="AB49" s="129" t="s">
+      <c r="U49" s="63"/>
+      <c r="V49" s="63"/>
+      <c r="W49" s="63"/>
+      <c r="X49" s="63"/>
+      <c r="Y49" s="63"/>
+      <c r="Z49" s="63"/>
+      <c r="AA49" s="73"/>
+      <c r="AB49" s="104" t="s">
         <v>79</v>
       </c>
-      <c r="AC49" s="130"/>
-      <c r="AD49" s="130"/>
-      <c r="AE49" s="130"/>
-      <c r="AF49" s="130"/>
-      <c r="AG49" s="146"/>
-      <c r="AH49" s="146"/>
-      <c r="AI49" s="146"/>
+      <c r="AC49" s="105"/>
+      <c r="AD49" s="105"/>
+      <c r="AE49" s="105"/>
+      <c r="AF49" s="105"/>
+      <c r="AG49" s="61"/>
+      <c r="AH49" s="61"/>
+      <c r="AI49" s="61"/>
       <c r="AJ49" s="33" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="50" spans="1:36" ht="18" customHeight="1">
       <c r="A50" s="10"/>
-      <c r="B50" s="127" t="s">
+      <c r="B50" s="63" t="s">
         <v>75</v>
       </c>
-      <c r="C50" s="127"/>
-      <c r="D50" s="127"/>
-      <c r="E50" s="127"/>
-      <c r="F50" s="127"/>
-      <c r="G50" s="127"/>
-      <c r="H50" s="127"/>
-      <c r="I50" s="128"/>
+      <c r="C50" s="63"/>
+      <c r="D50" s="63"/>
+      <c r="E50" s="63"/>
+      <c r="F50" s="63"/>
+      <c r="G50" s="63"/>
+      <c r="H50" s="63"/>
+      <c r="I50" s="73"/>
       <c r="J50" s="10"/>
-      <c r="K50" s="172" t="s">
+      <c r="K50" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="L50" s="172"/>
-      <c r="M50" s="172"/>
-      <c r="N50" s="172"/>
-      <c r="O50" s="172"/>
-      <c r="P50" s="172"/>
-      <c r="Q50" s="172"/>
-      <c r="R50" s="173"/>
+      <c r="L50" s="3"/>
+      <c r="M50" s="3"/>
+      <c r="N50" s="3"/>
+      <c r="O50" s="3"/>
+      <c r="P50" s="3"/>
+      <c r="Q50" s="3"/>
+      <c r="R50" s="12"/>
       <c r="S50" s="10"/>
-      <c r="T50" s="127" t="s">
+      <c r="T50" s="63" t="s">
         <v>26</v>
       </c>
-      <c r="U50" s="127"/>
-      <c r="V50" s="127"/>
-      <c r="W50" s="127"/>
-      <c r="X50" s="127"/>
-      <c r="Y50" s="127"/>
-      <c r="Z50" s="127"/>
-      <c r="AA50" s="128"/>
-      <c r="AB50" s="133" t="s">
+      <c r="U50" s="63"/>
+      <c r="V50" s="63"/>
+      <c r="W50" s="63"/>
+      <c r="X50" s="63"/>
+      <c r="Y50" s="63"/>
+      <c r="Z50" s="63"/>
+      <c r="AA50" s="73"/>
+      <c r="AB50" s="108" t="s">
         <v>38</v>
       </c>
-      <c r="AC50" s="134"/>
-      <c r="AD50" s="134"/>
-      <c r="AE50" s="134"/>
-      <c r="AF50" s="134"/>
-      <c r="AG50" s="134"/>
-      <c r="AH50" s="134"/>
-      <c r="AI50" s="134"/>
-      <c r="AJ50" s="135"/>
+      <c r="AC50" s="109"/>
+      <c r="AD50" s="109"/>
+      <c r="AE50" s="109"/>
+      <c r="AF50" s="109"/>
+      <c r="AG50" s="109"/>
+      <c r="AH50" s="109"/>
+      <c r="AI50" s="109"/>
+      <c r="AJ50" s="110"/>
     </row>
     <row r="51" spans="1:36" ht="18" customHeight="1">
       <c r="A51" s="10"/>
-      <c r="B51" s="127" t="s">
+      <c r="B51" s="63" t="s">
         <v>40</v>
       </c>
-      <c r="C51" s="127"/>
-      <c r="D51" s="127"/>
-      <c r="E51" s="127"/>
-      <c r="F51" s="127"/>
-      <c r="G51" s="127"/>
-      <c r="H51" s="127"/>
-      <c r="I51" s="128"/>
+      <c r="C51" s="63"/>
+      <c r="D51" s="63"/>
+      <c r="E51" s="63"/>
+      <c r="F51" s="63"/>
+      <c r="G51" s="63"/>
+      <c r="H51" s="63"/>
+      <c r="I51" s="73"/>
       <c r="J51" s="10"/>
-      <c r="K51" s="172" t="s">
+      <c r="K51" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="L51" s="172"/>
-      <c r="M51" s="172"/>
-      <c r="N51" s="172"/>
-      <c r="O51" s="172"/>
-      <c r="P51" s="172"/>
-      <c r="Q51" s="172"/>
-      <c r="R51" s="173"/>
+      <c r="L51" s="3"/>
+      <c r="M51" s="3"/>
+      <c r="N51" s="3"/>
+      <c r="O51" s="3"/>
+      <c r="P51" s="3"/>
+      <c r="Q51" s="3"/>
+      <c r="R51" s="12"/>
       <c r="S51" s="10"/>
-      <c r="T51" s="127" t="s">
+      <c r="T51" s="63" t="s">
         <v>29</v>
       </c>
-      <c r="U51" s="127"/>
-      <c r="V51" s="127"/>
-      <c r="W51" s="126"/>
-      <c r="X51" s="126"/>
-      <c r="Y51" s="126"/>
+      <c r="U51" s="63"/>
+      <c r="V51" s="63"/>
+      <c r="W51" s="96"/>
+      <c r="X51" s="96"/>
+      <c r="Y51" s="96"/>
       <c r="Z51" s="3" t="s">
         <v>30</v>
       </c>
       <c r="AA51" s="4"/>
       <c r="AB51" s="10"/>
-      <c r="AC51" s="136" t="s">
+      <c r="AC51" s="111" t="s">
         <v>76</v>
       </c>
-      <c r="AD51" s="136"/>
-      <c r="AE51" s="136"/>
-      <c r="AF51" s="136"/>
-      <c r="AG51" s="136"/>
-      <c r="AH51" s="136"/>
-      <c r="AI51" s="136"/>
-      <c r="AJ51" s="137"/>
+      <c r="AD51" s="111"/>
+      <c r="AE51" s="111"/>
+      <c r="AF51" s="111"/>
+      <c r="AG51" s="111"/>
+      <c r="AH51" s="111"/>
+      <c r="AI51" s="111"/>
+      <c r="AJ51" s="112"/>
     </row>
     <row r="52" spans="1:36" ht="18" customHeight="1">
       <c r="A52" s="10"/>
-      <c r="B52" s="127" t="s">
+      <c r="B52" s="63" t="s">
         <v>43</v>
       </c>
-      <c r="C52" s="127"/>
-      <c r="D52" s="138"/>
-      <c r="E52" s="138"/>
-      <c r="F52" s="138"/>
-      <c r="G52" s="138"/>
-      <c r="H52" s="138"/>
+      <c r="C52" s="63"/>
+      <c r="D52" s="113"/>
+      <c r="E52" s="113"/>
+      <c r="F52" s="113"/>
+      <c r="G52" s="113"/>
+      <c r="H52" s="113"/>
       <c r="I52" s="4"/>
       <c r="J52" s="10"/>
-      <c r="K52" s="172" t="s">
+      <c r="K52" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="L52" s="172"/>
-      <c r="M52" s="172"/>
-      <c r="N52" s="172"/>
-      <c r="O52" s="172"/>
-      <c r="P52" s="172"/>
-      <c r="Q52" s="172"/>
-      <c r="R52" s="173"/>
+      <c r="L52" s="3"/>
+      <c r="M52" s="3"/>
+      <c r="N52" s="3"/>
+      <c r="O52" s="3"/>
+      <c r="P52" s="3"/>
+      <c r="Q52" s="3"/>
+      <c r="R52" s="12"/>
       <c r="S52" s="10"/>
-      <c r="T52" s="127" t="s">
+      <c r="T52" s="63" t="s">
         <v>32</v>
       </c>
-      <c r="U52" s="127"/>
-      <c r="V52" s="127"/>
-      <c r="W52" s="126"/>
-      <c r="X52" s="126"/>
-      <c r="Y52" s="126"/>
+      <c r="U52" s="63"/>
+      <c r="V52" s="63"/>
+      <c r="W52" s="96"/>
+      <c r="X52" s="96"/>
+      <c r="Y52" s="96"/>
       <c r="Z52" s="3" t="s">
         <v>30</v>
       </c>
       <c r="AA52" s="4"/>
       <c r="AB52" s="10"/>
-      <c r="AC52" s="127" t="s">
+      <c r="AC52" s="63" t="s">
         <v>42</v>
       </c>
-      <c r="AD52" s="127"/>
-      <c r="AE52" s="127"/>
-      <c r="AF52" s="127"/>
-      <c r="AG52" s="127"/>
-      <c r="AH52" s="127"/>
-      <c r="AI52" s="127"/>
-      <c r="AJ52" s="128"/>
+      <c r="AD52" s="63"/>
+      <c r="AE52" s="63"/>
+      <c r="AF52" s="63"/>
+      <c r="AG52" s="63"/>
+      <c r="AH52" s="63"/>
+      <c r="AI52" s="63"/>
+      <c r="AJ52" s="73"/>
     </row>
     <row r="53" spans="1:36" ht="18" customHeight="1">
       <c r="A53" s="13"/>
       <c r="B53" s="7"/>
       <c r="C53" s="7"/>
-      <c r="D53" s="149"/>
-      <c r="E53" s="149"/>
-      <c r="F53" s="149"/>
-      <c r="G53" s="149"/>
-      <c r="H53" s="149"/>
+      <c r="D53" s="101"/>
+      <c r="E53" s="101"/>
+      <c r="F53" s="101"/>
+      <c r="G53" s="101"/>
+      <c r="H53" s="101"/>
       <c r="I53" s="8"/>
-      <c r="J53" s="129"/>
-      <c r="K53" s="130"/>
-      <c r="L53" s="130"/>
-      <c r="M53" s="130"/>
-      <c r="N53" s="130"/>
-      <c r="O53" s="130"/>
-      <c r="P53" s="130"/>
-      <c r="Q53" s="130"/>
-      <c r="R53" s="131"/>
+      <c r="J53" s="104"/>
+      <c r="K53" s="105"/>
+      <c r="L53" s="105"/>
+      <c r="M53" s="105"/>
+      <c r="N53" s="105"/>
+      <c r="O53" s="105"/>
+      <c r="P53" s="105"/>
+      <c r="Q53" s="105"/>
+      <c r="R53" s="106"/>
       <c r="S53" s="13"/>
-      <c r="T53" s="145" t="s">
+      <c r="T53" s="97" t="s">
         <v>35</v>
       </c>
-      <c r="U53" s="145"/>
-      <c r="V53" s="145"/>
-      <c r="W53" s="146"/>
-      <c r="X53" s="146"/>
-      <c r="Y53" s="146"/>
+      <c r="U53" s="97"/>
+      <c r="V53" s="97"/>
+      <c r="W53" s="61"/>
+      <c r="X53" s="61"/>
+      <c r="Y53" s="61"/>
       <c r="Z53" s="6" t="s">
         <v>36</v>
       </c>
       <c r="AA53" s="8"/>
       <c r="AB53" s="13"/>
-      <c r="AC53" s="145" t="s">
+      <c r="AC53" s="97" t="s">
         <v>45</v>
       </c>
-      <c r="AD53" s="145"/>
-      <c r="AE53" s="145"/>
-      <c r="AF53" s="97"/>
-      <c r="AG53" s="97"/>
-      <c r="AH53" s="97"/>
+      <c r="AD53" s="97"/>
+      <c r="AE53" s="97"/>
+      <c r="AF53" s="107"/>
+      <c r="AG53" s="107"/>
+      <c r="AH53" s="107"/>
       <c r="AI53" s="7"/>
       <c r="AJ53" s="8"/>
     </row>
     <row r="54" spans="1:36" ht="18" customHeight="1">
-      <c r="A54" s="147" t="s">
+      <c r="A54" s="99" t="s">
         <v>46</v>
       </c>
-      <c r="B54" s="147"/>
-      <c r="C54" s="147"/>
-      <c r="D54" s="147"/>
-      <c r="E54" s="147"/>
-      <c r="F54" s="147"/>
-      <c r="G54" s="147"/>
-      <c r="H54" s="147"/>
-      <c r="I54" s="147"/>
-      <c r="J54" s="147"/>
-      <c r="K54" s="147"/>
-      <c r="L54" s="147"/>
-      <c r="M54" s="147"/>
-      <c r="N54" s="148"/>
-      <c r="O54" s="148"/>
-      <c r="P54" s="148"/>
-      <c r="Q54" s="148"/>
-      <c r="R54" s="148"/>
-      <c r="S54" s="148"/>
-      <c r="T54" s="148"/>
-      <c r="U54" s="148"/>
-      <c r="V54" s="148"/>
-      <c r="W54" s="148"/>
-      <c r="X54" s="148"/>
-      <c r="Y54" s="148"/>
-      <c r="Z54" s="148"/>
-      <c r="AA54" s="148"/>
-      <c r="AB54" s="148"/>
-      <c r="AC54" s="148"/>
-      <c r="AD54" s="148"/>
-      <c r="AE54" s="148"/>
-      <c r="AF54" s="148"/>
-      <c r="AG54" s="148"/>
-      <c r="AH54" s="148"/>
-      <c r="AI54" s="148"/>
-      <c r="AJ54" s="148"/>
+      <c r="B54" s="99"/>
+      <c r="C54" s="99"/>
+      <c r="D54" s="99"/>
+      <c r="E54" s="99"/>
+      <c r="F54" s="99"/>
+      <c r="G54" s="99"/>
+      <c r="H54" s="99"/>
+      <c r="I54" s="99"/>
+      <c r="J54" s="99"/>
+      <c r="K54" s="99"/>
+      <c r="L54" s="99"/>
+      <c r="M54" s="99"/>
+      <c r="N54" s="100"/>
+      <c r="O54" s="100"/>
+      <c r="P54" s="100"/>
+      <c r="Q54" s="100"/>
+      <c r="R54" s="100"/>
+      <c r="S54" s="100"/>
+      <c r="T54" s="100"/>
+      <c r="U54" s="100"/>
+      <c r="V54" s="100"/>
+      <c r="W54" s="100"/>
+      <c r="X54" s="100"/>
+      <c r="Y54" s="100"/>
+      <c r="Z54" s="100"/>
+      <c r="AA54" s="100"/>
+      <c r="AB54" s="100"/>
+      <c r="AC54" s="100"/>
+      <c r="AD54" s="100"/>
+      <c r="AE54" s="100"/>
+      <c r="AF54" s="100"/>
+      <c r="AG54" s="100"/>
+      <c r="AH54" s="100"/>
+      <c r="AI54" s="100"/>
+      <c r="AJ54" s="100"/>
     </row>
     <row r="55" spans="1:36" ht="18" customHeight="1">
-      <c r="A55" s="140"/>
-      <c r="B55" s="61"/>
-      <c r="C55" s="61"/>
-      <c r="D55" s="61"/>
-      <c r="E55" s="61"/>
-      <c r="F55" s="61"/>
-      <c r="G55" s="61"/>
-      <c r="H55" s="61"/>
-      <c r="I55" s="61"/>
-      <c r="J55" s="61"/>
-      <c r="K55" s="61"/>
-      <c r="L55" s="61"/>
-      <c r="N55" s="61"/>
-      <c r="O55" s="61"/>
-      <c r="P55" s="61"/>
-      <c r="Q55" s="61"/>
-      <c r="R55" s="61"/>
-      <c r="S55" s="61"/>
-      <c r="T55" s="61"/>
-      <c r="U55" s="61"/>
-      <c r="V55" s="61"/>
-      <c r="W55" s="61"/>
-      <c r="X55" s="61"/>
-      <c r="Y55" s="140"/>
-      <c r="Z55" s="140"/>
-      <c r="AA55" s="140"/>
-      <c r="AB55" s="150" t="s">
+      <c r="A55" s="90"/>
+      <c r="B55" s="98"/>
+      <c r="C55" s="98"/>
+      <c r="D55" s="98"/>
+      <c r="E55" s="98"/>
+      <c r="F55" s="98"/>
+      <c r="G55" s="98"/>
+      <c r="H55" s="98"/>
+      <c r="I55" s="98"/>
+      <c r="J55" s="98"/>
+      <c r="K55" s="98"/>
+      <c r="L55" s="98"/>
+      <c r="N55" s="98"/>
+      <c r="O55" s="98"/>
+      <c r="P55" s="98"/>
+      <c r="Q55" s="98"/>
+      <c r="R55" s="98"/>
+      <c r="S55" s="98"/>
+      <c r="T55" s="98"/>
+      <c r="U55" s="98"/>
+      <c r="V55" s="98"/>
+      <c r="W55" s="98"/>
+      <c r="X55" s="98"/>
+      <c r="Y55" s="90"/>
+      <c r="Z55" s="90"/>
+      <c r="AA55" s="90"/>
+      <c r="AB55" s="102" t="s">
         <v>93</v>
       </c>
-      <c r="AC55" s="96"/>
-      <c r="AD55" s="96"/>
-      <c r="AE55" s="96"/>
-      <c r="AF55" s="96"/>
-      <c r="AG55" s="96"/>
-      <c r="AH55" s="96"/>
-      <c r="AI55" s="96"/>
-      <c r="AJ55" s="96"/>
+      <c r="AC55" s="103"/>
+      <c r="AD55" s="103"/>
+      <c r="AE55" s="103"/>
+      <c r="AF55" s="103"/>
+      <c r="AG55" s="103"/>
+      <c r="AH55" s="103"/>
+      <c r="AI55" s="103"/>
+      <c r="AJ55" s="103"/>
     </row>
     <row r="56" spans="1:36" ht="18" customHeight="1">
-      <c r="A56" s="140"/>
-      <c r="B56" s="61"/>
-      <c r="C56" s="61"/>
-      <c r="D56" s="61"/>
-      <c r="E56" s="61"/>
-      <c r="F56" s="61"/>
-      <c r="G56" s="61"/>
-      <c r="H56" s="61"/>
-      <c r="I56" s="61"/>
-      <c r="J56" s="61"/>
-      <c r="K56" s="61"/>
-      <c r="L56" s="61"/>
-      <c r="N56" s="61"/>
-      <c r="O56" s="61"/>
-      <c r="P56" s="61"/>
-      <c r="Q56" s="61"/>
-      <c r="R56" s="61"/>
-      <c r="S56" s="61"/>
-      <c r="T56" s="61"/>
-      <c r="U56" s="61"/>
-      <c r="V56" s="61"/>
-      <c r="W56" s="61"/>
-      <c r="X56" s="61"/>
-      <c r="Y56" s="140"/>
-      <c r="Z56" s="140"/>
-      <c r="AA56" s="140"/>
-      <c r="AB56" s="141" t="s">
+      <c r="A56" s="90"/>
+      <c r="B56" s="98"/>
+      <c r="C56" s="98"/>
+      <c r="D56" s="98"/>
+      <c r="E56" s="98"/>
+      <c r="F56" s="98"/>
+      <c r="G56" s="98"/>
+      <c r="H56" s="98"/>
+      <c r="I56" s="98"/>
+      <c r="J56" s="98"/>
+      <c r="K56" s="98"/>
+      <c r="L56" s="98"/>
+      <c r="N56" s="98"/>
+      <c r="O56" s="98"/>
+      <c r="P56" s="98"/>
+      <c r="Q56" s="98"/>
+      <c r="R56" s="98"/>
+      <c r="S56" s="98"/>
+      <c r="T56" s="98"/>
+      <c r="U56" s="98"/>
+      <c r="V56" s="98"/>
+      <c r="W56" s="98"/>
+      <c r="X56" s="98"/>
+      <c r="Y56" s="90"/>
+      <c r="Z56" s="90"/>
+      <c r="AA56" s="90"/>
+      <c r="AB56" s="92" t="s">
         <v>47</v>
       </c>
-      <c r="AC56" s="141"/>
-      <c r="AD56" s="141"/>
-      <c r="AE56" s="141"/>
-      <c r="AF56" s="141"/>
-      <c r="AG56" s="141"/>
-      <c r="AH56" s="141"/>
-      <c r="AI56" s="141"/>
-      <c r="AJ56" s="141"/>
+      <c r="AC56" s="92"/>
+      <c r="AD56" s="92"/>
+      <c r="AE56" s="92"/>
+      <c r="AF56" s="92"/>
+      <c r="AG56" s="92"/>
+      <c r="AH56" s="92"/>
+      <c r="AI56" s="92"/>
+      <c r="AJ56" s="92"/>
     </row>
     <row r="57" spans="1:36" ht="18" customHeight="1">
-      <c r="A57" s="140"/>
-      <c r="B57" s="61"/>
-      <c r="C57" s="61"/>
-      <c r="D57" s="61"/>
-      <c r="E57" s="61"/>
-      <c r="F57" s="61"/>
-      <c r="G57" s="61"/>
-      <c r="H57" s="61"/>
-      <c r="I57" s="61"/>
-      <c r="J57" s="61"/>
-      <c r="K57" s="61"/>
-      <c r="L57" s="61"/>
-      <c r="N57" s="61"/>
-      <c r="O57" s="61"/>
-      <c r="P57" s="61"/>
-      <c r="Q57" s="61"/>
-      <c r="R57" s="61"/>
-      <c r="S57" s="61"/>
-      <c r="T57" s="61"/>
-      <c r="U57" s="61"/>
-      <c r="V57" s="61"/>
-      <c r="W57" s="61"/>
-      <c r="X57" s="61"/>
-      <c r="Y57" s="140"/>
-      <c r="Z57" s="140"/>
-      <c r="AA57" s="140"/>
-      <c r="AB57" s="140"/>
-      <c r="AC57" s="140"/>
-      <c r="AD57" s="140"/>
-      <c r="AE57" s="140"/>
-      <c r="AF57" s="140"/>
-      <c r="AG57" s="140"/>
-      <c r="AH57" s="140"/>
-      <c r="AI57" s="140"/>
-      <c r="AJ57" s="140"/>
+      <c r="A57" s="90"/>
+      <c r="B57" s="98"/>
+      <c r="C57" s="98"/>
+      <c r="D57" s="98"/>
+      <c r="E57" s="98"/>
+      <c r="F57" s="98"/>
+      <c r="G57" s="98"/>
+      <c r="H57" s="98"/>
+      <c r="I57" s="98"/>
+      <c r="J57" s="98"/>
+      <c r="K57" s="98"/>
+      <c r="L57" s="98"/>
+      <c r="N57" s="98"/>
+      <c r="O57" s="98"/>
+      <c r="P57" s="98"/>
+      <c r="Q57" s="98"/>
+      <c r="R57" s="98"/>
+      <c r="S57" s="98"/>
+      <c r="T57" s="98"/>
+      <c r="U57" s="98"/>
+      <c r="V57" s="98"/>
+      <c r="W57" s="98"/>
+      <c r="X57" s="98"/>
+      <c r="Y57" s="90"/>
+      <c r="Z57" s="90"/>
+      <c r="AA57" s="90"/>
+      <c r="AB57" s="90"/>
+      <c r="AC57" s="90"/>
+      <c r="AD57" s="90"/>
+      <c r="AE57" s="90"/>
+      <c r="AF57" s="90"/>
+      <c r="AG57" s="90"/>
+      <c r="AH57" s="90"/>
+      <c r="AI57" s="90"/>
+      <c r="AJ57" s="90"/>
     </row>
     <row r="58" spans="1:36" ht="18" customHeight="1">
-      <c r="A58" s="51"/>
-      <c r="B58" s="52"/>
-      <c r="C58" s="52"/>
-      <c r="D58" s="52"/>
-      <c r="E58" s="52"/>
-      <c r="F58" s="52"/>
-      <c r="G58" s="52"/>
-      <c r="H58" s="52"/>
-      <c r="I58" s="52"/>
-      <c r="J58" s="52"/>
-      <c r="K58" s="52"/>
-      <c r="L58" s="52"/>
-      <c r="N58" s="52"/>
-      <c r="O58" s="52"/>
-      <c r="P58" s="52"/>
-      <c r="Q58" s="52"/>
-      <c r="R58" s="52"/>
-      <c r="S58" s="52"/>
-      <c r="T58" s="52"/>
-      <c r="U58" s="52"/>
-      <c r="V58" s="52"/>
-      <c r="W58" s="52"/>
-      <c r="X58" s="52"/>
-      <c r="Y58" s="140"/>
-      <c r="Z58" s="140"/>
-      <c r="AA58" s="140"/>
-      <c r="AB58" s="140"/>
-      <c r="AC58" s="140"/>
-      <c r="AD58" s="140"/>
-      <c r="AE58" s="140"/>
-      <c r="AF58" s="140"/>
-      <c r="AG58" s="140"/>
-      <c r="AH58" s="140"/>
-      <c r="AI58" s="140"/>
-      <c r="AJ58" s="140"/>
+      <c r="A58" s="49"/>
+      <c r="B58" s="50"/>
+      <c r="C58" s="50"/>
+      <c r="D58" s="50"/>
+      <c r="E58" s="50"/>
+      <c r="F58" s="50"/>
+      <c r="G58" s="50"/>
+      <c r="H58" s="50"/>
+      <c r="I58" s="50"/>
+      <c r="J58" s="50"/>
+      <c r="K58" s="50"/>
+      <c r="L58" s="50"/>
+      <c r="N58" s="50"/>
+      <c r="O58" s="50"/>
+      <c r="P58" s="50"/>
+      <c r="Q58" s="50"/>
+      <c r="R58" s="50"/>
+      <c r="S58" s="50"/>
+      <c r="T58" s="50"/>
+      <c r="U58" s="50"/>
+      <c r="V58" s="50"/>
+      <c r="W58" s="50"/>
+      <c r="X58" s="50"/>
+      <c r="Y58" s="90"/>
+      <c r="Z58" s="90"/>
+      <c r="AA58" s="90"/>
+      <c r="AB58" s="90"/>
+      <c r="AC58" s="90"/>
+      <c r="AD58" s="90"/>
+      <c r="AE58" s="90"/>
+      <c r="AF58" s="90"/>
+      <c r="AG58" s="90"/>
+      <c r="AH58" s="90"/>
+      <c r="AI58" s="90"/>
+      <c r="AJ58" s="90"/>
     </row>
     <row r="59" spans="1:36" ht="18" customHeight="1">
-      <c r="A59" s="140"/>
-      <c r="B59" s="140"/>
-      <c r="C59" s="140"/>
-      <c r="D59" s="140"/>
-      <c r="E59" s="140"/>
-      <c r="F59" s="140"/>
-      <c r="G59" s="140"/>
-      <c r="H59" s="140"/>
-      <c r="I59" s="140"/>
-      <c r="J59" s="140"/>
-      <c r="K59" s="140"/>
-      <c r="L59" s="140"/>
-      <c r="M59" s="140"/>
-      <c r="N59" s="140"/>
-      <c r="O59" s="140"/>
-      <c r="P59" s="140"/>
-      <c r="Q59" s="140"/>
-      <c r="R59" s="140"/>
-      <c r="S59" s="140"/>
-      <c r="T59" s="140"/>
-      <c r="U59" s="140"/>
-      <c r="V59" s="140"/>
-      <c r="W59" s="140"/>
-      <c r="X59" s="140"/>
-      <c r="Y59" s="140"/>
-      <c r="Z59" s="140"/>
-      <c r="AA59" s="140"/>
-      <c r="AB59" s="77"/>
-      <c r="AC59" s="77"/>
-      <c r="AD59" s="77"/>
-      <c r="AE59" s="77"/>
-      <c r="AF59" s="77"/>
-      <c r="AG59" s="77"/>
-      <c r="AH59" s="77"/>
-      <c r="AI59" s="77"/>
-      <c r="AJ59" s="77"/>
+      <c r="A59" s="90"/>
+      <c r="B59" s="90"/>
+      <c r="C59" s="90"/>
+      <c r="D59" s="90"/>
+      <c r="E59" s="90"/>
+      <c r="F59" s="90"/>
+      <c r="G59" s="90"/>
+      <c r="H59" s="90"/>
+      <c r="I59" s="90"/>
+      <c r="J59" s="90"/>
+      <c r="K59" s="90"/>
+      <c r="L59" s="90"/>
+      <c r="M59" s="90"/>
+      <c r="N59" s="90"/>
+      <c r="O59" s="90"/>
+      <c r="P59" s="90"/>
+      <c r="Q59" s="90"/>
+      <c r="R59" s="90"/>
+      <c r="S59" s="90"/>
+      <c r="T59" s="90"/>
+      <c r="U59" s="90"/>
+      <c r="V59" s="90"/>
+      <c r="W59" s="90"/>
+      <c r="X59" s="90"/>
+      <c r="Y59" s="90"/>
+      <c r="Z59" s="90"/>
+      <c r="AA59" s="90"/>
+      <c r="AB59" s="91"/>
+      <c r="AC59" s="91"/>
+      <c r="AD59" s="91"/>
+      <c r="AE59" s="91"/>
+      <c r="AF59" s="91"/>
+      <c r="AG59" s="91"/>
+      <c r="AH59" s="91"/>
+      <c r="AI59" s="91"/>
+      <c r="AJ59" s="91"/>
     </row>
     <row r="60" spans="1:36" ht="18" customHeight="1">
-      <c r="Y60" s="140"/>
-      <c r="Z60" s="140"/>
-      <c r="AA60" s="140"/>
-      <c r="AB60" s="139" t="s">
+      <c r="Y60" s="90"/>
+      <c r="Z60" s="90"/>
+      <c r="AA60" s="90"/>
+      <c r="AB60" s="89" t="s">
         <v>92</v>
       </c>
-      <c r="AC60" s="139"/>
-      <c r="AD60" s="139"/>
-      <c r="AE60" s="139"/>
-      <c r="AF60" s="139"/>
-      <c r="AG60" s="139"/>
-      <c r="AH60" s="139"/>
-      <c r="AI60" s="139"/>
-      <c r="AJ60" s="139"/>
+      <c r="AC60" s="89"/>
+      <c r="AD60" s="89"/>
+      <c r="AE60" s="89"/>
+      <c r="AF60" s="89"/>
+      <c r="AG60" s="89"/>
+      <c r="AH60" s="89"/>
+      <c r="AI60" s="89"/>
+      <c r="AJ60" s="89"/>
     </row>
     <row r="61" spans="1:36" ht="16.5" customHeight="1"/>
     <row r="62" spans="1:36" ht="18" hidden="1" customHeight="1"/>
@@ -10047,27 +10030,71 @@
     <row r="657"/>
     <row r="658"/>
   </sheetData>
-  <mergeCells count="110">
-    <mergeCell ref="X47:Z47"/>
-    <mergeCell ref="AG49:AI49"/>
-    <mergeCell ref="W45:Z45"/>
-    <mergeCell ref="T51:V51"/>
-    <mergeCell ref="A27:AJ29"/>
-    <mergeCell ref="A36:R36"/>
-    <mergeCell ref="B47:I47"/>
-    <mergeCell ref="S43:AA43"/>
-    <mergeCell ref="B51:I51"/>
-    <mergeCell ref="AF44:AI44"/>
-    <mergeCell ref="A30:O30"/>
-    <mergeCell ref="B44:I44"/>
-    <mergeCell ref="AB43:AJ43"/>
-    <mergeCell ref="J43:R43"/>
-    <mergeCell ref="W44:Y44"/>
-    <mergeCell ref="A31:AJ35"/>
-    <mergeCell ref="A37:AJ40"/>
-    <mergeCell ref="B45:I45"/>
-    <mergeCell ref="AB47:AE47"/>
-    <mergeCell ref="B46:I46"/>
+  <mergeCells count="112">
+    <mergeCell ref="B57:L57"/>
+    <mergeCell ref="N57:X57"/>
+    <mergeCell ref="Q2:Z2"/>
+    <mergeCell ref="Q3:Z3"/>
+    <mergeCell ref="A11:P11"/>
+    <mergeCell ref="K5:O5"/>
+    <mergeCell ref="K6:O6"/>
+    <mergeCell ref="P6:X6"/>
+    <mergeCell ref="A41:R41"/>
+    <mergeCell ref="Q11:AJ11"/>
+    <mergeCell ref="C7:I7"/>
+    <mergeCell ref="D8:R8"/>
+    <mergeCell ref="X8:AJ8"/>
+    <mergeCell ref="A10:AJ10"/>
+    <mergeCell ref="K7:O7"/>
+    <mergeCell ref="A25:AJ25"/>
+    <mergeCell ref="AB3:AC3"/>
+    <mergeCell ref="AC6:AE6"/>
+    <mergeCell ref="AC7:AE7"/>
+    <mergeCell ref="Y5:Z5"/>
+    <mergeCell ref="A22:AJ23"/>
+    <mergeCell ref="A17:T20"/>
+    <mergeCell ref="C5:I5"/>
+    <mergeCell ref="AF19:AG19"/>
+    <mergeCell ref="A43:I43"/>
+    <mergeCell ref="AI19:AJ19"/>
+    <mergeCell ref="A14:H14"/>
+    <mergeCell ref="I14:AJ14"/>
+    <mergeCell ref="AI17:AJ17"/>
+    <mergeCell ref="AF17:AG17"/>
+    <mergeCell ref="A15:AJ15"/>
+    <mergeCell ref="AF18:AG18"/>
+    <mergeCell ref="AA5:AJ5"/>
+    <mergeCell ref="V7:W7"/>
+    <mergeCell ref="AI18:AJ18"/>
+    <mergeCell ref="U16:AD16"/>
+    <mergeCell ref="AE16:AJ16"/>
+    <mergeCell ref="A16:T16"/>
+    <mergeCell ref="X9:AJ9"/>
+    <mergeCell ref="P7:T7"/>
+    <mergeCell ref="P5:X5"/>
+    <mergeCell ref="X7:AB7"/>
+    <mergeCell ref="AF46:AI46"/>
+    <mergeCell ref="T50:AA50"/>
+    <mergeCell ref="AF45:AI45"/>
+    <mergeCell ref="AB48:AF48"/>
+    <mergeCell ref="AI7:AJ7"/>
+    <mergeCell ref="C6:I6"/>
+    <mergeCell ref="AB46:AE46"/>
+    <mergeCell ref="S44:V44"/>
+    <mergeCell ref="S45:V45"/>
+    <mergeCell ref="S46:W46"/>
+    <mergeCell ref="X46:Z46"/>
+    <mergeCell ref="AB44:AE44"/>
+    <mergeCell ref="D9:H9"/>
+    <mergeCell ref="AF53:AH53"/>
+    <mergeCell ref="AB50:AJ50"/>
+    <mergeCell ref="AC51:AJ51"/>
+    <mergeCell ref="B49:I49"/>
+    <mergeCell ref="B52:C52"/>
+    <mergeCell ref="D52:H52"/>
+    <mergeCell ref="S47:W47"/>
+    <mergeCell ref="T49:AA49"/>
+    <mergeCell ref="W52:Y52"/>
     <mergeCell ref="AB60:AJ60"/>
     <mergeCell ref="AB57:AJ59"/>
     <mergeCell ref="AB56:AJ56"/>
@@ -10092,72 +10119,30 @@
     <mergeCell ref="W51:Y51"/>
     <mergeCell ref="AC52:AJ52"/>
     <mergeCell ref="J53:R53"/>
+    <mergeCell ref="X47:Z47"/>
+    <mergeCell ref="AG49:AI49"/>
+    <mergeCell ref="W45:Z45"/>
+    <mergeCell ref="T51:V51"/>
+    <mergeCell ref="A27:AJ29"/>
+    <mergeCell ref="A36:R36"/>
+    <mergeCell ref="B47:I47"/>
+    <mergeCell ref="S43:AA43"/>
+    <mergeCell ref="B51:I51"/>
+    <mergeCell ref="AF44:AI44"/>
+    <mergeCell ref="A30:O30"/>
+    <mergeCell ref="B44:I44"/>
+    <mergeCell ref="AB43:AJ43"/>
+    <mergeCell ref="J43:R43"/>
+    <mergeCell ref="W44:Y44"/>
+    <mergeCell ref="A31:AJ35"/>
+    <mergeCell ref="A37:AJ40"/>
+    <mergeCell ref="B45:I45"/>
+    <mergeCell ref="AB47:AE47"/>
+    <mergeCell ref="B46:I46"/>
     <mergeCell ref="AB45:AE45"/>
     <mergeCell ref="B48:I48"/>
     <mergeCell ref="AF47:AI47"/>
     <mergeCell ref="AB49:AF49"/>
-    <mergeCell ref="AF53:AH53"/>
-    <mergeCell ref="AB50:AJ50"/>
-    <mergeCell ref="AC51:AJ51"/>
-    <mergeCell ref="B49:I49"/>
-    <mergeCell ref="B52:C52"/>
-    <mergeCell ref="D52:H52"/>
-    <mergeCell ref="S47:W47"/>
-    <mergeCell ref="T49:AA49"/>
-    <mergeCell ref="W52:Y52"/>
-    <mergeCell ref="AF46:AI46"/>
-    <mergeCell ref="T50:AA50"/>
-    <mergeCell ref="AF45:AI45"/>
-    <mergeCell ref="AB48:AF48"/>
-    <mergeCell ref="AI7:AJ7"/>
-    <mergeCell ref="C6:I6"/>
-    <mergeCell ref="AB46:AE46"/>
-    <mergeCell ref="S44:V44"/>
-    <mergeCell ref="S45:V45"/>
-    <mergeCell ref="S46:W46"/>
-    <mergeCell ref="X46:Z46"/>
-    <mergeCell ref="AB44:AE44"/>
-    <mergeCell ref="D9:H9"/>
-    <mergeCell ref="AD3:AJ3"/>
-    <mergeCell ref="Y5:Z5"/>
-    <mergeCell ref="A22:AJ23"/>
-    <mergeCell ref="A17:T20"/>
-    <mergeCell ref="C5:I5"/>
-    <mergeCell ref="AF19:AG19"/>
-    <mergeCell ref="A43:I43"/>
-    <mergeCell ref="AI19:AJ19"/>
-    <mergeCell ref="A14:H14"/>
-    <mergeCell ref="I14:AJ14"/>
-    <mergeCell ref="AI17:AJ17"/>
-    <mergeCell ref="AF17:AG17"/>
-    <mergeCell ref="A15:AJ15"/>
-    <mergeCell ref="AF18:AG18"/>
-    <mergeCell ref="AA5:AJ5"/>
-    <mergeCell ref="V7:W7"/>
-    <mergeCell ref="AI18:AJ18"/>
-    <mergeCell ref="U16:AD16"/>
-    <mergeCell ref="AE16:AJ16"/>
-    <mergeCell ref="A16:T16"/>
-    <mergeCell ref="X9:AJ9"/>
-    <mergeCell ref="P7:T7"/>
-    <mergeCell ref="P5:X5"/>
-    <mergeCell ref="X7:AB7"/>
-    <mergeCell ref="B57:L57"/>
-    <mergeCell ref="N57:X57"/>
-    <mergeCell ref="Q2:Z2"/>
-    <mergeCell ref="Q3:Z3"/>
-    <mergeCell ref="A11:P11"/>
-    <mergeCell ref="K5:O5"/>
-    <mergeCell ref="K6:O6"/>
-    <mergeCell ref="P6:X6"/>
-    <mergeCell ref="A41:R41"/>
-    <mergeCell ref="Q11:AJ11"/>
-    <mergeCell ref="C7:I7"/>
-    <mergeCell ref="D8:R8"/>
-    <mergeCell ref="X8:AJ8"/>
-    <mergeCell ref="A10:AJ10"/>
-    <mergeCell ref="K7:O7"/>
-    <mergeCell ref="A25:AJ25"/>
   </mergeCells>
   <phoneticPr fontId="0" type="noConversion"/>
   <printOptions horizontalCentered="1"/>
